--- a/api/2/xlsx/fr/SectorCOFOG.xlsx
+++ b/api/2/xlsx/fr/SectorCOFOG.xlsx
@@ -22,75 +22,75 @@
     <t>status</t>
   </si>
   <si>
+    <t>codeforiati:cofog-group</t>
+  </si>
+  <si>
+    <t>codeforiati:category-code</t>
+  </si>
+  <si>
+    <t>codeforiati:group-code</t>
+  </si>
+  <si>
     <t>codeforiati:cofog-division</t>
   </si>
   <si>
-    <t>codeforiati:category-code</t>
-  </si>
-  <si>
-    <t>codeforiati:group-code</t>
-  </si>
-  <si>
     <t>codeforiati:cofog-class</t>
   </si>
   <si>
-    <t>codeforiati:cofog-group</t>
-  </si>
-  <si>
     <t>11110</t>
   </si>
   <si>
     <t>active</t>
   </si>
   <si>
+    <t>09.8 - Education n.e.c.</t>
+  </si>
+  <si>
+    <t>111</t>
+  </si>
+  <si>
+    <t>110</t>
+  </si>
+  <si>
     <t>09 - Education</t>
   </si>
   <si>
-    <t>111</t>
-  </si>
-  <si>
-    <t>110</t>
-  </si>
-  <si>
     <t>09.8.0 - Education n.e.c. (CS)</t>
   </si>
   <si>
-    <t>09.8 - Education n.e.c.</t>
-  </si>
-  <si>
     <t>11120</t>
   </si>
   <si>
+    <t>09.6 - Subsidiary services to education</t>
+  </si>
+  <si>
     <t>09.6.0 - Subsidiary services to education (IS)</t>
   </si>
   <si>
-    <t>09.6 - Subsidiary services to education</t>
-  </si>
-  <si>
     <t>11130</t>
   </si>
   <si>
     <t>11182</t>
   </si>
   <si>
+    <t>09.7 - R&amp;D Education</t>
+  </si>
+  <si>
     <t>09.7.0 - R&amp;D Education (CS)</t>
   </si>
   <si>
-    <t>09.7 - R&amp;D Education</t>
-  </si>
-  <si>
     <t>11220</t>
   </si>
   <si>
+    <t>09.1 - Pre‐primary and primary education</t>
+  </si>
+  <si>
     <t>112</t>
   </si>
   <si>
     <t>09.1.2 - Primary education (IS)</t>
   </si>
   <si>
-    <t>09.1 - Pre‐primary and primary education</t>
-  </si>
-  <si>
     <t>11230</t>
   </si>
   <si>
@@ -109,24 +109,24 @@
     <t>11250</t>
   </si>
   <si>
+    <t>07.4 - Public health services</t>
+  </si>
+  <si>
     <t>07 - Health</t>
   </si>
   <si>
     <t>07.4.0 - Public health services (IS)</t>
   </si>
   <si>
-    <t>07.4 - Public health services</t>
-  </si>
-  <si>
     <t>11260</t>
   </si>
   <si>
+    <t>09.2 - Secondary education</t>
+  </si>
+  <si>
     <t>09.2.1 - Lower‐secondary education (IS)</t>
   </si>
   <si>
-    <t>09.2 - Secondary education</t>
-  </si>
-  <si>
     <t>11320</t>
   </si>
   <si>
@@ -139,36 +139,39 @@
     <t>11330</t>
   </si>
   <si>
+    <t>09.5 - Education not definable by level</t>
+  </si>
+  <si>
     <t>09.5.0 - Education not definable by level (IS)</t>
   </si>
   <si>
-    <t>09.5 - Education not definable by level</t>
-  </si>
-  <si>
     <t>11420</t>
   </si>
   <si>
+    <t>09.4 - Tertiary education</t>
+  </si>
+  <si>
     <t>114</t>
   </si>
   <si>
     <t>09.4.1 - First stage of tertiary education (IS)</t>
   </si>
   <si>
-    <t>09.4 - Tertiary education</t>
-  </si>
-  <si>
     <t>11430</t>
   </si>
   <si>
+    <t>09.3 - Post‐secondary non‐tertiary education</t>
+  </si>
+  <si>
     <t>09.3.0 - Post‐secondary non‐tertiary education (IS)</t>
   </si>
   <si>
-    <t>09.3 - Post‐secondary non‐tertiary education</t>
-  </si>
-  <si>
     <t>12110</t>
   </si>
   <si>
+    <t>07.6 - Health n.e.c.</t>
+  </si>
+  <si>
     <t>121</t>
   </si>
   <si>
@@ -178,30 +181,27 @@
     <t>07.6.0 - Health n.e.c. (CS)</t>
   </si>
   <si>
-    <t>07.6 - Health n.e.c.</t>
-  </si>
-  <si>
     <t>12181</t>
   </si>
   <si>
     <t>12182</t>
   </si>
   <si>
+    <t>07.5 - R&amp;D Health</t>
+  </si>
+  <si>
     <t>07.5.0 - R&amp;D Health (CS)</t>
   </si>
   <si>
-    <t>07.5 - R&amp;D Health</t>
-  </si>
-  <si>
     <t>12191</t>
   </si>
   <si>
+    <t>07.2 - Outpatient services</t>
+  </si>
+  <si>
     <t>07.2.1 - General medical services (IS)</t>
   </si>
   <si>
-    <t>07.2 - Outpatient services</t>
-  </si>
-  <si>
     <t>12196</t>
   </si>
   <si>
@@ -214,12 +214,12 @@
     <t>12230</t>
   </si>
   <si>
+    <t>07.3 - Hospital services</t>
+  </si>
+  <si>
     <t>07.3.1 - General hospital services (IS)</t>
   </si>
   <si>
-    <t>07.3 - Hospital services</t>
-  </si>
-  <si>
     <t>12240</t>
   </si>
   <si>
@@ -286,30 +286,30 @@
     <t>14010</t>
   </si>
   <si>
+    <t>06.3 - Water supply</t>
+  </si>
+  <si>
+    <t>140</t>
+  </si>
+  <si>
     <t>06 - Housing and community amenities</t>
   </si>
   <si>
-    <t>140</t>
-  </si>
-  <si>
     <t>06.3.0 - Water supply (CS)</t>
   </si>
   <si>
-    <t>06.3 - Water supply</t>
-  </si>
-  <si>
     <t>14015</t>
   </si>
   <si>
+    <t>05.6 - Environmental protection n.e.c.</t>
+  </si>
+  <si>
     <t>05 - Environmental protection</t>
   </si>
   <si>
     <t>05.6.0 - Environmental protection n.e.c. (CS)</t>
   </si>
   <si>
-    <t>05.6 - Environmental protection n.e.c.</t>
-  </si>
-  <si>
     <t>14020</t>
   </si>
   <si>
@@ -319,12 +319,12 @@
     <t>14022</t>
   </si>
   <si>
+    <t>05.2 - Waste water management</t>
+  </si>
+  <si>
     <t>05.2.0 - Waste water management (CS)</t>
   </si>
   <si>
-    <t>05.2 - Waste water management</t>
-  </si>
-  <si>
     <t>14030</t>
   </si>
   <si>
@@ -340,63 +340,63 @@
     <t>14050</t>
   </si>
   <si>
+    <t>05.1 - Waste management</t>
+  </si>
+  <si>
     <t>05.1.0 - Waste management (CS)</t>
   </si>
   <si>
-    <t>05.1 - Waste management</t>
-  </si>
-  <si>
     <t>14081</t>
   </si>
   <si>
     <t>15110</t>
   </si>
   <si>
+    <t>01.3 - General services</t>
+  </si>
+  <si>
+    <t>151</t>
+  </si>
+  <si>
+    <t>150</t>
+  </si>
+  <si>
     <t>01 - General public services</t>
   </si>
   <si>
-    <t>151</t>
-  </si>
-  <si>
-    <t>150</t>
-  </si>
-  <si>
     <t>01.3.1 - General personnel services (CS)</t>
   </si>
   <si>
-    <t>01.3 - General services</t>
-  </si>
-  <si>
     <t>15111</t>
   </si>
   <si>
+    <t>01.1 - Executive and legislative organs, financial and fiscal affairs, external affairs</t>
+  </si>
+  <si>
     <t>01.1.2 - Financial and fiscal affairs (CS)</t>
   </si>
   <si>
-    <t>01.1 - Executive and legislative organs, financial and fiscal affairs, external affairs</t>
-  </si>
-  <si>
     <t>15112</t>
   </si>
   <si>
+    <t>01.8 - Transfers of a general character between different levels of government</t>
+  </si>
+  <si>
     <t>01.8.0 - Transfers of a general character between different levels of government (CS)</t>
   </si>
   <si>
-    <t>01.8 - Transfers of a general character between different levels of government</t>
-  </si>
-  <si>
     <t>15113</t>
   </si>
   <si>
+    <t>03.6 - Public order and safety n.e.c.</t>
+  </si>
+  <si>
     <t>03 - Public order and safety</t>
   </si>
   <si>
     <t>03.6.0 - Public order and safety n.e.c. (CS)</t>
   </si>
   <si>
-    <t>03.6 - Public order and safety n.e.c.</t>
-  </si>
-  <si>
     <t>15114</t>
   </si>
   <si>
@@ -424,12 +424,12 @@
     <t>15123</t>
   </si>
   <si>
+    <t>01.2 - Foreign economic aid</t>
+  </si>
+  <si>
     <t>01.2.2 - Economic aid routed through international organizations (CS)</t>
   </si>
   <si>
-    <t>01.2 - Foreign economic aid</t>
-  </si>
-  <si>
     <t>15124</t>
   </si>
   <si>
@@ -460,30 +460,30 @@
     <t>15131</t>
   </si>
   <si>
+    <t>03.3 - Law courts</t>
+  </si>
+  <si>
     <t>03.3.0 - Law courts (CS)</t>
   </si>
   <si>
-    <t>03.3 - Law courts</t>
-  </si>
-  <si>
     <t>15132</t>
   </si>
   <si>
+    <t>03.1 - Police services</t>
+  </si>
+  <si>
     <t>03.1.0 - Police services (CS)</t>
   </si>
   <si>
-    <t>03.1 - Police services</t>
-  </si>
-  <si>
     <t>15133</t>
   </si>
   <si>
+    <t>03.2 - Fire‐protection services</t>
+  </si>
+  <si>
     <t>03.2.0 - Fire‐protection services (CS)</t>
   </si>
   <si>
-    <t>03.2 - Fire‐protection services</t>
-  </si>
-  <si>
     <t>15134</t>
   </si>
   <si>
@@ -496,24 +496,24 @@
     <t>15137</t>
   </si>
   <si>
+    <t>03.4 - Prisons</t>
+  </si>
+  <si>
     <t>03.4.0 - Prisons (CS)</t>
   </si>
   <si>
-    <t>03.4 - Prisons</t>
-  </si>
-  <si>
     <t>15142</t>
   </si>
   <si>
+    <t>04.1 - General economic, commercial and labour affairs</t>
+  </si>
+  <si>
     <t>04 - Economic affairs</t>
   </si>
   <si>
     <t>04.1.1 - General economic and commercial affairs (CS)</t>
   </si>
   <si>
-    <t>04.1 - General economic, commercial and labour affairs</t>
-  </si>
-  <si>
     <t>15143</t>
   </si>
   <si>
@@ -526,12 +526,12 @@
     <t>15151</t>
   </si>
   <si>
+    <t>01.6 - General public services n.e.c.</t>
+  </si>
+  <si>
     <t>01.6.0 - General public services n.e.c. (CS)</t>
   </si>
   <si>
-    <t>01.6 - General public services n.e.c.</t>
-  </si>
-  <si>
     <t>15152</t>
   </si>
   <si>
@@ -541,12 +541,12 @@
     <t>15153</t>
   </si>
   <si>
+    <t>04.6 - Communication</t>
+  </si>
+  <si>
     <t>04.6.0 - Communication (CS)</t>
   </si>
   <si>
-    <t>04.6 - Communication</t>
-  </si>
-  <si>
     <t>15154</t>
   </si>
   <si>
@@ -562,15 +562,15 @@
     <t>15170</t>
   </si>
   <si>
+    <t>10.7 - Social exclusion n.e.c.</t>
+  </si>
+  <si>
     <t>10 - Social protection</t>
   </si>
   <si>
     <t>10.7.0 - Social exclusion n.e.c. (IS)</t>
   </si>
   <si>
-    <t>10.7 - Social exclusion n.e.c.</t>
-  </si>
-  <si>
     <t>15180</t>
   </si>
   <si>
@@ -583,12 +583,12 @@
     <t>15196</t>
   </si>
   <si>
+    <t>01.5 - R&amp;D General public services</t>
+  </si>
+  <si>
     <t>01.5.0 - R&amp;D General public services (CS)</t>
   </si>
   <si>
-    <t>01.5 - R&amp;D General public services</t>
-  </si>
-  <si>
     <t>15210</t>
   </si>
   <si>
@@ -601,15 +601,15 @@
     <t>15230</t>
   </si>
   <si>
+    <t>02.3 - Foreign military aid</t>
+  </si>
+  <si>
     <t>02 - Defence</t>
   </si>
   <si>
     <t>02.3.0 - Foreign military aid (CS)</t>
   </si>
   <si>
-    <t>02.3 - Foreign military aid</t>
-  </si>
-  <si>
     <t>15240</t>
   </si>
   <si>
@@ -622,15 +622,15 @@
     <t>16010</t>
   </si>
   <si>
+    <t>10.9 - Social protection n.e.c.</t>
+  </si>
+  <si>
     <t>160</t>
   </si>
   <si>
     <t>10.9.0 - Social protection n.e.c. (CS)</t>
   </si>
   <si>
-    <t>10.9 - Social protection n.e.c.</t>
-  </si>
-  <si>
     <t>16011</t>
   </si>
   <si>
@@ -640,12 +640,12 @@
     <t>16013</t>
   </si>
   <si>
+    <t>10.2 - Old age</t>
+  </si>
+  <si>
     <t>10.2.0 - Old age (IS)</t>
   </si>
   <si>
-    <t>10.2 - Old age</t>
-  </si>
-  <si>
     <t>16014</t>
   </si>
   <si>
@@ -655,45 +655,45 @@
     <t>16020</t>
   </si>
   <si>
+    <t>10.5 - Unemployment</t>
+  </si>
+  <si>
     <t>10.5.0 - Unemployment (IS)</t>
   </si>
   <si>
-    <t>10.5 - Unemployment</t>
-  </si>
-  <si>
     <t>16030</t>
   </si>
   <si>
+    <t>06.6 - Housing and community amenities n.e.c.</t>
+  </si>
+  <si>
     <t>06.6.0 - Housing and community amenities n.e.c. (CS)</t>
   </si>
   <si>
-    <t>06.6 - Housing and community amenities n.e.c.</t>
-  </si>
-  <si>
     <t>16040</t>
   </si>
   <si>
+    <t>06.1 - Housing development</t>
+  </si>
+  <si>
     <t>06.1.0 - Housing development (CS)</t>
   </si>
   <si>
-    <t>06.1 - Housing development</t>
-  </si>
-  <si>
     <t>16050</t>
   </si>
   <si>
     <t>16061</t>
   </si>
   <si>
+    <t>08.2 - Cultural services</t>
+  </si>
+  <si>
     <t>08 - Recreation, culture and religion</t>
   </si>
   <si>
     <t>08.2.0 - Cultural services (IS)</t>
   </si>
   <si>
-    <t>08.2 - Cultural services</t>
-  </si>
-  <si>
     <t>16062</t>
   </si>
   <si>
@@ -706,12 +706,12 @@
     <t>16065</t>
   </si>
   <si>
+    <t>08.1 - Recreational and sporting services</t>
+  </si>
+  <si>
     <t>08.1.0 - Recreational and sporting services (IS)</t>
   </si>
   <si>
-    <t>08.1 - Recreational and sporting services</t>
-  </si>
-  <si>
     <t>16066</t>
   </si>
   <si>
@@ -742,12 +742,12 @@
     <t>21020</t>
   </si>
   <si>
+    <t>04.5 - Transport</t>
+  </si>
+  <si>
     <t>04.5.1 - Road transport (CS)</t>
   </si>
   <si>
-    <t>04.5 - Transport</t>
-  </si>
-  <si>
     <t>21021</t>
   </si>
   <si>
@@ -781,12 +781,12 @@
     <t>21061</t>
   </si>
   <si>
+    <t>04.7 - Other industries</t>
+  </si>
+  <si>
     <t>04.7.1 - Distributive trades, storage and warehousing (CS)</t>
   </si>
   <si>
-    <t>04.7 - Other industries</t>
-  </si>
-  <si>
     <t>21081</t>
   </si>
   <si>
@@ -811,18 +811,21 @@
     <t>22030</t>
   </si>
   <si>
+    <t>08.3 - Broadcasting and publishing services</t>
+  </si>
+  <si>
     <t>08.3.0 - Broadcasting and publishing services (CS)</t>
   </si>
   <si>
-    <t>08.3 - Broadcasting and publishing services</t>
-  </si>
-  <si>
     <t>22040</t>
   </si>
   <si>
     <t>23110</t>
   </si>
   <si>
+    <t>04.3 - Fuel and energy</t>
+  </si>
+  <si>
     <t>231</t>
   </si>
   <si>
@@ -832,21 +835,18 @@
     <t>04.3.5 - Electricity (CS)</t>
   </si>
   <si>
-    <t>04.3 - Fuel and energy</t>
-  </si>
-  <si>
     <t>23111</t>
   </si>
   <si>
     <t>23112</t>
   </si>
   <si>
+    <t>04.8 - R&amp;D Economic affairs</t>
+  </si>
+  <si>
     <t>04.8.3 - R&amp;D Fuel and energy (CS)</t>
   </si>
   <si>
-    <t>04.8 - R&amp;D Economic affairs</t>
-  </si>
-  <si>
     <t>23181</t>
   </si>
   <si>
@@ -991,6 +991,9 @@
     <t>31110</t>
   </si>
   <si>
+    <t>04.2 - Agriculture, forestry, fishing and hunting</t>
+  </si>
+  <si>
     <t>311</t>
   </si>
   <si>
@@ -1000,9 +1003,6 @@
     <t>04.2.1 - Agriculture (CS)</t>
   </si>
   <si>
-    <t>04.2 - Agriculture, forestry, fishing and hunting</t>
-  </si>
-  <si>
     <t>31120</t>
   </si>
   <si>
@@ -1105,6 +1105,9 @@
     <t>32110</t>
   </si>
   <si>
+    <t>04.4 - Mining, manufacturing and construction</t>
+  </si>
+  <si>
     <t>321</t>
   </si>
   <si>
@@ -1114,9 +1117,6 @@
     <t>04.4.2 - Manufacturing (CS)</t>
   </si>
   <si>
-    <t>04.4 - Mining, manufacturing and construction</t>
-  </si>
-  <si>
     <t>32120</t>
   </si>
   <si>
@@ -1261,12 +1261,12 @@
     <t>41030</t>
   </si>
   <si>
+    <t>05.4 - Protection of biodiversity and landscape</t>
+  </si>
+  <si>
     <t>05.4.0 - Protection of biodiversity and landscape (CS)</t>
   </si>
   <si>
-    <t>05.4 - Protection of biodiversity and landscape</t>
-  </si>
-  <si>
     <t>41040</t>
   </si>
   <si>
@@ -1279,27 +1279,27 @@
     <t>43010</t>
   </si>
   <si>
+    <t>04.9 - Economic affairs n.e.c.</t>
+  </si>
+  <si>
     <t>430</t>
   </si>
   <si>
     <t>04.9.0 - Economic affairs n.e.c. (CS)</t>
   </si>
   <si>
-    <t>04.9 - Economic affairs n.e.c.</t>
-  </si>
-  <si>
     <t>43030</t>
   </si>
   <si>
     <t>43031</t>
   </si>
   <si>
+    <t>06.2 - Community development</t>
+  </si>
+  <si>
     <t>06.2.0 - Community development (CS)</t>
   </si>
   <si>
-    <t>06.2 - Community development</t>
-  </si>
-  <si>
     <t>43032</t>
   </si>
   <si>
@@ -1318,24 +1318,24 @@
     <t>43060</t>
   </si>
   <si>
+    <t>02.2 - Civil defence</t>
+  </si>
+  <si>
     <t>02.2.0 - Civil defence (CS)</t>
   </si>
   <si>
-    <t>02.2 - Civil defence</t>
-  </si>
-  <si>
     <t>43071</t>
   </si>
   <si>
     <t>43072</t>
   </si>
   <si>
+    <t>10.4 - Family and children</t>
+  </si>
+  <si>
     <t>10.4.0 - Family and children (IS)</t>
   </si>
   <si>
-    <t>10.4 - Family and children</t>
-  </si>
-  <si>
     <t>43073</t>
   </si>
   <si>
@@ -1345,12 +1345,12 @@
     <t>43082</t>
   </si>
   <si>
+    <t>01.4 - Basic research</t>
+  </si>
+  <si>
     <t>01.4.0 - Basic research (CS)</t>
   </si>
   <si>
-    <t>01.4 - Basic research</t>
-  </si>
-  <si>
     <t>51010</t>
   </si>
   <si>
@@ -1375,13 +1375,13 @@
     <t>60010</t>
   </si>
   <si>
+    <t>01.7 - Public debt transactions</t>
+  </si>
+  <si>
     <t>600</t>
   </si>
   <si>
     <t>01.7.0 - Public debt transactions (CS)</t>
-  </si>
-  <si>
-    <t>01.7 - Public debt transactions</t>
   </si>
   <si>
     <t>60020</t>
@@ -1863,7 +1863,7 @@
         <v>8</v>
       </c>
       <c r="C3" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="D3" t="s">
         <v>10</v>
@@ -1872,7 +1872,7 @@
         <v>11</v>
       </c>
       <c r="F3" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="G3" t="s">
         <v>16</v>
@@ -1909,7 +1909,7 @@
         <v>8</v>
       </c>
       <c r="C5" t="s">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="D5" t="s">
         <v>10</v>
@@ -1918,7 +1918,7 @@
         <v>11</v>
       </c>
       <c r="F5" t="s">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="G5" t="s">
         <v>20</v>
@@ -1932,16 +1932,16 @@
         <v>8</v>
       </c>
       <c r="C6" t="s">
-        <v>9</v>
+        <v>22</v>
       </c>
       <c r="D6" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E6" t="s">
         <v>11</v>
       </c>
       <c r="F6" t="s">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="G6" t="s">
         <v>24</v>
@@ -1958,7 +1958,7 @@
         <v>9</v>
       </c>
       <c r="D7" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E7" t="s">
         <v>11</v>
@@ -1978,16 +1978,16 @@
         <v>8</v>
       </c>
       <c r="C8" t="s">
-        <v>9</v>
+        <v>22</v>
       </c>
       <c r="D8" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E8" t="s">
         <v>11</v>
       </c>
       <c r="F8" t="s">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="G8" t="s">
         <v>24</v>
@@ -2001,16 +2001,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="s">
-        <v>9</v>
+        <v>22</v>
       </c>
       <c r="D9" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E9" t="s">
         <v>11</v>
       </c>
       <c r="F9" t="s">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="G9" t="s">
         <v>24</v>
@@ -2024,19 +2024,19 @@
         <v>8</v>
       </c>
       <c r="C10" t="s">
-        <v>9</v>
+        <v>22</v>
       </c>
       <c r="D10" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E10" t="s">
         <v>11</v>
       </c>
       <c r="F10" t="s">
+        <v>12</v>
+      </c>
+      <c r="G10" t="s">
         <v>29</v>
-      </c>
-      <c r="G10" t="s">
-        <v>24</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -2050,7 +2050,7 @@
         <v>31</v>
       </c>
       <c r="D11" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E11" t="s">
         <v>11</v>
@@ -2070,16 +2070,16 @@
         <v>8</v>
       </c>
       <c r="C12" t="s">
-        <v>9</v>
+        <v>35</v>
       </c>
       <c r="D12" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E12" t="s">
         <v>11</v>
       </c>
       <c r="F12" t="s">
-        <v>35</v>
+        <v>12</v>
       </c>
       <c r="G12" t="s">
         <v>36</v>
@@ -2093,7 +2093,7 @@
         <v>8</v>
       </c>
       <c r="C13" t="s">
-        <v>9</v>
+        <v>35</v>
       </c>
       <c r="D13" t="s">
         <v>38</v>
@@ -2102,10 +2102,10 @@
         <v>11</v>
       </c>
       <c r="F13" t="s">
+        <v>12</v>
+      </c>
+      <c r="G13" t="s">
         <v>39</v>
-      </c>
-      <c r="G13" t="s">
-        <v>36</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -2116,7 +2116,7 @@
         <v>8</v>
       </c>
       <c r="C14" t="s">
-        <v>9</v>
+        <v>41</v>
       </c>
       <c r="D14" t="s">
         <v>38</v>
@@ -2125,7 +2125,7 @@
         <v>11</v>
       </c>
       <c r="F14" t="s">
-        <v>41</v>
+        <v>12</v>
       </c>
       <c r="G14" t="s">
         <v>42</v>
@@ -2139,16 +2139,16 @@
         <v>8</v>
       </c>
       <c r="C15" t="s">
-        <v>9</v>
+        <v>44</v>
       </c>
       <c r="D15" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E15" t="s">
         <v>11</v>
       </c>
       <c r="F15" t="s">
-        <v>45</v>
+        <v>12</v>
       </c>
       <c r="G15" t="s">
         <v>46</v>
@@ -2162,16 +2162,16 @@
         <v>8</v>
       </c>
       <c r="C16" t="s">
-        <v>9</v>
+        <v>48</v>
       </c>
       <c r="D16" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E16" t="s">
         <v>11</v>
       </c>
       <c r="F16" t="s">
-        <v>48</v>
+        <v>12</v>
       </c>
       <c r="G16" t="s">
         <v>49</v>
@@ -2185,16 +2185,16 @@
         <v>8</v>
       </c>
       <c r="C17" t="s">
-        <v>31</v>
+        <v>51</v>
       </c>
       <c r="D17" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E17" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F17" t="s">
-        <v>53</v>
+        <v>32</v>
       </c>
       <c r="G17" t="s">
         <v>54</v>
@@ -2208,16 +2208,16 @@
         <v>8</v>
       </c>
       <c r="C18" t="s">
-        <v>31</v>
+        <v>51</v>
       </c>
       <c r="D18" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E18" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F18" t="s">
-        <v>53</v>
+        <v>32</v>
       </c>
       <c r="G18" t="s">
         <v>54</v>
@@ -2231,16 +2231,16 @@
         <v>8</v>
       </c>
       <c r="C19" t="s">
-        <v>31</v>
+        <v>57</v>
       </c>
       <c r="D19" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E19" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F19" t="s">
-        <v>57</v>
+        <v>32</v>
       </c>
       <c r="G19" t="s">
         <v>58</v>
@@ -2254,16 +2254,16 @@
         <v>8</v>
       </c>
       <c r="C20" t="s">
-        <v>31</v>
+        <v>60</v>
       </c>
       <c r="D20" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E20" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F20" t="s">
-        <v>60</v>
+        <v>32</v>
       </c>
       <c r="G20" t="s">
         <v>61</v>
@@ -2277,16 +2277,16 @@
         <v>8</v>
       </c>
       <c r="C21" t="s">
-        <v>31</v>
+        <v>51</v>
       </c>
       <c r="D21" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E21" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F21" t="s">
-        <v>53</v>
+        <v>32</v>
       </c>
       <c r="G21" t="s">
         <v>54</v>
@@ -2306,7 +2306,7 @@
         <v>64</v>
       </c>
       <c r="E22" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F22" t="s">
         <v>32</v>
@@ -2323,16 +2323,16 @@
         <v>8</v>
       </c>
       <c r="C23" t="s">
-        <v>31</v>
+        <v>66</v>
       </c>
       <c r="D23" t="s">
         <v>64</v>
       </c>
       <c r="E23" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F23" t="s">
-        <v>66</v>
+        <v>32</v>
       </c>
       <c r="G23" t="s">
         <v>67</v>
@@ -2352,7 +2352,7 @@
         <v>64</v>
       </c>
       <c r="E24" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F24" t="s">
         <v>32</v>
@@ -2375,7 +2375,7 @@
         <v>64</v>
       </c>
       <c r="E25" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F25" t="s">
         <v>32</v>
@@ -2398,7 +2398,7 @@
         <v>64</v>
       </c>
       <c r="E26" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F26" t="s">
         <v>32</v>
@@ -2421,7 +2421,7 @@
         <v>64</v>
       </c>
       <c r="E27" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F27" t="s">
         <v>32</v>
@@ -2444,7 +2444,7 @@
         <v>64</v>
       </c>
       <c r="E28" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F28" t="s">
         <v>32</v>
@@ -2467,7 +2467,7 @@
         <v>64</v>
       </c>
       <c r="E29" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F29" t="s">
         <v>32</v>
@@ -2484,16 +2484,16 @@
         <v>8</v>
       </c>
       <c r="C30" t="s">
-        <v>31</v>
+        <v>51</v>
       </c>
       <c r="D30" t="s">
         <v>64</v>
       </c>
       <c r="E30" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F30" t="s">
-        <v>53</v>
+        <v>32</v>
       </c>
       <c r="G30" t="s">
         <v>54</v>
@@ -2513,7 +2513,7 @@
         <v>76</v>
       </c>
       <c r="E31" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F31" t="s">
         <v>32</v>
@@ -2536,7 +2536,7 @@
         <v>76</v>
       </c>
       <c r="E32" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F32" t="s">
         <v>32</v>
@@ -2559,7 +2559,7 @@
         <v>76</v>
       </c>
       <c r="E33" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F33" t="s">
         <v>32</v>
@@ -2582,7 +2582,7 @@
         <v>76</v>
       </c>
       <c r="E34" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F34" t="s">
         <v>32</v>
@@ -2605,7 +2605,7 @@
         <v>76</v>
       </c>
       <c r="E35" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F35" t="s">
         <v>32</v>
@@ -2622,16 +2622,16 @@
         <v>8</v>
       </c>
       <c r="C36" t="s">
-        <v>31</v>
+        <v>57</v>
       </c>
       <c r="D36" t="s">
         <v>76</v>
       </c>
       <c r="E36" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F36" t="s">
-        <v>57</v>
+        <v>32</v>
       </c>
       <c r="G36" t="s">
         <v>58</v>
@@ -2725,13 +2725,13 @@
         <v>8</v>
       </c>
       <c r="C41" t="s">
-        <v>31</v>
+        <v>51</v>
       </c>
       <c r="E41" t="s">
         <v>83</v>
       </c>
       <c r="F41" t="s">
-        <v>53</v>
+        <v>32</v>
       </c>
       <c r="G41" t="s">
         <v>54</v>
@@ -2745,13 +2745,13 @@
         <v>8</v>
       </c>
       <c r="C42" t="s">
-        <v>31</v>
+        <v>57</v>
       </c>
       <c r="E42" t="s">
         <v>83</v>
       </c>
       <c r="F42" t="s">
-        <v>57</v>
+        <v>32</v>
       </c>
       <c r="G42" t="s">
         <v>58</v>
@@ -2845,13 +2845,13 @@
         <v>8</v>
       </c>
       <c r="C47" t="s">
-        <v>95</v>
+        <v>101</v>
       </c>
       <c r="E47" t="s">
         <v>91</v>
       </c>
       <c r="F47" t="s">
-        <v>101</v>
+        <v>96</v>
       </c>
       <c r="G47" t="s">
         <v>102</v>
@@ -2905,13 +2905,13 @@
         <v>8</v>
       </c>
       <c r="C50" t="s">
-        <v>95</v>
+        <v>101</v>
       </c>
       <c r="E50" t="s">
         <v>91</v>
       </c>
       <c r="F50" t="s">
-        <v>101</v>
+        <v>96</v>
       </c>
       <c r="G50" t="s">
         <v>102</v>
@@ -2945,13 +2945,13 @@
         <v>8</v>
       </c>
       <c r="C52" t="s">
-        <v>95</v>
+        <v>108</v>
       </c>
       <c r="E52" t="s">
         <v>91</v>
       </c>
       <c r="F52" t="s">
-        <v>108</v>
+        <v>96</v>
       </c>
       <c r="G52" t="s">
         <v>109</v>
@@ -3008,7 +3008,7 @@
         <v>8</v>
       </c>
       <c r="C55" t="s">
-        <v>112</v>
+        <v>118</v>
       </c>
       <c r="D55" t="s">
         <v>113</v>
@@ -3017,7 +3017,7 @@
         <v>114</v>
       </c>
       <c r="F55" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="G55" t="s">
         <v>119</v>
@@ -3031,7 +3031,7 @@
         <v>8</v>
       </c>
       <c r="C56" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="D56" t="s">
         <v>113</v>
@@ -3040,7 +3040,7 @@
         <v>114</v>
       </c>
       <c r="F56" t="s">
-        <v>121</v>
+        <v>115</v>
       </c>
       <c r="G56" t="s">
         <v>122</v>
@@ -3077,7 +3077,7 @@
         <v>8</v>
       </c>
       <c r="C58" t="s">
-        <v>112</v>
+        <v>118</v>
       </c>
       <c r="D58" t="s">
         <v>113</v>
@@ -3086,7 +3086,7 @@
         <v>114</v>
       </c>
       <c r="F58" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="G58" t="s">
         <v>119</v>
@@ -3100,7 +3100,7 @@
         <v>8</v>
       </c>
       <c r="C59" t="s">
-        <v>112</v>
+        <v>118</v>
       </c>
       <c r="D59" t="s">
         <v>113</v>
@@ -3109,7 +3109,7 @@
         <v>114</v>
       </c>
       <c r="F59" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="G59" t="s">
         <v>119</v>
@@ -3123,7 +3123,7 @@
         <v>8</v>
       </c>
       <c r="C60" t="s">
-        <v>112</v>
+        <v>118</v>
       </c>
       <c r="D60" t="s">
         <v>113</v>
@@ -3132,7 +3132,7 @@
         <v>114</v>
       </c>
       <c r="F60" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="G60" t="s">
         <v>119</v>
@@ -3146,7 +3146,7 @@
         <v>8</v>
       </c>
       <c r="C61" t="s">
-        <v>112</v>
+        <v>118</v>
       </c>
       <c r="D61" t="s">
         <v>113</v>
@@ -3155,7 +3155,7 @@
         <v>114</v>
       </c>
       <c r="F61" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="G61" t="s">
         <v>119</v>
@@ -3169,7 +3169,7 @@
         <v>8</v>
       </c>
       <c r="C62" t="s">
-        <v>112</v>
+        <v>118</v>
       </c>
       <c r="D62" t="s">
         <v>113</v>
@@ -3178,7 +3178,7 @@
         <v>114</v>
       </c>
       <c r="F62" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="G62" t="s">
         <v>119</v>
@@ -3192,7 +3192,7 @@
         <v>8</v>
       </c>
       <c r="C63" t="s">
-        <v>112</v>
+        <v>118</v>
       </c>
       <c r="D63" t="s">
         <v>113</v>
@@ -3201,10 +3201,10 @@
         <v>114</v>
       </c>
       <c r="F63" t="s">
+        <v>115</v>
+      </c>
+      <c r="G63" t="s">
         <v>133</v>
-      </c>
-      <c r="G63" t="s">
-        <v>119</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -3215,7 +3215,7 @@
         <v>8</v>
       </c>
       <c r="C64" t="s">
-        <v>112</v>
+        <v>118</v>
       </c>
       <c r="D64" t="s">
         <v>113</v>
@@ -3224,10 +3224,10 @@
         <v>114</v>
       </c>
       <c r="F64" t="s">
+        <v>115</v>
+      </c>
+      <c r="G64" t="s">
         <v>133</v>
-      </c>
-      <c r="G64" t="s">
-        <v>119</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -3238,7 +3238,7 @@
         <v>8</v>
       </c>
       <c r="C65" t="s">
-        <v>112</v>
+        <v>136</v>
       </c>
       <c r="D65" t="s">
         <v>113</v>
@@ -3247,7 +3247,7 @@
         <v>114</v>
       </c>
       <c r="F65" t="s">
-        <v>136</v>
+        <v>115</v>
       </c>
       <c r="G65" t="s">
         <v>137</v>
@@ -3284,7 +3284,7 @@
         <v>8</v>
       </c>
       <c r="C67" t="s">
-        <v>112</v>
+        <v>118</v>
       </c>
       <c r="D67" t="s">
         <v>113</v>
@@ -3293,7 +3293,7 @@
         <v>114</v>
       </c>
       <c r="F67" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="G67" t="s">
         <v>119</v>
@@ -3316,10 +3316,10 @@
         <v>114</v>
       </c>
       <c r="F68" t="s">
+        <v>115</v>
+      </c>
+      <c r="G68" t="s">
         <v>141</v>
-      </c>
-      <c r="G68" t="s">
-        <v>116</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -3339,10 +3339,10 @@
         <v>114</v>
       </c>
       <c r="F69" t="s">
+        <v>115</v>
+      </c>
+      <c r="G69" t="s">
         <v>143</v>
-      </c>
-      <c r="G69" t="s">
-        <v>116</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -3353,7 +3353,7 @@
         <v>8</v>
       </c>
       <c r="C70" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="D70" t="s">
         <v>113</v>
@@ -3362,7 +3362,7 @@
         <v>114</v>
       </c>
       <c r="F70" t="s">
-        <v>121</v>
+        <v>115</v>
       </c>
       <c r="G70" t="s">
         <v>122</v>
@@ -3376,7 +3376,7 @@
         <v>8</v>
       </c>
       <c r="C71" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="D71" t="s">
         <v>113</v>
@@ -3385,7 +3385,7 @@
         <v>114</v>
       </c>
       <c r="F71" t="s">
-        <v>121</v>
+        <v>115</v>
       </c>
       <c r="G71" t="s">
         <v>122</v>
@@ -3422,7 +3422,7 @@
         <v>8</v>
       </c>
       <c r="C73" t="s">
-        <v>124</v>
+        <v>148</v>
       </c>
       <c r="D73" t="s">
         <v>113</v>
@@ -3431,7 +3431,7 @@
         <v>114</v>
       </c>
       <c r="F73" t="s">
-        <v>148</v>
+        <v>125</v>
       </c>
       <c r="G73" t="s">
         <v>149</v>
@@ -3445,7 +3445,7 @@
         <v>8</v>
       </c>
       <c r="C74" t="s">
-        <v>124</v>
+        <v>151</v>
       </c>
       <c r="D74" t="s">
         <v>113</v>
@@ -3454,7 +3454,7 @@
         <v>114</v>
       </c>
       <c r="F74" t="s">
-        <v>151</v>
+        <v>125</v>
       </c>
       <c r="G74" t="s">
         <v>152</v>
@@ -3468,7 +3468,7 @@
         <v>8</v>
       </c>
       <c r="C75" t="s">
-        <v>124</v>
+        <v>154</v>
       </c>
       <c r="D75" t="s">
         <v>113</v>
@@ -3477,7 +3477,7 @@
         <v>114</v>
       </c>
       <c r="F75" t="s">
-        <v>154</v>
+        <v>125</v>
       </c>
       <c r="G75" t="s">
         <v>155</v>
@@ -3491,7 +3491,7 @@
         <v>8</v>
       </c>
       <c r="C76" t="s">
-        <v>124</v>
+        <v>148</v>
       </c>
       <c r="D76" t="s">
         <v>113</v>
@@ -3500,7 +3500,7 @@
         <v>114</v>
       </c>
       <c r="F76" t="s">
-        <v>148</v>
+        <v>125</v>
       </c>
       <c r="G76" t="s">
         <v>149</v>
@@ -3514,7 +3514,7 @@
         <v>8</v>
       </c>
       <c r="C77" t="s">
-        <v>124</v>
+        <v>148</v>
       </c>
       <c r="D77" t="s">
         <v>113</v>
@@ -3523,7 +3523,7 @@
         <v>114</v>
       </c>
       <c r="F77" t="s">
-        <v>148</v>
+        <v>125</v>
       </c>
       <c r="G77" t="s">
         <v>149</v>
@@ -3537,7 +3537,7 @@
         <v>8</v>
       </c>
       <c r="C78" t="s">
-        <v>124</v>
+        <v>151</v>
       </c>
       <c r="D78" t="s">
         <v>113</v>
@@ -3546,7 +3546,7 @@
         <v>114</v>
       </c>
       <c r="F78" t="s">
-        <v>151</v>
+        <v>125</v>
       </c>
       <c r="G78" t="s">
         <v>152</v>
@@ -3560,7 +3560,7 @@
         <v>8</v>
       </c>
       <c r="C79" t="s">
-        <v>124</v>
+        <v>160</v>
       </c>
       <c r="D79" t="s">
         <v>113</v>
@@ -3569,7 +3569,7 @@
         <v>114</v>
       </c>
       <c r="F79" t="s">
-        <v>160</v>
+        <v>125</v>
       </c>
       <c r="G79" t="s">
         <v>161</v>
@@ -3661,10 +3661,10 @@
         <v>114</v>
       </c>
       <c r="F83" t="s">
+        <v>115</v>
+      </c>
+      <c r="G83" t="s">
         <v>143</v>
-      </c>
-      <c r="G83" t="s">
-        <v>116</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -3675,7 +3675,7 @@
         <v>8</v>
       </c>
       <c r="C84" t="s">
-        <v>112</v>
+        <v>170</v>
       </c>
       <c r="D84" t="s">
         <v>113</v>
@@ -3684,7 +3684,7 @@
         <v>114</v>
       </c>
       <c r="F84" t="s">
-        <v>170</v>
+        <v>115</v>
       </c>
       <c r="G84" t="s">
         <v>171</v>
@@ -3698,7 +3698,7 @@
         <v>8</v>
       </c>
       <c r="C85" t="s">
-        <v>112</v>
+        <v>118</v>
       </c>
       <c r="D85" t="s">
         <v>113</v>
@@ -3707,10 +3707,10 @@
         <v>114</v>
       </c>
       <c r="F85" t="s">
+        <v>115</v>
+      </c>
+      <c r="G85" t="s">
         <v>173</v>
-      </c>
-      <c r="G85" t="s">
-        <v>119</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -3721,7 +3721,7 @@
         <v>8</v>
       </c>
       <c r="C86" t="s">
-        <v>163</v>
+        <v>175</v>
       </c>
       <c r="D86" t="s">
         <v>113</v>
@@ -3730,7 +3730,7 @@
         <v>114</v>
       </c>
       <c r="F86" t="s">
-        <v>175</v>
+        <v>164</v>
       </c>
       <c r="G86" t="s">
         <v>176</v>
@@ -3744,7 +3744,7 @@
         <v>8</v>
       </c>
       <c r="C87" t="s">
-        <v>112</v>
+        <v>118</v>
       </c>
       <c r="D87" t="s">
         <v>113</v>
@@ -3753,10 +3753,10 @@
         <v>114</v>
       </c>
       <c r="F87" t="s">
+        <v>115</v>
+      </c>
+      <c r="G87" t="s">
         <v>173</v>
-      </c>
-      <c r="G87" t="s">
-        <v>119</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -3767,7 +3767,7 @@
         <v>8</v>
       </c>
       <c r="C88" t="s">
-        <v>112</v>
+        <v>118</v>
       </c>
       <c r="D88" t="s">
         <v>113</v>
@@ -3776,7 +3776,7 @@
         <v>114</v>
       </c>
       <c r="F88" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="G88" t="s">
         <v>119</v>
@@ -3790,7 +3790,7 @@
         <v>8</v>
       </c>
       <c r="C89" t="s">
-        <v>112</v>
+        <v>118</v>
       </c>
       <c r="D89" t="s">
         <v>113</v>
@@ -3799,7 +3799,7 @@
         <v>114</v>
       </c>
       <c r="F89" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="G89" t="s">
         <v>119</v>
@@ -3882,7 +3882,7 @@
         <v>8</v>
       </c>
       <c r="C93" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="D93" t="s">
         <v>113</v>
@@ -3891,7 +3891,7 @@
         <v>114</v>
       </c>
       <c r="F93" t="s">
-        <v>121</v>
+        <v>115</v>
       </c>
       <c r="G93" t="s">
         <v>122</v>
@@ -3928,7 +3928,7 @@
         <v>8</v>
       </c>
       <c r="C95" t="s">
-        <v>112</v>
+        <v>189</v>
       </c>
       <c r="D95" t="s">
         <v>113</v>
@@ -3937,7 +3937,7 @@
         <v>114</v>
       </c>
       <c r="F95" t="s">
-        <v>189</v>
+        <v>115</v>
       </c>
       <c r="G95" t="s">
         <v>190</v>
@@ -4043,7 +4043,7 @@
         <v>8</v>
       </c>
       <c r="C100" t="s">
-        <v>124</v>
+        <v>154</v>
       </c>
       <c r="D100" t="s">
         <v>192</v>
@@ -4052,7 +4052,7 @@
         <v>114</v>
       </c>
       <c r="F100" t="s">
-        <v>154</v>
+        <v>125</v>
       </c>
       <c r="G100" t="s">
         <v>155</v>
@@ -4089,13 +4089,13 @@
         <v>8</v>
       </c>
       <c r="C102" t="s">
-        <v>182</v>
+        <v>202</v>
       </c>
       <c r="E102" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="F102" t="s">
-        <v>203</v>
+        <v>183</v>
       </c>
       <c r="G102" t="s">
         <v>204</v>
@@ -4109,13 +4109,13 @@
         <v>8</v>
       </c>
       <c r="C103" t="s">
-        <v>182</v>
+        <v>202</v>
       </c>
       <c r="E103" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="F103" t="s">
-        <v>203</v>
+        <v>183</v>
       </c>
       <c r="G103" t="s">
         <v>204</v>
@@ -4129,13 +4129,13 @@
         <v>8</v>
       </c>
       <c r="C104" t="s">
-        <v>182</v>
+        <v>202</v>
       </c>
       <c r="E104" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="F104" t="s">
-        <v>203</v>
+        <v>183</v>
       </c>
       <c r="G104" t="s">
         <v>204</v>
@@ -4149,13 +4149,13 @@
         <v>8</v>
       </c>
       <c r="C105" t="s">
-        <v>182</v>
+        <v>208</v>
       </c>
       <c r="E105" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="F105" t="s">
-        <v>208</v>
+        <v>183</v>
       </c>
       <c r="G105" t="s">
         <v>209</v>
@@ -4169,13 +4169,13 @@
         <v>8</v>
       </c>
       <c r="C106" t="s">
-        <v>182</v>
+        <v>202</v>
       </c>
       <c r="E106" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="F106" t="s">
-        <v>203</v>
+        <v>183</v>
       </c>
       <c r="G106" t="s">
         <v>204</v>
@@ -4192,7 +4192,7 @@
         <v>182</v>
       </c>
       <c r="E107" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="F107" t="s">
         <v>183</v>
@@ -4209,13 +4209,13 @@
         <v>8</v>
       </c>
       <c r="C108" t="s">
-        <v>182</v>
+        <v>213</v>
       </c>
       <c r="E108" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="F108" t="s">
-        <v>213</v>
+        <v>183</v>
       </c>
       <c r="G108" t="s">
         <v>214</v>
@@ -4229,13 +4229,13 @@
         <v>8</v>
       </c>
       <c r="C109" t="s">
-        <v>90</v>
+        <v>216</v>
       </c>
       <c r="E109" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="F109" t="s">
-        <v>216</v>
+        <v>92</v>
       </c>
       <c r="G109" t="s">
         <v>217</v>
@@ -4249,13 +4249,13 @@
         <v>8</v>
       </c>
       <c r="C110" t="s">
-        <v>90</v>
+        <v>219</v>
       </c>
       <c r="E110" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="F110" t="s">
-        <v>219</v>
+        <v>92</v>
       </c>
       <c r="G110" t="s">
         <v>220</v>
@@ -4269,13 +4269,13 @@
         <v>8</v>
       </c>
       <c r="C111" t="s">
-        <v>182</v>
+        <v>202</v>
       </c>
       <c r="E111" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="F111" t="s">
-        <v>203</v>
+        <v>183</v>
       </c>
       <c r="G111" t="s">
         <v>204</v>
@@ -4292,7 +4292,7 @@
         <v>223</v>
       </c>
       <c r="E112" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="F112" t="s">
         <v>224</v>
@@ -4312,13 +4312,13 @@
         <v>112</v>
       </c>
       <c r="E113" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="F113" t="s">
+        <v>115</v>
+      </c>
+      <c r="G113" t="s">
         <v>143</v>
-      </c>
-      <c r="G113" t="s">
-        <v>116</v>
       </c>
     </row>
     <row r="114" spans="1:7">
@@ -4329,13 +4329,13 @@
         <v>8</v>
       </c>
       <c r="C114" t="s">
-        <v>124</v>
+        <v>151</v>
       </c>
       <c r="E114" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="F114" t="s">
-        <v>151</v>
+        <v>125</v>
       </c>
       <c r="G114" t="s">
         <v>152</v>
@@ -4352,7 +4352,7 @@
         <v>182</v>
       </c>
       <c r="E115" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="F115" t="s">
         <v>183</v>
@@ -4369,13 +4369,13 @@
         <v>8</v>
       </c>
       <c r="C116" t="s">
-        <v>223</v>
+        <v>230</v>
       </c>
       <c r="E116" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="F116" t="s">
-        <v>230</v>
+        <v>224</v>
       </c>
       <c r="G116" t="s">
         <v>231</v>
@@ -4392,7 +4392,7 @@
         <v>223</v>
       </c>
       <c r="E117" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="F117" t="s">
         <v>224</v>
@@ -4412,13 +4412,13 @@
         <v>163</v>
       </c>
       <c r="E118" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="F118" t="s">
+        <v>164</v>
+      </c>
+      <c r="G118" t="s">
         <v>234</v>
-      </c>
-      <c r="G118" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="119" spans="1:7">
@@ -4432,7 +4432,7 @@
         <v>182</v>
       </c>
       <c r="E119" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="F119" t="s">
         <v>183</v>
@@ -4449,13 +4449,13 @@
         <v>8</v>
       </c>
       <c r="C120" t="s">
-        <v>112</v>
+        <v>170</v>
       </c>
       <c r="E120" t="s">
         <v>237</v>
       </c>
       <c r="F120" t="s">
-        <v>170</v>
+        <v>115</v>
       </c>
       <c r="G120" t="s">
         <v>171</v>
@@ -4475,10 +4475,10 @@
         <v>237</v>
       </c>
       <c r="F121" t="s">
+        <v>115</v>
+      </c>
+      <c r="G121" t="s">
         <v>143</v>
-      </c>
-      <c r="G121" t="s">
-        <v>116</v>
       </c>
     </row>
     <row r="122" spans="1:7">
@@ -4489,13 +4489,13 @@
         <v>8</v>
       </c>
       <c r="C122" t="s">
-        <v>112</v>
+        <v>170</v>
       </c>
       <c r="E122" t="s">
         <v>237</v>
       </c>
       <c r="F122" t="s">
-        <v>170</v>
+        <v>115</v>
       </c>
       <c r="G122" t="s">
         <v>171</v>
@@ -4509,13 +4509,13 @@
         <v>8</v>
       </c>
       <c r="C123" t="s">
-        <v>112</v>
+        <v>170</v>
       </c>
       <c r="E123" t="s">
         <v>237</v>
       </c>
       <c r="F123" t="s">
-        <v>170</v>
+        <v>115</v>
       </c>
       <c r="G123" t="s">
         <v>171</v>
@@ -4529,13 +4529,13 @@
         <v>8</v>
       </c>
       <c r="C124" t="s">
-        <v>163</v>
+        <v>242</v>
       </c>
       <c r="E124" t="s">
         <v>237</v>
       </c>
       <c r="F124" t="s">
-        <v>242</v>
+        <v>164</v>
       </c>
       <c r="G124" t="s">
         <v>243</v>
@@ -4549,13 +4549,13 @@
         <v>8</v>
       </c>
       <c r="C125" t="s">
-        <v>163</v>
+        <v>242</v>
       </c>
       <c r="E125" t="s">
         <v>237</v>
       </c>
       <c r="F125" t="s">
-        <v>242</v>
+        <v>164</v>
       </c>
       <c r="G125" t="s">
         <v>243</v>
@@ -4569,13 +4569,13 @@
         <v>8</v>
       </c>
       <c r="C126" t="s">
-        <v>163</v>
+        <v>242</v>
       </c>
       <c r="E126" t="s">
         <v>237</v>
       </c>
       <c r="F126" t="s">
-        <v>242</v>
+        <v>164</v>
       </c>
       <c r="G126" t="s">
         <v>243</v>
@@ -4589,13 +4589,13 @@
         <v>8</v>
       </c>
       <c r="C127" t="s">
-        <v>163</v>
+        <v>242</v>
       </c>
       <c r="E127" t="s">
         <v>237</v>
       </c>
       <c r="F127" t="s">
-        <v>242</v>
+        <v>164</v>
       </c>
       <c r="G127" t="s">
         <v>243</v>
@@ -4609,13 +4609,13 @@
         <v>8</v>
       </c>
       <c r="C128" t="s">
-        <v>163</v>
+        <v>242</v>
       </c>
       <c r="E128" t="s">
         <v>237</v>
       </c>
       <c r="F128" t="s">
-        <v>242</v>
+        <v>164</v>
       </c>
       <c r="G128" t="s">
         <v>243</v>
@@ -4629,16 +4629,16 @@
         <v>8</v>
       </c>
       <c r="C129" t="s">
-        <v>163</v>
+        <v>242</v>
       </c>
       <c r="E129" t="s">
         <v>237</v>
       </c>
       <c r="F129" t="s">
+        <v>164</v>
+      </c>
+      <c r="G129" t="s">
         <v>249</v>
-      </c>
-      <c r="G129" t="s">
-        <v>243</v>
       </c>
     </row>
     <row r="130" spans="1:7">
@@ -4649,16 +4649,16 @@
         <v>8</v>
       </c>
       <c r="C130" t="s">
-        <v>163</v>
+        <v>242</v>
       </c>
       <c r="E130" t="s">
         <v>237</v>
       </c>
       <c r="F130" t="s">
+        <v>164</v>
+      </c>
+      <c r="G130" t="s">
         <v>251</v>
-      </c>
-      <c r="G130" t="s">
-        <v>243</v>
       </c>
     </row>
     <row r="131" spans="1:7">
@@ -4669,16 +4669,16 @@
         <v>8</v>
       </c>
       <c r="C131" t="s">
-        <v>163</v>
+        <v>242</v>
       </c>
       <c r="E131" t="s">
         <v>237</v>
       </c>
       <c r="F131" t="s">
+        <v>164</v>
+      </c>
+      <c r="G131" t="s">
         <v>253</v>
-      </c>
-      <c r="G131" t="s">
-        <v>243</v>
       </c>
     </row>
     <row r="132" spans="1:7">
@@ -4689,13 +4689,13 @@
         <v>8</v>
       </c>
       <c r="C132" t="s">
-        <v>163</v>
+        <v>255</v>
       </c>
       <c r="E132" t="s">
         <v>237</v>
       </c>
       <c r="F132" t="s">
-        <v>255</v>
+        <v>164</v>
       </c>
       <c r="G132" t="s">
         <v>256</v>
@@ -4709,13 +4709,13 @@
         <v>8</v>
       </c>
       <c r="C133" t="s">
-        <v>112</v>
+        <v>189</v>
       </c>
       <c r="E133" t="s">
         <v>237</v>
       </c>
       <c r="F133" t="s">
-        <v>189</v>
+        <v>115</v>
       </c>
       <c r="G133" t="s">
         <v>190</v>
@@ -4729,13 +4729,13 @@
         <v>8</v>
       </c>
       <c r="C134" t="s">
-        <v>163</v>
+        <v>175</v>
       </c>
       <c r="E134" t="s">
         <v>259</v>
       </c>
       <c r="F134" t="s">
-        <v>175</v>
+        <v>164</v>
       </c>
       <c r="G134" t="s">
         <v>176</v>
@@ -4749,13 +4749,13 @@
         <v>8</v>
       </c>
       <c r="C135" t="s">
-        <v>163</v>
+        <v>175</v>
       </c>
       <c r="E135" t="s">
         <v>259</v>
       </c>
       <c r="F135" t="s">
-        <v>175</v>
+        <v>164</v>
       </c>
       <c r="G135" t="s">
         <v>176</v>
@@ -4769,13 +4769,13 @@
         <v>8</v>
       </c>
       <c r="C136" t="s">
-        <v>163</v>
+        <v>175</v>
       </c>
       <c r="E136" t="s">
         <v>259</v>
       </c>
       <c r="F136" t="s">
-        <v>175</v>
+        <v>164</v>
       </c>
       <c r="G136" t="s">
         <v>176</v>
@@ -4789,13 +4789,13 @@
         <v>8</v>
       </c>
       <c r="C137" t="s">
-        <v>163</v>
+        <v>175</v>
       </c>
       <c r="E137" t="s">
         <v>259</v>
       </c>
       <c r="F137" t="s">
-        <v>175</v>
+        <v>164</v>
       </c>
       <c r="G137" t="s">
         <v>176</v>
@@ -4809,13 +4809,13 @@
         <v>8</v>
       </c>
       <c r="C138" t="s">
-        <v>163</v>
+        <v>175</v>
       </c>
       <c r="E138" t="s">
         <v>259</v>
       </c>
       <c r="F138" t="s">
-        <v>175</v>
+        <v>164</v>
       </c>
       <c r="G138" t="s">
         <v>176</v>
@@ -4829,13 +4829,13 @@
         <v>8</v>
       </c>
       <c r="C139" t="s">
-        <v>223</v>
+        <v>265</v>
       </c>
       <c r="E139" t="s">
         <v>259</v>
       </c>
       <c r="F139" t="s">
-        <v>265</v>
+        <v>224</v>
       </c>
       <c r="G139" t="s">
         <v>266</v>
@@ -4849,13 +4849,13 @@
         <v>8</v>
       </c>
       <c r="C140" t="s">
-        <v>163</v>
+        <v>175</v>
       </c>
       <c r="E140" t="s">
         <v>259</v>
       </c>
       <c r="F140" t="s">
-        <v>175</v>
+        <v>164</v>
       </c>
       <c r="G140" t="s">
         <v>176</v>
@@ -4869,16 +4869,16 @@
         <v>8</v>
       </c>
       <c r="C141" t="s">
-        <v>163</v>
+        <v>269</v>
       </c>
       <c r="D141" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="E141" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="F141" t="s">
-        <v>271</v>
+        <v>164</v>
       </c>
       <c r="G141" t="s">
         <v>272</v>
@@ -4892,16 +4892,16 @@
         <v>8</v>
       </c>
       <c r="C142" t="s">
-        <v>163</v>
+        <v>269</v>
       </c>
       <c r="D142" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="E142" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="F142" t="s">
-        <v>271</v>
+        <v>164</v>
       </c>
       <c r="G142" t="s">
         <v>272</v>
@@ -4915,16 +4915,16 @@
         <v>8</v>
       </c>
       <c r="C143" t="s">
-        <v>163</v>
+        <v>275</v>
       </c>
       <c r="D143" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="E143" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="F143" t="s">
-        <v>275</v>
+        <v>164</v>
       </c>
       <c r="G143" t="s">
         <v>276</v>
@@ -4938,16 +4938,16 @@
         <v>8</v>
       </c>
       <c r="C144" t="s">
-        <v>163</v>
+        <v>275</v>
       </c>
       <c r="D144" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="E144" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="F144" t="s">
-        <v>275</v>
+        <v>164</v>
       </c>
       <c r="G144" t="s">
         <v>276</v>
@@ -4961,16 +4961,16 @@
         <v>8</v>
       </c>
       <c r="C145" t="s">
-        <v>163</v>
+        <v>275</v>
       </c>
       <c r="D145" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="E145" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="F145" t="s">
-        <v>275</v>
+        <v>164</v>
       </c>
       <c r="G145" t="s">
         <v>276</v>
@@ -4984,16 +4984,16 @@
         <v>8</v>
       </c>
       <c r="C146" t="s">
-        <v>163</v>
+        <v>269</v>
       </c>
       <c r="D146" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="E146" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="F146" t="s">
-        <v>271</v>
+        <v>164</v>
       </c>
       <c r="G146" t="s">
         <v>272</v>
@@ -5007,16 +5007,16 @@
         <v>8</v>
       </c>
       <c r="C147" t="s">
-        <v>163</v>
+        <v>269</v>
       </c>
       <c r="D147" t="s">
         <v>281</v>
       </c>
       <c r="E147" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="F147" t="s">
-        <v>271</v>
+        <v>164</v>
       </c>
       <c r="G147" t="s">
         <v>272</v>
@@ -5030,16 +5030,16 @@
         <v>8</v>
       </c>
       <c r="C148" t="s">
-        <v>163</v>
+        <v>269</v>
       </c>
       <c r="D148" t="s">
         <v>281</v>
       </c>
       <c r="E148" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="F148" t="s">
-        <v>271</v>
+        <v>164</v>
       </c>
       <c r="G148" t="s">
         <v>272</v>
@@ -5053,16 +5053,16 @@
         <v>8</v>
       </c>
       <c r="C149" t="s">
-        <v>163</v>
+        <v>269</v>
       </c>
       <c r="D149" t="s">
         <v>281</v>
       </c>
       <c r="E149" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="F149" t="s">
-        <v>271</v>
+        <v>164</v>
       </c>
       <c r="G149" t="s">
         <v>272</v>
@@ -5076,16 +5076,16 @@
         <v>8</v>
       </c>
       <c r="C150" t="s">
-        <v>163</v>
+        <v>269</v>
       </c>
       <c r="D150" t="s">
         <v>281</v>
       </c>
       <c r="E150" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="F150" t="s">
-        <v>271</v>
+        <v>164</v>
       </c>
       <c r="G150" t="s">
         <v>272</v>
@@ -5099,16 +5099,16 @@
         <v>8</v>
       </c>
       <c r="C151" t="s">
-        <v>163</v>
+        <v>269</v>
       </c>
       <c r="D151" t="s">
         <v>281</v>
       </c>
       <c r="E151" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="F151" t="s">
-        <v>271</v>
+        <v>164</v>
       </c>
       <c r="G151" t="s">
         <v>272</v>
@@ -5122,16 +5122,16 @@
         <v>8</v>
       </c>
       <c r="C152" t="s">
-        <v>163</v>
+        <v>269</v>
       </c>
       <c r="D152" t="s">
         <v>281</v>
       </c>
       <c r="E152" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="F152" t="s">
-        <v>271</v>
+        <v>164</v>
       </c>
       <c r="G152" t="s">
         <v>272</v>
@@ -5145,16 +5145,16 @@
         <v>8</v>
       </c>
       <c r="C153" t="s">
-        <v>163</v>
+        <v>269</v>
       </c>
       <c r="D153" t="s">
         <v>281</v>
       </c>
       <c r="E153" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="F153" t="s">
-        <v>271</v>
+        <v>164</v>
       </c>
       <c r="G153" t="s">
         <v>272</v>
@@ -5168,16 +5168,16 @@
         <v>8</v>
       </c>
       <c r="C154" t="s">
-        <v>163</v>
+        <v>269</v>
       </c>
       <c r="D154" t="s">
         <v>281</v>
       </c>
       <c r="E154" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="F154" t="s">
-        <v>271</v>
+        <v>164</v>
       </c>
       <c r="G154" t="s">
         <v>272</v>
@@ -5191,16 +5191,16 @@
         <v>8</v>
       </c>
       <c r="C155" t="s">
-        <v>163</v>
+        <v>269</v>
       </c>
       <c r="D155" t="s">
         <v>281</v>
       </c>
       <c r="E155" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="F155" t="s">
-        <v>271</v>
+        <v>164</v>
       </c>
       <c r="G155" t="s">
         <v>272</v>
@@ -5214,16 +5214,16 @@
         <v>8</v>
       </c>
       <c r="C156" t="s">
-        <v>163</v>
+        <v>269</v>
       </c>
       <c r="D156" t="s">
         <v>291</v>
       </c>
       <c r="E156" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="F156" t="s">
-        <v>271</v>
+        <v>164</v>
       </c>
       <c r="G156" t="s">
         <v>272</v>
@@ -5237,19 +5237,19 @@
         <v>8</v>
       </c>
       <c r="C157" t="s">
-        <v>163</v>
+        <v>269</v>
       </c>
       <c r="D157" t="s">
         <v>291</v>
       </c>
       <c r="E157" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="F157" t="s">
+        <v>164</v>
+      </c>
+      <c r="G157" t="s">
         <v>293</v>
-      </c>
-      <c r="G157" t="s">
-        <v>272</v>
       </c>
     </row>
     <row r="158" spans="1:7">
@@ -5260,16 +5260,16 @@
         <v>8</v>
       </c>
       <c r="C158" t="s">
-        <v>163</v>
+        <v>269</v>
       </c>
       <c r="D158" t="s">
         <v>291</v>
       </c>
       <c r="E158" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="F158" t="s">
-        <v>271</v>
+        <v>164</v>
       </c>
       <c r="G158" t="s">
         <v>272</v>
@@ -5283,16 +5283,16 @@
         <v>8</v>
       </c>
       <c r="C159" t="s">
-        <v>163</v>
+        <v>269</v>
       </c>
       <c r="D159" t="s">
         <v>291</v>
       </c>
       <c r="E159" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="F159" t="s">
-        <v>271</v>
+        <v>164</v>
       </c>
       <c r="G159" t="s">
         <v>272</v>
@@ -5306,16 +5306,16 @@
         <v>8</v>
       </c>
       <c r="C160" t="s">
-        <v>163</v>
+        <v>269</v>
       </c>
       <c r="D160" t="s">
         <v>291</v>
       </c>
       <c r="E160" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="F160" t="s">
-        <v>271</v>
+        <v>164</v>
       </c>
       <c r="G160" t="s">
         <v>272</v>
@@ -5329,16 +5329,16 @@
         <v>8</v>
       </c>
       <c r="C161" t="s">
-        <v>163</v>
+        <v>269</v>
       </c>
       <c r="D161" t="s">
         <v>291</v>
       </c>
       <c r="E161" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="F161" t="s">
-        <v>271</v>
+        <v>164</v>
       </c>
       <c r="G161" t="s">
         <v>272</v>
@@ -5352,16 +5352,16 @@
         <v>8</v>
       </c>
       <c r="C162" t="s">
-        <v>163</v>
+        <v>269</v>
       </c>
       <c r="D162" t="s">
         <v>299</v>
       </c>
       <c r="E162" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="F162" t="s">
-        <v>271</v>
+        <v>164</v>
       </c>
       <c r="G162" t="s">
         <v>272</v>
@@ -5375,19 +5375,19 @@
         <v>8</v>
       </c>
       <c r="C163" t="s">
-        <v>163</v>
+        <v>269</v>
       </c>
       <c r="D163" t="s">
         <v>301</v>
       </c>
       <c r="E163" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="F163" t="s">
+        <v>164</v>
+      </c>
+      <c r="G163" t="s">
         <v>302</v>
-      </c>
-      <c r="G163" t="s">
-        <v>272</v>
       </c>
     </row>
     <row r="164" spans="1:7">
@@ -5398,16 +5398,16 @@
         <v>8</v>
       </c>
       <c r="C164" t="s">
-        <v>163</v>
+        <v>269</v>
       </c>
       <c r="D164" t="s">
         <v>304</v>
       </c>
       <c r="E164" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="F164" t="s">
-        <v>271</v>
+        <v>164</v>
       </c>
       <c r="G164" t="s">
         <v>272</v>
@@ -5421,16 +5421,16 @@
         <v>8</v>
       </c>
       <c r="C165" t="s">
-        <v>163</v>
+        <v>269</v>
       </c>
       <c r="D165" t="s">
         <v>304</v>
       </c>
       <c r="E165" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="F165" t="s">
-        <v>271</v>
+        <v>164</v>
       </c>
       <c r="G165" t="s">
         <v>272</v>
@@ -5444,16 +5444,16 @@
         <v>8</v>
       </c>
       <c r="C166" t="s">
-        <v>163</v>
+        <v>269</v>
       </c>
       <c r="D166" t="s">
         <v>304</v>
       </c>
       <c r="E166" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="F166" t="s">
-        <v>271</v>
+        <v>164</v>
       </c>
       <c r="G166" t="s">
         <v>272</v>
@@ -5467,16 +5467,16 @@
         <v>8</v>
       </c>
       <c r="C167" t="s">
-        <v>163</v>
+        <v>269</v>
       </c>
       <c r="D167" t="s">
         <v>304</v>
       </c>
       <c r="E167" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="F167" t="s">
-        <v>271</v>
+        <v>164</v>
       </c>
       <c r="G167" t="s">
         <v>272</v>
@@ -5490,19 +5490,19 @@
         <v>8</v>
       </c>
       <c r="C168" t="s">
-        <v>163</v>
+        <v>269</v>
       </c>
       <c r="D168" t="s">
         <v>304</v>
       </c>
       <c r="E168" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="F168" t="s">
+        <v>164</v>
+      </c>
+      <c r="G168" t="s">
         <v>309</v>
-      </c>
-      <c r="G168" t="s">
-        <v>272</v>
       </c>
     </row>
     <row r="169" spans="1:7">
@@ -5513,19 +5513,19 @@
         <v>8</v>
       </c>
       <c r="C169" t="s">
-        <v>163</v>
+        <v>269</v>
       </c>
       <c r="D169" t="s">
         <v>304</v>
       </c>
       <c r="E169" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="F169" t="s">
+        <v>164</v>
+      </c>
+      <c r="G169" t="s">
         <v>309</v>
-      </c>
-      <c r="G169" t="s">
-        <v>272</v>
       </c>
     </row>
     <row r="170" spans="1:7">
@@ -5536,16 +5536,16 @@
         <v>8</v>
       </c>
       <c r="C170" t="s">
-        <v>163</v>
+        <v>269</v>
       </c>
       <c r="D170" t="s">
         <v>304</v>
       </c>
       <c r="E170" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="F170" t="s">
-        <v>271</v>
+        <v>164</v>
       </c>
       <c r="G170" t="s">
         <v>272</v>
@@ -5579,13 +5579,13 @@
         <v>8</v>
       </c>
       <c r="C172" t="s">
-        <v>112</v>
+        <v>118</v>
       </c>
       <c r="E172" t="s">
         <v>313</v>
       </c>
       <c r="F172" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="G172" t="s">
         <v>119</v>
@@ -5759,16 +5759,16 @@
         <v>8</v>
       </c>
       <c r="C181" t="s">
-        <v>163</v>
+        <v>325</v>
       </c>
       <c r="D181" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="E181" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="F181" t="s">
-        <v>327</v>
+        <v>164</v>
       </c>
       <c r="G181" t="s">
         <v>328</v>
@@ -5782,16 +5782,16 @@
         <v>8</v>
       </c>
       <c r="C182" t="s">
-        <v>163</v>
+        <v>325</v>
       </c>
       <c r="D182" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="E182" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="F182" t="s">
-        <v>327</v>
+        <v>164</v>
       </c>
       <c r="G182" t="s">
         <v>328</v>
@@ -5805,16 +5805,16 @@
         <v>8</v>
       </c>
       <c r="C183" t="s">
-        <v>163</v>
+        <v>325</v>
       </c>
       <c r="D183" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="E183" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="F183" t="s">
-        <v>327</v>
+        <v>164</v>
       </c>
       <c r="G183" t="s">
         <v>328</v>
@@ -5828,16 +5828,16 @@
         <v>8</v>
       </c>
       <c r="C184" t="s">
-        <v>163</v>
+        <v>325</v>
       </c>
       <c r="D184" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="E184" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="F184" t="s">
-        <v>327</v>
+        <v>164</v>
       </c>
       <c r="G184" t="s">
         <v>328</v>
@@ -5851,16 +5851,16 @@
         <v>8</v>
       </c>
       <c r="C185" t="s">
-        <v>163</v>
+        <v>325</v>
       </c>
       <c r="D185" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="E185" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="F185" t="s">
-        <v>327</v>
+        <v>164</v>
       </c>
       <c r="G185" t="s">
         <v>328</v>
@@ -5874,16 +5874,16 @@
         <v>8</v>
       </c>
       <c r="C186" t="s">
-        <v>163</v>
+        <v>325</v>
       </c>
       <c r="D186" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="E186" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="F186" t="s">
-        <v>327</v>
+        <v>164</v>
       </c>
       <c r="G186" t="s">
         <v>328</v>
@@ -5897,16 +5897,16 @@
         <v>8</v>
       </c>
       <c r="C187" t="s">
-        <v>163</v>
+        <v>325</v>
       </c>
       <c r="D187" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="E187" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="F187" t="s">
-        <v>327</v>
+        <v>164</v>
       </c>
       <c r="G187" t="s">
         <v>328</v>
@@ -5920,16 +5920,16 @@
         <v>8</v>
       </c>
       <c r="C188" t="s">
-        <v>163</v>
+        <v>325</v>
       </c>
       <c r="D188" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="E188" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="F188" t="s">
-        <v>327</v>
+        <v>164</v>
       </c>
       <c r="G188" t="s">
         <v>328</v>
@@ -5943,16 +5943,16 @@
         <v>8</v>
       </c>
       <c r="C189" t="s">
-        <v>163</v>
+        <v>325</v>
       </c>
       <c r="D189" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="E189" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="F189" t="s">
-        <v>327</v>
+        <v>164</v>
       </c>
       <c r="G189" t="s">
         <v>328</v>
@@ -5966,16 +5966,16 @@
         <v>8</v>
       </c>
       <c r="C190" t="s">
-        <v>163</v>
+        <v>325</v>
       </c>
       <c r="D190" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="E190" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="F190" t="s">
-        <v>327</v>
+        <v>164</v>
       </c>
       <c r="G190" t="s">
         <v>328</v>
@@ -5989,16 +5989,16 @@
         <v>8</v>
       </c>
       <c r="C191" t="s">
-        <v>163</v>
+        <v>325</v>
       </c>
       <c r="D191" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="E191" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="F191" t="s">
-        <v>327</v>
+        <v>164</v>
       </c>
       <c r="G191" t="s">
         <v>328</v>
@@ -6012,16 +6012,16 @@
         <v>8</v>
       </c>
       <c r="C192" t="s">
-        <v>163</v>
+        <v>325</v>
       </c>
       <c r="D192" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="E192" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="F192" t="s">
-        <v>327</v>
+        <v>164</v>
       </c>
       <c r="G192" t="s">
         <v>328</v>
@@ -6035,19 +6035,19 @@
         <v>8</v>
       </c>
       <c r="C193" t="s">
-        <v>163</v>
+        <v>275</v>
       </c>
       <c r="D193" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="E193" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="F193" t="s">
+        <v>164</v>
+      </c>
+      <c r="G193" t="s">
         <v>341</v>
-      </c>
-      <c r="G193" t="s">
-        <v>276</v>
       </c>
     </row>
     <row r="194" spans="1:7">
@@ -6058,16 +6058,16 @@
         <v>8</v>
       </c>
       <c r="C194" t="s">
-        <v>163</v>
+        <v>325</v>
       </c>
       <c r="D194" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="E194" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="F194" t="s">
-        <v>327</v>
+        <v>164</v>
       </c>
       <c r="G194" t="s">
         <v>328</v>
@@ -6081,16 +6081,16 @@
         <v>8</v>
       </c>
       <c r="C195" t="s">
-        <v>163</v>
+        <v>325</v>
       </c>
       <c r="D195" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="E195" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="F195" t="s">
-        <v>327</v>
+        <v>164</v>
       </c>
       <c r="G195" t="s">
         <v>328</v>
@@ -6104,16 +6104,16 @@
         <v>8</v>
       </c>
       <c r="C196" t="s">
-        <v>163</v>
+        <v>325</v>
       </c>
       <c r="D196" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="E196" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="F196" t="s">
-        <v>327</v>
+        <v>164</v>
       </c>
       <c r="G196" t="s">
         <v>328</v>
@@ -6127,16 +6127,16 @@
         <v>8</v>
       </c>
       <c r="C197" t="s">
-        <v>163</v>
+        <v>325</v>
       </c>
       <c r="D197" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="E197" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="F197" t="s">
-        <v>327</v>
+        <v>164</v>
       </c>
       <c r="G197" t="s">
         <v>328</v>
@@ -6150,16 +6150,16 @@
         <v>8</v>
       </c>
       <c r="C198" t="s">
-        <v>163</v>
+        <v>325</v>
       </c>
       <c r="D198" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="E198" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="F198" t="s">
-        <v>327</v>
+        <v>164</v>
       </c>
       <c r="G198" t="s">
         <v>328</v>
@@ -6173,19 +6173,19 @@
         <v>8</v>
       </c>
       <c r="C199" t="s">
-        <v>163</v>
+        <v>325</v>
       </c>
       <c r="D199" t="s">
         <v>348</v>
       </c>
       <c r="E199" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="F199" t="s">
+        <v>164</v>
+      </c>
+      <c r="G199" t="s">
         <v>349</v>
-      </c>
-      <c r="G199" t="s">
-        <v>328</v>
       </c>
     </row>
     <row r="200" spans="1:7">
@@ -6196,19 +6196,19 @@
         <v>8</v>
       </c>
       <c r="C200" t="s">
-        <v>163</v>
+        <v>325</v>
       </c>
       <c r="D200" t="s">
         <v>348</v>
       </c>
       <c r="E200" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="F200" t="s">
+        <v>164</v>
+      </c>
+      <c r="G200" t="s">
         <v>349</v>
-      </c>
-      <c r="G200" t="s">
-        <v>328</v>
       </c>
     </row>
     <row r="201" spans="1:7">
@@ -6219,19 +6219,19 @@
         <v>8</v>
       </c>
       <c r="C201" t="s">
-        <v>163</v>
+        <v>325</v>
       </c>
       <c r="D201" t="s">
         <v>348</v>
       </c>
       <c r="E201" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="F201" t="s">
+        <v>164</v>
+      </c>
+      <c r="G201" t="s">
         <v>349</v>
-      </c>
-      <c r="G201" t="s">
-        <v>328</v>
       </c>
     </row>
     <row r="202" spans="1:7">
@@ -6242,19 +6242,19 @@
         <v>8</v>
       </c>
       <c r="C202" t="s">
-        <v>163</v>
+        <v>325</v>
       </c>
       <c r="D202" t="s">
         <v>348</v>
       </c>
       <c r="E202" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="F202" t="s">
+        <v>164</v>
+      </c>
+      <c r="G202" t="s">
         <v>349</v>
-      </c>
-      <c r="G202" t="s">
-        <v>328</v>
       </c>
     </row>
     <row r="203" spans="1:7">
@@ -6265,19 +6265,19 @@
         <v>8</v>
       </c>
       <c r="C203" t="s">
-        <v>163</v>
+        <v>275</v>
       </c>
       <c r="D203" t="s">
         <v>348</v>
       </c>
       <c r="E203" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="F203" t="s">
+        <v>164</v>
+      </c>
+      <c r="G203" t="s">
         <v>341</v>
-      </c>
-      <c r="G203" t="s">
-        <v>276</v>
       </c>
     </row>
     <row r="204" spans="1:7">
@@ -6288,19 +6288,19 @@
         <v>8</v>
       </c>
       <c r="C204" t="s">
-        <v>163</v>
+        <v>325</v>
       </c>
       <c r="D204" t="s">
         <v>348</v>
       </c>
       <c r="E204" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="F204" t="s">
+        <v>164</v>
+      </c>
+      <c r="G204" t="s">
         <v>349</v>
-      </c>
-      <c r="G204" t="s">
-        <v>328</v>
       </c>
     </row>
     <row r="205" spans="1:7">
@@ -6311,19 +6311,19 @@
         <v>8</v>
       </c>
       <c r="C205" t="s">
-        <v>163</v>
+        <v>325</v>
       </c>
       <c r="D205" t="s">
         <v>356</v>
       </c>
       <c r="E205" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="F205" t="s">
+        <v>164</v>
+      </c>
+      <c r="G205" t="s">
         <v>357</v>
-      </c>
-      <c r="G205" t="s">
-        <v>328</v>
       </c>
     </row>
     <row r="206" spans="1:7">
@@ -6334,19 +6334,19 @@
         <v>8</v>
       </c>
       <c r="C206" t="s">
-        <v>163</v>
+        <v>325</v>
       </c>
       <c r="D206" t="s">
         <v>356</v>
       </c>
       <c r="E206" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="F206" t="s">
+        <v>164</v>
+      </c>
+      <c r="G206" t="s">
         <v>357</v>
-      </c>
-      <c r="G206" t="s">
-        <v>328</v>
       </c>
     </row>
     <row r="207" spans="1:7">
@@ -6357,19 +6357,19 @@
         <v>8</v>
       </c>
       <c r="C207" t="s">
-        <v>163</v>
+        <v>325</v>
       </c>
       <c r="D207" t="s">
         <v>356</v>
       </c>
       <c r="E207" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="F207" t="s">
+        <v>164</v>
+      </c>
+      <c r="G207" t="s">
         <v>357</v>
-      </c>
-      <c r="G207" t="s">
-        <v>328</v>
       </c>
     </row>
     <row r="208" spans="1:7">
@@ -6380,19 +6380,19 @@
         <v>8</v>
       </c>
       <c r="C208" t="s">
-        <v>163</v>
+        <v>275</v>
       </c>
       <c r="D208" t="s">
         <v>356</v>
       </c>
       <c r="E208" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="F208" t="s">
+        <v>164</v>
+      </c>
+      <c r="G208" t="s">
         <v>341</v>
-      </c>
-      <c r="G208" t="s">
-        <v>276</v>
       </c>
     </row>
     <row r="209" spans="1:7">
@@ -6403,19 +6403,19 @@
         <v>8</v>
       </c>
       <c r="C209" t="s">
-        <v>163</v>
+        <v>325</v>
       </c>
       <c r="D209" t="s">
         <v>356</v>
       </c>
       <c r="E209" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="F209" t="s">
+        <v>164</v>
+      </c>
+      <c r="G209" t="s">
         <v>357</v>
-      </c>
-      <c r="G209" t="s">
-        <v>328</v>
       </c>
     </row>
     <row r="210" spans="1:7">
@@ -6426,16 +6426,16 @@
         <v>8</v>
       </c>
       <c r="C210" t="s">
-        <v>163</v>
+        <v>363</v>
       </c>
       <c r="D210" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="E210" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="F210" t="s">
-        <v>365</v>
+        <v>164</v>
       </c>
       <c r="G210" t="s">
         <v>366</v>
@@ -6449,16 +6449,16 @@
         <v>8</v>
       </c>
       <c r="C211" t="s">
-        <v>163</v>
+        <v>363</v>
       </c>
       <c r="D211" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="E211" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="F211" t="s">
-        <v>365</v>
+        <v>164</v>
       </c>
       <c r="G211" t="s">
         <v>366</v>
@@ -6472,16 +6472,16 @@
         <v>8</v>
       </c>
       <c r="C212" t="s">
-        <v>163</v>
+        <v>363</v>
       </c>
       <c r="D212" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="E212" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="F212" t="s">
-        <v>365</v>
+        <v>164</v>
       </c>
       <c r="G212" t="s">
         <v>366</v>
@@ -6495,16 +6495,16 @@
         <v>8</v>
       </c>
       <c r="C213" t="s">
-        <v>163</v>
+        <v>363</v>
       </c>
       <c r="D213" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="E213" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="F213" t="s">
-        <v>365</v>
+        <v>164</v>
       </c>
       <c r="G213" t="s">
         <v>366</v>
@@ -6518,16 +6518,16 @@
         <v>8</v>
       </c>
       <c r="C214" t="s">
-        <v>163</v>
+        <v>363</v>
       </c>
       <c r="D214" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="E214" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="F214" t="s">
-        <v>365</v>
+        <v>164</v>
       </c>
       <c r="G214" t="s">
         <v>366</v>
@@ -6541,19 +6541,19 @@
         <v>8</v>
       </c>
       <c r="C215" t="s">
-        <v>163</v>
+        <v>325</v>
       </c>
       <c r="D215" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="E215" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="F215" t="s">
+        <v>164</v>
+      </c>
+      <c r="G215" t="s">
         <v>349</v>
-      </c>
-      <c r="G215" t="s">
-        <v>328</v>
       </c>
     </row>
     <row r="216" spans="1:7">
@@ -6564,16 +6564,16 @@
         <v>8</v>
       </c>
       <c r="C216" t="s">
-        <v>163</v>
+        <v>363</v>
       </c>
       <c r="D216" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="E216" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="F216" t="s">
-        <v>365</v>
+        <v>164</v>
       </c>
       <c r="G216" t="s">
         <v>366</v>
@@ -6587,16 +6587,16 @@
         <v>8</v>
       </c>
       <c r="C217" t="s">
-        <v>163</v>
+        <v>363</v>
       </c>
       <c r="D217" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="E217" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="F217" t="s">
-        <v>365</v>
+        <v>164</v>
       </c>
       <c r="G217" t="s">
         <v>366</v>
@@ -6610,16 +6610,16 @@
         <v>8</v>
       </c>
       <c r="C218" t="s">
-        <v>163</v>
+        <v>363</v>
       </c>
       <c r="D218" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="E218" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="F218" t="s">
-        <v>365</v>
+        <v>164</v>
       </c>
       <c r="G218" t="s">
         <v>366</v>
@@ -6633,16 +6633,16 @@
         <v>8</v>
       </c>
       <c r="C219" t="s">
-        <v>163</v>
+        <v>363</v>
       </c>
       <c r="D219" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="E219" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="F219" t="s">
-        <v>365</v>
+        <v>164</v>
       </c>
       <c r="G219" t="s">
         <v>366</v>
@@ -6656,19 +6656,19 @@
         <v>8</v>
       </c>
       <c r="C220" t="s">
-        <v>163</v>
+        <v>269</v>
       </c>
       <c r="D220" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="E220" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="F220" t="s">
+        <v>164</v>
+      </c>
+      <c r="G220" t="s">
         <v>309</v>
-      </c>
-      <c r="G220" t="s">
-        <v>272</v>
       </c>
     </row>
     <row r="221" spans="1:7">
@@ -6679,16 +6679,16 @@
         <v>8</v>
       </c>
       <c r="C221" t="s">
-        <v>163</v>
+        <v>363</v>
       </c>
       <c r="D221" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="E221" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="F221" t="s">
-        <v>365</v>
+        <v>164</v>
       </c>
       <c r="G221" t="s">
         <v>366</v>
@@ -6702,16 +6702,16 @@
         <v>8</v>
       </c>
       <c r="C222" t="s">
-        <v>163</v>
+        <v>363</v>
       </c>
       <c r="D222" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="E222" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="F222" t="s">
-        <v>365</v>
+        <v>164</v>
       </c>
       <c r="G222" t="s">
         <v>366</v>
@@ -6725,16 +6725,16 @@
         <v>8</v>
       </c>
       <c r="C223" t="s">
-        <v>163</v>
+        <v>363</v>
       </c>
       <c r="D223" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="E223" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="F223" t="s">
-        <v>365</v>
+        <v>164</v>
       </c>
       <c r="G223" t="s">
         <v>366</v>
@@ -6748,16 +6748,16 @@
         <v>8</v>
       </c>
       <c r="C224" t="s">
-        <v>163</v>
+        <v>363</v>
       </c>
       <c r="D224" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="E224" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="F224" t="s">
-        <v>365</v>
+        <v>164</v>
       </c>
       <c r="G224" t="s">
         <v>366</v>
@@ -6771,16 +6771,16 @@
         <v>8</v>
       </c>
       <c r="C225" t="s">
-        <v>163</v>
+        <v>363</v>
       </c>
       <c r="D225" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="E225" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="F225" t="s">
-        <v>365</v>
+        <v>164</v>
       </c>
       <c r="G225" t="s">
         <v>366</v>
@@ -6794,16 +6794,16 @@
         <v>8</v>
       </c>
       <c r="C226" t="s">
-        <v>163</v>
+        <v>275</v>
       </c>
       <c r="D226" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="E226" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="F226" t="s">
-        <v>275</v>
+        <v>164</v>
       </c>
       <c r="G226" t="s">
         <v>276</v>
@@ -6817,16 +6817,16 @@
         <v>8</v>
       </c>
       <c r="C227" t="s">
-        <v>163</v>
+        <v>363</v>
       </c>
       <c r="D227" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="E227" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="F227" t="s">
-        <v>365</v>
+        <v>164</v>
       </c>
       <c r="G227" t="s">
         <v>366</v>
@@ -6843,10 +6843,10 @@
         <v>163</v>
       </c>
       <c r="D228" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="E228" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="F228" t="s">
         <v>164</v>
@@ -6863,19 +6863,19 @@
         <v>8</v>
       </c>
       <c r="C229" t="s">
-        <v>163</v>
+        <v>363</v>
       </c>
       <c r="D229" t="s">
         <v>386</v>
       </c>
       <c r="E229" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="F229" t="s">
+        <v>164</v>
+      </c>
+      <c r="G229" t="s">
         <v>387</v>
-      </c>
-      <c r="G229" t="s">
-        <v>366</v>
       </c>
     </row>
     <row r="230" spans="1:7">
@@ -6886,19 +6886,19 @@
         <v>8</v>
       </c>
       <c r="C230" t="s">
-        <v>163</v>
+        <v>363</v>
       </c>
       <c r="D230" t="s">
         <v>386</v>
       </c>
       <c r="E230" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="F230" t="s">
+        <v>164</v>
+      </c>
+      <c r="G230" t="s">
         <v>387</v>
-      </c>
-      <c r="G230" t="s">
-        <v>366</v>
       </c>
     </row>
     <row r="231" spans="1:7">
@@ -6909,19 +6909,19 @@
         <v>8</v>
       </c>
       <c r="C231" t="s">
-        <v>163</v>
+        <v>269</v>
       </c>
       <c r="D231" t="s">
         <v>386</v>
       </c>
       <c r="E231" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="F231" t="s">
+        <v>164</v>
+      </c>
+      <c r="G231" t="s">
         <v>293</v>
-      </c>
-      <c r="G231" t="s">
-        <v>272</v>
       </c>
     </row>
     <row r="232" spans="1:7">
@@ -6932,19 +6932,19 @@
         <v>8</v>
       </c>
       <c r="C232" t="s">
-        <v>163</v>
+        <v>269</v>
       </c>
       <c r="D232" t="s">
         <v>386</v>
       </c>
       <c r="E232" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="F232" t="s">
+        <v>164</v>
+      </c>
+      <c r="G232" t="s">
         <v>309</v>
-      </c>
-      <c r="G232" t="s">
-        <v>272</v>
       </c>
     </row>
     <row r="233" spans="1:7">
@@ -6955,19 +6955,19 @@
         <v>8</v>
       </c>
       <c r="C233" t="s">
-        <v>163</v>
+        <v>363</v>
       </c>
       <c r="D233" t="s">
         <v>386</v>
       </c>
       <c r="E233" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="F233" t="s">
+        <v>164</v>
+      </c>
+      <c r="G233" t="s">
         <v>387</v>
-      </c>
-      <c r="G233" t="s">
-        <v>366</v>
       </c>
     </row>
     <row r="234" spans="1:7">
@@ -6978,19 +6978,19 @@
         <v>8</v>
       </c>
       <c r="C234" t="s">
-        <v>163</v>
+        <v>363</v>
       </c>
       <c r="D234" t="s">
         <v>386</v>
       </c>
       <c r="E234" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="F234" t="s">
+        <v>164</v>
+      </c>
+      <c r="G234" t="s">
         <v>387</v>
-      </c>
-      <c r="G234" t="s">
-        <v>366</v>
       </c>
     </row>
     <row r="235" spans="1:7">
@@ -7001,19 +7001,19 @@
         <v>8</v>
       </c>
       <c r="C235" t="s">
-        <v>163</v>
+        <v>363</v>
       </c>
       <c r="D235" t="s">
         <v>386</v>
       </c>
       <c r="E235" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="F235" t="s">
+        <v>164</v>
+      </c>
+      <c r="G235" t="s">
         <v>387</v>
-      </c>
-      <c r="G235" t="s">
-        <v>366</v>
       </c>
     </row>
     <row r="236" spans="1:7">
@@ -7024,19 +7024,19 @@
         <v>8</v>
       </c>
       <c r="C236" t="s">
-        <v>163</v>
+        <v>363</v>
       </c>
       <c r="D236" t="s">
         <v>386</v>
       </c>
       <c r="E236" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="F236" t="s">
+        <v>164</v>
+      </c>
+      <c r="G236" t="s">
         <v>387</v>
-      </c>
-      <c r="G236" t="s">
-        <v>366</v>
       </c>
     </row>
     <row r="237" spans="1:7">
@@ -7047,19 +7047,19 @@
         <v>8</v>
       </c>
       <c r="C237" t="s">
-        <v>163</v>
+        <v>363</v>
       </c>
       <c r="D237" t="s">
         <v>386</v>
       </c>
       <c r="E237" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="F237" t="s">
+        <v>164</v>
+      </c>
+      <c r="G237" t="s">
         <v>387</v>
-      </c>
-      <c r="G237" t="s">
-        <v>366</v>
       </c>
     </row>
     <row r="238" spans="1:7">
@@ -7070,19 +7070,19 @@
         <v>8</v>
       </c>
       <c r="C238" t="s">
-        <v>163</v>
+        <v>363</v>
       </c>
       <c r="D238" t="s">
         <v>386</v>
       </c>
       <c r="E238" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="F238" t="s">
+        <v>164</v>
+      </c>
+      <c r="G238" t="s">
         <v>387</v>
-      </c>
-      <c r="G238" t="s">
-        <v>366</v>
       </c>
     </row>
     <row r="239" spans="1:7">
@@ -7093,19 +7093,19 @@
         <v>8</v>
       </c>
       <c r="C239" t="s">
-        <v>163</v>
+        <v>363</v>
       </c>
       <c r="D239" t="s">
         <v>398</v>
       </c>
       <c r="E239" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="F239" t="s">
+        <v>164</v>
+      </c>
+      <c r="G239" t="s">
         <v>399</v>
-      </c>
-      <c r="G239" t="s">
-        <v>366</v>
       </c>
     </row>
     <row r="240" spans="1:7">
@@ -7254,7 +7254,7 @@
         <v>8</v>
       </c>
       <c r="C246" t="s">
-        <v>163</v>
+        <v>255</v>
       </c>
       <c r="D246" t="s">
         <v>409</v>
@@ -7263,10 +7263,10 @@
         <v>402</v>
       </c>
       <c r="F246" t="s">
+        <v>164</v>
+      </c>
+      <c r="G246" t="s">
         <v>410</v>
-      </c>
-      <c r="G246" t="s">
-        <v>256</v>
       </c>
     </row>
     <row r="247" spans="1:7">
@@ -7317,13 +7317,13 @@
         <v>8</v>
       </c>
       <c r="C249" t="s">
-        <v>95</v>
+        <v>415</v>
       </c>
       <c r="E249" t="s">
         <v>412</v>
       </c>
       <c r="F249" t="s">
-        <v>415</v>
+        <v>96</v>
       </c>
       <c r="G249" t="s">
         <v>416</v>
@@ -7397,13 +7397,13 @@
         <v>8</v>
       </c>
       <c r="C253" t="s">
-        <v>163</v>
+        <v>421</v>
       </c>
       <c r="E253" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="F253" t="s">
-        <v>422</v>
+        <v>164</v>
       </c>
       <c r="G253" t="s">
         <v>423</v>
@@ -7417,13 +7417,13 @@
         <v>8</v>
       </c>
       <c r="C254" t="s">
-        <v>90</v>
+        <v>219</v>
       </c>
       <c r="E254" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="F254" t="s">
-        <v>219</v>
+        <v>92</v>
       </c>
       <c r="G254" t="s">
         <v>220</v>
@@ -7437,13 +7437,13 @@
         <v>8</v>
       </c>
       <c r="C255" t="s">
-        <v>90</v>
+        <v>426</v>
       </c>
       <c r="E255" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="F255" t="s">
-        <v>426</v>
+        <v>92</v>
       </c>
       <c r="G255" t="s">
         <v>427</v>
@@ -7457,13 +7457,13 @@
         <v>8</v>
       </c>
       <c r="C256" t="s">
-        <v>90</v>
+        <v>426</v>
       </c>
       <c r="E256" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="F256" t="s">
-        <v>426</v>
+        <v>92</v>
       </c>
       <c r="G256" t="s">
         <v>427</v>
@@ -7477,13 +7477,13 @@
         <v>8</v>
       </c>
       <c r="C257" t="s">
-        <v>90</v>
+        <v>426</v>
       </c>
       <c r="E257" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="F257" t="s">
-        <v>426</v>
+        <v>92</v>
       </c>
       <c r="G257" t="s">
         <v>427</v>
@@ -7497,13 +7497,13 @@
         <v>8</v>
       </c>
       <c r="C258" t="s">
-        <v>163</v>
+        <v>325</v>
       </c>
       <c r="E258" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="F258" t="s">
-        <v>327</v>
+        <v>164</v>
       </c>
       <c r="G258" t="s">
         <v>328</v>
@@ -7517,13 +7517,13 @@
         <v>8</v>
       </c>
       <c r="C259" t="s">
-        <v>90</v>
+        <v>426</v>
       </c>
       <c r="E259" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="F259" t="s">
-        <v>426</v>
+        <v>92</v>
       </c>
       <c r="G259" t="s">
         <v>427</v>
@@ -7540,7 +7540,7 @@
         <v>163</v>
       </c>
       <c r="E260" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="F260" t="s">
         <v>164</v>
@@ -7557,13 +7557,13 @@
         <v>8</v>
       </c>
       <c r="C261" t="s">
-        <v>195</v>
+        <v>434</v>
       </c>
       <c r="E261" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="F261" t="s">
-        <v>434</v>
+        <v>196</v>
       </c>
       <c r="G261" t="s">
         <v>435</v>
@@ -7580,7 +7580,7 @@
         <v>163</v>
       </c>
       <c r="E262" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="F262" t="s">
         <v>164</v>
@@ -7597,13 +7597,13 @@
         <v>8</v>
       </c>
       <c r="C263" t="s">
-        <v>182</v>
+        <v>438</v>
       </c>
       <c r="E263" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="F263" t="s">
-        <v>438</v>
+        <v>183</v>
       </c>
       <c r="G263" t="s">
         <v>439</v>
@@ -7620,7 +7620,7 @@
         <v>31</v>
       </c>
       <c r="E264" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="F264" t="s">
         <v>32</v>
@@ -7640,7 +7640,7 @@
         <v>9</v>
       </c>
       <c r="E265" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="F265" t="s">
         <v>12</v>
@@ -7657,13 +7657,13 @@
         <v>8</v>
       </c>
       <c r="C266" t="s">
-        <v>112</v>
+        <v>443</v>
       </c>
       <c r="E266" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="F266" t="s">
-        <v>443</v>
+        <v>115</v>
       </c>
       <c r="G266" t="s">
         <v>444</v>
@@ -7677,13 +7677,13 @@
         <v>8</v>
       </c>
       <c r="C267" t="s">
-        <v>112</v>
+        <v>118</v>
       </c>
       <c r="E267" t="s">
         <v>446</v>
       </c>
       <c r="F267" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="G267" t="s">
         <v>119</v>
@@ -7697,13 +7697,13 @@
         <v>8</v>
       </c>
       <c r="C268" t="s">
-        <v>182</v>
+        <v>202</v>
       </c>
       <c r="E268" t="s">
         <v>448</v>
       </c>
       <c r="F268" t="s">
-        <v>203</v>
+        <v>183</v>
       </c>
       <c r="G268" t="s">
         <v>204</v>
@@ -7717,13 +7717,13 @@
         <v>8</v>
       </c>
       <c r="C269" t="s">
-        <v>112</v>
+        <v>118</v>
       </c>
       <c r="E269" t="s">
         <v>450</v>
       </c>
       <c r="F269" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="G269" t="s">
         <v>119</v>
@@ -7737,13 +7737,13 @@
         <v>8</v>
       </c>
       <c r="C270" t="s">
-        <v>112</v>
+        <v>118</v>
       </c>
       <c r="E270" t="s">
         <v>450</v>
       </c>
       <c r="F270" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="G270" t="s">
         <v>119</v>
@@ -7757,13 +7757,13 @@
         <v>8</v>
       </c>
       <c r="C271" t="s">
-        <v>112</v>
+        <v>453</v>
       </c>
       <c r="E271" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="F271" t="s">
-        <v>454</v>
+        <v>115</v>
       </c>
       <c r="G271" t="s">
         <v>455</v>
@@ -7777,13 +7777,13 @@
         <v>8</v>
       </c>
       <c r="C272" t="s">
-        <v>112</v>
+        <v>453</v>
       </c>
       <c r="E272" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="F272" t="s">
-        <v>454</v>
+        <v>115</v>
       </c>
       <c r="G272" t="s">
         <v>455</v>
@@ -7797,13 +7797,13 @@
         <v>8</v>
       </c>
       <c r="C273" t="s">
-        <v>112</v>
+        <v>453</v>
       </c>
       <c r="E273" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="F273" t="s">
-        <v>454</v>
+        <v>115</v>
       </c>
       <c r="G273" t="s">
         <v>455</v>
@@ -7817,13 +7817,13 @@
         <v>8</v>
       </c>
       <c r="C274" t="s">
-        <v>112</v>
+        <v>453</v>
       </c>
       <c r="E274" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="F274" t="s">
-        <v>454</v>
+        <v>115</v>
       </c>
       <c r="G274" t="s">
         <v>455</v>
@@ -7837,13 +7837,13 @@
         <v>8</v>
       </c>
       <c r="C275" t="s">
-        <v>112</v>
+        <v>453</v>
       </c>
       <c r="E275" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="F275" t="s">
-        <v>454</v>
+        <v>115</v>
       </c>
       <c r="G275" t="s">
         <v>455</v>
@@ -7857,13 +7857,13 @@
         <v>8</v>
       </c>
       <c r="C276" t="s">
-        <v>112</v>
+        <v>453</v>
       </c>
       <c r="E276" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="F276" t="s">
-        <v>454</v>
+        <v>115</v>
       </c>
       <c r="G276" t="s">
         <v>455</v>
@@ -7877,13 +7877,13 @@
         <v>8</v>
       </c>
       <c r="C277" t="s">
-        <v>112</v>
+        <v>453</v>
       </c>
       <c r="E277" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="F277" t="s">
-        <v>454</v>
+        <v>115</v>
       </c>
       <c r="G277" t="s">
         <v>455</v>
@@ -7897,13 +7897,13 @@
         <v>8</v>
       </c>
       <c r="C278" t="s">
-        <v>182</v>
+        <v>202</v>
       </c>
       <c r="E278" t="s">
         <v>463</v>
       </c>
       <c r="F278" t="s">
-        <v>203</v>
+        <v>183</v>
       </c>
       <c r="G278" t="s">
         <v>204</v>
@@ -7917,13 +7917,13 @@
         <v>8</v>
       </c>
       <c r="C279" t="s">
-        <v>31</v>
+        <v>51</v>
       </c>
       <c r="E279" t="s">
         <v>463</v>
       </c>
       <c r="F279" t="s">
-        <v>53</v>
+        <v>32</v>
       </c>
       <c r="G279" t="s">
         <v>54</v>
@@ -7957,13 +7957,13 @@
         <v>8</v>
       </c>
       <c r="C281" t="s">
-        <v>112</v>
+        <v>170</v>
       </c>
       <c r="E281" t="s">
         <v>463</v>
       </c>
       <c r="F281" t="s">
-        <v>170</v>
+        <v>115</v>
       </c>
       <c r="G281" t="s">
         <v>171</v>
@@ -7997,16 +7997,16 @@
         <v>8</v>
       </c>
       <c r="C283" t="s">
-        <v>163</v>
+        <v>363</v>
       </c>
       <c r="E283" t="s">
         <v>469</v>
       </c>
       <c r="F283" t="s">
+        <v>164</v>
+      </c>
+      <c r="G283" t="s">
         <v>399</v>
-      </c>
-      <c r="G283" t="s">
-        <v>366</v>
       </c>
     </row>
     <row r="284" spans="1:7">
@@ -8037,13 +8037,13 @@
         <v>8</v>
       </c>
       <c r="C285" t="s">
-        <v>112</v>
+        <v>170</v>
       </c>
       <c r="E285" t="s">
         <v>473</v>
       </c>
       <c r="F285" t="s">
-        <v>170</v>
+        <v>115</v>
       </c>
       <c r="G285" t="s">
         <v>171</v>
@@ -8057,13 +8057,13 @@
         <v>8</v>
       </c>
       <c r="C286" t="s">
-        <v>182</v>
+        <v>438</v>
       </c>
       <c r="E286" t="s">
         <v>475</v>
       </c>
       <c r="F286" t="s">
-        <v>438</v>
+        <v>183</v>
       </c>
       <c r="G286" t="s">
         <v>439</v>
@@ -8077,13 +8077,13 @@
         <v>8</v>
       </c>
       <c r="C287" t="s">
-        <v>182</v>
+        <v>438</v>
       </c>
       <c r="E287" t="s">
         <v>475</v>
       </c>
       <c r="F287" t="s">
-        <v>438</v>
+        <v>183</v>
       </c>
       <c r="G287" t="s">
         <v>439</v>
@@ -8097,13 +8097,13 @@
         <v>8</v>
       </c>
       <c r="C288" t="s">
-        <v>9</v>
+        <v>41</v>
       </c>
       <c r="E288" t="s">
         <v>475</v>
       </c>
       <c r="F288" t="s">
-        <v>41</v>
+        <v>12</v>
       </c>
       <c r="G288" t="s">
         <v>42</v>
@@ -8157,13 +8157,13 @@
         <v>8</v>
       </c>
       <c r="C291" t="s">
-        <v>112</v>
+        <v>170</v>
       </c>
       <c r="E291" t="s">
         <v>475</v>
       </c>
       <c r="F291" t="s">
-        <v>170</v>
+        <v>115</v>
       </c>
       <c r="G291" t="s">
         <v>171</v>
@@ -8177,13 +8177,13 @@
         <v>8</v>
       </c>
       <c r="C292" t="s">
-        <v>112</v>
+        <v>170</v>
       </c>
       <c r="E292" t="s">
         <v>475</v>
       </c>
       <c r="F292" t="s">
-        <v>170</v>
+        <v>115</v>
       </c>
       <c r="G292" t="s">
         <v>171</v>
@@ -8197,13 +8197,13 @@
         <v>8</v>
       </c>
       <c r="C293" t="s">
-        <v>112</v>
+        <v>170</v>
       </c>
       <c r="E293" t="s">
         <v>475</v>
       </c>
       <c r="F293" t="s">
-        <v>170</v>
+        <v>115</v>
       </c>
       <c r="G293" t="s">
         <v>171</v>
@@ -8217,13 +8217,13 @@
         <v>8</v>
       </c>
       <c r="C294" t="s">
-        <v>112</v>
+        <v>170</v>
       </c>
       <c r="E294" t="s">
         <v>475</v>
       </c>
       <c r="F294" t="s">
-        <v>170</v>
+        <v>115</v>
       </c>
       <c r="G294" t="s">
         <v>171</v>
@@ -8237,13 +8237,13 @@
         <v>8</v>
       </c>
       <c r="C295" t="s">
-        <v>112</v>
+        <v>170</v>
       </c>
       <c r="E295" t="s">
         <v>485</v>
       </c>
       <c r="F295" t="s">
-        <v>170</v>
+        <v>115</v>
       </c>
       <c r="G295" t="s">
         <v>171</v>
@@ -8257,13 +8257,13 @@
         <v>8</v>
       </c>
       <c r="C296" t="s">
-        <v>112</v>
+        <v>170</v>
       </c>
       <c r="E296" t="s">
         <v>485</v>
       </c>
       <c r="F296" t="s">
-        <v>170</v>
+        <v>115</v>
       </c>
       <c r="G296" t="s">
         <v>171</v>

--- a/api/2/xlsx/fr/SectorCOFOG.xlsx
+++ b/api/2/xlsx/fr/SectorCOFOG.xlsx
@@ -31,12 +31,12 @@
     <t>codeforiati:group-code</t>
   </si>
   <si>
+    <t>codeforiati:cofog-class</t>
+  </si>
+  <si>
     <t>codeforiati:cofog-division</t>
   </si>
   <si>
-    <t>codeforiati:cofog-class</t>
-  </si>
-  <si>
     <t>11110</t>
   </si>
   <si>
@@ -52,12 +52,12 @@
     <t>110</t>
   </si>
   <si>
+    <t>09.8.0 - Education n.e.c. (CS)</t>
+  </si>
+  <si>
     <t>09 - Education</t>
   </si>
   <si>
-    <t>09.8.0 - Education n.e.c. (CS)</t>
-  </si>
-  <si>
     <t>11120</t>
   </si>
   <si>
@@ -112,12 +112,12 @@
     <t>07.4 - Public health services</t>
   </si>
   <si>
+    <t>07.4.0 - Public health services (IS)</t>
+  </si>
+  <si>
     <t>07 - Health</t>
   </si>
   <si>
-    <t>07.4.0 - Public health services (IS)</t>
-  </si>
-  <si>
     <t>11260</t>
   </si>
   <si>
@@ -292,24 +292,24 @@
     <t>140</t>
   </si>
   <si>
+    <t>06.3.0 - Water supply (CS)</t>
+  </si>
+  <si>
     <t>06 - Housing and community amenities</t>
   </si>
   <si>
-    <t>06.3.0 - Water supply (CS)</t>
-  </si>
-  <si>
     <t>14015</t>
   </si>
   <si>
     <t>05.6 - Environmental protection n.e.c.</t>
   </si>
   <si>
+    <t>05.6.0 - Environmental protection n.e.c. (CS)</t>
+  </si>
+  <si>
     <t>05 - Environmental protection</t>
   </si>
   <si>
-    <t>05.6.0 - Environmental protection n.e.c. (CS)</t>
-  </si>
-  <si>
     <t>14020</t>
   </si>
   <si>
@@ -361,12 +361,12 @@
     <t>150</t>
   </si>
   <si>
+    <t>01.3.1 - General personnel services (CS)</t>
+  </si>
+  <si>
     <t>01 - General public services</t>
   </si>
   <si>
-    <t>01.3.1 - General personnel services (CS)</t>
-  </si>
-  <si>
     <t>15111</t>
   </si>
   <si>
@@ -391,12 +391,12 @@
     <t>03.6 - Public order and safety n.e.c.</t>
   </si>
   <si>
+    <t>03.6.0 - Public order and safety n.e.c. (CS)</t>
+  </si>
+  <si>
     <t>03 - Public order and safety</t>
   </si>
   <si>
-    <t>03.6.0 - Public order and safety n.e.c. (CS)</t>
-  </si>
-  <si>
     <t>15114</t>
   </si>
   <si>
@@ -508,12 +508,12 @@
     <t>04.1 - General economic, commercial and labour affairs</t>
   </si>
   <si>
+    <t>04.1.1 - General economic and commercial affairs (CS)</t>
+  </si>
+  <si>
     <t>04 - Economic affairs</t>
   </si>
   <si>
-    <t>04.1.1 - General economic and commercial affairs (CS)</t>
-  </si>
-  <si>
     <t>15143</t>
   </si>
   <si>
@@ -565,12 +565,12 @@
     <t>10.7 - Social exclusion n.e.c.</t>
   </si>
   <si>
+    <t>10.7.0 - Social exclusion n.e.c. (IS)</t>
+  </si>
+  <si>
     <t>10 - Social protection</t>
   </si>
   <si>
-    <t>10.7.0 - Social exclusion n.e.c. (IS)</t>
-  </si>
-  <si>
     <t>15180</t>
   </si>
   <si>
@@ -604,12 +604,12 @@
     <t>02.3 - Foreign military aid</t>
   </si>
   <si>
+    <t>02.3.0 - Foreign military aid (CS)</t>
+  </si>
+  <si>
     <t>02 - Defence</t>
   </si>
   <si>
-    <t>02.3.0 - Foreign military aid (CS)</t>
-  </si>
-  <si>
     <t>15240</t>
   </si>
   <si>
@@ -688,10 +688,10 @@
     <t>08.2 - Cultural services</t>
   </si>
   <si>
+    <t>08.2.0 - Cultural services (IS)</t>
+  </si>
+  <si>
     <t>08 - Recreation, culture and religion</t>
-  </si>
-  <si>
-    <t>08.2.0 - Cultural services (IS)</t>
   </si>
   <si>
     <t>16062</t>
@@ -1872,10 +1872,10 @@
         <v>11</v>
       </c>
       <c r="F3" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="G3" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -1918,10 +1918,10 @@
         <v>11</v>
       </c>
       <c r="F5" t="s">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="G5" t="s">
-        <v>20</v>
+        <v>13</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -1941,10 +1941,10 @@
         <v>11</v>
       </c>
       <c r="F6" t="s">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="G6" t="s">
-        <v>24</v>
+        <v>13</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -1987,10 +1987,10 @@
         <v>11</v>
       </c>
       <c r="F8" t="s">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="G8" t="s">
-        <v>24</v>
+        <v>13</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -2010,10 +2010,10 @@
         <v>11</v>
       </c>
       <c r="F9" t="s">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="G9" t="s">
-        <v>24</v>
+        <v>13</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -2033,10 +2033,10 @@
         <v>11</v>
       </c>
       <c r="F10" t="s">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="G10" t="s">
-        <v>29</v>
+        <v>13</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -2079,10 +2079,10 @@
         <v>11</v>
       </c>
       <c r="F12" t="s">
-        <v>12</v>
+        <v>36</v>
       </c>
       <c r="G12" t="s">
-        <v>36</v>
+        <v>13</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -2102,10 +2102,10 @@
         <v>11</v>
       </c>
       <c r="F13" t="s">
-        <v>12</v>
+        <v>39</v>
       </c>
       <c r="G13" t="s">
-        <v>39</v>
+        <v>13</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -2125,10 +2125,10 @@
         <v>11</v>
       </c>
       <c r="F14" t="s">
-        <v>12</v>
+        <v>42</v>
       </c>
       <c r="G14" t="s">
-        <v>42</v>
+        <v>13</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -2148,10 +2148,10 @@
         <v>11</v>
       </c>
       <c r="F15" t="s">
-        <v>12</v>
+        <v>46</v>
       </c>
       <c r="G15" t="s">
-        <v>46</v>
+        <v>13</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -2171,10 +2171,10 @@
         <v>11</v>
       </c>
       <c r="F16" t="s">
-        <v>12</v>
+        <v>49</v>
       </c>
       <c r="G16" t="s">
-        <v>49</v>
+        <v>13</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -2194,10 +2194,10 @@
         <v>53</v>
       </c>
       <c r="F17" t="s">
-        <v>32</v>
+        <v>54</v>
       </c>
       <c r="G17" t="s">
-        <v>54</v>
+        <v>33</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -2217,10 +2217,10 @@
         <v>53</v>
       </c>
       <c r="F18" t="s">
-        <v>32</v>
+        <v>54</v>
       </c>
       <c r="G18" t="s">
-        <v>54</v>
+        <v>33</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -2240,10 +2240,10 @@
         <v>53</v>
       </c>
       <c r="F19" t="s">
-        <v>32</v>
+        <v>58</v>
       </c>
       <c r="G19" t="s">
-        <v>58</v>
+        <v>33</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -2263,10 +2263,10 @@
         <v>53</v>
       </c>
       <c r="F20" t="s">
-        <v>32</v>
+        <v>61</v>
       </c>
       <c r="G20" t="s">
-        <v>61</v>
+        <v>33</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -2286,10 +2286,10 @@
         <v>53</v>
       </c>
       <c r="F21" t="s">
-        <v>32</v>
+        <v>54</v>
       </c>
       <c r="G21" t="s">
-        <v>54</v>
+        <v>33</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -2332,10 +2332,10 @@
         <v>53</v>
       </c>
       <c r="F23" t="s">
-        <v>32</v>
+        <v>67</v>
       </c>
       <c r="G23" t="s">
-        <v>67</v>
+        <v>33</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -2493,10 +2493,10 @@
         <v>53</v>
       </c>
       <c r="F30" t="s">
-        <v>32</v>
+        <v>54</v>
       </c>
       <c r="G30" t="s">
-        <v>54</v>
+        <v>33</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -2631,10 +2631,10 @@
         <v>53</v>
       </c>
       <c r="F36" t="s">
-        <v>32</v>
+        <v>58</v>
       </c>
       <c r="G36" t="s">
-        <v>58</v>
+        <v>33</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -2731,10 +2731,10 @@
         <v>83</v>
       </c>
       <c r="F41" t="s">
-        <v>32</v>
+        <v>54</v>
       </c>
       <c r="G41" t="s">
-        <v>54</v>
+        <v>33</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -2751,10 +2751,10 @@
         <v>83</v>
       </c>
       <c r="F42" t="s">
-        <v>32</v>
+        <v>58</v>
       </c>
       <c r="G42" t="s">
-        <v>58</v>
+        <v>33</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -2851,10 +2851,10 @@
         <v>91</v>
       </c>
       <c r="F47" t="s">
-        <v>96</v>
+        <v>102</v>
       </c>
       <c r="G47" t="s">
-        <v>102</v>
+        <v>97</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -2911,10 +2911,10 @@
         <v>91</v>
       </c>
       <c r="F50" t="s">
-        <v>96</v>
+        <v>102</v>
       </c>
       <c r="G50" t="s">
-        <v>102</v>
+        <v>97</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -2951,10 +2951,10 @@
         <v>91</v>
       </c>
       <c r="F52" t="s">
-        <v>96</v>
+        <v>109</v>
       </c>
       <c r="G52" t="s">
-        <v>109</v>
+        <v>97</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -3017,10 +3017,10 @@
         <v>114</v>
       </c>
       <c r="F55" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="G55" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -3040,10 +3040,10 @@
         <v>114</v>
       </c>
       <c r="F56" t="s">
-        <v>115</v>
+        <v>122</v>
       </c>
       <c r="G56" t="s">
-        <v>122</v>
+        <v>116</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -3086,10 +3086,10 @@
         <v>114</v>
       </c>
       <c r="F58" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="G58" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -3109,10 +3109,10 @@
         <v>114</v>
       </c>
       <c r="F59" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="G59" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -3132,10 +3132,10 @@
         <v>114</v>
       </c>
       <c r="F60" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="G60" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -3155,10 +3155,10 @@
         <v>114</v>
       </c>
       <c r="F61" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="G61" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -3178,10 +3178,10 @@
         <v>114</v>
       </c>
       <c r="F62" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="G62" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -3201,10 +3201,10 @@
         <v>114</v>
       </c>
       <c r="F63" t="s">
-        <v>115</v>
+        <v>133</v>
       </c>
       <c r="G63" t="s">
-        <v>133</v>
+        <v>116</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -3224,10 +3224,10 @@
         <v>114</v>
       </c>
       <c r="F64" t="s">
-        <v>115</v>
+        <v>133</v>
       </c>
       <c r="G64" t="s">
-        <v>133</v>
+        <v>116</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -3247,10 +3247,10 @@
         <v>114</v>
       </c>
       <c r="F65" t="s">
-        <v>115</v>
+        <v>137</v>
       </c>
       <c r="G65" t="s">
-        <v>137</v>
+        <v>116</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -3293,10 +3293,10 @@
         <v>114</v>
       </c>
       <c r="F67" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="G67" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -3316,10 +3316,10 @@
         <v>114</v>
       </c>
       <c r="F68" t="s">
-        <v>115</v>
+        <v>141</v>
       </c>
       <c r="G68" t="s">
-        <v>141</v>
+        <v>116</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -3339,10 +3339,10 @@
         <v>114</v>
       </c>
       <c r="F69" t="s">
-        <v>115</v>
+        <v>143</v>
       </c>
       <c r="G69" t="s">
-        <v>143</v>
+        <v>116</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -3362,10 +3362,10 @@
         <v>114</v>
       </c>
       <c r="F70" t="s">
-        <v>115</v>
+        <v>122</v>
       </c>
       <c r="G70" t="s">
-        <v>122</v>
+        <v>116</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -3385,10 +3385,10 @@
         <v>114</v>
       </c>
       <c r="F71" t="s">
-        <v>115</v>
+        <v>122</v>
       </c>
       <c r="G71" t="s">
-        <v>122</v>
+        <v>116</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -3431,10 +3431,10 @@
         <v>114</v>
       </c>
       <c r="F73" t="s">
-        <v>125</v>
+        <v>149</v>
       </c>
       <c r="G73" t="s">
-        <v>149</v>
+        <v>126</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -3454,10 +3454,10 @@
         <v>114</v>
       </c>
       <c r="F74" t="s">
-        <v>125</v>
+        <v>152</v>
       </c>
       <c r="G74" t="s">
-        <v>152</v>
+        <v>126</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -3477,10 +3477,10 @@
         <v>114</v>
       </c>
       <c r="F75" t="s">
-        <v>125</v>
+        <v>155</v>
       </c>
       <c r="G75" t="s">
-        <v>155</v>
+        <v>126</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -3500,10 +3500,10 @@
         <v>114</v>
       </c>
       <c r="F76" t="s">
-        <v>125</v>
+        <v>149</v>
       </c>
       <c r="G76" t="s">
-        <v>149</v>
+        <v>126</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -3523,10 +3523,10 @@
         <v>114</v>
       </c>
       <c r="F77" t="s">
-        <v>125</v>
+        <v>149</v>
       </c>
       <c r="G77" t="s">
-        <v>149</v>
+        <v>126</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -3546,10 +3546,10 @@
         <v>114</v>
       </c>
       <c r="F78" t="s">
-        <v>125</v>
+        <v>152</v>
       </c>
       <c r="G78" t="s">
-        <v>152</v>
+        <v>126</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -3569,10 +3569,10 @@
         <v>114</v>
       </c>
       <c r="F79" t="s">
-        <v>125</v>
+        <v>161</v>
       </c>
       <c r="G79" t="s">
-        <v>161</v>
+        <v>126</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -3661,10 +3661,10 @@
         <v>114</v>
       </c>
       <c r="F83" t="s">
-        <v>115</v>
+        <v>143</v>
       </c>
       <c r="G83" t="s">
-        <v>143</v>
+        <v>116</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -3684,10 +3684,10 @@
         <v>114</v>
       </c>
       <c r="F84" t="s">
-        <v>115</v>
+        <v>171</v>
       </c>
       <c r="G84" t="s">
-        <v>171</v>
+        <v>116</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -3707,10 +3707,10 @@
         <v>114</v>
       </c>
       <c r="F85" t="s">
-        <v>115</v>
+        <v>173</v>
       </c>
       <c r="G85" t="s">
-        <v>173</v>
+        <v>116</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -3730,10 +3730,10 @@
         <v>114</v>
       </c>
       <c r="F86" t="s">
-        <v>164</v>
+        <v>176</v>
       </c>
       <c r="G86" t="s">
-        <v>176</v>
+        <v>165</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -3753,10 +3753,10 @@
         <v>114</v>
       </c>
       <c r="F87" t="s">
-        <v>115</v>
+        <v>173</v>
       </c>
       <c r="G87" t="s">
-        <v>173</v>
+        <v>116</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -3776,10 +3776,10 @@
         <v>114</v>
       </c>
       <c r="F88" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="G88" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -3799,10 +3799,10 @@
         <v>114</v>
       </c>
       <c r="F89" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="G89" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -3891,10 +3891,10 @@
         <v>114</v>
       </c>
       <c r="F93" t="s">
-        <v>115</v>
+        <v>122</v>
       </c>
       <c r="G93" t="s">
-        <v>122</v>
+        <v>116</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -3937,10 +3937,10 @@
         <v>114</v>
       </c>
       <c r="F95" t="s">
-        <v>115</v>
+        <v>190</v>
       </c>
       <c r="G95" t="s">
-        <v>190</v>
+        <v>116</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -4052,10 +4052,10 @@
         <v>114</v>
       </c>
       <c r="F100" t="s">
-        <v>125</v>
+        <v>155</v>
       </c>
       <c r="G100" t="s">
-        <v>155</v>
+        <v>126</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -4095,10 +4095,10 @@
         <v>203</v>
       </c>
       <c r="F102" t="s">
-        <v>183</v>
+        <v>204</v>
       </c>
       <c r="G102" t="s">
-        <v>204</v>
+        <v>184</v>
       </c>
     </row>
     <row r="103" spans="1:7">
@@ -4115,10 +4115,10 @@
         <v>203</v>
       </c>
       <c r="F103" t="s">
-        <v>183</v>
+        <v>204</v>
       </c>
       <c r="G103" t="s">
-        <v>204</v>
+        <v>184</v>
       </c>
     </row>
     <row r="104" spans="1:7">
@@ -4135,10 +4135,10 @@
         <v>203</v>
       </c>
       <c r="F104" t="s">
-        <v>183</v>
+        <v>204</v>
       </c>
       <c r="G104" t="s">
-        <v>204</v>
+        <v>184</v>
       </c>
     </row>
     <row r="105" spans="1:7">
@@ -4155,10 +4155,10 @@
         <v>203</v>
       </c>
       <c r="F105" t="s">
-        <v>183</v>
+        <v>209</v>
       </c>
       <c r="G105" t="s">
-        <v>209</v>
+        <v>184</v>
       </c>
     </row>
     <row r="106" spans="1:7">
@@ -4175,10 +4175,10 @@
         <v>203</v>
       </c>
       <c r="F106" t="s">
-        <v>183</v>
+        <v>204</v>
       </c>
       <c r="G106" t="s">
-        <v>204</v>
+        <v>184</v>
       </c>
     </row>
     <row r="107" spans="1:7">
@@ -4215,10 +4215,10 @@
         <v>203</v>
       </c>
       <c r="F108" t="s">
-        <v>183</v>
+        <v>214</v>
       </c>
       <c r="G108" t="s">
-        <v>214</v>
+        <v>184</v>
       </c>
     </row>
     <row r="109" spans="1:7">
@@ -4235,10 +4235,10 @@
         <v>203</v>
       </c>
       <c r="F109" t="s">
-        <v>92</v>
+        <v>217</v>
       </c>
       <c r="G109" t="s">
-        <v>217</v>
+        <v>93</v>
       </c>
     </row>
     <row r="110" spans="1:7">
@@ -4255,10 +4255,10 @@
         <v>203</v>
       </c>
       <c r="F110" t="s">
-        <v>92</v>
+        <v>220</v>
       </c>
       <c r="G110" t="s">
-        <v>220</v>
+        <v>93</v>
       </c>
     </row>
     <row r="111" spans="1:7">
@@ -4275,10 +4275,10 @@
         <v>203</v>
       </c>
       <c r="F111" t="s">
-        <v>183</v>
+        <v>204</v>
       </c>
       <c r="G111" t="s">
-        <v>204</v>
+        <v>184</v>
       </c>
     </row>
     <row r="112" spans="1:7">
@@ -4315,10 +4315,10 @@
         <v>203</v>
       </c>
       <c r="F113" t="s">
-        <v>115</v>
+        <v>143</v>
       </c>
       <c r="G113" t="s">
-        <v>143</v>
+        <v>116</v>
       </c>
     </row>
     <row r="114" spans="1:7">
@@ -4335,10 +4335,10 @@
         <v>203</v>
       </c>
       <c r="F114" t="s">
-        <v>125</v>
+        <v>152</v>
       </c>
       <c r="G114" t="s">
-        <v>152</v>
+        <v>126</v>
       </c>
     </row>
     <row r="115" spans="1:7">
@@ -4375,10 +4375,10 @@
         <v>203</v>
       </c>
       <c r="F116" t="s">
-        <v>224</v>
+        <v>231</v>
       </c>
       <c r="G116" t="s">
-        <v>231</v>
+        <v>225</v>
       </c>
     </row>
     <row r="117" spans="1:7">
@@ -4415,10 +4415,10 @@
         <v>203</v>
       </c>
       <c r="F118" t="s">
-        <v>164</v>
+        <v>234</v>
       </c>
       <c r="G118" t="s">
-        <v>234</v>
+        <v>165</v>
       </c>
     </row>
     <row r="119" spans="1:7">
@@ -4455,10 +4455,10 @@
         <v>237</v>
       </c>
       <c r="F120" t="s">
-        <v>115</v>
+        <v>171</v>
       </c>
       <c r="G120" t="s">
-        <v>171</v>
+        <v>116</v>
       </c>
     </row>
     <row r="121" spans="1:7">
@@ -4475,10 +4475,10 @@
         <v>237</v>
       </c>
       <c r="F121" t="s">
-        <v>115</v>
+        <v>143</v>
       </c>
       <c r="G121" t="s">
-        <v>143</v>
+        <v>116</v>
       </c>
     </row>
     <row r="122" spans="1:7">
@@ -4495,10 +4495,10 @@
         <v>237</v>
       </c>
       <c r="F122" t="s">
-        <v>115</v>
+        <v>171</v>
       </c>
       <c r="G122" t="s">
-        <v>171</v>
+        <v>116</v>
       </c>
     </row>
     <row r="123" spans="1:7">
@@ -4515,10 +4515,10 @@
         <v>237</v>
       </c>
       <c r="F123" t="s">
-        <v>115</v>
+        <v>171</v>
       </c>
       <c r="G123" t="s">
-        <v>171</v>
+        <v>116</v>
       </c>
     </row>
     <row r="124" spans="1:7">
@@ -4535,10 +4535,10 @@
         <v>237</v>
       </c>
       <c r="F124" t="s">
-        <v>164</v>
+        <v>243</v>
       </c>
       <c r="G124" t="s">
-        <v>243</v>
+        <v>165</v>
       </c>
     </row>
     <row r="125" spans="1:7">
@@ -4555,10 +4555,10 @@
         <v>237</v>
       </c>
       <c r="F125" t="s">
-        <v>164</v>
+        <v>243</v>
       </c>
       <c r="G125" t="s">
-        <v>243</v>
+        <v>165</v>
       </c>
     </row>
     <row r="126" spans="1:7">
@@ -4575,10 +4575,10 @@
         <v>237</v>
       </c>
       <c r="F126" t="s">
-        <v>164</v>
+        <v>243</v>
       </c>
       <c r="G126" t="s">
-        <v>243</v>
+        <v>165</v>
       </c>
     </row>
     <row r="127" spans="1:7">
@@ -4595,10 +4595,10 @@
         <v>237</v>
       </c>
       <c r="F127" t="s">
-        <v>164</v>
+        <v>243</v>
       </c>
       <c r="G127" t="s">
-        <v>243</v>
+        <v>165</v>
       </c>
     </row>
     <row r="128" spans="1:7">
@@ -4615,10 +4615,10 @@
         <v>237</v>
       </c>
       <c r="F128" t="s">
-        <v>164</v>
+        <v>243</v>
       </c>
       <c r="G128" t="s">
-        <v>243</v>
+        <v>165</v>
       </c>
     </row>
     <row r="129" spans="1:7">
@@ -4635,10 +4635,10 @@
         <v>237</v>
       </c>
       <c r="F129" t="s">
-        <v>164</v>
+        <v>249</v>
       </c>
       <c r="G129" t="s">
-        <v>249</v>
+        <v>165</v>
       </c>
     </row>
     <row r="130" spans="1:7">
@@ -4655,10 +4655,10 @@
         <v>237</v>
       </c>
       <c r="F130" t="s">
-        <v>164</v>
+        <v>251</v>
       </c>
       <c r="G130" t="s">
-        <v>251</v>
+        <v>165</v>
       </c>
     </row>
     <row r="131" spans="1:7">
@@ -4675,10 +4675,10 @@
         <v>237</v>
       </c>
       <c r="F131" t="s">
-        <v>164</v>
+        <v>253</v>
       </c>
       <c r="G131" t="s">
-        <v>253</v>
+        <v>165</v>
       </c>
     </row>
     <row r="132" spans="1:7">
@@ -4695,10 +4695,10 @@
         <v>237</v>
       </c>
       <c r="F132" t="s">
-        <v>164</v>
+        <v>256</v>
       </c>
       <c r="G132" t="s">
-        <v>256</v>
+        <v>165</v>
       </c>
     </row>
     <row r="133" spans="1:7">
@@ -4715,10 +4715,10 @@
         <v>237</v>
       </c>
       <c r="F133" t="s">
-        <v>115</v>
+        <v>190</v>
       </c>
       <c r="G133" t="s">
-        <v>190</v>
+        <v>116</v>
       </c>
     </row>
     <row r="134" spans="1:7">
@@ -4735,10 +4735,10 @@
         <v>259</v>
       </c>
       <c r="F134" t="s">
-        <v>164</v>
+        <v>176</v>
       </c>
       <c r="G134" t="s">
-        <v>176</v>
+        <v>165</v>
       </c>
     </row>
     <row r="135" spans="1:7">
@@ -4755,10 +4755,10 @@
         <v>259</v>
       </c>
       <c r="F135" t="s">
-        <v>164</v>
+        <v>176</v>
       </c>
       <c r="G135" t="s">
-        <v>176</v>
+        <v>165</v>
       </c>
     </row>
     <row r="136" spans="1:7">
@@ -4775,10 +4775,10 @@
         <v>259</v>
       </c>
       <c r="F136" t="s">
-        <v>164</v>
+        <v>176</v>
       </c>
       <c r="G136" t="s">
-        <v>176</v>
+        <v>165</v>
       </c>
     </row>
     <row r="137" spans="1:7">
@@ -4795,10 +4795,10 @@
         <v>259</v>
       </c>
       <c r="F137" t="s">
-        <v>164</v>
+        <v>176</v>
       </c>
       <c r="G137" t="s">
-        <v>176</v>
+        <v>165</v>
       </c>
     </row>
     <row r="138" spans="1:7">
@@ -4815,10 +4815,10 @@
         <v>259</v>
       </c>
       <c r="F138" t="s">
-        <v>164</v>
+        <v>176</v>
       </c>
       <c r="G138" t="s">
-        <v>176</v>
+        <v>165</v>
       </c>
     </row>
     <row r="139" spans="1:7">
@@ -4835,10 +4835,10 @@
         <v>259</v>
       </c>
       <c r="F139" t="s">
-        <v>224</v>
+        <v>266</v>
       </c>
       <c r="G139" t="s">
-        <v>266</v>
+        <v>225</v>
       </c>
     </row>
     <row r="140" spans="1:7">
@@ -4855,10 +4855,10 @@
         <v>259</v>
       </c>
       <c r="F140" t="s">
-        <v>164</v>
+        <v>176</v>
       </c>
       <c r="G140" t="s">
-        <v>176</v>
+        <v>165</v>
       </c>
     </row>
     <row r="141" spans="1:7">
@@ -4878,10 +4878,10 @@
         <v>271</v>
       </c>
       <c r="F141" t="s">
-        <v>164</v>
+        <v>272</v>
       </c>
       <c r="G141" t="s">
-        <v>272</v>
+        <v>165</v>
       </c>
     </row>
     <row r="142" spans="1:7">
@@ -4901,10 +4901,10 @@
         <v>271</v>
       </c>
       <c r="F142" t="s">
-        <v>164</v>
+        <v>272</v>
       </c>
       <c r="G142" t="s">
-        <v>272</v>
+        <v>165</v>
       </c>
     </row>
     <row r="143" spans="1:7">
@@ -4924,10 +4924,10 @@
         <v>271</v>
       </c>
       <c r="F143" t="s">
-        <v>164</v>
+        <v>276</v>
       </c>
       <c r="G143" t="s">
-        <v>276</v>
+        <v>165</v>
       </c>
     </row>
     <row r="144" spans="1:7">
@@ -4947,10 +4947,10 @@
         <v>271</v>
       </c>
       <c r="F144" t="s">
-        <v>164</v>
+        <v>276</v>
       </c>
       <c r="G144" t="s">
-        <v>276</v>
+        <v>165</v>
       </c>
     </row>
     <row r="145" spans="1:7">
@@ -4970,10 +4970,10 @@
         <v>271</v>
       </c>
       <c r="F145" t="s">
-        <v>164</v>
+        <v>276</v>
       </c>
       <c r="G145" t="s">
-        <v>276</v>
+        <v>165</v>
       </c>
     </row>
     <row r="146" spans="1:7">
@@ -4993,10 +4993,10 @@
         <v>271</v>
       </c>
       <c r="F146" t="s">
-        <v>164</v>
+        <v>272</v>
       </c>
       <c r="G146" t="s">
-        <v>272</v>
+        <v>165</v>
       </c>
     </row>
     <row r="147" spans="1:7">
@@ -5016,10 +5016,10 @@
         <v>271</v>
       </c>
       <c r="F147" t="s">
-        <v>164</v>
+        <v>272</v>
       </c>
       <c r="G147" t="s">
-        <v>272</v>
+        <v>165</v>
       </c>
     </row>
     <row r="148" spans="1:7">
@@ -5039,10 +5039,10 @@
         <v>271</v>
       </c>
       <c r="F148" t="s">
-        <v>164</v>
+        <v>272</v>
       </c>
       <c r="G148" t="s">
-        <v>272</v>
+        <v>165</v>
       </c>
     </row>
     <row r="149" spans="1:7">
@@ -5062,10 +5062,10 @@
         <v>271</v>
       </c>
       <c r="F149" t="s">
-        <v>164</v>
+        <v>272</v>
       </c>
       <c r="G149" t="s">
-        <v>272</v>
+        <v>165</v>
       </c>
     </row>
     <row r="150" spans="1:7">
@@ -5085,10 +5085,10 @@
         <v>271</v>
       </c>
       <c r="F150" t="s">
-        <v>164</v>
+        <v>272</v>
       </c>
       <c r="G150" t="s">
-        <v>272</v>
+        <v>165</v>
       </c>
     </row>
     <row r="151" spans="1:7">
@@ -5108,10 +5108,10 @@
         <v>271</v>
       </c>
       <c r="F151" t="s">
-        <v>164</v>
+        <v>272</v>
       </c>
       <c r="G151" t="s">
-        <v>272</v>
+        <v>165</v>
       </c>
     </row>
     <row r="152" spans="1:7">
@@ -5131,10 +5131,10 @@
         <v>271</v>
       </c>
       <c r="F152" t="s">
-        <v>164</v>
+        <v>272</v>
       </c>
       <c r="G152" t="s">
-        <v>272</v>
+        <v>165</v>
       </c>
     </row>
     <row r="153" spans="1:7">
@@ -5154,10 +5154,10 @@
         <v>271</v>
       </c>
       <c r="F153" t="s">
-        <v>164</v>
+        <v>272</v>
       </c>
       <c r="G153" t="s">
-        <v>272</v>
+        <v>165</v>
       </c>
     </row>
     <row r="154" spans="1:7">
@@ -5177,10 +5177,10 @@
         <v>271</v>
       </c>
       <c r="F154" t="s">
-        <v>164</v>
+        <v>272</v>
       </c>
       <c r="G154" t="s">
-        <v>272</v>
+        <v>165</v>
       </c>
     </row>
     <row r="155" spans="1:7">
@@ -5200,10 +5200,10 @@
         <v>271</v>
       </c>
       <c r="F155" t="s">
-        <v>164</v>
+        <v>272</v>
       </c>
       <c r="G155" t="s">
-        <v>272</v>
+        <v>165</v>
       </c>
     </row>
     <row r="156" spans="1:7">
@@ -5223,10 +5223,10 @@
         <v>271</v>
       </c>
       <c r="F156" t="s">
-        <v>164</v>
+        <v>272</v>
       </c>
       <c r="G156" t="s">
-        <v>272</v>
+        <v>165</v>
       </c>
     </row>
     <row r="157" spans="1:7">
@@ -5246,10 +5246,10 @@
         <v>271</v>
       </c>
       <c r="F157" t="s">
-        <v>164</v>
+        <v>293</v>
       </c>
       <c r="G157" t="s">
-        <v>293</v>
+        <v>165</v>
       </c>
     </row>
     <row r="158" spans="1:7">
@@ -5269,10 +5269,10 @@
         <v>271</v>
       </c>
       <c r="F158" t="s">
-        <v>164</v>
+        <v>272</v>
       </c>
       <c r="G158" t="s">
-        <v>272</v>
+        <v>165</v>
       </c>
     </row>
     <row r="159" spans="1:7">
@@ -5292,10 +5292,10 @@
         <v>271</v>
       </c>
       <c r="F159" t="s">
-        <v>164</v>
+        <v>272</v>
       </c>
       <c r="G159" t="s">
-        <v>272</v>
+        <v>165</v>
       </c>
     </row>
     <row r="160" spans="1:7">
@@ -5315,10 +5315,10 @@
         <v>271</v>
       </c>
       <c r="F160" t="s">
-        <v>164</v>
+        <v>272</v>
       </c>
       <c r="G160" t="s">
-        <v>272</v>
+        <v>165</v>
       </c>
     </row>
     <row r="161" spans="1:7">
@@ -5338,10 +5338,10 @@
         <v>271</v>
       </c>
       <c r="F161" t="s">
-        <v>164</v>
+        <v>272</v>
       </c>
       <c r="G161" t="s">
-        <v>272</v>
+        <v>165</v>
       </c>
     </row>
     <row r="162" spans="1:7">
@@ -5361,10 +5361,10 @@
         <v>271</v>
       </c>
       <c r="F162" t="s">
-        <v>164</v>
+        <v>272</v>
       </c>
       <c r="G162" t="s">
-        <v>272</v>
+        <v>165</v>
       </c>
     </row>
     <row r="163" spans="1:7">
@@ -5384,10 +5384,10 @@
         <v>271</v>
       </c>
       <c r="F163" t="s">
-        <v>164</v>
+        <v>302</v>
       </c>
       <c r="G163" t="s">
-        <v>302</v>
+        <v>165</v>
       </c>
     </row>
     <row r="164" spans="1:7">
@@ -5407,10 +5407,10 @@
         <v>271</v>
       </c>
       <c r="F164" t="s">
-        <v>164</v>
+        <v>272</v>
       </c>
       <c r="G164" t="s">
-        <v>272</v>
+        <v>165</v>
       </c>
     </row>
     <row r="165" spans="1:7">
@@ -5430,10 +5430,10 @@
         <v>271</v>
       </c>
       <c r="F165" t="s">
-        <v>164</v>
+        <v>272</v>
       </c>
       <c r="G165" t="s">
-        <v>272</v>
+        <v>165</v>
       </c>
     </row>
     <row r="166" spans="1:7">
@@ -5453,10 +5453,10 @@
         <v>271</v>
       </c>
       <c r="F166" t="s">
-        <v>164</v>
+        <v>272</v>
       </c>
       <c r="G166" t="s">
-        <v>272</v>
+        <v>165</v>
       </c>
     </row>
     <row r="167" spans="1:7">
@@ -5476,10 +5476,10 @@
         <v>271</v>
       </c>
       <c r="F167" t="s">
-        <v>164</v>
+        <v>272</v>
       </c>
       <c r="G167" t="s">
-        <v>272</v>
+        <v>165</v>
       </c>
     </row>
     <row r="168" spans="1:7">
@@ -5499,10 +5499,10 @@
         <v>271</v>
       </c>
       <c r="F168" t="s">
-        <v>164</v>
+        <v>309</v>
       </c>
       <c r="G168" t="s">
-        <v>309</v>
+        <v>165</v>
       </c>
     </row>
     <row r="169" spans="1:7">
@@ -5522,10 +5522,10 @@
         <v>271</v>
       </c>
       <c r="F169" t="s">
-        <v>164</v>
+        <v>309</v>
       </c>
       <c r="G169" t="s">
-        <v>309</v>
+        <v>165</v>
       </c>
     </row>
     <row r="170" spans="1:7">
@@ -5545,10 +5545,10 @@
         <v>271</v>
       </c>
       <c r="F170" t="s">
-        <v>164</v>
+        <v>272</v>
       </c>
       <c r="G170" t="s">
-        <v>272</v>
+        <v>165</v>
       </c>
     </row>
     <row r="171" spans="1:7">
@@ -5585,10 +5585,10 @@
         <v>313</v>
       </c>
       <c r="F172" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="G172" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
     </row>
     <row r="173" spans="1:7">
@@ -5768,10 +5768,10 @@
         <v>327</v>
       </c>
       <c r="F181" t="s">
-        <v>164</v>
+        <v>328</v>
       </c>
       <c r="G181" t="s">
-        <v>328</v>
+        <v>165</v>
       </c>
     </row>
     <row r="182" spans="1:7">
@@ -5791,10 +5791,10 @@
         <v>327</v>
       </c>
       <c r="F182" t="s">
-        <v>164</v>
+        <v>328</v>
       </c>
       <c r="G182" t="s">
-        <v>328</v>
+        <v>165</v>
       </c>
     </row>
     <row r="183" spans="1:7">
@@ -5814,10 +5814,10 @@
         <v>327</v>
       </c>
       <c r="F183" t="s">
-        <v>164</v>
+        <v>328</v>
       </c>
       <c r="G183" t="s">
-        <v>328</v>
+        <v>165</v>
       </c>
     </row>
     <row r="184" spans="1:7">
@@ -5837,10 +5837,10 @@
         <v>327</v>
       </c>
       <c r="F184" t="s">
-        <v>164</v>
+        <v>328</v>
       </c>
       <c r="G184" t="s">
-        <v>328</v>
+        <v>165</v>
       </c>
     </row>
     <row r="185" spans="1:7">
@@ -5860,10 +5860,10 @@
         <v>327</v>
       </c>
       <c r="F185" t="s">
-        <v>164</v>
+        <v>328</v>
       </c>
       <c r="G185" t="s">
-        <v>328</v>
+        <v>165</v>
       </c>
     </row>
     <row r="186" spans="1:7">
@@ -5883,10 +5883,10 @@
         <v>327</v>
       </c>
       <c r="F186" t="s">
-        <v>164</v>
+        <v>328</v>
       </c>
       <c r="G186" t="s">
-        <v>328</v>
+        <v>165</v>
       </c>
     </row>
     <row r="187" spans="1:7">
@@ -5906,10 +5906,10 @@
         <v>327</v>
       </c>
       <c r="F187" t="s">
-        <v>164</v>
+        <v>328</v>
       </c>
       <c r="G187" t="s">
-        <v>328</v>
+        <v>165</v>
       </c>
     </row>
     <row r="188" spans="1:7">
@@ -5929,10 +5929,10 @@
         <v>327</v>
       </c>
       <c r="F188" t="s">
-        <v>164</v>
+        <v>328</v>
       </c>
       <c r="G188" t="s">
-        <v>328</v>
+        <v>165</v>
       </c>
     </row>
     <row r="189" spans="1:7">
@@ -5952,10 +5952,10 @@
         <v>327</v>
       </c>
       <c r="F189" t="s">
-        <v>164</v>
+        <v>328</v>
       </c>
       <c r="G189" t="s">
-        <v>328</v>
+        <v>165</v>
       </c>
     </row>
     <row r="190" spans="1:7">
@@ -5975,10 +5975,10 @@
         <v>327</v>
       </c>
       <c r="F190" t="s">
-        <v>164</v>
+        <v>328</v>
       </c>
       <c r="G190" t="s">
-        <v>328</v>
+        <v>165</v>
       </c>
     </row>
     <row r="191" spans="1:7">
@@ -5998,10 +5998,10 @@
         <v>327</v>
       </c>
       <c r="F191" t="s">
-        <v>164</v>
+        <v>328</v>
       </c>
       <c r="G191" t="s">
-        <v>328</v>
+        <v>165</v>
       </c>
     </row>
     <row r="192" spans="1:7">
@@ -6021,10 +6021,10 @@
         <v>327</v>
       </c>
       <c r="F192" t="s">
-        <v>164</v>
+        <v>328</v>
       </c>
       <c r="G192" t="s">
-        <v>328</v>
+        <v>165</v>
       </c>
     </row>
     <row r="193" spans="1:7">
@@ -6044,10 +6044,10 @@
         <v>327</v>
       </c>
       <c r="F193" t="s">
-        <v>164</v>
+        <v>341</v>
       </c>
       <c r="G193" t="s">
-        <v>341</v>
+        <v>165</v>
       </c>
     </row>
     <row r="194" spans="1:7">
@@ -6067,10 +6067,10 @@
         <v>327</v>
       </c>
       <c r="F194" t="s">
-        <v>164</v>
+        <v>328</v>
       </c>
       <c r="G194" t="s">
-        <v>328</v>
+        <v>165</v>
       </c>
     </row>
     <row r="195" spans="1:7">
@@ -6090,10 +6090,10 @@
         <v>327</v>
       </c>
       <c r="F195" t="s">
-        <v>164</v>
+        <v>328</v>
       </c>
       <c r="G195" t="s">
-        <v>328</v>
+        <v>165</v>
       </c>
     </row>
     <row r="196" spans="1:7">
@@ -6113,10 +6113,10 @@
         <v>327</v>
       </c>
       <c r="F196" t="s">
-        <v>164</v>
+        <v>328</v>
       </c>
       <c r="G196" t="s">
-        <v>328</v>
+        <v>165</v>
       </c>
     </row>
     <row r="197" spans="1:7">
@@ -6136,10 +6136,10 @@
         <v>327</v>
       </c>
       <c r="F197" t="s">
-        <v>164</v>
+        <v>328</v>
       </c>
       <c r="G197" t="s">
-        <v>328</v>
+        <v>165</v>
       </c>
     </row>
     <row r="198" spans="1:7">
@@ -6159,10 +6159,10 @@
         <v>327</v>
       </c>
       <c r="F198" t="s">
-        <v>164</v>
+        <v>328</v>
       </c>
       <c r="G198" t="s">
-        <v>328</v>
+        <v>165</v>
       </c>
     </row>
     <row r="199" spans="1:7">
@@ -6182,10 +6182,10 @@
         <v>327</v>
       </c>
       <c r="F199" t="s">
-        <v>164</v>
+        <v>349</v>
       </c>
       <c r="G199" t="s">
-        <v>349</v>
+        <v>165</v>
       </c>
     </row>
     <row r="200" spans="1:7">
@@ -6205,10 +6205,10 @@
         <v>327</v>
       </c>
       <c r="F200" t="s">
-        <v>164</v>
+        <v>349</v>
       </c>
       <c r="G200" t="s">
-        <v>349</v>
+        <v>165</v>
       </c>
     </row>
     <row r="201" spans="1:7">
@@ -6228,10 +6228,10 @@
         <v>327</v>
       </c>
       <c r="F201" t="s">
-        <v>164</v>
+        <v>349</v>
       </c>
       <c r="G201" t="s">
-        <v>349</v>
+        <v>165</v>
       </c>
     </row>
     <row r="202" spans="1:7">
@@ -6251,10 +6251,10 @@
         <v>327</v>
       </c>
       <c r="F202" t="s">
-        <v>164</v>
+        <v>349</v>
       </c>
       <c r="G202" t="s">
-        <v>349</v>
+        <v>165</v>
       </c>
     </row>
     <row r="203" spans="1:7">
@@ -6274,10 +6274,10 @@
         <v>327</v>
       </c>
       <c r="F203" t="s">
-        <v>164</v>
+        <v>341</v>
       </c>
       <c r="G203" t="s">
-        <v>341</v>
+        <v>165</v>
       </c>
     </row>
     <row r="204" spans="1:7">
@@ -6297,10 +6297,10 @@
         <v>327</v>
       </c>
       <c r="F204" t="s">
-        <v>164</v>
+        <v>349</v>
       </c>
       <c r="G204" t="s">
-        <v>349</v>
+        <v>165</v>
       </c>
     </row>
     <row r="205" spans="1:7">
@@ -6320,10 +6320,10 @@
         <v>327</v>
       </c>
       <c r="F205" t="s">
-        <v>164</v>
+        <v>357</v>
       </c>
       <c r="G205" t="s">
-        <v>357</v>
+        <v>165</v>
       </c>
     </row>
     <row r="206" spans="1:7">
@@ -6343,10 +6343,10 @@
         <v>327</v>
       </c>
       <c r="F206" t="s">
-        <v>164</v>
+        <v>357</v>
       </c>
       <c r="G206" t="s">
-        <v>357</v>
+        <v>165</v>
       </c>
     </row>
     <row r="207" spans="1:7">
@@ -6366,10 +6366,10 @@
         <v>327</v>
       </c>
       <c r="F207" t="s">
-        <v>164</v>
+        <v>357</v>
       </c>
       <c r="G207" t="s">
-        <v>357</v>
+        <v>165</v>
       </c>
     </row>
     <row r="208" spans="1:7">
@@ -6389,10 +6389,10 @@
         <v>327</v>
       </c>
       <c r="F208" t="s">
-        <v>164</v>
+        <v>341</v>
       </c>
       <c r="G208" t="s">
-        <v>341</v>
+        <v>165</v>
       </c>
     </row>
     <row r="209" spans="1:7">
@@ -6412,10 +6412,10 @@
         <v>327</v>
       </c>
       <c r="F209" t="s">
-        <v>164</v>
+        <v>357</v>
       </c>
       <c r="G209" t="s">
-        <v>357</v>
+        <v>165</v>
       </c>
     </row>
     <row r="210" spans="1:7">
@@ -6435,10 +6435,10 @@
         <v>365</v>
       </c>
       <c r="F210" t="s">
-        <v>164</v>
+        <v>366</v>
       </c>
       <c r="G210" t="s">
-        <v>366</v>
+        <v>165</v>
       </c>
     </row>
     <row r="211" spans="1:7">
@@ -6458,10 +6458,10 @@
         <v>365</v>
       </c>
       <c r="F211" t="s">
-        <v>164</v>
+        <v>366</v>
       </c>
       <c r="G211" t="s">
-        <v>366</v>
+        <v>165</v>
       </c>
     </row>
     <row r="212" spans="1:7">
@@ -6481,10 +6481,10 @@
         <v>365</v>
       </c>
       <c r="F212" t="s">
-        <v>164</v>
+        <v>366</v>
       </c>
       <c r="G212" t="s">
-        <v>366</v>
+        <v>165</v>
       </c>
     </row>
     <row r="213" spans="1:7">
@@ -6504,10 +6504,10 @@
         <v>365</v>
       </c>
       <c r="F213" t="s">
-        <v>164</v>
+        <v>366</v>
       </c>
       <c r="G213" t="s">
-        <v>366</v>
+        <v>165</v>
       </c>
     </row>
     <row r="214" spans="1:7">
@@ -6527,10 +6527,10 @@
         <v>365</v>
       </c>
       <c r="F214" t="s">
-        <v>164</v>
+        <v>366</v>
       </c>
       <c r="G214" t="s">
-        <v>366</v>
+        <v>165</v>
       </c>
     </row>
     <row r="215" spans="1:7">
@@ -6550,10 +6550,10 @@
         <v>365</v>
       </c>
       <c r="F215" t="s">
-        <v>164</v>
+        <v>349</v>
       </c>
       <c r="G215" t="s">
-        <v>349</v>
+        <v>165</v>
       </c>
     </row>
     <row r="216" spans="1:7">
@@ -6573,10 +6573,10 @@
         <v>365</v>
       </c>
       <c r="F216" t="s">
-        <v>164</v>
+        <v>366</v>
       </c>
       <c r="G216" t="s">
-        <v>366</v>
+        <v>165</v>
       </c>
     </row>
     <row r="217" spans="1:7">
@@ -6596,10 +6596,10 @@
         <v>365</v>
       </c>
       <c r="F217" t="s">
-        <v>164</v>
+        <v>366</v>
       </c>
       <c r="G217" t="s">
-        <v>366</v>
+        <v>165</v>
       </c>
     </row>
     <row r="218" spans="1:7">
@@ -6619,10 +6619,10 @@
         <v>365</v>
       </c>
       <c r="F218" t="s">
-        <v>164</v>
+        <v>366</v>
       </c>
       <c r="G218" t="s">
-        <v>366</v>
+        <v>165</v>
       </c>
     </row>
     <row r="219" spans="1:7">
@@ -6642,10 +6642,10 @@
         <v>365</v>
       </c>
       <c r="F219" t="s">
-        <v>164</v>
+        <v>366</v>
       </c>
       <c r="G219" t="s">
-        <v>366</v>
+        <v>165</v>
       </c>
     </row>
     <row r="220" spans="1:7">
@@ -6665,10 +6665,10 @@
         <v>365</v>
       </c>
       <c r="F220" t="s">
-        <v>164</v>
+        <v>309</v>
       </c>
       <c r="G220" t="s">
-        <v>309</v>
+        <v>165</v>
       </c>
     </row>
     <row r="221" spans="1:7">
@@ -6688,10 +6688,10 @@
         <v>365</v>
       </c>
       <c r="F221" t="s">
-        <v>164</v>
+        <v>366</v>
       </c>
       <c r="G221" t="s">
-        <v>366</v>
+        <v>165</v>
       </c>
     </row>
     <row r="222" spans="1:7">
@@ -6711,10 +6711,10 @@
         <v>365</v>
       </c>
       <c r="F222" t="s">
-        <v>164</v>
+        <v>366</v>
       </c>
       <c r="G222" t="s">
-        <v>366</v>
+        <v>165</v>
       </c>
     </row>
     <row r="223" spans="1:7">
@@ -6734,10 +6734,10 @@
         <v>365</v>
       </c>
       <c r="F223" t="s">
-        <v>164</v>
+        <v>366</v>
       </c>
       <c r="G223" t="s">
-        <v>366</v>
+        <v>165</v>
       </c>
     </row>
     <row r="224" spans="1:7">
@@ -6757,10 +6757,10 @@
         <v>365</v>
       </c>
       <c r="F224" t="s">
-        <v>164</v>
+        <v>366</v>
       </c>
       <c r="G224" t="s">
-        <v>366</v>
+        <v>165</v>
       </c>
     </row>
     <row r="225" spans="1:7">
@@ -6780,10 +6780,10 @@
         <v>365</v>
       </c>
       <c r="F225" t="s">
-        <v>164</v>
+        <v>366</v>
       </c>
       <c r="G225" t="s">
-        <v>366</v>
+        <v>165</v>
       </c>
     </row>
     <row r="226" spans="1:7">
@@ -6803,10 +6803,10 @@
         <v>365</v>
       </c>
       <c r="F226" t="s">
-        <v>164</v>
+        <v>276</v>
       </c>
       <c r="G226" t="s">
-        <v>276</v>
+        <v>165</v>
       </c>
     </row>
     <row r="227" spans="1:7">
@@ -6826,10 +6826,10 @@
         <v>365</v>
       </c>
       <c r="F227" t="s">
-        <v>164</v>
+        <v>366</v>
       </c>
       <c r="G227" t="s">
-        <v>366</v>
+        <v>165</v>
       </c>
     </row>
     <row r="228" spans="1:7">
@@ -6872,10 +6872,10 @@
         <v>365</v>
       </c>
       <c r="F229" t="s">
-        <v>164</v>
+        <v>387</v>
       </c>
       <c r="G229" t="s">
-        <v>387</v>
+        <v>165</v>
       </c>
     </row>
     <row r="230" spans="1:7">
@@ -6895,10 +6895,10 @@
         <v>365</v>
       </c>
       <c r="F230" t="s">
-        <v>164</v>
+        <v>387</v>
       </c>
       <c r="G230" t="s">
-        <v>387</v>
+        <v>165</v>
       </c>
     </row>
     <row r="231" spans="1:7">
@@ -6918,10 +6918,10 @@
         <v>365</v>
       </c>
       <c r="F231" t="s">
-        <v>164</v>
+        <v>293</v>
       </c>
       <c r="G231" t="s">
-        <v>293</v>
+        <v>165</v>
       </c>
     </row>
     <row r="232" spans="1:7">
@@ -6941,10 +6941,10 @@
         <v>365</v>
       </c>
       <c r="F232" t="s">
-        <v>164</v>
+        <v>309</v>
       </c>
       <c r="G232" t="s">
-        <v>309</v>
+        <v>165</v>
       </c>
     </row>
     <row r="233" spans="1:7">
@@ -6964,10 +6964,10 @@
         <v>365</v>
       </c>
       <c r="F233" t="s">
-        <v>164</v>
+        <v>387</v>
       </c>
       <c r="G233" t="s">
-        <v>387</v>
+        <v>165</v>
       </c>
     </row>
     <row r="234" spans="1:7">
@@ -6987,10 +6987,10 @@
         <v>365</v>
       </c>
       <c r="F234" t="s">
-        <v>164</v>
+        <v>387</v>
       </c>
       <c r="G234" t="s">
-        <v>387</v>
+        <v>165</v>
       </c>
     </row>
     <row r="235" spans="1:7">
@@ -7010,10 +7010,10 @@
         <v>365</v>
       </c>
       <c r="F235" t="s">
-        <v>164</v>
+        <v>387</v>
       </c>
       <c r="G235" t="s">
-        <v>387</v>
+        <v>165</v>
       </c>
     </row>
     <row r="236" spans="1:7">
@@ -7033,10 +7033,10 @@
         <v>365</v>
       </c>
       <c r="F236" t="s">
-        <v>164</v>
+        <v>387</v>
       </c>
       <c r="G236" t="s">
-        <v>387</v>
+        <v>165</v>
       </c>
     </row>
     <row r="237" spans="1:7">
@@ -7056,10 +7056,10 @@
         <v>365</v>
       </c>
       <c r="F237" t="s">
-        <v>164</v>
+        <v>387</v>
       </c>
       <c r="G237" t="s">
-        <v>387</v>
+        <v>165</v>
       </c>
     </row>
     <row r="238" spans="1:7">
@@ -7079,10 +7079,10 @@
         <v>365</v>
       </c>
       <c r="F238" t="s">
-        <v>164</v>
+        <v>387</v>
       </c>
       <c r="G238" t="s">
-        <v>387</v>
+        <v>165</v>
       </c>
     </row>
     <row r="239" spans="1:7">
@@ -7102,10 +7102,10 @@
         <v>365</v>
       </c>
       <c r="F239" t="s">
-        <v>164</v>
+        <v>399</v>
       </c>
       <c r="G239" t="s">
-        <v>399</v>
+        <v>165</v>
       </c>
     </row>
     <row r="240" spans="1:7">
@@ -7263,10 +7263,10 @@
         <v>402</v>
       </c>
       <c r="F246" t="s">
-        <v>164</v>
+        <v>410</v>
       </c>
       <c r="G246" t="s">
-        <v>410</v>
+        <v>165</v>
       </c>
     </row>
     <row r="247" spans="1:7">
@@ -7323,10 +7323,10 @@
         <v>412</v>
       </c>
       <c r="F249" t="s">
-        <v>96</v>
+        <v>416</v>
       </c>
       <c r="G249" t="s">
-        <v>416</v>
+        <v>97</v>
       </c>
     </row>
     <row r="250" spans="1:7">
@@ -7403,10 +7403,10 @@
         <v>422</v>
       </c>
       <c r="F253" t="s">
-        <v>164</v>
+        <v>423</v>
       </c>
       <c r="G253" t="s">
-        <v>423</v>
+        <v>165</v>
       </c>
     </row>
     <row r="254" spans="1:7">
@@ -7423,10 +7423,10 @@
         <v>422</v>
       </c>
       <c r="F254" t="s">
-        <v>92</v>
+        <v>220</v>
       </c>
       <c r="G254" t="s">
-        <v>220</v>
+        <v>93</v>
       </c>
     </row>
     <row r="255" spans="1:7">
@@ -7443,10 +7443,10 @@
         <v>422</v>
       </c>
       <c r="F255" t="s">
-        <v>92</v>
+        <v>427</v>
       </c>
       <c r="G255" t="s">
-        <v>427</v>
+        <v>93</v>
       </c>
     </row>
     <row r="256" spans="1:7">
@@ -7463,10 +7463,10 @@
         <v>422</v>
       </c>
       <c r="F256" t="s">
-        <v>92</v>
+        <v>427</v>
       </c>
       <c r="G256" t="s">
-        <v>427</v>
+        <v>93</v>
       </c>
     </row>
     <row r="257" spans="1:7">
@@ -7483,10 +7483,10 @@
         <v>422</v>
       </c>
       <c r="F257" t="s">
-        <v>92</v>
+        <v>427</v>
       </c>
       <c r="G257" t="s">
-        <v>427</v>
+        <v>93</v>
       </c>
     </row>
     <row r="258" spans="1:7">
@@ -7503,10 +7503,10 @@
         <v>422</v>
       </c>
       <c r="F258" t="s">
-        <v>164</v>
+        <v>328</v>
       </c>
       <c r="G258" t="s">
-        <v>328</v>
+        <v>165</v>
       </c>
     </row>
     <row r="259" spans="1:7">
@@ -7523,10 +7523,10 @@
         <v>422</v>
       </c>
       <c r="F259" t="s">
-        <v>92</v>
+        <v>427</v>
       </c>
       <c r="G259" t="s">
-        <v>427</v>
+        <v>93</v>
       </c>
     </row>
     <row r="260" spans="1:7">
@@ -7563,10 +7563,10 @@
         <v>422</v>
       </c>
       <c r="F261" t="s">
-        <v>196</v>
+        <v>435</v>
       </c>
       <c r="G261" t="s">
-        <v>435</v>
+        <v>197</v>
       </c>
     </row>
     <row r="262" spans="1:7">
@@ -7603,10 +7603,10 @@
         <v>422</v>
       </c>
       <c r="F263" t="s">
-        <v>183</v>
+        <v>439</v>
       </c>
       <c r="G263" t="s">
-        <v>439</v>
+        <v>184</v>
       </c>
     </row>
     <row r="264" spans="1:7">
@@ -7663,10 +7663,10 @@
         <v>422</v>
       </c>
       <c r="F266" t="s">
-        <v>115</v>
+        <v>444</v>
       </c>
       <c r="G266" t="s">
-        <v>444</v>
+        <v>116</v>
       </c>
     </row>
     <row r="267" spans="1:7">
@@ -7683,10 +7683,10 @@
         <v>446</v>
       </c>
       <c r="F267" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="G267" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
     </row>
     <row r="268" spans="1:7">
@@ -7703,10 +7703,10 @@
         <v>448</v>
       </c>
       <c r="F268" t="s">
-        <v>183</v>
+        <v>204</v>
       </c>
       <c r="G268" t="s">
-        <v>204</v>
+        <v>184</v>
       </c>
     </row>
     <row r="269" spans="1:7">
@@ -7723,10 +7723,10 @@
         <v>450</v>
       </c>
       <c r="F269" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="G269" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
     </row>
     <row r="270" spans="1:7">
@@ -7743,10 +7743,10 @@
         <v>450</v>
       </c>
       <c r="F270" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="G270" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
     </row>
     <row r="271" spans="1:7">
@@ -7763,10 +7763,10 @@
         <v>454</v>
       </c>
       <c r="F271" t="s">
-        <v>115</v>
+        <v>455</v>
       </c>
       <c r="G271" t="s">
-        <v>455</v>
+        <v>116</v>
       </c>
     </row>
     <row r="272" spans="1:7">
@@ -7783,10 +7783,10 @@
         <v>454</v>
       </c>
       <c r="F272" t="s">
-        <v>115</v>
+        <v>455</v>
       </c>
       <c r="G272" t="s">
-        <v>455</v>
+        <v>116</v>
       </c>
     </row>
     <row r="273" spans="1:7">
@@ -7803,10 +7803,10 @@
         <v>454</v>
       </c>
       <c r="F273" t="s">
-        <v>115</v>
+        <v>455</v>
       </c>
       <c r="G273" t="s">
-        <v>455</v>
+        <v>116</v>
       </c>
     </row>
     <row r="274" spans="1:7">
@@ -7823,10 +7823,10 @@
         <v>454</v>
       </c>
       <c r="F274" t="s">
-        <v>115</v>
+        <v>455</v>
       </c>
       <c r="G274" t="s">
-        <v>455</v>
+        <v>116</v>
       </c>
     </row>
     <row r="275" spans="1:7">
@@ -7843,10 +7843,10 @@
         <v>454</v>
       </c>
       <c r="F275" t="s">
-        <v>115</v>
+        <v>455</v>
       </c>
       <c r="G275" t="s">
-        <v>455</v>
+        <v>116</v>
       </c>
     </row>
     <row r="276" spans="1:7">
@@ -7863,10 +7863,10 @@
         <v>454</v>
       </c>
       <c r="F276" t="s">
-        <v>115</v>
+        <v>455</v>
       </c>
       <c r="G276" t="s">
-        <v>455</v>
+        <v>116</v>
       </c>
     </row>
     <row r="277" spans="1:7">
@@ -7883,10 +7883,10 @@
         <v>454</v>
       </c>
       <c r="F277" t="s">
-        <v>115</v>
+        <v>455</v>
       </c>
       <c r="G277" t="s">
-        <v>455</v>
+        <v>116</v>
       </c>
     </row>
     <row r="278" spans="1:7">
@@ -7903,10 +7903,10 @@
         <v>463</v>
       </c>
       <c r="F278" t="s">
-        <v>183</v>
+        <v>204</v>
       </c>
       <c r="G278" t="s">
-        <v>204</v>
+        <v>184</v>
       </c>
     </row>
     <row r="279" spans="1:7">
@@ -7923,10 +7923,10 @@
         <v>463</v>
       </c>
       <c r="F279" t="s">
-        <v>32</v>
+        <v>54</v>
       </c>
       <c r="G279" t="s">
-        <v>54</v>
+        <v>33</v>
       </c>
     </row>
     <row r="280" spans="1:7">
@@ -7963,10 +7963,10 @@
         <v>463</v>
       </c>
       <c r="F281" t="s">
-        <v>115</v>
+        <v>171</v>
       </c>
       <c r="G281" t="s">
-        <v>171</v>
+        <v>116</v>
       </c>
     </row>
     <row r="282" spans="1:7">
@@ -8003,10 +8003,10 @@
         <v>469</v>
       </c>
       <c r="F283" t="s">
-        <v>164</v>
+        <v>399</v>
       </c>
       <c r="G283" t="s">
-        <v>399</v>
+        <v>165</v>
       </c>
     </row>
     <row r="284" spans="1:7">
@@ -8043,10 +8043,10 @@
         <v>473</v>
       </c>
       <c r="F285" t="s">
-        <v>115</v>
+        <v>171</v>
       </c>
       <c r="G285" t="s">
-        <v>171</v>
+        <v>116</v>
       </c>
     </row>
     <row r="286" spans="1:7">
@@ -8063,10 +8063,10 @@
         <v>475</v>
       </c>
       <c r="F286" t="s">
-        <v>183</v>
+        <v>439</v>
       </c>
       <c r="G286" t="s">
-        <v>439</v>
+        <v>184</v>
       </c>
     </row>
     <row r="287" spans="1:7">
@@ -8083,10 +8083,10 @@
         <v>475</v>
       </c>
       <c r="F287" t="s">
-        <v>183</v>
+        <v>439</v>
       </c>
       <c r="G287" t="s">
-        <v>439</v>
+        <v>184</v>
       </c>
     </row>
     <row r="288" spans="1:7">
@@ -8103,10 +8103,10 @@
         <v>475</v>
       </c>
       <c r="F288" t="s">
-        <v>12</v>
+        <v>42</v>
       </c>
       <c r="G288" t="s">
-        <v>42</v>
+        <v>13</v>
       </c>
     </row>
     <row r="289" spans="1:7">
@@ -8163,10 +8163,10 @@
         <v>475</v>
       </c>
       <c r="F291" t="s">
-        <v>115</v>
+        <v>171</v>
       </c>
       <c r="G291" t="s">
-        <v>171</v>
+        <v>116</v>
       </c>
     </row>
     <row r="292" spans="1:7">
@@ -8183,10 +8183,10 @@
         <v>475</v>
       </c>
       <c r="F292" t="s">
-        <v>115</v>
+        <v>171</v>
       </c>
       <c r="G292" t="s">
-        <v>171</v>
+        <v>116</v>
       </c>
     </row>
     <row r="293" spans="1:7">
@@ -8203,10 +8203,10 @@
         <v>475</v>
       </c>
       <c r="F293" t="s">
-        <v>115</v>
+        <v>171</v>
       </c>
       <c r="G293" t="s">
-        <v>171</v>
+        <v>116</v>
       </c>
     </row>
     <row r="294" spans="1:7">
@@ -8223,10 +8223,10 @@
         <v>475</v>
       </c>
       <c r="F294" t="s">
-        <v>115</v>
+        <v>171</v>
       </c>
       <c r="G294" t="s">
-        <v>171</v>
+        <v>116</v>
       </c>
     </row>
     <row r="295" spans="1:7">
@@ -8243,10 +8243,10 @@
         <v>485</v>
       </c>
       <c r="F295" t="s">
-        <v>115</v>
+        <v>171</v>
       </c>
       <c r="G295" t="s">
-        <v>171</v>
+        <v>116</v>
       </c>
     </row>
     <row r="296" spans="1:7">
@@ -8263,10 +8263,10 @@
         <v>485</v>
       </c>
       <c r="F296" t="s">
-        <v>115</v>
+        <v>171</v>
       </c>
       <c r="G296" t="s">
-        <v>171</v>
+        <v>116</v>
       </c>
     </row>
   </sheetData>

--- a/api/2/xlsx/fr/SectorCOFOG.xlsx
+++ b/api/2/xlsx/fr/SectorCOFOG.xlsx
@@ -22,75 +22,75 @@
     <t>status</t>
   </si>
   <si>
+    <t>codeforiati:cofog-class</t>
+  </si>
+  <si>
+    <t>codeforiati:category-code</t>
+  </si>
+  <si>
+    <t>codeforiati:group-code</t>
+  </si>
+  <si>
+    <t>codeforiati:cofog-division</t>
+  </si>
+  <si>
     <t>codeforiati:cofog-group</t>
   </si>
   <si>
-    <t>codeforiati:category-code</t>
-  </si>
-  <si>
-    <t>codeforiati:group-code</t>
-  </si>
-  <si>
-    <t>codeforiati:cofog-class</t>
-  </si>
-  <si>
-    <t>codeforiati:cofog-division</t>
-  </si>
-  <si>
     <t>11110</t>
   </si>
   <si>
     <t>active</t>
   </si>
   <si>
+    <t>09.8.0 - Education n.e.c. (CS)</t>
+  </si>
+  <si>
+    <t>111</t>
+  </si>
+  <si>
+    <t>110</t>
+  </si>
+  <si>
+    <t>09 - Education</t>
+  </si>
+  <si>
     <t>09.8 - Education n.e.c.</t>
   </si>
   <si>
-    <t>111</t>
-  </si>
-  <si>
-    <t>110</t>
-  </si>
-  <si>
-    <t>09.8.0 - Education n.e.c. (CS)</t>
-  </si>
-  <si>
-    <t>09 - Education</t>
-  </si>
-  <si>
     <t>11120</t>
   </si>
   <si>
+    <t>09.6.0 - Subsidiary services to education (IS)</t>
+  </si>
+  <si>
     <t>09.6 - Subsidiary services to education</t>
   </si>
   <si>
-    <t>09.6.0 - Subsidiary services to education (IS)</t>
-  </si>
-  <si>
     <t>11130</t>
   </si>
   <si>
     <t>11182</t>
   </si>
   <si>
+    <t>09.7.0 - R&amp;D Education (CS)</t>
+  </si>
+  <si>
     <t>09.7 - R&amp;D Education</t>
   </si>
   <si>
-    <t>09.7.0 - R&amp;D Education (CS)</t>
-  </si>
-  <si>
     <t>11220</t>
   </si>
   <si>
+    <t>09.1.2 - Primary education (IS)</t>
+  </si>
+  <si>
+    <t>112</t>
+  </si>
+  <si>
     <t>09.1 - Pre‐primary and primary education</t>
   </si>
   <si>
-    <t>112</t>
-  </si>
-  <si>
-    <t>09.1.2 - Primary education (IS)</t>
-  </si>
-  <si>
     <t>11230</t>
   </si>
   <si>
@@ -109,99 +109,99 @@
     <t>11250</t>
   </si>
   <si>
+    <t>07.4.0 - Public health services (IS)</t>
+  </si>
+  <si>
+    <t>07 - Health</t>
+  </si>
+  <si>
     <t>07.4 - Public health services</t>
   </si>
   <si>
-    <t>07.4.0 - Public health services (IS)</t>
-  </si>
-  <si>
-    <t>07 - Health</t>
-  </si>
-  <si>
     <t>11260</t>
   </si>
   <si>
+    <t>09.2.1 - Lower‐secondary education (IS)</t>
+  </si>
+  <si>
     <t>09.2 - Secondary education</t>
   </si>
   <si>
-    <t>09.2.1 - Lower‐secondary education (IS)</t>
-  </si>
-  <si>
     <t>11320</t>
   </si>
   <si>
+    <t>09.2.2 - Upper‐secondary education (IS)</t>
+  </si>
+  <si>
     <t>113</t>
   </si>
   <si>
-    <t>09.2.2 - Upper‐secondary education (IS)</t>
-  </si>
-  <si>
     <t>11330</t>
   </si>
   <si>
+    <t>09.5.0 - Education not definable by level (IS)</t>
+  </si>
+  <si>
     <t>09.5 - Education not definable by level</t>
   </si>
   <si>
-    <t>09.5.0 - Education not definable by level (IS)</t>
-  </si>
-  <si>
     <t>11420</t>
   </si>
   <si>
+    <t>09.4.1 - First stage of tertiary education (IS)</t>
+  </si>
+  <si>
+    <t>114</t>
+  </si>
+  <si>
     <t>09.4 - Tertiary education</t>
   </si>
   <si>
-    <t>114</t>
-  </si>
-  <si>
-    <t>09.4.1 - First stage of tertiary education (IS)</t>
-  </si>
-  <si>
     <t>11430</t>
   </si>
   <si>
+    <t>09.3.0 - Post‐secondary non‐tertiary education (IS)</t>
+  </si>
+  <si>
     <t>09.3 - Post‐secondary non‐tertiary education</t>
   </si>
   <si>
-    <t>09.3.0 - Post‐secondary non‐tertiary education (IS)</t>
-  </si>
-  <si>
     <t>12110</t>
   </si>
   <si>
+    <t>07.6.0 - Health n.e.c. (CS)</t>
+  </si>
+  <si>
+    <t>121</t>
+  </si>
+  <si>
+    <t>120</t>
+  </si>
+  <si>
     <t>07.6 - Health n.e.c.</t>
   </si>
   <si>
-    <t>121</t>
-  </si>
-  <si>
-    <t>120</t>
-  </si>
-  <si>
-    <t>07.6.0 - Health n.e.c. (CS)</t>
-  </si>
-  <si>
     <t>12181</t>
   </si>
   <si>
     <t>12182</t>
   </si>
   <si>
+    <t>07.5.0 - R&amp;D Health (CS)</t>
+  </si>
+  <si>
     <t>07.5 - R&amp;D Health</t>
   </si>
   <si>
-    <t>07.5.0 - R&amp;D Health (CS)</t>
-  </si>
-  <si>
     <t>12191</t>
   </si>
   <si>
+    <t>07.2.1 - General medical services (IS)</t>
+  </si>
+  <si>
     <t>07.2 - Outpatient services</t>
   </si>
   <si>
-    <t>07.2.1 - General medical services (IS)</t>
-  </si>
-  <si>
     <t>12196</t>
   </si>
   <si>
@@ -214,12 +214,12 @@
     <t>12230</t>
   </si>
   <si>
+    <t>07.3.1 - General hospital services (IS)</t>
+  </si>
+  <si>
     <t>07.3 - Hospital services</t>
   </si>
   <si>
-    <t>07.3.1 - General hospital services (IS)</t>
-  </si>
-  <si>
     <t>12240</t>
   </si>
   <si>
@@ -286,30 +286,30 @@
     <t>14010</t>
   </si>
   <si>
+    <t>06.3.0 - Water supply (CS)</t>
+  </si>
+  <si>
+    <t>140</t>
+  </si>
+  <si>
+    <t>06 - Housing and community amenities</t>
+  </si>
+  <si>
     <t>06.3 - Water supply</t>
   </si>
   <si>
-    <t>140</t>
-  </si>
-  <si>
-    <t>06.3.0 - Water supply (CS)</t>
-  </si>
-  <si>
-    <t>06 - Housing and community amenities</t>
-  </si>
-  <si>
     <t>14015</t>
   </si>
   <si>
+    <t>05.6.0 - Environmental protection n.e.c. (CS)</t>
+  </si>
+  <si>
+    <t>05 - Environmental protection</t>
+  </si>
+  <si>
     <t>05.6 - Environmental protection n.e.c.</t>
   </si>
   <si>
-    <t>05.6.0 - Environmental protection n.e.c. (CS)</t>
-  </si>
-  <si>
-    <t>05 - Environmental protection</t>
-  </si>
-  <si>
     <t>14020</t>
   </si>
   <si>
@@ -319,12 +319,12 @@
     <t>14022</t>
   </si>
   <si>
+    <t>05.2.0 - Waste water management (CS)</t>
+  </si>
+  <si>
     <t>05.2 - Waste water management</t>
   </si>
   <si>
-    <t>05.2.0 - Waste water management (CS)</t>
-  </si>
-  <si>
     <t>14030</t>
   </si>
   <si>
@@ -340,63 +340,63 @@
     <t>14050</t>
   </si>
   <si>
+    <t>05.1.0 - Waste management (CS)</t>
+  </si>
+  <si>
     <t>05.1 - Waste management</t>
   </si>
   <si>
-    <t>05.1.0 - Waste management (CS)</t>
-  </si>
-  <si>
     <t>14081</t>
   </si>
   <si>
     <t>15110</t>
   </si>
   <si>
+    <t>01.3.1 - General personnel services (CS)</t>
+  </si>
+  <si>
+    <t>151</t>
+  </si>
+  <si>
+    <t>150</t>
+  </si>
+  <si>
+    <t>01 - General public services</t>
+  </si>
+  <si>
     <t>01.3 - General services</t>
   </si>
   <si>
-    <t>151</t>
-  </si>
-  <si>
-    <t>150</t>
-  </si>
-  <si>
-    <t>01.3.1 - General personnel services (CS)</t>
-  </si>
-  <si>
-    <t>01 - General public services</t>
-  </si>
-  <si>
     <t>15111</t>
   </si>
   <si>
+    <t>01.1.2 - Financial and fiscal affairs (CS)</t>
+  </si>
+  <si>
     <t>01.1 - Executive and legislative organs, financial and fiscal affairs, external affairs</t>
   </si>
   <si>
-    <t>01.1.2 - Financial and fiscal affairs (CS)</t>
-  </si>
-  <si>
     <t>15112</t>
   </si>
   <si>
+    <t>01.8.0 - Transfers of a general character between different levels of government (CS)</t>
+  </si>
+  <si>
     <t>01.8 - Transfers of a general character between different levels of government</t>
   </si>
   <si>
-    <t>01.8.0 - Transfers of a general character between different levels of government (CS)</t>
-  </si>
-  <si>
     <t>15113</t>
   </si>
   <si>
+    <t>03.6.0 - Public order and safety n.e.c. (CS)</t>
+  </si>
+  <si>
+    <t>03 - Public order and safety</t>
+  </si>
+  <si>
     <t>03.6 - Public order and safety n.e.c.</t>
   </si>
   <si>
-    <t>03.6.0 - Public order and safety n.e.c. (CS)</t>
-  </si>
-  <si>
-    <t>03 - Public order and safety</t>
-  </si>
-  <si>
     <t>15114</t>
   </si>
   <si>
@@ -424,12 +424,12 @@
     <t>15123</t>
   </si>
   <si>
+    <t>01.2.2 - Economic aid routed through international organizations (CS)</t>
+  </si>
+  <si>
     <t>01.2 - Foreign economic aid</t>
   </si>
   <si>
-    <t>01.2.2 - Economic aid routed through international organizations (CS)</t>
-  </si>
-  <si>
     <t>15124</t>
   </si>
   <si>
@@ -460,30 +460,30 @@
     <t>15131</t>
   </si>
   <si>
+    <t>03.3.0 - Law courts (CS)</t>
+  </si>
+  <si>
     <t>03.3 - Law courts</t>
   </si>
   <si>
-    <t>03.3.0 - Law courts (CS)</t>
-  </si>
-  <si>
     <t>15132</t>
   </si>
   <si>
+    <t>03.1.0 - Police services (CS)</t>
+  </si>
+  <si>
     <t>03.1 - Police services</t>
   </si>
   <si>
-    <t>03.1.0 - Police services (CS)</t>
-  </si>
-  <si>
     <t>15133</t>
   </si>
   <si>
+    <t>03.2.0 - Fire‐protection services (CS)</t>
+  </si>
+  <si>
     <t>03.2 - Fire‐protection services</t>
   </si>
   <si>
-    <t>03.2.0 - Fire‐protection services (CS)</t>
-  </si>
-  <si>
     <t>15134</t>
   </si>
   <si>
@@ -496,24 +496,24 @@
     <t>15137</t>
   </si>
   <si>
+    <t>03.4.0 - Prisons (CS)</t>
+  </si>
+  <si>
     <t>03.4 - Prisons</t>
   </si>
   <si>
-    <t>03.4.0 - Prisons (CS)</t>
-  </si>
-  <si>
     <t>15142</t>
   </si>
   <si>
+    <t>04.1.1 - General economic and commercial affairs (CS)</t>
+  </si>
+  <si>
+    <t>04 - Economic affairs</t>
+  </si>
+  <si>
     <t>04.1 - General economic, commercial and labour affairs</t>
   </si>
   <si>
-    <t>04.1.1 - General economic and commercial affairs (CS)</t>
-  </si>
-  <si>
-    <t>04 - Economic affairs</t>
-  </si>
-  <si>
     <t>15143</t>
   </si>
   <si>
@@ -526,12 +526,12 @@
     <t>15151</t>
   </si>
   <si>
+    <t>01.6.0 - General public services n.e.c. (CS)</t>
+  </si>
+  <si>
     <t>01.6 - General public services n.e.c.</t>
   </si>
   <si>
-    <t>01.6.0 - General public services n.e.c. (CS)</t>
-  </si>
-  <si>
     <t>15152</t>
   </si>
   <si>
@@ -541,12 +541,12 @@
     <t>15153</t>
   </si>
   <si>
+    <t>04.6.0 - Communication (CS)</t>
+  </si>
+  <si>
     <t>04.6 - Communication</t>
   </si>
   <si>
-    <t>04.6.0 - Communication (CS)</t>
-  </si>
-  <si>
     <t>15154</t>
   </si>
   <si>
@@ -562,15 +562,15 @@
     <t>15170</t>
   </si>
   <si>
+    <t>10.7.0 - Social exclusion n.e.c. (IS)</t>
+  </si>
+  <si>
+    <t>10 - Social protection</t>
+  </si>
+  <si>
     <t>10.7 - Social exclusion n.e.c.</t>
   </si>
   <si>
-    <t>10.7.0 - Social exclusion n.e.c. (IS)</t>
-  </si>
-  <si>
-    <t>10 - Social protection</t>
-  </si>
-  <si>
     <t>15180</t>
   </si>
   <si>
@@ -583,12 +583,12 @@
     <t>15196</t>
   </si>
   <si>
+    <t>01.5.0 - R&amp;D General public services (CS)</t>
+  </si>
+  <si>
     <t>01.5 - R&amp;D General public services</t>
   </si>
   <si>
-    <t>01.5.0 - R&amp;D General public services (CS)</t>
-  </si>
-  <si>
     <t>15210</t>
   </si>
   <si>
@@ -601,15 +601,15 @@
     <t>15230</t>
   </si>
   <si>
+    <t>02.3.0 - Foreign military aid (CS)</t>
+  </si>
+  <si>
+    <t>02 - Defence</t>
+  </si>
+  <si>
     <t>02.3 - Foreign military aid</t>
   </si>
   <si>
-    <t>02.3.0 - Foreign military aid (CS)</t>
-  </si>
-  <si>
-    <t>02 - Defence</t>
-  </si>
-  <si>
     <t>15240</t>
   </si>
   <si>
@@ -622,15 +622,15 @@
     <t>16010</t>
   </si>
   <si>
+    <t>10.9.0 - Social protection n.e.c. (CS)</t>
+  </si>
+  <si>
+    <t>160</t>
+  </si>
+  <si>
     <t>10.9 - Social protection n.e.c.</t>
   </si>
   <si>
-    <t>160</t>
-  </si>
-  <si>
-    <t>10.9.0 - Social protection n.e.c. (CS)</t>
-  </si>
-  <si>
     <t>16011</t>
   </si>
   <si>
@@ -640,12 +640,12 @@
     <t>16013</t>
   </si>
   <si>
+    <t>10.2.0 - Old age (IS)</t>
+  </si>
+  <si>
     <t>10.2 - Old age</t>
   </si>
   <si>
-    <t>10.2.0 - Old age (IS)</t>
-  </si>
-  <si>
     <t>16014</t>
   </si>
   <si>
@@ -655,45 +655,45 @@
     <t>16020</t>
   </si>
   <si>
+    <t>10.5.0 - Unemployment (IS)</t>
+  </si>
+  <si>
     <t>10.5 - Unemployment</t>
   </si>
   <si>
-    <t>10.5.0 - Unemployment (IS)</t>
-  </si>
-  <si>
     <t>16030</t>
   </si>
   <si>
+    <t>06.6.0 - Housing and community amenities n.e.c. (CS)</t>
+  </si>
+  <si>
     <t>06.6 - Housing and community amenities n.e.c.</t>
   </si>
   <si>
-    <t>06.6.0 - Housing and community amenities n.e.c. (CS)</t>
-  </si>
-  <si>
     <t>16040</t>
   </si>
   <si>
+    <t>06.1.0 - Housing development (CS)</t>
+  </si>
+  <si>
     <t>06.1 - Housing development</t>
   </si>
   <si>
-    <t>06.1.0 - Housing development (CS)</t>
-  </si>
-  <si>
     <t>16050</t>
   </si>
   <si>
     <t>16061</t>
   </si>
   <si>
+    <t>08.2.0 - Cultural services (IS)</t>
+  </si>
+  <si>
+    <t>08 - Recreation, culture and religion</t>
+  </si>
+  <si>
     <t>08.2 - Cultural services</t>
   </si>
   <si>
-    <t>08.2.0 - Cultural services (IS)</t>
-  </si>
-  <si>
-    <t>08 - Recreation, culture and religion</t>
-  </si>
-  <si>
     <t>16062</t>
   </si>
   <si>
@@ -706,12 +706,12 @@
     <t>16065</t>
   </si>
   <si>
+    <t>08.1.0 - Recreational and sporting services (IS)</t>
+  </si>
+  <si>
     <t>08.1 - Recreational and sporting services</t>
   </si>
   <si>
-    <t>08.1.0 - Recreational and sporting services (IS)</t>
-  </si>
-  <si>
     <t>16066</t>
   </si>
   <si>
@@ -742,12 +742,12 @@
     <t>21020</t>
   </si>
   <si>
+    <t>04.5.1 - Road transport (CS)</t>
+  </si>
+  <si>
     <t>04.5 - Transport</t>
   </si>
   <si>
-    <t>04.5.1 - Road transport (CS)</t>
-  </si>
-  <si>
     <t>21021</t>
   </si>
   <si>
@@ -781,12 +781,12 @@
     <t>21061</t>
   </si>
   <si>
+    <t>04.7.1 - Distributive trades, storage and warehousing (CS)</t>
+  </si>
+  <si>
     <t>04.7 - Other industries</t>
   </si>
   <si>
-    <t>04.7.1 - Distributive trades, storage and warehousing (CS)</t>
-  </si>
-  <si>
     <t>21081</t>
   </si>
   <si>
@@ -811,42 +811,42 @@
     <t>22030</t>
   </si>
   <si>
+    <t>08.3.0 - Broadcasting and publishing services (CS)</t>
+  </si>
+  <si>
     <t>08.3 - Broadcasting and publishing services</t>
   </si>
   <si>
-    <t>08.3.0 - Broadcasting and publishing services (CS)</t>
-  </si>
-  <si>
     <t>22040</t>
   </si>
   <si>
     <t>23110</t>
   </si>
   <si>
+    <t>04.3.5 - Electricity (CS)</t>
+  </si>
+  <si>
+    <t>231</t>
+  </si>
+  <si>
+    <t>230</t>
+  </si>
+  <si>
     <t>04.3 - Fuel and energy</t>
   </si>
   <si>
-    <t>231</t>
-  </si>
-  <si>
-    <t>230</t>
-  </si>
-  <si>
-    <t>04.3.5 - Electricity (CS)</t>
-  </si>
-  <si>
     <t>23111</t>
   </si>
   <si>
     <t>23112</t>
   </si>
   <si>
+    <t>04.8.3 - R&amp;D Fuel and energy (CS)</t>
+  </si>
+  <si>
     <t>04.8 - R&amp;D Economic affairs</t>
   </si>
   <si>
-    <t>04.8.3 - R&amp;D Fuel and energy (CS)</t>
-  </si>
-  <si>
     <t>23181</t>
   </si>
   <si>
@@ -919,12 +919,12 @@
     <t>23510</t>
   </si>
   <si>
+    <t>04.3.3 - Nuclear fuel (CS)</t>
+  </si>
+  <si>
     <t>235</t>
   </si>
   <si>
-    <t>04.3.3 - Nuclear fuel (CS)</t>
-  </si>
-  <si>
     <t>23610</t>
   </si>
   <si>
@@ -991,18 +991,18 @@
     <t>31110</t>
   </si>
   <si>
+    <t>04.2.1 - Agriculture (CS)</t>
+  </si>
+  <si>
+    <t>311</t>
+  </si>
+  <si>
+    <t>310</t>
+  </si>
+  <si>
     <t>04.2 - Agriculture, forestry, fishing and hunting</t>
   </si>
   <si>
-    <t>311</t>
-  </si>
-  <si>
-    <t>310</t>
-  </si>
-  <si>
-    <t>04.2.1 - Agriculture (CS)</t>
-  </si>
-  <si>
     <t>31120</t>
   </si>
   <si>
@@ -1060,12 +1060,12 @@
     <t>31210</t>
   </si>
   <si>
+    <t>04.2.2 - Forestry (CS)</t>
+  </si>
+  <si>
     <t>312</t>
   </si>
   <si>
-    <t>04.2.2 - Forestry (CS)</t>
-  </si>
-  <si>
     <t>31220</t>
   </si>
   <si>
@@ -1084,12 +1084,12 @@
     <t>31310</t>
   </si>
   <si>
+    <t>04.2.3 - Fishing and hunting (CS)</t>
+  </si>
+  <si>
     <t>313</t>
   </si>
   <si>
-    <t>04.2.3 - Fishing and hunting (CS)</t>
-  </si>
-  <si>
     <t>31320</t>
   </si>
   <si>
@@ -1105,18 +1105,18 @@
     <t>32110</t>
   </si>
   <si>
+    <t>04.4.2 - Manufacturing (CS)</t>
+  </si>
+  <si>
+    <t>321</t>
+  </si>
+  <si>
+    <t>320</t>
+  </si>
+  <si>
     <t>04.4 - Mining, manufacturing and construction</t>
   </si>
   <si>
-    <t>321</t>
-  </si>
-  <si>
-    <t>320</t>
-  </si>
-  <si>
-    <t>04.4.2 - Manufacturing (CS)</t>
-  </si>
-  <si>
     <t>32120</t>
   </si>
   <si>
@@ -1174,12 +1174,12 @@
     <t>32210</t>
   </si>
   <si>
+    <t>04.4.1 - Mining of mineral resources other than mineral fuels (CS)</t>
+  </si>
+  <si>
     <t>322</t>
   </si>
   <si>
-    <t>04.4.1 - Mining of mineral resources other than mineral fuels (CS)</t>
-  </si>
-  <si>
     <t>32220</t>
   </si>
   <si>
@@ -1210,12 +1210,12 @@
     <t>32310</t>
   </si>
   <si>
+    <t>04.4.3 - Construction (CS)</t>
+  </si>
+  <si>
     <t>323</t>
   </si>
   <si>
-    <t>04.4.3 - Construction (CS)</t>
-  </si>
-  <si>
     <t>33110</t>
   </si>
   <si>
@@ -1243,12 +1243,12 @@
     <t>33210</t>
   </si>
   <si>
+    <t>04.7.3 - Tourism (CS)</t>
+  </si>
+  <si>
     <t>332</t>
   </si>
   <si>
-    <t>04.7.3 - Tourism (CS)</t>
-  </si>
-  <si>
     <t>41010</t>
   </si>
   <si>
@@ -1261,12 +1261,12 @@
     <t>41030</t>
   </si>
   <si>
+    <t>05.4.0 - Protection of biodiversity and landscape (CS)</t>
+  </si>
+  <si>
     <t>05.4 - Protection of biodiversity and landscape</t>
   </si>
   <si>
-    <t>05.4.0 - Protection of biodiversity and landscape (CS)</t>
-  </si>
-  <si>
     <t>41040</t>
   </si>
   <si>
@@ -1279,27 +1279,27 @@
     <t>43010</t>
   </si>
   <si>
+    <t>04.9.0 - Economic affairs n.e.c. (CS)</t>
+  </si>
+  <si>
+    <t>430</t>
+  </si>
+  <si>
     <t>04.9 - Economic affairs n.e.c.</t>
   </si>
   <si>
-    <t>430</t>
-  </si>
-  <si>
-    <t>04.9.0 - Economic affairs n.e.c. (CS)</t>
-  </si>
-  <si>
     <t>43030</t>
   </si>
   <si>
     <t>43031</t>
   </si>
   <si>
+    <t>06.2.0 - Community development (CS)</t>
+  </si>
+  <si>
     <t>06.2 - Community development</t>
   </si>
   <si>
-    <t>06.2.0 - Community development (CS)</t>
-  </si>
-  <si>
     <t>43032</t>
   </si>
   <si>
@@ -1318,24 +1318,24 @@
     <t>43060</t>
   </si>
   <si>
+    <t>02.2.0 - Civil defence (CS)</t>
+  </si>
+  <si>
     <t>02.2 - Civil defence</t>
   </si>
   <si>
-    <t>02.2.0 - Civil defence (CS)</t>
-  </si>
-  <si>
     <t>43071</t>
   </si>
   <si>
     <t>43072</t>
   </si>
   <si>
+    <t>10.4.0 - Family and children (IS)</t>
+  </si>
+  <si>
     <t>10.4 - Family and children</t>
   </si>
   <si>
-    <t>10.4.0 - Family and children (IS)</t>
-  </si>
-  <si>
     <t>43073</t>
   </si>
   <si>
@@ -1345,12 +1345,12 @@
     <t>43082</t>
   </si>
   <si>
+    <t>01.4.0 - Basic research (CS)</t>
+  </si>
+  <si>
     <t>01.4 - Basic research</t>
   </si>
   <si>
-    <t>01.4.0 - Basic research (CS)</t>
-  </si>
-  <si>
     <t>51010</t>
   </si>
   <si>
@@ -1375,13 +1375,13 @@
     <t>60010</t>
   </si>
   <si>
+    <t>01.7.0 - Public debt transactions (CS)</t>
+  </si>
+  <si>
+    <t>600</t>
+  </si>
+  <si>
     <t>01.7 - Public debt transactions</t>
-  </si>
-  <si>
-    <t>600</t>
-  </si>
-  <si>
-    <t>01.7.0 - Public debt transactions (CS)</t>
   </si>
   <si>
     <t>60020</t>
@@ -1872,10 +1872,10 @@
         <v>11</v>
       </c>
       <c r="F3" t="s">
+        <v>12</v>
+      </c>
+      <c r="G3" t="s">
         <v>16</v>
-      </c>
-      <c r="G3" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -1918,10 +1918,10 @@
         <v>11</v>
       </c>
       <c r="F5" t="s">
+        <v>12</v>
+      </c>
+      <c r="G5" t="s">
         <v>20</v>
-      </c>
-      <c r="G5" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -1941,10 +1941,10 @@
         <v>11</v>
       </c>
       <c r="F6" t="s">
+        <v>12</v>
+      </c>
+      <c r="G6" t="s">
         <v>24</v>
-      </c>
-      <c r="G6" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -1987,10 +1987,10 @@
         <v>11</v>
       </c>
       <c r="F8" t="s">
+        <v>12</v>
+      </c>
+      <c r="G8" t="s">
         <v>24</v>
-      </c>
-      <c r="G8" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -2010,10 +2010,10 @@
         <v>11</v>
       </c>
       <c r="F9" t="s">
+        <v>12</v>
+      </c>
+      <c r="G9" t="s">
         <v>24</v>
-      </c>
-      <c r="G9" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -2024,7 +2024,7 @@
         <v>8</v>
       </c>
       <c r="C10" t="s">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="D10" t="s">
         <v>23</v>
@@ -2033,10 +2033,10 @@
         <v>11</v>
       </c>
       <c r="F10" t="s">
-        <v>29</v>
+        <v>12</v>
       </c>
       <c r="G10" t="s">
-        <v>13</v>
+        <v>24</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -2079,10 +2079,10 @@
         <v>11</v>
       </c>
       <c r="F12" t="s">
+        <v>12</v>
+      </c>
+      <c r="G12" t="s">
         <v>36</v>
-      </c>
-      <c r="G12" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -2093,19 +2093,19 @@
         <v>8</v>
       </c>
       <c r="C13" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="D13" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="E13" t="s">
         <v>11</v>
       </c>
       <c r="F13" t="s">
-        <v>39</v>
+        <v>12</v>
       </c>
       <c r="G13" t="s">
-        <v>13</v>
+        <v>36</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -2119,16 +2119,16 @@
         <v>41</v>
       </c>
       <c r="D14" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="E14" t="s">
         <v>11</v>
       </c>
       <c r="F14" t="s">
+        <v>12</v>
+      </c>
+      <c r="G14" t="s">
         <v>42</v>
-      </c>
-      <c r="G14" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -2148,10 +2148,10 @@
         <v>11</v>
       </c>
       <c r="F15" t="s">
+        <v>12</v>
+      </c>
+      <c r="G15" t="s">
         <v>46</v>
-      </c>
-      <c r="G15" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -2171,10 +2171,10 @@
         <v>11</v>
       </c>
       <c r="F16" t="s">
+        <v>12</v>
+      </c>
+      <c r="G16" t="s">
         <v>49</v>
-      </c>
-      <c r="G16" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -2194,10 +2194,10 @@
         <v>53</v>
       </c>
       <c r="F17" t="s">
+        <v>32</v>
+      </c>
+      <c r="G17" t="s">
         <v>54</v>
-      </c>
-      <c r="G17" t="s">
-        <v>33</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -2217,10 +2217,10 @@
         <v>53</v>
       </c>
       <c r="F18" t="s">
+        <v>32</v>
+      </c>
+      <c r="G18" t="s">
         <v>54</v>
-      </c>
-      <c r="G18" t="s">
-        <v>33</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -2240,10 +2240,10 @@
         <v>53</v>
       </c>
       <c r="F19" t="s">
+        <v>32</v>
+      </c>
+      <c r="G19" t="s">
         <v>58</v>
-      </c>
-      <c r="G19" t="s">
-        <v>33</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -2263,10 +2263,10 @@
         <v>53</v>
       </c>
       <c r="F20" t="s">
+        <v>32</v>
+      </c>
+      <c r="G20" t="s">
         <v>61</v>
-      </c>
-      <c r="G20" t="s">
-        <v>33</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -2286,10 +2286,10 @@
         <v>53</v>
       </c>
       <c r="F21" t="s">
+        <v>32</v>
+      </c>
+      <c r="G21" t="s">
         <v>54</v>
-      </c>
-      <c r="G21" t="s">
-        <v>33</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -2332,10 +2332,10 @@
         <v>53</v>
       </c>
       <c r="F23" t="s">
+        <v>32</v>
+      </c>
+      <c r="G23" t="s">
         <v>67</v>
-      </c>
-      <c r="G23" t="s">
-        <v>33</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -2493,10 +2493,10 @@
         <v>53</v>
       </c>
       <c r="F30" t="s">
+        <v>32</v>
+      </c>
+      <c r="G30" t="s">
         <v>54</v>
-      </c>
-      <c r="G30" t="s">
-        <v>33</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -2631,10 +2631,10 @@
         <v>53</v>
       </c>
       <c r="F36" t="s">
+        <v>32</v>
+      </c>
+      <c r="G36" t="s">
         <v>58</v>
-      </c>
-      <c r="G36" t="s">
-        <v>33</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -2731,10 +2731,10 @@
         <v>83</v>
       </c>
       <c r="F41" t="s">
+        <v>32</v>
+      </c>
+      <c r="G41" t="s">
         <v>54</v>
-      </c>
-      <c r="G41" t="s">
-        <v>33</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -2751,10 +2751,10 @@
         <v>83</v>
       </c>
       <c r="F42" t="s">
+        <v>32</v>
+      </c>
+      <c r="G42" t="s">
         <v>58</v>
-      </c>
-      <c r="G42" t="s">
-        <v>33</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -2851,10 +2851,10 @@
         <v>91</v>
       </c>
       <c r="F47" t="s">
+        <v>96</v>
+      </c>
+      <c r="G47" t="s">
         <v>102</v>
-      </c>
-      <c r="G47" t="s">
-        <v>97</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -2911,10 +2911,10 @@
         <v>91</v>
       </c>
       <c r="F50" t="s">
+        <v>96</v>
+      </c>
+      <c r="G50" t="s">
         <v>102</v>
-      </c>
-      <c r="G50" t="s">
-        <v>97</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -2951,10 +2951,10 @@
         <v>91</v>
       </c>
       <c r="F52" t="s">
+        <v>96</v>
+      </c>
+      <c r="G52" t="s">
         <v>109</v>
-      </c>
-      <c r="G52" t="s">
-        <v>97</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -3017,10 +3017,10 @@
         <v>114</v>
       </c>
       <c r="F55" t="s">
+        <v>115</v>
+      </c>
+      <c r="G55" t="s">
         <v>119</v>
-      </c>
-      <c r="G55" t="s">
-        <v>116</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -3040,10 +3040,10 @@
         <v>114</v>
       </c>
       <c r="F56" t="s">
+        <v>115</v>
+      </c>
+      <c r="G56" t="s">
         <v>122</v>
-      </c>
-      <c r="G56" t="s">
-        <v>116</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -3086,10 +3086,10 @@
         <v>114</v>
       </c>
       <c r="F58" t="s">
+        <v>115</v>
+      </c>
+      <c r="G58" t="s">
         <v>119</v>
-      </c>
-      <c r="G58" t="s">
-        <v>116</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -3109,10 +3109,10 @@
         <v>114</v>
       </c>
       <c r="F59" t="s">
+        <v>115</v>
+      </c>
+      <c r="G59" t="s">
         <v>119</v>
-      </c>
-      <c r="G59" t="s">
-        <v>116</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -3132,10 +3132,10 @@
         <v>114</v>
       </c>
       <c r="F60" t="s">
+        <v>115</v>
+      </c>
+      <c r="G60" t="s">
         <v>119</v>
-      </c>
-      <c r="G60" t="s">
-        <v>116</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -3155,10 +3155,10 @@
         <v>114</v>
       </c>
       <c r="F61" t="s">
+        <v>115</v>
+      </c>
+      <c r="G61" t="s">
         <v>119</v>
-      </c>
-      <c r="G61" t="s">
-        <v>116</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -3178,10 +3178,10 @@
         <v>114</v>
       </c>
       <c r="F62" t="s">
+        <v>115</v>
+      </c>
+      <c r="G62" t="s">
         <v>119</v>
-      </c>
-      <c r="G62" t="s">
-        <v>116</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -3192,7 +3192,7 @@
         <v>8</v>
       </c>
       <c r="C63" t="s">
-        <v>118</v>
+        <v>133</v>
       </c>
       <c r="D63" t="s">
         <v>113</v>
@@ -3201,10 +3201,10 @@
         <v>114</v>
       </c>
       <c r="F63" t="s">
-        <v>133</v>
+        <v>115</v>
       </c>
       <c r="G63" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -3215,7 +3215,7 @@
         <v>8</v>
       </c>
       <c r="C64" t="s">
-        <v>118</v>
+        <v>133</v>
       </c>
       <c r="D64" t="s">
         <v>113</v>
@@ -3224,10 +3224,10 @@
         <v>114</v>
       </c>
       <c r="F64" t="s">
-        <v>133</v>
+        <v>115</v>
       </c>
       <c r="G64" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -3247,10 +3247,10 @@
         <v>114</v>
       </c>
       <c r="F65" t="s">
+        <v>115</v>
+      </c>
+      <c r="G65" t="s">
         <v>137</v>
-      </c>
-      <c r="G65" t="s">
-        <v>116</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -3293,10 +3293,10 @@
         <v>114</v>
       </c>
       <c r="F67" t="s">
+        <v>115</v>
+      </c>
+      <c r="G67" t="s">
         <v>119</v>
-      </c>
-      <c r="G67" t="s">
-        <v>116</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -3307,7 +3307,7 @@
         <v>8</v>
       </c>
       <c r="C68" t="s">
-        <v>112</v>
+        <v>141</v>
       </c>
       <c r="D68" t="s">
         <v>113</v>
@@ -3316,7 +3316,7 @@
         <v>114</v>
       </c>
       <c r="F68" t="s">
-        <v>141</v>
+        <v>115</v>
       </c>
       <c r="G68" t="s">
         <v>116</v>
@@ -3330,7 +3330,7 @@
         <v>8</v>
       </c>
       <c r="C69" t="s">
-        <v>112</v>
+        <v>143</v>
       </c>
       <c r="D69" t="s">
         <v>113</v>
@@ -3339,7 +3339,7 @@
         <v>114</v>
       </c>
       <c r="F69" t="s">
-        <v>143</v>
+        <v>115</v>
       </c>
       <c r="G69" t="s">
         <v>116</v>
@@ -3362,10 +3362,10 @@
         <v>114</v>
       </c>
       <c r="F70" t="s">
+        <v>115</v>
+      </c>
+      <c r="G70" t="s">
         <v>122</v>
-      </c>
-      <c r="G70" t="s">
-        <v>116</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -3385,10 +3385,10 @@
         <v>114</v>
       </c>
       <c r="F71" t="s">
+        <v>115</v>
+      </c>
+      <c r="G71" t="s">
         <v>122</v>
-      </c>
-      <c r="G71" t="s">
-        <v>116</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -3431,10 +3431,10 @@
         <v>114</v>
       </c>
       <c r="F73" t="s">
+        <v>125</v>
+      </c>
+      <c r="G73" t="s">
         <v>149</v>
-      </c>
-      <c r="G73" t="s">
-        <v>126</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -3454,10 +3454,10 @@
         <v>114</v>
       </c>
       <c r="F74" t="s">
+        <v>125</v>
+      </c>
+      <c r="G74" t="s">
         <v>152</v>
-      </c>
-      <c r="G74" t="s">
-        <v>126</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -3477,10 +3477,10 @@
         <v>114</v>
       </c>
       <c r="F75" t="s">
+        <v>125</v>
+      </c>
+      <c r="G75" t="s">
         <v>155</v>
-      </c>
-      <c r="G75" t="s">
-        <v>126</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -3500,10 +3500,10 @@
         <v>114</v>
       </c>
       <c r="F76" t="s">
+        <v>125</v>
+      </c>
+      <c r="G76" t="s">
         <v>149</v>
-      </c>
-      <c r="G76" t="s">
-        <v>126</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -3523,10 +3523,10 @@
         <v>114</v>
       </c>
       <c r="F77" t="s">
+        <v>125</v>
+      </c>
+      <c r="G77" t="s">
         <v>149</v>
-      </c>
-      <c r="G77" t="s">
-        <v>126</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -3546,10 +3546,10 @@
         <v>114</v>
       </c>
       <c r="F78" t="s">
+        <v>125</v>
+      </c>
+      <c r="G78" t="s">
         <v>152</v>
-      </c>
-      <c r="G78" t="s">
-        <v>126</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -3569,10 +3569,10 @@
         <v>114</v>
       </c>
       <c r="F79" t="s">
+        <v>125</v>
+      </c>
+      <c r="G79" t="s">
         <v>161</v>
-      </c>
-      <c r="G79" t="s">
-        <v>126</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -3652,7 +3652,7 @@
         <v>8</v>
       </c>
       <c r="C83" t="s">
-        <v>112</v>
+        <v>143</v>
       </c>
       <c r="D83" t="s">
         <v>113</v>
@@ -3661,7 +3661,7 @@
         <v>114</v>
       </c>
       <c r="F83" t="s">
-        <v>143</v>
+        <v>115</v>
       </c>
       <c r="G83" t="s">
         <v>116</v>
@@ -3684,10 +3684,10 @@
         <v>114</v>
       </c>
       <c r="F84" t="s">
+        <v>115</v>
+      </c>
+      <c r="G84" t="s">
         <v>171</v>
-      </c>
-      <c r="G84" t="s">
-        <v>116</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -3698,7 +3698,7 @@
         <v>8</v>
       </c>
       <c r="C85" t="s">
-        <v>118</v>
+        <v>173</v>
       </c>
       <c r="D85" t="s">
         <v>113</v>
@@ -3707,10 +3707,10 @@
         <v>114</v>
       </c>
       <c r="F85" t="s">
-        <v>173</v>
+        <v>115</v>
       </c>
       <c r="G85" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -3730,10 +3730,10 @@
         <v>114</v>
       </c>
       <c r="F86" t="s">
+        <v>164</v>
+      </c>
+      <c r="G86" t="s">
         <v>176</v>
-      </c>
-      <c r="G86" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -3744,7 +3744,7 @@
         <v>8</v>
       </c>
       <c r="C87" t="s">
-        <v>118</v>
+        <v>173</v>
       </c>
       <c r="D87" t="s">
         <v>113</v>
@@ -3753,10 +3753,10 @@
         <v>114</v>
       </c>
       <c r="F87" t="s">
-        <v>173</v>
+        <v>115</v>
       </c>
       <c r="G87" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -3776,10 +3776,10 @@
         <v>114</v>
       </c>
       <c r="F88" t="s">
+        <v>115</v>
+      </c>
+      <c r="G88" t="s">
         <v>119</v>
-      </c>
-      <c r="G88" t="s">
-        <v>116</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -3799,10 +3799,10 @@
         <v>114</v>
       </c>
       <c r="F89" t="s">
+        <v>115</v>
+      </c>
+      <c r="G89" t="s">
         <v>119</v>
-      </c>
-      <c r="G89" t="s">
-        <v>116</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -3891,10 +3891,10 @@
         <v>114</v>
       </c>
       <c r="F93" t="s">
+        <v>115</v>
+      </c>
+      <c r="G93" t="s">
         <v>122</v>
-      </c>
-      <c r="G93" t="s">
-        <v>116</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -3937,10 +3937,10 @@
         <v>114</v>
       </c>
       <c r="F95" t="s">
+        <v>115</v>
+      </c>
+      <c r="G95" t="s">
         <v>190</v>
-      </c>
-      <c r="G95" t="s">
-        <v>116</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -4052,10 +4052,10 @@
         <v>114</v>
       </c>
       <c r="F100" t="s">
+        <v>125</v>
+      </c>
+      <c r="G100" t="s">
         <v>155</v>
-      </c>
-      <c r="G100" t="s">
-        <v>126</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -4095,10 +4095,10 @@
         <v>203</v>
       </c>
       <c r="F102" t="s">
+        <v>183</v>
+      </c>
+      <c r="G102" t="s">
         <v>204</v>
-      </c>
-      <c r="G102" t="s">
-        <v>184</v>
       </c>
     </row>
     <row r="103" spans="1:7">
@@ -4115,10 +4115,10 @@
         <v>203</v>
       </c>
       <c r="F103" t="s">
+        <v>183</v>
+      </c>
+      <c r="G103" t="s">
         <v>204</v>
-      </c>
-      <c r="G103" t="s">
-        <v>184</v>
       </c>
     </row>
     <row r="104" spans="1:7">
@@ -4135,10 +4135,10 @@
         <v>203</v>
       </c>
       <c r="F104" t="s">
+        <v>183</v>
+      </c>
+      <c r="G104" t="s">
         <v>204</v>
-      </c>
-      <c r="G104" t="s">
-        <v>184</v>
       </c>
     </row>
     <row r="105" spans="1:7">
@@ -4155,10 +4155,10 @@
         <v>203</v>
       </c>
       <c r="F105" t="s">
+        <v>183</v>
+      </c>
+      <c r="G105" t="s">
         <v>209</v>
-      </c>
-      <c r="G105" t="s">
-        <v>184</v>
       </c>
     </row>
     <row r="106" spans="1:7">
@@ -4175,10 +4175,10 @@
         <v>203</v>
       </c>
       <c r="F106" t="s">
+        <v>183</v>
+      </c>
+      <c r="G106" t="s">
         <v>204</v>
-      </c>
-      <c r="G106" t="s">
-        <v>184</v>
       </c>
     </row>
     <row r="107" spans="1:7">
@@ -4215,10 +4215,10 @@
         <v>203</v>
       </c>
       <c r="F108" t="s">
+        <v>183</v>
+      </c>
+      <c r="G108" t="s">
         <v>214</v>
-      </c>
-      <c r="G108" t="s">
-        <v>184</v>
       </c>
     </row>
     <row r="109" spans="1:7">
@@ -4235,10 +4235,10 @@
         <v>203</v>
       </c>
       <c r="F109" t="s">
+        <v>92</v>
+      </c>
+      <c r="G109" t="s">
         <v>217</v>
-      </c>
-      <c r="G109" t="s">
-        <v>93</v>
       </c>
     </row>
     <row r="110" spans="1:7">
@@ -4255,10 +4255,10 @@
         <v>203</v>
       </c>
       <c r="F110" t="s">
+        <v>92</v>
+      </c>
+      <c r="G110" t="s">
         <v>220</v>
-      </c>
-      <c r="G110" t="s">
-        <v>93</v>
       </c>
     </row>
     <row r="111" spans="1:7">
@@ -4275,10 +4275,10 @@
         <v>203</v>
       </c>
       <c r="F111" t="s">
+        <v>183</v>
+      </c>
+      <c r="G111" t="s">
         <v>204</v>
-      </c>
-      <c r="G111" t="s">
-        <v>184</v>
       </c>
     </row>
     <row r="112" spans="1:7">
@@ -4309,13 +4309,13 @@
         <v>8</v>
       </c>
       <c r="C113" t="s">
-        <v>112</v>
+        <v>143</v>
       </c>
       <c r="E113" t="s">
         <v>203</v>
       </c>
       <c r="F113" t="s">
-        <v>143</v>
+        <v>115</v>
       </c>
       <c r="G113" t="s">
         <v>116</v>
@@ -4335,10 +4335,10 @@
         <v>203</v>
       </c>
       <c r="F114" t="s">
+        <v>125</v>
+      </c>
+      <c r="G114" t="s">
         <v>152</v>
-      </c>
-      <c r="G114" t="s">
-        <v>126</v>
       </c>
     </row>
     <row r="115" spans="1:7">
@@ -4375,10 +4375,10 @@
         <v>203</v>
       </c>
       <c r="F116" t="s">
+        <v>224</v>
+      </c>
+      <c r="G116" t="s">
         <v>231</v>
-      </c>
-      <c r="G116" t="s">
-        <v>225</v>
       </c>
     </row>
     <row r="117" spans="1:7">
@@ -4409,13 +4409,13 @@
         <v>8</v>
       </c>
       <c r="C118" t="s">
-        <v>163</v>
+        <v>234</v>
       </c>
       <c r="E118" t="s">
         <v>203</v>
       </c>
       <c r="F118" t="s">
-        <v>234</v>
+        <v>164</v>
       </c>
       <c r="G118" t="s">
         <v>165</v>
@@ -4455,10 +4455,10 @@
         <v>237</v>
       </c>
       <c r="F120" t="s">
+        <v>115</v>
+      </c>
+      <c r="G120" t="s">
         <v>171</v>
-      </c>
-      <c r="G120" t="s">
-        <v>116</v>
       </c>
     </row>
     <row r="121" spans="1:7">
@@ -4469,13 +4469,13 @@
         <v>8</v>
       </c>
       <c r="C121" t="s">
-        <v>112</v>
+        <v>143</v>
       </c>
       <c r="E121" t="s">
         <v>237</v>
       </c>
       <c r="F121" t="s">
-        <v>143</v>
+        <v>115</v>
       </c>
       <c r="G121" t="s">
         <v>116</v>
@@ -4495,10 +4495,10 @@
         <v>237</v>
       </c>
       <c r="F122" t="s">
+        <v>115</v>
+      </c>
+      <c r="G122" t="s">
         <v>171</v>
-      </c>
-      <c r="G122" t="s">
-        <v>116</v>
       </c>
     </row>
     <row r="123" spans="1:7">
@@ -4515,10 +4515,10 @@
         <v>237</v>
       </c>
       <c r="F123" t="s">
+        <v>115</v>
+      </c>
+      <c r="G123" t="s">
         <v>171</v>
-      </c>
-      <c r="G123" t="s">
-        <v>116</v>
       </c>
     </row>
     <row r="124" spans="1:7">
@@ -4535,10 +4535,10 @@
         <v>237</v>
       </c>
       <c r="F124" t="s">
+        <v>164</v>
+      </c>
+      <c r="G124" t="s">
         <v>243</v>
-      </c>
-      <c r="G124" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="125" spans="1:7">
@@ -4555,10 +4555,10 @@
         <v>237</v>
       </c>
       <c r="F125" t="s">
+        <v>164</v>
+      </c>
+      <c r="G125" t="s">
         <v>243</v>
-      </c>
-      <c r="G125" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="126" spans="1:7">
@@ -4575,10 +4575,10 @@
         <v>237</v>
       </c>
       <c r="F126" t="s">
+        <v>164</v>
+      </c>
+      <c r="G126" t="s">
         <v>243</v>
-      </c>
-      <c r="G126" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="127" spans="1:7">
@@ -4595,10 +4595,10 @@
         <v>237</v>
       </c>
       <c r="F127" t="s">
+        <v>164</v>
+      </c>
+      <c r="G127" t="s">
         <v>243</v>
-      </c>
-      <c r="G127" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="128" spans="1:7">
@@ -4615,10 +4615,10 @@
         <v>237</v>
       </c>
       <c r="F128" t="s">
+        <v>164</v>
+      </c>
+      <c r="G128" t="s">
         <v>243</v>
-      </c>
-      <c r="G128" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="129" spans="1:7">
@@ -4629,16 +4629,16 @@
         <v>8</v>
       </c>
       <c r="C129" t="s">
-        <v>242</v>
+        <v>249</v>
       </c>
       <c r="E129" t="s">
         <v>237</v>
       </c>
       <c r="F129" t="s">
-        <v>249</v>
+        <v>164</v>
       </c>
       <c r="G129" t="s">
-        <v>165</v>
+        <v>243</v>
       </c>
     </row>
     <row r="130" spans="1:7">
@@ -4649,16 +4649,16 @@
         <v>8</v>
       </c>
       <c r="C130" t="s">
-        <v>242</v>
+        <v>251</v>
       </c>
       <c r="E130" t="s">
         <v>237</v>
       </c>
       <c r="F130" t="s">
-        <v>251</v>
+        <v>164</v>
       </c>
       <c r="G130" t="s">
-        <v>165</v>
+        <v>243</v>
       </c>
     </row>
     <row r="131" spans="1:7">
@@ -4669,16 +4669,16 @@
         <v>8</v>
       </c>
       <c r="C131" t="s">
-        <v>242</v>
+        <v>253</v>
       </c>
       <c r="E131" t="s">
         <v>237</v>
       </c>
       <c r="F131" t="s">
-        <v>253</v>
+        <v>164</v>
       </c>
       <c r="G131" t="s">
-        <v>165</v>
+        <v>243</v>
       </c>
     </row>
     <row r="132" spans="1:7">
@@ -4695,10 +4695,10 @@
         <v>237</v>
       </c>
       <c r="F132" t="s">
+        <v>164</v>
+      </c>
+      <c r="G132" t="s">
         <v>256</v>
-      </c>
-      <c r="G132" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="133" spans="1:7">
@@ -4715,10 +4715,10 @@
         <v>237</v>
       </c>
       <c r="F133" t="s">
+        <v>115</v>
+      </c>
+      <c r="G133" t="s">
         <v>190</v>
-      </c>
-      <c r="G133" t="s">
-        <v>116</v>
       </c>
     </row>
     <row r="134" spans="1:7">
@@ -4735,10 +4735,10 @@
         <v>259</v>
       </c>
       <c r="F134" t="s">
+        <v>164</v>
+      </c>
+      <c r="G134" t="s">
         <v>176</v>
-      </c>
-      <c r="G134" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="135" spans="1:7">
@@ -4755,10 +4755,10 @@
         <v>259</v>
       </c>
       <c r="F135" t="s">
+        <v>164</v>
+      </c>
+      <c r="G135" t="s">
         <v>176</v>
-      </c>
-      <c r="G135" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="136" spans="1:7">
@@ -4775,10 +4775,10 @@
         <v>259</v>
       </c>
       <c r="F136" t="s">
+        <v>164</v>
+      </c>
+      <c r="G136" t="s">
         <v>176</v>
-      </c>
-      <c r="G136" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="137" spans="1:7">
@@ -4795,10 +4795,10 @@
         <v>259</v>
       </c>
       <c r="F137" t="s">
+        <v>164</v>
+      </c>
+      <c r="G137" t="s">
         <v>176</v>
-      </c>
-      <c r="G137" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="138" spans="1:7">
@@ -4815,10 +4815,10 @@
         <v>259</v>
       </c>
       <c r="F138" t="s">
+        <v>164</v>
+      </c>
+      <c r="G138" t="s">
         <v>176</v>
-      </c>
-      <c r="G138" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="139" spans="1:7">
@@ -4835,10 +4835,10 @@
         <v>259</v>
       </c>
       <c r="F139" t="s">
+        <v>224</v>
+      </c>
+      <c r="G139" t="s">
         <v>266</v>
-      </c>
-      <c r="G139" t="s">
-        <v>225</v>
       </c>
     </row>
     <row r="140" spans="1:7">
@@ -4855,10 +4855,10 @@
         <v>259</v>
       </c>
       <c r="F140" t="s">
+        <v>164</v>
+      </c>
+      <c r="G140" t="s">
         <v>176</v>
-      </c>
-      <c r="G140" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="141" spans="1:7">
@@ -4878,10 +4878,10 @@
         <v>271</v>
       </c>
       <c r="F141" t="s">
+        <v>164</v>
+      </c>
+      <c r="G141" t="s">
         <v>272</v>
-      </c>
-      <c r="G141" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="142" spans="1:7">
@@ -4901,10 +4901,10 @@
         <v>271</v>
       </c>
       <c r="F142" t="s">
+        <v>164</v>
+      </c>
+      <c r="G142" t="s">
         <v>272</v>
-      </c>
-      <c r="G142" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="143" spans="1:7">
@@ -4924,10 +4924,10 @@
         <v>271</v>
       </c>
       <c r="F143" t="s">
+        <v>164</v>
+      </c>
+      <c r="G143" t="s">
         <v>276</v>
-      </c>
-      <c r="G143" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="144" spans="1:7">
@@ -4947,10 +4947,10 @@
         <v>271</v>
       </c>
       <c r="F144" t="s">
+        <v>164</v>
+      </c>
+      <c r="G144" t="s">
         <v>276</v>
-      </c>
-      <c r="G144" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="145" spans="1:7">
@@ -4970,10 +4970,10 @@
         <v>271</v>
       </c>
       <c r="F145" t="s">
+        <v>164</v>
+      </c>
+      <c r="G145" t="s">
         <v>276</v>
-      </c>
-      <c r="G145" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="146" spans="1:7">
@@ -4993,10 +4993,10 @@
         <v>271</v>
       </c>
       <c r="F146" t="s">
+        <v>164</v>
+      </c>
+      <c r="G146" t="s">
         <v>272</v>
-      </c>
-      <c r="G146" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="147" spans="1:7">
@@ -5016,10 +5016,10 @@
         <v>271</v>
       </c>
       <c r="F147" t="s">
+        <v>164</v>
+      </c>
+      <c r="G147" t="s">
         <v>272</v>
-      </c>
-      <c r="G147" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="148" spans="1:7">
@@ -5039,10 +5039,10 @@
         <v>271</v>
       </c>
       <c r="F148" t="s">
+        <v>164</v>
+      </c>
+      <c r="G148" t="s">
         <v>272</v>
-      </c>
-      <c r="G148" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="149" spans="1:7">
@@ -5062,10 +5062,10 @@
         <v>271</v>
       </c>
       <c r="F149" t="s">
+        <v>164</v>
+      </c>
+      <c r="G149" t="s">
         <v>272</v>
-      </c>
-      <c r="G149" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="150" spans="1:7">
@@ -5085,10 +5085,10 @@
         <v>271</v>
       </c>
       <c r="F150" t="s">
+        <v>164</v>
+      </c>
+      <c r="G150" t="s">
         <v>272</v>
-      </c>
-      <c r="G150" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="151" spans="1:7">
@@ -5108,10 +5108,10 @@
         <v>271</v>
       </c>
       <c r="F151" t="s">
+        <v>164</v>
+      </c>
+      <c r="G151" t="s">
         <v>272</v>
-      </c>
-      <c r="G151" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="152" spans="1:7">
@@ -5131,10 +5131,10 @@
         <v>271</v>
       </c>
       <c r="F152" t="s">
+        <v>164</v>
+      </c>
+      <c r="G152" t="s">
         <v>272</v>
-      </c>
-      <c r="G152" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="153" spans="1:7">
@@ -5154,10 +5154,10 @@
         <v>271</v>
       </c>
       <c r="F153" t="s">
+        <v>164</v>
+      </c>
+      <c r="G153" t="s">
         <v>272</v>
-      </c>
-      <c r="G153" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="154" spans="1:7">
@@ -5177,10 +5177,10 @@
         <v>271</v>
       </c>
       <c r="F154" t="s">
+        <v>164</v>
+      </c>
+      <c r="G154" t="s">
         <v>272</v>
-      </c>
-      <c r="G154" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="155" spans="1:7">
@@ -5200,10 +5200,10 @@
         <v>271</v>
       </c>
       <c r="F155" t="s">
+        <v>164</v>
+      </c>
+      <c r="G155" t="s">
         <v>272</v>
-      </c>
-      <c r="G155" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="156" spans="1:7">
@@ -5223,10 +5223,10 @@
         <v>271</v>
       </c>
       <c r="F156" t="s">
+        <v>164</v>
+      </c>
+      <c r="G156" t="s">
         <v>272</v>
-      </c>
-      <c r="G156" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="157" spans="1:7">
@@ -5237,7 +5237,7 @@
         <v>8</v>
       </c>
       <c r="C157" t="s">
-        <v>269</v>
+        <v>293</v>
       </c>
       <c r="D157" t="s">
         <v>291</v>
@@ -5246,10 +5246,10 @@
         <v>271</v>
       </c>
       <c r="F157" t="s">
-        <v>293</v>
+        <v>164</v>
       </c>
       <c r="G157" t="s">
-        <v>165</v>
+        <v>272</v>
       </c>
     </row>
     <row r="158" spans="1:7">
@@ -5269,10 +5269,10 @@
         <v>271</v>
       </c>
       <c r="F158" t="s">
+        <v>164</v>
+      </c>
+      <c r="G158" t="s">
         <v>272</v>
-      </c>
-      <c r="G158" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="159" spans="1:7">
@@ -5292,10 +5292,10 @@
         <v>271</v>
       </c>
       <c r="F159" t="s">
+        <v>164</v>
+      </c>
+      <c r="G159" t="s">
         <v>272</v>
-      </c>
-      <c r="G159" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="160" spans="1:7">
@@ -5315,10 +5315,10 @@
         <v>271</v>
       </c>
       <c r="F160" t="s">
+        <v>164</v>
+      </c>
+      <c r="G160" t="s">
         <v>272</v>
-      </c>
-      <c r="G160" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="161" spans="1:7">
@@ -5338,10 +5338,10 @@
         <v>271</v>
       </c>
       <c r="F161" t="s">
+        <v>164</v>
+      </c>
+      <c r="G161" t="s">
         <v>272</v>
-      </c>
-      <c r="G161" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="162" spans="1:7">
@@ -5361,10 +5361,10 @@
         <v>271</v>
       </c>
       <c r="F162" t="s">
+        <v>164</v>
+      </c>
+      <c r="G162" t="s">
         <v>272</v>
-      </c>
-      <c r="G162" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="163" spans="1:7">
@@ -5375,19 +5375,19 @@
         <v>8</v>
       </c>
       <c r="C163" t="s">
-        <v>269</v>
+        <v>301</v>
       </c>
       <c r="D163" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="E163" t="s">
         <v>271</v>
       </c>
       <c r="F163" t="s">
-        <v>302</v>
+        <v>164</v>
       </c>
       <c r="G163" t="s">
-        <v>165</v>
+        <v>272</v>
       </c>
     </row>
     <row r="164" spans="1:7">
@@ -5407,10 +5407,10 @@
         <v>271</v>
       </c>
       <c r="F164" t="s">
+        <v>164</v>
+      </c>
+      <c r="G164" t="s">
         <v>272</v>
-      </c>
-      <c r="G164" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="165" spans="1:7">
@@ -5430,10 +5430,10 @@
         <v>271</v>
       </c>
       <c r="F165" t="s">
+        <v>164</v>
+      </c>
+      <c r="G165" t="s">
         <v>272</v>
-      </c>
-      <c r="G165" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="166" spans="1:7">
@@ -5453,10 +5453,10 @@
         <v>271</v>
       </c>
       <c r="F166" t="s">
+        <v>164</v>
+      </c>
+      <c r="G166" t="s">
         <v>272</v>
-      </c>
-      <c r="G166" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="167" spans="1:7">
@@ -5476,10 +5476,10 @@
         <v>271</v>
       </c>
       <c r="F167" t="s">
+        <v>164</v>
+      </c>
+      <c r="G167" t="s">
         <v>272</v>
-      </c>
-      <c r="G167" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="168" spans="1:7">
@@ -5490,7 +5490,7 @@
         <v>8</v>
       </c>
       <c r="C168" t="s">
-        <v>269</v>
+        <v>309</v>
       </c>
       <c r="D168" t="s">
         <v>304</v>
@@ -5499,10 +5499,10 @@
         <v>271</v>
       </c>
       <c r="F168" t="s">
-        <v>309</v>
+        <v>164</v>
       </c>
       <c r="G168" t="s">
-        <v>165</v>
+        <v>272</v>
       </c>
     </row>
     <row r="169" spans="1:7">
@@ -5513,7 +5513,7 @@
         <v>8</v>
       </c>
       <c r="C169" t="s">
-        <v>269</v>
+        <v>309</v>
       </c>
       <c r="D169" t="s">
         <v>304</v>
@@ -5522,10 +5522,10 @@
         <v>271</v>
       </c>
       <c r="F169" t="s">
-        <v>309</v>
+        <v>164</v>
       </c>
       <c r="G169" t="s">
-        <v>165</v>
+        <v>272</v>
       </c>
     </row>
     <row r="170" spans="1:7">
@@ -5545,10 +5545,10 @@
         <v>271</v>
       </c>
       <c r="F170" t="s">
+        <v>164</v>
+      </c>
+      <c r="G170" t="s">
         <v>272</v>
-      </c>
-      <c r="G170" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="171" spans="1:7">
@@ -5585,10 +5585,10 @@
         <v>313</v>
       </c>
       <c r="F172" t="s">
+        <v>115</v>
+      </c>
+      <c r="G172" t="s">
         <v>119</v>
-      </c>
-      <c r="G172" t="s">
-        <v>116</v>
       </c>
     </row>
     <row r="173" spans="1:7">
@@ -5768,10 +5768,10 @@
         <v>327</v>
       </c>
       <c r="F181" t="s">
+        <v>164</v>
+      </c>
+      <c r="G181" t="s">
         <v>328</v>
-      </c>
-      <c r="G181" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="182" spans="1:7">
@@ -5791,10 +5791,10 @@
         <v>327</v>
       </c>
       <c r="F182" t="s">
+        <v>164</v>
+      </c>
+      <c r="G182" t="s">
         <v>328</v>
-      </c>
-      <c r="G182" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="183" spans="1:7">
@@ -5814,10 +5814,10 @@
         <v>327</v>
       </c>
       <c r="F183" t="s">
+        <v>164</v>
+      </c>
+      <c r="G183" t="s">
         <v>328</v>
-      </c>
-      <c r="G183" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="184" spans="1:7">
@@ -5837,10 +5837,10 @@
         <v>327</v>
       </c>
       <c r="F184" t="s">
+        <v>164</v>
+      </c>
+      <c r="G184" t="s">
         <v>328</v>
-      </c>
-      <c r="G184" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="185" spans="1:7">
@@ -5860,10 +5860,10 @@
         <v>327</v>
       </c>
       <c r="F185" t="s">
+        <v>164</v>
+      </c>
+      <c r="G185" t="s">
         <v>328</v>
-      </c>
-      <c r="G185" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="186" spans="1:7">
@@ -5883,10 +5883,10 @@
         <v>327</v>
       </c>
       <c r="F186" t="s">
+        <v>164</v>
+      </c>
+      <c r="G186" t="s">
         <v>328</v>
-      </c>
-      <c r="G186" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="187" spans="1:7">
@@ -5906,10 +5906,10 @@
         <v>327</v>
       </c>
       <c r="F187" t="s">
+        <v>164</v>
+      </c>
+      <c r="G187" t="s">
         <v>328</v>
-      </c>
-      <c r="G187" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="188" spans="1:7">
@@ -5929,10 +5929,10 @@
         <v>327</v>
       </c>
       <c r="F188" t="s">
+        <v>164</v>
+      </c>
+      <c r="G188" t="s">
         <v>328</v>
-      </c>
-      <c r="G188" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="189" spans="1:7">
@@ -5952,10 +5952,10 @@
         <v>327</v>
       </c>
       <c r="F189" t="s">
+        <v>164</v>
+      </c>
+      <c r="G189" t="s">
         <v>328</v>
-      </c>
-      <c r="G189" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="190" spans="1:7">
@@ -5975,10 +5975,10 @@
         <v>327</v>
       </c>
       <c r="F190" t="s">
+        <v>164</v>
+      </c>
+      <c r="G190" t="s">
         <v>328</v>
-      </c>
-      <c r="G190" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="191" spans="1:7">
@@ -5998,10 +5998,10 @@
         <v>327</v>
       </c>
       <c r="F191" t="s">
+        <v>164</v>
+      </c>
+      <c r="G191" t="s">
         <v>328</v>
-      </c>
-      <c r="G191" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="192" spans="1:7">
@@ -6021,10 +6021,10 @@
         <v>327</v>
       </c>
       <c r="F192" t="s">
+        <v>164</v>
+      </c>
+      <c r="G192" t="s">
         <v>328</v>
-      </c>
-      <c r="G192" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="193" spans="1:7">
@@ -6035,7 +6035,7 @@
         <v>8</v>
       </c>
       <c r="C193" t="s">
-        <v>275</v>
+        <v>341</v>
       </c>
       <c r="D193" t="s">
         <v>326</v>
@@ -6044,10 +6044,10 @@
         <v>327</v>
       </c>
       <c r="F193" t="s">
-        <v>341</v>
+        <v>164</v>
       </c>
       <c r="G193" t="s">
-        <v>165</v>
+        <v>276</v>
       </c>
     </row>
     <row r="194" spans="1:7">
@@ -6067,10 +6067,10 @@
         <v>327</v>
       </c>
       <c r="F194" t="s">
+        <v>164</v>
+      </c>
+      <c r="G194" t="s">
         <v>328</v>
-      </c>
-      <c r="G194" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="195" spans="1:7">
@@ -6090,10 +6090,10 @@
         <v>327</v>
       </c>
       <c r="F195" t="s">
+        <v>164</v>
+      </c>
+      <c r="G195" t="s">
         <v>328</v>
-      </c>
-      <c r="G195" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="196" spans="1:7">
@@ -6113,10 +6113,10 @@
         <v>327</v>
       </c>
       <c r="F196" t="s">
+        <v>164</v>
+      </c>
+      <c r="G196" t="s">
         <v>328</v>
-      </c>
-      <c r="G196" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="197" spans="1:7">
@@ -6136,10 +6136,10 @@
         <v>327</v>
       </c>
       <c r="F197" t="s">
+        <v>164</v>
+      </c>
+      <c r="G197" t="s">
         <v>328</v>
-      </c>
-      <c r="G197" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="198" spans="1:7">
@@ -6159,10 +6159,10 @@
         <v>327</v>
       </c>
       <c r="F198" t="s">
+        <v>164</v>
+      </c>
+      <c r="G198" t="s">
         <v>328</v>
-      </c>
-      <c r="G198" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="199" spans="1:7">
@@ -6173,19 +6173,19 @@
         <v>8</v>
       </c>
       <c r="C199" t="s">
-        <v>325</v>
+        <v>348</v>
       </c>
       <c r="D199" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="E199" t="s">
         <v>327</v>
       </c>
       <c r="F199" t="s">
-        <v>349</v>
+        <v>164</v>
       </c>
       <c r="G199" t="s">
-        <v>165</v>
+        <v>328</v>
       </c>
     </row>
     <row r="200" spans="1:7">
@@ -6196,19 +6196,19 @@
         <v>8</v>
       </c>
       <c r="C200" t="s">
-        <v>325</v>
+        <v>348</v>
       </c>
       <c r="D200" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="E200" t="s">
         <v>327</v>
       </c>
       <c r="F200" t="s">
-        <v>349</v>
+        <v>164</v>
       </c>
       <c r="G200" t="s">
-        <v>165</v>
+        <v>328</v>
       </c>
     </row>
     <row r="201" spans="1:7">
@@ -6219,19 +6219,19 @@
         <v>8</v>
       </c>
       <c r="C201" t="s">
-        <v>325</v>
+        <v>348</v>
       </c>
       <c r="D201" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="E201" t="s">
         <v>327</v>
       </c>
       <c r="F201" t="s">
-        <v>349</v>
+        <v>164</v>
       </c>
       <c r="G201" t="s">
-        <v>165</v>
+        <v>328</v>
       </c>
     </row>
     <row r="202" spans="1:7">
@@ -6242,19 +6242,19 @@
         <v>8</v>
       </c>
       <c r="C202" t="s">
-        <v>325</v>
+        <v>348</v>
       </c>
       <c r="D202" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="E202" t="s">
         <v>327</v>
       </c>
       <c r="F202" t="s">
-        <v>349</v>
+        <v>164</v>
       </c>
       <c r="G202" t="s">
-        <v>165</v>
+        <v>328</v>
       </c>
     </row>
     <row r="203" spans="1:7">
@@ -6265,19 +6265,19 @@
         <v>8</v>
       </c>
       <c r="C203" t="s">
-        <v>275</v>
+        <v>341</v>
       </c>
       <c r="D203" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="E203" t="s">
         <v>327</v>
       </c>
       <c r="F203" t="s">
-        <v>341</v>
+        <v>164</v>
       </c>
       <c r="G203" t="s">
-        <v>165</v>
+        <v>276</v>
       </c>
     </row>
     <row r="204" spans="1:7">
@@ -6288,19 +6288,19 @@
         <v>8</v>
       </c>
       <c r="C204" t="s">
-        <v>325</v>
+        <v>348</v>
       </c>
       <c r="D204" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="E204" t="s">
         <v>327</v>
       </c>
       <c r="F204" t="s">
-        <v>349</v>
+        <v>164</v>
       </c>
       <c r="G204" t="s">
-        <v>165</v>
+        <v>328</v>
       </c>
     </row>
     <row r="205" spans="1:7">
@@ -6311,19 +6311,19 @@
         <v>8</v>
       </c>
       <c r="C205" t="s">
-        <v>325</v>
+        <v>356</v>
       </c>
       <c r="D205" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="E205" t="s">
         <v>327</v>
       </c>
       <c r="F205" t="s">
-        <v>357</v>
+        <v>164</v>
       </c>
       <c r="G205" t="s">
-        <v>165</v>
+        <v>328</v>
       </c>
     </row>
     <row r="206" spans="1:7">
@@ -6334,19 +6334,19 @@
         <v>8</v>
       </c>
       <c r="C206" t="s">
-        <v>325</v>
+        <v>356</v>
       </c>
       <c r="D206" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="E206" t="s">
         <v>327</v>
       </c>
       <c r="F206" t="s">
-        <v>357</v>
+        <v>164</v>
       </c>
       <c r="G206" t="s">
-        <v>165</v>
+        <v>328</v>
       </c>
     </row>
     <row r="207" spans="1:7">
@@ -6357,19 +6357,19 @@
         <v>8</v>
       </c>
       <c r="C207" t="s">
-        <v>325</v>
+        <v>356</v>
       </c>
       <c r="D207" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="E207" t="s">
         <v>327</v>
       </c>
       <c r="F207" t="s">
-        <v>357</v>
+        <v>164</v>
       </c>
       <c r="G207" t="s">
-        <v>165</v>
+        <v>328</v>
       </c>
     </row>
     <row r="208" spans="1:7">
@@ -6380,19 +6380,19 @@
         <v>8</v>
       </c>
       <c r="C208" t="s">
-        <v>275</v>
+        <v>341</v>
       </c>
       <c r="D208" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="E208" t="s">
         <v>327</v>
       </c>
       <c r="F208" t="s">
-        <v>341</v>
+        <v>164</v>
       </c>
       <c r="G208" t="s">
-        <v>165</v>
+        <v>276</v>
       </c>
     </row>
     <row r="209" spans="1:7">
@@ -6403,19 +6403,19 @@
         <v>8</v>
       </c>
       <c r="C209" t="s">
-        <v>325</v>
+        <v>356</v>
       </c>
       <c r="D209" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="E209" t="s">
         <v>327</v>
       </c>
       <c r="F209" t="s">
-        <v>357</v>
+        <v>164</v>
       </c>
       <c r="G209" t="s">
-        <v>165</v>
+        <v>328</v>
       </c>
     </row>
     <row r="210" spans="1:7">
@@ -6435,10 +6435,10 @@
         <v>365</v>
       </c>
       <c r="F210" t="s">
+        <v>164</v>
+      </c>
+      <c r="G210" t="s">
         <v>366</v>
-      </c>
-      <c r="G210" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="211" spans="1:7">
@@ -6458,10 +6458,10 @@
         <v>365</v>
       </c>
       <c r="F211" t="s">
+        <v>164</v>
+      </c>
+      <c r="G211" t="s">
         <v>366</v>
-      </c>
-      <c r="G211" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="212" spans="1:7">
@@ -6481,10 +6481,10 @@
         <v>365</v>
       </c>
       <c r="F212" t="s">
+        <v>164</v>
+      </c>
+      <c r="G212" t="s">
         <v>366</v>
-      </c>
-      <c r="G212" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="213" spans="1:7">
@@ -6504,10 +6504,10 @@
         <v>365</v>
       </c>
       <c r="F213" t="s">
+        <v>164</v>
+      </c>
+      <c r="G213" t="s">
         <v>366</v>
-      </c>
-      <c r="G213" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="214" spans="1:7">
@@ -6527,10 +6527,10 @@
         <v>365</v>
       </c>
       <c r="F214" t="s">
+        <v>164</v>
+      </c>
+      <c r="G214" t="s">
         <v>366</v>
-      </c>
-      <c r="G214" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="215" spans="1:7">
@@ -6541,7 +6541,7 @@
         <v>8</v>
       </c>
       <c r="C215" t="s">
-        <v>325</v>
+        <v>348</v>
       </c>
       <c r="D215" t="s">
         <v>364</v>
@@ -6550,10 +6550,10 @@
         <v>365</v>
       </c>
       <c r="F215" t="s">
-        <v>349</v>
+        <v>164</v>
       </c>
       <c r="G215" t="s">
-        <v>165</v>
+        <v>328</v>
       </c>
     </row>
     <row r="216" spans="1:7">
@@ -6573,10 +6573,10 @@
         <v>365</v>
       </c>
       <c r="F216" t="s">
+        <v>164</v>
+      </c>
+      <c r="G216" t="s">
         <v>366</v>
-      </c>
-      <c r="G216" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="217" spans="1:7">
@@ -6596,10 +6596,10 @@
         <v>365</v>
       </c>
       <c r="F217" t="s">
+        <v>164</v>
+      </c>
+      <c r="G217" t="s">
         <v>366</v>
-      </c>
-      <c r="G217" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="218" spans="1:7">
@@ -6619,10 +6619,10 @@
         <v>365</v>
       </c>
       <c r="F218" t="s">
+        <v>164</v>
+      </c>
+      <c r="G218" t="s">
         <v>366</v>
-      </c>
-      <c r="G218" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="219" spans="1:7">
@@ -6642,10 +6642,10 @@
         <v>365</v>
       </c>
       <c r="F219" t="s">
+        <v>164</v>
+      </c>
+      <c r="G219" t="s">
         <v>366</v>
-      </c>
-      <c r="G219" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="220" spans="1:7">
@@ -6656,7 +6656,7 @@
         <v>8</v>
       </c>
       <c r="C220" t="s">
-        <v>269</v>
+        <v>309</v>
       </c>
       <c r="D220" t="s">
         <v>364</v>
@@ -6665,10 +6665,10 @@
         <v>365</v>
       </c>
       <c r="F220" t="s">
-        <v>309</v>
+        <v>164</v>
       </c>
       <c r="G220" t="s">
-        <v>165</v>
+        <v>272</v>
       </c>
     </row>
     <row r="221" spans="1:7">
@@ -6688,10 +6688,10 @@
         <v>365</v>
       </c>
       <c r="F221" t="s">
+        <v>164</v>
+      </c>
+      <c r="G221" t="s">
         <v>366</v>
-      </c>
-      <c r="G221" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="222" spans="1:7">
@@ -6711,10 +6711,10 @@
         <v>365</v>
       </c>
       <c r="F222" t="s">
+        <v>164</v>
+      </c>
+      <c r="G222" t="s">
         <v>366</v>
-      </c>
-      <c r="G222" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="223" spans="1:7">
@@ -6734,10 +6734,10 @@
         <v>365</v>
       </c>
       <c r="F223" t="s">
+        <v>164</v>
+      </c>
+      <c r="G223" t="s">
         <v>366</v>
-      </c>
-      <c r="G223" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="224" spans="1:7">
@@ -6757,10 +6757,10 @@
         <v>365</v>
       </c>
       <c r="F224" t="s">
+        <v>164</v>
+      </c>
+      <c r="G224" t="s">
         <v>366</v>
-      </c>
-      <c r="G224" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="225" spans="1:7">
@@ -6780,10 +6780,10 @@
         <v>365</v>
       </c>
       <c r="F225" t="s">
+        <v>164</v>
+      </c>
+      <c r="G225" t="s">
         <v>366</v>
-      </c>
-      <c r="G225" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="226" spans="1:7">
@@ -6803,10 +6803,10 @@
         <v>365</v>
       </c>
       <c r="F226" t="s">
+        <v>164</v>
+      </c>
+      <c r="G226" t="s">
         <v>276</v>
-      </c>
-      <c r="G226" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="227" spans="1:7">
@@ -6826,10 +6826,10 @@
         <v>365</v>
       </c>
       <c r="F227" t="s">
+        <v>164</v>
+      </c>
+      <c r="G227" t="s">
         <v>366</v>
-      </c>
-      <c r="G227" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="228" spans="1:7">
@@ -6863,19 +6863,19 @@
         <v>8</v>
       </c>
       <c r="C229" t="s">
-        <v>363</v>
+        <v>386</v>
       </c>
       <c r="D229" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="E229" t="s">
         <v>365</v>
       </c>
       <c r="F229" t="s">
-        <v>387</v>
+        <v>164</v>
       </c>
       <c r="G229" t="s">
-        <v>165</v>
+        <v>366</v>
       </c>
     </row>
     <row r="230" spans="1:7">
@@ -6886,19 +6886,19 @@
         <v>8</v>
       </c>
       <c r="C230" t="s">
-        <v>363</v>
+        <v>386</v>
       </c>
       <c r="D230" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="E230" t="s">
         <v>365</v>
       </c>
       <c r="F230" t="s">
-        <v>387</v>
+        <v>164</v>
       </c>
       <c r="G230" t="s">
-        <v>165</v>
+        <v>366</v>
       </c>
     </row>
     <row r="231" spans="1:7">
@@ -6909,19 +6909,19 @@
         <v>8</v>
       </c>
       <c r="C231" t="s">
-        <v>269</v>
+        <v>293</v>
       </c>
       <c r="D231" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="E231" t="s">
         <v>365</v>
       </c>
       <c r="F231" t="s">
-        <v>293</v>
+        <v>164</v>
       </c>
       <c r="G231" t="s">
-        <v>165</v>
+        <v>272</v>
       </c>
     </row>
     <row r="232" spans="1:7">
@@ -6932,19 +6932,19 @@
         <v>8</v>
       </c>
       <c r="C232" t="s">
-        <v>269</v>
+        <v>309</v>
       </c>
       <c r="D232" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="E232" t="s">
         <v>365</v>
       </c>
       <c r="F232" t="s">
-        <v>309</v>
+        <v>164</v>
       </c>
       <c r="G232" t="s">
-        <v>165</v>
+        <v>272</v>
       </c>
     </row>
     <row r="233" spans="1:7">
@@ -6955,19 +6955,19 @@
         <v>8</v>
       </c>
       <c r="C233" t="s">
-        <v>363</v>
+        <v>386</v>
       </c>
       <c r="D233" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="E233" t="s">
         <v>365</v>
       </c>
       <c r="F233" t="s">
-        <v>387</v>
+        <v>164</v>
       </c>
       <c r="G233" t="s">
-        <v>165</v>
+        <v>366</v>
       </c>
     </row>
     <row r="234" spans="1:7">
@@ -6978,19 +6978,19 @@
         <v>8</v>
       </c>
       <c r="C234" t="s">
-        <v>363</v>
+        <v>386</v>
       </c>
       <c r="D234" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="E234" t="s">
         <v>365</v>
       </c>
       <c r="F234" t="s">
-        <v>387</v>
+        <v>164</v>
       </c>
       <c r="G234" t="s">
-        <v>165</v>
+        <v>366</v>
       </c>
     </row>
     <row r="235" spans="1:7">
@@ -7001,19 +7001,19 @@
         <v>8</v>
       </c>
       <c r="C235" t="s">
-        <v>363</v>
+        <v>386</v>
       </c>
       <c r="D235" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="E235" t="s">
         <v>365</v>
       </c>
       <c r="F235" t="s">
-        <v>387</v>
+        <v>164</v>
       </c>
       <c r="G235" t="s">
-        <v>165</v>
+        <v>366</v>
       </c>
     </row>
     <row r="236" spans="1:7">
@@ -7024,19 +7024,19 @@
         <v>8</v>
       </c>
       <c r="C236" t="s">
-        <v>363</v>
+        <v>386</v>
       </c>
       <c r="D236" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="E236" t="s">
         <v>365</v>
       </c>
       <c r="F236" t="s">
-        <v>387</v>
+        <v>164</v>
       </c>
       <c r="G236" t="s">
-        <v>165</v>
+        <v>366</v>
       </c>
     </row>
     <row r="237" spans="1:7">
@@ -7047,19 +7047,19 @@
         <v>8</v>
       </c>
       <c r="C237" t="s">
-        <v>363</v>
+        <v>386</v>
       </c>
       <c r="D237" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="E237" t="s">
         <v>365</v>
       </c>
       <c r="F237" t="s">
-        <v>387</v>
+        <v>164</v>
       </c>
       <c r="G237" t="s">
-        <v>165</v>
+        <v>366</v>
       </c>
     </row>
     <row r="238" spans="1:7">
@@ -7070,19 +7070,19 @@
         <v>8</v>
       </c>
       <c r="C238" t="s">
-        <v>363</v>
+        <v>386</v>
       </c>
       <c r="D238" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="E238" t="s">
         <v>365</v>
       </c>
       <c r="F238" t="s">
-        <v>387</v>
+        <v>164</v>
       </c>
       <c r="G238" t="s">
-        <v>165</v>
+        <v>366</v>
       </c>
     </row>
     <row r="239" spans="1:7">
@@ -7093,19 +7093,19 @@
         <v>8</v>
       </c>
       <c r="C239" t="s">
-        <v>363</v>
+        <v>398</v>
       </c>
       <c r="D239" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="E239" t="s">
         <v>365</v>
       </c>
       <c r="F239" t="s">
-        <v>399</v>
+        <v>164</v>
       </c>
       <c r="G239" t="s">
-        <v>165</v>
+        <v>366</v>
       </c>
     </row>
     <row r="240" spans="1:7">
@@ -7254,19 +7254,19 @@
         <v>8</v>
       </c>
       <c r="C246" t="s">
-        <v>255</v>
+        <v>409</v>
       </c>
       <c r="D246" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="E246" t="s">
         <v>402</v>
       </c>
       <c r="F246" t="s">
-        <v>410</v>
+        <v>164</v>
       </c>
       <c r="G246" t="s">
-        <v>165</v>
+        <v>256</v>
       </c>
     </row>
     <row r="247" spans="1:7">
@@ -7323,10 +7323,10 @@
         <v>412</v>
       </c>
       <c r="F249" t="s">
+        <v>96</v>
+      </c>
+      <c r="G249" t="s">
         <v>416</v>
-      </c>
-      <c r="G249" t="s">
-        <v>97</v>
       </c>
     </row>
     <row r="250" spans="1:7">
@@ -7403,10 +7403,10 @@
         <v>422</v>
       </c>
       <c r="F253" t="s">
+        <v>164</v>
+      </c>
+      <c r="G253" t="s">
         <v>423</v>
-      </c>
-      <c r="G253" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="254" spans="1:7">
@@ -7423,10 +7423,10 @@
         <v>422</v>
       </c>
       <c r="F254" t="s">
+        <v>92</v>
+      </c>
+      <c r="G254" t="s">
         <v>220</v>
-      </c>
-      <c r="G254" t="s">
-        <v>93</v>
       </c>
     </row>
     <row r="255" spans="1:7">
@@ -7443,10 +7443,10 @@
         <v>422</v>
       </c>
       <c r="F255" t="s">
+        <v>92</v>
+      </c>
+      <c r="G255" t="s">
         <v>427</v>
-      </c>
-      <c r="G255" t="s">
-        <v>93</v>
       </c>
     </row>
     <row r="256" spans="1:7">
@@ -7463,10 +7463,10 @@
         <v>422</v>
       </c>
       <c r="F256" t="s">
+        <v>92</v>
+      </c>
+      <c r="G256" t="s">
         <v>427</v>
-      </c>
-      <c r="G256" t="s">
-        <v>93</v>
       </c>
     </row>
     <row r="257" spans="1:7">
@@ -7483,10 +7483,10 @@
         <v>422</v>
       </c>
       <c r="F257" t="s">
+        <v>92</v>
+      </c>
+      <c r="G257" t="s">
         <v>427</v>
-      </c>
-      <c r="G257" t="s">
-        <v>93</v>
       </c>
     </row>
     <row r="258" spans="1:7">
@@ -7503,10 +7503,10 @@
         <v>422</v>
       </c>
       <c r="F258" t="s">
+        <v>164</v>
+      </c>
+      <c r="G258" t="s">
         <v>328</v>
-      </c>
-      <c r="G258" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="259" spans="1:7">
@@ -7523,10 +7523,10 @@
         <v>422</v>
       </c>
       <c r="F259" t="s">
+        <v>92</v>
+      </c>
+      <c r="G259" t="s">
         <v>427</v>
-      </c>
-      <c r="G259" t="s">
-        <v>93</v>
       </c>
     </row>
     <row r="260" spans="1:7">
@@ -7563,10 +7563,10 @@
         <v>422</v>
       </c>
       <c r="F261" t="s">
+        <v>196</v>
+      </c>
+      <c r="G261" t="s">
         <v>435</v>
-      </c>
-      <c r="G261" t="s">
-        <v>197</v>
       </c>
     </row>
     <row r="262" spans="1:7">
@@ -7603,10 +7603,10 @@
         <v>422</v>
       </c>
       <c r="F263" t="s">
+        <v>183</v>
+      </c>
+      <c r="G263" t="s">
         <v>439</v>
-      </c>
-      <c r="G263" t="s">
-        <v>184</v>
       </c>
     </row>
     <row r="264" spans="1:7">
@@ -7663,10 +7663,10 @@
         <v>422</v>
       </c>
       <c r="F266" t="s">
+        <v>115</v>
+      </c>
+      <c r="G266" t="s">
         <v>444</v>
-      </c>
-      <c r="G266" t="s">
-        <v>116</v>
       </c>
     </row>
     <row r="267" spans="1:7">
@@ -7683,10 +7683,10 @@
         <v>446</v>
       </c>
       <c r="F267" t="s">
+        <v>115</v>
+      </c>
+      <c r="G267" t="s">
         <v>119</v>
-      </c>
-      <c r="G267" t="s">
-        <v>116</v>
       </c>
     </row>
     <row r="268" spans="1:7">
@@ -7703,10 +7703,10 @@
         <v>448</v>
       </c>
       <c r="F268" t="s">
+        <v>183</v>
+      </c>
+      <c r="G268" t="s">
         <v>204</v>
-      </c>
-      <c r="G268" t="s">
-        <v>184</v>
       </c>
     </row>
     <row r="269" spans="1:7">
@@ -7723,10 +7723,10 @@
         <v>450</v>
       </c>
       <c r="F269" t="s">
+        <v>115</v>
+      </c>
+      <c r="G269" t="s">
         <v>119</v>
-      </c>
-      <c r="G269" t="s">
-        <v>116</v>
       </c>
     </row>
     <row r="270" spans="1:7">
@@ -7743,10 +7743,10 @@
         <v>450</v>
       </c>
       <c r="F270" t="s">
+        <v>115</v>
+      </c>
+      <c r="G270" t="s">
         <v>119</v>
-      </c>
-      <c r="G270" t="s">
-        <v>116</v>
       </c>
     </row>
     <row r="271" spans="1:7">
@@ -7763,10 +7763,10 @@
         <v>454</v>
       </c>
       <c r="F271" t="s">
+        <v>115</v>
+      </c>
+      <c r="G271" t="s">
         <v>455</v>
-      </c>
-      <c r="G271" t="s">
-        <v>116</v>
       </c>
     </row>
     <row r="272" spans="1:7">
@@ -7783,10 +7783,10 @@
         <v>454</v>
       </c>
       <c r="F272" t="s">
+        <v>115</v>
+      </c>
+      <c r="G272" t="s">
         <v>455</v>
-      </c>
-      <c r="G272" t="s">
-        <v>116</v>
       </c>
     </row>
     <row r="273" spans="1:7">
@@ -7803,10 +7803,10 @@
         <v>454</v>
       </c>
       <c r="F273" t="s">
+        <v>115</v>
+      </c>
+      <c r="G273" t="s">
         <v>455</v>
-      </c>
-      <c r="G273" t="s">
-        <v>116</v>
       </c>
     </row>
     <row r="274" spans="1:7">
@@ -7823,10 +7823,10 @@
         <v>454</v>
       </c>
       <c r="F274" t="s">
+        <v>115</v>
+      </c>
+      <c r="G274" t="s">
         <v>455</v>
-      </c>
-      <c r="G274" t="s">
-        <v>116</v>
       </c>
     </row>
     <row r="275" spans="1:7">
@@ -7843,10 +7843,10 @@
         <v>454</v>
       </c>
       <c r="F275" t="s">
+        <v>115</v>
+      </c>
+      <c r="G275" t="s">
         <v>455</v>
-      </c>
-      <c r="G275" t="s">
-        <v>116</v>
       </c>
     </row>
     <row r="276" spans="1:7">
@@ -7863,10 +7863,10 @@
         <v>454</v>
       </c>
       <c r="F276" t="s">
+        <v>115</v>
+      </c>
+      <c r="G276" t="s">
         <v>455</v>
-      </c>
-      <c r="G276" t="s">
-        <v>116</v>
       </c>
     </row>
     <row r="277" spans="1:7">
@@ -7883,10 +7883,10 @@
         <v>454</v>
       </c>
       <c r="F277" t="s">
+        <v>115</v>
+      </c>
+      <c r="G277" t="s">
         <v>455</v>
-      </c>
-      <c r="G277" t="s">
-        <v>116</v>
       </c>
     </row>
     <row r="278" spans="1:7">
@@ -7903,10 +7903,10 @@
         <v>463</v>
       </c>
       <c r="F278" t="s">
+        <v>183</v>
+      </c>
+      <c r="G278" t="s">
         <v>204</v>
-      </c>
-      <c r="G278" t="s">
-        <v>184</v>
       </c>
     </row>
     <row r="279" spans="1:7">
@@ -7923,10 +7923,10 @@
         <v>463</v>
       </c>
       <c r="F279" t="s">
+        <v>32</v>
+      </c>
+      <c r="G279" t="s">
         <v>54</v>
-      </c>
-      <c r="G279" t="s">
-        <v>33</v>
       </c>
     </row>
     <row r="280" spans="1:7">
@@ -7963,10 +7963,10 @@
         <v>463</v>
       </c>
       <c r="F281" t="s">
+        <v>115</v>
+      </c>
+      <c r="G281" t="s">
         <v>171</v>
-      </c>
-      <c r="G281" t="s">
-        <v>116</v>
       </c>
     </row>
     <row r="282" spans="1:7">
@@ -7997,16 +7997,16 @@
         <v>8</v>
       </c>
       <c r="C283" t="s">
-        <v>363</v>
+        <v>398</v>
       </c>
       <c r="E283" t="s">
         <v>469</v>
       </c>
       <c r="F283" t="s">
-        <v>399</v>
+        <v>164</v>
       </c>
       <c r="G283" t="s">
-        <v>165</v>
+        <v>366</v>
       </c>
     </row>
     <row r="284" spans="1:7">
@@ -8043,10 +8043,10 @@
         <v>473</v>
       </c>
       <c r="F285" t="s">
+        <v>115</v>
+      </c>
+      <c r="G285" t="s">
         <v>171</v>
-      </c>
-      <c r="G285" t="s">
-        <v>116</v>
       </c>
     </row>
     <row r="286" spans="1:7">
@@ -8063,10 +8063,10 @@
         <v>475</v>
       </c>
       <c r="F286" t="s">
+        <v>183</v>
+      </c>
+      <c r="G286" t="s">
         <v>439</v>
-      </c>
-      <c r="G286" t="s">
-        <v>184</v>
       </c>
     </row>
     <row r="287" spans="1:7">
@@ -8083,10 +8083,10 @@
         <v>475</v>
       </c>
       <c r="F287" t="s">
+        <v>183</v>
+      </c>
+      <c r="G287" t="s">
         <v>439</v>
-      </c>
-      <c r="G287" t="s">
-        <v>184</v>
       </c>
     </row>
     <row r="288" spans="1:7">
@@ -8103,10 +8103,10 @@
         <v>475</v>
       </c>
       <c r="F288" t="s">
+        <v>12</v>
+      </c>
+      <c r="G288" t="s">
         <v>42</v>
-      </c>
-      <c r="G288" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="289" spans="1:7">
@@ -8163,10 +8163,10 @@
         <v>475</v>
       </c>
       <c r="F291" t="s">
+        <v>115</v>
+      </c>
+      <c r="G291" t="s">
         <v>171</v>
-      </c>
-      <c r="G291" t="s">
-        <v>116</v>
       </c>
     </row>
     <row r="292" spans="1:7">
@@ -8183,10 +8183,10 @@
         <v>475</v>
       </c>
       <c r="F292" t="s">
+        <v>115</v>
+      </c>
+      <c r="G292" t="s">
         <v>171</v>
-      </c>
-      <c r="G292" t="s">
-        <v>116</v>
       </c>
     </row>
     <row r="293" spans="1:7">
@@ -8203,10 +8203,10 @@
         <v>475</v>
       </c>
       <c r="F293" t="s">
+        <v>115</v>
+      </c>
+      <c r="G293" t="s">
         <v>171</v>
-      </c>
-      <c r="G293" t="s">
-        <v>116</v>
       </c>
     </row>
     <row r="294" spans="1:7">
@@ -8223,10 +8223,10 @@
         <v>475</v>
       </c>
       <c r="F294" t="s">
+        <v>115</v>
+      </c>
+      <c r="G294" t="s">
         <v>171</v>
-      </c>
-      <c r="G294" t="s">
-        <v>116</v>
       </c>
     </row>
     <row r="295" spans="1:7">
@@ -8243,10 +8243,10 @@
         <v>485</v>
       </c>
       <c r="F295" t="s">
+        <v>115</v>
+      </c>
+      <c r="G295" t="s">
         <v>171</v>
-      </c>
-      <c r="G295" t="s">
-        <v>116</v>
       </c>
     </row>
     <row r="296" spans="1:7">
@@ -8263,10 +8263,10 @@
         <v>485</v>
       </c>
       <c r="F296" t="s">
+        <v>115</v>
+      </c>
+      <c r="G296" t="s">
         <v>171</v>
-      </c>
-      <c r="G296" t="s">
-        <v>116</v>
       </c>
     </row>
   </sheetData>

--- a/api/2/xlsx/fr/SectorCOFOG.xlsx
+++ b/api/2/xlsx/fr/SectorCOFOG.xlsx
@@ -22,42 +22,42 @@
     <t>status</t>
   </si>
   <si>
+    <t>codeforiati:cofog-division</t>
+  </si>
+  <si>
     <t>codeforiati:cofog-class</t>
   </si>
   <si>
+    <t>codeforiati:cofog-group</t>
+  </si>
+  <si>
+    <t>codeforiati:group-code</t>
+  </si>
+  <si>
     <t>codeforiati:category-code</t>
   </si>
   <si>
-    <t>codeforiati:group-code</t>
-  </si>
-  <si>
-    <t>codeforiati:cofog-division</t>
-  </si>
-  <si>
-    <t>codeforiati:cofog-group</t>
-  </si>
-  <si>
     <t>11110</t>
   </si>
   <si>
     <t>active</t>
   </si>
   <si>
+    <t>09 - Education</t>
+  </si>
+  <si>
     <t>09.8.0 - Education n.e.c. (CS)</t>
   </si>
   <si>
+    <t>09.8 - Education n.e.c.</t>
+  </si>
+  <si>
+    <t>110</t>
+  </si>
+  <si>
     <t>111</t>
   </si>
   <si>
-    <t>110</t>
-  </si>
-  <si>
-    <t>09 - Education</t>
-  </si>
-  <si>
-    <t>09.8 - Education n.e.c.</t>
-  </si>
-  <si>
     <t>11120</t>
   </si>
   <si>
@@ -85,12 +85,12 @@
     <t>09.1.2 - Primary education (IS)</t>
   </si>
   <si>
+    <t>09.1 - Pre‐primary and primary education</t>
+  </si>
+  <si>
     <t>112</t>
   </si>
   <si>
-    <t>09.1 - Pre‐primary and primary education</t>
-  </si>
-  <si>
     <t>11230</t>
   </si>
   <si>
@@ -109,12 +109,12 @@
     <t>11250</t>
   </si>
   <si>
+    <t>07 - Health</t>
+  </si>
+  <si>
     <t>07.4.0 - Public health services (IS)</t>
   </si>
   <si>
-    <t>07 - Health</t>
-  </si>
-  <si>
     <t>07.4 - Public health services</t>
   </si>
   <si>
@@ -151,12 +151,12 @@
     <t>09.4.1 - First stage of tertiary education (IS)</t>
   </si>
   <si>
+    <t>09.4 - Tertiary education</t>
+  </si>
+  <si>
     <t>114</t>
   </si>
   <si>
-    <t>09.4 - Tertiary education</t>
-  </si>
-  <si>
     <t>11430</t>
   </si>
   <si>
@@ -172,15 +172,15 @@
     <t>07.6.0 - Health n.e.c. (CS)</t>
   </si>
   <si>
+    <t>07.6 - Health n.e.c.</t>
+  </si>
+  <si>
+    <t>120</t>
+  </si>
+  <si>
     <t>121</t>
   </si>
   <si>
-    <t>120</t>
-  </si>
-  <si>
-    <t>07.6 - Health n.e.c.</t>
-  </si>
-  <si>
     <t>12181</t>
   </si>
   <si>
@@ -286,27 +286,27 @@
     <t>14010</t>
   </si>
   <si>
+    <t>06 - Housing and community amenities</t>
+  </si>
+  <si>
     <t>06.3.0 - Water supply (CS)</t>
   </si>
   <si>
+    <t>06.3 - Water supply</t>
+  </si>
+  <si>
     <t>140</t>
   </si>
   <si>
-    <t>06 - Housing and community amenities</t>
-  </si>
-  <si>
-    <t>06.3 - Water supply</t>
-  </si>
-  <si>
     <t>14015</t>
   </si>
   <si>
+    <t>05 - Environmental protection</t>
+  </si>
+  <si>
     <t>05.6.0 - Environmental protection n.e.c. (CS)</t>
   </si>
   <si>
-    <t>05 - Environmental protection</t>
-  </si>
-  <si>
     <t>05.6 - Environmental protection n.e.c.</t>
   </si>
   <si>
@@ -352,21 +352,21 @@
     <t>15110</t>
   </si>
   <si>
+    <t>01 - General public services</t>
+  </si>
+  <si>
     <t>01.3.1 - General personnel services (CS)</t>
   </si>
   <si>
+    <t>01.3 - General services</t>
+  </si>
+  <si>
+    <t>150</t>
+  </si>
+  <si>
     <t>151</t>
   </si>
   <si>
-    <t>150</t>
-  </si>
-  <si>
-    <t>01 - General public services</t>
-  </si>
-  <si>
-    <t>01.3 - General services</t>
-  </si>
-  <si>
     <t>15111</t>
   </si>
   <si>
@@ -388,12 +388,12 @@
     <t>15113</t>
   </si>
   <si>
+    <t>03 - Public order and safety</t>
+  </si>
+  <si>
     <t>03.6.0 - Public order and safety n.e.c. (CS)</t>
   </si>
   <si>
-    <t>03 - Public order and safety</t>
-  </si>
-  <si>
     <t>03.6 - Public order and safety n.e.c.</t>
   </si>
   <si>
@@ -505,12 +505,12 @@
     <t>15142</t>
   </si>
   <si>
+    <t>04 - Economic affairs</t>
+  </si>
+  <si>
     <t>04.1.1 - General economic and commercial affairs (CS)</t>
   </si>
   <si>
-    <t>04 - Economic affairs</t>
-  </si>
-  <si>
     <t>04.1 - General economic, commercial and labour affairs</t>
   </si>
   <si>
@@ -562,12 +562,12 @@
     <t>15170</t>
   </si>
   <si>
+    <t>10 - Social protection</t>
+  </si>
+  <si>
     <t>10.7.0 - Social exclusion n.e.c. (IS)</t>
   </si>
   <si>
-    <t>10 - Social protection</t>
-  </si>
-  <si>
     <t>10.7 - Social exclusion n.e.c.</t>
   </si>
   <si>
@@ -601,12 +601,12 @@
     <t>15230</t>
   </si>
   <si>
+    <t>02 - Defence</t>
+  </si>
+  <si>
     <t>02.3.0 - Foreign military aid (CS)</t>
   </si>
   <si>
-    <t>02 - Defence</t>
-  </si>
-  <si>
     <t>02.3 - Foreign military aid</t>
   </si>
   <si>
@@ -625,12 +625,12 @@
     <t>10.9.0 - Social protection n.e.c. (CS)</t>
   </si>
   <si>
+    <t>10.9 - Social protection n.e.c.</t>
+  </si>
+  <si>
     <t>160</t>
   </si>
   <si>
-    <t>10.9 - Social protection n.e.c.</t>
-  </si>
-  <si>
     <t>16011</t>
   </si>
   <si>
@@ -685,12 +685,12 @@
     <t>16061</t>
   </si>
   <si>
+    <t>08 - Recreation, culture and religion</t>
+  </si>
+  <si>
     <t>08.2.0 - Cultural services (IS)</t>
   </si>
   <si>
-    <t>08 - Recreation, culture and religion</t>
-  </si>
-  <si>
     <t>08.2 - Cultural services</t>
   </si>
   <si>
@@ -826,15 +826,15 @@
     <t>04.3.5 - Electricity (CS)</t>
   </si>
   <si>
+    <t>04.3 - Fuel and energy</t>
+  </si>
+  <si>
+    <t>230</t>
+  </si>
+  <si>
     <t>231</t>
   </si>
   <si>
-    <t>230</t>
-  </si>
-  <si>
-    <t>04.3 - Fuel and energy</t>
-  </si>
-  <si>
     <t>23111</t>
   </si>
   <si>
@@ -994,15 +994,15 @@
     <t>04.2.1 - Agriculture (CS)</t>
   </si>
   <si>
+    <t>04.2 - Agriculture, forestry, fishing and hunting</t>
+  </si>
+  <si>
+    <t>310</t>
+  </si>
+  <si>
     <t>311</t>
   </si>
   <si>
-    <t>310</t>
-  </si>
-  <si>
-    <t>04.2 - Agriculture, forestry, fishing and hunting</t>
-  </si>
-  <si>
     <t>31120</t>
   </si>
   <si>
@@ -1108,15 +1108,15 @@
     <t>04.4.2 - Manufacturing (CS)</t>
   </si>
   <si>
+    <t>04.4 - Mining, manufacturing and construction</t>
+  </si>
+  <si>
+    <t>320</t>
+  </si>
+  <si>
     <t>321</t>
   </si>
   <si>
-    <t>320</t>
-  </si>
-  <si>
-    <t>04.4 - Mining, manufacturing and construction</t>
-  </si>
-  <si>
     <t>32120</t>
   </si>
   <si>
@@ -1219,12 +1219,12 @@
     <t>33110</t>
   </si>
   <si>
+    <t>330</t>
+  </si>
+  <si>
     <t>331</t>
   </si>
   <si>
-    <t>330</t>
-  </si>
-  <si>
     <t>33120</t>
   </si>
   <si>
@@ -1282,12 +1282,12 @@
     <t>04.9.0 - Economic affairs n.e.c. (CS)</t>
   </si>
   <si>
+    <t>04.9 - Economic affairs n.e.c.</t>
+  </si>
+  <si>
     <t>430</t>
   </si>
   <si>
-    <t>04.9 - Economic affairs n.e.c.</t>
-  </si>
-  <si>
     <t>43030</t>
   </si>
   <si>
@@ -1378,10 +1378,10 @@
     <t>01.7.0 - Public debt transactions (CS)</t>
   </si>
   <si>
+    <t>01.7 - Public debt transactions</t>
+  </si>
+  <si>
     <t>600</t>
-  </si>
-  <si>
-    <t>01.7 - Public debt transactions</t>
   </si>
   <si>
     <t>60020</t>
@@ -1863,19 +1863,19 @@
         <v>8</v>
       </c>
       <c r="C3" t="s">
+        <v>9</v>
+      </c>
+      <c r="D3" t="s">
         <v>15</v>
       </c>
-      <c r="D3" t="s">
-        <v>10</v>
-      </c>
       <c r="E3" t="s">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="F3" t="s">
         <v>12</v>
       </c>
       <c r="G3" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -1909,19 +1909,19 @@
         <v>8</v>
       </c>
       <c r="C5" t="s">
+        <v>9</v>
+      </c>
+      <c r="D5" t="s">
         <v>19</v>
       </c>
-      <c r="D5" t="s">
-        <v>10</v>
-      </c>
       <c r="E5" t="s">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="F5" t="s">
         <v>12</v>
       </c>
       <c r="G5" t="s">
-        <v>20</v>
+        <v>13</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -1932,13 +1932,13 @@
         <v>8</v>
       </c>
       <c r="C6" t="s">
+        <v>9</v>
+      </c>
+      <c r="D6" t="s">
         <v>22</v>
       </c>
-      <c r="D6" t="s">
+      <c r="E6" t="s">
         <v>23</v>
-      </c>
-      <c r="E6" t="s">
-        <v>11</v>
       </c>
       <c r="F6" t="s">
         <v>12</v>
@@ -1958,7 +1958,7 @@
         <v>9</v>
       </c>
       <c r="D7" t="s">
-        <v>23</v>
+        <v>10</v>
       </c>
       <c r="E7" t="s">
         <v>11</v>
@@ -1967,7 +1967,7 @@
         <v>12</v>
       </c>
       <c r="G7" t="s">
-        <v>13</v>
+        <v>24</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -1978,13 +1978,13 @@
         <v>8</v>
       </c>
       <c r="C8" t="s">
+        <v>9</v>
+      </c>
+      <c r="D8" t="s">
         <v>22</v>
       </c>
-      <c r="D8" t="s">
+      <c r="E8" t="s">
         <v>23</v>
-      </c>
-      <c r="E8" t="s">
-        <v>11</v>
       </c>
       <c r="F8" t="s">
         <v>12</v>
@@ -2001,13 +2001,13 @@
         <v>8</v>
       </c>
       <c r="C9" t="s">
+        <v>9</v>
+      </c>
+      <c r="D9" t="s">
         <v>22</v>
       </c>
-      <c r="D9" t="s">
+      <c r="E9" t="s">
         <v>23</v>
-      </c>
-      <c r="E9" t="s">
-        <v>11</v>
       </c>
       <c r="F9" t="s">
         <v>12</v>
@@ -2024,13 +2024,13 @@
         <v>8</v>
       </c>
       <c r="C10" t="s">
+        <v>9</v>
+      </c>
+      <c r="D10" t="s">
         <v>29</v>
       </c>
-      <c r="D10" t="s">
+      <c r="E10" t="s">
         <v>23</v>
-      </c>
-      <c r="E10" t="s">
-        <v>11</v>
       </c>
       <c r="F10" t="s">
         <v>12</v>
@@ -2050,16 +2050,16 @@
         <v>31</v>
       </c>
       <c r="D11" t="s">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="E11" t="s">
-        <v>11</v>
+        <v>33</v>
       </c>
       <c r="F11" t="s">
-        <v>32</v>
+        <v>12</v>
       </c>
       <c r="G11" t="s">
-        <v>33</v>
+        <v>24</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -2070,19 +2070,19 @@
         <v>8</v>
       </c>
       <c r="C12" t="s">
+        <v>9</v>
+      </c>
+      <c r="D12" t="s">
         <v>35</v>
       </c>
-      <c r="D12" t="s">
-        <v>23</v>
-      </c>
       <c r="E12" t="s">
-        <v>11</v>
+        <v>36</v>
       </c>
       <c r="F12" t="s">
         <v>12</v>
       </c>
       <c r="G12" t="s">
-        <v>36</v>
+        <v>24</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -2093,19 +2093,19 @@
         <v>8</v>
       </c>
       <c r="C13" t="s">
+        <v>9</v>
+      </c>
+      <c r="D13" t="s">
         <v>38</v>
       </c>
-      <c r="D13" t="s">
-        <v>39</v>
-      </c>
       <c r="E13" t="s">
-        <v>11</v>
+        <v>36</v>
       </c>
       <c r="F13" t="s">
         <v>12</v>
       </c>
       <c r="G13" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -2116,19 +2116,19 @@
         <v>8</v>
       </c>
       <c r="C14" t="s">
+        <v>9</v>
+      </c>
+      <c r="D14" t="s">
         <v>41</v>
       </c>
-      <c r="D14" t="s">
-        <v>39</v>
-      </c>
       <c r="E14" t="s">
-        <v>11</v>
+        <v>42</v>
       </c>
       <c r="F14" t="s">
         <v>12</v>
       </c>
       <c r="G14" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -2139,13 +2139,13 @@
         <v>8</v>
       </c>
       <c r="C15" t="s">
+        <v>9</v>
+      </c>
+      <c r="D15" t="s">
         <v>44</v>
       </c>
-      <c r="D15" t="s">
+      <c r="E15" t="s">
         <v>45</v>
-      </c>
-      <c r="E15" t="s">
-        <v>11</v>
       </c>
       <c r="F15" t="s">
         <v>12</v>
@@ -2162,19 +2162,19 @@
         <v>8</v>
       </c>
       <c r="C16" t="s">
+        <v>9</v>
+      </c>
+      <c r="D16" t="s">
         <v>48</v>
       </c>
-      <c r="D16" t="s">
-        <v>45</v>
-      </c>
       <c r="E16" t="s">
-        <v>11</v>
+        <v>49</v>
       </c>
       <c r="F16" t="s">
         <v>12</v>
       </c>
       <c r="G16" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -2185,16 +2185,16 @@
         <v>8</v>
       </c>
       <c r="C17" t="s">
+        <v>31</v>
+      </c>
+      <c r="D17" t="s">
         <v>51</v>
       </c>
-      <c r="D17" t="s">
+      <c r="E17" t="s">
         <v>52</v>
       </c>
-      <c r="E17" t="s">
+      <c r="F17" t="s">
         <v>53</v>
-      </c>
-      <c r="F17" t="s">
-        <v>32</v>
       </c>
       <c r="G17" t="s">
         <v>54</v>
@@ -2208,16 +2208,16 @@
         <v>8</v>
       </c>
       <c r="C18" t="s">
+        <v>31</v>
+      </c>
+      <c r="D18" t="s">
         <v>51</v>
       </c>
-      <c r="D18" t="s">
+      <c r="E18" t="s">
         <v>52</v>
       </c>
-      <c r="E18" t="s">
+      <c r="F18" t="s">
         <v>53</v>
-      </c>
-      <c r="F18" t="s">
-        <v>32</v>
       </c>
       <c r="G18" t="s">
         <v>54</v>
@@ -2231,19 +2231,19 @@
         <v>8</v>
       </c>
       <c r="C19" t="s">
+        <v>31</v>
+      </c>
+      <c r="D19" t="s">
         <v>57</v>
       </c>
-      <c r="D19" t="s">
-        <v>52</v>
-      </c>
       <c r="E19" t="s">
+        <v>58</v>
+      </c>
+      <c r="F19" t="s">
         <v>53</v>
       </c>
-      <c r="F19" t="s">
-        <v>32</v>
-      </c>
       <c r="G19" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -2254,19 +2254,19 @@
         <v>8</v>
       </c>
       <c r="C20" t="s">
+        <v>31</v>
+      </c>
+      <c r="D20" t="s">
         <v>60</v>
       </c>
-      <c r="D20" t="s">
-        <v>52</v>
-      </c>
       <c r="E20" t="s">
+        <v>61</v>
+      </c>
+      <c r="F20" t="s">
         <v>53</v>
       </c>
-      <c r="F20" t="s">
-        <v>32</v>
-      </c>
       <c r="G20" t="s">
-        <v>61</v>
+        <v>54</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -2277,16 +2277,16 @@
         <v>8</v>
       </c>
       <c r="C21" t="s">
+        <v>31</v>
+      </c>
+      <c r="D21" t="s">
         <v>51</v>
       </c>
-      <c r="D21" t="s">
+      <c r="E21" t="s">
         <v>52</v>
       </c>
-      <c r="E21" t="s">
+      <c r="F21" t="s">
         <v>53</v>
-      </c>
-      <c r="F21" t="s">
-        <v>32</v>
       </c>
       <c r="G21" t="s">
         <v>54</v>
@@ -2303,16 +2303,16 @@
         <v>31</v>
       </c>
       <c r="D22" t="s">
+        <v>32</v>
+      </c>
+      <c r="E22" t="s">
+        <v>33</v>
+      </c>
+      <c r="F22" t="s">
+        <v>53</v>
+      </c>
+      <c r="G22" t="s">
         <v>64</v>
-      </c>
-      <c r="E22" t="s">
-        <v>53</v>
-      </c>
-      <c r="F22" t="s">
-        <v>32</v>
-      </c>
-      <c r="G22" t="s">
-        <v>33</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -2323,19 +2323,19 @@
         <v>8</v>
       </c>
       <c r="C23" t="s">
+        <v>31</v>
+      </c>
+      <c r="D23" t="s">
         <v>66</v>
       </c>
-      <c r="D23" t="s">
+      <c r="E23" t="s">
+        <v>67</v>
+      </c>
+      <c r="F23" t="s">
+        <v>53</v>
+      </c>
+      <c r="G23" t="s">
         <v>64</v>
-      </c>
-      <c r="E23" t="s">
-        <v>53</v>
-      </c>
-      <c r="F23" t="s">
-        <v>32</v>
-      </c>
-      <c r="G23" t="s">
-        <v>67</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -2349,16 +2349,16 @@
         <v>31</v>
       </c>
       <c r="D24" t="s">
+        <v>32</v>
+      </c>
+      <c r="E24" t="s">
+        <v>33</v>
+      </c>
+      <c r="F24" t="s">
+        <v>53</v>
+      </c>
+      <c r="G24" t="s">
         <v>64</v>
-      </c>
-      <c r="E24" t="s">
-        <v>53</v>
-      </c>
-      <c r="F24" t="s">
-        <v>32</v>
-      </c>
-      <c r="G24" t="s">
-        <v>33</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -2372,16 +2372,16 @@
         <v>31</v>
       </c>
       <c r="D25" t="s">
+        <v>32</v>
+      </c>
+      <c r="E25" t="s">
+        <v>33</v>
+      </c>
+      <c r="F25" t="s">
+        <v>53</v>
+      </c>
+      <c r="G25" t="s">
         <v>64</v>
-      </c>
-      <c r="E25" t="s">
-        <v>53</v>
-      </c>
-      <c r="F25" t="s">
-        <v>32</v>
-      </c>
-      <c r="G25" t="s">
-        <v>33</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -2395,16 +2395,16 @@
         <v>31</v>
       </c>
       <c r="D26" t="s">
+        <v>32</v>
+      </c>
+      <c r="E26" t="s">
+        <v>33</v>
+      </c>
+      <c r="F26" t="s">
+        <v>53</v>
+      </c>
+      <c r="G26" t="s">
         <v>64</v>
-      </c>
-      <c r="E26" t="s">
-        <v>53</v>
-      </c>
-      <c r="F26" t="s">
-        <v>32</v>
-      </c>
-      <c r="G26" t="s">
-        <v>33</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -2418,16 +2418,16 @@
         <v>31</v>
       </c>
       <c r="D27" t="s">
+        <v>32</v>
+      </c>
+      <c r="E27" t="s">
+        <v>33</v>
+      </c>
+      <c r="F27" t="s">
+        <v>53</v>
+      </c>
+      <c r="G27" t="s">
         <v>64</v>
-      </c>
-      <c r="E27" t="s">
-        <v>53</v>
-      </c>
-      <c r="F27" t="s">
-        <v>32</v>
-      </c>
-      <c r="G27" t="s">
-        <v>33</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -2441,16 +2441,16 @@
         <v>31</v>
       </c>
       <c r="D28" t="s">
+        <v>32</v>
+      </c>
+      <c r="E28" t="s">
+        <v>33</v>
+      </c>
+      <c r="F28" t="s">
+        <v>53</v>
+      </c>
+      <c r="G28" t="s">
         <v>64</v>
-      </c>
-      <c r="E28" t="s">
-        <v>53</v>
-      </c>
-      <c r="F28" t="s">
-        <v>32</v>
-      </c>
-      <c r="G28" t="s">
-        <v>33</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -2464,16 +2464,16 @@
         <v>31</v>
       </c>
       <c r="D29" t="s">
+        <v>32</v>
+      </c>
+      <c r="E29" t="s">
+        <v>33</v>
+      </c>
+      <c r="F29" t="s">
+        <v>53</v>
+      </c>
+      <c r="G29" t="s">
         <v>64</v>
-      </c>
-      <c r="E29" t="s">
-        <v>53</v>
-      </c>
-      <c r="F29" t="s">
-        <v>32</v>
-      </c>
-      <c r="G29" t="s">
-        <v>33</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -2484,19 +2484,19 @@
         <v>8</v>
       </c>
       <c r="C30" t="s">
+        <v>31</v>
+      </c>
+      <c r="D30" t="s">
         <v>51</v>
       </c>
-      <c r="D30" t="s">
+      <c r="E30" t="s">
+        <v>52</v>
+      </c>
+      <c r="F30" t="s">
+        <v>53</v>
+      </c>
+      <c r="G30" t="s">
         <v>64</v>
-      </c>
-      <c r="E30" t="s">
-        <v>53</v>
-      </c>
-      <c r="F30" t="s">
-        <v>32</v>
-      </c>
-      <c r="G30" t="s">
-        <v>54</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -2510,16 +2510,16 @@
         <v>31</v>
       </c>
       <c r="D31" t="s">
+        <v>32</v>
+      </c>
+      <c r="E31" t="s">
+        <v>33</v>
+      </c>
+      <c r="F31" t="s">
+        <v>53</v>
+      </c>
+      <c r="G31" t="s">
         <v>76</v>
-      </c>
-      <c r="E31" t="s">
-        <v>53</v>
-      </c>
-      <c r="F31" t="s">
-        <v>32</v>
-      </c>
-      <c r="G31" t="s">
-        <v>33</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -2533,16 +2533,16 @@
         <v>31</v>
       </c>
       <c r="D32" t="s">
+        <v>32</v>
+      </c>
+      <c r="E32" t="s">
+        <v>33</v>
+      </c>
+      <c r="F32" t="s">
+        <v>53</v>
+      </c>
+      <c r="G32" t="s">
         <v>76</v>
-      </c>
-      <c r="E32" t="s">
-        <v>53</v>
-      </c>
-      <c r="F32" t="s">
-        <v>32</v>
-      </c>
-      <c r="G32" t="s">
-        <v>33</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -2556,16 +2556,16 @@
         <v>31</v>
       </c>
       <c r="D33" t="s">
+        <v>32</v>
+      </c>
+      <c r="E33" t="s">
+        <v>33</v>
+      </c>
+      <c r="F33" t="s">
+        <v>53</v>
+      </c>
+      <c r="G33" t="s">
         <v>76</v>
-      </c>
-      <c r="E33" t="s">
-        <v>53</v>
-      </c>
-      <c r="F33" t="s">
-        <v>32</v>
-      </c>
-      <c r="G33" t="s">
-        <v>33</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -2579,16 +2579,16 @@
         <v>31</v>
       </c>
       <c r="D34" t="s">
+        <v>32</v>
+      </c>
+      <c r="E34" t="s">
+        <v>33</v>
+      </c>
+      <c r="F34" t="s">
+        <v>53</v>
+      </c>
+      <c r="G34" t="s">
         <v>76</v>
-      </c>
-      <c r="E34" t="s">
-        <v>53</v>
-      </c>
-      <c r="F34" t="s">
-        <v>32</v>
-      </c>
-      <c r="G34" t="s">
-        <v>33</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -2602,16 +2602,16 @@
         <v>31</v>
       </c>
       <c r="D35" t="s">
+        <v>32</v>
+      </c>
+      <c r="E35" t="s">
+        <v>33</v>
+      </c>
+      <c r="F35" t="s">
+        <v>53</v>
+      </c>
+      <c r="G35" t="s">
         <v>76</v>
-      </c>
-      <c r="E35" t="s">
-        <v>53</v>
-      </c>
-      <c r="F35" t="s">
-        <v>32</v>
-      </c>
-      <c r="G35" t="s">
-        <v>33</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -2622,19 +2622,19 @@
         <v>8</v>
       </c>
       <c r="C36" t="s">
+        <v>31</v>
+      </c>
+      <c r="D36" t="s">
         <v>57</v>
       </c>
-      <c r="D36" t="s">
+      <c r="E36" t="s">
+        <v>58</v>
+      </c>
+      <c r="F36" t="s">
+        <v>53</v>
+      </c>
+      <c r="G36" t="s">
         <v>76</v>
-      </c>
-      <c r="E36" t="s">
-        <v>53</v>
-      </c>
-      <c r="F36" t="s">
-        <v>32</v>
-      </c>
-      <c r="G36" t="s">
-        <v>58</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -2647,14 +2647,14 @@
       <c r="C37" t="s">
         <v>31</v>
       </c>
+      <c r="D37" t="s">
+        <v>32</v>
+      </c>
       <c r="E37" t="s">
+        <v>33</v>
+      </c>
+      <c r="F37" t="s">
         <v>83</v>
-      </c>
-      <c r="F37" t="s">
-        <v>32</v>
-      </c>
-      <c r="G37" t="s">
-        <v>33</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -2667,14 +2667,14 @@
       <c r="C38" t="s">
         <v>31</v>
       </c>
+      <c r="D38" t="s">
+        <v>32</v>
+      </c>
       <c r="E38" t="s">
+        <v>33</v>
+      </c>
+      <c r="F38" t="s">
         <v>83</v>
-      </c>
-      <c r="F38" t="s">
-        <v>32</v>
-      </c>
-      <c r="G38" t="s">
-        <v>33</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -2687,14 +2687,14 @@
       <c r="C39" t="s">
         <v>31</v>
       </c>
+      <c r="D39" t="s">
+        <v>32</v>
+      </c>
       <c r="E39" t="s">
+        <v>33</v>
+      </c>
+      <c r="F39" t="s">
         <v>83</v>
-      </c>
-      <c r="F39" t="s">
-        <v>32</v>
-      </c>
-      <c r="G39" t="s">
-        <v>33</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -2707,14 +2707,14 @@
       <c r="C40" t="s">
         <v>31</v>
       </c>
+      <c r="D40" t="s">
+        <v>32</v>
+      </c>
       <c r="E40" t="s">
+        <v>33</v>
+      </c>
+      <c r="F40" t="s">
         <v>83</v>
-      </c>
-      <c r="F40" t="s">
-        <v>32</v>
-      </c>
-      <c r="G40" t="s">
-        <v>33</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -2725,16 +2725,16 @@
         <v>8</v>
       </c>
       <c r="C41" t="s">
+        <v>31</v>
+      </c>
+      <c r="D41" t="s">
         <v>51</v>
       </c>
       <c r="E41" t="s">
+        <v>52</v>
+      </c>
+      <c r="F41" t="s">
         <v>83</v>
-      </c>
-      <c r="F41" t="s">
-        <v>32</v>
-      </c>
-      <c r="G41" t="s">
-        <v>54</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -2745,16 +2745,16 @@
         <v>8</v>
       </c>
       <c r="C42" t="s">
+        <v>31</v>
+      </c>
+      <c r="D42" t="s">
         <v>57</v>
       </c>
       <c r="E42" t="s">
+        <v>58</v>
+      </c>
+      <c r="F42" t="s">
         <v>83</v>
-      </c>
-      <c r="F42" t="s">
-        <v>32</v>
-      </c>
-      <c r="G42" t="s">
-        <v>58</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -2767,13 +2767,13 @@
       <c r="C43" t="s">
         <v>90</v>
       </c>
+      <c r="D43" t="s">
+        <v>91</v>
+      </c>
       <c r="E43" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="F43" t="s">
-        <v>92</v>
-      </c>
-      <c r="G43" t="s">
         <v>93</v>
       </c>
     </row>
@@ -2787,14 +2787,14 @@
       <c r="C44" t="s">
         <v>95</v>
       </c>
+      <c r="D44" t="s">
+        <v>96</v>
+      </c>
       <c r="E44" t="s">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="F44" t="s">
-        <v>96</v>
-      </c>
-      <c r="G44" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -2807,13 +2807,13 @@
       <c r="C45" t="s">
         <v>90</v>
       </c>
+      <c r="D45" t="s">
+        <v>91</v>
+      </c>
       <c r="E45" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="F45" t="s">
-        <v>92</v>
-      </c>
-      <c r="G45" t="s">
         <v>93</v>
       </c>
     </row>
@@ -2827,13 +2827,13 @@
       <c r="C46" t="s">
         <v>90</v>
       </c>
+      <c r="D46" t="s">
+        <v>91</v>
+      </c>
       <c r="E46" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="F46" t="s">
-        <v>92</v>
-      </c>
-      <c r="G46" t="s">
         <v>93</v>
       </c>
     </row>
@@ -2845,16 +2845,16 @@
         <v>8</v>
       </c>
       <c r="C47" t="s">
+        <v>95</v>
+      </c>
+      <c r="D47" t="s">
         <v>101</v>
       </c>
       <c r="E47" t="s">
-        <v>91</v>
+        <v>102</v>
       </c>
       <c r="F47" t="s">
-        <v>96</v>
-      </c>
-      <c r="G47" t="s">
-        <v>102</v>
+        <v>93</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -2867,13 +2867,13 @@
       <c r="C48" t="s">
         <v>90</v>
       </c>
+      <c r="D48" t="s">
+        <v>91</v>
+      </c>
       <c r="E48" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="F48" t="s">
-        <v>92</v>
-      </c>
-      <c r="G48" t="s">
         <v>93</v>
       </c>
     </row>
@@ -2887,13 +2887,13 @@
       <c r="C49" t="s">
         <v>90</v>
       </c>
+      <c r="D49" t="s">
+        <v>91</v>
+      </c>
       <c r="E49" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="F49" t="s">
-        <v>92</v>
-      </c>
-      <c r="G49" t="s">
         <v>93</v>
       </c>
     </row>
@@ -2905,16 +2905,16 @@
         <v>8</v>
       </c>
       <c r="C50" t="s">
+        <v>95</v>
+      </c>
+      <c r="D50" t="s">
         <v>101</v>
       </c>
       <c r="E50" t="s">
-        <v>91</v>
+        <v>102</v>
       </c>
       <c r="F50" t="s">
-        <v>96</v>
-      </c>
-      <c r="G50" t="s">
-        <v>102</v>
+        <v>93</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -2927,13 +2927,13 @@
       <c r="C51" t="s">
         <v>90</v>
       </c>
+      <c r="D51" t="s">
+        <v>91</v>
+      </c>
       <c r="E51" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="F51" t="s">
-        <v>92</v>
-      </c>
-      <c r="G51" t="s">
         <v>93</v>
       </c>
     </row>
@@ -2945,16 +2945,16 @@
         <v>8</v>
       </c>
       <c r="C52" t="s">
+        <v>95</v>
+      </c>
+      <c r="D52" t="s">
         <v>108</v>
       </c>
       <c r="E52" t="s">
-        <v>91</v>
+        <v>109</v>
       </c>
       <c r="F52" t="s">
-        <v>96</v>
-      </c>
-      <c r="G52" t="s">
-        <v>109</v>
+        <v>93</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -2967,14 +2967,14 @@
       <c r="C53" t="s">
         <v>9</v>
       </c>
+      <c r="D53" t="s">
+        <v>10</v>
+      </c>
       <c r="E53" t="s">
-        <v>91</v>
+        <v>11</v>
       </c>
       <c r="F53" t="s">
-        <v>12</v>
-      </c>
-      <c r="G53" t="s">
-        <v>13</v>
+        <v>93</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -3008,19 +3008,19 @@
         <v>8</v>
       </c>
       <c r="C55" t="s">
+        <v>112</v>
+      </c>
+      <c r="D55" t="s">
         <v>118</v>
       </c>
-      <c r="D55" t="s">
-        <v>113</v>
-      </c>
       <c r="E55" t="s">
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="F55" t="s">
         <v>115</v>
       </c>
       <c r="G55" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -3031,19 +3031,19 @@
         <v>8</v>
       </c>
       <c r="C56" t="s">
+        <v>112</v>
+      </c>
+      <c r="D56" t="s">
         <v>121</v>
       </c>
-      <c r="D56" t="s">
-        <v>113</v>
-      </c>
       <c r="E56" t="s">
-        <v>114</v>
+        <v>122</v>
       </c>
       <c r="F56" t="s">
         <v>115</v>
       </c>
       <c r="G56" t="s">
-        <v>122</v>
+        <v>116</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -3057,16 +3057,16 @@
         <v>124</v>
       </c>
       <c r="D57" t="s">
-        <v>113</v>
+        <v>125</v>
       </c>
       <c r="E57" t="s">
-        <v>114</v>
+        <v>126</v>
       </c>
       <c r="F57" t="s">
-        <v>125</v>
+        <v>115</v>
       </c>
       <c r="G57" t="s">
-        <v>126</v>
+        <v>116</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -3077,19 +3077,19 @@
         <v>8</v>
       </c>
       <c r="C58" t="s">
+        <v>112</v>
+      </c>
+      <c r="D58" t="s">
         <v>118</v>
       </c>
-      <c r="D58" t="s">
-        <v>113</v>
-      </c>
       <c r="E58" t="s">
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="F58" t="s">
         <v>115</v>
       </c>
       <c r="G58" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -3100,19 +3100,19 @@
         <v>8</v>
       </c>
       <c r="C59" t="s">
+        <v>112</v>
+      </c>
+      <c r="D59" t="s">
         <v>118</v>
       </c>
-      <c r="D59" t="s">
-        <v>113</v>
-      </c>
       <c r="E59" t="s">
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="F59" t="s">
         <v>115</v>
       </c>
       <c r="G59" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -3123,19 +3123,19 @@
         <v>8</v>
       </c>
       <c r="C60" t="s">
+        <v>112</v>
+      </c>
+      <c r="D60" t="s">
         <v>118</v>
       </c>
-      <c r="D60" t="s">
-        <v>113</v>
-      </c>
       <c r="E60" t="s">
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="F60" t="s">
         <v>115</v>
       </c>
       <c r="G60" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -3146,19 +3146,19 @@
         <v>8</v>
       </c>
       <c r="C61" t="s">
+        <v>112</v>
+      </c>
+      <c r="D61" t="s">
         <v>118</v>
       </c>
-      <c r="D61" t="s">
-        <v>113</v>
-      </c>
       <c r="E61" t="s">
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="F61" t="s">
         <v>115</v>
       </c>
       <c r="G61" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -3169,19 +3169,19 @@
         <v>8</v>
       </c>
       <c r="C62" t="s">
+        <v>112</v>
+      </c>
+      <c r="D62" t="s">
         <v>118</v>
       </c>
-      <c r="D62" t="s">
-        <v>113</v>
-      </c>
       <c r="E62" t="s">
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="F62" t="s">
         <v>115</v>
       </c>
       <c r="G62" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -3192,19 +3192,19 @@
         <v>8</v>
       </c>
       <c r="C63" t="s">
+        <v>112</v>
+      </c>
+      <c r="D63" t="s">
         <v>133</v>
       </c>
-      <c r="D63" t="s">
-        <v>113</v>
-      </c>
       <c r="E63" t="s">
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="F63" t="s">
         <v>115</v>
       </c>
       <c r="G63" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -3215,19 +3215,19 @@
         <v>8</v>
       </c>
       <c r="C64" t="s">
+        <v>112</v>
+      </c>
+      <c r="D64" t="s">
         <v>133</v>
       </c>
-      <c r="D64" t="s">
-        <v>113</v>
-      </c>
       <c r="E64" t="s">
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="F64" t="s">
         <v>115</v>
       </c>
       <c r="G64" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -3238,19 +3238,19 @@
         <v>8</v>
       </c>
       <c r="C65" t="s">
+        <v>112</v>
+      </c>
+      <c r="D65" t="s">
         <v>136</v>
       </c>
-      <c r="D65" t="s">
-        <v>113</v>
-      </c>
       <c r="E65" t="s">
-        <v>114</v>
+        <v>137</v>
       </c>
       <c r="F65" t="s">
         <v>115</v>
       </c>
       <c r="G65" t="s">
-        <v>137</v>
+        <v>116</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -3284,19 +3284,19 @@
         <v>8</v>
       </c>
       <c r="C67" t="s">
+        <v>112</v>
+      </c>
+      <c r="D67" t="s">
         <v>118</v>
       </c>
-      <c r="D67" t="s">
-        <v>113</v>
-      </c>
       <c r="E67" t="s">
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="F67" t="s">
         <v>115</v>
       </c>
       <c r="G67" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -3307,10 +3307,10 @@
         <v>8</v>
       </c>
       <c r="C68" t="s">
+        <v>112</v>
+      </c>
+      <c r="D68" t="s">
         <v>141</v>
-      </c>
-      <c r="D68" t="s">
-        <v>113</v>
       </c>
       <c r="E68" t="s">
         <v>114</v>
@@ -3330,10 +3330,10 @@
         <v>8</v>
       </c>
       <c r="C69" t="s">
+        <v>112</v>
+      </c>
+      <c r="D69" t="s">
         <v>143</v>
-      </c>
-      <c r="D69" t="s">
-        <v>113</v>
       </c>
       <c r="E69" t="s">
         <v>114</v>
@@ -3353,19 +3353,19 @@
         <v>8</v>
       </c>
       <c r="C70" t="s">
+        <v>112</v>
+      </c>
+      <c r="D70" t="s">
         <v>121</v>
       </c>
-      <c r="D70" t="s">
-        <v>113</v>
-      </c>
       <c r="E70" t="s">
-        <v>114</v>
+        <v>122</v>
       </c>
       <c r="F70" t="s">
         <v>115</v>
       </c>
       <c r="G70" t="s">
-        <v>122</v>
+        <v>116</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -3376,19 +3376,19 @@
         <v>8</v>
       </c>
       <c r="C71" t="s">
+        <v>112</v>
+      </c>
+      <c r="D71" t="s">
         <v>121</v>
       </c>
-      <c r="D71" t="s">
-        <v>113</v>
-      </c>
       <c r="E71" t="s">
-        <v>114</v>
+        <v>122</v>
       </c>
       <c r="F71" t="s">
         <v>115</v>
       </c>
       <c r="G71" t="s">
-        <v>122</v>
+        <v>116</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -3422,19 +3422,19 @@
         <v>8</v>
       </c>
       <c r="C73" t="s">
+        <v>124</v>
+      </c>
+      <c r="D73" t="s">
         <v>148</v>
       </c>
-      <c r="D73" t="s">
-        <v>113</v>
-      </c>
       <c r="E73" t="s">
-        <v>114</v>
+        <v>149</v>
       </c>
       <c r="F73" t="s">
-        <v>125</v>
+        <v>115</v>
       </c>
       <c r="G73" t="s">
-        <v>149</v>
+        <v>116</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -3445,19 +3445,19 @@
         <v>8</v>
       </c>
       <c r="C74" t="s">
+        <v>124</v>
+      </c>
+      <c r="D74" t="s">
         <v>151</v>
       </c>
-      <c r="D74" t="s">
-        <v>113</v>
-      </c>
       <c r="E74" t="s">
-        <v>114</v>
+        <v>152</v>
       </c>
       <c r="F74" t="s">
-        <v>125</v>
+        <v>115</v>
       </c>
       <c r="G74" t="s">
-        <v>152</v>
+        <v>116</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -3468,19 +3468,19 @@
         <v>8</v>
       </c>
       <c r="C75" t="s">
+        <v>124</v>
+      </c>
+      <c r="D75" t="s">
         <v>154</v>
       </c>
-      <c r="D75" t="s">
-        <v>113</v>
-      </c>
       <c r="E75" t="s">
-        <v>114</v>
+        <v>155</v>
       </c>
       <c r="F75" t="s">
-        <v>125</v>
+        <v>115</v>
       </c>
       <c r="G75" t="s">
-        <v>155</v>
+        <v>116</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -3491,19 +3491,19 @@
         <v>8</v>
       </c>
       <c r="C76" t="s">
+        <v>124</v>
+      </c>
+      <c r="D76" t="s">
         <v>148</v>
       </c>
-      <c r="D76" t="s">
-        <v>113</v>
-      </c>
       <c r="E76" t="s">
-        <v>114</v>
+        <v>149</v>
       </c>
       <c r="F76" t="s">
-        <v>125</v>
+        <v>115</v>
       </c>
       <c r="G76" t="s">
-        <v>149</v>
+        <v>116</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -3514,19 +3514,19 @@
         <v>8</v>
       </c>
       <c r="C77" t="s">
+        <v>124</v>
+      </c>
+      <c r="D77" t="s">
         <v>148</v>
       </c>
-      <c r="D77" t="s">
-        <v>113</v>
-      </c>
       <c r="E77" t="s">
-        <v>114</v>
+        <v>149</v>
       </c>
       <c r="F77" t="s">
-        <v>125</v>
+        <v>115</v>
       </c>
       <c r="G77" t="s">
-        <v>149</v>
+        <v>116</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -3537,19 +3537,19 @@
         <v>8</v>
       </c>
       <c r="C78" t="s">
+        <v>124</v>
+      </c>
+      <c r="D78" t="s">
         <v>151</v>
       </c>
-      <c r="D78" t="s">
-        <v>113</v>
-      </c>
       <c r="E78" t="s">
-        <v>114</v>
+        <v>152</v>
       </c>
       <c r="F78" t="s">
-        <v>125</v>
+        <v>115</v>
       </c>
       <c r="G78" t="s">
-        <v>152</v>
+        <v>116</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -3560,19 +3560,19 @@
         <v>8</v>
       </c>
       <c r="C79" t="s">
+        <v>124</v>
+      </c>
+      <c r="D79" t="s">
         <v>160</v>
       </c>
-      <c r="D79" t="s">
-        <v>113</v>
-      </c>
       <c r="E79" t="s">
-        <v>114</v>
+        <v>161</v>
       </c>
       <c r="F79" t="s">
-        <v>125</v>
+        <v>115</v>
       </c>
       <c r="G79" t="s">
-        <v>161</v>
+        <v>116</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -3586,16 +3586,16 @@
         <v>163</v>
       </c>
       <c r="D80" t="s">
-        <v>113</v>
+        <v>164</v>
       </c>
       <c r="E80" t="s">
-        <v>114</v>
+        <v>165</v>
       </c>
       <c r="F80" t="s">
-        <v>164</v>
+        <v>115</v>
       </c>
       <c r="G80" t="s">
-        <v>165</v>
+        <v>116</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -3609,16 +3609,16 @@
         <v>163</v>
       </c>
       <c r="D81" t="s">
-        <v>113</v>
+        <v>164</v>
       </c>
       <c r="E81" t="s">
-        <v>114</v>
+        <v>165</v>
       </c>
       <c r="F81" t="s">
-        <v>164</v>
+        <v>115</v>
       </c>
       <c r="G81" t="s">
-        <v>165</v>
+        <v>116</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -3632,16 +3632,16 @@
         <v>163</v>
       </c>
       <c r="D82" t="s">
-        <v>113</v>
+        <v>164</v>
       </c>
       <c r="E82" t="s">
-        <v>114</v>
+        <v>165</v>
       </c>
       <c r="F82" t="s">
-        <v>164</v>
+        <v>115</v>
       </c>
       <c r="G82" t="s">
-        <v>165</v>
+        <v>116</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -3652,10 +3652,10 @@
         <v>8</v>
       </c>
       <c r="C83" t="s">
+        <v>112</v>
+      </c>
+      <c r="D83" t="s">
         <v>143</v>
-      </c>
-      <c r="D83" t="s">
-        <v>113</v>
       </c>
       <c r="E83" t="s">
         <v>114</v>
@@ -3675,19 +3675,19 @@
         <v>8</v>
       </c>
       <c r="C84" t="s">
+        <v>112</v>
+      </c>
+      <c r="D84" t="s">
         <v>170</v>
       </c>
-      <c r="D84" t="s">
-        <v>113</v>
-      </c>
       <c r="E84" t="s">
-        <v>114</v>
+        <v>171</v>
       </c>
       <c r="F84" t="s">
         <v>115</v>
       </c>
       <c r="G84" t="s">
-        <v>171</v>
+        <v>116</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -3698,19 +3698,19 @@
         <v>8</v>
       </c>
       <c r="C85" t="s">
+        <v>112</v>
+      </c>
+      <c r="D85" t="s">
         <v>173</v>
       </c>
-      <c r="D85" t="s">
-        <v>113</v>
-      </c>
       <c r="E85" t="s">
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="F85" t="s">
         <v>115</v>
       </c>
       <c r="G85" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -3721,19 +3721,19 @@
         <v>8</v>
       </c>
       <c r="C86" t="s">
+        <v>163</v>
+      </c>
+      <c r="D86" t="s">
         <v>175</v>
       </c>
-      <c r="D86" t="s">
-        <v>113</v>
-      </c>
       <c r="E86" t="s">
-        <v>114</v>
+        <v>176</v>
       </c>
       <c r="F86" t="s">
-        <v>164</v>
+        <v>115</v>
       </c>
       <c r="G86" t="s">
-        <v>176</v>
+        <v>116</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -3744,19 +3744,19 @@
         <v>8</v>
       </c>
       <c r="C87" t="s">
+        <v>112</v>
+      </c>
+      <c r="D87" t="s">
         <v>173</v>
       </c>
-      <c r="D87" t="s">
-        <v>113</v>
-      </c>
       <c r="E87" t="s">
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="F87" t="s">
         <v>115</v>
       </c>
       <c r="G87" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -3767,19 +3767,19 @@
         <v>8</v>
       </c>
       <c r="C88" t="s">
+        <v>112</v>
+      </c>
+      <c r="D88" t="s">
         <v>118</v>
       </c>
-      <c r="D88" t="s">
-        <v>113</v>
-      </c>
       <c r="E88" t="s">
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="F88" t="s">
         <v>115</v>
       </c>
       <c r="G88" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -3790,19 +3790,19 @@
         <v>8</v>
       </c>
       <c r="C89" t="s">
+        <v>112</v>
+      </c>
+      <c r="D89" t="s">
         <v>118</v>
       </c>
-      <c r="D89" t="s">
-        <v>113</v>
-      </c>
       <c r="E89" t="s">
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="F89" t="s">
         <v>115</v>
       </c>
       <c r="G89" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -3816,16 +3816,16 @@
         <v>124</v>
       </c>
       <c r="D90" t="s">
-        <v>113</v>
+        <v>125</v>
       </c>
       <c r="E90" t="s">
-        <v>114</v>
+        <v>126</v>
       </c>
       <c r="F90" t="s">
-        <v>125</v>
+        <v>115</v>
       </c>
       <c r="G90" t="s">
-        <v>126</v>
+        <v>116</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -3839,16 +3839,16 @@
         <v>182</v>
       </c>
       <c r="D91" t="s">
-        <v>113</v>
+        <v>183</v>
       </c>
       <c r="E91" t="s">
-        <v>114</v>
+        <v>184</v>
       </c>
       <c r="F91" t="s">
-        <v>183</v>
+        <v>115</v>
       </c>
       <c r="G91" t="s">
-        <v>184</v>
+        <v>116</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -3862,16 +3862,16 @@
         <v>124</v>
       </c>
       <c r="D92" t="s">
-        <v>113</v>
+        <v>125</v>
       </c>
       <c r="E92" t="s">
-        <v>114</v>
+        <v>126</v>
       </c>
       <c r="F92" t="s">
-        <v>125</v>
+        <v>115</v>
       </c>
       <c r="G92" t="s">
-        <v>126</v>
+        <v>116</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -3882,19 +3882,19 @@
         <v>8</v>
       </c>
       <c r="C93" t="s">
+        <v>112</v>
+      </c>
+      <c r="D93" t="s">
         <v>121</v>
       </c>
-      <c r="D93" t="s">
-        <v>113</v>
-      </c>
       <c r="E93" t="s">
-        <v>114</v>
+        <v>122</v>
       </c>
       <c r="F93" t="s">
         <v>115</v>
       </c>
       <c r="G93" t="s">
-        <v>122</v>
+        <v>116</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -3908,16 +3908,16 @@
         <v>124</v>
       </c>
       <c r="D94" t="s">
-        <v>113</v>
+        <v>125</v>
       </c>
       <c r="E94" t="s">
-        <v>114</v>
+        <v>126</v>
       </c>
       <c r="F94" t="s">
-        <v>125</v>
+        <v>115</v>
       </c>
       <c r="G94" t="s">
-        <v>126</v>
+        <v>116</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -3928,19 +3928,19 @@
         <v>8</v>
       </c>
       <c r="C95" t="s">
+        <v>112</v>
+      </c>
+      <c r="D95" t="s">
         <v>189</v>
       </c>
-      <c r="D95" t="s">
-        <v>113</v>
-      </c>
       <c r="E95" t="s">
-        <v>114</v>
+        <v>190</v>
       </c>
       <c r="F95" t="s">
         <v>115</v>
       </c>
       <c r="G95" t="s">
-        <v>190</v>
+        <v>116</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -3954,16 +3954,16 @@
         <v>124</v>
       </c>
       <c r="D96" t="s">
+        <v>125</v>
+      </c>
+      <c r="E96" t="s">
+        <v>126</v>
+      </c>
+      <c r="F96" t="s">
+        <v>115</v>
+      </c>
+      <c r="G96" t="s">
         <v>192</v>
-      </c>
-      <c r="E96" t="s">
-        <v>114</v>
-      </c>
-      <c r="F96" t="s">
-        <v>125</v>
-      </c>
-      <c r="G96" t="s">
-        <v>126</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -3977,16 +3977,16 @@
         <v>124</v>
       </c>
       <c r="D97" t="s">
+        <v>125</v>
+      </c>
+      <c r="E97" t="s">
+        <v>126</v>
+      </c>
+      <c r="F97" t="s">
+        <v>115</v>
+      </c>
+      <c r="G97" t="s">
         <v>192</v>
-      </c>
-      <c r="E97" t="s">
-        <v>114</v>
-      </c>
-      <c r="F97" t="s">
-        <v>125</v>
-      </c>
-      <c r="G97" t="s">
-        <v>126</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -4000,16 +4000,16 @@
         <v>195</v>
       </c>
       <c r="D98" t="s">
+        <v>196</v>
+      </c>
+      <c r="E98" t="s">
+        <v>197</v>
+      </c>
+      <c r="F98" t="s">
+        <v>115</v>
+      </c>
+      <c r="G98" t="s">
         <v>192</v>
-      </c>
-      <c r="E98" t="s">
-        <v>114</v>
-      </c>
-      <c r="F98" t="s">
-        <v>196</v>
-      </c>
-      <c r="G98" t="s">
-        <v>197</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -4023,16 +4023,16 @@
         <v>124</v>
       </c>
       <c r="D99" t="s">
+        <v>125</v>
+      </c>
+      <c r="E99" t="s">
+        <v>126</v>
+      </c>
+      <c r="F99" t="s">
+        <v>115</v>
+      </c>
+      <c r="G99" t="s">
         <v>192</v>
-      </c>
-      <c r="E99" t="s">
-        <v>114</v>
-      </c>
-      <c r="F99" t="s">
-        <v>125</v>
-      </c>
-      <c r="G99" t="s">
-        <v>126</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -4043,19 +4043,19 @@
         <v>8</v>
       </c>
       <c r="C100" t="s">
+        <v>124</v>
+      </c>
+      <c r="D100" t="s">
         <v>154</v>
       </c>
-      <c r="D100" t="s">
+      <c r="E100" t="s">
+        <v>155</v>
+      </c>
+      <c r="F100" t="s">
+        <v>115</v>
+      </c>
+      <c r="G100" t="s">
         <v>192</v>
-      </c>
-      <c r="E100" t="s">
-        <v>114</v>
-      </c>
-      <c r="F100" t="s">
-        <v>125</v>
-      </c>
-      <c r="G100" t="s">
-        <v>155</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -4069,16 +4069,16 @@
         <v>124</v>
       </c>
       <c r="D101" t="s">
+        <v>125</v>
+      </c>
+      <c r="E101" t="s">
+        <v>126</v>
+      </c>
+      <c r="F101" t="s">
+        <v>115</v>
+      </c>
+      <c r="G101" t="s">
         <v>192</v>
-      </c>
-      <c r="E101" t="s">
-        <v>114</v>
-      </c>
-      <c r="F101" t="s">
-        <v>125</v>
-      </c>
-      <c r="G101" t="s">
-        <v>126</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -4089,15 +4089,15 @@
         <v>8</v>
       </c>
       <c r="C102" t="s">
+        <v>182</v>
+      </c>
+      <c r="D102" t="s">
         <v>202</v>
       </c>
       <c r="E102" t="s">
         <v>203</v>
       </c>
       <c r="F102" t="s">
-        <v>183</v>
-      </c>
-      <c r="G102" t="s">
         <v>204</v>
       </c>
     </row>
@@ -4109,15 +4109,15 @@
         <v>8</v>
       </c>
       <c r="C103" t="s">
+        <v>182</v>
+      </c>
+      <c r="D103" t="s">
         <v>202</v>
       </c>
       <c r="E103" t="s">
         <v>203</v>
       </c>
       <c r="F103" t="s">
-        <v>183</v>
-      </c>
-      <c r="G103" t="s">
         <v>204</v>
       </c>
     </row>
@@ -4129,15 +4129,15 @@
         <v>8</v>
       </c>
       <c r="C104" t="s">
+        <v>182</v>
+      </c>
+      <c r="D104" t="s">
         <v>202</v>
       </c>
       <c r="E104" t="s">
         <v>203</v>
       </c>
       <c r="F104" t="s">
-        <v>183</v>
-      </c>
-      <c r="G104" t="s">
         <v>204</v>
       </c>
     </row>
@@ -4149,16 +4149,16 @@
         <v>8</v>
       </c>
       <c r="C105" t="s">
+        <v>182</v>
+      </c>
+      <c r="D105" t="s">
         <v>208</v>
       </c>
       <c r="E105" t="s">
-        <v>203</v>
+        <v>209</v>
       </c>
       <c r="F105" t="s">
-        <v>183</v>
-      </c>
-      <c r="G105" t="s">
-        <v>209</v>
+        <v>204</v>
       </c>
     </row>
     <row r="106" spans="1:7">
@@ -4169,15 +4169,15 @@
         <v>8</v>
       </c>
       <c r="C106" t="s">
+        <v>182</v>
+      </c>
+      <c r="D106" t="s">
         <v>202</v>
       </c>
       <c r="E106" t="s">
         <v>203</v>
       </c>
       <c r="F106" t="s">
-        <v>183</v>
-      </c>
-      <c r="G106" t="s">
         <v>204</v>
       </c>
     </row>
@@ -4191,14 +4191,14 @@
       <c r="C107" t="s">
         <v>182</v>
       </c>
+      <c r="D107" t="s">
+        <v>183</v>
+      </c>
       <c r="E107" t="s">
-        <v>203</v>
+        <v>184</v>
       </c>
       <c r="F107" t="s">
-        <v>183</v>
-      </c>
-      <c r="G107" t="s">
-        <v>184</v>
+        <v>204</v>
       </c>
     </row>
     <row r="108" spans="1:7">
@@ -4209,16 +4209,16 @@
         <v>8</v>
       </c>
       <c r="C108" t="s">
+        <v>182</v>
+      </c>
+      <c r="D108" t="s">
         <v>213</v>
       </c>
       <c r="E108" t="s">
-        <v>203</v>
+        <v>214</v>
       </c>
       <c r="F108" t="s">
-        <v>183</v>
-      </c>
-      <c r="G108" t="s">
-        <v>214</v>
+        <v>204</v>
       </c>
     </row>
     <row r="109" spans="1:7">
@@ -4229,16 +4229,16 @@
         <v>8</v>
       </c>
       <c r="C109" t="s">
+        <v>90</v>
+      </c>
+      <c r="D109" t="s">
         <v>216</v>
       </c>
       <c r="E109" t="s">
-        <v>203</v>
+        <v>217</v>
       </c>
       <c r="F109" t="s">
-        <v>92</v>
-      </c>
-      <c r="G109" t="s">
-        <v>217</v>
+        <v>204</v>
       </c>
     </row>
     <row r="110" spans="1:7">
@@ -4249,16 +4249,16 @@
         <v>8</v>
       </c>
       <c r="C110" t="s">
+        <v>90</v>
+      </c>
+      <c r="D110" t="s">
         <v>219</v>
       </c>
       <c r="E110" t="s">
-        <v>203</v>
+        <v>220</v>
       </c>
       <c r="F110" t="s">
-        <v>92</v>
-      </c>
-      <c r="G110" t="s">
-        <v>220</v>
+        <v>204</v>
       </c>
     </row>
     <row r="111" spans="1:7">
@@ -4269,15 +4269,15 @@
         <v>8</v>
       </c>
       <c r="C111" t="s">
+        <v>182</v>
+      </c>
+      <c r="D111" t="s">
         <v>202</v>
       </c>
       <c r="E111" t="s">
         <v>203</v>
       </c>
       <c r="F111" t="s">
-        <v>183</v>
-      </c>
-      <c r="G111" t="s">
         <v>204</v>
       </c>
     </row>
@@ -4291,17 +4291,17 @@
       <c r="C112" t="s">
         <v>223</v>
       </c>
+      <c r="D112" t="s">
+        <v>224</v>
+      </c>
       <c r="E112" t="s">
-        <v>203</v>
+        <v>225</v>
       </c>
       <c r="F112" t="s">
-        <v>224</v>
-      </c>
-      <c r="G112" t="s">
-        <v>225</v>
-      </c>
-    </row>
-    <row r="113" spans="1:7">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="113" spans="1:6">
       <c r="A113" t="s">
         <v>226</v>
       </c>
@@ -4309,19 +4309,19 @@
         <v>8</v>
       </c>
       <c r="C113" t="s">
+        <v>112</v>
+      </c>
+      <c r="D113" t="s">
         <v>143</v>
       </c>
       <c r="E113" t="s">
-        <v>203</v>
+        <v>114</v>
       </c>
       <c r="F113" t="s">
-        <v>115</v>
-      </c>
-      <c r="G113" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="114" spans="1:7">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="114" spans="1:6">
       <c r="A114" t="s">
         <v>227</v>
       </c>
@@ -4329,19 +4329,19 @@
         <v>8</v>
       </c>
       <c r="C114" t="s">
+        <v>124</v>
+      </c>
+      <c r="D114" t="s">
         <v>151</v>
       </c>
       <c r="E114" t="s">
-        <v>203</v>
+        <v>152</v>
       </c>
       <c r="F114" t="s">
-        <v>125</v>
-      </c>
-      <c r="G114" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="115" spans="1:7">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="115" spans="1:6">
       <c r="A115" t="s">
         <v>228</v>
       </c>
@@ -4351,17 +4351,17 @@
       <c r="C115" t="s">
         <v>182</v>
       </c>
+      <c r="D115" t="s">
+        <v>183</v>
+      </c>
       <c r="E115" t="s">
-        <v>203</v>
+        <v>184</v>
       </c>
       <c r="F115" t="s">
-        <v>183</v>
-      </c>
-      <c r="G115" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="116" spans="1:7">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="116" spans="1:6">
       <c r="A116" t="s">
         <v>229</v>
       </c>
@@ -4369,19 +4369,19 @@
         <v>8</v>
       </c>
       <c r="C116" t="s">
+        <v>223</v>
+      </c>
+      <c r="D116" t="s">
         <v>230</v>
       </c>
       <c r="E116" t="s">
-        <v>203</v>
+        <v>231</v>
       </c>
       <c r="F116" t="s">
-        <v>224</v>
-      </c>
-      <c r="G116" t="s">
-        <v>231</v>
-      </c>
-    </row>
-    <row r="117" spans="1:7">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="117" spans="1:6">
       <c r="A117" t="s">
         <v>232</v>
       </c>
@@ -4391,17 +4391,17 @@
       <c r="C117" t="s">
         <v>223</v>
       </c>
+      <c r="D117" t="s">
+        <v>224</v>
+      </c>
       <c r="E117" t="s">
-        <v>203</v>
+        <v>225</v>
       </c>
       <c r="F117" t="s">
-        <v>224</v>
-      </c>
-      <c r="G117" t="s">
-        <v>225</v>
-      </c>
-    </row>
-    <row r="118" spans="1:7">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="118" spans="1:6">
       <c r="A118" t="s">
         <v>233</v>
       </c>
@@ -4409,19 +4409,19 @@
         <v>8</v>
       </c>
       <c r="C118" t="s">
+        <v>163</v>
+      </c>
+      <c r="D118" t="s">
         <v>234</v>
       </c>
       <c r="E118" t="s">
-        <v>203</v>
+        <v>165</v>
       </c>
       <c r="F118" t="s">
-        <v>164</v>
-      </c>
-      <c r="G118" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="119" spans="1:7">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="119" spans="1:6">
       <c r="A119" t="s">
         <v>235</v>
       </c>
@@ -4431,17 +4431,17 @@
       <c r="C119" t="s">
         <v>182</v>
       </c>
+      <c r="D119" t="s">
+        <v>183</v>
+      </c>
       <c r="E119" t="s">
-        <v>203</v>
+        <v>184</v>
       </c>
       <c r="F119" t="s">
-        <v>183</v>
-      </c>
-      <c r="G119" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="120" spans="1:7">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="120" spans="1:6">
       <c r="A120" t="s">
         <v>236</v>
       </c>
@@ -4449,19 +4449,19 @@
         <v>8</v>
       </c>
       <c r="C120" t="s">
+        <v>112</v>
+      </c>
+      <c r="D120" t="s">
         <v>170</v>
       </c>
       <c r="E120" t="s">
+        <v>171</v>
+      </c>
+      <c r="F120" t="s">
         <v>237</v>
       </c>
-      <c r="F120" t="s">
-        <v>115</v>
-      </c>
-      <c r="G120" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="121" spans="1:7">
+    </row>
+    <row r="121" spans="1:6">
       <c r="A121" t="s">
         <v>238</v>
       </c>
@@ -4469,19 +4469,19 @@
         <v>8</v>
       </c>
       <c r="C121" t="s">
+        <v>112</v>
+      </c>
+      <c r="D121" t="s">
         <v>143</v>
       </c>
       <c r="E121" t="s">
+        <v>114</v>
+      </c>
+      <c r="F121" t="s">
         <v>237</v>
       </c>
-      <c r="F121" t="s">
-        <v>115</v>
-      </c>
-      <c r="G121" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="122" spans="1:7">
+    </row>
+    <row r="122" spans="1:6">
       <c r="A122" t="s">
         <v>239</v>
       </c>
@@ -4489,19 +4489,19 @@
         <v>8</v>
       </c>
       <c r="C122" t="s">
+        <v>112</v>
+      </c>
+      <c r="D122" t="s">
         <v>170</v>
       </c>
       <c r="E122" t="s">
+        <v>171</v>
+      </c>
+      <c r="F122" t="s">
         <v>237</v>
       </c>
-      <c r="F122" t="s">
-        <v>115</v>
-      </c>
-      <c r="G122" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="123" spans="1:7">
+    </row>
+    <row r="123" spans="1:6">
       <c r="A123" t="s">
         <v>240</v>
       </c>
@@ -4509,19 +4509,19 @@
         <v>8</v>
       </c>
       <c r="C123" t="s">
+        <v>112</v>
+      </c>
+      <c r="D123" t="s">
         <v>170</v>
       </c>
       <c r="E123" t="s">
+        <v>171</v>
+      </c>
+      <c r="F123" t="s">
         <v>237</v>
       </c>
-      <c r="F123" t="s">
-        <v>115</v>
-      </c>
-      <c r="G123" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="124" spans="1:7">
+    </row>
+    <row r="124" spans="1:6">
       <c r="A124" t="s">
         <v>241</v>
       </c>
@@ -4529,19 +4529,19 @@
         <v>8</v>
       </c>
       <c r="C124" t="s">
+        <v>163</v>
+      </c>
+      <c r="D124" t="s">
         <v>242</v>
       </c>
       <c r="E124" t="s">
+        <v>243</v>
+      </c>
+      <c r="F124" t="s">
         <v>237</v>
       </c>
-      <c r="F124" t="s">
-        <v>164</v>
-      </c>
-      <c r="G124" t="s">
-        <v>243</v>
-      </c>
-    </row>
-    <row r="125" spans="1:7">
+    </row>
+    <row r="125" spans="1:6">
       <c r="A125" t="s">
         <v>244</v>
       </c>
@@ -4549,19 +4549,19 @@
         <v>8</v>
       </c>
       <c r="C125" t="s">
+        <v>163</v>
+      </c>
+      <c r="D125" t="s">
         <v>242</v>
       </c>
       <c r="E125" t="s">
+        <v>243</v>
+      </c>
+      <c r="F125" t="s">
         <v>237</v>
       </c>
-      <c r="F125" t="s">
-        <v>164</v>
-      </c>
-      <c r="G125" t="s">
-        <v>243</v>
-      </c>
-    </row>
-    <row r="126" spans="1:7">
+    </row>
+    <row r="126" spans="1:6">
       <c r="A126" t="s">
         <v>245</v>
       </c>
@@ -4569,19 +4569,19 @@
         <v>8</v>
       </c>
       <c r="C126" t="s">
+        <v>163</v>
+      </c>
+      <c r="D126" t="s">
         <v>242</v>
       </c>
       <c r="E126" t="s">
+        <v>243</v>
+      </c>
+      <c r="F126" t="s">
         <v>237</v>
       </c>
-      <c r="F126" t="s">
-        <v>164</v>
-      </c>
-      <c r="G126" t="s">
-        <v>243</v>
-      </c>
-    </row>
-    <row r="127" spans="1:7">
+    </row>
+    <row r="127" spans="1:6">
       <c r="A127" t="s">
         <v>246</v>
       </c>
@@ -4589,19 +4589,19 @@
         <v>8</v>
       </c>
       <c r="C127" t="s">
+        <v>163</v>
+      </c>
+      <c r="D127" t="s">
         <v>242</v>
       </c>
       <c r="E127" t="s">
+        <v>243</v>
+      </c>
+      <c r="F127" t="s">
         <v>237</v>
       </c>
-      <c r="F127" t="s">
-        <v>164</v>
-      </c>
-      <c r="G127" t="s">
-        <v>243</v>
-      </c>
-    </row>
-    <row r="128" spans="1:7">
+    </row>
+    <row r="128" spans="1:6">
       <c r="A128" t="s">
         <v>247</v>
       </c>
@@ -4609,16 +4609,16 @@
         <v>8</v>
       </c>
       <c r="C128" t="s">
+        <v>163</v>
+      </c>
+      <c r="D128" t="s">
         <v>242</v>
       </c>
       <c r="E128" t="s">
+        <v>243</v>
+      </c>
+      <c r="F128" t="s">
         <v>237</v>
-      </c>
-      <c r="F128" t="s">
-        <v>164</v>
-      </c>
-      <c r="G128" t="s">
-        <v>243</v>
       </c>
     </row>
     <row r="129" spans="1:7">
@@ -4629,16 +4629,16 @@
         <v>8</v>
       </c>
       <c r="C129" t="s">
+        <v>163</v>
+      </c>
+      <c r="D129" t="s">
         <v>249</v>
       </c>
       <c r="E129" t="s">
+        <v>243</v>
+      </c>
+      <c r="F129" t="s">
         <v>237</v>
-      </c>
-      <c r="F129" t="s">
-        <v>164</v>
-      </c>
-      <c r="G129" t="s">
-        <v>243</v>
       </c>
     </row>
     <row r="130" spans="1:7">
@@ -4649,16 +4649,16 @@
         <v>8</v>
       </c>
       <c r="C130" t="s">
+        <v>163</v>
+      </c>
+      <c r="D130" t="s">
         <v>251</v>
       </c>
       <c r="E130" t="s">
+        <v>243</v>
+      </c>
+      <c r="F130" t="s">
         <v>237</v>
-      </c>
-      <c r="F130" t="s">
-        <v>164</v>
-      </c>
-      <c r="G130" t="s">
-        <v>243</v>
       </c>
     </row>
     <row r="131" spans="1:7">
@@ -4669,16 +4669,16 @@
         <v>8</v>
       </c>
       <c r="C131" t="s">
+        <v>163</v>
+      </c>
+      <c r="D131" t="s">
         <v>253</v>
       </c>
       <c r="E131" t="s">
+        <v>243</v>
+      </c>
+      <c r="F131" t="s">
         <v>237</v>
-      </c>
-      <c r="F131" t="s">
-        <v>164</v>
-      </c>
-      <c r="G131" t="s">
-        <v>243</v>
       </c>
     </row>
     <row r="132" spans="1:7">
@@ -4689,16 +4689,16 @@
         <v>8</v>
       </c>
       <c r="C132" t="s">
+        <v>163</v>
+      </c>
+      <c r="D132" t="s">
         <v>255</v>
       </c>
       <c r="E132" t="s">
+        <v>256</v>
+      </c>
+      <c r="F132" t="s">
         <v>237</v>
-      </c>
-      <c r="F132" t="s">
-        <v>164</v>
-      </c>
-      <c r="G132" t="s">
-        <v>256</v>
       </c>
     </row>
     <row r="133" spans="1:7">
@@ -4709,16 +4709,16 @@
         <v>8</v>
       </c>
       <c r="C133" t="s">
+        <v>112</v>
+      </c>
+      <c r="D133" t="s">
         <v>189</v>
       </c>
       <c r="E133" t="s">
+        <v>190</v>
+      </c>
+      <c r="F133" t="s">
         <v>237</v>
-      </c>
-      <c r="F133" t="s">
-        <v>115</v>
-      </c>
-      <c r="G133" t="s">
-        <v>190</v>
       </c>
     </row>
     <row r="134" spans="1:7">
@@ -4729,16 +4729,16 @@
         <v>8</v>
       </c>
       <c r="C134" t="s">
+        <v>163</v>
+      </c>
+      <c r="D134" t="s">
         <v>175</v>
       </c>
       <c r="E134" t="s">
+        <v>176</v>
+      </c>
+      <c r="F134" t="s">
         <v>259</v>
-      </c>
-      <c r="F134" t="s">
-        <v>164</v>
-      </c>
-      <c r="G134" t="s">
-        <v>176</v>
       </c>
     </row>
     <row r="135" spans="1:7">
@@ -4749,16 +4749,16 @@
         <v>8</v>
       </c>
       <c r="C135" t="s">
+        <v>163</v>
+      </c>
+      <c r="D135" t="s">
         <v>175</v>
       </c>
       <c r="E135" t="s">
+        <v>176</v>
+      </c>
+      <c r="F135" t="s">
         <v>259</v>
-      </c>
-      <c r="F135" t="s">
-        <v>164</v>
-      </c>
-      <c r="G135" t="s">
-        <v>176</v>
       </c>
     </row>
     <row r="136" spans="1:7">
@@ -4769,16 +4769,16 @@
         <v>8</v>
       </c>
       <c r="C136" t="s">
+        <v>163</v>
+      </c>
+      <c r="D136" t="s">
         <v>175</v>
       </c>
       <c r="E136" t="s">
+        <v>176</v>
+      </c>
+      <c r="F136" t="s">
         <v>259</v>
-      </c>
-      <c r="F136" t="s">
-        <v>164</v>
-      </c>
-      <c r="G136" t="s">
-        <v>176</v>
       </c>
     </row>
     <row r="137" spans="1:7">
@@ -4789,16 +4789,16 @@
         <v>8</v>
       </c>
       <c r="C137" t="s">
+        <v>163</v>
+      </c>
+      <c r="D137" t="s">
         <v>175</v>
       </c>
       <c r="E137" t="s">
+        <v>176</v>
+      </c>
+      <c r="F137" t="s">
         <v>259</v>
-      </c>
-      <c r="F137" t="s">
-        <v>164</v>
-      </c>
-      <c r="G137" t="s">
-        <v>176</v>
       </c>
     </row>
     <row r="138" spans="1:7">
@@ -4809,16 +4809,16 @@
         <v>8</v>
       </c>
       <c r="C138" t="s">
+        <v>163</v>
+      </c>
+      <c r="D138" t="s">
         <v>175</v>
       </c>
       <c r="E138" t="s">
+        <v>176</v>
+      </c>
+      <c r="F138" t="s">
         <v>259</v>
-      </c>
-      <c r="F138" t="s">
-        <v>164</v>
-      </c>
-      <c r="G138" t="s">
-        <v>176</v>
       </c>
     </row>
     <row r="139" spans="1:7">
@@ -4829,16 +4829,16 @@
         <v>8</v>
       </c>
       <c r="C139" t="s">
+        <v>223</v>
+      </c>
+      <c r="D139" t="s">
         <v>265</v>
       </c>
       <c r="E139" t="s">
+        <v>266</v>
+      </c>
+      <c r="F139" t="s">
         <v>259</v>
-      </c>
-      <c r="F139" t="s">
-        <v>224</v>
-      </c>
-      <c r="G139" t="s">
-        <v>266</v>
       </c>
     </row>
     <row r="140" spans="1:7">
@@ -4849,16 +4849,16 @@
         <v>8</v>
       </c>
       <c r="C140" t="s">
+        <v>163</v>
+      </c>
+      <c r="D140" t="s">
         <v>175</v>
       </c>
       <c r="E140" t="s">
+        <v>176</v>
+      </c>
+      <c r="F140" t="s">
         <v>259</v>
-      </c>
-      <c r="F140" t="s">
-        <v>164</v>
-      </c>
-      <c r="G140" t="s">
-        <v>176</v>
       </c>
     </row>
     <row r="141" spans="1:7">
@@ -4869,16 +4869,16 @@
         <v>8</v>
       </c>
       <c r="C141" t="s">
+        <v>163</v>
+      </c>
+      <c r="D141" t="s">
         <v>269</v>
       </c>
-      <c r="D141" t="s">
+      <c r="E141" t="s">
         <v>270</v>
       </c>
-      <c r="E141" t="s">
+      <c r="F141" t="s">
         <v>271</v>
-      </c>
-      <c r="F141" t="s">
-        <v>164</v>
       </c>
       <c r="G141" t="s">
         <v>272</v>
@@ -4892,16 +4892,16 @@
         <v>8</v>
       </c>
       <c r="C142" t="s">
+        <v>163</v>
+      </c>
+      <c r="D142" t="s">
         <v>269</v>
       </c>
-      <c r="D142" t="s">
+      <c r="E142" t="s">
         <v>270</v>
       </c>
-      <c r="E142" t="s">
+      <c r="F142" t="s">
         <v>271</v>
-      </c>
-      <c r="F142" t="s">
-        <v>164</v>
       </c>
       <c r="G142" t="s">
         <v>272</v>
@@ -4915,19 +4915,19 @@
         <v>8</v>
       </c>
       <c r="C143" t="s">
+        <v>163</v>
+      </c>
+      <c r="D143" t="s">
         <v>275</v>
       </c>
-      <c r="D143" t="s">
-        <v>270</v>
-      </c>
       <c r="E143" t="s">
+        <v>276</v>
+      </c>
+      <c r="F143" t="s">
         <v>271</v>
       </c>
-      <c r="F143" t="s">
-        <v>164</v>
-      </c>
       <c r="G143" t="s">
-        <v>276</v>
+        <v>272</v>
       </c>
     </row>
     <row r="144" spans="1:7">
@@ -4938,19 +4938,19 @@
         <v>8</v>
       </c>
       <c r="C144" t="s">
+        <v>163</v>
+      </c>
+      <c r="D144" t="s">
         <v>275</v>
       </c>
-      <c r="D144" t="s">
-        <v>270</v>
-      </c>
       <c r="E144" t="s">
+        <v>276</v>
+      </c>
+      <c r="F144" t="s">
         <v>271</v>
       </c>
-      <c r="F144" t="s">
-        <v>164</v>
-      </c>
       <c r="G144" t="s">
-        <v>276</v>
+        <v>272</v>
       </c>
     </row>
     <row r="145" spans="1:7">
@@ -4961,19 +4961,19 @@
         <v>8</v>
       </c>
       <c r="C145" t="s">
+        <v>163</v>
+      </c>
+      <c r="D145" t="s">
         <v>275</v>
       </c>
-      <c r="D145" t="s">
-        <v>270</v>
-      </c>
       <c r="E145" t="s">
+        <v>276</v>
+      </c>
+      <c r="F145" t="s">
         <v>271</v>
       </c>
-      <c r="F145" t="s">
-        <v>164</v>
-      </c>
       <c r="G145" t="s">
-        <v>276</v>
+        <v>272</v>
       </c>
     </row>
     <row r="146" spans="1:7">
@@ -4984,16 +4984,16 @@
         <v>8</v>
       </c>
       <c r="C146" t="s">
+        <v>163</v>
+      </c>
+      <c r="D146" t="s">
         <v>269</v>
       </c>
-      <c r="D146" t="s">
+      <c r="E146" t="s">
         <v>270</v>
       </c>
-      <c r="E146" t="s">
+      <c r="F146" t="s">
         <v>271</v>
-      </c>
-      <c r="F146" t="s">
-        <v>164</v>
       </c>
       <c r="G146" t="s">
         <v>272</v>
@@ -5007,19 +5007,19 @@
         <v>8</v>
       </c>
       <c r="C147" t="s">
+        <v>163</v>
+      </c>
+      <c r="D147" t="s">
         <v>269</v>
       </c>
-      <c r="D147" t="s">
+      <c r="E147" t="s">
+        <v>270</v>
+      </c>
+      <c r="F147" t="s">
+        <v>271</v>
+      </c>
+      <c r="G147" t="s">
         <v>281</v>
-      </c>
-      <c r="E147" t="s">
-        <v>271</v>
-      </c>
-      <c r="F147" t="s">
-        <v>164</v>
-      </c>
-      <c r="G147" t="s">
-        <v>272</v>
       </c>
     </row>
     <row r="148" spans="1:7">
@@ -5030,19 +5030,19 @@
         <v>8</v>
       </c>
       <c r="C148" t="s">
+        <v>163</v>
+      </c>
+      <c r="D148" t="s">
         <v>269</v>
       </c>
-      <c r="D148" t="s">
+      <c r="E148" t="s">
+        <v>270</v>
+      </c>
+      <c r="F148" t="s">
+        <v>271</v>
+      </c>
+      <c r="G148" t="s">
         <v>281</v>
-      </c>
-      <c r="E148" t="s">
-        <v>271</v>
-      </c>
-      <c r="F148" t="s">
-        <v>164</v>
-      </c>
-      <c r="G148" t="s">
-        <v>272</v>
       </c>
     </row>
     <row r="149" spans="1:7">
@@ -5053,19 +5053,19 @@
         <v>8</v>
       </c>
       <c r="C149" t="s">
+        <v>163</v>
+      </c>
+      <c r="D149" t="s">
         <v>269</v>
       </c>
-      <c r="D149" t="s">
+      <c r="E149" t="s">
+        <v>270</v>
+      </c>
+      <c r="F149" t="s">
+        <v>271</v>
+      </c>
+      <c r="G149" t="s">
         <v>281</v>
-      </c>
-      <c r="E149" t="s">
-        <v>271</v>
-      </c>
-      <c r="F149" t="s">
-        <v>164</v>
-      </c>
-      <c r="G149" t="s">
-        <v>272</v>
       </c>
     </row>
     <row r="150" spans="1:7">
@@ -5076,19 +5076,19 @@
         <v>8</v>
       </c>
       <c r="C150" t="s">
+        <v>163</v>
+      </c>
+      <c r="D150" t="s">
         <v>269</v>
       </c>
-      <c r="D150" t="s">
+      <c r="E150" t="s">
+        <v>270</v>
+      </c>
+      <c r="F150" t="s">
+        <v>271</v>
+      </c>
+      <c r="G150" t="s">
         <v>281</v>
-      </c>
-      <c r="E150" t="s">
-        <v>271</v>
-      </c>
-      <c r="F150" t="s">
-        <v>164</v>
-      </c>
-      <c r="G150" t="s">
-        <v>272</v>
       </c>
     </row>
     <row r="151" spans="1:7">
@@ -5099,19 +5099,19 @@
         <v>8</v>
       </c>
       <c r="C151" t="s">
+        <v>163</v>
+      </c>
+      <c r="D151" t="s">
         <v>269</v>
       </c>
-      <c r="D151" t="s">
+      <c r="E151" t="s">
+        <v>270</v>
+      </c>
+      <c r="F151" t="s">
+        <v>271</v>
+      </c>
+      <c r="G151" t="s">
         <v>281</v>
-      </c>
-      <c r="E151" t="s">
-        <v>271</v>
-      </c>
-      <c r="F151" t="s">
-        <v>164</v>
-      </c>
-      <c r="G151" t="s">
-        <v>272</v>
       </c>
     </row>
     <row r="152" spans="1:7">
@@ -5122,19 +5122,19 @@
         <v>8</v>
       </c>
       <c r="C152" t="s">
+        <v>163</v>
+      </c>
+      <c r="D152" t="s">
         <v>269</v>
       </c>
-      <c r="D152" t="s">
+      <c r="E152" t="s">
+        <v>270</v>
+      </c>
+      <c r="F152" t="s">
+        <v>271</v>
+      </c>
+      <c r="G152" t="s">
         <v>281</v>
-      </c>
-      <c r="E152" t="s">
-        <v>271</v>
-      </c>
-      <c r="F152" t="s">
-        <v>164</v>
-      </c>
-      <c r="G152" t="s">
-        <v>272</v>
       </c>
     </row>
     <row r="153" spans="1:7">
@@ -5145,19 +5145,19 @@
         <v>8</v>
       </c>
       <c r="C153" t="s">
+        <v>163</v>
+      </c>
+      <c r="D153" t="s">
         <v>269</v>
       </c>
-      <c r="D153" t="s">
+      <c r="E153" t="s">
+        <v>270</v>
+      </c>
+      <c r="F153" t="s">
+        <v>271</v>
+      </c>
+      <c r="G153" t="s">
         <v>281</v>
-      </c>
-      <c r="E153" t="s">
-        <v>271</v>
-      </c>
-      <c r="F153" t="s">
-        <v>164</v>
-      </c>
-      <c r="G153" t="s">
-        <v>272</v>
       </c>
     </row>
     <row r="154" spans="1:7">
@@ -5168,19 +5168,19 @@
         <v>8</v>
       </c>
       <c r="C154" t="s">
+        <v>163</v>
+      </c>
+      <c r="D154" t="s">
         <v>269</v>
       </c>
-      <c r="D154" t="s">
+      <c r="E154" t="s">
+        <v>270</v>
+      </c>
+      <c r="F154" t="s">
+        <v>271</v>
+      </c>
+      <c r="G154" t="s">
         <v>281</v>
-      </c>
-      <c r="E154" t="s">
-        <v>271</v>
-      </c>
-      <c r="F154" t="s">
-        <v>164</v>
-      </c>
-      <c r="G154" t="s">
-        <v>272</v>
       </c>
     </row>
     <row r="155" spans="1:7">
@@ -5191,19 +5191,19 @@
         <v>8</v>
       </c>
       <c r="C155" t="s">
+        <v>163</v>
+      </c>
+      <c r="D155" t="s">
         <v>269</v>
       </c>
-      <c r="D155" t="s">
+      <c r="E155" t="s">
+        <v>270</v>
+      </c>
+      <c r="F155" t="s">
+        <v>271</v>
+      </c>
+      <c r="G155" t="s">
         <v>281</v>
-      </c>
-      <c r="E155" t="s">
-        <v>271</v>
-      </c>
-      <c r="F155" t="s">
-        <v>164</v>
-      </c>
-      <c r="G155" t="s">
-        <v>272</v>
       </c>
     </row>
     <row r="156" spans="1:7">
@@ -5214,19 +5214,19 @@
         <v>8</v>
       </c>
       <c r="C156" t="s">
+        <v>163</v>
+      </c>
+      <c r="D156" t="s">
         <v>269</v>
       </c>
-      <c r="D156" t="s">
+      <c r="E156" t="s">
+        <v>270</v>
+      </c>
+      <c r="F156" t="s">
+        <v>271</v>
+      </c>
+      <c r="G156" t="s">
         <v>291</v>
-      </c>
-      <c r="E156" t="s">
-        <v>271</v>
-      </c>
-      <c r="F156" t="s">
-        <v>164</v>
-      </c>
-      <c r="G156" t="s">
-        <v>272</v>
       </c>
     </row>
     <row r="157" spans="1:7">
@@ -5237,19 +5237,19 @@
         <v>8</v>
       </c>
       <c r="C157" t="s">
+        <v>163</v>
+      </c>
+      <c r="D157" t="s">
         <v>293</v>
       </c>
-      <c r="D157" t="s">
+      <c r="E157" t="s">
+        <v>270</v>
+      </c>
+      <c r="F157" t="s">
+        <v>271</v>
+      </c>
+      <c r="G157" t="s">
         <v>291</v>
-      </c>
-      <c r="E157" t="s">
-        <v>271</v>
-      </c>
-      <c r="F157" t="s">
-        <v>164</v>
-      </c>
-      <c r="G157" t="s">
-        <v>272</v>
       </c>
     </row>
     <row r="158" spans="1:7">
@@ -5260,19 +5260,19 @@
         <v>8</v>
       </c>
       <c r="C158" t="s">
+        <v>163</v>
+      </c>
+      <c r="D158" t="s">
         <v>269</v>
       </c>
-      <c r="D158" t="s">
+      <c r="E158" t="s">
+        <v>270</v>
+      </c>
+      <c r="F158" t="s">
+        <v>271</v>
+      </c>
+      <c r="G158" t="s">
         <v>291</v>
-      </c>
-      <c r="E158" t="s">
-        <v>271</v>
-      </c>
-      <c r="F158" t="s">
-        <v>164</v>
-      </c>
-      <c r="G158" t="s">
-        <v>272</v>
       </c>
     </row>
     <row r="159" spans="1:7">
@@ -5283,19 +5283,19 @@
         <v>8</v>
       </c>
       <c r="C159" t="s">
+        <v>163</v>
+      </c>
+      <c r="D159" t="s">
         <v>269</v>
       </c>
-      <c r="D159" t="s">
+      <c r="E159" t="s">
+        <v>270</v>
+      </c>
+      <c r="F159" t="s">
+        <v>271</v>
+      </c>
+      <c r="G159" t="s">
         <v>291</v>
-      </c>
-      <c r="E159" t="s">
-        <v>271</v>
-      </c>
-      <c r="F159" t="s">
-        <v>164</v>
-      </c>
-      <c r="G159" t="s">
-        <v>272</v>
       </c>
     </row>
     <row r="160" spans="1:7">
@@ -5306,19 +5306,19 @@
         <v>8</v>
       </c>
       <c r="C160" t="s">
+        <v>163</v>
+      </c>
+      <c r="D160" t="s">
         <v>269</v>
       </c>
-      <c r="D160" t="s">
+      <c r="E160" t="s">
+        <v>270</v>
+      </c>
+      <c r="F160" t="s">
+        <v>271</v>
+      </c>
+      <c r="G160" t="s">
         <v>291</v>
-      </c>
-      <c r="E160" t="s">
-        <v>271</v>
-      </c>
-      <c r="F160" t="s">
-        <v>164</v>
-      </c>
-      <c r="G160" t="s">
-        <v>272</v>
       </c>
     </row>
     <row r="161" spans="1:7">
@@ -5329,19 +5329,19 @@
         <v>8</v>
       </c>
       <c r="C161" t="s">
+        <v>163</v>
+      </c>
+      <c r="D161" t="s">
         <v>269</v>
       </c>
-      <c r="D161" t="s">
+      <c r="E161" t="s">
+        <v>270</v>
+      </c>
+      <c r="F161" t="s">
+        <v>271</v>
+      </c>
+      <c r="G161" t="s">
         <v>291</v>
-      </c>
-      <c r="E161" t="s">
-        <v>271</v>
-      </c>
-      <c r="F161" t="s">
-        <v>164</v>
-      </c>
-      <c r="G161" t="s">
-        <v>272</v>
       </c>
     </row>
     <row r="162" spans="1:7">
@@ -5352,19 +5352,19 @@
         <v>8</v>
       </c>
       <c r="C162" t="s">
+        <v>163</v>
+      </c>
+      <c r="D162" t="s">
         <v>269</v>
       </c>
-      <c r="D162" t="s">
+      <c r="E162" t="s">
+        <v>270</v>
+      </c>
+      <c r="F162" t="s">
+        <v>271</v>
+      </c>
+      <c r="G162" t="s">
         <v>299</v>
-      </c>
-      <c r="E162" t="s">
-        <v>271</v>
-      </c>
-      <c r="F162" t="s">
-        <v>164</v>
-      </c>
-      <c r="G162" t="s">
-        <v>272</v>
       </c>
     </row>
     <row r="163" spans="1:7">
@@ -5375,19 +5375,19 @@
         <v>8</v>
       </c>
       <c r="C163" t="s">
+        <v>163</v>
+      </c>
+      <c r="D163" t="s">
         <v>301</v>
       </c>
-      <c r="D163" t="s">
+      <c r="E163" t="s">
+        <v>270</v>
+      </c>
+      <c r="F163" t="s">
+        <v>271</v>
+      </c>
+      <c r="G163" t="s">
         <v>302</v>
-      </c>
-      <c r="E163" t="s">
-        <v>271</v>
-      </c>
-      <c r="F163" t="s">
-        <v>164</v>
-      </c>
-      <c r="G163" t="s">
-        <v>272</v>
       </c>
     </row>
     <row r="164" spans="1:7">
@@ -5398,19 +5398,19 @@
         <v>8</v>
       </c>
       <c r="C164" t="s">
+        <v>163</v>
+      </c>
+      <c r="D164" t="s">
         <v>269</v>
       </c>
-      <c r="D164" t="s">
+      <c r="E164" t="s">
+        <v>270</v>
+      </c>
+      <c r="F164" t="s">
+        <v>271</v>
+      </c>
+      <c r="G164" t="s">
         <v>304</v>
-      </c>
-      <c r="E164" t="s">
-        <v>271</v>
-      </c>
-      <c r="F164" t="s">
-        <v>164</v>
-      </c>
-      <c r="G164" t="s">
-        <v>272</v>
       </c>
     </row>
     <row r="165" spans="1:7">
@@ -5421,19 +5421,19 @@
         <v>8</v>
       </c>
       <c r="C165" t="s">
+        <v>163</v>
+      </c>
+      <c r="D165" t="s">
         <v>269</v>
       </c>
-      <c r="D165" t="s">
+      <c r="E165" t="s">
+        <v>270</v>
+      </c>
+      <c r="F165" t="s">
+        <v>271</v>
+      </c>
+      <c r="G165" t="s">
         <v>304</v>
-      </c>
-      <c r="E165" t="s">
-        <v>271</v>
-      </c>
-      <c r="F165" t="s">
-        <v>164</v>
-      </c>
-      <c r="G165" t="s">
-        <v>272</v>
       </c>
     </row>
     <row r="166" spans="1:7">
@@ -5444,19 +5444,19 @@
         <v>8</v>
       </c>
       <c r="C166" t="s">
+        <v>163</v>
+      </c>
+      <c r="D166" t="s">
         <v>269</v>
       </c>
-      <c r="D166" t="s">
+      <c r="E166" t="s">
+        <v>270</v>
+      </c>
+      <c r="F166" t="s">
+        <v>271</v>
+      </c>
+      <c r="G166" t="s">
         <v>304</v>
-      </c>
-      <c r="E166" t="s">
-        <v>271</v>
-      </c>
-      <c r="F166" t="s">
-        <v>164</v>
-      </c>
-      <c r="G166" t="s">
-        <v>272</v>
       </c>
     </row>
     <row r="167" spans="1:7">
@@ -5467,19 +5467,19 @@
         <v>8</v>
       </c>
       <c r="C167" t="s">
+        <v>163</v>
+      </c>
+      <c r="D167" t="s">
         <v>269</v>
       </c>
-      <c r="D167" t="s">
+      <c r="E167" t="s">
+        <v>270</v>
+      </c>
+      <c r="F167" t="s">
+        <v>271</v>
+      </c>
+      <c r="G167" t="s">
         <v>304</v>
-      </c>
-      <c r="E167" t="s">
-        <v>271</v>
-      </c>
-      <c r="F167" t="s">
-        <v>164</v>
-      </c>
-      <c r="G167" t="s">
-        <v>272</v>
       </c>
     </row>
     <row r="168" spans="1:7">
@@ -5490,19 +5490,19 @@
         <v>8</v>
       </c>
       <c r="C168" t="s">
+        <v>163</v>
+      </c>
+      <c r="D168" t="s">
         <v>309</v>
       </c>
-      <c r="D168" t="s">
+      <c r="E168" t="s">
+        <v>270</v>
+      </c>
+      <c r="F168" t="s">
+        <v>271</v>
+      </c>
+      <c r="G168" t="s">
         <v>304</v>
-      </c>
-      <c r="E168" t="s">
-        <v>271</v>
-      </c>
-      <c r="F168" t="s">
-        <v>164</v>
-      </c>
-      <c r="G168" t="s">
-        <v>272</v>
       </c>
     </row>
     <row r="169" spans="1:7">
@@ -5513,19 +5513,19 @@
         <v>8</v>
       </c>
       <c r="C169" t="s">
+        <v>163</v>
+      </c>
+      <c r="D169" t="s">
         <v>309</v>
       </c>
-      <c r="D169" t="s">
+      <c r="E169" t="s">
+        <v>270</v>
+      </c>
+      <c r="F169" t="s">
+        <v>271</v>
+      </c>
+      <c r="G169" t="s">
         <v>304</v>
-      </c>
-      <c r="E169" t="s">
-        <v>271</v>
-      </c>
-      <c r="F169" t="s">
-        <v>164</v>
-      </c>
-      <c r="G169" t="s">
-        <v>272</v>
       </c>
     </row>
     <row r="170" spans="1:7">
@@ -5536,19 +5536,19 @@
         <v>8</v>
       </c>
       <c r="C170" t="s">
+        <v>163</v>
+      </c>
+      <c r="D170" t="s">
         <v>269</v>
       </c>
-      <c r="D170" t="s">
+      <c r="E170" t="s">
+        <v>270</v>
+      </c>
+      <c r="F170" t="s">
+        <v>271</v>
+      </c>
+      <c r="G170" t="s">
         <v>304</v>
-      </c>
-      <c r="E170" t="s">
-        <v>271</v>
-      </c>
-      <c r="F170" t="s">
-        <v>164</v>
-      </c>
-      <c r="G170" t="s">
-        <v>272</v>
       </c>
     </row>
     <row r="171" spans="1:7">
@@ -5561,14 +5561,14 @@
       <c r="C171" t="s">
         <v>163</v>
       </c>
+      <c r="D171" t="s">
+        <v>164</v>
+      </c>
       <c r="E171" t="s">
+        <v>165</v>
+      </c>
+      <c r="F171" t="s">
         <v>313</v>
-      </c>
-      <c r="F171" t="s">
-        <v>164</v>
-      </c>
-      <c r="G171" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="172" spans="1:7">
@@ -5579,16 +5579,16 @@
         <v>8</v>
       </c>
       <c r="C172" t="s">
+        <v>112</v>
+      </c>
+      <c r="D172" t="s">
         <v>118</v>
       </c>
       <c r="E172" t="s">
+        <v>119</v>
+      </c>
+      <c r="F172" t="s">
         <v>313</v>
-      </c>
-      <c r="F172" t="s">
-        <v>115</v>
-      </c>
-      <c r="G172" t="s">
-        <v>119</v>
       </c>
     </row>
     <row r="173" spans="1:7">
@@ -5601,14 +5601,14 @@
       <c r="C173" t="s">
         <v>163</v>
       </c>
+      <c r="D173" t="s">
+        <v>164</v>
+      </c>
       <c r="E173" t="s">
+        <v>165</v>
+      </c>
+      <c r="F173" t="s">
         <v>313</v>
-      </c>
-      <c r="F173" t="s">
-        <v>164</v>
-      </c>
-      <c r="G173" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="174" spans="1:7">
@@ -5621,14 +5621,14 @@
       <c r="C174" t="s">
         <v>163</v>
       </c>
+      <c r="D174" t="s">
+        <v>164</v>
+      </c>
       <c r="E174" t="s">
+        <v>165</v>
+      </c>
+      <c r="F174" t="s">
         <v>313</v>
-      </c>
-      <c r="F174" t="s">
-        <v>164</v>
-      </c>
-      <c r="G174" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="175" spans="1:7">
@@ -5641,14 +5641,14 @@
       <c r="C175" t="s">
         <v>163</v>
       </c>
+      <c r="D175" t="s">
+        <v>164</v>
+      </c>
       <c r="E175" t="s">
+        <v>165</v>
+      </c>
+      <c r="F175" t="s">
         <v>313</v>
-      </c>
-      <c r="F175" t="s">
-        <v>164</v>
-      </c>
-      <c r="G175" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="176" spans="1:7">
@@ -5661,14 +5661,14 @@
       <c r="C176" t="s">
         <v>163</v>
       </c>
+      <c r="D176" t="s">
+        <v>164</v>
+      </c>
       <c r="E176" t="s">
+        <v>165</v>
+      </c>
+      <c r="F176" t="s">
         <v>313</v>
-      </c>
-      <c r="F176" t="s">
-        <v>164</v>
-      </c>
-      <c r="G176" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="177" spans="1:7">
@@ -5681,14 +5681,14 @@
       <c r="C177" t="s">
         <v>163</v>
       </c>
+      <c r="D177" t="s">
+        <v>164</v>
+      </c>
       <c r="E177" t="s">
+        <v>165</v>
+      </c>
+      <c r="F177" t="s">
         <v>320</v>
-      </c>
-      <c r="F177" t="s">
-        <v>164</v>
-      </c>
-      <c r="G177" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="178" spans="1:7">
@@ -5701,14 +5701,14 @@
       <c r="C178" t="s">
         <v>163</v>
       </c>
+      <c r="D178" t="s">
+        <v>164</v>
+      </c>
       <c r="E178" t="s">
+        <v>165</v>
+      </c>
+      <c r="F178" t="s">
         <v>320</v>
-      </c>
-      <c r="F178" t="s">
-        <v>164</v>
-      </c>
-      <c r="G178" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="179" spans="1:7">
@@ -5721,14 +5721,14 @@
       <c r="C179" t="s">
         <v>163</v>
       </c>
+      <c r="D179" t="s">
+        <v>164</v>
+      </c>
       <c r="E179" t="s">
+        <v>165</v>
+      </c>
+      <c r="F179" t="s">
         <v>320</v>
-      </c>
-      <c r="F179" t="s">
-        <v>164</v>
-      </c>
-      <c r="G179" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="180" spans="1:7">
@@ -5741,14 +5741,14 @@
       <c r="C180" t="s">
         <v>163</v>
       </c>
+      <c r="D180" t="s">
+        <v>164</v>
+      </c>
       <c r="E180" t="s">
+        <v>165</v>
+      </c>
+      <c r="F180" t="s">
         <v>320</v>
-      </c>
-      <c r="F180" t="s">
-        <v>164</v>
-      </c>
-      <c r="G180" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="181" spans="1:7">
@@ -5759,16 +5759,16 @@
         <v>8</v>
       </c>
       <c r="C181" t="s">
+        <v>163</v>
+      </c>
+      <c r="D181" t="s">
         <v>325</v>
       </c>
-      <c r="D181" t="s">
+      <c r="E181" t="s">
         <v>326</v>
       </c>
-      <c r="E181" t="s">
+      <c r="F181" t="s">
         <v>327</v>
-      </c>
-      <c r="F181" t="s">
-        <v>164</v>
       </c>
       <c r="G181" t="s">
         <v>328</v>
@@ -5782,16 +5782,16 @@
         <v>8</v>
       </c>
       <c r="C182" t="s">
+        <v>163</v>
+      </c>
+      <c r="D182" t="s">
         <v>325</v>
       </c>
-      <c r="D182" t="s">
+      <c r="E182" t="s">
         <v>326</v>
       </c>
-      <c r="E182" t="s">
+      <c r="F182" t="s">
         <v>327</v>
-      </c>
-      <c r="F182" t="s">
-        <v>164</v>
       </c>
       <c r="G182" t="s">
         <v>328</v>
@@ -5805,16 +5805,16 @@
         <v>8</v>
       </c>
       <c r="C183" t="s">
+        <v>163</v>
+      </c>
+      <c r="D183" t="s">
         <v>325</v>
       </c>
-      <c r="D183" t="s">
+      <c r="E183" t="s">
         <v>326</v>
       </c>
-      <c r="E183" t="s">
+      <c r="F183" t="s">
         <v>327</v>
-      </c>
-      <c r="F183" t="s">
-        <v>164</v>
       </c>
       <c r="G183" t="s">
         <v>328</v>
@@ -5828,16 +5828,16 @@
         <v>8</v>
       </c>
       <c r="C184" t="s">
+        <v>163</v>
+      </c>
+      <c r="D184" t="s">
         <v>325</v>
       </c>
-      <c r="D184" t="s">
+      <c r="E184" t="s">
         <v>326</v>
       </c>
-      <c r="E184" t="s">
+      <c r="F184" t="s">
         <v>327</v>
-      </c>
-      <c r="F184" t="s">
-        <v>164</v>
       </c>
       <c r="G184" t="s">
         <v>328</v>
@@ -5851,16 +5851,16 @@
         <v>8</v>
       </c>
       <c r="C185" t="s">
+        <v>163</v>
+      </c>
+      <c r="D185" t="s">
         <v>325</v>
       </c>
-      <c r="D185" t="s">
+      <c r="E185" t="s">
         <v>326</v>
       </c>
-      <c r="E185" t="s">
+      <c r="F185" t="s">
         <v>327</v>
-      </c>
-      <c r="F185" t="s">
-        <v>164</v>
       </c>
       <c r="G185" t="s">
         <v>328</v>
@@ -5874,16 +5874,16 @@
         <v>8</v>
       </c>
       <c r="C186" t="s">
+        <v>163</v>
+      </c>
+      <c r="D186" t="s">
         <v>325</v>
       </c>
-      <c r="D186" t="s">
+      <c r="E186" t="s">
         <v>326</v>
       </c>
-      <c r="E186" t="s">
+      <c r="F186" t="s">
         <v>327</v>
-      </c>
-      <c r="F186" t="s">
-        <v>164</v>
       </c>
       <c r="G186" t="s">
         <v>328</v>
@@ -5897,16 +5897,16 @@
         <v>8</v>
       </c>
       <c r="C187" t="s">
+        <v>163</v>
+      </c>
+      <c r="D187" t="s">
         <v>325</v>
       </c>
-      <c r="D187" t="s">
+      <c r="E187" t="s">
         <v>326</v>
       </c>
-      <c r="E187" t="s">
+      <c r="F187" t="s">
         <v>327</v>
-      </c>
-      <c r="F187" t="s">
-        <v>164</v>
       </c>
       <c r="G187" t="s">
         <v>328</v>
@@ -5920,16 +5920,16 @@
         <v>8</v>
       </c>
       <c r="C188" t="s">
+        <v>163</v>
+      </c>
+      <c r="D188" t="s">
         <v>325</v>
       </c>
-      <c r="D188" t="s">
+      <c r="E188" t="s">
         <v>326</v>
       </c>
-      <c r="E188" t="s">
+      <c r="F188" t="s">
         <v>327</v>
-      </c>
-      <c r="F188" t="s">
-        <v>164</v>
       </c>
       <c r="G188" t="s">
         <v>328</v>
@@ -5943,16 +5943,16 @@
         <v>8</v>
       </c>
       <c r="C189" t="s">
+        <v>163</v>
+      </c>
+      <c r="D189" t="s">
         <v>325</v>
       </c>
-      <c r="D189" t="s">
+      <c r="E189" t="s">
         <v>326</v>
       </c>
-      <c r="E189" t="s">
+      <c r="F189" t="s">
         <v>327</v>
-      </c>
-      <c r="F189" t="s">
-        <v>164</v>
       </c>
       <c r="G189" t="s">
         <v>328</v>
@@ -5966,16 +5966,16 @@
         <v>8</v>
       </c>
       <c r="C190" t="s">
+        <v>163</v>
+      </c>
+      <c r="D190" t="s">
         <v>325</v>
       </c>
-      <c r="D190" t="s">
+      <c r="E190" t="s">
         <v>326</v>
       </c>
-      <c r="E190" t="s">
+      <c r="F190" t="s">
         <v>327</v>
-      </c>
-      <c r="F190" t="s">
-        <v>164</v>
       </c>
       <c r="G190" t="s">
         <v>328</v>
@@ -5989,16 +5989,16 @@
         <v>8</v>
       </c>
       <c r="C191" t="s">
+        <v>163</v>
+      </c>
+      <c r="D191" t="s">
         <v>325</v>
       </c>
-      <c r="D191" t="s">
+      <c r="E191" t="s">
         <v>326</v>
       </c>
-      <c r="E191" t="s">
+      <c r="F191" t="s">
         <v>327</v>
-      </c>
-      <c r="F191" t="s">
-        <v>164</v>
       </c>
       <c r="G191" t="s">
         <v>328</v>
@@ -6012,16 +6012,16 @@
         <v>8</v>
       </c>
       <c r="C192" t="s">
+        <v>163</v>
+      </c>
+      <c r="D192" t="s">
         <v>325</v>
       </c>
-      <c r="D192" t="s">
+      <c r="E192" t="s">
         <v>326</v>
       </c>
-      <c r="E192" t="s">
+      <c r="F192" t="s">
         <v>327</v>
-      </c>
-      <c r="F192" t="s">
-        <v>164</v>
       </c>
       <c r="G192" t="s">
         <v>328</v>
@@ -6035,19 +6035,19 @@
         <v>8</v>
       </c>
       <c r="C193" t="s">
+        <v>163</v>
+      </c>
+      <c r="D193" t="s">
         <v>341</v>
       </c>
-      <c r="D193" t="s">
-        <v>326</v>
-      </c>
       <c r="E193" t="s">
+        <v>276</v>
+      </c>
+      <c r="F193" t="s">
         <v>327</v>
       </c>
-      <c r="F193" t="s">
-        <v>164</v>
-      </c>
       <c r="G193" t="s">
-        <v>276</v>
+        <v>328</v>
       </c>
     </row>
     <row r="194" spans="1:7">
@@ -6058,16 +6058,16 @@
         <v>8</v>
       </c>
       <c r="C194" t="s">
+        <v>163</v>
+      </c>
+      <c r="D194" t="s">
         <v>325</v>
       </c>
-      <c r="D194" t="s">
+      <c r="E194" t="s">
         <v>326</v>
       </c>
-      <c r="E194" t="s">
+      <c r="F194" t="s">
         <v>327</v>
-      </c>
-      <c r="F194" t="s">
-        <v>164</v>
       </c>
       <c r="G194" t="s">
         <v>328</v>
@@ -6081,16 +6081,16 @@
         <v>8</v>
       </c>
       <c r="C195" t="s">
+        <v>163</v>
+      </c>
+      <c r="D195" t="s">
         <v>325</v>
       </c>
-      <c r="D195" t="s">
+      <c r="E195" t="s">
         <v>326</v>
       </c>
-      <c r="E195" t="s">
+      <c r="F195" t="s">
         <v>327</v>
-      </c>
-      <c r="F195" t="s">
-        <v>164</v>
       </c>
       <c r="G195" t="s">
         <v>328</v>
@@ -6104,16 +6104,16 @@
         <v>8</v>
       </c>
       <c r="C196" t="s">
+        <v>163</v>
+      </c>
+      <c r="D196" t="s">
         <v>325</v>
       </c>
-      <c r="D196" t="s">
+      <c r="E196" t="s">
         <v>326</v>
       </c>
-      <c r="E196" t="s">
+      <c r="F196" t="s">
         <v>327</v>
-      </c>
-      <c r="F196" t="s">
-        <v>164</v>
       </c>
       <c r="G196" t="s">
         <v>328</v>
@@ -6127,16 +6127,16 @@
         <v>8</v>
       </c>
       <c r="C197" t="s">
+        <v>163</v>
+      </c>
+      <c r="D197" t="s">
         <v>325</v>
       </c>
-      <c r="D197" t="s">
+      <c r="E197" t="s">
         <v>326</v>
       </c>
-      <c r="E197" t="s">
+      <c r="F197" t="s">
         <v>327</v>
-      </c>
-      <c r="F197" t="s">
-        <v>164</v>
       </c>
       <c r="G197" t="s">
         <v>328</v>
@@ -6150,16 +6150,16 @@
         <v>8</v>
       </c>
       <c r="C198" t="s">
+        <v>163</v>
+      </c>
+      <c r="D198" t="s">
         <v>325</v>
       </c>
-      <c r="D198" t="s">
+      <c r="E198" t="s">
         <v>326</v>
       </c>
-      <c r="E198" t="s">
+      <c r="F198" t="s">
         <v>327</v>
-      </c>
-      <c r="F198" t="s">
-        <v>164</v>
       </c>
       <c r="G198" t="s">
         <v>328</v>
@@ -6173,19 +6173,19 @@
         <v>8</v>
       </c>
       <c r="C199" t="s">
+        <v>163</v>
+      </c>
+      <c r="D199" t="s">
         <v>348</v>
       </c>
-      <c r="D199" t="s">
+      <c r="E199" t="s">
+        <v>326</v>
+      </c>
+      <c r="F199" t="s">
+        <v>327</v>
+      </c>
+      <c r="G199" t="s">
         <v>349</v>
-      </c>
-      <c r="E199" t="s">
-        <v>327</v>
-      </c>
-      <c r="F199" t="s">
-        <v>164</v>
-      </c>
-      <c r="G199" t="s">
-        <v>328</v>
       </c>
     </row>
     <row r="200" spans="1:7">
@@ -6196,19 +6196,19 @@
         <v>8</v>
       </c>
       <c r="C200" t="s">
+        <v>163</v>
+      </c>
+      <c r="D200" t="s">
         <v>348</v>
       </c>
-      <c r="D200" t="s">
+      <c r="E200" t="s">
+        <v>326</v>
+      </c>
+      <c r="F200" t="s">
+        <v>327</v>
+      </c>
+      <c r="G200" t="s">
         <v>349</v>
-      </c>
-      <c r="E200" t="s">
-        <v>327</v>
-      </c>
-      <c r="F200" t="s">
-        <v>164</v>
-      </c>
-      <c r="G200" t="s">
-        <v>328</v>
       </c>
     </row>
     <row r="201" spans="1:7">
@@ -6219,19 +6219,19 @@
         <v>8</v>
       </c>
       <c r="C201" t="s">
+        <v>163</v>
+      </c>
+      <c r="D201" t="s">
         <v>348</v>
       </c>
-      <c r="D201" t="s">
+      <c r="E201" t="s">
+        <v>326</v>
+      </c>
+      <c r="F201" t="s">
+        <v>327</v>
+      </c>
+      <c r="G201" t="s">
         <v>349</v>
-      </c>
-      <c r="E201" t="s">
-        <v>327</v>
-      </c>
-      <c r="F201" t="s">
-        <v>164</v>
-      </c>
-      <c r="G201" t="s">
-        <v>328</v>
       </c>
     </row>
     <row r="202" spans="1:7">
@@ -6242,19 +6242,19 @@
         <v>8</v>
       </c>
       <c r="C202" t="s">
+        <v>163</v>
+      </c>
+      <c r="D202" t="s">
         <v>348</v>
       </c>
-      <c r="D202" t="s">
+      <c r="E202" t="s">
+        <v>326</v>
+      </c>
+      <c r="F202" t="s">
+        <v>327</v>
+      </c>
+      <c r="G202" t="s">
         <v>349</v>
-      </c>
-      <c r="E202" t="s">
-        <v>327</v>
-      </c>
-      <c r="F202" t="s">
-        <v>164</v>
-      </c>
-      <c r="G202" t="s">
-        <v>328</v>
       </c>
     </row>
     <row r="203" spans="1:7">
@@ -6265,19 +6265,19 @@
         <v>8</v>
       </c>
       <c r="C203" t="s">
+        <v>163</v>
+      </c>
+      <c r="D203" t="s">
         <v>341</v>
       </c>
-      <c r="D203" t="s">
+      <c r="E203" t="s">
+        <v>276</v>
+      </c>
+      <c r="F203" t="s">
+        <v>327</v>
+      </c>
+      <c r="G203" t="s">
         <v>349</v>
-      </c>
-      <c r="E203" t="s">
-        <v>327</v>
-      </c>
-      <c r="F203" t="s">
-        <v>164</v>
-      </c>
-      <c r="G203" t="s">
-        <v>276</v>
       </c>
     </row>
     <row r="204" spans="1:7">
@@ -6288,19 +6288,19 @@
         <v>8</v>
       </c>
       <c r="C204" t="s">
+        <v>163</v>
+      </c>
+      <c r="D204" t="s">
         <v>348</v>
       </c>
-      <c r="D204" t="s">
+      <c r="E204" t="s">
+        <v>326</v>
+      </c>
+      <c r="F204" t="s">
+        <v>327</v>
+      </c>
+      <c r="G204" t="s">
         <v>349</v>
-      </c>
-      <c r="E204" t="s">
-        <v>327</v>
-      </c>
-      <c r="F204" t="s">
-        <v>164</v>
-      </c>
-      <c r="G204" t="s">
-        <v>328</v>
       </c>
     </row>
     <row r="205" spans="1:7">
@@ -6311,19 +6311,19 @@
         <v>8</v>
       </c>
       <c r="C205" t="s">
+        <v>163</v>
+      </c>
+      <c r="D205" t="s">
         <v>356</v>
       </c>
-      <c r="D205" t="s">
+      <c r="E205" t="s">
+        <v>326</v>
+      </c>
+      <c r="F205" t="s">
+        <v>327</v>
+      </c>
+      <c r="G205" t="s">
         <v>357</v>
-      </c>
-      <c r="E205" t="s">
-        <v>327</v>
-      </c>
-      <c r="F205" t="s">
-        <v>164</v>
-      </c>
-      <c r="G205" t="s">
-        <v>328</v>
       </c>
     </row>
     <row r="206" spans="1:7">
@@ -6334,19 +6334,19 @@
         <v>8</v>
       </c>
       <c r="C206" t="s">
+        <v>163</v>
+      </c>
+      <c r="D206" t="s">
         <v>356</v>
       </c>
-      <c r="D206" t="s">
+      <c r="E206" t="s">
+        <v>326</v>
+      </c>
+      <c r="F206" t="s">
+        <v>327</v>
+      </c>
+      <c r="G206" t="s">
         <v>357</v>
-      </c>
-      <c r="E206" t="s">
-        <v>327</v>
-      </c>
-      <c r="F206" t="s">
-        <v>164</v>
-      </c>
-      <c r="G206" t="s">
-        <v>328</v>
       </c>
     </row>
     <row r="207" spans="1:7">
@@ -6357,19 +6357,19 @@
         <v>8</v>
       </c>
       <c r="C207" t="s">
+        <v>163</v>
+      </c>
+      <c r="D207" t="s">
         <v>356</v>
       </c>
-      <c r="D207" t="s">
+      <c r="E207" t="s">
+        <v>326</v>
+      </c>
+      <c r="F207" t="s">
+        <v>327</v>
+      </c>
+      <c r="G207" t="s">
         <v>357</v>
-      </c>
-      <c r="E207" t="s">
-        <v>327</v>
-      </c>
-      <c r="F207" t="s">
-        <v>164</v>
-      </c>
-      <c r="G207" t="s">
-        <v>328</v>
       </c>
     </row>
     <row r="208" spans="1:7">
@@ -6380,19 +6380,19 @@
         <v>8</v>
       </c>
       <c r="C208" t="s">
+        <v>163</v>
+      </c>
+      <c r="D208" t="s">
         <v>341</v>
       </c>
-      <c r="D208" t="s">
+      <c r="E208" t="s">
+        <v>276</v>
+      </c>
+      <c r="F208" t="s">
+        <v>327</v>
+      </c>
+      <c r="G208" t="s">
         <v>357</v>
-      </c>
-      <c r="E208" t="s">
-        <v>327</v>
-      </c>
-      <c r="F208" t="s">
-        <v>164</v>
-      </c>
-      <c r="G208" t="s">
-        <v>276</v>
       </c>
     </row>
     <row r="209" spans="1:7">
@@ -6403,19 +6403,19 @@
         <v>8</v>
       </c>
       <c r="C209" t="s">
+        <v>163</v>
+      </c>
+      <c r="D209" t="s">
         <v>356</v>
       </c>
-      <c r="D209" t="s">
+      <c r="E209" t="s">
+        <v>326</v>
+      </c>
+      <c r="F209" t="s">
+        <v>327</v>
+      </c>
+      <c r="G209" t="s">
         <v>357</v>
-      </c>
-      <c r="E209" t="s">
-        <v>327</v>
-      </c>
-      <c r="F209" t="s">
-        <v>164</v>
-      </c>
-      <c r="G209" t="s">
-        <v>328</v>
       </c>
     </row>
     <row r="210" spans="1:7">
@@ -6426,16 +6426,16 @@
         <v>8</v>
       </c>
       <c r="C210" t="s">
+        <v>163</v>
+      </c>
+      <c r="D210" t="s">
         <v>363</v>
       </c>
-      <c r="D210" t="s">
+      <c r="E210" t="s">
         <v>364</v>
       </c>
-      <c r="E210" t="s">
+      <c r="F210" t="s">
         <v>365</v>
-      </c>
-      <c r="F210" t="s">
-        <v>164</v>
       </c>
       <c r="G210" t="s">
         <v>366</v>
@@ -6449,16 +6449,16 @@
         <v>8</v>
       </c>
       <c r="C211" t="s">
+        <v>163</v>
+      </c>
+      <c r="D211" t="s">
         <v>363</v>
       </c>
-      <c r="D211" t="s">
+      <c r="E211" t="s">
         <v>364</v>
       </c>
-      <c r="E211" t="s">
+      <c r="F211" t="s">
         <v>365</v>
-      </c>
-      <c r="F211" t="s">
-        <v>164</v>
       </c>
       <c r="G211" t="s">
         <v>366</v>
@@ -6472,16 +6472,16 @@
         <v>8</v>
       </c>
       <c r="C212" t="s">
+        <v>163</v>
+      </c>
+      <c r="D212" t="s">
         <v>363</v>
       </c>
-      <c r="D212" t="s">
+      <c r="E212" t="s">
         <v>364</v>
       </c>
-      <c r="E212" t="s">
+      <c r="F212" t="s">
         <v>365</v>
-      </c>
-      <c r="F212" t="s">
-        <v>164</v>
       </c>
       <c r="G212" t="s">
         <v>366</v>
@@ -6495,16 +6495,16 @@
         <v>8</v>
       </c>
       <c r="C213" t="s">
+        <v>163</v>
+      </c>
+      <c r="D213" t="s">
         <v>363</v>
       </c>
-      <c r="D213" t="s">
+      <c r="E213" t="s">
         <v>364</v>
       </c>
-      <c r="E213" t="s">
+      <c r="F213" t="s">
         <v>365</v>
-      </c>
-      <c r="F213" t="s">
-        <v>164</v>
       </c>
       <c r="G213" t="s">
         <v>366</v>
@@ -6518,16 +6518,16 @@
         <v>8</v>
       </c>
       <c r="C214" t="s">
+        <v>163</v>
+      </c>
+      <c r="D214" t="s">
         <v>363</v>
       </c>
-      <c r="D214" t="s">
+      <c r="E214" t="s">
         <v>364</v>
       </c>
-      <c r="E214" t="s">
+      <c r="F214" t="s">
         <v>365</v>
-      </c>
-      <c r="F214" t="s">
-        <v>164</v>
       </c>
       <c r="G214" t="s">
         <v>366</v>
@@ -6541,19 +6541,19 @@
         <v>8</v>
       </c>
       <c r="C215" t="s">
+        <v>163</v>
+      </c>
+      <c r="D215" t="s">
         <v>348</v>
       </c>
-      <c r="D215" t="s">
-        <v>364</v>
-      </c>
       <c r="E215" t="s">
+        <v>326</v>
+      </c>
+      <c r="F215" t="s">
         <v>365</v>
       </c>
-      <c r="F215" t="s">
-        <v>164</v>
-      </c>
       <c r="G215" t="s">
-        <v>328</v>
+        <v>366</v>
       </c>
     </row>
     <row r="216" spans="1:7">
@@ -6564,16 +6564,16 @@
         <v>8</v>
       </c>
       <c r="C216" t="s">
+        <v>163</v>
+      </c>
+      <c r="D216" t="s">
         <v>363</v>
       </c>
-      <c r="D216" t="s">
+      <c r="E216" t="s">
         <v>364</v>
       </c>
-      <c r="E216" t="s">
+      <c r="F216" t="s">
         <v>365</v>
-      </c>
-      <c r="F216" t="s">
-        <v>164</v>
       </c>
       <c r="G216" t="s">
         <v>366</v>
@@ -6587,16 +6587,16 @@
         <v>8</v>
       </c>
       <c r="C217" t="s">
+        <v>163</v>
+      </c>
+      <c r="D217" t="s">
         <v>363</v>
       </c>
-      <c r="D217" t="s">
+      <c r="E217" t="s">
         <v>364</v>
       </c>
-      <c r="E217" t="s">
+      <c r="F217" t="s">
         <v>365</v>
-      </c>
-      <c r="F217" t="s">
-        <v>164</v>
       </c>
       <c r="G217" t="s">
         <v>366</v>
@@ -6610,16 +6610,16 @@
         <v>8</v>
       </c>
       <c r="C218" t="s">
+        <v>163</v>
+      </c>
+      <c r="D218" t="s">
         <v>363</v>
       </c>
-      <c r="D218" t="s">
+      <c r="E218" t="s">
         <v>364</v>
       </c>
-      <c r="E218" t="s">
+      <c r="F218" t="s">
         <v>365</v>
-      </c>
-      <c r="F218" t="s">
-        <v>164</v>
       </c>
       <c r="G218" t="s">
         <v>366</v>
@@ -6633,16 +6633,16 @@
         <v>8</v>
       </c>
       <c r="C219" t="s">
+        <v>163</v>
+      </c>
+      <c r="D219" t="s">
         <v>363</v>
       </c>
-      <c r="D219" t="s">
+      <c r="E219" t="s">
         <v>364</v>
       </c>
-      <c r="E219" t="s">
+      <c r="F219" t="s">
         <v>365</v>
-      </c>
-      <c r="F219" t="s">
-        <v>164</v>
       </c>
       <c r="G219" t="s">
         <v>366</v>
@@ -6656,19 +6656,19 @@
         <v>8</v>
       </c>
       <c r="C220" t="s">
+        <v>163</v>
+      </c>
+      <c r="D220" t="s">
         <v>309</v>
       </c>
-      <c r="D220" t="s">
-        <v>364</v>
-      </c>
       <c r="E220" t="s">
+        <v>270</v>
+      </c>
+      <c r="F220" t="s">
         <v>365</v>
       </c>
-      <c r="F220" t="s">
-        <v>164</v>
-      </c>
       <c r="G220" t="s">
-        <v>272</v>
+        <v>366</v>
       </c>
     </row>
     <row r="221" spans="1:7">
@@ -6679,16 +6679,16 @@
         <v>8</v>
       </c>
       <c r="C221" t="s">
+        <v>163</v>
+      </c>
+      <c r="D221" t="s">
         <v>363</v>
       </c>
-      <c r="D221" t="s">
+      <c r="E221" t="s">
         <v>364</v>
       </c>
-      <c r="E221" t="s">
+      <c r="F221" t="s">
         <v>365</v>
-      </c>
-      <c r="F221" t="s">
-        <v>164</v>
       </c>
       <c r="G221" t="s">
         <v>366</v>
@@ -6702,16 +6702,16 @@
         <v>8</v>
       </c>
       <c r="C222" t="s">
+        <v>163</v>
+      </c>
+      <c r="D222" t="s">
         <v>363</v>
       </c>
-      <c r="D222" t="s">
+      <c r="E222" t="s">
         <v>364</v>
       </c>
-      <c r="E222" t="s">
+      <c r="F222" t="s">
         <v>365</v>
-      </c>
-      <c r="F222" t="s">
-        <v>164</v>
       </c>
       <c r="G222" t="s">
         <v>366</v>
@@ -6725,16 +6725,16 @@
         <v>8</v>
       </c>
       <c r="C223" t="s">
+        <v>163</v>
+      </c>
+      <c r="D223" t="s">
         <v>363</v>
       </c>
-      <c r="D223" t="s">
+      <c r="E223" t="s">
         <v>364</v>
       </c>
-      <c r="E223" t="s">
+      <c r="F223" t="s">
         <v>365</v>
-      </c>
-      <c r="F223" t="s">
-        <v>164</v>
       </c>
       <c r="G223" t="s">
         <v>366</v>
@@ -6748,16 +6748,16 @@
         <v>8</v>
       </c>
       <c r="C224" t="s">
+        <v>163</v>
+      </c>
+      <c r="D224" t="s">
         <v>363</v>
       </c>
-      <c r="D224" t="s">
+      <c r="E224" t="s">
         <v>364</v>
       </c>
-      <c r="E224" t="s">
+      <c r="F224" t="s">
         <v>365</v>
-      </c>
-      <c r="F224" t="s">
-        <v>164</v>
       </c>
       <c r="G224" t="s">
         <v>366</v>
@@ -6771,16 +6771,16 @@
         <v>8</v>
       </c>
       <c r="C225" t="s">
+        <v>163</v>
+      </c>
+      <c r="D225" t="s">
         <v>363</v>
       </c>
-      <c r="D225" t="s">
+      <c r="E225" t="s">
         <v>364</v>
       </c>
-      <c r="E225" t="s">
+      <c r="F225" t="s">
         <v>365</v>
-      </c>
-      <c r="F225" t="s">
-        <v>164</v>
       </c>
       <c r="G225" t="s">
         <v>366</v>
@@ -6794,19 +6794,19 @@
         <v>8</v>
       </c>
       <c r="C226" t="s">
+        <v>163</v>
+      </c>
+      <c r="D226" t="s">
         <v>275</v>
       </c>
-      <c r="D226" t="s">
-        <v>364</v>
-      </c>
       <c r="E226" t="s">
+        <v>276</v>
+      </c>
+      <c r="F226" t="s">
         <v>365</v>
       </c>
-      <c r="F226" t="s">
-        <v>164</v>
-      </c>
       <c r="G226" t="s">
-        <v>276</v>
+        <v>366</v>
       </c>
     </row>
     <row r="227" spans="1:7">
@@ -6817,16 +6817,16 @@
         <v>8</v>
       </c>
       <c r="C227" t="s">
+        <v>163</v>
+      </c>
+      <c r="D227" t="s">
         <v>363</v>
       </c>
-      <c r="D227" t="s">
+      <c r="E227" t="s">
         <v>364</v>
       </c>
-      <c r="E227" t="s">
+      <c r="F227" t="s">
         <v>365</v>
-      </c>
-      <c r="F227" t="s">
-        <v>164</v>
       </c>
       <c r="G227" t="s">
         <v>366</v>
@@ -6843,16 +6843,16 @@
         <v>163</v>
       </c>
       <c r="D228" t="s">
-        <v>364</v>
+        <v>164</v>
       </c>
       <c r="E228" t="s">
+        <v>165</v>
+      </c>
+      <c r="F228" t="s">
         <v>365</v>
       </c>
-      <c r="F228" t="s">
-        <v>164</v>
-      </c>
       <c r="G228" t="s">
-        <v>165</v>
+        <v>366</v>
       </c>
     </row>
     <row r="229" spans="1:7">
@@ -6863,19 +6863,19 @@
         <v>8</v>
       </c>
       <c r="C229" t="s">
+        <v>163</v>
+      </c>
+      <c r="D229" t="s">
         <v>386</v>
       </c>
-      <c r="D229" t="s">
+      <c r="E229" t="s">
+        <v>364</v>
+      </c>
+      <c r="F229" t="s">
+        <v>365</v>
+      </c>
+      <c r="G229" t="s">
         <v>387</v>
-      </c>
-      <c r="E229" t="s">
-        <v>365</v>
-      </c>
-      <c r="F229" t="s">
-        <v>164</v>
-      </c>
-      <c r="G229" t="s">
-        <v>366</v>
       </c>
     </row>
     <row r="230" spans="1:7">
@@ -6886,19 +6886,19 @@
         <v>8</v>
       </c>
       <c r="C230" t="s">
+        <v>163</v>
+      </c>
+      <c r="D230" t="s">
         <v>386</v>
       </c>
-      <c r="D230" t="s">
+      <c r="E230" t="s">
+        <v>364</v>
+      </c>
+      <c r="F230" t="s">
+        <v>365</v>
+      </c>
+      <c r="G230" t="s">
         <v>387</v>
-      </c>
-      <c r="E230" t="s">
-        <v>365</v>
-      </c>
-      <c r="F230" t="s">
-        <v>164</v>
-      </c>
-      <c r="G230" t="s">
-        <v>366</v>
       </c>
     </row>
     <row r="231" spans="1:7">
@@ -6909,19 +6909,19 @@
         <v>8</v>
       </c>
       <c r="C231" t="s">
+        <v>163</v>
+      </c>
+      <c r="D231" t="s">
         <v>293</v>
       </c>
-      <c r="D231" t="s">
+      <c r="E231" t="s">
+        <v>270</v>
+      </c>
+      <c r="F231" t="s">
+        <v>365</v>
+      </c>
+      <c r="G231" t="s">
         <v>387</v>
-      </c>
-      <c r="E231" t="s">
-        <v>365</v>
-      </c>
-      <c r="F231" t="s">
-        <v>164</v>
-      </c>
-      <c r="G231" t="s">
-        <v>272</v>
       </c>
     </row>
     <row r="232" spans="1:7">
@@ -6932,19 +6932,19 @@
         <v>8</v>
       </c>
       <c r="C232" t="s">
+        <v>163</v>
+      </c>
+      <c r="D232" t="s">
         <v>309</v>
       </c>
-      <c r="D232" t="s">
+      <c r="E232" t="s">
+        <v>270</v>
+      </c>
+      <c r="F232" t="s">
+        <v>365</v>
+      </c>
+      <c r="G232" t="s">
         <v>387</v>
-      </c>
-      <c r="E232" t="s">
-        <v>365</v>
-      </c>
-      <c r="F232" t="s">
-        <v>164</v>
-      </c>
-      <c r="G232" t="s">
-        <v>272</v>
       </c>
     </row>
     <row r="233" spans="1:7">
@@ -6955,19 +6955,19 @@
         <v>8</v>
       </c>
       <c r="C233" t="s">
+        <v>163</v>
+      </c>
+      <c r="D233" t="s">
         <v>386</v>
       </c>
-      <c r="D233" t="s">
+      <c r="E233" t="s">
+        <v>364</v>
+      </c>
+      <c r="F233" t="s">
+        <v>365</v>
+      </c>
+      <c r="G233" t="s">
         <v>387</v>
-      </c>
-      <c r="E233" t="s">
-        <v>365</v>
-      </c>
-      <c r="F233" t="s">
-        <v>164</v>
-      </c>
-      <c r="G233" t="s">
-        <v>366</v>
       </c>
     </row>
     <row r="234" spans="1:7">
@@ -6978,19 +6978,19 @@
         <v>8</v>
       </c>
       <c r="C234" t="s">
+        <v>163</v>
+      </c>
+      <c r="D234" t="s">
         <v>386</v>
       </c>
-      <c r="D234" t="s">
+      <c r="E234" t="s">
+        <v>364</v>
+      </c>
+      <c r="F234" t="s">
+        <v>365</v>
+      </c>
+      <c r="G234" t="s">
         <v>387</v>
-      </c>
-      <c r="E234" t="s">
-        <v>365</v>
-      </c>
-      <c r="F234" t="s">
-        <v>164</v>
-      </c>
-      <c r="G234" t="s">
-        <v>366</v>
       </c>
     </row>
     <row r="235" spans="1:7">
@@ -7001,19 +7001,19 @@
         <v>8</v>
       </c>
       <c r="C235" t="s">
+        <v>163</v>
+      </c>
+      <c r="D235" t="s">
         <v>386</v>
       </c>
-      <c r="D235" t="s">
+      <c r="E235" t="s">
+        <v>364</v>
+      </c>
+      <c r="F235" t="s">
+        <v>365</v>
+      </c>
+      <c r="G235" t="s">
         <v>387</v>
-      </c>
-      <c r="E235" t="s">
-        <v>365</v>
-      </c>
-      <c r="F235" t="s">
-        <v>164</v>
-      </c>
-      <c r="G235" t="s">
-        <v>366</v>
       </c>
     </row>
     <row r="236" spans="1:7">
@@ -7024,19 +7024,19 @@
         <v>8</v>
       </c>
       <c r="C236" t="s">
+        <v>163</v>
+      </c>
+      <c r="D236" t="s">
         <v>386</v>
       </c>
-      <c r="D236" t="s">
+      <c r="E236" t="s">
+        <v>364</v>
+      </c>
+      <c r="F236" t="s">
+        <v>365</v>
+      </c>
+      <c r="G236" t="s">
         <v>387</v>
-      </c>
-      <c r="E236" t="s">
-        <v>365</v>
-      </c>
-      <c r="F236" t="s">
-        <v>164</v>
-      </c>
-      <c r="G236" t="s">
-        <v>366</v>
       </c>
     </row>
     <row r="237" spans="1:7">
@@ -7047,19 +7047,19 @@
         <v>8</v>
       </c>
       <c r="C237" t="s">
+        <v>163</v>
+      </c>
+      <c r="D237" t="s">
         <v>386</v>
       </c>
-      <c r="D237" t="s">
+      <c r="E237" t="s">
+        <v>364</v>
+      </c>
+      <c r="F237" t="s">
+        <v>365</v>
+      </c>
+      <c r="G237" t="s">
         <v>387</v>
-      </c>
-      <c r="E237" t="s">
-        <v>365</v>
-      </c>
-      <c r="F237" t="s">
-        <v>164</v>
-      </c>
-      <c r="G237" t="s">
-        <v>366</v>
       </c>
     </row>
     <row r="238" spans="1:7">
@@ -7070,19 +7070,19 @@
         <v>8</v>
       </c>
       <c r="C238" t="s">
+        <v>163</v>
+      </c>
+      <c r="D238" t="s">
         <v>386</v>
       </c>
-      <c r="D238" t="s">
+      <c r="E238" t="s">
+        <v>364</v>
+      </c>
+      <c r="F238" t="s">
+        <v>365</v>
+      </c>
+      <c r="G238" t="s">
         <v>387</v>
-      </c>
-      <c r="E238" t="s">
-        <v>365</v>
-      </c>
-      <c r="F238" t="s">
-        <v>164</v>
-      </c>
-      <c r="G238" t="s">
-        <v>366</v>
       </c>
     </row>
     <row r="239" spans="1:7">
@@ -7093,19 +7093,19 @@
         <v>8</v>
       </c>
       <c r="C239" t="s">
+        <v>163</v>
+      </c>
+      <c r="D239" t="s">
         <v>398</v>
       </c>
-      <c r="D239" t="s">
+      <c r="E239" t="s">
+        <v>364</v>
+      </c>
+      <c r="F239" t="s">
+        <v>365</v>
+      </c>
+      <c r="G239" t="s">
         <v>399</v>
-      </c>
-      <c r="E239" t="s">
-        <v>365</v>
-      </c>
-      <c r="F239" t="s">
-        <v>164</v>
-      </c>
-      <c r="G239" t="s">
-        <v>366</v>
       </c>
     </row>
     <row r="240" spans="1:7">
@@ -7119,16 +7119,16 @@
         <v>163</v>
       </c>
       <c r="D240" t="s">
+        <v>164</v>
+      </c>
+      <c r="E240" t="s">
+        <v>165</v>
+      </c>
+      <c r="F240" t="s">
         <v>401</v>
       </c>
-      <c r="E240" t="s">
+      <c r="G240" t="s">
         <v>402</v>
-      </c>
-      <c r="F240" t="s">
-        <v>164</v>
-      </c>
-      <c r="G240" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="241" spans="1:7">
@@ -7142,16 +7142,16 @@
         <v>163</v>
       </c>
       <c r="D241" t="s">
+        <v>164</v>
+      </c>
+      <c r="E241" t="s">
+        <v>165</v>
+      </c>
+      <c r="F241" t="s">
         <v>401</v>
       </c>
-      <c r="E241" t="s">
+      <c r="G241" t="s">
         <v>402</v>
-      </c>
-      <c r="F241" t="s">
-        <v>164</v>
-      </c>
-      <c r="G241" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="242" spans="1:7">
@@ -7165,16 +7165,16 @@
         <v>163</v>
       </c>
       <c r="D242" t="s">
+        <v>164</v>
+      </c>
+      <c r="E242" t="s">
+        <v>165</v>
+      </c>
+      <c r="F242" t="s">
         <v>401</v>
       </c>
-      <c r="E242" t="s">
+      <c r="G242" t="s">
         <v>402</v>
-      </c>
-      <c r="F242" t="s">
-        <v>164</v>
-      </c>
-      <c r="G242" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="243" spans="1:7">
@@ -7188,16 +7188,16 @@
         <v>163</v>
       </c>
       <c r="D243" t="s">
+        <v>164</v>
+      </c>
+      <c r="E243" t="s">
+        <v>165</v>
+      </c>
+      <c r="F243" t="s">
         <v>401</v>
       </c>
-      <c r="E243" t="s">
+      <c r="G243" t="s">
         <v>402</v>
-      </c>
-      <c r="F243" t="s">
-        <v>164</v>
-      </c>
-      <c r="G243" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="244" spans="1:7">
@@ -7211,16 +7211,16 @@
         <v>163</v>
       </c>
       <c r="D244" t="s">
+        <v>164</v>
+      </c>
+      <c r="E244" t="s">
+        <v>165</v>
+      </c>
+      <c r="F244" t="s">
         <v>401</v>
       </c>
-      <c r="E244" t="s">
+      <c r="G244" t="s">
         <v>402</v>
-      </c>
-      <c r="F244" t="s">
-        <v>164</v>
-      </c>
-      <c r="G244" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="245" spans="1:7">
@@ -7234,16 +7234,16 @@
         <v>163</v>
       </c>
       <c r="D245" t="s">
+        <v>164</v>
+      </c>
+      <c r="E245" t="s">
+        <v>165</v>
+      </c>
+      <c r="F245" t="s">
         <v>401</v>
       </c>
-      <c r="E245" t="s">
+      <c r="G245" t="s">
         <v>402</v>
-      </c>
-      <c r="F245" t="s">
-        <v>164</v>
-      </c>
-      <c r="G245" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="246" spans="1:7">
@@ -7254,19 +7254,19 @@
         <v>8</v>
       </c>
       <c r="C246" t="s">
+        <v>163</v>
+      </c>
+      <c r="D246" t="s">
         <v>409</v>
       </c>
-      <c r="D246" t="s">
+      <c r="E246" t="s">
+        <v>256</v>
+      </c>
+      <c r="F246" t="s">
+        <v>401</v>
+      </c>
+      <c r="G246" t="s">
         <v>410</v>
-      </c>
-      <c r="E246" t="s">
-        <v>402</v>
-      </c>
-      <c r="F246" t="s">
-        <v>164</v>
-      </c>
-      <c r="G246" t="s">
-        <v>256</v>
       </c>
     </row>
     <row r="247" spans="1:7">
@@ -7279,14 +7279,14 @@
       <c r="C247" t="s">
         <v>95</v>
       </c>
+      <c r="D247" t="s">
+        <v>96</v>
+      </c>
       <c r="E247" t="s">
+        <v>97</v>
+      </c>
+      <c r="F247" t="s">
         <v>412</v>
-      </c>
-      <c r="F247" t="s">
-        <v>96</v>
-      </c>
-      <c r="G247" t="s">
-        <v>97</v>
       </c>
     </row>
     <row r="248" spans="1:7">
@@ -7299,14 +7299,14 @@
       <c r="C248" t="s">
         <v>95</v>
       </c>
+      <c r="D248" t="s">
+        <v>96</v>
+      </c>
       <c r="E248" t="s">
+        <v>97</v>
+      </c>
+      <c r="F248" t="s">
         <v>412</v>
-      </c>
-      <c r="F248" t="s">
-        <v>96</v>
-      </c>
-      <c r="G248" t="s">
-        <v>97</v>
       </c>
     </row>
     <row r="249" spans="1:7">
@@ -7317,16 +7317,16 @@
         <v>8</v>
       </c>
       <c r="C249" t="s">
+        <v>95</v>
+      </c>
+      <c r="D249" t="s">
         <v>415</v>
       </c>
       <c r="E249" t="s">
+        <v>416</v>
+      </c>
+      <c r="F249" t="s">
         <v>412</v>
-      </c>
-      <c r="F249" t="s">
-        <v>96</v>
-      </c>
-      <c r="G249" t="s">
-        <v>416</v>
       </c>
     </row>
     <row r="250" spans="1:7">
@@ -7339,14 +7339,14 @@
       <c r="C250" t="s">
         <v>95</v>
       </c>
+      <c r="D250" t="s">
+        <v>96</v>
+      </c>
       <c r="E250" t="s">
+        <v>97</v>
+      </c>
+      <c r="F250" t="s">
         <v>412</v>
-      </c>
-      <c r="F250" t="s">
-        <v>96</v>
-      </c>
-      <c r="G250" t="s">
-        <v>97</v>
       </c>
     </row>
     <row r="251" spans="1:7">
@@ -7359,14 +7359,14 @@
       <c r="C251" t="s">
         <v>95</v>
       </c>
+      <c r="D251" t="s">
+        <v>96</v>
+      </c>
       <c r="E251" t="s">
+        <v>97</v>
+      </c>
+      <c r="F251" t="s">
         <v>412</v>
-      </c>
-      <c r="F251" t="s">
-        <v>96</v>
-      </c>
-      <c r="G251" t="s">
-        <v>97</v>
       </c>
     </row>
     <row r="252" spans="1:7">
@@ -7379,14 +7379,14 @@
       <c r="C252" t="s">
         <v>95</v>
       </c>
+      <c r="D252" t="s">
+        <v>96</v>
+      </c>
       <c r="E252" t="s">
+        <v>97</v>
+      </c>
+      <c r="F252" t="s">
         <v>412</v>
-      </c>
-      <c r="F252" t="s">
-        <v>96</v>
-      </c>
-      <c r="G252" t="s">
-        <v>97</v>
       </c>
     </row>
     <row r="253" spans="1:7">
@@ -7397,15 +7397,15 @@
         <v>8</v>
       </c>
       <c r="C253" t="s">
+        <v>163</v>
+      </c>
+      <c r="D253" t="s">
         <v>421</v>
       </c>
       <c r="E253" t="s">
         <v>422</v>
       </c>
       <c r="F253" t="s">
-        <v>164</v>
-      </c>
-      <c r="G253" t="s">
         <v>423</v>
       </c>
     </row>
@@ -7417,16 +7417,16 @@
         <v>8</v>
       </c>
       <c r="C254" t="s">
+        <v>90</v>
+      </c>
+      <c r="D254" t="s">
         <v>219</v>
       </c>
       <c r="E254" t="s">
-        <v>422</v>
+        <v>220</v>
       </c>
       <c r="F254" t="s">
-        <v>92</v>
-      </c>
-      <c r="G254" t="s">
-        <v>220</v>
+        <v>423</v>
       </c>
     </row>
     <row r="255" spans="1:7">
@@ -7437,16 +7437,16 @@
         <v>8</v>
       </c>
       <c r="C255" t="s">
+        <v>90</v>
+      </c>
+      <c r="D255" t="s">
         <v>426</v>
       </c>
       <c r="E255" t="s">
-        <v>422</v>
+        <v>427</v>
       </c>
       <c r="F255" t="s">
-        <v>92</v>
-      </c>
-      <c r="G255" t="s">
-        <v>427</v>
+        <v>423</v>
       </c>
     </row>
     <row r="256" spans="1:7">
@@ -7457,19 +7457,19 @@
         <v>8</v>
       </c>
       <c r="C256" t="s">
+        <v>90</v>
+      </c>
+      <c r="D256" t="s">
         <v>426</v>
       </c>
       <c r="E256" t="s">
-        <v>422</v>
+        <v>427</v>
       </c>
       <c r="F256" t="s">
-        <v>92</v>
-      </c>
-      <c r="G256" t="s">
-        <v>427</v>
-      </c>
-    </row>
-    <row r="257" spans="1:7">
+        <v>423</v>
+      </c>
+    </row>
+    <row r="257" spans="1:6">
       <c r="A257" t="s">
         <v>429</v>
       </c>
@@ -7477,19 +7477,19 @@
         <v>8</v>
       </c>
       <c r="C257" t="s">
+        <v>90</v>
+      </c>
+      <c r="D257" t="s">
         <v>426</v>
       </c>
       <c r="E257" t="s">
-        <v>422</v>
+        <v>427</v>
       </c>
       <c r="F257" t="s">
-        <v>92</v>
-      </c>
-      <c r="G257" t="s">
-        <v>427</v>
-      </c>
-    </row>
-    <row r="258" spans="1:7">
+        <v>423</v>
+      </c>
+    </row>
+    <row r="258" spans="1:6">
       <c r="A258" t="s">
         <v>430</v>
       </c>
@@ -7497,19 +7497,19 @@
         <v>8</v>
       </c>
       <c r="C258" t="s">
+        <v>163</v>
+      </c>
+      <c r="D258" t="s">
         <v>325</v>
       </c>
       <c r="E258" t="s">
-        <v>422</v>
+        <v>326</v>
       </c>
       <c r="F258" t="s">
-        <v>164</v>
-      </c>
-      <c r="G258" t="s">
-        <v>328</v>
-      </c>
-    </row>
-    <row r="259" spans="1:7">
+        <v>423</v>
+      </c>
+    </row>
+    <row r="259" spans="1:6">
       <c r="A259" t="s">
         <v>431</v>
       </c>
@@ -7517,19 +7517,19 @@
         <v>8</v>
       </c>
       <c r="C259" t="s">
+        <v>90</v>
+      </c>
+      <c r="D259" t="s">
         <v>426</v>
       </c>
       <c r="E259" t="s">
-        <v>422</v>
+        <v>427</v>
       </c>
       <c r="F259" t="s">
-        <v>92</v>
-      </c>
-      <c r="G259" t="s">
-        <v>427</v>
-      </c>
-    </row>
-    <row r="260" spans="1:7">
+        <v>423</v>
+      </c>
+    </row>
+    <row r="260" spans="1:6">
       <c r="A260" t="s">
         <v>432</v>
       </c>
@@ -7539,17 +7539,17 @@
       <c r="C260" t="s">
         <v>163</v>
       </c>
+      <c r="D260" t="s">
+        <v>164</v>
+      </c>
       <c r="E260" t="s">
-        <v>422</v>
+        <v>165</v>
       </c>
       <c r="F260" t="s">
-        <v>164</v>
-      </c>
-      <c r="G260" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="261" spans="1:7">
+        <v>423</v>
+      </c>
+    </row>
+    <row r="261" spans="1:6">
       <c r="A261" t="s">
         <v>433</v>
       </c>
@@ -7557,19 +7557,19 @@
         <v>8</v>
       </c>
       <c r="C261" t="s">
+        <v>195</v>
+      </c>
+      <c r="D261" t="s">
         <v>434</v>
       </c>
       <c r="E261" t="s">
-        <v>422</v>
+        <v>435</v>
       </c>
       <c r="F261" t="s">
-        <v>196</v>
-      </c>
-      <c r="G261" t="s">
-        <v>435</v>
-      </c>
-    </row>
-    <row r="262" spans="1:7">
+        <v>423</v>
+      </c>
+    </row>
+    <row r="262" spans="1:6">
       <c r="A262" t="s">
         <v>436</v>
       </c>
@@ -7579,17 +7579,17 @@
       <c r="C262" t="s">
         <v>163</v>
       </c>
+      <c r="D262" t="s">
+        <v>164</v>
+      </c>
       <c r="E262" t="s">
-        <v>422</v>
+        <v>165</v>
       </c>
       <c r="F262" t="s">
-        <v>164</v>
-      </c>
-      <c r="G262" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="263" spans="1:7">
+        <v>423</v>
+      </c>
+    </row>
+    <row r="263" spans="1:6">
       <c r="A263" t="s">
         <v>437</v>
       </c>
@@ -7597,19 +7597,19 @@
         <v>8</v>
       </c>
       <c r="C263" t="s">
+        <v>182</v>
+      </c>
+      <c r="D263" t="s">
         <v>438</v>
       </c>
       <c r="E263" t="s">
-        <v>422</v>
+        <v>439</v>
       </c>
       <c r="F263" t="s">
-        <v>183</v>
-      </c>
-      <c r="G263" t="s">
-        <v>439</v>
-      </c>
-    </row>
-    <row r="264" spans="1:7">
+        <v>423</v>
+      </c>
+    </row>
+    <row r="264" spans="1:6">
       <c r="A264" t="s">
         <v>440</v>
       </c>
@@ -7619,17 +7619,17 @@
       <c r="C264" t="s">
         <v>31</v>
       </c>
+      <c r="D264" t="s">
+        <v>32</v>
+      </c>
       <c r="E264" t="s">
-        <v>422</v>
+        <v>33</v>
       </c>
       <c r="F264" t="s">
-        <v>32</v>
-      </c>
-      <c r="G264" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="265" spans="1:7">
+        <v>423</v>
+      </c>
+    </row>
+    <row r="265" spans="1:6">
       <c r="A265" t="s">
         <v>441</v>
       </c>
@@ -7639,17 +7639,17 @@
       <c r="C265" t="s">
         <v>9</v>
       </c>
+      <c r="D265" t="s">
+        <v>10</v>
+      </c>
       <c r="E265" t="s">
-        <v>422</v>
+        <v>11</v>
       </c>
       <c r="F265" t="s">
-        <v>12</v>
-      </c>
-      <c r="G265" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="266" spans="1:7">
+        <v>423</v>
+      </c>
+    </row>
+    <row r="266" spans="1:6">
       <c r="A266" t="s">
         <v>442</v>
       </c>
@@ -7657,19 +7657,19 @@
         <v>8</v>
       </c>
       <c r="C266" t="s">
+        <v>112</v>
+      </c>
+      <c r="D266" t="s">
         <v>443</v>
       </c>
       <c r="E266" t="s">
-        <v>422</v>
+        <v>444</v>
       </c>
       <c r="F266" t="s">
-        <v>115</v>
-      </c>
-      <c r="G266" t="s">
-        <v>444</v>
-      </c>
-    </row>
-    <row r="267" spans="1:7">
+        <v>423</v>
+      </c>
+    </row>
+    <row r="267" spans="1:6">
       <c r="A267" t="s">
         <v>445</v>
       </c>
@@ -7677,19 +7677,19 @@
         <v>8</v>
       </c>
       <c r="C267" t="s">
+        <v>112</v>
+      </c>
+      <c r="D267" t="s">
         <v>118</v>
       </c>
       <c r="E267" t="s">
+        <v>119</v>
+      </c>
+      <c r="F267" t="s">
         <v>446</v>
       </c>
-      <c r="F267" t="s">
-        <v>115</v>
-      </c>
-      <c r="G267" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="268" spans="1:7">
+    </row>
+    <row r="268" spans="1:6">
       <c r="A268" t="s">
         <v>447</v>
       </c>
@@ -7697,19 +7697,19 @@
         <v>8</v>
       </c>
       <c r="C268" t="s">
+        <v>182</v>
+      </c>
+      <c r="D268" t="s">
         <v>202</v>
       </c>
       <c r="E268" t="s">
+        <v>203</v>
+      </c>
+      <c r="F268" t="s">
         <v>448</v>
       </c>
-      <c r="F268" t="s">
-        <v>183</v>
-      </c>
-      <c r="G268" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="269" spans="1:7">
+    </row>
+    <row r="269" spans="1:6">
       <c r="A269" t="s">
         <v>449</v>
       </c>
@@ -7717,19 +7717,19 @@
         <v>8</v>
       </c>
       <c r="C269" t="s">
+        <v>112</v>
+      </c>
+      <c r="D269" t="s">
         <v>118</v>
       </c>
       <c r="E269" t="s">
+        <v>119</v>
+      </c>
+      <c r="F269" t="s">
         <v>450</v>
       </c>
-      <c r="F269" t="s">
-        <v>115</v>
-      </c>
-      <c r="G269" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="270" spans="1:7">
+    </row>
+    <row r="270" spans="1:6">
       <c r="A270" t="s">
         <v>451</v>
       </c>
@@ -7737,19 +7737,19 @@
         <v>8</v>
       </c>
       <c r="C270" t="s">
+        <v>112</v>
+      </c>
+      <c r="D270" t="s">
         <v>118</v>
       </c>
       <c r="E270" t="s">
+        <v>119</v>
+      </c>
+      <c r="F270" t="s">
         <v>450</v>
       </c>
-      <c r="F270" t="s">
-        <v>115</v>
-      </c>
-      <c r="G270" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="271" spans="1:7">
+    </row>
+    <row r="271" spans="1:6">
       <c r="A271" t="s">
         <v>452</v>
       </c>
@@ -7757,19 +7757,19 @@
         <v>8</v>
       </c>
       <c r="C271" t="s">
+        <v>112</v>
+      </c>
+      <c r="D271" t="s">
         <v>453</v>
       </c>
       <c r="E271" t="s">
         <v>454</v>
       </c>
       <c r="F271" t="s">
-        <v>115</v>
-      </c>
-      <c r="G271" t="s">
         <v>455</v>
       </c>
     </row>
-    <row r="272" spans="1:7">
+    <row r="272" spans="1:6">
       <c r="A272" t="s">
         <v>456</v>
       </c>
@@ -7777,19 +7777,19 @@
         <v>8</v>
       </c>
       <c r="C272" t="s">
+        <v>112</v>
+      </c>
+      <c r="D272" t="s">
         <v>453</v>
       </c>
       <c r="E272" t="s">
         <v>454</v>
       </c>
       <c r="F272" t="s">
-        <v>115</v>
-      </c>
-      <c r="G272" t="s">
         <v>455</v>
       </c>
     </row>
-    <row r="273" spans="1:7">
+    <row r="273" spans="1:6">
       <c r="A273" t="s">
         <v>457</v>
       </c>
@@ -7797,19 +7797,19 @@
         <v>8</v>
       </c>
       <c r="C273" t="s">
+        <v>112</v>
+      </c>
+      <c r="D273" t="s">
         <v>453</v>
       </c>
       <c r="E273" t="s">
         <v>454</v>
       </c>
       <c r="F273" t="s">
-        <v>115</v>
-      </c>
-      <c r="G273" t="s">
         <v>455</v>
       </c>
     </row>
-    <row r="274" spans="1:7">
+    <row r="274" spans="1:6">
       <c r="A274" t="s">
         <v>458</v>
       </c>
@@ -7817,19 +7817,19 @@
         <v>8</v>
       </c>
       <c r="C274" t="s">
+        <v>112</v>
+      </c>
+      <c r="D274" t="s">
         <v>453</v>
       </c>
       <c r="E274" t="s">
         <v>454</v>
       </c>
       <c r="F274" t="s">
-        <v>115</v>
-      </c>
-      <c r="G274" t="s">
         <v>455</v>
       </c>
     </row>
-    <row r="275" spans="1:7">
+    <row r="275" spans="1:6">
       <c r="A275" t="s">
         <v>459</v>
       </c>
@@ -7837,19 +7837,19 @@
         <v>8</v>
       </c>
       <c r="C275" t="s">
+        <v>112</v>
+      </c>
+      <c r="D275" t="s">
         <v>453</v>
       </c>
       <c r="E275" t="s">
         <v>454</v>
       </c>
       <c r="F275" t="s">
-        <v>115</v>
-      </c>
-      <c r="G275" t="s">
         <v>455</v>
       </c>
     </row>
-    <row r="276" spans="1:7">
+    <row r="276" spans="1:6">
       <c r="A276" t="s">
         <v>460</v>
       </c>
@@ -7857,19 +7857,19 @@
         <v>8</v>
       </c>
       <c r="C276" t="s">
+        <v>112</v>
+      </c>
+      <c r="D276" t="s">
         <v>453</v>
       </c>
       <c r="E276" t="s">
         <v>454</v>
       </c>
       <c r="F276" t="s">
-        <v>115</v>
-      </c>
-      <c r="G276" t="s">
         <v>455</v>
       </c>
     </row>
-    <row r="277" spans="1:7">
+    <row r="277" spans="1:6">
       <c r="A277" t="s">
         <v>461</v>
       </c>
@@ -7877,19 +7877,19 @@
         <v>8</v>
       </c>
       <c r="C277" t="s">
+        <v>112</v>
+      </c>
+      <c r="D277" t="s">
         <v>453</v>
       </c>
       <c r="E277" t="s">
         <v>454</v>
       </c>
       <c r="F277" t="s">
-        <v>115</v>
-      </c>
-      <c r="G277" t="s">
         <v>455</v>
       </c>
     </row>
-    <row r="278" spans="1:7">
+    <row r="278" spans="1:6">
       <c r="A278" t="s">
         <v>462</v>
       </c>
@@ -7897,19 +7897,19 @@
         <v>8</v>
       </c>
       <c r="C278" t="s">
+        <v>182</v>
+      </c>
+      <c r="D278" t="s">
         <v>202</v>
       </c>
       <c r="E278" t="s">
+        <v>203</v>
+      </c>
+      <c r="F278" t="s">
         <v>463</v>
       </c>
-      <c r="F278" t="s">
-        <v>183</v>
-      </c>
-      <c r="G278" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="279" spans="1:7">
+    </row>
+    <row r="279" spans="1:6">
       <c r="A279" t="s">
         <v>464</v>
       </c>
@@ -7917,19 +7917,19 @@
         <v>8</v>
       </c>
       <c r="C279" t="s">
+        <v>31</v>
+      </c>
+      <c r="D279" t="s">
         <v>51</v>
       </c>
       <c r="E279" t="s">
+        <v>52</v>
+      </c>
+      <c r="F279" t="s">
         <v>463</v>
       </c>
-      <c r="F279" t="s">
-        <v>32</v>
-      </c>
-      <c r="G279" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="280" spans="1:7">
+    </row>
+    <row r="280" spans="1:6">
       <c r="A280" t="s">
         <v>465</v>
       </c>
@@ -7939,17 +7939,17 @@
       <c r="C280" t="s">
         <v>9</v>
       </c>
+      <c r="D280" t="s">
+        <v>10</v>
+      </c>
       <c r="E280" t="s">
+        <v>11</v>
+      </c>
+      <c r="F280" t="s">
         <v>463</v>
       </c>
-      <c r="F280" t="s">
-        <v>12</v>
-      </c>
-      <c r="G280" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="281" spans="1:7">
+    </row>
+    <row r="281" spans="1:6">
       <c r="A281" t="s">
         <v>466</v>
       </c>
@@ -7957,19 +7957,19 @@
         <v>8</v>
       </c>
       <c r="C281" t="s">
+        <v>112</v>
+      </c>
+      <c r="D281" t="s">
         <v>170</v>
       </c>
       <c r="E281" t="s">
+        <v>171</v>
+      </c>
+      <c r="F281" t="s">
         <v>463</v>
       </c>
-      <c r="F281" t="s">
-        <v>115</v>
-      </c>
-      <c r="G281" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="282" spans="1:7">
+    </row>
+    <row r="282" spans="1:6">
       <c r="A282" t="s">
         <v>467</v>
       </c>
@@ -7979,17 +7979,17 @@
       <c r="C282" t="s">
         <v>124</v>
       </c>
+      <c r="D282" t="s">
+        <v>125</v>
+      </c>
       <c r="E282" t="s">
+        <v>126</v>
+      </c>
+      <c r="F282" t="s">
         <v>463</v>
       </c>
-      <c r="F282" t="s">
-        <v>125</v>
-      </c>
-      <c r="G282" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="283" spans="1:7">
+    </row>
+    <row r="283" spans="1:6">
       <c r="A283" t="s">
         <v>468</v>
       </c>
@@ -7997,19 +7997,19 @@
         <v>8</v>
       </c>
       <c r="C283" t="s">
+        <v>163</v>
+      </c>
+      <c r="D283" t="s">
         <v>398</v>
       </c>
       <c r="E283" t="s">
+        <v>364</v>
+      </c>
+      <c r="F283" t="s">
         <v>469</v>
       </c>
-      <c r="F283" t="s">
-        <v>164</v>
-      </c>
-      <c r="G283" t="s">
-        <v>366</v>
-      </c>
-    </row>
-    <row r="284" spans="1:7">
+    </row>
+    <row r="284" spans="1:6">
       <c r="A284" t="s">
         <v>470</v>
       </c>
@@ -8019,17 +8019,17 @@
       <c r="C284" t="s">
         <v>124</v>
       </c>
+      <c r="D284" t="s">
+        <v>125</v>
+      </c>
       <c r="E284" t="s">
+        <v>126</v>
+      </c>
+      <c r="F284" t="s">
         <v>471</v>
       </c>
-      <c r="F284" t="s">
-        <v>125</v>
-      </c>
-      <c r="G284" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="285" spans="1:7">
+    </row>
+    <row r="285" spans="1:6">
       <c r="A285" t="s">
         <v>472</v>
       </c>
@@ -8037,19 +8037,19 @@
         <v>8</v>
       </c>
       <c r="C285" t="s">
+        <v>112</v>
+      </c>
+      <c r="D285" t="s">
         <v>170</v>
       </c>
       <c r="E285" t="s">
+        <v>171</v>
+      </c>
+      <c r="F285" t="s">
         <v>473</v>
       </c>
-      <c r="F285" t="s">
-        <v>115</v>
-      </c>
-      <c r="G285" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="286" spans="1:7">
+    </row>
+    <row r="286" spans="1:6">
       <c r="A286" t="s">
         <v>474</v>
       </c>
@@ -8057,19 +8057,19 @@
         <v>8</v>
       </c>
       <c r="C286" t="s">
+        <v>182</v>
+      </c>
+      <c r="D286" t="s">
         <v>438</v>
       </c>
       <c r="E286" t="s">
+        <v>439</v>
+      </c>
+      <c r="F286" t="s">
         <v>475</v>
       </c>
-      <c r="F286" t="s">
-        <v>183</v>
-      </c>
-      <c r="G286" t="s">
-        <v>439</v>
-      </c>
-    </row>
-    <row r="287" spans="1:7">
+    </row>
+    <row r="287" spans="1:6">
       <c r="A287" t="s">
         <v>476</v>
       </c>
@@ -8077,19 +8077,19 @@
         <v>8</v>
       </c>
       <c r="C287" t="s">
+        <v>182</v>
+      </c>
+      <c r="D287" t="s">
         <v>438</v>
       </c>
       <c r="E287" t="s">
+        <v>439</v>
+      </c>
+      <c r="F287" t="s">
         <v>475</v>
       </c>
-      <c r="F287" t="s">
-        <v>183</v>
-      </c>
-      <c r="G287" t="s">
-        <v>439</v>
-      </c>
-    </row>
-    <row r="288" spans="1:7">
+    </row>
+    <row r="288" spans="1:6">
       <c r="A288" t="s">
         <v>477</v>
       </c>
@@ -8097,19 +8097,19 @@
         <v>8</v>
       </c>
       <c r="C288" t="s">
+        <v>9</v>
+      </c>
+      <c r="D288" t="s">
         <v>41</v>
       </c>
       <c r="E288" t="s">
+        <v>42</v>
+      </c>
+      <c r="F288" t="s">
         <v>475</v>
       </c>
-      <c r="F288" t="s">
-        <v>12</v>
-      </c>
-      <c r="G288" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="289" spans="1:7">
+    </row>
+    <row r="289" spans="1:6">
       <c r="A289" t="s">
         <v>478</v>
       </c>
@@ -8119,17 +8119,17 @@
       <c r="C289" t="s">
         <v>31</v>
       </c>
+      <c r="D289" t="s">
+        <v>32</v>
+      </c>
       <c r="E289" t="s">
+        <v>33</v>
+      </c>
+      <c r="F289" t="s">
         <v>475</v>
       </c>
-      <c r="F289" t="s">
-        <v>32</v>
-      </c>
-      <c r="G289" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="290" spans="1:7">
+    </row>
+    <row r="290" spans="1:6">
       <c r="A290" t="s">
         <v>479</v>
       </c>
@@ -8139,17 +8139,17 @@
       <c r="C290" t="s">
         <v>31</v>
       </c>
+      <c r="D290" t="s">
+        <v>32</v>
+      </c>
       <c r="E290" t="s">
+        <v>33</v>
+      </c>
+      <c r="F290" t="s">
         <v>475</v>
       </c>
-      <c r="F290" t="s">
-        <v>32</v>
-      </c>
-      <c r="G290" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="291" spans="1:7">
+    </row>
+    <row r="291" spans="1:6">
       <c r="A291" t="s">
         <v>480</v>
       </c>
@@ -8157,19 +8157,19 @@
         <v>8</v>
       </c>
       <c r="C291" t="s">
+        <v>112</v>
+      </c>
+      <c r="D291" t="s">
         <v>170</v>
       </c>
       <c r="E291" t="s">
+        <v>171</v>
+      </c>
+      <c r="F291" t="s">
         <v>475</v>
       </c>
-      <c r="F291" t="s">
-        <v>115</v>
-      </c>
-      <c r="G291" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="292" spans="1:7">
+    </row>
+    <row r="292" spans="1:6">
       <c r="A292" t="s">
         <v>481</v>
       </c>
@@ -8177,19 +8177,19 @@
         <v>8</v>
       </c>
       <c r="C292" t="s">
+        <v>112</v>
+      </c>
+      <c r="D292" t="s">
         <v>170</v>
       </c>
       <c r="E292" t="s">
+        <v>171</v>
+      </c>
+      <c r="F292" t="s">
         <v>475</v>
       </c>
-      <c r="F292" t="s">
-        <v>115</v>
-      </c>
-      <c r="G292" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="293" spans="1:7">
+    </row>
+    <row r="293" spans="1:6">
       <c r="A293" t="s">
         <v>482</v>
       </c>
@@ -8197,19 +8197,19 @@
         <v>8</v>
       </c>
       <c r="C293" t="s">
+        <v>112</v>
+      </c>
+      <c r="D293" t="s">
         <v>170</v>
       </c>
       <c r="E293" t="s">
+        <v>171</v>
+      </c>
+      <c r="F293" t="s">
         <v>475</v>
       </c>
-      <c r="F293" t="s">
-        <v>115</v>
-      </c>
-      <c r="G293" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="294" spans="1:7">
+    </row>
+    <row r="294" spans="1:6">
       <c r="A294" t="s">
         <v>483</v>
       </c>
@@ -8217,19 +8217,19 @@
         <v>8</v>
       </c>
       <c r="C294" t="s">
+        <v>112</v>
+      </c>
+      <c r="D294" t="s">
         <v>170</v>
       </c>
       <c r="E294" t="s">
+        <v>171</v>
+      </c>
+      <c r="F294" t="s">
         <v>475</v>
       </c>
-      <c r="F294" t="s">
-        <v>115</v>
-      </c>
-      <c r="G294" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="295" spans="1:7">
+    </row>
+    <row r="295" spans="1:6">
       <c r="A295" t="s">
         <v>484</v>
       </c>
@@ -8237,19 +8237,19 @@
         <v>8</v>
       </c>
       <c r="C295" t="s">
+        <v>112</v>
+      </c>
+      <c r="D295" t="s">
         <v>170</v>
       </c>
       <c r="E295" t="s">
+        <v>171</v>
+      </c>
+      <c r="F295" t="s">
         <v>485</v>
       </c>
-      <c r="F295" t="s">
-        <v>115</v>
-      </c>
-      <c r="G295" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="296" spans="1:7">
+    </row>
+    <row r="296" spans="1:6">
       <c r="A296" t="s">
         <v>486</v>
       </c>
@@ -8257,16 +8257,16 @@
         <v>8</v>
       </c>
       <c r="C296" t="s">
+        <v>112</v>
+      </c>
+      <c r="D296" t="s">
         <v>170</v>
       </c>
       <c r="E296" t="s">
+        <v>171</v>
+      </c>
+      <c r="F296" t="s">
         <v>485</v>
-      </c>
-      <c r="F296" t="s">
-        <v>115</v>
-      </c>
-      <c r="G296" t="s">
-        <v>171</v>
       </c>
     </row>
   </sheetData>

--- a/api/2/xlsx/fr/SectorCOFOG.xlsx
+++ b/api/2/xlsx/fr/SectorCOFOG.xlsx
@@ -22,18 +22,18 @@
     <t>status</t>
   </si>
   <si>
+    <t>codeforiati:cofog-class</t>
+  </si>
+  <si>
+    <t>codeforiati:group-code</t>
+  </si>
+  <si>
+    <t>codeforiati:cofog-group</t>
+  </si>
+  <si>
     <t>codeforiati:cofog-division</t>
   </si>
   <si>
-    <t>codeforiati:cofog-class</t>
-  </si>
-  <si>
-    <t>codeforiati:cofog-group</t>
-  </si>
-  <si>
-    <t>codeforiati:group-code</t>
-  </si>
-  <si>
     <t>codeforiati:category-code</t>
   </si>
   <si>
@@ -43,18 +43,18 @@
     <t>active</t>
   </si>
   <si>
+    <t>09.8.0 - Education n.e.c. (CS)</t>
+  </si>
+  <si>
+    <t>110</t>
+  </si>
+  <si>
+    <t>09.8 - Education n.e.c.</t>
+  </si>
+  <si>
     <t>09 - Education</t>
   </si>
   <si>
-    <t>09.8.0 - Education n.e.c. (CS)</t>
-  </si>
-  <si>
-    <t>09.8 - Education n.e.c.</t>
-  </si>
-  <si>
-    <t>110</t>
-  </si>
-  <si>
     <t>111</t>
   </si>
   <si>
@@ -109,15 +109,15 @@
     <t>11250</t>
   </si>
   <si>
+    <t>07.4.0 - Public health services (IS)</t>
+  </si>
+  <si>
+    <t>07.4 - Public health services</t>
+  </si>
+  <si>
     <t>07 - Health</t>
   </si>
   <si>
-    <t>07.4.0 - Public health services (IS)</t>
-  </si>
-  <si>
-    <t>07.4 - Public health services</t>
-  </si>
-  <si>
     <t>11260</t>
   </si>
   <si>
@@ -172,12 +172,12 @@
     <t>07.6.0 - Health n.e.c. (CS)</t>
   </si>
   <si>
+    <t>120</t>
+  </si>
+  <si>
     <t>07.6 - Health n.e.c.</t>
   </si>
   <si>
-    <t>120</t>
-  </si>
-  <si>
     <t>121</t>
   </si>
   <si>
@@ -286,30 +286,30 @@
     <t>14010</t>
   </si>
   <si>
+    <t>06.3.0 - Water supply (CS)</t>
+  </si>
+  <si>
+    <t>140</t>
+  </si>
+  <si>
+    <t>06.3 - Water supply</t>
+  </si>
+  <si>
     <t>06 - Housing and community amenities</t>
   </si>
   <si>
-    <t>06.3.0 - Water supply (CS)</t>
-  </si>
-  <si>
-    <t>06.3 - Water supply</t>
-  </si>
-  <si>
-    <t>140</t>
-  </si>
-  <si>
     <t>14015</t>
   </si>
   <si>
+    <t>05.6.0 - Environmental protection n.e.c. (CS)</t>
+  </si>
+  <si>
+    <t>05.6 - Environmental protection n.e.c.</t>
+  </si>
+  <si>
     <t>05 - Environmental protection</t>
   </si>
   <si>
-    <t>05.6.0 - Environmental protection n.e.c. (CS)</t>
-  </si>
-  <si>
-    <t>05.6 - Environmental protection n.e.c.</t>
-  </si>
-  <si>
     <t>14020</t>
   </si>
   <si>
@@ -352,18 +352,18 @@
     <t>15110</t>
   </si>
   <si>
+    <t>01.3.1 - General personnel services (CS)</t>
+  </si>
+  <si>
+    <t>150</t>
+  </si>
+  <si>
+    <t>01.3 - General services</t>
+  </si>
+  <si>
     <t>01 - General public services</t>
   </si>
   <si>
-    <t>01.3.1 - General personnel services (CS)</t>
-  </si>
-  <si>
-    <t>01.3 - General services</t>
-  </si>
-  <si>
-    <t>150</t>
-  </si>
-  <si>
     <t>151</t>
   </si>
   <si>
@@ -388,15 +388,15 @@
     <t>15113</t>
   </si>
   <si>
+    <t>03.6.0 - Public order and safety n.e.c. (CS)</t>
+  </si>
+  <si>
+    <t>03.6 - Public order and safety n.e.c.</t>
+  </si>
+  <si>
     <t>03 - Public order and safety</t>
   </si>
   <si>
-    <t>03.6.0 - Public order and safety n.e.c. (CS)</t>
-  </si>
-  <si>
-    <t>03.6 - Public order and safety n.e.c.</t>
-  </si>
-  <si>
     <t>15114</t>
   </si>
   <si>
@@ -505,15 +505,15 @@
     <t>15142</t>
   </si>
   <si>
+    <t>04.1.1 - General economic and commercial affairs (CS)</t>
+  </si>
+  <si>
+    <t>04.1 - General economic, commercial and labour affairs</t>
+  </si>
+  <si>
     <t>04 - Economic affairs</t>
   </si>
   <si>
-    <t>04.1.1 - General economic and commercial affairs (CS)</t>
-  </si>
-  <si>
-    <t>04.1 - General economic, commercial and labour affairs</t>
-  </si>
-  <si>
     <t>15143</t>
   </si>
   <si>
@@ -562,15 +562,15 @@
     <t>15170</t>
   </si>
   <si>
+    <t>10.7.0 - Social exclusion n.e.c. (IS)</t>
+  </si>
+  <si>
+    <t>10.7 - Social exclusion n.e.c.</t>
+  </si>
+  <si>
     <t>10 - Social protection</t>
   </si>
   <si>
-    <t>10.7.0 - Social exclusion n.e.c. (IS)</t>
-  </si>
-  <si>
-    <t>10.7 - Social exclusion n.e.c.</t>
-  </si>
-  <si>
     <t>15180</t>
   </si>
   <si>
@@ -601,15 +601,15 @@
     <t>15230</t>
   </si>
   <si>
+    <t>02.3.0 - Foreign military aid (CS)</t>
+  </si>
+  <si>
+    <t>02.3 - Foreign military aid</t>
+  </si>
+  <si>
     <t>02 - Defence</t>
   </si>
   <si>
-    <t>02.3.0 - Foreign military aid (CS)</t>
-  </si>
-  <si>
-    <t>02.3 - Foreign military aid</t>
-  </si>
-  <si>
     <t>15240</t>
   </si>
   <si>
@@ -625,12 +625,12 @@
     <t>10.9.0 - Social protection n.e.c. (CS)</t>
   </si>
   <si>
+    <t>160</t>
+  </si>
+  <si>
     <t>10.9 - Social protection n.e.c.</t>
   </si>
   <si>
-    <t>160</t>
-  </si>
-  <si>
     <t>16011</t>
   </si>
   <si>
@@ -685,15 +685,15 @@
     <t>16061</t>
   </si>
   <si>
+    <t>08.2.0 - Cultural services (IS)</t>
+  </si>
+  <si>
+    <t>08.2 - Cultural services</t>
+  </si>
+  <si>
     <t>08 - Recreation, culture and religion</t>
   </si>
   <si>
-    <t>08.2.0 - Cultural services (IS)</t>
-  </si>
-  <si>
-    <t>08.2 - Cultural services</t>
-  </si>
-  <si>
     <t>16062</t>
   </si>
   <si>
@@ -826,12 +826,12 @@
     <t>04.3.5 - Electricity (CS)</t>
   </si>
   <si>
+    <t>230</t>
+  </si>
+  <si>
     <t>04.3 - Fuel and energy</t>
   </si>
   <si>
-    <t>230</t>
-  </si>
-  <si>
     <t>231</t>
   </si>
   <si>
@@ -994,12 +994,12 @@
     <t>04.2.1 - Agriculture (CS)</t>
   </si>
   <si>
+    <t>310</t>
+  </si>
+  <si>
     <t>04.2 - Agriculture, forestry, fishing and hunting</t>
   </si>
   <si>
-    <t>310</t>
-  </si>
-  <si>
     <t>311</t>
   </si>
   <si>
@@ -1108,12 +1108,12 @@
     <t>04.4.2 - Manufacturing (CS)</t>
   </si>
   <si>
+    <t>320</t>
+  </si>
+  <si>
     <t>04.4 - Mining, manufacturing and construction</t>
   </si>
   <si>
-    <t>320</t>
-  </si>
-  <si>
     <t>321</t>
   </si>
   <si>
@@ -1282,12 +1282,12 @@
     <t>04.9.0 - Economic affairs n.e.c. (CS)</t>
   </si>
   <si>
+    <t>430</t>
+  </si>
+  <si>
     <t>04.9 - Economic affairs n.e.c.</t>
   </si>
   <si>
-    <t>430</t>
-  </si>
-  <si>
     <t>43030</t>
   </si>
   <si>
@@ -1378,10 +1378,10 @@
     <t>01.7.0 - Public debt transactions (CS)</t>
   </si>
   <si>
+    <t>600</t>
+  </si>
+  <si>
     <t>01.7 - Public debt transactions</t>
-  </si>
-  <si>
-    <t>600</t>
   </si>
   <si>
     <t>60020</t>
@@ -1863,10 +1863,10 @@
         <v>8</v>
       </c>
       <c r="C3" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="D3" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="E3" t="s">
         <v>16</v>
@@ -1909,10 +1909,10 @@
         <v>8</v>
       </c>
       <c r="C5" t="s">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="D5" t="s">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="E5" t="s">
         <v>20</v>
@@ -1932,10 +1932,10 @@
         <v>8</v>
       </c>
       <c r="C6" t="s">
-        <v>9</v>
+        <v>22</v>
       </c>
       <c r="D6" t="s">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="E6" t="s">
         <v>23</v>
@@ -1978,10 +1978,10 @@
         <v>8</v>
       </c>
       <c r="C8" t="s">
-        <v>9</v>
+        <v>22</v>
       </c>
       <c r="D8" t="s">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="E8" t="s">
         <v>23</v>
@@ -2001,10 +2001,10 @@
         <v>8</v>
       </c>
       <c r="C9" t="s">
-        <v>9</v>
+        <v>22</v>
       </c>
       <c r="D9" t="s">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="E9" t="s">
         <v>23</v>
@@ -2024,10 +2024,10 @@
         <v>8</v>
       </c>
       <c r="C10" t="s">
-        <v>9</v>
+        <v>29</v>
       </c>
       <c r="D10" t="s">
-        <v>29</v>
+        <v>10</v>
       </c>
       <c r="E10" t="s">
         <v>23</v>
@@ -2050,13 +2050,13 @@
         <v>31</v>
       </c>
       <c r="D11" t="s">
+        <v>10</v>
+      </c>
+      <c r="E11" t="s">
         <v>32</v>
       </c>
-      <c r="E11" t="s">
+      <c r="F11" t="s">
         <v>33</v>
-      </c>
-      <c r="F11" t="s">
-        <v>12</v>
       </c>
       <c r="G11" t="s">
         <v>24</v>
@@ -2070,10 +2070,10 @@
         <v>8</v>
       </c>
       <c r="C12" t="s">
-        <v>9</v>
+        <v>35</v>
       </c>
       <c r="D12" t="s">
-        <v>35</v>
+        <v>10</v>
       </c>
       <c r="E12" t="s">
         <v>36</v>
@@ -2093,10 +2093,10 @@
         <v>8</v>
       </c>
       <c r="C13" t="s">
-        <v>9</v>
+        <v>38</v>
       </c>
       <c r="D13" t="s">
-        <v>38</v>
+        <v>10</v>
       </c>
       <c r="E13" t="s">
         <v>36</v>
@@ -2116,10 +2116,10 @@
         <v>8</v>
       </c>
       <c r="C14" t="s">
-        <v>9</v>
+        <v>41</v>
       </c>
       <c r="D14" t="s">
-        <v>41</v>
+        <v>10</v>
       </c>
       <c r="E14" t="s">
         <v>42</v>
@@ -2139,10 +2139,10 @@
         <v>8</v>
       </c>
       <c r="C15" t="s">
-        <v>9</v>
+        <v>44</v>
       </c>
       <c r="D15" t="s">
-        <v>44</v>
+        <v>10</v>
       </c>
       <c r="E15" t="s">
         <v>45</v>
@@ -2162,10 +2162,10 @@
         <v>8</v>
       </c>
       <c r="C16" t="s">
-        <v>9</v>
+        <v>48</v>
       </c>
       <c r="D16" t="s">
-        <v>48</v>
+        <v>10</v>
       </c>
       <c r="E16" t="s">
         <v>49</v>
@@ -2185,16 +2185,16 @@
         <v>8</v>
       </c>
       <c r="C17" t="s">
-        <v>31</v>
+        <v>51</v>
       </c>
       <c r="D17" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E17" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F17" t="s">
-        <v>53</v>
+        <v>33</v>
       </c>
       <c r="G17" t="s">
         <v>54</v>
@@ -2208,16 +2208,16 @@
         <v>8</v>
       </c>
       <c r="C18" t="s">
-        <v>31</v>
+        <v>51</v>
       </c>
       <c r="D18" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E18" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F18" t="s">
-        <v>53</v>
+        <v>33</v>
       </c>
       <c r="G18" t="s">
         <v>54</v>
@@ -2231,16 +2231,16 @@
         <v>8</v>
       </c>
       <c r="C19" t="s">
-        <v>31</v>
+        <v>57</v>
       </c>
       <c r="D19" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="E19" t="s">
         <v>58</v>
       </c>
       <c r="F19" t="s">
-        <v>53</v>
+        <v>33</v>
       </c>
       <c r="G19" t="s">
         <v>54</v>
@@ -2254,16 +2254,16 @@
         <v>8</v>
       </c>
       <c r="C20" t="s">
-        <v>31</v>
+        <v>60</v>
       </c>
       <c r="D20" t="s">
-        <v>60</v>
+        <v>52</v>
       </c>
       <c r="E20" t="s">
         <v>61</v>
       </c>
       <c r="F20" t="s">
-        <v>53</v>
+        <v>33</v>
       </c>
       <c r="G20" t="s">
         <v>54</v>
@@ -2277,16 +2277,16 @@
         <v>8</v>
       </c>
       <c r="C21" t="s">
-        <v>31</v>
+        <v>51</v>
       </c>
       <c r="D21" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E21" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F21" t="s">
-        <v>53</v>
+        <v>33</v>
       </c>
       <c r="G21" t="s">
         <v>54</v>
@@ -2303,13 +2303,13 @@
         <v>31</v>
       </c>
       <c r="D22" t="s">
+        <v>52</v>
+      </c>
+      <c r="E22" t="s">
         <v>32</v>
       </c>
-      <c r="E22" t="s">
+      <c r="F22" t="s">
         <v>33</v>
-      </c>
-      <c r="F22" t="s">
-        <v>53</v>
       </c>
       <c r="G22" t="s">
         <v>64</v>
@@ -2323,16 +2323,16 @@
         <v>8</v>
       </c>
       <c r="C23" t="s">
-        <v>31</v>
+        <v>66</v>
       </c>
       <c r="D23" t="s">
-        <v>66</v>
+        <v>52</v>
       </c>
       <c r="E23" t="s">
         <v>67</v>
       </c>
       <c r="F23" t="s">
-        <v>53</v>
+        <v>33</v>
       </c>
       <c r="G23" t="s">
         <v>64</v>
@@ -2349,13 +2349,13 @@
         <v>31</v>
       </c>
       <c r="D24" t="s">
+        <v>52</v>
+      </c>
+      <c r="E24" t="s">
         <v>32</v>
       </c>
-      <c r="E24" t="s">
+      <c r="F24" t="s">
         <v>33</v>
-      </c>
-      <c r="F24" t="s">
-        <v>53</v>
       </c>
       <c r="G24" t="s">
         <v>64</v>
@@ -2372,13 +2372,13 @@
         <v>31</v>
       </c>
       <c r="D25" t="s">
+        <v>52</v>
+      </c>
+      <c r="E25" t="s">
         <v>32</v>
       </c>
-      <c r="E25" t="s">
+      <c r="F25" t="s">
         <v>33</v>
-      </c>
-      <c r="F25" t="s">
-        <v>53</v>
       </c>
       <c r="G25" t="s">
         <v>64</v>
@@ -2395,13 +2395,13 @@
         <v>31</v>
       </c>
       <c r="D26" t="s">
+        <v>52</v>
+      </c>
+      <c r="E26" t="s">
         <v>32</v>
       </c>
-      <c r="E26" t="s">
+      <c r="F26" t="s">
         <v>33</v>
-      </c>
-      <c r="F26" t="s">
-        <v>53</v>
       </c>
       <c r="G26" t="s">
         <v>64</v>
@@ -2418,13 +2418,13 @@
         <v>31</v>
       </c>
       <c r="D27" t="s">
+        <v>52</v>
+      </c>
+      <c r="E27" t="s">
         <v>32</v>
       </c>
-      <c r="E27" t="s">
+      <c r="F27" t="s">
         <v>33</v>
-      </c>
-      <c r="F27" t="s">
-        <v>53</v>
       </c>
       <c r="G27" t="s">
         <v>64</v>
@@ -2441,13 +2441,13 @@
         <v>31</v>
       </c>
       <c r="D28" t="s">
+        <v>52</v>
+      </c>
+      <c r="E28" t="s">
         <v>32</v>
       </c>
-      <c r="E28" t="s">
+      <c r="F28" t="s">
         <v>33</v>
-      </c>
-      <c r="F28" t="s">
-        <v>53</v>
       </c>
       <c r="G28" t="s">
         <v>64</v>
@@ -2464,13 +2464,13 @@
         <v>31</v>
       </c>
       <c r="D29" t="s">
+        <v>52</v>
+      </c>
+      <c r="E29" t="s">
         <v>32</v>
       </c>
-      <c r="E29" t="s">
+      <c r="F29" t="s">
         <v>33</v>
-      </c>
-      <c r="F29" t="s">
-        <v>53</v>
       </c>
       <c r="G29" t="s">
         <v>64</v>
@@ -2484,16 +2484,16 @@
         <v>8</v>
       </c>
       <c r="C30" t="s">
-        <v>31</v>
+        <v>51</v>
       </c>
       <c r="D30" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E30" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F30" t="s">
-        <v>53</v>
+        <v>33</v>
       </c>
       <c r="G30" t="s">
         <v>64</v>
@@ -2510,13 +2510,13 @@
         <v>31</v>
       </c>
       <c r="D31" t="s">
+        <v>52</v>
+      </c>
+      <c r="E31" t="s">
         <v>32</v>
       </c>
-      <c r="E31" t="s">
+      <c r="F31" t="s">
         <v>33</v>
-      </c>
-      <c r="F31" t="s">
-        <v>53</v>
       </c>
       <c r="G31" t="s">
         <v>76</v>
@@ -2533,13 +2533,13 @@
         <v>31</v>
       </c>
       <c r="D32" t="s">
+        <v>52</v>
+      </c>
+      <c r="E32" t="s">
         <v>32</v>
       </c>
-      <c r="E32" t="s">
+      <c r="F32" t="s">
         <v>33</v>
-      </c>
-      <c r="F32" t="s">
-        <v>53</v>
       </c>
       <c r="G32" t="s">
         <v>76</v>
@@ -2556,13 +2556,13 @@
         <v>31</v>
       </c>
       <c r="D33" t="s">
+        <v>52</v>
+      </c>
+      <c r="E33" t="s">
         <v>32</v>
       </c>
-      <c r="E33" t="s">
+      <c r="F33" t="s">
         <v>33</v>
-      </c>
-      <c r="F33" t="s">
-        <v>53</v>
       </c>
       <c r="G33" t="s">
         <v>76</v>
@@ -2579,13 +2579,13 @@
         <v>31</v>
       </c>
       <c r="D34" t="s">
+        <v>52</v>
+      </c>
+      <c r="E34" t="s">
         <v>32</v>
       </c>
-      <c r="E34" t="s">
+      <c r="F34" t="s">
         <v>33</v>
-      </c>
-      <c r="F34" t="s">
-        <v>53</v>
       </c>
       <c r="G34" t="s">
         <v>76</v>
@@ -2602,13 +2602,13 @@
         <v>31</v>
       </c>
       <c r="D35" t="s">
+        <v>52</v>
+      </c>
+      <c r="E35" t="s">
         <v>32</v>
       </c>
-      <c r="E35" t="s">
+      <c r="F35" t="s">
         <v>33</v>
-      </c>
-      <c r="F35" t="s">
-        <v>53</v>
       </c>
       <c r="G35" t="s">
         <v>76</v>
@@ -2622,16 +2622,16 @@
         <v>8</v>
       </c>
       <c r="C36" t="s">
-        <v>31</v>
+        <v>57</v>
       </c>
       <c r="D36" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="E36" t="s">
         <v>58</v>
       </c>
       <c r="F36" t="s">
-        <v>53</v>
+        <v>33</v>
       </c>
       <c r="G36" t="s">
         <v>76</v>
@@ -2648,13 +2648,13 @@
         <v>31</v>
       </c>
       <c r="D37" t="s">
+        <v>83</v>
+      </c>
+      <c r="E37" t="s">
         <v>32</v>
       </c>
-      <c r="E37" t="s">
+      <c r="F37" t="s">
         <v>33</v>
-      </c>
-      <c r="F37" t="s">
-        <v>83</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -2668,13 +2668,13 @@
         <v>31</v>
       </c>
       <c r="D38" t="s">
+        <v>83</v>
+      </c>
+      <c r="E38" t="s">
         <v>32</v>
       </c>
-      <c r="E38" t="s">
+      <c r="F38" t="s">
         <v>33</v>
-      </c>
-      <c r="F38" t="s">
-        <v>83</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -2688,13 +2688,13 @@
         <v>31</v>
       </c>
       <c r="D39" t="s">
+        <v>83</v>
+      </c>
+      <c r="E39" t="s">
         <v>32</v>
       </c>
-      <c r="E39" t="s">
+      <c r="F39" t="s">
         <v>33</v>
-      </c>
-      <c r="F39" t="s">
-        <v>83</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -2708,13 +2708,13 @@
         <v>31</v>
       </c>
       <c r="D40" t="s">
+        <v>83</v>
+      </c>
+      <c r="E40" t="s">
         <v>32</v>
       </c>
-      <c r="E40" t="s">
+      <c r="F40" t="s">
         <v>33</v>
-      </c>
-      <c r="F40" t="s">
-        <v>83</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -2725,16 +2725,16 @@
         <v>8</v>
       </c>
       <c r="C41" t="s">
-        <v>31</v>
+        <v>51</v>
       </c>
       <c r="D41" t="s">
-        <v>51</v>
+        <v>83</v>
       </c>
       <c r="E41" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F41" t="s">
-        <v>83</v>
+        <v>33</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -2745,16 +2745,16 @@
         <v>8</v>
       </c>
       <c r="C42" t="s">
-        <v>31</v>
+        <v>57</v>
       </c>
       <c r="D42" t="s">
-        <v>57</v>
+        <v>83</v>
       </c>
       <c r="E42" t="s">
         <v>58</v>
       </c>
       <c r="F42" t="s">
-        <v>83</v>
+        <v>33</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -2788,13 +2788,13 @@
         <v>95</v>
       </c>
       <c r="D44" t="s">
+        <v>91</v>
+      </c>
+      <c r="E44" t="s">
         <v>96</v>
       </c>
-      <c r="E44" t="s">
+      <c r="F44" t="s">
         <v>97</v>
-      </c>
-      <c r="F44" t="s">
-        <v>93</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -2845,16 +2845,16 @@
         <v>8</v>
       </c>
       <c r="C47" t="s">
-        <v>95</v>
+        <v>101</v>
       </c>
       <c r="D47" t="s">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="E47" t="s">
         <v>102</v>
       </c>
       <c r="F47" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -2905,16 +2905,16 @@
         <v>8</v>
       </c>
       <c r="C50" t="s">
-        <v>95</v>
+        <v>101</v>
       </c>
       <c r="D50" t="s">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="E50" t="s">
         <v>102</v>
       </c>
       <c r="F50" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -2945,16 +2945,16 @@
         <v>8</v>
       </c>
       <c r="C52" t="s">
-        <v>95</v>
+        <v>108</v>
       </c>
       <c r="D52" t="s">
-        <v>108</v>
+        <v>91</v>
       </c>
       <c r="E52" t="s">
         <v>109</v>
       </c>
       <c r="F52" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -2968,13 +2968,13 @@
         <v>9</v>
       </c>
       <c r="D53" t="s">
-        <v>10</v>
+        <v>91</v>
       </c>
       <c r="E53" t="s">
         <v>11</v>
       </c>
       <c r="F53" t="s">
-        <v>93</v>
+        <v>12</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -3008,10 +3008,10 @@
         <v>8</v>
       </c>
       <c r="C55" t="s">
-        <v>112</v>
+        <v>118</v>
       </c>
       <c r="D55" t="s">
-        <v>118</v>
+        <v>113</v>
       </c>
       <c r="E55" t="s">
         <v>119</v>
@@ -3031,10 +3031,10 @@
         <v>8</v>
       </c>
       <c r="C56" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="D56" t="s">
-        <v>121</v>
+        <v>113</v>
       </c>
       <c r="E56" t="s">
         <v>122</v>
@@ -3057,13 +3057,13 @@
         <v>124</v>
       </c>
       <c r="D57" t="s">
+        <v>113</v>
+      </c>
+      <c r="E57" t="s">
         <v>125</v>
       </c>
-      <c r="E57" t="s">
+      <c r="F57" t="s">
         <v>126</v>
-      </c>
-      <c r="F57" t="s">
-        <v>115</v>
       </c>
       <c r="G57" t="s">
         <v>116</v>
@@ -3077,10 +3077,10 @@
         <v>8</v>
       </c>
       <c r="C58" t="s">
-        <v>112</v>
+        <v>118</v>
       </c>
       <c r="D58" t="s">
-        <v>118</v>
+        <v>113</v>
       </c>
       <c r="E58" t="s">
         <v>119</v>
@@ -3100,10 +3100,10 @@
         <v>8</v>
       </c>
       <c r="C59" t="s">
-        <v>112</v>
+        <v>118</v>
       </c>
       <c r="D59" t="s">
-        <v>118</v>
+        <v>113</v>
       </c>
       <c r="E59" t="s">
         <v>119</v>
@@ -3123,10 +3123,10 @@
         <v>8</v>
       </c>
       <c r="C60" t="s">
-        <v>112</v>
+        <v>118</v>
       </c>
       <c r="D60" t="s">
-        <v>118</v>
+        <v>113</v>
       </c>
       <c r="E60" t="s">
         <v>119</v>
@@ -3146,10 +3146,10 @@
         <v>8</v>
       </c>
       <c r="C61" t="s">
-        <v>112</v>
+        <v>118</v>
       </c>
       <c r="D61" t="s">
-        <v>118</v>
+        <v>113</v>
       </c>
       <c r="E61" t="s">
         <v>119</v>
@@ -3169,10 +3169,10 @@
         <v>8</v>
       </c>
       <c r="C62" t="s">
-        <v>112</v>
+        <v>118</v>
       </c>
       <c r="D62" t="s">
-        <v>118</v>
+        <v>113</v>
       </c>
       <c r="E62" t="s">
         <v>119</v>
@@ -3192,10 +3192,10 @@
         <v>8</v>
       </c>
       <c r="C63" t="s">
-        <v>112</v>
+        <v>133</v>
       </c>
       <c r="D63" t="s">
-        <v>133</v>
+        <v>113</v>
       </c>
       <c r="E63" t="s">
         <v>119</v>
@@ -3215,10 +3215,10 @@
         <v>8</v>
       </c>
       <c r="C64" t="s">
-        <v>112</v>
+        <v>133</v>
       </c>
       <c r="D64" t="s">
-        <v>133</v>
+        <v>113</v>
       </c>
       <c r="E64" t="s">
         <v>119</v>
@@ -3238,10 +3238,10 @@
         <v>8</v>
       </c>
       <c r="C65" t="s">
-        <v>112</v>
+        <v>136</v>
       </c>
       <c r="D65" t="s">
-        <v>136</v>
+        <v>113</v>
       </c>
       <c r="E65" t="s">
         <v>137</v>
@@ -3284,10 +3284,10 @@
         <v>8</v>
       </c>
       <c r="C67" t="s">
-        <v>112</v>
+        <v>118</v>
       </c>
       <c r="D67" t="s">
-        <v>118</v>
+        <v>113</v>
       </c>
       <c r="E67" t="s">
         <v>119</v>
@@ -3307,10 +3307,10 @@
         <v>8</v>
       </c>
       <c r="C68" t="s">
-        <v>112</v>
+        <v>141</v>
       </c>
       <c r="D68" t="s">
-        <v>141</v>
+        <v>113</v>
       </c>
       <c r="E68" t="s">
         <v>114</v>
@@ -3330,10 +3330,10 @@
         <v>8</v>
       </c>
       <c r="C69" t="s">
-        <v>112</v>
+        <v>143</v>
       </c>
       <c r="D69" t="s">
-        <v>143</v>
+        <v>113</v>
       </c>
       <c r="E69" t="s">
         <v>114</v>
@@ -3353,10 +3353,10 @@
         <v>8</v>
       </c>
       <c r="C70" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="D70" t="s">
-        <v>121</v>
+        <v>113</v>
       </c>
       <c r="E70" t="s">
         <v>122</v>
@@ -3376,10 +3376,10 @@
         <v>8</v>
       </c>
       <c r="C71" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="D71" t="s">
-        <v>121</v>
+        <v>113</v>
       </c>
       <c r="E71" t="s">
         <v>122</v>
@@ -3422,16 +3422,16 @@
         <v>8</v>
       </c>
       <c r="C73" t="s">
-        <v>124</v>
+        <v>148</v>
       </c>
       <c r="D73" t="s">
-        <v>148</v>
+        <v>113</v>
       </c>
       <c r="E73" t="s">
         <v>149</v>
       </c>
       <c r="F73" t="s">
-        <v>115</v>
+        <v>126</v>
       </c>
       <c r="G73" t="s">
         <v>116</v>
@@ -3445,16 +3445,16 @@
         <v>8</v>
       </c>
       <c r="C74" t="s">
-        <v>124</v>
+        <v>151</v>
       </c>
       <c r="D74" t="s">
-        <v>151</v>
+        <v>113</v>
       </c>
       <c r="E74" t="s">
         <v>152</v>
       </c>
       <c r="F74" t="s">
-        <v>115</v>
+        <v>126</v>
       </c>
       <c r="G74" t="s">
         <v>116</v>
@@ -3468,16 +3468,16 @@
         <v>8</v>
       </c>
       <c r="C75" t="s">
-        <v>124</v>
+        <v>154</v>
       </c>
       <c r="D75" t="s">
-        <v>154</v>
+        <v>113</v>
       </c>
       <c r="E75" t="s">
         <v>155</v>
       </c>
       <c r="F75" t="s">
-        <v>115</v>
+        <v>126</v>
       </c>
       <c r="G75" t="s">
         <v>116</v>
@@ -3491,16 +3491,16 @@
         <v>8</v>
       </c>
       <c r="C76" t="s">
-        <v>124</v>
+        <v>148</v>
       </c>
       <c r="D76" t="s">
-        <v>148</v>
+        <v>113</v>
       </c>
       <c r="E76" t="s">
         <v>149</v>
       </c>
       <c r="F76" t="s">
-        <v>115</v>
+        <v>126</v>
       </c>
       <c r="G76" t="s">
         <v>116</v>
@@ -3514,16 +3514,16 @@
         <v>8</v>
       </c>
       <c r="C77" t="s">
-        <v>124</v>
+        <v>148</v>
       </c>
       <c r="D77" t="s">
-        <v>148</v>
+        <v>113</v>
       </c>
       <c r="E77" t="s">
         <v>149</v>
       </c>
       <c r="F77" t="s">
-        <v>115</v>
+        <v>126</v>
       </c>
       <c r="G77" t="s">
         <v>116</v>
@@ -3537,16 +3537,16 @@
         <v>8</v>
       </c>
       <c r="C78" t="s">
-        <v>124</v>
+        <v>151</v>
       </c>
       <c r="D78" t="s">
-        <v>151</v>
+        <v>113</v>
       </c>
       <c r="E78" t="s">
         <v>152</v>
       </c>
       <c r="F78" t="s">
-        <v>115</v>
+        <v>126</v>
       </c>
       <c r="G78" t="s">
         <v>116</v>
@@ -3560,16 +3560,16 @@
         <v>8</v>
       </c>
       <c r="C79" t="s">
-        <v>124</v>
+        <v>160</v>
       </c>
       <c r="D79" t="s">
-        <v>160</v>
+        <v>113</v>
       </c>
       <c r="E79" t="s">
         <v>161</v>
       </c>
       <c r="F79" t="s">
-        <v>115</v>
+        <v>126</v>
       </c>
       <c r="G79" t="s">
         <v>116</v>
@@ -3586,13 +3586,13 @@
         <v>163</v>
       </c>
       <c r="D80" t="s">
+        <v>113</v>
+      </c>
+      <c r="E80" t="s">
         <v>164</v>
       </c>
-      <c r="E80" t="s">
-        <v>165</v>
-      </c>
       <c r="F80" t="s">
-        <v>115</v>
+        <v>165</v>
       </c>
       <c r="G80" t="s">
         <v>116</v>
@@ -3609,13 +3609,13 @@
         <v>163</v>
       </c>
       <c r="D81" t="s">
+        <v>113</v>
+      </c>
+      <c r="E81" t="s">
         <v>164</v>
       </c>
-      <c r="E81" t="s">
-        <v>165</v>
-      </c>
       <c r="F81" t="s">
-        <v>115</v>
+        <v>165</v>
       </c>
       <c r="G81" t="s">
         <v>116</v>
@@ -3632,13 +3632,13 @@
         <v>163</v>
       </c>
       <c r="D82" t="s">
+        <v>113</v>
+      </c>
+      <c r="E82" t="s">
         <v>164</v>
       </c>
-      <c r="E82" t="s">
-        <v>165</v>
-      </c>
       <c r="F82" t="s">
-        <v>115</v>
+        <v>165</v>
       </c>
       <c r="G82" t="s">
         <v>116</v>
@@ -3652,10 +3652,10 @@
         <v>8</v>
       </c>
       <c r="C83" t="s">
-        <v>112</v>
+        <v>143</v>
       </c>
       <c r="D83" t="s">
-        <v>143</v>
+        <v>113</v>
       </c>
       <c r="E83" t="s">
         <v>114</v>
@@ -3675,10 +3675,10 @@
         <v>8</v>
       </c>
       <c r="C84" t="s">
-        <v>112</v>
+        <v>170</v>
       </c>
       <c r="D84" t="s">
-        <v>170</v>
+        <v>113</v>
       </c>
       <c r="E84" t="s">
         <v>171</v>
@@ -3698,10 +3698,10 @@
         <v>8</v>
       </c>
       <c r="C85" t="s">
-        <v>112</v>
+        <v>173</v>
       </c>
       <c r="D85" t="s">
-        <v>173</v>
+        <v>113</v>
       </c>
       <c r="E85" t="s">
         <v>119</v>
@@ -3721,16 +3721,16 @@
         <v>8</v>
       </c>
       <c r="C86" t="s">
-        <v>163</v>
+        <v>175</v>
       </c>
       <c r="D86" t="s">
-        <v>175</v>
+        <v>113</v>
       </c>
       <c r="E86" t="s">
         <v>176</v>
       </c>
       <c r="F86" t="s">
-        <v>115</v>
+        <v>165</v>
       </c>
       <c r="G86" t="s">
         <v>116</v>
@@ -3744,10 +3744,10 @@
         <v>8</v>
       </c>
       <c r="C87" t="s">
-        <v>112</v>
+        <v>173</v>
       </c>
       <c r="D87" t="s">
-        <v>173</v>
+        <v>113</v>
       </c>
       <c r="E87" t="s">
         <v>119</v>
@@ -3767,10 +3767,10 @@
         <v>8</v>
       </c>
       <c r="C88" t="s">
-        <v>112</v>
+        <v>118</v>
       </c>
       <c r="D88" t="s">
-        <v>118</v>
+        <v>113</v>
       </c>
       <c r="E88" t="s">
         <v>119</v>
@@ -3790,10 +3790,10 @@
         <v>8</v>
       </c>
       <c r="C89" t="s">
-        <v>112</v>
+        <v>118</v>
       </c>
       <c r="D89" t="s">
-        <v>118</v>
+        <v>113</v>
       </c>
       <c r="E89" t="s">
         <v>119</v>
@@ -3816,13 +3816,13 @@
         <v>124</v>
       </c>
       <c r="D90" t="s">
+        <v>113</v>
+      </c>
+      <c r="E90" t="s">
         <v>125</v>
       </c>
-      <c r="E90" t="s">
+      <c r="F90" t="s">
         <v>126</v>
-      </c>
-      <c r="F90" t="s">
-        <v>115</v>
       </c>
       <c r="G90" t="s">
         <v>116</v>
@@ -3839,13 +3839,13 @@
         <v>182</v>
       </c>
       <c r="D91" t="s">
+        <v>113</v>
+      </c>
+      <c r="E91" t="s">
         <v>183</v>
       </c>
-      <c r="E91" t="s">
+      <c r="F91" t="s">
         <v>184</v>
-      </c>
-      <c r="F91" t="s">
-        <v>115</v>
       </c>
       <c r="G91" t="s">
         <v>116</v>
@@ -3862,13 +3862,13 @@
         <v>124</v>
       </c>
       <c r="D92" t="s">
+        <v>113</v>
+      </c>
+      <c r="E92" t="s">
         <v>125</v>
       </c>
-      <c r="E92" t="s">
+      <c r="F92" t="s">
         <v>126</v>
-      </c>
-      <c r="F92" t="s">
-        <v>115</v>
       </c>
       <c r="G92" t="s">
         <v>116</v>
@@ -3882,10 +3882,10 @@
         <v>8</v>
       </c>
       <c r="C93" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="D93" t="s">
-        <v>121</v>
+        <v>113</v>
       </c>
       <c r="E93" t="s">
         <v>122</v>
@@ -3908,13 +3908,13 @@
         <v>124</v>
       </c>
       <c r="D94" t="s">
+        <v>113</v>
+      </c>
+      <c r="E94" t="s">
         <v>125</v>
       </c>
-      <c r="E94" t="s">
+      <c r="F94" t="s">
         <v>126</v>
-      </c>
-      <c r="F94" t="s">
-        <v>115</v>
       </c>
       <c r="G94" t="s">
         <v>116</v>
@@ -3928,10 +3928,10 @@
         <v>8</v>
       </c>
       <c r="C95" t="s">
-        <v>112</v>
+        <v>189</v>
       </c>
       <c r="D95" t="s">
-        <v>189</v>
+        <v>113</v>
       </c>
       <c r="E95" t="s">
         <v>190</v>
@@ -3954,13 +3954,13 @@
         <v>124</v>
       </c>
       <c r="D96" t="s">
+        <v>113</v>
+      </c>
+      <c r="E96" t="s">
         <v>125</v>
       </c>
-      <c r="E96" t="s">
+      <c r="F96" t="s">
         <v>126</v>
-      </c>
-      <c r="F96" t="s">
-        <v>115</v>
       </c>
       <c r="G96" t="s">
         <v>192</v>
@@ -3977,13 +3977,13 @@
         <v>124</v>
       </c>
       <c r="D97" t="s">
+        <v>113</v>
+      </c>
+      <c r="E97" t="s">
         <v>125</v>
       </c>
-      <c r="E97" t="s">
+      <c r="F97" t="s">
         <v>126</v>
-      </c>
-      <c r="F97" t="s">
-        <v>115</v>
       </c>
       <c r="G97" t="s">
         <v>192</v>
@@ -4000,13 +4000,13 @@
         <v>195</v>
       </c>
       <c r="D98" t="s">
+        <v>113</v>
+      </c>
+      <c r="E98" t="s">
         <v>196</v>
       </c>
-      <c r="E98" t="s">
+      <c r="F98" t="s">
         <v>197</v>
-      </c>
-      <c r="F98" t="s">
-        <v>115</v>
       </c>
       <c r="G98" t="s">
         <v>192</v>
@@ -4023,13 +4023,13 @@
         <v>124</v>
       </c>
       <c r="D99" t="s">
+        <v>113</v>
+      </c>
+      <c r="E99" t="s">
         <v>125</v>
       </c>
-      <c r="E99" t="s">
+      <c r="F99" t="s">
         <v>126</v>
-      </c>
-      <c r="F99" t="s">
-        <v>115</v>
       </c>
       <c r="G99" t="s">
         <v>192</v>
@@ -4043,16 +4043,16 @@
         <v>8</v>
       </c>
       <c r="C100" t="s">
-        <v>124</v>
+        <v>154</v>
       </c>
       <c r="D100" t="s">
-        <v>154</v>
+        <v>113</v>
       </c>
       <c r="E100" t="s">
         <v>155</v>
       </c>
       <c r="F100" t="s">
-        <v>115</v>
+        <v>126</v>
       </c>
       <c r="G100" t="s">
         <v>192</v>
@@ -4069,13 +4069,13 @@
         <v>124</v>
       </c>
       <c r="D101" t="s">
+        <v>113</v>
+      </c>
+      <c r="E101" t="s">
         <v>125</v>
       </c>
-      <c r="E101" t="s">
+      <c r="F101" t="s">
         <v>126</v>
-      </c>
-      <c r="F101" t="s">
-        <v>115</v>
       </c>
       <c r="G101" t="s">
         <v>192</v>
@@ -4089,16 +4089,16 @@
         <v>8</v>
       </c>
       <c r="C102" t="s">
-        <v>182</v>
+        <v>202</v>
       </c>
       <c r="D102" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="E102" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="F102" t="s">
-        <v>204</v>
+        <v>184</v>
       </c>
     </row>
     <row r="103" spans="1:7">
@@ -4109,16 +4109,16 @@
         <v>8</v>
       </c>
       <c r="C103" t="s">
-        <v>182</v>
+        <v>202</v>
       </c>
       <c r="D103" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="E103" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="F103" t="s">
-        <v>204</v>
+        <v>184</v>
       </c>
     </row>
     <row r="104" spans="1:7">
@@ -4129,16 +4129,16 @@
         <v>8</v>
       </c>
       <c r="C104" t="s">
-        <v>182</v>
+        <v>202</v>
       </c>
       <c r="D104" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="E104" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="F104" t="s">
-        <v>204</v>
+        <v>184</v>
       </c>
     </row>
     <row r="105" spans="1:7">
@@ -4149,16 +4149,16 @@
         <v>8</v>
       </c>
       <c r="C105" t="s">
-        <v>182</v>
+        <v>208</v>
       </c>
       <c r="D105" t="s">
-        <v>208</v>
+        <v>203</v>
       </c>
       <c r="E105" t="s">
         <v>209</v>
       </c>
       <c r="F105" t="s">
-        <v>204</v>
+        <v>184</v>
       </c>
     </row>
     <row r="106" spans="1:7">
@@ -4169,16 +4169,16 @@
         <v>8</v>
       </c>
       <c r="C106" t="s">
-        <v>182</v>
+        <v>202</v>
       </c>
       <c r="D106" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="E106" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="F106" t="s">
-        <v>204</v>
+        <v>184</v>
       </c>
     </row>
     <row r="107" spans="1:7">
@@ -4192,13 +4192,13 @@
         <v>182</v>
       </c>
       <c r="D107" t="s">
+        <v>203</v>
+      </c>
+      <c r="E107" t="s">
         <v>183</v>
       </c>
-      <c r="E107" t="s">
+      <c r="F107" t="s">
         <v>184</v>
-      </c>
-      <c r="F107" t="s">
-        <v>204</v>
       </c>
     </row>
     <row r="108" spans="1:7">
@@ -4209,16 +4209,16 @@
         <v>8</v>
       </c>
       <c r="C108" t="s">
-        <v>182</v>
+        <v>213</v>
       </c>
       <c r="D108" t="s">
-        <v>213</v>
+        <v>203</v>
       </c>
       <c r="E108" t="s">
         <v>214</v>
       </c>
       <c r="F108" t="s">
-        <v>204</v>
+        <v>184</v>
       </c>
     </row>
     <row r="109" spans="1:7">
@@ -4229,16 +4229,16 @@
         <v>8</v>
       </c>
       <c r="C109" t="s">
-        <v>90</v>
+        <v>216</v>
       </c>
       <c r="D109" t="s">
-        <v>216</v>
+        <v>203</v>
       </c>
       <c r="E109" t="s">
         <v>217</v>
       </c>
       <c r="F109" t="s">
-        <v>204</v>
+        <v>93</v>
       </c>
     </row>
     <row r="110" spans="1:7">
@@ -4249,16 +4249,16 @@
         <v>8</v>
       </c>
       <c r="C110" t="s">
-        <v>90</v>
+        <v>219</v>
       </c>
       <c r="D110" t="s">
-        <v>219</v>
+        <v>203</v>
       </c>
       <c r="E110" t="s">
         <v>220</v>
       </c>
       <c r="F110" t="s">
-        <v>204</v>
+        <v>93</v>
       </c>
     </row>
     <row r="111" spans="1:7">
@@ -4269,16 +4269,16 @@
         <v>8</v>
       </c>
       <c r="C111" t="s">
-        <v>182</v>
+        <v>202</v>
       </c>
       <c r="D111" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="E111" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="F111" t="s">
-        <v>204</v>
+        <v>184</v>
       </c>
     </row>
     <row r="112" spans="1:7">
@@ -4292,13 +4292,13 @@
         <v>223</v>
       </c>
       <c r="D112" t="s">
+        <v>203</v>
+      </c>
+      <c r="E112" t="s">
         <v>224</v>
       </c>
-      <c r="E112" t="s">
+      <c r="F112" t="s">
         <v>225</v>
-      </c>
-      <c r="F112" t="s">
-        <v>204</v>
       </c>
     </row>
     <row r="113" spans="1:6">
@@ -4309,16 +4309,16 @@
         <v>8</v>
       </c>
       <c r="C113" t="s">
-        <v>112</v>
+        <v>143</v>
       </c>
       <c r="D113" t="s">
-        <v>143</v>
+        <v>203</v>
       </c>
       <c r="E113" t="s">
         <v>114</v>
       </c>
       <c r="F113" t="s">
-        <v>204</v>
+        <v>115</v>
       </c>
     </row>
     <row r="114" spans="1:6">
@@ -4329,16 +4329,16 @@
         <v>8</v>
       </c>
       <c r="C114" t="s">
-        <v>124</v>
+        <v>151</v>
       </c>
       <c r="D114" t="s">
-        <v>151</v>
+        <v>203</v>
       </c>
       <c r="E114" t="s">
         <v>152</v>
       </c>
       <c r="F114" t="s">
-        <v>204</v>
+        <v>126</v>
       </c>
     </row>
     <row r="115" spans="1:6">
@@ -4352,13 +4352,13 @@
         <v>182</v>
       </c>
       <c r="D115" t="s">
+        <v>203</v>
+      </c>
+      <c r="E115" t="s">
         <v>183</v>
       </c>
-      <c r="E115" t="s">
+      <c r="F115" t="s">
         <v>184</v>
-      </c>
-      <c r="F115" t="s">
-        <v>204</v>
       </c>
     </row>
     <row r="116" spans="1:6">
@@ -4369,16 +4369,16 @@
         <v>8</v>
       </c>
       <c r="C116" t="s">
-        <v>223</v>
+        <v>230</v>
       </c>
       <c r="D116" t="s">
-        <v>230</v>
+        <v>203</v>
       </c>
       <c r="E116" t="s">
         <v>231</v>
       </c>
       <c r="F116" t="s">
-        <v>204</v>
+        <v>225</v>
       </c>
     </row>
     <row r="117" spans="1:6">
@@ -4392,13 +4392,13 @@
         <v>223</v>
       </c>
       <c r="D117" t="s">
+        <v>203</v>
+      </c>
+      <c r="E117" t="s">
         <v>224</v>
       </c>
-      <c r="E117" t="s">
+      <c r="F117" t="s">
         <v>225</v>
-      </c>
-      <c r="F117" t="s">
-        <v>204</v>
       </c>
     </row>
     <row r="118" spans="1:6">
@@ -4409,16 +4409,16 @@
         <v>8</v>
       </c>
       <c r="C118" t="s">
-        <v>163</v>
+        <v>234</v>
       </c>
       <c r="D118" t="s">
-        <v>234</v>
+        <v>203</v>
       </c>
       <c r="E118" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="F118" t="s">
-        <v>204</v>
+        <v>165</v>
       </c>
     </row>
     <row r="119" spans="1:6">
@@ -4432,13 +4432,13 @@
         <v>182</v>
       </c>
       <c r="D119" t="s">
+        <v>203</v>
+      </c>
+      <c r="E119" t="s">
         <v>183</v>
       </c>
-      <c r="E119" t="s">
+      <c r="F119" t="s">
         <v>184</v>
-      </c>
-      <c r="F119" t="s">
-        <v>204</v>
       </c>
     </row>
     <row r="120" spans="1:6">
@@ -4449,16 +4449,16 @@
         <v>8</v>
       </c>
       <c r="C120" t="s">
-        <v>112</v>
+        <v>170</v>
       </c>
       <c r="D120" t="s">
-        <v>170</v>
+        <v>237</v>
       </c>
       <c r="E120" t="s">
         <v>171</v>
       </c>
       <c r="F120" t="s">
-        <v>237</v>
+        <v>115</v>
       </c>
     </row>
     <row r="121" spans="1:6">
@@ -4469,16 +4469,16 @@
         <v>8</v>
       </c>
       <c r="C121" t="s">
-        <v>112</v>
+        <v>143</v>
       </c>
       <c r="D121" t="s">
-        <v>143</v>
+        <v>237</v>
       </c>
       <c r="E121" t="s">
         <v>114</v>
       </c>
       <c r="F121" t="s">
-        <v>237</v>
+        <v>115</v>
       </c>
     </row>
     <row r="122" spans="1:6">
@@ -4489,16 +4489,16 @@
         <v>8</v>
       </c>
       <c r="C122" t="s">
-        <v>112</v>
+        <v>170</v>
       </c>
       <c r="D122" t="s">
-        <v>170</v>
+        <v>237</v>
       </c>
       <c r="E122" t="s">
         <v>171</v>
       </c>
       <c r="F122" t="s">
-        <v>237</v>
+        <v>115</v>
       </c>
     </row>
     <row r="123" spans="1:6">
@@ -4509,16 +4509,16 @@
         <v>8</v>
       </c>
       <c r="C123" t="s">
-        <v>112</v>
+        <v>170</v>
       </c>
       <c r="D123" t="s">
-        <v>170</v>
+        <v>237</v>
       </c>
       <c r="E123" t="s">
         <v>171</v>
       </c>
       <c r="F123" t="s">
-        <v>237</v>
+        <v>115</v>
       </c>
     </row>
     <row r="124" spans="1:6">
@@ -4529,16 +4529,16 @@
         <v>8</v>
       </c>
       <c r="C124" t="s">
-        <v>163</v>
+        <v>242</v>
       </c>
       <c r="D124" t="s">
-        <v>242</v>
+        <v>237</v>
       </c>
       <c r="E124" t="s">
         <v>243</v>
       </c>
       <c r="F124" t="s">
-        <v>237</v>
+        <v>165</v>
       </c>
     </row>
     <row r="125" spans="1:6">
@@ -4549,16 +4549,16 @@
         <v>8</v>
       </c>
       <c r="C125" t="s">
-        <v>163</v>
+        <v>242</v>
       </c>
       <c r="D125" t="s">
-        <v>242</v>
+        <v>237</v>
       </c>
       <c r="E125" t="s">
         <v>243</v>
       </c>
       <c r="F125" t="s">
-        <v>237</v>
+        <v>165</v>
       </c>
     </row>
     <row r="126" spans="1:6">
@@ -4569,16 +4569,16 @@
         <v>8</v>
       </c>
       <c r="C126" t="s">
-        <v>163</v>
+        <v>242</v>
       </c>
       <c r="D126" t="s">
-        <v>242</v>
+        <v>237</v>
       </c>
       <c r="E126" t="s">
         <v>243</v>
       </c>
       <c r="F126" t="s">
-        <v>237</v>
+        <v>165</v>
       </c>
     </row>
     <row r="127" spans="1:6">
@@ -4589,16 +4589,16 @@
         <v>8</v>
       </c>
       <c r="C127" t="s">
-        <v>163</v>
+        <v>242</v>
       </c>
       <c r="D127" t="s">
-        <v>242</v>
+        <v>237</v>
       </c>
       <c r="E127" t="s">
         <v>243</v>
       </c>
       <c r="F127" t="s">
-        <v>237</v>
+        <v>165</v>
       </c>
     </row>
     <row r="128" spans="1:6">
@@ -4609,16 +4609,16 @@
         <v>8</v>
       </c>
       <c r="C128" t="s">
-        <v>163</v>
+        <v>242</v>
       </c>
       <c r="D128" t="s">
-        <v>242</v>
+        <v>237</v>
       </c>
       <c r="E128" t="s">
         <v>243</v>
       </c>
       <c r="F128" t="s">
-        <v>237</v>
+        <v>165</v>
       </c>
     </row>
     <row r="129" spans="1:7">
@@ -4629,16 +4629,16 @@
         <v>8</v>
       </c>
       <c r="C129" t="s">
-        <v>163</v>
+        <v>249</v>
       </c>
       <c r="D129" t="s">
-        <v>249</v>
+        <v>237</v>
       </c>
       <c r="E129" t="s">
         <v>243</v>
       </c>
       <c r="F129" t="s">
-        <v>237</v>
+        <v>165</v>
       </c>
     </row>
     <row r="130" spans="1:7">
@@ -4649,16 +4649,16 @@
         <v>8</v>
       </c>
       <c r="C130" t="s">
-        <v>163</v>
+        <v>251</v>
       </c>
       <c r="D130" t="s">
-        <v>251</v>
+        <v>237</v>
       </c>
       <c r="E130" t="s">
         <v>243</v>
       </c>
       <c r="F130" t="s">
-        <v>237</v>
+        <v>165</v>
       </c>
     </row>
     <row r="131" spans="1:7">
@@ -4669,16 +4669,16 @@
         <v>8</v>
       </c>
       <c r="C131" t="s">
-        <v>163</v>
+        <v>253</v>
       </c>
       <c r="D131" t="s">
-        <v>253</v>
+        <v>237</v>
       </c>
       <c r="E131" t="s">
         <v>243</v>
       </c>
       <c r="F131" t="s">
-        <v>237</v>
+        <v>165</v>
       </c>
     </row>
     <row r="132" spans="1:7">
@@ -4689,16 +4689,16 @@
         <v>8</v>
       </c>
       <c r="C132" t="s">
-        <v>163</v>
+        <v>255</v>
       </c>
       <c r="D132" t="s">
-        <v>255</v>
+        <v>237</v>
       </c>
       <c r="E132" t="s">
         <v>256</v>
       </c>
       <c r="F132" t="s">
-        <v>237</v>
+        <v>165</v>
       </c>
     </row>
     <row r="133" spans="1:7">
@@ -4709,16 +4709,16 @@
         <v>8</v>
       </c>
       <c r="C133" t="s">
-        <v>112</v>
+        <v>189</v>
       </c>
       <c r="D133" t="s">
-        <v>189</v>
+        <v>237</v>
       </c>
       <c r="E133" t="s">
         <v>190</v>
       </c>
       <c r="F133" t="s">
-        <v>237</v>
+        <v>115</v>
       </c>
     </row>
     <row r="134" spans="1:7">
@@ -4729,16 +4729,16 @@
         <v>8</v>
       </c>
       <c r="C134" t="s">
-        <v>163</v>
+        <v>175</v>
       </c>
       <c r="D134" t="s">
-        <v>175</v>
+        <v>259</v>
       </c>
       <c r="E134" t="s">
         <v>176</v>
       </c>
       <c r="F134" t="s">
-        <v>259</v>
+        <v>165</v>
       </c>
     </row>
     <row r="135" spans="1:7">
@@ -4749,16 +4749,16 @@
         <v>8</v>
       </c>
       <c r="C135" t="s">
-        <v>163</v>
+        <v>175</v>
       </c>
       <c r="D135" t="s">
-        <v>175</v>
+        <v>259</v>
       </c>
       <c r="E135" t="s">
         <v>176</v>
       </c>
       <c r="F135" t="s">
-        <v>259</v>
+        <v>165</v>
       </c>
     </row>
     <row r="136" spans="1:7">
@@ -4769,16 +4769,16 @@
         <v>8</v>
       </c>
       <c r="C136" t="s">
-        <v>163</v>
+        <v>175</v>
       </c>
       <c r="D136" t="s">
-        <v>175</v>
+        <v>259</v>
       </c>
       <c r="E136" t="s">
         <v>176</v>
       </c>
       <c r="F136" t="s">
-        <v>259</v>
+        <v>165</v>
       </c>
     </row>
     <row r="137" spans="1:7">
@@ -4789,16 +4789,16 @@
         <v>8</v>
       </c>
       <c r="C137" t="s">
-        <v>163</v>
+        <v>175</v>
       </c>
       <c r="D137" t="s">
-        <v>175</v>
+        <v>259</v>
       </c>
       <c r="E137" t="s">
         <v>176</v>
       </c>
       <c r="F137" t="s">
-        <v>259</v>
+        <v>165</v>
       </c>
     </row>
     <row r="138" spans="1:7">
@@ -4809,16 +4809,16 @@
         <v>8</v>
       </c>
       <c r="C138" t="s">
-        <v>163</v>
+        <v>175</v>
       </c>
       <c r="D138" t="s">
-        <v>175</v>
+        <v>259</v>
       </c>
       <c r="E138" t="s">
         <v>176</v>
       </c>
       <c r="F138" t="s">
-        <v>259</v>
+        <v>165</v>
       </c>
     </row>
     <row r="139" spans="1:7">
@@ -4829,16 +4829,16 @@
         <v>8</v>
       </c>
       <c r="C139" t="s">
-        <v>223</v>
+        <v>265</v>
       </c>
       <c r="D139" t="s">
-        <v>265</v>
+        <v>259</v>
       </c>
       <c r="E139" t="s">
         <v>266</v>
       </c>
       <c r="F139" t="s">
-        <v>259</v>
+        <v>225</v>
       </c>
     </row>
     <row r="140" spans="1:7">
@@ -4849,16 +4849,16 @@
         <v>8</v>
       </c>
       <c r="C140" t="s">
-        <v>163</v>
+        <v>175</v>
       </c>
       <c r="D140" t="s">
-        <v>175</v>
+        <v>259</v>
       </c>
       <c r="E140" t="s">
         <v>176</v>
       </c>
       <c r="F140" t="s">
-        <v>259</v>
+        <v>165</v>
       </c>
     </row>
     <row r="141" spans="1:7">
@@ -4869,16 +4869,16 @@
         <v>8</v>
       </c>
       <c r="C141" t="s">
-        <v>163</v>
+        <v>269</v>
       </c>
       <c r="D141" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="E141" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="F141" t="s">
-        <v>271</v>
+        <v>165</v>
       </c>
       <c r="G141" t="s">
         <v>272</v>
@@ -4892,16 +4892,16 @@
         <v>8</v>
       </c>
       <c r="C142" t="s">
-        <v>163</v>
+        <v>269</v>
       </c>
       <c r="D142" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="E142" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="F142" t="s">
-        <v>271</v>
+        <v>165</v>
       </c>
       <c r="G142" t="s">
         <v>272</v>
@@ -4915,16 +4915,16 @@
         <v>8</v>
       </c>
       <c r="C143" t="s">
-        <v>163</v>
+        <v>275</v>
       </c>
       <c r="D143" t="s">
-        <v>275</v>
+        <v>270</v>
       </c>
       <c r="E143" t="s">
         <v>276</v>
       </c>
       <c r="F143" t="s">
-        <v>271</v>
+        <v>165</v>
       </c>
       <c r="G143" t="s">
         <v>272</v>
@@ -4938,16 +4938,16 @@
         <v>8</v>
       </c>
       <c r="C144" t="s">
-        <v>163</v>
+        <v>275</v>
       </c>
       <c r="D144" t="s">
-        <v>275</v>
+        <v>270</v>
       </c>
       <c r="E144" t="s">
         <v>276</v>
       </c>
       <c r="F144" t="s">
-        <v>271</v>
+        <v>165</v>
       </c>
       <c r="G144" t="s">
         <v>272</v>
@@ -4961,16 +4961,16 @@
         <v>8</v>
       </c>
       <c r="C145" t="s">
-        <v>163</v>
+        <v>275</v>
       </c>
       <c r="D145" t="s">
-        <v>275</v>
+        <v>270</v>
       </c>
       <c r="E145" t="s">
         <v>276</v>
       </c>
       <c r="F145" t="s">
-        <v>271</v>
+        <v>165</v>
       </c>
       <c r="G145" t="s">
         <v>272</v>
@@ -4984,16 +4984,16 @@
         <v>8</v>
       </c>
       <c r="C146" t="s">
-        <v>163</v>
+        <v>269</v>
       </c>
       <c r="D146" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="E146" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="F146" t="s">
-        <v>271</v>
+        <v>165</v>
       </c>
       <c r="G146" t="s">
         <v>272</v>
@@ -5007,16 +5007,16 @@
         <v>8</v>
       </c>
       <c r="C147" t="s">
-        <v>163</v>
+        <v>269</v>
       </c>
       <c r="D147" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="E147" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="F147" t="s">
-        <v>271</v>
+        <v>165</v>
       </c>
       <c r="G147" t="s">
         <v>281</v>
@@ -5030,16 +5030,16 @@
         <v>8</v>
       </c>
       <c r="C148" t="s">
-        <v>163</v>
+        <v>269</v>
       </c>
       <c r="D148" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="E148" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="F148" t="s">
-        <v>271</v>
+        <v>165</v>
       </c>
       <c r="G148" t="s">
         <v>281</v>
@@ -5053,16 +5053,16 @@
         <v>8</v>
       </c>
       <c r="C149" t="s">
-        <v>163</v>
+        <v>269</v>
       </c>
       <c r="D149" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="E149" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="F149" t="s">
-        <v>271</v>
+        <v>165</v>
       </c>
       <c r="G149" t="s">
         <v>281</v>
@@ -5076,16 +5076,16 @@
         <v>8</v>
       </c>
       <c r="C150" t="s">
-        <v>163</v>
+        <v>269</v>
       </c>
       <c r="D150" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="E150" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="F150" t="s">
-        <v>271</v>
+        <v>165</v>
       </c>
       <c r="G150" t="s">
         <v>281</v>
@@ -5099,16 +5099,16 @@
         <v>8</v>
       </c>
       <c r="C151" t="s">
-        <v>163</v>
+        <v>269</v>
       </c>
       <c r="D151" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="E151" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="F151" t="s">
-        <v>271</v>
+        <v>165</v>
       </c>
       <c r="G151" t="s">
         <v>281</v>
@@ -5122,16 +5122,16 @@
         <v>8</v>
       </c>
       <c r="C152" t="s">
-        <v>163</v>
+        <v>269</v>
       </c>
       <c r="D152" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="E152" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="F152" t="s">
-        <v>271</v>
+        <v>165</v>
       </c>
       <c r="G152" t="s">
         <v>281</v>
@@ -5145,16 +5145,16 @@
         <v>8</v>
       </c>
       <c r="C153" t="s">
-        <v>163</v>
+        <v>269</v>
       </c>
       <c r="D153" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="E153" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="F153" t="s">
-        <v>271</v>
+        <v>165</v>
       </c>
       <c r="G153" t="s">
         <v>281</v>
@@ -5168,16 +5168,16 @@
         <v>8</v>
       </c>
       <c r="C154" t="s">
-        <v>163</v>
+        <v>269</v>
       </c>
       <c r="D154" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="E154" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="F154" t="s">
-        <v>271</v>
+        <v>165</v>
       </c>
       <c r="G154" t="s">
         <v>281</v>
@@ -5191,16 +5191,16 @@
         <v>8</v>
       </c>
       <c r="C155" t="s">
-        <v>163</v>
+        <v>269</v>
       </c>
       <c r="D155" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="E155" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="F155" t="s">
-        <v>271</v>
+        <v>165</v>
       </c>
       <c r="G155" t="s">
         <v>281</v>
@@ -5214,16 +5214,16 @@
         <v>8</v>
       </c>
       <c r="C156" t="s">
-        <v>163</v>
+        <v>269</v>
       </c>
       <c r="D156" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="E156" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="F156" t="s">
-        <v>271</v>
+        <v>165</v>
       </c>
       <c r="G156" t="s">
         <v>291</v>
@@ -5237,16 +5237,16 @@
         <v>8</v>
       </c>
       <c r="C157" t="s">
-        <v>163</v>
+        <v>293</v>
       </c>
       <c r="D157" t="s">
-        <v>293</v>
+        <v>270</v>
       </c>
       <c r="E157" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="F157" t="s">
-        <v>271</v>
+        <v>165</v>
       </c>
       <c r="G157" t="s">
         <v>291</v>
@@ -5260,16 +5260,16 @@
         <v>8</v>
       </c>
       <c r="C158" t="s">
-        <v>163</v>
+        <v>269</v>
       </c>
       <c r="D158" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="E158" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="F158" t="s">
-        <v>271</v>
+        <v>165</v>
       </c>
       <c r="G158" t="s">
         <v>291</v>
@@ -5283,16 +5283,16 @@
         <v>8</v>
       </c>
       <c r="C159" t="s">
-        <v>163</v>
+        <v>269</v>
       </c>
       <c r="D159" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="E159" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="F159" t="s">
-        <v>271</v>
+        <v>165</v>
       </c>
       <c r="G159" t="s">
         <v>291</v>
@@ -5306,16 +5306,16 @@
         <v>8</v>
       </c>
       <c r="C160" t="s">
-        <v>163</v>
+        <v>269</v>
       </c>
       <c r="D160" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="E160" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="F160" t="s">
-        <v>271</v>
+        <v>165</v>
       </c>
       <c r="G160" t="s">
         <v>291</v>
@@ -5329,16 +5329,16 @@
         <v>8</v>
       </c>
       <c r="C161" t="s">
-        <v>163</v>
+        <v>269</v>
       </c>
       <c r="D161" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="E161" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="F161" t="s">
-        <v>271</v>
+        <v>165</v>
       </c>
       <c r="G161" t="s">
         <v>291</v>
@@ -5352,16 +5352,16 @@
         <v>8</v>
       </c>
       <c r="C162" t="s">
-        <v>163</v>
+        <v>269</v>
       </c>
       <c r="D162" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="E162" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="F162" t="s">
-        <v>271</v>
+        <v>165</v>
       </c>
       <c r="G162" t="s">
         <v>299</v>
@@ -5375,16 +5375,16 @@
         <v>8</v>
       </c>
       <c r="C163" t="s">
-        <v>163</v>
+        <v>301</v>
       </c>
       <c r="D163" t="s">
-        <v>301</v>
+        <v>270</v>
       </c>
       <c r="E163" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="F163" t="s">
-        <v>271</v>
+        <v>165</v>
       </c>
       <c r="G163" t="s">
         <v>302</v>
@@ -5398,16 +5398,16 @@
         <v>8</v>
       </c>
       <c r="C164" t="s">
-        <v>163</v>
+        <v>269</v>
       </c>
       <c r="D164" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="E164" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="F164" t="s">
-        <v>271</v>
+        <v>165</v>
       </c>
       <c r="G164" t="s">
         <v>304</v>
@@ -5421,16 +5421,16 @@
         <v>8</v>
       </c>
       <c r="C165" t="s">
-        <v>163</v>
+        <v>269</v>
       </c>
       <c r="D165" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="E165" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="F165" t="s">
-        <v>271</v>
+        <v>165</v>
       </c>
       <c r="G165" t="s">
         <v>304</v>
@@ -5444,16 +5444,16 @@
         <v>8</v>
       </c>
       <c r="C166" t="s">
-        <v>163</v>
+        <v>269</v>
       </c>
       <c r="D166" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="E166" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="F166" t="s">
-        <v>271</v>
+        <v>165</v>
       </c>
       <c r="G166" t="s">
         <v>304</v>
@@ -5467,16 +5467,16 @@
         <v>8</v>
       </c>
       <c r="C167" t="s">
-        <v>163</v>
+        <v>269</v>
       </c>
       <c r="D167" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="E167" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="F167" t="s">
-        <v>271</v>
+        <v>165</v>
       </c>
       <c r="G167" t="s">
         <v>304</v>
@@ -5490,16 +5490,16 @@
         <v>8</v>
       </c>
       <c r="C168" t="s">
-        <v>163</v>
+        <v>309</v>
       </c>
       <c r="D168" t="s">
-        <v>309</v>
+        <v>270</v>
       </c>
       <c r="E168" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="F168" t="s">
-        <v>271</v>
+        <v>165</v>
       </c>
       <c r="G168" t="s">
         <v>304</v>
@@ -5513,16 +5513,16 @@
         <v>8</v>
       </c>
       <c r="C169" t="s">
-        <v>163</v>
+        <v>309</v>
       </c>
       <c r="D169" t="s">
-        <v>309</v>
+        <v>270</v>
       </c>
       <c r="E169" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="F169" t="s">
-        <v>271</v>
+        <v>165</v>
       </c>
       <c r="G169" t="s">
         <v>304</v>
@@ -5536,16 +5536,16 @@
         <v>8</v>
       </c>
       <c r="C170" t="s">
-        <v>163</v>
+        <v>269</v>
       </c>
       <c r="D170" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="E170" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="F170" t="s">
-        <v>271</v>
+        <v>165</v>
       </c>
       <c r="G170" t="s">
         <v>304</v>
@@ -5562,13 +5562,13 @@
         <v>163</v>
       </c>
       <c r="D171" t="s">
+        <v>313</v>
+      </c>
+      <c r="E171" t="s">
         <v>164</v>
       </c>
-      <c r="E171" t="s">
-        <v>165</v>
-      </c>
       <c r="F171" t="s">
-        <v>313</v>
+        <v>165</v>
       </c>
     </row>
     <row r="172" spans="1:7">
@@ -5579,16 +5579,16 @@
         <v>8</v>
       </c>
       <c r="C172" t="s">
-        <v>112</v>
+        <v>118</v>
       </c>
       <c r="D172" t="s">
-        <v>118</v>
+        <v>313</v>
       </c>
       <c r="E172" t="s">
         <v>119</v>
       </c>
       <c r="F172" t="s">
-        <v>313</v>
+        <v>115</v>
       </c>
     </row>
     <row r="173" spans="1:7">
@@ -5602,13 +5602,13 @@
         <v>163</v>
       </c>
       <c r="D173" t="s">
+        <v>313</v>
+      </c>
+      <c r="E173" t="s">
         <v>164</v>
       </c>
-      <c r="E173" t="s">
-        <v>165</v>
-      </c>
       <c r="F173" t="s">
-        <v>313</v>
+        <v>165</v>
       </c>
     </row>
     <row r="174" spans="1:7">
@@ -5622,13 +5622,13 @@
         <v>163</v>
       </c>
       <c r="D174" t="s">
+        <v>313</v>
+      </c>
+      <c r="E174" t="s">
         <v>164</v>
       </c>
-      <c r="E174" t="s">
-        <v>165</v>
-      </c>
       <c r="F174" t="s">
-        <v>313</v>
+        <v>165</v>
       </c>
     </row>
     <row r="175" spans="1:7">
@@ -5642,13 +5642,13 @@
         <v>163</v>
       </c>
       <c r="D175" t="s">
+        <v>313</v>
+      </c>
+      <c r="E175" t="s">
         <v>164</v>
       </c>
-      <c r="E175" t="s">
-        <v>165</v>
-      </c>
       <c r="F175" t="s">
-        <v>313</v>
+        <v>165</v>
       </c>
     </row>
     <row r="176" spans="1:7">
@@ -5662,13 +5662,13 @@
         <v>163</v>
       </c>
       <c r="D176" t="s">
+        <v>313</v>
+      </c>
+      <c r="E176" t="s">
         <v>164</v>
       </c>
-      <c r="E176" t="s">
-        <v>165</v>
-      </c>
       <c r="F176" t="s">
-        <v>313</v>
+        <v>165</v>
       </c>
     </row>
     <row r="177" spans="1:7">
@@ -5682,13 +5682,13 @@
         <v>163</v>
       </c>
       <c r="D177" t="s">
+        <v>320</v>
+      </c>
+      <c r="E177" t="s">
         <v>164</v>
       </c>
-      <c r="E177" t="s">
-        <v>165</v>
-      </c>
       <c r="F177" t="s">
-        <v>320</v>
+        <v>165</v>
       </c>
     </row>
     <row r="178" spans="1:7">
@@ -5702,13 +5702,13 @@
         <v>163</v>
       </c>
       <c r="D178" t="s">
+        <v>320</v>
+      </c>
+      <c r="E178" t="s">
         <v>164</v>
       </c>
-      <c r="E178" t="s">
-        <v>165</v>
-      </c>
       <c r="F178" t="s">
-        <v>320</v>
+        <v>165</v>
       </c>
     </row>
     <row r="179" spans="1:7">
@@ -5722,13 +5722,13 @@
         <v>163</v>
       </c>
       <c r="D179" t="s">
+        <v>320</v>
+      </c>
+      <c r="E179" t="s">
         <v>164</v>
       </c>
-      <c r="E179" t="s">
-        <v>165</v>
-      </c>
       <c r="F179" t="s">
-        <v>320</v>
+        <v>165</v>
       </c>
     </row>
     <row r="180" spans="1:7">
@@ -5742,13 +5742,13 @@
         <v>163</v>
       </c>
       <c r="D180" t="s">
+        <v>320</v>
+      </c>
+      <c r="E180" t="s">
         <v>164</v>
       </c>
-      <c r="E180" t="s">
-        <v>165</v>
-      </c>
       <c r="F180" t="s">
-        <v>320</v>
+        <v>165</v>
       </c>
     </row>
     <row r="181" spans="1:7">
@@ -5759,16 +5759,16 @@
         <v>8</v>
       </c>
       <c r="C181" t="s">
-        <v>163</v>
+        <v>325</v>
       </c>
       <c r="D181" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="E181" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="F181" t="s">
-        <v>327</v>
+        <v>165</v>
       </c>
       <c r="G181" t="s">
         <v>328</v>
@@ -5782,16 +5782,16 @@
         <v>8</v>
       </c>
       <c r="C182" t="s">
-        <v>163</v>
+        <v>325</v>
       </c>
       <c r="D182" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="E182" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="F182" t="s">
-        <v>327</v>
+        <v>165</v>
       </c>
       <c r="G182" t="s">
         <v>328</v>
@@ -5805,16 +5805,16 @@
         <v>8</v>
       </c>
       <c r="C183" t="s">
-        <v>163</v>
+        <v>325</v>
       </c>
       <c r="D183" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="E183" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="F183" t="s">
-        <v>327</v>
+        <v>165</v>
       </c>
       <c r="G183" t="s">
         <v>328</v>
@@ -5828,16 +5828,16 @@
         <v>8</v>
       </c>
       <c r="C184" t="s">
-        <v>163</v>
+        <v>325</v>
       </c>
       <c r="D184" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="E184" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="F184" t="s">
-        <v>327</v>
+        <v>165</v>
       </c>
       <c r="G184" t="s">
         <v>328</v>
@@ -5851,16 +5851,16 @@
         <v>8</v>
       </c>
       <c r="C185" t="s">
-        <v>163</v>
+        <v>325</v>
       </c>
       <c r="D185" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="E185" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="F185" t="s">
-        <v>327</v>
+        <v>165</v>
       </c>
       <c r="G185" t="s">
         <v>328</v>
@@ -5874,16 +5874,16 @@
         <v>8</v>
       </c>
       <c r="C186" t="s">
-        <v>163</v>
+        <v>325</v>
       </c>
       <c r="D186" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="E186" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="F186" t="s">
-        <v>327</v>
+        <v>165</v>
       </c>
       <c r="G186" t="s">
         <v>328</v>
@@ -5897,16 +5897,16 @@
         <v>8</v>
       </c>
       <c r="C187" t="s">
-        <v>163</v>
+        <v>325</v>
       </c>
       <c r="D187" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="E187" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="F187" t="s">
-        <v>327</v>
+        <v>165</v>
       </c>
       <c r="G187" t="s">
         <v>328</v>
@@ -5920,16 +5920,16 @@
         <v>8</v>
       </c>
       <c r="C188" t="s">
-        <v>163</v>
+        <v>325</v>
       </c>
       <c r="D188" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="E188" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="F188" t="s">
-        <v>327</v>
+        <v>165</v>
       </c>
       <c r="G188" t="s">
         <v>328</v>
@@ -5943,16 +5943,16 @@
         <v>8</v>
       </c>
       <c r="C189" t="s">
-        <v>163</v>
+        <v>325</v>
       </c>
       <c r="D189" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="E189" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="F189" t="s">
-        <v>327</v>
+        <v>165</v>
       </c>
       <c r="G189" t="s">
         <v>328</v>
@@ -5966,16 +5966,16 @@
         <v>8</v>
       </c>
       <c r="C190" t="s">
-        <v>163</v>
+        <v>325</v>
       </c>
       <c r="D190" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="E190" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="F190" t="s">
-        <v>327</v>
+        <v>165</v>
       </c>
       <c r="G190" t="s">
         <v>328</v>
@@ -5989,16 +5989,16 @@
         <v>8</v>
       </c>
       <c r="C191" t="s">
-        <v>163</v>
+        <v>325</v>
       </c>
       <c r="D191" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="E191" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="F191" t="s">
-        <v>327</v>
+        <v>165</v>
       </c>
       <c r="G191" t="s">
         <v>328</v>
@@ -6012,16 +6012,16 @@
         <v>8</v>
       </c>
       <c r="C192" t="s">
-        <v>163</v>
+        <v>325</v>
       </c>
       <c r="D192" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="E192" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="F192" t="s">
-        <v>327</v>
+        <v>165</v>
       </c>
       <c r="G192" t="s">
         <v>328</v>
@@ -6035,16 +6035,16 @@
         <v>8</v>
       </c>
       <c r="C193" t="s">
-        <v>163</v>
+        <v>341</v>
       </c>
       <c r="D193" t="s">
-        <v>341</v>
+        <v>326</v>
       </c>
       <c r="E193" t="s">
         <v>276</v>
       </c>
       <c r="F193" t="s">
-        <v>327</v>
+        <v>165</v>
       </c>
       <c r="G193" t="s">
         <v>328</v>
@@ -6058,16 +6058,16 @@
         <v>8</v>
       </c>
       <c r="C194" t="s">
-        <v>163</v>
+        <v>325</v>
       </c>
       <c r="D194" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="E194" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="F194" t="s">
-        <v>327</v>
+        <v>165</v>
       </c>
       <c r="G194" t="s">
         <v>328</v>
@@ -6081,16 +6081,16 @@
         <v>8</v>
       </c>
       <c r="C195" t="s">
-        <v>163</v>
+        <v>325</v>
       </c>
       <c r="D195" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="E195" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="F195" t="s">
-        <v>327</v>
+        <v>165</v>
       </c>
       <c r="G195" t="s">
         <v>328</v>
@@ -6104,16 +6104,16 @@
         <v>8</v>
       </c>
       <c r="C196" t="s">
-        <v>163</v>
+        <v>325</v>
       </c>
       <c r="D196" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="E196" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="F196" t="s">
-        <v>327</v>
+        <v>165</v>
       </c>
       <c r="G196" t="s">
         <v>328</v>
@@ -6127,16 +6127,16 @@
         <v>8</v>
       </c>
       <c r="C197" t="s">
-        <v>163</v>
+        <v>325</v>
       </c>
       <c r="D197" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="E197" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="F197" t="s">
-        <v>327</v>
+        <v>165</v>
       </c>
       <c r="G197" t="s">
         <v>328</v>
@@ -6150,16 +6150,16 @@
         <v>8</v>
       </c>
       <c r="C198" t="s">
-        <v>163</v>
+        <v>325</v>
       </c>
       <c r="D198" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="E198" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="F198" t="s">
-        <v>327</v>
+        <v>165</v>
       </c>
       <c r="G198" t="s">
         <v>328</v>
@@ -6173,16 +6173,16 @@
         <v>8</v>
       </c>
       <c r="C199" t="s">
-        <v>163</v>
+        <v>348</v>
       </c>
       <c r="D199" t="s">
-        <v>348</v>
+        <v>326</v>
       </c>
       <c r="E199" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="F199" t="s">
-        <v>327</v>
+        <v>165</v>
       </c>
       <c r="G199" t="s">
         <v>349</v>
@@ -6196,16 +6196,16 @@
         <v>8</v>
       </c>
       <c r="C200" t="s">
-        <v>163</v>
+        <v>348</v>
       </c>
       <c r="D200" t="s">
-        <v>348</v>
+        <v>326</v>
       </c>
       <c r="E200" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="F200" t="s">
-        <v>327</v>
+        <v>165</v>
       </c>
       <c r="G200" t="s">
         <v>349</v>
@@ -6219,16 +6219,16 @@
         <v>8</v>
       </c>
       <c r="C201" t="s">
-        <v>163</v>
+        <v>348</v>
       </c>
       <c r="D201" t="s">
-        <v>348</v>
+        <v>326</v>
       </c>
       <c r="E201" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="F201" t="s">
-        <v>327</v>
+        <v>165</v>
       </c>
       <c r="G201" t="s">
         <v>349</v>
@@ -6242,16 +6242,16 @@
         <v>8</v>
       </c>
       <c r="C202" t="s">
-        <v>163</v>
+        <v>348</v>
       </c>
       <c r="D202" t="s">
-        <v>348</v>
+        <v>326</v>
       </c>
       <c r="E202" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="F202" t="s">
-        <v>327</v>
+        <v>165</v>
       </c>
       <c r="G202" t="s">
         <v>349</v>
@@ -6265,16 +6265,16 @@
         <v>8</v>
       </c>
       <c r="C203" t="s">
-        <v>163</v>
+        <v>341</v>
       </c>
       <c r="D203" t="s">
-        <v>341</v>
+        <v>326</v>
       </c>
       <c r="E203" t="s">
         <v>276</v>
       </c>
       <c r="F203" t="s">
-        <v>327</v>
+        <v>165</v>
       </c>
       <c r="G203" t="s">
         <v>349</v>
@@ -6288,16 +6288,16 @@
         <v>8</v>
       </c>
       <c r="C204" t="s">
-        <v>163</v>
+        <v>348</v>
       </c>
       <c r="D204" t="s">
-        <v>348</v>
+        <v>326</v>
       </c>
       <c r="E204" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="F204" t="s">
-        <v>327</v>
+        <v>165</v>
       </c>
       <c r="G204" t="s">
         <v>349</v>
@@ -6311,16 +6311,16 @@
         <v>8</v>
       </c>
       <c r="C205" t="s">
-        <v>163</v>
+        <v>356</v>
       </c>
       <c r="D205" t="s">
-        <v>356</v>
+        <v>326</v>
       </c>
       <c r="E205" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="F205" t="s">
-        <v>327</v>
+        <v>165</v>
       </c>
       <c r="G205" t="s">
         <v>357</v>
@@ -6334,16 +6334,16 @@
         <v>8</v>
       </c>
       <c r="C206" t="s">
-        <v>163</v>
+        <v>356</v>
       </c>
       <c r="D206" t="s">
-        <v>356</v>
+        <v>326</v>
       </c>
       <c r="E206" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="F206" t="s">
-        <v>327</v>
+        <v>165</v>
       </c>
       <c r="G206" t="s">
         <v>357</v>
@@ -6357,16 +6357,16 @@
         <v>8</v>
       </c>
       <c r="C207" t="s">
-        <v>163</v>
+        <v>356</v>
       </c>
       <c r="D207" t="s">
-        <v>356</v>
+        <v>326</v>
       </c>
       <c r="E207" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="F207" t="s">
-        <v>327</v>
+        <v>165</v>
       </c>
       <c r="G207" t="s">
         <v>357</v>
@@ -6380,16 +6380,16 @@
         <v>8</v>
       </c>
       <c r="C208" t="s">
-        <v>163</v>
+        <v>341</v>
       </c>
       <c r="D208" t="s">
-        <v>341</v>
+        <v>326</v>
       </c>
       <c r="E208" t="s">
         <v>276</v>
       </c>
       <c r="F208" t="s">
-        <v>327</v>
+        <v>165</v>
       </c>
       <c r="G208" t="s">
         <v>357</v>
@@ -6403,16 +6403,16 @@
         <v>8</v>
       </c>
       <c r="C209" t="s">
-        <v>163</v>
+        <v>356</v>
       </c>
       <c r="D209" t="s">
-        <v>356</v>
+        <v>326</v>
       </c>
       <c r="E209" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="F209" t="s">
-        <v>327</v>
+        <v>165</v>
       </c>
       <c r="G209" t="s">
         <v>357</v>
@@ -6426,16 +6426,16 @@
         <v>8</v>
       </c>
       <c r="C210" t="s">
-        <v>163</v>
+        <v>363</v>
       </c>
       <c r="D210" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="E210" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="F210" t="s">
-        <v>365</v>
+        <v>165</v>
       </c>
       <c r="G210" t="s">
         <v>366</v>
@@ -6449,16 +6449,16 @@
         <v>8</v>
       </c>
       <c r="C211" t="s">
-        <v>163</v>
+        <v>363</v>
       </c>
       <c r="D211" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="E211" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="F211" t="s">
-        <v>365</v>
+        <v>165</v>
       </c>
       <c r="G211" t="s">
         <v>366</v>
@@ -6472,16 +6472,16 @@
         <v>8</v>
       </c>
       <c r="C212" t="s">
-        <v>163</v>
+        <v>363</v>
       </c>
       <c r="D212" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="E212" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="F212" t="s">
-        <v>365</v>
+        <v>165</v>
       </c>
       <c r="G212" t="s">
         <v>366</v>
@@ -6495,16 +6495,16 @@
         <v>8</v>
       </c>
       <c r="C213" t="s">
-        <v>163</v>
+        <v>363</v>
       </c>
       <c r="D213" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="E213" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="F213" t="s">
-        <v>365</v>
+        <v>165</v>
       </c>
       <c r="G213" t="s">
         <v>366</v>
@@ -6518,16 +6518,16 @@
         <v>8</v>
       </c>
       <c r="C214" t="s">
-        <v>163</v>
+        <v>363</v>
       </c>
       <c r="D214" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="E214" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="F214" t="s">
-        <v>365</v>
+        <v>165</v>
       </c>
       <c r="G214" t="s">
         <v>366</v>
@@ -6541,16 +6541,16 @@
         <v>8</v>
       </c>
       <c r="C215" t="s">
-        <v>163</v>
+        <v>348</v>
       </c>
       <c r="D215" t="s">
-        <v>348</v>
+        <v>364</v>
       </c>
       <c r="E215" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="F215" t="s">
-        <v>365</v>
+        <v>165</v>
       </c>
       <c r="G215" t="s">
         <v>366</v>
@@ -6564,16 +6564,16 @@
         <v>8</v>
       </c>
       <c r="C216" t="s">
-        <v>163</v>
+        <v>363</v>
       </c>
       <c r="D216" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="E216" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="F216" t="s">
-        <v>365</v>
+        <v>165</v>
       </c>
       <c r="G216" t="s">
         <v>366</v>
@@ -6587,16 +6587,16 @@
         <v>8</v>
       </c>
       <c r="C217" t="s">
-        <v>163</v>
+        <v>363</v>
       </c>
       <c r="D217" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="E217" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="F217" t="s">
-        <v>365</v>
+        <v>165</v>
       </c>
       <c r="G217" t="s">
         <v>366</v>
@@ -6610,16 +6610,16 @@
         <v>8</v>
       </c>
       <c r="C218" t="s">
-        <v>163</v>
+        <v>363</v>
       </c>
       <c r="D218" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="E218" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="F218" t="s">
-        <v>365</v>
+        <v>165</v>
       </c>
       <c r="G218" t="s">
         <v>366</v>
@@ -6633,16 +6633,16 @@
         <v>8</v>
       </c>
       <c r="C219" t="s">
-        <v>163</v>
+        <v>363</v>
       </c>
       <c r="D219" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="E219" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="F219" t="s">
-        <v>365</v>
+        <v>165</v>
       </c>
       <c r="G219" t="s">
         <v>366</v>
@@ -6656,16 +6656,16 @@
         <v>8</v>
       </c>
       <c r="C220" t="s">
-        <v>163</v>
+        <v>309</v>
       </c>
       <c r="D220" t="s">
-        <v>309</v>
+        <v>364</v>
       </c>
       <c r="E220" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="F220" t="s">
-        <v>365</v>
+        <v>165</v>
       </c>
       <c r="G220" t="s">
         <v>366</v>
@@ -6679,16 +6679,16 @@
         <v>8</v>
       </c>
       <c r="C221" t="s">
-        <v>163</v>
+        <v>363</v>
       </c>
       <c r="D221" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="E221" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="F221" t="s">
-        <v>365</v>
+        <v>165</v>
       </c>
       <c r="G221" t="s">
         <v>366</v>
@@ -6702,16 +6702,16 @@
         <v>8</v>
       </c>
       <c r="C222" t="s">
-        <v>163</v>
+        <v>363</v>
       </c>
       <c r="D222" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="E222" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="F222" t="s">
-        <v>365</v>
+        <v>165</v>
       </c>
       <c r="G222" t="s">
         <v>366</v>
@@ -6725,16 +6725,16 @@
         <v>8</v>
       </c>
       <c r="C223" t="s">
-        <v>163</v>
+        <v>363</v>
       </c>
       <c r="D223" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="E223" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="F223" t="s">
-        <v>365</v>
+        <v>165</v>
       </c>
       <c r="G223" t="s">
         <v>366</v>
@@ -6748,16 +6748,16 @@
         <v>8</v>
       </c>
       <c r="C224" t="s">
-        <v>163</v>
+        <v>363</v>
       </c>
       <c r="D224" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="E224" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="F224" t="s">
-        <v>365</v>
+        <v>165</v>
       </c>
       <c r="G224" t="s">
         <v>366</v>
@@ -6771,16 +6771,16 @@
         <v>8</v>
       </c>
       <c r="C225" t="s">
-        <v>163</v>
+        <v>363</v>
       </c>
       <c r="D225" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="E225" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="F225" t="s">
-        <v>365</v>
+        <v>165</v>
       </c>
       <c r="G225" t="s">
         <v>366</v>
@@ -6794,16 +6794,16 @@
         <v>8</v>
       </c>
       <c r="C226" t="s">
-        <v>163</v>
+        <v>275</v>
       </c>
       <c r="D226" t="s">
-        <v>275</v>
+        <v>364</v>
       </c>
       <c r="E226" t="s">
         <v>276</v>
       </c>
       <c r="F226" t="s">
-        <v>365</v>
+        <v>165</v>
       </c>
       <c r="G226" t="s">
         <v>366</v>
@@ -6817,16 +6817,16 @@
         <v>8</v>
       </c>
       <c r="C227" t="s">
-        <v>163</v>
+        <v>363</v>
       </c>
       <c r="D227" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="E227" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="F227" t="s">
-        <v>365</v>
+        <v>165</v>
       </c>
       <c r="G227" t="s">
         <v>366</v>
@@ -6843,13 +6843,13 @@
         <v>163</v>
       </c>
       <c r="D228" t="s">
+        <v>364</v>
+      </c>
+      <c r="E228" t="s">
         <v>164</v>
       </c>
-      <c r="E228" t="s">
-        <v>165</v>
-      </c>
       <c r="F228" t="s">
-        <v>365</v>
+        <v>165</v>
       </c>
       <c r="G228" t="s">
         <v>366</v>
@@ -6863,16 +6863,16 @@
         <v>8</v>
       </c>
       <c r="C229" t="s">
-        <v>163</v>
+        <v>386</v>
       </c>
       <c r="D229" t="s">
-        <v>386</v>
+        <v>364</v>
       </c>
       <c r="E229" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="F229" t="s">
-        <v>365</v>
+        <v>165</v>
       </c>
       <c r="G229" t="s">
         <v>387</v>
@@ -6886,16 +6886,16 @@
         <v>8</v>
       </c>
       <c r="C230" t="s">
-        <v>163</v>
+        <v>386</v>
       </c>
       <c r="D230" t="s">
-        <v>386</v>
+        <v>364</v>
       </c>
       <c r="E230" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="F230" t="s">
-        <v>365</v>
+        <v>165</v>
       </c>
       <c r="G230" t="s">
         <v>387</v>
@@ -6909,16 +6909,16 @@
         <v>8</v>
       </c>
       <c r="C231" t="s">
-        <v>163</v>
+        <v>293</v>
       </c>
       <c r="D231" t="s">
-        <v>293</v>
+        <v>364</v>
       </c>
       <c r="E231" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="F231" t="s">
-        <v>365</v>
+        <v>165</v>
       </c>
       <c r="G231" t="s">
         <v>387</v>
@@ -6932,16 +6932,16 @@
         <v>8</v>
       </c>
       <c r="C232" t="s">
-        <v>163</v>
+        <v>309</v>
       </c>
       <c r="D232" t="s">
-        <v>309</v>
+        <v>364</v>
       </c>
       <c r="E232" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="F232" t="s">
-        <v>365</v>
+        <v>165</v>
       </c>
       <c r="G232" t="s">
         <v>387</v>
@@ -6955,16 +6955,16 @@
         <v>8</v>
       </c>
       <c r="C233" t="s">
-        <v>163</v>
+        <v>386</v>
       </c>
       <c r="D233" t="s">
-        <v>386</v>
+        <v>364</v>
       </c>
       <c r="E233" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="F233" t="s">
-        <v>365</v>
+        <v>165</v>
       </c>
       <c r="G233" t="s">
         <v>387</v>
@@ -6978,16 +6978,16 @@
         <v>8</v>
       </c>
       <c r="C234" t="s">
-        <v>163</v>
+        <v>386</v>
       </c>
       <c r="D234" t="s">
-        <v>386</v>
+        <v>364</v>
       </c>
       <c r="E234" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="F234" t="s">
-        <v>365</v>
+        <v>165</v>
       </c>
       <c r="G234" t="s">
         <v>387</v>
@@ -7001,16 +7001,16 @@
         <v>8</v>
       </c>
       <c r="C235" t="s">
-        <v>163</v>
+        <v>386</v>
       </c>
       <c r="D235" t="s">
-        <v>386</v>
+        <v>364</v>
       </c>
       <c r="E235" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="F235" t="s">
-        <v>365</v>
+        <v>165</v>
       </c>
       <c r="G235" t="s">
         <v>387</v>
@@ -7024,16 +7024,16 @@
         <v>8</v>
       </c>
       <c r="C236" t="s">
-        <v>163</v>
+        <v>386</v>
       </c>
       <c r="D236" t="s">
-        <v>386</v>
+        <v>364</v>
       </c>
       <c r="E236" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="F236" t="s">
-        <v>365</v>
+        <v>165</v>
       </c>
       <c r="G236" t="s">
         <v>387</v>
@@ -7047,16 +7047,16 @@
         <v>8</v>
       </c>
       <c r="C237" t="s">
-        <v>163</v>
+        <v>386</v>
       </c>
       <c r="D237" t="s">
-        <v>386</v>
+        <v>364</v>
       </c>
       <c r="E237" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="F237" t="s">
-        <v>365</v>
+        <v>165</v>
       </c>
       <c r="G237" t="s">
         <v>387</v>
@@ -7070,16 +7070,16 @@
         <v>8</v>
       </c>
       <c r="C238" t="s">
-        <v>163</v>
+        <v>386</v>
       </c>
       <c r="D238" t="s">
-        <v>386</v>
+        <v>364</v>
       </c>
       <c r="E238" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="F238" t="s">
-        <v>365</v>
+        <v>165</v>
       </c>
       <c r="G238" t="s">
         <v>387</v>
@@ -7093,16 +7093,16 @@
         <v>8</v>
       </c>
       <c r="C239" t="s">
-        <v>163</v>
+        <v>398</v>
       </c>
       <c r="D239" t="s">
-        <v>398</v>
+        <v>364</v>
       </c>
       <c r="E239" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="F239" t="s">
-        <v>365</v>
+        <v>165</v>
       </c>
       <c r="G239" t="s">
         <v>399</v>
@@ -7119,13 +7119,13 @@
         <v>163</v>
       </c>
       <c r="D240" t="s">
+        <v>401</v>
+      </c>
+      <c r="E240" t="s">
         <v>164</v>
       </c>
-      <c r="E240" t="s">
-        <v>165</v>
-      </c>
       <c r="F240" t="s">
-        <v>401</v>
+        <v>165</v>
       </c>
       <c r="G240" t="s">
         <v>402</v>
@@ -7142,13 +7142,13 @@
         <v>163</v>
       </c>
       <c r="D241" t="s">
+        <v>401</v>
+      </c>
+      <c r="E241" t="s">
         <v>164</v>
       </c>
-      <c r="E241" t="s">
-        <v>165</v>
-      </c>
       <c r="F241" t="s">
-        <v>401</v>
+        <v>165</v>
       </c>
       <c r="G241" t="s">
         <v>402</v>
@@ -7165,13 +7165,13 @@
         <v>163</v>
       </c>
       <c r="D242" t="s">
+        <v>401</v>
+      </c>
+      <c r="E242" t="s">
         <v>164</v>
       </c>
-      <c r="E242" t="s">
-        <v>165</v>
-      </c>
       <c r="F242" t="s">
-        <v>401</v>
+        <v>165</v>
       </c>
       <c r="G242" t="s">
         <v>402</v>
@@ -7188,13 +7188,13 @@
         <v>163</v>
       </c>
       <c r="D243" t="s">
+        <v>401</v>
+      </c>
+      <c r="E243" t="s">
         <v>164</v>
       </c>
-      <c r="E243" t="s">
-        <v>165</v>
-      </c>
       <c r="F243" t="s">
-        <v>401</v>
+        <v>165</v>
       </c>
       <c r="G243" t="s">
         <v>402</v>
@@ -7211,13 +7211,13 @@
         <v>163</v>
       </c>
       <c r="D244" t="s">
+        <v>401</v>
+      </c>
+      <c r="E244" t="s">
         <v>164</v>
       </c>
-      <c r="E244" t="s">
-        <v>165</v>
-      </c>
       <c r="F244" t="s">
-        <v>401</v>
+        <v>165</v>
       </c>
       <c r="G244" t="s">
         <v>402</v>
@@ -7234,13 +7234,13 @@
         <v>163</v>
       </c>
       <c r="D245" t="s">
+        <v>401</v>
+      </c>
+      <c r="E245" t="s">
         <v>164</v>
       </c>
-      <c r="E245" t="s">
-        <v>165</v>
-      </c>
       <c r="F245" t="s">
-        <v>401</v>
+        <v>165</v>
       </c>
       <c r="G245" t="s">
         <v>402</v>
@@ -7254,16 +7254,16 @@
         <v>8</v>
       </c>
       <c r="C246" t="s">
-        <v>163</v>
+        <v>409</v>
       </c>
       <c r="D246" t="s">
-        <v>409</v>
+        <v>401</v>
       </c>
       <c r="E246" t="s">
         <v>256</v>
       </c>
       <c r="F246" t="s">
-        <v>401</v>
+        <v>165</v>
       </c>
       <c r="G246" t="s">
         <v>410</v>
@@ -7280,13 +7280,13 @@
         <v>95</v>
       </c>
       <c r="D247" t="s">
+        <v>412</v>
+      </c>
+      <c r="E247" t="s">
         <v>96</v>
       </c>
-      <c r="E247" t="s">
+      <c r="F247" t="s">
         <v>97</v>
-      </c>
-      <c r="F247" t="s">
-        <v>412</v>
       </c>
     </row>
     <row r="248" spans="1:7">
@@ -7300,13 +7300,13 @@
         <v>95</v>
       </c>
       <c r="D248" t="s">
+        <v>412</v>
+      </c>
+      <c r="E248" t="s">
         <v>96</v>
       </c>
-      <c r="E248" t="s">
+      <c r="F248" t="s">
         <v>97</v>
-      </c>
-      <c r="F248" t="s">
-        <v>412</v>
       </c>
     </row>
     <row r="249" spans="1:7">
@@ -7317,16 +7317,16 @@
         <v>8</v>
       </c>
       <c r="C249" t="s">
-        <v>95</v>
+        <v>415</v>
       </c>
       <c r="D249" t="s">
-        <v>415</v>
+        <v>412</v>
       </c>
       <c r="E249" t="s">
         <v>416</v>
       </c>
       <c r="F249" t="s">
-        <v>412</v>
+        <v>97</v>
       </c>
     </row>
     <row r="250" spans="1:7">
@@ -7340,13 +7340,13 @@
         <v>95</v>
       </c>
       <c r="D250" t="s">
+        <v>412</v>
+      </c>
+      <c r="E250" t="s">
         <v>96</v>
       </c>
-      <c r="E250" t="s">
+      <c r="F250" t="s">
         <v>97</v>
-      </c>
-      <c r="F250" t="s">
-        <v>412</v>
       </c>
     </row>
     <row r="251" spans="1:7">
@@ -7360,13 +7360,13 @@
         <v>95</v>
       </c>
       <c r="D251" t="s">
+        <v>412</v>
+      </c>
+      <c r="E251" t="s">
         <v>96</v>
       </c>
-      <c r="E251" t="s">
+      <c r="F251" t="s">
         <v>97</v>
-      </c>
-      <c r="F251" t="s">
-        <v>412</v>
       </c>
     </row>
     <row r="252" spans="1:7">
@@ -7380,13 +7380,13 @@
         <v>95</v>
       </c>
       <c r="D252" t="s">
+        <v>412</v>
+      </c>
+      <c r="E252" t="s">
         <v>96</v>
       </c>
-      <c r="E252" t="s">
+      <c r="F252" t="s">
         <v>97</v>
-      </c>
-      <c r="F252" t="s">
-        <v>412</v>
       </c>
     </row>
     <row r="253" spans="1:7">
@@ -7397,16 +7397,16 @@
         <v>8</v>
       </c>
       <c r="C253" t="s">
-        <v>163</v>
+        <v>421</v>
       </c>
       <c r="D253" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="E253" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="F253" t="s">
-        <v>423</v>
+        <v>165</v>
       </c>
     </row>
     <row r="254" spans="1:7">
@@ -7417,16 +7417,16 @@
         <v>8</v>
       </c>
       <c r="C254" t="s">
-        <v>90</v>
+        <v>219</v>
       </c>
       <c r="D254" t="s">
-        <v>219</v>
+        <v>422</v>
       </c>
       <c r="E254" t="s">
         <v>220</v>
       </c>
       <c r="F254" t="s">
-        <v>423</v>
+        <v>93</v>
       </c>
     </row>
     <row r="255" spans="1:7">
@@ -7437,16 +7437,16 @@
         <v>8</v>
       </c>
       <c r="C255" t="s">
-        <v>90</v>
+        <v>426</v>
       </c>
       <c r="D255" t="s">
-        <v>426</v>
+        <v>422</v>
       </c>
       <c r="E255" t="s">
         <v>427</v>
       </c>
       <c r="F255" t="s">
-        <v>423</v>
+        <v>93</v>
       </c>
     </row>
     <row r="256" spans="1:7">
@@ -7457,16 +7457,16 @@
         <v>8</v>
       </c>
       <c r="C256" t="s">
-        <v>90</v>
+        <v>426</v>
       </c>
       <c r="D256" t="s">
-        <v>426</v>
+        <v>422</v>
       </c>
       <c r="E256" t="s">
         <v>427</v>
       </c>
       <c r="F256" t="s">
-        <v>423</v>
+        <v>93</v>
       </c>
     </row>
     <row r="257" spans="1:6">
@@ -7477,16 +7477,16 @@
         <v>8</v>
       </c>
       <c r="C257" t="s">
-        <v>90</v>
+        <v>426</v>
       </c>
       <c r="D257" t="s">
-        <v>426</v>
+        <v>422</v>
       </c>
       <c r="E257" t="s">
         <v>427</v>
       </c>
       <c r="F257" t="s">
-        <v>423</v>
+        <v>93</v>
       </c>
     </row>
     <row r="258" spans="1:6">
@@ -7497,16 +7497,16 @@
         <v>8</v>
       </c>
       <c r="C258" t="s">
-        <v>163</v>
+        <v>325</v>
       </c>
       <c r="D258" t="s">
-        <v>325</v>
+        <v>422</v>
       </c>
       <c r="E258" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="F258" t="s">
-        <v>423</v>
+        <v>165</v>
       </c>
     </row>
     <row r="259" spans="1:6">
@@ -7517,16 +7517,16 @@
         <v>8</v>
       </c>
       <c r="C259" t="s">
-        <v>90</v>
+        <v>426</v>
       </c>
       <c r="D259" t="s">
-        <v>426</v>
+        <v>422</v>
       </c>
       <c r="E259" t="s">
         <v>427</v>
       </c>
       <c r="F259" t="s">
-        <v>423</v>
+        <v>93</v>
       </c>
     </row>
     <row r="260" spans="1:6">
@@ -7540,13 +7540,13 @@
         <v>163</v>
       </c>
       <c r="D260" t="s">
+        <v>422</v>
+      </c>
+      <c r="E260" t="s">
         <v>164</v>
       </c>
-      <c r="E260" t="s">
-        <v>165</v>
-      </c>
       <c r="F260" t="s">
-        <v>423</v>
+        <v>165</v>
       </c>
     </row>
     <row r="261" spans="1:6">
@@ -7557,16 +7557,16 @@
         <v>8</v>
       </c>
       <c r="C261" t="s">
-        <v>195</v>
+        <v>434</v>
       </c>
       <c r="D261" t="s">
-        <v>434</v>
+        <v>422</v>
       </c>
       <c r="E261" t="s">
         <v>435</v>
       </c>
       <c r="F261" t="s">
-        <v>423</v>
+        <v>197</v>
       </c>
     </row>
     <row r="262" spans="1:6">
@@ -7580,13 +7580,13 @@
         <v>163</v>
       </c>
       <c r="D262" t="s">
+        <v>422</v>
+      </c>
+      <c r="E262" t="s">
         <v>164</v>
       </c>
-      <c r="E262" t="s">
-        <v>165</v>
-      </c>
       <c r="F262" t="s">
-        <v>423</v>
+        <v>165</v>
       </c>
     </row>
     <row r="263" spans="1:6">
@@ -7597,16 +7597,16 @@
         <v>8</v>
       </c>
       <c r="C263" t="s">
-        <v>182</v>
+        <v>438</v>
       </c>
       <c r="D263" t="s">
-        <v>438</v>
+        <v>422</v>
       </c>
       <c r="E263" t="s">
         <v>439</v>
       </c>
       <c r="F263" t="s">
-        <v>423</v>
+        <v>184</v>
       </c>
     </row>
     <row r="264" spans="1:6">
@@ -7620,13 +7620,13 @@
         <v>31</v>
       </c>
       <c r="D264" t="s">
+        <v>422</v>
+      </c>
+      <c r="E264" t="s">
         <v>32</v>
       </c>
-      <c r="E264" t="s">
+      <c r="F264" t="s">
         <v>33</v>
-      </c>
-      <c r="F264" t="s">
-        <v>423</v>
       </c>
     </row>
     <row r="265" spans="1:6">
@@ -7640,13 +7640,13 @@
         <v>9</v>
       </c>
       <c r="D265" t="s">
-        <v>10</v>
+        <v>422</v>
       </c>
       <c r="E265" t="s">
         <v>11</v>
       </c>
       <c r="F265" t="s">
-        <v>423</v>
+        <v>12</v>
       </c>
     </row>
     <row r="266" spans="1:6">
@@ -7657,16 +7657,16 @@
         <v>8</v>
       </c>
       <c r="C266" t="s">
-        <v>112</v>
+        <v>443</v>
       </c>
       <c r="D266" t="s">
-        <v>443</v>
+        <v>422</v>
       </c>
       <c r="E266" t="s">
         <v>444</v>
       </c>
       <c r="F266" t="s">
-        <v>423</v>
+        <v>115</v>
       </c>
     </row>
     <row r="267" spans="1:6">
@@ -7677,16 +7677,16 @@
         <v>8</v>
       </c>
       <c r="C267" t="s">
-        <v>112</v>
+        <v>118</v>
       </c>
       <c r="D267" t="s">
-        <v>118</v>
+        <v>446</v>
       </c>
       <c r="E267" t="s">
         <v>119</v>
       </c>
       <c r="F267" t="s">
-        <v>446</v>
+        <v>115</v>
       </c>
     </row>
     <row r="268" spans="1:6">
@@ -7697,16 +7697,16 @@
         <v>8</v>
       </c>
       <c r="C268" t="s">
-        <v>182</v>
+        <v>202</v>
       </c>
       <c r="D268" t="s">
-        <v>202</v>
+        <v>448</v>
       </c>
       <c r="E268" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="F268" t="s">
-        <v>448</v>
+        <v>184</v>
       </c>
     </row>
     <row r="269" spans="1:6">
@@ -7717,16 +7717,16 @@
         <v>8</v>
       </c>
       <c r="C269" t="s">
-        <v>112</v>
+        <v>118</v>
       </c>
       <c r="D269" t="s">
-        <v>118</v>
+        <v>450</v>
       </c>
       <c r="E269" t="s">
         <v>119</v>
       </c>
       <c r="F269" t="s">
-        <v>450</v>
+        <v>115</v>
       </c>
     </row>
     <row r="270" spans="1:6">
@@ -7737,16 +7737,16 @@
         <v>8</v>
       </c>
       <c r="C270" t="s">
-        <v>112</v>
+        <v>118</v>
       </c>
       <c r="D270" t="s">
-        <v>118</v>
+        <v>450</v>
       </c>
       <c r="E270" t="s">
         <v>119</v>
       </c>
       <c r="F270" t="s">
-        <v>450</v>
+        <v>115</v>
       </c>
     </row>
     <row r="271" spans="1:6">
@@ -7757,16 +7757,16 @@
         <v>8</v>
       </c>
       <c r="C271" t="s">
-        <v>112</v>
+        <v>453</v>
       </c>
       <c r="D271" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="E271" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="F271" t="s">
-        <v>455</v>
+        <v>115</v>
       </c>
     </row>
     <row r="272" spans="1:6">
@@ -7777,16 +7777,16 @@
         <v>8</v>
       </c>
       <c r="C272" t="s">
-        <v>112</v>
+        <v>453</v>
       </c>
       <c r="D272" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="E272" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="F272" t="s">
-        <v>455</v>
+        <v>115</v>
       </c>
     </row>
     <row r="273" spans="1:6">
@@ -7797,16 +7797,16 @@
         <v>8</v>
       </c>
       <c r="C273" t="s">
-        <v>112</v>
+        <v>453</v>
       </c>
       <c r="D273" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="E273" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="F273" t="s">
-        <v>455</v>
+        <v>115</v>
       </c>
     </row>
     <row r="274" spans="1:6">
@@ -7817,16 +7817,16 @@
         <v>8</v>
       </c>
       <c r="C274" t="s">
-        <v>112</v>
+        <v>453</v>
       </c>
       <c r="D274" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="E274" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="F274" t="s">
-        <v>455</v>
+        <v>115</v>
       </c>
     </row>
     <row r="275" spans="1:6">
@@ -7837,16 +7837,16 @@
         <v>8</v>
       </c>
       <c r="C275" t="s">
-        <v>112</v>
+        <v>453</v>
       </c>
       <c r="D275" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="E275" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="F275" t="s">
-        <v>455</v>
+        <v>115</v>
       </c>
     </row>
     <row r="276" spans="1:6">
@@ -7857,16 +7857,16 @@
         <v>8</v>
       </c>
       <c r="C276" t="s">
-        <v>112</v>
+        <v>453</v>
       </c>
       <c r="D276" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="E276" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="F276" t="s">
-        <v>455</v>
+        <v>115</v>
       </c>
     </row>
     <row r="277" spans="1:6">
@@ -7877,16 +7877,16 @@
         <v>8</v>
       </c>
       <c r="C277" t="s">
-        <v>112</v>
+        <v>453</v>
       </c>
       <c r="D277" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="E277" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="F277" t="s">
-        <v>455</v>
+        <v>115</v>
       </c>
     </row>
     <row r="278" spans="1:6">
@@ -7897,16 +7897,16 @@
         <v>8</v>
       </c>
       <c r="C278" t="s">
-        <v>182</v>
+        <v>202</v>
       </c>
       <c r="D278" t="s">
-        <v>202</v>
+        <v>463</v>
       </c>
       <c r="E278" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="F278" t="s">
-        <v>463</v>
+        <v>184</v>
       </c>
     </row>
     <row r="279" spans="1:6">
@@ -7917,16 +7917,16 @@
         <v>8</v>
       </c>
       <c r="C279" t="s">
-        <v>31</v>
+        <v>51</v>
       </c>
       <c r="D279" t="s">
-        <v>51</v>
+        <v>463</v>
       </c>
       <c r="E279" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F279" t="s">
-        <v>463</v>
+        <v>33</v>
       </c>
     </row>
     <row r="280" spans="1:6">
@@ -7940,13 +7940,13 @@
         <v>9</v>
       </c>
       <c r="D280" t="s">
-        <v>10</v>
+        <v>463</v>
       </c>
       <c r="E280" t="s">
         <v>11</v>
       </c>
       <c r="F280" t="s">
-        <v>463</v>
+        <v>12</v>
       </c>
     </row>
     <row r="281" spans="1:6">
@@ -7957,16 +7957,16 @@
         <v>8</v>
       </c>
       <c r="C281" t="s">
-        <v>112</v>
+        <v>170</v>
       </c>
       <c r="D281" t="s">
-        <v>170</v>
+        <v>463</v>
       </c>
       <c r="E281" t="s">
         <v>171</v>
       </c>
       <c r="F281" t="s">
-        <v>463</v>
+        <v>115</v>
       </c>
     </row>
     <row r="282" spans="1:6">
@@ -7980,13 +7980,13 @@
         <v>124</v>
       </c>
       <c r="D282" t="s">
+        <v>463</v>
+      </c>
+      <c r="E282" t="s">
         <v>125</v>
       </c>
-      <c r="E282" t="s">
+      <c r="F282" t="s">
         <v>126</v>
-      </c>
-      <c r="F282" t="s">
-        <v>463</v>
       </c>
     </row>
     <row r="283" spans="1:6">
@@ -7997,16 +7997,16 @@
         <v>8</v>
       </c>
       <c r="C283" t="s">
-        <v>163</v>
+        <v>398</v>
       </c>
       <c r="D283" t="s">
-        <v>398</v>
+        <v>469</v>
       </c>
       <c r="E283" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="F283" t="s">
-        <v>469</v>
+        <v>165</v>
       </c>
     </row>
     <row r="284" spans="1:6">
@@ -8020,13 +8020,13 @@
         <v>124</v>
       </c>
       <c r="D284" t="s">
+        <v>471</v>
+      </c>
+      <c r="E284" t="s">
         <v>125</v>
       </c>
-      <c r="E284" t="s">
+      <c r="F284" t="s">
         <v>126</v>
-      </c>
-      <c r="F284" t="s">
-        <v>471</v>
       </c>
     </row>
     <row r="285" spans="1:6">
@@ -8037,16 +8037,16 @@
         <v>8</v>
       </c>
       <c r="C285" t="s">
-        <v>112</v>
+        <v>170</v>
       </c>
       <c r="D285" t="s">
-        <v>170</v>
+        <v>473</v>
       </c>
       <c r="E285" t="s">
         <v>171</v>
       </c>
       <c r="F285" t="s">
-        <v>473</v>
+        <v>115</v>
       </c>
     </row>
     <row r="286" spans="1:6">
@@ -8057,16 +8057,16 @@
         <v>8</v>
       </c>
       <c r="C286" t="s">
-        <v>182</v>
+        <v>438</v>
       </c>
       <c r="D286" t="s">
-        <v>438</v>
+        <v>475</v>
       </c>
       <c r="E286" t="s">
         <v>439</v>
       </c>
       <c r="F286" t="s">
-        <v>475</v>
+        <v>184</v>
       </c>
     </row>
     <row r="287" spans="1:6">
@@ -8077,16 +8077,16 @@
         <v>8</v>
       </c>
       <c r="C287" t="s">
-        <v>182</v>
+        <v>438</v>
       </c>
       <c r="D287" t="s">
-        <v>438</v>
+        <v>475</v>
       </c>
       <c r="E287" t="s">
         <v>439</v>
       </c>
       <c r="F287" t="s">
-        <v>475</v>
+        <v>184</v>
       </c>
     </row>
     <row r="288" spans="1:6">
@@ -8097,16 +8097,16 @@
         <v>8</v>
       </c>
       <c r="C288" t="s">
-        <v>9</v>
+        <v>41</v>
       </c>
       <c r="D288" t="s">
-        <v>41</v>
+        <v>475</v>
       </c>
       <c r="E288" t="s">
         <v>42</v>
       </c>
       <c r="F288" t="s">
-        <v>475</v>
+        <v>12</v>
       </c>
     </row>
     <row r="289" spans="1:6">
@@ -8120,13 +8120,13 @@
         <v>31</v>
       </c>
       <c r="D289" t="s">
+        <v>475</v>
+      </c>
+      <c r="E289" t="s">
         <v>32</v>
       </c>
-      <c r="E289" t="s">
+      <c r="F289" t="s">
         <v>33</v>
-      </c>
-      <c r="F289" t="s">
-        <v>475</v>
       </c>
     </row>
     <row r="290" spans="1:6">
@@ -8140,13 +8140,13 @@
         <v>31</v>
       </c>
       <c r="D290" t="s">
+        <v>475</v>
+      </c>
+      <c r="E290" t="s">
         <v>32</v>
       </c>
-      <c r="E290" t="s">
+      <c r="F290" t="s">
         <v>33</v>
-      </c>
-      <c r="F290" t="s">
-        <v>475</v>
       </c>
     </row>
     <row r="291" spans="1:6">
@@ -8157,16 +8157,16 @@
         <v>8</v>
       </c>
       <c r="C291" t="s">
-        <v>112</v>
+        <v>170</v>
       </c>
       <c r="D291" t="s">
-        <v>170</v>
+        <v>475</v>
       </c>
       <c r="E291" t="s">
         <v>171</v>
       </c>
       <c r="F291" t="s">
-        <v>475</v>
+        <v>115</v>
       </c>
     </row>
     <row r="292" spans="1:6">
@@ -8177,16 +8177,16 @@
         <v>8</v>
       </c>
       <c r="C292" t="s">
-        <v>112</v>
+        <v>170</v>
       </c>
       <c r="D292" t="s">
-        <v>170</v>
+        <v>475</v>
       </c>
       <c r="E292" t="s">
         <v>171</v>
       </c>
       <c r="F292" t="s">
-        <v>475</v>
+        <v>115</v>
       </c>
     </row>
     <row r="293" spans="1:6">
@@ -8197,16 +8197,16 @@
         <v>8</v>
       </c>
       <c r="C293" t="s">
-        <v>112</v>
+        <v>170</v>
       </c>
       <c r="D293" t="s">
-        <v>170</v>
+        <v>475</v>
       </c>
       <c r="E293" t="s">
         <v>171</v>
       </c>
       <c r="F293" t="s">
-        <v>475</v>
+        <v>115</v>
       </c>
     </row>
     <row r="294" spans="1:6">
@@ -8217,16 +8217,16 @@
         <v>8</v>
       </c>
       <c r="C294" t="s">
-        <v>112</v>
+        <v>170</v>
       </c>
       <c r="D294" t="s">
-        <v>170</v>
+        <v>475</v>
       </c>
       <c r="E294" t="s">
         <v>171</v>
       </c>
       <c r="F294" t="s">
-        <v>475</v>
+        <v>115</v>
       </c>
     </row>
     <row r="295" spans="1:6">
@@ -8237,16 +8237,16 @@
         <v>8</v>
       </c>
       <c r="C295" t="s">
-        <v>112</v>
+        <v>170</v>
       </c>
       <c r="D295" t="s">
-        <v>170</v>
+        <v>485</v>
       </c>
       <c r="E295" t="s">
         <v>171</v>
       </c>
       <c r="F295" t="s">
-        <v>485</v>
+        <v>115</v>
       </c>
     </row>
     <row r="296" spans="1:6">
@@ -8257,16 +8257,16 @@
         <v>8</v>
       </c>
       <c r="C296" t="s">
-        <v>112</v>
+        <v>170</v>
       </c>
       <c r="D296" t="s">
-        <v>170</v>
+        <v>485</v>
       </c>
       <c r="E296" t="s">
         <v>171</v>
       </c>
       <c r="F296" t="s">
-        <v>485</v>
+        <v>115</v>
       </c>
     </row>
   </sheetData>

--- a/api/2/xlsx/fr/SectorCOFOG.xlsx
+++ b/api/2/xlsx/fr/SectorCOFOG.xlsx
@@ -22,72 +22,72 @@
     <t>status</t>
   </si>
   <si>
+    <t>codeforiati:cofog-group</t>
+  </si>
+  <si>
     <t>codeforiati:cofog-class</t>
   </si>
   <si>
+    <t>codeforiati:cofog-division</t>
+  </si>
+  <si>
+    <t>codeforiati:category-code</t>
+  </si>
+  <si>
     <t>codeforiati:group-code</t>
   </si>
   <si>
-    <t>codeforiati:cofog-group</t>
-  </si>
-  <si>
-    <t>codeforiati:cofog-division</t>
-  </si>
-  <si>
-    <t>codeforiati:category-code</t>
-  </si>
-  <si>
     <t>11110</t>
   </si>
   <si>
     <t>active</t>
   </si>
   <si>
+    <t>09.8 - Education n.e.c.</t>
+  </si>
+  <si>
     <t>09.8.0 - Education n.e.c. (CS)</t>
   </si>
   <si>
+    <t>09 - Education</t>
+  </si>
+  <si>
+    <t>111</t>
+  </si>
+  <si>
     <t>110</t>
   </si>
   <si>
-    <t>09.8 - Education n.e.c.</t>
-  </si>
-  <si>
-    <t>09 - Education</t>
-  </si>
-  <si>
-    <t>111</t>
-  </si>
-  <si>
     <t>11120</t>
   </si>
   <si>
+    <t>09.6 - Subsidiary services to education</t>
+  </si>
+  <si>
     <t>09.6.0 - Subsidiary services to education (IS)</t>
   </si>
   <si>
-    <t>09.6 - Subsidiary services to education</t>
-  </si>
-  <si>
     <t>11130</t>
   </si>
   <si>
     <t>11182</t>
   </si>
   <si>
+    <t>09.7 - R&amp;D Education</t>
+  </si>
+  <si>
     <t>09.7.0 - R&amp;D Education (CS)</t>
   </si>
   <si>
-    <t>09.7 - R&amp;D Education</t>
-  </si>
-  <si>
     <t>11220</t>
   </si>
   <si>
+    <t>09.1 - Pre‐primary and primary education</t>
+  </si>
+  <si>
     <t>09.1.2 - Primary education (IS)</t>
   </si>
   <si>
-    <t>09.1 - Pre‐primary and primary education</t>
-  </si>
-  <si>
     <t>112</t>
   </si>
   <si>
@@ -109,24 +109,24 @@
     <t>11250</t>
   </si>
   <si>
+    <t>07.4 - Public health services</t>
+  </si>
+  <si>
     <t>07.4.0 - Public health services (IS)</t>
   </si>
   <si>
-    <t>07.4 - Public health services</t>
-  </si>
-  <si>
     <t>07 - Health</t>
   </si>
   <si>
     <t>11260</t>
   </si>
   <si>
+    <t>09.2 - Secondary education</t>
+  </si>
+  <si>
     <t>09.2.1 - Lower‐secondary education (IS)</t>
   </si>
   <si>
-    <t>09.2 - Secondary education</t>
-  </si>
-  <si>
     <t>11320</t>
   </si>
   <si>
@@ -139,69 +139,69 @@
     <t>11330</t>
   </si>
   <si>
+    <t>09.5 - Education not definable by level</t>
+  </si>
+  <si>
     <t>09.5.0 - Education not definable by level (IS)</t>
   </si>
   <si>
-    <t>09.5 - Education not definable by level</t>
-  </si>
-  <si>
     <t>11420</t>
   </si>
   <si>
+    <t>09.4 - Tertiary education</t>
+  </si>
+  <si>
     <t>09.4.1 - First stage of tertiary education (IS)</t>
   </si>
   <si>
-    <t>09.4 - Tertiary education</t>
-  </si>
-  <si>
     <t>114</t>
   </si>
   <si>
     <t>11430</t>
   </si>
   <si>
+    <t>09.3 - Post‐secondary non‐tertiary education</t>
+  </si>
+  <si>
     <t>09.3.0 - Post‐secondary non‐tertiary education (IS)</t>
   </si>
   <si>
-    <t>09.3 - Post‐secondary non‐tertiary education</t>
-  </si>
-  <si>
     <t>12110</t>
   </si>
   <si>
+    <t>07.6 - Health n.e.c.</t>
+  </si>
+  <si>
     <t>07.6.0 - Health n.e.c. (CS)</t>
   </si>
   <si>
+    <t>121</t>
+  </si>
+  <si>
     <t>120</t>
   </si>
   <si>
-    <t>07.6 - Health n.e.c.</t>
-  </si>
-  <si>
-    <t>121</t>
-  </si>
-  <si>
     <t>12181</t>
   </si>
   <si>
     <t>12182</t>
   </si>
   <si>
+    <t>07.5 - R&amp;D Health</t>
+  </si>
+  <si>
     <t>07.5.0 - R&amp;D Health (CS)</t>
   </si>
   <si>
-    <t>07.5 - R&amp;D Health</t>
-  </si>
-  <si>
     <t>12191</t>
   </si>
   <si>
+    <t>07.2 - Outpatient services</t>
+  </si>
+  <si>
     <t>07.2.1 - General medical services (IS)</t>
   </si>
   <si>
-    <t>07.2 - Outpatient services</t>
-  </si>
-  <si>
     <t>12196</t>
   </si>
   <si>
@@ -214,12 +214,12 @@
     <t>12230</t>
   </si>
   <si>
+    <t>07.3 - Hospital services</t>
+  </si>
+  <si>
     <t>07.3.1 - General hospital services (IS)</t>
   </si>
   <si>
-    <t>07.3 - Hospital services</t>
-  </si>
-  <si>
     <t>12240</t>
   </si>
   <si>
@@ -286,27 +286,27 @@
     <t>14010</t>
   </si>
   <si>
+    <t>06.3 - Water supply</t>
+  </si>
+  <si>
     <t>06.3.0 - Water supply (CS)</t>
   </si>
   <si>
+    <t>06 - Housing and community amenities</t>
+  </si>
+  <si>
     <t>140</t>
   </si>
   <si>
-    <t>06.3 - Water supply</t>
-  </si>
-  <si>
-    <t>06 - Housing and community amenities</t>
-  </si>
-  <si>
     <t>14015</t>
   </si>
   <si>
+    <t>05.6 - Environmental protection n.e.c.</t>
+  </si>
+  <si>
     <t>05.6.0 - Environmental protection n.e.c. (CS)</t>
   </si>
   <si>
-    <t>05.6 - Environmental protection n.e.c.</t>
-  </si>
-  <si>
     <t>05 - Environmental protection</t>
   </si>
   <si>
@@ -319,12 +319,12 @@
     <t>14022</t>
   </si>
   <si>
+    <t>05.2 - Waste water management</t>
+  </si>
+  <si>
     <t>05.2.0 - Waste water management (CS)</t>
   </si>
   <si>
-    <t>05.2 - Waste water management</t>
-  </si>
-  <si>
     <t>14030</t>
   </si>
   <si>
@@ -340,60 +340,60 @@
     <t>14050</t>
   </si>
   <si>
+    <t>05.1 - Waste management</t>
+  </si>
+  <si>
     <t>05.1.0 - Waste management (CS)</t>
   </si>
   <si>
-    <t>05.1 - Waste management</t>
-  </si>
-  <si>
     <t>14081</t>
   </si>
   <si>
     <t>15110</t>
   </si>
   <si>
+    <t>01.3 - General services</t>
+  </si>
+  <si>
     <t>01.3.1 - General personnel services (CS)</t>
   </si>
   <si>
+    <t>01 - General public services</t>
+  </si>
+  <si>
+    <t>151</t>
+  </si>
+  <si>
     <t>150</t>
   </si>
   <si>
-    <t>01.3 - General services</t>
-  </si>
-  <si>
-    <t>01 - General public services</t>
-  </si>
-  <si>
-    <t>151</t>
-  </si>
-  <si>
     <t>15111</t>
   </si>
   <si>
+    <t>01.1 - Executive and legislative organs, financial and fiscal affairs, external affairs</t>
+  </si>
+  <si>
     <t>01.1.2 - Financial and fiscal affairs (CS)</t>
   </si>
   <si>
-    <t>01.1 - Executive and legislative organs, financial and fiscal affairs, external affairs</t>
-  </si>
-  <si>
     <t>15112</t>
   </si>
   <si>
+    <t>01.8 - Transfers of a general character between different levels of government</t>
+  </si>
+  <si>
     <t>01.8.0 - Transfers of a general character between different levels of government (CS)</t>
   </si>
   <si>
-    <t>01.8 - Transfers of a general character between different levels of government</t>
-  </si>
-  <si>
     <t>15113</t>
   </si>
   <si>
+    <t>03.6 - Public order and safety n.e.c.</t>
+  </si>
+  <si>
     <t>03.6.0 - Public order and safety n.e.c. (CS)</t>
   </si>
   <si>
-    <t>03.6 - Public order and safety n.e.c.</t>
-  </si>
-  <si>
     <t>03 - Public order and safety</t>
   </si>
   <si>
@@ -424,12 +424,12 @@
     <t>15123</t>
   </si>
   <si>
+    <t>01.2 - Foreign economic aid</t>
+  </si>
+  <si>
     <t>01.2.2 - Economic aid routed through international organizations (CS)</t>
   </si>
   <si>
-    <t>01.2 - Foreign economic aid</t>
-  </si>
-  <si>
     <t>15124</t>
   </si>
   <si>
@@ -460,30 +460,30 @@
     <t>15131</t>
   </si>
   <si>
+    <t>03.3 - Law courts</t>
+  </si>
+  <si>
     <t>03.3.0 - Law courts (CS)</t>
   </si>
   <si>
-    <t>03.3 - Law courts</t>
-  </si>
-  <si>
     <t>15132</t>
   </si>
   <si>
+    <t>03.1 - Police services</t>
+  </si>
+  <si>
     <t>03.1.0 - Police services (CS)</t>
   </si>
   <si>
-    <t>03.1 - Police services</t>
-  </si>
-  <si>
     <t>15133</t>
   </si>
   <si>
+    <t>03.2 - Fire‐protection services</t>
+  </si>
+  <si>
     <t>03.2.0 - Fire‐protection services (CS)</t>
   </si>
   <si>
-    <t>03.2 - Fire‐protection services</t>
-  </si>
-  <si>
     <t>15134</t>
   </si>
   <si>
@@ -496,21 +496,21 @@
     <t>15137</t>
   </si>
   <si>
+    <t>03.4 - Prisons</t>
+  </si>
+  <si>
     <t>03.4.0 - Prisons (CS)</t>
   </si>
   <si>
-    <t>03.4 - Prisons</t>
-  </si>
-  <si>
     <t>15142</t>
   </si>
   <si>
+    <t>04.1 - General economic, commercial and labour affairs</t>
+  </si>
+  <si>
     <t>04.1.1 - General economic and commercial affairs (CS)</t>
   </si>
   <si>
-    <t>04.1 - General economic, commercial and labour affairs</t>
-  </si>
-  <si>
     <t>04 - Economic affairs</t>
   </si>
   <si>
@@ -526,12 +526,12 @@
     <t>15151</t>
   </si>
   <si>
+    <t>01.6 - General public services n.e.c.</t>
+  </si>
+  <si>
     <t>01.6.0 - General public services n.e.c. (CS)</t>
   </si>
   <si>
-    <t>01.6 - General public services n.e.c.</t>
-  </si>
-  <si>
     <t>15152</t>
   </si>
   <si>
@@ -541,12 +541,12 @@
     <t>15153</t>
   </si>
   <si>
+    <t>04.6 - Communication</t>
+  </si>
+  <si>
     <t>04.6.0 - Communication (CS)</t>
   </si>
   <si>
-    <t>04.6 - Communication</t>
-  </si>
-  <si>
     <t>15154</t>
   </si>
   <si>
@@ -562,12 +562,12 @@
     <t>15170</t>
   </si>
   <si>
+    <t>10.7 - Social exclusion n.e.c.</t>
+  </si>
+  <si>
     <t>10.7.0 - Social exclusion n.e.c. (IS)</t>
   </si>
   <si>
-    <t>10.7 - Social exclusion n.e.c.</t>
-  </si>
-  <si>
     <t>10 - Social protection</t>
   </si>
   <si>
@@ -583,12 +583,12 @@
     <t>15196</t>
   </si>
   <si>
+    <t>01.5 - R&amp;D General public services</t>
+  </si>
+  <si>
     <t>01.5.0 - R&amp;D General public services (CS)</t>
   </si>
   <si>
-    <t>01.5 - R&amp;D General public services</t>
-  </si>
-  <si>
     <t>15210</t>
   </si>
   <si>
@@ -601,12 +601,12 @@
     <t>15230</t>
   </si>
   <si>
+    <t>02.3 - Foreign military aid</t>
+  </si>
+  <si>
     <t>02.3.0 - Foreign military aid (CS)</t>
   </si>
   <si>
-    <t>02.3 - Foreign military aid</t>
-  </si>
-  <si>
     <t>02 - Defence</t>
   </si>
   <si>
@@ -622,15 +622,15 @@
     <t>16010</t>
   </si>
   <si>
+    <t>10.9 - Social protection n.e.c.</t>
+  </si>
+  <si>
     <t>10.9.0 - Social protection n.e.c. (CS)</t>
   </si>
   <si>
     <t>160</t>
   </si>
   <si>
-    <t>10.9 - Social protection n.e.c.</t>
-  </si>
-  <si>
     <t>16011</t>
   </si>
   <si>
@@ -640,12 +640,12 @@
     <t>16013</t>
   </si>
   <si>
+    <t>10.2 - Old age</t>
+  </si>
+  <si>
     <t>10.2.0 - Old age (IS)</t>
   </si>
   <si>
-    <t>10.2 - Old age</t>
-  </si>
-  <si>
     <t>16014</t>
   </si>
   <si>
@@ -655,42 +655,42 @@
     <t>16020</t>
   </si>
   <si>
+    <t>10.5 - Unemployment</t>
+  </si>
+  <si>
     <t>10.5.0 - Unemployment (IS)</t>
   </si>
   <si>
-    <t>10.5 - Unemployment</t>
-  </si>
-  <si>
     <t>16030</t>
   </si>
   <si>
+    <t>06.6 - Housing and community amenities n.e.c.</t>
+  </si>
+  <si>
     <t>06.6.0 - Housing and community amenities n.e.c. (CS)</t>
   </si>
   <si>
-    <t>06.6 - Housing and community amenities n.e.c.</t>
-  </si>
-  <si>
     <t>16040</t>
   </si>
   <si>
+    <t>06.1 - Housing development</t>
+  </si>
+  <si>
     <t>06.1.0 - Housing development (CS)</t>
   </si>
   <si>
-    <t>06.1 - Housing development</t>
-  </si>
-  <si>
     <t>16050</t>
   </si>
   <si>
     <t>16061</t>
   </si>
   <si>
+    <t>08.2 - Cultural services</t>
+  </si>
+  <si>
     <t>08.2.0 - Cultural services (IS)</t>
   </si>
   <si>
-    <t>08.2 - Cultural services</t>
-  </si>
-  <si>
     <t>08 - Recreation, culture and religion</t>
   </si>
   <si>
@@ -706,12 +706,12 @@
     <t>16065</t>
   </si>
   <si>
+    <t>08.1 - Recreational and sporting services</t>
+  </si>
+  <si>
     <t>08.1.0 - Recreational and sporting services (IS)</t>
   </si>
   <si>
-    <t>08.1 - Recreational and sporting services</t>
-  </si>
-  <si>
     <t>16066</t>
   </si>
   <si>
@@ -742,12 +742,12 @@
     <t>21020</t>
   </si>
   <si>
+    <t>04.5 - Transport</t>
+  </si>
+  <si>
     <t>04.5.1 - Road transport (CS)</t>
   </si>
   <si>
-    <t>04.5 - Transport</t>
-  </si>
-  <si>
     <t>21021</t>
   </si>
   <si>
@@ -781,12 +781,12 @@
     <t>21061</t>
   </si>
   <si>
+    <t>04.7 - Other industries</t>
+  </si>
+  <si>
     <t>04.7.1 - Distributive trades, storage and warehousing (CS)</t>
   </si>
   <si>
-    <t>04.7 - Other industries</t>
-  </si>
-  <si>
     <t>21081</t>
   </si>
   <si>
@@ -811,42 +811,42 @@
     <t>22030</t>
   </si>
   <si>
+    <t>08.3 - Broadcasting and publishing services</t>
+  </si>
+  <si>
     <t>08.3.0 - Broadcasting and publishing services (CS)</t>
   </si>
   <si>
-    <t>08.3 - Broadcasting and publishing services</t>
-  </si>
-  <si>
     <t>22040</t>
   </si>
   <si>
     <t>23110</t>
   </si>
   <si>
+    <t>04.3 - Fuel and energy</t>
+  </si>
+  <si>
     <t>04.3.5 - Electricity (CS)</t>
   </si>
   <si>
+    <t>231</t>
+  </si>
+  <si>
     <t>230</t>
   </si>
   <si>
-    <t>04.3 - Fuel and energy</t>
-  </si>
-  <si>
-    <t>231</t>
-  </si>
-  <si>
     <t>23111</t>
   </si>
   <si>
     <t>23112</t>
   </si>
   <si>
+    <t>04.8 - R&amp;D Economic affairs</t>
+  </si>
+  <si>
     <t>04.8.3 - R&amp;D Fuel and energy (CS)</t>
   </si>
   <si>
-    <t>04.8 - R&amp;D Economic affairs</t>
-  </si>
-  <si>
     <t>23181</t>
   </si>
   <si>
@@ -991,18 +991,18 @@
     <t>31110</t>
   </si>
   <si>
+    <t>04.2 - Agriculture, forestry, fishing and hunting</t>
+  </si>
+  <si>
     <t>04.2.1 - Agriculture (CS)</t>
   </si>
   <si>
+    <t>311</t>
+  </si>
+  <si>
     <t>310</t>
   </si>
   <si>
-    <t>04.2 - Agriculture, forestry, fishing and hunting</t>
-  </si>
-  <si>
-    <t>311</t>
-  </si>
-  <si>
     <t>31120</t>
   </si>
   <si>
@@ -1105,18 +1105,18 @@
     <t>32110</t>
   </si>
   <si>
+    <t>04.4 - Mining, manufacturing and construction</t>
+  </si>
+  <si>
     <t>04.4.2 - Manufacturing (CS)</t>
   </si>
   <si>
+    <t>321</t>
+  </si>
+  <si>
     <t>320</t>
   </si>
   <si>
-    <t>04.4 - Mining, manufacturing and construction</t>
-  </si>
-  <si>
-    <t>321</t>
-  </si>
-  <si>
     <t>32120</t>
   </si>
   <si>
@@ -1219,12 +1219,12 @@
     <t>33110</t>
   </si>
   <si>
+    <t>331</t>
+  </si>
+  <si>
     <t>330</t>
   </si>
   <si>
-    <t>331</t>
-  </si>
-  <si>
     <t>33120</t>
   </si>
   <si>
@@ -1261,12 +1261,12 @@
     <t>41030</t>
   </si>
   <si>
+    <t>05.4 - Protection of biodiversity and landscape</t>
+  </si>
+  <si>
     <t>05.4.0 - Protection of biodiversity and landscape (CS)</t>
   </si>
   <si>
-    <t>05.4 - Protection of biodiversity and landscape</t>
-  </si>
-  <si>
     <t>41040</t>
   </si>
   <si>
@@ -1279,27 +1279,27 @@
     <t>43010</t>
   </si>
   <si>
+    <t>04.9 - Economic affairs n.e.c.</t>
+  </si>
+  <si>
     <t>04.9.0 - Economic affairs n.e.c. (CS)</t>
   </si>
   <si>
     <t>430</t>
   </si>
   <si>
-    <t>04.9 - Economic affairs n.e.c.</t>
-  </si>
-  <si>
     <t>43030</t>
   </si>
   <si>
     <t>43031</t>
   </si>
   <si>
+    <t>06.2 - Community development</t>
+  </si>
+  <si>
     <t>06.2.0 - Community development (CS)</t>
   </si>
   <si>
-    <t>06.2 - Community development</t>
-  </si>
-  <si>
     <t>43032</t>
   </si>
   <si>
@@ -1318,24 +1318,24 @@
     <t>43060</t>
   </si>
   <si>
+    <t>02.2 - Civil defence</t>
+  </si>
+  <si>
     <t>02.2.0 - Civil defence (CS)</t>
   </si>
   <si>
-    <t>02.2 - Civil defence</t>
-  </si>
-  <si>
     <t>43071</t>
   </si>
   <si>
     <t>43072</t>
   </si>
   <si>
+    <t>10.4 - Family and children</t>
+  </si>
+  <si>
     <t>10.4.0 - Family and children (IS)</t>
   </si>
   <si>
-    <t>10.4 - Family and children</t>
-  </si>
-  <si>
     <t>43073</t>
   </si>
   <si>
@@ -1345,12 +1345,12 @@
     <t>43082</t>
   </si>
   <si>
+    <t>01.4 - Basic research</t>
+  </si>
+  <si>
     <t>01.4.0 - Basic research (CS)</t>
   </si>
   <si>
-    <t>01.4 - Basic research</t>
-  </si>
-  <si>
     <t>51010</t>
   </si>
   <si>
@@ -1375,13 +1375,13 @@
     <t>60010</t>
   </si>
   <si>
+    <t>01.7 - Public debt transactions</t>
+  </si>
+  <si>
     <t>01.7.0 - Public debt transactions (CS)</t>
   </si>
   <si>
     <t>600</t>
-  </si>
-  <si>
-    <t>01.7 - Public debt transactions</t>
   </si>
   <si>
     <t>60020</t>
@@ -1866,10 +1866,10 @@
         <v>15</v>
       </c>
       <c r="D3" t="s">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="E3" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="F3" t="s">
         <v>12</v>
@@ -1912,10 +1912,10 @@
         <v>19</v>
       </c>
       <c r="D5" t="s">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="E5" t="s">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="F5" t="s">
         <v>12</v>
@@ -1935,16 +1935,16 @@
         <v>22</v>
       </c>
       <c r="D6" t="s">
-        <v>10</v>
+        <v>23</v>
       </c>
       <c r="E6" t="s">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="F6" t="s">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="G6" t="s">
-        <v>24</v>
+        <v>13</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -1964,10 +1964,10 @@
         <v>11</v>
       </c>
       <c r="F7" t="s">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="G7" t="s">
-        <v>24</v>
+        <v>13</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -1981,16 +1981,16 @@
         <v>22</v>
       </c>
       <c r="D8" t="s">
-        <v>10</v>
+        <v>23</v>
       </c>
       <c r="E8" t="s">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="F8" t="s">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="G8" t="s">
-        <v>24</v>
+        <v>13</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -2004,16 +2004,16 @@
         <v>22</v>
       </c>
       <c r="D9" t="s">
-        <v>10</v>
+        <v>23</v>
       </c>
       <c r="E9" t="s">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="F9" t="s">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="G9" t="s">
-        <v>24</v>
+        <v>13</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -2024,19 +2024,19 @@
         <v>8</v>
       </c>
       <c r="C10" t="s">
+        <v>22</v>
+      </c>
+      <c r="D10" t="s">
         <v>29</v>
       </c>
-      <c r="D10" t="s">
-        <v>10</v>
-      </c>
       <c r="E10" t="s">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="F10" t="s">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="G10" t="s">
-        <v>24</v>
+        <v>13</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -2050,16 +2050,16 @@
         <v>31</v>
       </c>
       <c r="D11" t="s">
-        <v>10</v>
+        <v>32</v>
       </c>
       <c r="E11" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F11" t="s">
-        <v>33</v>
+        <v>24</v>
       </c>
       <c r="G11" t="s">
-        <v>24</v>
+        <v>13</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -2073,16 +2073,16 @@
         <v>35</v>
       </c>
       <c r="D12" t="s">
-        <v>10</v>
+        <v>36</v>
       </c>
       <c r="E12" t="s">
-        <v>36</v>
+        <v>11</v>
       </c>
       <c r="F12" t="s">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="G12" t="s">
-        <v>24</v>
+        <v>13</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -2093,19 +2093,19 @@
         <v>8</v>
       </c>
       <c r="C13" t="s">
+        <v>35</v>
+      </c>
+      <c r="D13" t="s">
         <v>38</v>
       </c>
-      <c r="D13" t="s">
-        <v>10</v>
-      </c>
       <c r="E13" t="s">
-        <v>36</v>
+        <v>11</v>
       </c>
       <c r="F13" t="s">
-        <v>12</v>
+        <v>39</v>
       </c>
       <c r="G13" t="s">
-        <v>39</v>
+        <v>13</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -2119,16 +2119,16 @@
         <v>41</v>
       </c>
       <c r="D14" t="s">
-        <v>10</v>
+        <v>42</v>
       </c>
       <c r="E14" t="s">
-        <v>42</v>
+        <v>11</v>
       </c>
       <c r="F14" t="s">
-        <v>12</v>
+        <v>39</v>
       </c>
       <c r="G14" t="s">
-        <v>39</v>
+        <v>13</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -2142,16 +2142,16 @@
         <v>44</v>
       </c>
       <c r="D15" t="s">
-        <v>10</v>
+        <v>45</v>
       </c>
       <c r="E15" t="s">
-        <v>45</v>
+        <v>11</v>
       </c>
       <c r="F15" t="s">
-        <v>12</v>
+        <v>46</v>
       </c>
       <c r="G15" t="s">
-        <v>46</v>
+        <v>13</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -2165,16 +2165,16 @@
         <v>48</v>
       </c>
       <c r="D16" t="s">
-        <v>10</v>
+        <v>49</v>
       </c>
       <c r="E16" t="s">
-        <v>49</v>
+        <v>11</v>
       </c>
       <c r="F16" t="s">
-        <v>12</v>
+        <v>46</v>
       </c>
       <c r="G16" t="s">
-        <v>46</v>
+        <v>13</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -2191,10 +2191,10 @@
         <v>52</v>
       </c>
       <c r="E17" t="s">
+        <v>33</v>
+      </c>
+      <c r="F17" t="s">
         <v>53</v>
-      </c>
-      <c r="F17" t="s">
-        <v>33</v>
       </c>
       <c r="G17" t="s">
         <v>54</v>
@@ -2214,10 +2214,10 @@
         <v>52</v>
       </c>
       <c r="E18" t="s">
+        <v>33</v>
+      </c>
+      <c r="F18" t="s">
         <v>53</v>
-      </c>
-      <c r="F18" t="s">
-        <v>33</v>
       </c>
       <c r="G18" t="s">
         <v>54</v>
@@ -2234,13 +2234,13 @@
         <v>57</v>
       </c>
       <c r="D19" t="s">
-        <v>52</v>
+        <v>58</v>
       </c>
       <c r="E19" t="s">
-        <v>58</v>
+        <v>33</v>
       </c>
       <c r="F19" t="s">
-        <v>33</v>
+        <v>53</v>
       </c>
       <c r="G19" t="s">
         <v>54</v>
@@ -2257,13 +2257,13 @@
         <v>60</v>
       </c>
       <c r="D20" t="s">
-        <v>52</v>
+        <v>61</v>
       </c>
       <c r="E20" t="s">
-        <v>61</v>
+        <v>33</v>
       </c>
       <c r="F20" t="s">
-        <v>33</v>
+        <v>53</v>
       </c>
       <c r="G20" t="s">
         <v>54</v>
@@ -2283,10 +2283,10 @@
         <v>52</v>
       </c>
       <c r="E21" t="s">
+        <v>33</v>
+      </c>
+      <c r="F21" t="s">
         <v>53</v>
-      </c>
-      <c r="F21" t="s">
-        <v>33</v>
       </c>
       <c r="G21" t="s">
         <v>54</v>
@@ -2303,16 +2303,16 @@
         <v>31</v>
       </c>
       <c r="D22" t="s">
-        <v>52</v>
+        <v>32</v>
       </c>
       <c r="E22" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F22" t="s">
-        <v>33</v>
+        <v>64</v>
       </c>
       <c r="G22" t="s">
-        <v>64</v>
+        <v>54</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -2326,16 +2326,16 @@
         <v>66</v>
       </c>
       <c r="D23" t="s">
-        <v>52</v>
+        <v>67</v>
       </c>
       <c r="E23" t="s">
-        <v>67</v>
+        <v>33</v>
       </c>
       <c r="F23" t="s">
-        <v>33</v>
+        <v>64</v>
       </c>
       <c r="G23" t="s">
-        <v>64</v>
+        <v>54</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -2349,16 +2349,16 @@
         <v>31</v>
       </c>
       <c r="D24" t="s">
-        <v>52</v>
+        <v>32</v>
       </c>
       <c r="E24" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F24" t="s">
-        <v>33</v>
+        <v>64</v>
       </c>
       <c r="G24" t="s">
-        <v>64</v>
+        <v>54</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -2372,16 +2372,16 @@
         <v>31</v>
       </c>
       <c r="D25" t="s">
-        <v>52</v>
+        <v>32</v>
       </c>
       <c r="E25" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F25" t="s">
-        <v>33</v>
+        <v>64</v>
       </c>
       <c r="G25" t="s">
-        <v>64</v>
+        <v>54</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -2395,16 +2395,16 @@
         <v>31</v>
       </c>
       <c r="D26" t="s">
-        <v>52</v>
+        <v>32</v>
       </c>
       <c r="E26" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F26" t="s">
-        <v>33</v>
+        <v>64</v>
       </c>
       <c r="G26" t="s">
-        <v>64</v>
+        <v>54</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -2418,16 +2418,16 @@
         <v>31</v>
       </c>
       <c r="D27" t="s">
-        <v>52</v>
+        <v>32</v>
       </c>
       <c r="E27" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F27" t="s">
-        <v>33</v>
+        <v>64</v>
       </c>
       <c r="G27" t="s">
-        <v>64</v>
+        <v>54</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -2441,16 +2441,16 @@
         <v>31</v>
       </c>
       <c r="D28" t="s">
-        <v>52</v>
+        <v>32</v>
       </c>
       <c r="E28" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F28" t="s">
-        <v>33</v>
+        <v>64</v>
       </c>
       <c r="G28" t="s">
-        <v>64</v>
+        <v>54</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -2464,16 +2464,16 @@
         <v>31</v>
       </c>
       <c r="D29" t="s">
-        <v>52</v>
+        <v>32</v>
       </c>
       <c r="E29" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F29" t="s">
-        <v>33</v>
+        <v>64</v>
       </c>
       <c r="G29" t="s">
-        <v>64</v>
+        <v>54</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -2490,13 +2490,13 @@
         <v>52</v>
       </c>
       <c r="E30" t="s">
-        <v>53</v>
+        <v>33</v>
       </c>
       <c r="F30" t="s">
-        <v>33</v>
+        <v>64</v>
       </c>
       <c r="G30" t="s">
-        <v>64</v>
+        <v>54</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -2510,16 +2510,16 @@
         <v>31</v>
       </c>
       <c r="D31" t="s">
-        <v>52</v>
+        <v>32</v>
       </c>
       <c r="E31" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F31" t="s">
-        <v>33</v>
+        <v>76</v>
       </c>
       <c r="G31" t="s">
-        <v>76</v>
+        <v>54</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -2533,16 +2533,16 @@
         <v>31</v>
       </c>
       <c r="D32" t="s">
-        <v>52</v>
+        <v>32</v>
       </c>
       <c r="E32" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F32" t="s">
-        <v>33</v>
+        <v>76</v>
       </c>
       <c r="G32" t="s">
-        <v>76</v>
+        <v>54</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -2556,16 +2556,16 @@
         <v>31</v>
       </c>
       <c r="D33" t="s">
-        <v>52</v>
+        <v>32</v>
       </c>
       <c r="E33" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F33" t="s">
-        <v>33</v>
+        <v>76</v>
       </c>
       <c r="G33" t="s">
-        <v>76</v>
+        <v>54</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -2579,16 +2579,16 @@
         <v>31</v>
       </c>
       <c r="D34" t="s">
-        <v>52</v>
+        <v>32</v>
       </c>
       <c r="E34" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F34" t="s">
-        <v>33</v>
+        <v>76</v>
       </c>
       <c r="G34" t="s">
-        <v>76</v>
+        <v>54</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -2602,16 +2602,16 @@
         <v>31</v>
       </c>
       <c r="D35" t="s">
-        <v>52</v>
+        <v>32</v>
       </c>
       <c r="E35" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F35" t="s">
-        <v>33</v>
+        <v>76</v>
       </c>
       <c r="G35" t="s">
-        <v>76</v>
+        <v>54</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -2625,16 +2625,16 @@
         <v>57</v>
       </c>
       <c r="D36" t="s">
-        <v>52</v>
+        <v>58</v>
       </c>
       <c r="E36" t="s">
-        <v>58</v>
+        <v>33</v>
       </c>
       <c r="F36" t="s">
-        <v>33</v>
+        <v>76</v>
       </c>
       <c r="G36" t="s">
-        <v>76</v>
+        <v>54</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -2648,13 +2648,13 @@
         <v>31</v>
       </c>
       <c r="D37" t="s">
+        <v>32</v>
+      </c>
+      <c r="E37" t="s">
+        <v>33</v>
+      </c>
+      <c r="G37" t="s">
         <v>83</v>
-      </c>
-      <c r="E37" t="s">
-        <v>32</v>
-      </c>
-      <c r="F37" t="s">
-        <v>33</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -2668,13 +2668,13 @@
         <v>31</v>
       </c>
       <c r="D38" t="s">
+        <v>32</v>
+      </c>
+      <c r="E38" t="s">
+        <v>33</v>
+      </c>
+      <c r="G38" t="s">
         <v>83</v>
-      </c>
-      <c r="E38" t="s">
-        <v>32</v>
-      </c>
-      <c r="F38" t="s">
-        <v>33</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -2688,13 +2688,13 @@
         <v>31</v>
       </c>
       <c r="D39" t="s">
+        <v>32</v>
+      </c>
+      <c r="E39" t="s">
+        <v>33</v>
+      </c>
+      <c r="G39" t="s">
         <v>83</v>
-      </c>
-      <c r="E39" t="s">
-        <v>32</v>
-      </c>
-      <c r="F39" t="s">
-        <v>33</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -2708,13 +2708,13 @@
         <v>31</v>
       </c>
       <c r="D40" t="s">
+        <v>32</v>
+      </c>
+      <c r="E40" t="s">
+        <v>33</v>
+      </c>
+      <c r="G40" t="s">
         <v>83</v>
-      </c>
-      <c r="E40" t="s">
-        <v>32</v>
-      </c>
-      <c r="F40" t="s">
-        <v>33</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -2728,13 +2728,13 @@
         <v>51</v>
       </c>
       <c r="D41" t="s">
+        <v>52</v>
+      </c>
+      <c r="E41" t="s">
+        <v>33</v>
+      </c>
+      <c r="G41" t="s">
         <v>83</v>
-      </c>
-      <c r="E41" t="s">
-        <v>53</v>
-      </c>
-      <c r="F41" t="s">
-        <v>33</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -2748,13 +2748,13 @@
         <v>57</v>
       </c>
       <c r="D42" t="s">
+        <v>58</v>
+      </c>
+      <c r="E42" t="s">
+        <v>33</v>
+      </c>
+      <c r="G42" t="s">
         <v>83</v>
-      </c>
-      <c r="E42" t="s">
-        <v>58</v>
-      </c>
-      <c r="F42" t="s">
-        <v>33</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -2773,7 +2773,7 @@
       <c r="E43" t="s">
         <v>92</v>
       </c>
-      <c r="F43" t="s">
+      <c r="G43" t="s">
         <v>93</v>
       </c>
     </row>
@@ -2788,13 +2788,13 @@
         <v>95</v>
       </c>
       <c r="D44" t="s">
-        <v>91</v>
+        <v>96</v>
       </c>
       <c r="E44" t="s">
-        <v>96</v>
-      </c>
-      <c r="F44" t="s">
         <v>97</v>
+      </c>
+      <c r="G44" t="s">
+        <v>93</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -2813,7 +2813,7 @@
       <c r="E45" t="s">
         <v>92</v>
       </c>
-      <c r="F45" t="s">
+      <c r="G45" t="s">
         <v>93</v>
       </c>
     </row>
@@ -2833,7 +2833,7 @@
       <c r="E46" t="s">
         <v>92</v>
       </c>
-      <c r="F46" t="s">
+      <c r="G46" t="s">
         <v>93</v>
       </c>
     </row>
@@ -2848,13 +2848,13 @@
         <v>101</v>
       </c>
       <c r="D47" t="s">
-        <v>91</v>
+        <v>102</v>
       </c>
       <c r="E47" t="s">
-        <v>102</v>
-      </c>
-      <c r="F47" t="s">
         <v>97</v>
+      </c>
+      <c r="G47" t="s">
+        <v>93</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -2873,7 +2873,7 @@
       <c r="E48" t="s">
         <v>92</v>
       </c>
-      <c r="F48" t="s">
+      <c r="G48" t="s">
         <v>93</v>
       </c>
     </row>
@@ -2893,7 +2893,7 @@
       <c r="E49" t="s">
         <v>92</v>
       </c>
-      <c r="F49" t="s">
+      <c r="G49" t="s">
         <v>93</v>
       </c>
     </row>
@@ -2908,13 +2908,13 @@
         <v>101</v>
       </c>
       <c r="D50" t="s">
-        <v>91</v>
+        <v>102</v>
       </c>
       <c r="E50" t="s">
-        <v>102</v>
-      </c>
-      <c r="F50" t="s">
         <v>97</v>
+      </c>
+      <c r="G50" t="s">
+        <v>93</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -2933,7 +2933,7 @@
       <c r="E51" t="s">
         <v>92</v>
       </c>
-      <c r="F51" t="s">
+      <c r="G51" t="s">
         <v>93</v>
       </c>
     </row>
@@ -2948,13 +2948,13 @@
         <v>108</v>
       </c>
       <c r="D52" t="s">
-        <v>91</v>
+        <v>109</v>
       </c>
       <c r="E52" t="s">
-        <v>109</v>
-      </c>
-      <c r="F52" t="s">
         <v>97</v>
+      </c>
+      <c r="G52" t="s">
+        <v>93</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -2968,13 +2968,13 @@
         <v>9</v>
       </c>
       <c r="D53" t="s">
-        <v>91</v>
+        <v>10</v>
       </c>
       <c r="E53" t="s">
         <v>11</v>
       </c>
-      <c r="F53" t="s">
-        <v>12</v>
+      <c r="G53" t="s">
+        <v>93</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -3011,10 +3011,10 @@
         <v>118</v>
       </c>
       <c r="D55" t="s">
-        <v>113</v>
+        <v>119</v>
       </c>
       <c r="E55" t="s">
-        <v>119</v>
+        <v>114</v>
       </c>
       <c r="F55" t="s">
         <v>115</v>
@@ -3034,10 +3034,10 @@
         <v>121</v>
       </c>
       <c r="D56" t="s">
-        <v>113</v>
+        <v>122</v>
       </c>
       <c r="E56" t="s">
-        <v>122</v>
+        <v>114</v>
       </c>
       <c r="F56" t="s">
         <v>115</v>
@@ -3057,13 +3057,13 @@
         <v>124</v>
       </c>
       <c r="D57" t="s">
-        <v>113</v>
+        <v>125</v>
       </c>
       <c r="E57" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="F57" t="s">
-        <v>126</v>
+        <v>115</v>
       </c>
       <c r="G57" t="s">
         <v>116</v>
@@ -3080,10 +3080,10 @@
         <v>118</v>
       </c>
       <c r="D58" t="s">
-        <v>113</v>
+        <v>119</v>
       </c>
       <c r="E58" t="s">
-        <v>119</v>
+        <v>114</v>
       </c>
       <c r="F58" t="s">
         <v>115</v>
@@ -3103,10 +3103,10 @@
         <v>118</v>
       </c>
       <c r="D59" t="s">
-        <v>113</v>
+        <v>119</v>
       </c>
       <c r="E59" t="s">
-        <v>119</v>
+        <v>114</v>
       </c>
       <c r="F59" t="s">
         <v>115</v>
@@ -3126,10 +3126,10 @@
         <v>118</v>
       </c>
       <c r="D60" t="s">
-        <v>113</v>
+        <v>119</v>
       </c>
       <c r="E60" t="s">
-        <v>119</v>
+        <v>114</v>
       </c>
       <c r="F60" t="s">
         <v>115</v>
@@ -3149,10 +3149,10 @@
         <v>118</v>
       </c>
       <c r="D61" t="s">
-        <v>113</v>
+        <v>119</v>
       </c>
       <c r="E61" t="s">
-        <v>119</v>
+        <v>114</v>
       </c>
       <c r="F61" t="s">
         <v>115</v>
@@ -3172,10 +3172,10 @@
         <v>118</v>
       </c>
       <c r="D62" t="s">
-        <v>113</v>
+        <v>119</v>
       </c>
       <c r="E62" t="s">
-        <v>119</v>
+        <v>114</v>
       </c>
       <c r="F62" t="s">
         <v>115</v>
@@ -3192,13 +3192,13 @@
         <v>8</v>
       </c>
       <c r="C63" t="s">
+        <v>118</v>
+      </c>
+      <c r="D63" t="s">
         <v>133</v>
       </c>
-      <c r="D63" t="s">
-        <v>113</v>
-      </c>
       <c r="E63" t="s">
-        <v>119</v>
+        <v>114</v>
       </c>
       <c r="F63" t="s">
         <v>115</v>
@@ -3215,13 +3215,13 @@
         <v>8</v>
       </c>
       <c r="C64" t="s">
+        <v>118</v>
+      </c>
+      <c r="D64" t="s">
         <v>133</v>
       </c>
-      <c r="D64" t="s">
-        <v>113</v>
-      </c>
       <c r="E64" t="s">
-        <v>119</v>
+        <v>114</v>
       </c>
       <c r="F64" t="s">
         <v>115</v>
@@ -3241,10 +3241,10 @@
         <v>136</v>
       </c>
       <c r="D65" t="s">
-        <v>113</v>
+        <v>137</v>
       </c>
       <c r="E65" t="s">
-        <v>137</v>
+        <v>114</v>
       </c>
       <c r="F65" t="s">
         <v>115</v>
@@ -3287,10 +3287,10 @@
         <v>118</v>
       </c>
       <c r="D67" t="s">
-        <v>113</v>
+        <v>119</v>
       </c>
       <c r="E67" t="s">
-        <v>119</v>
+        <v>114</v>
       </c>
       <c r="F67" t="s">
         <v>115</v>
@@ -3307,10 +3307,10 @@
         <v>8</v>
       </c>
       <c r="C68" t="s">
+        <v>112</v>
+      </c>
+      <c r="D68" t="s">
         <v>141</v>
-      </c>
-      <c r="D68" t="s">
-        <v>113</v>
       </c>
       <c r="E68" t="s">
         <v>114</v>
@@ -3330,10 +3330,10 @@
         <v>8</v>
       </c>
       <c r="C69" t="s">
+        <v>112</v>
+      </c>
+      <c r="D69" t="s">
         <v>143</v>
-      </c>
-      <c r="D69" t="s">
-        <v>113</v>
       </c>
       <c r="E69" t="s">
         <v>114</v>
@@ -3356,10 +3356,10 @@
         <v>121</v>
       </c>
       <c r="D70" t="s">
-        <v>113</v>
+        <v>122</v>
       </c>
       <c r="E70" t="s">
-        <v>122</v>
+        <v>114</v>
       </c>
       <c r="F70" t="s">
         <v>115</v>
@@ -3379,10 +3379,10 @@
         <v>121</v>
       </c>
       <c r="D71" t="s">
-        <v>113</v>
+        <v>122</v>
       </c>
       <c r="E71" t="s">
-        <v>122</v>
+        <v>114</v>
       </c>
       <c r="F71" t="s">
         <v>115</v>
@@ -3425,13 +3425,13 @@
         <v>148</v>
       </c>
       <c r="D73" t="s">
-        <v>113</v>
+        <v>149</v>
       </c>
       <c r="E73" t="s">
-        <v>149</v>
+        <v>126</v>
       </c>
       <c r="F73" t="s">
-        <v>126</v>
+        <v>115</v>
       </c>
       <c r="G73" t="s">
         <v>116</v>
@@ -3448,13 +3448,13 @@
         <v>151</v>
       </c>
       <c r="D74" t="s">
-        <v>113</v>
+        <v>152</v>
       </c>
       <c r="E74" t="s">
-        <v>152</v>
+        <v>126</v>
       </c>
       <c r="F74" t="s">
-        <v>126</v>
+        <v>115</v>
       </c>
       <c r="G74" t="s">
         <v>116</v>
@@ -3471,13 +3471,13 @@
         <v>154</v>
       </c>
       <c r="D75" t="s">
-        <v>113</v>
+        <v>155</v>
       </c>
       <c r="E75" t="s">
-        <v>155</v>
+        <v>126</v>
       </c>
       <c r="F75" t="s">
-        <v>126</v>
+        <v>115</v>
       </c>
       <c r="G75" t="s">
         <v>116</v>
@@ -3494,13 +3494,13 @@
         <v>148</v>
       </c>
       <c r="D76" t="s">
-        <v>113</v>
+        <v>149</v>
       </c>
       <c r="E76" t="s">
-        <v>149</v>
+        <v>126</v>
       </c>
       <c r="F76" t="s">
-        <v>126</v>
+        <v>115</v>
       </c>
       <c r="G76" t="s">
         <v>116</v>
@@ -3517,13 +3517,13 @@
         <v>148</v>
       </c>
       <c r="D77" t="s">
-        <v>113</v>
+        <v>149</v>
       </c>
       <c r="E77" t="s">
-        <v>149</v>
+        <v>126</v>
       </c>
       <c r="F77" t="s">
-        <v>126</v>
+        <v>115</v>
       </c>
       <c r="G77" t="s">
         <v>116</v>
@@ -3540,13 +3540,13 @@
         <v>151</v>
       </c>
       <c r="D78" t="s">
-        <v>113</v>
+        <v>152</v>
       </c>
       <c r="E78" t="s">
-        <v>152</v>
+        <v>126</v>
       </c>
       <c r="F78" t="s">
-        <v>126</v>
+        <v>115</v>
       </c>
       <c r="G78" t="s">
         <v>116</v>
@@ -3563,13 +3563,13 @@
         <v>160</v>
       </c>
       <c r="D79" t="s">
-        <v>113</v>
+        <v>161</v>
       </c>
       <c r="E79" t="s">
-        <v>161</v>
+        <v>126</v>
       </c>
       <c r="F79" t="s">
-        <v>126</v>
+        <v>115</v>
       </c>
       <c r="G79" t="s">
         <v>116</v>
@@ -3586,13 +3586,13 @@
         <v>163</v>
       </c>
       <c r="D80" t="s">
-        <v>113</v>
+        <v>164</v>
       </c>
       <c r="E80" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="F80" t="s">
-        <v>165</v>
+        <v>115</v>
       </c>
       <c r="G80" t="s">
         <v>116</v>
@@ -3609,13 +3609,13 @@
         <v>163</v>
       </c>
       <c r="D81" t="s">
-        <v>113</v>
+        <v>164</v>
       </c>
       <c r="E81" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="F81" t="s">
-        <v>165</v>
+        <v>115</v>
       </c>
       <c r="G81" t="s">
         <v>116</v>
@@ -3632,13 +3632,13 @@
         <v>163</v>
       </c>
       <c r="D82" t="s">
-        <v>113</v>
+        <v>164</v>
       </c>
       <c r="E82" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="F82" t="s">
-        <v>165</v>
+        <v>115</v>
       </c>
       <c r="G82" t="s">
         <v>116</v>
@@ -3652,10 +3652,10 @@
         <v>8</v>
       </c>
       <c r="C83" t="s">
+        <v>112</v>
+      </c>
+      <c r="D83" t="s">
         <v>143</v>
-      </c>
-      <c r="D83" t="s">
-        <v>113</v>
       </c>
       <c r="E83" t="s">
         <v>114</v>
@@ -3678,10 +3678,10 @@
         <v>170</v>
       </c>
       <c r="D84" t="s">
-        <v>113</v>
+        <v>171</v>
       </c>
       <c r="E84" t="s">
-        <v>171</v>
+        <v>114</v>
       </c>
       <c r="F84" t="s">
         <v>115</v>
@@ -3698,13 +3698,13 @@
         <v>8</v>
       </c>
       <c r="C85" t="s">
+        <v>118</v>
+      </c>
+      <c r="D85" t="s">
         <v>173</v>
       </c>
-      <c r="D85" t="s">
-        <v>113</v>
-      </c>
       <c r="E85" t="s">
-        <v>119</v>
+        <v>114</v>
       </c>
       <c r="F85" t="s">
         <v>115</v>
@@ -3724,13 +3724,13 @@
         <v>175</v>
       </c>
       <c r="D86" t="s">
-        <v>113</v>
+        <v>176</v>
       </c>
       <c r="E86" t="s">
-        <v>176</v>
+        <v>165</v>
       </c>
       <c r="F86" t="s">
-        <v>165</v>
+        <v>115</v>
       </c>
       <c r="G86" t="s">
         <v>116</v>
@@ -3744,13 +3744,13 @@
         <v>8</v>
       </c>
       <c r="C87" t="s">
+        <v>118</v>
+      </c>
+      <c r="D87" t="s">
         <v>173</v>
       </c>
-      <c r="D87" t="s">
-        <v>113</v>
-      </c>
       <c r="E87" t="s">
-        <v>119</v>
+        <v>114</v>
       </c>
       <c r="F87" t="s">
         <v>115</v>
@@ -3770,10 +3770,10 @@
         <v>118</v>
       </c>
       <c r="D88" t="s">
-        <v>113</v>
+        <v>119</v>
       </c>
       <c r="E88" t="s">
-        <v>119</v>
+        <v>114</v>
       </c>
       <c r="F88" t="s">
         <v>115</v>
@@ -3793,10 +3793,10 @@
         <v>118</v>
       </c>
       <c r="D89" t="s">
-        <v>113</v>
+        <v>119</v>
       </c>
       <c r="E89" t="s">
-        <v>119</v>
+        <v>114</v>
       </c>
       <c r="F89" t="s">
         <v>115</v>
@@ -3816,13 +3816,13 @@
         <v>124</v>
       </c>
       <c r="D90" t="s">
-        <v>113</v>
+        <v>125</v>
       </c>
       <c r="E90" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="F90" t="s">
-        <v>126</v>
+        <v>115</v>
       </c>
       <c r="G90" t="s">
         <v>116</v>
@@ -3839,13 +3839,13 @@
         <v>182</v>
       </c>
       <c r="D91" t="s">
-        <v>113</v>
+        <v>183</v>
       </c>
       <c r="E91" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="F91" t="s">
-        <v>184</v>
+        <v>115</v>
       </c>
       <c r="G91" t="s">
         <v>116</v>
@@ -3862,13 +3862,13 @@
         <v>124</v>
       </c>
       <c r="D92" t="s">
-        <v>113</v>
+        <v>125</v>
       </c>
       <c r="E92" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="F92" t="s">
-        <v>126</v>
+        <v>115</v>
       </c>
       <c r="G92" t="s">
         <v>116</v>
@@ -3885,10 +3885,10 @@
         <v>121</v>
       </c>
       <c r="D93" t="s">
-        <v>113</v>
+        <v>122</v>
       </c>
       <c r="E93" t="s">
-        <v>122</v>
+        <v>114</v>
       </c>
       <c r="F93" t="s">
         <v>115</v>
@@ -3908,13 +3908,13 @@
         <v>124</v>
       </c>
       <c r="D94" t="s">
-        <v>113</v>
+        <v>125</v>
       </c>
       <c r="E94" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="F94" t="s">
-        <v>126</v>
+        <v>115</v>
       </c>
       <c r="G94" t="s">
         <v>116</v>
@@ -3931,10 +3931,10 @@
         <v>189</v>
       </c>
       <c r="D95" t="s">
-        <v>113</v>
+        <v>190</v>
       </c>
       <c r="E95" t="s">
-        <v>190</v>
+        <v>114</v>
       </c>
       <c r="F95" t="s">
         <v>115</v>
@@ -3954,16 +3954,16 @@
         <v>124</v>
       </c>
       <c r="D96" t="s">
-        <v>113</v>
+        <v>125</v>
       </c>
       <c r="E96" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="F96" t="s">
-        <v>126</v>
+        <v>192</v>
       </c>
       <c r="G96" t="s">
-        <v>192</v>
+        <v>116</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -3977,16 +3977,16 @@
         <v>124</v>
       </c>
       <c r="D97" t="s">
-        <v>113</v>
+        <v>125</v>
       </c>
       <c r="E97" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="F97" t="s">
-        <v>126</v>
+        <v>192</v>
       </c>
       <c r="G97" t="s">
-        <v>192</v>
+        <v>116</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -4000,16 +4000,16 @@
         <v>195</v>
       </c>
       <c r="D98" t="s">
-        <v>113</v>
+        <v>196</v>
       </c>
       <c r="E98" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="F98" t="s">
-        <v>197</v>
+        <v>192</v>
       </c>
       <c r="G98" t="s">
-        <v>192</v>
+        <v>116</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -4023,16 +4023,16 @@
         <v>124</v>
       </c>
       <c r="D99" t="s">
-        <v>113</v>
+        <v>125</v>
       </c>
       <c r="E99" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="F99" t="s">
-        <v>126</v>
+        <v>192</v>
       </c>
       <c r="G99" t="s">
-        <v>192</v>
+        <v>116</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -4046,16 +4046,16 @@
         <v>154</v>
       </c>
       <c r="D100" t="s">
-        <v>113</v>
+        <v>155</v>
       </c>
       <c r="E100" t="s">
-        <v>155</v>
+        <v>126</v>
       </c>
       <c r="F100" t="s">
-        <v>126</v>
+        <v>192</v>
       </c>
       <c r="G100" t="s">
-        <v>192</v>
+        <v>116</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -4069,16 +4069,16 @@
         <v>124</v>
       </c>
       <c r="D101" t="s">
-        <v>113</v>
+        <v>125</v>
       </c>
       <c r="E101" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="F101" t="s">
-        <v>126</v>
+        <v>192</v>
       </c>
       <c r="G101" t="s">
-        <v>192</v>
+        <v>116</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -4095,10 +4095,10 @@
         <v>203</v>
       </c>
       <c r="E102" t="s">
+        <v>184</v>
+      </c>
+      <c r="G102" t="s">
         <v>204</v>
-      </c>
-      <c r="F102" t="s">
-        <v>184</v>
       </c>
     </row>
     <row r="103" spans="1:7">
@@ -4115,10 +4115,10 @@
         <v>203</v>
       </c>
       <c r="E103" t="s">
+        <v>184</v>
+      </c>
+      <c r="G103" t="s">
         <v>204</v>
-      </c>
-      <c r="F103" t="s">
-        <v>184</v>
       </c>
     </row>
     <row r="104" spans="1:7">
@@ -4135,10 +4135,10 @@
         <v>203</v>
       </c>
       <c r="E104" t="s">
+        <v>184</v>
+      </c>
+      <c r="G104" t="s">
         <v>204</v>
-      </c>
-      <c r="F104" t="s">
-        <v>184</v>
       </c>
     </row>
     <row r="105" spans="1:7">
@@ -4152,13 +4152,13 @@
         <v>208</v>
       </c>
       <c r="D105" t="s">
-        <v>203</v>
+        <v>209</v>
       </c>
       <c r="E105" t="s">
-        <v>209</v>
-      </c>
-      <c r="F105" t="s">
         <v>184</v>
+      </c>
+      <c r="G105" t="s">
+        <v>204</v>
       </c>
     </row>
     <row r="106" spans="1:7">
@@ -4175,10 +4175,10 @@
         <v>203</v>
       </c>
       <c r="E106" t="s">
+        <v>184</v>
+      </c>
+      <c r="G106" t="s">
         <v>204</v>
-      </c>
-      <c r="F106" t="s">
-        <v>184</v>
       </c>
     </row>
     <row r="107" spans="1:7">
@@ -4192,13 +4192,13 @@
         <v>182</v>
       </c>
       <c r="D107" t="s">
-        <v>203</v>
+        <v>183</v>
       </c>
       <c r="E107" t="s">
-        <v>183</v>
-      </c>
-      <c r="F107" t="s">
         <v>184</v>
+      </c>
+      <c r="G107" t="s">
+        <v>204</v>
       </c>
     </row>
     <row r="108" spans="1:7">
@@ -4212,13 +4212,13 @@
         <v>213</v>
       </c>
       <c r="D108" t="s">
-        <v>203</v>
+        <v>214</v>
       </c>
       <c r="E108" t="s">
-        <v>214</v>
-      </c>
-      <c r="F108" t="s">
         <v>184</v>
+      </c>
+      <c r="G108" t="s">
+        <v>204</v>
       </c>
     </row>
     <row r="109" spans="1:7">
@@ -4232,13 +4232,13 @@
         <v>216</v>
       </c>
       <c r="D109" t="s">
-        <v>203</v>
+        <v>217</v>
       </c>
       <c r="E109" t="s">
-        <v>217</v>
-      </c>
-      <c r="F109" t="s">
-        <v>93</v>
+        <v>92</v>
+      </c>
+      <c r="G109" t="s">
+        <v>204</v>
       </c>
     </row>
     <row r="110" spans="1:7">
@@ -4252,13 +4252,13 @@
         <v>219</v>
       </c>
       <c r="D110" t="s">
-        <v>203</v>
+        <v>220</v>
       </c>
       <c r="E110" t="s">
-        <v>220</v>
-      </c>
-      <c r="F110" t="s">
-        <v>93</v>
+        <v>92</v>
+      </c>
+      <c r="G110" t="s">
+        <v>204</v>
       </c>
     </row>
     <row r="111" spans="1:7">
@@ -4275,10 +4275,10 @@
         <v>203</v>
       </c>
       <c r="E111" t="s">
+        <v>184</v>
+      </c>
+      <c r="G111" t="s">
         <v>204</v>
-      </c>
-      <c r="F111" t="s">
-        <v>184</v>
       </c>
     </row>
     <row r="112" spans="1:7">
@@ -4292,16 +4292,16 @@
         <v>223</v>
       </c>
       <c r="D112" t="s">
-        <v>203</v>
+        <v>224</v>
       </c>
       <c r="E112" t="s">
-        <v>224</v>
-      </c>
-      <c r="F112" t="s">
         <v>225</v>
       </c>
-    </row>
-    <row r="113" spans="1:6">
+      <c r="G112" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="113" spans="1:7">
       <c r="A113" t="s">
         <v>226</v>
       </c>
@@ -4309,19 +4309,19 @@
         <v>8</v>
       </c>
       <c r="C113" t="s">
+        <v>112</v>
+      </c>
+      <c r="D113" t="s">
         <v>143</v>
-      </c>
-      <c r="D113" t="s">
-        <v>203</v>
       </c>
       <c r="E113" t="s">
         <v>114</v>
       </c>
-      <c r="F113" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="114" spans="1:6">
+      <c r="G113" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="114" spans="1:7">
       <c r="A114" t="s">
         <v>227</v>
       </c>
@@ -4332,16 +4332,16 @@
         <v>151</v>
       </c>
       <c r="D114" t="s">
-        <v>203</v>
+        <v>152</v>
       </c>
       <c r="E114" t="s">
-        <v>152</v>
-      </c>
-      <c r="F114" t="s">
         <v>126</v>
       </c>
-    </row>
-    <row r="115" spans="1:6">
+      <c r="G114" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="115" spans="1:7">
       <c r="A115" t="s">
         <v>228</v>
       </c>
@@ -4352,16 +4352,16 @@
         <v>182</v>
       </c>
       <c r="D115" t="s">
-        <v>203</v>
+        <v>183</v>
       </c>
       <c r="E115" t="s">
-        <v>183</v>
-      </c>
-      <c r="F115" t="s">
         <v>184</v>
       </c>
-    </row>
-    <row r="116" spans="1:6">
+      <c r="G115" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="116" spans="1:7">
       <c r="A116" t="s">
         <v>229</v>
       </c>
@@ -4372,16 +4372,16 @@
         <v>230</v>
       </c>
       <c r="D116" t="s">
-        <v>203</v>
+        <v>231</v>
       </c>
       <c r="E116" t="s">
-        <v>231</v>
-      </c>
-      <c r="F116" t="s">
         <v>225</v>
       </c>
-    </row>
-    <row r="117" spans="1:6">
+      <c r="G116" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="117" spans="1:7">
       <c r="A117" t="s">
         <v>232</v>
       </c>
@@ -4392,16 +4392,16 @@
         <v>223</v>
       </c>
       <c r="D117" t="s">
-        <v>203</v>
+        <v>224</v>
       </c>
       <c r="E117" t="s">
-        <v>224</v>
-      </c>
-      <c r="F117" t="s">
         <v>225</v>
       </c>
-    </row>
-    <row r="118" spans="1:6">
+      <c r="G117" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="118" spans="1:7">
       <c r="A118" t="s">
         <v>233</v>
       </c>
@@ -4409,19 +4409,19 @@
         <v>8</v>
       </c>
       <c r="C118" t="s">
+        <v>163</v>
+      </c>
+      <c r="D118" t="s">
         <v>234</v>
       </c>
-      <c r="D118" t="s">
-        <v>203</v>
-      </c>
       <c r="E118" t="s">
-        <v>164</v>
-      </c>
-      <c r="F118" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="119" spans="1:6">
+        <v>165</v>
+      </c>
+      <c r="G118" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="119" spans="1:7">
       <c r="A119" t="s">
         <v>235</v>
       </c>
@@ -4432,16 +4432,16 @@
         <v>182</v>
       </c>
       <c r="D119" t="s">
-        <v>203</v>
+        <v>183</v>
       </c>
       <c r="E119" t="s">
-        <v>183</v>
-      </c>
-      <c r="F119" t="s">
         <v>184</v>
       </c>
-    </row>
-    <row r="120" spans="1:6">
+      <c r="G119" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="120" spans="1:7">
       <c r="A120" t="s">
         <v>236</v>
       </c>
@@ -4452,16 +4452,16 @@
         <v>170</v>
       </c>
       <c r="D120" t="s">
+        <v>171</v>
+      </c>
+      <c r="E120" t="s">
+        <v>114</v>
+      </c>
+      <c r="G120" t="s">
         <v>237</v>
       </c>
-      <c r="E120" t="s">
-        <v>171</v>
-      </c>
-      <c r="F120" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="121" spans="1:6">
+    </row>
+    <row r="121" spans="1:7">
       <c r="A121" t="s">
         <v>238</v>
       </c>
@@ -4469,19 +4469,19 @@
         <v>8</v>
       </c>
       <c r="C121" t="s">
+        <v>112</v>
+      </c>
+      <c r="D121" t="s">
         <v>143</v>
-      </c>
-      <c r="D121" t="s">
-        <v>237</v>
       </c>
       <c r="E121" t="s">
         <v>114</v>
       </c>
-      <c r="F121" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="122" spans="1:6">
+      <c r="G121" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="122" spans="1:7">
       <c r="A122" t="s">
         <v>239</v>
       </c>
@@ -4492,16 +4492,16 @@
         <v>170</v>
       </c>
       <c r="D122" t="s">
+        <v>171</v>
+      </c>
+      <c r="E122" t="s">
+        <v>114</v>
+      </c>
+      <c r="G122" t="s">
         <v>237</v>
       </c>
-      <c r="E122" t="s">
-        <v>171</v>
-      </c>
-      <c r="F122" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="123" spans="1:6">
+    </row>
+    <row r="123" spans="1:7">
       <c r="A123" t="s">
         <v>240</v>
       </c>
@@ -4512,16 +4512,16 @@
         <v>170</v>
       </c>
       <c r="D123" t="s">
+        <v>171</v>
+      </c>
+      <c r="E123" t="s">
+        <v>114</v>
+      </c>
+      <c r="G123" t="s">
         <v>237</v>
       </c>
-      <c r="E123" t="s">
-        <v>171</v>
-      </c>
-      <c r="F123" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="124" spans="1:6">
+    </row>
+    <row r="124" spans="1:7">
       <c r="A124" t="s">
         <v>241</v>
       </c>
@@ -4532,16 +4532,16 @@
         <v>242</v>
       </c>
       <c r="D124" t="s">
+        <v>243</v>
+      </c>
+      <c r="E124" t="s">
+        <v>165</v>
+      </c>
+      <c r="G124" t="s">
         <v>237</v>
       </c>
-      <c r="E124" t="s">
-        <v>243</v>
-      </c>
-      <c r="F124" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="125" spans="1:6">
+    </row>
+    <row r="125" spans="1:7">
       <c r="A125" t="s">
         <v>244</v>
       </c>
@@ -4552,16 +4552,16 @@
         <v>242</v>
       </c>
       <c r="D125" t="s">
+        <v>243</v>
+      </c>
+      <c r="E125" t="s">
+        <v>165</v>
+      </c>
+      <c r="G125" t="s">
         <v>237</v>
       </c>
-      <c r="E125" t="s">
-        <v>243</v>
-      </c>
-      <c r="F125" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="126" spans="1:6">
+    </row>
+    <row r="126" spans="1:7">
       <c r="A126" t="s">
         <v>245</v>
       </c>
@@ -4572,16 +4572,16 @@
         <v>242</v>
       </c>
       <c r="D126" t="s">
+        <v>243</v>
+      </c>
+      <c r="E126" t="s">
+        <v>165</v>
+      </c>
+      <c r="G126" t="s">
         <v>237</v>
       </c>
-      <c r="E126" t="s">
-        <v>243</v>
-      </c>
-      <c r="F126" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="127" spans="1:6">
+    </row>
+    <row r="127" spans="1:7">
       <c r="A127" t="s">
         <v>246</v>
       </c>
@@ -4592,16 +4592,16 @@
         <v>242</v>
       </c>
       <c r="D127" t="s">
+        <v>243</v>
+      </c>
+      <c r="E127" t="s">
+        <v>165</v>
+      </c>
+      <c r="G127" t="s">
         <v>237</v>
       </c>
-      <c r="E127" t="s">
-        <v>243</v>
-      </c>
-      <c r="F127" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="128" spans="1:6">
+    </row>
+    <row r="128" spans="1:7">
       <c r="A128" t="s">
         <v>247</v>
       </c>
@@ -4612,13 +4612,13 @@
         <v>242</v>
       </c>
       <c r="D128" t="s">
+        <v>243</v>
+      </c>
+      <c r="E128" t="s">
+        <v>165</v>
+      </c>
+      <c r="G128" t="s">
         <v>237</v>
-      </c>
-      <c r="E128" t="s">
-        <v>243</v>
-      </c>
-      <c r="F128" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="129" spans="1:7">
@@ -4629,16 +4629,16 @@
         <v>8</v>
       </c>
       <c r="C129" t="s">
+        <v>242</v>
+      </c>
+      <c r="D129" t="s">
         <v>249</v>
       </c>
-      <c r="D129" t="s">
+      <c r="E129" t="s">
+        <v>165</v>
+      </c>
+      <c r="G129" t="s">
         <v>237</v>
-      </c>
-      <c r="E129" t="s">
-        <v>243</v>
-      </c>
-      <c r="F129" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="130" spans="1:7">
@@ -4649,16 +4649,16 @@
         <v>8</v>
       </c>
       <c r="C130" t="s">
+        <v>242</v>
+      </c>
+      <c r="D130" t="s">
         <v>251</v>
       </c>
-      <c r="D130" t="s">
+      <c r="E130" t="s">
+        <v>165</v>
+      </c>
+      <c r="G130" t="s">
         <v>237</v>
-      </c>
-      <c r="E130" t="s">
-        <v>243</v>
-      </c>
-      <c r="F130" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="131" spans="1:7">
@@ -4669,16 +4669,16 @@
         <v>8</v>
       </c>
       <c r="C131" t="s">
+        <v>242</v>
+      </c>
+      <c r="D131" t="s">
         <v>253</v>
       </c>
-      <c r="D131" t="s">
+      <c r="E131" t="s">
+        <v>165</v>
+      </c>
+      <c r="G131" t="s">
         <v>237</v>
-      </c>
-      <c r="E131" t="s">
-        <v>243</v>
-      </c>
-      <c r="F131" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="132" spans="1:7">
@@ -4692,13 +4692,13 @@
         <v>255</v>
       </c>
       <c r="D132" t="s">
+        <v>256</v>
+      </c>
+      <c r="E132" t="s">
+        <v>165</v>
+      </c>
+      <c r="G132" t="s">
         <v>237</v>
-      </c>
-      <c r="E132" t="s">
-        <v>256</v>
-      </c>
-      <c r="F132" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="133" spans="1:7">
@@ -4712,13 +4712,13 @@
         <v>189</v>
       </c>
       <c r="D133" t="s">
+        <v>190</v>
+      </c>
+      <c r="E133" t="s">
+        <v>114</v>
+      </c>
+      <c r="G133" t="s">
         <v>237</v>
-      </c>
-      <c r="E133" t="s">
-        <v>190</v>
-      </c>
-      <c r="F133" t="s">
-        <v>115</v>
       </c>
     </row>
     <row r="134" spans="1:7">
@@ -4732,13 +4732,13 @@
         <v>175</v>
       </c>
       <c r="D134" t="s">
+        <v>176</v>
+      </c>
+      <c r="E134" t="s">
+        <v>165</v>
+      </c>
+      <c r="G134" t="s">
         <v>259</v>
-      </c>
-      <c r="E134" t="s">
-        <v>176</v>
-      </c>
-      <c r="F134" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="135" spans="1:7">
@@ -4752,13 +4752,13 @@
         <v>175</v>
       </c>
       <c r="D135" t="s">
+        <v>176</v>
+      </c>
+      <c r="E135" t="s">
+        <v>165</v>
+      </c>
+      <c r="G135" t="s">
         <v>259</v>
-      </c>
-      <c r="E135" t="s">
-        <v>176</v>
-      </c>
-      <c r="F135" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="136" spans="1:7">
@@ -4772,13 +4772,13 @@
         <v>175</v>
       </c>
       <c r="D136" t="s">
+        <v>176</v>
+      </c>
+      <c r="E136" t="s">
+        <v>165</v>
+      </c>
+      <c r="G136" t="s">
         <v>259</v>
-      </c>
-      <c r="E136" t="s">
-        <v>176</v>
-      </c>
-      <c r="F136" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="137" spans="1:7">
@@ -4792,13 +4792,13 @@
         <v>175</v>
       </c>
       <c r="D137" t="s">
+        <v>176</v>
+      </c>
+      <c r="E137" t="s">
+        <v>165</v>
+      </c>
+      <c r="G137" t="s">
         <v>259</v>
-      </c>
-      <c r="E137" t="s">
-        <v>176</v>
-      </c>
-      <c r="F137" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="138" spans="1:7">
@@ -4812,13 +4812,13 @@
         <v>175</v>
       </c>
       <c r="D138" t="s">
+        <v>176</v>
+      </c>
+      <c r="E138" t="s">
+        <v>165</v>
+      </c>
+      <c r="G138" t="s">
         <v>259</v>
-      </c>
-      <c r="E138" t="s">
-        <v>176</v>
-      </c>
-      <c r="F138" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="139" spans="1:7">
@@ -4832,13 +4832,13 @@
         <v>265</v>
       </c>
       <c r="D139" t="s">
+        <v>266</v>
+      </c>
+      <c r="E139" t="s">
+        <v>225</v>
+      </c>
+      <c r="G139" t="s">
         <v>259</v>
-      </c>
-      <c r="E139" t="s">
-        <v>266</v>
-      </c>
-      <c r="F139" t="s">
-        <v>225</v>
       </c>
     </row>
     <row r="140" spans="1:7">
@@ -4852,13 +4852,13 @@
         <v>175</v>
       </c>
       <c r="D140" t="s">
+        <v>176</v>
+      </c>
+      <c r="E140" t="s">
+        <v>165</v>
+      </c>
+      <c r="G140" t="s">
         <v>259</v>
-      </c>
-      <c r="E140" t="s">
-        <v>176</v>
-      </c>
-      <c r="F140" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="141" spans="1:7">
@@ -4875,10 +4875,10 @@
         <v>270</v>
       </c>
       <c r="E141" t="s">
+        <v>165</v>
+      </c>
+      <c r="F141" t="s">
         <v>271</v>
-      </c>
-      <c r="F141" t="s">
-        <v>165</v>
       </c>
       <c r="G141" t="s">
         <v>272</v>
@@ -4898,10 +4898,10 @@
         <v>270</v>
       </c>
       <c r="E142" t="s">
+        <v>165</v>
+      </c>
+      <c r="F142" t="s">
         <v>271</v>
-      </c>
-      <c r="F142" t="s">
-        <v>165</v>
       </c>
       <c r="G142" t="s">
         <v>272</v>
@@ -4918,13 +4918,13 @@
         <v>275</v>
       </c>
       <c r="D143" t="s">
-        <v>270</v>
+        <v>276</v>
       </c>
       <c r="E143" t="s">
-        <v>276</v>
+        <v>165</v>
       </c>
       <c r="F143" t="s">
-        <v>165</v>
+        <v>271</v>
       </c>
       <c r="G143" t="s">
         <v>272</v>
@@ -4941,13 +4941,13 @@
         <v>275</v>
       </c>
       <c r="D144" t="s">
-        <v>270</v>
+        <v>276</v>
       </c>
       <c r="E144" t="s">
-        <v>276</v>
+        <v>165</v>
       </c>
       <c r="F144" t="s">
-        <v>165</v>
+        <v>271</v>
       </c>
       <c r="G144" t="s">
         <v>272</v>
@@ -4964,13 +4964,13 @@
         <v>275</v>
       </c>
       <c r="D145" t="s">
-        <v>270</v>
+        <v>276</v>
       </c>
       <c r="E145" t="s">
-        <v>276</v>
+        <v>165</v>
       </c>
       <c r="F145" t="s">
-        <v>165</v>
+        <v>271</v>
       </c>
       <c r="G145" t="s">
         <v>272</v>
@@ -4990,10 +4990,10 @@
         <v>270</v>
       </c>
       <c r="E146" t="s">
+        <v>165</v>
+      </c>
+      <c r="F146" t="s">
         <v>271</v>
-      </c>
-      <c r="F146" t="s">
-        <v>165</v>
       </c>
       <c r="G146" t="s">
         <v>272</v>
@@ -5013,13 +5013,13 @@
         <v>270</v>
       </c>
       <c r="E147" t="s">
-        <v>271</v>
+        <v>165</v>
       </c>
       <c r="F147" t="s">
-        <v>165</v>
+        <v>281</v>
       </c>
       <c r="G147" t="s">
-        <v>281</v>
+        <v>272</v>
       </c>
     </row>
     <row r="148" spans="1:7">
@@ -5036,13 +5036,13 @@
         <v>270</v>
       </c>
       <c r="E148" t="s">
-        <v>271</v>
+        <v>165</v>
       </c>
       <c r="F148" t="s">
-        <v>165</v>
+        <v>281</v>
       </c>
       <c r="G148" t="s">
-        <v>281</v>
+        <v>272</v>
       </c>
     </row>
     <row r="149" spans="1:7">
@@ -5059,13 +5059,13 @@
         <v>270</v>
       </c>
       <c r="E149" t="s">
-        <v>271</v>
+        <v>165</v>
       </c>
       <c r="F149" t="s">
-        <v>165</v>
+        <v>281</v>
       </c>
       <c r="G149" t="s">
-        <v>281</v>
+        <v>272</v>
       </c>
     </row>
     <row r="150" spans="1:7">
@@ -5082,13 +5082,13 @@
         <v>270</v>
       </c>
       <c r="E150" t="s">
-        <v>271</v>
+        <v>165</v>
       </c>
       <c r="F150" t="s">
-        <v>165</v>
+        <v>281</v>
       </c>
       <c r="G150" t="s">
-        <v>281</v>
+        <v>272</v>
       </c>
     </row>
     <row r="151" spans="1:7">
@@ -5105,13 +5105,13 @@
         <v>270</v>
       </c>
       <c r="E151" t="s">
-        <v>271</v>
+        <v>165</v>
       </c>
       <c r="F151" t="s">
-        <v>165</v>
+        <v>281</v>
       </c>
       <c r="G151" t="s">
-        <v>281</v>
+        <v>272</v>
       </c>
     </row>
     <row r="152" spans="1:7">
@@ -5128,13 +5128,13 @@
         <v>270</v>
       </c>
       <c r="E152" t="s">
-        <v>271</v>
+        <v>165</v>
       </c>
       <c r="F152" t="s">
-        <v>165</v>
+        <v>281</v>
       </c>
       <c r="G152" t="s">
-        <v>281</v>
+        <v>272</v>
       </c>
     </row>
     <row r="153" spans="1:7">
@@ -5151,13 +5151,13 @@
         <v>270</v>
       </c>
       <c r="E153" t="s">
-        <v>271</v>
+        <v>165</v>
       </c>
       <c r="F153" t="s">
-        <v>165</v>
+        <v>281</v>
       </c>
       <c r="G153" t="s">
-        <v>281</v>
+        <v>272</v>
       </c>
     </row>
     <row r="154" spans="1:7">
@@ -5174,13 +5174,13 @@
         <v>270</v>
       </c>
       <c r="E154" t="s">
-        <v>271</v>
+        <v>165</v>
       </c>
       <c r="F154" t="s">
-        <v>165</v>
+        <v>281</v>
       </c>
       <c r="G154" t="s">
-        <v>281</v>
+        <v>272</v>
       </c>
     </row>
     <row r="155" spans="1:7">
@@ -5197,13 +5197,13 @@
         <v>270</v>
       </c>
       <c r="E155" t="s">
-        <v>271</v>
+        <v>165</v>
       </c>
       <c r="F155" t="s">
-        <v>165</v>
+        <v>281</v>
       </c>
       <c r="G155" t="s">
-        <v>281</v>
+        <v>272</v>
       </c>
     </row>
     <row r="156" spans="1:7">
@@ -5220,13 +5220,13 @@
         <v>270</v>
       </c>
       <c r="E156" t="s">
-        <v>271</v>
+        <v>165</v>
       </c>
       <c r="F156" t="s">
-        <v>165</v>
+        <v>291</v>
       </c>
       <c r="G156" t="s">
-        <v>291</v>
+        <v>272</v>
       </c>
     </row>
     <row r="157" spans="1:7">
@@ -5237,19 +5237,19 @@
         <v>8</v>
       </c>
       <c r="C157" t="s">
+        <v>269</v>
+      </c>
+      <c r="D157" t="s">
         <v>293</v>
       </c>
-      <c r="D157" t="s">
-        <v>270</v>
-      </c>
       <c r="E157" t="s">
-        <v>271</v>
+        <v>165</v>
       </c>
       <c r="F157" t="s">
-        <v>165</v>
+        <v>291</v>
       </c>
       <c r="G157" t="s">
-        <v>291</v>
+        <v>272</v>
       </c>
     </row>
     <row r="158" spans="1:7">
@@ -5266,13 +5266,13 @@
         <v>270</v>
       </c>
       <c r="E158" t="s">
-        <v>271</v>
+        <v>165</v>
       </c>
       <c r="F158" t="s">
-        <v>165</v>
+        <v>291</v>
       </c>
       <c r="G158" t="s">
-        <v>291</v>
+        <v>272</v>
       </c>
     </row>
     <row r="159" spans="1:7">
@@ -5289,13 +5289,13 @@
         <v>270</v>
       </c>
       <c r="E159" t="s">
-        <v>271</v>
+        <v>165</v>
       </c>
       <c r="F159" t="s">
-        <v>165</v>
+        <v>291</v>
       </c>
       <c r="G159" t="s">
-        <v>291</v>
+        <v>272</v>
       </c>
     </row>
     <row r="160" spans="1:7">
@@ -5312,13 +5312,13 @@
         <v>270</v>
       </c>
       <c r="E160" t="s">
-        <v>271</v>
+        <v>165</v>
       </c>
       <c r="F160" t="s">
-        <v>165</v>
+        <v>291</v>
       </c>
       <c r="G160" t="s">
-        <v>291</v>
+        <v>272</v>
       </c>
     </row>
     <row r="161" spans="1:7">
@@ -5335,13 +5335,13 @@
         <v>270</v>
       </c>
       <c r="E161" t="s">
-        <v>271</v>
+        <v>165</v>
       </c>
       <c r="F161" t="s">
-        <v>165</v>
+        <v>291</v>
       </c>
       <c r="G161" t="s">
-        <v>291</v>
+        <v>272</v>
       </c>
     </row>
     <row r="162" spans="1:7">
@@ -5358,13 +5358,13 @@
         <v>270</v>
       </c>
       <c r="E162" t="s">
-        <v>271</v>
+        <v>165</v>
       </c>
       <c r="F162" t="s">
-        <v>165</v>
+        <v>299</v>
       </c>
       <c r="G162" t="s">
-        <v>299</v>
+        <v>272</v>
       </c>
     </row>
     <row r="163" spans="1:7">
@@ -5375,19 +5375,19 @@
         <v>8</v>
       </c>
       <c r="C163" t="s">
+        <v>269</v>
+      </c>
+      <c r="D163" t="s">
         <v>301</v>
       </c>
-      <c r="D163" t="s">
-        <v>270</v>
-      </c>
       <c r="E163" t="s">
-        <v>271</v>
+        <v>165</v>
       </c>
       <c r="F163" t="s">
-        <v>165</v>
+        <v>302</v>
       </c>
       <c r="G163" t="s">
-        <v>302</v>
+        <v>272</v>
       </c>
     </row>
     <row r="164" spans="1:7">
@@ -5404,13 +5404,13 @@
         <v>270</v>
       </c>
       <c r="E164" t="s">
-        <v>271</v>
+        <v>165</v>
       </c>
       <c r="F164" t="s">
-        <v>165</v>
+        <v>304</v>
       </c>
       <c r="G164" t="s">
-        <v>304</v>
+        <v>272</v>
       </c>
     </row>
     <row r="165" spans="1:7">
@@ -5427,13 +5427,13 @@
         <v>270</v>
       </c>
       <c r="E165" t="s">
-        <v>271</v>
+        <v>165</v>
       </c>
       <c r="F165" t="s">
-        <v>165</v>
+        <v>304</v>
       </c>
       <c r="G165" t="s">
-        <v>304</v>
+        <v>272</v>
       </c>
     </row>
     <row r="166" spans="1:7">
@@ -5450,13 +5450,13 @@
         <v>270</v>
       </c>
       <c r="E166" t="s">
-        <v>271</v>
+        <v>165</v>
       </c>
       <c r="F166" t="s">
-        <v>165</v>
+        <v>304</v>
       </c>
       <c r="G166" t="s">
-        <v>304</v>
+        <v>272</v>
       </c>
     </row>
     <row r="167" spans="1:7">
@@ -5473,13 +5473,13 @@
         <v>270</v>
       </c>
       <c r="E167" t="s">
-        <v>271</v>
+        <v>165</v>
       </c>
       <c r="F167" t="s">
-        <v>165</v>
+        <v>304</v>
       </c>
       <c r="G167" t="s">
-        <v>304</v>
+        <v>272</v>
       </c>
     </row>
     <row r="168" spans="1:7">
@@ -5490,19 +5490,19 @@
         <v>8</v>
       </c>
       <c r="C168" t="s">
+        <v>269</v>
+      </c>
+      <c r="D168" t="s">
         <v>309</v>
       </c>
-      <c r="D168" t="s">
-        <v>270</v>
-      </c>
       <c r="E168" t="s">
-        <v>271</v>
+        <v>165</v>
       </c>
       <c r="F168" t="s">
-        <v>165</v>
+        <v>304</v>
       </c>
       <c r="G168" t="s">
-        <v>304</v>
+        <v>272</v>
       </c>
     </row>
     <row r="169" spans="1:7">
@@ -5513,19 +5513,19 @@
         <v>8</v>
       </c>
       <c r="C169" t="s">
+        <v>269</v>
+      </c>
+      <c r="D169" t="s">
         <v>309</v>
       </c>
-      <c r="D169" t="s">
-        <v>270</v>
-      </c>
       <c r="E169" t="s">
-        <v>271</v>
+        <v>165</v>
       </c>
       <c r="F169" t="s">
-        <v>165</v>
+        <v>304</v>
       </c>
       <c r="G169" t="s">
-        <v>304</v>
+        <v>272</v>
       </c>
     </row>
     <row r="170" spans="1:7">
@@ -5542,13 +5542,13 @@
         <v>270</v>
       </c>
       <c r="E170" t="s">
-        <v>271</v>
+        <v>165</v>
       </c>
       <c r="F170" t="s">
-        <v>165</v>
+        <v>304</v>
       </c>
       <c r="G170" t="s">
-        <v>304</v>
+        <v>272</v>
       </c>
     </row>
     <row r="171" spans="1:7">
@@ -5562,13 +5562,13 @@
         <v>163</v>
       </c>
       <c r="D171" t="s">
+        <v>164</v>
+      </c>
+      <c r="E171" t="s">
+        <v>165</v>
+      </c>
+      <c r="G171" t="s">
         <v>313</v>
-      </c>
-      <c r="E171" t="s">
-        <v>164</v>
-      </c>
-      <c r="F171" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="172" spans="1:7">
@@ -5582,13 +5582,13 @@
         <v>118</v>
       </c>
       <c r="D172" t="s">
+        <v>119</v>
+      </c>
+      <c r="E172" t="s">
+        <v>114</v>
+      </c>
+      <c r="G172" t="s">
         <v>313</v>
-      </c>
-      <c r="E172" t="s">
-        <v>119</v>
-      </c>
-      <c r="F172" t="s">
-        <v>115</v>
       </c>
     </row>
     <row r="173" spans="1:7">
@@ -5602,13 +5602,13 @@
         <v>163</v>
       </c>
       <c r="D173" t="s">
+        <v>164</v>
+      </c>
+      <c r="E173" t="s">
+        <v>165</v>
+      </c>
+      <c r="G173" t="s">
         <v>313</v>
-      </c>
-      <c r="E173" t="s">
-        <v>164</v>
-      </c>
-      <c r="F173" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="174" spans="1:7">
@@ -5622,13 +5622,13 @@
         <v>163</v>
       </c>
       <c r="D174" t="s">
+        <v>164</v>
+      </c>
+      <c r="E174" t="s">
+        <v>165</v>
+      </c>
+      <c r="G174" t="s">
         <v>313</v>
-      </c>
-      <c r="E174" t="s">
-        <v>164</v>
-      </c>
-      <c r="F174" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="175" spans="1:7">
@@ -5642,13 +5642,13 @@
         <v>163</v>
       </c>
       <c r="D175" t="s">
+        <v>164</v>
+      </c>
+      <c r="E175" t="s">
+        <v>165</v>
+      </c>
+      <c r="G175" t="s">
         <v>313</v>
-      </c>
-      <c r="E175" t="s">
-        <v>164</v>
-      </c>
-      <c r="F175" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="176" spans="1:7">
@@ -5662,13 +5662,13 @@
         <v>163</v>
       </c>
       <c r="D176" t="s">
+        <v>164</v>
+      </c>
+      <c r="E176" t="s">
+        <v>165</v>
+      </c>
+      <c r="G176" t="s">
         <v>313</v>
-      </c>
-      <c r="E176" t="s">
-        <v>164</v>
-      </c>
-      <c r="F176" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="177" spans="1:7">
@@ -5682,13 +5682,13 @@
         <v>163</v>
       </c>
       <c r="D177" t="s">
+        <v>164</v>
+      </c>
+      <c r="E177" t="s">
+        <v>165</v>
+      </c>
+      <c r="G177" t="s">
         <v>320</v>
-      </c>
-      <c r="E177" t="s">
-        <v>164</v>
-      </c>
-      <c r="F177" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="178" spans="1:7">
@@ -5702,13 +5702,13 @@
         <v>163</v>
       </c>
       <c r="D178" t="s">
+        <v>164</v>
+      </c>
+      <c r="E178" t="s">
+        <v>165</v>
+      </c>
+      <c r="G178" t="s">
         <v>320</v>
-      </c>
-      <c r="E178" t="s">
-        <v>164</v>
-      </c>
-      <c r="F178" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="179" spans="1:7">
@@ -5722,13 +5722,13 @@
         <v>163</v>
       </c>
       <c r="D179" t="s">
+        <v>164</v>
+      </c>
+      <c r="E179" t="s">
+        <v>165</v>
+      </c>
+      <c r="G179" t="s">
         <v>320</v>
-      </c>
-      <c r="E179" t="s">
-        <v>164</v>
-      </c>
-      <c r="F179" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="180" spans="1:7">
@@ -5742,13 +5742,13 @@
         <v>163</v>
       </c>
       <c r="D180" t="s">
+        <v>164</v>
+      </c>
+      <c r="E180" t="s">
+        <v>165</v>
+      </c>
+      <c r="G180" t="s">
         <v>320</v>
-      </c>
-      <c r="E180" t="s">
-        <v>164</v>
-      </c>
-      <c r="F180" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="181" spans="1:7">
@@ -5765,10 +5765,10 @@
         <v>326</v>
       </c>
       <c r="E181" t="s">
+        <v>165</v>
+      </c>
+      <c r="F181" t="s">
         <v>327</v>
-      </c>
-      <c r="F181" t="s">
-        <v>165</v>
       </c>
       <c r="G181" t="s">
         <v>328</v>
@@ -5788,10 +5788,10 @@
         <v>326</v>
       </c>
       <c r="E182" t="s">
+        <v>165</v>
+      </c>
+      <c r="F182" t="s">
         <v>327</v>
-      </c>
-      <c r="F182" t="s">
-        <v>165</v>
       </c>
       <c r="G182" t="s">
         <v>328</v>
@@ -5811,10 +5811,10 @@
         <v>326</v>
       </c>
       <c r="E183" t="s">
+        <v>165</v>
+      </c>
+      <c r="F183" t="s">
         <v>327</v>
-      </c>
-      <c r="F183" t="s">
-        <v>165</v>
       </c>
       <c r="G183" t="s">
         <v>328</v>
@@ -5834,10 +5834,10 @@
         <v>326</v>
       </c>
       <c r="E184" t="s">
+        <v>165</v>
+      </c>
+      <c r="F184" t="s">
         <v>327</v>
-      </c>
-      <c r="F184" t="s">
-        <v>165</v>
       </c>
       <c r="G184" t="s">
         <v>328</v>
@@ -5857,10 +5857,10 @@
         <v>326</v>
       </c>
       <c r="E185" t="s">
+        <v>165</v>
+      </c>
+      <c r="F185" t="s">
         <v>327</v>
-      </c>
-      <c r="F185" t="s">
-        <v>165</v>
       </c>
       <c r="G185" t="s">
         <v>328</v>
@@ -5880,10 +5880,10 @@
         <v>326</v>
       </c>
       <c r="E186" t="s">
+        <v>165</v>
+      </c>
+      <c r="F186" t="s">
         <v>327</v>
-      </c>
-      <c r="F186" t="s">
-        <v>165</v>
       </c>
       <c r="G186" t="s">
         <v>328</v>
@@ -5903,10 +5903,10 @@
         <v>326</v>
       </c>
       <c r="E187" t="s">
+        <v>165</v>
+      </c>
+      <c r="F187" t="s">
         <v>327</v>
-      </c>
-      <c r="F187" t="s">
-        <v>165</v>
       </c>
       <c r="G187" t="s">
         <v>328</v>
@@ -5926,10 +5926,10 @@
         <v>326</v>
       </c>
       <c r="E188" t="s">
+        <v>165</v>
+      </c>
+      <c r="F188" t="s">
         <v>327</v>
-      </c>
-      <c r="F188" t="s">
-        <v>165</v>
       </c>
       <c r="G188" t="s">
         <v>328</v>
@@ -5949,10 +5949,10 @@
         <v>326</v>
       </c>
       <c r="E189" t="s">
+        <v>165</v>
+      </c>
+      <c r="F189" t="s">
         <v>327</v>
-      </c>
-      <c r="F189" t="s">
-        <v>165</v>
       </c>
       <c r="G189" t="s">
         <v>328</v>
@@ -5972,10 +5972,10 @@
         <v>326</v>
       </c>
       <c r="E190" t="s">
+        <v>165</v>
+      </c>
+      <c r="F190" t="s">
         <v>327</v>
-      </c>
-      <c r="F190" t="s">
-        <v>165</v>
       </c>
       <c r="G190" t="s">
         <v>328</v>
@@ -5995,10 +5995,10 @@
         <v>326</v>
       </c>
       <c r="E191" t="s">
+        <v>165</v>
+      </c>
+      <c r="F191" t="s">
         <v>327</v>
-      </c>
-      <c r="F191" t="s">
-        <v>165</v>
       </c>
       <c r="G191" t="s">
         <v>328</v>
@@ -6018,10 +6018,10 @@
         <v>326</v>
       </c>
       <c r="E192" t="s">
+        <v>165</v>
+      </c>
+      <c r="F192" t="s">
         <v>327</v>
-      </c>
-      <c r="F192" t="s">
-        <v>165</v>
       </c>
       <c r="G192" t="s">
         <v>328</v>
@@ -6035,16 +6035,16 @@
         <v>8</v>
       </c>
       <c r="C193" t="s">
+        <v>275</v>
+      </c>
+      <c r="D193" t="s">
         <v>341</v>
       </c>
-      <c r="D193" t="s">
-        <v>326</v>
-      </c>
       <c r="E193" t="s">
-        <v>276</v>
+        <v>165</v>
       </c>
       <c r="F193" t="s">
-        <v>165</v>
+        <v>327</v>
       </c>
       <c r="G193" t="s">
         <v>328</v>
@@ -6064,10 +6064,10 @@
         <v>326</v>
       </c>
       <c r="E194" t="s">
+        <v>165</v>
+      </c>
+      <c r="F194" t="s">
         <v>327</v>
-      </c>
-      <c r="F194" t="s">
-        <v>165</v>
       </c>
       <c r="G194" t="s">
         <v>328</v>
@@ -6087,10 +6087,10 @@
         <v>326</v>
       </c>
       <c r="E195" t="s">
+        <v>165</v>
+      </c>
+      <c r="F195" t="s">
         <v>327</v>
-      </c>
-      <c r="F195" t="s">
-        <v>165</v>
       </c>
       <c r="G195" t="s">
         <v>328</v>
@@ -6110,10 +6110,10 @@
         <v>326</v>
       </c>
       <c r="E196" t="s">
+        <v>165</v>
+      </c>
+      <c r="F196" t="s">
         <v>327</v>
-      </c>
-      <c r="F196" t="s">
-        <v>165</v>
       </c>
       <c r="G196" t="s">
         <v>328</v>
@@ -6133,10 +6133,10 @@
         <v>326</v>
       </c>
       <c r="E197" t="s">
+        <v>165</v>
+      </c>
+      <c r="F197" t="s">
         <v>327</v>
-      </c>
-      <c r="F197" t="s">
-        <v>165</v>
       </c>
       <c r="G197" t="s">
         <v>328</v>
@@ -6156,10 +6156,10 @@
         <v>326</v>
       </c>
       <c r="E198" t="s">
+        <v>165</v>
+      </c>
+      <c r="F198" t="s">
         <v>327</v>
-      </c>
-      <c r="F198" t="s">
-        <v>165</v>
       </c>
       <c r="G198" t="s">
         <v>328</v>
@@ -6173,19 +6173,19 @@
         <v>8</v>
       </c>
       <c r="C199" t="s">
+        <v>325</v>
+      </c>
+      <c r="D199" t="s">
         <v>348</v>
       </c>
-      <c r="D199" t="s">
-        <v>326</v>
-      </c>
       <c r="E199" t="s">
-        <v>327</v>
+        <v>165</v>
       </c>
       <c r="F199" t="s">
-        <v>165</v>
+        <v>349</v>
       </c>
       <c r="G199" t="s">
-        <v>349</v>
+        <v>328</v>
       </c>
     </row>
     <row r="200" spans="1:7">
@@ -6196,19 +6196,19 @@
         <v>8</v>
       </c>
       <c r="C200" t="s">
+        <v>325</v>
+      </c>
+      <c r="D200" t="s">
         <v>348</v>
       </c>
-      <c r="D200" t="s">
-        <v>326</v>
-      </c>
       <c r="E200" t="s">
-        <v>327</v>
+        <v>165</v>
       </c>
       <c r="F200" t="s">
-        <v>165</v>
+        <v>349</v>
       </c>
       <c r="G200" t="s">
-        <v>349</v>
+        <v>328</v>
       </c>
     </row>
     <row r="201" spans="1:7">
@@ -6219,19 +6219,19 @@
         <v>8</v>
       </c>
       <c r="C201" t="s">
+        <v>325</v>
+      </c>
+      <c r="D201" t="s">
         <v>348</v>
       </c>
-      <c r="D201" t="s">
-        <v>326</v>
-      </c>
       <c r="E201" t="s">
-        <v>327</v>
+        <v>165</v>
       </c>
       <c r="F201" t="s">
-        <v>165</v>
+        <v>349</v>
       </c>
       <c r="G201" t="s">
-        <v>349</v>
+        <v>328</v>
       </c>
     </row>
     <row r="202" spans="1:7">
@@ -6242,19 +6242,19 @@
         <v>8</v>
       </c>
       <c r="C202" t="s">
+        <v>325</v>
+      </c>
+      <c r="D202" t="s">
         <v>348</v>
       </c>
-      <c r="D202" t="s">
-        <v>326</v>
-      </c>
       <c r="E202" t="s">
-        <v>327</v>
+        <v>165</v>
       </c>
       <c r="F202" t="s">
-        <v>165</v>
+        <v>349</v>
       </c>
       <c r="G202" t="s">
-        <v>349</v>
+        <v>328</v>
       </c>
     </row>
     <row r="203" spans="1:7">
@@ -6265,19 +6265,19 @@
         <v>8</v>
       </c>
       <c r="C203" t="s">
+        <v>275</v>
+      </c>
+      <c r="D203" t="s">
         <v>341</v>
       </c>
-      <c r="D203" t="s">
-        <v>326</v>
-      </c>
       <c r="E203" t="s">
-        <v>276</v>
+        <v>165</v>
       </c>
       <c r="F203" t="s">
-        <v>165</v>
+        <v>349</v>
       </c>
       <c r="G203" t="s">
-        <v>349</v>
+        <v>328</v>
       </c>
     </row>
     <row r="204" spans="1:7">
@@ -6288,19 +6288,19 @@
         <v>8</v>
       </c>
       <c r="C204" t="s">
+        <v>325</v>
+      </c>
+      <c r="D204" t="s">
         <v>348</v>
       </c>
-      <c r="D204" t="s">
-        <v>326</v>
-      </c>
       <c r="E204" t="s">
-        <v>327</v>
+        <v>165</v>
       </c>
       <c r="F204" t="s">
-        <v>165</v>
+        <v>349</v>
       </c>
       <c r="G204" t="s">
-        <v>349</v>
+        <v>328</v>
       </c>
     </row>
     <row r="205" spans="1:7">
@@ -6311,19 +6311,19 @@
         <v>8</v>
       </c>
       <c r="C205" t="s">
+        <v>325</v>
+      </c>
+      <c r="D205" t="s">
         <v>356</v>
       </c>
-      <c r="D205" t="s">
-        <v>326</v>
-      </c>
       <c r="E205" t="s">
-        <v>327</v>
+        <v>165</v>
       </c>
       <c r="F205" t="s">
-        <v>165</v>
+        <v>357</v>
       </c>
       <c r="G205" t="s">
-        <v>357</v>
+        <v>328</v>
       </c>
     </row>
     <row r="206" spans="1:7">
@@ -6334,19 +6334,19 @@
         <v>8</v>
       </c>
       <c r="C206" t="s">
+        <v>325</v>
+      </c>
+      <c r="D206" t="s">
         <v>356</v>
       </c>
-      <c r="D206" t="s">
-        <v>326</v>
-      </c>
       <c r="E206" t="s">
-        <v>327</v>
+        <v>165</v>
       </c>
       <c r="F206" t="s">
-        <v>165</v>
+        <v>357</v>
       </c>
       <c r="G206" t="s">
-        <v>357</v>
+        <v>328</v>
       </c>
     </row>
     <row r="207" spans="1:7">
@@ -6357,19 +6357,19 @@
         <v>8</v>
       </c>
       <c r="C207" t="s">
+        <v>325</v>
+      </c>
+      <c r="D207" t="s">
         <v>356</v>
       </c>
-      <c r="D207" t="s">
-        <v>326</v>
-      </c>
       <c r="E207" t="s">
-        <v>327</v>
+        <v>165</v>
       </c>
       <c r="F207" t="s">
-        <v>165</v>
+        <v>357</v>
       </c>
       <c r="G207" t="s">
-        <v>357</v>
+        <v>328</v>
       </c>
     </row>
     <row r="208" spans="1:7">
@@ -6380,19 +6380,19 @@
         <v>8</v>
       </c>
       <c r="C208" t="s">
+        <v>275</v>
+      </c>
+      <c r="D208" t="s">
         <v>341</v>
       </c>
-      <c r="D208" t="s">
-        <v>326</v>
-      </c>
       <c r="E208" t="s">
-        <v>276</v>
+        <v>165</v>
       </c>
       <c r="F208" t="s">
-        <v>165</v>
+        <v>357</v>
       </c>
       <c r="G208" t="s">
-        <v>357</v>
+        <v>328</v>
       </c>
     </row>
     <row r="209" spans="1:7">
@@ -6403,19 +6403,19 @@
         <v>8</v>
       </c>
       <c r="C209" t="s">
+        <v>325</v>
+      </c>
+      <c r="D209" t="s">
         <v>356</v>
       </c>
-      <c r="D209" t="s">
-        <v>326</v>
-      </c>
       <c r="E209" t="s">
-        <v>327</v>
+        <v>165</v>
       </c>
       <c r="F209" t="s">
-        <v>165</v>
+        <v>357</v>
       </c>
       <c r="G209" t="s">
-        <v>357</v>
+        <v>328</v>
       </c>
     </row>
     <row r="210" spans="1:7">
@@ -6432,10 +6432,10 @@
         <v>364</v>
       </c>
       <c r="E210" t="s">
+        <v>165</v>
+      </c>
+      <c r="F210" t="s">
         <v>365</v>
-      </c>
-      <c r="F210" t="s">
-        <v>165</v>
       </c>
       <c r="G210" t="s">
         <v>366</v>
@@ -6455,10 +6455,10 @@
         <v>364</v>
       </c>
       <c r="E211" t="s">
+        <v>165</v>
+      </c>
+      <c r="F211" t="s">
         <v>365</v>
-      </c>
-      <c r="F211" t="s">
-        <v>165</v>
       </c>
       <c r="G211" t="s">
         <v>366</v>
@@ -6478,10 +6478,10 @@
         <v>364</v>
       </c>
       <c r="E212" t="s">
+        <v>165</v>
+      </c>
+      <c r="F212" t="s">
         <v>365</v>
-      </c>
-      <c r="F212" t="s">
-        <v>165</v>
       </c>
       <c r="G212" t="s">
         <v>366</v>
@@ -6501,10 +6501,10 @@
         <v>364</v>
       </c>
       <c r="E213" t="s">
+        <v>165</v>
+      </c>
+      <c r="F213" t="s">
         <v>365</v>
-      </c>
-      <c r="F213" t="s">
-        <v>165</v>
       </c>
       <c r="G213" t="s">
         <v>366</v>
@@ -6524,10 +6524,10 @@
         <v>364</v>
       </c>
       <c r="E214" t="s">
+        <v>165</v>
+      </c>
+      <c r="F214" t="s">
         <v>365</v>
-      </c>
-      <c r="F214" t="s">
-        <v>165</v>
       </c>
       <c r="G214" t="s">
         <v>366</v>
@@ -6541,16 +6541,16 @@
         <v>8</v>
       </c>
       <c r="C215" t="s">
+        <v>325</v>
+      </c>
+      <c r="D215" t="s">
         <v>348</v>
       </c>
-      <c r="D215" t="s">
-        <v>364</v>
-      </c>
       <c r="E215" t="s">
-        <v>327</v>
+        <v>165</v>
       </c>
       <c r="F215" t="s">
-        <v>165</v>
+        <v>365</v>
       </c>
       <c r="G215" t="s">
         <v>366</v>
@@ -6570,10 +6570,10 @@
         <v>364</v>
       </c>
       <c r="E216" t="s">
+        <v>165</v>
+      </c>
+      <c r="F216" t="s">
         <v>365</v>
-      </c>
-      <c r="F216" t="s">
-        <v>165</v>
       </c>
       <c r="G216" t="s">
         <v>366</v>
@@ -6593,10 +6593,10 @@
         <v>364</v>
       </c>
       <c r="E217" t="s">
+        <v>165</v>
+      </c>
+      <c r="F217" t="s">
         <v>365</v>
-      </c>
-      <c r="F217" t="s">
-        <v>165</v>
       </c>
       <c r="G217" t="s">
         <v>366</v>
@@ -6616,10 +6616,10 @@
         <v>364</v>
       </c>
       <c r="E218" t="s">
+        <v>165</v>
+      </c>
+      <c r="F218" t="s">
         <v>365</v>
-      </c>
-      <c r="F218" t="s">
-        <v>165</v>
       </c>
       <c r="G218" t="s">
         <v>366</v>
@@ -6639,10 +6639,10 @@
         <v>364</v>
       </c>
       <c r="E219" t="s">
+        <v>165</v>
+      </c>
+      <c r="F219" t="s">
         <v>365</v>
-      </c>
-      <c r="F219" t="s">
-        <v>165</v>
       </c>
       <c r="G219" t="s">
         <v>366</v>
@@ -6656,16 +6656,16 @@
         <v>8</v>
       </c>
       <c r="C220" t="s">
+        <v>269</v>
+      </c>
+      <c r="D220" t="s">
         <v>309</v>
       </c>
-      <c r="D220" t="s">
-        <v>364</v>
-      </c>
       <c r="E220" t="s">
-        <v>271</v>
+        <v>165</v>
       </c>
       <c r="F220" t="s">
-        <v>165</v>
+        <v>365</v>
       </c>
       <c r="G220" t="s">
         <v>366</v>
@@ -6685,10 +6685,10 @@
         <v>364</v>
       </c>
       <c r="E221" t="s">
+        <v>165</v>
+      </c>
+      <c r="F221" t="s">
         <v>365</v>
-      </c>
-      <c r="F221" t="s">
-        <v>165</v>
       </c>
       <c r="G221" t="s">
         <v>366</v>
@@ -6708,10 +6708,10 @@
         <v>364</v>
       </c>
       <c r="E222" t="s">
+        <v>165</v>
+      </c>
+      <c r="F222" t="s">
         <v>365</v>
-      </c>
-      <c r="F222" t="s">
-        <v>165</v>
       </c>
       <c r="G222" t="s">
         <v>366</v>
@@ -6731,10 +6731,10 @@
         <v>364</v>
       </c>
       <c r="E223" t="s">
+        <v>165</v>
+      </c>
+      <c r="F223" t="s">
         <v>365</v>
-      </c>
-      <c r="F223" t="s">
-        <v>165</v>
       </c>
       <c r="G223" t="s">
         <v>366</v>
@@ -6754,10 +6754,10 @@
         <v>364</v>
       </c>
       <c r="E224" t="s">
+        <v>165</v>
+      </c>
+      <c r="F224" t="s">
         <v>365</v>
-      </c>
-      <c r="F224" t="s">
-        <v>165</v>
       </c>
       <c r="G224" t="s">
         <v>366</v>
@@ -6777,10 +6777,10 @@
         <v>364</v>
       </c>
       <c r="E225" t="s">
+        <v>165</v>
+      </c>
+      <c r="F225" t="s">
         <v>365</v>
-      </c>
-      <c r="F225" t="s">
-        <v>165</v>
       </c>
       <c r="G225" t="s">
         <v>366</v>
@@ -6797,13 +6797,13 @@
         <v>275</v>
       </c>
       <c r="D226" t="s">
-        <v>364</v>
+        <v>276</v>
       </c>
       <c r="E226" t="s">
-        <v>276</v>
+        <v>165</v>
       </c>
       <c r="F226" t="s">
-        <v>165</v>
+        <v>365</v>
       </c>
       <c r="G226" t="s">
         <v>366</v>
@@ -6823,10 +6823,10 @@
         <v>364</v>
       </c>
       <c r="E227" t="s">
+        <v>165</v>
+      </c>
+      <c r="F227" t="s">
         <v>365</v>
-      </c>
-      <c r="F227" t="s">
-        <v>165</v>
       </c>
       <c r="G227" t="s">
         <v>366</v>
@@ -6843,13 +6843,13 @@
         <v>163</v>
       </c>
       <c r="D228" t="s">
-        <v>364</v>
+        <v>164</v>
       </c>
       <c r="E228" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="F228" t="s">
-        <v>165</v>
+        <v>365</v>
       </c>
       <c r="G228" t="s">
         <v>366</v>
@@ -6863,19 +6863,19 @@
         <v>8</v>
       </c>
       <c r="C229" t="s">
+        <v>363</v>
+      </c>
+      <c r="D229" t="s">
         <v>386</v>
       </c>
-      <c r="D229" t="s">
-        <v>364</v>
-      </c>
       <c r="E229" t="s">
-        <v>365</v>
+        <v>165</v>
       </c>
       <c r="F229" t="s">
-        <v>165</v>
+        <v>387</v>
       </c>
       <c r="G229" t="s">
-        <v>387</v>
+        <v>366</v>
       </c>
     </row>
     <row r="230" spans="1:7">
@@ -6886,19 +6886,19 @@
         <v>8</v>
       </c>
       <c r="C230" t="s">
+        <v>363</v>
+      </c>
+      <c r="D230" t="s">
         <v>386</v>
       </c>
-      <c r="D230" t="s">
-        <v>364</v>
-      </c>
       <c r="E230" t="s">
-        <v>365</v>
+        <v>165</v>
       </c>
       <c r="F230" t="s">
-        <v>165</v>
+        <v>387</v>
       </c>
       <c r="G230" t="s">
-        <v>387</v>
+        <v>366</v>
       </c>
     </row>
     <row r="231" spans="1:7">
@@ -6909,19 +6909,19 @@
         <v>8</v>
       </c>
       <c r="C231" t="s">
+        <v>269</v>
+      </c>
+      <c r="D231" t="s">
         <v>293</v>
       </c>
-      <c r="D231" t="s">
-        <v>364</v>
-      </c>
       <c r="E231" t="s">
-        <v>271</v>
+        <v>165</v>
       </c>
       <c r="F231" t="s">
-        <v>165</v>
+        <v>387</v>
       </c>
       <c r="G231" t="s">
-        <v>387</v>
+        <v>366</v>
       </c>
     </row>
     <row r="232" spans="1:7">
@@ -6932,19 +6932,19 @@
         <v>8</v>
       </c>
       <c r="C232" t="s">
+        <v>269</v>
+      </c>
+      <c r="D232" t="s">
         <v>309</v>
       </c>
-      <c r="D232" t="s">
-        <v>364</v>
-      </c>
       <c r="E232" t="s">
-        <v>271</v>
+        <v>165</v>
       </c>
       <c r="F232" t="s">
-        <v>165</v>
+        <v>387</v>
       </c>
       <c r="G232" t="s">
-        <v>387</v>
+        <v>366</v>
       </c>
     </row>
     <row r="233" spans="1:7">
@@ -6955,19 +6955,19 @@
         <v>8</v>
       </c>
       <c r="C233" t="s">
+        <v>363</v>
+      </c>
+      <c r="D233" t="s">
         <v>386</v>
       </c>
-      <c r="D233" t="s">
-        <v>364</v>
-      </c>
       <c r="E233" t="s">
-        <v>365</v>
+        <v>165</v>
       </c>
       <c r="F233" t="s">
-        <v>165</v>
+        <v>387</v>
       </c>
       <c r="G233" t="s">
-        <v>387</v>
+        <v>366</v>
       </c>
     </row>
     <row r="234" spans="1:7">
@@ -6978,19 +6978,19 @@
         <v>8</v>
       </c>
       <c r="C234" t="s">
+        <v>363</v>
+      </c>
+      <c r="D234" t="s">
         <v>386</v>
       </c>
-      <c r="D234" t="s">
-        <v>364</v>
-      </c>
       <c r="E234" t="s">
-        <v>365</v>
+        <v>165</v>
       </c>
       <c r="F234" t="s">
-        <v>165</v>
+        <v>387</v>
       </c>
       <c r="G234" t="s">
-        <v>387</v>
+        <v>366</v>
       </c>
     </row>
     <row r="235" spans="1:7">
@@ -7001,19 +7001,19 @@
         <v>8</v>
       </c>
       <c r="C235" t="s">
+        <v>363</v>
+      </c>
+      <c r="D235" t="s">
         <v>386</v>
       </c>
-      <c r="D235" t="s">
-        <v>364</v>
-      </c>
       <c r="E235" t="s">
-        <v>365</v>
+        <v>165</v>
       </c>
       <c r="F235" t="s">
-        <v>165</v>
+        <v>387</v>
       </c>
       <c r="G235" t="s">
-        <v>387</v>
+        <v>366</v>
       </c>
     </row>
     <row r="236" spans="1:7">
@@ -7024,19 +7024,19 @@
         <v>8</v>
       </c>
       <c r="C236" t="s">
+        <v>363</v>
+      </c>
+      <c r="D236" t="s">
         <v>386</v>
       </c>
-      <c r="D236" t="s">
-        <v>364</v>
-      </c>
       <c r="E236" t="s">
-        <v>365</v>
+        <v>165</v>
       </c>
       <c r="F236" t="s">
-        <v>165</v>
+        <v>387</v>
       </c>
       <c r="G236" t="s">
-        <v>387</v>
+        <v>366</v>
       </c>
     </row>
     <row r="237" spans="1:7">
@@ -7047,19 +7047,19 @@
         <v>8</v>
       </c>
       <c r="C237" t="s">
+        <v>363</v>
+      </c>
+      <c r="D237" t="s">
         <v>386</v>
       </c>
-      <c r="D237" t="s">
-        <v>364</v>
-      </c>
       <c r="E237" t="s">
-        <v>365</v>
+        <v>165</v>
       </c>
       <c r="F237" t="s">
-        <v>165</v>
+        <v>387</v>
       </c>
       <c r="G237" t="s">
-        <v>387</v>
+        <v>366</v>
       </c>
     </row>
     <row r="238" spans="1:7">
@@ -7070,19 +7070,19 @@
         <v>8</v>
       </c>
       <c r="C238" t="s">
+        <v>363</v>
+      </c>
+      <c r="D238" t="s">
         <v>386</v>
       </c>
-      <c r="D238" t="s">
-        <v>364</v>
-      </c>
       <c r="E238" t="s">
-        <v>365</v>
+        <v>165</v>
       </c>
       <c r="F238" t="s">
-        <v>165</v>
+        <v>387</v>
       </c>
       <c r="G238" t="s">
-        <v>387</v>
+        <v>366</v>
       </c>
     </row>
     <row r="239" spans="1:7">
@@ -7093,19 +7093,19 @@
         <v>8</v>
       </c>
       <c r="C239" t="s">
+        <v>363</v>
+      </c>
+      <c r="D239" t="s">
         <v>398</v>
       </c>
-      <c r="D239" t="s">
-        <v>364</v>
-      </c>
       <c r="E239" t="s">
-        <v>365</v>
+        <v>165</v>
       </c>
       <c r="F239" t="s">
-        <v>165</v>
+        <v>399</v>
       </c>
       <c r="G239" t="s">
-        <v>399</v>
+        <v>366</v>
       </c>
     </row>
     <row r="240" spans="1:7">
@@ -7119,13 +7119,13 @@
         <v>163</v>
       </c>
       <c r="D240" t="s">
+        <v>164</v>
+      </c>
+      <c r="E240" t="s">
+        <v>165</v>
+      </c>
+      <c r="F240" t="s">
         <v>401</v>
-      </c>
-      <c r="E240" t="s">
-        <v>164</v>
-      </c>
-      <c r="F240" t="s">
-        <v>165</v>
       </c>
       <c r="G240" t="s">
         <v>402</v>
@@ -7142,13 +7142,13 @@
         <v>163</v>
       </c>
       <c r="D241" t="s">
+        <v>164</v>
+      </c>
+      <c r="E241" t="s">
+        <v>165</v>
+      </c>
+      <c r="F241" t="s">
         <v>401</v>
-      </c>
-      <c r="E241" t="s">
-        <v>164</v>
-      </c>
-      <c r="F241" t="s">
-        <v>165</v>
       </c>
       <c r="G241" t="s">
         <v>402</v>
@@ -7165,13 +7165,13 @@
         <v>163</v>
       </c>
       <c r="D242" t="s">
+        <v>164</v>
+      </c>
+      <c r="E242" t="s">
+        <v>165</v>
+      </c>
+      <c r="F242" t="s">
         <v>401</v>
-      </c>
-      <c r="E242" t="s">
-        <v>164</v>
-      </c>
-      <c r="F242" t="s">
-        <v>165</v>
       </c>
       <c r="G242" t="s">
         <v>402</v>
@@ -7188,13 +7188,13 @@
         <v>163</v>
       </c>
       <c r="D243" t="s">
+        <v>164</v>
+      </c>
+      <c r="E243" t="s">
+        <v>165</v>
+      </c>
+      <c r="F243" t="s">
         <v>401</v>
-      </c>
-      <c r="E243" t="s">
-        <v>164</v>
-      </c>
-      <c r="F243" t="s">
-        <v>165</v>
       </c>
       <c r="G243" t="s">
         <v>402</v>
@@ -7211,13 +7211,13 @@
         <v>163</v>
       </c>
       <c r="D244" t="s">
+        <v>164</v>
+      </c>
+      <c r="E244" t="s">
+        <v>165</v>
+      </c>
+      <c r="F244" t="s">
         <v>401</v>
-      </c>
-      <c r="E244" t="s">
-        <v>164</v>
-      </c>
-      <c r="F244" t="s">
-        <v>165</v>
       </c>
       <c r="G244" t="s">
         <v>402</v>
@@ -7234,13 +7234,13 @@
         <v>163</v>
       </c>
       <c r="D245" t="s">
+        <v>164</v>
+      </c>
+      <c r="E245" t="s">
+        <v>165</v>
+      </c>
+      <c r="F245" t="s">
         <v>401</v>
-      </c>
-      <c r="E245" t="s">
-        <v>164</v>
-      </c>
-      <c r="F245" t="s">
-        <v>165</v>
       </c>
       <c r="G245" t="s">
         <v>402</v>
@@ -7254,19 +7254,19 @@
         <v>8</v>
       </c>
       <c r="C246" t="s">
+        <v>255</v>
+      </c>
+      <c r="D246" t="s">
         <v>409</v>
       </c>
-      <c r="D246" t="s">
-        <v>401</v>
-      </c>
       <c r="E246" t="s">
-        <v>256</v>
+        <v>165</v>
       </c>
       <c r="F246" t="s">
-        <v>165</v>
+        <v>410</v>
       </c>
       <c r="G246" t="s">
-        <v>410</v>
+        <v>402</v>
       </c>
     </row>
     <row r="247" spans="1:7">
@@ -7280,13 +7280,13 @@
         <v>95</v>
       </c>
       <c r="D247" t="s">
+        <v>96</v>
+      </c>
+      <c r="E247" t="s">
+        <v>97</v>
+      </c>
+      <c r="G247" t="s">
         <v>412</v>
-      </c>
-      <c r="E247" t="s">
-        <v>96</v>
-      </c>
-      <c r="F247" t="s">
-        <v>97</v>
       </c>
     </row>
     <row r="248" spans="1:7">
@@ -7300,13 +7300,13 @@
         <v>95</v>
       </c>
       <c r="D248" t="s">
+        <v>96</v>
+      </c>
+      <c r="E248" t="s">
+        <v>97</v>
+      </c>
+      <c r="G248" t="s">
         <v>412</v>
-      </c>
-      <c r="E248" t="s">
-        <v>96</v>
-      </c>
-      <c r="F248" t="s">
-        <v>97</v>
       </c>
     </row>
     <row r="249" spans="1:7">
@@ -7320,13 +7320,13 @@
         <v>415</v>
       </c>
       <c r="D249" t="s">
+        <v>416</v>
+      </c>
+      <c r="E249" t="s">
+        <v>97</v>
+      </c>
+      <c r="G249" t="s">
         <v>412</v>
-      </c>
-      <c r="E249" t="s">
-        <v>416</v>
-      </c>
-      <c r="F249" t="s">
-        <v>97</v>
       </c>
     </row>
     <row r="250" spans="1:7">
@@ -7340,13 +7340,13 @@
         <v>95</v>
       </c>
       <c r="D250" t="s">
+        <v>96</v>
+      </c>
+      <c r="E250" t="s">
+        <v>97</v>
+      </c>
+      <c r="G250" t="s">
         <v>412</v>
-      </c>
-      <c r="E250" t="s">
-        <v>96</v>
-      </c>
-      <c r="F250" t="s">
-        <v>97</v>
       </c>
     </row>
     <row r="251" spans="1:7">
@@ -7360,13 +7360,13 @@
         <v>95</v>
       </c>
       <c r="D251" t="s">
+        <v>96</v>
+      </c>
+      <c r="E251" t="s">
+        <v>97</v>
+      </c>
+      <c r="G251" t="s">
         <v>412</v>
-      </c>
-      <c r="E251" t="s">
-        <v>96</v>
-      </c>
-      <c r="F251" t="s">
-        <v>97</v>
       </c>
     </row>
     <row r="252" spans="1:7">
@@ -7380,13 +7380,13 @@
         <v>95</v>
       </c>
       <c r="D252" t="s">
+        <v>96</v>
+      </c>
+      <c r="E252" t="s">
+        <v>97</v>
+      </c>
+      <c r="G252" t="s">
         <v>412</v>
-      </c>
-      <c r="E252" t="s">
-        <v>96</v>
-      </c>
-      <c r="F252" t="s">
-        <v>97</v>
       </c>
     </row>
     <row r="253" spans="1:7">
@@ -7403,10 +7403,10 @@
         <v>422</v>
       </c>
       <c r="E253" t="s">
+        <v>165</v>
+      </c>
+      <c r="G253" t="s">
         <v>423</v>
-      </c>
-      <c r="F253" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="254" spans="1:7">
@@ -7420,13 +7420,13 @@
         <v>219</v>
       </c>
       <c r="D254" t="s">
-        <v>422</v>
+        <v>220</v>
       </c>
       <c r="E254" t="s">
-        <v>220</v>
-      </c>
-      <c r="F254" t="s">
-        <v>93</v>
+        <v>92</v>
+      </c>
+      <c r="G254" t="s">
+        <v>423</v>
       </c>
     </row>
     <row r="255" spans="1:7">
@@ -7440,13 +7440,13 @@
         <v>426</v>
       </c>
       <c r="D255" t="s">
-        <v>422</v>
+        <v>427</v>
       </c>
       <c r="E255" t="s">
-        <v>427</v>
-      </c>
-      <c r="F255" t="s">
-        <v>93</v>
+        <v>92</v>
+      </c>
+      <c r="G255" t="s">
+        <v>423</v>
       </c>
     </row>
     <row r="256" spans="1:7">
@@ -7460,16 +7460,16 @@
         <v>426</v>
       </c>
       <c r="D256" t="s">
-        <v>422</v>
+        <v>427</v>
       </c>
       <c r="E256" t="s">
-        <v>427</v>
-      </c>
-      <c r="F256" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="257" spans="1:6">
+        <v>92</v>
+      </c>
+      <c r="G256" t="s">
+        <v>423</v>
+      </c>
+    </row>
+    <row r="257" spans="1:7">
       <c r="A257" t="s">
         <v>429</v>
       </c>
@@ -7480,16 +7480,16 @@
         <v>426</v>
       </c>
       <c r="D257" t="s">
-        <v>422</v>
+        <v>427</v>
       </c>
       <c r="E257" t="s">
-        <v>427</v>
-      </c>
-      <c r="F257" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="258" spans="1:6">
+        <v>92</v>
+      </c>
+      <c r="G257" t="s">
+        <v>423</v>
+      </c>
+    </row>
+    <row r="258" spans="1:7">
       <c r="A258" t="s">
         <v>430</v>
       </c>
@@ -7500,16 +7500,16 @@
         <v>325</v>
       </c>
       <c r="D258" t="s">
-        <v>422</v>
+        <v>326</v>
       </c>
       <c r="E258" t="s">
-        <v>327</v>
-      </c>
-      <c r="F258" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="259" spans="1:6">
+        <v>165</v>
+      </c>
+      <c r="G258" t="s">
+        <v>423</v>
+      </c>
+    </row>
+    <row r="259" spans="1:7">
       <c r="A259" t="s">
         <v>431</v>
       </c>
@@ -7520,16 +7520,16 @@
         <v>426</v>
       </c>
       <c r="D259" t="s">
-        <v>422</v>
+        <v>427</v>
       </c>
       <c r="E259" t="s">
-        <v>427</v>
-      </c>
-      <c r="F259" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="260" spans="1:6">
+        <v>92</v>
+      </c>
+      <c r="G259" t="s">
+        <v>423</v>
+      </c>
+    </row>
+    <row r="260" spans="1:7">
       <c r="A260" t="s">
         <v>432</v>
       </c>
@@ -7540,16 +7540,16 @@
         <v>163</v>
       </c>
       <c r="D260" t="s">
-        <v>422</v>
+        <v>164</v>
       </c>
       <c r="E260" t="s">
-        <v>164</v>
-      </c>
-      <c r="F260" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="261" spans="1:6">
+        <v>165</v>
+      </c>
+      <c r="G260" t="s">
+        <v>423</v>
+      </c>
+    </row>
+    <row r="261" spans="1:7">
       <c r="A261" t="s">
         <v>433</v>
       </c>
@@ -7560,16 +7560,16 @@
         <v>434</v>
       </c>
       <c r="D261" t="s">
-        <v>422</v>
+        <v>435</v>
       </c>
       <c r="E261" t="s">
-        <v>435</v>
-      </c>
-      <c r="F261" t="s">
         <v>197</v>
       </c>
-    </row>
-    <row r="262" spans="1:6">
+      <c r="G261" t="s">
+        <v>423</v>
+      </c>
+    </row>
+    <row r="262" spans="1:7">
       <c r="A262" t="s">
         <v>436</v>
       </c>
@@ -7580,16 +7580,16 @@
         <v>163</v>
       </c>
       <c r="D262" t="s">
-        <v>422</v>
+        <v>164</v>
       </c>
       <c r="E262" t="s">
-        <v>164</v>
-      </c>
-      <c r="F262" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="263" spans="1:6">
+        <v>165</v>
+      </c>
+      <c r="G262" t="s">
+        <v>423</v>
+      </c>
+    </row>
+    <row r="263" spans="1:7">
       <c r="A263" t="s">
         <v>437</v>
       </c>
@@ -7600,16 +7600,16 @@
         <v>438</v>
       </c>
       <c r="D263" t="s">
-        <v>422</v>
+        <v>439</v>
       </c>
       <c r="E263" t="s">
-        <v>439</v>
-      </c>
-      <c r="F263" t="s">
         <v>184</v>
       </c>
-    </row>
-    <row r="264" spans="1:6">
+      <c r="G263" t="s">
+        <v>423</v>
+      </c>
+    </row>
+    <row r="264" spans="1:7">
       <c r="A264" t="s">
         <v>440</v>
       </c>
@@ -7620,16 +7620,16 @@
         <v>31</v>
       </c>
       <c r="D264" t="s">
-        <v>422</v>
+        <v>32</v>
       </c>
       <c r="E264" t="s">
-        <v>32</v>
-      </c>
-      <c r="F264" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="265" spans="1:6">
+      <c r="G264" t="s">
+        <v>423</v>
+      </c>
+    </row>
+    <row r="265" spans="1:7">
       <c r="A265" t="s">
         <v>441</v>
       </c>
@@ -7640,16 +7640,16 @@
         <v>9</v>
       </c>
       <c r="D265" t="s">
-        <v>422</v>
+        <v>10</v>
       </c>
       <c r="E265" t="s">
         <v>11</v>
       </c>
-      <c r="F265" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="266" spans="1:6">
+      <c r="G265" t="s">
+        <v>423</v>
+      </c>
+    </row>
+    <row r="266" spans="1:7">
       <c r="A266" t="s">
         <v>442</v>
       </c>
@@ -7660,16 +7660,16 @@
         <v>443</v>
       </c>
       <c r="D266" t="s">
-        <v>422</v>
+        <v>444</v>
       </c>
       <c r="E266" t="s">
-        <v>444</v>
-      </c>
-      <c r="F266" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="267" spans="1:6">
+        <v>114</v>
+      </c>
+      <c r="G266" t="s">
+        <v>423</v>
+      </c>
+    </row>
+    <row r="267" spans="1:7">
       <c r="A267" t="s">
         <v>445</v>
       </c>
@@ -7680,16 +7680,16 @@
         <v>118</v>
       </c>
       <c r="D267" t="s">
+        <v>119</v>
+      </c>
+      <c r="E267" t="s">
+        <v>114</v>
+      </c>
+      <c r="G267" t="s">
         <v>446</v>
       </c>
-      <c r="E267" t="s">
-        <v>119</v>
-      </c>
-      <c r="F267" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="268" spans="1:6">
+    </row>
+    <row r="268" spans="1:7">
       <c r="A268" t="s">
         <v>447</v>
       </c>
@@ -7700,16 +7700,16 @@
         <v>202</v>
       </c>
       <c r="D268" t="s">
+        <v>203</v>
+      </c>
+      <c r="E268" t="s">
+        <v>184</v>
+      </c>
+      <c r="G268" t="s">
         <v>448</v>
       </c>
-      <c r="E268" t="s">
-        <v>204</v>
-      </c>
-      <c r="F268" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="269" spans="1:6">
+    </row>
+    <row r="269" spans="1:7">
       <c r="A269" t="s">
         <v>449</v>
       </c>
@@ -7720,16 +7720,16 @@
         <v>118</v>
       </c>
       <c r="D269" t="s">
+        <v>119</v>
+      </c>
+      <c r="E269" t="s">
+        <v>114</v>
+      </c>
+      <c r="G269" t="s">
         <v>450</v>
       </c>
-      <c r="E269" t="s">
-        <v>119</v>
-      </c>
-      <c r="F269" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="270" spans="1:6">
+    </row>
+    <row r="270" spans="1:7">
       <c r="A270" t="s">
         <v>451</v>
       </c>
@@ -7740,16 +7740,16 @@
         <v>118</v>
       </c>
       <c r="D270" t="s">
+        <v>119</v>
+      </c>
+      <c r="E270" t="s">
+        <v>114</v>
+      </c>
+      <c r="G270" t="s">
         <v>450</v>
       </c>
-      <c r="E270" t="s">
-        <v>119</v>
-      </c>
-      <c r="F270" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="271" spans="1:6">
+    </row>
+    <row r="271" spans="1:7">
       <c r="A271" t="s">
         <v>452</v>
       </c>
@@ -7763,13 +7763,13 @@
         <v>454</v>
       </c>
       <c r="E271" t="s">
+        <v>114</v>
+      </c>
+      <c r="G271" t="s">
         <v>455</v>
       </c>
-      <c r="F271" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="272" spans="1:6">
+    </row>
+    <row r="272" spans="1:7">
       <c r="A272" t="s">
         <v>456</v>
       </c>
@@ -7783,13 +7783,13 @@
         <v>454</v>
       </c>
       <c r="E272" t="s">
+        <v>114</v>
+      </c>
+      <c r="G272" t="s">
         <v>455</v>
       </c>
-      <c r="F272" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="273" spans="1:6">
+    </row>
+    <row r="273" spans="1:7">
       <c r="A273" t="s">
         <v>457</v>
       </c>
@@ -7803,13 +7803,13 @@
         <v>454</v>
       </c>
       <c r="E273" t="s">
+        <v>114</v>
+      </c>
+      <c r="G273" t="s">
         <v>455</v>
       </c>
-      <c r="F273" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="274" spans="1:6">
+    </row>
+    <row r="274" spans="1:7">
       <c r="A274" t="s">
         <v>458</v>
       </c>
@@ -7823,13 +7823,13 @@
         <v>454</v>
       </c>
       <c r="E274" t="s">
+        <v>114</v>
+      </c>
+      <c r="G274" t="s">
         <v>455</v>
       </c>
-      <c r="F274" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="275" spans="1:6">
+    </row>
+    <row r="275" spans="1:7">
       <c r="A275" t="s">
         <v>459</v>
       </c>
@@ -7843,13 +7843,13 @@
         <v>454</v>
       </c>
       <c r="E275" t="s">
+        <v>114</v>
+      </c>
+      <c r="G275" t="s">
         <v>455</v>
       </c>
-      <c r="F275" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="276" spans="1:6">
+    </row>
+    <row r="276" spans="1:7">
       <c r="A276" t="s">
         <v>460</v>
       </c>
@@ -7863,13 +7863,13 @@
         <v>454</v>
       </c>
       <c r="E276" t="s">
+        <v>114</v>
+      </c>
+      <c r="G276" t="s">
         <v>455</v>
       </c>
-      <c r="F276" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="277" spans="1:6">
+    </row>
+    <row r="277" spans="1:7">
       <c r="A277" t="s">
         <v>461</v>
       </c>
@@ -7883,13 +7883,13 @@
         <v>454</v>
       </c>
       <c r="E277" t="s">
+        <v>114</v>
+      </c>
+      <c r="G277" t="s">
         <v>455</v>
       </c>
-      <c r="F277" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="278" spans="1:6">
+    </row>
+    <row r="278" spans="1:7">
       <c r="A278" t="s">
         <v>462</v>
       </c>
@@ -7900,16 +7900,16 @@
         <v>202</v>
       </c>
       <c r="D278" t="s">
+        <v>203</v>
+      </c>
+      <c r="E278" t="s">
+        <v>184</v>
+      </c>
+      <c r="G278" t="s">
         <v>463</v>
       </c>
-      <c r="E278" t="s">
-        <v>204</v>
-      </c>
-      <c r="F278" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="279" spans="1:6">
+    </row>
+    <row r="279" spans="1:7">
       <c r="A279" t="s">
         <v>464</v>
       </c>
@@ -7920,16 +7920,16 @@
         <v>51</v>
       </c>
       <c r="D279" t="s">
+        <v>52</v>
+      </c>
+      <c r="E279" t="s">
+        <v>33</v>
+      </c>
+      <c r="G279" t="s">
         <v>463</v>
       </c>
-      <c r="E279" t="s">
-        <v>53</v>
-      </c>
-      <c r="F279" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="280" spans="1:6">
+    </row>
+    <row r="280" spans="1:7">
       <c r="A280" t="s">
         <v>465</v>
       </c>
@@ -7940,16 +7940,16 @@
         <v>9</v>
       </c>
       <c r="D280" t="s">
-        <v>463</v>
+        <v>10</v>
       </c>
       <c r="E280" t="s">
         <v>11</v>
       </c>
-      <c r="F280" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="281" spans="1:6">
+      <c r="G280" t="s">
+        <v>463</v>
+      </c>
+    </row>
+    <row r="281" spans="1:7">
       <c r="A281" t="s">
         <v>466</v>
       </c>
@@ -7960,16 +7960,16 @@
         <v>170</v>
       </c>
       <c r="D281" t="s">
+        <v>171</v>
+      </c>
+      <c r="E281" t="s">
+        <v>114</v>
+      </c>
+      <c r="G281" t="s">
         <v>463</v>
       </c>
-      <c r="E281" t="s">
-        <v>171</v>
-      </c>
-      <c r="F281" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="282" spans="1:6">
+    </row>
+    <row r="282" spans="1:7">
       <c r="A282" t="s">
         <v>467</v>
       </c>
@@ -7980,16 +7980,16 @@
         <v>124</v>
       </c>
       <c r="D282" t="s">
+        <v>125</v>
+      </c>
+      <c r="E282" t="s">
+        <v>126</v>
+      </c>
+      <c r="G282" t="s">
         <v>463</v>
       </c>
-      <c r="E282" t="s">
-        <v>125</v>
-      </c>
-      <c r="F282" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="283" spans="1:6">
+    </row>
+    <row r="283" spans="1:7">
       <c r="A283" t="s">
         <v>468</v>
       </c>
@@ -7997,19 +7997,19 @@
         <v>8</v>
       </c>
       <c r="C283" t="s">
+        <v>363</v>
+      </c>
+      <c r="D283" t="s">
         <v>398</v>
       </c>
-      <c r="D283" t="s">
+      <c r="E283" t="s">
+        <v>165</v>
+      </c>
+      <c r="G283" t="s">
         <v>469</v>
       </c>
-      <c r="E283" t="s">
-        <v>365</v>
-      </c>
-      <c r="F283" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="284" spans="1:6">
+    </row>
+    <row r="284" spans="1:7">
       <c r="A284" t="s">
         <v>470</v>
       </c>
@@ -8020,16 +8020,16 @@
         <v>124</v>
       </c>
       <c r="D284" t="s">
+        <v>125</v>
+      </c>
+      <c r="E284" t="s">
+        <v>126</v>
+      </c>
+      <c r="G284" t="s">
         <v>471</v>
       </c>
-      <c r="E284" t="s">
-        <v>125</v>
-      </c>
-      <c r="F284" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="285" spans="1:6">
+    </row>
+    <row r="285" spans="1:7">
       <c r="A285" t="s">
         <v>472</v>
       </c>
@@ -8040,16 +8040,16 @@
         <v>170</v>
       </c>
       <c r="D285" t="s">
+        <v>171</v>
+      </c>
+      <c r="E285" t="s">
+        <v>114</v>
+      </c>
+      <c r="G285" t="s">
         <v>473</v>
       </c>
-      <c r="E285" t="s">
-        <v>171</v>
-      </c>
-      <c r="F285" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="286" spans="1:6">
+    </row>
+    <row r="286" spans="1:7">
       <c r="A286" t="s">
         <v>474</v>
       </c>
@@ -8060,16 +8060,16 @@
         <v>438</v>
       </c>
       <c r="D286" t="s">
+        <v>439</v>
+      </c>
+      <c r="E286" t="s">
+        <v>184</v>
+      </c>
+      <c r="G286" t="s">
         <v>475</v>
       </c>
-      <c r="E286" t="s">
-        <v>439</v>
-      </c>
-      <c r="F286" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="287" spans="1:6">
+    </row>
+    <row r="287" spans="1:7">
       <c r="A287" t="s">
         <v>476</v>
       </c>
@@ -8080,16 +8080,16 @@
         <v>438</v>
       </c>
       <c r="D287" t="s">
+        <v>439</v>
+      </c>
+      <c r="E287" t="s">
+        <v>184</v>
+      </c>
+      <c r="G287" t="s">
         <v>475</v>
       </c>
-      <c r="E287" t="s">
-        <v>439</v>
-      </c>
-      <c r="F287" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="288" spans="1:6">
+    </row>
+    <row r="288" spans="1:7">
       <c r="A288" t="s">
         <v>477</v>
       </c>
@@ -8100,16 +8100,16 @@
         <v>41</v>
       </c>
       <c r="D288" t="s">
+        <v>42</v>
+      </c>
+      <c r="E288" t="s">
+        <v>11</v>
+      </c>
+      <c r="G288" t="s">
         <v>475</v>
       </c>
-      <c r="E288" t="s">
-        <v>42</v>
-      </c>
-      <c r="F288" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="289" spans="1:6">
+    </row>
+    <row r="289" spans="1:7">
       <c r="A289" t="s">
         <v>478</v>
       </c>
@@ -8120,16 +8120,16 @@
         <v>31</v>
       </c>
       <c r="D289" t="s">
+        <v>32</v>
+      </c>
+      <c r="E289" t="s">
+        <v>33</v>
+      </c>
+      <c r="G289" t="s">
         <v>475</v>
       </c>
-      <c r="E289" t="s">
-        <v>32</v>
-      </c>
-      <c r="F289" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="290" spans="1:6">
+    </row>
+    <row r="290" spans="1:7">
       <c r="A290" t="s">
         <v>479</v>
       </c>
@@ -8140,16 +8140,16 @@
         <v>31</v>
       </c>
       <c r="D290" t="s">
+        <v>32</v>
+      </c>
+      <c r="E290" t="s">
+        <v>33</v>
+      </c>
+      <c r="G290" t="s">
         <v>475</v>
       </c>
-      <c r="E290" t="s">
-        <v>32</v>
-      </c>
-      <c r="F290" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="291" spans="1:6">
+    </row>
+    <row r="291" spans="1:7">
       <c r="A291" t="s">
         <v>480</v>
       </c>
@@ -8160,16 +8160,16 @@
         <v>170</v>
       </c>
       <c r="D291" t="s">
+        <v>171</v>
+      </c>
+      <c r="E291" t="s">
+        <v>114</v>
+      </c>
+      <c r="G291" t="s">
         <v>475</v>
       </c>
-      <c r="E291" t="s">
-        <v>171</v>
-      </c>
-      <c r="F291" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="292" spans="1:6">
+    </row>
+    <row r="292" spans="1:7">
       <c r="A292" t="s">
         <v>481</v>
       </c>
@@ -8180,16 +8180,16 @@
         <v>170</v>
       </c>
       <c r="D292" t="s">
+        <v>171</v>
+      </c>
+      <c r="E292" t="s">
+        <v>114</v>
+      </c>
+      <c r="G292" t="s">
         <v>475</v>
       </c>
-      <c r="E292" t="s">
-        <v>171</v>
-      </c>
-      <c r="F292" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="293" spans="1:6">
+    </row>
+    <row r="293" spans="1:7">
       <c r="A293" t="s">
         <v>482</v>
       </c>
@@ -8200,16 +8200,16 @@
         <v>170</v>
       </c>
       <c r="D293" t="s">
+        <v>171</v>
+      </c>
+      <c r="E293" t="s">
+        <v>114</v>
+      </c>
+      <c r="G293" t="s">
         <v>475</v>
       </c>
-      <c r="E293" t="s">
-        <v>171</v>
-      </c>
-      <c r="F293" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="294" spans="1:6">
+    </row>
+    <row r="294" spans="1:7">
       <c r="A294" t="s">
         <v>483</v>
       </c>
@@ -8220,16 +8220,16 @@
         <v>170</v>
       </c>
       <c r="D294" t="s">
+        <v>171</v>
+      </c>
+      <c r="E294" t="s">
+        <v>114</v>
+      </c>
+      <c r="G294" t="s">
         <v>475</v>
       </c>
-      <c r="E294" t="s">
-        <v>171</v>
-      </c>
-      <c r="F294" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="295" spans="1:6">
+    </row>
+    <row r="295" spans="1:7">
       <c r="A295" t="s">
         <v>484</v>
       </c>
@@ -8240,16 +8240,16 @@
         <v>170</v>
       </c>
       <c r="D295" t="s">
+        <v>171</v>
+      </c>
+      <c r="E295" t="s">
+        <v>114</v>
+      </c>
+      <c r="G295" t="s">
         <v>485</v>
       </c>
-      <c r="E295" t="s">
-        <v>171</v>
-      </c>
-      <c r="F295" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="296" spans="1:6">
+    </row>
+    <row r="296" spans="1:7">
       <c r="A296" t="s">
         <v>486</v>
       </c>
@@ -8260,13 +8260,13 @@
         <v>170</v>
       </c>
       <c r="D296" t="s">
+        <v>171</v>
+      </c>
+      <c r="E296" t="s">
+        <v>114</v>
+      </c>
+      <c r="G296" t="s">
         <v>485</v>
-      </c>
-      <c r="E296" t="s">
-        <v>171</v>
-      </c>
-      <c r="F296" t="s">
-        <v>115</v>
       </c>
     </row>
   </sheetData>

--- a/api/2/xlsx/fr/SectorCOFOG.xlsx
+++ b/api/2/xlsx/fr/SectorCOFOG.xlsx
@@ -22,75 +22,75 @@
     <t>status</t>
   </si>
   <si>
+    <t>codeforiati:cofog-class</t>
+  </si>
+  <si>
+    <t>codeforiati:category-code</t>
+  </si>
+  <si>
     <t>codeforiati:cofog-group</t>
   </si>
   <si>
-    <t>codeforiati:cofog-class</t>
+    <t>codeforiati:group-code</t>
   </si>
   <si>
     <t>codeforiati:cofog-division</t>
   </si>
   <si>
-    <t>codeforiati:category-code</t>
-  </si>
-  <si>
-    <t>codeforiati:group-code</t>
-  </si>
-  <si>
     <t>11110</t>
   </si>
   <si>
     <t>active</t>
   </si>
   <si>
+    <t>09.8.0 - Education n.e.c. (CS)</t>
+  </si>
+  <si>
+    <t>111</t>
+  </si>
+  <si>
     <t>09.8 - Education n.e.c.</t>
   </si>
   <si>
-    <t>09.8.0 - Education n.e.c. (CS)</t>
+    <t>110</t>
   </si>
   <si>
     <t>09 - Education</t>
   </si>
   <si>
-    <t>111</t>
-  </si>
-  <si>
-    <t>110</t>
-  </si>
-  <si>
     <t>11120</t>
   </si>
   <si>
+    <t>09.6.0 - Subsidiary services to education (IS)</t>
+  </si>
+  <si>
     <t>09.6 - Subsidiary services to education</t>
   </si>
   <si>
-    <t>09.6.0 - Subsidiary services to education (IS)</t>
-  </si>
-  <si>
     <t>11130</t>
   </si>
   <si>
     <t>11182</t>
   </si>
   <si>
+    <t>09.7.0 - R&amp;D Education (CS)</t>
+  </si>
+  <si>
     <t>09.7 - R&amp;D Education</t>
   </si>
   <si>
-    <t>09.7.0 - R&amp;D Education (CS)</t>
-  </si>
-  <si>
     <t>11220</t>
   </si>
   <si>
+    <t>09.1.2 - Primary education (IS)</t>
+  </si>
+  <si>
+    <t>112</t>
+  </si>
+  <si>
     <t>09.1 - Pre‐primary and primary education</t>
   </si>
   <si>
-    <t>09.1.2 - Primary education (IS)</t>
-  </si>
-  <si>
-    <t>112</t>
-  </si>
-  <si>
     <t>11230</t>
   </si>
   <si>
@@ -109,24 +109,24 @@
     <t>11250</t>
   </si>
   <si>
+    <t>07.4.0 - Public health services (IS)</t>
+  </si>
+  <si>
     <t>07.4 - Public health services</t>
   </si>
   <si>
-    <t>07.4.0 - Public health services (IS)</t>
-  </si>
-  <si>
     <t>07 - Health</t>
   </si>
   <si>
     <t>11260</t>
   </si>
   <si>
+    <t>09.2.1 - Lower‐secondary education (IS)</t>
+  </si>
+  <si>
     <t>09.2 - Secondary education</t>
   </si>
   <si>
-    <t>09.2.1 - Lower‐secondary education (IS)</t>
-  </si>
-  <si>
     <t>11320</t>
   </si>
   <si>
@@ -139,45 +139,45 @@
     <t>11330</t>
   </si>
   <si>
+    <t>09.5.0 - Education not definable by level (IS)</t>
+  </si>
+  <si>
     <t>09.5 - Education not definable by level</t>
   </si>
   <si>
-    <t>09.5.0 - Education not definable by level (IS)</t>
-  </si>
-  <si>
     <t>11420</t>
   </si>
   <si>
+    <t>09.4.1 - First stage of tertiary education (IS)</t>
+  </si>
+  <si>
+    <t>114</t>
+  </si>
+  <si>
     <t>09.4 - Tertiary education</t>
   </si>
   <si>
-    <t>09.4.1 - First stage of tertiary education (IS)</t>
-  </si>
-  <si>
-    <t>114</t>
-  </si>
-  <si>
     <t>11430</t>
   </si>
   <si>
+    <t>09.3.0 - Post‐secondary non‐tertiary education (IS)</t>
+  </si>
+  <si>
     <t>09.3 - Post‐secondary non‐tertiary education</t>
   </si>
   <si>
-    <t>09.3.0 - Post‐secondary non‐tertiary education (IS)</t>
-  </si>
-  <si>
     <t>12110</t>
   </si>
   <si>
+    <t>07.6.0 - Health n.e.c. (CS)</t>
+  </si>
+  <si>
+    <t>121</t>
+  </si>
+  <si>
     <t>07.6 - Health n.e.c.</t>
   </si>
   <si>
-    <t>07.6.0 - Health n.e.c. (CS)</t>
-  </si>
-  <si>
-    <t>121</t>
-  </si>
-  <si>
     <t>120</t>
   </si>
   <si>
@@ -187,21 +187,21 @@
     <t>12182</t>
   </si>
   <si>
+    <t>07.5.0 - R&amp;D Health (CS)</t>
+  </si>
+  <si>
     <t>07.5 - R&amp;D Health</t>
   </si>
   <si>
-    <t>07.5.0 - R&amp;D Health (CS)</t>
-  </si>
-  <si>
     <t>12191</t>
   </si>
   <si>
+    <t>07.2.1 - General medical services (IS)</t>
+  </si>
+  <si>
     <t>07.2 - Outpatient services</t>
   </si>
   <si>
-    <t>07.2.1 - General medical services (IS)</t>
-  </si>
-  <si>
     <t>12196</t>
   </si>
   <si>
@@ -214,12 +214,12 @@
     <t>12230</t>
   </si>
   <si>
+    <t>07.3.1 - General hospital services (IS)</t>
+  </si>
+  <si>
     <t>07.3 - Hospital services</t>
   </si>
   <si>
-    <t>07.3.1 - General hospital services (IS)</t>
-  </si>
-  <si>
     <t>12240</t>
   </si>
   <si>
@@ -286,27 +286,27 @@
     <t>14010</t>
   </si>
   <si>
+    <t>06.3.0 - Water supply (CS)</t>
+  </si>
+  <si>
     <t>06.3 - Water supply</t>
   </si>
   <si>
-    <t>06.3.0 - Water supply (CS)</t>
+    <t>140</t>
   </si>
   <si>
     <t>06 - Housing and community amenities</t>
   </si>
   <si>
-    <t>140</t>
-  </si>
-  <si>
     <t>14015</t>
   </si>
   <si>
+    <t>05.6.0 - Environmental protection n.e.c. (CS)</t>
+  </si>
+  <si>
     <t>05.6 - Environmental protection n.e.c.</t>
   </si>
   <si>
-    <t>05.6.0 - Environmental protection n.e.c. (CS)</t>
-  </si>
-  <si>
     <t>05 - Environmental protection</t>
   </si>
   <si>
@@ -319,12 +319,12 @@
     <t>14022</t>
   </si>
   <si>
+    <t>05.2.0 - Waste water management (CS)</t>
+  </si>
+  <si>
     <t>05.2 - Waste water management</t>
   </si>
   <si>
-    <t>05.2.0 - Waste water management (CS)</t>
-  </si>
-  <si>
     <t>14030</t>
   </si>
   <si>
@@ -340,60 +340,60 @@
     <t>14050</t>
   </si>
   <si>
+    <t>05.1.0 - Waste management (CS)</t>
+  </si>
+  <si>
     <t>05.1 - Waste management</t>
   </si>
   <si>
-    <t>05.1.0 - Waste management (CS)</t>
-  </si>
-  <si>
     <t>14081</t>
   </si>
   <si>
     <t>15110</t>
   </si>
   <si>
+    <t>01.3.1 - General personnel services (CS)</t>
+  </si>
+  <si>
+    <t>151</t>
+  </si>
+  <si>
     <t>01.3 - General services</t>
   </si>
   <si>
-    <t>01.3.1 - General personnel services (CS)</t>
+    <t>150</t>
   </si>
   <si>
     <t>01 - General public services</t>
   </si>
   <si>
-    <t>151</t>
-  </si>
-  <si>
-    <t>150</t>
-  </si>
-  <si>
     <t>15111</t>
   </si>
   <si>
+    <t>01.1.2 - Financial and fiscal affairs (CS)</t>
+  </si>
+  <si>
     <t>01.1 - Executive and legislative organs, financial and fiscal affairs, external affairs</t>
   </si>
   <si>
-    <t>01.1.2 - Financial and fiscal affairs (CS)</t>
-  </si>
-  <si>
     <t>15112</t>
   </si>
   <si>
+    <t>01.8.0 - Transfers of a general character between different levels of government (CS)</t>
+  </si>
+  <si>
     <t>01.8 - Transfers of a general character between different levels of government</t>
   </si>
   <si>
-    <t>01.8.0 - Transfers of a general character between different levels of government (CS)</t>
-  </si>
-  <si>
     <t>15113</t>
   </si>
   <si>
+    <t>03.6.0 - Public order and safety n.e.c. (CS)</t>
+  </si>
+  <si>
     <t>03.6 - Public order and safety n.e.c.</t>
   </si>
   <si>
-    <t>03.6.0 - Public order and safety n.e.c. (CS)</t>
-  </si>
-  <si>
     <t>03 - Public order and safety</t>
   </si>
   <si>
@@ -424,12 +424,12 @@
     <t>15123</t>
   </si>
   <si>
+    <t>01.2.2 - Economic aid routed through international organizations (CS)</t>
+  </si>
+  <si>
     <t>01.2 - Foreign economic aid</t>
   </si>
   <si>
-    <t>01.2.2 - Economic aid routed through international organizations (CS)</t>
-  </si>
-  <si>
     <t>15124</t>
   </si>
   <si>
@@ -460,30 +460,30 @@
     <t>15131</t>
   </si>
   <si>
+    <t>03.3.0 - Law courts (CS)</t>
+  </si>
+  <si>
     <t>03.3 - Law courts</t>
   </si>
   <si>
-    <t>03.3.0 - Law courts (CS)</t>
-  </si>
-  <si>
     <t>15132</t>
   </si>
   <si>
+    <t>03.1.0 - Police services (CS)</t>
+  </si>
+  <si>
     <t>03.1 - Police services</t>
   </si>
   <si>
-    <t>03.1.0 - Police services (CS)</t>
-  </si>
-  <si>
     <t>15133</t>
   </si>
   <si>
+    <t>03.2.0 - Fire‐protection services (CS)</t>
+  </si>
+  <si>
     <t>03.2 - Fire‐protection services</t>
   </si>
   <si>
-    <t>03.2.0 - Fire‐protection services (CS)</t>
-  </si>
-  <si>
     <t>15134</t>
   </si>
   <si>
@@ -496,21 +496,21 @@
     <t>15137</t>
   </si>
   <si>
+    <t>03.4.0 - Prisons (CS)</t>
+  </si>
+  <si>
     <t>03.4 - Prisons</t>
   </si>
   <si>
-    <t>03.4.0 - Prisons (CS)</t>
-  </si>
-  <si>
     <t>15142</t>
   </si>
   <si>
+    <t>04.1.1 - General economic and commercial affairs (CS)</t>
+  </si>
+  <si>
     <t>04.1 - General economic, commercial and labour affairs</t>
   </si>
   <si>
-    <t>04.1.1 - General economic and commercial affairs (CS)</t>
-  </si>
-  <si>
     <t>04 - Economic affairs</t>
   </si>
   <si>
@@ -526,12 +526,12 @@
     <t>15151</t>
   </si>
   <si>
+    <t>01.6.0 - General public services n.e.c. (CS)</t>
+  </si>
+  <si>
     <t>01.6 - General public services n.e.c.</t>
   </si>
   <si>
-    <t>01.6.0 - General public services n.e.c. (CS)</t>
-  </si>
-  <si>
     <t>15152</t>
   </si>
   <si>
@@ -541,12 +541,12 @@
     <t>15153</t>
   </si>
   <si>
+    <t>04.6.0 - Communication (CS)</t>
+  </si>
+  <si>
     <t>04.6 - Communication</t>
   </si>
   <si>
-    <t>04.6.0 - Communication (CS)</t>
-  </si>
-  <si>
     <t>15154</t>
   </si>
   <si>
@@ -562,12 +562,12 @@
     <t>15170</t>
   </si>
   <si>
+    <t>10.7.0 - Social exclusion n.e.c. (IS)</t>
+  </si>
+  <si>
     <t>10.7 - Social exclusion n.e.c.</t>
   </si>
   <si>
-    <t>10.7.0 - Social exclusion n.e.c. (IS)</t>
-  </si>
-  <si>
     <t>10 - Social protection</t>
   </si>
   <si>
@@ -583,12 +583,12 @@
     <t>15196</t>
   </si>
   <si>
+    <t>01.5.0 - R&amp;D General public services (CS)</t>
+  </si>
+  <si>
     <t>01.5 - R&amp;D General public services</t>
   </si>
   <si>
-    <t>01.5.0 - R&amp;D General public services (CS)</t>
-  </si>
-  <si>
     <t>15210</t>
   </si>
   <si>
@@ -601,12 +601,12 @@
     <t>15230</t>
   </si>
   <si>
+    <t>02.3.0 - Foreign military aid (CS)</t>
+  </si>
+  <si>
     <t>02.3 - Foreign military aid</t>
   </si>
   <si>
-    <t>02.3.0 - Foreign military aid (CS)</t>
-  </si>
-  <si>
     <t>02 - Defence</t>
   </si>
   <si>
@@ -622,12 +622,12 @@
     <t>16010</t>
   </si>
   <si>
+    <t>10.9.0 - Social protection n.e.c. (CS)</t>
+  </si>
+  <si>
     <t>10.9 - Social protection n.e.c.</t>
   </si>
   <si>
-    <t>10.9.0 - Social protection n.e.c. (CS)</t>
-  </si>
-  <si>
     <t>160</t>
   </si>
   <si>
@@ -640,12 +640,12 @@
     <t>16013</t>
   </si>
   <si>
+    <t>10.2.0 - Old age (IS)</t>
+  </si>
+  <si>
     <t>10.2 - Old age</t>
   </si>
   <si>
-    <t>10.2.0 - Old age (IS)</t>
-  </si>
-  <si>
     <t>16014</t>
   </si>
   <si>
@@ -655,42 +655,42 @@
     <t>16020</t>
   </si>
   <si>
+    <t>10.5.0 - Unemployment (IS)</t>
+  </si>
+  <si>
     <t>10.5 - Unemployment</t>
   </si>
   <si>
-    <t>10.5.0 - Unemployment (IS)</t>
-  </si>
-  <si>
     <t>16030</t>
   </si>
   <si>
+    <t>06.6.0 - Housing and community amenities n.e.c. (CS)</t>
+  </si>
+  <si>
     <t>06.6 - Housing and community amenities n.e.c.</t>
   </si>
   <si>
-    <t>06.6.0 - Housing and community amenities n.e.c. (CS)</t>
-  </si>
-  <si>
     <t>16040</t>
   </si>
   <si>
+    <t>06.1.0 - Housing development (CS)</t>
+  </si>
+  <si>
     <t>06.1 - Housing development</t>
   </si>
   <si>
-    <t>06.1.0 - Housing development (CS)</t>
-  </si>
-  <si>
     <t>16050</t>
   </si>
   <si>
     <t>16061</t>
   </si>
   <si>
+    <t>08.2.0 - Cultural services (IS)</t>
+  </si>
+  <si>
     <t>08.2 - Cultural services</t>
   </si>
   <si>
-    <t>08.2.0 - Cultural services (IS)</t>
-  </si>
-  <si>
     <t>08 - Recreation, culture and religion</t>
   </si>
   <si>
@@ -706,12 +706,12 @@
     <t>16065</t>
   </si>
   <si>
+    <t>08.1.0 - Recreational and sporting services (IS)</t>
+  </si>
+  <si>
     <t>08.1 - Recreational and sporting services</t>
   </si>
   <si>
-    <t>08.1.0 - Recreational and sporting services (IS)</t>
-  </si>
-  <si>
     <t>16066</t>
   </si>
   <si>
@@ -742,12 +742,12 @@
     <t>21020</t>
   </si>
   <si>
+    <t>04.5.1 - Road transport (CS)</t>
+  </si>
+  <si>
     <t>04.5 - Transport</t>
   </si>
   <si>
-    <t>04.5.1 - Road transport (CS)</t>
-  </si>
-  <si>
     <t>21021</t>
   </si>
   <si>
@@ -781,12 +781,12 @@
     <t>21061</t>
   </si>
   <si>
+    <t>04.7.1 - Distributive trades, storage and warehousing (CS)</t>
+  </si>
+  <si>
     <t>04.7 - Other industries</t>
   </si>
   <si>
-    <t>04.7.1 - Distributive trades, storage and warehousing (CS)</t>
-  </si>
-  <si>
     <t>21081</t>
   </si>
   <si>
@@ -811,27 +811,27 @@
     <t>22030</t>
   </si>
   <si>
+    <t>08.3.0 - Broadcasting and publishing services (CS)</t>
+  </si>
+  <si>
     <t>08.3 - Broadcasting and publishing services</t>
   </si>
   <si>
-    <t>08.3.0 - Broadcasting and publishing services (CS)</t>
-  </si>
-  <si>
     <t>22040</t>
   </si>
   <si>
     <t>23110</t>
   </si>
   <si>
+    <t>04.3.5 - Electricity (CS)</t>
+  </si>
+  <si>
+    <t>231</t>
+  </si>
+  <si>
     <t>04.3 - Fuel and energy</t>
   </si>
   <si>
-    <t>04.3.5 - Electricity (CS)</t>
-  </si>
-  <si>
-    <t>231</t>
-  </si>
-  <si>
     <t>230</t>
   </si>
   <si>
@@ -841,12 +841,12 @@
     <t>23112</t>
   </si>
   <si>
+    <t>04.8.3 - R&amp;D Fuel and energy (CS)</t>
+  </si>
+  <si>
     <t>04.8 - R&amp;D Economic affairs</t>
   </si>
   <si>
-    <t>04.8.3 - R&amp;D Fuel and energy (CS)</t>
-  </si>
-  <si>
     <t>23181</t>
   </si>
   <si>
@@ -991,15 +991,15 @@
     <t>31110</t>
   </si>
   <si>
+    <t>04.2.1 - Agriculture (CS)</t>
+  </si>
+  <si>
+    <t>311</t>
+  </si>
+  <si>
     <t>04.2 - Agriculture, forestry, fishing and hunting</t>
   </si>
   <si>
-    <t>04.2.1 - Agriculture (CS)</t>
-  </si>
-  <si>
-    <t>311</t>
-  </si>
-  <si>
     <t>310</t>
   </si>
   <si>
@@ -1105,15 +1105,15 @@
     <t>32110</t>
   </si>
   <si>
+    <t>04.4.2 - Manufacturing (CS)</t>
+  </si>
+  <si>
+    <t>321</t>
+  </si>
+  <si>
     <t>04.4 - Mining, manufacturing and construction</t>
   </si>
   <si>
-    <t>04.4.2 - Manufacturing (CS)</t>
-  </si>
-  <si>
-    <t>321</t>
-  </si>
-  <si>
     <t>320</t>
   </si>
   <si>
@@ -1261,12 +1261,12 @@
     <t>41030</t>
   </si>
   <si>
+    <t>05.4.0 - Protection of biodiversity and landscape (CS)</t>
+  </si>
+  <si>
     <t>05.4 - Protection of biodiversity and landscape</t>
   </si>
   <si>
-    <t>05.4.0 - Protection of biodiversity and landscape (CS)</t>
-  </si>
-  <si>
     <t>41040</t>
   </si>
   <si>
@@ -1279,12 +1279,12 @@
     <t>43010</t>
   </si>
   <si>
+    <t>04.9.0 - Economic affairs n.e.c. (CS)</t>
+  </si>
+  <si>
     <t>04.9 - Economic affairs n.e.c.</t>
   </si>
   <si>
-    <t>04.9.0 - Economic affairs n.e.c. (CS)</t>
-  </si>
-  <si>
     <t>430</t>
   </si>
   <si>
@@ -1294,12 +1294,12 @@
     <t>43031</t>
   </si>
   <si>
+    <t>06.2.0 - Community development (CS)</t>
+  </si>
+  <si>
     <t>06.2 - Community development</t>
   </si>
   <si>
-    <t>06.2.0 - Community development (CS)</t>
-  </si>
-  <si>
     <t>43032</t>
   </si>
   <si>
@@ -1318,24 +1318,24 @@
     <t>43060</t>
   </si>
   <si>
+    <t>02.2.0 - Civil defence (CS)</t>
+  </si>
+  <si>
     <t>02.2 - Civil defence</t>
   </si>
   <si>
-    <t>02.2.0 - Civil defence (CS)</t>
-  </si>
-  <si>
     <t>43071</t>
   </si>
   <si>
     <t>43072</t>
   </si>
   <si>
+    <t>10.4.0 - Family and children (IS)</t>
+  </si>
+  <si>
     <t>10.4 - Family and children</t>
   </si>
   <si>
-    <t>10.4.0 - Family and children (IS)</t>
-  </si>
-  <si>
     <t>43073</t>
   </si>
   <si>
@@ -1345,12 +1345,12 @@
     <t>43082</t>
   </si>
   <si>
+    <t>01.4.0 - Basic research (CS)</t>
+  </si>
+  <si>
     <t>01.4 - Basic research</t>
   </si>
   <si>
-    <t>01.4.0 - Basic research (CS)</t>
-  </si>
-  <si>
     <t>51010</t>
   </si>
   <si>
@@ -1375,10 +1375,10 @@
     <t>60010</t>
   </si>
   <si>
+    <t>01.7.0 - Public debt transactions (CS)</t>
+  </si>
+  <si>
     <t>01.7 - Public debt transactions</t>
-  </si>
-  <si>
-    <t>01.7.0 - Public debt transactions (CS)</t>
   </si>
   <si>
     <t>600</t>
@@ -1866,10 +1866,10 @@
         <v>15</v>
       </c>
       <c r="D3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E3" t="s">
         <v>16</v>
-      </c>
-      <c r="E3" t="s">
-        <v>11</v>
       </c>
       <c r="F3" t="s">
         <v>12</v>
@@ -1912,10 +1912,10 @@
         <v>19</v>
       </c>
       <c r="D5" t="s">
+        <v>10</v>
+      </c>
+      <c r="E5" t="s">
         <v>20</v>
-      </c>
-      <c r="E5" t="s">
-        <v>11</v>
       </c>
       <c r="F5" t="s">
         <v>12</v>
@@ -1938,10 +1938,10 @@
         <v>23</v>
       </c>
       <c r="E6" t="s">
-        <v>11</v>
+        <v>24</v>
       </c>
       <c r="F6" t="s">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="G6" t="s">
         <v>13</v>
@@ -1958,13 +1958,13 @@
         <v>9</v>
       </c>
       <c r="D7" t="s">
-        <v>10</v>
+        <v>23</v>
       </c>
       <c r="E7" t="s">
         <v>11</v>
       </c>
       <c r="F7" t="s">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="G7" t="s">
         <v>13</v>
@@ -1984,10 +1984,10 @@
         <v>23</v>
       </c>
       <c r="E8" t="s">
-        <v>11</v>
+        <v>24</v>
       </c>
       <c r="F8" t="s">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="G8" t="s">
         <v>13</v>
@@ -2007,10 +2007,10 @@
         <v>23</v>
       </c>
       <c r="E9" t="s">
-        <v>11</v>
+        <v>24</v>
       </c>
       <c r="F9" t="s">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="G9" t="s">
         <v>13</v>
@@ -2024,16 +2024,16 @@
         <v>8</v>
       </c>
       <c r="C10" t="s">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="D10" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="E10" t="s">
-        <v>11</v>
+        <v>24</v>
       </c>
       <c r="F10" t="s">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="G10" t="s">
         <v>13</v>
@@ -2050,16 +2050,16 @@
         <v>31</v>
       </c>
       <c r="D11" t="s">
+        <v>23</v>
+      </c>
+      <c r="E11" t="s">
         <v>32</v>
       </c>
-      <c r="E11" t="s">
+      <c r="F11" t="s">
+        <v>12</v>
+      </c>
+      <c r="G11" t="s">
         <v>33</v>
-      </c>
-      <c r="F11" t="s">
-        <v>24</v>
-      </c>
-      <c r="G11" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -2073,13 +2073,13 @@
         <v>35</v>
       </c>
       <c r="D12" t="s">
+        <v>23</v>
+      </c>
+      <c r="E12" t="s">
         <v>36</v>
       </c>
-      <c r="E12" t="s">
-        <v>11</v>
-      </c>
       <c r="F12" t="s">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="G12" t="s">
         <v>13</v>
@@ -2093,16 +2093,16 @@
         <v>8</v>
       </c>
       <c r="C13" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="D13" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="E13" t="s">
-        <v>11</v>
+        <v>36</v>
       </c>
       <c r="F13" t="s">
-        <v>39</v>
+        <v>12</v>
       </c>
       <c r="G13" t="s">
         <v>13</v>
@@ -2119,13 +2119,13 @@
         <v>41</v>
       </c>
       <c r="D14" t="s">
+        <v>39</v>
+      </c>
+      <c r="E14" t="s">
         <v>42</v>
       </c>
-      <c r="E14" t="s">
-        <v>11</v>
-      </c>
       <c r="F14" t="s">
-        <v>39</v>
+        <v>12</v>
       </c>
       <c r="G14" t="s">
         <v>13</v>
@@ -2145,10 +2145,10 @@
         <v>45</v>
       </c>
       <c r="E15" t="s">
-        <v>11</v>
+        <v>46</v>
       </c>
       <c r="F15" t="s">
-        <v>46</v>
+        <v>12</v>
       </c>
       <c r="G15" t="s">
         <v>13</v>
@@ -2165,13 +2165,13 @@
         <v>48</v>
       </c>
       <c r="D16" t="s">
+        <v>45</v>
+      </c>
+      <c r="E16" t="s">
         <v>49</v>
       </c>
-      <c r="E16" t="s">
-        <v>11</v>
-      </c>
       <c r="F16" t="s">
-        <v>46</v>
+        <v>12</v>
       </c>
       <c r="G16" t="s">
         <v>13</v>
@@ -2191,13 +2191,13 @@
         <v>52</v>
       </c>
       <c r="E17" t="s">
+        <v>53</v>
+      </c>
+      <c r="F17" t="s">
+        <v>54</v>
+      </c>
+      <c r="G17" t="s">
         <v>33</v>
-      </c>
-      <c r="F17" t="s">
-        <v>53</v>
-      </c>
-      <c r="G17" t="s">
-        <v>54</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -2214,13 +2214,13 @@
         <v>52</v>
       </c>
       <c r="E18" t="s">
+        <v>53</v>
+      </c>
+      <c r="F18" t="s">
+        <v>54</v>
+      </c>
+      <c r="G18" t="s">
         <v>33</v>
-      </c>
-      <c r="F18" t="s">
-        <v>53</v>
-      </c>
-      <c r="G18" t="s">
-        <v>54</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -2234,16 +2234,16 @@
         <v>57</v>
       </c>
       <c r="D19" t="s">
+        <v>52</v>
+      </c>
+      <c r="E19" t="s">
         <v>58</v>
       </c>
-      <c r="E19" t="s">
+      <c r="F19" t="s">
+        <v>54</v>
+      </c>
+      <c r="G19" t="s">
         <v>33</v>
-      </c>
-      <c r="F19" t="s">
-        <v>53</v>
-      </c>
-      <c r="G19" t="s">
-        <v>54</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -2257,16 +2257,16 @@
         <v>60</v>
       </c>
       <c r="D20" t="s">
+        <v>52</v>
+      </c>
+      <c r="E20" t="s">
         <v>61</v>
       </c>
-      <c r="E20" t="s">
+      <c r="F20" t="s">
+        <v>54</v>
+      </c>
+      <c r="G20" t="s">
         <v>33</v>
-      </c>
-      <c r="F20" t="s">
-        <v>53</v>
-      </c>
-      <c r="G20" t="s">
-        <v>54</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -2283,13 +2283,13 @@
         <v>52</v>
       </c>
       <c r="E21" t="s">
+        <v>53</v>
+      </c>
+      <c r="F21" t="s">
+        <v>54</v>
+      </c>
+      <c r="G21" t="s">
         <v>33</v>
-      </c>
-      <c r="F21" t="s">
-        <v>53</v>
-      </c>
-      <c r="G21" t="s">
-        <v>54</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -2303,16 +2303,16 @@
         <v>31</v>
       </c>
       <c r="D22" t="s">
+        <v>64</v>
+      </c>
+      <c r="E22" t="s">
         <v>32</v>
       </c>
-      <c r="E22" t="s">
+      <c r="F22" t="s">
+        <v>54</v>
+      </c>
+      <c r="G22" t="s">
         <v>33</v>
-      </c>
-      <c r="F22" t="s">
-        <v>64</v>
-      </c>
-      <c r="G22" t="s">
-        <v>54</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -2326,16 +2326,16 @@
         <v>66</v>
       </c>
       <c r="D23" t="s">
+        <v>64</v>
+      </c>
+      <c r="E23" t="s">
         <v>67</v>
       </c>
-      <c r="E23" t="s">
+      <c r="F23" t="s">
+        <v>54</v>
+      </c>
+      <c r="G23" t="s">
         <v>33</v>
-      </c>
-      <c r="F23" t="s">
-        <v>64</v>
-      </c>
-      <c r="G23" t="s">
-        <v>54</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -2349,16 +2349,16 @@
         <v>31</v>
       </c>
       <c r="D24" t="s">
+        <v>64</v>
+      </c>
+      <c r="E24" t="s">
         <v>32</v>
       </c>
-      <c r="E24" t="s">
+      <c r="F24" t="s">
+        <v>54</v>
+      </c>
+      <c r="G24" t="s">
         <v>33</v>
-      </c>
-      <c r="F24" t="s">
-        <v>64</v>
-      </c>
-      <c r="G24" t="s">
-        <v>54</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -2372,16 +2372,16 @@
         <v>31</v>
       </c>
       <c r="D25" t="s">
+        <v>64</v>
+      </c>
+      <c r="E25" t="s">
         <v>32</v>
       </c>
-      <c r="E25" t="s">
+      <c r="F25" t="s">
+        <v>54</v>
+      </c>
+      <c r="G25" t="s">
         <v>33</v>
-      </c>
-      <c r="F25" t="s">
-        <v>64</v>
-      </c>
-      <c r="G25" t="s">
-        <v>54</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -2395,16 +2395,16 @@
         <v>31</v>
       </c>
       <c r="D26" t="s">
+        <v>64</v>
+      </c>
+      <c r="E26" t="s">
         <v>32</v>
       </c>
-      <c r="E26" t="s">
+      <c r="F26" t="s">
+        <v>54</v>
+      </c>
+      <c r="G26" t="s">
         <v>33</v>
-      </c>
-      <c r="F26" t="s">
-        <v>64</v>
-      </c>
-      <c r="G26" t="s">
-        <v>54</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -2418,16 +2418,16 @@
         <v>31</v>
       </c>
       <c r="D27" t="s">
+        <v>64</v>
+      </c>
+      <c r="E27" t="s">
         <v>32</v>
       </c>
-      <c r="E27" t="s">
+      <c r="F27" t="s">
+        <v>54</v>
+      </c>
+      <c r="G27" t="s">
         <v>33</v>
-      </c>
-      <c r="F27" t="s">
-        <v>64</v>
-      </c>
-      <c r="G27" t="s">
-        <v>54</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -2441,16 +2441,16 @@
         <v>31</v>
       </c>
       <c r="D28" t="s">
+        <v>64</v>
+      </c>
+      <c r="E28" t="s">
         <v>32</v>
       </c>
-      <c r="E28" t="s">
+      <c r="F28" t="s">
+        <v>54</v>
+      </c>
+      <c r="G28" t="s">
         <v>33</v>
-      </c>
-      <c r="F28" t="s">
-        <v>64</v>
-      </c>
-      <c r="G28" t="s">
-        <v>54</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -2464,16 +2464,16 @@
         <v>31</v>
       </c>
       <c r="D29" t="s">
+        <v>64</v>
+      </c>
+      <c r="E29" t="s">
         <v>32</v>
       </c>
-      <c r="E29" t="s">
+      <c r="F29" t="s">
+        <v>54</v>
+      </c>
+      <c r="G29" t="s">
         <v>33</v>
-      </c>
-      <c r="F29" t="s">
-        <v>64</v>
-      </c>
-      <c r="G29" t="s">
-        <v>54</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -2487,16 +2487,16 @@
         <v>51</v>
       </c>
       <c r="D30" t="s">
-        <v>52</v>
+        <v>64</v>
       </c>
       <c r="E30" t="s">
+        <v>53</v>
+      </c>
+      <c r="F30" t="s">
+        <v>54</v>
+      </c>
+      <c r="G30" t="s">
         <v>33</v>
-      </c>
-      <c r="F30" t="s">
-        <v>64</v>
-      </c>
-      <c r="G30" t="s">
-        <v>54</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -2510,16 +2510,16 @@
         <v>31</v>
       </c>
       <c r="D31" t="s">
+        <v>76</v>
+      </c>
+      <c r="E31" t="s">
         <v>32</v>
       </c>
-      <c r="E31" t="s">
+      <c r="F31" t="s">
+        <v>54</v>
+      </c>
+      <c r="G31" t="s">
         <v>33</v>
-      </c>
-      <c r="F31" t="s">
-        <v>76</v>
-      </c>
-      <c r="G31" t="s">
-        <v>54</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -2533,16 +2533,16 @@
         <v>31</v>
       </c>
       <c r="D32" t="s">
+        <v>76</v>
+      </c>
+      <c r="E32" t="s">
         <v>32</v>
       </c>
-      <c r="E32" t="s">
+      <c r="F32" t="s">
+        <v>54</v>
+      </c>
+      <c r="G32" t="s">
         <v>33</v>
-      </c>
-      <c r="F32" t="s">
-        <v>76</v>
-      </c>
-      <c r="G32" t="s">
-        <v>54</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -2556,16 +2556,16 @@
         <v>31</v>
       </c>
       <c r="D33" t="s">
+        <v>76</v>
+      </c>
+      <c r="E33" t="s">
         <v>32</v>
       </c>
-      <c r="E33" t="s">
+      <c r="F33" t="s">
+        <v>54</v>
+      </c>
+      <c r="G33" t="s">
         <v>33</v>
-      </c>
-      <c r="F33" t="s">
-        <v>76</v>
-      </c>
-      <c r="G33" t="s">
-        <v>54</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -2579,16 +2579,16 @@
         <v>31</v>
       </c>
       <c r="D34" t="s">
+        <v>76</v>
+      </c>
+      <c r="E34" t="s">
         <v>32</v>
       </c>
-      <c r="E34" t="s">
+      <c r="F34" t="s">
+        <v>54</v>
+      </c>
+      <c r="G34" t="s">
         <v>33</v>
-      </c>
-      <c r="F34" t="s">
-        <v>76</v>
-      </c>
-      <c r="G34" t="s">
-        <v>54</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -2602,16 +2602,16 @@
         <v>31</v>
       </c>
       <c r="D35" t="s">
+        <v>76</v>
+      </c>
+      <c r="E35" t="s">
         <v>32</v>
       </c>
-      <c r="E35" t="s">
+      <c r="F35" t="s">
+        <v>54</v>
+      </c>
+      <c r="G35" t="s">
         <v>33</v>
-      </c>
-      <c r="F35" t="s">
-        <v>76</v>
-      </c>
-      <c r="G35" t="s">
-        <v>54</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -2625,16 +2625,16 @@
         <v>57</v>
       </c>
       <c r="D36" t="s">
+        <v>76</v>
+      </c>
+      <c r="E36" t="s">
         <v>58</v>
       </c>
-      <c r="E36" t="s">
+      <c r="F36" t="s">
+        <v>54</v>
+      </c>
+      <c r="G36" t="s">
         <v>33</v>
-      </c>
-      <c r="F36" t="s">
-        <v>76</v>
-      </c>
-      <c r="G36" t="s">
-        <v>54</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -2647,14 +2647,14 @@
       <c r="C37" t="s">
         <v>31</v>
       </c>
-      <c r="D37" t="s">
+      <c r="E37" t="s">
         <v>32</v>
       </c>
-      <c r="E37" t="s">
+      <c r="F37" t="s">
+        <v>83</v>
+      </c>
+      <c r="G37" t="s">
         <v>33</v>
-      </c>
-      <c r="G37" t="s">
-        <v>83</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -2667,14 +2667,14 @@
       <c r="C38" t="s">
         <v>31</v>
       </c>
-      <c r="D38" t="s">
+      <c r="E38" t="s">
         <v>32</v>
       </c>
-      <c r="E38" t="s">
+      <c r="F38" t="s">
+        <v>83</v>
+      </c>
+      <c r="G38" t="s">
         <v>33</v>
-      </c>
-      <c r="G38" t="s">
-        <v>83</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -2687,14 +2687,14 @@
       <c r="C39" t="s">
         <v>31</v>
       </c>
-      <c r="D39" t="s">
+      <c r="E39" t="s">
         <v>32</v>
       </c>
-      <c r="E39" t="s">
+      <c r="F39" t="s">
+        <v>83</v>
+      </c>
+      <c r="G39" t="s">
         <v>33</v>
-      </c>
-      <c r="G39" t="s">
-        <v>83</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -2707,14 +2707,14 @@
       <c r="C40" t="s">
         <v>31</v>
       </c>
-      <c r="D40" t="s">
+      <c r="E40" t="s">
         <v>32</v>
       </c>
-      <c r="E40" t="s">
+      <c r="F40" t="s">
+        <v>83</v>
+      </c>
+      <c r="G40" t="s">
         <v>33</v>
-      </c>
-      <c r="G40" t="s">
-        <v>83</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -2727,14 +2727,14 @@
       <c r="C41" t="s">
         <v>51</v>
       </c>
-      <c r="D41" t="s">
-        <v>52</v>
-      </c>
       <c r="E41" t="s">
+        <v>53</v>
+      </c>
+      <c r="F41" t="s">
+        <v>83</v>
+      </c>
+      <c r="G41" t="s">
         <v>33</v>
-      </c>
-      <c r="G41" t="s">
-        <v>83</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -2747,14 +2747,14 @@
       <c r="C42" t="s">
         <v>57</v>
       </c>
-      <c r="D42" t="s">
+      <c r="E42" t="s">
         <v>58</v>
       </c>
-      <c r="E42" t="s">
+      <c r="F42" t="s">
+        <v>83</v>
+      </c>
+      <c r="G42" t="s">
         <v>33</v>
-      </c>
-      <c r="G42" t="s">
-        <v>83</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -2767,10 +2767,10 @@
       <c r="C43" t="s">
         <v>90</v>
       </c>
-      <c r="D43" t="s">
+      <c r="E43" t="s">
         <v>91</v>
       </c>
-      <c r="E43" t="s">
+      <c r="F43" t="s">
         <v>92</v>
       </c>
       <c r="G43" t="s">
@@ -2787,14 +2787,14 @@
       <c r="C44" t="s">
         <v>95</v>
       </c>
-      <c r="D44" t="s">
+      <c r="E44" t="s">
         <v>96</v>
       </c>
-      <c r="E44" t="s">
+      <c r="F44" t="s">
+        <v>92</v>
+      </c>
+      <c r="G44" t="s">
         <v>97</v>
-      </c>
-      <c r="G44" t="s">
-        <v>93</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -2807,10 +2807,10 @@
       <c r="C45" t="s">
         <v>90</v>
       </c>
-      <c r="D45" t="s">
+      <c r="E45" t="s">
         <v>91</v>
       </c>
-      <c r="E45" t="s">
+      <c r="F45" t="s">
         <v>92</v>
       </c>
       <c r="G45" t="s">
@@ -2827,10 +2827,10 @@
       <c r="C46" t="s">
         <v>90</v>
       </c>
-      <c r="D46" t="s">
+      <c r="E46" t="s">
         <v>91</v>
       </c>
-      <c r="E46" t="s">
+      <c r="F46" t="s">
         <v>92</v>
       </c>
       <c r="G46" t="s">
@@ -2847,14 +2847,14 @@
       <c r="C47" t="s">
         <v>101</v>
       </c>
-      <c r="D47" t="s">
+      <c r="E47" t="s">
         <v>102</v>
       </c>
-      <c r="E47" t="s">
+      <c r="F47" t="s">
+        <v>92</v>
+      </c>
+      <c r="G47" t="s">
         <v>97</v>
-      </c>
-      <c r="G47" t="s">
-        <v>93</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -2867,10 +2867,10 @@
       <c r="C48" t="s">
         <v>90</v>
       </c>
-      <c r="D48" t="s">
+      <c r="E48" t="s">
         <v>91</v>
       </c>
-      <c r="E48" t="s">
+      <c r="F48" t="s">
         <v>92</v>
       </c>
       <c r="G48" t="s">
@@ -2887,10 +2887,10 @@
       <c r="C49" t="s">
         <v>90</v>
       </c>
-      <c r="D49" t="s">
+      <c r="E49" t="s">
         <v>91</v>
       </c>
-      <c r="E49" t="s">
+      <c r="F49" t="s">
         <v>92</v>
       </c>
       <c r="G49" t="s">
@@ -2907,14 +2907,14 @@
       <c r="C50" t="s">
         <v>101</v>
       </c>
-      <c r="D50" t="s">
+      <c r="E50" t="s">
         <v>102</v>
       </c>
-      <c r="E50" t="s">
+      <c r="F50" t="s">
+        <v>92</v>
+      </c>
+      <c r="G50" t="s">
         <v>97</v>
-      </c>
-      <c r="G50" t="s">
-        <v>93</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -2927,10 +2927,10 @@
       <c r="C51" t="s">
         <v>90</v>
       </c>
-      <c r="D51" t="s">
+      <c r="E51" t="s">
         <v>91</v>
       </c>
-      <c r="E51" t="s">
+      <c r="F51" t="s">
         <v>92</v>
       </c>
       <c r="G51" t="s">
@@ -2947,14 +2947,14 @@
       <c r="C52" t="s">
         <v>108</v>
       </c>
-      <c r="D52" t="s">
+      <c r="E52" t="s">
         <v>109</v>
       </c>
-      <c r="E52" t="s">
+      <c r="F52" t="s">
+        <v>92</v>
+      </c>
+      <c r="G52" t="s">
         <v>97</v>
-      </c>
-      <c r="G52" t="s">
-        <v>93</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -2967,14 +2967,14 @@
       <c r="C53" t="s">
         <v>9</v>
       </c>
-      <c r="D53" t="s">
-        <v>10</v>
-      </c>
       <c r="E53" t="s">
         <v>11</v>
       </c>
+      <c r="F53" t="s">
+        <v>92</v>
+      </c>
       <c r="G53" t="s">
-        <v>93</v>
+        <v>13</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -3011,10 +3011,10 @@
         <v>118</v>
       </c>
       <c r="D55" t="s">
+        <v>113</v>
+      </c>
+      <c r="E55" t="s">
         <v>119</v>
-      </c>
-      <c r="E55" t="s">
-        <v>114</v>
       </c>
       <c r="F55" t="s">
         <v>115</v>
@@ -3034,10 +3034,10 @@
         <v>121</v>
       </c>
       <c r="D56" t="s">
+        <v>113</v>
+      </c>
+      <c r="E56" t="s">
         <v>122</v>
-      </c>
-      <c r="E56" t="s">
-        <v>114</v>
       </c>
       <c r="F56" t="s">
         <v>115</v>
@@ -3057,16 +3057,16 @@
         <v>124</v>
       </c>
       <c r="D57" t="s">
+        <v>113</v>
+      </c>
+      <c r="E57" t="s">
         <v>125</v>
-      </c>
-      <c r="E57" t="s">
-        <v>126</v>
       </c>
       <c r="F57" t="s">
         <v>115</v>
       </c>
       <c r="G57" t="s">
-        <v>116</v>
+        <v>126</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -3080,10 +3080,10 @@
         <v>118</v>
       </c>
       <c r="D58" t="s">
+        <v>113</v>
+      </c>
+      <c r="E58" t="s">
         <v>119</v>
-      </c>
-      <c r="E58" t="s">
-        <v>114</v>
       </c>
       <c r="F58" t="s">
         <v>115</v>
@@ -3103,10 +3103,10 @@
         <v>118</v>
       </c>
       <c r="D59" t="s">
+        <v>113</v>
+      </c>
+      <c r="E59" t="s">
         <v>119</v>
-      </c>
-      <c r="E59" t="s">
-        <v>114</v>
       </c>
       <c r="F59" t="s">
         <v>115</v>
@@ -3126,10 +3126,10 @@
         <v>118</v>
       </c>
       <c r="D60" t="s">
+        <v>113</v>
+      </c>
+      <c r="E60" t="s">
         <v>119</v>
-      </c>
-      <c r="E60" t="s">
-        <v>114</v>
       </c>
       <c r="F60" t="s">
         <v>115</v>
@@ -3149,10 +3149,10 @@
         <v>118</v>
       </c>
       <c r="D61" t="s">
+        <v>113</v>
+      </c>
+      <c r="E61" t="s">
         <v>119</v>
-      </c>
-      <c r="E61" t="s">
-        <v>114</v>
       </c>
       <c r="F61" t="s">
         <v>115</v>
@@ -3172,10 +3172,10 @@
         <v>118</v>
       </c>
       <c r="D62" t="s">
+        <v>113</v>
+      </c>
+      <c r="E62" t="s">
         <v>119</v>
-      </c>
-      <c r="E62" t="s">
-        <v>114</v>
       </c>
       <c r="F62" t="s">
         <v>115</v>
@@ -3192,13 +3192,13 @@
         <v>8</v>
       </c>
       <c r="C63" t="s">
-        <v>118</v>
+        <v>133</v>
       </c>
       <c r="D63" t="s">
-        <v>133</v>
+        <v>113</v>
       </c>
       <c r="E63" t="s">
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="F63" t="s">
         <v>115</v>
@@ -3215,13 +3215,13 @@
         <v>8</v>
       </c>
       <c r="C64" t="s">
-        <v>118</v>
+        <v>133</v>
       </c>
       <c r="D64" t="s">
-        <v>133</v>
+        <v>113</v>
       </c>
       <c r="E64" t="s">
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="F64" t="s">
         <v>115</v>
@@ -3241,10 +3241,10 @@
         <v>136</v>
       </c>
       <c r="D65" t="s">
+        <v>113</v>
+      </c>
+      <c r="E65" t="s">
         <v>137</v>
-      </c>
-      <c r="E65" t="s">
-        <v>114</v>
       </c>
       <c r="F65" t="s">
         <v>115</v>
@@ -3287,10 +3287,10 @@
         <v>118</v>
       </c>
       <c r="D67" t="s">
+        <v>113</v>
+      </c>
+      <c r="E67" t="s">
         <v>119</v>
-      </c>
-      <c r="E67" t="s">
-        <v>114</v>
       </c>
       <c r="F67" t="s">
         <v>115</v>
@@ -3307,10 +3307,10 @@
         <v>8</v>
       </c>
       <c r="C68" t="s">
-        <v>112</v>
+        <v>141</v>
       </c>
       <c r="D68" t="s">
-        <v>141</v>
+        <v>113</v>
       </c>
       <c r="E68" t="s">
         <v>114</v>
@@ -3330,10 +3330,10 @@
         <v>8</v>
       </c>
       <c r="C69" t="s">
-        <v>112</v>
+        <v>143</v>
       </c>
       <c r="D69" t="s">
-        <v>143</v>
+        <v>113</v>
       </c>
       <c r="E69" t="s">
         <v>114</v>
@@ -3356,10 +3356,10 @@
         <v>121</v>
       </c>
       <c r="D70" t="s">
+        <v>113</v>
+      </c>
+      <c r="E70" t="s">
         <v>122</v>
-      </c>
-      <c r="E70" t="s">
-        <v>114</v>
       </c>
       <c r="F70" t="s">
         <v>115</v>
@@ -3379,10 +3379,10 @@
         <v>121</v>
       </c>
       <c r="D71" t="s">
+        <v>113</v>
+      </c>
+      <c r="E71" t="s">
         <v>122</v>
-      </c>
-      <c r="E71" t="s">
-        <v>114</v>
       </c>
       <c r="F71" t="s">
         <v>115</v>
@@ -3425,16 +3425,16 @@
         <v>148</v>
       </c>
       <c r="D73" t="s">
+        <v>113</v>
+      </c>
+      <c r="E73" t="s">
         <v>149</v>
-      </c>
-      <c r="E73" t="s">
-        <v>126</v>
       </c>
       <c r="F73" t="s">
         <v>115</v>
       </c>
       <c r="G73" t="s">
-        <v>116</v>
+        <v>126</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -3448,16 +3448,16 @@
         <v>151</v>
       </c>
       <c r="D74" t="s">
+        <v>113</v>
+      </c>
+      <c r="E74" t="s">
         <v>152</v>
-      </c>
-      <c r="E74" t="s">
-        <v>126</v>
       </c>
       <c r="F74" t="s">
         <v>115</v>
       </c>
       <c r="G74" t="s">
-        <v>116</v>
+        <v>126</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -3471,16 +3471,16 @@
         <v>154</v>
       </c>
       <c r="D75" t="s">
+        <v>113</v>
+      </c>
+      <c r="E75" t="s">
         <v>155</v>
-      </c>
-      <c r="E75" t="s">
-        <v>126</v>
       </c>
       <c r="F75" t="s">
         <v>115</v>
       </c>
       <c r="G75" t="s">
-        <v>116</v>
+        <v>126</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -3494,16 +3494,16 @@
         <v>148</v>
       </c>
       <c r="D76" t="s">
+        <v>113</v>
+      </c>
+      <c r="E76" t="s">
         <v>149</v>
-      </c>
-      <c r="E76" t="s">
-        <v>126</v>
       </c>
       <c r="F76" t="s">
         <v>115</v>
       </c>
       <c r="G76" t="s">
-        <v>116</v>
+        <v>126</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -3517,16 +3517,16 @@
         <v>148</v>
       </c>
       <c r="D77" t="s">
+        <v>113</v>
+      </c>
+      <c r="E77" t="s">
         <v>149</v>
-      </c>
-      <c r="E77" t="s">
-        <v>126</v>
       </c>
       <c r="F77" t="s">
         <v>115</v>
       </c>
       <c r="G77" t="s">
-        <v>116</v>
+        <v>126</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -3540,16 +3540,16 @@
         <v>151</v>
       </c>
       <c r="D78" t="s">
+        <v>113</v>
+      </c>
+      <c r="E78" t="s">
         <v>152</v>
-      </c>
-      <c r="E78" t="s">
-        <v>126</v>
       </c>
       <c r="F78" t="s">
         <v>115</v>
       </c>
       <c r="G78" t="s">
-        <v>116</v>
+        <v>126</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -3563,16 +3563,16 @@
         <v>160</v>
       </c>
       <c r="D79" t="s">
+        <v>113</v>
+      </c>
+      <c r="E79" t="s">
         <v>161</v>
-      </c>
-      <c r="E79" t="s">
-        <v>126</v>
       </c>
       <c r="F79" t="s">
         <v>115</v>
       </c>
       <c r="G79" t="s">
-        <v>116</v>
+        <v>126</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -3586,16 +3586,16 @@
         <v>163</v>
       </c>
       <c r="D80" t="s">
+        <v>113</v>
+      </c>
+      <c r="E80" t="s">
         <v>164</v>
-      </c>
-      <c r="E80" t="s">
-        <v>165</v>
       </c>
       <c r="F80" t="s">
         <v>115</v>
       </c>
       <c r="G80" t="s">
-        <v>116</v>
+        <v>165</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -3609,16 +3609,16 @@
         <v>163</v>
       </c>
       <c r="D81" t="s">
+        <v>113</v>
+      </c>
+      <c r="E81" t="s">
         <v>164</v>
-      </c>
-      <c r="E81" t="s">
-        <v>165</v>
       </c>
       <c r="F81" t="s">
         <v>115</v>
       </c>
       <c r="G81" t="s">
-        <v>116</v>
+        <v>165</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -3632,16 +3632,16 @@
         <v>163</v>
       </c>
       <c r="D82" t="s">
+        <v>113</v>
+      </c>
+      <c r="E82" t="s">
         <v>164</v>
-      </c>
-      <c r="E82" t="s">
-        <v>165</v>
       </c>
       <c r="F82" t="s">
         <v>115</v>
       </c>
       <c r="G82" t="s">
-        <v>116</v>
+        <v>165</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -3652,10 +3652,10 @@
         <v>8</v>
       </c>
       <c r="C83" t="s">
-        <v>112</v>
+        <v>143</v>
       </c>
       <c r="D83" t="s">
-        <v>143</v>
+        <v>113</v>
       </c>
       <c r="E83" t="s">
         <v>114</v>
@@ -3678,10 +3678,10 @@
         <v>170</v>
       </c>
       <c r="D84" t="s">
+        <v>113</v>
+      </c>
+      <c r="E84" t="s">
         <v>171</v>
-      </c>
-      <c r="E84" t="s">
-        <v>114</v>
       </c>
       <c r="F84" t="s">
         <v>115</v>
@@ -3698,13 +3698,13 @@
         <v>8</v>
       </c>
       <c r="C85" t="s">
-        <v>118</v>
+        <v>173</v>
       </c>
       <c r="D85" t="s">
-        <v>173</v>
+        <v>113</v>
       </c>
       <c r="E85" t="s">
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="F85" t="s">
         <v>115</v>
@@ -3724,16 +3724,16 @@
         <v>175</v>
       </c>
       <c r="D86" t="s">
+        <v>113</v>
+      </c>
+      <c r="E86" t="s">
         <v>176</v>
-      </c>
-      <c r="E86" t="s">
-        <v>165</v>
       </c>
       <c r="F86" t="s">
         <v>115</v>
       </c>
       <c r="G86" t="s">
-        <v>116</v>
+        <v>165</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -3744,13 +3744,13 @@
         <v>8</v>
       </c>
       <c r="C87" t="s">
-        <v>118</v>
+        <v>173</v>
       </c>
       <c r="D87" t="s">
-        <v>173</v>
+        <v>113</v>
       </c>
       <c r="E87" t="s">
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="F87" t="s">
         <v>115</v>
@@ -3770,10 +3770,10 @@
         <v>118</v>
       </c>
       <c r="D88" t="s">
+        <v>113</v>
+      </c>
+      <c r="E88" t="s">
         <v>119</v>
-      </c>
-      <c r="E88" t="s">
-        <v>114</v>
       </c>
       <c r="F88" t="s">
         <v>115</v>
@@ -3793,10 +3793,10 @@
         <v>118</v>
       </c>
       <c r="D89" t="s">
+        <v>113</v>
+      </c>
+      <c r="E89" t="s">
         <v>119</v>
-      </c>
-      <c r="E89" t="s">
-        <v>114</v>
       </c>
       <c r="F89" t="s">
         <v>115</v>
@@ -3816,16 +3816,16 @@
         <v>124</v>
       </c>
       <c r="D90" t="s">
+        <v>113</v>
+      </c>
+      <c r="E90" t="s">
         <v>125</v>
-      </c>
-      <c r="E90" t="s">
-        <v>126</v>
       </c>
       <c r="F90" t="s">
         <v>115</v>
       </c>
       <c r="G90" t="s">
-        <v>116</v>
+        <v>126</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -3839,16 +3839,16 @@
         <v>182</v>
       </c>
       <c r="D91" t="s">
+        <v>113</v>
+      </c>
+      <c r="E91" t="s">
         <v>183</v>
-      </c>
-      <c r="E91" t="s">
-        <v>184</v>
       </c>
       <c r="F91" t="s">
         <v>115</v>
       </c>
       <c r="G91" t="s">
-        <v>116</v>
+        <v>184</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -3862,16 +3862,16 @@
         <v>124</v>
       </c>
       <c r="D92" t="s">
+        <v>113</v>
+      </c>
+      <c r="E92" t="s">
         <v>125</v>
-      </c>
-      <c r="E92" t="s">
-        <v>126</v>
       </c>
       <c r="F92" t="s">
         <v>115</v>
       </c>
       <c r="G92" t="s">
-        <v>116</v>
+        <v>126</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -3885,10 +3885,10 @@
         <v>121</v>
       </c>
       <c r="D93" t="s">
+        <v>113</v>
+      </c>
+      <c r="E93" t="s">
         <v>122</v>
-      </c>
-      <c r="E93" t="s">
-        <v>114</v>
       </c>
       <c r="F93" t="s">
         <v>115</v>
@@ -3908,16 +3908,16 @@
         <v>124</v>
       </c>
       <c r="D94" t="s">
+        <v>113</v>
+      </c>
+      <c r="E94" t="s">
         <v>125</v>
-      </c>
-      <c r="E94" t="s">
-        <v>126</v>
       </c>
       <c r="F94" t="s">
         <v>115</v>
       </c>
       <c r="G94" t="s">
-        <v>116</v>
+        <v>126</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -3931,10 +3931,10 @@
         <v>189</v>
       </c>
       <c r="D95" t="s">
+        <v>113</v>
+      </c>
+      <c r="E95" t="s">
         <v>190</v>
-      </c>
-      <c r="E95" t="s">
-        <v>114</v>
       </c>
       <c r="F95" t="s">
         <v>115</v>
@@ -3954,16 +3954,16 @@
         <v>124</v>
       </c>
       <c r="D96" t="s">
+        <v>192</v>
+      </c>
+      <c r="E96" t="s">
         <v>125</v>
       </c>
-      <c r="E96" t="s">
+      <c r="F96" t="s">
+        <v>115</v>
+      </c>
+      <c r="G96" t="s">
         <v>126</v>
-      </c>
-      <c r="F96" t="s">
-        <v>192</v>
-      </c>
-      <c r="G96" t="s">
-        <v>116</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -3977,16 +3977,16 @@
         <v>124</v>
       </c>
       <c r="D97" t="s">
+        <v>192</v>
+      </c>
+      <c r="E97" t="s">
         <v>125</v>
       </c>
-      <c r="E97" t="s">
+      <c r="F97" t="s">
+        <v>115</v>
+      </c>
+      <c r="G97" t="s">
         <v>126</v>
-      </c>
-      <c r="F97" t="s">
-        <v>192</v>
-      </c>
-      <c r="G97" t="s">
-        <v>116</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -4000,16 +4000,16 @@
         <v>195</v>
       </c>
       <c r="D98" t="s">
+        <v>192</v>
+      </c>
+      <c r="E98" t="s">
         <v>196</v>
       </c>
-      <c r="E98" t="s">
+      <c r="F98" t="s">
+        <v>115</v>
+      </c>
+      <c r="G98" t="s">
         <v>197</v>
-      </c>
-      <c r="F98" t="s">
-        <v>192</v>
-      </c>
-      <c r="G98" t="s">
-        <v>116</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -4023,16 +4023,16 @@
         <v>124</v>
       </c>
       <c r="D99" t="s">
+        <v>192</v>
+      </c>
+      <c r="E99" t="s">
         <v>125</v>
       </c>
-      <c r="E99" t="s">
+      <c r="F99" t="s">
+        <v>115</v>
+      </c>
+      <c r="G99" t="s">
         <v>126</v>
-      </c>
-      <c r="F99" t="s">
-        <v>192</v>
-      </c>
-      <c r="G99" t="s">
-        <v>116</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -4046,16 +4046,16 @@
         <v>154</v>
       </c>
       <c r="D100" t="s">
+        <v>192</v>
+      </c>
+      <c r="E100" t="s">
         <v>155</v>
       </c>
-      <c r="E100" t="s">
+      <c r="F100" t="s">
+        <v>115</v>
+      </c>
+      <c r="G100" t="s">
         <v>126</v>
-      </c>
-      <c r="F100" t="s">
-        <v>192</v>
-      </c>
-      <c r="G100" t="s">
-        <v>116</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -4069,16 +4069,16 @@
         <v>124</v>
       </c>
       <c r="D101" t="s">
+        <v>192</v>
+      </c>
+      <c r="E101" t="s">
         <v>125</v>
       </c>
-      <c r="E101" t="s">
+      <c r="F101" t="s">
+        <v>115</v>
+      </c>
+      <c r="G101" t="s">
         <v>126</v>
-      </c>
-      <c r="F101" t="s">
-        <v>192</v>
-      </c>
-      <c r="G101" t="s">
-        <v>116</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -4091,14 +4091,14 @@
       <c r="C102" t="s">
         <v>202</v>
       </c>
-      <c r="D102" t="s">
+      <c r="E102" t="s">
         <v>203</v>
       </c>
-      <c r="E102" t="s">
+      <c r="F102" t="s">
+        <v>204</v>
+      </c>
+      <c r="G102" t="s">
         <v>184</v>
-      </c>
-      <c r="G102" t="s">
-        <v>204</v>
       </c>
     </row>
     <row r="103" spans="1:7">
@@ -4111,14 +4111,14 @@
       <c r="C103" t="s">
         <v>202</v>
       </c>
-      <c r="D103" t="s">
+      <c r="E103" t="s">
         <v>203</v>
       </c>
-      <c r="E103" t="s">
+      <c r="F103" t="s">
+        <v>204</v>
+      </c>
+      <c r="G103" t="s">
         <v>184</v>
-      </c>
-      <c r="G103" t="s">
-        <v>204</v>
       </c>
     </row>
     <row r="104" spans="1:7">
@@ -4131,14 +4131,14 @@
       <c r="C104" t="s">
         <v>202</v>
       </c>
-      <c r="D104" t="s">
+      <c r="E104" t="s">
         <v>203</v>
       </c>
-      <c r="E104" t="s">
+      <c r="F104" t="s">
+        <v>204</v>
+      </c>
+      <c r="G104" t="s">
         <v>184</v>
-      </c>
-      <c r="G104" t="s">
-        <v>204</v>
       </c>
     </row>
     <row r="105" spans="1:7">
@@ -4151,14 +4151,14 @@
       <c r="C105" t="s">
         <v>208</v>
       </c>
-      <c r="D105" t="s">
+      <c r="E105" t="s">
         <v>209</v>
       </c>
-      <c r="E105" t="s">
+      <c r="F105" t="s">
+        <v>204</v>
+      </c>
+      <c r="G105" t="s">
         <v>184</v>
-      </c>
-      <c r="G105" t="s">
-        <v>204</v>
       </c>
     </row>
     <row r="106" spans="1:7">
@@ -4171,14 +4171,14 @@
       <c r="C106" t="s">
         <v>202</v>
       </c>
-      <c r="D106" t="s">
+      <c r="E106" t="s">
         <v>203</v>
       </c>
-      <c r="E106" t="s">
+      <c r="F106" t="s">
+        <v>204</v>
+      </c>
+      <c r="G106" t="s">
         <v>184</v>
-      </c>
-      <c r="G106" t="s">
-        <v>204</v>
       </c>
     </row>
     <row r="107" spans="1:7">
@@ -4191,14 +4191,14 @@
       <c r="C107" t="s">
         <v>182</v>
       </c>
-      <c r="D107" t="s">
+      <c r="E107" t="s">
         <v>183</v>
       </c>
-      <c r="E107" t="s">
+      <c r="F107" t="s">
+        <v>204</v>
+      </c>
+      <c r="G107" t="s">
         <v>184</v>
-      </c>
-      <c r="G107" t="s">
-        <v>204</v>
       </c>
     </row>
     <row r="108" spans="1:7">
@@ -4211,14 +4211,14 @@
       <c r="C108" t="s">
         <v>213</v>
       </c>
-      <c r="D108" t="s">
+      <c r="E108" t="s">
         <v>214</v>
       </c>
-      <c r="E108" t="s">
+      <c r="F108" t="s">
+        <v>204</v>
+      </c>
+      <c r="G108" t="s">
         <v>184</v>
-      </c>
-      <c r="G108" t="s">
-        <v>204</v>
       </c>
     </row>
     <row r="109" spans="1:7">
@@ -4231,14 +4231,14 @@
       <c r="C109" t="s">
         <v>216</v>
       </c>
-      <c r="D109" t="s">
+      <c r="E109" t="s">
         <v>217</v>
       </c>
-      <c r="E109" t="s">
-        <v>92</v>
+      <c r="F109" t="s">
+        <v>204</v>
       </c>
       <c r="G109" t="s">
-        <v>204</v>
+        <v>93</v>
       </c>
     </row>
     <row r="110" spans="1:7">
@@ -4251,14 +4251,14 @@
       <c r="C110" t="s">
         <v>219</v>
       </c>
-      <c r="D110" t="s">
+      <c r="E110" t="s">
         <v>220</v>
       </c>
-      <c r="E110" t="s">
-        <v>92</v>
+      <c r="F110" t="s">
+        <v>204</v>
       </c>
       <c r="G110" t="s">
-        <v>204</v>
+        <v>93</v>
       </c>
     </row>
     <row r="111" spans="1:7">
@@ -4271,14 +4271,14 @@
       <c r="C111" t="s">
         <v>202</v>
       </c>
-      <c r="D111" t="s">
+      <c r="E111" t="s">
         <v>203</v>
       </c>
-      <c r="E111" t="s">
+      <c r="F111" t="s">
+        <v>204</v>
+      </c>
+      <c r="G111" t="s">
         <v>184</v>
-      </c>
-      <c r="G111" t="s">
-        <v>204</v>
       </c>
     </row>
     <row r="112" spans="1:7">
@@ -4291,14 +4291,14 @@
       <c r="C112" t="s">
         <v>223</v>
       </c>
-      <c r="D112" t="s">
+      <c r="E112" t="s">
         <v>224</v>
       </c>
-      <c r="E112" t="s">
+      <c r="F112" t="s">
+        <v>204</v>
+      </c>
+      <c r="G112" t="s">
         <v>225</v>
-      </c>
-      <c r="G112" t="s">
-        <v>204</v>
       </c>
     </row>
     <row r="113" spans="1:7">
@@ -4309,16 +4309,16 @@
         <v>8</v>
       </c>
       <c r="C113" t="s">
-        <v>112</v>
-      </c>
-      <c r="D113" t="s">
         <v>143</v>
       </c>
       <c r="E113" t="s">
         <v>114</v>
       </c>
+      <c r="F113" t="s">
+        <v>204</v>
+      </c>
       <c r="G113" t="s">
-        <v>204</v>
+        <v>116</v>
       </c>
     </row>
     <row r="114" spans="1:7">
@@ -4331,14 +4331,14 @@
       <c r="C114" t="s">
         <v>151</v>
       </c>
-      <c r="D114" t="s">
+      <c r="E114" t="s">
         <v>152</v>
       </c>
-      <c r="E114" t="s">
+      <c r="F114" t="s">
+        <v>204</v>
+      </c>
+      <c r="G114" t="s">
         <v>126</v>
-      </c>
-      <c r="G114" t="s">
-        <v>204</v>
       </c>
     </row>
     <row r="115" spans="1:7">
@@ -4351,14 +4351,14 @@
       <c r="C115" t="s">
         <v>182</v>
       </c>
-      <c r="D115" t="s">
+      <c r="E115" t="s">
         <v>183</v>
       </c>
-      <c r="E115" t="s">
+      <c r="F115" t="s">
+        <v>204</v>
+      </c>
+      <c r="G115" t="s">
         <v>184</v>
-      </c>
-      <c r="G115" t="s">
-        <v>204</v>
       </c>
     </row>
     <row r="116" spans="1:7">
@@ -4371,14 +4371,14 @@
       <c r="C116" t="s">
         <v>230</v>
       </c>
-      <c r="D116" t="s">
+      <c r="E116" t="s">
         <v>231</v>
       </c>
-      <c r="E116" t="s">
+      <c r="F116" t="s">
+        <v>204</v>
+      </c>
+      <c r="G116" t="s">
         <v>225</v>
-      </c>
-      <c r="G116" t="s">
-        <v>204</v>
       </c>
     </row>
     <row r="117" spans="1:7">
@@ -4391,14 +4391,14 @@
       <c r="C117" t="s">
         <v>223</v>
       </c>
-      <c r="D117" t="s">
+      <c r="E117" t="s">
         <v>224</v>
       </c>
-      <c r="E117" t="s">
+      <c r="F117" t="s">
+        <v>204</v>
+      </c>
+      <c r="G117" t="s">
         <v>225</v>
-      </c>
-      <c r="G117" t="s">
-        <v>204</v>
       </c>
     </row>
     <row r="118" spans="1:7">
@@ -4409,16 +4409,16 @@
         <v>8</v>
       </c>
       <c r="C118" t="s">
-        <v>163</v>
-      </c>
-      <c r="D118" t="s">
         <v>234</v>
       </c>
       <c r="E118" t="s">
-        <v>165</v>
+        <v>164</v>
+      </c>
+      <c r="F118" t="s">
+        <v>204</v>
       </c>
       <c r="G118" t="s">
-        <v>204</v>
+        <v>165</v>
       </c>
     </row>
     <row r="119" spans="1:7">
@@ -4431,14 +4431,14 @@
       <c r="C119" t="s">
         <v>182</v>
       </c>
-      <c r="D119" t="s">
+      <c r="E119" t="s">
         <v>183</v>
       </c>
-      <c r="E119" t="s">
+      <c r="F119" t="s">
+        <v>204</v>
+      </c>
+      <c r="G119" t="s">
         <v>184</v>
-      </c>
-      <c r="G119" t="s">
-        <v>204</v>
       </c>
     </row>
     <row r="120" spans="1:7">
@@ -4451,14 +4451,14 @@
       <c r="C120" t="s">
         <v>170</v>
       </c>
-      <c r="D120" t="s">
+      <c r="E120" t="s">
         <v>171</v>
       </c>
-      <c r="E120" t="s">
-        <v>114</v>
+      <c r="F120" t="s">
+        <v>237</v>
       </c>
       <c r="G120" t="s">
-        <v>237</v>
+        <v>116</v>
       </c>
     </row>
     <row r="121" spans="1:7">
@@ -4469,16 +4469,16 @@
         <v>8</v>
       </c>
       <c r="C121" t="s">
-        <v>112</v>
-      </c>
-      <c r="D121" t="s">
         <v>143</v>
       </c>
       <c r="E121" t="s">
         <v>114</v>
       </c>
+      <c r="F121" t="s">
+        <v>237</v>
+      </c>
       <c r="G121" t="s">
-        <v>237</v>
+        <v>116</v>
       </c>
     </row>
     <row r="122" spans="1:7">
@@ -4491,14 +4491,14 @@
       <c r="C122" t="s">
         <v>170</v>
       </c>
-      <c r="D122" t="s">
+      <c r="E122" t="s">
         <v>171</v>
       </c>
-      <c r="E122" t="s">
-        <v>114</v>
+      <c r="F122" t="s">
+        <v>237</v>
       </c>
       <c r="G122" t="s">
-        <v>237</v>
+        <v>116</v>
       </c>
     </row>
     <row r="123" spans="1:7">
@@ -4511,14 +4511,14 @@
       <c r="C123" t="s">
         <v>170</v>
       </c>
-      <c r="D123" t="s">
+      <c r="E123" t="s">
         <v>171</v>
       </c>
-      <c r="E123" t="s">
-        <v>114</v>
+      <c r="F123" t="s">
+        <v>237</v>
       </c>
       <c r="G123" t="s">
-        <v>237</v>
+        <v>116</v>
       </c>
     </row>
     <row r="124" spans="1:7">
@@ -4531,14 +4531,14 @@
       <c r="C124" t="s">
         <v>242</v>
       </c>
-      <c r="D124" t="s">
+      <c r="E124" t="s">
         <v>243</v>
       </c>
-      <c r="E124" t="s">
-        <v>165</v>
+      <c r="F124" t="s">
+        <v>237</v>
       </c>
       <c r="G124" t="s">
-        <v>237</v>
+        <v>165</v>
       </c>
     </row>
     <row r="125" spans="1:7">
@@ -4551,14 +4551,14 @@
       <c r="C125" t="s">
         <v>242</v>
       </c>
-      <c r="D125" t="s">
+      <c r="E125" t="s">
         <v>243</v>
       </c>
-      <c r="E125" t="s">
-        <v>165</v>
+      <c r="F125" t="s">
+        <v>237</v>
       </c>
       <c r="G125" t="s">
-        <v>237</v>
+        <v>165</v>
       </c>
     </row>
     <row r="126" spans="1:7">
@@ -4571,14 +4571,14 @@
       <c r="C126" t="s">
         <v>242</v>
       </c>
-      <c r="D126" t="s">
+      <c r="E126" t="s">
         <v>243</v>
       </c>
-      <c r="E126" t="s">
-        <v>165</v>
+      <c r="F126" t="s">
+        <v>237</v>
       </c>
       <c r="G126" t="s">
-        <v>237</v>
+        <v>165</v>
       </c>
     </row>
     <row r="127" spans="1:7">
@@ -4591,14 +4591,14 @@
       <c r="C127" t="s">
         <v>242</v>
       </c>
-      <c r="D127" t="s">
+      <c r="E127" t="s">
         <v>243</v>
       </c>
-      <c r="E127" t="s">
-        <v>165</v>
+      <c r="F127" t="s">
+        <v>237</v>
       </c>
       <c r="G127" t="s">
-        <v>237</v>
+        <v>165</v>
       </c>
     </row>
     <row r="128" spans="1:7">
@@ -4611,14 +4611,14 @@
       <c r="C128" t="s">
         <v>242</v>
       </c>
-      <c r="D128" t="s">
+      <c r="E128" t="s">
         <v>243</v>
       </c>
-      <c r="E128" t="s">
-        <v>165</v>
+      <c r="F128" t="s">
+        <v>237</v>
       </c>
       <c r="G128" t="s">
-        <v>237</v>
+        <v>165</v>
       </c>
     </row>
     <row r="129" spans="1:7">
@@ -4629,16 +4629,16 @@
         <v>8</v>
       </c>
       <c r="C129" t="s">
-        <v>242</v>
-      </c>
-      <c r="D129" t="s">
         <v>249</v>
       </c>
       <c r="E129" t="s">
-        <v>165</v>
+        <v>243</v>
+      </c>
+      <c r="F129" t="s">
+        <v>237</v>
       </c>
       <c r="G129" t="s">
-        <v>237</v>
+        <v>165</v>
       </c>
     </row>
     <row r="130" spans="1:7">
@@ -4649,16 +4649,16 @@
         <v>8</v>
       </c>
       <c r="C130" t="s">
-        <v>242</v>
-      </c>
-      <c r="D130" t="s">
         <v>251</v>
       </c>
       <c r="E130" t="s">
-        <v>165</v>
+        <v>243</v>
+      </c>
+      <c r="F130" t="s">
+        <v>237</v>
       </c>
       <c r="G130" t="s">
-        <v>237</v>
+        <v>165</v>
       </c>
     </row>
     <row r="131" spans="1:7">
@@ -4669,16 +4669,16 @@
         <v>8</v>
       </c>
       <c r="C131" t="s">
-        <v>242</v>
-      </c>
-      <c r="D131" t="s">
         <v>253</v>
       </c>
       <c r="E131" t="s">
-        <v>165</v>
+        <v>243</v>
+      </c>
+      <c r="F131" t="s">
+        <v>237</v>
       </c>
       <c r="G131" t="s">
-        <v>237</v>
+        <v>165</v>
       </c>
     </row>
     <row r="132" spans="1:7">
@@ -4691,14 +4691,14 @@
       <c r="C132" t="s">
         <v>255</v>
       </c>
-      <c r="D132" t="s">
+      <c r="E132" t="s">
         <v>256</v>
       </c>
-      <c r="E132" t="s">
-        <v>165</v>
+      <c r="F132" t="s">
+        <v>237</v>
       </c>
       <c r="G132" t="s">
-        <v>237</v>
+        <v>165</v>
       </c>
     </row>
     <row r="133" spans="1:7">
@@ -4711,14 +4711,14 @@
       <c r="C133" t="s">
         <v>189</v>
       </c>
-      <c r="D133" t="s">
+      <c r="E133" t="s">
         <v>190</v>
       </c>
-      <c r="E133" t="s">
-        <v>114</v>
+      <c r="F133" t="s">
+        <v>237</v>
       </c>
       <c r="G133" t="s">
-        <v>237</v>
+        <v>116</v>
       </c>
     </row>
     <row r="134" spans="1:7">
@@ -4731,14 +4731,14 @@
       <c r="C134" t="s">
         <v>175</v>
       </c>
-      <c r="D134" t="s">
+      <c r="E134" t="s">
         <v>176</v>
       </c>
-      <c r="E134" t="s">
-        <v>165</v>
+      <c r="F134" t="s">
+        <v>259</v>
       </c>
       <c r="G134" t="s">
-        <v>259</v>
+        <v>165</v>
       </c>
     </row>
     <row r="135" spans="1:7">
@@ -4751,14 +4751,14 @@
       <c r="C135" t="s">
         <v>175</v>
       </c>
-      <c r="D135" t="s">
+      <c r="E135" t="s">
         <v>176</v>
       </c>
-      <c r="E135" t="s">
-        <v>165</v>
+      <c r="F135" t="s">
+        <v>259</v>
       </c>
       <c r="G135" t="s">
-        <v>259</v>
+        <v>165</v>
       </c>
     </row>
     <row r="136" spans="1:7">
@@ -4771,14 +4771,14 @@
       <c r="C136" t="s">
         <v>175</v>
       </c>
-      <c r="D136" t="s">
+      <c r="E136" t="s">
         <v>176</v>
       </c>
-      <c r="E136" t="s">
-        <v>165</v>
+      <c r="F136" t="s">
+        <v>259</v>
       </c>
       <c r="G136" t="s">
-        <v>259</v>
+        <v>165</v>
       </c>
     </row>
     <row r="137" spans="1:7">
@@ -4791,14 +4791,14 @@
       <c r="C137" t="s">
         <v>175</v>
       </c>
-      <c r="D137" t="s">
+      <c r="E137" t="s">
         <v>176</v>
       </c>
-      <c r="E137" t="s">
-        <v>165</v>
+      <c r="F137" t="s">
+        <v>259</v>
       </c>
       <c r="G137" t="s">
-        <v>259</v>
+        <v>165</v>
       </c>
     </row>
     <row r="138" spans="1:7">
@@ -4811,14 +4811,14 @@
       <c r="C138" t="s">
         <v>175</v>
       </c>
-      <c r="D138" t="s">
+      <c r="E138" t="s">
         <v>176</v>
       </c>
-      <c r="E138" t="s">
-        <v>165</v>
+      <c r="F138" t="s">
+        <v>259</v>
       </c>
       <c r="G138" t="s">
-        <v>259</v>
+        <v>165</v>
       </c>
     </row>
     <row r="139" spans="1:7">
@@ -4831,14 +4831,14 @@
       <c r="C139" t="s">
         <v>265</v>
       </c>
-      <c r="D139" t="s">
+      <c r="E139" t="s">
         <v>266</v>
       </c>
-      <c r="E139" t="s">
+      <c r="F139" t="s">
+        <v>259</v>
+      </c>
+      <c r="G139" t="s">
         <v>225</v>
-      </c>
-      <c r="G139" t="s">
-        <v>259</v>
       </c>
     </row>
     <row r="140" spans="1:7">
@@ -4851,14 +4851,14 @@
       <c r="C140" t="s">
         <v>175</v>
       </c>
-      <c r="D140" t="s">
+      <c r="E140" t="s">
         <v>176</v>
       </c>
-      <c r="E140" t="s">
-        <v>165</v>
+      <c r="F140" t="s">
+        <v>259</v>
       </c>
       <c r="G140" t="s">
-        <v>259</v>
+        <v>165</v>
       </c>
     </row>
     <row r="141" spans="1:7">
@@ -4875,13 +4875,13 @@
         <v>270</v>
       </c>
       <c r="E141" t="s">
-        <v>165</v>
+        <v>271</v>
       </c>
       <c r="F141" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="G141" t="s">
-        <v>272</v>
+        <v>165</v>
       </c>
     </row>
     <row r="142" spans="1:7">
@@ -4898,13 +4898,13 @@
         <v>270</v>
       </c>
       <c r="E142" t="s">
-        <v>165</v>
+        <v>271</v>
       </c>
       <c r="F142" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="G142" t="s">
-        <v>272</v>
+        <v>165</v>
       </c>
     </row>
     <row r="143" spans="1:7">
@@ -4918,16 +4918,16 @@
         <v>275</v>
       </c>
       <c r="D143" t="s">
+        <v>270</v>
+      </c>
+      <c r="E143" t="s">
         <v>276</v>
       </c>
-      <c r="E143" t="s">
-        <v>165</v>
-      </c>
       <c r="F143" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="G143" t="s">
-        <v>272</v>
+        <v>165</v>
       </c>
     </row>
     <row r="144" spans="1:7">
@@ -4941,16 +4941,16 @@
         <v>275</v>
       </c>
       <c r="D144" t="s">
+        <v>270</v>
+      </c>
+      <c r="E144" t="s">
         <v>276</v>
       </c>
-      <c r="E144" t="s">
-        <v>165</v>
-      </c>
       <c r="F144" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="G144" t="s">
-        <v>272</v>
+        <v>165</v>
       </c>
     </row>
     <row r="145" spans="1:7">
@@ -4964,16 +4964,16 @@
         <v>275</v>
       </c>
       <c r="D145" t="s">
+        <v>270</v>
+      </c>
+      <c r="E145" t="s">
         <v>276</v>
       </c>
-      <c r="E145" t="s">
-        <v>165</v>
-      </c>
       <c r="F145" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="G145" t="s">
-        <v>272</v>
+        <v>165</v>
       </c>
     </row>
     <row r="146" spans="1:7">
@@ -4990,13 +4990,13 @@
         <v>270</v>
       </c>
       <c r="E146" t="s">
-        <v>165</v>
+        <v>271</v>
       </c>
       <c r="F146" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="G146" t="s">
-        <v>272</v>
+        <v>165</v>
       </c>
     </row>
     <row r="147" spans="1:7">
@@ -5010,16 +5010,16 @@
         <v>269</v>
       </c>
       <c r="D147" t="s">
-        <v>270</v>
+        <v>281</v>
       </c>
       <c r="E147" t="s">
-        <v>165</v>
+        <v>271</v>
       </c>
       <c r="F147" t="s">
-        <v>281</v>
+        <v>272</v>
       </c>
       <c r="G147" t="s">
-        <v>272</v>
+        <v>165</v>
       </c>
     </row>
     <row r="148" spans="1:7">
@@ -5033,16 +5033,16 @@
         <v>269</v>
       </c>
       <c r="D148" t="s">
-        <v>270</v>
+        <v>281</v>
       </c>
       <c r="E148" t="s">
-        <v>165</v>
+        <v>271</v>
       </c>
       <c r="F148" t="s">
-        <v>281</v>
+        <v>272</v>
       </c>
       <c r="G148" t="s">
-        <v>272</v>
+        <v>165</v>
       </c>
     </row>
     <row r="149" spans="1:7">
@@ -5056,16 +5056,16 @@
         <v>269</v>
       </c>
       <c r="D149" t="s">
-        <v>270</v>
+        <v>281</v>
       </c>
       <c r="E149" t="s">
-        <v>165</v>
+        <v>271</v>
       </c>
       <c r="F149" t="s">
-        <v>281</v>
+        <v>272</v>
       </c>
       <c r="G149" t="s">
-        <v>272</v>
+        <v>165</v>
       </c>
     </row>
     <row r="150" spans="1:7">
@@ -5079,16 +5079,16 @@
         <v>269</v>
       </c>
       <c r="D150" t="s">
-        <v>270</v>
+        <v>281</v>
       </c>
       <c r="E150" t="s">
-        <v>165</v>
+        <v>271</v>
       </c>
       <c r="F150" t="s">
-        <v>281</v>
+        <v>272</v>
       </c>
       <c r="G150" t="s">
-        <v>272</v>
+        <v>165</v>
       </c>
     </row>
     <row r="151" spans="1:7">
@@ -5102,16 +5102,16 @@
         <v>269</v>
       </c>
       <c r="D151" t="s">
-        <v>270</v>
+        <v>281</v>
       </c>
       <c r="E151" t="s">
-        <v>165</v>
+        <v>271</v>
       </c>
       <c r="F151" t="s">
-        <v>281</v>
+        <v>272</v>
       </c>
       <c r="G151" t="s">
-        <v>272</v>
+        <v>165</v>
       </c>
     </row>
     <row r="152" spans="1:7">
@@ -5125,16 +5125,16 @@
         <v>269</v>
       </c>
       <c r="D152" t="s">
-        <v>270</v>
+        <v>281</v>
       </c>
       <c r="E152" t="s">
-        <v>165</v>
+        <v>271</v>
       </c>
       <c r="F152" t="s">
-        <v>281</v>
+        <v>272</v>
       </c>
       <c r="G152" t="s">
-        <v>272</v>
+        <v>165</v>
       </c>
     </row>
     <row r="153" spans="1:7">
@@ -5148,16 +5148,16 @@
         <v>269</v>
       </c>
       <c r="D153" t="s">
-        <v>270</v>
+        <v>281</v>
       </c>
       <c r="E153" t="s">
-        <v>165</v>
+        <v>271</v>
       </c>
       <c r="F153" t="s">
-        <v>281</v>
+        <v>272</v>
       </c>
       <c r="G153" t="s">
-        <v>272</v>
+        <v>165</v>
       </c>
     </row>
     <row r="154" spans="1:7">
@@ -5171,16 +5171,16 @@
         <v>269</v>
       </c>
       <c r="D154" t="s">
-        <v>270</v>
+        <v>281</v>
       </c>
       <c r="E154" t="s">
-        <v>165</v>
+        <v>271</v>
       </c>
       <c r="F154" t="s">
-        <v>281</v>
+        <v>272</v>
       </c>
       <c r="G154" t="s">
-        <v>272</v>
+        <v>165</v>
       </c>
     </row>
     <row r="155" spans="1:7">
@@ -5194,16 +5194,16 @@
         <v>269</v>
       </c>
       <c r="D155" t="s">
-        <v>270</v>
+        <v>281</v>
       </c>
       <c r="E155" t="s">
-        <v>165</v>
+        <v>271</v>
       </c>
       <c r="F155" t="s">
-        <v>281</v>
+        <v>272</v>
       </c>
       <c r="G155" t="s">
-        <v>272</v>
+        <v>165</v>
       </c>
     </row>
     <row r="156" spans="1:7">
@@ -5217,16 +5217,16 @@
         <v>269</v>
       </c>
       <c r="D156" t="s">
-        <v>270</v>
+        <v>291</v>
       </c>
       <c r="E156" t="s">
-        <v>165</v>
+        <v>271</v>
       </c>
       <c r="F156" t="s">
-        <v>291</v>
+        <v>272</v>
       </c>
       <c r="G156" t="s">
-        <v>272</v>
+        <v>165</v>
       </c>
     </row>
     <row r="157" spans="1:7">
@@ -5237,19 +5237,19 @@
         <v>8</v>
       </c>
       <c r="C157" t="s">
-        <v>269</v>
+        <v>293</v>
       </c>
       <c r="D157" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="E157" t="s">
-        <v>165</v>
+        <v>271</v>
       </c>
       <c r="F157" t="s">
-        <v>291</v>
+        <v>272</v>
       </c>
       <c r="G157" t="s">
-        <v>272</v>
+        <v>165</v>
       </c>
     </row>
     <row r="158" spans="1:7">
@@ -5263,16 +5263,16 @@
         <v>269</v>
       </c>
       <c r="D158" t="s">
-        <v>270</v>
+        <v>291</v>
       </c>
       <c r="E158" t="s">
-        <v>165</v>
+        <v>271</v>
       </c>
       <c r="F158" t="s">
-        <v>291</v>
+        <v>272</v>
       </c>
       <c r="G158" t="s">
-        <v>272</v>
+        <v>165</v>
       </c>
     </row>
     <row r="159" spans="1:7">
@@ -5286,16 +5286,16 @@
         <v>269</v>
       </c>
       <c r="D159" t="s">
-        <v>270</v>
+        <v>291</v>
       </c>
       <c r="E159" t="s">
-        <v>165</v>
+        <v>271</v>
       </c>
       <c r="F159" t="s">
-        <v>291</v>
+        <v>272</v>
       </c>
       <c r="G159" t="s">
-        <v>272</v>
+        <v>165</v>
       </c>
     </row>
     <row r="160" spans="1:7">
@@ -5309,16 +5309,16 @@
         <v>269</v>
       </c>
       <c r="D160" t="s">
-        <v>270</v>
+        <v>291</v>
       </c>
       <c r="E160" t="s">
-        <v>165</v>
+        <v>271</v>
       </c>
       <c r="F160" t="s">
-        <v>291</v>
+        <v>272</v>
       </c>
       <c r="G160" t="s">
-        <v>272</v>
+        <v>165</v>
       </c>
     </row>
     <row r="161" spans="1:7">
@@ -5332,16 +5332,16 @@
         <v>269</v>
       </c>
       <c r="D161" t="s">
-        <v>270</v>
+        <v>291</v>
       </c>
       <c r="E161" t="s">
-        <v>165</v>
+        <v>271</v>
       </c>
       <c r="F161" t="s">
-        <v>291</v>
+        <v>272</v>
       </c>
       <c r="G161" t="s">
-        <v>272</v>
+        <v>165</v>
       </c>
     </row>
     <row r="162" spans="1:7">
@@ -5355,16 +5355,16 @@
         <v>269</v>
       </c>
       <c r="D162" t="s">
-        <v>270</v>
+        <v>299</v>
       </c>
       <c r="E162" t="s">
-        <v>165</v>
+        <v>271</v>
       </c>
       <c r="F162" t="s">
-        <v>299</v>
+        <v>272</v>
       </c>
       <c r="G162" t="s">
-        <v>272</v>
+        <v>165</v>
       </c>
     </row>
     <row r="163" spans="1:7">
@@ -5375,19 +5375,19 @@
         <v>8</v>
       </c>
       <c r="C163" t="s">
-        <v>269</v>
+        <v>301</v>
       </c>
       <c r="D163" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="E163" t="s">
-        <v>165</v>
+        <v>271</v>
       </c>
       <c r="F163" t="s">
-        <v>302</v>
+        <v>272</v>
       </c>
       <c r="G163" t="s">
-        <v>272</v>
+        <v>165</v>
       </c>
     </row>
     <row r="164" spans="1:7">
@@ -5401,16 +5401,16 @@
         <v>269</v>
       </c>
       <c r="D164" t="s">
-        <v>270</v>
+        <v>304</v>
       </c>
       <c r="E164" t="s">
-        <v>165</v>
+        <v>271</v>
       </c>
       <c r="F164" t="s">
-        <v>304</v>
+        <v>272</v>
       </c>
       <c r="G164" t="s">
-        <v>272</v>
+        <v>165</v>
       </c>
     </row>
     <row r="165" spans="1:7">
@@ -5424,16 +5424,16 @@
         <v>269</v>
       </c>
       <c r="D165" t="s">
-        <v>270</v>
+        <v>304</v>
       </c>
       <c r="E165" t="s">
-        <v>165</v>
+        <v>271</v>
       </c>
       <c r="F165" t="s">
-        <v>304</v>
+        <v>272</v>
       </c>
       <c r="G165" t="s">
-        <v>272</v>
+        <v>165</v>
       </c>
     </row>
     <row r="166" spans="1:7">
@@ -5447,16 +5447,16 @@
         <v>269</v>
       </c>
       <c r="D166" t="s">
-        <v>270</v>
+        <v>304</v>
       </c>
       <c r="E166" t="s">
-        <v>165</v>
+        <v>271</v>
       </c>
       <c r="F166" t="s">
-        <v>304</v>
+        <v>272</v>
       </c>
       <c r="G166" t="s">
-        <v>272</v>
+        <v>165</v>
       </c>
     </row>
     <row r="167" spans="1:7">
@@ -5470,16 +5470,16 @@
         <v>269</v>
       </c>
       <c r="D167" t="s">
-        <v>270</v>
+        <v>304</v>
       </c>
       <c r="E167" t="s">
-        <v>165</v>
+        <v>271</v>
       </c>
       <c r="F167" t="s">
-        <v>304</v>
+        <v>272</v>
       </c>
       <c r="G167" t="s">
-        <v>272</v>
+        <v>165</v>
       </c>
     </row>
     <row r="168" spans="1:7">
@@ -5490,19 +5490,19 @@
         <v>8</v>
       </c>
       <c r="C168" t="s">
-        <v>269</v>
+        <v>309</v>
       </c>
       <c r="D168" t="s">
-        <v>309</v>
+        <v>304</v>
       </c>
       <c r="E168" t="s">
-        <v>165</v>
+        <v>271</v>
       </c>
       <c r="F168" t="s">
-        <v>304</v>
+        <v>272</v>
       </c>
       <c r="G168" t="s">
-        <v>272</v>
+        <v>165</v>
       </c>
     </row>
     <row r="169" spans="1:7">
@@ -5513,19 +5513,19 @@
         <v>8</v>
       </c>
       <c r="C169" t="s">
-        <v>269</v>
+        <v>309</v>
       </c>
       <c r="D169" t="s">
-        <v>309</v>
+        <v>304</v>
       </c>
       <c r="E169" t="s">
-        <v>165</v>
+        <v>271</v>
       </c>
       <c r="F169" t="s">
-        <v>304</v>
+        <v>272</v>
       </c>
       <c r="G169" t="s">
-        <v>272</v>
+        <v>165</v>
       </c>
     </row>
     <row r="170" spans="1:7">
@@ -5539,16 +5539,16 @@
         <v>269</v>
       </c>
       <c r="D170" t="s">
-        <v>270</v>
+        <v>304</v>
       </c>
       <c r="E170" t="s">
-        <v>165</v>
+        <v>271</v>
       </c>
       <c r="F170" t="s">
-        <v>304</v>
+        <v>272</v>
       </c>
       <c r="G170" t="s">
-        <v>272</v>
+        <v>165</v>
       </c>
     </row>
     <row r="171" spans="1:7">
@@ -5561,14 +5561,14 @@
       <c r="C171" t="s">
         <v>163</v>
       </c>
-      <c r="D171" t="s">
+      <c r="E171" t="s">
         <v>164</v>
       </c>
-      <c r="E171" t="s">
-        <v>165</v>
+      <c r="F171" t="s">
+        <v>313</v>
       </c>
       <c r="G171" t="s">
-        <v>313</v>
+        <v>165</v>
       </c>
     </row>
     <row r="172" spans="1:7">
@@ -5581,14 +5581,14 @@
       <c r="C172" t="s">
         <v>118</v>
       </c>
-      <c r="D172" t="s">
+      <c r="E172" t="s">
         <v>119</v>
       </c>
-      <c r="E172" t="s">
-        <v>114</v>
+      <c r="F172" t="s">
+        <v>313</v>
       </c>
       <c r="G172" t="s">
-        <v>313</v>
+        <v>116</v>
       </c>
     </row>
     <row r="173" spans="1:7">
@@ -5601,14 +5601,14 @@
       <c r="C173" t="s">
         <v>163</v>
       </c>
-      <c r="D173" t="s">
+      <c r="E173" t="s">
         <v>164</v>
       </c>
-      <c r="E173" t="s">
-        <v>165</v>
+      <c r="F173" t="s">
+        <v>313</v>
       </c>
       <c r="G173" t="s">
-        <v>313</v>
+        <v>165</v>
       </c>
     </row>
     <row r="174" spans="1:7">
@@ -5621,14 +5621,14 @@
       <c r="C174" t="s">
         <v>163</v>
       </c>
-      <c r="D174" t="s">
+      <c r="E174" t="s">
         <v>164</v>
       </c>
-      <c r="E174" t="s">
-        <v>165</v>
+      <c r="F174" t="s">
+        <v>313</v>
       </c>
       <c r="G174" t="s">
-        <v>313</v>
+        <v>165</v>
       </c>
     </row>
     <row r="175" spans="1:7">
@@ -5641,14 +5641,14 @@
       <c r="C175" t="s">
         <v>163</v>
       </c>
-      <c r="D175" t="s">
+      <c r="E175" t="s">
         <v>164</v>
       </c>
-      <c r="E175" t="s">
-        <v>165</v>
+      <c r="F175" t="s">
+        <v>313</v>
       </c>
       <c r="G175" t="s">
-        <v>313</v>
+        <v>165</v>
       </c>
     </row>
     <row r="176" spans="1:7">
@@ -5661,14 +5661,14 @@
       <c r="C176" t="s">
         <v>163</v>
       </c>
-      <c r="D176" t="s">
+      <c r="E176" t="s">
         <v>164</v>
       </c>
-      <c r="E176" t="s">
-        <v>165</v>
+      <c r="F176" t="s">
+        <v>313</v>
       </c>
       <c r="G176" t="s">
-        <v>313</v>
+        <v>165</v>
       </c>
     </row>
     <row r="177" spans="1:7">
@@ -5681,14 +5681,14 @@
       <c r="C177" t="s">
         <v>163</v>
       </c>
-      <c r="D177" t="s">
+      <c r="E177" t="s">
         <v>164</v>
       </c>
-      <c r="E177" t="s">
-        <v>165</v>
+      <c r="F177" t="s">
+        <v>320</v>
       </c>
       <c r="G177" t="s">
-        <v>320</v>
+        <v>165</v>
       </c>
     </row>
     <row r="178" spans="1:7">
@@ -5701,14 +5701,14 @@
       <c r="C178" t="s">
         <v>163</v>
       </c>
-      <c r="D178" t="s">
+      <c r="E178" t="s">
         <v>164</v>
       </c>
-      <c r="E178" t="s">
-        <v>165</v>
+      <c r="F178" t="s">
+        <v>320</v>
       </c>
       <c r="G178" t="s">
-        <v>320</v>
+        <v>165</v>
       </c>
     </row>
     <row r="179" spans="1:7">
@@ -5721,14 +5721,14 @@
       <c r="C179" t="s">
         <v>163</v>
       </c>
-      <c r="D179" t="s">
+      <c r="E179" t="s">
         <v>164</v>
       </c>
-      <c r="E179" t="s">
-        <v>165</v>
+      <c r="F179" t="s">
+        <v>320</v>
       </c>
       <c r="G179" t="s">
-        <v>320</v>
+        <v>165</v>
       </c>
     </row>
     <row r="180" spans="1:7">
@@ -5741,14 +5741,14 @@
       <c r="C180" t="s">
         <v>163</v>
       </c>
-      <c r="D180" t="s">
+      <c r="E180" t="s">
         <v>164</v>
       </c>
-      <c r="E180" t="s">
-        <v>165</v>
+      <c r="F180" t="s">
+        <v>320</v>
       </c>
       <c r="G180" t="s">
-        <v>320</v>
+        <v>165</v>
       </c>
     </row>
     <row r="181" spans="1:7">
@@ -5765,13 +5765,13 @@
         <v>326</v>
       </c>
       <c r="E181" t="s">
-        <v>165</v>
+        <v>327</v>
       </c>
       <c r="F181" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="G181" t="s">
-        <v>328</v>
+        <v>165</v>
       </c>
     </row>
     <row r="182" spans="1:7">
@@ -5788,13 +5788,13 @@
         <v>326</v>
       </c>
       <c r="E182" t="s">
-        <v>165</v>
+        <v>327</v>
       </c>
       <c r="F182" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="G182" t="s">
-        <v>328</v>
+        <v>165</v>
       </c>
     </row>
     <row r="183" spans="1:7">
@@ -5811,13 +5811,13 @@
         <v>326</v>
       </c>
       <c r="E183" t="s">
-        <v>165</v>
+        <v>327</v>
       </c>
       <c r="F183" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="G183" t="s">
-        <v>328</v>
+        <v>165</v>
       </c>
     </row>
     <row r="184" spans="1:7">
@@ -5834,13 +5834,13 @@
         <v>326</v>
       </c>
       <c r="E184" t="s">
-        <v>165</v>
+        <v>327</v>
       </c>
       <c r="F184" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="G184" t="s">
-        <v>328</v>
+        <v>165</v>
       </c>
     </row>
     <row r="185" spans="1:7">
@@ -5857,13 +5857,13 @@
         <v>326</v>
       </c>
       <c r="E185" t="s">
-        <v>165</v>
+        <v>327</v>
       </c>
       <c r="F185" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="G185" t="s">
-        <v>328</v>
+        <v>165</v>
       </c>
     </row>
     <row r="186" spans="1:7">
@@ -5880,13 +5880,13 @@
         <v>326</v>
       </c>
       <c r="E186" t="s">
-        <v>165</v>
+        <v>327</v>
       </c>
       <c r="F186" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="G186" t="s">
-        <v>328</v>
+        <v>165</v>
       </c>
     </row>
     <row r="187" spans="1:7">
@@ -5903,13 +5903,13 @@
         <v>326</v>
       </c>
       <c r="E187" t="s">
-        <v>165</v>
+        <v>327</v>
       </c>
       <c r="F187" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="G187" t="s">
-        <v>328</v>
+        <v>165</v>
       </c>
     </row>
     <row r="188" spans="1:7">
@@ -5926,13 +5926,13 @@
         <v>326</v>
       </c>
       <c r="E188" t="s">
-        <v>165</v>
+        <v>327</v>
       </c>
       <c r="F188" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="G188" t="s">
-        <v>328</v>
+        <v>165</v>
       </c>
     </row>
     <row r="189" spans="1:7">
@@ -5949,13 +5949,13 @@
         <v>326</v>
       </c>
       <c r="E189" t="s">
-        <v>165</v>
+        <v>327</v>
       </c>
       <c r="F189" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="G189" t="s">
-        <v>328</v>
+        <v>165</v>
       </c>
     </row>
     <row r="190" spans="1:7">
@@ -5972,13 +5972,13 @@
         <v>326</v>
       </c>
       <c r="E190" t="s">
-        <v>165</v>
+        <v>327</v>
       </c>
       <c r="F190" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="G190" t="s">
-        <v>328</v>
+        <v>165</v>
       </c>
     </row>
     <row r="191" spans="1:7">
@@ -5995,13 +5995,13 @@
         <v>326</v>
       </c>
       <c r="E191" t="s">
-        <v>165</v>
+        <v>327</v>
       </c>
       <c r="F191" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="G191" t="s">
-        <v>328</v>
+        <v>165</v>
       </c>
     </row>
     <row r="192" spans="1:7">
@@ -6018,13 +6018,13 @@
         <v>326</v>
       </c>
       <c r="E192" t="s">
-        <v>165</v>
+        <v>327</v>
       </c>
       <c r="F192" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="G192" t="s">
-        <v>328</v>
+        <v>165</v>
       </c>
     </row>
     <row r="193" spans="1:7">
@@ -6035,19 +6035,19 @@
         <v>8</v>
       </c>
       <c r="C193" t="s">
-        <v>275</v>
+        <v>341</v>
       </c>
       <c r="D193" t="s">
-        <v>341</v>
+        <v>326</v>
       </c>
       <c r="E193" t="s">
-        <v>165</v>
+        <v>276</v>
       </c>
       <c r="F193" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="G193" t="s">
-        <v>328</v>
+        <v>165</v>
       </c>
     </row>
     <row r="194" spans="1:7">
@@ -6064,13 +6064,13 @@
         <v>326</v>
       </c>
       <c r="E194" t="s">
-        <v>165</v>
+        <v>327</v>
       </c>
       <c r="F194" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="G194" t="s">
-        <v>328</v>
+        <v>165</v>
       </c>
     </row>
     <row r="195" spans="1:7">
@@ -6087,13 +6087,13 @@
         <v>326</v>
       </c>
       <c r="E195" t="s">
-        <v>165</v>
+        <v>327</v>
       </c>
       <c r="F195" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="G195" t="s">
-        <v>328</v>
+        <v>165</v>
       </c>
     </row>
     <row r="196" spans="1:7">
@@ -6110,13 +6110,13 @@
         <v>326</v>
       </c>
       <c r="E196" t="s">
-        <v>165</v>
+        <v>327</v>
       </c>
       <c r="F196" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="G196" t="s">
-        <v>328</v>
+        <v>165</v>
       </c>
     </row>
     <row r="197" spans="1:7">
@@ -6133,13 +6133,13 @@
         <v>326</v>
       </c>
       <c r="E197" t="s">
-        <v>165</v>
+        <v>327</v>
       </c>
       <c r="F197" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="G197" t="s">
-        <v>328</v>
+        <v>165</v>
       </c>
     </row>
     <row r="198" spans="1:7">
@@ -6156,13 +6156,13 @@
         <v>326</v>
       </c>
       <c r="E198" t="s">
-        <v>165</v>
+        <v>327</v>
       </c>
       <c r="F198" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="G198" t="s">
-        <v>328</v>
+        <v>165</v>
       </c>
     </row>
     <row r="199" spans="1:7">
@@ -6173,19 +6173,19 @@
         <v>8</v>
       </c>
       <c r="C199" t="s">
-        <v>325</v>
+        <v>348</v>
       </c>
       <c r="D199" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="E199" t="s">
-        <v>165</v>
+        <v>327</v>
       </c>
       <c r="F199" t="s">
-        <v>349</v>
+        <v>328</v>
       </c>
       <c r="G199" t="s">
-        <v>328</v>
+        <v>165</v>
       </c>
     </row>
     <row r="200" spans="1:7">
@@ -6196,19 +6196,19 @@
         <v>8</v>
       </c>
       <c r="C200" t="s">
-        <v>325</v>
+        <v>348</v>
       </c>
       <c r="D200" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="E200" t="s">
-        <v>165</v>
+        <v>327</v>
       </c>
       <c r="F200" t="s">
-        <v>349</v>
+        <v>328</v>
       </c>
       <c r="G200" t="s">
-        <v>328</v>
+        <v>165</v>
       </c>
     </row>
     <row r="201" spans="1:7">
@@ -6219,19 +6219,19 @@
         <v>8</v>
       </c>
       <c r="C201" t="s">
-        <v>325</v>
+        <v>348</v>
       </c>
       <c r="D201" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="E201" t="s">
-        <v>165</v>
+        <v>327</v>
       </c>
       <c r="F201" t="s">
-        <v>349</v>
+        <v>328</v>
       </c>
       <c r="G201" t="s">
-        <v>328</v>
+        <v>165</v>
       </c>
     </row>
     <row r="202" spans="1:7">
@@ -6242,19 +6242,19 @@
         <v>8</v>
       </c>
       <c r="C202" t="s">
-        <v>325</v>
+        <v>348</v>
       </c>
       <c r="D202" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="E202" t="s">
-        <v>165</v>
+        <v>327</v>
       </c>
       <c r="F202" t="s">
-        <v>349</v>
+        <v>328</v>
       </c>
       <c r="G202" t="s">
-        <v>328</v>
+        <v>165</v>
       </c>
     </row>
     <row r="203" spans="1:7">
@@ -6265,19 +6265,19 @@
         <v>8</v>
       </c>
       <c r="C203" t="s">
-        <v>275</v>
+        <v>341</v>
       </c>
       <c r="D203" t="s">
-        <v>341</v>
+        <v>349</v>
       </c>
       <c r="E203" t="s">
-        <v>165</v>
+        <v>276</v>
       </c>
       <c r="F203" t="s">
-        <v>349</v>
+        <v>328</v>
       </c>
       <c r="G203" t="s">
-        <v>328</v>
+        <v>165</v>
       </c>
     </row>
     <row r="204" spans="1:7">
@@ -6288,19 +6288,19 @@
         <v>8</v>
       </c>
       <c r="C204" t="s">
-        <v>325</v>
+        <v>348</v>
       </c>
       <c r="D204" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="E204" t="s">
-        <v>165</v>
+        <v>327</v>
       </c>
       <c r="F204" t="s">
-        <v>349</v>
+        <v>328</v>
       </c>
       <c r="G204" t="s">
-        <v>328</v>
+        <v>165</v>
       </c>
     </row>
     <row r="205" spans="1:7">
@@ -6311,19 +6311,19 @@
         <v>8</v>
       </c>
       <c r="C205" t="s">
-        <v>325</v>
+        <v>356</v>
       </c>
       <c r="D205" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="E205" t="s">
-        <v>165</v>
+        <v>327</v>
       </c>
       <c r="F205" t="s">
-        <v>357</v>
+        <v>328</v>
       </c>
       <c r="G205" t="s">
-        <v>328</v>
+        <v>165</v>
       </c>
     </row>
     <row r="206" spans="1:7">
@@ -6334,19 +6334,19 @@
         <v>8</v>
       </c>
       <c r="C206" t="s">
-        <v>325</v>
+        <v>356</v>
       </c>
       <c r="D206" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="E206" t="s">
-        <v>165</v>
+        <v>327</v>
       </c>
       <c r="F206" t="s">
-        <v>357</v>
+        <v>328</v>
       </c>
       <c r="G206" t="s">
-        <v>328</v>
+        <v>165</v>
       </c>
     </row>
     <row r="207" spans="1:7">
@@ -6357,19 +6357,19 @@
         <v>8</v>
       </c>
       <c r="C207" t="s">
-        <v>325</v>
+        <v>356</v>
       </c>
       <c r="D207" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="E207" t="s">
-        <v>165</v>
+        <v>327</v>
       </c>
       <c r="F207" t="s">
-        <v>357</v>
+        <v>328</v>
       </c>
       <c r="G207" t="s">
-        <v>328</v>
+        <v>165</v>
       </c>
     </row>
     <row r="208" spans="1:7">
@@ -6380,19 +6380,19 @@
         <v>8</v>
       </c>
       <c r="C208" t="s">
-        <v>275</v>
+        <v>341</v>
       </c>
       <c r="D208" t="s">
-        <v>341</v>
+        <v>357</v>
       </c>
       <c r="E208" t="s">
-        <v>165</v>
+        <v>276</v>
       </c>
       <c r="F208" t="s">
-        <v>357</v>
+        <v>328</v>
       </c>
       <c r="G208" t="s">
-        <v>328</v>
+        <v>165</v>
       </c>
     </row>
     <row r="209" spans="1:7">
@@ -6403,19 +6403,19 @@
         <v>8</v>
       </c>
       <c r="C209" t="s">
-        <v>325</v>
+        <v>356</v>
       </c>
       <c r="D209" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="E209" t="s">
-        <v>165</v>
+        <v>327</v>
       </c>
       <c r="F209" t="s">
-        <v>357</v>
+        <v>328</v>
       </c>
       <c r="G209" t="s">
-        <v>328</v>
+        <v>165</v>
       </c>
     </row>
     <row r="210" spans="1:7">
@@ -6432,13 +6432,13 @@
         <v>364</v>
       </c>
       <c r="E210" t="s">
-        <v>165</v>
+        <v>365</v>
       </c>
       <c r="F210" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="G210" t="s">
-        <v>366</v>
+        <v>165</v>
       </c>
     </row>
     <row r="211" spans="1:7">
@@ -6455,13 +6455,13 @@
         <v>364</v>
       </c>
       <c r="E211" t="s">
-        <v>165</v>
+        <v>365</v>
       </c>
       <c r="F211" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="G211" t="s">
-        <v>366</v>
+        <v>165</v>
       </c>
     </row>
     <row r="212" spans="1:7">
@@ -6478,13 +6478,13 @@
         <v>364</v>
       </c>
       <c r="E212" t="s">
-        <v>165</v>
+        <v>365</v>
       </c>
       <c r="F212" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="G212" t="s">
-        <v>366</v>
+        <v>165</v>
       </c>
     </row>
     <row r="213" spans="1:7">
@@ -6501,13 +6501,13 @@
         <v>364</v>
       </c>
       <c r="E213" t="s">
-        <v>165</v>
+        <v>365</v>
       </c>
       <c r="F213" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="G213" t="s">
-        <v>366</v>
+        <v>165</v>
       </c>
     </row>
     <row r="214" spans="1:7">
@@ -6524,13 +6524,13 @@
         <v>364</v>
       </c>
       <c r="E214" t="s">
-        <v>165</v>
+        <v>365</v>
       </c>
       <c r="F214" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="G214" t="s">
-        <v>366</v>
+        <v>165</v>
       </c>
     </row>
     <row r="215" spans="1:7">
@@ -6541,19 +6541,19 @@
         <v>8</v>
       </c>
       <c r="C215" t="s">
-        <v>325</v>
+        <v>348</v>
       </c>
       <c r="D215" t="s">
-        <v>348</v>
+        <v>364</v>
       </c>
       <c r="E215" t="s">
-        <v>165</v>
+        <v>327</v>
       </c>
       <c r="F215" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="G215" t="s">
-        <v>366</v>
+        <v>165</v>
       </c>
     </row>
     <row r="216" spans="1:7">
@@ -6570,13 +6570,13 @@
         <v>364</v>
       </c>
       <c r="E216" t="s">
-        <v>165</v>
+        <v>365</v>
       </c>
       <c r="F216" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="G216" t="s">
-        <v>366</v>
+        <v>165</v>
       </c>
     </row>
     <row r="217" spans="1:7">
@@ -6593,13 +6593,13 @@
         <v>364</v>
       </c>
       <c r="E217" t="s">
-        <v>165</v>
+        <v>365</v>
       </c>
       <c r="F217" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="G217" t="s">
-        <v>366</v>
+        <v>165</v>
       </c>
     </row>
     <row r="218" spans="1:7">
@@ -6616,13 +6616,13 @@
         <v>364</v>
       </c>
       <c r="E218" t="s">
-        <v>165</v>
+        <v>365</v>
       </c>
       <c r="F218" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="G218" t="s">
-        <v>366</v>
+        <v>165</v>
       </c>
     </row>
     <row r="219" spans="1:7">
@@ -6639,13 +6639,13 @@
         <v>364</v>
       </c>
       <c r="E219" t="s">
-        <v>165</v>
+        <v>365</v>
       </c>
       <c r="F219" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="G219" t="s">
-        <v>366</v>
+        <v>165</v>
       </c>
     </row>
     <row r="220" spans="1:7">
@@ -6656,19 +6656,19 @@
         <v>8</v>
       </c>
       <c r="C220" t="s">
-        <v>269</v>
+        <v>309</v>
       </c>
       <c r="D220" t="s">
-        <v>309</v>
+        <v>364</v>
       </c>
       <c r="E220" t="s">
-        <v>165</v>
+        <v>271</v>
       </c>
       <c r="F220" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="G220" t="s">
-        <v>366</v>
+        <v>165</v>
       </c>
     </row>
     <row r="221" spans="1:7">
@@ -6685,13 +6685,13 @@
         <v>364</v>
       </c>
       <c r="E221" t="s">
-        <v>165</v>
+        <v>365</v>
       </c>
       <c r="F221" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="G221" t="s">
-        <v>366</v>
+        <v>165</v>
       </c>
     </row>
     <row r="222" spans="1:7">
@@ -6708,13 +6708,13 @@
         <v>364</v>
       </c>
       <c r="E222" t="s">
-        <v>165</v>
+        <v>365</v>
       </c>
       <c r="F222" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="G222" t="s">
-        <v>366</v>
+        <v>165</v>
       </c>
     </row>
     <row r="223" spans="1:7">
@@ -6731,13 +6731,13 @@
         <v>364</v>
       </c>
       <c r="E223" t="s">
-        <v>165</v>
+        <v>365</v>
       </c>
       <c r="F223" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="G223" t="s">
-        <v>366</v>
+        <v>165</v>
       </c>
     </row>
     <row r="224" spans="1:7">
@@ -6754,13 +6754,13 @@
         <v>364</v>
       </c>
       <c r="E224" t="s">
-        <v>165</v>
+        <v>365</v>
       </c>
       <c r="F224" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="G224" t="s">
-        <v>366</v>
+        <v>165</v>
       </c>
     </row>
     <row r="225" spans="1:7">
@@ -6777,13 +6777,13 @@
         <v>364</v>
       </c>
       <c r="E225" t="s">
-        <v>165</v>
+        <v>365</v>
       </c>
       <c r="F225" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="G225" t="s">
-        <v>366</v>
+        <v>165</v>
       </c>
     </row>
     <row r="226" spans="1:7">
@@ -6797,16 +6797,16 @@
         <v>275</v>
       </c>
       <c r="D226" t="s">
+        <v>364</v>
+      </c>
+      <c r="E226" t="s">
         <v>276</v>
       </c>
-      <c r="E226" t="s">
-        <v>165</v>
-      </c>
       <c r="F226" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="G226" t="s">
-        <v>366</v>
+        <v>165</v>
       </c>
     </row>
     <row r="227" spans="1:7">
@@ -6823,13 +6823,13 @@
         <v>364</v>
       </c>
       <c r="E227" t="s">
-        <v>165</v>
+        <v>365</v>
       </c>
       <c r="F227" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="G227" t="s">
-        <v>366</v>
+        <v>165</v>
       </c>
     </row>
     <row r="228" spans="1:7">
@@ -6843,16 +6843,16 @@
         <v>163</v>
       </c>
       <c r="D228" t="s">
+        <v>364</v>
+      </c>
+      <c r="E228" t="s">
         <v>164</v>
       </c>
-      <c r="E228" t="s">
-        <v>165</v>
-      </c>
       <c r="F228" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="G228" t="s">
-        <v>366</v>
+        <v>165</v>
       </c>
     </row>
     <row r="229" spans="1:7">
@@ -6863,19 +6863,19 @@
         <v>8</v>
       </c>
       <c r="C229" t="s">
-        <v>363</v>
+        <v>386</v>
       </c>
       <c r="D229" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="E229" t="s">
-        <v>165</v>
+        <v>365</v>
       </c>
       <c r="F229" t="s">
-        <v>387</v>
+        <v>366</v>
       </c>
       <c r="G229" t="s">
-        <v>366</v>
+        <v>165</v>
       </c>
     </row>
     <row r="230" spans="1:7">
@@ -6886,19 +6886,19 @@
         <v>8</v>
       </c>
       <c r="C230" t="s">
-        <v>363</v>
+        <v>386</v>
       </c>
       <c r="D230" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="E230" t="s">
-        <v>165</v>
+        <v>365</v>
       </c>
       <c r="F230" t="s">
-        <v>387</v>
+        <v>366</v>
       </c>
       <c r="G230" t="s">
-        <v>366</v>
+        <v>165</v>
       </c>
     </row>
     <row r="231" spans="1:7">
@@ -6909,19 +6909,19 @@
         <v>8</v>
       </c>
       <c r="C231" t="s">
-        <v>269</v>
+        <v>293</v>
       </c>
       <c r="D231" t="s">
-        <v>293</v>
+        <v>387</v>
       </c>
       <c r="E231" t="s">
-        <v>165</v>
+        <v>271</v>
       </c>
       <c r="F231" t="s">
-        <v>387</v>
+        <v>366</v>
       </c>
       <c r="G231" t="s">
-        <v>366</v>
+        <v>165</v>
       </c>
     </row>
     <row r="232" spans="1:7">
@@ -6932,19 +6932,19 @@
         <v>8</v>
       </c>
       <c r="C232" t="s">
-        <v>269</v>
+        <v>309</v>
       </c>
       <c r="D232" t="s">
-        <v>309</v>
+        <v>387</v>
       </c>
       <c r="E232" t="s">
-        <v>165</v>
+        <v>271</v>
       </c>
       <c r="F232" t="s">
-        <v>387</v>
+        <v>366</v>
       </c>
       <c r="G232" t="s">
-        <v>366</v>
+        <v>165</v>
       </c>
     </row>
     <row r="233" spans="1:7">
@@ -6955,19 +6955,19 @@
         <v>8</v>
       </c>
       <c r="C233" t="s">
-        <v>363</v>
+        <v>386</v>
       </c>
       <c r="D233" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="E233" t="s">
-        <v>165</v>
+        <v>365</v>
       </c>
       <c r="F233" t="s">
-        <v>387</v>
+        <v>366</v>
       </c>
       <c r="G233" t="s">
-        <v>366</v>
+        <v>165</v>
       </c>
     </row>
     <row r="234" spans="1:7">
@@ -6978,19 +6978,19 @@
         <v>8</v>
       </c>
       <c r="C234" t="s">
-        <v>363</v>
+        <v>386</v>
       </c>
       <c r="D234" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="E234" t="s">
-        <v>165</v>
+        <v>365</v>
       </c>
       <c r="F234" t="s">
-        <v>387</v>
+        <v>366</v>
       </c>
       <c r="G234" t="s">
-        <v>366</v>
+        <v>165</v>
       </c>
     </row>
     <row r="235" spans="1:7">
@@ -7001,19 +7001,19 @@
         <v>8</v>
       </c>
       <c r="C235" t="s">
-        <v>363</v>
+        <v>386</v>
       </c>
       <c r="D235" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="E235" t="s">
-        <v>165</v>
+        <v>365</v>
       </c>
       <c r="F235" t="s">
-        <v>387</v>
+        <v>366</v>
       </c>
       <c r="G235" t="s">
-        <v>366</v>
+        <v>165</v>
       </c>
     </row>
     <row r="236" spans="1:7">
@@ -7024,19 +7024,19 @@
         <v>8</v>
       </c>
       <c r="C236" t="s">
-        <v>363</v>
+        <v>386</v>
       </c>
       <c r="D236" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="E236" t="s">
-        <v>165</v>
+        <v>365</v>
       </c>
       <c r="F236" t="s">
-        <v>387</v>
+        <v>366</v>
       </c>
       <c r="G236" t="s">
-        <v>366</v>
+        <v>165</v>
       </c>
     </row>
     <row r="237" spans="1:7">
@@ -7047,19 +7047,19 @@
         <v>8</v>
       </c>
       <c r="C237" t="s">
-        <v>363</v>
+        <v>386</v>
       </c>
       <c r="D237" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="E237" t="s">
-        <v>165</v>
+        <v>365</v>
       </c>
       <c r="F237" t="s">
-        <v>387</v>
+        <v>366</v>
       </c>
       <c r="G237" t="s">
-        <v>366</v>
+        <v>165</v>
       </c>
     </row>
     <row r="238" spans="1:7">
@@ -7070,19 +7070,19 @@
         <v>8</v>
       </c>
       <c r="C238" t="s">
-        <v>363</v>
+        <v>386</v>
       </c>
       <c r="D238" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="E238" t="s">
-        <v>165</v>
+        <v>365</v>
       </c>
       <c r="F238" t="s">
-        <v>387</v>
+        <v>366</v>
       </c>
       <c r="G238" t="s">
-        <v>366</v>
+        <v>165</v>
       </c>
     </row>
     <row r="239" spans="1:7">
@@ -7093,19 +7093,19 @@
         <v>8</v>
       </c>
       <c r="C239" t="s">
-        <v>363</v>
+        <v>398</v>
       </c>
       <c r="D239" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="E239" t="s">
-        <v>165</v>
+        <v>365</v>
       </c>
       <c r="F239" t="s">
-        <v>399</v>
+        <v>366</v>
       </c>
       <c r="G239" t="s">
-        <v>366</v>
+        <v>165</v>
       </c>
     </row>
     <row r="240" spans="1:7">
@@ -7119,16 +7119,16 @@
         <v>163</v>
       </c>
       <c r="D240" t="s">
+        <v>401</v>
+      </c>
+      <c r="E240" t="s">
         <v>164</v>
       </c>
-      <c r="E240" t="s">
-        <v>165</v>
-      </c>
       <c r="F240" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="G240" t="s">
-        <v>402</v>
+        <v>165</v>
       </c>
     </row>
     <row r="241" spans="1:7">
@@ -7142,16 +7142,16 @@
         <v>163</v>
       </c>
       <c r="D241" t="s">
+        <v>401</v>
+      </c>
+      <c r="E241" t="s">
         <v>164</v>
       </c>
-      <c r="E241" t="s">
-        <v>165</v>
-      </c>
       <c r="F241" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="G241" t="s">
-        <v>402</v>
+        <v>165</v>
       </c>
     </row>
     <row r="242" spans="1:7">
@@ -7165,16 +7165,16 @@
         <v>163</v>
       </c>
       <c r="D242" t="s">
+        <v>401</v>
+      </c>
+      <c r="E242" t="s">
         <v>164</v>
       </c>
-      <c r="E242" t="s">
-        <v>165</v>
-      </c>
       <c r="F242" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="G242" t="s">
-        <v>402</v>
+        <v>165</v>
       </c>
     </row>
     <row r="243" spans="1:7">
@@ -7188,16 +7188,16 @@
         <v>163</v>
       </c>
       <c r="D243" t="s">
+        <v>401</v>
+      </c>
+      <c r="E243" t="s">
         <v>164</v>
       </c>
-      <c r="E243" t="s">
-        <v>165</v>
-      </c>
       <c r="F243" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="G243" t="s">
-        <v>402</v>
+        <v>165</v>
       </c>
     </row>
     <row r="244" spans="1:7">
@@ -7211,16 +7211,16 @@
         <v>163</v>
       </c>
       <c r="D244" t="s">
+        <v>401</v>
+      </c>
+      <c r="E244" t="s">
         <v>164</v>
       </c>
-      <c r="E244" t="s">
-        <v>165</v>
-      </c>
       <c r="F244" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="G244" t="s">
-        <v>402</v>
+        <v>165</v>
       </c>
     </row>
     <row r="245" spans="1:7">
@@ -7234,16 +7234,16 @@
         <v>163</v>
       </c>
       <c r="D245" t="s">
+        <v>401</v>
+      </c>
+      <c r="E245" t="s">
         <v>164</v>
       </c>
-      <c r="E245" t="s">
-        <v>165</v>
-      </c>
       <c r="F245" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="G245" t="s">
-        <v>402</v>
+        <v>165</v>
       </c>
     </row>
     <row r="246" spans="1:7">
@@ -7254,19 +7254,19 @@
         <v>8</v>
       </c>
       <c r="C246" t="s">
-        <v>255</v>
+        <v>409</v>
       </c>
       <c r="D246" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="E246" t="s">
-        <v>165</v>
+        <v>256</v>
       </c>
       <c r="F246" t="s">
-        <v>410</v>
+        <v>402</v>
       </c>
       <c r="G246" t="s">
-        <v>402</v>
+        <v>165</v>
       </c>
     </row>
     <row r="247" spans="1:7">
@@ -7279,14 +7279,14 @@
       <c r="C247" t="s">
         <v>95</v>
       </c>
-      <c r="D247" t="s">
+      <c r="E247" t="s">
         <v>96</v>
       </c>
-      <c r="E247" t="s">
+      <c r="F247" t="s">
+        <v>412</v>
+      </c>
+      <c r="G247" t="s">
         <v>97</v>
-      </c>
-      <c r="G247" t="s">
-        <v>412</v>
       </c>
     </row>
     <row r="248" spans="1:7">
@@ -7299,14 +7299,14 @@
       <c r="C248" t="s">
         <v>95</v>
       </c>
-      <c r="D248" t="s">
+      <c r="E248" t="s">
         <v>96</v>
       </c>
-      <c r="E248" t="s">
+      <c r="F248" t="s">
+        <v>412</v>
+      </c>
+      <c r="G248" t="s">
         <v>97</v>
-      </c>
-      <c r="G248" t="s">
-        <v>412</v>
       </c>
     </row>
     <row r="249" spans="1:7">
@@ -7319,14 +7319,14 @@
       <c r="C249" t="s">
         <v>415</v>
       </c>
-      <c r="D249" t="s">
+      <c r="E249" t="s">
         <v>416</v>
       </c>
-      <c r="E249" t="s">
+      <c r="F249" t="s">
+        <v>412</v>
+      </c>
+      <c r="G249" t="s">
         <v>97</v>
-      </c>
-      <c r="G249" t="s">
-        <v>412</v>
       </c>
     </row>
     <row r="250" spans="1:7">
@@ -7339,14 +7339,14 @@
       <c r="C250" t="s">
         <v>95</v>
       </c>
-      <c r="D250" t="s">
+      <c r="E250" t="s">
         <v>96</v>
       </c>
-      <c r="E250" t="s">
+      <c r="F250" t="s">
+        <v>412</v>
+      </c>
+      <c r="G250" t="s">
         <v>97</v>
-      </c>
-      <c r="G250" t="s">
-        <v>412</v>
       </c>
     </row>
     <row r="251" spans="1:7">
@@ -7359,14 +7359,14 @@
       <c r="C251" t="s">
         <v>95</v>
       </c>
-      <c r="D251" t="s">
+      <c r="E251" t="s">
         <v>96</v>
       </c>
-      <c r="E251" t="s">
+      <c r="F251" t="s">
+        <v>412</v>
+      </c>
+      <c r="G251" t="s">
         <v>97</v>
-      </c>
-      <c r="G251" t="s">
-        <v>412</v>
       </c>
     </row>
     <row r="252" spans="1:7">
@@ -7379,14 +7379,14 @@
       <c r="C252" t="s">
         <v>95</v>
       </c>
-      <c r="D252" t="s">
+      <c r="E252" t="s">
         <v>96</v>
       </c>
-      <c r="E252" t="s">
+      <c r="F252" t="s">
+        <v>412</v>
+      </c>
+      <c r="G252" t="s">
         <v>97</v>
-      </c>
-      <c r="G252" t="s">
-        <v>412</v>
       </c>
     </row>
     <row r="253" spans="1:7">
@@ -7399,14 +7399,14 @@
       <c r="C253" t="s">
         <v>421</v>
       </c>
-      <c r="D253" t="s">
+      <c r="E253" t="s">
         <v>422</v>
       </c>
-      <c r="E253" t="s">
-        <v>165</v>
+      <c r="F253" t="s">
+        <v>423</v>
       </c>
       <c r="G253" t="s">
-        <v>423</v>
+        <v>165</v>
       </c>
     </row>
     <row r="254" spans="1:7">
@@ -7419,14 +7419,14 @@
       <c r="C254" t="s">
         <v>219</v>
       </c>
-      <c r="D254" t="s">
+      <c r="E254" t="s">
         <v>220</v>
       </c>
-      <c r="E254" t="s">
-        <v>92</v>
+      <c r="F254" t="s">
+        <v>423</v>
       </c>
       <c r="G254" t="s">
-        <v>423</v>
+        <v>93</v>
       </c>
     </row>
     <row r="255" spans="1:7">
@@ -7439,14 +7439,14 @@
       <c r="C255" t="s">
         <v>426</v>
       </c>
-      <c r="D255" t="s">
+      <c r="E255" t="s">
         <v>427</v>
       </c>
-      <c r="E255" t="s">
-        <v>92</v>
+      <c r="F255" t="s">
+        <v>423</v>
       </c>
       <c r="G255" t="s">
-        <v>423</v>
+        <v>93</v>
       </c>
     </row>
     <row r="256" spans="1:7">
@@ -7459,14 +7459,14 @@
       <c r="C256" t="s">
         <v>426</v>
       </c>
-      <c r="D256" t="s">
+      <c r="E256" t="s">
         <v>427</v>
       </c>
-      <c r="E256" t="s">
-        <v>92</v>
+      <c r="F256" t="s">
+        <v>423</v>
       </c>
       <c r="G256" t="s">
-        <v>423</v>
+        <v>93</v>
       </c>
     </row>
     <row r="257" spans="1:7">
@@ -7479,14 +7479,14 @@
       <c r="C257" t="s">
         <v>426</v>
       </c>
-      <c r="D257" t="s">
+      <c r="E257" t="s">
         <v>427</v>
       </c>
-      <c r="E257" t="s">
-        <v>92</v>
+      <c r="F257" t="s">
+        <v>423</v>
       </c>
       <c r="G257" t="s">
-        <v>423</v>
+        <v>93</v>
       </c>
     </row>
     <row r="258" spans="1:7">
@@ -7499,14 +7499,14 @@
       <c r="C258" t="s">
         <v>325</v>
       </c>
-      <c r="D258" t="s">
-        <v>326</v>
-      </c>
       <c r="E258" t="s">
-        <v>165</v>
+        <v>327</v>
+      </c>
+      <c r="F258" t="s">
+        <v>423</v>
       </c>
       <c r="G258" t="s">
-        <v>423</v>
+        <v>165</v>
       </c>
     </row>
     <row r="259" spans="1:7">
@@ -7519,14 +7519,14 @@
       <c r="C259" t="s">
         <v>426</v>
       </c>
-      <c r="D259" t="s">
+      <c r="E259" t="s">
         <v>427</v>
       </c>
-      <c r="E259" t="s">
-        <v>92</v>
+      <c r="F259" t="s">
+        <v>423</v>
       </c>
       <c r="G259" t="s">
-        <v>423</v>
+        <v>93</v>
       </c>
     </row>
     <row r="260" spans="1:7">
@@ -7539,14 +7539,14 @@
       <c r="C260" t="s">
         <v>163</v>
       </c>
-      <c r="D260" t="s">
+      <c r="E260" t="s">
         <v>164</v>
       </c>
-      <c r="E260" t="s">
-        <v>165</v>
+      <c r="F260" t="s">
+        <v>423</v>
       </c>
       <c r="G260" t="s">
-        <v>423</v>
+        <v>165</v>
       </c>
     </row>
     <row r="261" spans="1:7">
@@ -7559,14 +7559,14 @@
       <c r="C261" t="s">
         <v>434</v>
       </c>
-      <c r="D261" t="s">
+      <c r="E261" t="s">
         <v>435</v>
       </c>
-      <c r="E261" t="s">
+      <c r="F261" t="s">
+        <v>423</v>
+      </c>
+      <c r="G261" t="s">
         <v>197</v>
-      </c>
-      <c r="G261" t="s">
-        <v>423</v>
       </c>
     </row>
     <row r="262" spans="1:7">
@@ -7579,14 +7579,14 @@
       <c r="C262" t="s">
         <v>163</v>
       </c>
-      <c r="D262" t="s">
+      <c r="E262" t="s">
         <v>164</v>
       </c>
-      <c r="E262" t="s">
-        <v>165</v>
+      <c r="F262" t="s">
+        <v>423</v>
       </c>
       <c r="G262" t="s">
-        <v>423</v>
+        <v>165</v>
       </c>
     </row>
     <row r="263" spans="1:7">
@@ -7599,14 +7599,14 @@
       <c r="C263" t="s">
         <v>438</v>
       </c>
-      <c r="D263" t="s">
+      <c r="E263" t="s">
         <v>439</v>
       </c>
-      <c r="E263" t="s">
+      <c r="F263" t="s">
+        <v>423</v>
+      </c>
+      <c r="G263" t="s">
         <v>184</v>
-      </c>
-      <c r="G263" t="s">
-        <v>423</v>
       </c>
     </row>
     <row r="264" spans="1:7">
@@ -7619,14 +7619,14 @@
       <c r="C264" t="s">
         <v>31</v>
       </c>
-      <c r="D264" t="s">
+      <c r="E264" t="s">
         <v>32</v>
       </c>
-      <c r="E264" t="s">
+      <c r="F264" t="s">
+        <v>423</v>
+      </c>
+      <c r="G264" t="s">
         <v>33</v>
-      </c>
-      <c r="G264" t="s">
-        <v>423</v>
       </c>
     </row>
     <row r="265" spans="1:7">
@@ -7639,14 +7639,14 @@
       <c r="C265" t="s">
         <v>9</v>
       </c>
-      <c r="D265" t="s">
-        <v>10</v>
-      </c>
       <c r="E265" t="s">
         <v>11</v>
       </c>
+      <c r="F265" t="s">
+        <v>423</v>
+      </c>
       <c r="G265" t="s">
-        <v>423</v>
+        <v>13</v>
       </c>
     </row>
     <row r="266" spans="1:7">
@@ -7659,14 +7659,14 @@
       <c r="C266" t="s">
         <v>443</v>
       </c>
-      <c r="D266" t="s">
+      <c r="E266" t="s">
         <v>444</v>
       </c>
-      <c r="E266" t="s">
-        <v>114</v>
+      <c r="F266" t="s">
+        <v>423</v>
       </c>
       <c r="G266" t="s">
-        <v>423</v>
+        <v>116</v>
       </c>
     </row>
     <row r="267" spans="1:7">
@@ -7679,14 +7679,14 @@
       <c r="C267" t="s">
         <v>118</v>
       </c>
-      <c r="D267" t="s">
+      <c r="E267" t="s">
         <v>119</v>
       </c>
-      <c r="E267" t="s">
-        <v>114</v>
+      <c r="F267" t="s">
+        <v>446</v>
       </c>
       <c r="G267" t="s">
-        <v>446</v>
+        <v>116</v>
       </c>
     </row>
     <row r="268" spans="1:7">
@@ -7699,14 +7699,14 @@
       <c r="C268" t="s">
         <v>202</v>
       </c>
-      <c r="D268" t="s">
+      <c r="E268" t="s">
         <v>203</v>
       </c>
-      <c r="E268" t="s">
+      <c r="F268" t="s">
+        <v>448</v>
+      </c>
+      <c r="G268" t="s">
         <v>184</v>
-      </c>
-      <c r="G268" t="s">
-        <v>448</v>
       </c>
     </row>
     <row r="269" spans="1:7">
@@ -7719,14 +7719,14 @@
       <c r="C269" t="s">
         <v>118</v>
       </c>
-      <c r="D269" t="s">
+      <c r="E269" t="s">
         <v>119</v>
       </c>
-      <c r="E269" t="s">
-        <v>114</v>
+      <c r="F269" t="s">
+        <v>450</v>
       </c>
       <c r="G269" t="s">
-        <v>450</v>
+        <v>116</v>
       </c>
     </row>
     <row r="270" spans="1:7">
@@ -7739,14 +7739,14 @@
       <c r="C270" t="s">
         <v>118</v>
       </c>
-      <c r="D270" t="s">
+      <c r="E270" t="s">
         <v>119</v>
       </c>
-      <c r="E270" t="s">
-        <v>114</v>
+      <c r="F270" t="s">
+        <v>450</v>
       </c>
       <c r="G270" t="s">
-        <v>450</v>
+        <v>116</v>
       </c>
     </row>
     <row r="271" spans="1:7">
@@ -7759,14 +7759,14 @@
       <c r="C271" t="s">
         <v>453</v>
       </c>
-      <c r="D271" t="s">
+      <c r="E271" t="s">
         <v>454</v>
       </c>
-      <c r="E271" t="s">
-        <v>114</v>
+      <c r="F271" t="s">
+        <v>455</v>
       </c>
       <c r="G271" t="s">
-        <v>455</v>
+        <v>116</v>
       </c>
     </row>
     <row r="272" spans="1:7">
@@ -7779,14 +7779,14 @@
       <c r="C272" t="s">
         <v>453</v>
       </c>
-      <c r="D272" t="s">
+      <c r="E272" t="s">
         <v>454</v>
       </c>
-      <c r="E272" t="s">
-        <v>114</v>
+      <c r="F272" t="s">
+        <v>455</v>
       </c>
       <c r="G272" t="s">
-        <v>455</v>
+        <v>116</v>
       </c>
     </row>
     <row r="273" spans="1:7">
@@ -7799,14 +7799,14 @@
       <c r="C273" t="s">
         <v>453</v>
       </c>
-      <c r="D273" t="s">
+      <c r="E273" t="s">
         <v>454</v>
       </c>
-      <c r="E273" t="s">
-        <v>114</v>
+      <c r="F273" t="s">
+        <v>455</v>
       </c>
       <c r="G273" t="s">
-        <v>455</v>
+        <v>116</v>
       </c>
     </row>
     <row r="274" spans="1:7">
@@ -7819,14 +7819,14 @@
       <c r="C274" t="s">
         <v>453</v>
       </c>
-      <c r="D274" t="s">
+      <c r="E274" t="s">
         <v>454</v>
       </c>
-      <c r="E274" t="s">
-        <v>114</v>
+      <c r="F274" t="s">
+        <v>455</v>
       </c>
       <c r="G274" t="s">
-        <v>455</v>
+        <v>116</v>
       </c>
     </row>
     <row r="275" spans="1:7">
@@ -7839,14 +7839,14 @@
       <c r="C275" t="s">
         <v>453</v>
       </c>
-      <c r="D275" t="s">
+      <c r="E275" t="s">
         <v>454</v>
       </c>
-      <c r="E275" t="s">
-        <v>114</v>
+      <c r="F275" t="s">
+        <v>455</v>
       </c>
       <c r="G275" t="s">
-        <v>455</v>
+        <v>116</v>
       </c>
     </row>
     <row r="276" spans="1:7">
@@ -7859,14 +7859,14 @@
       <c r="C276" t="s">
         <v>453</v>
       </c>
-      <c r="D276" t="s">
+      <c r="E276" t="s">
         <v>454</v>
       </c>
-      <c r="E276" t="s">
-        <v>114</v>
+      <c r="F276" t="s">
+        <v>455</v>
       </c>
       <c r="G276" t="s">
-        <v>455</v>
+        <v>116</v>
       </c>
     </row>
     <row r="277" spans="1:7">
@@ -7879,14 +7879,14 @@
       <c r="C277" t="s">
         <v>453</v>
       </c>
-      <c r="D277" t="s">
+      <c r="E277" t="s">
         <v>454</v>
       </c>
-      <c r="E277" t="s">
-        <v>114</v>
+      <c r="F277" t="s">
+        <v>455</v>
       </c>
       <c r="G277" t="s">
-        <v>455</v>
+        <v>116</v>
       </c>
     </row>
     <row r="278" spans="1:7">
@@ -7899,14 +7899,14 @@
       <c r="C278" t="s">
         <v>202</v>
       </c>
-      <c r="D278" t="s">
+      <c r="E278" t="s">
         <v>203</v>
       </c>
-      <c r="E278" t="s">
+      <c r="F278" t="s">
+        <v>463</v>
+      </c>
+      <c r="G278" t="s">
         <v>184</v>
-      </c>
-      <c r="G278" t="s">
-        <v>463</v>
       </c>
     </row>
     <row r="279" spans="1:7">
@@ -7919,14 +7919,14 @@
       <c r="C279" t="s">
         <v>51</v>
       </c>
-      <c r="D279" t="s">
-        <v>52</v>
-      </c>
       <c r="E279" t="s">
+        <v>53</v>
+      </c>
+      <c r="F279" t="s">
+        <v>463</v>
+      </c>
+      <c r="G279" t="s">
         <v>33</v>
-      </c>
-      <c r="G279" t="s">
-        <v>463</v>
       </c>
     </row>
     <row r="280" spans="1:7">
@@ -7939,14 +7939,14 @@
       <c r="C280" t="s">
         <v>9</v>
       </c>
-      <c r="D280" t="s">
-        <v>10</v>
-      </c>
       <c r="E280" t="s">
         <v>11</v>
       </c>
+      <c r="F280" t="s">
+        <v>463</v>
+      </c>
       <c r="G280" t="s">
-        <v>463</v>
+        <v>13</v>
       </c>
     </row>
     <row r="281" spans="1:7">
@@ -7959,14 +7959,14 @@
       <c r="C281" t="s">
         <v>170</v>
       </c>
-      <c r="D281" t="s">
+      <c r="E281" t="s">
         <v>171</v>
       </c>
-      <c r="E281" t="s">
-        <v>114</v>
+      <c r="F281" t="s">
+        <v>463</v>
       </c>
       <c r="G281" t="s">
-        <v>463</v>
+        <v>116</v>
       </c>
     </row>
     <row r="282" spans="1:7">
@@ -7979,14 +7979,14 @@
       <c r="C282" t="s">
         <v>124</v>
       </c>
-      <c r="D282" t="s">
+      <c r="E282" t="s">
         <v>125</v>
       </c>
-      <c r="E282" t="s">
+      <c r="F282" t="s">
+        <v>463</v>
+      </c>
+      <c r="G282" t="s">
         <v>126</v>
-      </c>
-      <c r="G282" t="s">
-        <v>463</v>
       </c>
     </row>
     <row r="283" spans="1:7">
@@ -7997,16 +7997,16 @@
         <v>8</v>
       </c>
       <c r="C283" t="s">
-        <v>363</v>
-      </c>
-      <c r="D283" t="s">
         <v>398</v>
       </c>
       <c r="E283" t="s">
-        <v>165</v>
+        <v>365</v>
+      </c>
+      <c r="F283" t="s">
+        <v>469</v>
       </c>
       <c r="G283" t="s">
-        <v>469</v>
+        <v>165</v>
       </c>
     </row>
     <row r="284" spans="1:7">
@@ -8019,14 +8019,14 @@
       <c r="C284" t="s">
         <v>124</v>
       </c>
-      <c r="D284" t="s">
+      <c r="E284" t="s">
         <v>125</v>
       </c>
-      <c r="E284" t="s">
+      <c r="F284" t="s">
+        <v>471</v>
+      </c>
+      <c r="G284" t="s">
         <v>126</v>
-      </c>
-      <c r="G284" t="s">
-        <v>471</v>
       </c>
     </row>
     <row r="285" spans="1:7">
@@ -8039,14 +8039,14 @@
       <c r="C285" t="s">
         <v>170</v>
       </c>
-      <c r="D285" t="s">
+      <c r="E285" t="s">
         <v>171</v>
       </c>
-      <c r="E285" t="s">
-        <v>114</v>
+      <c r="F285" t="s">
+        <v>473</v>
       </c>
       <c r="G285" t="s">
-        <v>473</v>
+        <v>116</v>
       </c>
     </row>
     <row r="286" spans="1:7">
@@ -8059,14 +8059,14 @@
       <c r="C286" t="s">
         <v>438</v>
       </c>
-      <c r="D286" t="s">
+      <c r="E286" t="s">
         <v>439</v>
       </c>
-      <c r="E286" t="s">
+      <c r="F286" t="s">
+        <v>475</v>
+      </c>
+      <c r="G286" t="s">
         <v>184</v>
-      </c>
-      <c r="G286" t="s">
-        <v>475</v>
       </c>
     </row>
     <row r="287" spans="1:7">
@@ -8079,14 +8079,14 @@
       <c r="C287" t="s">
         <v>438</v>
       </c>
-      <c r="D287" t="s">
+      <c r="E287" t="s">
         <v>439</v>
       </c>
-      <c r="E287" t="s">
+      <c r="F287" t="s">
+        <v>475</v>
+      </c>
+      <c r="G287" t="s">
         <v>184</v>
-      </c>
-      <c r="G287" t="s">
-        <v>475</v>
       </c>
     </row>
     <row r="288" spans="1:7">
@@ -8099,14 +8099,14 @@
       <c r="C288" t="s">
         <v>41</v>
       </c>
-      <c r="D288" t="s">
+      <c r="E288" t="s">
         <v>42</v>
       </c>
-      <c r="E288" t="s">
-        <v>11</v>
+      <c r="F288" t="s">
+        <v>475</v>
       </c>
       <c r="G288" t="s">
-        <v>475</v>
+        <v>13</v>
       </c>
     </row>
     <row r="289" spans="1:7">
@@ -8119,14 +8119,14 @@
       <c r="C289" t="s">
         <v>31</v>
       </c>
-      <c r="D289" t="s">
+      <c r="E289" t="s">
         <v>32</v>
       </c>
-      <c r="E289" t="s">
+      <c r="F289" t="s">
+        <v>475</v>
+      </c>
+      <c r="G289" t="s">
         <v>33</v>
-      </c>
-      <c r="G289" t="s">
-        <v>475</v>
       </c>
     </row>
     <row r="290" spans="1:7">
@@ -8139,14 +8139,14 @@
       <c r="C290" t="s">
         <v>31</v>
       </c>
-      <c r="D290" t="s">
+      <c r="E290" t="s">
         <v>32</v>
       </c>
-      <c r="E290" t="s">
+      <c r="F290" t="s">
+        <v>475</v>
+      </c>
+      <c r="G290" t="s">
         <v>33</v>
-      </c>
-      <c r="G290" t="s">
-        <v>475</v>
       </c>
     </row>
     <row r="291" spans="1:7">
@@ -8159,14 +8159,14 @@
       <c r="C291" t="s">
         <v>170</v>
       </c>
-      <c r="D291" t="s">
+      <c r="E291" t="s">
         <v>171</v>
       </c>
-      <c r="E291" t="s">
-        <v>114</v>
+      <c r="F291" t="s">
+        <v>475</v>
       </c>
       <c r="G291" t="s">
-        <v>475</v>
+        <v>116</v>
       </c>
     </row>
     <row r="292" spans="1:7">
@@ -8179,14 +8179,14 @@
       <c r="C292" t="s">
         <v>170</v>
       </c>
-      <c r="D292" t="s">
+      <c r="E292" t="s">
         <v>171</v>
       </c>
-      <c r="E292" t="s">
-        <v>114</v>
+      <c r="F292" t="s">
+        <v>475</v>
       </c>
       <c r="G292" t="s">
-        <v>475</v>
+        <v>116</v>
       </c>
     </row>
     <row r="293" spans="1:7">
@@ -8199,14 +8199,14 @@
       <c r="C293" t="s">
         <v>170</v>
       </c>
-      <c r="D293" t="s">
+      <c r="E293" t="s">
         <v>171</v>
       </c>
-      <c r="E293" t="s">
-        <v>114</v>
+      <c r="F293" t="s">
+        <v>475</v>
       </c>
       <c r="G293" t="s">
-        <v>475</v>
+        <v>116</v>
       </c>
     </row>
     <row r="294" spans="1:7">
@@ -8219,14 +8219,14 @@
       <c r="C294" t="s">
         <v>170</v>
       </c>
-      <c r="D294" t="s">
+      <c r="E294" t="s">
         <v>171</v>
       </c>
-      <c r="E294" t="s">
-        <v>114</v>
+      <c r="F294" t="s">
+        <v>475</v>
       </c>
       <c r="G294" t="s">
-        <v>475</v>
+        <v>116</v>
       </c>
     </row>
     <row r="295" spans="1:7">
@@ -8239,14 +8239,14 @@
       <c r="C295" t="s">
         <v>170</v>
       </c>
-      <c r="D295" t="s">
+      <c r="E295" t="s">
         <v>171</v>
       </c>
-      <c r="E295" t="s">
-        <v>114</v>
+      <c r="F295" t="s">
+        <v>485</v>
       </c>
       <c r="G295" t="s">
-        <v>485</v>
+        <v>116</v>
       </c>
     </row>
     <row r="296" spans="1:7">
@@ -8259,14 +8259,14 @@
       <c r="C296" t="s">
         <v>170</v>
       </c>
-      <c r="D296" t="s">
+      <c r="E296" t="s">
         <v>171</v>
       </c>
-      <c r="E296" t="s">
-        <v>114</v>
+      <c r="F296" t="s">
+        <v>485</v>
       </c>
       <c r="G296" t="s">
-        <v>485</v>
+        <v>116</v>
       </c>
     </row>
   </sheetData>

--- a/api/2/xlsx/fr/SectorCOFOG.xlsx
+++ b/api/2/xlsx/fr/SectorCOFOG.xlsx
@@ -22,18 +22,18 @@
     <t>status</t>
   </si>
   <si>
+    <t>codeforiati:category-code</t>
+  </si>
+  <si>
+    <t>codeforiati:group-code</t>
+  </si>
+  <si>
     <t>codeforiati:cofog-class</t>
   </si>
   <si>
-    <t>codeforiati:category-code</t>
-  </si>
-  <si>
     <t>codeforiati:cofog-group</t>
   </si>
   <si>
-    <t>codeforiati:group-code</t>
-  </si>
-  <si>
     <t>codeforiati:cofog-division</t>
   </si>
   <si>
@@ -43,18 +43,18 @@
     <t>active</t>
   </si>
   <si>
+    <t>111</t>
+  </si>
+  <si>
+    <t>110</t>
+  </si>
+  <si>
     <t>09.8.0 - Education n.e.c. (CS)</t>
   </si>
   <si>
-    <t>111</t>
-  </si>
-  <si>
     <t>09.8 - Education n.e.c.</t>
   </si>
   <si>
-    <t>110</t>
-  </si>
-  <si>
     <t>09 - Education</t>
   </si>
   <si>
@@ -82,12 +82,12 @@
     <t>11220</t>
   </si>
   <si>
+    <t>112</t>
+  </si>
+  <si>
     <t>09.1.2 - Primary education (IS)</t>
   </si>
   <si>
-    <t>112</t>
-  </si>
-  <si>
     <t>09.1 - Pre‐primary and primary education</t>
   </si>
   <si>
@@ -130,12 +130,12 @@
     <t>11320</t>
   </si>
   <si>
+    <t>113</t>
+  </si>
+  <si>
     <t>09.2.2 - Upper‐secondary education (IS)</t>
   </si>
   <si>
-    <t>113</t>
-  </si>
-  <si>
     <t>11330</t>
   </si>
   <si>
@@ -148,12 +148,12 @@
     <t>11420</t>
   </si>
   <si>
+    <t>114</t>
+  </si>
+  <si>
     <t>09.4.1 - First stage of tertiary education (IS)</t>
   </si>
   <si>
-    <t>114</t>
-  </si>
-  <si>
     <t>09.4 - Tertiary education</t>
   </si>
   <si>
@@ -169,18 +169,18 @@
     <t>12110</t>
   </si>
   <si>
+    <t>121</t>
+  </si>
+  <si>
+    <t>120</t>
+  </si>
+  <si>
     <t>07.6.0 - Health n.e.c. (CS)</t>
   </si>
   <si>
-    <t>121</t>
-  </si>
-  <si>
     <t>07.6 - Health n.e.c.</t>
   </si>
   <si>
-    <t>120</t>
-  </si>
-  <si>
     <t>12181</t>
   </si>
   <si>
@@ -286,15 +286,15 @@
     <t>14010</t>
   </si>
   <si>
+    <t>140</t>
+  </si>
+  <si>
     <t>06.3.0 - Water supply (CS)</t>
   </si>
   <si>
     <t>06.3 - Water supply</t>
   </si>
   <si>
-    <t>140</t>
-  </si>
-  <si>
     <t>06 - Housing and community amenities</t>
   </si>
   <si>
@@ -352,18 +352,18 @@
     <t>15110</t>
   </si>
   <si>
+    <t>151</t>
+  </si>
+  <si>
+    <t>150</t>
+  </si>
+  <si>
     <t>01.3.1 - General personnel services (CS)</t>
   </si>
   <si>
-    <t>151</t>
-  </si>
-  <si>
     <t>01.3 - General services</t>
   </si>
   <si>
-    <t>150</t>
-  </si>
-  <si>
     <t>01 - General public services</t>
   </si>
   <si>
@@ -622,15 +622,15 @@
     <t>16010</t>
   </si>
   <si>
+    <t>160</t>
+  </si>
+  <si>
     <t>10.9.0 - Social protection n.e.c. (CS)</t>
   </si>
   <si>
     <t>10.9 - Social protection n.e.c.</t>
   </si>
   <si>
-    <t>160</t>
-  </si>
-  <si>
     <t>16011</t>
   </si>
   <si>
@@ -823,18 +823,18 @@
     <t>23110</t>
   </si>
   <si>
+    <t>231</t>
+  </si>
+  <si>
+    <t>230</t>
+  </si>
+  <si>
     <t>04.3.5 - Electricity (CS)</t>
   </si>
   <si>
-    <t>231</t>
-  </si>
-  <si>
     <t>04.3 - Fuel and energy</t>
   </si>
   <si>
-    <t>230</t>
-  </si>
-  <si>
     <t>23111</t>
   </si>
   <si>
@@ -919,12 +919,12 @@
     <t>23510</t>
   </si>
   <si>
+    <t>235</t>
+  </si>
+  <si>
     <t>04.3.3 - Nuclear fuel (CS)</t>
   </si>
   <si>
-    <t>235</t>
-  </si>
-  <si>
     <t>23610</t>
   </si>
   <si>
@@ -991,18 +991,18 @@
     <t>31110</t>
   </si>
   <si>
+    <t>311</t>
+  </si>
+  <si>
+    <t>310</t>
+  </si>
+  <si>
     <t>04.2.1 - Agriculture (CS)</t>
   </si>
   <si>
-    <t>311</t>
-  </si>
-  <si>
     <t>04.2 - Agriculture, forestry, fishing and hunting</t>
   </si>
   <si>
-    <t>310</t>
-  </si>
-  <si>
     <t>31120</t>
   </si>
   <si>
@@ -1060,12 +1060,12 @@
     <t>31210</t>
   </si>
   <si>
+    <t>312</t>
+  </si>
+  <si>
     <t>04.2.2 - Forestry (CS)</t>
   </si>
   <si>
-    <t>312</t>
-  </si>
-  <si>
     <t>31220</t>
   </si>
   <si>
@@ -1084,12 +1084,12 @@
     <t>31310</t>
   </si>
   <si>
+    <t>313</t>
+  </si>
+  <si>
     <t>04.2.3 - Fishing and hunting (CS)</t>
   </si>
   <si>
-    <t>313</t>
-  </si>
-  <si>
     <t>31320</t>
   </si>
   <si>
@@ -1105,18 +1105,18 @@
     <t>32110</t>
   </si>
   <si>
+    <t>321</t>
+  </si>
+  <si>
+    <t>320</t>
+  </si>
+  <si>
     <t>04.4.2 - Manufacturing (CS)</t>
   </si>
   <si>
-    <t>321</t>
-  </si>
-  <si>
     <t>04.4 - Mining, manufacturing and construction</t>
   </si>
   <si>
-    <t>320</t>
-  </si>
-  <si>
     <t>32120</t>
   </si>
   <si>
@@ -1174,12 +1174,12 @@
     <t>32210</t>
   </si>
   <si>
+    <t>322</t>
+  </si>
+  <si>
     <t>04.4.1 - Mining of mineral resources other than mineral fuels (CS)</t>
   </si>
   <si>
-    <t>322</t>
-  </si>
-  <si>
     <t>32220</t>
   </si>
   <si>
@@ -1210,12 +1210,12 @@
     <t>32310</t>
   </si>
   <si>
+    <t>323</t>
+  </si>
+  <si>
     <t>04.4.3 - Construction (CS)</t>
   </si>
   <si>
-    <t>323</t>
-  </si>
-  <si>
     <t>33110</t>
   </si>
   <si>
@@ -1243,12 +1243,12 @@
     <t>33210</t>
   </si>
   <si>
+    <t>332</t>
+  </si>
+  <si>
     <t>04.7.3 - Tourism (CS)</t>
   </si>
   <si>
-    <t>332</t>
-  </si>
-  <si>
     <t>41010</t>
   </si>
   <si>
@@ -1279,15 +1279,15 @@
     <t>43010</t>
   </si>
   <si>
+    <t>430</t>
+  </si>
+  <si>
     <t>04.9.0 - Economic affairs n.e.c. (CS)</t>
   </si>
   <si>
     <t>04.9 - Economic affairs n.e.c.</t>
   </si>
   <si>
-    <t>430</t>
-  </si>
-  <si>
     <t>43030</t>
   </si>
   <si>
@@ -1375,13 +1375,13 @@
     <t>60010</t>
   </si>
   <si>
+    <t>600</t>
+  </si>
+  <si>
     <t>01.7.0 - Public debt transactions (CS)</t>
   </si>
   <si>
     <t>01.7 - Public debt transactions</t>
-  </si>
-  <si>
-    <t>600</t>
   </si>
   <si>
     <t>60020</t>
@@ -1863,16 +1863,16 @@
         <v>8</v>
       </c>
       <c r="C3" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="D3" t="s">
         <v>10</v>
       </c>
       <c r="E3" t="s">
+        <v>15</v>
+      </c>
+      <c r="F3" t="s">
         <v>16</v>
-      </c>
-      <c r="F3" t="s">
-        <v>12</v>
       </c>
       <c r="G3" t="s">
         <v>13</v>
@@ -1909,16 +1909,16 @@
         <v>8</v>
       </c>
       <c r="C5" t="s">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="D5" t="s">
         <v>10</v>
       </c>
       <c r="E5" t="s">
+        <v>19</v>
+      </c>
+      <c r="F5" t="s">
         <v>20</v>
-      </c>
-      <c r="F5" t="s">
-        <v>12</v>
       </c>
       <c r="G5" t="s">
         <v>13</v>
@@ -1935,13 +1935,13 @@
         <v>22</v>
       </c>
       <c r="D6" t="s">
+        <v>10</v>
+      </c>
+      <c r="E6" t="s">
         <v>23</v>
       </c>
-      <c r="E6" t="s">
+      <c r="F6" t="s">
         <v>24</v>
-      </c>
-      <c r="F6" t="s">
-        <v>12</v>
       </c>
       <c r="G6" t="s">
         <v>13</v>
@@ -1955,10 +1955,10 @@
         <v>8</v>
       </c>
       <c r="C7" t="s">
-        <v>9</v>
+        <v>22</v>
       </c>
       <c r="D7" t="s">
-        <v>23</v>
+        <v>10</v>
       </c>
       <c r="E7" t="s">
         <v>11</v>
@@ -1981,13 +1981,13 @@
         <v>22</v>
       </c>
       <c r="D8" t="s">
+        <v>10</v>
+      </c>
+      <c r="E8" t="s">
         <v>23</v>
       </c>
-      <c r="E8" t="s">
+      <c r="F8" t="s">
         <v>24</v>
-      </c>
-      <c r="F8" t="s">
-        <v>12</v>
       </c>
       <c r="G8" t="s">
         <v>13</v>
@@ -2004,13 +2004,13 @@
         <v>22</v>
       </c>
       <c r="D9" t="s">
+        <v>10</v>
+      </c>
+      <c r="E9" t="s">
         <v>23</v>
       </c>
-      <c r="E9" t="s">
+      <c r="F9" t="s">
         <v>24</v>
-      </c>
-      <c r="F9" t="s">
-        <v>12</v>
       </c>
       <c r="G9" t="s">
         <v>13</v>
@@ -2024,16 +2024,16 @@
         <v>8</v>
       </c>
       <c r="C10" t="s">
+        <v>22</v>
+      </c>
+      <c r="D10" t="s">
+        <v>10</v>
+      </c>
+      <c r="E10" t="s">
         <v>29</v>
       </c>
-      <c r="D10" t="s">
-        <v>23</v>
-      </c>
-      <c r="E10" t="s">
+      <c r="F10" t="s">
         <v>24</v>
-      </c>
-      <c r="F10" t="s">
-        <v>12</v>
       </c>
       <c r="G10" t="s">
         <v>13</v>
@@ -2047,16 +2047,16 @@
         <v>8</v>
       </c>
       <c r="C11" t="s">
+        <v>22</v>
+      </c>
+      <c r="D11" t="s">
+        <v>10</v>
+      </c>
+      <c r="E11" t="s">
         <v>31</v>
       </c>
-      <c r="D11" t="s">
-        <v>23</v>
-      </c>
-      <c r="E11" t="s">
+      <c r="F11" t="s">
         <v>32</v>
-      </c>
-      <c r="F11" t="s">
-        <v>12</v>
       </c>
       <c r="G11" t="s">
         <v>33</v>
@@ -2070,16 +2070,16 @@
         <v>8</v>
       </c>
       <c r="C12" t="s">
+        <v>22</v>
+      </c>
+      <c r="D12" t="s">
+        <v>10</v>
+      </c>
+      <c r="E12" t="s">
         <v>35</v>
       </c>
-      <c r="D12" t="s">
-        <v>23</v>
-      </c>
-      <c r="E12" t="s">
+      <c r="F12" t="s">
         <v>36</v>
-      </c>
-      <c r="F12" t="s">
-        <v>12</v>
       </c>
       <c r="G12" t="s">
         <v>13</v>
@@ -2096,13 +2096,13 @@
         <v>38</v>
       </c>
       <c r="D13" t="s">
+        <v>10</v>
+      </c>
+      <c r="E13" t="s">
         <v>39</v>
       </c>
-      <c r="E13" t="s">
+      <c r="F13" t="s">
         <v>36</v>
-      </c>
-      <c r="F13" t="s">
-        <v>12</v>
       </c>
       <c r="G13" t="s">
         <v>13</v>
@@ -2116,16 +2116,16 @@
         <v>8</v>
       </c>
       <c r="C14" t="s">
+        <v>38</v>
+      </c>
+      <c r="D14" t="s">
+        <v>10</v>
+      </c>
+      <c r="E14" t="s">
         <v>41</v>
       </c>
-      <c r="D14" t="s">
-        <v>39</v>
-      </c>
-      <c r="E14" t="s">
+      <c r="F14" t="s">
         <v>42</v>
-      </c>
-      <c r="F14" t="s">
-        <v>12</v>
       </c>
       <c r="G14" t="s">
         <v>13</v>
@@ -2142,13 +2142,13 @@
         <v>44</v>
       </c>
       <c r="D15" t="s">
+        <v>10</v>
+      </c>
+      <c r="E15" t="s">
         <v>45</v>
       </c>
-      <c r="E15" t="s">
+      <c r="F15" t="s">
         <v>46</v>
-      </c>
-      <c r="F15" t="s">
-        <v>12</v>
       </c>
       <c r="G15" t="s">
         <v>13</v>
@@ -2162,16 +2162,16 @@
         <v>8</v>
       </c>
       <c r="C16" t="s">
+        <v>44</v>
+      </c>
+      <c r="D16" t="s">
+        <v>10</v>
+      </c>
+      <c r="E16" t="s">
         <v>48</v>
       </c>
-      <c r="D16" t="s">
-        <v>45</v>
-      </c>
-      <c r="E16" t="s">
+      <c r="F16" t="s">
         <v>49</v>
-      </c>
-      <c r="F16" t="s">
-        <v>12</v>
       </c>
       <c r="G16" t="s">
         <v>13</v>
@@ -2231,16 +2231,16 @@
         <v>8</v>
       </c>
       <c r="C19" t="s">
-        <v>57</v>
+        <v>51</v>
       </c>
       <c r="D19" t="s">
         <v>52</v>
       </c>
       <c r="E19" t="s">
+        <v>57</v>
+      </c>
+      <c r="F19" t="s">
         <v>58</v>
-      </c>
-      <c r="F19" t="s">
-        <v>54</v>
       </c>
       <c r="G19" t="s">
         <v>33</v>
@@ -2254,16 +2254,16 @@
         <v>8</v>
       </c>
       <c r="C20" t="s">
-        <v>60</v>
+        <v>51</v>
       </c>
       <c r="D20" t="s">
         <v>52</v>
       </c>
       <c r="E20" t="s">
+        <v>60</v>
+      </c>
+      <c r="F20" t="s">
         <v>61</v>
-      </c>
-      <c r="F20" t="s">
-        <v>54</v>
       </c>
       <c r="G20" t="s">
         <v>33</v>
@@ -2300,16 +2300,16 @@
         <v>8</v>
       </c>
       <c r="C22" t="s">
+        <v>64</v>
+      </c>
+      <c r="D22" t="s">
+        <v>52</v>
+      </c>
+      <c r="E22" t="s">
         <v>31</v>
       </c>
-      <c r="D22" t="s">
-        <v>64</v>
-      </c>
-      <c r="E22" t="s">
+      <c r="F22" t="s">
         <v>32</v>
-      </c>
-      <c r="F22" t="s">
-        <v>54</v>
       </c>
       <c r="G22" t="s">
         <v>33</v>
@@ -2323,16 +2323,16 @@
         <v>8</v>
       </c>
       <c r="C23" t="s">
+        <v>64</v>
+      </c>
+      <c r="D23" t="s">
+        <v>52</v>
+      </c>
+      <c r="E23" t="s">
         <v>66</v>
       </c>
-      <c r="D23" t="s">
-        <v>64</v>
-      </c>
-      <c r="E23" t="s">
+      <c r="F23" t="s">
         <v>67</v>
-      </c>
-      <c r="F23" t="s">
-        <v>54</v>
       </c>
       <c r="G23" t="s">
         <v>33</v>
@@ -2346,16 +2346,16 @@
         <v>8</v>
       </c>
       <c r="C24" t="s">
+        <v>64</v>
+      </c>
+      <c r="D24" t="s">
+        <v>52</v>
+      </c>
+      <c r="E24" t="s">
         <v>31</v>
       </c>
-      <c r="D24" t="s">
-        <v>64</v>
-      </c>
-      <c r="E24" t="s">
+      <c r="F24" t="s">
         <v>32</v>
-      </c>
-      <c r="F24" t="s">
-        <v>54</v>
       </c>
       <c r="G24" t="s">
         <v>33</v>
@@ -2369,16 +2369,16 @@
         <v>8</v>
       </c>
       <c r="C25" t="s">
+        <v>64</v>
+      </c>
+      <c r="D25" t="s">
+        <v>52</v>
+      </c>
+      <c r="E25" t="s">
         <v>31</v>
       </c>
-      <c r="D25" t="s">
-        <v>64</v>
-      </c>
-      <c r="E25" t="s">
+      <c r="F25" t="s">
         <v>32</v>
-      </c>
-      <c r="F25" t="s">
-        <v>54</v>
       </c>
       <c r="G25" t="s">
         <v>33</v>
@@ -2392,16 +2392,16 @@
         <v>8</v>
       </c>
       <c r="C26" t="s">
+        <v>64</v>
+      </c>
+      <c r="D26" t="s">
+        <v>52</v>
+      </c>
+      <c r="E26" t="s">
         <v>31</v>
       </c>
-      <c r="D26" t="s">
-        <v>64</v>
-      </c>
-      <c r="E26" t="s">
+      <c r="F26" t="s">
         <v>32</v>
-      </c>
-      <c r="F26" t="s">
-        <v>54</v>
       </c>
       <c r="G26" t="s">
         <v>33</v>
@@ -2415,16 +2415,16 @@
         <v>8</v>
       </c>
       <c r="C27" t="s">
+        <v>64</v>
+      </c>
+      <c r="D27" t="s">
+        <v>52</v>
+      </c>
+      <c r="E27" t="s">
         <v>31</v>
       </c>
-      <c r="D27" t="s">
-        <v>64</v>
-      </c>
-      <c r="E27" t="s">
+      <c r="F27" t="s">
         <v>32</v>
-      </c>
-      <c r="F27" t="s">
-        <v>54</v>
       </c>
       <c r="G27" t="s">
         <v>33</v>
@@ -2438,16 +2438,16 @@
         <v>8</v>
       </c>
       <c r="C28" t="s">
+        <v>64</v>
+      </c>
+      <c r="D28" t="s">
+        <v>52</v>
+      </c>
+      <c r="E28" t="s">
         <v>31</v>
       </c>
-      <c r="D28" t="s">
-        <v>64</v>
-      </c>
-      <c r="E28" t="s">
+      <c r="F28" t="s">
         <v>32</v>
-      </c>
-      <c r="F28" t="s">
-        <v>54</v>
       </c>
       <c r="G28" t="s">
         <v>33</v>
@@ -2461,16 +2461,16 @@
         <v>8</v>
       </c>
       <c r="C29" t="s">
+        <v>64</v>
+      </c>
+      <c r="D29" t="s">
+        <v>52</v>
+      </c>
+      <c r="E29" t="s">
         <v>31</v>
       </c>
-      <c r="D29" t="s">
-        <v>64</v>
-      </c>
-      <c r="E29" t="s">
+      <c r="F29" t="s">
         <v>32</v>
-      </c>
-      <c r="F29" t="s">
-        <v>54</v>
       </c>
       <c r="G29" t="s">
         <v>33</v>
@@ -2484,10 +2484,10 @@
         <v>8</v>
       </c>
       <c r="C30" t="s">
-        <v>51</v>
+        <v>64</v>
       </c>
       <c r="D30" t="s">
-        <v>64</v>
+        <v>52</v>
       </c>
       <c r="E30" t="s">
         <v>53</v>
@@ -2507,16 +2507,16 @@
         <v>8</v>
       </c>
       <c r="C31" t="s">
+        <v>76</v>
+      </c>
+      <c r="D31" t="s">
+        <v>52</v>
+      </c>
+      <c r="E31" t="s">
         <v>31</v>
       </c>
-      <c r="D31" t="s">
-        <v>76</v>
-      </c>
-      <c r="E31" t="s">
+      <c r="F31" t="s">
         <v>32</v>
-      </c>
-      <c r="F31" t="s">
-        <v>54</v>
       </c>
       <c r="G31" t="s">
         <v>33</v>
@@ -2530,16 +2530,16 @@
         <v>8</v>
       </c>
       <c r="C32" t="s">
+        <v>76</v>
+      </c>
+      <c r="D32" t="s">
+        <v>52</v>
+      </c>
+      <c r="E32" t="s">
         <v>31</v>
       </c>
-      <c r="D32" t="s">
-        <v>76</v>
-      </c>
-      <c r="E32" t="s">
+      <c r="F32" t="s">
         <v>32</v>
-      </c>
-      <c r="F32" t="s">
-        <v>54</v>
       </c>
       <c r="G32" t="s">
         <v>33</v>
@@ -2553,16 +2553,16 @@
         <v>8</v>
       </c>
       <c r="C33" t="s">
+        <v>76</v>
+      </c>
+      <c r="D33" t="s">
+        <v>52</v>
+      </c>
+      <c r="E33" t="s">
         <v>31</v>
       </c>
-      <c r="D33" t="s">
-        <v>76</v>
-      </c>
-      <c r="E33" t="s">
+      <c r="F33" t="s">
         <v>32</v>
-      </c>
-      <c r="F33" t="s">
-        <v>54</v>
       </c>
       <c r="G33" t="s">
         <v>33</v>
@@ -2576,16 +2576,16 @@
         <v>8</v>
       </c>
       <c r="C34" t="s">
+        <v>76</v>
+      </c>
+      <c r="D34" t="s">
+        <v>52</v>
+      </c>
+      <c r="E34" t="s">
         <v>31</v>
       </c>
-      <c r="D34" t="s">
-        <v>76</v>
-      </c>
-      <c r="E34" t="s">
+      <c r="F34" t="s">
         <v>32</v>
-      </c>
-      <c r="F34" t="s">
-        <v>54</v>
       </c>
       <c r="G34" t="s">
         <v>33</v>
@@ -2599,16 +2599,16 @@
         <v>8</v>
       </c>
       <c r="C35" t="s">
+        <v>76</v>
+      </c>
+      <c r="D35" t="s">
+        <v>52</v>
+      </c>
+      <c r="E35" t="s">
         <v>31</v>
       </c>
-      <c r="D35" t="s">
-        <v>76</v>
-      </c>
-      <c r="E35" t="s">
+      <c r="F35" t="s">
         <v>32</v>
-      </c>
-      <c r="F35" t="s">
-        <v>54</v>
       </c>
       <c r="G35" t="s">
         <v>33</v>
@@ -2622,16 +2622,16 @@
         <v>8</v>
       </c>
       <c r="C36" t="s">
+        <v>76</v>
+      </c>
+      <c r="D36" t="s">
+        <v>52</v>
+      </c>
+      <c r="E36" t="s">
         <v>57</v>
       </c>
-      <c r="D36" t="s">
-        <v>76</v>
-      </c>
-      <c r="E36" t="s">
+      <c r="F36" t="s">
         <v>58</v>
-      </c>
-      <c r="F36" t="s">
-        <v>54</v>
       </c>
       <c r="G36" t="s">
         <v>33</v>
@@ -2644,14 +2644,14 @@
       <c r="B37" t="s">
         <v>8</v>
       </c>
-      <c r="C37" t="s">
+      <c r="D37" t="s">
+        <v>83</v>
+      </c>
+      <c r="E37" t="s">
         <v>31</v>
       </c>
-      <c r="E37" t="s">
+      <c r="F37" t="s">
         <v>32</v>
-      </c>
-      <c r="F37" t="s">
-        <v>83</v>
       </c>
       <c r="G37" t="s">
         <v>33</v>
@@ -2664,14 +2664,14 @@
       <c r="B38" t="s">
         <v>8</v>
       </c>
-      <c r="C38" t="s">
+      <c r="D38" t="s">
+        <v>83</v>
+      </c>
+      <c r="E38" t="s">
         <v>31</v>
       </c>
-      <c r="E38" t="s">
+      <c r="F38" t="s">
         <v>32</v>
-      </c>
-      <c r="F38" t="s">
-        <v>83</v>
       </c>
       <c r="G38" t="s">
         <v>33</v>
@@ -2684,14 +2684,14 @@
       <c r="B39" t="s">
         <v>8</v>
       </c>
-      <c r="C39" t="s">
+      <c r="D39" t="s">
+        <v>83</v>
+      </c>
+      <c r="E39" t="s">
         <v>31</v>
       </c>
-      <c r="E39" t="s">
+      <c r="F39" t="s">
         <v>32</v>
-      </c>
-      <c r="F39" t="s">
-        <v>83</v>
       </c>
       <c r="G39" t="s">
         <v>33</v>
@@ -2704,14 +2704,14 @@
       <c r="B40" t="s">
         <v>8</v>
       </c>
-      <c r="C40" t="s">
+      <c r="D40" t="s">
+        <v>83</v>
+      </c>
+      <c r="E40" t="s">
         <v>31</v>
       </c>
-      <c r="E40" t="s">
+      <c r="F40" t="s">
         <v>32</v>
-      </c>
-      <c r="F40" t="s">
-        <v>83</v>
       </c>
       <c r="G40" t="s">
         <v>33</v>
@@ -2724,14 +2724,14 @@
       <c r="B41" t="s">
         <v>8</v>
       </c>
-      <c r="C41" t="s">
-        <v>51</v>
+      <c r="D41" t="s">
+        <v>83</v>
       </c>
       <c r="E41" t="s">
         <v>53</v>
       </c>
       <c r="F41" t="s">
-        <v>83</v>
+        <v>54</v>
       </c>
       <c r="G41" t="s">
         <v>33</v>
@@ -2744,14 +2744,14 @@
       <c r="B42" t="s">
         <v>8</v>
       </c>
-      <c r="C42" t="s">
+      <c r="D42" t="s">
+        <v>83</v>
+      </c>
+      <c r="E42" t="s">
         <v>57</v>
       </c>
-      <c r="E42" t="s">
+      <c r="F42" t="s">
         <v>58</v>
-      </c>
-      <c r="F42" t="s">
-        <v>83</v>
       </c>
       <c r="G42" t="s">
         <v>33</v>
@@ -2764,7 +2764,7 @@
       <c r="B43" t="s">
         <v>8</v>
       </c>
-      <c r="C43" t="s">
+      <c r="D43" t="s">
         <v>90</v>
       </c>
       <c r="E43" t="s">
@@ -2784,14 +2784,14 @@
       <c r="B44" t="s">
         <v>8</v>
       </c>
-      <c r="C44" t="s">
+      <c r="D44" t="s">
+        <v>90</v>
+      </c>
+      <c r="E44" t="s">
         <v>95</v>
       </c>
-      <c r="E44" t="s">
+      <c r="F44" t="s">
         <v>96</v>
-      </c>
-      <c r="F44" t="s">
-        <v>92</v>
       </c>
       <c r="G44" t="s">
         <v>97</v>
@@ -2804,7 +2804,7 @@
       <c r="B45" t="s">
         <v>8</v>
       </c>
-      <c r="C45" t="s">
+      <c r="D45" t="s">
         <v>90</v>
       </c>
       <c r="E45" t="s">
@@ -2824,7 +2824,7 @@
       <c r="B46" t="s">
         <v>8</v>
       </c>
-      <c r="C46" t="s">
+      <c r="D46" t="s">
         <v>90</v>
       </c>
       <c r="E46" t="s">
@@ -2844,14 +2844,14 @@
       <c r="B47" t="s">
         <v>8</v>
       </c>
-      <c r="C47" t="s">
+      <c r="D47" t="s">
+        <v>90</v>
+      </c>
+      <c r="E47" t="s">
         <v>101</v>
       </c>
-      <c r="E47" t="s">
+      <c r="F47" t="s">
         <v>102</v>
-      </c>
-      <c r="F47" t="s">
-        <v>92</v>
       </c>
       <c r="G47" t="s">
         <v>97</v>
@@ -2864,7 +2864,7 @@
       <c r="B48" t="s">
         <v>8</v>
       </c>
-      <c r="C48" t="s">
+      <c r="D48" t="s">
         <v>90</v>
       </c>
       <c r="E48" t="s">
@@ -2884,7 +2884,7 @@
       <c r="B49" t="s">
         <v>8</v>
       </c>
-      <c r="C49" t="s">
+      <c r="D49" t="s">
         <v>90</v>
       </c>
       <c r="E49" t="s">
@@ -2904,14 +2904,14 @@
       <c r="B50" t="s">
         <v>8</v>
       </c>
-      <c r="C50" t="s">
+      <c r="D50" t="s">
+        <v>90</v>
+      </c>
+      <c r="E50" t="s">
         <v>101</v>
       </c>
-      <c r="E50" t="s">
+      <c r="F50" t="s">
         <v>102</v>
-      </c>
-      <c r="F50" t="s">
-        <v>92</v>
       </c>
       <c r="G50" t="s">
         <v>97</v>
@@ -2924,7 +2924,7 @@
       <c r="B51" t="s">
         <v>8</v>
       </c>
-      <c r="C51" t="s">
+      <c r="D51" t="s">
         <v>90</v>
       </c>
       <c r="E51" t="s">
@@ -2944,14 +2944,14 @@
       <c r="B52" t="s">
         <v>8</v>
       </c>
-      <c r="C52" t="s">
+      <c r="D52" t="s">
+        <v>90</v>
+      </c>
+      <c r="E52" t="s">
         <v>108</v>
       </c>
-      <c r="E52" t="s">
+      <c r="F52" t="s">
         <v>109</v>
-      </c>
-      <c r="F52" t="s">
-        <v>92</v>
       </c>
       <c r="G52" t="s">
         <v>97</v>
@@ -2964,14 +2964,14 @@
       <c r="B53" t="s">
         <v>8</v>
       </c>
-      <c r="C53" t="s">
-        <v>9</v>
+      <c r="D53" t="s">
+        <v>90</v>
       </c>
       <c r="E53" t="s">
         <v>11</v>
       </c>
       <c r="F53" t="s">
-        <v>92</v>
+        <v>12</v>
       </c>
       <c r="G53" t="s">
         <v>13</v>
@@ -3008,16 +3008,16 @@
         <v>8</v>
       </c>
       <c r="C55" t="s">
-        <v>118</v>
+        <v>112</v>
       </c>
       <c r="D55" t="s">
         <v>113</v>
       </c>
       <c r="E55" t="s">
+        <v>118</v>
+      </c>
+      <c r="F55" t="s">
         <v>119</v>
-      </c>
-      <c r="F55" t="s">
-        <v>115</v>
       </c>
       <c r="G55" t="s">
         <v>116</v>
@@ -3031,16 +3031,16 @@
         <v>8</v>
       </c>
       <c r="C56" t="s">
-        <v>121</v>
+        <v>112</v>
       </c>
       <c r="D56" t="s">
         <v>113</v>
       </c>
       <c r="E56" t="s">
+        <v>121</v>
+      </c>
+      <c r="F56" t="s">
         <v>122</v>
-      </c>
-      <c r="F56" t="s">
-        <v>115</v>
       </c>
       <c r="G56" t="s">
         <v>116</v>
@@ -3054,16 +3054,16 @@
         <v>8</v>
       </c>
       <c r="C57" t="s">
-        <v>124</v>
+        <v>112</v>
       </c>
       <c r="D57" t="s">
         <v>113</v>
       </c>
       <c r="E57" t="s">
+        <v>124</v>
+      </c>
+      <c r="F57" t="s">
         <v>125</v>
-      </c>
-      <c r="F57" t="s">
-        <v>115</v>
       </c>
       <c r="G57" t="s">
         <v>126</v>
@@ -3077,16 +3077,16 @@
         <v>8</v>
       </c>
       <c r="C58" t="s">
-        <v>118</v>
+        <v>112</v>
       </c>
       <c r="D58" t="s">
         <v>113</v>
       </c>
       <c r="E58" t="s">
+        <v>118</v>
+      </c>
+      <c r="F58" t="s">
         <v>119</v>
-      </c>
-      <c r="F58" t="s">
-        <v>115</v>
       </c>
       <c r="G58" t="s">
         <v>116</v>
@@ -3100,16 +3100,16 @@
         <v>8</v>
       </c>
       <c r="C59" t="s">
-        <v>118</v>
+        <v>112</v>
       </c>
       <c r="D59" t="s">
         <v>113</v>
       </c>
       <c r="E59" t="s">
+        <v>118</v>
+      </c>
+      <c r="F59" t="s">
         <v>119</v>
-      </c>
-      <c r="F59" t="s">
-        <v>115</v>
       </c>
       <c r="G59" t="s">
         <v>116</v>
@@ -3123,16 +3123,16 @@
         <v>8</v>
       </c>
       <c r="C60" t="s">
-        <v>118</v>
+        <v>112</v>
       </c>
       <c r="D60" t="s">
         <v>113</v>
       </c>
       <c r="E60" t="s">
+        <v>118</v>
+      </c>
+      <c r="F60" t="s">
         <v>119</v>
-      </c>
-      <c r="F60" t="s">
-        <v>115</v>
       </c>
       <c r="G60" t="s">
         <v>116</v>
@@ -3146,16 +3146,16 @@
         <v>8</v>
       </c>
       <c r="C61" t="s">
-        <v>118</v>
+        <v>112</v>
       </c>
       <c r="D61" t="s">
         <v>113</v>
       </c>
       <c r="E61" t="s">
+        <v>118</v>
+      </c>
+      <c r="F61" t="s">
         <v>119</v>
-      </c>
-      <c r="F61" t="s">
-        <v>115</v>
       </c>
       <c r="G61" t="s">
         <v>116</v>
@@ -3169,16 +3169,16 @@
         <v>8</v>
       </c>
       <c r="C62" t="s">
-        <v>118</v>
+        <v>112</v>
       </c>
       <c r="D62" t="s">
         <v>113</v>
       </c>
       <c r="E62" t="s">
+        <v>118</v>
+      </c>
+      <c r="F62" t="s">
         <v>119</v>
-      </c>
-      <c r="F62" t="s">
-        <v>115</v>
       </c>
       <c r="G62" t="s">
         <v>116</v>
@@ -3192,16 +3192,16 @@
         <v>8</v>
       </c>
       <c r="C63" t="s">
-        <v>133</v>
+        <v>112</v>
       </c>
       <c r="D63" t="s">
         <v>113</v>
       </c>
       <c r="E63" t="s">
+        <v>133</v>
+      </c>
+      <c r="F63" t="s">
         <v>119</v>
-      </c>
-      <c r="F63" t="s">
-        <v>115</v>
       </c>
       <c r="G63" t="s">
         <v>116</v>
@@ -3215,16 +3215,16 @@
         <v>8</v>
       </c>
       <c r="C64" t="s">
-        <v>133</v>
+        <v>112</v>
       </c>
       <c r="D64" t="s">
         <v>113</v>
       </c>
       <c r="E64" t="s">
+        <v>133</v>
+      </c>
+      <c r="F64" t="s">
         <v>119</v>
-      </c>
-      <c r="F64" t="s">
-        <v>115</v>
       </c>
       <c r="G64" t="s">
         <v>116</v>
@@ -3238,16 +3238,16 @@
         <v>8</v>
       </c>
       <c r="C65" t="s">
-        <v>136</v>
+        <v>112</v>
       </c>
       <c r="D65" t="s">
         <v>113</v>
       </c>
       <c r="E65" t="s">
+        <v>136</v>
+      </c>
+      <c r="F65" t="s">
         <v>137</v>
-      </c>
-      <c r="F65" t="s">
-        <v>115</v>
       </c>
       <c r="G65" t="s">
         <v>116</v>
@@ -3284,16 +3284,16 @@
         <v>8</v>
       </c>
       <c r="C67" t="s">
-        <v>118</v>
+        <v>112</v>
       </c>
       <c r="D67" t="s">
         <v>113</v>
       </c>
       <c r="E67" t="s">
+        <v>118</v>
+      </c>
+      <c r="F67" t="s">
         <v>119</v>
-      </c>
-      <c r="F67" t="s">
-        <v>115</v>
       </c>
       <c r="G67" t="s">
         <v>116</v>
@@ -3307,13 +3307,13 @@
         <v>8</v>
       </c>
       <c r="C68" t="s">
-        <v>141</v>
+        <v>112</v>
       </c>
       <c r="D68" t="s">
         <v>113</v>
       </c>
       <c r="E68" t="s">
-        <v>114</v>
+        <v>141</v>
       </c>
       <c r="F68" t="s">
         <v>115</v>
@@ -3330,13 +3330,13 @@
         <v>8</v>
       </c>
       <c r="C69" t="s">
-        <v>143</v>
+        <v>112</v>
       </c>
       <c r="D69" t="s">
         <v>113</v>
       </c>
       <c r="E69" t="s">
-        <v>114</v>
+        <v>143</v>
       </c>
       <c r="F69" t="s">
         <v>115</v>
@@ -3353,16 +3353,16 @@
         <v>8</v>
       </c>
       <c r="C70" t="s">
-        <v>121</v>
+        <v>112</v>
       </c>
       <c r="D70" t="s">
         <v>113</v>
       </c>
       <c r="E70" t="s">
+        <v>121</v>
+      </c>
+      <c r="F70" t="s">
         <v>122</v>
-      </c>
-      <c r="F70" t="s">
-        <v>115</v>
       </c>
       <c r="G70" t="s">
         <v>116</v>
@@ -3376,16 +3376,16 @@
         <v>8</v>
       </c>
       <c r="C71" t="s">
-        <v>121</v>
+        <v>112</v>
       </c>
       <c r="D71" t="s">
         <v>113</v>
       </c>
       <c r="E71" t="s">
+        <v>121</v>
+      </c>
+      <c r="F71" t="s">
         <v>122</v>
-      </c>
-      <c r="F71" t="s">
-        <v>115</v>
       </c>
       <c r="G71" t="s">
         <v>116</v>
@@ -3422,16 +3422,16 @@
         <v>8</v>
       </c>
       <c r="C73" t="s">
-        <v>148</v>
+        <v>112</v>
       </c>
       <c r="D73" t="s">
         <v>113</v>
       </c>
       <c r="E73" t="s">
+        <v>148</v>
+      </c>
+      <c r="F73" t="s">
         <v>149</v>
-      </c>
-      <c r="F73" t="s">
-        <v>115</v>
       </c>
       <c r="G73" t="s">
         <v>126</v>
@@ -3445,16 +3445,16 @@
         <v>8</v>
       </c>
       <c r="C74" t="s">
-        <v>151</v>
+        <v>112</v>
       </c>
       <c r="D74" t="s">
         <v>113</v>
       </c>
       <c r="E74" t="s">
+        <v>151</v>
+      </c>
+      <c r="F74" t="s">
         <v>152</v>
-      </c>
-      <c r="F74" t="s">
-        <v>115</v>
       </c>
       <c r="G74" t="s">
         <v>126</v>
@@ -3468,16 +3468,16 @@
         <v>8</v>
       </c>
       <c r="C75" t="s">
-        <v>154</v>
+        <v>112</v>
       </c>
       <c r="D75" t="s">
         <v>113</v>
       </c>
       <c r="E75" t="s">
+        <v>154</v>
+      </c>
+      <c r="F75" t="s">
         <v>155</v>
-      </c>
-      <c r="F75" t="s">
-        <v>115</v>
       </c>
       <c r="G75" t="s">
         <v>126</v>
@@ -3491,16 +3491,16 @@
         <v>8</v>
       </c>
       <c r="C76" t="s">
-        <v>148</v>
+        <v>112</v>
       </c>
       <c r="D76" t="s">
         <v>113</v>
       </c>
       <c r="E76" t="s">
+        <v>148</v>
+      </c>
+      <c r="F76" t="s">
         <v>149</v>
-      </c>
-      <c r="F76" t="s">
-        <v>115</v>
       </c>
       <c r="G76" t="s">
         <v>126</v>
@@ -3514,16 +3514,16 @@
         <v>8</v>
       </c>
       <c r="C77" t="s">
-        <v>148</v>
+        <v>112</v>
       </c>
       <c r="D77" t="s">
         <v>113</v>
       </c>
       <c r="E77" t="s">
+        <v>148</v>
+      </c>
+      <c r="F77" t="s">
         <v>149</v>
-      </c>
-      <c r="F77" t="s">
-        <v>115</v>
       </c>
       <c r="G77" t="s">
         <v>126</v>
@@ -3537,16 +3537,16 @@
         <v>8</v>
       </c>
       <c r="C78" t="s">
-        <v>151</v>
+        <v>112</v>
       </c>
       <c r="D78" t="s">
         <v>113</v>
       </c>
       <c r="E78" t="s">
+        <v>151</v>
+      </c>
+      <c r="F78" t="s">
         <v>152</v>
-      </c>
-      <c r="F78" t="s">
-        <v>115</v>
       </c>
       <c r="G78" t="s">
         <v>126</v>
@@ -3560,16 +3560,16 @@
         <v>8</v>
       </c>
       <c r="C79" t="s">
-        <v>160</v>
+        <v>112</v>
       </c>
       <c r="D79" t="s">
         <v>113</v>
       </c>
       <c r="E79" t="s">
+        <v>160</v>
+      </c>
+      <c r="F79" t="s">
         <v>161</v>
-      </c>
-      <c r="F79" t="s">
-        <v>115</v>
       </c>
       <c r="G79" t="s">
         <v>126</v>
@@ -3583,16 +3583,16 @@
         <v>8</v>
       </c>
       <c r="C80" t="s">
-        <v>163</v>
+        <v>112</v>
       </c>
       <c r="D80" t="s">
         <v>113</v>
       </c>
       <c r="E80" t="s">
+        <v>163</v>
+      </c>
+      <c r="F80" t="s">
         <v>164</v>
-      </c>
-      <c r="F80" t="s">
-        <v>115</v>
       </c>
       <c r="G80" t="s">
         <v>165</v>
@@ -3606,16 +3606,16 @@
         <v>8</v>
       </c>
       <c r="C81" t="s">
-        <v>163</v>
+        <v>112</v>
       </c>
       <c r="D81" t="s">
         <v>113</v>
       </c>
       <c r="E81" t="s">
+        <v>163</v>
+      </c>
+      <c r="F81" t="s">
         <v>164</v>
-      </c>
-      <c r="F81" t="s">
-        <v>115</v>
       </c>
       <c r="G81" t="s">
         <v>165</v>
@@ -3629,16 +3629,16 @@
         <v>8</v>
       </c>
       <c r="C82" t="s">
-        <v>163</v>
+        <v>112</v>
       </c>
       <c r="D82" t="s">
         <v>113</v>
       </c>
       <c r="E82" t="s">
+        <v>163</v>
+      </c>
+      <c r="F82" t="s">
         <v>164</v>
-      </c>
-      <c r="F82" t="s">
-        <v>115</v>
       </c>
       <c r="G82" t="s">
         <v>165</v>
@@ -3652,13 +3652,13 @@
         <v>8</v>
       </c>
       <c r="C83" t="s">
-        <v>143</v>
+        <v>112</v>
       </c>
       <c r="D83" t="s">
         <v>113</v>
       </c>
       <c r="E83" t="s">
-        <v>114</v>
+        <v>143</v>
       </c>
       <c r="F83" t="s">
         <v>115</v>
@@ -3675,16 +3675,16 @@
         <v>8</v>
       </c>
       <c r="C84" t="s">
-        <v>170</v>
+        <v>112</v>
       </c>
       <c r="D84" t="s">
         <v>113</v>
       </c>
       <c r="E84" t="s">
+        <v>170</v>
+      </c>
+      <c r="F84" t="s">
         <v>171</v>
-      </c>
-      <c r="F84" t="s">
-        <v>115</v>
       </c>
       <c r="G84" t="s">
         <v>116</v>
@@ -3698,16 +3698,16 @@
         <v>8</v>
       </c>
       <c r="C85" t="s">
-        <v>173</v>
+        <v>112</v>
       </c>
       <c r="D85" t="s">
         <v>113</v>
       </c>
       <c r="E85" t="s">
+        <v>173</v>
+      </c>
+      <c r="F85" t="s">
         <v>119</v>
-      </c>
-      <c r="F85" t="s">
-        <v>115</v>
       </c>
       <c r="G85" t="s">
         <v>116</v>
@@ -3721,16 +3721,16 @@
         <v>8</v>
       </c>
       <c r="C86" t="s">
-        <v>175</v>
+        <v>112</v>
       </c>
       <c r="D86" t="s">
         <v>113</v>
       </c>
       <c r="E86" t="s">
+        <v>175</v>
+      </c>
+      <c r="F86" t="s">
         <v>176</v>
-      </c>
-      <c r="F86" t="s">
-        <v>115</v>
       </c>
       <c r="G86" t="s">
         <v>165</v>
@@ -3744,16 +3744,16 @@
         <v>8</v>
       </c>
       <c r="C87" t="s">
-        <v>173</v>
+        <v>112</v>
       </c>
       <c r="D87" t="s">
         <v>113</v>
       </c>
       <c r="E87" t="s">
+        <v>173</v>
+      </c>
+      <c r="F87" t="s">
         <v>119</v>
-      </c>
-      <c r="F87" t="s">
-        <v>115</v>
       </c>
       <c r="G87" t="s">
         <v>116</v>
@@ -3767,16 +3767,16 @@
         <v>8</v>
       </c>
       <c r="C88" t="s">
-        <v>118</v>
+        <v>112</v>
       </c>
       <c r="D88" t="s">
         <v>113</v>
       </c>
       <c r="E88" t="s">
+        <v>118</v>
+      </c>
+      <c r="F88" t="s">
         <v>119</v>
-      </c>
-      <c r="F88" t="s">
-        <v>115</v>
       </c>
       <c r="G88" t="s">
         <v>116</v>
@@ -3790,16 +3790,16 @@
         <v>8</v>
       </c>
       <c r="C89" t="s">
-        <v>118</v>
+        <v>112</v>
       </c>
       <c r="D89" t="s">
         <v>113</v>
       </c>
       <c r="E89" t="s">
+        <v>118</v>
+      </c>
+      <c r="F89" t="s">
         <v>119</v>
-      </c>
-      <c r="F89" t="s">
-        <v>115</v>
       </c>
       <c r="G89" t="s">
         <v>116</v>
@@ -3813,16 +3813,16 @@
         <v>8</v>
       </c>
       <c r="C90" t="s">
-        <v>124</v>
+        <v>112</v>
       </c>
       <c r="D90" t="s">
         <v>113</v>
       </c>
       <c r="E90" t="s">
+        <v>124</v>
+      </c>
+      <c r="F90" t="s">
         <v>125</v>
-      </c>
-      <c r="F90" t="s">
-        <v>115</v>
       </c>
       <c r="G90" t="s">
         <v>126</v>
@@ -3836,16 +3836,16 @@
         <v>8</v>
       </c>
       <c r="C91" t="s">
-        <v>182</v>
+        <v>112</v>
       </c>
       <c r="D91" t="s">
         <v>113</v>
       </c>
       <c r="E91" t="s">
+        <v>182</v>
+      </c>
+      <c r="F91" t="s">
         <v>183</v>
-      </c>
-      <c r="F91" t="s">
-        <v>115</v>
       </c>
       <c r="G91" t="s">
         <v>184</v>
@@ -3859,16 +3859,16 @@
         <v>8</v>
       </c>
       <c r="C92" t="s">
-        <v>124</v>
+        <v>112</v>
       </c>
       <c r="D92" t="s">
         <v>113</v>
       </c>
       <c r="E92" t="s">
+        <v>124</v>
+      </c>
+      <c r="F92" t="s">
         <v>125</v>
-      </c>
-      <c r="F92" t="s">
-        <v>115</v>
       </c>
       <c r="G92" t="s">
         <v>126</v>
@@ -3882,16 +3882,16 @@
         <v>8</v>
       </c>
       <c r="C93" t="s">
-        <v>121</v>
+        <v>112</v>
       </c>
       <c r="D93" t="s">
         <v>113</v>
       </c>
       <c r="E93" t="s">
+        <v>121</v>
+      </c>
+      <c r="F93" t="s">
         <v>122</v>
-      </c>
-      <c r="F93" t="s">
-        <v>115</v>
       </c>
       <c r="G93" t="s">
         <v>116</v>
@@ -3905,16 +3905,16 @@
         <v>8</v>
       </c>
       <c r="C94" t="s">
-        <v>124</v>
+        <v>112</v>
       </c>
       <c r="D94" t="s">
         <v>113</v>
       </c>
       <c r="E94" t="s">
+        <v>124</v>
+      </c>
+      <c r="F94" t="s">
         <v>125</v>
-      </c>
-      <c r="F94" t="s">
-        <v>115</v>
       </c>
       <c r="G94" t="s">
         <v>126</v>
@@ -3928,16 +3928,16 @@
         <v>8</v>
       </c>
       <c r="C95" t="s">
-        <v>189</v>
+        <v>112</v>
       </c>
       <c r="D95" t="s">
         <v>113</v>
       </c>
       <c r="E95" t="s">
+        <v>189</v>
+      </c>
+      <c r="F95" t="s">
         <v>190</v>
-      </c>
-      <c r="F95" t="s">
-        <v>115</v>
       </c>
       <c r="G95" t="s">
         <v>116</v>
@@ -3951,16 +3951,16 @@
         <v>8</v>
       </c>
       <c r="C96" t="s">
+        <v>192</v>
+      </c>
+      <c r="D96" t="s">
+        <v>113</v>
+      </c>
+      <c r="E96" t="s">
         <v>124</v>
       </c>
-      <c r="D96" t="s">
-        <v>192</v>
-      </c>
-      <c r="E96" t="s">
+      <c r="F96" t="s">
         <v>125</v>
-      </c>
-      <c r="F96" t="s">
-        <v>115</v>
       </c>
       <c r="G96" t="s">
         <v>126</v>
@@ -3974,16 +3974,16 @@
         <v>8</v>
       </c>
       <c r="C97" t="s">
+        <v>192</v>
+      </c>
+      <c r="D97" t="s">
+        <v>113</v>
+      </c>
+      <c r="E97" t="s">
         <v>124</v>
       </c>
-      <c r="D97" t="s">
-        <v>192</v>
-      </c>
-      <c r="E97" t="s">
+      <c r="F97" t="s">
         <v>125</v>
-      </c>
-      <c r="F97" t="s">
-        <v>115</v>
       </c>
       <c r="G97" t="s">
         <v>126</v>
@@ -3997,16 +3997,16 @@
         <v>8</v>
       </c>
       <c r="C98" t="s">
+        <v>192</v>
+      </c>
+      <c r="D98" t="s">
+        <v>113</v>
+      </c>
+      <c r="E98" t="s">
         <v>195</v>
       </c>
-      <c r="D98" t="s">
-        <v>192</v>
-      </c>
-      <c r="E98" t="s">
+      <c r="F98" t="s">
         <v>196</v>
-      </c>
-      <c r="F98" t="s">
-        <v>115</v>
       </c>
       <c r="G98" t="s">
         <v>197</v>
@@ -4020,16 +4020,16 @@
         <v>8</v>
       </c>
       <c r="C99" t="s">
+        <v>192</v>
+      </c>
+      <c r="D99" t="s">
+        <v>113</v>
+      </c>
+      <c r="E99" t="s">
         <v>124</v>
       </c>
-      <c r="D99" t="s">
-        <v>192</v>
-      </c>
-      <c r="E99" t="s">
+      <c r="F99" t="s">
         <v>125</v>
-      </c>
-      <c r="F99" t="s">
-        <v>115</v>
       </c>
       <c r="G99" t="s">
         <v>126</v>
@@ -4043,16 +4043,16 @@
         <v>8</v>
       </c>
       <c r="C100" t="s">
+        <v>192</v>
+      </c>
+      <c r="D100" t="s">
+        <v>113</v>
+      </c>
+      <c r="E100" t="s">
         <v>154</v>
       </c>
-      <c r="D100" t="s">
-        <v>192</v>
-      </c>
-      <c r="E100" t="s">
+      <c r="F100" t="s">
         <v>155</v>
-      </c>
-      <c r="F100" t="s">
-        <v>115</v>
       </c>
       <c r="G100" t="s">
         <v>126</v>
@@ -4066,16 +4066,16 @@
         <v>8</v>
       </c>
       <c r="C101" t="s">
+        <v>192</v>
+      </c>
+      <c r="D101" t="s">
+        <v>113</v>
+      </c>
+      <c r="E101" t="s">
         <v>124</v>
       </c>
-      <c r="D101" t="s">
-        <v>192</v>
-      </c>
-      <c r="E101" t="s">
+      <c r="F101" t="s">
         <v>125</v>
-      </c>
-      <c r="F101" t="s">
-        <v>115</v>
       </c>
       <c r="G101" t="s">
         <v>126</v>
@@ -4088,7 +4088,7 @@
       <c r="B102" t="s">
         <v>8</v>
       </c>
-      <c r="C102" t="s">
+      <c r="D102" t="s">
         <v>202</v>
       </c>
       <c r="E102" t="s">
@@ -4108,7 +4108,7 @@
       <c r="B103" t="s">
         <v>8</v>
       </c>
-      <c r="C103" t="s">
+      <c r="D103" t="s">
         <v>202</v>
       </c>
       <c r="E103" t="s">
@@ -4128,7 +4128,7 @@
       <c r="B104" t="s">
         <v>8</v>
       </c>
-      <c r="C104" t="s">
+      <c r="D104" t="s">
         <v>202</v>
       </c>
       <c r="E104" t="s">
@@ -4148,14 +4148,14 @@
       <c r="B105" t="s">
         <v>8</v>
       </c>
-      <c r="C105" t="s">
+      <c r="D105" t="s">
+        <v>202</v>
+      </c>
+      <c r="E105" t="s">
         <v>208</v>
       </c>
-      <c r="E105" t="s">
+      <c r="F105" t="s">
         <v>209</v>
-      </c>
-      <c r="F105" t="s">
-        <v>204</v>
       </c>
       <c r="G105" t="s">
         <v>184</v>
@@ -4168,7 +4168,7 @@
       <c r="B106" t="s">
         <v>8</v>
       </c>
-      <c r="C106" t="s">
+      <c r="D106" t="s">
         <v>202</v>
       </c>
       <c r="E106" t="s">
@@ -4188,14 +4188,14 @@
       <c r="B107" t="s">
         <v>8</v>
       </c>
-      <c r="C107" t="s">
+      <c r="D107" t="s">
+        <v>202</v>
+      </c>
+      <c r="E107" t="s">
         <v>182</v>
       </c>
-      <c r="E107" t="s">
+      <c r="F107" t="s">
         <v>183</v>
-      </c>
-      <c r="F107" t="s">
-        <v>204</v>
       </c>
       <c r="G107" t="s">
         <v>184</v>
@@ -4208,14 +4208,14 @@
       <c r="B108" t="s">
         <v>8</v>
       </c>
-      <c r="C108" t="s">
+      <c r="D108" t="s">
+        <v>202</v>
+      </c>
+      <c r="E108" t="s">
         <v>213</v>
       </c>
-      <c r="E108" t="s">
+      <c r="F108" t="s">
         <v>214</v>
-      </c>
-      <c r="F108" t="s">
-        <v>204</v>
       </c>
       <c r="G108" t="s">
         <v>184</v>
@@ -4228,14 +4228,14 @@
       <c r="B109" t="s">
         <v>8</v>
       </c>
-      <c r="C109" t="s">
+      <c r="D109" t="s">
+        <v>202</v>
+      </c>
+      <c r="E109" t="s">
         <v>216</v>
       </c>
-      <c r="E109" t="s">
+      <c r="F109" t="s">
         <v>217</v>
-      </c>
-      <c r="F109" t="s">
-        <v>204</v>
       </c>
       <c r="G109" t="s">
         <v>93</v>
@@ -4248,14 +4248,14 @@
       <c r="B110" t="s">
         <v>8</v>
       </c>
-      <c r="C110" t="s">
+      <c r="D110" t="s">
+        <v>202</v>
+      </c>
+      <c r="E110" t="s">
         <v>219</v>
       </c>
-      <c r="E110" t="s">
+      <c r="F110" t="s">
         <v>220</v>
-      </c>
-      <c r="F110" t="s">
-        <v>204</v>
       </c>
       <c r="G110" t="s">
         <v>93</v>
@@ -4268,7 +4268,7 @@
       <c r="B111" t="s">
         <v>8</v>
       </c>
-      <c r="C111" t="s">
+      <c r="D111" t="s">
         <v>202</v>
       </c>
       <c r="E111" t="s">
@@ -4288,14 +4288,14 @@
       <c r="B112" t="s">
         <v>8</v>
       </c>
-      <c r="C112" t="s">
+      <c r="D112" t="s">
+        <v>202</v>
+      </c>
+      <c r="E112" t="s">
         <v>223</v>
       </c>
-      <c r="E112" t="s">
+      <c r="F112" t="s">
         <v>224</v>
-      </c>
-      <c r="F112" t="s">
-        <v>204</v>
       </c>
       <c r="G112" t="s">
         <v>225</v>
@@ -4308,14 +4308,14 @@
       <c r="B113" t="s">
         <v>8</v>
       </c>
-      <c r="C113" t="s">
+      <c r="D113" t="s">
+        <v>202</v>
+      </c>
+      <c r="E113" t="s">
         <v>143</v>
       </c>
-      <c r="E113" t="s">
-        <v>114</v>
-      </c>
       <c r="F113" t="s">
-        <v>204</v>
+        <v>115</v>
       </c>
       <c r="G113" t="s">
         <v>116</v>
@@ -4328,14 +4328,14 @@
       <c r="B114" t="s">
         <v>8</v>
       </c>
-      <c r="C114" t="s">
+      <c r="D114" t="s">
+        <v>202</v>
+      </c>
+      <c r="E114" t="s">
         <v>151</v>
       </c>
-      <c r="E114" t="s">
+      <c r="F114" t="s">
         <v>152</v>
-      </c>
-      <c r="F114" t="s">
-        <v>204</v>
       </c>
       <c r="G114" t="s">
         <v>126</v>
@@ -4348,14 +4348,14 @@
       <c r="B115" t="s">
         <v>8</v>
       </c>
-      <c r="C115" t="s">
+      <c r="D115" t="s">
+        <v>202</v>
+      </c>
+      <c r="E115" t="s">
         <v>182</v>
       </c>
-      <c r="E115" t="s">
+      <c r="F115" t="s">
         <v>183</v>
-      </c>
-      <c r="F115" t="s">
-        <v>204</v>
       </c>
       <c r="G115" t="s">
         <v>184</v>
@@ -4368,14 +4368,14 @@
       <c r="B116" t="s">
         <v>8</v>
       </c>
-      <c r="C116" t="s">
+      <c r="D116" t="s">
+        <v>202</v>
+      </c>
+      <c r="E116" t="s">
         <v>230</v>
       </c>
-      <c r="E116" t="s">
+      <c r="F116" t="s">
         <v>231</v>
-      </c>
-      <c r="F116" t="s">
-        <v>204</v>
       </c>
       <c r="G116" t="s">
         <v>225</v>
@@ -4388,14 +4388,14 @@
       <c r="B117" t="s">
         <v>8</v>
       </c>
-      <c r="C117" t="s">
+      <c r="D117" t="s">
+        <v>202</v>
+      </c>
+      <c r="E117" t="s">
         <v>223</v>
       </c>
-      <c r="E117" t="s">
+      <c r="F117" t="s">
         <v>224</v>
-      </c>
-      <c r="F117" t="s">
-        <v>204</v>
       </c>
       <c r="G117" t="s">
         <v>225</v>
@@ -4408,14 +4408,14 @@
       <c r="B118" t="s">
         <v>8</v>
       </c>
-      <c r="C118" t="s">
+      <c r="D118" t="s">
+        <v>202</v>
+      </c>
+      <c r="E118" t="s">
         <v>234</v>
       </c>
-      <c r="E118" t="s">
+      <c r="F118" t="s">
         <v>164</v>
-      </c>
-      <c r="F118" t="s">
-        <v>204</v>
       </c>
       <c r="G118" t="s">
         <v>165</v>
@@ -4428,14 +4428,14 @@
       <c r="B119" t="s">
         <v>8</v>
       </c>
-      <c r="C119" t="s">
+      <c r="D119" t="s">
+        <v>202</v>
+      </c>
+      <c r="E119" t="s">
         <v>182</v>
       </c>
-      <c r="E119" t="s">
+      <c r="F119" t="s">
         <v>183</v>
-      </c>
-      <c r="F119" t="s">
-        <v>204</v>
       </c>
       <c r="G119" t="s">
         <v>184</v>
@@ -4448,14 +4448,14 @@
       <c r="B120" t="s">
         <v>8</v>
       </c>
-      <c r="C120" t="s">
+      <c r="D120" t="s">
+        <v>237</v>
+      </c>
+      <c r="E120" t="s">
         <v>170</v>
       </c>
-      <c r="E120" t="s">
+      <c r="F120" t="s">
         <v>171</v>
-      </c>
-      <c r="F120" t="s">
-        <v>237</v>
       </c>
       <c r="G120" t="s">
         <v>116</v>
@@ -4468,14 +4468,14 @@
       <c r="B121" t="s">
         <v>8</v>
       </c>
-      <c r="C121" t="s">
+      <c r="D121" t="s">
+        <v>237</v>
+      </c>
+      <c r="E121" t="s">
         <v>143</v>
       </c>
-      <c r="E121" t="s">
-        <v>114</v>
-      </c>
       <c r="F121" t="s">
-        <v>237</v>
+        <v>115</v>
       </c>
       <c r="G121" t="s">
         <v>116</v>
@@ -4488,14 +4488,14 @@
       <c r="B122" t="s">
         <v>8</v>
       </c>
-      <c r="C122" t="s">
+      <c r="D122" t="s">
+        <v>237</v>
+      </c>
+      <c r="E122" t="s">
         <v>170</v>
       </c>
-      <c r="E122" t="s">
+      <c r="F122" t="s">
         <v>171</v>
-      </c>
-      <c r="F122" t="s">
-        <v>237</v>
       </c>
       <c r="G122" t="s">
         <v>116</v>
@@ -4508,14 +4508,14 @@
       <c r="B123" t="s">
         <v>8</v>
       </c>
-      <c r="C123" t="s">
+      <c r="D123" t="s">
+        <v>237</v>
+      </c>
+      <c r="E123" t="s">
         <v>170</v>
       </c>
-      <c r="E123" t="s">
+      <c r="F123" t="s">
         <v>171</v>
-      </c>
-      <c r="F123" t="s">
-        <v>237</v>
       </c>
       <c r="G123" t="s">
         <v>116</v>
@@ -4528,14 +4528,14 @@
       <c r="B124" t="s">
         <v>8</v>
       </c>
-      <c r="C124" t="s">
+      <c r="D124" t="s">
+        <v>237</v>
+      </c>
+      <c r="E124" t="s">
         <v>242</v>
       </c>
-      <c r="E124" t="s">
+      <c r="F124" t="s">
         <v>243</v>
-      </c>
-      <c r="F124" t="s">
-        <v>237</v>
       </c>
       <c r="G124" t="s">
         <v>165</v>
@@ -4548,14 +4548,14 @@
       <c r="B125" t="s">
         <v>8</v>
       </c>
-      <c r="C125" t="s">
+      <c r="D125" t="s">
+        <v>237</v>
+      </c>
+      <c r="E125" t="s">
         <v>242</v>
       </c>
-      <c r="E125" t="s">
+      <c r="F125" t="s">
         <v>243</v>
-      </c>
-      <c r="F125" t="s">
-        <v>237</v>
       </c>
       <c r="G125" t="s">
         <v>165</v>
@@ -4568,14 +4568,14 @@
       <c r="B126" t="s">
         <v>8</v>
       </c>
-      <c r="C126" t="s">
+      <c r="D126" t="s">
+        <v>237</v>
+      </c>
+      <c r="E126" t="s">
         <v>242</v>
       </c>
-      <c r="E126" t="s">
+      <c r="F126" t="s">
         <v>243</v>
-      </c>
-      <c r="F126" t="s">
-        <v>237</v>
       </c>
       <c r="G126" t="s">
         <v>165</v>
@@ -4588,14 +4588,14 @@
       <c r="B127" t="s">
         <v>8</v>
       </c>
-      <c r="C127" t="s">
+      <c r="D127" t="s">
+        <v>237</v>
+      </c>
+      <c r="E127" t="s">
         <v>242</v>
       </c>
-      <c r="E127" t="s">
+      <c r="F127" t="s">
         <v>243</v>
-      </c>
-      <c r="F127" t="s">
-        <v>237</v>
       </c>
       <c r="G127" t="s">
         <v>165</v>
@@ -4608,14 +4608,14 @@
       <c r="B128" t="s">
         <v>8</v>
       </c>
-      <c r="C128" t="s">
+      <c r="D128" t="s">
+        <v>237</v>
+      </c>
+      <c r="E128" t="s">
         <v>242</v>
       </c>
-      <c r="E128" t="s">
+      <c r="F128" t="s">
         <v>243</v>
-      </c>
-      <c r="F128" t="s">
-        <v>237</v>
       </c>
       <c r="G128" t="s">
         <v>165</v>
@@ -4628,14 +4628,14 @@
       <c r="B129" t="s">
         <v>8</v>
       </c>
-      <c r="C129" t="s">
+      <c r="D129" t="s">
+        <v>237</v>
+      </c>
+      <c r="E129" t="s">
         <v>249</v>
       </c>
-      <c r="E129" t="s">
+      <c r="F129" t="s">
         <v>243</v>
-      </c>
-      <c r="F129" t="s">
-        <v>237</v>
       </c>
       <c r="G129" t="s">
         <v>165</v>
@@ -4648,14 +4648,14 @@
       <c r="B130" t="s">
         <v>8</v>
       </c>
-      <c r="C130" t="s">
+      <c r="D130" t="s">
+        <v>237</v>
+      </c>
+      <c r="E130" t="s">
         <v>251</v>
       </c>
-      <c r="E130" t="s">
+      <c r="F130" t="s">
         <v>243</v>
-      </c>
-      <c r="F130" t="s">
-        <v>237</v>
       </c>
       <c r="G130" t="s">
         <v>165</v>
@@ -4668,14 +4668,14 @@
       <c r="B131" t="s">
         <v>8</v>
       </c>
-      <c r="C131" t="s">
+      <c r="D131" t="s">
+        <v>237</v>
+      </c>
+      <c r="E131" t="s">
         <v>253</v>
       </c>
-      <c r="E131" t="s">
+      <c r="F131" t="s">
         <v>243</v>
-      </c>
-      <c r="F131" t="s">
-        <v>237</v>
       </c>
       <c r="G131" t="s">
         <v>165</v>
@@ -4688,14 +4688,14 @@
       <c r="B132" t="s">
         <v>8</v>
       </c>
-      <c r="C132" t="s">
+      <c r="D132" t="s">
+        <v>237</v>
+      </c>
+      <c r="E132" t="s">
         <v>255</v>
       </c>
-      <c r="E132" t="s">
+      <c r="F132" t="s">
         <v>256</v>
-      </c>
-      <c r="F132" t="s">
-        <v>237</v>
       </c>
       <c r="G132" t="s">
         <v>165</v>
@@ -4708,14 +4708,14 @@
       <c r="B133" t="s">
         <v>8</v>
       </c>
-      <c r="C133" t="s">
+      <c r="D133" t="s">
+        <v>237</v>
+      </c>
+      <c r="E133" t="s">
         <v>189</v>
       </c>
-      <c r="E133" t="s">
+      <c r="F133" t="s">
         <v>190</v>
-      </c>
-      <c r="F133" t="s">
-        <v>237</v>
       </c>
       <c r="G133" t="s">
         <v>116</v>
@@ -4728,14 +4728,14 @@
       <c r="B134" t="s">
         <v>8</v>
       </c>
-      <c r="C134" t="s">
+      <c r="D134" t="s">
+        <v>259</v>
+      </c>
+      <c r="E134" t="s">
         <v>175</v>
       </c>
-      <c r="E134" t="s">
+      <c r="F134" t="s">
         <v>176</v>
-      </c>
-      <c r="F134" t="s">
-        <v>259</v>
       </c>
       <c r="G134" t="s">
         <v>165</v>
@@ -4748,14 +4748,14 @@
       <c r="B135" t="s">
         <v>8</v>
       </c>
-      <c r="C135" t="s">
+      <c r="D135" t="s">
+        <v>259</v>
+      </c>
+      <c r="E135" t="s">
         <v>175</v>
       </c>
-      <c r="E135" t="s">
+      <c r="F135" t="s">
         <v>176</v>
-      </c>
-      <c r="F135" t="s">
-        <v>259</v>
       </c>
       <c r="G135" t="s">
         <v>165</v>
@@ -4768,14 +4768,14 @@
       <c r="B136" t="s">
         <v>8</v>
       </c>
-      <c r="C136" t="s">
+      <c r="D136" t="s">
+        <v>259</v>
+      </c>
+      <c r="E136" t="s">
         <v>175</v>
       </c>
-      <c r="E136" t="s">
+      <c r="F136" t="s">
         <v>176</v>
-      </c>
-      <c r="F136" t="s">
-        <v>259</v>
       </c>
       <c r="G136" t="s">
         <v>165</v>
@@ -4788,14 +4788,14 @@
       <c r="B137" t="s">
         <v>8</v>
       </c>
-      <c r="C137" t="s">
+      <c r="D137" t="s">
+        <v>259</v>
+      </c>
+      <c r="E137" t="s">
         <v>175</v>
       </c>
-      <c r="E137" t="s">
+      <c r="F137" t="s">
         <v>176</v>
-      </c>
-      <c r="F137" t="s">
-        <v>259</v>
       </c>
       <c r="G137" t="s">
         <v>165</v>
@@ -4808,14 +4808,14 @@
       <c r="B138" t="s">
         <v>8</v>
       </c>
-      <c r="C138" t="s">
+      <c r="D138" t="s">
+        <v>259</v>
+      </c>
+      <c r="E138" t="s">
         <v>175</v>
       </c>
-      <c r="E138" t="s">
+      <c r="F138" t="s">
         <v>176</v>
-      </c>
-      <c r="F138" t="s">
-        <v>259</v>
       </c>
       <c r="G138" t="s">
         <v>165</v>
@@ -4828,14 +4828,14 @@
       <c r="B139" t="s">
         <v>8</v>
       </c>
-      <c r="C139" t="s">
+      <c r="D139" t="s">
+        <v>259</v>
+      </c>
+      <c r="E139" t="s">
         <v>265</v>
       </c>
-      <c r="E139" t="s">
+      <c r="F139" t="s">
         <v>266</v>
-      </c>
-      <c r="F139" t="s">
-        <v>259</v>
       </c>
       <c r="G139" t="s">
         <v>225</v>
@@ -4848,14 +4848,14 @@
       <c r="B140" t="s">
         <v>8</v>
       </c>
-      <c r="C140" t="s">
+      <c r="D140" t="s">
+        <v>259</v>
+      </c>
+      <c r="E140" t="s">
         <v>175</v>
       </c>
-      <c r="E140" t="s">
+      <c r="F140" t="s">
         <v>176</v>
-      </c>
-      <c r="F140" t="s">
-        <v>259</v>
       </c>
       <c r="G140" t="s">
         <v>165</v>
@@ -4915,16 +4915,16 @@
         <v>8</v>
       </c>
       <c r="C143" t="s">
-        <v>275</v>
+        <v>269</v>
       </c>
       <c r="D143" t="s">
         <v>270</v>
       </c>
       <c r="E143" t="s">
+        <v>275</v>
+      </c>
+      <c r="F143" t="s">
         <v>276</v>
-      </c>
-      <c r="F143" t="s">
-        <v>272</v>
       </c>
       <c r="G143" t="s">
         <v>165</v>
@@ -4938,16 +4938,16 @@
         <v>8</v>
       </c>
       <c r="C144" t="s">
-        <v>275</v>
+        <v>269</v>
       </c>
       <c r="D144" t="s">
         <v>270</v>
       </c>
       <c r="E144" t="s">
+        <v>275</v>
+      </c>
+      <c r="F144" t="s">
         <v>276</v>
-      </c>
-      <c r="F144" t="s">
-        <v>272</v>
       </c>
       <c r="G144" t="s">
         <v>165</v>
@@ -4961,16 +4961,16 @@
         <v>8</v>
       </c>
       <c r="C145" t="s">
-        <v>275</v>
+        <v>269</v>
       </c>
       <c r="D145" t="s">
         <v>270</v>
       </c>
       <c r="E145" t="s">
+        <v>275</v>
+      </c>
+      <c r="F145" t="s">
         <v>276</v>
-      </c>
-      <c r="F145" t="s">
-        <v>272</v>
       </c>
       <c r="G145" t="s">
         <v>165</v>
@@ -5007,10 +5007,10 @@
         <v>8</v>
       </c>
       <c r="C147" t="s">
-        <v>269</v>
+        <v>281</v>
       </c>
       <c r="D147" t="s">
-        <v>281</v>
+        <v>270</v>
       </c>
       <c r="E147" t="s">
         <v>271</v>
@@ -5030,10 +5030,10 @@
         <v>8</v>
       </c>
       <c r="C148" t="s">
-        <v>269</v>
+        <v>281</v>
       </c>
       <c r="D148" t="s">
-        <v>281</v>
+        <v>270</v>
       </c>
       <c r="E148" t="s">
         <v>271</v>
@@ -5053,10 +5053,10 @@
         <v>8</v>
       </c>
       <c r="C149" t="s">
-        <v>269</v>
+        <v>281</v>
       </c>
       <c r="D149" t="s">
-        <v>281</v>
+        <v>270</v>
       </c>
       <c r="E149" t="s">
         <v>271</v>
@@ -5076,10 +5076,10 @@
         <v>8</v>
       </c>
       <c r="C150" t="s">
-        <v>269</v>
+        <v>281</v>
       </c>
       <c r="D150" t="s">
-        <v>281</v>
+        <v>270</v>
       </c>
       <c r="E150" t="s">
         <v>271</v>
@@ -5099,10 +5099,10 @@
         <v>8</v>
       </c>
       <c r="C151" t="s">
-        <v>269</v>
+        <v>281</v>
       </c>
       <c r="D151" t="s">
-        <v>281</v>
+        <v>270</v>
       </c>
       <c r="E151" t="s">
         <v>271</v>
@@ -5122,10 +5122,10 @@
         <v>8</v>
       </c>
       <c r="C152" t="s">
-        <v>269</v>
+        <v>281</v>
       </c>
       <c r="D152" t="s">
-        <v>281</v>
+        <v>270</v>
       </c>
       <c r="E152" t="s">
         <v>271</v>
@@ -5145,10 +5145,10 @@
         <v>8</v>
       </c>
       <c r="C153" t="s">
-        <v>269</v>
+        <v>281</v>
       </c>
       <c r="D153" t="s">
-        <v>281</v>
+        <v>270</v>
       </c>
       <c r="E153" t="s">
         <v>271</v>
@@ -5168,10 +5168,10 @@
         <v>8</v>
       </c>
       <c r="C154" t="s">
-        <v>269</v>
+        <v>281</v>
       </c>
       <c r="D154" t="s">
-        <v>281</v>
+        <v>270</v>
       </c>
       <c r="E154" t="s">
         <v>271</v>
@@ -5191,10 +5191,10 @@
         <v>8</v>
       </c>
       <c r="C155" t="s">
-        <v>269</v>
+        <v>281</v>
       </c>
       <c r="D155" t="s">
-        <v>281</v>
+        <v>270</v>
       </c>
       <c r="E155" t="s">
         <v>271</v>
@@ -5214,10 +5214,10 @@
         <v>8</v>
       </c>
       <c r="C156" t="s">
-        <v>269</v>
+        <v>291</v>
       </c>
       <c r="D156" t="s">
-        <v>291</v>
+        <v>270</v>
       </c>
       <c r="E156" t="s">
         <v>271</v>
@@ -5237,13 +5237,13 @@
         <v>8</v>
       </c>
       <c r="C157" t="s">
+        <v>291</v>
+      </c>
+      <c r="D157" t="s">
+        <v>270</v>
+      </c>
+      <c r="E157" t="s">
         <v>293</v>
-      </c>
-      <c r="D157" t="s">
-        <v>291</v>
-      </c>
-      <c r="E157" t="s">
-        <v>271</v>
       </c>
       <c r="F157" t="s">
         <v>272</v>
@@ -5260,10 +5260,10 @@
         <v>8</v>
       </c>
       <c r="C158" t="s">
-        <v>269</v>
+        <v>291</v>
       </c>
       <c r="D158" t="s">
-        <v>291</v>
+        <v>270</v>
       </c>
       <c r="E158" t="s">
         <v>271</v>
@@ -5283,10 +5283,10 @@
         <v>8</v>
       </c>
       <c r="C159" t="s">
-        <v>269</v>
+        <v>291</v>
       </c>
       <c r="D159" t="s">
-        <v>291</v>
+        <v>270</v>
       </c>
       <c r="E159" t="s">
         <v>271</v>
@@ -5306,10 +5306,10 @@
         <v>8</v>
       </c>
       <c r="C160" t="s">
-        <v>269</v>
+        <v>291</v>
       </c>
       <c r="D160" t="s">
-        <v>291</v>
+        <v>270</v>
       </c>
       <c r="E160" t="s">
         <v>271</v>
@@ -5329,10 +5329,10 @@
         <v>8</v>
       </c>
       <c r="C161" t="s">
-        <v>269</v>
+        <v>291</v>
       </c>
       <c r="D161" t="s">
-        <v>291</v>
+        <v>270</v>
       </c>
       <c r="E161" t="s">
         <v>271</v>
@@ -5352,10 +5352,10 @@
         <v>8</v>
       </c>
       <c r="C162" t="s">
-        <v>269</v>
+        <v>299</v>
       </c>
       <c r="D162" t="s">
-        <v>299</v>
+        <v>270</v>
       </c>
       <c r="E162" t="s">
         <v>271</v>
@@ -5378,10 +5378,10 @@
         <v>301</v>
       </c>
       <c r="D163" t="s">
+        <v>270</v>
+      </c>
+      <c r="E163" t="s">
         <v>302</v>
-      </c>
-      <c r="E163" t="s">
-        <v>271</v>
       </c>
       <c r="F163" t="s">
         <v>272</v>
@@ -5398,10 +5398,10 @@
         <v>8</v>
       </c>
       <c r="C164" t="s">
-        <v>269</v>
+        <v>304</v>
       </c>
       <c r="D164" t="s">
-        <v>304</v>
+        <v>270</v>
       </c>
       <c r="E164" t="s">
         <v>271</v>
@@ -5421,10 +5421,10 @@
         <v>8</v>
       </c>
       <c r="C165" t="s">
-        <v>269</v>
+        <v>304</v>
       </c>
       <c r="D165" t="s">
-        <v>304</v>
+        <v>270</v>
       </c>
       <c r="E165" t="s">
         <v>271</v>
@@ -5444,10 +5444,10 @@
         <v>8</v>
       </c>
       <c r="C166" t="s">
-        <v>269</v>
+        <v>304</v>
       </c>
       <c r="D166" t="s">
-        <v>304</v>
+        <v>270</v>
       </c>
       <c r="E166" t="s">
         <v>271</v>
@@ -5467,10 +5467,10 @@
         <v>8</v>
       </c>
       <c r="C167" t="s">
-        <v>269</v>
+        <v>304</v>
       </c>
       <c r="D167" t="s">
-        <v>304</v>
+        <v>270</v>
       </c>
       <c r="E167" t="s">
         <v>271</v>
@@ -5490,13 +5490,13 @@
         <v>8</v>
       </c>
       <c r="C168" t="s">
+        <v>304</v>
+      </c>
+      <c r="D168" t="s">
+        <v>270</v>
+      </c>
+      <c r="E168" t="s">
         <v>309</v>
-      </c>
-      <c r="D168" t="s">
-        <v>304</v>
-      </c>
-      <c r="E168" t="s">
-        <v>271</v>
       </c>
       <c r="F168" t="s">
         <v>272</v>
@@ -5513,13 +5513,13 @@
         <v>8</v>
       </c>
       <c r="C169" t="s">
+        <v>304</v>
+      </c>
+      <c r="D169" t="s">
+        <v>270</v>
+      </c>
+      <c r="E169" t="s">
         <v>309</v>
-      </c>
-      <c r="D169" t="s">
-        <v>304</v>
-      </c>
-      <c r="E169" t="s">
-        <v>271</v>
       </c>
       <c r="F169" t="s">
         <v>272</v>
@@ -5536,10 +5536,10 @@
         <v>8</v>
       </c>
       <c r="C170" t="s">
-        <v>269</v>
+        <v>304</v>
       </c>
       <c r="D170" t="s">
-        <v>304</v>
+        <v>270</v>
       </c>
       <c r="E170" t="s">
         <v>271</v>
@@ -5558,14 +5558,14 @@
       <c r="B171" t="s">
         <v>8</v>
       </c>
-      <c r="C171" t="s">
+      <c r="D171" t="s">
+        <v>313</v>
+      </c>
+      <c r="E171" t="s">
         <v>163</v>
       </c>
-      <c r="E171" t="s">
+      <c r="F171" t="s">
         <v>164</v>
-      </c>
-      <c r="F171" t="s">
-        <v>313</v>
       </c>
       <c r="G171" t="s">
         <v>165</v>
@@ -5578,14 +5578,14 @@
       <c r="B172" t="s">
         <v>8</v>
       </c>
-      <c r="C172" t="s">
+      <c r="D172" t="s">
+        <v>313</v>
+      </c>
+      <c r="E172" t="s">
         <v>118</v>
       </c>
-      <c r="E172" t="s">
+      <c r="F172" t="s">
         <v>119</v>
-      </c>
-      <c r="F172" t="s">
-        <v>313</v>
       </c>
       <c r="G172" t="s">
         <v>116</v>
@@ -5598,14 +5598,14 @@
       <c r="B173" t="s">
         <v>8</v>
       </c>
-      <c r="C173" t="s">
+      <c r="D173" t="s">
+        <v>313</v>
+      </c>
+      <c r="E173" t="s">
         <v>163</v>
       </c>
-      <c r="E173" t="s">
+      <c r="F173" t="s">
         <v>164</v>
-      </c>
-      <c r="F173" t="s">
-        <v>313</v>
       </c>
       <c r="G173" t="s">
         <v>165</v>
@@ -5618,14 +5618,14 @@
       <c r="B174" t="s">
         <v>8</v>
       </c>
-      <c r="C174" t="s">
+      <c r="D174" t="s">
+        <v>313</v>
+      </c>
+      <c r="E174" t="s">
         <v>163</v>
       </c>
-      <c r="E174" t="s">
+      <c r="F174" t="s">
         <v>164</v>
-      </c>
-      <c r="F174" t="s">
-        <v>313</v>
       </c>
       <c r="G174" t="s">
         <v>165</v>
@@ -5638,14 +5638,14 @@
       <c r="B175" t="s">
         <v>8</v>
       </c>
-      <c r="C175" t="s">
+      <c r="D175" t="s">
+        <v>313</v>
+      </c>
+      <c r="E175" t="s">
         <v>163</v>
       </c>
-      <c r="E175" t="s">
+      <c r="F175" t="s">
         <v>164</v>
-      </c>
-      <c r="F175" t="s">
-        <v>313</v>
       </c>
       <c r="G175" t="s">
         <v>165</v>
@@ -5658,14 +5658,14 @@
       <c r="B176" t="s">
         <v>8</v>
       </c>
-      <c r="C176" t="s">
+      <c r="D176" t="s">
+        <v>313</v>
+      </c>
+      <c r="E176" t="s">
         <v>163</v>
       </c>
-      <c r="E176" t="s">
+      <c r="F176" t="s">
         <v>164</v>
-      </c>
-      <c r="F176" t="s">
-        <v>313</v>
       </c>
       <c r="G176" t="s">
         <v>165</v>
@@ -5678,14 +5678,14 @@
       <c r="B177" t="s">
         <v>8</v>
       </c>
-      <c r="C177" t="s">
+      <c r="D177" t="s">
+        <v>320</v>
+      </c>
+      <c r="E177" t="s">
         <v>163</v>
       </c>
-      <c r="E177" t="s">
+      <c r="F177" t="s">
         <v>164</v>
-      </c>
-      <c r="F177" t="s">
-        <v>320</v>
       </c>
       <c r="G177" t="s">
         <v>165</v>
@@ -5698,14 +5698,14 @@
       <c r="B178" t="s">
         <v>8</v>
       </c>
-      <c r="C178" t="s">
+      <c r="D178" t="s">
+        <v>320</v>
+      </c>
+      <c r="E178" t="s">
         <v>163</v>
       </c>
-      <c r="E178" t="s">
+      <c r="F178" t="s">
         <v>164</v>
-      </c>
-      <c r="F178" t="s">
-        <v>320</v>
       </c>
       <c r="G178" t="s">
         <v>165</v>
@@ -5718,14 +5718,14 @@
       <c r="B179" t="s">
         <v>8</v>
       </c>
-      <c r="C179" t="s">
+      <c r="D179" t="s">
+        <v>320</v>
+      </c>
+      <c r="E179" t="s">
         <v>163</v>
       </c>
-      <c r="E179" t="s">
+      <c r="F179" t="s">
         <v>164</v>
-      </c>
-      <c r="F179" t="s">
-        <v>320</v>
       </c>
       <c r="G179" t="s">
         <v>165</v>
@@ -5738,14 +5738,14 @@
       <c r="B180" t="s">
         <v>8</v>
       </c>
-      <c r="C180" t="s">
+      <c r="D180" t="s">
+        <v>320</v>
+      </c>
+      <c r="E180" t="s">
         <v>163</v>
       </c>
-      <c r="E180" t="s">
+      <c r="F180" t="s">
         <v>164</v>
-      </c>
-      <c r="F180" t="s">
-        <v>320</v>
       </c>
       <c r="G180" t="s">
         <v>165</v>
@@ -6035,16 +6035,16 @@
         <v>8</v>
       </c>
       <c r="C193" t="s">
-        <v>341</v>
+        <v>325</v>
       </c>
       <c r="D193" t="s">
         <v>326</v>
       </c>
       <c r="E193" t="s">
+        <v>341</v>
+      </c>
+      <c r="F193" t="s">
         <v>276</v>
-      </c>
-      <c r="F193" t="s">
-        <v>328</v>
       </c>
       <c r="G193" t="s">
         <v>165</v>
@@ -6176,10 +6176,10 @@
         <v>348</v>
       </c>
       <c r="D199" t="s">
+        <v>326</v>
+      </c>
+      <c r="E199" t="s">
         <v>349</v>
-      </c>
-      <c r="E199" t="s">
-        <v>327</v>
       </c>
       <c r="F199" t="s">
         <v>328</v>
@@ -6199,10 +6199,10 @@
         <v>348</v>
       </c>
       <c r="D200" t="s">
+        <v>326</v>
+      </c>
+      <c r="E200" t="s">
         <v>349</v>
-      </c>
-      <c r="E200" t="s">
-        <v>327</v>
       </c>
       <c r="F200" t="s">
         <v>328</v>
@@ -6222,10 +6222,10 @@
         <v>348</v>
       </c>
       <c r="D201" t="s">
+        <v>326</v>
+      </c>
+      <c r="E201" t="s">
         <v>349</v>
-      </c>
-      <c r="E201" t="s">
-        <v>327</v>
       </c>
       <c r="F201" t="s">
         <v>328</v>
@@ -6245,10 +6245,10 @@
         <v>348</v>
       </c>
       <c r="D202" t="s">
+        <v>326</v>
+      </c>
+      <c r="E202" t="s">
         <v>349</v>
-      </c>
-      <c r="E202" t="s">
-        <v>327</v>
       </c>
       <c r="F202" t="s">
         <v>328</v>
@@ -6265,16 +6265,16 @@
         <v>8</v>
       </c>
       <c r="C203" t="s">
+        <v>348</v>
+      </c>
+      <c r="D203" t="s">
+        <v>326</v>
+      </c>
+      <c r="E203" t="s">
         <v>341</v>
       </c>
-      <c r="D203" t="s">
-        <v>349</v>
-      </c>
-      <c r="E203" t="s">
+      <c r="F203" t="s">
         <v>276</v>
-      </c>
-      <c r="F203" t="s">
-        <v>328</v>
       </c>
       <c r="G203" t="s">
         <v>165</v>
@@ -6291,10 +6291,10 @@
         <v>348</v>
       </c>
       <c r="D204" t="s">
+        <v>326</v>
+      </c>
+      <c r="E204" t="s">
         <v>349</v>
-      </c>
-      <c r="E204" t="s">
-        <v>327</v>
       </c>
       <c r="F204" t="s">
         <v>328</v>
@@ -6314,10 +6314,10 @@
         <v>356</v>
       </c>
       <c r="D205" t="s">
+        <v>326</v>
+      </c>
+      <c r="E205" t="s">
         <v>357</v>
-      </c>
-      <c r="E205" t="s">
-        <v>327</v>
       </c>
       <c r="F205" t="s">
         <v>328</v>
@@ -6337,10 +6337,10 @@
         <v>356</v>
       </c>
       <c r="D206" t="s">
+        <v>326</v>
+      </c>
+      <c r="E206" t="s">
         <v>357</v>
-      </c>
-      <c r="E206" t="s">
-        <v>327</v>
       </c>
       <c r="F206" t="s">
         <v>328</v>
@@ -6360,10 +6360,10 @@
         <v>356</v>
       </c>
       <c r="D207" t="s">
+        <v>326</v>
+      </c>
+      <c r="E207" t="s">
         <v>357</v>
-      </c>
-      <c r="E207" t="s">
-        <v>327</v>
       </c>
       <c r="F207" t="s">
         <v>328</v>
@@ -6380,16 +6380,16 @@
         <v>8</v>
       </c>
       <c r="C208" t="s">
+        <v>356</v>
+      </c>
+      <c r="D208" t="s">
+        <v>326</v>
+      </c>
+      <c r="E208" t="s">
         <v>341</v>
       </c>
-      <c r="D208" t="s">
-        <v>357</v>
-      </c>
-      <c r="E208" t="s">
+      <c r="F208" t="s">
         <v>276</v>
-      </c>
-      <c r="F208" t="s">
-        <v>328</v>
       </c>
       <c r="G208" t="s">
         <v>165</v>
@@ -6406,10 +6406,10 @@
         <v>356</v>
       </c>
       <c r="D209" t="s">
+        <v>326</v>
+      </c>
+      <c r="E209" t="s">
         <v>357</v>
-      </c>
-      <c r="E209" t="s">
-        <v>327</v>
       </c>
       <c r="F209" t="s">
         <v>328</v>
@@ -6541,16 +6541,16 @@
         <v>8</v>
       </c>
       <c r="C215" t="s">
-        <v>348</v>
+        <v>363</v>
       </c>
       <c r="D215" t="s">
         <v>364</v>
       </c>
       <c r="E215" t="s">
-        <v>327</v>
+        <v>349</v>
       </c>
       <c r="F215" t="s">
-        <v>366</v>
+        <v>328</v>
       </c>
       <c r="G215" t="s">
         <v>165</v>
@@ -6656,16 +6656,16 @@
         <v>8</v>
       </c>
       <c r="C220" t="s">
-        <v>309</v>
+        <v>363</v>
       </c>
       <c r="D220" t="s">
         <v>364</v>
       </c>
       <c r="E220" t="s">
-        <v>271</v>
+        <v>309</v>
       </c>
       <c r="F220" t="s">
-        <v>366</v>
+        <v>272</v>
       </c>
       <c r="G220" t="s">
         <v>165</v>
@@ -6794,16 +6794,16 @@
         <v>8</v>
       </c>
       <c r="C226" t="s">
-        <v>275</v>
+        <v>363</v>
       </c>
       <c r="D226" t="s">
         <v>364</v>
       </c>
       <c r="E226" t="s">
+        <v>275</v>
+      </c>
+      <c r="F226" t="s">
         <v>276</v>
-      </c>
-      <c r="F226" t="s">
-        <v>366</v>
       </c>
       <c r="G226" t="s">
         <v>165</v>
@@ -6840,16 +6840,16 @@
         <v>8</v>
       </c>
       <c r="C228" t="s">
-        <v>163</v>
+        <v>363</v>
       </c>
       <c r="D228" t="s">
         <v>364</v>
       </c>
       <c r="E228" t="s">
+        <v>163</v>
+      </c>
+      <c r="F228" t="s">
         <v>164</v>
-      </c>
-      <c r="F228" t="s">
-        <v>366</v>
       </c>
       <c r="G228" t="s">
         <v>165</v>
@@ -6866,10 +6866,10 @@
         <v>386</v>
       </c>
       <c r="D229" t="s">
+        <v>364</v>
+      </c>
+      <c r="E229" t="s">
         <v>387</v>
-      </c>
-      <c r="E229" t="s">
-        <v>365</v>
       </c>
       <c r="F229" t="s">
         <v>366</v>
@@ -6889,10 +6889,10 @@
         <v>386</v>
       </c>
       <c r="D230" t="s">
+        <v>364</v>
+      </c>
+      <c r="E230" t="s">
         <v>387</v>
-      </c>
-      <c r="E230" t="s">
-        <v>365</v>
       </c>
       <c r="F230" t="s">
         <v>366</v>
@@ -6909,16 +6909,16 @@
         <v>8</v>
       </c>
       <c r="C231" t="s">
+        <v>386</v>
+      </c>
+      <c r="D231" t="s">
+        <v>364</v>
+      </c>
+      <c r="E231" t="s">
         <v>293</v>
       </c>
-      <c r="D231" t="s">
-        <v>387</v>
-      </c>
-      <c r="E231" t="s">
-        <v>271</v>
-      </c>
       <c r="F231" t="s">
-        <v>366</v>
+        <v>272</v>
       </c>
       <c r="G231" t="s">
         <v>165</v>
@@ -6932,16 +6932,16 @@
         <v>8</v>
       </c>
       <c r="C232" t="s">
+        <v>386</v>
+      </c>
+      <c r="D232" t="s">
+        <v>364</v>
+      </c>
+      <c r="E232" t="s">
         <v>309</v>
       </c>
-      <c r="D232" t="s">
-        <v>387</v>
-      </c>
-      <c r="E232" t="s">
-        <v>271</v>
-      </c>
       <c r="F232" t="s">
-        <v>366</v>
+        <v>272</v>
       </c>
       <c r="G232" t="s">
         <v>165</v>
@@ -6958,10 +6958,10 @@
         <v>386</v>
       </c>
       <c r="D233" t="s">
+        <v>364</v>
+      </c>
+      <c r="E233" t="s">
         <v>387</v>
-      </c>
-      <c r="E233" t="s">
-        <v>365</v>
       </c>
       <c r="F233" t="s">
         <v>366</v>
@@ -6981,10 +6981,10 @@
         <v>386</v>
       </c>
       <c r="D234" t="s">
+        <v>364</v>
+      </c>
+      <c r="E234" t="s">
         <v>387</v>
-      </c>
-      <c r="E234" t="s">
-        <v>365</v>
       </c>
       <c r="F234" t="s">
         <v>366</v>
@@ -7004,10 +7004,10 @@
         <v>386</v>
       </c>
       <c r="D235" t="s">
+        <v>364</v>
+      </c>
+      <c r="E235" t="s">
         <v>387</v>
-      </c>
-      <c r="E235" t="s">
-        <v>365</v>
       </c>
       <c r="F235" t="s">
         <v>366</v>
@@ -7027,10 +7027,10 @@
         <v>386</v>
       </c>
       <c r="D236" t="s">
+        <v>364</v>
+      </c>
+      <c r="E236" t="s">
         <v>387</v>
-      </c>
-      <c r="E236" t="s">
-        <v>365</v>
       </c>
       <c r="F236" t="s">
         <v>366</v>
@@ -7050,10 +7050,10 @@
         <v>386</v>
       </c>
       <c r="D237" t="s">
+        <v>364</v>
+      </c>
+      <c r="E237" t="s">
         <v>387</v>
-      </c>
-      <c r="E237" t="s">
-        <v>365</v>
       </c>
       <c r="F237" t="s">
         <v>366</v>
@@ -7073,10 +7073,10 @@
         <v>386</v>
       </c>
       <c r="D238" t="s">
+        <v>364</v>
+      </c>
+      <c r="E238" t="s">
         <v>387</v>
-      </c>
-      <c r="E238" t="s">
-        <v>365</v>
       </c>
       <c r="F238" t="s">
         <v>366</v>
@@ -7096,10 +7096,10 @@
         <v>398</v>
       </c>
       <c r="D239" t="s">
+        <v>364</v>
+      </c>
+      <c r="E239" t="s">
         <v>399</v>
-      </c>
-      <c r="E239" t="s">
-        <v>365</v>
       </c>
       <c r="F239" t="s">
         <v>366</v>
@@ -7116,16 +7116,16 @@
         <v>8</v>
       </c>
       <c r="C240" t="s">
+        <v>401</v>
+      </c>
+      <c r="D240" t="s">
+        <v>402</v>
+      </c>
+      <c r="E240" t="s">
         <v>163</v>
       </c>
-      <c r="D240" t="s">
-        <v>401</v>
-      </c>
-      <c r="E240" t="s">
+      <c r="F240" t="s">
         <v>164</v>
-      </c>
-      <c r="F240" t="s">
-        <v>402</v>
       </c>
       <c r="G240" t="s">
         <v>165</v>
@@ -7139,16 +7139,16 @@
         <v>8</v>
       </c>
       <c r="C241" t="s">
+        <v>401</v>
+      </c>
+      <c r="D241" t="s">
+        <v>402</v>
+      </c>
+      <c r="E241" t="s">
         <v>163</v>
       </c>
-      <c r="D241" t="s">
-        <v>401</v>
-      </c>
-      <c r="E241" t="s">
+      <c r="F241" t="s">
         <v>164</v>
-      </c>
-      <c r="F241" t="s">
-        <v>402</v>
       </c>
       <c r="G241" t="s">
         <v>165</v>
@@ -7162,16 +7162,16 @@
         <v>8</v>
       </c>
       <c r="C242" t="s">
+        <v>401</v>
+      </c>
+      <c r="D242" t="s">
+        <v>402</v>
+      </c>
+      <c r="E242" t="s">
         <v>163</v>
       </c>
-      <c r="D242" t="s">
-        <v>401</v>
-      </c>
-      <c r="E242" t="s">
+      <c r="F242" t="s">
         <v>164</v>
-      </c>
-      <c r="F242" t="s">
-        <v>402</v>
       </c>
       <c r="G242" t="s">
         <v>165</v>
@@ -7185,16 +7185,16 @@
         <v>8</v>
       </c>
       <c r="C243" t="s">
+        <v>401</v>
+      </c>
+      <c r="D243" t="s">
+        <v>402</v>
+      </c>
+      <c r="E243" t="s">
         <v>163</v>
       </c>
-      <c r="D243" t="s">
-        <v>401</v>
-      </c>
-      <c r="E243" t="s">
+      <c r="F243" t="s">
         <v>164</v>
-      </c>
-      <c r="F243" t="s">
-        <v>402</v>
       </c>
       <c r="G243" t="s">
         <v>165</v>
@@ -7208,16 +7208,16 @@
         <v>8</v>
       </c>
       <c r="C244" t="s">
+        <v>401</v>
+      </c>
+      <c r="D244" t="s">
+        <v>402</v>
+      </c>
+      <c r="E244" t="s">
         <v>163</v>
       </c>
-      <c r="D244" t="s">
-        <v>401</v>
-      </c>
-      <c r="E244" t="s">
+      <c r="F244" t="s">
         <v>164</v>
-      </c>
-      <c r="F244" t="s">
-        <v>402</v>
       </c>
       <c r="G244" t="s">
         <v>165</v>
@@ -7231,16 +7231,16 @@
         <v>8</v>
       </c>
       <c r="C245" t="s">
+        <v>401</v>
+      </c>
+      <c r="D245" t="s">
+        <v>402</v>
+      </c>
+      <c r="E245" t="s">
         <v>163</v>
       </c>
-      <c r="D245" t="s">
-        <v>401</v>
-      </c>
-      <c r="E245" t="s">
+      <c r="F245" t="s">
         <v>164</v>
-      </c>
-      <c r="F245" t="s">
-        <v>402</v>
       </c>
       <c r="G245" t="s">
         <v>165</v>
@@ -7257,13 +7257,13 @@
         <v>409</v>
       </c>
       <c r="D246" t="s">
+        <v>402</v>
+      </c>
+      <c r="E246" t="s">
         <v>410</v>
       </c>
-      <c r="E246" t="s">
+      <c r="F246" t="s">
         <v>256</v>
-      </c>
-      <c r="F246" t="s">
-        <v>402</v>
       </c>
       <c r="G246" t="s">
         <v>165</v>
@@ -7276,14 +7276,14 @@
       <c r="B247" t="s">
         <v>8</v>
       </c>
-      <c r="C247" t="s">
+      <c r="D247" t="s">
+        <v>412</v>
+      </c>
+      <c r="E247" t="s">
         <v>95</v>
       </c>
-      <c r="E247" t="s">
+      <c r="F247" t="s">
         <v>96</v>
-      </c>
-      <c r="F247" t="s">
-        <v>412</v>
       </c>
       <c r="G247" t="s">
         <v>97</v>
@@ -7296,14 +7296,14 @@
       <c r="B248" t="s">
         <v>8</v>
       </c>
-      <c r="C248" t="s">
+      <c r="D248" t="s">
+        <v>412</v>
+      </c>
+      <c r="E248" t="s">
         <v>95</v>
       </c>
-      <c r="E248" t="s">
+      <c r="F248" t="s">
         <v>96</v>
-      </c>
-      <c r="F248" t="s">
-        <v>412</v>
       </c>
       <c r="G248" t="s">
         <v>97</v>
@@ -7316,14 +7316,14 @@
       <c r="B249" t="s">
         <v>8</v>
       </c>
-      <c r="C249" t="s">
+      <c r="D249" t="s">
+        <v>412</v>
+      </c>
+      <c r="E249" t="s">
         <v>415</v>
       </c>
-      <c r="E249" t="s">
+      <c r="F249" t="s">
         <v>416</v>
-      </c>
-      <c r="F249" t="s">
-        <v>412</v>
       </c>
       <c r="G249" t="s">
         <v>97</v>
@@ -7336,14 +7336,14 @@
       <c r="B250" t="s">
         <v>8</v>
       </c>
-      <c r="C250" t="s">
+      <c r="D250" t="s">
+        <v>412</v>
+      </c>
+      <c r="E250" t="s">
         <v>95</v>
       </c>
-      <c r="E250" t="s">
+      <c r="F250" t="s">
         <v>96</v>
-      </c>
-      <c r="F250" t="s">
-        <v>412</v>
       </c>
       <c r="G250" t="s">
         <v>97</v>
@@ -7356,14 +7356,14 @@
       <c r="B251" t="s">
         <v>8</v>
       </c>
-      <c r="C251" t="s">
+      <c r="D251" t="s">
+        <v>412</v>
+      </c>
+      <c r="E251" t="s">
         <v>95</v>
       </c>
-      <c r="E251" t="s">
+      <c r="F251" t="s">
         <v>96</v>
-      </c>
-      <c r="F251" t="s">
-        <v>412</v>
       </c>
       <c r="G251" t="s">
         <v>97</v>
@@ -7376,14 +7376,14 @@
       <c r="B252" t="s">
         <v>8</v>
       </c>
-      <c r="C252" t="s">
+      <c r="D252" t="s">
+        <v>412</v>
+      </c>
+      <c r="E252" t="s">
         <v>95</v>
       </c>
-      <c r="E252" t="s">
+      <c r="F252" t="s">
         <v>96</v>
-      </c>
-      <c r="F252" t="s">
-        <v>412</v>
       </c>
       <c r="G252" t="s">
         <v>97</v>
@@ -7396,7 +7396,7 @@
       <c r="B253" t="s">
         <v>8</v>
       </c>
-      <c r="C253" t="s">
+      <c r="D253" t="s">
         <v>421</v>
       </c>
       <c r="E253" t="s">
@@ -7416,14 +7416,14 @@
       <c r="B254" t="s">
         <v>8</v>
       </c>
-      <c r="C254" t="s">
+      <c r="D254" t="s">
+        <v>421</v>
+      </c>
+      <c r="E254" t="s">
         <v>219</v>
       </c>
-      <c r="E254" t="s">
+      <c r="F254" t="s">
         <v>220</v>
-      </c>
-      <c r="F254" t="s">
-        <v>423</v>
       </c>
       <c r="G254" t="s">
         <v>93</v>
@@ -7436,14 +7436,14 @@
       <c r="B255" t="s">
         <v>8</v>
       </c>
-      <c r="C255" t="s">
+      <c r="D255" t="s">
+        <v>421</v>
+      </c>
+      <c r="E255" t="s">
         <v>426</v>
       </c>
-      <c r="E255" t="s">
+      <c r="F255" t="s">
         <v>427</v>
-      </c>
-      <c r="F255" t="s">
-        <v>423</v>
       </c>
       <c r="G255" t="s">
         <v>93</v>
@@ -7456,14 +7456,14 @@
       <c r="B256" t="s">
         <v>8</v>
       </c>
-      <c r="C256" t="s">
+      <c r="D256" t="s">
+        <v>421</v>
+      </c>
+      <c r="E256" t="s">
         <v>426</v>
       </c>
-      <c r="E256" t="s">
+      <c r="F256" t="s">
         <v>427</v>
-      </c>
-      <c r="F256" t="s">
-        <v>423</v>
       </c>
       <c r="G256" t="s">
         <v>93</v>
@@ -7476,14 +7476,14 @@
       <c r="B257" t="s">
         <v>8</v>
       </c>
-      <c r="C257" t="s">
+      <c r="D257" t="s">
+        <v>421</v>
+      </c>
+      <c r="E257" t="s">
         <v>426</v>
       </c>
-      <c r="E257" t="s">
+      <c r="F257" t="s">
         <v>427</v>
-      </c>
-      <c r="F257" t="s">
-        <v>423</v>
       </c>
       <c r="G257" t="s">
         <v>93</v>
@@ -7496,14 +7496,14 @@
       <c r="B258" t="s">
         <v>8</v>
       </c>
-      <c r="C258" t="s">
-        <v>325</v>
+      <c r="D258" t="s">
+        <v>421</v>
       </c>
       <c r="E258" t="s">
         <v>327</v>
       </c>
       <c r="F258" t="s">
-        <v>423</v>
+        <v>328</v>
       </c>
       <c r="G258" t="s">
         <v>165</v>
@@ -7516,14 +7516,14 @@
       <c r="B259" t="s">
         <v>8</v>
       </c>
-      <c r="C259" t="s">
+      <c r="D259" t="s">
+        <v>421</v>
+      </c>
+      <c r="E259" t="s">
         <v>426</v>
       </c>
-      <c r="E259" t="s">
+      <c r="F259" t="s">
         <v>427</v>
-      </c>
-      <c r="F259" t="s">
-        <v>423</v>
       </c>
       <c r="G259" t="s">
         <v>93</v>
@@ -7536,14 +7536,14 @@
       <c r="B260" t="s">
         <v>8</v>
       </c>
-      <c r="C260" t="s">
+      <c r="D260" t="s">
+        <v>421</v>
+      </c>
+      <c r="E260" t="s">
         <v>163</v>
       </c>
-      <c r="E260" t="s">
+      <c r="F260" t="s">
         <v>164</v>
-      </c>
-      <c r="F260" t="s">
-        <v>423</v>
       </c>
       <c r="G260" t="s">
         <v>165</v>
@@ -7556,14 +7556,14 @@
       <c r="B261" t="s">
         <v>8</v>
       </c>
-      <c r="C261" t="s">
+      <c r="D261" t="s">
+        <v>421</v>
+      </c>
+      <c r="E261" t="s">
         <v>434</v>
       </c>
-      <c r="E261" t="s">
+      <c r="F261" t="s">
         <v>435</v>
-      </c>
-      <c r="F261" t="s">
-        <v>423</v>
       </c>
       <c r="G261" t="s">
         <v>197</v>
@@ -7576,14 +7576,14 @@
       <c r="B262" t="s">
         <v>8</v>
       </c>
-      <c r="C262" t="s">
+      <c r="D262" t="s">
+        <v>421</v>
+      </c>
+      <c r="E262" t="s">
         <v>163</v>
       </c>
-      <c r="E262" t="s">
+      <c r="F262" t="s">
         <v>164</v>
-      </c>
-      <c r="F262" t="s">
-        <v>423</v>
       </c>
       <c r="G262" t="s">
         <v>165</v>
@@ -7596,14 +7596,14 @@
       <c r="B263" t="s">
         <v>8</v>
       </c>
-      <c r="C263" t="s">
+      <c r="D263" t="s">
+        <v>421</v>
+      </c>
+      <c r="E263" t="s">
         <v>438</v>
       </c>
-      <c r="E263" t="s">
+      <c r="F263" t="s">
         <v>439</v>
-      </c>
-      <c r="F263" t="s">
-        <v>423</v>
       </c>
       <c r="G263" t="s">
         <v>184</v>
@@ -7616,14 +7616,14 @@
       <c r="B264" t="s">
         <v>8</v>
       </c>
-      <c r="C264" t="s">
+      <c r="D264" t="s">
+        <v>421</v>
+      </c>
+      <c r="E264" t="s">
         <v>31</v>
       </c>
-      <c r="E264" t="s">
+      <c r="F264" t="s">
         <v>32</v>
-      </c>
-      <c r="F264" t="s">
-        <v>423</v>
       </c>
       <c r="G264" t="s">
         <v>33</v>
@@ -7636,14 +7636,14 @@
       <c r="B265" t="s">
         <v>8</v>
       </c>
-      <c r="C265" t="s">
-        <v>9</v>
+      <c r="D265" t="s">
+        <v>421</v>
       </c>
       <c r="E265" t="s">
         <v>11</v>
       </c>
       <c r="F265" t="s">
-        <v>423</v>
+        <v>12</v>
       </c>
       <c r="G265" t="s">
         <v>13</v>
@@ -7656,14 +7656,14 @@
       <c r="B266" t="s">
         <v>8</v>
       </c>
-      <c r="C266" t="s">
+      <c r="D266" t="s">
+        <v>421</v>
+      </c>
+      <c r="E266" t="s">
         <v>443</v>
       </c>
-      <c r="E266" t="s">
+      <c r="F266" t="s">
         <v>444</v>
-      </c>
-      <c r="F266" t="s">
-        <v>423</v>
       </c>
       <c r="G266" t="s">
         <v>116</v>
@@ -7676,14 +7676,14 @@
       <c r="B267" t="s">
         <v>8</v>
       </c>
-      <c r="C267" t="s">
+      <c r="D267" t="s">
+        <v>446</v>
+      </c>
+      <c r="E267" t="s">
         <v>118</v>
       </c>
-      <c r="E267" t="s">
+      <c r="F267" t="s">
         <v>119</v>
-      </c>
-      <c r="F267" t="s">
-        <v>446</v>
       </c>
       <c r="G267" t="s">
         <v>116</v>
@@ -7696,14 +7696,14 @@
       <c r="B268" t="s">
         <v>8</v>
       </c>
-      <c r="C268" t="s">
-        <v>202</v>
+      <c r="D268" t="s">
+        <v>448</v>
       </c>
       <c r="E268" t="s">
         <v>203</v>
       </c>
       <c r="F268" t="s">
-        <v>448</v>
+        <v>204</v>
       </c>
       <c r="G268" t="s">
         <v>184</v>
@@ -7716,14 +7716,14 @@
       <c r="B269" t="s">
         <v>8</v>
       </c>
-      <c r="C269" t="s">
+      <c r="D269" t="s">
+        <v>450</v>
+      </c>
+      <c r="E269" t="s">
         <v>118</v>
       </c>
-      <c r="E269" t="s">
+      <c r="F269" t="s">
         <v>119</v>
-      </c>
-      <c r="F269" t="s">
-        <v>450</v>
       </c>
       <c r="G269" t="s">
         <v>116</v>
@@ -7736,14 +7736,14 @@
       <c r="B270" t="s">
         <v>8</v>
       </c>
-      <c r="C270" t="s">
+      <c r="D270" t="s">
+        <v>450</v>
+      </c>
+      <c r="E270" t="s">
         <v>118</v>
       </c>
-      <c r="E270" t="s">
+      <c r="F270" t="s">
         <v>119</v>
-      </c>
-      <c r="F270" t="s">
-        <v>450</v>
       </c>
       <c r="G270" t="s">
         <v>116</v>
@@ -7756,7 +7756,7 @@
       <c r="B271" t="s">
         <v>8</v>
       </c>
-      <c r="C271" t="s">
+      <c r="D271" t="s">
         <v>453</v>
       </c>
       <c r="E271" t="s">
@@ -7776,7 +7776,7 @@
       <c r="B272" t="s">
         <v>8</v>
       </c>
-      <c r="C272" t="s">
+      <c r="D272" t="s">
         <v>453</v>
       </c>
       <c r="E272" t="s">
@@ -7796,7 +7796,7 @@
       <c r="B273" t="s">
         <v>8</v>
       </c>
-      <c r="C273" t="s">
+      <c r="D273" t="s">
         <v>453</v>
       </c>
       <c r="E273" t="s">
@@ -7816,7 +7816,7 @@
       <c r="B274" t="s">
         <v>8</v>
       </c>
-      <c r="C274" t="s">
+      <c r="D274" t="s">
         <v>453</v>
       </c>
       <c r="E274" t="s">
@@ -7836,7 +7836,7 @@
       <c r="B275" t="s">
         <v>8</v>
       </c>
-      <c r="C275" t="s">
+      <c r="D275" t="s">
         <v>453</v>
       </c>
       <c r="E275" t="s">
@@ -7856,7 +7856,7 @@
       <c r="B276" t="s">
         <v>8</v>
       </c>
-      <c r="C276" t="s">
+      <c r="D276" t="s">
         <v>453</v>
       </c>
       <c r="E276" t="s">
@@ -7876,7 +7876,7 @@
       <c r="B277" t="s">
         <v>8</v>
       </c>
-      <c r="C277" t="s">
+      <c r="D277" t="s">
         <v>453</v>
       </c>
       <c r="E277" t="s">
@@ -7896,14 +7896,14 @@
       <c r="B278" t="s">
         <v>8</v>
       </c>
-      <c r="C278" t="s">
-        <v>202</v>
+      <c r="D278" t="s">
+        <v>463</v>
       </c>
       <c r="E278" t="s">
         <v>203</v>
       </c>
       <c r="F278" t="s">
-        <v>463</v>
+        <v>204</v>
       </c>
       <c r="G278" t="s">
         <v>184</v>
@@ -7916,14 +7916,14 @@
       <c r="B279" t="s">
         <v>8</v>
       </c>
-      <c r="C279" t="s">
-        <v>51</v>
+      <c r="D279" t="s">
+        <v>463</v>
       </c>
       <c r="E279" t="s">
         <v>53</v>
       </c>
       <c r="F279" t="s">
-        <v>463</v>
+        <v>54</v>
       </c>
       <c r="G279" t="s">
         <v>33</v>
@@ -7936,14 +7936,14 @@
       <c r="B280" t="s">
         <v>8</v>
       </c>
-      <c r="C280" t="s">
-        <v>9</v>
+      <c r="D280" t="s">
+        <v>463</v>
       </c>
       <c r="E280" t="s">
         <v>11</v>
       </c>
       <c r="F280" t="s">
-        <v>463</v>
+        <v>12</v>
       </c>
       <c r="G280" t="s">
         <v>13</v>
@@ -7956,14 +7956,14 @@
       <c r="B281" t="s">
         <v>8</v>
       </c>
-      <c r="C281" t="s">
+      <c r="D281" t="s">
+        <v>463</v>
+      </c>
+      <c r="E281" t="s">
         <v>170</v>
       </c>
-      <c r="E281" t="s">
+      <c r="F281" t="s">
         <v>171</v>
-      </c>
-      <c r="F281" t="s">
-        <v>463</v>
       </c>
       <c r="G281" t="s">
         <v>116</v>
@@ -7976,14 +7976,14 @@
       <c r="B282" t="s">
         <v>8</v>
       </c>
-      <c r="C282" t="s">
+      <c r="D282" t="s">
+        <v>463</v>
+      </c>
+      <c r="E282" t="s">
         <v>124</v>
       </c>
-      <c r="E282" t="s">
+      <c r="F282" t="s">
         <v>125</v>
-      </c>
-      <c r="F282" t="s">
-        <v>463</v>
       </c>
       <c r="G282" t="s">
         <v>126</v>
@@ -7996,14 +7996,14 @@
       <c r="B283" t="s">
         <v>8</v>
       </c>
-      <c r="C283" t="s">
-        <v>398</v>
+      <c r="D283" t="s">
+        <v>469</v>
       </c>
       <c r="E283" t="s">
-        <v>365</v>
+        <v>399</v>
       </c>
       <c r="F283" t="s">
-        <v>469</v>
+        <v>366</v>
       </c>
       <c r="G283" t="s">
         <v>165</v>
@@ -8016,14 +8016,14 @@
       <c r="B284" t="s">
         <v>8</v>
       </c>
-      <c r="C284" t="s">
+      <c r="D284" t="s">
+        <v>471</v>
+      </c>
+      <c r="E284" t="s">
         <v>124</v>
       </c>
-      <c r="E284" t="s">
+      <c r="F284" t="s">
         <v>125</v>
-      </c>
-      <c r="F284" t="s">
-        <v>471</v>
       </c>
       <c r="G284" t="s">
         <v>126</v>
@@ -8036,14 +8036,14 @@
       <c r="B285" t="s">
         <v>8</v>
       </c>
-      <c r="C285" t="s">
+      <c r="D285" t="s">
+        <v>473</v>
+      </c>
+      <c r="E285" t="s">
         <v>170</v>
       </c>
-      <c r="E285" t="s">
+      <c r="F285" t="s">
         <v>171</v>
-      </c>
-      <c r="F285" t="s">
-        <v>473</v>
       </c>
       <c r="G285" t="s">
         <v>116</v>
@@ -8056,14 +8056,14 @@
       <c r="B286" t="s">
         <v>8</v>
       </c>
-      <c r="C286" t="s">
+      <c r="D286" t="s">
+        <v>475</v>
+      </c>
+      <c r="E286" t="s">
         <v>438</v>
       </c>
-      <c r="E286" t="s">
+      <c r="F286" t="s">
         <v>439</v>
-      </c>
-      <c r="F286" t="s">
-        <v>475</v>
       </c>
       <c r="G286" t="s">
         <v>184</v>
@@ -8076,14 +8076,14 @@
       <c r="B287" t="s">
         <v>8</v>
       </c>
-      <c r="C287" t="s">
+      <c r="D287" t="s">
+        <v>475</v>
+      </c>
+      <c r="E287" t="s">
         <v>438</v>
       </c>
-      <c r="E287" t="s">
+      <c r="F287" t="s">
         <v>439</v>
-      </c>
-      <c r="F287" t="s">
-        <v>475</v>
       </c>
       <c r="G287" t="s">
         <v>184</v>
@@ -8096,14 +8096,14 @@
       <c r="B288" t="s">
         <v>8</v>
       </c>
-      <c r="C288" t="s">
+      <c r="D288" t="s">
+        <v>475</v>
+      </c>
+      <c r="E288" t="s">
         <v>41</v>
       </c>
-      <c r="E288" t="s">
+      <c r="F288" t="s">
         <v>42</v>
-      </c>
-      <c r="F288" t="s">
-        <v>475</v>
       </c>
       <c r="G288" t="s">
         <v>13</v>
@@ -8116,14 +8116,14 @@
       <c r="B289" t="s">
         <v>8</v>
       </c>
-      <c r="C289" t="s">
+      <c r="D289" t="s">
+        <v>475</v>
+      </c>
+      <c r="E289" t="s">
         <v>31</v>
       </c>
-      <c r="E289" t="s">
+      <c r="F289" t="s">
         <v>32</v>
-      </c>
-      <c r="F289" t="s">
-        <v>475</v>
       </c>
       <c r="G289" t="s">
         <v>33</v>
@@ -8136,14 +8136,14 @@
       <c r="B290" t="s">
         <v>8</v>
       </c>
-      <c r="C290" t="s">
+      <c r="D290" t="s">
+        <v>475</v>
+      </c>
+      <c r="E290" t="s">
         <v>31</v>
       </c>
-      <c r="E290" t="s">
+      <c r="F290" t="s">
         <v>32</v>
-      </c>
-      <c r="F290" t="s">
-        <v>475</v>
       </c>
       <c r="G290" t="s">
         <v>33</v>
@@ -8156,14 +8156,14 @@
       <c r="B291" t="s">
         <v>8</v>
       </c>
-      <c r="C291" t="s">
+      <c r="D291" t="s">
+        <v>475</v>
+      </c>
+      <c r="E291" t="s">
         <v>170</v>
       </c>
-      <c r="E291" t="s">
+      <c r="F291" t="s">
         <v>171</v>
-      </c>
-      <c r="F291" t="s">
-        <v>475</v>
       </c>
       <c r="G291" t="s">
         <v>116</v>
@@ -8176,14 +8176,14 @@
       <c r="B292" t="s">
         <v>8</v>
       </c>
-      <c r="C292" t="s">
+      <c r="D292" t="s">
+        <v>475</v>
+      </c>
+      <c r="E292" t="s">
         <v>170</v>
       </c>
-      <c r="E292" t="s">
+      <c r="F292" t="s">
         <v>171</v>
-      </c>
-      <c r="F292" t="s">
-        <v>475</v>
       </c>
       <c r="G292" t="s">
         <v>116</v>
@@ -8196,14 +8196,14 @@
       <c r="B293" t="s">
         <v>8</v>
       </c>
-      <c r="C293" t="s">
+      <c r="D293" t="s">
+        <v>475</v>
+      </c>
+      <c r="E293" t="s">
         <v>170</v>
       </c>
-      <c r="E293" t="s">
+      <c r="F293" t="s">
         <v>171</v>
-      </c>
-      <c r="F293" t="s">
-        <v>475</v>
       </c>
       <c r="G293" t="s">
         <v>116</v>
@@ -8216,14 +8216,14 @@
       <c r="B294" t="s">
         <v>8</v>
       </c>
-      <c r="C294" t="s">
+      <c r="D294" t="s">
+        <v>475</v>
+      </c>
+      <c r="E294" t="s">
         <v>170</v>
       </c>
-      <c r="E294" t="s">
+      <c r="F294" t="s">
         <v>171</v>
-      </c>
-      <c r="F294" t="s">
-        <v>475</v>
       </c>
       <c r="G294" t="s">
         <v>116</v>
@@ -8236,14 +8236,14 @@
       <c r="B295" t="s">
         <v>8</v>
       </c>
-      <c r="C295" t="s">
+      <c r="D295" t="s">
+        <v>485</v>
+      </c>
+      <c r="E295" t="s">
         <v>170</v>
       </c>
-      <c r="E295" t="s">
+      <c r="F295" t="s">
         <v>171</v>
-      </c>
-      <c r="F295" t="s">
-        <v>485</v>
       </c>
       <c r="G295" t="s">
         <v>116</v>
@@ -8256,14 +8256,14 @@
       <c r="B296" t="s">
         <v>8</v>
       </c>
-      <c r="C296" t="s">
+      <c r="D296" t="s">
+        <v>485</v>
+      </c>
+      <c r="E296" t="s">
         <v>170</v>
       </c>
-      <c r="E296" t="s">
+      <c r="F296" t="s">
         <v>171</v>
-      </c>
-      <c r="F296" t="s">
-        <v>485</v>
       </c>
       <c r="G296" t="s">
         <v>116</v>

--- a/api/2/xlsx/fr/SectorCOFOG.xlsx
+++ b/api/2/xlsx/fr/SectorCOFOG.xlsx
@@ -22,75 +22,75 @@
     <t>status</t>
   </si>
   <si>
+    <t>codeforiati:group-code</t>
+  </si>
+  <si>
+    <t>codeforiati:cofog-group</t>
+  </si>
+  <si>
     <t>codeforiati:category-code</t>
   </si>
   <si>
-    <t>codeforiati:group-code</t>
+    <t>codeforiati:cofog-division</t>
   </si>
   <si>
     <t>codeforiati:cofog-class</t>
   </si>
   <si>
-    <t>codeforiati:cofog-group</t>
-  </si>
-  <si>
-    <t>codeforiati:cofog-division</t>
-  </si>
-  <si>
     <t>11110</t>
   </si>
   <si>
     <t>active</t>
   </si>
   <si>
+    <t>110</t>
+  </si>
+  <si>
+    <t>09.8 - Education n.e.c.</t>
+  </si>
+  <si>
     <t>111</t>
   </si>
   <si>
-    <t>110</t>
+    <t>09 - Education</t>
   </si>
   <si>
     <t>09.8.0 - Education n.e.c. (CS)</t>
   </si>
   <si>
-    <t>09.8 - Education n.e.c.</t>
-  </si>
-  <si>
-    <t>09 - Education</t>
-  </si>
-  <si>
     <t>11120</t>
   </si>
   <si>
+    <t>09.6 - Subsidiary services to education</t>
+  </si>
+  <si>
     <t>09.6.0 - Subsidiary services to education (IS)</t>
   </si>
   <si>
-    <t>09.6 - Subsidiary services to education</t>
-  </si>
-  <si>
     <t>11130</t>
   </si>
   <si>
     <t>11182</t>
   </si>
   <si>
+    <t>09.7 - R&amp;D Education</t>
+  </si>
+  <si>
     <t>09.7.0 - R&amp;D Education (CS)</t>
   </si>
   <si>
-    <t>09.7 - R&amp;D Education</t>
-  </si>
-  <si>
     <t>11220</t>
   </si>
   <si>
+    <t>09.1 - Pre‐primary and primary education</t>
+  </si>
+  <si>
     <t>112</t>
   </si>
   <si>
     <t>09.1.2 - Primary education (IS)</t>
   </si>
   <si>
-    <t>09.1 - Pre‐primary and primary education</t>
-  </si>
-  <si>
     <t>11230</t>
   </si>
   <si>
@@ -109,24 +109,24 @@
     <t>11250</t>
   </si>
   <si>
+    <t>07.4 - Public health services</t>
+  </si>
+  <si>
+    <t>07 - Health</t>
+  </si>
+  <si>
     <t>07.4.0 - Public health services (IS)</t>
   </si>
   <si>
-    <t>07.4 - Public health services</t>
-  </si>
-  <si>
-    <t>07 - Health</t>
-  </si>
-  <si>
     <t>11260</t>
   </si>
   <si>
+    <t>09.2 - Secondary education</t>
+  </si>
+  <si>
     <t>09.2.1 - Lower‐secondary education (IS)</t>
   </si>
   <si>
-    <t>09.2 - Secondary education</t>
-  </si>
-  <si>
     <t>11320</t>
   </si>
   <si>
@@ -139,69 +139,69 @@
     <t>11330</t>
   </si>
   <si>
+    <t>09.5 - Education not definable by level</t>
+  </si>
+  <si>
     <t>09.5.0 - Education not definable by level (IS)</t>
   </si>
   <si>
-    <t>09.5 - Education not definable by level</t>
-  </si>
-  <si>
     <t>11420</t>
   </si>
   <si>
+    <t>09.4 - Tertiary education</t>
+  </si>
+  <si>
     <t>114</t>
   </si>
   <si>
     <t>09.4.1 - First stage of tertiary education (IS)</t>
   </si>
   <si>
-    <t>09.4 - Tertiary education</t>
-  </si>
-  <si>
     <t>11430</t>
   </si>
   <si>
+    <t>09.3 - Post‐secondary non‐tertiary education</t>
+  </si>
+  <si>
     <t>09.3.0 - Post‐secondary non‐tertiary education (IS)</t>
   </si>
   <si>
-    <t>09.3 - Post‐secondary non‐tertiary education</t>
-  </si>
-  <si>
     <t>12110</t>
   </si>
   <si>
+    <t>120</t>
+  </si>
+  <si>
+    <t>07.6 - Health n.e.c.</t>
+  </si>
+  <si>
     <t>121</t>
   </si>
   <si>
-    <t>120</t>
-  </si>
-  <si>
     <t>07.6.0 - Health n.e.c. (CS)</t>
   </si>
   <si>
-    <t>07.6 - Health n.e.c.</t>
-  </si>
-  <si>
     <t>12181</t>
   </si>
   <si>
     <t>12182</t>
   </si>
   <si>
+    <t>07.5 - R&amp;D Health</t>
+  </si>
+  <si>
     <t>07.5.0 - R&amp;D Health (CS)</t>
   </si>
   <si>
-    <t>07.5 - R&amp;D Health</t>
-  </si>
-  <si>
     <t>12191</t>
   </si>
   <si>
+    <t>07.2 - Outpatient services</t>
+  </si>
+  <si>
     <t>07.2.1 - General medical services (IS)</t>
   </si>
   <si>
-    <t>07.2 - Outpatient services</t>
-  </si>
-  <si>
     <t>12196</t>
   </si>
   <si>
@@ -214,12 +214,12 @@
     <t>12230</t>
   </si>
   <si>
+    <t>07.3 - Hospital services</t>
+  </si>
+  <si>
     <t>07.3.1 - General hospital services (IS)</t>
   </si>
   <si>
-    <t>07.3 - Hospital services</t>
-  </si>
-  <si>
     <t>12240</t>
   </si>
   <si>
@@ -289,27 +289,27 @@
     <t>140</t>
   </si>
   <si>
+    <t>06.3 - Water supply</t>
+  </si>
+  <si>
+    <t>06 - Housing and community amenities</t>
+  </si>
+  <si>
     <t>06.3.0 - Water supply (CS)</t>
   </si>
   <si>
-    <t>06.3 - Water supply</t>
-  </si>
-  <si>
-    <t>06 - Housing and community amenities</t>
-  </si>
-  <si>
     <t>14015</t>
   </si>
   <si>
+    <t>05.6 - Environmental protection n.e.c.</t>
+  </si>
+  <si>
+    <t>05 - Environmental protection</t>
+  </si>
+  <si>
     <t>05.6.0 - Environmental protection n.e.c. (CS)</t>
   </si>
   <si>
-    <t>05.6 - Environmental protection n.e.c.</t>
-  </si>
-  <si>
-    <t>05 - Environmental protection</t>
-  </si>
-  <si>
     <t>14020</t>
   </si>
   <si>
@@ -319,12 +319,12 @@
     <t>14022</t>
   </si>
   <si>
+    <t>05.2 - Waste water management</t>
+  </si>
+  <si>
     <t>05.2.0 - Waste water management (CS)</t>
   </si>
   <si>
-    <t>05.2 - Waste water management</t>
-  </si>
-  <si>
     <t>14030</t>
   </si>
   <si>
@@ -340,63 +340,63 @@
     <t>14050</t>
   </si>
   <si>
+    <t>05.1 - Waste management</t>
+  </si>
+  <si>
     <t>05.1.0 - Waste management (CS)</t>
   </si>
   <si>
-    <t>05.1 - Waste management</t>
-  </si>
-  <si>
     <t>14081</t>
   </si>
   <si>
     <t>15110</t>
   </si>
   <si>
+    <t>150</t>
+  </si>
+  <si>
+    <t>01.3 - General services</t>
+  </si>
+  <si>
     <t>151</t>
   </si>
   <si>
-    <t>150</t>
+    <t>01 - General public services</t>
   </si>
   <si>
     <t>01.3.1 - General personnel services (CS)</t>
   </si>
   <si>
-    <t>01.3 - General services</t>
-  </si>
-  <si>
-    <t>01 - General public services</t>
-  </si>
-  <si>
     <t>15111</t>
   </si>
   <si>
+    <t>01.1 - Executive and legislative organs, financial and fiscal affairs, external affairs</t>
+  </si>
+  <si>
     <t>01.1.2 - Financial and fiscal affairs (CS)</t>
   </si>
   <si>
-    <t>01.1 - Executive and legislative organs, financial and fiscal affairs, external affairs</t>
-  </si>
-  <si>
     <t>15112</t>
   </si>
   <si>
+    <t>01.8 - Transfers of a general character between different levels of government</t>
+  </si>
+  <si>
     <t>01.8.0 - Transfers of a general character between different levels of government (CS)</t>
   </si>
   <si>
-    <t>01.8 - Transfers of a general character between different levels of government</t>
-  </si>
-  <si>
     <t>15113</t>
   </si>
   <si>
+    <t>03.6 - Public order and safety n.e.c.</t>
+  </si>
+  <si>
+    <t>03 - Public order and safety</t>
+  </si>
+  <si>
     <t>03.6.0 - Public order and safety n.e.c. (CS)</t>
   </si>
   <si>
-    <t>03.6 - Public order and safety n.e.c.</t>
-  </si>
-  <si>
-    <t>03 - Public order and safety</t>
-  </si>
-  <si>
     <t>15114</t>
   </si>
   <si>
@@ -424,12 +424,12 @@
     <t>15123</t>
   </si>
   <si>
+    <t>01.2 - Foreign economic aid</t>
+  </si>
+  <si>
     <t>01.2.2 - Economic aid routed through international organizations (CS)</t>
   </si>
   <si>
-    <t>01.2 - Foreign economic aid</t>
-  </si>
-  <si>
     <t>15124</t>
   </si>
   <si>
@@ -460,30 +460,30 @@
     <t>15131</t>
   </si>
   <si>
+    <t>03.3 - Law courts</t>
+  </si>
+  <si>
     <t>03.3.0 - Law courts (CS)</t>
   </si>
   <si>
-    <t>03.3 - Law courts</t>
-  </si>
-  <si>
     <t>15132</t>
   </si>
   <si>
+    <t>03.1 - Police services</t>
+  </si>
+  <si>
     <t>03.1.0 - Police services (CS)</t>
   </si>
   <si>
-    <t>03.1 - Police services</t>
-  </si>
-  <si>
     <t>15133</t>
   </si>
   <si>
+    <t>03.2 - Fire‐protection services</t>
+  </si>
+  <si>
     <t>03.2.0 - Fire‐protection services (CS)</t>
   </si>
   <si>
-    <t>03.2 - Fire‐protection services</t>
-  </si>
-  <si>
     <t>15134</t>
   </si>
   <si>
@@ -496,24 +496,24 @@
     <t>15137</t>
   </si>
   <si>
+    <t>03.4 - Prisons</t>
+  </si>
+  <si>
     <t>03.4.0 - Prisons (CS)</t>
   </si>
   <si>
-    <t>03.4 - Prisons</t>
-  </si>
-  <si>
     <t>15142</t>
   </si>
   <si>
+    <t>04.1 - General economic, commercial and labour affairs</t>
+  </si>
+  <si>
+    <t>04 - Economic affairs</t>
+  </si>
+  <si>
     <t>04.1.1 - General economic and commercial affairs (CS)</t>
   </si>
   <si>
-    <t>04.1 - General economic, commercial and labour affairs</t>
-  </si>
-  <si>
-    <t>04 - Economic affairs</t>
-  </si>
-  <si>
     <t>15143</t>
   </si>
   <si>
@@ -526,12 +526,12 @@
     <t>15151</t>
   </si>
   <si>
+    <t>01.6 - General public services n.e.c.</t>
+  </si>
+  <si>
     <t>01.6.0 - General public services n.e.c. (CS)</t>
   </si>
   <si>
-    <t>01.6 - General public services n.e.c.</t>
-  </si>
-  <si>
     <t>15152</t>
   </si>
   <si>
@@ -541,12 +541,12 @@
     <t>15153</t>
   </si>
   <si>
+    <t>04.6 - Communication</t>
+  </si>
+  <si>
     <t>04.6.0 - Communication (CS)</t>
   </si>
   <si>
-    <t>04.6 - Communication</t>
-  </si>
-  <si>
     <t>15154</t>
   </si>
   <si>
@@ -562,15 +562,15 @@
     <t>15170</t>
   </si>
   <si>
+    <t>10.7 - Social exclusion n.e.c.</t>
+  </si>
+  <si>
+    <t>10 - Social protection</t>
+  </si>
+  <si>
     <t>10.7.0 - Social exclusion n.e.c. (IS)</t>
   </si>
   <si>
-    <t>10.7 - Social exclusion n.e.c.</t>
-  </si>
-  <si>
-    <t>10 - Social protection</t>
-  </si>
-  <si>
     <t>15180</t>
   </si>
   <si>
@@ -583,12 +583,12 @@
     <t>15196</t>
   </si>
   <si>
+    <t>01.5 - R&amp;D General public services</t>
+  </si>
+  <si>
     <t>01.5.0 - R&amp;D General public services (CS)</t>
   </si>
   <si>
-    <t>01.5 - R&amp;D General public services</t>
-  </si>
-  <si>
     <t>15210</t>
   </si>
   <si>
@@ -601,15 +601,15 @@
     <t>15230</t>
   </si>
   <si>
+    <t>02.3 - Foreign military aid</t>
+  </si>
+  <si>
+    <t>02 - Defence</t>
+  </si>
+  <si>
     <t>02.3.0 - Foreign military aid (CS)</t>
   </si>
   <si>
-    <t>02.3 - Foreign military aid</t>
-  </si>
-  <si>
-    <t>02 - Defence</t>
-  </si>
-  <si>
     <t>15240</t>
   </si>
   <si>
@@ -625,12 +625,12 @@
     <t>160</t>
   </si>
   <si>
+    <t>10.9 - Social protection n.e.c.</t>
+  </si>
+  <si>
     <t>10.9.0 - Social protection n.e.c. (CS)</t>
   </si>
   <si>
-    <t>10.9 - Social protection n.e.c.</t>
-  </si>
-  <si>
     <t>16011</t>
   </si>
   <si>
@@ -640,12 +640,12 @@
     <t>16013</t>
   </si>
   <si>
+    <t>10.2 - Old age</t>
+  </si>
+  <si>
     <t>10.2.0 - Old age (IS)</t>
   </si>
   <si>
-    <t>10.2 - Old age</t>
-  </si>
-  <si>
     <t>16014</t>
   </si>
   <si>
@@ -655,45 +655,45 @@
     <t>16020</t>
   </si>
   <si>
+    <t>10.5 - Unemployment</t>
+  </si>
+  <si>
     <t>10.5.0 - Unemployment (IS)</t>
   </si>
   <si>
-    <t>10.5 - Unemployment</t>
-  </si>
-  <si>
     <t>16030</t>
   </si>
   <si>
+    <t>06.6 - Housing and community amenities n.e.c.</t>
+  </si>
+  <si>
     <t>06.6.0 - Housing and community amenities n.e.c. (CS)</t>
   </si>
   <si>
-    <t>06.6 - Housing and community amenities n.e.c.</t>
-  </si>
-  <si>
     <t>16040</t>
   </si>
   <si>
+    <t>06.1 - Housing development</t>
+  </si>
+  <si>
     <t>06.1.0 - Housing development (CS)</t>
   </si>
   <si>
-    <t>06.1 - Housing development</t>
-  </si>
-  <si>
     <t>16050</t>
   </si>
   <si>
     <t>16061</t>
   </si>
   <si>
+    <t>08.2 - Cultural services</t>
+  </si>
+  <si>
+    <t>08 - Recreation, culture and religion</t>
+  </si>
+  <si>
     <t>08.2.0 - Cultural services (IS)</t>
   </si>
   <si>
-    <t>08.2 - Cultural services</t>
-  </si>
-  <si>
-    <t>08 - Recreation, culture and religion</t>
-  </si>
-  <si>
     <t>16062</t>
   </si>
   <si>
@@ -706,12 +706,12 @@
     <t>16065</t>
   </si>
   <si>
+    <t>08.1 - Recreational and sporting services</t>
+  </si>
+  <si>
     <t>08.1.0 - Recreational and sporting services (IS)</t>
   </si>
   <si>
-    <t>08.1 - Recreational and sporting services</t>
-  </si>
-  <si>
     <t>16066</t>
   </si>
   <si>
@@ -742,12 +742,12 @@
     <t>21020</t>
   </si>
   <si>
+    <t>04.5 - Transport</t>
+  </si>
+  <si>
     <t>04.5.1 - Road transport (CS)</t>
   </si>
   <si>
-    <t>04.5 - Transport</t>
-  </si>
-  <si>
     <t>21021</t>
   </si>
   <si>
@@ -781,12 +781,12 @@
     <t>21061</t>
   </si>
   <si>
+    <t>04.7 - Other industries</t>
+  </si>
+  <si>
     <t>04.7.1 - Distributive trades, storage and warehousing (CS)</t>
   </si>
   <si>
-    <t>04.7 - Other industries</t>
-  </si>
-  <si>
     <t>21081</t>
   </si>
   <si>
@@ -811,42 +811,42 @@
     <t>22030</t>
   </si>
   <si>
+    <t>08.3 - Broadcasting and publishing services</t>
+  </si>
+  <si>
     <t>08.3.0 - Broadcasting and publishing services (CS)</t>
   </si>
   <si>
-    <t>08.3 - Broadcasting and publishing services</t>
-  </si>
-  <si>
     <t>22040</t>
   </si>
   <si>
     <t>23110</t>
   </si>
   <si>
+    <t>230</t>
+  </si>
+  <si>
+    <t>04.3 - Fuel and energy</t>
+  </si>
+  <si>
     <t>231</t>
   </si>
   <si>
-    <t>230</t>
-  </si>
-  <si>
     <t>04.3.5 - Electricity (CS)</t>
   </si>
   <si>
-    <t>04.3 - Fuel and energy</t>
-  </si>
-  <si>
     <t>23111</t>
   </si>
   <si>
     <t>23112</t>
   </si>
   <si>
+    <t>04.8 - R&amp;D Economic affairs</t>
+  </si>
+  <si>
     <t>04.8.3 - R&amp;D Fuel and energy (CS)</t>
   </si>
   <si>
-    <t>04.8 - R&amp;D Economic affairs</t>
-  </si>
-  <si>
     <t>23181</t>
   </si>
   <si>
@@ -991,18 +991,18 @@
     <t>31110</t>
   </si>
   <si>
+    <t>310</t>
+  </si>
+  <si>
+    <t>04.2 - Agriculture, forestry, fishing and hunting</t>
+  </si>
+  <si>
     <t>311</t>
   </si>
   <si>
-    <t>310</t>
-  </si>
-  <si>
     <t>04.2.1 - Agriculture (CS)</t>
   </si>
   <si>
-    <t>04.2 - Agriculture, forestry, fishing and hunting</t>
-  </si>
-  <si>
     <t>31120</t>
   </si>
   <si>
@@ -1105,18 +1105,18 @@
     <t>32110</t>
   </si>
   <si>
+    <t>320</t>
+  </si>
+  <si>
+    <t>04.4 - Mining, manufacturing and construction</t>
+  </si>
+  <si>
     <t>321</t>
   </si>
   <si>
-    <t>320</t>
-  </si>
-  <si>
     <t>04.4.2 - Manufacturing (CS)</t>
   </si>
   <si>
-    <t>04.4 - Mining, manufacturing and construction</t>
-  </si>
-  <si>
     <t>32120</t>
   </si>
   <si>
@@ -1219,12 +1219,12 @@
     <t>33110</t>
   </si>
   <si>
+    <t>330</t>
+  </si>
+  <si>
     <t>331</t>
   </si>
   <si>
-    <t>330</t>
-  </si>
-  <si>
     <t>33120</t>
   </si>
   <si>
@@ -1261,12 +1261,12 @@
     <t>41030</t>
   </si>
   <si>
+    <t>05.4 - Protection of biodiversity and landscape</t>
+  </si>
+  <si>
     <t>05.4.0 - Protection of biodiversity and landscape (CS)</t>
   </si>
   <si>
-    <t>05.4 - Protection of biodiversity and landscape</t>
-  </si>
-  <si>
     <t>41040</t>
   </si>
   <si>
@@ -1282,24 +1282,24 @@
     <t>430</t>
   </si>
   <si>
+    <t>04.9 - Economic affairs n.e.c.</t>
+  </si>
+  <si>
     <t>04.9.0 - Economic affairs n.e.c. (CS)</t>
   </si>
   <si>
-    <t>04.9 - Economic affairs n.e.c.</t>
-  </si>
-  <si>
     <t>43030</t>
   </si>
   <si>
     <t>43031</t>
   </si>
   <si>
+    <t>06.2 - Community development</t>
+  </si>
+  <si>
     <t>06.2.0 - Community development (CS)</t>
   </si>
   <si>
-    <t>06.2 - Community development</t>
-  </si>
-  <si>
     <t>43032</t>
   </si>
   <si>
@@ -1318,24 +1318,24 @@
     <t>43060</t>
   </si>
   <si>
+    <t>02.2 - Civil defence</t>
+  </si>
+  <si>
     <t>02.2.0 - Civil defence (CS)</t>
   </si>
   <si>
-    <t>02.2 - Civil defence</t>
-  </si>
-  <si>
     <t>43071</t>
   </si>
   <si>
     <t>43072</t>
   </si>
   <si>
+    <t>10.4 - Family and children</t>
+  </si>
+  <si>
     <t>10.4.0 - Family and children (IS)</t>
   </si>
   <si>
-    <t>10.4 - Family and children</t>
-  </si>
-  <si>
     <t>43073</t>
   </si>
   <si>
@@ -1345,12 +1345,12 @@
     <t>43082</t>
   </si>
   <si>
+    <t>01.4 - Basic research</t>
+  </si>
+  <si>
     <t>01.4.0 - Basic research (CS)</t>
   </si>
   <si>
-    <t>01.4 - Basic research</t>
-  </si>
-  <si>
     <t>51010</t>
   </si>
   <si>
@@ -1378,10 +1378,10 @@
     <t>600</t>
   </si>
   <si>
+    <t>01.7 - Public debt transactions</t>
+  </si>
+  <si>
     <t>01.7.0 - Public debt transactions (CS)</t>
-  </si>
-  <si>
-    <t>01.7 - Public debt transactions</t>
   </si>
   <si>
     <t>60020</t>
@@ -1866,16 +1866,16 @@
         <v>9</v>
       </c>
       <c r="D3" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="E3" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="F3" t="s">
+        <v>12</v>
+      </c>
+      <c r="G3" t="s">
         <v>16</v>
-      </c>
-      <c r="G3" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -1912,16 +1912,16 @@
         <v>9</v>
       </c>
       <c r="D5" t="s">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="E5" t="s">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="F5" t="s">
+        <v>12</v>
+      </c>
+      <c r="G5" t="s">
         <v>20</v>
-      </c>
-      <c r="G5" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -1932,19 +1932,19 @@
         <v>8</v>
       </c>
       <c r="C6" t="s">
+        <v>9</v>
+      </c>
+      <c r="D6" t="s">
         <v>22</v>
-      </c>
-      <c r="D6" t="s">
-        <v>10</v>
       </c>
       <c r="E6" t="s">
         <v>23</v>
       </c>
       <c r="F6" t="s">
+        <v>12</v>
+      </c>
+      <c r="G6" t="s">
         <v>24</v>
-      </c>
-      <c r="G6" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -1955,13 +1955,13 @@
         <v>8</v>
       </c>
       <c r="C7" t="s">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="D7" t="s">
         <v>10</v>
       </c>
       <c r="E7" t="s">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="F7" t="s">
         <v>12</v>
@@ -1978,19 +1978,19 @@
         <v>8</v>
       </c>
       <c r="C8" t="s">
+        <v>9</v>
+      </c>
+      <c r="D8" t="s">
         <v>22</v>
-      </c>
-      <c r="D8" t="s">
-        <v>10</v>
       </c>
       <c r="E8" t="s">
         <v>23</v>
       </c>
       <c r="F8" t="s">
+        <v>12</v>
+      </c>
+      <c r="G8" t="s">
         <v>24</v>
-      </c>
-      <c r="G8" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -2001,19 +2001,19 @@
         <v>8</v>
       </c>
       <c r="C9" t="s">
+        <v>9</v>
+      </c>
+      <c r="D9" t="s">
         <v>22</v>
-      </c>
-      <c r="D9" t="s">
-        <v>10</v>
       </c>
       <c r="E9" t="s">
         <v>23</v>
       </c>
       <c r="F9" t="s">
+        <v>12</v>
+      </c>
+      <c r="G9" t="s">
         <v>24</v>
-      </c>
-      <c r="G9" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -2024,19 +2024,19 @@
         <v>8</v>
       </c>
       <c r="C10" t="s">
+        <v>9</v>
+      </c>
+      <c r="D10" t="s">
         <v>22</v>
       </c>
-      <c r="D10" t="s">
-        <v>10</v>
-      </c>
       <c r="E10" t="s">
+        <v>23</v>
+      </c>
+      <c r="F10" t="s">
+        <v>12</v>
+      </c>
+      <c r="G10" t="s">
         <v>29</v>
-      </c>
-      <c r="F10" t="s">
-        <v>24</v>
-      </c>
-      <c r="G10" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -2047,13 +2047,13 @@
         <v>8</v>
       </c>
       <c r="C11" t="s">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="D11" t="s">
-        <v>10</v>
+        <v>31</v>
       </c>
       <c r="E11" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="F11" t="s">
         <v>32</v>
@@ -2070,19 +2070,19 @@
         <v>8</v>
       </c>
       <c r="C12" t="s">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="D12" t="s">
-        <v>10</v>
+        <v>35</v>
       </c>
       <c r="E12" t="s">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="F12" t="s">
+        <v>12</v>
+      </c>
+      <c r="G12" t="s">
         <v>36</v>
-      </c>
-      <c r="G12" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -2093,19 +2093,19 @@
         <v>8</v>
       </c>
       <c r="C13" t="s">
+        <v>9</v>
+      </c>
+      <c r="D13" t="s">
+        <v>35</v>
+      </c>
+      <c r="E13" t="s">
         <v>38</v>
       </c>
-      <c r="D13" t="s">
-        <v>10</v>
-      </c>
-      <c r="E13" t="s">
+      <c r="F13" t="s">
+        <v>12</v>
+      </c>
+      <c r="G13" t="s">
         <v>39</v>
-      </c>
-      <c r="F13" t="s">
-        <v>36</v>
-      </c>
-      <c r="G13" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -2116,19 +2116,19 @@
         <v>8</v>
       </c>
       <c r="C14" t="s">
+        <v>9</v>
+      </c>
+      <c r="D14" t="s">
+        <v>41</v>
+      </c>
+      <c r="E14" t="s">
         <v>38</v>
       </c>
-      <c r="D14" t="s">
-        <v>10</v>
-      </c>
-      <c r="E14" t="s">
-        <v>41</v>
-      </c>
       <c r="F14" t="s">
+        <v>12</v>
+      </c>
+      <c r="G14" t="s">
         <v>42</v>
-      </c>
-      <c r="G14" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -2139,19 +2139,19 @@
         <v>8</v>
       </c>
       <c r="C15" t="s">
+        <v>9</v>
+      </c>
+      <c r="D15" t="s">
         <v>44</v>
-      </c>
-      <c r="D15" t="s">
-        <v>10</v>
       </c>
       <c r="E15" t="s">
         <v>45</v>
       </c>
       <c r="F15" t="s">
+        <v>12</v>
+      </c>
+      <c r="G15" t="s">
         <v>46</v>
-      </c>
-      <c r="G15" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -2162,19 +2162,19 @@
         <v>8</v>
       </c>
       <c r="C16" t="s">
-        <v>44</v>
+        <v>9</v>
       </c>
       <c r="D16" t="s">
-        <v>10</v>
+        <v>48</v>
       </c>
       <c r="E16" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="F16" t="s">
+        <v>12</v>
+      </c>
+      <c r="G16" t="s">
         <v>49</v>
-      </c>
-      <c r="G16" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -2194,10 +2194,10 @@
         <v>53</v>
       </c>
       <c r="F17" t="s">
+        <v>32</v>
+      </c>
+      <c r="G17" t="s">
         <v>54</v>
-      </c>
-      <c r="G17" t="s">
-        <v>33</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -2217,10 +2217,10 @@
         <v>53</v>
       </c>
       <c r="F18" t="s">
+        <v>32</v>
+      </c>
+      <c r="G18" t="s">
         <v>54</v>
-      </c>
-      <c r="G18" t="s">
-        <v>33</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -2234,16 +2234,16 @@
         <v>51</v>
       </c>
       <c r="D19" t="s">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="E19" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="F19" t="s">
+        <v>32</v>
+      </c>
+      <c r="G19" t="s">
         <v>58</v>
-      </c>
-      <c r="G19" t="s">
-        <v>33</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -2257,16 +2257,16 @@
         <v>51</v>
       </c>
       <c r="D20" t="s">
-        <v>52</v>
+        <v>60</v>
       </c>
       <c r="E20" t="s">
-        <v>60</v>
+        <v>53</v>
       </c>
       <c r="F20" t="s">
+        <v>32</v>
+      </c>
+      <c r="G20" t="s">
         <v>61</v>
-      </c>
-      <c r="G20" t="s">
-        <v>33</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -2286,10 +2286,10 @@
         <v>53</v>
       </c>
       <c r="F21" t="s">
+        <v>32</v>
+      </c>
+      <c r="G21" t="s">
         <v>54</v>
-      </c>
-      <c r="G21" t="s">
-        <v>33</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -2300,13 +2300,13 @@
         <v>8</v>
       </c>
       <c r="C22" t="s">
+        <v>51</v>
+      </c>
+      <c r="D22" t="s">
+        <v>31</v>
+      </c>
+      <c r="E22" t="s">
         <v>64</v>
-      </c>
-      <c r="D22" t="s">
-        <v>52</v>
-      </c>
-      <c r="E22" t="s">
-        <v>31</v>
       </c>
       <c r="F22" t="s">
         <v>32</v>
@@ -2323,19 +2323,19 @@
         <v>8</v>
       </c>
       <c r="C23" t="s">
+        <v>51</v>
+      </c>
+      <c r="D23" t="s">
+        <v>66</v>
+      </c>
+      <c r="E23" t="s">
         <v>64</v>
       </c>
-      <c r="D23" t="s">
-        <v>52</v>
-      </c>
-      <c r="E23" t="s">
-        <v>66</v>
-      </c>
       <c r="F23" t="s">
+        <v>32</v>
+      </c>
+      <c r="G23" t="s">
         <v>67</v>
-      </c>
-      <c r="G23" t="s">
-        <v>33</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -2346,13 +2346,13 @@
         <v>8</v>
       </c>
       <c r="C24" t="s">
+        <v>51</v>
+      </c>
+      <c r="D24" t="s">
+        <v>31</v>
+      </c>
+      <c r="E24" t="s">
         <v>64</v>
-      </c>
-      <c r="D24" t="s">
-        <v>52</v>
-      </c>
-      <c r="E24" t="s">
-        <v>31</v>
       </c>
       <c r="F24" t="s">
         <v>32</v>
@@ -2369,13 +2369,13 @@
         <v>8</v>
       </c>
       <c r="C25" t="s">
+        <v>51</v>
+      </c>
+      <c r="D25" t="s">
+        <v>31</v>
+      </c>
+      <c r="E25" t="s">
         <v>64</v>
-      </c>
-      <c r="D25" t="s">
-        <v>52</v>
-      </c>
-      <c r="E25" t="s">
-        <v>31</v>
       </c>
       <c r="F25" t="s">
         <v>32</v>
@@ -2392,13 +2392,13 @@
         <v>8</v>
       </c>
       <c r="C26" t="s">
+        <v>51</v>
+      </c>
+      <c r="D26" t="s">
+        <v>31</v>
+      </c>
+      <c r="E26" t="s">
         <v>64</v>
-      </c>
-      <c r="D26" t="s">
-        <v>52</v>
-      </c>
-      <c r="E26" t="s">
-        <v>31</v>
       </c>
       <c r="F26" t="s">
         <v>32</v>
@@ -2415,13 +2415,13 @@
         <v>8</v>
       </c>
       <c r="C27" t="s">
+        <v>51</v>
+      </c>
+      <c r="D27" t="s">
+        <v>31</v>
+      </c>
+      <c r="E27" t="s">
         <v>64</v>
-      </c>
-      <c r="D27" t="s">
-        <v>52</v>
-      </c>
-      <c r="E27" t="s">
-        <v>31</v>
       </c>
       <c r="F27" t="s">
         <v>32</v>
@@ -2438,13 +2438,13 @@
         <v>8</v>
       </c>
       <c r="C28" t="s">
+        <v>51</v>
+      </c>
+      <c r="D28" t="s">
+        <v>31</v>
+      </c>
+      <c r="E28" t="s">
         <v>64</v>
-      </c>
-      <c r="D28" t="s">
-        <v>52</v>
-      </c>
-      <c r="E28" t="s">
-        <v>31</v>
       </c>
       <c r="F28" t="s">
         <v>32</v>
@@ -2461,13 +2461,13 @@
         <v>8</v>
       </c>
       <c r="C29" t="s">
+        <v>51</v>
+      </c>
+      <c r="D29" t="s">
+        <v>31</v>
+      </c>
+      <c r="E29" t="s">
         <v>64</v>
-      </c>
-      <c r="D29" t="s">
-        <v>52</v>
-      </c>
-      <c r="E29" t="s">
-        <v>31</v>
       </c>
       <c r="F29" t="s">
         <v>32</v>
@@ -2484,19 +2484,19 @@
         <v>8</v>
       </c>
       <c r="C30" t="s">
-        <v>64</v>
+        <v>51</v>
       </c>
       <c r="D30" t="s">
         <v>52</v>
       </c>
       <c r="E30" t="s">
-        <v>53</v>
+        <v>64</v>
       </c>
       <c r="F30" t="s">
+        <v>32</v>
+      </c>
+      <c r="G30" t="s">
         <v>54</v>
-      </c>
-      <c r="G30" t="s">
-        <v>33</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -2507,13 +2507,13 @@
         <v>8</v>
       </c>
       <c r="C31" t="s">
+        <v>51</v>
+      </c>
+      <c r="D31" t="s">
+        <v>31</v>
+      </c>
+      <c r="E31" t="s">
         <v>76</v>
-      </c>
-      <c r="D31" t="s">
-        <v>52</v>
-      </c>
-      <c r="E31" t="s">
-        <v>31</v>
       </c>
       <c r="F31" t="s">
         <v>32</v>
@@ -2530,13 +2530,13 @@
         <v>8</v>
       </c>
       <c r="C32" t="s">
+        <v>51</v>
+      </c>
+      <c r="D32" t="s">
+        <v>31</v>
+      </c>
+      <c r="E32" t="s">
         <v>76</v>
-      </c>
-      <c r="D32" t="s">
-        <v>52</v>
-      </c>
-      <c r="E32" t="s">
-        <v>31</v>
       </c>
       <c r="F32" t="s">
         <v>32</v>
@@ -2553,13 +2553,13 @@
         <v>8</v>
       </c>
       <c r="C33" t="s">
+        <v>51</v>
+      </c>
+      <c r="D33" t="s">
+        <v>31</v>
+      </c>
+      <c r="E33" t="s">
         <v>76</v>
-      </c>
-      <c r="D33" t="s">
-        <v>52</v>
-      </c>
-      <c r="E33" t="s">
-        <v>31</v>
       </c>
       <c r="F33" t="s">
         <v>32</v>
@@ -2576,13 +2576,13 @@
         <v>8</v>
       </c>
       <c r="C34" t="s">
+        <v>51</v>
+      </c>
+      <c r="D34" t="s">
+        <v>31</v>
+      </c>
+      <c r="E34" t="s">
         <v>76</v>
-      </c>
-      <c r="D34" t="s">
-        <v>52</v>
-      </c>
-      <c r="E34" t="s">
-        <v>31</v>
       </c>
       <c r="F34" t="s">
         <v>32</v>
@@ -2599,13 +2599,13 @@
         <v>8</v>
       </c>
       <c r="C35" t="s">
+        <v>51</v>
+      </c>
+      <c r="D35" t="s">
+        <v>31</v>
+      </c>
+      <c r="E35" t="s">
         <v>76</v>
-      </c>
-      <c r="D35" t="s">
-        <v>52</v>
-      </c>
-      <c r="E35" t="s">
-        <v>31</v>
       </c>
       <c r="F35" t="s">
         <v>32</v>
@@ -2622,19 +2622,19 @@
         <v>8</v>
       </c>
       <c r="C36" t="s">
+        <v>51</v>
+      </c>
+      <c r="D36" t="s">
+        <v>57</v>
+      </c>
+      <c r="E36" t="s">
         <v>76</v>
       </c>
-      <c r="D36" t="s">
-        <v>52</v>
-      </c>
-      <c r="E36" t="s">
-        <v>57</v>
-      </c>
       <c r="F36" t="s">
+        <v>32</v>
+      </c>
+      <c r="G36" t="s">
         <v>58</v>
-      </c>
-      <c r="G36" t="s">
-        <v>33</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -2644,10 +2644,10 @@
       <c r="B37" t="s">
         <v>8</v>
       </c>
+      <c r="C37" t="s">
+        <v>83</v>
+      </c>
       <c r="D37" t="s">
-        <v>83</v>
-      </c>
-      <c r="E37" t="s">
         <v>31</v>
       </c>
       <c r="F37" t="s">
@@ -2664,10 +2664,10 @@
       <c r="B38" t="s">
         <v>8</v>
       </c>
+      <c r="C38" t="s">
+        <v>83</v>
+      </c>
       <c r="D38" t="s">
-        <v>83</v>
-      </c>
-      <c r="E38" t="s">
         <v>31</v>
       </c>
       <c r="F38" t="s">
@@ -2684,10 +2684,10 @@
       <c r="B39" t="s">
         <v>8</v>
       </c>
+      <c r="C39" t="s">
+        <v>83</v>
+      </c>
       <c r="D39" t="s">
-        <v>83</v>
-      </c>
-      <c r="E39" t="s">
         <v>31</v>
       </c>
       <c r="F39" t="s">
@@ -2704,10 +2704,10 @@
       <c r="B40" t="s">
         <v>8</v>
       </c>
+      <c r="C40" t="s">
+        <v>83</v>
+      </c>
       <c r="D40" t="s">
-        <v>83</v>
-      </c>
-      <c r="E40" t="s">
         <v>31</v>
       </c>
       <c r="F40" t="s">
@@ -2724,17 +2724,17 @@
       <c r="B41" t="s">
         <v>8</v>
       </c>
+      <c r="C41" t="s">
+        <v>83</v>
+      </c>
       <c r="D41" t="s">
-        <v>83</v>
-      </c>
-      <c r="E41" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="F41" t="s">
+        <v>32</v>
+      </c>
+      <c r="G41" t="s">
         <v>54</v>
-      </c>
-      <c r="G41" t="s">
-        <v>33</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -2744,17 +2744,17 @@
       <c r="B42" t="s">
         <v>8</v>
       </c>
+      <c r="C42" t="s">
+        <v>83</v>
+      </c>
       <c r="D42" t="s">
-        <v>83</v>
-      </c>
-      <c r="E42" t="s">
         <v>57</v>
       </c>
       <c r="F42" t="s">
+        <v>32</v>
+      </c>
+      <c r="G42" t="s">
         <v>58</v>
-      </c>
-      <c r="G42" t="s">
-        <v>33</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -2764,10 +2764,10 @@
       <c r="B43" t="s">
         <v>8</v>
       </c>
+      <c r="C43" t="s">
+        <v>90</v>
+      </c>
       <c r="D43" t="s">
-        <v>90</v>
-      </c>
-      <c r="E43" t="s">
         <v>91</v>
       </c>
       <c r="F43" t="s">
@@ -2784,10 +2784,10 @@
       <c r="B44" t="s">
         <v>8</v>
       </c>
+      <c r="C44" t="s">
+        <v>90</v>
+      </c>
       <c r="D44" t="s">
-        <v>90</v>
-      </c>
-      <c r="E44" t="s">
         <v>95</v>
       </c>
       <c r="F44" t="s">
@@ -2804,10 +2804,10 @@
       <c r="B45" t="s">
         <v>8</v>
       </c>
+      <c r="C45" t="s">
+        <v>90</v>
+      </c>
       <c r="D45" t="s">
-        <v>90</v>
-      </c>
-      <c r="E45" t="s">
         <v>91</v>
       </c>
       <c r="F45" t="s">
@@ -2824,10 +2824,10 @@
       <c r="B46" t="s">
         <v>8</v>
       </c>
+      <c r="C46" t="s">
+        <v>90</v>
+      </c>
       <c r="D46" t="s">
-        <v>90</v>
-      </c>
-      <c r="E46" t="s">
         <v>91</v>
       </c>
       <c r="F46" t="s">
@@ -2844,17 +2844,17 @@
       <c r="B47" t="s">
         <v>8</v>
       </c>
+      <c r="C47" t="s">
+        <v>90</v>
+      </c>
       <c r="D47" t="s">
-        <v>90</v>
-      </c>
-      <c r="E47" t="s">
         <v>101</v>
       </c>
       <c r="F47" t="s">
+        <v>96</v>
+      </c>
+      <c r="G47" t="s">
         <v>102</v>
-      </c>
-      <c r="G47" t="s">
-        <v>97</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -2864,10 +2864,10 @@
       <c r="B48" t="s">
         <v>8</v>
       </c>
+      <c r="C48" t="s">
+        <v>90</v>
+      </c>
       <c r="D48" t="s">
-        <v>90</v>
-      </c>
-      <c r="E48" t="s">
         <v>91</v>
       </c>
       <c r="F48" t="s">
@@ -2884,10 +2884,10 @@
       <c r="B49" t="s">
         <v>8</v>
       </c>
+      <c r="C49" t="s">
+        <v>90</v>
+      </c>
       <c r="D49" t="s">
-        <v>90</v>
-      </c>
-      <c r="E49" t="s">
         <v>91</v>
       </c>
       <c r="F49" t="s">
@@ -2904,17 +2904,17 @@
       <c r="B50" t="s">
         <v>8</v>
       </c>
+      <c r="C50" t="s">
+        <v>90</v>
+      </c>
       <c r="D50" t="s">
-        <v>90</v>
-      </c>
-      <c r="E50" t="s">
         <v>101</v>
       </c>
       <c r="F50" t="s">
+        <v>96</v>
+      </c>
+      <c r="G50" t="s">
         <v>102</v>
-      </c>
-      <c r="G50" t="s">
-        <v>97</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -2924,10 +2924,10 @@
       <c r="B51" t="s">
         <v>8</v>
       </c>
+      <c r="C51" t="s">
+        <v>90</v>
+      </c>
       <c r="D51" t="s">
-        <v>90</v>
-      </c>
-      <c r="E51" t="s">
         <v>91</v>
       </c>
       <c r="F51" t="s">
@@ -2944,17 +2944,17 @@
       <c r="B52" t="s">
         <v>8</v>
       </c>
+      <c r="C52" t="s">
+        <v>90</v>
+      </c>
       <c r="D52" t="s">
-        <v>90</v>
-      </c>
-      <c r="E52" t="s">
         <v>108</v>
       </c>
       <c r="F52" t="s">
+        <v>96</v>
+      </c>
+      <c r="G52" t="s">
         <v>109</v>
-      </c>
-      <c r="G52" t="s">
-        <v>97</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -2964,11 +2964,11 @@
       <c r="B53" t="s">
         <v>8</v>
       </c>
+      <c r="C53" t="s">
+        <v>90</v>
+      </c>
       <c r="D53" t="s">
-        <v>90</v>
-      </c>
-      <c r="E53" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F53" t="s">
         <v>12</v>
@@ -3011,16 +3011,16 @@
         <v>112</v>
       </c>
       <c r="D55" t="s">
-        <v>113</v>
+        <v>118</v>
       </c>
       <c r="E55" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="F55" t="s">
+        <v>115</v>
+      </c>
+      <c r="G55" t="s">
         <v>119</v>
-      </c>
-      <c r="G55" t="s">
-        <v>116</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -3034,16 +3034,16 @@
         <v>112</v>
       </c>
       <c r="D56" t="s">
-        <v>113</v>
+        <v>121</v>
       </c>
       <c r="E56" t="s">
-        <v>121</v>
+        <v>114</v>
       </c>
       <c r="F56" t="s">
+        <v>115</v>
+      </c>
+      <c r="G56" t="s">
         <v>122</v>
-      </c>
-      <c r="G56" t="s">
-        <v>116</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -3057,10 +3057,10 @@
         <v>112</v>
       </c>
       <c r="D57" t="s">
-        <v>113</v>
+        <v>124</v>
       </c>
       <c r="E57" t="s">
-        <v>124</v>
+        <v>114</v>
       </c>
       <c r="F57" t="s">
         <v>125</v>
@@ -3080,16 +3080,16 @@
         <v>112</v>
       </c>
       <c r="D58" t="s">
-        <v>113</v>
+        <v>118</v>
       </c>
       <c r="E58" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="F58" t="s">
+        <v>115</v>
+      </c>
+      <c r="G58" t="s">
         <v>119</v>
-      </c>
-      <c r="G58" t="s">
-        <v>116</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -3103,16 +3103,16 @@
         <v>112</v>
       </c>
       <c r="D59" t="s">
-        <v>113</v>
+        <v>118</v>
       </c>
       <c r="E59" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="F59" t="s">
+        <v>115</v>
+      </c>
+      <c r="G59" t="s">
         <v>119</v>
-      </c>
-      <c r="G59" t="s">
-        <v>116</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -3126,16 +3126,16 @@
         <v>112</v>
       </c>
       <c r="D60" t="s">
-        <v>113</v>
+        <v>118</v>
       </c>
       <c r="E60" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="F60" t="s">
+        <v>115</v>
+      </c>
+      <c r="G60" t="s">
         <v>119</v>
-      </c>
-      <c r="G60" t="s">
-        <v>116</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -3149,16 +3149,16 @@
         <v>112</v>
       </c>
       <c r="D61" t="s">
-        <v>113</v>
+        <v>118</v>
       </c>
       <c r="E61" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="F61" t="s">
+        <v>115</v>
+      </c>
+      <c r="G61" t="s">
         <v>119</v>
-      </c>
-      <c r="G61" t="s">
-        <v>116</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -3172,16 +3172,16 @@
         <v>112</v>
       </c>
       <c r="D62" t="s">
-        <v>113</v>
+        <v>118</v>
       </c>
       <c r="E62" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="F62" t="s">
+        <v>115</v>
+      </c>
+      <c r="G62" t="s">
         <v>119</v>
-      </c>
-      <c r="G62" t="s">
-        <v>116</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -3195,16 +3195,16 @@
         <v>112</v>
       </c>
       <c r="D63" t="s">
-        <v>113</v>
+        <v>118</v>
       </c>
       <c r="E63" t="s">
+        <v>114</v>
+      </c>
+      <c r="F63" t="s">
+        <v>115</v>
+      </c>
+      <c r="G63" t="s">
         <v>133</v>
-      </c>
-      <c r="F63" t="s">
-        <v>119</v>
-      </c>
-      <c r="G63" t="s">
-        <v>116</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -3218,16 +3218,16 @@
         <v>112</v>
       </c>
       <c r="D64" t="s">
-        <v>113</v>
+        <v>118</v>
       </c>
       <c r="E64" t="s">
+        <v>114</v>
+      </c>
+      <c r="F64" t="s">
+        <v>115</v>
+      </c>
+      <c r="G64" t="s">
         <v>133</v>
-      </c>
-      <c r="F64" t="s">
-        <v>119</v>
-      </c>
-      <c r="G64" t="s">
-        <v>116</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -3241,16 +3241,16 @@
         <v>112</v>
       </c>
       <c r="D65" t="s">
-        <v>113</v>
+        <v>136</v>
       </c>
       <c r="E65" t="s">
-        <v>136</v>
+        <v>114</v>
       </c>
       <c r="F65" t="s">
+        <v>115</v>
+      </c>
+      <c r="G65" t="s">
         <v>137</v>
-      </c>
-      <c r="G65" t="s">
-        <v>116</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -3287,16 +3287,16 @@
         <v>112</v>
       </c>
       <c r="D67" t="s">
-        <v>113</v>
+        <v>118</v>
       </c>
       <c r="E67" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="F67" t="s">
+        <v>115</v>
+      </c>
+      <c r="G67" t="s">
         <v>119</v>
-      </c>
-      <c r="G67" t="s">
-        <v>116</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -3313,13 +3313,13 @@
         <v>113</v>
       </c>
       <c r="E68" t="s">
-        <v>141</v>
+        <v>114</v>
       </c>
       <c r="F68" t="s">
         <v>115</v>
       </c>
       <c r="G68" t="s">
-        <v>116</v>
+        <v>141</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -3336,13 +3336,13 @@
         <v>113</v>
       </c>
       <c r="E69" t="s">
-        <v>143</v>
+        <v>114</v>
       </c>
       <c r="F69" t="s">
         <v>115</v>
       </c>
       <c r="G69" t="s">
-        <v>116</v>
+        <v>143</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -3356,16 +3356,16 @@
         <v>112</v>
       </c>
       <c r="D70" t="s">
-        <v>113</v>
+        <v>121</v>
       </c>
       <c r="E70" t="s">
-        <v>121</v>
+        <v>114</v>
       </c>
       <c r="F70" t="s">
+        <v>115</v>
+      </c>
+      <c r="G70" t="s">
         <v>122</v>
-      </c>
-      <c r="G70" t="s">
-        <v>116</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -3379,16 +3379,16 @@
         <v>112</v>
       </c>
       <c r="D71" t="s">
-        <v>113</v>
+        <v>121</v>
       </c>
       <c r="E71" t="s">
-        <v>121</v>
+        <v>114</v>
       </c>
       <c r="F71" t="s">
+        <v>115</v>
+      </c>
+      <c r="G71" t="s">
         <v>122</v>
-      </c>
-      <c r="G71" t="s">
-        <v>116</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -3425,16 +3425,16 @@
         <v>112</v>
       </c>
       <c r="D73" t="s">
-        <v>113</v>
+        <v>148</v>
       </c>
       <c r="E73" t="s">
-        <v>148</v>
+        <v>114</v>
       </c>
       <c r="F73" t="s">
+        <v>125</v>
+      </c>
+      <c r="G73" t="s">
         <v>149</v>
-      </c>
-      <c r="G73" t="s">
-        <v>126</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -3448,16 +3448,16 @@
         <v>112</v>
       </c>
       <c r="D74" t="s">
-        <v>113</v>
+        <v>151</v>
       </c>
       <c r="E74" t="s">
-        <v>151</v>
+        <v>114</v>
       </c>
       <c r="F74" t="s">
+        <v>125</v>
+      </c>
+      <c r="G74" t="s">
         <v>152</v>
-      </c>
-      <c r="G74" t="s">
-        <v>126</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -3471,16 +3471,16 @@
         <v>112</v>
       </c>
       <c r="D75" t="s">
-        <v>113</v>
+        <v>154</v>
       </c>
       <c r="E75" t="s">
-        <v>154</v>
+        <v>114</v>
       </c>
       <c r="F75" t="s">
+        <v>125</v>
+      </c>
+      <c r="G75" t="s">
         <v>155</v>
-      </c>
-      <c r="G75" t="s">
-        <v>126</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -3494,16 +3494,16 @@
         <v>112</v>
       </c>
       <c r="D76" t="s">
-        <v>113</v>
+        <v>148</v>
       </c>
       <c r="E76" t="s">
-        <v>148</v>
+        <v>114</v>
       </c>
       <c r="F76" t="s">
+        <v>125</v>
+      </c>
+      <c r="G76" t="s">
         <v>149</v>
-      </c>
-      <c r="G76" t="s">
-        <v>126</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -3517,16 +3517,16 @@
         <v>112</v>
       </c>
       <c r="D77" t="s">
-        <v>113</v>
+        <v>148</v>
       </c>
       <c r="E77" t="s">
-        <v>148</v>
+        <v>114</v>
       </c>
       <c r="F77" t="s">
+        <v>125</v>
+      </c>
+      <c r="G77" t="s">
         <v>149</v>
-      </c>
-      <c r="G77" t="s">
-        <v>126</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -3540,16 +3540,16 @@
         <v>112</v>
       </c>
       <c r="D78" t="s">
-        <v>113</v>
+        <v>151</v>
       </c>
       <c r="E78" t="s">
-        <v>151</v>
+        <v>114</v>
       </c>
       <c r="F78" t="s">
+        <v>125</v>
+      </c>
+      <c r="G78" t="s">
         <v>152</v>
-      </c>
-      <c r="G78" t="s">
-        <v>126</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -3563,16 +3563,16 @@
         <v>112</v>
       </c>
       <c r="D79" t="s">
-        <v>113</v>
+        <v>160</v>
       </c>
       <c r="E79" t="s">
-        <v>160</v>
+        <v>114</v>
       </c>
       <c r="F79" t="s">
+        <v>125</v>
+      </c>
+      <c r="G79" t="s">
         <v>161</v>
-      </c>
-      <c r="G79" t="s">
-        <v>126</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -3586,10 +3586,10 @@
         <v>112</v>
       </c>
       <c r="D80" t="s">
-        <v>113</v>
+        <v>163</v>
       </c>
       <c r="E80" t="s">
-        <v>163</v>
+        <v>114</v>
       </c>
       <c r="F80" t="s">
         <v>164</v>
@@ -3609,10 +3609,10 @@
         <v>112</v>
       </c>
       <c r="D81" t="s">
-        <v>113</v>
+        <v>163</v>
       </c>
       <c r="E81" t="s">
-        <v>163</v>
+        <v>114</v>
       </c>
       <c r="F81" t="s">
         <v>164</v>
@@ -3632,10 +3632,10 @@
         <v>112</v>
       </c>
       <c r="D82" t="s">
-        <v>113</v>
+        <v>163</v>
       </c>
       <c r="E82" t="s">
-        <v>163</v>
+        <v>114</v>
       </c>
       <c r="F82" t="s">
         <v>164</v>
@@ -3658,13 +3658,13 @@
         <v>113</v>
       </c>
       <c r="E83" t="s">
-        <v>143</v>
+        <v>114</v>
       </c>
       <c r="F83" t="s">
         <v>115</v>
       </c>
       <c r="G83" t="s">
-        <v>116</v>
+        <v>143</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -3678,16 +3678,16 @@
         <v>112</v>
       </c>
       <c r="D84" t="s">
-        <v>113</v>
+        <v>170</v>
       </c>
       <c r="E84" t="s">
-        <v>170</v>
+        <v>114</v>
       </c>
       <c r="F84" t="s">
+        <v>115</v>
+      </c>
+      <c r="G84" t="s">
         <v>171</v>
-      </c>
-      <c r="G84" t="s">
-        <v>116</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -3701,16 +3701,16 @@
         <v>112</v>
       </c>
       <c r="D85" t="s">
-        <v>113</v>
+        <v>118</v>
       </c>
       <c r="E85" t="s">
+        <v>114</v>
+      </c>
+      <c r="F85" t="s">
+        <v>115</v>
+      </c>
+      <c r="G85" t="s">
         <v>173</v>
-      </c>
-      <c r="F85" t="s">
-        <v>119</v>
-      </c>
-      <c r="G85" t="s">
-        <v>116</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -3724,16 +3724,16 @@
         <v>112</v>
       </c>
       <c r="D86" t="s">
-        <v>113</v>
+        <v>175</v>
       </c>
       <c r="E86" t="s">
-        <v>175</v>
+        <v>114</v>
       </c>
       <c r="F86" t="s">
+        <v>164</v>
+      </c>
+      <c r="G86" t="s">
         <v>176</v>
-      </c>
-      <c r="G86" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -3747,16 +3747,16 @@
         <v>112</v>
       </c>
       <c r="D87" t="s">
-        <v>113</v>
+        <v>118</v>
       </c>
       <c r="E87" t="s">
+        <v>114</v>
+      </c>
+      <c r="F87" t="s">
+        <v>115</v>
+      </c>
+      <c r="G87" t="s">
         <v>173</v>
-      </c>
-      <c r="F87" t="s">
-        <v>119</v>
-      </c>
-      <c r="G87" t="s">
-        <v>116</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -3770,16 +3770,16 @@
         <v>112</v>
       </c>
       <c r="D88" t="s">
-        <v>113</v>
+        <v>118</v>
       </c>
       <c r="E88" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="F88" t="s">
+        <v>115</v>
+      </c>
+      <c r="G88" t="s">
         <v>119</v>
-      </c>
-      <c r="G88" t="s">
-        <v>116</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -3793,16 +3793,16 @@
         <v>112</v>
       </c>
       <c r="D89" t="s">
-        <v>113</v>
+        <v>118</v>
       </c>
       <c r="E89" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="F89" t="s">
+        <v>115</v>
+      </c>
+      <c r="G89" t="s">
         <v>119</v>
-      </c>
-      <c r="G89" t="s">
-        <v>116</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -3816,10 +3816,10 @@
         <v>112</v>
       </c>
       <c r="D90" t="s">
-        <v>113</v>
+        <v>124</v>
       </c>
       <c r="E90" t="s">
-        <v>124</v>
+        <v>114</v>
       </c>
       <c r="F90" t="s">
         <v>125</v>
@@ -3839,10 +3839,10 @@
         <v>112</v>
       </c>
       <c r="D91" t="s">
-        <v>113</v>
+        <v>182</v>
       </c>
       <c r="E91" t="s">
-        <v>182</v>
+        <v>114</v>
       </c>
       <c r="F91" t="s">
         <v>183</v>
@@ -3862,10 +3862,10 @@
         <v>112</v>
       </c>
       <c r="D92" t="s">
-        <v>113</v>
+        <v>124</v>
       </c>
       <c r="E92" t="s">
-        <v>124</v>
+        <v>114</v>
       </c>
       <c r="F92" t="s">
         <v>125</v>
@@ -3885,16 +3885,16 @@
         <v>112</v>
       </c>
       <c r="D93" t="s">
-        <v>113</v>
+        <v>121</v>
       </c>
       <c r="E93" t="s">
-        <v>121</v>
+        <v>114</v>
       </c>
       <c r="F93" t="s">
+        <v>115</v>
+      </c>
+      <c r="G93" t="s">
         <v>122</v>
-      </c>
-      <c r="G93" t="s">
-        <v>116</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -3908,10 +3908,10 @@
         <v>112</v>
       </c>
       <c r="D94" t="s">
-        <v>113</v>
+        <v>124</v>
       </c>
       <c r="E94" t="s">
-        <v>124</v>
+        <v>114</v>
       </c>
       <c r="F94" t="s">
         <v>125</v>
@@ -3931,16 +3931,16 @@
         <v>112</v>
       </c>
       <c r="D95" t="s">
-        <v>113</v>
+        <v>189</v>
       </c>
       <c r="E95" t="s">
-        <v>189</v>
+        <v>114</v>
       </c>
       <c r="F95" t="s">
+        <v>115</v>
+      </c>
+      <c r="G95" t="s">
         <v>190</v>
-      </c>
-      <c r="G95" t="s">
-        <v>116</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -3951,13 +3951,13 @@
         <v>8</v>
       </c>
       <c r="C96" t="s">
+        <v>112</v>
+      </c>
+      <c r="D96" t="s">
+        <v>124</v>
+      </c>
+      <c r="E96" t="s">
         <v>192</v>
-      </c>
-      <c r="D96" t="s">
-        <v>113</v>
-      </c>
-      <c r="E96" t="s">
-        <v>124</v>
       </c>
       <c r="F96" t="s">
         <v>125</v>
@@ -3974,13 +3974,13 @@
         <v>8</v>
       </c>
       <c r="C97" t="s">
+        <v>112</v>
+      </c>
+      <c r="D97" t="s">
+        <v>124</v>
+      </c>
+      <c r="E97" t="s">
         <v>192</v>
-      </c>
-      <c r="D97" t="s">
-        <v>113</v>
-      </c>
-      <c r="E97" t="s">
-        <v>124</v>
       </c>
       <c r="F97" t="s">
         <v>125</v>
@@ -3997,13 +3997,13 @@
         <v>8</v>
       </c>
       <c r="C98" t="s">
+        <v>112</v>
+      </c>
+      <c r="D98" t="s">
+        <v>195</v>
+      </c>
+      <c r="E98" t="s">
         <v>192</v>
-      </c>
-      <c r="D98" t="s">
-        <v>113</v>
-      </c>
-      <c r="E98" t="s">
-        <v>195</v>
       </c>
       <c r="F98" t="s">
         <v>196</v>
@@ -4020,13 +4020,13 @@
         <v>8</v>
       </c>
       <c r="C99" t="s">
+        <v>112</v>
+      </c>
+      <c r="D99" t="s">
+        <v>124</v>
+      </c>
+      <c r="E99" t="s">
         <v>192</v>
-      </c>
-      <c r="D99" t="s">
-        <v>113</v>
-      </c>
-      <c r="E99" t="s">
-        <v>124</v>
       </c>
       <c r="F99" t="s">
         <v>125</v>
@@ -4043,19 +4043,19 @@
         <v>8</v>
       </c>
       <c r="C100" t="s">
+        <v>112</v>
+      </c>
+      <c r="D100" t="s">
+        <v>154</v>
+      </c>
+      <c r="E100" t="s">
         <v>192</v>
       </c>
-      <c r="D100" t="s">
-        <v>113</v>
-      </c>
-      <c r="E100" t="s">
-        <v>154</v>
-      </c>
       <c r="F100" t="s">
+        <v>125</v>
+      </c>
+      <c r="G100" t="s">
         <v>155</v>
-      </c>
-      <c r="G100" t="s">
-        <v>126</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -4066,13 +4066,13 @@
         <v>8</v>
       </c>
       <c r="C101" t="s">
+        <v>112</v>
+      </c>
+      <c r="D101" t="s">
+        <v>124</v>
+      </c>
+      <c r="E101" t="s">
         <v>192</v>
-      </c>
-      <c r="D101" t="s">
-        <v>113</v>
-      </c>
-      <c r="E101" t="s">
-        <v>124</v>
       </c>
       <c r="F101" t="s">
         <v>125</v>
@@ -4088,17 +4088,17 @@
       <c r="B102" t="s">
         <v>8</v>
       </c>
+      <c r="C102" t="s">
+        <v>202</v>
+      </c>
       <c r="D102" t="s">
-        <v>202</v>
-      </c>
-      <c r="E102" t="s">
         <v>203</v>
       </c>
       <c r="F102" t="s">
+        <v>183</v>
+      </c>
+      <c r="G102" t="s">
         <v>204</v>
-      </c>
-      <c r="G102" t="s">
-        <v>184</v>
       </c>
     </row>
     <row r="103" spans="1:7">
@@ -4108,17 +4108,17 @@
       <c r="B103" t="s">
         <v>8</v>
       </c>
+      <c r="C103" t="s">
+        <v>202</v>
+      </c>
       <c r="D103" t="s">
-        <v>202</v>
-      </c>
-      <c r="E103" t="s">
         <v>203</v>
       </c>
       <c r="F103" t="s">
+        <v>183</v>
+      </c>
+      <c r="G103" t="s">
         <v>204</v>
-      </c>
-      <c r="G103" t="s">
-        <v>184</v>
       </c>
     </row>
     <row r="104" spans="1:7">
@@ -4128,17 +4128,17 @@
       <c r="B104" t="s">
         <v>8</v>
       </c>
+      <c r="C104" t="s">
+        <v>202</v>
+      </c>
       <c r="D104" t="s">
-        <v>202</v>
-      </c>
-      <c r="E104" t="s">
         <v>203</v>
       </c>
       <c r="F104" t="s">
+        <v>183</v>
+      </c>
+      <c r="G104" t="s">
         <v>204</v>
-      </c>
-      <c r="G104" t="s">
-        <v>184</v>
       </c>
     </row>
     <row r="105" spans="1:7">
@@ -4148,17 +4148,17 @@
       <c r="B105" t="s">
         <v>8</v>
       </c>
+      <c r="C105" t="s">
+        <v>202</v>
+      </c>
       <c r="D105" t="s">
-        <v>202</v>
-      </c>
-      <c r="E105" t="s">
         <v>208</v>
       </c>
       <c r="F105" t="s">
+        <v>183</v>
+      </c>
+      <c r="G105" t="s">
         <v>209</v>
-      </c>
-      <c r="G105" t="s">
-        <v>184</v>
       </c>
     </row>
     <row r="106" spans="1:7">
@@ -4168,17 +4168,17 @@
       <c r="B106" t="s">
         <v>8</v>
       </c>
+      <c r="C106" t="s">
+        <v>202</v>
+      </c>
       <c r="D106" t="s">
-        <v>202</v>
-      </c>
-      <c r="E106" t="s">
         <v>203</v>
       </c>
       <c r="F106" t="s">
+        <v>183</v>
+      </c>
+      <c r="G106" t="s">
         <v>204</v>
-      </c>
-      <c r="G106" t="s">
-        <v>184</v>
       </c>
     </row>
     <row r="107" spans="1:7">
@@ -4188,10 +4188,10 @@
       <c r="B107" t="s">
         <v>8</v>
       </c>
+      <c r="C107" t="s">
+        <v>202</v>
+      </c>
       <c r="D107" t="s">
-        <v>202</v>
-      </c>
-      <c r="E107" t="s">
         <v>182</v>
       </c>
       <c r="F107" t="s">
@@ -4208,17 +4208,17 @@
       <c r="B108" t="s">
         <v>8</v>
       </c>
+      <c r="C108" t="s">
+        <v>202</v>
+      </c>
       <c r="D108" t="s">
-        <v>202</v>
-      </c>
-      <c r="E108" t="s">
         <v>213</v>
       </c>
       <c r="F108" t="s">
+        <v>183</v>
+      </c>
+      <c r="G108" t="s">
         <v>214</v>
-      </c>
-      <c r="G108" t="s">
-        <v>184</v>
       </c>
     </row>
     <row r="109" spans="1:7">
@@ -4228,17 +4228,17 @@
       <c r="B109" t="s">
         <v>8</v>
       </c>
+      <c r="C109" t="s">
+        <v>202</v>
+      </c>
       <c r="D109" t="s">
-        <v>202</v>
-      </c>
-      <c r="E109" t="s">
         <v>216</v>
       </c>
       <c r="F109" t="s">
+        <v>92</v>
+      </c>
+      <c r="G109" t="s">
         <v>217</v>
-      </c>
-      <c r="G109" t="s">
-        <v>93</v>
       </c>
     </row>
     <row r="110" spans="1:7">
@@ -4248,17 +4248,17 @@
       <c r="B110" t="s">
         <v>8</v>
       </c>
+      <c r="C110" t="s">
+        <v>202</v>
+      </c>
       <c r="D110" t="s">
-        <v>202</v>
-      </c>
-      <c r="E110" t="s">
         <v>219</v>
       </c>
       <c r="F110" t="s">
+        <v>92</v>
+      </c>
+      <c r="G110" t="s">
         <v>220</v>
-      </c>
-      <c r="G110" t="s">
-        <v>93</v>
       </c>
     </row>
     <row r="111" spans="1:7">
@@ -4268,17 +4268,17 @@
       <c r="B111" t="s">
         <v>8</v>
       </c>
+      <c r="C111" t="s">
+        <v>202</v>
+      </c>
       <c r="D111" t="s">
-        <v>202</v>
-      </c>
-      <c r="E111" t="s">
         <v>203</v>
       </c>
       <c r="F111" t="s">
+        <v>183</v>
+      </c>
+      <c r="G111" t="s">
         <v>204</v>
-      </c>
-      <c r="G111" t="s">
-        <v>184</v>
       </c>
     </row>
     <row r="112" spans="1:7">
@@ -4288,10 +4288,10 @@
       <c r="B112" t="s">
         <v>8</v>
       </c>
+      <c r="C112" t="s">
+        <v>202</v>
+      </c>
       <c r="D112" t="s">
-        <v>202</v>
-      </c>
-      <c r="E112" t="s">
         <v>223</v>
       </c>
       <c r="F112" t="s">
@@ -4308,17 +4308,17 @@
       <c r="B113" t="s">
         <v>8</v>
       </c>
+      <c r="C113" t="s">
+        <v>202</v>
+      </c>
       <c r="D113" t="s">
-        <v>202</v>
-      </c>
-      <c r="E113" t="s">
-        <v>143</v>
+        <v>113</v>
       </c>
       <c r="F113" t="s">
         <v>115</v>
       </c>
       <c r="G113" t="s">
-        <v>116</v>
+        <v>143</v>
       </c>
     </row>
     <row r="114" spans="1:7">
@@ -4328,17 +4328,17 @@
       <c r="B114" t="s">
         <v>8</v>
       </c>
+      <c r="C114" t="s">
+        <v>202</v>
+      </c>
       <c r="D114" t="s">
-        <v>202</v>
-      </c>
-      <c r="E114" t="s">
         <v>151</v>
       </c>
       <c r="F114" t="s">
+        <v>125</v>
+      </c>
+      <c r="G114" t="s">
         <v>152</v>
-      </c>
-      <c r="G114" t="s">
-        <v>126</v>
       </c>
     </row>
     <row r="115" spans="1:7">
@@ -4348,10 +4348,10 @@
       <c r="B115" t="s">
         <v>8</v>
       </c>
+      <c r="C115" t="s">
+        <v>202</v>
+      </c>
       <c r="D115" t="s">
-        <v>202</v>
-      </c>
-      <c r="E115" t="s">
         <v>182</v>
       </c>
       <c r="F115" t="s">
@@ -4368,17 +4368,17 @@
       <c r="B116" t="s">
         <v>8</v>
       </c>
+      <c r="C116" t="s">
+        <v>202</v>
+      </c>
       <c r="D116" t="s">
-        <v>202</v>
-      </c>
-      <c r="E116" t="s">
         <v>230</v>
       </c>
       <c r="F116" t="s">
+        <v>224</v>
+      </c>
+      <c r="G116" t="s">
         <v>231</v>
-      </c>
-      <c r="G116" t="s">
-        <v>225</v>
       </c>
     </row>
     <row r="117" spans="1:7">
@@ -4388,10 +4388,10 @@
       <c r="B117" t="s">
         <v>8</v>
       </c>
+      <c r="C117" t="s">
+        <v>202</v>
+      </c>
       <c r="D117" t="s">
-        <v>202</v>
-      </c>
-      <c r="E117" t="s">
         <v>223</v>
       </c>
       <c r="F117" t="s">
@@ -4408,17 +4408,17 @@
       <c r="B118" t="s">
         <v>8</v>
       </c>
+      <c r="C118" t="s">
+        <v>202</v>
+      </c>
       <c r="D118" t="s">
-        <v>202</v>
-      </c>
-      <c r="E118" t="s">
+        <v>163</v>
+      </c>
+      <c r="F118" t="s">
+        <v>164</v>
+      </c>
+      <c r="G118" t="s">
         <v>234</v>
-      </c>
-      <c r="F118" t="s">
-        <v>164</v>
-      </c>
-      <c r="G118" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="119" spans="1:7">
@@ -4428,10 +4428,10 @@
       <c r="B119" t="s">
         <v>8</v>
       </c>
+      <c r="C119" t="s">
+        <v>202</v>
+      </c>
       <c r="D119" t="s">
-        <v>202</v>
-      </c>
-      <c r="E119" t="s">
         <v>182</v>
       </c>
       <c r="F119" t="s">
@@ -4448,17 +4448,17 @@
       <c r="B120" t="s">
         <v>8</v>
       </c>
+      <c r="C120" t="s">
+        <v>237</v>
+      </c>
       <c r="D120" t="s">
-        <v>237</v>
-      </c>
-      <c r="E120" t="s">
         <v>170</v>
       </c>
       <c r="F120" t="s">
+        <v>115</v>
+      </c>
+      <c r="G120" t="s">
         <v>171</v>
-      </c>
-      <c r="G120" t="s">
-        <v>116</v>
       </c>
     </row>
     <row r="121" spans="1:7">
@@ -4468,17 +4468,17 @@
       <c r="B121" t="s">
         <v>8</v>
       </c>
+      <c r="C121" t="s">
+        <v>237</v>
+      </c>
       <c r="D121" t="s">
-        <v>237</v>
-      </c>
-      <c r="E121" t="s">
-        <v>143</v>
+        <v>113</v>
       </c>
       <c r="F121" t="s">
         <v>115</v>
       </c>
       <c r="G121" t="s">
-        <v>116</v>
+        <v>143</v>
       </c>
     </row>
     <row r="122" spans="1:7">
@@ -4488,17 +4488,17 @@
       <c r="B122" t="s">
         <v>8</v>
       </c>
+      <c r="C122" t="s">
+        <v>237</v>
+      </c>
       <c r="D122" t="s">
-        <v>237</v>
-      </c>
-      <c r="E122" t="s">
         <v>170</v>
       </c>
       <c r="F122" t="s">
+        <v>115</v>
+      </c>
+      <c r="G122" t="s">
         <v>171</v>
-      </c>
-      <c r="G122" t="s">
-        <v>116</v>
       </c>
     </row>
     <row r="123" spans="1:7">
@@ -4508,17 +4508,17 @@
       <c r="B123" t="s">
         <v>8</v>
       </c>
+      <c r="C123" t="s">
+        <v>237</v>
+      </c>
       <c r="D123" t="s">
-        <v>237</v>
-      </c>
-      <c r="E123" t="s">
         <v>170</v>
       </c>
       <c r="F123" t="s">
+        <v>115</v>
+      </c>
+      <c r="G123" t="s">
         <v>171</v>
-      </c>
-      <c r="G123" t="s">
-        <v>116</v>
       </c>
     </row>
     <row r="124" spans="1:7">
@@ -4528,17 +4528,17 @@
       <c r="B124" t="s">
         <v>8</v>
       </c>
+      <c r="C124" t="s">
+        <v>237</v>
+      </c>
       <c r="D124" t="s">
-        <v>237</v>
-      </c>
-      <c r="E124" t="s">
         <v>242</v>
       </c>
       <c r="F124" t="s">
+        <v>164</v>
+      </c>
+      <c r="G124" t="s">
         <v>243</v>
-      </c>
-      <c r="G124" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="125" spans="1:7">
@@ -4548,17 +4548,17 @@
       <c r="B125" t="s">
         <v>8</v>
       </c>
+      <c r="C125" t="s">
+        <v>237</v>
+      </c>
       <c r="D125" t="s">
-        <v>237</v>
-      </c>
-      <c r="E125" t="s">
         <v>242</v>
       </c>
       <c r="F125" t="s">
+        <v>164</v>
+      </c>
+      <c r="G125" t="s">
         <v>243</v>
-      </c>
-      <c r="G125" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="126" spans="1:7">
@@ -4568,17 +4568,17 @@
       <c r="B126" t="s">
         <v>8</v>
       </c>
+      <c r="C126" t="s">
+        <v>237</v>
+      </c>
       <c r="D126" t="s">
-        <v>237</v>
-      </c>
-      <c r="E126" t="s">
         <v>242</v>
       </c>
       <c r="F126" t="s">
+        <v>164</v>
+      </c>
+      <c r="G126" t="s">
         <v>243</v>
-      </c>
-      <c r="G126" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="127" spans="1:7">
@@ -4588,17 +4588,17 @@
       <c r="B127" t="s">
         <v>8</v>
       </c>
+      <c r="C127" t="s">
+        <v>237</v>
+      </c>
       <c r="D127" t="s">
-        <v>237</v>
-      </c>
-      <c r="E127" t="s">
         <v>242</v>
       </c>
       <c r="F127" t="s">
+        <v>164</v>
+      </c>
+      <c r="G127" t="s">
         <v>243</v>
-      </c>
-      <c r="G127" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="128" spans="1:7">
@@ -4608,17 +4608,17 @@
       <c r="B128" t="s">
         <v>8</v>
       </c>
+      <c r="C128" t="s">
+        <v>237</v>
+      </c>
       <c r="D128" t="s">
-        <v>237</v>
-      </c>
-      <c r="E128" t="s">
         <v>242</v>
       </c>
       <c r="F128" t="s">
+        <v>164</v>
+      </c>
+      <c r="G128" t="s">
         <v>243</v>
-      </c>
-      <c r="G128" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="129" spans="1:7">
@@ -4628,17 +4628,17 @@
       <c r="B129" t="s">
         <v>8</v>
       </c>
+      <c r="C129" t="s">
+        <v>237</v>
+      </c>
       <c r="D129" t="s">
-        <v>237</v>
-      </c>
-      <c r="E129" t="s">
+        <v>242</v>
+      </c>
+      <c r="F129" t="s">
+        <v>164</v>
+      </c>
+      <c r="G129" t="s">
         <v>249</v>
-      </c>
-      <c r="F129" t="s">
-        <v>243</v>
-      </c>
-      <c r="G129" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="130" spans="1:7">
@@ -4648,17 +4648,17 @@
       <c r="B130" t="s">
         <v>8</v>
       </c>
+      <c r="C130" t="s">
+        <v>237</v>
+      </c>
       <c r="D130" t="s">
-        <v>237</v>
-      </c>
-      <c r="E130" t="s">
+        <v>242</v>
+      </c>
+      <c r="F130" t="s">
+        <v>164</v>
+      </c>
+      <c r="G130" t="s">
         <v>251</v>
-      </c>
-      <c r="F130" t="s">
-        <v>243</v>
-      </c>
-      <c r="G130" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="131" spans="1:7">
@@ -4668,17 +4668,17 @@
       <c r="B131" t="s">
         <v>8</v>
       </c>
+      <c r="C131" t="s">
+        <v>237</v>
+      </c>
       <c r="D131" t="s">
-        <v>237</v>
-      </c>
-      <c r="E131" t="s">
+        <v>242</v>
+      </c>
+      <c r="F131" t="s">
+        <v>164</v>
+      </c>
+      <c r="G131" t="s">
         <v>253</v>
-      </c>
-      <c r="F131" t="s">
-        <v>243</v>
-      </c>
-      <c r="G131" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="132" spans="1:7">
@@ -4688,17 +4688,17 @@
       <c r="B132" t="s">
         <v>8</v>
       </c>
+      <c r="C132" t="s">
+        <v>237</v>
+      </c>
       <c r="D132" t="s">
-        <v>237</v>
-      </c>
-      <c r="E132" t="s">
         <v>255</v>
       </c>
       <c r="F132" t="s">
+        <v>164</v>
+      </c>
+      <c r="G132" t="s">
         <v>256</v>
-      </c>
-      <c r="G132" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="133" spans="1:7">
@@ -4708,17 +4708,17 @@
       <c r="B133" t="s">
         <v>8</v>
       </c>
+      <c r="C133" t="s">
+        <v>237</v>
+      </c>
       <c r="D133" t="s">
-        <v>237</v>
-      </c>
-      <c r="E133" t="s">
         <v>189</v>
       </c>
       <c r="F133" t="s">
+        <v>115</v>
+      </c>
+      <c r="G133" t="s">
         <v>190</v>
-      </c>
-      <c r="G133" t="s">
-        <v>116</v>
       </c>
     </row>
     <row r="134" spans="1:7">
@@ -4728,17 +4728,17 @@
       <c r="B134" t="s">
         <v>8</v>
       </c>
+      <c r="C134" t="s">
+        <v>259</v>
+      </c>
       <c r="D134" t="s">
-        <v>259</v>
-      </c>
-      <c r="E134" t="s">
         <v>175</v>
       </c>
       <c r="F134" t="s">
+        <v>164</v>
+      </c>
+      <c r="G134" t="s">
         <v>176</v>
-      </c>
-      <c r="G134" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="135" spans="1:7">
@@ -4748,17 +4748,17 @@
       <c r="B135" t="s">
         <v>8</v>
       </c>
+      <c r="C135" t="s">
+        <v>259</v>
+      </c>
       <c r="D135" t="s">
-        <v>259</v>
-      </c>
-      <c r="E135" t="s">
         <v>175</v>
       </c>
       <c r="F135" t="s">
+        <v>164</v>
+      </c>
+      <c r="G135" t="s">
         <v>176</v>
-      </c>
-      <c r="G135" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="136" spans="1:7">
@@ -4768,17 +4768,17 @@
       <c r="B136" t="s">
         <v>8</v>
       </c>
+      <c r="C136" t="s">
+        <v>259</v>
+      </c>
       <c r="D136" t="s">
-        <v>259</v>
-      </c>
-      <c r="E136" t="s">
         <v>175</v>
       </c>
       <c r="F136" t="s">
+        <v>164</v>
+      </c>
+      <c r="G136" t="s">
         <v>176</v>
-      </c>
-      <c r="G136" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="137" spans="1:7">
@@ -4788,17 +4788,17 @@
       <c r="B137" t="s">
         <v>8</v>
       </c>
+      <c r="C137" t="s">
+        <v>259</v>
+      </c>
       <c r="D137" t="s">
-        <v>259</v>
-      </c>
-      <c r="E137" t="s">
         <v>175</v>
       </c>
       <c r="F137" t="s">
+        <v>164</v>
+      </c>
+      <c r="G137" t="s">
         <v>176</v>
-      </c>
-      <c r="G137" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="138" spans="1:7">
@@ -4808,17 +4808,17 @@
       <c r="B138" t="s">
         <v>8</v>
       </c>
+      <c r="C138" t="s">
+        <v>259</v>
+      </c>
       <c r="D138" t="s">
-        <v>259</v>
-      </c>
-      <c r="E138" t="s">
         <v>175</v>
       </c>
       <c r="F138" t="s">
+        <v>164</v>
+      </c>
+      <c r="G138" t="s">
         <v>176</v>
-      </c>
-      <c r="G138" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="139" spans="1:7">
@@ -4828,17 +4828,17 @@
       <c r="B139" t="s">
         <v>8</v>
       </c>
+      <c r="C139" t="s">
+        <v>259</v>
+      </c>
       <c r="D139" t="s">
-        <v>259</v>
-      </c>
-      <c r="E139" t="s">
         <v>265</v>
       </c>
       <c r="F139" t="s">
+        <v>224</v>
+      </c>
+      <c r="G139" t="s">
         <v>266</v>
-      </c>
-      <c r="G139" t="s">
-        <v>225</v>
       </c>
     </row>
     <row r="140" spans="1:7">
@@ -4848,17 +4848,17 @@
       <c r="B140" t="s">
         <v>8</v>
       </c>
+      <c r="C140" t="s">
+        <v>259</v>
+      </c>
       <c r="D140" t="s">
-        <v>259</v>
-      </c>
-      <c r="E140" t="s">
         <v>175</v>
       </c>
       <c r="F140" t="s">
+        <v>164</v>
+      </c>
+      <c r="G140" t="s">
         <v>176</v>
-      </c>
-      <c r="G140" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="141" spans="1:7">
@@ -4878,10 +4878,10 @@
         <v>271</v>
       </c>
       <c r="F141" t="s">
+        <v>164</v>
+      </c>
+      <c r="G141" t="s">
         <v>272</v>
-      </c>
-      <c r="G141" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="142" spans="1:7">
@@ -4901,10 +4901,10 @@
         <v>271</v>
       </c>
       <c r="F142" t="s">
+        <v>164</v>
+      </c>
+      <c r="G142" t="s">
         <v>272</v>
-      </c>
-      <c r="G142" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="143" spans="1:7">
@@ -4918,16 +4918,16 @@
         <v>269</v>
       </c>
       <c r="D143" t="s">
-        <v>270</v>
+        <v>275</v>
       </c>
       <c r="E143" t="s">
-        <v>275</v>
+        <v>271</v>
       </c>
       <c r="F143" t="s">
+        <v>164</v>
+      </c>
+      <c r="G143" t="s">
         <v>276</v>
-      </c>
-      <c r="G143" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="144" spans="1:7">
@@ -4941,16 +4941,16 @@
         <v>269</v>
       </c>
       <c r="D144" t="s">
-        <v>270</v>
+        <v>275</v>
       </c>
       <c r="E144" t="s">
-        <v>275</v>
+        <v>271</v>
       </c>
       <c r="F144" t="s">
+        <v>164</v>
+      </c>
+      <c r="G144" t="s">
         <v>276</v>
-      </c>
-      <c r="G144" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="145" spans="1:7">
@@ -4964,16 +4964,16 @@
         <v>269</v>
       </c>
       <c r="D145" t="s">
-        <v>270</v>
+        <v>275</v>
       </c>
       <c r="E145" t="s">
-        <v>275</v>
+        <v>271</v>
       </c>
       <c r="F145" t="s">
+        <v>164</v>
+      </c>
+      <c r="G145" t="s">
         <v>276</v>
-      </c>
-      <c r="G145" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="146" spans="1:7">
@@ -4993,10 +4993,10 @@
         <v>271</v>
       </c>
       <c r="F146" t="s">
+        <v>164</v>
+      </c>
+      <c r="G146" t="s">
         <v>272</v>
-      </c>
-      <c r="G146" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="147" spans="1:7">
@@ -5007,19 +5007,19 @@
         <v>8</v>
       </c>
       <c r="C147" t="s">
-        <v>281</v>
+        <v>269</v>
       </c>
       <c r="D147" t="s">
         <v>270</v>
       </c>
       <c r="E147" t="s">
-        <v>271</v>
+        <v>281</v>
       </c>
       <c r="F147" t="s">
+        <v>164</v>
+      </c>
+      <c r="G147" t="s">
         <v>272</v>
-      </c>
-      <c r="G147" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="148" spans="1:7">
@@ -5030,19 +5030,19 @@
         <v>8</v>
       </c>
       <c r="C148" t="s">
-        <v>281</v>
+        <v>269</v>
       </c>
       <c r="D148" t="s">
         <v>270</v>
       </c>
       <c r="E148" t="s">
-        <v>271</v>
+        <v>281</v>
       </c>
       <c r="F148" t="s">
+        <v>164</v>
+      </c>
+      <c r="G148" t="s">
         <v>272</v>
-      </c>
-      <c r="G148" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="149" spans="1:7">
@@ -5053,19 +5053,19 @@
         <v>8</v>
       </c>
       <c r="C149" t="s">
-        <v>281</v>
+        <v>269</v>
       </c>
       <c r="D149" t="s">
         <v>270</v>
       </c>
       <c r="E149" t="s">
-        <v>271</v>
+        <v>281</v>
       </c>
       <c r="F149" t="s">
+        <v>164</v>
+      </c>
+      <c r="G149" t="s">
         <v>272</v>
-      </c>
-      <c r="G149" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="150" spans="1:7">
@@ -5076,19 +5076,19 @@
         <v>8</v>
       </c>
       <c r="C150" t="s">
-        <v>281</v>
+        <v>269</v>
       </c>
       <c r="D150" t="s">
         <v>270</v>
       </c>
       <c r="E150" t="s">
-        <v>271</v>
+        <v>281</v>
       </c>
       <c r="F150" t="s">
+        <v>164</v>
+      </c>
+      <c r="G150" t="s">
         <v>272</v>
-      </c>
-      <c r="G150" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="151" spans="1:7">
@@ -5099,19 +5099,19 @@
         <v>8</v>
       </c>
       <c r="C151" t="s">
-        <v>281</v>
+        <v>269</v>
       </c>
       <c r="D151" t="s">
         <v>270</v>
       </c>
       <c r="E151" t="s">
-        <v>271</v>
+        <v>281</v>
       </c>
       <c r="F151" t="s">
+        <v>164</v>
+      </c>
+      <c r="G151" t="s">
         <v>272</v>
-      </c>
-      <c r="G151" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="152" spans="1:7">
@@ -5122,19 +5122,19 @@
         <v>8</v>
       </c>
       <c r="C152" t="s">
-        <v>281</v>
+        <v>269</v>
       </c>
       <c r="D152" t="s">
         <v>270</v>
       </c>
       <c r="E152" t="s">
-        <v>271</v>
+        <v>281</v>
       </c>
       <c r="F152" t="s">
+        <v>164</v>
+      </c>
+      <c r="G152" t="s">
         <v>272</v>
-      </c>
-      <c r="G152" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="153" spans="1:7">
@@ -5145,19 +5145,19 @@
         <v>8</v>
       </c>
       <c r="C153" t="s">
-        <v>281</v>
+        <v>269</v>
       </c>
       <c r="D153" t="s">
         <v>270</v>
       </c>
       <c r="E153" t="s">
-        <v>271</v>
+        <v>281</v>
       </c>
       <c r="F153" t="s">
+        <v>164</v>
+      </c>
+      <c r="G153" t="s">
         <v>272</v>
-      </c>
-      <c r="G153" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="154" spans="1:7">
@@ -5168,19 +5168,19 @@
         <v>8</v>
       </c>
       <c r="C154" t="s">
-        <v>281</v>
+        <v>269</v>
       </c>
       <c r="D154" t="s">
         <v>270</v>
       </c>
       <c r="E154" t="s">
-        <v>271</v>
+        <v>281</v>
       </c>
       <c r="F154" t="s">
+        <v>164</v>
+      </c>
+      <c r="G154" t="s">
         <v>272</v>
-      </c>
-      <c r="G154" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="155" spans="1:7">
@@ -5191,19 +5191,19 @@
         <v>8</v>
       </c>
       <c r="C155" t="s">
-        <v>281</v>
+        <v>269</v>
       </c>
       <c r="D155" t="s">
         <v>270</v>
       </c>
       <c r="E155" t="s">
-        <v>271</v>
+        <v>281</v>
       </c>
       <c r="F155" t="s">
+        <v>164</v>
+      </c>
+      <c r="G155" t="s">
         <v>272</v>
-      </c>
-      <c r="G155" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="156" spans="1:7">
@@ -5214,19 +5214,19 @@
         <v>8</v>
       </c>
       <c r="C156" t="s">
-        <v>291</v>
+        <v>269</v>
       </c>
       <c r="D156" t="s">
         <v>270</v>
       </c>
       <c r="E156" t="s">
-        <v>271</v>
+        <v>291</v>
       </c>
       <c r="F156" t="s">
+        <v>164</v>
+      </c>
+      <c r="G156" t="s">
         <v>272</v>
-      </c>
-      <c r="G156" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="157" spans="1:7">
@@ -5237,19 +5237,19 @@
         <v>8</v>
       </c>
       <c r="C157" t="s">
-        <v>291</v>
+        <v>269</v>
       </c>
       <c r="D157" t="s">
         <v>270</v>
       </c>
       <c r="E157" t="s">
+        <v>291</v>
+      </c>
+      <c r="F157" t="s">
+        <v>164</v>
+      </c>
+      <c r="G157" t="s">
         <v>293</v>
-      </c>
-      <c r="F157" t="s">
-        <v>272</v>
-      </c>
-      <c r="G157" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="158" spans="1:7">
@@ -5260,19 +5260,19 @@
         <v>8</v>
       </c>
       <c r="C158" t="s">
-        <v>291</v>
+        <v>269</v>
       </c>
       <c r="D158" t="s">
         <v>270</v>
       </c>
       <c r="E158" t="s">
-        <v>271</v>
+        <v>291</v>
       </c>
       <c r="F158" t="s">
+        <v>164</v>
+      </c>
+      <c r="G158" t="s">
         <v>272</v>
-      </c>
-      <c r="G158" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="159" spans="1:7">
@@ -5283,19 +5283,19 @@
         <v>8</v>
       </c>
       <c r="C159" t="s">
-        <v>291</v>
+        <v>269</v>
       </c>
       <c r="D159" t="s">
         <v>270</v>
       </c>
       <c r="E159" t="s">
-        <v>271</v>
+        <v>291</v>
       </c>
       <c r="F159" t="s">
+        <v>164</v>
+      </c>
+      <c r="G159" t="s">
         <v>272</v>
-      </c>
-      <c r="G159" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="160" spans="1:7">
@@ -5306,19 +5306,19 @@
         <v>8</v>
       </c>
       <c r="C160" t="s">
-        <v>291</v>
+        <v>269</v>
       </c>
       <c r="D160" t="s">
         <v>270</v>
       </c>
       <c r="E160" t="s">
-        <v>271</v>
+        <v>291</v>
       </c>
       <c r="F160" t="s">
+        <v>164</v>
+      </c>
+      <c r="G160" t="s">
         <v>272</v>
-      </c>
-      <c r="G160" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="161" spans="1:7">
@@ -5329,19 +5329,19 @@
         <v>8</v>
       </c>
       <c r="C161" t="s">
-        <v>291</v>
+        <v>269</v>
       </c>
       <c r="D161" t="s">
         <v>270</v>
       </c>
       <c r="E161" t="s">
-        <v>271</v>
+        <v>291</v>
       </c>
       <c r="F161" t="s">
+        <v>164</v>
+      </c>
+      <c r="G161" t="s">
         <v>272</v>
-      </c>
-      <c r="G161" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="162" spans="1:7">
@@ -5352,19 +5352,19 @@
         <v>8</v>
       </c>
       <c r="C162" t="s">
-        <v>299</v>
+        <v>269</v>
       </c>
       <c r="D162" t="s">
         <v>270</v>
       </c>
       <c r="E162" t="s">
-        <v>271</v>
+        <v>299</v>
       </c>
       <c r="F162" t="s">
+        <v>164</v>
+      </c>
+      <c r="G162" t="s">
         <v>272</v>
-      </c>
-      <c r="G162" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="163" spans="1:7">
@@ -5375,19 +5375,19 @@
         <v>8</v>
       </c>
       <c r="C163" t="s">
-        <v>301</v>
+        <v>269</v>
       </c>
       <c r="D163" t="s">
         <v>270</v>
       </c>
       <c r="E163" t="s">
+        <v>301</v>
+      </c>
+      <c r="F163" t="s">
+        <v>164</v>
+      </c>
+      <c r="G163" t="s">
         <v>302</v>
-      </c>
-      <c r="F163" t="s">
-        <v>272</v>
-      </c>
-      <c r="G163" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="164" spans="1:7">
@@ -5398,19 +5398,19 @@
         <v>8</v>
       </c>
       <c r="C164" t="s">
-        <v>304</v>
+        <v>269</v>
       </c>
       <c r="D164" t="s">
         <v>270</v>
       </c>
       <c r="E164" t="s">
-        <v>271</v>
+        <v>304</v>
       </c>
       <c r="F164" t="s">
+        <v>164</v>
+      </c>
+      <c r="G164" t="s">
         <v>272</v>
-      </c>
-      <c r="G164" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="165" spans="1:7">
@@ -5421,19 +5421,19 @@
         <v>8</v>
       </c>
       <c r="C165" t="s">
-        <v>304</v>
+        <v>269</v>
       </c>
       <c r="D165" t="s">
         <v>270</v>
       </c>
       <c r="E165" t="s">
-        <v>271</v>
+        <v>304</v>
       </c>
       <c r="F165" t="s">
+        <v>164</v>
+      </c>
+      <c r="G165" t="s">
         <v>272</v>
-      </c>
-      <c r="G165" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="166" spans="1:7">
@@ -5444,19 +5444,19 @@
         <v>8</v>
       </c>
       <c r="C166" t="s">
-        <v>304</v>
+        <v>269</v>
       </c>
       <c r="D166" t="s">
         <v>270</v>
       </c>
       <c r="E166" t="s">
-        <v>271</v>
+        <v>304</v>
       </c>
       <c r="F166" t="s">
+        <v>164</v>
+      </c>
+      <c r="G166" t="s">
         <v>272</v>
-      </c>
-      <c r="G166" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="167" spans="1:7">
@@ -5467,19 +5467,19 @@
         <v>8</v>
       </c>
       <c r="C167" t="s">
-        <v>304</v>
+        <v>269</v>
       </c>
       <c r="D167" t="s">
         <v>270</v>
       </c>
       <c r="E167" t="s">
-        <v>271</v>
+        <v>304</v>
       </c>
       <c r="F167" t="s">
+        <v>164</v>
+      </c>
+      <c r="G167" t="s">
         <v>272</v>
-      </c>
-      <c r="G167" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="168" spans="1:7">
@@ -5490,19 +5490,19 @@
         <v>8</v>
       </c>
       <c r="C168" t="s">
-        <v>304</v>
+        <v>269</v>
       </c>
       <c r="D168" t="s">
         <v>270</v>
       </c>
       <c r="E168" t="s">
+        <v>304</v>
+      </c>
+      <c r="F168" t="s">
+        <v>164</v>
+      </c>
+      <c r="G168" t="s">
         <v>309</v>
-      </c>
-      <c r="F168" t="s">
-        <v>272</v>
-      </c>
-      <c r="G168" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="169" spans="1:7">
@@ -5513,19 +5513,19 @@
         <v>8</v>
       </c>
       <c r="C169" t="s">
-        <v>304</v>
+        <v>269</v>
       </c>
       <c r="D169" t="s">
         <v>270</v>
       </c>
       <c r="E169" t="s">
+        <v>304</v>
+      </c>
+      <c r="F169" t="s">
+        <v>164</v>
+      </c>
+      <c r="G169" t="s">
         <v>309</v>
-      </c>
-      <c r="F169" t="s">
-        <v>272</v>
-      </c>
-      <c r="G169" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="170" spans="1:7">
@@ -5536,19 +5536,19 @@
         <v>8</v>
       </c>
       <c r="C170" t="s">
-        <v>304</v>
+        <v>269</v>
       </c>
       <c r="D170" t="s">
         <v>270</v>
       </c>
       <c r="E170" t="s">
-        <v>271</v>
+        <v>304</v>
       </c>
       <c r="F170" t="s">
+        <v>164</v>
+      </c>
+      <c r="G170" t="s">
         <v>272</v>
-      </c>
-      <c r="G170" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="171" spans="1:7">
@@ -5558,10 +5558,10 @@
       <c r="B171" t="s">
         <v>8</v>
       </c>
+      <c r="C171" t="s">
+        <v>313</v>
+      </c>
       <c r="D171" t="s">
-        <v>313</v>
-      </c>
-      <c r="E171" t="s">
         <v>163</v>
       </c>
       <c r="F171" t="s">
@@ -5578,17 +5578,17 @@
       <c r="B172" t="s">
         <v>8</v>
       </c>
+      <c r="C172" t="s">
+        <v>313</v>
+      </c>
       <c r="D172" t="s">
-        <v>313</v>
-      </c>
-      <c r="E172" t="s">
         <v>118</v>
       </c>
       <c r="F172" t="s">
+        <v>115</v>
+      </c>
+      <c r="G172" t="s">
         <v>119</v>
-      </c>
-      <c r="G172" t="s">
-        <v>116</v>
       </c>
     </row>
     <row r="173" spans="1:7">
@@ -5598,10 +5598,10 @@
       <c r="B173" t="s">
         <v>8</v>
       </c>
+      <c r="C173" t="s">
+        <v>313</v>
+      </c>
       <c r="D173" t="s">
-        <v>313</v>
-      </c>
-      <c r="E173" t="s">
         <v>163</v>
       </c>
       <c r="F173" t="s">
@@ -5618,10 +5618,10 @@
       <c r="B174" t="s">
         <v>8</v>
       </c>
+      <c r="C174" t="s">
+        <v>313</v>
+      </c>
       <c r="D174" t="s">
-        <v>313</v>
-      </c>
-      <c r="E174" t="s">
         <v>163</v>
       </c>
       <c r="F174" t="s">
@@ -5638,10 +5638,10 @@
       <c r="B175" t="s">
         <v>8</v>
       </c>
+      <c r="C175" t="s">
+        <v>313</v>
+      </c>
       <c r="D175" t="s">
-        <v>313</v>
-      </c>
-      <c r="E175" t="s">
         <v>163</v>
       </c>
       <c r="F175" t="s">
@@ -5658,10 +5658,10 @@
       <c r="B176" t="s">
         <v>8</v>
       </c>
+      <c r="C176" t="s">
+        <v>313</v>
+      </c>
       <c r="D176" t="s">
-        <v>313</v>
-      </c>
-      <c r="E176" t="s">
         <v>163</v>
       </c>
       <c r="F176" t="s">
@@ -5678,10 +5678,10 @@
       <c r="B177" t="s">
         <v>8</v>
       </c>
+      <c r="C177" t="s">
+        <v>320</v>
+      </c>
       <c r="D177" t="s">
-        <v>320</v>
-      </c>
-      <c r="E177" t="s">
         <v>163</v>
       </c>
       <c r="F177" t="s">
@@ -5698,10 +5698,10 @@
       <c r="B178" t="s">
         <v>8</v>
       </c>
+      <c r="C178" t="s">
+        <v>320</v>
+      </c>
       <c r="D178" t="s">
-        <v>320</v>
-      </c>
-      <c r="E178" t="s">
         <v>163</v>
       </c>
       <c r="F178" t="s">
@@ -5718,10 +5718,10 @@
       <c r="B179" t="s">
         <v>8</v>
       </c>
+      <c r="C179" t="s">
+        <v>320</v>
+      </c>
       <c r="D179" t="s">
-        <v>320</v>
-      </c>
-      <c r="E179" t="s">
         <v>163</v>
       </c>
       <c r="F179" t="s">
@@ -5738,10 +5738,10 @@
       <c r="B180" t="s">
         <v>8</v>
       </c>
+      <c r="C180" t="s">
+        <v>320</v>
+      </c>
       <c r="D180" t="s">
-        <v>320</v>
-      </c>
-      <c r="E180" t="s">
         <v>163</v>
       </c>
       <c r="F180" t="s">
@@ -5768,10 +5768,10 @@
         <v>327</v>
       </c>
       <c r="F181" t="s">
+        <v>164</v>
+      </c>
+      <c r="G181" t="s">
         <v>328</v>
-      </c>
-      <c r="G181" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="182" spans="1:7">
@@ -5791,10 +5791,10 @@
         <v>327</v>
       </c>
       <c r="F182" t="s">
+        <v>164</v>
+      </c>
+      <c r="G182" t="s">
         <v>328</v>
-      </c>
-      <c r="G182" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="183" spans="1:7">
@@ -5814,10 +5814,10 @@
         <v>327</v>
       </c>
       <c r="F183" t="s">
+        <v>164</v>
+      </c>
+      <c r="G183" t="s">
         <v>328</v>
-      </c>
-      <c r="G183" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="184" spans="1:7">
@@ -5837,10 +5837,10 @@
         <v>327</v>
       </c>
       <c r="F184" t="s">
+        <v>164</v>
+      </c>
+      <c r="G184" t="s">
         <v>328</v>
-      </c>
-      <c r="G184" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="185" spans="1:7">
@@ -5860,10 +5860,10 @@
         <v>327</v>
       </c>
       <c r="F185" t="s">
+        <v>164</v>
+      </c>
+      <c r="G185" t="s">
         <v>328</v>
-      </c>
-      <c r="G185" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="186" spans="1:7">
@@ -5883,10 +5883,10 @@
         <v>327</v>
       </c>
       <c r="F186" t="s">
+        <v>164</v>
+      </c>
+      <c r="G186" t="s">
         <v>328</v>
-      </c>
-      <c r="G186" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="187" spans="1:7">
@@ -5906,10 +5906,10 @@
         <v>327</v>
       </c>
       <c r="F187" t="s">
+        <v>164</v>
+      </c>
+      <c r="G187" t="s">
         <v>328</v>
-      </c>
-      <c r="G187" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="188" spans="1:7">
@@ -5929,10 +5929,10 @@
         <v>327</v>
       </c>
       <c r="F188" t="s">
+        <v>164</v>
+      </c>
+      <c r="G188" t="s">
         <v>328</v>
-      </c>
-      <c r="G188" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="189" spans="1:7">
@@ -5952,10 +5952,10 @@
         <v>327</v>
       </c>
       <c r="F189" t="s">
+        <v>164</v>
+      </c>
+      <c r="G189" t="s">
         <v>328</v>
-      </c>
-      <c r="G189" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="190" spans="1:7">
@@ -5975,10 +5975,10 @@
         <v>327</v>
       </c>
       <c r="F190" t="s">
+        <v>164</v>
+      </c>
+      <c r="G190" t="s">
         <v>328</v>
-      </c>
-      <c r="G190" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="191" spans="1:7">
@@ -5998,10 +5998,10 @@
         <v>327</v>
       </c>
       <c r="F191" t="s">
+        <v>164</v>
+      </c>
+      <c r="G191" t="s">
         <v>328</v>
-      </c>
-      <c r="G191" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="192" spans="1:7">
@@ -6021,10 +6021,10 @@
         <v>327</v>
       </c>
       <c r="F192" t="s">
+        <v>164</v>
+      </c>
+      <c r="G192" t="s">
         <v>328</v>
-      </c>
-      <c r="G192" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="193" spans="1:7">
@@ -6038,16 +6038,16 @@
         <v>325</v>
       </c>
       <c r="D193" t="s">
-        <v>326</v>
+        <v>275</v>
       </c>
       <c r="E193" t="s">
+        <v>327</v>
+      </c>
+      <c r="F193" t="s">
+        <v>164</v>
+      </c>
+      <c r="G193" t="s">
         <v>341</v>
-      </c>
-      <c r="F193" t="s">
-        <v>276</v>
-      </c>
-      <c r="G193" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="194" spans="1:7">
@@ -6067,10 +6067,10 @@
         <v>327</v>
       </c>
       <c r="F194" t="s">
+        <v>164</v>
+      </c>
+      <c r="G194" t="s">
         <v>328</v>
-      </c>
-      <c r="G194" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="195" spans="1:7">
@@ -6090,10 +6090,10 @@
         <v>327</v>
       </c>
       <c r="F195" t="s">
+        <v>164</v>
+      </c>
+      <c r="G195" t="s">
         <v>328</v>
-      </c>
-      <c r="G195" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="196" spans="1:7">
@@ -6113,10 +6113,10 @@
         <v>327</v>
       </c>
       <c r="F196" t="s">
+        <v>164</v>
+      </c>
+      <c r="G196" t="s">
         <v>328</v>
-      </c>
-      <c r="G196" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="197" spans="1:7">
@@ -6136,10 +6136,10 @@
         <v>327</v>
       </c>
       <c r="F197" t="s">
+        <v>164</v>
+      </c>
+      <c r="G197" t="s">
         <v>328</v>
-      </c>
-      <c r="G197" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="198" spans="1:7">
@@ -6159,10 +6159,10 @@
         <v>327</v>
       </c>
       <c r="F198" t="s">
+        <v>164</v>
+      </c>
+      <c r="G198" t="s">
         <v>328</v>
-      </c>
-      <c r="G198" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="199" spans="1:7">
@@ -6173,19 +6173,19 @@
         <v>8</v>
       </c>
       <c r="C199" t="s">
-        <v>348</v>
+        <v>325</v>
       </c>
       <c r="D199" t="s">
         <v>326</v>
       </c>
       <c r="E199" t="s">
+        <v>348</v>
+      </c>
+      <c r="F199" t="s">
+        <v>164</v>
+      </c>
+      <c r="G199" t="s">
         <v>349</v>
-      </c>
-      <c r="F199" t="s">
-        <v>328</v>
-      </c>
-      <c r="G199" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="200" spans="1:7">
@@ -6196,19 +6196,19 @@
         <v>8</v>
       </c>
       <c r="C200" t="s">
-        <v>348</v>
+        <v>325</v>
       </c>
       <c r="D200" t="s">
         <v>326</v>
       </c>
       <c r="E200" t="s">
+        <v>348</v>
+      </c>
+      <c r="F200" t="s">
+        <v>164</v>
+      </c>
+      <c r="G200" t="s">
         <v>349</v>
-      </c>
-      <c r="F200" t="s">
-        <v>328</v>
-      </c>
-      <c r="G200" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="201" spans="1:7">
@@ -6219,19 +6219,19 @@
         <v>8</v>
       </c>
       <c r="C201" t="s">
-        <v>348</v>
+        <v>325</v>
       </c>
       <c r="D201" t="s">
         <v>326</v>
       </c>
       <c r="E201" t="s">
+        <v>348</v>
+      </c>
+      <c r="F201" t="s">
+        <v>164</v>
+      </c>
+      <c r="G201" t="s">
         <v>349</v>
-      </c>
-      <c r="F201" t="s">
-        <v>328</v>
-      </c>
-      <c r="G201" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="202" spans="1:7">
@@ -6242,19 +6242,19 @@
         <v>8</v>
       </c>
       <c r="C202" t="s">
-        <v>348</v>
+        <v>325</v>
       </c>
       <c r="D202" t="s">
         <v>326</v>
       </c>
       <c r="E202" t="s">
+        <v>348</v>
+      </c>
+      <c r="F202" t="s">
+        <v>164</v>
+      </c>
+      <c r="G202" t="s">
         <v>349</v>
-      </c>
-      <c r="F202" t="s">
-        <v>328</v>
-      </c>
-      <c r="G202" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="203" spans="1:7">
@@ -6265,19 +6265,19 @@
         <v>8</v>
       </c>
       <c r="C203" t="s">
+        <v>325</v>
+      </c>
+      <c r="D203" t="s">
+        <v>275</v>
+      </c>
+      <c r="E203" t="s">
         <v>348</v>
       </c>
-      <c r="D203" t="s">
-        <v>326</v>
-      </c>
-      <c r="E203" t="s">
+      <c r="F203" t="s">
+        <v>164</v>
+      </c>
+      <c r="G203" t="s">
         <v>341</v>
-      </c>
-      <c r="F203" t="s">
-        <v>276</v>
-      </c>
-      <c r="G203" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="204" spans="1:7">
@@ -6288,19 +6288,19 @@
         <v>8</v>
       </c>
       <c r="C204" t="s">
-        <v>348</v>
+        <v>325</v>
       </c>
       <c r="D204" t="s">
         <v>326</v>
       </c>
       <c r="E204" t="s">
+        <v>348</v>
+      </c>
+      <c r="F204" t="s">
+        <v>164</v>
+      </c>
+      <c r="G204" t="s">
         <v>349</v>
-      </c>
-      <c r="F204" t="s">
-        <v>328</v>
-      </c>
-      <c r="G204" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="205" spans="1:7">
@@ -6311,19 +6311,19 @@
         <v>8</v>
       </c>
       <c r="C205" t="s">
-        <v>356</v>
+        <v>325</v>
       </c>
       <c r="D205" t="s">
         <v>326</v>
       </c>
       <c r="E205" t="s">
+        <v>356</v>
+      </c>
+      <c r="F205" t="s">
+        <v>164</v>
+      </c>
+      <c r="G205" t="s">
         <v>357</v>
-      </c>
-      <c r="F205" t="s">
-        <v>328</v>
-      </c>
-      <c r="G205" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="206" spans="1:7">
@@ -6334,19 +6334,19 @@
         <v>8</v>
       </c>
       <c r="C206" t="s">
-        <v>356</v>
+        <v>325</v>
       </c>
       <c r="D206" t="s">
         <v>326</v>
       </c>
       <c r="E206" t="s">
+        <v>356</v>
+      </c>
+      <c r="F206" t="s">
+        <v>164</v>
+      </c>
+      <c r="G206" t="s">
         <v>357</v>
-      </c>
-      <c r="F206" t="s">
-        <v>328</v>
-      </c>
-      <c r="G206" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="207" spans="1:7">
@@ -6357,19 +6357,19 @@
         <v>8</v>
       </c>
       <c r="C207" t="s">
-        <v>356</v>
+        <v>325</v>
       </c>
       <c r="D207" t="s">
         <v>326</v>
       </c>
       <c r="E207" t="s">
+        <v>356</v>
+      </c>
+      <c r="F207" t="s">
+        <v>164</v>
+      </c>
+      <c r="G207" t="s">
         <v>357</v>
-      </c>
-      <c r="F207" t="s">
-        <v>328</v>
-      </c>
-      <c r="G207" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="208" spans="1:7">
@@ -6380,19 +6380,19 @@
         <v>8</v>
       </c>
       <c r="C208" t="s">
+        <v>325</v>
+      </c>
+      <c r="D208" t="s">
+        <v>275</v>
+      </c>
+      <c r="E208" t="s">
         <v>356</v>
       </c>
-      <c r="D208" t="s">
-        <v>326</v>
-      </c>
-      <c r="E208" t="s">
+      <c r="F208" t="s">
+        <v>164</v>
+      </c>
+      <c r="G208" t="s">
         <v>341</v>
-      </c>
-      <c r="F208" t="s">
-        <v>276</v>
-      </c>
-      <c r="G208" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="209" spans="1:7">
@@ -6403,19 +6403,19 @@
         <v>8</v>
       </c>
       <c r="C209" t="s">
-        <v>356</v>
+        <v>325</v>
       </c>
       <c r="D209" t="s">
         <v>326</v>
       </c>
       <c r="E209" t="s">
+        <v>356</v>
+      </c>
+      <c r="F209" t="s">
+        <v>164</v>
+      </c>
+      <c r="G209" t="s">
         <v>357</v>
-      </c>
-      <c r="F209" t="s">
-        <v>328</v>
-      </c>
-      <c r="G209" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="210" spans="1:7">
@@ -6435,10 +6435,10 @@
         <v>365</v>
       </c>
       <c r="F210" t="s">
+        <v>164</v>
+      </c>
+      <c r="G210" t="s">
         <v>366</v>
-      </c>
-      <c r="G210" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="211" spans="1:7">
@@ -6458,10 +6458,10 @@
         <v>365</v>
       </c>
       <c r="F211" t="s">
+        <v>164</v>
+      </c>
+      <c r="G211" t="s">
         <v>366</v>
-      </c>
-      <c r="G211" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="212" spans="1:7">
@@ -6481,10 +6481,10 @@
         <v>365</v>
       </c>
       <c r="F212" t="s">
+        <v>164</v>
+      </c>
+      <c r="G212" t="s">
         <v>366</v>
-      </c>
-      <c r="G212" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="213" spans="1:7">
@@ -6504,10 +6504,10 @@
         <v>365</v>
       </c>
       <c r="F213" t="s">
+        <v>164</v>
+      </c>
+      <c r="G213" t="s">
         <v>366</v>
-      </c>
-      <c r="G213" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="214" spans="1:7">
@@ -6527,10 +6527,10 @@
         <v>365</v>
       </c>
       <c r="F214" t="s">
+        <v>164</v>
+      </c>
+      <c r="G214" t="s">
         <v>366</v>
-      </c>
-      <c r="G214" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="215" spans="1:7">
@@ -6544,16 +6544,16 @@
         <v>363</v>
       </c>
       <c r="D215" t="s">
-        <v>364</v>
+        <v>326</v>
       </c>
       <c r="E215" t="s">
+        <v>365</v>
+      </c>
+      <c r="F215" t="s">
+        <v>164</v>
+      </c>
+      <c r="G215" t="s">
         <v>349</v>
-      </c>
-      <c r="F215" t="s">
-        <v>328</v>
-      </c>
-      <c r="G215" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="216" spans="1:7">
@@ -6573,10 +6573,10 @@
         <v>365</v>
       </c>
       <c r="F216" t="s">
+        <v>164</v>
+      </c>
+      <c r="G216" t="s">
         <v>366</v>
-      </c>
-      <c r="G216" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="217" spans="1:7">
@@ -6596,10 +6596,10 @@
         <v>365</v>
       </c>
       <c r="F217" t="s">
+        <v>164</v>
+      </c>
+      <c r="G217" t="s">
         <v>366</v>
-      </c>
-      <c r="G217" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="218" spans="1:7">
@@ -6619,10 +6619,10 @@
         <v>365</v>
       </c>
       <c r="F218" t="s">
+        <v>164</v>
+      </c>
+      <c r="G218" t="s">
         <v>366</v>
-      </c>
-      <c r="G218" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="219" spans="1:7">
@@ -6642,10 +6642,10 @@
         <v>365</v>
       </c>
       <c r="F219" t="s">
+        <v>164</v>
+      </c>
+      <c r="G219" t="s">
         <v>366</v>
-      </c>
-      <c r="G219" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="220" spans="1:7">
@@ -6659,16 +6659,16 @@
         <v>363</v>
       </c>
       <c r="D220" t="s">
-        <v>364</v>
+        <v>270</v>
       </c>
       <c r="E220" t="s">
+        <v>365</v>
+      </c>
+      <c r="F220" t="s">
+        <v>164</v>
+      </c>
+      <c r="G220" t="s">
         <v>309</v>
-      </c>
-      <c r="F220" t="s">
-        <v>272</v>
-      </c>
-      <c r="G220" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="221" spans="1:7">
@@ -6688,10 +6688,10 @@
         <v>365</v>
       </c>
       <c r="F221" t="s">
+        <v>164</v>
+      </c>
+      <c r="G221" t="s">
         <v>366</v>
-      </c>
-      <c r="G221" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="222" spans="1:7">
@@ -6711,10 +6711,10 @@
         <v>365</v>
       </c>
       <c r="F222" t="s">
+        <v>164</v>
+      </c>
+      <c r="G222" t="s">
         <v>366</v>
-      </c>
-      <c r="G222" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="223" spans="1:7">
@@ -6734,10 +6734,10 @@
         <v>365</v>
       </c>
       <c r="F223" t="s">
+        <v>164</v>
+      </c>
+      <c r="G223" t="s">
         <v>366</v>
-      </c>
-      <c r="G223" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="224" spans="1:7">
@@ -6757,10 +6757,10 @@
         <v>365</v>
       </c>
       <c r="F224" t="s">
+        <v>164</v>
+      </c>
+      <c r="G224" t="s">
         <v>366</v>
-      </c>
-      <c r="G224" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="225" spans="1:7">
@@ -6780,10 +6780,10 @@
         <v>365</v>
       </c>
       <c r="F225" t="s">
+        <v>164</v>
+      </c>
+      <c r="G225" t="s">
         <v>366</v>
-      </c>
-      <c r="G225" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="226" spans="1:7">
@@ -6797,16 +6797,16 @@
         <v>363</v>
       </c>
       <c r="D226" t="s">
-        <v>364</v>
+        <v>275</v>
       </c>
       <c r="E226" t="s">
-        <v>275</v>
+        <v>365</v>
       </c>
       <c r="F226" t="s">
+        <v>164</v>
+      </c>
+      <c r="G226" t="s">
         <v>276</v>
-      </c>
-      <c r="G226" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="227" spans="1:7">
@@ -6826,10 +6826,10 @@
         <v>365</v>
       </c>
       <c r="F227" t="s">
+        <v>164</v>
+      </c>
+      <c r="G227" t="s">
         <v>366</v>
-      </c>
-      <c r="G227" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="228" spans="1:7">
@@ -6843,10 +6843,10 @@
         <v>363</v>
       </c>
       <c r="D228" t="s">
-        <v>364</v>
+        <v>163</v>
       </c>
       <c r="E228" t="s">
-        <v>163</v>
+        <v>365</v>
       </c>
       <c r="F228" t="s">
         <v>164</v>
@@ -6863,19 +6863,19 @@
         <v>8</v>
       </c>
       <c r="C229" t="s">
-        <v>386</v>
+        <v>363</v>
       </c>
       <c r="D229" t="s">
         <v>364</v>
       </c>
       <c r="E229" t="s">
+        <v>386</v>
+      </c>
+      <c r="F229" t="s">
+        <v>164</v>
+      </c>
+      <c r="G229" t="s">
         <v>387</v>
-      </c>
-      <c r="F229" t="s">
-        <v>366</v>
-      </c>
-      <c r="G229" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="230" spans="1:7">
@@ -6886,19 +6886,19 @@
         <v>8</v>
       </c>
       <c r="C230" t="s">
-        <v>386</v>
+        <v>363</v>
       </c>
       <c r="D230" t="s">
         <v>364</v>
       </c>
       <c r="E230" t="s">
+        <v>386</v>
+      </c>
+      <c r="F230" t="s">
+        <v>164</v>
+      </c>
+      <c r="G230" t="s">
         <v>387</v>
-      </c>
-      <c r="F230" t="s">
-        <v>366</v>
-      </c>
-      <c r="G230" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="231" spans="1:7">
@@ -6909,19 +6909,19 @@
         <v>8</v>
       </c>
       <c r="C231" t="s">
+        <v>363</v>
+      </c>
+      <c r="D231" t="s">
+        <v>270</v>
+      </c>
+      <c r="E231" t="s">
         <v>386</v>
       </c>
-      <c r="D231" t="s">
-        <v>364</v>
-      </c>
-      <c r="E231" t="s">
+      <c r="F231" t="s">
+        <v>164</v>
+      </c>
+      <c r="G231" t="s">
         <v>293</v>
-      </c>
-      <c r="F231" t="s">
-        <v>272</v>
-      </c>
-      <c r="G231" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="232" spans="1:7">
@@ -6932,19 +6932,19 @@
         <v>8</v>
       </c>
       <c r="C232" t="s">
+        <v>363</v>
+      </c>
+      <c r="D232" t="s">
+        <v>270</v>
+      </c>
+      <c r="E232" t="s">
         <v>386</v>
       </c>
-      <c r="D232" t="s">
-        <v>364</v>
-      </c>
-      <c r="E232" t="s">
+      <c r="F232" t="s">
+        <v>164</v>
+      </c>
+      <c r="G232" t="s">
         <v>309</v>
-      </c>
-      <c r="F232" t="s">
-        <v>272</v>
-      </c>
-      <c r="G232" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="233" spans="1:7">
@@ -6955,19 +6955,19 @@
         <v>8</v>
       </c>
       <c r="C233" t="s">
-        <v>386</v>
+        <v>363</v>
       </c>
       <c r="D233" t="s">
         <v>364</v>
       </c>
       <c r="E233" t="s">
+        <v>386</v>
+      </c>
+      <c r="F233" t="s">
+        <v>164</v>
+      </c>
+      <c r="G233" t="s">
         <v>387</v>
-      </c>
-      <c r="F233" t="s">
-        <v>366</v>
-      </c>
-      <c r="G233" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="234" spans="1:7">
@@ -6978,19 +6978,19 @@
         <v>8</v>
       </c>
       <c r="C234" t="s">
-        <v>386</v>
+        <v>363</v>
       </c>
       <c r="D234" t="s">
         <v>364</v>
       </c>
       <c r="E234" t="s">
+        <v>386</v>
+      </c>
+      <c r="F234" t="s">
+        <v>164</v>
+      </c>
+      <c r="G234" t="s">
         <v>387</v>
-      </c>
-      <c r="F234" t="s">
-        <v>366</v>
-      </c>
-      <c r="G234" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="235" spans="1:7">
@@ -7001,19 +7001,19 @@
         <v>8</v>
       </c>
       <c r="C235" t="s">
-        <v>386</v>
+        <v>363</v>
       </c>
       <c r="D235" t="s">
         <v>364</v>
       </c>
       <c r="E235" t="s">
+        <v>386</v>
+      </c>
+      <c r="F235" t="s">
+        <v>164</v>
+      </c>
+      <c r="G235" t="s">
         <v>387</v>
-      </c>
-      <c r="F235" t="s">
-        <v>366</v>
-      </c>
-      <c r="G235" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="236" spans="1:7">
@@ -7024,19 +7024,19 @@
         <v>8</v>
       </c>
       <c r="C236" t="s">
-        <v>386</v>
+        <v>363</v>
       </c>
       <c r="D236" t="s">
         <v>364</v>
       </c>
       <c r="E236" t="s">
+        <v>386</v>
+      </c>
+      <c r="F236" t="s">
+        <v>164</v>
+      </c>
+      <c r="G236" t="s">
         <v>387</v>
-      </c>
-      <c r="F236" t="s">
-        <v>366</v>
-      </c>
-      <c r="G236" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="237" spans="1:7">
@@ -7047,19 +7047,19 @@
         <v>8</v>
       </c>
       <c r="C237" t="s">
-        <v>386</v>
+        <v>363</v>
       </c>
       <c r="D237" t="s">
         <v>364</v>
       </c>
       <c r="E237" t="s">
+        <v>386</v>
+      </c>
+      <c r="F237" t="s">
+        <v>164</v>
+      </c>
+      <c r="G237" t="s">
         <v>387</v>
-      </c>
-      <c r="F237" t="s">
-        <v>366</v>
-      </c>
-      <c r="G237" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="238" spans="1:7">
@@ -7070,19 +7070,19 @@
         <v>8</v>
       </c>
       <c r="C238" t="s">
-        <v>386</v>
+        <v>363</v>
       </c>
       <c r="D238" t="s">
         <v>364</v>
       </c>
       <c r="E238" t="s">
+        <v>386</v>
+      </c>
+      <c r="F238" t="s">
+        <v>164</v>
+      </c>
+      <c r="G238" t="s">
         <v>387</v>
-      </c>
-      <c r="F238" t="s">
-        <v>366</v>
-      </c>
-      <c r="G238" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="239" spans="1:7">
@@ -7093,19 +7093,19 @@
         <v>8</v>
       </c>
       <c r="C239" t="s">
-        <v>398</v>
+        <v>363</v>
       </c>
       <c r="D239" t="s">
         <v>364</v>
       </c>
       <c r="E239" t="s">
+        <v>398</v>
+      </c>
+      <c r="F239" t="s">
+        <v>164</v>
+      </c>
+      <c r="G239" t="s">
         <v>399</v>
-      </c>
-      <c r="F239" t="s">
-        <v>366</v>
-      </c>
-      <c r="G239" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="240" spans="1:7">
@@ -7119,10 +7119,10 @@
         <v>401</v>
       </c>
       <c r="D240" t="s">
+        <v>163</v>
+      </c>
+      <c r="E240" t="s">
         <v>402</v>
-      </c>
-      <c r="E240" t="s">
-        <v>163</v>
       </c>
       <c r="F240" t="s">
         <v>164</v>
@@ -7142,10 +7142,10 @@
         <v>401</v>
       </c>
       <c r="D241" t="s">
+        <v>163</v>
+      </c>
+      <c r="E241" t="s">
         <v>402</v>
-      </c>
-      <c r="E241" t="s">
-        <v>163</v>
       </c>
       <c r="F241" t="s">
         <v>164</v>
@@ -7165,10 +7165,10 @@
         <v>401</v>
       </c>
       <c r="D242" t="s">
+        <v>163</v>
+      </c>
+      <c r="E242" t="s">
         <v>402</v>
-      </c>
-      <c r="E242" t="s">
-        <v>163</v>
       </c>
       <c r="F242" t="s">
         <v>164</v>
@@ -7188,10 +7188,10 @@
         <v>401</v>
       </c>
       <c r="D243" t="s">
+        <v>163</v>
+      </c>
+      <c r="E243" t="s">
         <v>402</v>
-      </c>
-      <c r="E243" t="s">
-        <v>163</v>
       </c>
       <c r="F243" t="s">
         <v>164</v>
@@ -7211,10 +7211,10 @@
         <v>401</v>
       </c>
       <c r="D244" t="s">
+        <v>163</v>
+      </c>
+      <c r="E244" t="s">
         <v>402</v>
-      </c>
-      <c r="E244" t="s">
-        <v>163</v>
       </c>
       <c r="F244" t="s">
         <v>164</v>
@@ -7234,10 +7234,10 @@
         <v>401</v>
       </c>
       <c r="D245" t="s">
+        <v>163</v>
+      </c>
+      <c r="E245" t="s">
         <v>402</v>
-      </c>
-      <c r="E245" t="s">
-        <v>163</v>
       </c>
       <c r="F245" t="s">
         <v>164</v>
@@ -7254,19 +7254,19 @@
         <v>8</v>
       </c>
       <c r="C246" t="s">
+        <v>401</v>
+      </c>
+      <c r="D246" t="s">
+        <v>255</v>
+      </c>
+      <c r="E246" t="s">
         <v>409</v>
       </c>
-      <c r="D246" t="s">
-        <v>402</v>
-      </c>
-      <c r="E246" t="s">
+      <c r="F246" t="s">
+        <v>164</v>
+      </c>
+      <c r="G246" t="s">
         <v>410</v>
-      </c>
-      <c r="F246" t="s">
-        <v>256</v>
-      </c>
-      <c r="G246" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="247" spans="1:7">
@@ -7276,10 +7276,10 @@
       <c r="B247" t="s">
         <v>8</v>
       </c>
+      <c r="C247" t="s">
+        <v>412</v>
+      </c>
       <c r="D247" t="s">
-        <v>412</v>
-      </c>
-      <c r="E247" t="s">
         <v>95</v>
       </c>
       <c r="F247" t="s">
@@ -7296,10 +7296,10 @@
       <c r="B248" t="s">
         <v>8</v>
       </c>
+      <c r="C248" t="s">
+        <v>412</v>
+      </c>
       <c r="D248" t="s">
-        <v>412</v>
-      </c>
-      <c r="E248" t="s">
         <v>95</v>
       </c>
       <c r="F248" t="s">
@@ -7316,17 +7316,17 @@
       <c r="B249" t="s">
         <v>8</v>
       </c>
+      <c r="C249" t="s">
+        <v>412</v>
+      </c>
       <c r="D249" t="s">
-        <v>412</v>
-      </c>
-      <c r="E249" t="s">
         <v>415</v>
       </c>
       <c r="F249" t="s">
+        <v>96</v>
+      </c>
+      <c r="G249" t="s">
         <v>416</v>
-      </c>
-      <c r="G249" t="s">
-        <v>97</v>
       </c>
     </row>
     <row r="250" spans="1:7">
@@ -7336,10 +7336,10 @@
       <c r="B250" t="s">
         <v>8</v>
       </c>
+      <c r="C250" t="s">
+        <v>412</v>
+      </c>
       <c r="D250" t="s">
-        <v>412</v>
-      </c>
-      <c r="E250" t="s">
         <v>95</v>
       </c>
       <c r="F250" t="s">
@@ -7356,10 +7356,10 @@
       <c r="B251" t="s">
         <v>8</v>
       </c>
+      <c r="C251" t="s">
+        <v>412</v>
+      </c>
       <c r="D251" t="s">
-        <v>412</v>
-      </c>
-      <c r="E251" t="s">
         <v>95</v>
       </c>
       <c r="F251" t="s">
@@ -7376,10 +7376,10 @@
       <c r="B252" t="s">
         <v>8</v>
       </c>
+      <c r="C252" t="s">
+        <v>412</v>
+      </c>
       <c r="D252" t="s">
-        <v>412</v>
-      </c>
-      <c r="E252" t="s">
         <v>95</v>
       </c>
       <c r="F252" t="s">
@@ -7396,17 +7396,17 @@
       <c r="B253" t="s">
         <v>8</v>
       </c>
+      <c r="C253" t="s">
+        <v>421</v>
+      </c>
       <c r="D253" t="s">
-        <v>421</v>
-      </c>
-      <c r="E253" t="s">
         <v>422</v>
       </c>
       <c r="F253" t="s">
+        <v>164</v>
+      </c>
+      <c r="G253" t="s">
         <v>423</v>
-      </c>
-      <c r="G253" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="254" spans="1:7">
@@ -7416,17 +7416,17 @@
       <c r="B254" t="s">
         <v>8</v>
       </c>
+      <c r="C254" t="s">
+        <v>421</v>
+      </c>
       <c r="D254" t="s">
-        <v>421</v>
-      </c>
-      <c r="E254" t="s">
         <v>219</v>
       </c>
       <c r="F254" t="s">
+        <v>92</v>
+      </c>
+      <c r="G254" t="s">
         <v>220</v>
-      </c>
-      <c r="G254" t="s">
-        <v>93</v>
       </c>
     </row>
     <row r="255" spans="1:7">
@@ -7436,17 +7436,17 @@
       <c r="B255" t="s">
         <v>8</v>
       </c>
+      <c r="C255" t="s">
+        <v>421</v>
+      </c>
       <c r="D255" t="s">
-        <v>421</v>
-      </c>
-      <c r="E255" t="s">
         <v>426</v>
       </c>
       <c r="F255" t="s">
+        <v>92</v>
+      </c>
+      <c r="G255" t="s">
         <v>427</v>
-      </c>
-      <c r="G255" t="s">
-        <v>93</v>
       </c>
     </row>
     <row r="256" spans="1:7">
@@ -7456,17 +7456,17 @@
       <c r="B256" t="s">
         <v>8</v>
       </c>
+      <c r="C256" t="s">
+        <v>421</v>
+      </c>
       <c r="D256" t="s">
-        <v>421</v>
-      </c>
-      <c r="E256" t="s">
         <v>426</v>
       </c>
       <c r="F256" t="s">
+        <v>92</v>
+      </c>
+      <c r="G256" t="s">
         <v>427</v>
-      </c>
-      <c r="G256" t="s">
-        <v>93</v>
       </c>
     </row>
     <row r="257" spans="1:7">
@@ -7476,17 +7476,17 @@
       <c r="B257" t="s">
         <v>8</v>
       </c>
+      <c r="C257" t="s">
+        <v>421</v>
+      </c>
       <c r="D257" t="s">
-        <v>421</v>
-      </c>
-      <c r="E257" t="s">
         <v>426</v>
       </c>
       <c r="F257" t="s">
+        <v>92</v>
+      </c>
+      <c r="G257" t="s">
         <v>427</v>
-      </c>
-      <c r="G257" t="s">
-        <v>93</v>
       </c>
     </row>
     <row r="258" spans="1:7">
@@ -7496,17 +7496,17 @@
       <c r="B258" t="s">
         <v>8</v>
       </c>
+      <c r="C258" t="s">
+        <v>421</v>
+      </c>
       <c r="D258" t="s">
-        <v>421</v>
-      </c>
-      <c r="E258" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="F258" t="s">
+        <v>164</v>
+      </c>
+      <c r="G258" t="s">
         <v>328</v>
-      </c>
-      <c r="G258" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="259" spans="1:7">
@@ -7516,17 +7516,17 @@
       <c r="B259" t="s">
         <v>8</v>
       </c>
+      <c r="C259" t="s">
+        <v>421</v>
+      </c>
       <c r="D259" t="s">
-        <v>421</v>
-      </c>
-      <c r="E259" t="s">
         <v>426</v>
       </c>
       <c r="F259" t="s">
+        <v>92</v>
+      </c>
+      <c r="G259" t="s">
         <v>427</v>
-      </c>
-      <c r="G259" t="s">
-        <v>93</v>
       </c>
     </row>
     <row r="260" spans="1:7">
@@ -7536,10 +7536,10 @@
       <c r="B260" t="s">
         <v>8</v>
       </c>
+      <c r="C260" t="s">
+        <v>421</v>
+      </c>
       <c r="D260" t="s">
-        <v>421</v>
-      </c>
-      <c r="E260" t="s">
         <v>163</v>
       </c>
       <c r="F260" t="s">
@@ -7556,17 +7556,17 @@
       <c r="B261" t="s">
         <v>8</v>
       </c>
+      <c r="C261" t="s">
+        <v>421</v>
+      </c>
       <c r="D261" t="s">
-        <v>421</v>
-      </c>
-      <c r="E261" t="s">
         <v>434</v>
       </c>
       <c r="F261" t="s">
+        <v>196</v>
+      </c>
+      <c r="G261" t="s">
         <v>435</v>
-      </c>
-      <c r="G261" t="s">
-        <v>197</v>
       </c>
     </row>
     <row r="262" spans="1:7">
@@ -7576,10 +7576,10 @@
       <c r="B262" t="s">
         <v>8</v>
       </c>
+      <c r="C262" t="s">
+        <v>421</v>
+      </c>
       <c r="D262" t="s">
-        <v>421</v>
-      </c>
-      <c r="E262" t="s">
         <v>163</v>
       </c>
       <c r="F262" t="s">
@@ -7596,17 +7596,17 @@
       <c r="B263" t="s">
         <v>8</v>
       </c>
+      <c r="C263" t="s">
+        <v>421</v>
+      </c>
       <c r="D263" t="s">
-        <v>421</v>
-      </c>
-      <c r="E263" t="s">
         <v>438</v>
       </c>
       <c r="F263" t="s">
+        <v>183</v>
+      </c>
+      <c r="G263" t="s">
         <v>439</v>
-      </c>
-      <c r="G263" t="s">
-        <v>184</v>
       </c>
     </row>
     <row r="264" spans="1:7">
@@ -7616,10 +7616,10 @@
       <c r="B264" t="s">
         <v>8</v>
       </c>
+      <c r="C264" t="s">
+        <v>421</v>
+      </c>
       <c r="D264" t="s">
-        <v>421</v>
-      </c>
-      <c r="E264" t="s">
         <v>31</v>
       </c>
       <c r="F264" t="s">
@@ -7636,11 +7636,11 @@
       <c r="B265" t="s">
         <v>8</v>
       </c>
+      <c r="C265" t="s">
+        <v>421</v>
+      </c>
       <c r="D265" t="s">
-        <v>421</v>
-      </c>
-      <c r="E265" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F265" t="s">
         <v>12</v>
@@ -7656,17 +7656,17 @@
       <c r="B266" t="s">
         <v>8</v>
       </c>
+      <c r="C266" t="s">
+        <v>421</v>
+      </c>
       <c r="D266" t="s">
-        <v>421</v>
-      </c>
-      <c r="E266" t="s">
         <v>443</v>
       </c>
       <c r="F266" t="s">
+        <v>115</v>
+      </c>
+      <c r="G266" t="s">
         <v>444</v>
-      </c>
-      <c r="G266" t="s">
-        <v>116</v>
       </c>
     </row>
     <row r="267" spans="1:7">
@@ -7676,17 +7676,17 @@
       <c r="B267" t="s">
         <v>8</v>
       </c>
+      <c r="C267" t="s">
+        <v>446</v>
+      </c>
       <c r="D267" t="s">
-        <v>446</v>
-      </c>
-      <c r="E267" t="s">
         <v>118</v>
       </c>
       <c r="F267" t="s">
+        <v>115</v>
+      </c>
+      <c r="G267" t="s">
         <v>119</v>
-      </c>
-      <c r="G267" t="s">
-        <v>116</v>
       </c>
     </row>
     <row r="268" spans="1:7">
@@ -7696,17 +7696,17 @@
       <c r="B268" t="s">
         <v>8</v>
       </c>
+      <c r="C268" t="s">
+        <v>448</v>
+      </c>
       <c r="D268" t="s">
-        <v>448</v>
-      </c>
-      <c r="E268" t="s">
         <v>203</v>
       </c>
       <c r="F268" t="s">
+        <v>183</v>
+      </c>
+      <c r="G268" t="s">
         <v>204</v>
-      </c>
-      <c r="G268" t="s">
-        <v>184</v>
       </c>
     </row>
     <row r="269" spans="1:7">
@@ -7716,17 +7716,17 @@
       <c r="B269" t="s">
         <v>8</v>
       </c>
+      <c r="C269" t="s">
+        <v>450</v>
+      </c>
       <c r="D269" t="s">
-        <v>450</v>
-      </c>
-      <c r="E269" t="s">
         <v>118</v>
       </c>
       <c r="F269" t="s">
+        <v>115</v>
+      </c>
+      <c r="G269" t="s">
         <v>119</v>
-      </c>
-      <c r="G269" t="s">
-        <v>116</v>
       </c>
     </row>
     <row r="270" spans="1:7">
@@ -7736,17 +7736,17 @@
       <c r="B270" t="s">
         <v>8</v>
       </c>
+      <c r="C270" t="s">
+        <v>450</v>
+      </c>
       <c r="D270" t="s">
-        <v>450</v>
-      </c>
-      <c r="E270" t="s">
         <v>118</v>
       </c>
       <c r="F270" t="s">
+        <v>115</v>
+      </c>
+      <c r="G270" t="s">
         <v>119</v>
-      </c>
-      <c r="G270" t="s">
-        <v>116</v>
       </c>
     </row>
     <row r="271" spans="1:7">
@@ -7756,17 +7756,17 @@
       <c r="B271" t="s">
         <v>8</v>
       </c>
+      <c r="C271" t="s">
+        <v>453</v>
+      </c>
       <c r="D271" t="s">
-        <v>453</v>
-      </c>
-      <c r="E271" t="s">
         <v>454</v>
       </c>
       <c r="F271" t="s">
+        <v>115</v>
+      </c>
+      <c r="G271" t="s">
         <v>455</v>
-      </c>
-      <c r="G271" t="s">
-        <v>116</v>
       </c>
     </row>
     <row r="272" spans="1:7">
@@ -7776,17 +7776,17 @@
       <c r="B272" t="s">
         <v>8</v>
       </c>
+      <c r="C272" t="s">
+        <v>453</v>
+      </c>
       <c r="D272" t="s">
-        <v>453</v>
-      </c>
-      <c r="E272" t="s">
         <v>454</v>
       </c>
       <c r="F272" t="s">
+        <v>115</v>
+      </c>
+      <c r="G272" t="s">
         <v>455</v>
-      </c>
-      <c r="G272" t="s">
-        <v>116</v>
       </c>
     </row>
     <row r="273" spans="1:7">
@@ -7796,17 +7796,17 @@
       <c r="B273" t="s">
         <v>8</v>
       </c>
+      <c r="C273" t="s">
+        <v>453</v>
+      </c>
       <c r="D273" t="s">
-        <v>453</v>
-      </c>
-      <c r="E273" t="s">
         <v>454</v>
       </c>
       <c r="F273" t="s">
+        <v>115</v>
+      </c>
+      <c r="G273" t="s">
         <v>455</v>
-      </c>
-      <c r="G273" t="s">
-        <v>116</v>
       </c>
     </row>
     <row r="274" spans="1:7">
@@ -7816,17 +7816,17 @@
       <c r="B274" t="s">
         <v>8</v>
       </c>
+      <c r="C274" t="s">
+        <v>453</v>
+      </c>
       <c r="D274" t="s">
-        <v>453</v>
-      </c>
-      <c r="E274" t="s">
         <v>454</v>
       </c>
       <c r="F274" t="s">
+        <v>115</v>
+      </c>
+      <c r="G274" t="s">
         <v>455</v>
-      </c>
-      <c r="G274" t="s">
-        <v>116</v>
       </c>
     </row>
     <row r="275" spans="1:7">
@@ -7836,17 +7836,17 @@
       <c r="B275" t="s">
         <v>8</v>
       </c>
+      <c r="C275" t="s">
+        <v>453</v>
+      </c>
       <c r="D275" t="s">
-        <v>453</v>
-      </c>
-      <c r="E275" t="s">
         <v>454</v>
       </c>
       <c r="F275" t="s">
+        <v>115</v>
+      </c>
+      <c r="G275" t="s">
         <v>455</v>
-      </c>
-      <c r="G275" t="s">
-        <v>116</v>
       </c>
     </row>
     <row r="276" spans="1:7">
@@ -7856,17 +7856,17 @@
       <c r="B276" t="s">
         <v>8</v>
       </c>
+      <c r="C276" t="s">
+        <v>453</v>
+      </c>
       <c r="D276" t="s">
-        <v>453</v>
-      </c>
-      <c r="E276" t="s">
         <v>454</v>
       </c>
       <c r="F276" t="s">
+        <v>115</v>
+      </c>
+      <c r="G276" t="s">
         <v>455</v>
-      </c>
-      <c r="G276" t="s">
-        <v>116</v>
       </c>
     </row>
     <row r="277" spans="1:7">
@@ -7876,17 +7876,17 @@
       <c r="B277" t="s">
         <v>8</v>
       </c>
+      <c r="C277" t="s">
+        <v>453</v>
+      </c>
       <c r="D277" t="s">
-        <v>453</v>
-      </c>
-      <c r="E277" t="s">
         <v>454</v>
       </c>
       <c r="F277" t="s">
+        <v>115</v>
+      </c>
+      <c r="G277" t="s">
         <v>455</v>
-      </c>
-      <c r="G277" t="s">
-        <v>116</v>
       </c>
     </row>
     <row r="278" spans="1:7">
@@ -7896,17 +7896,17 @@
       <c r="B278" t="s">
         <v>8</v>
       </c>
+      <c r="C278" t="s">
+        <v>463</v>
+      </c>
       <c r="D278" t="s">
-        <v>463</v>
-      </c>
-      <c r="E278" t="s">
         <v>203</v>
       </c>
       <c r="F278" t="s">
+        <v>183</v>
+      </c>
+      <c r="G278" t="s">
         <v>204</v>
-      </c>
-      <c r="G278" t="s">
-        <v>184</v>
       </c>
     </row>
     <row r="279" spans="1:7">
@@ -7916,17 +7916,17 @@
       <c r="B279" t="s">
         <v>8</v>
       </c>
+      <c r="C279" t="s">
+        <v>463</v>
+      </c>
       <c r="D279" t="s">
-        <v>463</v>
-      </c>
-      <c r="E279" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="F279" t="s">
+        <v>32</v>
+      </c>
+      <c r="G279" t="s">
         <v>54</v>
-      </c>
-      <c r="G279" t="s">
-        <v>33</v>
       </c>
     </row>
     <row r="280" spans="1:7">
@@ -7936,11 +7936,11 @@
       <c r="B280" t="s">
         <v>8</v>
       </c>
+      <c r="C280" t="s">
+        <v>463</v>
+      </c>
       <c r="D280" t="s">
-        <v>463</v>
-      </c>
-      <c r="E280" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F280" t="s">
         <v>12</v>
@@ -7956,17 +7956,17 @@
       <c r="B281" t="s">
         <v>8</v>
       </c>
+      <c r="C281" t="s">
+        <v>463</v>
+      </c>
       <c r="D281" t="s">
-        <v>463</v>
-      </c>
-      <c r="E281" t="s">
         <v>170</v>
       </c>
       <c r="F281" t="s">
+        <v>115</v>
+      </c>
+      <c r="G281" t="s">
         <v>171</v>
-      </c>
-      <c r="G281" t="s">
-        <v>116</v>
       </c>
     </row>
     <row r="282" spans="1:7">
@@ -7976,10 +7976,10 @@
       <c r="B282" t="s">
         <v>8</v>
       </c>
+      <c r="C282" t="s">
+        <v>463</v>
+      </c>
       <c r="D282" t="s">
-        <v>463</v>
-      </c>
-      <c r="E282" t="s">
         <v>124</v>
       </c>
       <c r="F282" t="s">
@@ -7996,17 +7996,17 @@
       <c r="B283" t="s">
         <v>8</v>
       </c>
+      <c r="C283" t="s">
+        <v>469</v>
+      </c>
       <c r="D283" t="s">
-        <v>469</v>
-      </c>
-      <c r="E283" t="s">
+        <v>364</v>
+      </c>
+      <c r="F283" t="s">
+        <v>164</v>
+      </c>
+      <c r="G283" t="s">
         <v>399</v>
-      </c>
-      <c r="F283" t="s">
-        <v>366</v>
-      </c>
-      <c r="G283" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="284" spans="1:7">
@@ -8016,10 +8016,10 @@
       <c r="B284" t="s">
         <v>8</v>
       </c>
+      <c r="C284" t="s">
+        <v>471</v>
+      </c>
       <c r="D284" t="s">
-        <v>471</v>
-      </c>
-      <c r="E284" t="s">
         <v>124</v>
       </c>
       <c r="F284" t="s">
@@ -8036,17 +8036,17 @@
       <c r="B285" t="s">
         <v>8</v>
       </c>
+      <c r="C285" t="s">
+        <v>473</v>
+      </c>
       <c r="D285" t="s">
-        <v>473</v>
-      </c>
-      <c r="E285" t="s">
         <v>170</v>
       </c>
       <c r="F285" t="s">
+        <v>115</v>
+      </c>
+      <c r="G285" t="s">
         <v>171</v>
-      </c>
-      <c r="G285" t="s">
-        <v>116</v>
       </c>
     </row>
     <row r="286" spans="1:7">
@@ -8056,17 +8056,17 @@
       <c r="B286" t="s">
         <v>8</v>
       </c>
+      <c r="C286" t="s">
+        <v>475</v>
+      </c>
       <c r="D286" t="s">
-        <v>475</v>
-      </c>
-      <c r="E286" t="s">
         <v>438</v>
       </c>
       <c r="F286" t="s">
+        <v>183</v>
+      </c>
+      <c r="G286" t="s">
         <v>439</v>
-      </c>
-      <c r="G286" t="s">
-        <v>184</v>
       </c>
     </row>
     <row r="287" spans="1:7">
@@ -8076,17 +8076,17 @@
       <c r="B287" t="s">
         <v>8</v>
       </c>
+      <c r="C287" t="s">
+        <v>475</v>
+      </c>
       <c r="D287" t="s">
-        <v>475</v>
-      </c>
-      <c r="E287" t="s">
         <v>438</v>
       </c>
       <c r="F287" t="s">
+        <v>183</v>
+      </c>
+      <c r="G287" t="s">
         <v>439</v>
-      </c>
-      <c r="G287" t="s">
-        <v>184</v>
       </c>
     </row>
     <row r="288" spans="1:7">
@@ -8096,17 +8096,17 @@
       <c r="B288" t="s">
         <v>8</v>
       </c>
+      <c r="C288" t="s">
+        <v>475</v>
+      </c>
       <c r="D288" t="s">
-        <v>475</v>
-      </c>
-      <c r="E288" t="s">
         <v>41</v>
       </c>
       <c r="F288" t="s">
+        <v>12</v>
+      </c>
+      <c r="G288" t="s">
         <v>42</v>
-      </c>
-      <c r="G288" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="289" spans="1:7">
@@ -8116,10 +8116,10 @@
       <c r="B289" t="s">
         <v>8</v>
       </c>
+      <c r="C289" t="s">
+        <v>475</v>
+      </c>
       <c r="D289" t="s">
-        <v>475</v>
-      </c>
-      <c r="E289" t="s">
         <v>31</v>
       </c>
       <c r="F289" t="s">
@@ -8136,10 +8136,10 @@
       <c r="B290" t="s">
         <v>8</v>
       </c>
+      <c r="C290" t="s">
+        <v>475</v>
+      </c>
       <c r="D290" t="s">
-        <v>475</v>
-      </c>
-      <c r="E290" t="s">
         <v>31</v>
       </c>
       <c r="F290" t="s">
@@ -8156,17 +8156,17 @@
       <c r="B291" t="s">
         <v>8</v>
       </c>
+      <c r="C291" t="s">
+        <v>475</v>
+      </c>
       <c r="D291" t="s">
-        <v>475</v>
-      </c>
-      <c r="E291" t="s">
         <v>170</v>
       </c>
       <c r="F291" t="s">
+        <v>115</v>
+      </c>
+      <c r="G291" t="s">
         <v>171</v>
-      </c>
-      <c r="G291" t="s">
-        <v>116</v>
       </c>
     </row>
     <row r="292" spans="1:7">
@@ -8176,17 +8176,17 @@
       <c r="B292" t="s">
         <v>8</v>
       </c>
+      <c r="C292" t="s">
+        <v>475</v>
+      </c>
       <c r="D292" t="s">
-        <v>475</v>
-      </c>
-      <c r="E292" t="s">
         <v>170</v>
       </c>
       <c r="F292" t="s">
+        <v>115</v>
+      </c>
+      <c r="G292" t="s">
         <v>171</v>
-      </c>
-      <c r="G292" t="s">
-        <v>116</v>
       </c>
     </row>
     <row r="293" spans="1:7">
@@ -8196,17 +8196,17 @@
       <c r="B293" t="s">
         <v>8</v>
       </c>
+      <c r="C293" t="s">
+        <v>475</v>
+      </c>
       <c r="D293" t="s">
-        <v>475</v>
-      </c>
-      <c r="E293" t="s">
         <v>170</v>
       </c>
       <c r="F293" t="s">
+        <v>115</v>
+      </c>
+      <c r="G293" t="s">
         <v>171</v>
-      </c>
-      <c r="G293" t="s">
-        <v>116</v>
       </c>
     </row>
     <row r="294" spans="1:7">
@@ -8216,17 +8216,17 @@
       <c r="B294" t="s">
         <v>8</v>
       </c>
+      <c r="C294" t="s">
+        <v>475</v>
+      </c>
       <c r="D294" t="s">
-        <v>475</v>
-      </c>
-      <c r="E294" t="s">
         <v>170</v>
       </c>
       <c r="F294" t="s">
+        <v>115</v>
+      </c>
+      <c r="G294" t="s">
         <v>171</v>
-      </c>
-      <c r="G294" t="s">
-        <v>116</v>
       </c>
     </row>
     <row r="295" spans="1:7">
@@ -8236,17 +8236,17 @@
       <c r="B295" t="s">
         <v>8</v>
       </c>
+      <c r="C295" t="s">
+        <v>485</v>
+      </c>
       <c r="D295" t="s">
-        <v>485</v>
-      </c>
-      <c r="E295" t="s">
         <v>170</v>
       </c>
       <c r="F295" t="s">
+        <v>115</v>
+      </c>
+      <c r="G295" t="s">
         <v>171</v>
-      </c>
-      <c r="G295" t="s">
-        <v>116</v>
       </c>
     </row>
     <row r="296" spans="1:7">
@@ -8256,17 +8256,17 @@
       <c r="B296" t="s">
         <v>8</v>
       </c>
+      <c r="C296" t="s">
+        <v>485</v>
+      </c>
       <c r="D296" t="s">
-        <v>485</v>
-      </c>
-      <c r="E296" t="s">
         <v>170</v>
       </c>
       <c r="F296" t="s">
+        <v>115</v>
+      </c>
+      <c r="G296" t="s">
         <v>171</v>
-      </c>
-      <c r="G296" t="s">
-        <v>116</v>
       </c>
     </row>
   </sheetData>

--- a/api/2/xlsx/fr/SectorCOFOG.xlsx
+++ b/api/2/xlsx/fr/SectorCOFOG.xlsx
@@ -22,75 +22,75 @@
     <t>status</t>
   </si>
   <si>
+    <t>codeforiati:cofog-class</t>
+  </si>
+  <si>
+    <t>codeforiati:category-code</t>
+  </si>
+  <si>
+    <t>codeforiati:cofog-division</t>
+  </si>
+  <si>
+    <t>codeforiati:cofog-group</t>
+  </si>
+  <si>
     <t>codeforiati:group-code</t>
   </si>
   <si>
-    <t>codeforiati:cofog-group</t>
-  </si>
-  <si>
-    <t>codeforiati:category-code</t>
-  </si>
-  <si>
-    <t>codeforiati:cofog-division</t>
-  </si>
-  <si>
-    <t>codeforiati:cofog-class</t>
-  </si>
-  <si>
     <t>11110</t>
   </si>
   <si>
     <t>active</t>
   </si>
   <si>
+    <t>09.8.0 - Education n.e.c. (CS)</t>
+  </si>
+  <si>
+    <t>111</t>
+  </si>
+  <si>
+    <t>09 - Education</t>
+  </si>
+  <si>
+    <t>09.8 - Education n.e.c.</t>
+  </si>
+  <si>
     <t>110</t>
   </si>
   <si>
-    <t>09.8 - Education n.e.c.</t>
-  </si>
-  <si>
-    <t>111</t>
-  </si>
-  <si>
-    <t>09 - Education</t>
-  </si>
-  <si>
-    <t>09.8.0 - Education n.e.c. (CS)</t>
-  </si>
-  <si>
     <t>11120</t>
   </si>
   <si>
+    <t>09.6.0 - Subsidiary services to education (IS)</t>
+  </si>
+  <si>
     <t>09.6 - Subsidiary services to education</t>
   </si>
   <si>
-    <t>09.6.0 - Subsidiary services to education (IS)</t>
-  </si>
-  <si>
     <t>11130</t>
   </si>
   <si>
     <t>11182</t>
   </si>
   <si>
+    <t>09.7.0 - R&amp;D Education (CS)</t>
+  </si>
+  <si>
     <t>09.7 - R&amp;D Education</t>
   </si>
   <si>
-    <t>09.7.0 - R&amp;D Education (CS)</t>
-  </si>
-  <si>
     <t>11220</t>
   </si>
   <si>
+    <t>09.1.2 - Primary education (IS)</t>
+  </si>
+  <si>
+    <t>112</t>
+  </si>
+  <si>
     <t>09.1 - Pre‐primary and primary education</t>
   </si>
   <si>
-    <t>112</t>
-  </si>
-  <si>
-    <t>09.1.2 - Primary education (IS)</t>
-  </si>
-  <si>
     <t>11230</t>
   </si>
   <si>
@@ -109,99 +109,99 @@
     <t>11250</t>
   </si>
   <si>
+    <t>07.4.0 - Public health services (IS)</t>
+  </si>
+  <si>
+    <t>07 - Health</t>
+  </si>
+  <si>
     <t>07.4 - Public health services</t>
   </si>
   <si>
-    <t>07 - Health</t>
-  </si>
-  <si>
-    <t>07.4.0 - Public health services (IS)</t>
-  </si>
-  <si>
     <t>11260</t>
   </si>
   <si>
+    <t>09.2.1 - Lower‐secondary education (IS)</t>
+  </si>
+  <si>
     <t>09.2 - Secondary education</t>
   </si>
   <si>
-    <t>09.2.1 - Lower‐secondary education (IS)</t>
-  </si>
-  <si>
     <t>11320</t>
   </si>
   <si>
+    <t>09.2.2 - Upper‐secondary education (IS)</t>
+  </si>
+  <si>
     <t>113</t>
   </si>
   <si>
-    <t>09.2.2 - Upper‐secondary education (IS)</t>
-  </si>
-  <si>
     <t>11330</t>
   </si>
   <si>
+    <t>09.5.0 - Education not definable by level (IS)</t>
+  </si>
+  <si>
     <t>09.5 - Education not definable by level</t>
   </si>
   <si>
-    <t>09.5.0 - Education not definable by level (IS)</t>
-  </si>
-  <si>
     <t>11420</t>
   </si>
   <si>
+    <t>09.4.1 - First stage of tertiary education (IS)</t>
+  </si>
+  <si>
+    <t>114</t>
+  </si>
+  <si>
     <t>09.4 - Tertiary education</t>
   </si>
   <si>
-    <t>114</t>
-  </si>
-  <si>
-    <t>09.4.1 - First stage of tertiary education (IS)</t>
-  </si>
-  <si>
     <t>11430</t>
   </si>
   <si>
+    <t>09.3.0 - Post‐secondary non‐tertiary education (IS)</t>
+  </si>
+  <si>
     <t>09.3 - Post‐secondary non‐tertiary education</t>
   </si>
   <si>
-    <t>09.3.0 - Post‐secondary non‐tertiary education (IS)</t>
-  </si>
-  <si>
     <t>12110</t>
   </si>
   <si>
+    <t>07.6.0 - Health n.e.c. (CS)</t>
+  </si>
+  <si>
+    <t>121</t>
+  </si>
+  <si>
+    <t>07.6 - Health n.e.c.</t>
+  </si>
+  <si>
     <t>120</t>
   </si>
   <si>
-    <t>07.6 - Health n.e.c.</t>
-  </si>
-  <si>
-    <t>121</t>
-  </si>
-  <si>
-    <t>07.6.0 - Health n.e.c. (CS)</t>
-  </si>
-  <si>
     <t>12181</t>
   </si>
   <si>
     <t>12182</t>
   </si>
   <si>
+    <t>07.5.0 - R&amp;D Health (CS)</t>
+  </si>
+  <si>
     <t>07.5 - R&amp;D Health</t>
   </si>
   <si>
-    <t>07.5.0 - R&amp;D Health (CS)</t>
-  </si>
-  <si>
     <t>12191</t>
   </si>
   <si>
+    <t>07.2.1 - General medical services (IS)</t>
+  </si>
+  <si>
     <t>07.2 - Outpatient services</t>
   </si>
   <si>
-    <t>07.2.1 - General medical services (IS)</t>
-  </si>
-  <si>
     <t>12196</t>
   </si>
   <si>
@@ -214,12 +214,12 @@
     <t>12230</t>
   </si>
   <si>
+    <t>07.3.1 - General hospital services (IS)</t>
+  </si>
+  <si>
     <t>07.3 - Hospital services</t>
   </si>
   <si>
-    <t>07.3.1 - General hospital services (IS)</t>
-  </si>
-  <si>
     <t>12240</t>
   </si>
   <si>
@@ -286,30 +286,30 @@
     <t>14010</t>
   </si>
   <si>
+    <t>06.3.0 - Water supply (CS)</t>
+  </si>
+  <si>
+    <t>06 - Housing and community amenities</t>
+  </si>
+  <si>
+    <t>06.3 - Water supply</t>
+  </si>
+  <si>
     <t>140</t>
   </si>
   <si>
-    <t>06.3 - Water supply</t>
-  </si>
-  <si>
-    <t>06 - Housing and community amenities</t>
-  </si>
-  <si>
-    <t>06.3.0 - Water supply (CS)</t>
-  </si>
-  <si>
     <t>14015</t>
   </si>
   <si>
+    <t>05.6.0 - Environmental protection n.e.c. (CS)</t>
+  </si>
+  <si>
+    <t>05 - Environmental protection</t>
+  </si>
+  <si>
     <t>05.6 - Environmental protection n.e.c.</t>
   </si>
   <si>
-    <t>05 - Environmental protection</t>
-  </si>
-  <si>
-    <t>05.6.0 - Environmental protection n.e.c. (CS)</t>
-  </si>
-  <si>
     <t>14020</t>
   </si>
   <si>
@@ -319,12 +319,12 @@
     <t>14022</t>
   </si>
   <si>
+    <t>05.2.0 - Waste water management (CS)</t>
+  </si>
+  <si>
     <t>05.2 - Waste water management</t>
   </si>
   <si>
-    <t>05.2.0 - Waste water management (CS)</t>
-  </si>
-  <si>
     <t>14030</t>
   </si>
   <si>
@@ -340,63 +340,63 @@
     <t>14050</t>
   </si>
   <si>
+    <t>05.1.0 - Waste management (CS)</t>
+  </si>
+  <si>
     <t>05.1 - Waste management</t>
   </si>
   <si>
-    <t>05.1.0 - Waste management (CS)</t>
-  </si>
-  <si>
     <t>14081</t>
   </si>
   <si>
     <t>15110</t>
   </si>
   <si>
+    <t>01.3.1 - General personnel services (CS)</t>
+  </si>
+  <si>
+    <t>151</t>
+  </si>
+  <si>
+    <t>01 - General public services</t>
+  </si>
+  <si>
+    <t>01.3 - General services</t>
+  </si>
+  <si>
     <t>150</t>
   </si>
   <si>
-    <t>01.3 - General services</t>
-  </si>
-  <si>
-    <t>151</t>
-  </si>
-  <si>
-    <t>01 - General public services</t>
-  </si>
-  <si>
-    <t>01.3.1 - General personnel services (CS)</t>
-  </si>
-  <si>
     <t>15111</t>
   </si>
   <si>
+    <t>01.1.2 - Financial and fiscal affairs (CS)</t>
+  </si>
+  <si>
     <t>01.1 - Executive and legislative organs, financial and fiscal affairs, external affairs</t>
   </si>
   <si>
-    <t>01.1.2 - Financial and fiscal affairs (CS)</t>
-  </si>
-  <si>
     <t>15112</t>
   </si>
   <si>
+    <t>01.8.0 - Transfers of a general character between different levels of government (CS)</t>
+  </si>
+  <si>
     <t>01.8 - Transfers of a general character between different levels of government</t>
   </si>
   <si>
-    <t>01.8.0 - Transfers of a general character between different levels of government (CS)</t>
-  </si>
-  <si>
     <t>15113</t>
   </si>
   <si>
+    <t>03.6.0 - Public order and safety n.e.c. (CS)</t>
+  </si>
+  <si>
+    <t>03 - Public order and safety</t>
+  </si>
+  <si>
     <t>03.6 - Public order and safety n.e.c.</t>
   </si>
   <si>
-    <t>03 - Public order and safety</t>
-  </si>
-  <si>
-    <t>03.6.0 - Public order and safety n.e.c. (CS)</t>
-  </si>
-  <si>
     <t>15114</t>
   </si>
   <si>
@@ -424,12 +424,12 @@
     <t>15123</t>
   </si>
   <si>
+    <t>01.2.2 - Economic aid routed through international organizations (CS)</t>
+  </si>
+  <si>
     <t>01.2 - Foreign economic aid</t>
   </si>
   <si>
-    <t>01.2.2 - Economic aid routed through international organizations (CS)</t>
-  </si>
-  <si>
     <t>15124</t>
   </si>
   <si>
@@ -460,30 +460,30 @@
     <t>15131</t>
   </si>
   <si>
+    <t>03.3.0 - Law courts (CS)</t>
+  </si>
+  <si>
     <t>03.3 - Law courts</t>
   </si>
   <si>
-    <t>03.3.0 - Law courts (CS)</t>
-  </si>
-  <si>
     <t>15132</t>
   </si>
   <si>
+    <t>03.1.0 - Police services (CS)</t>
+  </si>
+  <si>
     <t>03.1 - Police services</t>
   </si>
   <si>
-    <t>03.1.0 - Police services (CS)</t>
-  </si>
-  <si>
     <t>15133</t>
   </si>
   <si>
+    <t>03.2.0 - Fire‐protection services (CS)</t>
+  </si>
+  <si>
     <t>03.2 - Fire‐protection services</t>
   </si>
   <si>
-    <t>03.2.0 - Fire‐protection services (CS)</t>
-  </si>
-  <si>
     <t>15134</t>
   </si>
   <si>
@@ -496,24 +496,24 @@
     <t>15137</t>
   </si>
   <si>
+    <t>03.4.0 - Prisons (CS)</t>
+  </si>
+  <si>
     <t>03.4 - Prisons</t>
   </si>
   <si>
-    <t>03.4.0 - Prisons (CS)</t>
-  </si>
-  <si>
     <t>15142</t>
   </si>
   <si>
+    <t>04.1.1 - General economic and commercial affairs (CS)</t>
+  </si>
+  <si>
+    <t>04 - Economic affairs</t>
+  </si>
+  <si>
     <t>04.1 - General economic, commercial and labour affairs</t>
   </si>
   <si>
-    <t>04 - Economic affairs</t>
-  </si>
-  <si>
-    <t>04.1.1 - General economic and commercial affairs (CS)</t>
-  </si>
-  <si>
     <t>15143</t>
   </si>
   <si>
@@ -526,12 +526,12 @@
     <t>15151</t>
   </si>
   <si>
+    <t>01.6.0 - General public services n.e.c. (CS)</t>
+  </si>
+  <si>
     <t>01.6 - General public services n.e.c.</t>
   </si>
   <si>
-    <t>01.6.0 - General public services n.e.c. (CS)</t>
-  </si>
-  <si>
     <t>15152</t>
   </si>
   <si>
@@ -541,12 +541,12 @@
     <t>15153</t>
   </si>
   <si>
+    <t>04.6.0 - Communication (CS)</t>
+  </si>
+  <si>
     <t>04.6 - Communication</t>
   </si>
   <si>
-    <t>04.6.0 - Communication (CS)</t>
-  </si>
-  <si>
     <t>15154</t>
   </si>
   <si>
@@ -562,15 +562,15 @@
     <t>15170</t>
   </si>
   <si>
+    <t>10.7.0 - Social exclusion n.e.c. (IS)</t>
+  </si>
+  <si>
+    <t>10 - Social protection</t>
+  </si>
+  <si>
     <t>10.7 - Social exclusion n.e.c.</t>
   </si>
   <si>
-    <t>10 - Social protection</t>
-  </si>
-  <si>
-    <t>10.7.0 - Social exclusion n.e.c. (IS)</t>
-  </si>
-  <si>
     <t>15180</t>
   </si>
   <si>
@@ -583,12 +583,12 @@
     <t>15196</t>
   </si>
   <si>
+    <t>01.5.0 - R&amp;D General public services (CS)</t>
+  </si>
+  <si>
     <t>01.5 - R&amp;D General public services</t>
   </si>
   <si>
-    <t>01.5.0 - R&amp;D General public services (CS)</t>
-  </si>
-  <si>
     <t>15210</t>
   </si>
   <si>
@@ -601,15 +601,15 @@
     <t>15230</t>
   </si>
   <si>
+    <t>02.3.0 - Foreign military aid (CS)</t>
+  </si>
+  <si>
+    <t>02 - Defence</t>
+  </si>
+  <si>
     <t>02.3 - Foreign military aid</t>
   </si>
   <si>
-    <t>02 - Defence</t>
-  </si>
-  <si>
-    <t>02.3.0 - Foreign military aid (CS)</t>
-  </si>
-  <si>
     <t>15240</t>
   </si>
   <si>
@@ -622,15 +622,15 @@
     <t>16010</t>
   </si>
   <si>
+    <t>10.9.0 - Social protection n.e.c. (CS)</t>
+  </si>
+  <si>
+    <t>10.9 - Social protection n.e.c.</t>
+  </si>
+  <si>
     <t>160</t>
   </si>
   <si>
-    <t>10.9 - Social protection n.e.c.</t>
-  </si>
-  <si>
-    <t>10.9.0 - Social protection n.e.c. (CS)</t>
-  </si>
-  <si>
     <t>16011</t>
   </si>
   <si>
@@ -640,12 +640,12 @@
     <t>16013</t>
   </si>
   <si>
+    <t>10.2.0 - Old age (IS)</t>
+  </si>
+  <si>
     <t>10.2 - Old age</t>
   </si>
   <si>
-    <t>10.2.0 - Old age (IS)</t>
-  </si>
-  <si>
     <t>16014</t>
   </si>
   <si>
@@ -655,45 +655,45 @@
     <t>16020</t>
   </si>
   <si>
+    <t>10.5.0 - Unemployment (IS)</t>
+  </si>
+  <si>
     <t>10.5 - Unemployment</t>
   </si>
   <si>
-    <t>10.5.0 - Unemployment (IS)</t>
-  </si>
-  <si>
     <t>16030</t>
   </si>
   <si>
+    <t>06.6.0 - Housing and community amenities n.e.c. (CS)</t>
+  </si>
+  <si>
     <t>06.6 - Housing and community amenities n.e.c.</t>
   </si>
   <si>
-    <t>06.6.0 - Housing and community amenities n.e.c. (CS)</t>
-  </si>
-  <si>
     <t>16040</t>
   </si>
   <si>
+    <t>06.1.0 - Housing development (CS)</t>
+  </si>
+  <si>
     <t>06.1 - Housing development</t>
   </si>
   <si>
-    <t>06.1.0 - Housing development (CS)</t>
-  </si>
-  <si>
     <t>16050</t>
   </si>
   <si>
     <t>16061</t>
   </si>
   <si>
+    <t>08.2.0 - Cultural services (IS)</t>
+  </si>
+  <si>
+    <t>08 - Recreation, culture and religion</t>
+  </si>
+  <si>
     <t>08.2 - Cultural services</t>
   </si>
   <si>
-    <t>08 - Recreation, culture and religion</t>
-  </si>
-  <si>
-    <t>08.2.0 - Cultural services (IS)</t>
-  </si>
-  <si>
     <t>16062</t>
   </si>
   <si>
@@ -706,12 +706,12 @@
     <t>16065</t>
   </si>
   <si>
+    <t>08.1.0 - Recreational and sporting services (IS)</t>
+  </si>
+  <si>
     <t>08.1 - Recreational and sporting services</t>
   </si>
   <si>
-    <t>08.1.0 - Recreational and sporting services (IS)</t>
-  </si>
-  <si>
     <t>16066</t>
   </si>
   <si>
@@ -742,12 +742,12 @@
     <t>21020</t>
   </si>
   <si>
+    <t>04.5.1 - Road transport (CS)</t>
+  </si>
+  <si>
     <t>04.5 - Transport</t>
   </si>
   <si>
-    <t>04.5.1 - Road transport (CS)</t>
-  </si>
-  <si>
     <t>21021</t>
   </si>
   <si>
@@ -781,12 +781,12 @@
     <t>21061</t>
   </si>
   <si>
+    <t>04.7.1 - Distributive trades, storage and warehousing (CS)</t>
+  </si>
+  <si>
     <t>04.7 - Other industries</t>
   </si>
   <si>
-    <t>04.7.1 - Distributive trades, storage and warehousing (CS)</t>
-  </si>
-  <si>
     <t>21081</t>
   </si>
   <si>
@@ -811,42 +811,42 @@
     <t>22030</t>
   </si>
   <si>
+    <t>08.3.0 - Broadcasting and publishing services (CS)</t>
+  </si>
+  <si>
     <t>08.3 - Broadcasting and publishing services</t>
   </si>
   <si>
-    <t>08.3.0 - Broadcasting and publishing services (CS)</t>
-  </si>
-  <si>
     <t>22040</t>
   </si>
   <si>
     <t>23110</t>
   </si>
   <si>
+    <t>04.3.5 - Electricity (CS)</t>
+  </si>
+  <si>
+    <t>231</t>
+  </si>
+  <si>
+    <t>04.3 - Fuel and energy</t>
+  </si>
+  <si>
     <t>230</t>
   </si>
   <si>
-    <t>04.3 - Fuel and energy</t>
-  </si>
-  <si>
-    <t>231</t>
-  </si>
-  <si>
-    <t>04.3.5 - Electricity (CS)</t>
-  </si>
-  <si>
     <t>23111</t>
   </si>
   <si>
     <t>23112</t>
   </si>
   <si>
+    <t>04.8.3 - R&amp;D Fuel and energy (CS)</t>
+  </si>
+  <si>
     <t>04.8 - R&amp;D Economic affairs</t>
   </si>
   <si>
-    <t>04.8.3 - R&amp;D Fuel and energy (CS)</t>
-  </si>
-  <si>
     <t>23181</t>
   </si>
   <si>
@@ -919,12 +919,12 @@
     <t>23510</t>
   </si>
   <si>
+    <t>04.3.3 - Nuclear fuel (CS)</t>
+  </si>
+  <si>
     <t>235</t>
   </si>
   <si>
-    <t>04.3.3 - Nuclear fuel (CS)</t>
-  </si>
-  <si>
     <t>23610</t>
   </si>
   <si>
@@ -991,18 +991,18 @@
     <t>31110</t>
   </si>
   <si>
+    <t>04.2.1 - Agriculture (CS)</t>
+  </si>
+  <si>
+    <t>311</t>
+  </si>
+  <si>
+    <t>04.2 - Agriculture, forestry, fishing and hunting</t>
+  </si>
+  <si>
     <t>310</t>
   </si>
   <si>
-    <t>04.2 - Agriculture, forestry, fishing and hunting</t>
-  </si>
-  <si>
-    <t>311</t>
-  </si>
-  <si>
-    <t>04.2.1 - Agriculture (CS)</t>
-  </si>
-  <si>
     <t>31120</t>
   </si>
   <si>
@@ -1060,12 +1060,12 @@
     <t>31210</t>
   </si>
   <si>
+    <t>04.2.2 - Forestry (CS)</t>
+  </si>
+  <si>
     <t>312</t>
   </si>
   <si>
-    <t>04.2.2 - Forestry (CS)</t>
-  </si>
-  <si>
     <t>31220</t>
   </si>
   <si>
@@ -1084,12 +1084,12 @@
     <t>31310</t>
   </si>
   <si>
+    <t>04.2.3 - Fishing and hunting (CS)</t>
+  </si>
+  <si>
     <t>313</t>
   </si>
   <si>
-    <t>04.2.3 - Fishing and hunting (CS)</t>
-  </si>
-  <si>
     <t>31320</t>
   </si>
   <si>
@@ -1105,18 +1105,18 @@
     <t>32110</t>
   </si>
   <si>
+    <t>04.4.2 - Manufacturing (CS)</t>
+  </si>
+  <si>
+    <t>321</t>
+  </si>
+  <si>
+    <t>04.4 - Mining, manufacturing and construction</t>
+  </si>
+  <si>
     <t>320</t>
   </si>
   <si>
-    <t>04.4 - Mining, manufacturing and construction</t>
-  </si>
-  <si>
-    <t>321</t>
-  </si>
-  <si>
-    <t>04.4.2 - Manufacturing (CS)</t>
-  </si>
-  <si>
     <t>32120</t>
   </si>
   <si>
@@ -1174,12 +1174,12 @@
     <t>32210</t>
   </si>
   <si>
+    <t>04.4.1 - Mining of mineral resources other than mineral fuels (CS)</t>
+  </si>
+  <si>
     <t>322</t>
   </si>
   <si>
-    <t>04.4.1 - Mining of mineral resources other than mineral fuels (CS)</t>
-  </si>
-  <si>
     <t>32220</t>
   </si>
   <si>
@@ -1210,21 +1210,21 @@
     <t>32310</t>
   </si>
   <si>
+    <t>04.4.3 - Construction (CS)</t>
+  </si>
+  <si>
     <t>323</t>
   </si>
   <si>
-    <t>04.4.3 - Construction (CS)</t>
-  </si>
-  <si>
     <t>33110</t>
   </si>
   <si>
+    <t>331</t>
+  </si>
+  <si>
     <t>330</t>
   </si>
   <si>
-    <t>331</t>
-  </si>
-  <si>
     <t>33120</t>
   </si>
   <si>
@@ -1243,12 +1243,12 @@
     <t>33210</t>
   </si>
   <si>
+    <t>04.7.3 - Tourism (CS)</t>
+  </si>
+  <si>
     <t>332</t>
   </si>
   <si>
-    <t>04.7.3 - Tourism (CS)</t>
-  </si>
-  <si>
     <t>41010</t>
   </si>
   <si>
@@ -1261,12 +1261,12 @@
     <t>41030</t>
   </si>
   <si>
+    <t>05.4.0 - Protection of biodiversity and landscape (CS)</t>
+  </si>
+  <si>
     <t>05.4 - Protection of biodiversity and landscape</t>
   </si>
   <si>
-    <t>05.4.0 - Protection of biodiversity and landscape (CS)</t>
-  </si>
-  <si>
     <t>41040</t>
   </si>
   <si>
@@ -1279,27 +1279,27 @@
     <t>43010</t>
   </si>
   <si>
+    <t>04.9.0 - Economic affairs n.e.c. (CS)</t>
+  </si>
+  <si>
+    <t>04.9 - Economic affairs n.e.c.</t>
+  </si>
+  <si>
     <t>430</t>
   </si>
   <si>
-    <t>04.9 - Economic affairs n.e.c.</t>
-  </si>
-  <si>
-    <t>04.9.0 - Economic affairs n.e.c. (CS)</t>
-  </si>
-  <si>
     <t>43030</t>
   </si>
   <si>
     <t>43031</t>
   </si>
   <si>
+    <t>06.2.0 - Community development (CS)</t>
+  </si>
+  <si>
     <t>06.2 - Community development</t>
   </si>
   <si>
-    <t>06.2.0 - Community development (CS)</t>
-  </si>
-  <si>
     <t>43032</t>
   </si>
   <si>
@@ -1318,24 +1318,24 @@
     <t>43060</t>
   </si>
   <si>
+    <t>02.2.0 - Civil defence (CS)</t>
+  </si>
+  <si>
     <t>02.2 - Civil defence</t>
   </si>
   <si>
-    <t>02.2.0 - Civil defence (CS)</t>
-  </si>
-  <si>
     <t>43071</t>
   </si>
   <si>
     <t>43072</t>
   </si>
   <si>
+    <t>10.4.0 - Family and children (IS)</t>
+  </si>
+  <si>
     <t>10.4 - Family and children</t>
   </si>
   <si>
-    <t>10.4.0 - Family and children (IS)</t>
-  </si>
-  <si>
     <t>43073</t>
   </si>
   <si>
@@ -1345,12 +1345,12 @@
     <t>43082</t>
   </si>
   <si>
+    <t>01.4.0 - Basic research (CS)</t>
+  </si>
+  <si>
     <t>01.4 - Basic research</t>
   </si>
   <si>
-    <t>01.4.0 - Basic research (CS)</t>
-  </si>
-  <si>
     <t>51010</t>
   </si>
   <si>
@@ -1375,13 +1375,13 @@
     <t>60010</t>
   </si>
   <si>
+    <t>01.7.0 - Public debt transactions (CS)</t>
+  </si>
+  <si>
+    <t>01.7 - Public debt transactions</t>
+  </si>
+  <si>
     <t>600</t>
-  </si>
-  <si>
-    <t>01.7 - Public debt transactions</t>
-  </si>
-  <si>
-    <t>01.7.0 - Public debt transactions (CS)</t>
   </si>
   <si>
     <t>60020</t>
@@ -1863,19 +1863,19 @@
         <v>8</v>
       </c>
       <c r="C3" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="D3" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="E3" t="s">
         <v>11</v>
       </c>
       <c r="F3" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="G3" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -1909,19 +1909,19 @@
         <v>8</v>
       </c>
       <c r="C5" t="s">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="D5" t="s">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="E5" t="s">
         <v>11</v>
       </c>
       <c r="F5" t="s">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="G5" t="s">
-        <v>20</v>
+        <v>13</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -1932,19 +1932,19 @@
         <v>8</v>
       </c>
       <c r="C6" t="s">
-        <v>9</v>
+        <v>22</v>
       </c>
       <c r="D6" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E6" t="s">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="F6" t="s">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="G6" t="s">
-        <v>24</v>
+        <v>13</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -1958,10 +1958,10 @@
         <v>9</v>
       </c>
       <c r="D7" t="s">
-        <v>10</v>
+        <v>23</v>
       </c>
       <c r="E7" t="s">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="F7" t="s">
         <v>12</v>
@@ -1978,19 +1978,19 @@
         <v>8</v>
       </c>
       <c r="C8" t="s">
-        <v>9</v>
+        <v>22</v>
       </c>
       <c r="D8" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E8" t="s">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="F8" t="s">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="G8" t="s">
-        <v>24</v>
+        <v>13</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -2001,19 +2001,19 @@
         <v>8</v>
       </c>
       <c r="C9" t="s">
-        <v>9</v>
+        <v>22</v>
       </c>
       <c r="D9" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E9" t="s">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="F9" t="s">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="G9" t="s">
-        <v>24</v>
+        <v>13</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -2024,19 +2024,19 @@
         <v>8</v>
       </c>
       <c r="C10" t="s">
-        <v>9</v>
+        <v>29</v>
       </c>
       <c r="D10" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E10" t="s">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="F10" t="s">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="G10" t="s">
-        <v>29</v>
+        <v>13</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -2047,19 +2047,19 @@
         <v>8</v>
       </c>
       <c r="C11" t="s">
-        <v>9</v>
+        <v>31</v>
       </c>
       <c r="D11" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="E11" t="s">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="F11" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G11" t="s">
-        <v>33</v>
+        <v>13</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -2070,19 +2070,19 @@
         <v>8</v>
       </c>
       <c r="C12" t="s">
-        <v>9</v>
+        <v>35</v>
       </c>
       <c r="D12" t="s">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="E12" t="s">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="F12" t="s">
-        <v>12</v>
+        <v>36</v>
       </c>
       <c r="G12" t="s">
-        <v>36</v>
+        <v>13</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -2093,19 +2093,19 @@
         <v>8</v>
       </c>
       <c r="C13" t="s">
-        <v>9</v>
+        <v>38</v>
       </c>
       <c r="D13" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="E13" t="s">
-        <v>38</v>
+        <v>11</v>
       </c>
       <c r="F13" t="s">
-        <v>12</v>
+        <v>36</v>
       </c>
       <c r="G13" t="s">
-        <v>39</v>
+        <v>13</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -2116,19 +2116,19 @@
         <v>8</v>
       </c>
       <c r="C14" t="s">
-        <v>9</v>
+        <v>41</v>
       </c>
       <c r="D14" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="E14" t="s">
-        <v>38</v>
+        <v>11</v>
       </c>
       <c r="F14" t="s">
-        <v>12</v>
+        <v>42</v>
       </c>
       <c r="G14" t="s">
-        <v>42</v>
+        <v>13</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -2139,19 +2139,19 @@
         <v>8</v>
       </c>
       <c r="C15" t="s">
-        <v>9</v>
+        <v>44</v>
       </c>
       <c r="D15" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E15" t="s">
-        <v>45</v>
+        <v>11</v>
       </c>
       <c r="F15" t="s">
-        <v>12</v>
+        <v>46</v>
       </c>
       <c r="G15" t="s">
-        <v>46</v>
+        <v>13</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -2162,19 +2162,19 @@
         <v>8</v>
       </c>
       <c r="C16" t="s">
-        <v>9</v>
+        <v>48</v>
       </c>
       <c r="D16" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="E16" t="s">
-        <v>45</v>
+        <v>11</v>
       </c>
       <c r="F16" t="s">
-        <v>12</v>
+        <v>49</v>
       </c>
       <c r="G16" t="s">
-        <v>49</v>
+        <v>13</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -2191,10 +2191,10 @@
         <v>52</v>
       </c>
       <c r="E17" t="s">
+        <v>32</v>
+      </c>
+      <c r="F17" t="s">
         <v>53</v>
-      </c>
-      <c r="F17" t="s">
-        <v>32</v>
       </c>
       <c r="G17" t="s">
         <v>54</v>
@@ -2214,10 +2214,10 @@
         <v>52</v>
       </c>
       <c r="E18" t="s">
+        <v>32</v>
+      </c>
+      <c r="F18" t="s">
         <v>53</v>
-      </c>
-      <c r="F18" t="s">
-        <v>32</v>
       </c>
       <c r="G18" t="s">
         <v>54</v>
@@ -2231,19 +2231,19 @@
         <v>8</v>
       </c>
       <c r="C19" t="s">
-        <v>51</v>
+        <v>57</v>
       </c>
       <c r="D19" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="E19" t="s">
-        <v>53</v>
+        <v>32</v>
       </c>
       <c r="F19" t="s">
-        <v>32</v>
+        <v>58</v>
       </c>
       <c r="G19" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -2254,19 +2254,19 @@
         <v>8</v>
       </c>
       <c r="C20" t="s">
-        <v>51</v>
+        <v>60</v>
       </c>
       <c r="D20" t="s">
-        <v>60</v>
+        <v>52</v>
       </c>
       <c r="E20" t="s">
-        <v>53</v>
+        <v>32</v>
       </c>
       <c r="F20" t="s">
-        <v>32</v>
+        <v>61</v>
       </c>
       <c r="G20" t="s">
-        <v>61</v>
+        <v>54</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -2283,10 +2283,10 @@
         <v>52</v>
       </c>
       <c r="E21" t="s">
+        <v>32</v>
+      </c>
+      <c r="F21" t="s">
         <v>53</v>
-      </c>
-      <c r="F21" t="s">
-        <v>32</v>
       </c>
       <c r="G21" t="s">
         <v>54</v>
@@ -2300,19 +2300,19 @@
         <v>8</v>
       </c>
       <c r="C22" t="s">
-        <v>51</v>
+        <v>31</v>
       </c>
       <c r="D22" t="s">
-        <v>31</v>
+        <v>64</v>
       </c>
       <c r="E22" t="s">
-        <v>64</v>
+        <v>32</v>
       </c>
       <c r="F22" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G22" t="s">
-        <v>33</v>
+        <v>54</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -2323,19 +2323,19 @@
         <v>8</v>
       </c>
       <c r="C23" t="s">
-        <v>51</v>
+        <v>66</v>
       </c>
       <c r="D23" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="E23" t="s">
-        <v>64</v>
+        <v>32</v>
       </c>
       <c r="F23" t="s">
-        <v>32</v>
+        <v>67</v>
       </c>
       <c r="G23" t="s">
-        <v>67</v>
+        <v>54</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -2346,19 +2346,19 @@
         <v>8</v>
       </c>
       <c r="C24" t="s">
-        <v>51</v>
+        <v>31</v>
       </c>
       <c r="D24" t="s">
-        <v>31</v>
+        <v>64</v>
       </c>
       <c r="E24" t="s">
-        <v>64</v>
+        <v>32</v>
       </c>
       <c r="F24" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G24" t="s">
-        <v>33</v>
+        <v>54</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -2369,19 +2369,19 @@
         <v>8</v>
       </c>
       <c r="C25" t="s">
-        <v>51</v>
+        <v>31</v>
       </c>
       <c r="D25" t="s">
-        <v>31</v>
+        <v>64</v>
       </c>
       <c r="E25" t="s">
-        <v>64</v>
+        <v>32</v>
       </c>
       <c r="F25" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G25" t="s">
-        <v>33</v>
+        <v>54</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -2392,19 +2392,19 @@
         <v>8</v>
       </c>
       <c r="C26" t="s">
-        <v>51</v>
+        <v>31</v>
       </c>
       <c r="D26" t="s">
-        <v>31</v>
+        <v>64</v>
       </c>
       <c r="E26" t="s">
-        <v>64</v>
+        <v>32</v>
       </c>
       <c r="F26" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G26" t="s">
-        <v>33</v>
+        <v>54</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -2415,19 +2415,19 @@
         <v>8</v>
       </c>
       <c r="C27" t="s">
-        <v>51</v>
+        <v>31</v>
       </c>
       <c r="D27" t="s">
-        <v>31</v>
+        <v>64</v>
       </c>
       <c r="E27" t="s">
-        <v>64</v>
+        <v>32</v>
       </c>
       <c r="F27" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G27" t="s">
-        <v>33</v>
+        <v>54</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -2438,19 +2438,19 @@
         <v>8</v>
       </c>
       <c r="C28" t="s">
-        <v>51</v>
+        <v>31</v>
       </c>
       <c r="D28" t="s">
-        <v>31</v>
+        <v>64</v>
       </c>
       <c r="E28" t="s">
-        <v>64</v>
+        <v>32</v>
       </c>
       <c r="F28" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G28" t="s">
-        <v>33</v>
+        <v>54</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -2461,19 +2461,19 @@
         <v>8</v>
       </c>
       <c r="C29" t="s">
-        <v>51</v>
+        <v>31</v>
       </c>
       <c r="D29" t="s">
-        <v>31</v>
+        <v>64</v>
       </c>
       <c r="E29" t="s">
-        <v>64</v>
+        <v>32</v>
       </c>
       <c r="F29" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G29" t="s">
-        <v>33</v>
+        <v>54</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -2487,13 +2487,13 @@
         <v>51</v>
       </c>
       <c r="D30" t="s">
-        <v>52</v>
+        <v>64</v>
       </c>
       <c r="E30" t="s">
-        <v>64</v>
+        <v>32</v>
       </c>
       <c r="F30" t="s">
-        <v>32</v>
+        <v>53</v>
       </c>
       <c r="G30" t="s">
         <v>54</v>
@@ -2507,19 +2507,19 @@
         <v>8</v>
       </c>
       <c r="C31" t="s">
-        <v>51</v>
+        <v>31</v>
       </c>
       <c r="D31" t="s">
-        <v>31</v>
+        <v>76</v>
       </c>
       <c r="E31" t="s">
-        <v>76</v>
+        <v>32</v>
       </c>
       <c r="F31" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G31" t="s">
-        <v>33</v>
+        <v>54</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -2530,19 +2530,19 @@
         <v>8</v>
       </c>
       <c r="C32" t="s">
-        <v>51</v>
+        <v>31</v>
       </c>
       <c r="D32" t="s">
-        <v>31</v>
+        <v>76</v>
       </c>
       <c r="E32" t="s">
-        <v>76</v>
+        <v>32</v>
       </c>
       <c r="F32" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G32" t="s">
-        <v>33</v>
+        <v>54</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -2553,19 +2553,19 @@
         <v>8</v>
       </c>
       <c r="C33" t="s">
-        <v>51</v>
+        <v>31</v>
       </c>
       <c r="D33" t="s">
-        <v>31</v>
+        <v>76</v>
       </c>
       <c r="E33" t="s">
-        <v>76</v>
+        <v>32</v>
       </c>
       <c r="F33" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G33" t="s">
-        <v>33</v>
+        <v>54</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -2576,19 +2576,19 @@
         <v>8</v>
       </c>
       <c r="C34" t="s">
-        <v>51</v>
+        <v>31</v>
       </c>
       <c r="D34" t="s">
-        <v>31</v>
+        <v>76</v>
       </c>
       <c r="E34" t="s">
-        <v>76</v>
+        <v>32</v>
       </c>
       <c r="F34" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G34" t="s">
-        <v>33</v>
+        <v>54</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -2599,19 +2599,19 @@
         <v>8</v>
       </c>
       <c r="C35" t="s">
-        <v>51</v>
+        <v>31</v>
       </c>
       <c r="D35" t="s">
-        <v>31</v>
+        <v>76</v>
       </c>
       <c r="E35" t="s">
-        <v>76</v>
+        <v>32</v>
       </c>
       <c r="F35" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G35" t="s">
-        <v>33</v>
+        <v>54</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -2622,19 +2622,19 @@
         <v>8</v>
       </c>
       <c r="C36" t="s">
-        <v>51</v>
+        <v>57</v>
       </c>
       <c r="D36" t="s">
-        <v>57</v>
+        <v>76</v>
       </c>
       <c r="E36" t="s">
-        <v>76</v>
+        <v>32</v>
       </c>
       <c r="F36" t="s">
-        <v>32</v>
+        <v>58</v>
       </c>
       <c r="G36" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -2645,16 +2645,16 @@
         <v>8</v>
       </c>
       <c r="C37" t="s">
+        <v>31</v>
+      </c>
+      <c r="E37" t="s">
+        <v>32</v>
+      </c>
+      <c r="F37" t="s">
+        <v>33</v>
+      </c>
+      <c r="G37" t="s">
         <v>83</v>
-      </c>
-      <c r="D37" t="s">
-        <v>31</v>
-      </c>
-      <c r="F37" t="s">
-        <v>32</v>
-      </c>
-      <c r="G37" t="s">
-        <v>33</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -2665,16 +2665,16 @@
         <v>8</v>
       </c>
       <c r="C38" t="s">
+        <v>31</v>
+      </c>
+      <c r="E38" t="s">
+        <v>32</v>
+      </c>
+      <c r="F38" t="s">
+        <v>33</v>
+      </c>
+      <c r="G38" t="s">
         <v>83</v>
-      </c>
-      <c r="D38" t="s">
-        <v>31</v>
-      </c>
-      <c r="F38" t="s">
-        <v>32</v>
-      </c>
-      <c r="G38" t="s">
-        <v>33</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -2685,16 +2685,16 @@
         <v>8</v>
       </c>
       <c r="C39" t="s">
+        <v>31</v>
+      </c>
+      <c r="E39" t="s">
+        <v>32</v>
+      </c>
+      <c r="F39" t="s">
+        <v>33</v>
+      </c>
+      <c r="G39" t="s">
         <v>83</v>
-      </c>
-      <c r="D39" t="s">
-        <v>31</v>
-      </c>
-      <c r="F39" t="s">
-        <v>32</v>
-      </c>
-      <c r="G39" t="s">
-        <v>33</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -2705,16 +2705,16 @@
         <v>8</v>
       </c>
       <c r="C40" t="s">
+        <v>31</v>
+      </c>
+      <c r="E40" t="s">
+        <v>32</v>
+      </c>
+      <c r="F40" t="s">
+        <v>33</v>
+      </c>
+      <c r="G40" t="s">
         <v>83</v>
-      </c>
-      <c r="D40" t="s">
-        <v>31</v>
-      </c>
-      <c r="F40" t="s">
-        <v>32</v>
-      </c>
-      <c r="G40" t="s">
-        <v>33</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -2725,16 +2725,16 @@
         <v>8</v>
       </c>
       <c r="C41" t="s">
+        <v>51</v>
+      </c>
+      <c r="E41" t="s">
+        <v>32</v>
+      </c>
+      <c r="F41" t="s">
+        <v>53</v>
+      </c>
+      <c r="G41" t="s">
         <v>83</v>
-      </c>
-      <c r="D41" t="s">
-        <v>52</v>
-      </c>
-      <c r="F41" t="s">
-        <v>32</v>
-      </c>
-      <c r="G41" t="s">
-        <v>54</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -2745,16 +2745,16 @@
         <v>8</v>
       </c>
       <c r="C42" t="s">
+        <v>57</v>
+      </c>
+      <c r="E42" t="s">
+        <v>32</v>
+      </c>
+      <c r="F42" t="s">
+        <v>58</v>
+      </c>
+      <c r="G42" t="s">
         <v>83</v>
-      </c>
-      <c r="D42" t="s">
-        <v>57</v>
-      </c>
-      <c r="F42" t="s">
-        <v>32</v>
-      </c>
-      <c r="G42" t="s">
-        <v>58</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -2767,7 +2767,7 @@
       <c r="C43" t="s">
         <v>90</v>
       </c>
-      <c r="D43" t="s">
+      <c r="E43" t="s">
         <v>91</v>
       </c>
       <c r="F43" t="s">
@@ -2785,16 +2785,16 @@
         <v>8</v>
       </c>
       <c r="C44" t="s">
-        <v>90</v>
-      </c>
-      <c r="D44" t="s">
         <v>95</v>
       </c>
+      <c r="E44" t="s">
+        <v>96</v>
+      </c>
       <c r="F44" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="G44" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -2807,7 +2807,7 @@
       <c r="C45" t="s">
         <v>90</v>
       </c>
-      <c r="D45" t="s">
+      <c r="E45" t="s">
         <v>91</v>
       </c>
       <c r="F45" t="s">
@@ -2827,7 +2827,7 @@
       <c r="C46" t="s">
         <v>90</v>
       </c>
-      <c r="D46" t="s">
+      <c r="E46" t="s">
         <v>91</v>
       </c>
       <c r="F46" t="s">
@@ -2845,16 +2845,16 @@
         <v>8</v>
       </c>
       <c r="C47" t="s">
-        <v>90</v>
-      </c>
-      <c r="D47" t="s">
         <v>101</v>
       </c>
+      <c r="E47" t="s">
+        <v>96</v>
+      </c>
       <c r="F47" t="s">
-        <v>96</v>
+        <v>102</v>
       </c>
       <c r="G47" t="s">
-        <v>102</v>
+        <v>93</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -2867,7 +2867,7 @@
       <c r="C48" t="s">
         <v>90</v>
       </c>
-      <c r="D48" t="s">
+      <c r="E48" t="s">
         <v>91</v>
       </c>
       <c r="F48" t="s">
@@ -2887,7 +2887,7 @@
       <c r="C49" t="s">
         <v>90</v>
       </c>
-      <c r="D49" t="s">
+      <c r="E49" t="s">
         <v>91</v>
       </c>
       <c r="F49" t="s">
@@ -2905,16 +2905,16 @@
         <v>8</v>
       </c>
       <c r="C50" t="s">
-        <v>90</v>
-      </c>
-      <c r="D50" t="s">
         <v>101</v>
       </c>
+      <c r="E50" t="s">
+        <v>96</v>
+      </c>
       <c r="F50" t="s">
-        <v>96</v>
+        <v>102</v>
       </c>
       <c r="G50" t="s">
-        <v>102</v>
+        <v>93</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -2927,7 +2927,7 @@
       <c r="C51" t="s">
         <v>90</v>
       </c>
-      <c r="D51" t="s">
+      <c r="E51" t="s">
         <v>91</v>
       </c>
       <c r="F51" t="s">
@@ -2945,16 +2945,16 @@
         <v>8</v>
       </c>
       <c r="C52" t="s">
-        <v>90</v>
-      </c>
-      <c r="D52" t="s">
         <v>108</v>
       </c>
+      <c r="E52" t="s">
+        <v>96</v>
+      </c>
       <c r="F52" t="s">
-        <v>96</v>
+        <v>109</v>
       </c>
       <c r="G52" t="s">
-        <v>109</v>
+        <v>93</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -2965,16 +2965,16 @@
         <v>8</v>
       </c>
       <c r="C53" t="s">
-        <v>90</v>
-      </c>
-      <c r="D53" t="s">
-        <v>10</v>
+        <v>9</v>
+      </c>
+      <c r="E53" t="s">
+        <v>11</v>
       </c>
       <c r="F53" t="s">
         <v>12</v>
       </c>
       <c r="G53" t="s">
-        <v>13</v>
+        <v>93</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -3008,19 +3008,19 @@
         <v>8</v>
       </c>
       <c r="C55" t="s">
-        <v>112</v>
+        <v>118</v>
       </c>
       <c r="D55" t="s">
-        <v>118</v>
+        <v>113</v>
       </c>
       <c r="E55" t="s">
         <v>114</v>
       </c>
       <c r="F55" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="G55" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -3031,19 +3031,19 @@
         <v>8</v>
       </c>
       <c r="C56" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="D56" t="s">
-        <v>121</v>
+        <v>113</v>
       </c>
       <c r="E56" t="s">
         <v>114</v>
       </c>
       <c r="F56" t="s">
-        <v>115</v>
+        <v>122</v>
       </c>
       <c r="G56" t="s">
-        <v>122</v>
+        <v>116</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -3054,19 +3054,19 @@
         <v>8</v>
       </c>
       <c r="C57" t="s">
-        <v>112</v>
+        <v>124</v>
       </c>
       <c r="D57" t="s">
-        <v>124</v>
+        <v>113</v>
       </c>
       <c r="E57" t="s">
-        <v>114</v>
+        <v>125</v>
       </c>
       <c r="F57" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="G57" t="s">
-        <v>126</v>
+        <v>116</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -3077,19 +3077,19 @@
         <v>8</v>
       </c>
       <c r="C58" t="s">
-        <v>112</v>
+        <v>118</v>
       </c>
       <c r="D58" t="s">
-        <v>118</v>
+        <v>113</v>
       </c>
       <c r="E58" t="s">
         <v>114</v>
       </c>
       <c r="F58" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="G58" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -3100,19 +3100,19 @@
         <v>8</v>
       </c>
       <c r="C59" t="s">
-        <v>112</v>
+        <v>118</v>
       </c>
       <c r="D59" t="s">
-        <v>118</v>
+        <v>113</v>
       </c>
       <c r="E59" t="s">
         <v>114</v>
       </c>
       <c r="F59" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="G59" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -3123,19 +3123,19 @@
         <v>8</v>
       </c>
       <c r="C60" t="s">
-        <v>112</v>
+        <v>118</v>
       </c>
       <c r="D60" t="s">
-        <v>118</v>
+        <v>113</v>
       </c>
       <c r="E60" t="s">
         <v>114</v>
       </c>
       <c r="F60" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="G60" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -3146,19 +3146,19 @@
         <v>8</v>
       </c>
       <c r="C61" t="s">
-        <v>112</v>
+        <v>118</v>
       </c>
       <c r="D61" t="s">
-        <v>118</v>
+        <v>113</v>
       </c>
       <c r="E61" t="s">
         <v>114</v>
       </c>
       <c r="F61" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="G61" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -3169,19 +3169,19 @@
         <v>8</v>
       </c>
       <c r="C62" t="s">
-        <v>112</v>
+        <v>118</v>
       </c>
       <c r="D62" t="s">
-        <v>118</v>
+        <v>113</v>
       </c>
       <c r="E62" t="s">
         <v>114</v>
       </c>
       <c r="F62" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="G62" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -3192,19 +3192,19 @@
         <v>8</v>
       </c>
       <c r="C63" t="s">
-        <v>112</v>
+        <v>133</v>
       </c>
       <c r="D63" t="s">
-        <v>118</v>
+        <v>113</v>
       </c>
       <c r="E63" t="s">
         <v>114</v>
       </c>
       <c r="F63" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="G63" t="s">
-        <v>133</v>
+        <v>116</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -3215,19 +3215,19 @@
         <v>8</v>
       </c>
       <c r="C64" t="s">
-        <v>112</v>
+        <v>133</v>
       </c>
       <c r="D64" t="s">
-        <v>118</v>
+        <v>113</v>
       </c>
       <c r="E64" t="s">
         <v>114</v>
       </c>
       <c r="F64" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="G64" t="s">
-        <v>133</v>
+        <v>116</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -3238,19 +3238,19 @@
         <v>8</v>
       </c>
       <c r="C65" t="s">
-        <v>112</v>
+        <v>136</v>
       </c>
       <c r="D65" t="s">
-        <v>136</v>
+        <v>113</v>
       </c>
       <c r="E65" t="s">
         <v>114</v>
       </c>
       <c r="F65" t="s">
-        <v>115</v>
+        <v>137</v>
       </c>
       <c r="G65" t="s">
-        <v>137</v>
+        <v>116</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -3284,19 +3284,19 @@
         <v>8</v>
       </c>
       <c r="C67" t="s">
-        <v>112</v>
+        <v>118</v>
       </c>
       <c r="D67" t="s">
-        <v>118</v>
+        <v>113</v>
       </c>
       <c r="E67" t="s">
         <v>114</v>
       </c>
       <c r="F67" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="G67" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -3307,7 +3307,7 @@
         <v>8</v>
       </c>
       <c r="C68" t="s">
-        <v>112</v>
+        <v>141</v>
       </c>
       <c r="D68" t="s">
         <v>113</v>
@@ -3319,7 +3319,7 @@
         <v>115</v>
       </c>
       <c r="G68" t="s">
-        <v>141</v>
+        <v>116</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -3330,7 +3330,7 @@
         <v>8</v>
       </c>
       <c r="C69" t="s">
-        <v>112</v>
+        <v>143</v>
       </c>
       <c r="D69" t="s">
         <v>113</v>
@@ -3342,7 +3342,7 @@
         <v>115</v>
       </c>
       <c r="G69" t="s">
-        <v>143</v>
+        <v>116</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -3353,19 +3353,19 @@
         <v>8</v>
       </c>
       <c r="C70" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="D70" t="s">
-        <v>121</v>
+        <v>113</v>
       </c>
       <c r="E70" t="s">
         <v>114</v>
       </c>
       <c r="F70" t="s">
-        <v>115</v>
+        <v>122</v>
       </c>
       <c r="G70" t="s">
-        <v>122</v>
+        <v>116</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -3376,19 +3376,19 @@
         <v>8</v>
       </c>
       <c r="C71" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="D71" t="s">
-        <v>121</v>
+        <v>113</v>
       </c>
       <c r="E71" t="s">
         <v>114</v>
       </c>
       <c r="F71" t="s">
-        <v>115</v>
+        <v>122</v>
       </c>
       <c r="G71" t="s">
-        <v>122</v>
+        <v>116</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -3422,19 +3422,19 @@
         <v>8</v>
       </c>
       <c r="C73" t="s">
-        <v>112</v>
+        <v>148</v>
       </c>
       <c r="D73" t="s">
-        <v>148</v>
+        <v>113</v>
       </c>
       <c r="E73" t="s">
-        <v>114</v>
+        <v>125</v>
       </c>
       <c r="F73" t="s">
-        <v>125</v>
+        <v>149</v>
       </c>
       <c r="G73" t="s">
-        <v>149</v>
+        <v>116</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -3445,19 +3445,19 @@
         <v>8</v>
       </c>
       <c r="C74" t="s">
-        <v>112</v>
+        <v>151</v>
       </c>
       <c r="D74" t="s">
-        <v>151</v>
+        <v>113</v>
       </c>
       <c r="E74" t="s">
-        <v>114</v>
+        <v>125</v>
       </c>
       <c r="F74" t="s">
-        <v>125</v>
+        <v>152</v>
       </c>
       <c r="G74" t="s">
-        <v>152</v>
+        <v>116</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -3468,19 +3468,19 @@
         <v>8</v>
       </c>
       <c r="C75" t="s">
-        <v>112</v>
+        <v>154</v>
       </c>
       <c r="D75" t="s">
-        <v>154</v>
+        <v>113</v>
       </c>
       <c r="E75" t="s">
-        <v>114</v>
+        <v>125</v>
       </c>
       <c r="F75" t="s">
-        <v>125</v>
+        <v>155</v>
       </c>
       <c r="G75" t="s">
-        <v>155</v>
+        <v>116</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -3491,19 +3491,19 @@
         <v>8</v>
       </c>
       <c r="C76" t="s">
-        <v>112</v>
+        <v>148</v>
       </c>
       <c r="D76" t="s">
-        <v>148</v>
+        <v>113</v>
       </c>
       <c r="E76" t="s">
-        <v>114</v>
+        <v>125</v>
       </c>
       <c r="F76" t="s">
-        <v>125</v>
+        <v>149</v>
       </c>
       <c r="G76" t="s">
-        <v>149</v>
+        <v>116</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -3514,19 +3514,19 @@
         <v>8</v>
       </c>
       <c r="C77" t="s">
-        <v>112</v>
+        <v>148</v>
       </c>
       <c r="D77" t="s">
-        <v>148</v>
+        <v>113</v>
       </c>
       <c r="E77" t="s">
-        <v>114</v>
+        <v>125</v>
       </c>
       <c r="F77" t="s">
-        <v>125</v>
+        <v>149</v>
       </c>
       <c r="G77" t="s">
-        <v>149</v>
+        <v>116</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -3537,19 +3537,19 @@
         <v>8</v>
       </c>
       <c r="C78" t="s">
-        <v>112</v>
+        <v>151</v>
       </c>
       <c r="D78" t="s">
-        <v>151</v>
+        <v>113</v>
       </c>
       <c r="E78" t="s">
-        <v>114</v>
+        <v>125</v>
       </c>
       <c r="F78" t="s">
-        <v>125</v>
+        <v>152</v>
       </c>
       <c r="G78" t="s">
-        <v>152</v>
+        <v>116</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -3560,19 +3560,19 @@
         <v>8</v>
       </c>
       <c r="C79" t="s">
-        <v>112</v>
+        <v>160</v>
       </c>
       <c r="D79" t="s">
-        <v>160</v>
+        <v>113</v>
       </c>
       <c r="E79" t="s">
-        <v>114</v>
+        <v>125</v>
       </c>
       <c r="F79" t="s">
-        <v>125</v>
+        <v>161</v>
       </c>
       <c r="G79" t="s">
-        <v>161</v>
+        <v>116</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -3583,19 +3583,19 @@
         <v>8</v>
       </c>
       <c r="C80" t="s">
-        <v>112</v>
+        <v>163</v>
       </c>
       <c r="D80" t="s">
-        <v>163</v>
+        <v>113</v>
       </c>
       <c r="E80" t="s">
-        <v>114</v>
+        <v>164</v>
       </c>
       <c r="F80" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="G80" t="s">
-        <v>165</v>
+        <v>116</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -3606,19 +3606,19 @@
         <v>8</v>
       </c>
       <c r="C81" t="s">
-        <v>112</v>
+        <v>163</v>
       </c>
       <c r="D81" t="s">
-        <v>163</v>
+        <v>113</v>
       </c>
       <c r="E81" t="s">
-        <v>114</v>
+        <v>164</v>
       </c>
       <c r="F81" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="G81" t="s">
-        <v>165</v>
+        <v>116</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -3629,19 +3629,19 @@
         <v>8</v>
       </c>
       <c r="C82" t="s">
-        <v>112</v>
+        <v>163</v>
       </c>
       <c r="D82" t="s">
-        <v>163</v>
+        <v>113</v>
       </c>
       <c r="E82" t="s">
-        <v>114</v>
+        <v>164</v>
       </c>
       <c r="F82" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="G82" t="s">
-        <v>165</v>
+        <v>116</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -3652,7 +3652,7 @@
         <v>8</v>
       </c>
       <c r="C83" t="s">
-        <v>112</v>
+        <v>143</v>
       </c>
       <c r="D83" t="s">
         <v>113</v>
@@ -3664,7 +3664,7 @@
         <v>115</v>
       </c>
       <c r="G83" t="s">
-        <v>143</v>
+        <v>116</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -3675,19 +3675,19 @@
         <v>8</v>
       </c>
       <c r="C84" t="s">
-        <v>112</v>
+        <v>170</v>
       </c>
       <c r="D84" t="s">
-        <v>170</v>
+        <v>113</v>
       </c>
       <c r="E84" t="s">
         <v>114</v>
       </c>
       <c r="F84" t="s">
-        <v>115</v>
+        <v>171</v>
       </c>
       <c r="G84" t="s">
-        <v>171</v>
+        <v>116</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -3698,19 +3698,19 @@
         <v>8</v>
       </c>
       <c r="C85" t="s">
-        <v>112</v>
+        <v>173</v>
       </c>
       <c r="D85" t="s">
-        <v>118</v>
+        <v>113</v>
       </c>
       <c r="E85" t="s">
         <v>114</v>
       </c>
       <c r="F85" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="G85" t="s">
-        <v>173</v>
+        <v>116</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -3721,19 +3721,19 @@
         <v>8</v>
       </c>
       <c r="C86" t="s">
-        <v>112</v>
+        <v>175</v>
       </c>
       <c r="D86" t="s">
-        <v>175</v>
+        <v>113</v>
       </c>
       <c r="E86" t="s">
-        <v>114</v>
+        <v>164</v>
       </c>
       <c r="F86" t="s">
-        <v>164</v>
+        <v>176</v>
       </c>
       <c r="G86" t="s">
-        <v>176</v>
+        <v>116</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -3744,19 +3744,19 @@
         <v>8</v>
       </c>
       <c r="C87" t="s">
-        <v>112</v>
+        <v>173</v>
       </c>
       <c r="D87" t="s">
-        <v>118</v>
+        <v>113</v>
       </c>
       <c r="E87" t="s">
         <v>114</v>
       </c>
       <c r="F87" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="G87" t="s">
-        <v>173</v>
+        <v>116</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -3767,19 +3767,19 @@
         <v>8</v>
       </c>
       <c r="C88" t="s">
-        <v>112</v>
+        <v>118</v>
       </c>
       <c r="D88" t="s">
-        <v>118</v>
+        <v>113</v>
       </c>
       <c r="E88" t="s">
         <v>114</v>
       </c>
       <c r="F88" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="G88" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -3790,19 +3790,19 @@
         <v>8</v>
       </c>
       <c r="C89" t="s">
-        <v>112</v>
+        <v>118</v>
       </c>
       <c r="D89" t="s">
-        <v>118</v>
+        <v>113</v>
       </c>
       <c r="E89" t="s">
         <v>114</v>
       </c>
       <c r="F89" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="G89" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -3813,19 +3813,19 @@
         <v>8</v>
       </c>
       <c r="C90" t="s">
-        <v>112</v>
+        <v>124</v>
       </c>
       <c r="D90" t="s">
-        <v>124</v>
+        <v>113</v>
       </c>
       <c r="E90" t="s">
-        <v>114</v>
+        <v>125</v>
       </c>
       <c r="F90" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="G90" t="s">
-        <v>126</v>
+        <v>116</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -3836,19 +3836,19 @@
         <v>8</v>
       </c>
       <c r="C91" t="s">
-        <v>112</v>
+        <v>182</v>
       </c>
       <c r="D91" t="s">
-        <v>182</v>
+        <v>113</v>
       </c>
       <c r="E91" t="s">
-        <v>114</v>
+        <v>183</v>
       </c>
       <c r="F91" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="G91" t="s">
-        <v>184</v>
+        <v>116</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -3859,19 +3859,19 @@
         <v>8</v>
       </c>
       <c r="C92" t="s">
-        <v>112</v>
+        <v>124</v>
       </c>
       <c r="D92" t="s">
-        <v>124</v>
+        <v>113</v>
       </c>
       <c r="E92" t="s">
-        <v>114</v>
+        <v>125</v>
       </c>
       <c r="F92" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="G92" t="s">
-        <v>126</v>
+        <v>116</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -3882,19 +3882,19 @@
         <v>8</v>
       </c>
       <c r="C93" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="D93" t="s">
-        <v>121</v>
+        <v>113</v>
       </c>
       <c r="E93" t="s">
         <v>114</v>
       </c>
       <c r="F93" t="s">
-        <v>115</v>
+        <v>122</v>
       </c>
       <c r="G93" t="s">
-        <v>122</v>
+        <v>116</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -3905,19 +3905,19 @@
         <v>8</v>
       </c>
       <c r="C94" t="s">
-        <v>112</v>
+        <v>124</v>
       </c>
       <c r="D94" t="s">
-        <v>124</v>
+        <v>113</v>
       </c>
       <c r="E94" t="s">
-        <v>114</v>
+        <v>125</v>
       </c>
       <c r="F94" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="G94" t="s">
-        <v>126</v>
+        <v>116</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -3928,19 +3928,19 @@
         <v>8</v>
       </c>
       <c r="C95" t="s">
-        <v>112</v>
+        <v>189</v>
       </c>
       <c r="D95" t="s">
-        <v>189</v>
+        <v>113</v>
       </c>
       <c r="E95" t="s">
         <v>114</v>
       </c>
       <c r="F95" t="s">
-        <v>115</v>
+        <v>190</v>
       </c>
       <c r="G95" t="s">
-        <v>190</v>
+        <v>116</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -3951,19 +3951,19 @@
         <v>8</v>
       </c>
       <c r="C96" t="s">
-        <v>112</v>
+        <v>124</v>
       </c>
       <c r="D96" t="s">
-        <v>124</v>
+        <v>192</v>
       </c>
       <c r="E96" t="s">
-        <v>192</v>
+        <v>125</v>
       </c>
       <c r="F96" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="G96" t="s">
-        <v>126</v>
+        <v>116</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -3974,19 +3974,19 @@
         <v>8</v>
       </c>
       <c r="C97" t="s">
-        <v>112</v>
+        <v>124</v>
       </c>
       <c r="D97" t="s">
-        <v>124</v>
+        <v>192</v>
       </c>
       <c r="E97" t="s">
-        <v>192</v>
+        <v>125</v>
       </c>
       <c r="F97" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="G97" t="s">
-        <v>126</v>
+        <v>116</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -3997,19 +3997,19 @@
         <v>8</v>
       </c>
       <c r="C98" t="s">
-        <v>112</v>
+        <v>195</v>
       </c>
       <c r="D98" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="E98" t="s">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="F98" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="G98" t="s">
-        <v>197</v>
+        <v>116</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -4020,19 +4020,19 @@
         <v>8</v>
       </c>
       <c r="C99" t="s">
-        <v>112</v>
+        <v>124</v>
       </c>
       <c r="D99" t="s">
-        <v>124</v>
+        <v>192</v>
       </c>
       <c r="E99" t="s">
-        <v>192</v>
+        <v>125</v>
       </c>
       <c r="F99" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="G99" t="s">
-        <v>126</v>
+        <v>116</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -4043,19 +4043,19 @@
         <v>8</v>
       </c>
       <c r="C100" t="s">
-        <v>112</v>
+        <v>154</v>
       </c>
       <c r="D100" t="s">
-        <v>154</v>
+        <v>192</v>
       </c>
       <c r="E100" t="s">
-        <v>192</v>
+        <v>125</v>
       </c>
       <c r="F100" t="s">
-        <v>125</v>
+        <v>155</v>
       </c>
       <c r="G100" t="s">
-        <v>155</v>
+        <v>116</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -4066,19 +4066,19 @@
         <v>8</v>
       </c>
       <c r="C101" t="s">
-        <v>112</v>
+        <v>124</v>
       </c>
       <c r="D101" t="s">
-        <v>124</v>
+        <v>192</v>
       </c>
       <c r="E101" t="s">
-        <v>192</v>
+        <v>125</v>
       </c>
       <c r="F101" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="G101" t="s">
-        <v>126</v>
+        <v>116</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -4091,11 +4091,11 @@
       <c r="C102" t="s">
         <v>202</v>
       </c>
-      <c r="D102" t="s">
+      <c r="E102" t="s">
+        <v>183</v>
+      </c>
+      <c r="F102" t="s">
         <v>203</v>
-      </c>
-      <c r="F102" t="s">
-        <v>183</v>
       </c>
       <c r="G102" t="s">
         <v>204</v>
@@ -4111,11 +4111,11 @@
       <c r="C103" t="s">
         <v>202</v>
       </c>
-      <c r="D103" t="s">
+      <c r="E103" t="s">
+        <v>183</v>
+      </c>
+      <c r="F103" t="s">
         <v>203</v>
-      </c>
-      <c r="F103" t="s">
-        <v>183</v>
       </c>
       <c r="G103" t="s">
         <v>204</v>
@@ -4131,11 +4131,11 @@
       <c r="C104" t="s">
         <v>202</v>
       </c>
-      <c r="D104" t="s">
+      <c r="E104" t="s">
+        <v>183</v>
+      </c>
+      <c r="F104" t="s">
         <v>203</v>
-      </c>
-      <c r="F104" t="s">
-        <v>183</v>
       </c>
       <c r="G104" t="s">
         <v>204</v>
@@ -4149,16 +4149,16 @@
         <v>8</v>
       </c>
       <c r="C105" t="s">
-        <v>202</v>
-      </c>
-      <c r="D105" t="s">
         <v>208</v>
       </c>
+      <c r="E105" t="s">
+        <v>183</v>
+      </c>
       <c r="F105" t="s">
-        <v>183</v>
+        <v>209</v>
       </c>
       <c r="G105" t="s">
-        <v>209</v>
+        <v>204</v>
       </c>
     </row>
     <row r="106" spans="1:7">
@@ -4171,11 +4171,11 @@
       <c r="C106" t="s">
         <v>202</v>
       </c>
-      <c r="D106" t="s">
+      <c r="E106" t="s">
+        <v>183</v>
+      </c>
+      <c r="F106" t="s">
         <v>203</v>
-      </c>
-      <c r="F106" t="s">
-        <v>183</v>
       </c>
       <c r="G106" t="s">
         <v>204</v>
@@ -4189,16 +4189,16 @@
         <v>8</v>
       </c>
       <c r="C107" t="s">
-        <v>202</v>
-      </c>
-      <c r="D107" t="s">
         <v>182</v>
       </c>
+      <c r="E107" t="s">
+        <v>183</v>
+      </c>
       <c r="F107" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="G107" t="s">
-        <v>184</v>
+        <v>204</v>
       </c>
     </row>
     <row r="108" spans="1:7">
@@ -4209,16 +4209,16 @@
         <v>8</v>
       </c>
       <c r="C108" t="s">
-        <v>202</v>
-      </c>
-      <c r="D108" t="s">
         <v>213</v>
       </c>
+      <c r="E108" t="s">
+        <v>183</v>
+      </c>
       <c r="F108" t="s">
-        <v>183</v>
+        <v>214</v>
       </c>
       <c r="G108" t="s">
-        <v>214</v>
+        <v>204</v>
       </c>
     </row>
     <row r="109" spans="1:7">
@@ -4229,16 +4229,16 @@
         <v>8</v>
       </c>
       <c r="C109" t="s">
-        <v>202</v>
-      </c>
-      <c r="D109" t="s">
         <v>216</v>
       </c>
+      <c r="E109" t="s">
+        <v>91</v>
+      </c>
       <c r="F109" t="s">
-        <v>92</v>
+        <v>217</v>
       </c>
       <c r="G109" t="s">
-        <v>217</v>
+        <v>204</v>
       </c>
     </row>
     <row r="110" spans="1:7">
@@ -4249,16 +4249,16 @@
         <v>8</v>
       </c>
       <c r="C110" t="s">
-        <v>202</v>
-      </c>
-      <c r="D110" t="s">
         <v>219</v>
       </c>
+      <c r="E110" t="s">
+        <v>91</v>
+      </c>
       <c r="F110" t="s">
-        <v>92</v>
+        <v>220</v>
       </c>
       <c r="G110" t="s">
-        <v>220</v>
+        <v>204</v>
       </c>
     </row>
     <row r="111" spans="1:7">
@@ -4271,11 +4271,11 @@
       <c r="C111" t="s">
         <v>202</v>
       </c>
-      <c r="D111" t="s">
+      <c r="E111" t="s">
+        <v>183</v>
+      </c>
+      <c r="F111" t="s">
         <v>203</v>
-      </c>
-      <c r="F111" t="s">
-        <v>183</v>
       </c>
       <c r="G111" t="s">
         <v>204</v>
@@ -4289,16 +4289,16 @@
         <v>8</v>
       </c>
       <c r="C112" t="s">
-        <v>202</v>
-      </c>
-      <c r="D112" t="s">
         <v>223</v>
       </c>
+      <c r="E112" t="s">
+        <v>224</v>
+      </c>
       <c r="F112" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="G112" t="s">
-        <v>225</v>
+        <v>204</v>
       </c>
     </row>
     <row r="113" spans="1:7">
@@ -4309,16 +4309,16 @@
         <v>8</v>
       </c>
       <c r="C113" t="s">
-        <v>202</v>
-      </c>
-      <c r="D113" t="s">
-        <v>113</v>
+        <v>143</v>
+      </c>
+      <c r="E113" t="s">
+        <v>114</v>
       </c>
       <c r="F113" t="s">
         <v>115</v>
       </c>
       <c r="G113" t="s">
-        <v>143</v>
+        <v>204</v>
       </c>
     </row>
     <row r="114" spans="1:7">
@@ -4329,16 +4329,16 @@
         <v>8</v>
       </c>
       <c r="C114" t="s">
-        <v>202</v>
-      </c>
-      <c r="D114" t="s">
         <v>151</v>
       </c>
+      <c r="E114" t="s">
+        <v>125</v>
+      </c>
       <c r="F114" t="s">
-        <v>125</v>
+        <v>152</v>
       </c>
       <c r="G114" t="s">
-        <v>152</v>
+        <v>204</v>
       </c>
     </row>
     <row r="115" spans="1:7">
@@ -4349,16 +4349,16 @@
         <v>8</v>
       </c>
       <c r="C115" t="s">
-        <v>202</v>
-      </c>
-      <c r="D115" t="s">
         <v>182</v>
       </c>
+      <c r="E115" t="s">
+        <v>183</v>
+      </c>
       <c r="F115" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="G115" t="s">
-        <v>184</v>
+        <v>204</v>
       </c>
     </row>
     <row r="116" spans="1:7">
@@ -4369,16 +4369,16 @@
         <v>8</v>
       </c>
       <c r="C116" t="s">
-        <v>202</v>
-      </c>
-      <c r="D116" t="s">
         <v>230</v>
       </c>
+      <c r="E116" t="s">
+        <v>224</v>
+      </c>
       <c r="F116" t="s">
-        <v>224</v>
+        <v>231</v>
       </c>
       <c r="G116" t="s">
-        <v>231</v>
+        <v>204</v>
       </c>
     </row>
     <row r="117" spans="1:7">
@@ -4389,16 +4389,16 @@
         <v>8</v>
       </c>
       <c r="C117" t="s">
-        <v>202</v>
-      </c>
-      <c r="D117" t="s">
         <v>223</v>
       </c>
+      <c r="E117" t="s">
+        <v>224</v>
+      </c>
       <c r="F117" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="G117" t="s">
-        <v>225</v>
+        <v>204</v>
       </c>
     </row>
     <row r="118" spans="1:7">
@@ -4409,16 +4409,16 @@
         <v>8</v>
       </c>
       <c r="C118" t="s">
-        <v>202</v>
-      </c>
-      <c r="D118" t="s">
-        <v>163</v>
+        <v>234</v>
+      </c>
+      <c r="E118" t="s">
+        <v>164</v>
       </c>
       <c r="F118" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="G118" t="s">
-        <v>234</v>
+        <v>204</v>
       </c>
     </row>
     <row r="119" spans="1:7">
@@ -4429,16 +4429,16 @@
         <v>8</v>
       </c>
       <c r="C119" t="s">
-        <v>202</v>
-      </c>
-      <c r="D119" t="s">
         <v>182</v>
       </c>
+      <c r="E119" t="s">
+        <v>183</v>
+      </c>
       <c r="F119" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="G119" t="s">
-        <v>184</v>
+        <v>204</v>
       </c>
     </row>
     <row r="120" spans="1:7">
@@ -4449,16 +4449,16 @@
         <v>8</v>
       </c>
       <c r="C120" t="s">
+        <v>170</v>
+      </c>
+      <c r="E120" t="s">
+        <v>114</v>
+      </c>
+      <c r="F120" t="s">
+        <v>171</v>
+      </c>
+      <c r="G120" t="s">
         <v>237</v>
-      </c>
-      <c r="D120" t="s">
-        <v>170</v>
-      </c>
-      <c r="F120" t="s">
-        <v>115</v>
-      </c>
-      <c r="G120" t="s">
-        <v>171</v>
       </c>
     </row>
     <row r="121" spans="1:7">
@@ -4469,16 +4469,16 @@
         <v>8</v>
       </c>
       <c r="C121" t="s">
-        <v>237</v>
-      </c>
-      <c r="D121" t="s">
-        <v>113</v>
+        <v>143</v>
+      </c>
+      <c r="E121" t="s">
+        <v>114</v>
       </c>
       <c r="F121" t="s">
         <v>115</v>
       </c>
       <c r="G121" t="s">
-        <v>143</v>
+        <v>237</v>
       </c>
     </row>
     <row r="122" spans="1:7">
@@ -4489,16 +4489,16 @@
         <v>8</v>
       </c>
       <c r="C122" t="s">
+        <v>170</v>
+      </c>
+      <c r="E122" t="s">
+        <v>114</v>
+      </c>
+      <c r="F122" t="s">
+        <v>171</v>
+      </c>
+      <c r="G122" t="s">
         <v>237</v>
-      </c>
-      <c r="D122" t="s">
-        <v>170</v>
-      </c>
-      <c r="F122" t="s">
-        <v>115</v>
-      </c>
-      <c r="G122" t="s">
-        <v>171</v>
       </c>
     </row>
     <row r="123" spans="1:7">
@@ -4509,16 +4509,16 @@
         <v>8</v>
       </c>
       <c r="C123" t="s">
+        <v>170</v>
+      </c>
+      <c r="E123" t="s">
+        <v>114</v>
+      </c>
+      <c r="F123" t="s">
+        <v>171</v>
+      </c>
+      <c r="G123" t="s">
         <v>237</v>
-      </c>
-      <c r="D123" t="s">
-        <v>170</v>
-      </c>
-      <c r="F123" t="s">
-        <v>115</v>
-      </c>
-      <c r="G123" t="s">
-        <v>171</v>
       </c>
     </row>
     <row r="124" spans="1:7">
@@ -4529,16 +4529,16 @@
         <v>8</v>
       </c>
       <c r="C124" t="s">
+        <v>242</v>
+      </c>
+      <c r="E124" t="s">
+        <v>164</v>
+      </c>
+      <c r="F124" t="s">
+        <v>243</v>
+      </c>
+      <c r="G124" t="s">
         <v>237</v>
-      </c>
-      <c r="D124" t="s">
-        <v>242</v>
-      </c>
-      <c r="F124" t="s">
-        <v>164</v>
-      </c>
-      <c r="G124" t="s">
-        <v>243</v>
       </c>
     </row>
     <row r="125" spans="1:7">
@@ -4549,16 +4549,16 @@
         <v>8</v>
       </c>
       <c r="C125" t="s">
+        <v>242</v>
+      </c>
+      <c r="E125" t="s">
+        <v>164</v>
+      </c>
+      <c r="F125" t="s">
+        <v>243</v>
+      </c>
+      <c r="G125" t="s">
         <v>237</v>
-      </c>
-      <c r="D125" t="s">
-        <v>242</v>
-      </c>
-      <c r="F125" t="s">
-        <v>164</v>
-      </c>
-      <c r="G125" t="s">
-        <v>243</v>
       </c>
     </row>
     <row r="126" spans="1:7">
@@ -4569,16 +4569,16 @@
         <v>8</v>
       </c>
       <c r="C126" t="s">
+        <v>242</v>
+      </c>
+      <c r="E126" t="s">
+        <v>164</v>
+      </c>
+      <c r="F126" t="s">
+        <v>243</v>
+      </c>
+      <c r="G126" t="s">
         <v>237</v>
-      </c>
-      <c r="D126" t="s">
-        <v>242</v>
-      </c>
-      <c r="F126" t="s">
-        <v>164</v>
-      </c>
-      <c r="G126" t="s">
-        <v>243</v>
       </c>
     </row>
     <row r="127" spans="1:7">
@@ -4589,16 +4589,16 @@
         <v>8</v>
       </c>
       <c r="C127" t="s">
+        <v>242</v>
+      </c>
+      <c r="E127" t="s">
+        <v>164</v>
+      </c>
+      <c r="F127" t="s">
+        <v>243</v>
+      </c>
+      <c r="G127" t="s">
         <v>237</v>
-      </c>
-      <c r="D127" t="s">
-        <v>242</v>
-      </c>
-      <c r="F127" t="s">
-        <v>164</v>
-      </c>
-      <c r="G127" t="s">
-        <v>243</v>
       </c>
     </row>
     <row r="128" spans="1:7">
@@ -4609,16 +4609,16 @@
         <v>8</v>
       </c>
       <c r="C128" t="s">
+        <v>242</v>
+      </c>
+      <c r="E128" t="s">
+        <v>164</v>
+      </c>
+      <c r="F128" t="s">
+        <v>243</v>
+      </c>
+      <c r="G128" t="s">
         <v>237</v>
-      </c>
-      <c r="D128" t="s">
-        <v>242</v>
-      </c>
-      <c r="F128" t="s">
-        <v>164</v>
-      </c>
-      <c r="G128" t="s">
-        <v>243</v>
       </c>
     </row>
     <row r="129" spans="1:7">
@@ -4629,16 +4629,16 @@
         <v>8</v>
       </c>
       <c r="C129" t="s">
+        <v>249</v>
+      </c>
+      <c r="E129" t="s">
+        <v>164</v>
+      </c>
+      <c r="F129" t="s">
+        <v>243</v>
+      </c>
+      <c r="G129" t="s">
         <v>237</v>
-      </c>
-      <c r="D129" t="s">
-        <v>242</v>
-      </c>
-      <c r="F129" t="s">
-        <v>164</v>
-      </c>
-      <c r="G129" t="s">
-        <v>249</v>
       </c>
     </row>
     <row r="130" spans="1:7">
@@ -4649,16 +4649,16 @@
         <v>8</v>
       </c>
       <c r="C130" t="s">
+        <v>251</v>
+      </c>
+      <c r="E130" t="s">
+        <v>164</v>
+      </c>
+      <c r="F130" t="s">
+        <v>243</v>
+      </c>
+      <c r="G130" t="s">
         <v>237</v>
-      </c>
-      <c r="D130" t="s">
-        <v>242</v>
-      </c>
-      <c r="F130" t="s">
-        <v>164</v>
-      </c>
-      <c r="G130" t="s">
-        <v>251</v>
       </c>
     </row>
     <row r="131" spans="1:7">
@@ -4669,16 +4669,16 @@
         <v>8</v>
       </c>
       <c r="C131" t="s">
+        <v>253</v>
+      </c>
+      <c r="E131" t="s">
+        <v>164</v>
+      </c>
+      <c r="F131" t="s">
+        <v>243</v>
+      </c>
+      <c r="G131" t="s">
         <v>237</v>
-      </c>
-      <c r="D131" t="s">
-        <v>242</v>
-      </c>
-      <c r="F131" t="s">
-        <v>164</v>
-      </c>
-      <c r="G131" t="s">
-        <v>253</v>
       </c>
     </row>
     <row r="132" spans="1:7">
@@ -4689,16 +4689,16 @@
         <v>8</v>
       </c>
       <c r="C132" t="s">
+        <v>255</v>
+      </c>
+      <c r="E132" t="s">
+        <v>164</v>
+      </c>
+      <c r="F132" t="s">
+        <v>256</v>
+      </c>
+      <c r="G132" t="s">
         <v>237</v>
-      </c>
-      <c r="D132" t="s">
-        <v>255</v>
-      </c>
-      <c r="F132" t="s">
-        <v>164</v>
-      </c>
-      <c r="G132" t="s">
-        <v>256</v>
       </c>
     </row>
     <row r="133" spans="1:7">
@@ -4709,16 +4709,16 @@
         <v>8</v>
       </c>
       <c r="C133" t="s">
+        <v>189</v>
+      </c>
+      <c r="E133" t="s">
+        <v>114</v>
+      </c>
+      <c r="F133" t="s">
+        <v>190</v>
+      </c>
+      <c r="G133" t="s">
         <v>237</v>
-      </c>
-      <c r="D133" t="s">
-        <v>189</v>
-      </c>
-      <c r="F133" t="s">
-        <v>115</v>
-      </c>
-      <c r="G133" t="s">
-        <v>190</v>
       </c>
     </row>
     <row r="134" spans="1:7">
@@ -4729,16 +4729,16 @@
         <v>8</v>
       </c>
       <c r="C134" t="s">
+        <v>175</v>
+      </c>
+      <c r="E134" t="s">
+        <v>164</v>
+      </c>
+      <c r="F134" t="s">
+        <v>176</v>
+      </c>
+      <c r="G134" t="s">
         <v>259</v>
-      </c>
-      <c r="D134" t="s">
-        <v>175</v>
-      </c>
-      <c r="F134" t="s">
-        <v>164</v>
-      </c>
-      <c r="G134" t="s">
-        <v>176</v>
       </c>
     </row>
     <row r="135" spans="1:7">
@@ -4749,16 +4749,16 @@
         <v>8</v>
       </c>
       <c r="C135" t="s">
+        <v>175</v>
+      </c>
+      <c r="E135" t="s">
+        <v>164</v>
+      </c>
+      <c r="F135" t="s">
+        <v>176</v>
+      </c>
+      <c r="G135" t="s">
         <v>259</v>
-      </c>
-      <c r="D135" t="s">
-        <v>175</v>
-      </c>
-      <c r="F135" t="s">
-        <v>164</v>
-      </c>
-      <c r="G135" t="s">
-        <v>176</v>
       </c>
     </row>
     <row r="136" spans="1:7">
@@ -4769,16 +4769,16 @@
         <v>8</v>
       </c>
       <c r="C136" t="s">
+        <v>175</v>
+      </c>
+      <c r="E136" t="s">
+        <v>164</v>
+      </c>
+      <c r="F136" t="s">
+        <v>176</v>
+      </c>
+      <c r="G136" t="s">
         <v>259</v>
-      </c>
-      <c r="D136" t="s">
-        <v>175</v>
-      </c>
-      <c r="F136" t="s">
-        <v>164</v>
-      </c>
-      <c r="G136" t="s">
-        <v>176</v>
       </c>
     </row>
     <row r="137" spans="1:7">
@@ -4789,16 +4789,16 @@
         <v>8</v>
       </c>
       <c r="C137" t="s">
+        <v>175</v>
+      </c>
+      <c r="E137" t="s">
+        <v>164</v>
+      </c>
+      <c r="F137" t="s">
+        <v>176</v>
+      </c>
+      <c r="G137" t="s">
         <v>259</v>
-      </c>
-      <c r="D137" t="s">
-        <v>175</v>
-      </c>
-      <c r="F137" t="s">
-        <v>164</v>
-      </c>
-      <c r="G137" t="s">
-        <v>176</v>
       </c>
     </row>
     <row r="138" spans="1:7">
@@ -4809,16 +4809,16 @@
         <v>8</v>
       </c>
       <c r="C138" t="s">
+        <v>175</v>
+      </c>
+      <c r="E138" t="s">
+        <v>164</v>
+      </c>
+      <c r="F138" t="s">
+        <v>176</v>
+      </c>
+      <c r="G138" t="s">
         <v>259</v>
-      </c>
-      <c r="D138" t="s">
-        <v>175</v>
-      </c>
-      <c r="F138" t="s">
-        <v>164</v>
-      </c>
-      <c r="G138" t="s">
-        <v>176</v>
       </c>
     </row>
     <row r="139" spans="1:7">
@@ -4829,16 +4829,16 @@
         <v>8</v>
       </c>
       <c r="C139" t="s">
+        <v>265</v>
+      </c>
+      <c r="E139" t="s">
+        <v>224</v>
+      </c>
+      <c r="F139" t="s">
+        <v>266</v>
+      </c>
+      <c r="G139" t="s">
         <v>259</v>
-      </c>
-      <c r="D139" t="s">
-        <v>265</v>
-      </c>
-      <c r="F139" t="s">
-        <v>224</v>
-      </c>
-      <c r="G139" t="s">
-        <v>266</v>
       </c>
     </row>
     <row r="140" spans="1:7">
@@ -4849,16 +4849,16 @@
         <v>8</v>
       </c>
       <c r="C140" t="s">
+        <v>175</v>
+      </c>
+      <c r="E140" t="s">
+        <v>164</v>
+      </c>
+      <c r="F140" t="s">
+        <v>176</v>
+      </c>
+      <c r="G140" t="s">
         <v>259</v>
-      </c>
-      <c r="D140" t="s">
-        <v>175</v>
-      </c>
-      <c r="F140" t="s">
-        <v>164</v>
-      </c>
-      <c r="G140" t="s">
-        <v>176</v>
       </c>
     </row>
     <row r="141" spans="1:7">
@@ -4875,10 +4875,10 @@
         <v>270</v>
       </c>
       <c r="E141" t="s">
+        <v>164</v>
+      </c>
+      <c r="F141" t="s">
         <v>271</v>
-      </c>
-      <c r="F141" t="s">
-        <v>164</v>
       </c>
       <c r="G141" t="s">
         <v>272</v>
@@ -4898,10 +4898,10 @@
         <v>270</v>
       </c>
       <c r="E142" t="s">
+        <v>164</v>
+      </c>
+      <c r="F142" t="s">
         <v>271</v>
-      </c>
-      <c r="F142" t="s">
-        <v>164</v>
       </c>
       <c r="G142" t="s">
         <v>272</v>
@@ -4915,19 +4915,19 @@
         <v>8</v>
       </c>
       <c r="C143" t="s">
-        <v>269</v>
+        <v>275</v>
       </c>
       <c r="D143" t="s">
-        <v>275</v>
+        <v>270</v>
       </c>
       <c r="E143" t="s">
-        <v>271</v>
+        <v>164</v>
       </c>
       <c r="F143" t="s">
-        <v>164</v>
+        <v>276</v>
       </c>
       <c r="G143" t="s">
-        <v>276</v>
+        <v>272</v>
       </c>
     </row>
     <row r="144" spans="1:7">
@@ -4938,19 +4938,19 @@
         <v>8</v>
       </c>
       <c r="C144" t="s">
-        <v>269</v>
+        <v>275</v>
       </c>
       <c r="D144" t="s">
-        <v>275</v>
+        <v>270</v>
       </c>
       <c r="E144" t="s">
-        <v>271</v>
+        <v>164</v>
       </c>
       <c r="F144" t="s">
-        <v>164</v>
+        <v>276</v>
       </c>
       <c r="G144" t="s">
-        <v>276</v>
+        <v>272</v>
       </c>
     </row>
     <row r="145" spans="1:7">
@@ -4961,19 +4961,19 @@
         <v>8</v>
       </c>
       <c r="C145" t="s">
-        <v>269</v>
+        <v>275</v>
       </c>
       <c r="D145" t="s">
-        <v>275</v>
+        <v>270</v>
       </c>
       <c r="E145" t="s">
-        <v>271</v>
+        <v>164</v>
       </c>
       <c r="F145" t="s">
-        <v>164</v>
+        <v>276</v>
       </c>
       <c r="G145" t="s">
-        <v>276</v>
+        <v>272</v>
       </c>
     </row>
     <row r="146" spans="1:7">
@@ -4990,10 +4990,10 @@
         <v>270</v>
       </c>
       <c r="E146" t="s">
+        <v>164</v>
+      </c>
+      <c r="F146" t="s">
         <v>271</v>
-      </c>
-      <c r="F146" t="s">
-        <v>164</v>
       </c>
       <c r="G146" t="s">
         <v>272</v>
@@ -5010,13 +5010,13 @@
         <v>269</v>
       </c>
       <c r="D147" t="s">
-        <v>270</v>
+        <v>281</v>
       </c>
       <c r="E147" t="s">
-        <v>281</v>
+        <v>164</v>
       </c>
       <c r="F147" t="s">
-        <v>164</v>
+        <v>271</v>
       </c>
       <c r="G147" t="s">
         <v>272</v>
@@ -5033,13 +5033,13 @@
         <v>269</v>
       </c>
       <c r="D148" t="s">
-        <v>270</v>
+        <v>281</v>
       </c>
       <c r="E148" t="s">
-        <v>281</v>
+        <v>164</v>
       </c>
       <c r="F148" t="s">
-        <v>164</v>
+        <v>271</v>
       </c>
       <c r="G148" t="s">
         <v>272</v>
@@ -5056,13 +5056,13 @@
         <v>269</v>
       </c>
       <c r="D149" t="s">
-        <v>270</v>
+        <v>281</v>
       </c>
       <c r="E149" t="s">
-        <v>281</v>
+        <v>164</v>
       </c>
       <c r="F149" t="s">
-        <v>164</v>
+        <v>271</v>
       </c>
       <c r="G149" t="s">
         <v>272</v>
@@ -5079,13 +5079,13 @@
         <v>269</v>
       </c>
       <c r="D150" t="s">
-        <v>270</v>
+        <v>281</v>
       </c>
       <c r="E150" t="s">
-        <v>281</v>
+        <v>164</v>
       </c>
       <c r="F150" t="s">
-        <v>164</v>
+        <v>271</v>
       </c>
       <c r="G150" t="s">
         <v>272</v>
@@ -5102,13 +5102,13 @@
         <v>269</v>
       </c>
       <c r="D151" t="s">
-        <v>270</v>
+        <v>281</v>
       </c>
       <c r="E151" t="s">
-        <v>281</v>
+        <v>164</v>
       </c>
       <c r="F151" t="s">
-        <v>164</v>
+        <v>271</v>
       </c>
       <c r="G151" t="s">
         <v>272</v>
@@ -5125,13 +5125,13 @@
         <v>269</v>
       </c>
       <c r="D152" t="s">
-        <v>270</v>
+        <v>281</v>
       </c>
       <c r="E152" t="s">
-        <v>281</v>
+        <v>164</v>
       </c>
       <c r="F152" t="s">
-        <v>164</v>
+        <v>271</v>
       </c>
       <c r="G152" t="s">
         <v>272</v>
@@ -5148,13 +5148,13 @@
         <v>269</v>
       </c>
       <c r="D153" t="s">
-        <v>270</v>
+        <v>281</v>
       </c>
       <c r="E153" t="s">
-        <v>281</v>
+        <v>164</v>
       </c>
       <c r="F153" t="s">
-        <v>164</v>
+        <v>271</v>
       </c>
       <c r="G153" t="s">
         <v>272</v>
@@ -5171,13 +5171,13 @@
         <v>269</v>
       </c>
       <c r="D154" t="s">
-        <v>270</v>
+        <v>281</v>
       </c>
       <c r="E154" t="s">
-        <v>281</v>
+        <v>164</v>
       </c>
       <c r="F154" t="s">
-        <v>164</v>
+        <v>271</v>
       </c>
       <c r="G154" t="s">
         <v>272</v>
@@ -5194,13 +5194,13 @@
         <v>269</v>
       </c>
       <c r="D155" t="s">
-        <v>270</v>
+        <v>281</v>
       </c>
       <c r="E155" t="s">
-        <v>281</v>
+        <v>164</v>
       </c>
       <c r="F155" t="s">
-        <v>164</v>
+        <v>271</v>
       </c>
       <c r="G155" t="s">
         <v>272</v>
@@ -5217,13 +5217,13 @@
         <v>269</v>
       </c>
       <c r="D156" t="s">
-        <v>270</v>
+        <v>291</v>
       </c>
       <c r="E156" t="s">
-        <v>291</v>
+        <v>164</v>
       </c>
       <c r="F156" t="s">
-        <v>164</v>
+        <v>271</v>
       </c>
       <c r="G156" t="s">
         <v>272</v>
@@ -5237,19 +5237,19 @@
         <v>8</v>
       </c>
       <c r="C157" t="s">
-        <v>269</v>
+        <v>293</v>
       </c>
       <c r="D157" t="s">
-        <v>270</v>
+        <v>291</v>
       </c>
       <c r="E157" t="s">
-        <v>291</v>
+        <v>164</v>
       </c>
       <c r="F157" t="s">
-        <v>164</v>
+        <v>271</v>
       </c>
       <c r="G157" t="s">
-        <v>293</v>
+        <v>272</v>
       </c>
     </row>
     <row r="158" spans="1:7">
@@ -5263,13 +5263,13 @@
         <v>269</v>
       </c>
       <c r="D158" t="s">
-        <v>270</v>
+        <v>291</v>
       </c>
       <c r="E158" t="s">
-        <v>291</v>
+        <v>164</v>
       </c>
       <c r="F158" t="s">
-        <v>164</v>
+        <v>271</v>
       </c>
       <c r="G158" t="s">
         <v>272</v>
@@ -5286,13 +5286,13 @@
         <v>269</v>
       </c>
       <c r="D159" t="s">
-        <v>270</v>
+        <v>291</v>
       </c>
       <c r="E159" t="s">
-        <v>291</v>
+        <v>164</v>
       </c>
       <c r="F159" t="s">
-        <v>164</v>
+        <v>271</v>
       </c>
       <c r="G159" t="s">
         <v>272</v>
@@ -5309,13 +5309,13 @@
         <v>269</v>
       </c>
       <c r="D160" t="s">
-        <v>270</v>
+        <v>291</v>
       </c>
       <c r="E160" t="s">
-        <v>291</v>
+        <v>164</v>
       </c>
       <c r="F160" t="s">
-        <v>164</v>
+        <v>271</v>
       </c>
       <c r="G160" t="s">
         <v>272</v>
@@ -5332,13 +5332,13 @@
         <v>269</v>
       </c>
       <c r="D161" t="s">
-        <v>270</v>
+        <v>291</v>
       </c>
       <c r="E161" t="s">
-        <v>291</v>
+        <v>164</v>
       </c>
       <c r="F161" t="s">
-        <v>164</v>
+        <v>271</v>
       </c>
       <c r="G161" t="s">
         <v>272</v>
@@ -5355,13 +5355,13 @@
         <v>269</v>
       </c>
       <c r="D162" t="s">
-        <v>270</v>
+        <v>299</v>
       </c>
       <c r="E162" t="s">
-        <v>299</v>
+        <v>164</v>
       </c>
       <c r="F162" t="s">
-        <v>164</v>
+        <v>271</v>
       </c>
       <c r="G162" t="s">
         <v>272</v>
@@ -5375,19 +5375,19 @@
         <v>8</v>
       </c>
       <c r="C163" t="s">
-        <v>269</v>
+        <v>301</v>
       </c>
       <c r="D163" t="s">
-        <v>270</v>
+        <v>302</v>
       </c>
       <c r="E163" t="s">
-        <v>301</v>
+        <v>164</v>
       </c>
       <c r="F163" t="s">
-        <v>164</v>
+        <v>271</v>
       </c>
       <c r="G163" t="s">
-        <v>302</v>
+        <v>272</v>
       </c>
     </row>
     <row r="164" spans="1:7">
@@ -5401,13 +5401,13 @@
         <v>269</v>
       </c>
       <c r="D164" t="s">
-        <v>270</v>
+        <v>304</v>
       </c>
       <c r="E164" t="s">
-        <v>304</v>
+        <v>164</v>
       </c>
       <c r="F164" t="s">
-        <v>164</v>
+        <v>271</v>
       </c>
       <c r="G164" t="s">
         <v>272</v>
@@ -5424,13 +5424,13 @@
         <v>269</v>
       </c>
       <c r="D165" t="s">
-        <v>270</v>
+        <v>304</v>
       </c>
       <c r="E165" t="s">
-        <v>304</v>
+        <v>164</v>
       </c>
       <c r="F165" t="s">
-        <v>164</v>
+        <v>271</v>
       </c>
       <c r="G165" t="s">
         <v>272</v>
@@ -5447,13 +5447,13 @@
         <v>269</v>
       </c>
       <c r="D166" t="s">
-        <v>270</v>
+        <v>304</v>
       </c>
       <c r="E166" t="s">
-        <v>304</v>
+        <v>164</v>
       </c>
       <c r="F166" t="s">
-        <v>164</v>
+        <v>271</v>
       </c>
       <c r="G166" t="s">
         <v>272</v>
@@ -5470,13 +5470,13 @@
         <v>269</v>
       </c>
       <c r="D167" t="s">
-        <v>270</v>
+        <v>304</v>
       </c>
       <c r="E167" t="s">
-        <v>304</v>
+        <v>164</v>
       </c>
       <c r="F167" t="s">
-        <v>164</v>
+        <v>271</v>
       </c>
       <c r="G167" t="s">
         <v>272</v>
@@ -5490,19 +5490,19 @@
         <v>8</v>
       </c>
       <c r="C168" t="s">
-        <v>269</v>
+        <v>309</v>
       </c>
       <c r="D168" t="s">
-        <v>270</v>
+        <v>304</v>
       </c>
       <c r="E168" t="s">
-        <v>304</v>
+        <v>164</v>
       </c>
       <c r="F168" t="s">
-        <v>164</v>
+        <v>271</v>
       </c>
       <c r="G168" t="s">
-        <v>309</v>
+        <v>272</v>
       </c>
     </row>
     <row r="169" spans="1:7">
@@ -5513,19 +5513,19 @@
         <v>8</v>
       </c>
       <c r="C169" t="s">
-        <v>269</v>
+        <v>309</v>
       </c>
       <c r="D169" t="s">
-        <v>270</v>
+        <v>304</v>
       </c>
       <c r="E169" t="s">
-        <v>304</v>
+        <v>164</v>
       </c>
       <c r="F169" t="s">
-        <v>164</v>
+        <v>271</v>
       </c>
       <c r="G169" t="s">
-        <v>309</v>
+        <v>272</v>
       </c>
     </row>
     <row r="170" spans="1:7">
@@ -5539,13 +5539,13 @@
         <v>269</v>
       </c>
       <c r="D170" t="s">
-        <v>270</v>
+        <v>304</v>
       </c>
       <c r="E170" t="s">
-        <v>304</v>
+        <v>164</v>
       </c>
       <c r="F170" t="s">
-        <v>164</v>
+        <v>271</v>
       </c>
       <c r="G170" t="s">
         <v>272</v>
@@ -5559,16 +5559,16 @@
         <v>8</v>
       </c>
       <c r="C171" t="s">
+        <v>163</v>
+      </c>
+      <c r="E171" t="s">
+        <v>164</v>
+      </c>
+      <c r="F171" t="s">
+        <v>165</v>
+      </c>
+      <c r="G171" t="s">
         <v>313</v>
-      </c>
-      <c r="D171" t="s">
-        <v>163</v>
-      </c>
-      <c r="F171" t="s">
-        <v>164</v>
-      </c>
-      <c r="G171" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="172" spans="1:7">
@@ -5579,16 +5579,16 @@
         <v>8</v>
       </c>
       <c r="C172" t="s">
+        <v>118</v>
+      </c>
+      <c r="E172" t="s">
+        <v>114</v>
+      </c>
+      <c r="F172" t="s">
+        <v>119</v>
+      </c>
+      <c r="G172" t="s">
         <v>313</v>
-      </c>
-      <c r="D172" t="s">
-        <v>118</v>
-      </c>
-      <c r="F172" t="s">
-        <v>115</v>
-      </c>
-      <c r="G172" t="s">
-        <v>119</v>
       </c>
     </row>
     <row r="173" spans="1:7">
@@ -5599,16 +5599,16 @@
         <v>8</v>
       </c>
       <c r="C173" t="s">
+        <v>163</v>
+      </c>
+      <c r="E173" t="s">
+        <v>164</v>
+      </c>
+      <c r="F173" t="s">
+        <v>165</v>
+      </c>
+      <c r="G173" t="s">
         <v>313</v>
-      </c>
-      <c r="D173" t="s">
-        <v>163</v>
-      </c>
-      <c r="F173" t="s">
-        <v>164</v>
-      </c>
-      <c r="G173" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="174" spans="1:7">
@@ -5619,16 +5619,16 @@
         <v>8</v>
       </c>
       <c r="C174" t="s">
+        <v>163</v>
+      </c>
+      <c r="E174" t="s">
+        <v>164</v>
+      </c>
+      <c r="F174" t="s">
+        <v>165</v>
+      </c>
+      <c r="G174" t="s">
         <v>313</v>
-      </c>
-      <c r="D174" t="s">
-        <v>163</v>
-      </c>
-      <c r="F174" t="s">
-        <v>164</v>
-      </c>
-      <c r="G174" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="175" spans="1:7">
@@ -5639,16 +5639,16 @@
         <v>8</v>
       </c>
       <c r="C175" t="s">
+        <v>163</v>
+      </c>
+      <c r="E175" t="s">
+        <v>164</v>
+      </c>
+      <c r="F175" t="s">
+        <v>165</v>
+      </c>
+      <c r="G175" t="s">
         <v>313</v>
-      </c>
-      <c r="D175" t="s">
-        <v>163</v>
-      </c>
-      <c r="F175" t="s">
-        <v>164</v>
-      </c>
-      <c r="G175" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="176" spans="1:7">
@@ -5659,16 +5659,16 @@
         <v>8</v>
       </c>
       <c r="C176" t="s">
+        <v>163</v>
+      </c>
+      <c r="E176" t="s">
+        <v>164</v>
+      </c>
+      <c r="F176" t="s">
+        <v>165</v>
+      </c>
+      <c r="G176" t="s">
         <v>313</v>
-      </c>
-      <c r="D176" t="s">
-        <v>163</v>
-      </c>
-      <c r="F176" t="s">
-        <v>164</v>
-      </c>
-      <c r="G176" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="177" spans="1:7">
@@ -5679,16 +5679,16 @@
         <v>8</v>
       </c>
       <c r="C177" t="s">
+        <v>163</v>
+      </c>
+      <c r="E177" t="s">
+        <v>164</v>
+      </c>
+      <c r="F177" t="s">
+        <v>165</v>
+      </c>
+      <c r="G177" t="s">
         <v>320</v>
-      </c>
-      <c r="D177" t="s">
-        <v>163</v>
-      </c>
-      <c r="F177" t="s">
-        <v>164</v>
-      </c>
-      <c r="G177" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="178" spans="1:7">
@@ -5699,16 +5699,16 @@
         <v>8</v>
       </c>
       <c r="C178" t="s">
+        <v>163</v>
+      </c>
+      <c r="E178" t="s">
+        <v>164</v>
+      </c>
+      <c r="F178" t="s">
+        <v>165</v>
+      </c>
+      <c r="G178" t="s">
         <v>320</v>
-      </c>
-      <c r="D178" t="s">
-        <v>163</v>
-      </c>
-      <c r="F178" t="s">
-        <v>164</v>
-      </c>
-      <c r="G178" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="179" spans="1:7">
@@ -5719,16 +5719,16 @@
         <v>8</v>
       </c>
       <c r="C179" t="s">
+        <v>163</v>
+      </c>
+      <c r="E179" t="s">
+        <v>164</v>
+      </c>
+      <c r="F179" t="s">
+        <v>165</v>
+      </c>
+      <c r="G179" t="s">
         <v>320</v>
-      </c>
-      <c r="D179" t="s">
-        <v>163</v>
-      </c>
-      <c r="F179" t="s">
-        <v>164</v>
-      </c>
-      <c r="G179" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="180" spans="1:7">
@@ -5739,16 +5739,16 @@
         <v>8</v>
       </c>
       <c r="C180" t="s">
+        <v>163</v>
+      </c>
+      <c r="E180" t="s">
+        <v>164</v>
+      </c>
+      <c r="F180" t="s">
+        <v>165</v>
+      </c>
+      <c r="G180" t="s">
         <v>320</v>
-      </c>
-      <c r="D180" t="s">
-        <v>163</v>
-      </c>
-      <c r="F180" t="s">
-        <v>164</v>
-      </c>
-      <c r="G180" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="181" spans="1:7">
@@ -5765,10 +5765,10 @@
         <v>326</v>
       </c>
       <c r="E181" t="s">
+        <v>164</v>
+      </c>
+      <c r="F181" t="s">
         <v>327</v>
-      </c>
-      <c r="F181" t="s">
-        <v>164</v>
       </c>
       <c r="G181" t="s">
         <v>328</v>
@@ -5788,10 +5788,10 @@
         <v>326</v>
       </c>
       <c r="E182" t="s">
+        <v>164</v>
+      </c>
+      <c r="F182" t="s">
         <v>327</v>
-      </c>
-      <c r="F182" t="s">
-        <v>164</v>
       </c>
       <c r="G182" t="s">
         <v>328</v>
@@ -5811,10 +5811,10 @@
         <v>326</v>
       </c>
       <c r="E183" t="s">
+        <v>164</v>
+      </c>
+      <c r="F183" t="s">
         <v>327</v>
-      </c>
-      <c r="F183" t="s">
-        <v>164</v>
       </c>
       <c r="G183" t="s">
         <v>328</v>
@@ -5834,10 +5834,10 @@
         <v>326</v>
       </c>
       <c r="E184" t="s">
+        <v>164</v>
+      </c>
+      <c r="F184" t="s">
         <v>327</v>
-      </c>
-      <c r="F184" t="s">
-        <v>164</v>
       </c>
       <c r="G184" t="s">
         <v>328</v>
@@ -5857,10 +5857,10 @@
         <v>326</v>
       </c>
       <c r="E185" t="s">
+        <v>164</v>
+      </c>
+      <c r="F185" t="s">
         <v>327</v>
-      </c>
-      <c r="F185" t="s">
-        <v>164</v>
       </c>
       <c r="G185" t="s">
         <v>328</v>
@@ -5880,10 +5880,10 @@
         <v>326</v>
       </c>
       <c r="E186" t="s">
+        <v>164</v>
+      </c>
+      <c r="F186" t="s">
         <v>327</v>
-      </c>
-      <c r="F186" t="s">
-        <v>164</v>
       </c>
       <c r="G186" t="s">
         <v>328</v>
@@ -5903,10 +5903,10 @@
         <v>326</v>
       </c>
       <c r="E187" t="s">
+        <v>164</v>
+      </c>
+      <c r="F187" t="s">
         <v>327</v>
-      </c>
-      <c r="F187" t="s">
-        <v>164</v>
       </c>
       <c r="G187" t="s">
         <v>328</v>
@@ -5926,10 +5926,10 @@
         <v>326</v>
       </c>
       <c r="E188" t="s">
+        <v>164</v>
+      </c>
+      <c r="F188" t="s">
         <v>327</v>
-      </c>
-      <c r="F188" t="s">
-        <v>164</v>
       </c>
       <c r="G188" t="s">
         <v>328</v>
@@ -5949,10 +5949,10 @@
         <v>326</v>
       </c>
       <c r="E189" t="s">
+        <v>164</v>
+      </c>
+      <c r="F189" t="s">
         <v>327</v>
-      </c>
-      <c r="F189" t="s">
-        <v>164</v>
       </c>
       <c r="G189" t="s">
         <v>328</v>
@@ -5972,10 +5972,10 @@
         <v>326</v>
       </c>
       <c r="E190" t="s">
+        <v>164</v>
+      </c>
+      <c r="F190" t="s">
         <v>327</v>
-      </c>
-      <c r="F190" t="s">
-        <v>164</v>
       </c>
       <c r="G190" t="s">
         <v>328</v>
@@ -5995,10 +5995,10 @@
         <v>326</v>
       </c>
       <c r="E191" t="s">
+        <v>164</v>
+      </c>
+      <c r="F191" t="s">
         <v>327</v>
-      </c>
-      <c r="F191" t="s">
-        <v>164</v>
       </c>
       <c r="G191" t="s">
         <v>328</v>
@@ -6018,10 +6018,10 @@
         <v>326</v>
       </c>
       <c r="E192" t="s">
+        <v>164</v>
+      </c>
+      <c r="F192" t="s">
         <v>327</v>
-      </c>
-      <c r="F192" t="s">
-        <v>164</v>
       </c>
       <c r="G192" t="s">
         <v>328</v>
@@ -6035,19 +6035,19 @@
         <v>8</v>
       </c>
       <c r="C193" t="s">
-        <v>325</v>
+        <v>341</v>
       </c>
       <c r="D193" t="s">
-        <v>275</v>
+        <v>326</v>
       </c>
       <c r="E193" t="s">
-        <v>327</v>
+        <v>164</v>
       </c>
       <c r="F193" t="s">
-        <v>164</v>
+        <v>276</v>
       </c>
       <c r="G193" t="s">
-        <v>341</v>
+        <v>328</v>
       </c>
     </row>
     <row r="194" spans="1:7">
@@ -6064,10 +6064,10 @@
         <v>326</v>
       </c>
       <c r="E194" t="s">
+        <v>164</v>
+      </c>
+      <c r="F194" t="s">
         <v>327</v>
-      </c>
-      <c r="F194" t="s">
-        <v>164</v>
       </c>
       <c r="G194" t="s">
         <v>328</v>
@@ -6087,10 +6087,10 @@
         <v>326</v>
       </c>
       <c r="E195" t="s">
+        <v>164</v>
+      </c>
+      <c r="F195" t="s">
         <v>327</v>
-      </c>
-      <c r="F195" t="s">
-        <v>164</v>
       </c>
       <c r="G195" t="s">
         <v>328</v>
@@ -6110,10 +6110,10 @@
         <v>326</v>
       </c>
       <c r="E196" t="s">
+        <v>164</v>
+      </c>
+      <c r="F196" t="s">
         <v>327</v>
-      </c>
-      <c r="F196" t="s">
-        <v>164</v>
       </c>
       <c r="G196" t="s">
         <v>328</v>
@@ -6133,10 +6133,10 @@
         <v>326</v>
       </c>
       <c r="E197" t="s">
+        <v>164</v>
+      </c>
+      <c r="F197" t="s">
         <v>327</v>
-      </c>
-      <c r="F197" t="s">
-        <v>164</v>
       </c>
       <c r="G197" t="s">
         <v>328</v>
@@ -6156,10 +6156,10 @@
         <v>326</v>
       </c>
       <c r="E198" t="s">
+        <v>164</v>
+      </c>
+      <c r="F198" t="s">
         <v>327</v>
-      </c>
-      <c r="F198" t="s">
-        <v>164</v>
       </c>
       <c r="G198" t="s">
         <v>328</v>
@@ -6173,19 +6173,19 @@
         <v>8</v>
       </c>
       <c r="C199" t="s">
-        <v>325</v>
+        <v>348</v>
       </c>
       <c r="D199" t="s">
-        <v>326</v>
+        <v>349</v>
       </c>
       <c r="E199" t="s">
-        <v>348</v>
+        <v>164</v>
       </c>
       <c r="F199" t="s">
-        <v>164</v>
+        <v>327</v>
       </c>
       <c r="G199" t="s">
-        <v>349</v>
+        <v>328</v>
       </c>
     </row>
     <row r="200" spans="1:7">
@@ -6196,19 +6196,19 @@
         <v>8</v>
       </c>
       <c r="C200" t="s">
-        <v>325</v>
+        <v>348</v>
       </c>
       <c r="D200" t="s">
-        <v>326</v>
+        <v>349</v>
       </c>
       <c r="E200" t="s">
-        <v>348</v>
+        <v>164</v>
       </c>
       <c r="F200" t="s">
-        <v>164</v>
+        <v>327</v>
       </c>
       <c r="G200" t="s">
-        <v>349</v>
+        <v>328</v>
       </c>
     </row>
     <row r="201" spans="1:7">
@@ -6219,19 +6219,19 @@
         <v>8</v>
       </c>
       <c r="C201" t="s">
-        <v>325</v>
+        <v>348</v>
       </c>
       <c r="D201" t="s">
-        <v>326</v>
+        <v>349</v>
       </c>
       <c r="E201" t="s">
-        <v>348</v>
+        <v>164</v>
       </c>
       <c r="F201" t="s">
-        <v>164</v>
+        <v>327</v>
       </c>
       <c r="G201" t="s">
-        <v>349</v>
+        <v>328</v>
       </c>
     </row>
     <row r="202" spans="1:7">
@@ -6242,19 +6242,19 @@
         <v>8</v>
       </c>
       <c r="C202" t="s">
-        <v>325</v>
+        <v>348</v>
       </c>
       <c r="D202" t="s">
-        <v>326</v>
+        <v>349</v>
       </c>
       <c r="E202" t="s">
-        <v>348</v>
+        <v>164</v>
       </c>
       <c r="F202" t="s">
-        <v>164</v>
+        <v>327</v>
       </c>
       <c r="G202" t="s">
-        <v>349</v>
+        <v>328</v>
       </c>
     </row>
     <row r="203" spans="1:7">
@@ -6265,19 +6265,19 @@
         <v>8</v>
       </c>
       <c r="C203" t="s">
-        <v>325</v>
+        <v>341</v>
       </c>
       <c r="D203" t="s">
-        <v>275</v>
+        <v>349</v>
       </c>
       <c r="E203" t="s">
-        <v>348</v>
+        <v>164</v>
       </c>
       <c r="F203" t="s">
-        <v>164</v>
+        <v>276</v>
       </c>
       <c r="G203" t="s">
-        <v>341</v>
+        <v>328</v>
       </c>
     </row>
     <row r="204" spans="1:7">
@@ -6288,19 +6288,19 @@
         <v>8</v>
       </c>
       <c r="C204" t="s">
-        <v>325</v>
+        <v>348</v>
       </c>
       <c r="D204" t="s">
-        <v>326</v>
+        <v>349</v>
       </c>
       <c r="E204" t="s">
-        <v>348</v>
+        <v>164</v>
       </c>
       <c r="F204" t="s">
-        <v>164</v>
+        <v>327</v>
       </c>
       <c r="G204" t="s">
-        <v>349</v>
+        <v>328</v>
       </c>
     </row>
     <row r="205" spans="1:7">
@@ -6311,19 +6311,19 @@
         <v>8</v>
       </c>
       <c r="C205" t="s">
-        <v>325</v>
+        <v>356</v>
       </c>
       <c r="D205" t="s">
-        <v>326</v>
+        <v>357</v>
       </c>
       <c r="E205" t="s">
-        <v>356</v>
+        <v>164</v>
       </c>
       <c r="F205" t="s">
-        <v>164</v>
+        <v>327</v>
       </c>
       <c r="G205" t="s">
-        <v>357</v>
+        <v>328</v>
       </c>
     </row>
     <row r="206" spans="1:7">
@@ -6334,19 +6334,19 @@
         <v>8</v>
       </c>
       <c r="C206" t="s">
-        <v>325</v>
+        <v>356</v>
       </c>
       <c r="D206" t="s">
-        <v>326</v>
+        <v>357</v>
       </c>
       <c r="E206" t="s">
-        <v>356</v>
+        <v>164</v>
       </c>
       <c r="F206" t="s">
-        <v>164</v>
+        <v>327</v>
       </c>
       <c r="G206" t="s">
-        <v>357</v>
+        <v>328</v>
       </c>
     </row>
     <row r="207" spans="1:7">
@@ -6357,19 +6357,19 @@
         <v>8</v>
       </c>
       <c r="C207" t="s">
-        <v>325</v>
+        <v>356</v>
       </c>
       <c r="D207" t="s">
-        <v>326</v>
+        <v>357</v>
       </c>
       <c r="E207" t="s">
-        <v>356</v>
+        <v>164</v>
       </c>
       <c r="F207" t="s">
-        <v>164</v>
+        <v>327</v>
       </c>
       <c r="G207" t="s">
-        <v>357</v>
+        <v>328</v>
       </c>
     </row>
     <row r="208" spans="1:7">
@@ -6380,19 +6380,19 @@
         <v>8</v>
       </c>
       <c r="C208" t="s">
-        <v>325</v>
+        <v>341</v>
       </c>
       <c r="D208" t="s">
-        <v>275</v>
+        <v>357</v>
       </c>
       <c r="E208" t="s">
-        <v>356</v>
+        <v>164</v>
       </c>
       <c r="F208" t="s">
-        <v>164</v>
+        <v>276</v>
       </c>
       <c r="G208" t="s">
-        <v>341</v>
+        <v>328</v>
       </c>
     </row>
     <row r="209" spans="1:7">
@@ -6403,19 +6403,19 @@
         <v>8</v>
       </c>
       <c r="C209" t="s">
-        <v>325</v>
+        <v>356</v>
       </c>
       <c r="D209" t="s">
-        <v>326</v>
+        <v>357</v>
       </c>
       <c r="E209" t="s">
-        <v>356</v>
+        <v>164</v>
       </c>
       <c r="F209" t="s">
-        <v>164</v>
+        <v>327</v>
       </c>
       <c r="G209" t="s">
-        <v>357</v>
+        <v>328</v>
       </c>
     </row>
     <row r="210" spans="1:7">
@@ -6432,10 +6432,10 @@
         <v>364</v>
       </c>
       <c r="E210" t="s">
+        <v>164</v>
+      </c>
+      <c r="F210" t="s">
         <v>365</v>
-      </c>
-      <c r="F210" t="s">
-        <v>164</v>
       </c>
       <c r="G210" t="s">
         <v>366</v>
@@ -6455,10 +6455,10 @@
         <v>364</v>
       </c>
       <c r="E211" t="s">
+        <v>164</v>
+      </c>
+      <c r="F211" t="s">
         <v>365</v>
-      </c>
-      <c r="F211" t="s">
-        <v>164</v>
       </c>
       <c r="G211" t="s">
         <v>366</v>
@@ -6478,10 +6478,10 @@
         <v>364</v>
       </c>
       <c r="E212" t="s">
+        <v>164</v>
+      </c>
+      <c r="F212" t="s">
         <v>365</v>
-      </c>
-      <c r="F212" t="s">
-        <v>164</v>
       </c>
       <c r="G212" t="s">
         <v>366</v>
@@ -6501,10 +6501,10 @@
         <v>364</v>
       </c>
       <c r="E213" t="s">
+        <v>164</v>
+      </c>
+      <c r="F213" t="s">
         <v>365</v>
-      </c>
-      <c r="F213" t="s">
-        <v>164</v>
       </c>
       <c r="G213" t="s">
         <v>366</v>
@@ -6524,10 +6524,10 @@
         <v>364</v>
       </c>
       <c r="E214" t="s">
+        <v>164</v>
+      </c>
+      <c r="F214" t="s">
         <v>365</v>
-      </c>
-      <c r="F214" t="s">
-        <v>164</v>
       </c>
       <c r="G214" t="s">
         <v>366</v>
@@ -6541,19 +6541,19 @@
         <v>8</v>
       </c>
       <c r="C215" t="s">
-        <v>363</v>
+        <v>348</v>
       </c>
       <c r="D215" t="s">
-        <v>326</v>
+        <v>364</v>
       </c>
       <c r="E215" t="s">
-        <v>365</v>
+        <v>164</v>
       </c>
       <c r="F215" t="s">
-        <v>164</v>
+        <v>327</v>
       </c>
       <c r="G215" t="s">
-        <v>349</v>
+        <v>366</v>
       </c>
     </row>
     <row r="216" spans="1:7">
@@ -6570,10 +6570,10 @@
         <v>364</v>
       </c>
       <c r="E216" t="s">
+        <v>164</v>
+      </c>
+      <c r="F216" t="s">
         <v>365</v>
-      </c>
-      <c r="F216" t="s">
-        <v>164</v>
       </c>
       <c r="G216" t="s">
         <v>366</v>
@@ -6593,10 +6593,10 @@
         <v>364</v>
       </c>
       <c r="E217" t="s">
+        <v>164</v>
+      </c>
+      <c r="F217" t="s">
         <v>365</v>
-      </c>
-      <c r="F217" t="s">
-        <v>164</v>
       </c>
       <c r="G217" t="s">
         <v>366</v>
@@ -6616,10 +6616,10 @@
         <v>364</v>
       </c>
       <c r="E218" t="s">
+        <v>164</v>
+      </c>
+      <c r="F218" t="s">
         <v>365</v>
-      </c>
-      <c r="F218" t="s">
-        <v>164</v>
       </c>
       <c r="G218" t="s">
         <v>366</v>
@@ -6639,10 +6639,10 @@
         <v>364</v>
       </c>
       <c r="E219" t="s">
+        <v>164</v>
+      </c>
+      <c r="F219" t="s">
         <v>365</v>
-      </c>
-      <c r="F219" t="s">
-        <v>164</v>
       </c>
       <c r="G219" t="s">
         <v>366</v>
@@ -6656,19 +6656,19 @@
         <v>8</v>
       </c>
       <c r="C220" t="s">
-        <v>363</v>
+        <v>309</v>
       </c>
       <c r="D220" t="s">
-        <v>270</v>
+        <v>364</v>
       </c>
       <c r="E220" t="s">
-        <v>365</v>
+        <v>164</v>
       </c>
       <c r="F220" t="s">
-        <v>164</v>
+        <v>271</v>
       </c>
       <c r="G220" t="s">
-        <v>309</v>
+        <v>366</v>
       </c>
     </row>
     <row r="221" spans="1:7">
@@ -6685,10 +6685,10 @@
         <v>364</v>
       </c>
       <c r="E221" t="s">
+        <v>164</v>
+      </c>
+      <c r="F221" t="s">
         <v>365</v>
-      </c>
-      <c r="F221" t="s">
-        <v>164</v>
       </c>
       <c r="G221" t="s">
         <v>366</v>
@@ -6708,10 +6708,10 @@
         <v>364</v>
       </c>
       <c r="E222" t="s">
+        <v>164</v>
+      </c>
+      <c r="F222" t="s">
         <v>365</v>
-      </c>
-      <c r="F222" t="s">
-        <v>164</v>
       </c>
       <c r="G222" t="s">
         <v>366</v>
@@ -6731,10 +6731,10 @@
         <v>364</v>
       </c>
       <c r="E223" t="s">
+        <v>164</v>
+      </c>
+      <c r="F223" t="s">
         <v>365</v>
-      </c>
-      <c r="F223" t="s">
-        <v>164</v>
       </c>
       <c r="G223" t="s">
         <v>366</v>
@@ -6754,10 +6754,10 @@
         <v>364</v>
       </c>
       <c r="E224" t="s">
+        <v>164</v>
+      </c>
+      <c r="F224" t="s">
         <v>365</v>
-      </c>
-      <c r="F224" t="s">
-        <v>164</v>
       </c>
       <c r="G224" t="s">
         <v>366</v>
@@ -6777,10 +6777,10 @@
         <v>364</v>
       </c>
       <c r="E225" t="s">
+        <v>164</v>
+      </c>
+      <c r="F225" t="s">
         <v>365</v>
-      </c>
-      <c r="F225" t="s">
-        <v>164</v>
       </c>
       <c r="G225" t="s">
         <v>366</v>
@@ -6794,19 +6794,19 @@
         <v>8</v>
       </c>
       <c r="C226" t="s">
-        <v>363</v>
+        <v>275</v>
       </c>
       <c r="D226" t="s">
-        <v>275</v>
+        <v>364</v>
       </c>
       <c r="E226" t="s">
-        <v>365</v>
+        <v>164</v>
       </c>
       <c r="F226" t="s">
-        <v>164</v>
+        <v>276</v>
       </c>
       <c r="G226" t="s">
-        <v>276</v>
+        <v>366</v>
       </c>
     </row>
     <row r="227" spans="1:7">
@@ -6823,10 +6823,10 @@
         <v>364</v>
       </c>
       <c r="E227" t="s">
+        <v>164</v>
+      </c>
+      <c r="F227" t="s">
         <v>365</v>
-      </c>
-      <c r="F227" t="s">
-        <v>164</v>
       </c>
       <c r="G227" t="s">
         <v>366</v>
@@ -6840,19 +6840,19 @@
         <v>8</v>
       </c>
       <c r="C228" t="s">
-        <v>363</v>
+        <v>163</v>
       </c>
       <c r="D228" t="s">
-        <v>163</v>
+        <v>364</v>
       </c>
       <c r="E228" t="s">
-        <v>365</v>
+        <v>164</v>
       </c>
       <c r="F228" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="G228" t="s">
-        <v>165</v>
+        <v>366</v>
       </c>
     </row>
     <row r="229" spans="1:7">
@@ -6863,19 +6863,19 @@
         <v>8</v>
       </c>
       <c r="C229" t="s">
-        <v>363</v>
+        <v>386</v>
       </c>
       <c r="D229" t="s">
-        <v>364</v>
+        <v>387</v>
       </c>
       <c r="E229" t="s">
-        <v>386</v>
+        <v>164</v>
       </c>
       <c r="F229" t="s">
-        <v>164</v>
+        <v>365</v>
       </c>
       <c r="G229" t="s">
-        <v>387</v>
+        <v>366</v>
       </c>
     </row>
     <row r="230" spans="1:7">
@@ -6886,19 +6886,19 @@
         <v>8</v>
       </c>
       <c r="C230" t="s">
-        <v>363</v>
+        <v>386</v>
       </c>
       <c r="D230" t="s">
-        <v>364</v>
+        <v>387</v>
       </c>
       <c r="E230" t="s">
-        <v>386</v>
+        <v>164</v>
       </c>
       <c r="F230" t="s">
-        <v>164</v>
+        <v>365</v>
       </c>
       <c r="G230" t="s">
-        <v>387</v>
+        <v>366</v>
       </c>
     </row>
     <row r="231" spans="1:7">
@@ -6909,19 +6909,19 @@
         <v>8</v>
       </c>
       <c r="C231" t="s">
-        <v>363</v>
+        <v>293</v>
       </c>
       <c r="D231" t="s">
-        <v>270</v>
+        <v>387</v>
       </c>
       <c r="E231" t="s">
-        <v>386</v>
+        <v>164</v>
       </c>
       <c r="F231" t="s">
-        <v>164</v>
+        <v>271</v>
       </c>
       <c r="G231" t="s">
-        <v>293</v>
+        <v>366</v>
       </c>
     </row>
     <row r="232" spans="1:7">
@@ -6932,19 +6932,19 @@
         <v>8</v>
       </c>
       <c r="C232" t="s">
-        <v>363</v>
+        <v>309</v>
       </c>
       <c r="D232" t="s">
-        <v>270</v>
+        <v>387</v>
       </c>
       <c r="E232" t="s">
-        <v>386</v>
+        <v>164</v>
       </c>
       <c r="F232" t="s">
-        <v>164</v>
+        <v>271</v>
       </c>
       <c r="G232" t="s">
-        <v>309</v>
+        <v>366</v>
       </c>
     </row>
     <row r="233" spans="1:7">
@@ -6955,19 +6955,19 @@
         <v>8</v>
       </c>
       <c r="C233" t="s">
-        <v>363</v>
+        <v>386</v>
       </c>
       <c r="D233" t="s">
-        <v>364</v>
+        <v>387</v>
       </c>
       <c r="E233" t="s">
-        <v>386</v>
+        <v>164</v>
       </c>
       <c r="F233" t="s">
-        <v>164</v>
+        <v>365</v>
       </c>
       <c r="G233" t="s">
-        <v>387</v>
+        <v>366</v>
       </c>
     </row>
     <row r="234" spans="1:7">
@@ -6978,19 +6978,19 @@
         <v>8</v>
       </c>
       <c r="C234" t="s">
-        <v>363</v>
+        <v>386</v>
       </c>
       <c r="D234" t="s">
-        <v>364</v>
+        <v>387</v>
       </c>
       <c r="E234" t="s">
-        <v>386</v>
+        <v>164</v>
       </c>
       <c r="F234" t="s">
-        <v>164</v>
+        <v>365</v>
       </c>
       <c r="G234" t="s">
-        <v>387</v>
+        <v>366</v>
       </c>
     </row>
     <row r="235" spans="1:7">
@@ -7001,19 +7001,19 @@
         <v>8</v>
       </c>
       <c r="C235" t="s">
-        <v>363</v>
+        <v>386</v>
       </c>
       <c r="D235" t="s">
-        <v>364</v>
+        <v>387</v>
       </c>
       <c r="E235" t="s">
-        <v>386</v>
+        <v>164</v>
       </c>
       <c r="F235" t="s">
-        <v>164</v>
+        <v>365</v>
       </c>
       <c r="G235" t="s">
-        <v>387</v>
+        <v>366</v>
       </c>
     </row>
     <row r="236" spans="1:7">
@@ -7024,19 +7024,19 @@
         <v>8</v>
       </c>
       <c r="C236" t="s">
-        <v>363</v>
+        <v>386</v>
       </c>
       <c r="D236" t="s">
-        <v>364</v>
+        <v>387</v>
       </c>
       <c r="E236" t="s">
-        <v>386</v>
+        <v>164</v>
       </c>
       <c r="F236" t="s">
-        <v>164</v>
+        <v>365</v>
       </c>
       <c r="G236" t="s">
-        <v>387</v>
+        <v>366</v>
       </c>
     </row>
     <row r="237" spans="1:7">
@@ -7047,19 +7047,19 @@
         <v>8</v>
       </c>
       <c r="C237" t="s">
-        <v>363</v>
+        <v>386</v>
       </c>
       <c r="D237" t="s">
-        <v>364</v>
+        <v>387</v>
       </c>
       <c r="E237" t="s">
-        <v>386</v>
+        <v>164</v>
       </c>
       <c r="F237" t="s">
-        <v>164</v>
+        <v>365</v>
       </c>
       <c r="G237" t="s">
-        <v>387</v>
+        <v>366</v>
       </c>
     </row>
     <row r="238" spans="1:7">
@@ -7070,19 +7070,19 @@
         <v>8</v>
       </c>
       <c r="C238" t="s">
-        <v>363</v>
+        <v>386</v>
       </c>
       <c r="D238" t="s">
-        <v>364</v>
+        <v>387</v>
       </c>
       <c r="E238" t="s">
-        <v>386</v>
+        <v>164</v>
       </c>
       <c r="F238" t="s">
-        <v>164</v>
+        <v>365</v>
       </c>
       <c r="G238" t="s">
-        <v>387</v>
+        <v>366</v>
       </c>
     </row>
     <row r="239" spans="1:7">
@@ -7093,19 +7093,19 @@
         <v>8</v>
       </c>
       <c r="C239" t="s">
-        <v>363</v>
+        <v>398</v>
       </c>
       <c r="D239" t="s">
-        <v>364</v>
+        <v>399</v>
       </c>
       <c r="E239" t="s">
-        <v>398</v>
+        <v>164</v>
       </c>
       <c r="F239" t="s">
-        <v>164</v>
+        <v>365</v>
       </c>
       <c r="G239" t="s">
-        <v>399</v>
+        <v>366</v>
       </c>
     </row>
     <row r="240" spans="1:7">
@@ -7116,19 +7116,19 @@
         <v>8</v>
       </c>
       <c r="C240" t="s">
+        <v>163</v>
+      </c>
+      <c r="D240" t="s">
         <v>401</v>
       </c>
-      <c r="D240" t="s">
-        <v>163</v>
-      </c>
       <c r="E240" t="s">
+        <v>164</v>
+      </c>
+      <c r="F240" t="s">
+        <v>165</v>
+      </c>
+      <c r="G240" t="s">
         <v>402</v>
-      </c>
-      <c r="F240" t="s">
-        <v>164</v>
-      </c>
-      <c r="G240" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="241" spans="1:7">
@@ -7139,19 +7139,19 @@
         <v>8</v>
       </c>
       <c r="C241" t="s">
+        <v>163</v>
+      </c>
+      <c r="D241" t="s">
         <v>401</v>
       </c>
-      <c r="D241" t="s">
-        <v>163</v>
-      </c>
       <c r="E241" t="s">
+        <v>164</v>
+      </c>
+      <c r="F241" t="s">
+        <v>165</v>
+      </c>
+      <c r="G241" t="s">
         <v>402</v>
-      </c>
-      <c r="F241" t="s">
-        <v>164</v>
-      </c>
-      <c r="G241" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="242" spans="1:7">
@@ -7162,19 +7162,19 @@
         <v>8</v>
       </c>
       <c r="C242" t="s">
+        <v>163</v>
+      </c>
+      <c r="D242" t="s">
         <v>401</v>
       </c>
-      <c r="D242" t="s">
-        <v>163</v>
-      </c>
       <c r="E242" t="s">
+        <v>164</v>
+      </c>
+      <c r="F242" t="s">
+        <v>165</v>
+      </c>
+      <c r="G242" t="s">
         <v>402</v>
-      </c>
-      <c r="F242" t="s">
-        <v>164</v>
-      </c>
-      <c r="G242" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="243" spans="1:7">
@@ -7185,19 +7185,19 @@
         <v>8</v>
       </c>
       <c r="C243" t="s">
+        <v>163</v>
+      </c>
+      <c r="D243" t="s">
         <v>401</v>
       </c>
-      <c r="D243" t="s">
-        <v>163</v>
-      </c>
       <c r="E243" t="s">
+        <v>164</v>
+      </c>
+      <c r="F243" t="s">
+        <v>165</v>
+      </c>
+      <c r="G243" t="s">
         <v>402</v>
-      </c>
-      <c r="F243" t="s">
-        <v>164</v>
-      </c>
-      <c r="G243" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="244" spans="1:7">
@@ -7208,19 +7208,19 @@
         <v>8</v>
       </c>
       <c r="C244" t="s">
+        <v>163</v>
+      </c>
+      <c r="D244" t="s">
         <v>401</v>
       </c>
-      <c r="D244" t="s">
-        <v>163</v>
-      </c>
       <c r="E244" t="s">
+        <v>164</v>
+      </c>
+      <c r="F244" t="s">
+        <v>165</v>
+      </c>
+      <c r="G244" t="s">
         <v>402</v>
-      </c>
-      <c r="F244" t="s">
-        <v>164</v>
-      </c>
-      <c r="G244" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="245" spans="1:7">
@@ -7231,19 +7231,19 @@
         <v>8</v>
       </c>
       <c r="C245" t="s">
+        <v>163</v>
+      </c>
+      <c r="D245" t="s">
         <v>401</v>
       </c>
-      <c r="D245" t="s">
-        <v>163</v>
-      </c>
       <c r="E245" t="s">
+        <v>164</v>
+      </c>
+      <c r="F245" t="s">
+        <v>165</v>
+      </c>
+      <c r="G245" t="s">
         <v>402</v>
-      </c>
-      <c r="F245" t="s">
-        <v>164</v>
-      </c>
-      <c r="G245" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="246" spans="1:7">
@@ -7254,19 +7254,19 @@
         <v>8</v>
       </c>
       <c r="C246" t="s">
-        <v>401</v>
+        <v>409</v>
       </c>
       <c r="D246" t="s">
-        <v>255</v>
+        <v>410</v>
       </c>
       <c r="E246" t="s">
-        <v>409</v>
+        <v>164</v>
       </c>
       <c r="F246" t="s">
-        <v>164</v>
+        <v>256</v>
       </c>
       <c r="G246" t="s">
-        <v>410</v>
+        <v>402</v>
       </c>
     </row>
     <row r="247" spans="1:7">
@@ -7277,16 +7277,16 @@
         <v>8</v>
       </c>
       <c r="C247" t="s">
+        <v>95</v>
+      </c>
+      <c r="E247" t="s">
+        <v>96</v>
+      </c>
+      <c r="F247" t="s">
+        <v>97</v>
+      </c>
+      <c r="G247" t="s">
         <v>412</v>
-      </c>
-      <c r="D247" t="s">
-        <v>95</v>
-      </c>
-      <c r="F247" t="s">
-        <v>96</v>
-      </c>
-      <c r="G247" t="s">
-        <v>97</v>
       </c>
     </row>
     <row r="248" spans="1:7">
@@ -7297,16 +7297,16 @@
         <v>8</v>
       </c>
       <c r="C248" t="s">
+        <v>95</v>
+      </c>
+      <c r="E248" t="s">
+        <v>96</v>
+      </c>
+      <c r="F248" t="s">
+        <v>97</v>
+      </c>
+      <c r="G248" t="s">
         <v>412</v>
-      </c>
-      <c r="D248" t="s">
-        <v>95</v>
-      </c>
-      <c r="F248" t="s">
-        <v>96</v>
-      </c>
-      <c r="G248" t="s">
-        <v>97</v>
       </c>
     </row>
     <row r="249" spans="1:7">
@@ -7317,16 +7317,16 @@
         <v>8</v>
       </c>
       <c r="C249" t="s">
+        <v>415</v>
+      </c>
+      <c r="E249" t="s">
+        <v>96</v>
+      </c>
+      <c r="F249" t="s">
+        <v>416</v>
+      </c>
+      <c r="G249" t="s">
         <v>412</v>
-      </c>
-      <c r="D249" t="s">
-        <v>415</v>
-      </c>
-      <c r="F249" t="s">
-        <v>96</v>
-      </c>
-      <c r="G249" t="s">
-        <v>416</v>
       </c>
     </row>
     <row r="250" spans="1:7">
@@ -7337,16 +7337,16 @@
         <v>8</v>
       </c>
       <c r="C250" t="s">
+        <v>95</v>
+      </c>
+      <c r="E250" t="s">
+        <v>96</v>
+      </c>
+      <c r="F250" t="s">
+        <v>97</v>
+      </c>
+      <c r="G250" t="s">
         <v>412</v>
-      </c>
-      <c r="D250" t="s">
-        <v>95</v>
-      </c>
-      <c r="F250" t="s">
-        <v>96</v>
-      </c>
-      <c r="G250" t="s">
-        <v>97</v>
       </c>
     </row>
     <row r="251" spans="1:7">
@@ -7357,16 +7357,16 @@
         <v>8</v>
       </c>
       <c r="C251" t="s">
+        <v>95</v>
+      </c>
+      <c r="E251" t="s">
+        <v>96</v>
+      </c>
+      <c r="F251" t="s">
+        <v>97</v>
+      </c>
+      <c r="G251" t="s">
         <v>412</v>
-      </c>
-      <c r="D251" t="s">
-        <v>95</v>
-      </c>
-      <c r="F251" t="s">
-        <v>96</v>
-      </c>
-      <c r="G251" t="s">
-        <v>97</v>
       </c>
     </row>
     <row r="252" spans="1:7">
@@ -7377,16 +7377,16 @@
         <v>8</v>
       </c>
       <c r="C252" t="s">
+        <v>95</v>
+      </c>
+      <c r="E252" t="s">
+        <v>96</v>
+      </c>
+      <c r="F252" t="s">
+        <v>97</v>
+      </c>
+      <c r="G252" t="s">
         <v>412</v>
-      </c>
-      <c r="D252" t="s">
-        <v>95</v>
-      </c>
-      <c r="F252" t="s">
-        <v>96</v>
-      </c>
-      <c r="G252" t="s">
-        <v>97</v>
       </c>
     </row>
     <row r="253" spans="1:7">
@@ -7399,11 +7399,11 @@
       <c r="C253" t="s">
         <v>421</v>
       </c>
-      <c r="D253" t="s">
+      <c r="E253" t="s">
+        <v>164</v>
+      </c>
+      <c r="F253" t="s">
         <v>422</v>
-      </c>
-      <c r="F253" t="s">
-        <v>164</v>
       </c>
       <c r="G253" t="s">
         <v>423</v>
@@ -7417,16 +7417,16 @@
         <v>8</v>
       </c>
       <c r="C254" t="s">
-        <v>421</v>
-      </c>
-      <c r="D254" t="s">
         <v>219</v>
       </c>
+      <c r="E254" t="s">
+        <v>91</v>
+      </c>
       <c r="F254" t="s">
-        <v>92</v>
+        <v>220</v>
       </c>
       <c r="G254" t="s">
-        <v>220</v>
+        <v>423</v>
       </c>
     </row>
     <row r="255" spans="1:7">
@@ -7437,16 +7437,16 @@
         <v>8</v>
       </c>
       <c r="C255" t="s">
-        <v>421</v>
-      </c>
-      <c r="D255" t="s">
         <v>426</v>
       </c>
+      <c r="E255" t="s">
+        <v>91</v>
+      </c>
       <c r="F255" t="s">
-        <v>92</v>
+        <v>427</v>
       </c>
       <c r="G255" t="s">
-        <v>427</v>
+        <v>423</v>
       </c>
     </row>
     <row r="256" spans="1:7">
@@ -7457,16 +7457,16 @@
         <v>8</v>
       </c>
       <c r="C256" t="s">
-        <v>421</v>
-      </c>
-      <c r="D256" t="s">
         <v>426</v>
       </c>
+      <c r="E256" t="s">
+        <v>91</v>
+      </c>
       <c r="F256" t="s">
-        <v>92</v>
+        <v>427</v>
       </c>
       <c r="G256" t="s">
-        <v>427</v>
+        <v>423</v>
       </c>
     </row>
     <row r="257" spans="1:7">
@@ -7477,16 +7477,16 @@
         <v>8</v>
       </c>
       <c r="C257" t="s">
-        <v>421</v>
-      </c>
-      <c r="D257" t="s">
         <v>426</v>
       </c>
+      <c r="E257" t="s">
+        <v>91</v>
+      </c>
       <c r="F257" t="s">
-        <v>92</v>
+        <v>427</v>
       </c>
       <c r="G257" t="s">
-        <v>427</v>
+        <v>423</v>
       </c>
     </row>
     <row r="258" spans="1:7">
@@ -7497,16 +7497,16 @@
         <v>8</v>
       </c>
       <c r="C258" t="s">
-        <v>421</v>
-      </c>
-      <c r="D258" t="s">
-        <v>326</v>
+        <v>325</v>
+      </c>
+      <c r="E258" t="s">
+        <v>164</v>
       </c>
       <c r="F258" t="s">
-        <v>164</v>
+        <v>327</v>
       </c>
       <c r="G258" t="s">
-        <v>328</v>
+        <v>423</v>
       </c>
     </row>
     <row r="259" spans="1:7">
@@ -7517,16 +7517,16 @@
         <v>8</v>
       </c>
       <c r="C259" t="s">
-        <v>421</v>
-      </c>
-      <c r="D259" t="s">
         <v>426</v>
       </c>
+      <c r="E259" t="s">
+        <v>91</v>
+      </c>
       <c r="F259" t="s">
-        <v>92</v>
+        <v>427</v>
       </c>
       <c r="G259" t="s">
-        <v>427</v>
+        <v>423</v>
       </c>
     </row>
     <row r="260" spans="1:7">
@@ -7537,16 +7537,16 @@
         <v>8</v>
       </c>
       <c r="C260" t="s">
-        <v>421</v>
-      </c>
-      <c r="D260" t="s">
         <v>163</v>
       </c>
+      <c r="E260" t="s">
+        <v>164</v>
+      </c>
       <c r="F260" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="G260" t="s">
-        <v>165</v>
+        <v>423</v>
       </c>
     </row>
     <row r="261" spans="1:7">
@@ -7557,16 +7557,16 @@
         <v>8</v>
       </c>
       <c r="C261" t="s">
-        <v>421</v>
-      </c>
-      <c r="D261" t="s">
         <v>434</v>
       </c>
+      <c r="E261" t="s">
+        <v>196</v>
+      </c>
       <c r="F261" t="s">
-        <v>196</v>
+        <v>435</v>
       </c>
       <c r="G261" t="s">
-        <v>435</v>
+        <v>423</v>
       </c>
     </row>
     <row r="262" spans="1:7">
@@ -7577,16 +7577,16 @@
         <v>8</v>
       </c>
       <c r="C262" t="s">
-        <v>421</v>
-      </c>
-      <c r="D262" t="s">
         <v>163</v>
       </c>
+      <c r="E262" t="s">
+        <v>164</v>
+      </c>
       <c r="F262" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="G262" t="s">
-        <v>165</v>
+        <v>423</v>
       </c>
     </row>
     <row r="263" spans="1:7">
@@ -7597,16 +7597,16 @@
         <v>8</v>
       </c>
       <c r="C263" t="s">
-        <v>421</v>
-      </c>
-      <c r="D263" t="s">
         <v>438</v>
       </c>
+      <c r="E263" t="s">
+        <v>183</v>
+      </c>
       <c r="F263" t="s">
-        <v>183</v>
+        <v>439</v>
       </c>
       <c r="G263" t="s">
-        <v>439</v>
+        <v>423</v>
       </c>
     </row>
     <row r="264" spans="1:7">
@@ -7617,16 +7617,16 @@
         <v>8</v>
       </c>
       <c r="C264" t="s">
-        <v>421</v>
-      </c>
-      <c r="D264" t="s">
         <v>31</v>
       </c>
+      <c r="E264" t="s">
+        <v>32</v>
+      </c>
       <c r="F264" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G264" t="s">
-        <v>33</v>
+        <v>423</v>
       </c>
     </row>
     <row r="265" spans="1:7">
@@ -7637,16 +7637,16 @@
         <v>8</v>
       </c>
       <c r="C265" t="s">
-        <v>421</v>
-      </c>
-      <c r="D265" t="s">
-        <v>10</v>
+        <v>9</v>
+      </c>
+      <c r="E265" t="s">
+        <v>11</v>
       </c>
       <c r="F265" t="s">
         <v>12</v>
       </c>
       <c r="G265" t="s">
-        <v>13</v>
+        <v>423</v>
       </c>
     </row>
     <row r="266" spans="1:7">
@@ -7657,16 +7657,16 @@
         <v>8</v>
       </c>
       <c r="C266" t="s">
-        <v>421</v>
-      </c>
-      <c r="D266" t="s">
         <v>443</v>
       </c>
+      <c r="E266" t="s">
+        <v>114</v>
+      </c>
       <c r="F266" t="s">
-        <v>115</v>
+        <v>444</v>
       </c>
       <c r="G266" t="s">
-        <v>444</v>
+        <v>423</v>
       </c>
     </row>
     <row r="267" spans="1:7">
@@ -7677,16 +7677,16 @@
         <v>8</v>
       </c>
       <c r="C267" t="s">
+        <v>118</v>
+      </c>
+      <c r="E267" t="s">
+        <v>114</v>
+      </c>
+      <c r="F267" t="s">
+        <v>119</v>
+      </c>
+      <c r="G267" t="s">
         <v>446</v>
-      </c>
-      <c r="D267" t="s">
-        <v>118</v>
-      </c>
-      <c r="F267" t="s">
-        <v>115</v>
-      </c>
-      <c r="G267" t="s">
-        <v>119</v>
       </c>
     </row>
     <row r="268" spans="1:7">
@@ -7697,16 +7697,16 @@
         <v>8</v>
       </c>
       <c r="C268" t="s">
+        <v>202</v>
+      </c>
+      <c r="E268" t="s">
+        <v>183</v>
+      </c>
+      <c r="F268" t="s">
+        <v>203</v>
+      </c>
+      <c r="G268" t="s">
         <v>448</v>
-      </c>
-      <c r="D268" t="s">
-        <v>203</v>
-      </c>
-      <c r="F268" t="s">
-        <v>183</v>
-      </c>
-      <c r="G268" t="s">
-        <v>204</v>
       </c>
     </row>
     <row r="269" spans="1:7">
@@ -7717,16 +7717,16 @@
         <v>8</v>
       </c>
       <c r="C269" t="s">
+        <v>118</v>
+      </c>
+      <c r="E269" t="s">
+        <v>114</v>
+      </c>
+      <c r="F269" t="s">
+        <v>119</v>
+      </c>
+      <c r="G269" t="s">
         <v>450</v>
-      </c>
-      <c r="D269" t="s">
-        <v>118</v>
-      </c>
-      <c r="F269" t="s">
-        <v>115</v>
-      </c>
-      <c r="G269" t="s">
-        <v>119</v>
       </c>
     </row>
     <row r="270" spans="1:7">
@@ -7737,16 +7737,16 @@
         <v>8</v>
       </c>
       <c r="C270" t="s">
+        <v>118</v>
+      </c>
+      <c r="E270" t="s">
+        <v>114</v>
+      </c>
+      <c r="F270" t="s">
+        <v>119</v>
+      </c>
+      <c r="G270" t="s">
         <v>450</v>
-      </c>
-      <c r="D270" t="s">
-        <v>118</v>
-      </c>
-      <c r="F270" t="s">
-        <v>115</v>
-      </c>
-      <c r="G270" t="s">
-        <v>119</v>
       </c>
     </row>
     <row r="271" spans="1:7">
@@ -7759,11 +7759,11 @@
       <c r="C271" t="s">
         <v>453</v>
       </c>
-      <c r="D271" t="s">
+      <c r="E271" t="s">
+        <v>114</v>
+      </c>
+      <c r="F271" t="s">
         <v>454</v>
-      </c>
-      <c r="F271" t="s">
-        <v>115</v>
       </c>
       <c r="G271" t="s">
         <v>455</v>
@@ -7779,11 +7779,11 @@
       <c r="C272" t="s">
         <v>453</v>
       </c>
-      <c r="D272" t="s">
+      <c r="E272" t="s">
+        <v>114</v>
+      </c>
+      <c r="F272" t="s">
         <v>454</v>
-      </c>
-      <c r="F272" t="s">
-        <v>115</v>
       </c>
       <c r="G272" t="s">
         <v>455</v>
@@ -7799,11 +7799,11 @@
       <c r="C273" t="s">
         <v>453</v>
       </c>
-      <c r="D273" t="s">
+      <c r="E273" t="s">
+        <v>114</v>
+      </c>
+      <c r="F273" t="s">
         <v>454</v>
-      </c>
-      <c r="F273" t="s">
-        <v>115</v>
       </c>
       <c r="G273" t="s">
         <v>455</v>
@@ -7819,11 +7819,11 @@
       <c r="C274" t="s">
         <v>453</v>
       </c>
-      <c r="D274" t="s">
+      <c r="E274" t="s">
+        <v>114</v>
+      </c>
+      <c r="F274" t="s">
         <v>454</v>
-      </c>
-      <c r="F274" t="s">
-        <v>115</v>
       </c>
       <c r="G274" t="s">
         <v>455</v>
@@ -7839,11 +7839,11 @@
       <c r="C275" t="s">
         <v>453</v>
       </c>
-      <c r="D275" t="s">
+      <c r="E275" t="s">
+        <v>114</v>
+      </c>
+      <c r="F275" t="s">
         <v>454</v>
-      </c>
-      <c r="F275" t="s">
-        <v>115</v>
       </c>
       <c r="G275" t="s">
         <v>455</v>
@@ -7859,11 +7859,11 @@
       <c r="C276" t="s">
         <v>453</v>
       </c>
-      <c r="D276" t="s">
+      <c r="E276" t="s">
+        <v>114</v>
+      </c>
+      <c r="F276" t="s">
         <v>454</v>
-      </c>
-      <c r="F276" t="s">
-        <v>115</v>
       </c>
       <c r="G276" t="s">
         <v>455</v>
@@ -7879,11 +7879,11 @@
       <c r="C277" t="s">
         <v>453</v>
       </c>
-      <c r="D277" t="s">
+      <c r="E277" t="s">
+        <v>114</v>
+      </c>
+      <c r="F277" t="s">
         <v>454</v>
-      </c>
-      <c r="F277" t="s">
-        <v>115</v>
       </c>
       <c r="G277" t="s">
         <v>455</v>
@@ -7897,16 +7897,16 @@
         <v>8</v>
       </c>
       <c r="C278" t="s">
+        <v>202</v>
+      </c>
+      <c r="E278" t="s">
+        <v>183</v>
+      </c>
+      <c r="F278" t="s">
+        <v>203</v>
+      </c>
+      <c r="G278" t="s">
         <v>463</v>
-      </c>
-      <c r="D278" t="s">
-        <v>203</v>
-      </c>
-      <c r="F278" t="s">
-        <v>183</v>
-      </c>
-      <c r="G278" t="s">
-        <v>204</v>
       </c>
     </row>
     <row r="279" spans="1:7">
@@ -7917,16 +7917,16 @@
         <v>8</v>
       </c>
       <c r="C279" t="s">
+        <v>51</v>
+      </c>
+      <c r="E279" t="s">
+        <v>32</v>
+      </c>
+      <c r="F279" t="s">
+        <v>53</v>
+      </c>
+      <c r="G279" t="s">
         <v>463</v>
-      </c>
-      <c r="D279" t="s">
-        <v>52</v>
-      </c>
-      <c r="F279" t="s">
-        <v>32</v>
-      </c>
-      <c r="G279" t="s">
-        <v>54</v>
       </c>
     </row>
     <row r="280" spans="1:7">
@@ -7937,16 +7937,16 @@
         <v>8</v>
       </c>
       <c r="C280" t="s">
-        <v>463</v>
-      </c>
-      <c r="D280" t="s">
-        <v>10</v>
+        <v>9</v>
+      </c>
+      <c r="E280" t="s">
+        <v>11</v>
       </c>
       <c r="F280" t="s">
         <v>12</v>
       </c>
       <c r="G280" t="s">
-        <v>13</v>
+        <v>463</v>
       </c>
     </row>
     <row r="281" spans="1:7">
@@ -7957,16 +7957,16 @@
         <v>8</v>
       </c>
       <c r="C281" t="s">
+        <v>170</v>
+      </c>
+      <c r="E281" t="s">
+        <v>114</v>
+      </c>
+      <c r="F281" t="s">
+        <v>171</v>
+      </c>
+      <c r="G281" t="s">
         <v>463</v>
-      </c>
-      <c r="D281" t="s">
-        <v>170</v>
-      </c>
-      <c r="F281" t="s">
-        <v>115</v>
-      </c>
-      <c r="G281" t="s">
-        <v>171</v>
       </c>
     </row>
     <row r="282" spans="1:7">
@@ -7977,16 +7977,16 @@
         <v>8</v>
       </c>
       <c r="C282" t="s">
+        <v>124</v>
+      </c>
+      <c r="E282" t="s">
+        <v>125</v>
+      </c>
+      <c r="F282" t="s">
+        <v>126</v>
+      </c>
+      <c r="G282" t="s">
         <v>463</v>
-      </c>
-      <c r="D282" t="s">
-        <v>124</v>
-      </c>
-      <c r="F282" t="s">
-        <v>125</v>
-      </c>
-      <c r="G282" t="s">
-        <v>126</v>
       </c>
     </row>
     <row r="283" spans="1:7">
@@ -7997,16 +7997,16 @@
         <v>8</v>
       </c>
       <c r="C283" t="s">
+        <v>398</v>
+      </c>
+      <c r="E283" t="s">
+        <v>164</v>
+      </c>
+      <c r="F283" t="s">
+        <v>365</v>
+      </c>
+      <c r="G283" t="s">
         <v>469</v>
-      </c>
-      <c r="D283" t="s">
-        <v>364</v>
-      </c>
-      <c r="F283" t="s">
-        <v>164</v>
-      </c>
-      <c r="G283" t="s">
-        <v>399</v>
       </c>
     </row>
     <row r="284" spans="1:7">
@@ -8017,16 +8017,16 @@
         <v>8</v>
       </c>
       <c r="C284" t="s">
+        <v>124</v>
+      </c>
+      <c r="E284" t="s">
+        <v>125</v>
+      </c>
+      <c r="F284" t="s">
+        <v>126</v>
+      </c>
+      <c r="G284" t="s">
         <v>471</v>
-      </c>
-      <c r="D284" t="s">
-        <v>124</v>
-      </c>
-      <c r="F284" t="s">
-        <v>125</v>
-      </c>
-      <c r="G284" t="s">
-        <v>126</v>
       </c>
     </row>
     <row r="285" spans="1:7">
@@ -8037,16 +8037,16 @@
         <v>8</v>
       </c>
       <c r="C285" t="s">
+        <v>170</v>
+      </c>
+      <c r="E285" t="s">
+        <v>114</v>
+      </c>
+      <c r="F285" t="s">
+        <v>171</v>
+      </c>
+      <c r="G285" t="s">
         <v>473</v>
-      </c>
-      <c r="D285" t="s">
-        <v>170</v>
-      </c>
-      <c r="F285" t="s">
-        <v>115</v>
-      </c>
-      <c r="G285" t="s">
-        <v>171</v>
       </c>
     </row>
     <row r="286" spans="1:7">
@@ -8057,16 +8057,16 @@
         <v>8</v>
       </c>
       <c r="C286" t="s">
+        <v>438</v>
+      </c>
+      <c r="E286" t="s">
+        <v>183</v>
+      </c>
+      <c r="F286" t="s">
+        <v>439</v>
+      </c>
+      <c r="G286" t="s">
         <v>475</v>
-      </c>
-      <c r="D286" t="s">
-        <v>438</v>
-      </c>
-      <c r="F286" t="s">
-        <v>183</v>
-      </c>
-      <c r="G286" t="s">
-        <v>439</v>
       </c>
     </row>
     <row r="287" spans="1:7">
@@ -8077,16 +8077,16 @@
         <v>8</v>
       </c>
       <c r="C287" t="s">
+        <v>438</v>
+      </c>
+      <c r="E287" t="s">
+        <v>183</v>
+      </c>
+      <c r="F287" t="s">
+        <v>439</v>
+      </c>
+      <c r="G287" t="s">
         <v>475</v>
-      </c>
-      <c r="D287" t="s">
-        <v>438</v>
-      </c>
-      <c r="F287" t="s">
-        <v>183</v>
-      </c>
-      <c r="G287" t="s">
-        <v>439</v>
       </c>
     </row>
     <row r="288" spans="1:7">
@@ -8097,16 +8097,16 @@
         <v>8</v>
       </c>
       <c r="C288" t="s">
+        <v>41</v>
+      </c>
+      <c r="E288" t="s">
+        <v>11</v>
+      </c>
+      <c r="F288" t="s">
+        <v>42</v>
+      </c>
+      <c r="G288" t="s">
         <v>475</v>
-      </c>
-      <c r="D288" t="s">
-        <v>41</v>
-      </c>
-      <c r="F288" t="s">
-        <v>12</v>
-      </c>
-      <c r="G288" t="s">
-        <v>42</v>
       </c>
     </row>
     <row r="289" spans="1:7">
@@ -8117,16 +8117,16 @@
         <v>8</v>
       </c>
       <c r="C289" t="s">
+        <v>31</v>
+      </c>
+      <c r="E289" t="s">
+        <v>32</v>
+      </c>
+      <c r="F289" t="s">
+        <v>33</v>
+      </c>
+      <c r="G289" t="s">
         <v>475</v>
-      </c>
-      <c r="D289" t="s">
-        <v>31</v>
-      </c>
-      <c r="F289" t="s">
-        <v>32</v>
-      </c>
-      <c r="G289" t="s">
-        <v>33</v>
       </c>
     </row>
     <row r="290" spans="1:7">
@@ -8137,16 +8137,16 @@
         <v>8</v>
       </c>
       <c r="C290" t="s">
+        <v>31</v>
+      </c>
+      <c r="E290" t="s">
+        <v>32</v>
+      </c>
+      <c r="F290" t="s">
+        <v>33</v>
+      </c>
+      <c r="G290" t="s">
         <v>475</v>
-      </c>
-      <c r="D290" t="s">
-        <v>31</v>
-      </c>
-      <c r="F290" t="s">
-        <v>32</v>
-      </c>
-      <c r="G290" t="s">
-        <v>33</v>
       </c>
     </row>
     <row r="291" spans="1:7">
@@ -8157,16 +8157,16 @@
         <v>8</v>
       </c>
       <c r="C291" t="s">
+        <v>170</v>
+      </c>
+      <c r="E291" t="s">
+        <v>114</v>
+      </c>
+      <c r="F291" t="s">
+        <v>171</v>
+      </c>
+      <c r="G291" t="s">
         <v>475</v>
-      </c>
-      <c r="D291" t="s">
-        <v>170</v>
-      </c>
-      <c r="F291" t="s">
-        <v>115</v>
-      </c>
-      <c r="G291" t="s">
-        <v>171</v>
       </c>
     </row>
     <row r="292" spans="1:7">
@@ -8177,16 +8177,16 @@
         <v>8</v>
       </c>
       <c r="C292" t="s">
+        <v>170</v>
+      </c>
+      <c r="E292" t="s">
+        <v>114</v>
+      </c>
+      <c r="F292" t="s">
+        <v>171</v>
+      </c>
+      <c r="G292" t="s">
         <v>475</v>
-      </c>
-      <c r="D292" t="s">
-        <v>170</v>
-      </c>
-      <c r="F292" t="s">
-        <v>115</v>
-      </c>
-      <c r="G292" t="s">
-        <v>171</v>
       </c>
     </row>
     <row r="293" spans="1:7">
@@ -8197,16 +8197,16 @@
         <v>8</v>
       </c>
       <c r="C293" t="s">
+        <v>170</v>
+      </c>
+      <c r="E293" t="s">
+        <v>114</v>
+      </c>
+      <c r="F293" t="s">
+        <v>171</v>
+      </c>
+      <c r="G293" t="s">
         <v>475</v>
-      </c>
-      <c r="D293" t="s">
-        <v>170</v>
-      </c>
-      <c r="F293" t="s">
-        <v>115</v>
-      </c>
-      <c r="G293" t="s">
-        <v>171</v>
       </c>
     </row>
     <row r="294" spans="1:7">
@@ -8217,16 +8217,16 @@
         <v>8</v>
       </c>
       <c r="C294" t="s">
+        <v>170</v>
+      </c>
+      <c r="E294" t="s">
+        <v>114</v>
+      </c>
+      <c r="F294" t="s">
+        <v>171</v>
+      </c>
+      <c r="G294" t="s">
         <v>475</v>
-      </c>
-      <c r="D294" t="s">
-        <v>170</v>
-      </c>
-      <c r="F294" t="s">
-        <v>115</v>
-      </c>
-      <c r="G294" t="s">
-        <v>171</v>
       </c>
     </row>
     <row r="295" spans="1:7">
@@ -8237,16 +8237,16 @@
         <v>8</v>
       </c>
       <c r="C295" t="s">
+        <v>170</v>
+      </c>
+      <c r="E295" t="s">
+        <v>114</v>
+      </c>
+      <c r="F295" t="s">
+        <v>171</v>
+      </c>
+      <c r="G295" t="s">
         <v>485</v>
-      </c>
-      <c r="D295" t="s">
-        <v>170</v>
-      </c>
-      <c r="F295" t="s">
-        <v>115</v>
-      </c>
-      <c r="G295" t="s">
-        <v>171</v>
       </c>
     </row>
     <row r="296" spans="1:7">
@@ -8257,16 +8257,16 @@
         <v>8</v>
       </c>
       <c r="C296" t="s">
+        <v>170</v>
+      </c>
+      <c r="E296" t="s">
+        <v>114</v>
+      </c>
+      <c r="F296" t="s">
+        <v>171</v>
+      </c>
+      <c r="G296" t="s">
         <v>485</v>
-      </c>
-      <c r="D296" t="s">
-        <v>170</v>
-      </c>
-      <c r="F296" t="s">
-        <v>115</v>
-      </c>
-      <c r="G296" t="s">
-        <v>171</v>
       </c>
     </row>
   </sheetData>

--- a/api/2/xlsx/fr/SectorCOFOG.xlsx
+++ b/api/2/xlsx/fr/SectorCOFOG.xlsx
@@ -31,12 +31,12 @@
     <t>codeforiati:cofog-division</t>
   </si>
   <si>
+    <t>codeforiati:group-code</t>
+  </si>
+  <si>
     <t>codeforiati:cofog-group</t>
   </si>
   <si>
-    <t>codeforiati:group-code</t>
-  </si>
-  <si>
     <t>11110</t>
   </si>
   <si>
@@ -52,12 +52,12 @@
     <t>09 - Education</t>
   </si>
   <si>
+    <t>110</t>
+  </si>
+  <si>
     <t>09.8 - Education n.e.c.</t>
   </si>
   <si>
-    <t>110</t>
-  </si>
-  <si>
     <t>11120</t>
   </si>
   <si>
@@ -175,12 +175,12 @@
     <t>121</t>
   </si>
   <si>
+    <t>120</t>
+  </si>
+  <si>
     <t>07.6 - Health n.e.c.</t>
   </si>
   <si>
-    <t>120</t>
-  </si>
-  <si>
     <t>12181</t>
   </si>
   <si>
@@ -292,12 +292,12 @@
     <t>06 - Housing and community amenities</t>
   </si>
   <si>
+    <t>140</t>
+  </si>
+  <si>
     <t>06.3 - Water supply</t>
   </si>
   <si>
-    <t>140</t>
-  </si>
-  <si>
     <t>14015</t>
   </si>
   <si>
@@ -361,12 +361,12 @@
     <t>01 - General public services</t>
   </si>
   <si>
+    <t>150</t>
+  </si>
+  <si>
     <t>01.3 - General services</t>
   </si>
   <si>
-    <t>150</t>
-  </si>
-  <si>
     <t>15111</t>
   </si>
   <si>
@@ -625,12 +625,12 @@
     <t>10.9.0 - Social protection n.e.c. (CS)</t>
   </si>
   <si>
+    <t>160</t>
+  </si>
+  <si>
     <t>10.9 - Social protection n.e.c.</t>
   </si>
   <si>
-    <t>160</t>
-  </si>
-  <si>
     <t>16011</t>
   </si>
   <si>
@@ -829,12 +829,12 @@
     <t>231</t>
   </si>
   <si>
+    <t>230</t>
+  </si>
+  <si>
     <t>04.3 - Fuel and energy</t>
   </si>
   <si>
-    <t>230</t>
-  </si>
-  <si>
     <t>23111</t>
   </si>
   <si>
@@ -997,12 +997,12 @@
     <t>311</t>
   </si>
   <si>
+    <t>310</t>
+  </si>
+  <si>
     <t>04.2 - Agriculture, forestry, fishing and hunting</t>
   </si>
   <si>
-    <t>310</t>
-  </si>
-  <si>
     <t>31120</t>
   </si>
   <si>
@@ -1111,12 +1111,12 @@
     <t>321</t>
   </si>
   <si>
+    <t>320</t>
+  </si>
+  <si>
     <t>04.4 - Mining, manufacturing and construction</t>
   </si>
   <si>
-    <t>320</t>
-  </si>
-  <si>
     <t>32120</t>
   </si>
   <si>
@@ -1282,12 +1282,12 @@
     <t>04.9.0 - Economic affairs n.e.c. (CS)</t>
   </si>
   <si>
+    <t>430</t>
+  </si>
+  <si>
     <t>04.9 - Economic affairs n.e.c.</t>
   </si>
   <si>
-    <t>430</t>
-  </si>
-  <si>
     <t>43030</t>
   </si>
   <si>
@@ -1378,10 +1378,10 @@
     <t>01.7.0 - Public debt transactions (CS)</t>
   </si>
   <si>
+    <t>600</t>
+  </si>
+  <si>
     <t>01.7 - Public debt transactions</t>
-  </si>
-  <si>
-    <t>600</t>
   </si>
   <si>
     <t>60020</t>
@@ -1872,10 +1872,10 @@
         <v>11</v>
       </c>
       <c r="F3" t="s">
+        <v>12</v>
+      </c>
+      <c r="G3" t="s">
         <v>16</v>
-      </c>
-      <c r="G3" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -1918,10 +1918,10 @@
         <v>11</v>
       </c>
       <c r="F5" t="s">
+        <v>12</v>
+      </c>
+      <c r="G5" t="s">
         <v>20</v>
-      </c>
-      <c r="G5" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -1941,10 +1941,10 @@
         <v>11</v>
       </c>
       <c r="F6" t="s">
+        <v>12</v>
+      </c>
+      <c r="G6" t="s">
         <v>24</v>
-      </c>
-      <c r="G6" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -1987,10 +1987,10 @@
         <v>11</v>
       </c>
       <c r="F8" t="s">
+        <v>12</v>
+      </c>
+      <c r="G8" t="s">
         <v>24</v>
-      </c>
-      <c r="G8" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -2010,10 +2010,10 @@
         <v>11</v>
       </c>
       <c r="F9" t="s">
+        <v>12</v>
+      </c>
+      <c r="G9" t="s">
         <v>24</v>
-      </c>
-      <c r="G9" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -2033,10 +2033,10 @@
         <v>11</v>
       </c>
       <c r="F10" t="s">
+        <v>12</v>
+      </c>
+      <c r="G10" t="s">
         <v>24</v>
-      </c>
-      <c r="G10" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -2056,10 +2056,10 @@
         <v>32</v>
       </c>
       <c r="F11" t="s">
+        <v>12</v>
+      </c>
+      <c r="G11" t="s">
         <v>33</v>
-      </c>
-      <c r="G11" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -2079,10 +2079,10 @@
         <v>11</v>
       </c>
       <c r="F12" t="s">
+        <v>12</v>
+      </c>
+      <c r="G12" t="s">
         <v>36</v>
-      </c>
-      <c r="G12" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -2102,10 +2102,10 @@
         <v>11</v>
       </c>
       <c r="F13" t="s">
+        <v>12</v>
+      </c>
+      <c r="G13" t="s">
         <v>36</v>
-      </c>
-      <c r="G13" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -2125,10 +2125,10 @@
         <v>11</v>
       </c>
       <c r="F14" t="s">
+        <v>12</v>
+      </c>
+      <c r="G14" t="s">
         <v>42</v>
-      </c>
-      <c r="G14" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -2148,10 +2148,10 @@
         <v>11</v>
       </c>
       <c r="F15" t="s">
+        <v>12</v>
+      </c>
+      <c r="G15" t="s">
         <v>46</v>
-      </c>
-      <c r="G15" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -2171,10 +2171,10 @@
         <v>11</v>
       </c>
       <c r="F16" t="s">
+        <v>12</v>
+      </c>
+      <c r="G16" t="s">
         <v>49</v>
-      </c>
-      <c r="G16" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -2240,10 +2240,10 @@
         <v>32</v>
       </c>
       <c r="F19" t="s">
+        <v>53</v>
+      </c>
+      <c r="G19" t="s">
         <v>58</v>
-      </c>
-      <c r="G19" t="s">
-        <v>54</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -2263,10 +2263,10 @@
         <v>32</v>
       </c>
       <c r="F20" t="s">
+        <v>53</v>
+      </c>
+      <c r="G20" t="s">
         <v>61</v>
-      </c>
-      <c r="G20" t="s">
-        <v>54</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -2309,10 +2309,10 @@
         <v>32</v>
       </c>
       <c r="F22" t="s">
+        <v>53</v>
+      </c>
+      <c r="G22" t="s">
         <v>33</v>
-      </c>
-      <c r="G22" t="s">
-        <v>54</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -2332,10 +2332,10 @@
         <v>32</v>
       </c>
       <c r="F23" t="s">
+        <v>53</v>
+      </c>
+      <c r="G23" t="s">
         <v>67</v>
-      </c>
-      <c r="G23" t="s">
-        <v>54</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -2355,10 +2355,10 @@
         <v>32</v>
       </c>
       <c r="F24" t="s">
+        <v>53</v>
+      </c>
+      <c r="G24" t="s">
         <v>33</v>
-      </c>
-      <c r="G24" t="s">
-        <v>54</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -2378,10 +2378,10 @@
         <v>32</v>
       </c>
       <c r="F25" t="s">
+        <v>53</v>
+      </c>
+      <c r="G25" t="s">
         <v>33</v>
-      </c>
-      <c r="G25" t="s">
-        <v>54</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -2401,10 +2401,10 @@
         <v>32</v>
       </c>
       <c r="F26" t="s">
+        <v>53</v>
+      </c>
+      <c r="G26" t="s">
         <v>33</v>
-      </c>
-      <c r="G26" t="s">
-        <v>54</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -2424,10 +2424,10 @@
         <v>32</v>
       </c>
       <c r="F27" t="s">
+        <v>53</v>
+      </c>
+      <c r="G27" t="s">
         <v>33</v>
-      </c>
-      <c r="G27" t="s">
-        <v>54</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -2447,10 +2447,10 @@
         <v>32</v>
       </c>
       <c r="F28" t="s">
+        <v>53</v>
+      </c>
+      <c r="G28" t="s">
         <v>33</v>
-      </c>
-      <c r="G28" t="s">
-        <v>54</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -2470,10 +2470,10 @@
         <v>32</v>
       </c>
       <c r="F29" t="s">
+        <v>53</v>
+      </c>
+      <c r="G29" t="s">
         <v>33</v>
-      </c>
-      <c r="G29" t="s">
-        <v>54</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -2516,10 +2516,10 @@
         <v>32</v>
       </c>
       <c r="F31" t="s">
+        <v>53</v>
+      </c>
+      <c r="G31" t="s">
         <v>33</v>
-      </c>
-      <c r="G31" t="s">
-        <v>54</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -2539,10 +2539,10 @@
         <v>32</v>
       </c>
       <c r="F32" t="s">
+        <v>53</v>
+      </c>
+      <c r="G32" t="s">
         <v>33</v>
-      </c>
-      <c r="G32" t="s">
-        <v>54</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -2562,10 +2562,10 @@
         <v>32</v>
       </c>
       <c r="F33" t="s">
+        <v>53</v>
+      </c>
+      <c r="G33" t="s">
         <v>33</v>
-      </c>
-      <c r="G33" t="s">
-        <v>54</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -2585,10 +2585,10 @@
         <v>32</v>
       </c>
       <c r="F34" t="s">
+        <v>53</v>
+      </c>
+      <c r="G34" t="s">
         <v>33</v>
-      </c>
-      <c r="G34" t="s">
-        <v>54</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -2608,10 +2608,10 @@
         <v>32</v>
       </c>
       <c r="F35" t="s">
+        <v>53</v>
+      </c>
+      <c r="G35" t="s">
         <v>33</v>
-      </c>
-      <c r="G35" t="s">
-        <v>54</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -2631,10 +2631,10 @@
         <v>32</v>
       </c>
       <c r="F36" t="s">
+        <v>53</v>
+      </c>
+      <c r="G36" t="s">
         <v>58</v>
-      </c>
-      <c r="G36" t="s">
-        <v>54</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -2651,10 +2651,10 @@
         <v>32</v>
       </c>
       <c r="F37" t="s">
+        <v>83</v>
+      </c>
+      <c r="G37" t="s">
         <v>33</v>
-      </c>
-      <c r="G37" t="s">
-        <v>83</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -2671,10 +2671,10 @@
         <v>32</v>
       </c>
       <c r="F38" t="s">
+        <v>83</v>
+      </c>
+      <c r="G38" t="s">
         <v>33</v>
-      </c>
-      <c r="G38" t="s">
-        <v>83</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -2691,10 +2691,10 @@
         <v>32</v>
       </c>
       <c r="F39" t="s">
+        <v>83</v>
+      </c>
+      <c r="G39" t="s">
         <v>33</v>
-      </c>
-      <c r="G39" t="s">
-        <v>83</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -2711,10 +2711,10 @@
         <v>32</v>
       </c>
       <c r="F40" t="s">
+        <v>83</v>
+      </c>
+      <c r="G40" t="s">
         <v>33</v>
-      </c>
-      <c r="G40" t="s">
-        <v>83</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -2731,10 +2731,10 @@
         <v>32</v>
       </c>
       <c r="F41" t="s">
-        <v>53</v>
+        <v>83</v>
       </c>
       <c r="G41" t="s">
-        <v>83</v>
+        <v>54</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -2751,10 +2751,10 @@
         <v>32</v>
       </c>
       <c r="F42" t="s">
+        <v>83</v>
+      </c>
+      <c r="G42" t="s">
         <v>58</v>
-      </c>
-      <c r="G42" t="s">
-        <v>83</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -2791,10 +2791,10 @@
         <v>96</v>
       </c>
       <c r="F44" t="s">
+        <v>92</v>
+      </c>
+      <c r="G44" t="s">
         <v>97</v>
-      </c>
-      <c r="G44" t="s">
-        <v>93</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -2851,10 +2851,10 @@
         <v>96</v>
       </c>
       <c r="F47" t="s">
+        <v>92</v>
+      </c>
+      <c r="G47" t="s">
         <v>102</v>
-      </c>
-      <c r="G47" t="s">
-        <v>93</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -2911,10 +2911,10 @@
         <v>96</v>
       </c>
       <c r="F50" t="s">
+        <v>92</v>
+      </c>
+      <c r="G50" t="s">
         <v>102</v>
-      </c>
-      <c r="G50" t="s">
-        <v>93</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -2951,10 +2951,10 @@
         <v>96</v>
       </c>
       <c r="F52" t="s">
+        <v>92</v>
+      </c>
+      <c r="G52" t="s">
         <v>109</v>
-      </c>
-      <c r="G52" t="s">
-        <v>93</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -2971,10 +2971,10 @@
         <v>11</v>
       </c>
       <c r="F53" t="s">
-        <v>12</v>
+        <v>92</v>
       </c>
       <c r="G53" t="s">
-        <v>93</v>
+        <v>13</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -3017,10 +3017,10 @@
         <v>114</v>
       </c>
       <c r="F55" t="s">
+        <v>115</v>
+      </c>
+      <c r="G55" t="s">
         <v>119</v>
-      </c>
-      <c r="G55" t="s">
-        <v>116</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -3040,10 +3040,10 @@
         <v>114</v>
       </c>
       <c r="F56" t="s">
+        <v>115</v>
+      </c>
+      <c r="G56" t="s">
         <v>122</v>
-      </c>
-      <c r="G56" t="s">
-        <v>116</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -3063,10 +3063,10 @@
         <v>125</v>
       </c>
       <c r="F57" t="s">
+        <v>115</v>
+      </c>
+      <c r="G57" t="s">
         <v>126</v>
-      </c>
-      <c r="G57" t="s">
-        <v>116</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -3086,10 +3086,10 @@
         <v>114</v>
       </c>
       <c r="F58" t="s">
+        <v>115</v>
+      </c>
+      <c r="G58" t="s">
         <v>119</v>
-      </c>
-      <c r="G58" t="s">
-        <v>116</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -3109,10 +3109,10 @@
         <v>114</v>
       </c>
       <c r="F59" t="s">
+        <v>115</v>
+      </c>
+      <c r="G59" t="s">
         <v>119</v>
-      </c>
-      <c r="G59" t="s">
-        <v>116</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -3132,10 +3132,10 @@
         <v>114</v>
       </c>
       <c r="F60" t="s">
+        <v>115</v>
+      </c>
+      <c r="G60" t="s">
         <v>119</v>
-      </c>
-      <c r="G60" t="s">
-        <v>116</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -3155,10 +3155,10 @@
         <v>114</v>
       </c>
       <c r="F61" t="s">
+        <v>115</v>
+      </c>
+      <c r="G61" t="s">
         <v>119</v>
-      </c>
-      <c r="G61" t="s">
-        <v>116</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -3178,10 +3178,10 @@
         <v>114</v>
       </c>
       <c r="F62" t="s">
+        <v>115</v>
+      </c>
+      <c r="G62" t="s">
         <v>119</v>
-      </c>
-      <c r="G62" t="s">
-        <v>116</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -3201,10 +3201,10 @@
         <v>114</v>
       </c>
       <c r="F63" t="s">
+        <v>115</v>
+      </c>
+      <c r="G63" t="s">
         <v>119</v>
-      </c>
-      <c r="G63" t="s">
-        <v>116</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -3224,10 +3224,10 @@
         <v>114</v>
       </c>
       <c r="F64" t="s">
+        <v>115</v>
+      </c>
+      <c r="G64" t="s">
         <v>119</v>
-      </c>
-      <c r="G64" t="s">
-        <v>116</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -3247,10 +3247,10 @@
         <v>114</v>
       </c>
       <c r="F65" t="s">
+        <v>115</v>
+      </c>
+      <c r="G65" t="s">
         <v>137</v>
-      </c>
-      <c r="G65" t="s">
-        <v>116</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -3293,10 +3293,10 @@
         <v>114</v>
       </c>
       <c r="F67" t="s">
+        <v>115</v>
+      </c>
+      <c r="G67" t="s">
         <v>119</v>
-      </c>
-      <c r="G67" t="s">
-        <v>116</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -3362,10 +3362,10 @@
         <v>114</v>
       </c>
       <c r="F70" t="s">
+        <v>115</v>
+      </c>
+      <c r="G70" t="s">
         <v>122</v>
-      </c>
-      <c r="G70" t="s">
-        <v>116</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -3385,10 +3385,10 @@
         <v>114</v>
       </c>
       <c r="F71" t="s">
+        <v>115</v>
+      </c>
+      <c r="G71" t="s">
         <v>122</v>
-      </c>
-      <c r="G71" t="s">
-        <v>116</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -3431,10 +3431,10 @@
         <v>125</v>
       </c>
       <c r="F73" t="s">
+        <v>115</v>
+      </c>
+      <c r="G73" t="s">
         <v>149</v>
-      </c>
-      <c r="G73" t="s">
-        <v>116</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -3454,10 +3454,10 @@
         <v>125</v>
       </c>
       <c r="F74" t="s">
+        <v>115</v>
+      </c>
+      <c r="G74" t="s">
         <v>152</v>
-      </c>
-      <c r="G74" t="s">
-        <v>116</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -3477,10 +3477,10 @@
         <v>125</v>
       </c>
       <c r="F75" t="s">
+        <v>115</v>
+      </c>
+      <c r="G75" t="s">
         <v>155</v>
-      </c>
-      <c r="G75" t="s">
-        <v>116</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -3500,10 +3500,10 @@
         <v>125</v>
       </c>
       <c r="F76" t="s">
+        <v>115</v>
+      </c>
+      <c r="G76" t="s">
         <v>149</v>
-      </c>
-      <c r="G76" t="s">
-        <v>116</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -3523,10 +3523,10 @@
         <v>125</v>
       </c>
       <c r="F77" t="s">
+        <v>115</v>
+      </c>
+      <c r="G77" t="s">
         <v>149</v>
-      </c>
-      <c r="G77" t="s">
-        <v>116</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -3546,10 +3546,10 @@
         <v>125</v>
       </c>
       <c r="F78" t="s">
+        <v>115</v>
+      </c>
+      <c r="G78" t="s">
         <v>152</v>
-      </c>
-      <c r="G78" t="s">
-        <v>116</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -3569,10 +3569,10 @@
         <v>125</v>
       </c>
       <c r="F79" t="s">
+        <v>115</v>
+      </c>
+      <c r="G79" t="s">
         <v>161</v>
-      </c>
-      <c r="G79" t="s">
-        <v>116</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -3592,10 +3592,10 @@
         <v>164</v>
       </c>
       <c r="F80" t="s">
+        <v>115</v>
+      </c>
+      <c r="G80" t="s">
         <v>165</v>
-      </c>
-      <c r="G80" t="s">
-        <v>116</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -3615,10 +3615,10 @@
         <v>164</v>
       </c>
       <c r="F81" t="s">
+        <v>115</v>
+      </c>
+      <c r="G81" t="s">
         <v>165</v>
-      </c>
-      <c r="G81" t="s">
-        <v>116</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -3638,10 +3638,10 @@
         <v>164</v>
       </c>
       <c r="F82" t="s">
+        <v>115</v>
+      </c>
+      <c r="G82" t="s">
         <v>165</v>
-      </c>
-      <c r="G82" t="s">
-        <v>116</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -3684,10 +3684,10 @@
         <v>114</v>
       </c>
       <c r="F84" t="s">
+        <v>115</v>
+      </c>
+      <c r="G84" t="s">
         <v>171</v>
-      </c>
-      <c r="G84" t="s">
-        <v>116</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -3707,10 +3707,10 @@
         <v>114</v>
       </c>
       <c r="F85" t="s">
+        <v>115</v>
+      </c>
+      <c r="G85" t="s">
         <v>119</v>
-      </c>
-      <c r="G85" t="s">
-        <v>116</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -3730,10 +3730,10 @@
         <v>164</v>
       </c>
       <c r="F86" t="s">
+        <v>115</v>
+      </c>
+      <c r="G86" t="s">
         <v>176</v>
-      </c>
-      <c r="G86" t="s">
-        <v>116</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -3753,10 +3753,10 @@
         <v>114</v>
       </c>
       <c r="F87" t="s">
+        <v>115</v>
+      </c>
+      <c r="G87" t="s">
         <v>119</v>
-      </c>
-      <c r="G87" t="s">
-        <v>116</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -3776,10 +3776,10 @@
         <v>114</v>
       </c>
       <c r="F88" t="s">
+        <v>115</v>
+      </c>
+      <c r="G88" t="s">
         <v>119</v>
-      </c>
-      <c r="G88" t="s">
-        <v>116</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -3799,10 +3799,10 @@
         <v>114</v>
       </c>
       <c r="F89" t="s">
+        <v>115</v>
+      </c>
+      <c r="G89" t="s">
         <v>119</v>
-      </c>
-      <c r="G89" t="s">
-        <v>116</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -3822,10 +3822,10 @@
         <v>125</v>
       </c>
       <c r="F90" t="s">
+        <v>115</v>
+      </c>
+      <c r="G90" t="s">
         <v>126</v>
-      </c>
-      <c r="G90" t="s">
-        <v>116</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -3845,10 +3845,10 @@
         <v>183</v>
       </c>
       <c r="F91" t="s">
+        <v>115</v>
+      </c>
+      <c r="G91" t="s">
         <v>184</v>
-      </c>
-      <c r="G91" t="s">
-        <v>116</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -3868,10 +3868,10 @@
         <v>125</v>
       </c>
       <c r="F92" t="s">
+        <v>115</v>
+      </c>
+      <c r="G92" t="s">
         <v>126</v>
-      </c>
-      <c r="G92" t="s">
-        <v>116</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -3891,10 +3891,10 @@
         <v>114</v>
       </c>
       <c r="F93" t="s">
+        <v>115</v>
+      </c>
+      <c r="G93" t="s">
         <v>122</v>
-      </c>
-      <c r="G93" t="s">
-        <v>116</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -3914,10 +3914,10 @@
         <v>125</v>
       </c>
       <c r="F94" t="s">
+        <v>115</v>
+      </c>
+      <c r="G94" t="s">
         <v>126</v>
-      </c>
-      <c r="G94" t="s">
-        <v>116</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -3937,10 +3937,10 @@
         <v>114</v>
       </c>
       <c r="F95" t="s">
+        <v>115</v>
+      </c>
+      <c r="G95" t="s">
         <v>190</v>
-      </c>
-      <c r="G95" t="s">
-        <v>116</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -3960,10 +3960,10 @@
         <v>125</v>
       </c>
       <c r="F96" t="s">
+        <v>115</v>
+      </c>
+      <c r="G96" t="s">
         <v>126</v>
-      </c>
-      <c r="G96" t="s">
-        <v>116</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -3983,10 +3983,10 @@
         <v>125</v>
       </c>
       <c r="F97" t="s">
+        <v>115</v>
+      </c>
+      <c r="G97" t="s">
         <v>126</v>
-      </c>
-      <c r="G97" t="s">
-        <v>116</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -4006,10 +4006,10 @@
         <v>196</v>
       </c>
       <c r="F98" t="s">
+        <v>115</v>
+      </c>
+      <c r="G98" t="s">
         <v>197</v>
-      </c>
-      <c r="G98" t="s">
-        <v>116</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -4029,10 +4029,10 @@
         <v>125</v>
       </c>
       <c r="F99" t="s">
+        <v>115</v>
+      </c>
+      <c r="G99" t="s">
         <v>126</v>
-      </c>
-      <c r="G99" t="s">
-        <v>116</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -4052,10 +4052,10 @@
         <v>125</v>
       </c>
       <c r="F100" t="s">
+        <v>115</v>
+      </c>
+      <c r="G100" t="s">
         <v>155</v>
-      </c>
-      <c r="G100" t="s">
-        <v>116</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -4075,10 +4075,10 @@
         <v>125</v>
       </c>
       <c r="F101" t="s">
+        <v>115</v>
+      </c>
+      <c r="G101" t="s">
         <v>126</v>
-      </c>
-      <c r="G101" t="s">
-        <v>116</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -4155,10 +4155,10 @@
         <v>183</v>
       </c>
       <c r="F105" t="s">
+        <v>203</v>
+      </c>
+      <c r="G105" t="s">
         <v>209</v>
-      </c>
-      <c r="G105" t="s">
-        <v>204</v>
       </c>
     </row>
     <row r="106" spans="1:7">
@@ -4195,10 +4195,10 @@
         <v>183</v>
       </c>
       <c r="F107" t="s">
+        <v>203</v>
+      </c>
+      <c r="G107" t="s">
         <v>184</v>
-      </c>
-      <c r="G107" t="s">
-        <v>204</v>
       </c>
     </row>
     <row r="108" spans="1:7">
@@ -4215,10 +4215,10 @@
         <v>183</v>
       </c>
       <c r="F108" t="s">
+        <v>203</v>
+      </c>
+      <c r="G108" t="s">
         <v>214</v>
-      </c>
-      <c r="G108" t="s">
-        <v>204</v>
       </c>
     </row>
     <row r="109" spans="1:7">
@@ -4235,10 +4235,10 @@
         <v>91</v>
       </c>
       <c r="F109" t="s">
+        <v>203</v>
+      </c>
+      <c r="G109" t="s">
         <v>217</v>
-      </c>
-      <c r="G109" t="s">
-        <v>204</v>
       </c>
     </row>
     <row r="110" spans="1:7">
@@ -4255,10 +4255,10 @@
         <v>91</v>
       </c>
       <c r="F110" t="s">
+        <v>203</v>
+      </c>
+      <c r="G110" t="s">
         <v>220</v>
-      </c>
-      <c r="G110" t="s">
-        <v>204</v>
       </c>
     </row>
     <row r="111" spans="1:7">
@@ -4295,10 +4295,10 @@
         <v>224</v>
       </c>
       <c r="F112" t="s">
+        <v>203</v>
+      </c>
+      <c r="G112" t="s">
         <v>225</v>
-      </c>
-      <c r="G112" t="s">
-        <v>204</v>
       </c>
     </row>
     <row r="113" spans="1:7">
@@ -4315,10 +4315,10 @@
         <v>114</v>
       </c>
       <c r="F113" t="s">
-        <v>115</v>
+        <v>203</v>
       </c>
       <c r="G113" t="s">
-        <v>204</v>
+        <v>116</v>
       </c>
     </row>
     <row r="114" spans="1:7">
@@ -4335,10 +4335,10 @@
         <v>125</v>
       </c>
       <c r="F114" t="s">
+        <v>203</v>
+      </c>
+      <c r="G114" t="s">
         <v>152</v>
-      </c>
-      <c r="G114" t="s">
-        <v>204</v>
       </c>
     </row>
     <row r="115" spans="1:7">
@@ -4355,10 +4355,10 @@
         <v>183</v>
       </c>
       <c r="F115" t="s">
+        <v>203</v>
+      </c>
+      <c r="G115" t="s">
         <v>184</v>
-      </c>
-      <c r="G115" t="s">
-        <v>204</v>
       </c>
     </row>
     <row r="116" spans="1:7">
@@ -4375,10 +4375,10 @@
         <v>224</v>
       </c>
       <c r="F116" t="s">
+        <v>203</v>
+      </c>
+      <c r="G116" t="s">
         <v>231</v>
-      </c>
-      <c r="G116" t="s">
-        <v>204</v>
       </c>
     </row>
     <row r="117" spans="1:7">
@@ -4395,10 +4395,10 @@
         <v>224</v>
       </c>
       <c r="F117" t="s">
+        <v>203</v>
+      </c>
+      <c r="G117" t="s">
         <v>225</v>
-      </c>
-      <c r="G117" t="s">
-        <v>204</v>
       </c>
     </row>
     <row r="118" spans="1:7">
@@ -4415,10 +4415,10 @@
         <v>164</v>
       </c>
       <c r="F118" t="s">
+        <v>203</v>
+      </c>
+      <c r="G118" t="s">
         <v>165</v>
-      </c>
-      <c r="G118" t="s">
-        <v>204</v>
       </c>
     </row>
     <row r="119" spans="1:7">
@@ -4435,10 +4435,10 @@
         <v>183</v>
       </c>
       <c r="F119" t="s">
+        <v>203</v>
+      </c>
+      <c r="G119" t="s">
         <v>184</v>
-      </c>
-      <c r="G119" t="s">
-        <v>204</v>
       </c>
     </row>
     <row r="120" spans="1:7">
@@ -4455,10 +4455,10 @@
         <v>114</v>
       </c>
       <c r="F120" t="s">
+        <v>237</v>
+      </c>
+      <c r="G120" t="s">
         <v>171</v>
-      </c>
-      <c r="G120" t="s">
-        <v>237</v>
       </c>
     </row>
     <row r="121" spans="1:7">
@@ -4475,10 +4475,10 @@
         <v>114</v>
       </c>
       <c r="F121" t="s">
-        <v>115</v>
+        <v>237</v>
       </c>
       <c r="G121" t="s">
-        <v>237</v>
+        <v>116</v>
       </c>
     </row>
     <row r="122" spans="1:7">
@@ -4495,10 +4495,10 @@
         <v>114</v>
       </c>
       <c r="F122" t="s">
+        <v>237</v>
+      </c>
+      <c r="G122" t="s">
         <v>171</v>
-      </c>
-      <c r="G122" t="s">
-        <v>237</v>
       </c>
     </row>
     <row r="123" spans="1:7">
@@ -4515,10 +4515,10 @@
         <v>114</v>
       </c>
       <c r="F123" t="s">
+        <v>237</v>
+      </c>
+      <c r="G123" t="s">
         <v>171</v>
-      </c>
-      <c r="G123" t="s">
-        <v>237</v>
       </c>
     </row>
     <row r="124" spans="1:7">
@@ -4535,10 +4535,10 @@
         <v>164</v>
       </c>
       <c r="F124" t="s">
+        <v>237</v>
+      </c>
+      <c r="G124" t="s">
         <v>243</v>
-      </c>
-      <c r="G124" t="s">
-        <v>237</v>
       </c>
     </row>
     <row r="125" spans="1:7">
@@ -4555,10 +4555,10 @@
         <v>164</v>
       </c>
       <c r="F125" t="s">
+        <v>237</v>
+      </c>
+      <c r="G125" t="s">
         <v>243</v>
-      </c>
-      <c r="G125" t="s">
-        <v>237</v>
       </c>
     </row>
     <row r="126" spans="1:7">
@@ -4575,10 +4575,10 @@
         <v>164</v>
       </c>
       <c r="F126" t="s">
+        <v>237</v>
+      </c>
+      <c r="G126" t="s">
         <v>243</v>
-      </c>
-      <c r="G126" t="s">
-        <v>237</v>
       </c>
     </row>
     <row r="127" spans="1:7">
@@ -4595,10 +4595,10 @@
         <v>164</v>
       </c>
       <c r="F127" t="s">
+        <v>237</v>
+      </c>
+      <c r="G127" t="s">
         <v>243</v>
-      </c>
-      <c r="G127" t="s">
-        <v>237</v>
       </c>
     </row>
     <row r="128" spans="1:7">
@@ -4615,10 +4615,10 @@
         <v>164</v>
       </c>
       <c r="F128" t="s">
+        <v>237</v>
+      </c>
+      <c r="G128" t="s">
         <v>243</v>
-      </c>
-      <c r="G128" t="s">
-        <v>237</v>
       </c>
     </row>
     <row r="129" spans="1:7">
@@ -4635,10 +4635,10 @@
         <v>164</v>
       </c>
       <c r="F129" t="s">
+        <v>237</v>
+      </c>
+      <c r="G129" t="s">
         <v>243</v>
-      </c>
-      <c r="G129" t="s">
-        <v>237</v>
       </c>
     </row>
     <row r="130" spans="1:7">
@@ -4655,10 +4655,10 @@
         <v>164</v>
       </c>
       <c r="F130" t="s">
+        <v>237</v>
+      </c>
+      <c r="G130" t="s">
         <v>243</v>
-      </c>
-      <c r="G130" t="s">
-        <v>237</v>
       </c>
     </row>
     <row r="131" spans="1:7">
@@ -4675,10 +4675,10 @@
         <v>164</v>
       </c>
       <c r="F131" t="s">
+        <v>237</v>
+      </c>
+      <c r="G131" t="s">
         <v>243</v>
-      </c>
-      <c r="G131" t="s">
-        <v>237</v>
       </c>
     </row>
     <row r="132" spans="1:7">
@@ -4695,10 +4695,10 @@
         <v>164</v>
       </c>
       <c r="F132" t="s">
+        <v>237</v>
+      </c>
+      <c r="G132" t="s">
         <v>256</v>
-      </c>
-      <c r="G132" t="s">
-        <v>237</v>
       </c>
     </row>
     <row r="133" spans="1:7">
@@ -4715,10 +4715,10 @@
         <v>114</v>
       </c>
       <c r="F133" t="s">
+        <v>237</v>
+      </c>
+      <c r="G133" t="s">
         <v>190</v>
-      </c>
-      <c r="G133" t="s">
-        <v>237</v>
       </c>
     </row>
     <row r="134" spans="1:7">
@@ -4735,10 +4735,10 @@
         <v>164</v>
       </c>
       <c r="F134" t="s">
+        <v>259</v>
+      </c>
+      <c r="G134" t="s">
         <v>176</v>
-      </c>
-      <c r="G134" t="s">
-        <v>259</v>
       </c>
     </row>
     <row r="135" spans="1:7">
@@ -4755,10 +4755,10 @@
         <v>164</v>
       </c>
       <c r="F135" t="s">
+        <v>259</v>
+      </c>
+      <c r="G135" t="s">
         <v>176</v>
-      </c>
-      <c r="G135" t="s">
-        <v>259</v>
       </c>
     </row>
     <row r="136" spans="1:7">
@@ -4775,10 +4775,10 @@
         <v>164</v>
       </c>
       <c r="F136" t="s">
+        <v>259</v>
+      </c>
+      <c r="G136" t="s">
         <v>176</v>
-      </c>
-      <c r="G136" t="s">
-        <v>259</v>
       </c>
     </row>
     <row r="137" spans="1:7">
@@ -4795,10 +4795,10 @@
         <v>164</v>
       </c>
       <c r="F137" t="s">
+        <v>259</v>
+      </c>
+      <c r="G137" t="s">
         <v>176</v>
-      </c>
-      <c r="G137" t="s">
-        <v>259</v>
       </c>
     </row>
     <row r="138" spans="1:7">
@@ -4815,10 +4815,10 @@
         <v>164</v>
       </c>
       <c r="F138" t="s">
+        <v>259</v>
+      </c>
+      <c r="G138" t="s">
         <v>176</v>
-      </c>
-      <c r="G138" t="s">
-        <v>259</v>
       </c>
     </row>
     <row r="139" spans="1:7">
@@ -4835,10 +4835,10 @@
         <v>224</v>
       </c>
       <c r="F139" t="s">
+        <v>259</v>
+      </c>
+      <c r="G139" t="s">
         <v>266</v>
-      </c>
-      <c r="G139" t="s">
-        <v>259</v>
       </c>
     </row>
     <row r="140" spans="1:7">
@@ -4855,10 +4855,10 @@
         <v>164</v>
       </c>
       <c r="F140" t="s">
+        <v>259</v>
+      </c>
+      <c r="G140" t="s">
         <v>176</v>
-      </c>
-      <c r="G140" t="s">
-        <v>259</v>
       </c>
     </row>
     <row r="141" spans="1:7">
@@ -4924,10 +4924,10 @@
         <v>164</v>
       </c>
       <c r="F143" t="s">
+        <v>271</v>
+      </c>
+      <c r="G143" t="s">
         <v>276</v>
-      </c>
-      <c r="G143" t="s">
-        <v>272</v>
       </c>
     </row>
     <row r="144" spans="1:7">
@@ -4947,10 +4947,10 @@
         <v>164</v>
       </c>
       <c r="F144" t="s">
+        <v>271</v>
+      </c>
+      <c r="G144" t="s">
         <v>276</v>
-      </c>
-      <c r="G144" t="s">
-        <v>272</v>
       </c>
     </row>
     <row r="145" spans="1:7">
@@ -4970,10 +4970,10 @@
         <v>164</v>
       </c>
       <c r="F145" t="s">
+        <v>271</v>
+      </c>
+      <c r="G145" t="s">
         <v>276</v>
-      </c>
-      <c r="G145" t="s">
-        <v>272</v>
       </c>
     </row>
     <row r="146" spans="1:7">
@@ -5565,10 +5565,10 @@
         <v>164</v>
       </c>
       <c r="F171" t="s">
+        <v>313</v>
+      </c>
+      <c r="G171" t="s">
         <v>165</v>
-      </c>
-      <c r="G171" t="s">
-        <v>313</v>
       </c>
     </row>
     <row r="172" spans="1:7">
@@ -5585,10 +5585,10 @@
         <v>114</v>
       </c>
       <c r="F172" t="s">
+        <v>313</v>
+      </c>
+      <c r="G172" t="s">
         <v>119</v>
-      </c>
-      <c r="G172" t="s">
-        <v>313</v>
       </c>
     </row>
     <row r="173" spans="1:7">
@@ -5605,10 +5605,10 @@
         <v>164</v>
       </c>
       <c r="F173" t="s">
+        <v>313</v>
+      </c>
+      <c r="G173" t="s">
         <v>165</v>
-      </c>
-      <c r="G173" t="s">
-        <v>313</v>
       </c>
     </row>
     <row r="174" spans="1:7">
@@ -5625,10 +5625,10 @@
         <v>164</v>
       </c>
       <c r="F174" t="s">
+        <v>313</v>
+      </c>
+      <c r="G174" t="s">
         <v>165</v>
-      </c>
-      <c r="G174" t="s">
-        <v>313</v>
       </c>
     </row>
     <row r="175" spans="1:7">
@@ -5645,10 +5645,10 @@
         <v>164</v>
       </c>
       <c r="F175" t="s">
+        <v>313</v>
+      </c>
+      <c r="G175" t="s">
         <v>165</v>
-      </c>
-      <c r="G175" t="s">
-        <v>313</v>
       </c>
     </row>
     <row r="176" spans="1:7">
@@ -5665,10 +5665,10 @@
         <v>164</v>
       </c>
       <c r="F176" t="s">
+        <v>313</v>
+      </c>
+      <c r="G176" t="s">
         <v>165</v>
-      </c>
-      <c r="G176" t="s">
-        <v>313</v>
       </c>
     </row>
     <row r="177" spans="1:7">
@@ -5685,10 +5685,10 @@
         <v>164</v>
       </c>
       <c r="F177" t="s">
+        <v>320</v>
+      </c>
+      <c r="G177" t="s">
         <v>165</v>
-      </c>
-      <c r="G177" t="s">
-        <v>320</v>
       </c>
     </row>
     <row r="178" spans="1:7">
@@ -5705,10 +5705,10 @@
         <v>164</v>
       </c>
       <c r="F178" t="s">
+        <v>320</v>
+      </c>
+      <c r="G178" t="s">
         <v>165</v>
-      </c>
-      <c r="G178" t="s">
-        <v>320</v>
       </c>
     </row>
     <row r="179" spans="1:7">
@@ -5725,10 +5725,10 @@
         <v>164</v>
       </c>
       <c r="F179" t="s">
+        <v>320</v>
+      </c>
+      <c r="G179" t="s">
         <v>165</v>
-      </c>
-      <c r="G179" t="s">
-        <v>320</v>
       </c>
     </row>
     <row r="180" spans="1:7">
@@ -5745,10 +5745,10 @@
         <v>164</v>
       </c>
       <c r="F180" t="s">
+        <v>320</v>
+      </c>
+      <c r="G180" t="s">
         <v>165</v>
-      </c>
-      <c r="G180" t="s">
-        <v>320</v>
       </c>
     </row>
     <row r="181" spans="1:7">
@@ -6044,10 +6044,10 @@
         <v>164</v>
       </c>
       <c r="F193" t="s">
+        <v>327</v>
+      </c>
+      <c r="G193" t="s">
         <v>276</v>
-      </c>
-      <c r="G193" t="s">
-        <v>328</v>
       </c>
     </row>
     <row r="194" spans="1:7">
@@ -6274,10 +6274,10 @@
         <v>164</v>
       </c>
       <c r="F203" t="s">
+        <v>327</v>
+      </c>
+      <c r="G203" t="s">
         <v>276</v>
-      </c>
-      <c r="G203" t="s">
-        <v>328</v>
       </c>
     </row>
     <row r="204" spans="1:7">
@@ -6389,10 +6389,10 @@
         <v>164</v>
       </c>
       <c r="F208" t="s">
+        <v>327</v>
+      </c>
+      <c r="G208" t="s">
         <v>276</v>
-      </c>
-      <c r="G208" t="s">
-        <v>328</v>
       </c>
     </row>
     <row r="209" spans="1:7">
@@ -6550,10 +6550,10 @@
         <v>164</v>
       </c>
       <c r="F215" t="s">
-        <v>327</v>
+        <v>365</v>
       </c>
       <c r="G215" t="s">
-        <v>366</v>
+        <v>328</v>
       </c>
     </row>
     <row r="216" spans="1:7">
@@ -6665,10 +6665,10 @@
         <v>164</v>
       </c>
       <c r="F220" t="s">
-        <v>271</v>
+        <v>365</v>
       </c>
       <c r="G220" t="s">
-        <v>366</v>
+        <v>272</v>
       </c>
     </row>
     <row r="221" spans="1:7">
@@ -6803,10 +6803,10 @@
         <v>164</v>
       </c>
       <c r="F226" t="s">
+        <v>365</v>
+      </c>
+      <c r="G226" t="s">
         <v>276</v>
-      </c>
-      <c r="G226" t="s">
-        <v>366</v>
       </c>
     </row>
     <row r="227" spans="1:7">
@@ -6849,10 +6849,10 @@
         <v>164</v>
       </c>
       <c r="F228" t="s">
+        <v>365</v>
+      </c>
+      <c r="G228" t="s">
         <v>165</v>
-      </c>
-      <c r="G228" t="s">
-        <v>366</v>
       </c>
     </row>
     <row r="229" spans="1:7">
@@ -6918,10 +6918,10 @@
         <v>164</v>
       </c>
       <c r="F231" t="s">
-        <v>271</v>
+        <v>365</v>
       </c>
       <c r="G231" t="s">
-        <v>366</v>
+        <v>272</v>
       </c>
     </row>
     <row r="232" spans="1:7">
@@ -6941,10 +6941,10 @@
         <v>164</v>
       </c>
       <c r="F232" t="s">
-        <v>271</v>
+        <v>365</v>
       </c>
       <c r="G232" t="s">
-        <v>366</v>
+        <v>272</v>
       </c>
     </row>
     <row r="233" spans="1:7">
@@ -7125,10 +7125,10 @@
         <v>164</v>
       </c>
       <c r="F240" t="s">
+        <v>402</v>
+      </c>
+      <c r="G240" t="s">
         <v>165</v>
-      </c>
-      <c r="G240" t="s">
-        <v>402</v>
       </c>
     </row>
     <row r="241" spans="1:7">
@@ -7148,10 +7148,10 @@
         <v>164</v>
       </c>
       <c r="F241" t="s">
+        <v>402</v>
+      </c>
+      <c r="G241" t="s">
         <v>165</v>
-      </c>
-      <c r="G241" t="s">
-        <v>402</v>
       </c>
     </row>
     <row r="242" spans="1:7">
@@ -7171,10 +7171,10 @@
         <v>164</v>
       </c>
       <c r="F242" t="s">
+        <v>402</v>
+      </c>
+      <c r="G242" t="s">
         <v>165</v>
-      </c>
-      <c r="G242" t="s">
-        <v>402</v>
       </c>
     </row>
     <row r="243" spans="1:7">
@@ -7194,10 +7194,10 @@
         <v>164</v>
       </c>
       <c r="F243" t="s">
+        <v>402</v>
+      </c>
+      <c r="G243" t="s">
         <v>165</v>
-      </c>
-      <c r="G243" t="s">
-        <v>402</v>
       </c>
     </row>
     <row r="244" spans="1:7">
@@ -7217,10 +7217,10 @@
         <v>164</v>
       </c>
       <c r="F244" t="s">
+        <v>402</v>
+      </c>
+      <c r="G244" t="s">
         <v>165</v>
-      </c>
-      <c r="G244" t="s">
-        <v>402</v>
       </c>
     </row>
     <row r="245" spans="1:7">
@@ -7240,10 +7240,10 @@
         <v>164</v>
       </c>
       <c r="F245" t="s">
+        <v>402</v>
+      </c>
+      <c r="G245" t="s">
         <v>165</v>
-      </c>
-      <c r="G245" t="s">
-        <v>402</v>
       </c>
     </row>
     <row r="246" spans="1:7">
@@ -7263,10 +7263,10 @@
         <v>164</v>
       </c>
       <c r="F246" t="s">
+        <v>402</v>
+      </c>
+      <c r="G246" t="s">
         <v>256</v>
-      </c>
-      <c r="G246" t="s">
-        <v>402</v>
       </c>
     </row>
     <row r="247" spans="1:7">
@@ -7283,10 +7283,10 @@
         <v>96</v>
       </c>
       <c r="F247" t="s">
+        <v>412</v>
+      </c>
+      <c r="G247" t="s">
         <v>97</v>
-      </c>
-      <c r="G247" t="s">
-        <v>412</v>
       </c>
     </row>
     <row r="248" spans="1:7">
@@ -7303,10 +7303,10 @@
         <v>96</v>
       </c>
       <c r="F248" t="s">
+        <v>412</v>
+      </c>
+      <c r="G248" t="s">
         <v>97</v>
-      </c>
-      <c r="G248" t="s">
-        <v>412</v>
       </c>
     </row>
     <row r="249" spans="1:7">
@@ -7323,10 +7323,10 @@
         <v>96</v>
       </c>
       <c r="F249" t="s">
+        <v>412</v>
+      </c>
+      <c r="G249" t="s">
         <v>416</v>
-      </c>
-      <c r="G249" t="s">
-        <v>412</v>
       </c>
     </row>
     <row r="250" spans="1:7">
@@ -7343,10 +7343,10 @@
         <v>96</v>
       </c>
       <c r="F250" t="s">
+        <v>412</v>
+      </c>
+      <c r="G250" t="s">
         <v>97</v>
-      </c>
-      <c r="G250" t="s">
-        <v>412</v>
       </c>
     </row>
     <row r="251" spans="1:7">
@@ -7363,10 +7363,10 @@
         <v>96</v>
       </c>
       <c r="F251" t="s">
+        <v>412</v>
+      </c>
+      <c r="G251" t="s">
         <v>97</v>
-      </c>
-      <c r="G251" t="s">
-        <v>412</v>
       </c>
     </row>
     <row r="252" spans="1:7">
@@ -7383,10 +7383,10 @@
         <v>96</v>
       </c>
       <c r="F252" t="s">
+        <v>412</v>
+      </c>
+      <c r="G252" t="s">
         <v>97</v>
-      </c>
-      <c r="G252" t="s">
-        <v>412</v>
       </c>
     </row>
     <row r="253" spans="1:7">
@@ -7423,10 +7423,10 @@
         <v>91</v>
       </c>
       <c r="F254" t="s">
+        <v>422</v>
+      </c>
+      <c r="G254" t="s">
         <v>220</v>
-      </c>
-      <c r="G254" t="s">
-        <v>423</v>
       </c>
     </row>
     <row r="255" spans="1:7">
@@ -7443,10 +7443,10 @@
         <v>91</v>
       </c>
       <c r="F255" t="s">
+        <v>422</v>
+      </c>
+      <c r="G255" t="s">
         <v>427</v>
-      </c>
-      <c r="G255" t="s">
-        <v>423</v>
       </c>
     </row>
     <row r="256" spans="1:7">
@@ -7463,10 +7463,10 @@
         <v>91</v>
       </c>
       <c r="F256" t="s">
+        <v>422</v>
+      </c>
+      <c r="G256" t="s">
         <v>427</v>
-      </c>
-      <c r="G256" t="s">
-        <v>423</v>
       </c>
     </row>
     <row r="257" spans="1:7">
@@ -7483,10 +7483,10 @@
         <v>91</v>
       </c>
       <c r="F257" t="s">
+        <v>422</v>
+      </c>
+      <c r="G257" t="s">
         <v>427</v>
-      </c>
-      <c r="G257" t="s">
-        <v>423</v>
       </c>
     </row>
     <row r="258" spans="1:7">
@@ -7503,10 +7503,10 @@
         <v>164</v>
       </c>
       <c r="F258" t="s">
-        <v>327</v>
+        <v>422</v>
       </c>
       <c r="G258" t="s">
-        <v>423</v>
+        <v>328</v>
       </c>
     </row>
     <row r="259" spans="1:7">
@@ -7523,10 +7523,10 @@
         <v>91</v>
       </c>
       <c r="F259" t="s">
+        <v>422</v>
+      </c>
+      <c r="G259" t="s">
         <v>427</v>
-      </c>
-      <c r="G259" t="s">
-        <v>423</v>
       </c>
     </row>
     <row r="260" spans="1:7">
@@ -7543,10 +7543,10 @@
         <v>164</v>
       </c>
       <c r="F260" t="s">
+        <v>422</v>
+      </c>
+      <c r="G260" t="s">
         <v>165</v>
-      </c>
-      <c r="G260" t="s">
-        <v>423</v>
       </c>
     </row>
     <row r="261" spans="1:7">
@@ -7563,10 +7563,10 @@
         <v>196</v>
       </c>
       <c r="F261" t="s">
+        <v>422</v>
+      </c>
+      <c r="G261" t="s">
         <v>435</v>
-      </c>
-      <c r="G261" t="s">
-        <v>423</v>
       </c>
     </row>
     <row r="262" spans="1:7">
@@ -7583,10 +7583,10 @@
         <v>164</v>
       </c>
       <c r="F262" t="s">
+        <v>422</v>
+      </c>
+      <c r="G262" t="s">
         <v>165</v>
-      </c>
-      <c r="G262" t="s">
-        <v>423</v>
       </c>
     </row>
     <row r="263" spans="1:7">
@@ -7603,10 +7603,10 @@
         <v>183</v>
       </c>
       <c r="F263" t="s">
+        <v>422</v>
+      </c>
+      <c r="G263" t="s">
         <v>439</v>
-      </c>
-      <c r="G263" t="s">
-        <v>423</v>
       </c>
     </row>
     <row r="264" spans="1:7">
@@ -7623,10 +7623,10 @@
         <v>32</v>
       </c>
       <c r="F264" t="s">
+        <v>422</v>
+      </c>
+      <c r="G264" t="s">
         <v>33</v>
-      </c>
-      <c r="G264" t="s">
-        <v>423</v>
       </c>
     </row>
     <row r="265" spans="1:7">
@@ -7643,10 +7643,10 @@
         <v>11</v>
       </c>
       <c r="F265" t="s">
-        <v>12</v>
+        <v>422</v>
       </c>
       <c r="G265" t="s">
-        <v>423</v>
+        <v>13</v>
       </c>
     </row>
     <row r="266" spans="1:7">
@@ -7663,10 +7663,10 @@
         <v>114</v>
       </c>
       <c r="F266" t="s">
+        <v>422</v>
+      </c>
+      <c r="G266" t="s">
         <v>444</v>
-      </c>
-      <c r="G266" t="s">
-        <v>423</v>
       </c>
     </row>
     <row r="267" spans="1:7">
@@ -7683,10 +7683,10 @@
         <v>114</v>
       </c>
       <c r="F267" t="s">
+        <v>446</v>
+      </c>
+      <c r="G267" t="s">
         <v>119</v>
-      </c>
-      <c r="G267" t="s">
-        <v>446</v>
       </c>
     </row>
     <row r="268" spans="1:7">
@@ -7703,10 +7703,10 @@
         <v>183</v>
       </c>
       <c r="F268" t="s">
-        <v>203</v>
+        <v>448</v>
       </c>
       <c r="G268" t="s">
-        <v>448</v>
+        <v>204</v>
       </c>
     </row>
     <row r="269" spans="1:7">
@@ -7723,10 +7723,10 @@
         <v>114</v>
       </c>
       <c r="F269" t="s">
+        <v>450</v>
+      </c>
+      <c r="G269" t="s">
         <v>119</v>
-      </c>
-      <c r="G269" t="s">
-        <v>450</v>
       </c>
     </row>
     <row r="270" spans="1:7">
@@ -7743,10 +7743,10 @@
         <v>114</v>
       </c>
       <c r="F270" t="s">
+        <v>450</v>
+      </c>
+      <c r="G270" t="s">
         <v>119</v>
-      </c>
-      <c r="G270" t="s">
-        <v>450</v>
       </c>
     </row>
     <row r="271" spans="1:7">
@@ -7903,10 +7903,10 @@
         <v>183</v>
       </c>
       <c r="F278" t="s">
-        <v>203</v>
+        <v>463</v>
       </c>
       <c r="G278" t="s">
-        <v>463</v>
+        <v>204</v>
       </c>
     </row>
     <row r="279" spans="1:7">
@@ -7923,10 +7923,10 @@
         <v>32</v>
       </c>
       <c r="F279" t="s">
-        <v>53</v>
+        <v>463</v>
       </c>
       <c r="G279" t="s">
-        <v>463</v>
+        <v>54</v>
       </c>
     </row>
     <row r="280" spans="1:7">
@@ -7943,10 +7943,10 @@
         <v>11</v>
       </c>
       <c r="F280" t="s">
-        <v>12</v>
+        <v>463</v>
       </c>
       <c r="G280" t="s">
-        <v>463</v>
+        <v>13</v>
       </c>
     </row>
     <row r="281" spans="1:7">
@@ -7963,10 +7963,10 @@
         <v>114</v>
       </c>
       <c r="F281" t="s">
+        <v>463</v>
+      </c>
+      <c r="G281" t="s">
         <v>171</v>
-      </c>
-      <c r="G281" t="s">
-        <v>463</v>
       </c>
     </row>
     <row r="282" spans="1:7">
@@ -7983,10 +7983,10 @@
         <v>125</v>
       </c>
       <c r="F282" t="s">
+        <v>463</v>
+      </c>
+      <c r="G282" t="s">
         <v>126</v>
-      </c>
-      <c r="G282" t="s">
-        <v>463</v>
       </c>
     </row>
     <row r="283" spans="1:7">
@@ -8003,10 +8003,10 @@
         <v>164</v>
       </c>
       <c r="F283" t="s">
-        <v>365</v>
+        <v>469</v>
       </c>
       <c r="G283" t="s">
-        <v>469</v>
+        <v>366</v>
       </c>
     </row>
     <row r="284" spans="1:7">
@@ -8023,10 +8023,10 @@
         <v>125</v>
       </c>
       <c r="F284" t="s">
+        <v>471</v>
+      </c>
+      <c r="G284" t="s">
         <v>126</v>
-      </c>
-      <c r="G284" t="s">
-        <v>471</v>
       </c>
     </row>
     <row r="285" spans="1:7">
@@ -8043,10 +8043,10 @@
         <v>114</v>
       </c>
       <c r="F285" t="s">
+        <v>473</v>
+      </c>
+      <c r="G285" t="s">
         <v>171</v>
-      </c>
-      <c r="G285" t="s">
-        <v>473</v>
       </c>
     </row>
     <row r="286" spans="1:7">
@@ -8063,10 +8063,10 @@
         <v>183</v>
       </c>
       <c r="F286" t="s">
+        <v>475</v>
+      </c>
+      <c r="G286" t="s">
         <v>439</v>
-      </c>
-      <c r="G286" t="s">
-        <v>475</v>
       </c>
     </row>
     <row r="287" spans="1:7">
@@ -8083,10 +8083,10 @@
         <v>183</v>
       </c>
       <c r="F287" t="s">
+        <v>475</v>
+      </c>
+      <c r="G287" t="s">
         <v>439</v>
-      </c>
-      <c r="G287" t="s">
-        <v>475</v>
       </c>
     </row>
     <row r="288" spans="1:7">
@@ -8103,10 +8103,10 @@
         <v>11</v>
       </c>
       <c r="F288" t="s">
+        <v>475</v>
+      </c>
+      <c r="G288" t="s">
         <v>42</v>
-      </c>
-      <c r="G288" t="s">
-        <v>475</v>
       </c>
     </row>
     <row r="289" spans="1:7">
@@ -8123,10 +8123,10 @@
         <v>32</v>
       </c>
       <c r="F289" t="s">
+        <v>475</v>
+      </c>
+      <c r="G289" t="s">
         <v>33</v>
-      </c>
-      <c r="G289" t="s">
-        <v>475</v>
       </c>
     </row>
     <row r="290" spans="1:7">
@@ -8143,10 +8143,10 @@
         <v>32</v>
       </c>
       <c r="F290" t="s">
+        <v>475</v>
+      </c>
+      <c r="G290" t="s">
         <v>33</v>
-      </c>
-      <c r="G290" t="s">
-        <v>475</v>
       </c>
     </row>
     <row r="291" spans="1:7">
@@ -8163,10 +8163,10 @@
         <v>114</v>
       </c>
       <c r="F291" t="s">
+        <v>475</v>
+      </c>
+      <c r="G291" t="s">
         <v>171</v>
-      </c>
-      <c r="G291" t="s">
-        <v>475</v>
       </c>
     </row>
     <row r="292" spans="1:7">
@@ -8183,10 +8183,10 @@
         <v>114</v>
       </c>
       <c r="F292" t="s">
+        <v>475</v>
+      </c>
+      <c r="G292" t="s">
         <v>171</v>
-      </c>
-      <c r="G292" t="s">
-        <v>475</v>
       </c>
     </row>
     <row r="293" spans="1:7">
@@ -8203,10 +8203,10 @@
         <v>114</v>
       </c>
       <c r="F293" t="s">
+        <v>475</v>
+      </c>
+      <c r="G293" t="s">
         <v>171</v>
-      </c>
-      <c r="G293" t="s">
-        <v>475</v>
       </c>
     </row>
     <row r="294" spans="1:7">
@@ -8223,10 +8223,10 @@
         <v>114</v>
       </c>
       <c r="F294" t="s">
+        <v>475</v>
+      </c>
+      <c r="G294" t="s">
         <v>171</v>
-      </c>
-      <c r="G294" t="s">
-        <v>475</v>
       </c>
     </row>
     <row r="295" spans="1:7">
@@ -8243,10 +8243,10 @@
         <v>114</v>
       </c>
       <c r="F295" t="s">
+        <v>485</v>
+      </c>
+      <c r="G295" t="s">
         <v>171</v>
-      </c>
-      <c r="G295" t="s">
-        <v>485</v>
       </c>
     </row>
     <row r="296" spans="1:7">
@@ -8263,10 +8263,10 @@
         <v>114</v>
       </c>
       <c r="F296" t="s">
+        <v>485</v>
+      </c>
+      <c r="G296" t="s">
         <v>171</v>
-      </c>
-      <c r="G296" t="s">
-        <v>485</v>
       </c>
     </row>
   </sheetData>

--- a/api/2/xlsx/fr/SectorCOFOG.xlsx
+++ b/api/2/xlsx/fr/SectorCOFOG.xlsx
@@ -22,75 +22,75 @@
     <t>status</t>
   </si>
   <si>
+    <t>codeforiati:cofog-group</t>
+  </si>
+  <si>
     <t>codeforiati:cofog-class</t>
   </si>
   <si>
+    <t>codeforiati:cofog-division</t>
+  </si>
+  <si>
+    <t>codeforiati:group-code</t>
+  </si>
+  <si>
     <t>codeforiati:category-code</t>
   </si>
   <si>
-    <t>codeforiati:cofog-division</t>
-  </si>
-  <si>
-    <t>codeforiati:group-code</t>
-  </si>
-  <si>
-    <t>codeforiati:cofog-group</t>
-  </si>
-  <si>
     <t>11110</t>
   </si>
   <si>
     <t>active</t>
   </si>
   <si>
+    <t>09.8 - Education n.e.c.</t>
+  </si>
+  <si>
     <t>09.8.0 - Education n.e.c. (CS)</t>
   </si>
   <si>
+    <t>09 - Education</t>
+  </si>
+  <si>
+    <t>110</t>
+  </si>
+  <si>
     <t>111</t>
   </si>
   <si>
-    <t>09 - Education</t>
-  </si>
-  <si>
-    <t>110</t>
-  </si>
-  <si>
-    <t>09.8 - Education n.e.c.</t>
-  </si>
-  <si>
     <t>11120</t>
   </si>
   <si>
+    <t>09.6 - Subsidiary services to education</t>
+  </si>
+  <si>
     <t>09.6.0 - Subsidiary services to education (IS)</t>
   </si>
   <si>
-    <t>09.6 - Subsidiary services to education</t>
-  </si>
-  <si>
     <t>11130</t>
   </si>
   <si>
     <t>11182</t>
   </si>
   <si>
+    <t>09.7 - R&amp;D Education</t>
+  </si>
+  <si>
     <t>09.7.0 - R&amp;D Education (CS)</t>
   </si>
   <si>
-    <t>09.7 - R&amp;D Education</t>
-  </si>
-  <si>
     <t>11220</t>
   </si>
   <si>
+    <t>09.1 - Pre‐primary and primary education</t>
+  </si>
+  <si>
     <t>09.1.2 - Primary education (IS)</t>
   </si>
   <si>
     <t>112</t>
   </si>
   <si>
-    <t>09.1 - Pre‐primary and primary education</t>
-  </si>
-  <si>
     <t>11230</t>
   </si>
   <si>
@@ -109,24 +109,24 @@
     <t>11250</t>
   </si>
   <si>
+    <t>07.4 - Public health services</t>
+  </si>
+  <si>
     <t>07.4.0 - Public health services (IS)</t>
   </si>
   <si>
     <t>07 - Health</t>
   </si>
   <si>
-    <t>07.4 - Public health services</t>
-  </si>
-  <si>
     <t>11260</t>
   </si>
   <si>
+    <t>09.2 - Secondary education</t>
+  </si>
+  <si>
     <t>09.2.1 - Lower‐secondary education (IS)</t>
   </si>
   <si>
-    <t>09.2 - Secondary education</t>
-  </si>
-  <si>
     <t>11320</t>
   </si>
   <si>
@@ -139,69 +139,69 @@
     <t>11330</t>
   </si>
   <si>
+    <t>09.5 - Education not definable by level</t>
+  </si>
+  <si>
     <t>09.5.0 - Education not definable by level (IS)</t>
   </si>
   <si>
-    <t>09.5 - Education not definable by level</t>
-  </si>
-  <si>
     <t>11420</t>
   </si>
   <si>
+    <t>09.4 - Tertiary education</t>
+  </si>
+  <si>
     <t>09.4.1 - First stage of tertiary education (IS)</t>
   </si>
   <si>
     <t>114</t>
   </si>
   <si>
-    <t>09.4 - Tertiary education</t>
-  </si>
-  <si>
     <t>11430</t>
   </si>
   <si>
+    <t>09.3 - Post‐secondary non‐tertiary education</t>
+  </si>
+  <si>
     <t>09.3.0 - Post‐secondary non‐tertiary education (IS)</t>
   </si>
   <si>
-    <t>09.3 - Post‐secondary non‐tertiary education</t>
-  </si>
-  <si>
     <t>12110</t>
   </si>
   <si>
+    <t>07.6 - Health n.e.c.</t>
+  </si>
+  <si>
     <t>07.6.0 - Health n.e.c. (CS)</t>
   </si>
   <si>
+    <t>120</t>
+  </si>
+  <si>
     <t>121</t>
   </si>
   <si>
-    <t>120</t>
-  </si>
-  <si>
-    <t>07.6 - Health n.e.c.</t>
-  </si>
-  <si>
     <t>12181</t>
   </si>
   <si>
     <t>12182</t>
   </si>
   <si>
+    <t>07.5 - R&amp;D Health</t>
+  </si>
+  <si>
     <t>07.5.0 - R&amp;D Health (CS)</t>
   </si>
   <si>
-    <t>07.5 - R&amp;D Health</t>
-  </si>
-  <si>
     <t>12191</t>
   </si>
   <si>
+    <t>07.2 - Outpatient services</t>
+  </si>
+  <si>
     <t>07.2.1 - General medical services (IS)</t>
   </si>
   <si>
-    <t>07.2 - Outpatient services</t>
-  </si>
-  <si>
     <t>12196</t>
   </si>
   <si>
@@ -214,12 +214,12 @@
     <t>12230</t>
   </si>
   <si>
+    <t>07.3 - Hospital services</t>
+  </si>
+  <si>
     <t>07.3.1 - General hospital services (IS)</t>
   </si>
   <si>
-    <t>07.3 - Hospital services</t>
-  </si>
-  <si>
     <t>12240</t>
   </si>
   <si>
@@ -286,6 +286,9 @@
     <t>14010</t>
   </si>
   <si>
+    <t>06.3 - Water supply</t>
+  </si>
+  <si>
     <t>06.3.0 - Water supply (CS)</t>
   </si>
   <si>
@@ -295,21 +298,18 @@
     <t>140</t>
   </si>
   <si>
-    <t>06.3 - Water supply</t>
-  </si>
-  <si>
     <t>14015</t>
   </si>
   <si>
+    <t>05.6 - Environmental protection n.e.c.</t>
+  </si>
+  <si>
     <t>05.6.0 - Environmental protection n.e.c. (CS)</t>
   </si>
   <si>
     <t>05 - Environmental protection</t>
   </si>
   <si>
-    <t>05.6 - Environmental protection n.e.c.</t>
-  </si>
-  <si>
     <t>14020</t>
   </si>
   <si>
@@ -319,12 +319,12 @@
     <t>14022</t>
   </si>
   <si>
+    <t>05.2 - Waste water management</t>
+  </si>
+  <si>
     <t>05.2.0 - Waste water management (CS)</t>
   </si>
   <si>
-    <t>05.2 - Waste water management</t>
-  </si>
-  <si>
     <t>14030</t>
   </si>
   <si>
@@ -340,63 +340,63 @@
     <t>14050</t>
   </si>
   <si>
+    <t>05.1 - Waste management</t>
+  </si>
+  <si>
     <t>05.1.0 - Waste management (CS)</t>
   </si>
   <si>
-    <t>05.1 - Waste management</t>
-  </si>
-  <si>
     <t>14081</t>
   </si>
   <si>
     <t>15110</t>
   </si>
   <si>
+    <t>01.3 - General services</t>
+  </si>
+  <si>
     <t>01.3.1 - General personnel services (CS)</t>
   </si>
   <si>
+    <t>01 - General public services</t>
+  </si>
+  <si>
+    <t>150</t>
+  </si>
+  <si>
     <t>151</t>
   </si>
   <si>
-    <t>01 - General public services</t>
-  </si>
-  <si>
-    <t>150</t>
-  </si>
-  <si>
-    <t>01.3 - General services</t>
-  </si>
-  <si>
     <t>15111</t>
   </si>
   <si>
+    <t>01.1 - Executive and legislative organs, financial and fiscal affairs, external affairs</t>
+  </si>
+  <si>
     <t>01.1.2 - Financial and fiscal affairs (CS)</t>
   </si>
   <si>
-    <t>01.1 - Executive and legislative organs, financial and fiscal affairs, external affairs</t>
-  </si>
-  <si>
     <t>15112</t>
   </si>
   <si>
+    <t>01.8 - Transfers of a general character between different levels of government</t>
+  </si>
+  <si>
     <t>01.8.0 - Transfers of a general character between different levels of government (CS)</t>
   </si>
   <si>
-    <t>01.8 - Transfers of a general character between different levels of government</t>
-  </si>
-  <si>
     <t>15113</t>
   </si>
   <si>
+    <t>03.6 - Public order and safety n.e.c.</t>
+  </si>
+  <si>
     <t>03.6.0 - Public order and safety n.e.c. (CS)</t>
   </si>
   <si>
     <t>03 - Public order and safety</t>
   </si>
   <si>
-    <t>03.6 - Public order and safety n.e.c.</t>
-  </si>
-  <si>
     <t>15114</t>
   </si>
   <si>
@@ -424,12 +424,12 @@
     <t>15123</t>
   </si>
   <si>
+    <t>01.2 - Foreign economic aid</t>
+  </si>
+  <si>
     <t>01.2.2 - Economic aid routed through international organizations (CS)</t>
   </si>
   <si>
-    <t>01.2 - Foreign economic aid</t>
-  </si>
-  <si>
     <t>15124</t>
   </si>
   <si>
@@ -460,30 +460,30 @@
     <t>15131</t>
   </si>
   <si>
+    <t>03.3 - Law courts</t>
+  </si>
+  <si>
     <t>03.3.0 - Law courts (CS)</t>
   </si>
   <si>
-    <t>03.3 - Law courts</t>
-  </si>
-  <si>
     <t>15132</t>
   </si>
   <si>
+    <t>03.1 - Police services</t>
+  </si>
+  <si>
     <t>03.1.0 - Police services (CS)</t>
   </si>
   <si>
-    <t>03.1 - Police services</t>
-  </si>
-  <si>
     <t>15133</t>
   </si>
   <si>
+    <t>03.2 - Fire‐protection services</t>
+  </si>
+  <si>
     <t>03.2.0 - Fire‐protection services (CS)</t>
   </si>
   <si>
-    <t>03.2 - Fire‐protection services</t>
-  </si>
-  <si>
     <t>15134</t>
   </si>
   <si>
@@ -496,24 +496,24 @@
     <t>15137</t>
   </si>
   <si>
+    <t>03.4 - Prisons</t>
+  </si>
+  <si>
     <t>03.4.0 - Prisons (CS)</t>
   </si>
   <si>
-    <t>03.4 - Prisons</t>
-  </si>
-  <si>
     <t>15142</t>
   </si>
   <si>
+    <t>04.1 - General economic, commercial and labour affairs</t>
+  </si>
+  <si>
     <t>04.1.1 - General economic and commercial affairs (CS)</t>
   </si>
   <si>
     <t>04 - Economic affairs</t>
   </si>
   <si>
-    <t>04.1 - General economic, commercial and labour affairs</t>
-  </si>
-  <si>
     <t>15143</t>
   </si>
   <si>
@@ -526,12 +526,12 @@
     <t>15151</t>
   </si>
   <si>
+    <t>01.6 - General public services n.e.c.</t>
+  </si>
+  <si>
     <t>01.6.0 - General public services n.e.c. (CS)</t>
   </si>
   <si>
-    <t>01.6 - General public services n.e.c.</t>
-  </si>
-  <si>
     <t>15152</t>
   </si>
   <si>
@@ -541,12 +541,12 @@
     <t>15153</t>
   </si>
   <si>
+    <t>04.6 - Communication</t>
+  </si>
+  <si>
     <t>04.6.0 - Communication (CS)</t>
   </si>
   <si>
-    <t>04.6 - Communication</t>
-  </si>
-  <si>
     <t>15154</t>
   </si>
   <si>
@@ -562,15 +562,15 @@
     <t>15170</t>
   </si>
   <si>
+    <t>10.7 - Social exclusion n.e.c.</t>
+  </si>
+  <si>
     <t>10.7.0 - Social exclusion n.e.c. (IS)</t>
   </si>
   <si>
     <t>10 - Social protection</t>
   </si>
   <si>
-    <t>10.7 - Social exclusion n.e.c.</t>
-  </si>
-  <si>
     <t>15180</t>
   </si>
   <si>
@@ -583,12 +583,12 @@
     <t>15196</t>
   </si>
   <si>
+    <t>01.5 - R&amp;D General public services</t>
+  </si>
+  <si>
     <t>01.5.0 - R&amp;D General public services (CS)</t>
   </si>
   <si>
-    <t>01.5 - R&amp;D General public services</t>
-  </si>
-  <si>
     <t>15210</t>
   </si>
   <si>
@@ -601,15 +601,15 @@
     <t>15230</t>
   </si>
   <si>
+    <t>02.3 - Foreign military aid</t>
+  </si>
+  <si>
     <t>02.3.0 - Foreign military aid (CS)</t>
   </si>
   <si>
     <t>02 - Defence</t>
   </si>
   <si>
-    <t>02.3 - Foreign military aid</t>
-  </si>
-  <si>
     <t>15240</t>
   </si>
   <si>
@@ -622,15 +622,15 @@
     <t>16010</t>
   </si>
   <si>
+    <t>10.9 - Social protection n.e.c.</t>
+  </si>
+  <si>
     <t>10.9.0 - Social protection n.e.c. (CS)</t>
   </si>
   <si>
     <t>160</t>
   </si>
   <si>
-    <t>10.9 - Social protection n.e.c.</t>
-  </si>
-  <si>
     <t>16011</t>
   </si>
   <si>
@@ -640,12 +640,12 @@
     <t>16013</t>
   </si>
   <si>
+    <t>10.2 - Old age</t>
+  </si>
+  <si>
     <t>10.2.0 - Old age (IS)</t>
   </si>
   <si>
-    <t>10.2 - Old age</t>
-  </si>
-  <si>
     <t>16014</t>
   </si>
   <si>
@@ -655,45 +655,45 @@
     <t>16020</t>
   </si>
   <si>
+    <t>10.5 - Unemployment</t>
+  </si>
+  <si>
     <t>10.5.0 - Unemployment (IS)</t>
   </si>
   <si>
-    <t>10.5 - Unemployment</t>
-  </si>
-  <si>
     <t>16030</t>
   </si>
   <si>
+    <t>06.6 - Housing and community amenities n.e.c.</t>
+  </si>
+  <si>
     <t>06.6.0 - Housing and community amenities n.e.c. (CS)</t>
   </si>
   <si>
-    <t>06.6 - Housing and community amenities n.e.c.</t>
-  </si>
-  <si>
     <t>16040</t>
   </si>
   <si>
+    <t>06.1 - Housing development</t>
+  </si>
+  <si>
     <t>06.1.0 - Housing development (CS)</t>
   </si>
   <si>
-    <t>06.1 - Housing development</t>
-  </si>
-  <si>
     <t>16050</t>
   </si>
   <si>
     <t>16061</t>
   </si>
   <si>
+    <t>08.2 - Cultural services</t>
+  </si>
+  <si>
     <t>08.2.0 - Cultural services (IS)</t>
   </si>
   <si>
     <t>08 - Recreation, culture and religion</t>
   </si>
   <si>
-    <t>08.2 - Cultural services</t>
-  </si>
-  <si>
     <t>16062</t>
   </si>
   <si>
@@ -706,12 +706,12 @@
     <t>16065</t>
   </si>
   <si>
+    <t>08.1 - Recreational and sporting services</t>
+  </si>
+  <si>
     <t>08.1.0 - Recreational and sporting services (IS)</t>
   </si>
   <si>
-    <t>08.1 - Recreational and sporting services</t>
-  </si>
-  <si>
     <t>16066</t>
   </si>
   <si>
@@ -742,12 +742,12 @@
     <t>21020</t>
   </si>
   <si>
+    <t>04.5 - Transport</t>
+  </si>
+  <si>
     <t>04.5.1 - Road transport (CS)</t>
   </si>
   <si>
-    <t>04.5 - Transport</t>
-  </si>
-  <si>
     <t>21021</t>
   </si>
   <si>
@@ -781,12 +781,12 @@
     <t>21061</t>
   </si>
   <si>
+    <t>04.7 - Other industries</t>
+  </si>
+  <si>
     <t>04.7.1 - Distributive trades, storage and warehousing (CS)</t>
   </si>
   <si>
-    <t>04.7 - Other industries</t>
-  </si>
-  <si>
     <t>21081</t>
   </si>
   <si>
@@ -811,42 +811,42 @@
     <t>22030</t>
   </si>
   <si>
+    <t>08.3 - Broadcasting and publishing services</t>
+  </si>
+  <si>
     <t>08.3.0 - Broadcasting and publishing services (CS)</t>
   </si>
   <si>
-    <t>08.3 - Broadcasting and publishing services</t>
-  </si>
-  <si>
     <t>22040</t>
   </si>
   <si>
     <t>23110</t>
   </si>
   <si>
+    <t>04.3 - Fuel and energy</t>
+  </si>
+  <si>
     <t>04.3.5 - Electricity (CS)</t>
   </si>
   <si>
+    <t>230</t>
+  </si>
+  <si>
     <t>231</t>
   </si>
   <si>
-    <t>230</t>
-  </si>
-  <si>
-    <t>04.3 - Fuel and energy</t>
-  </si>
-  <si>
     <t>23111</t>
   </si>
   <si>
     <t>23112</t>
   </si>
   <si>
+    <t>04.8 - R&amp;D Economic affairs</t>
+  </si>
+  <si>
     <t>04.8.3 - R&amp;D Fuel and energy (CS)</t>
   </si>
   <si>
-    <t>04.8 - R&amp;D Economic affairs</t>
-  </si>
-  <si>
     <t>23181</t>
   </si>
   <si>
@@ -991,18 +991,18 @@
     <t>31110</t>
   </si>
   <si>
+    <t>04.2 - Agriculture, forestry, fishing and hunting</t>
+  </si>
+  <si>
     <t>04.2.1 - Agriculture (CS)</t>
   </si>
   <si>
+    <t>310</t>
+  </si>
+  <si>
     <t>311</t>
   </si>
   <si>
-    <t>310</t>
-  </si>
-  <si>
-    <t>04.2 - Agriculture, forestry, fishing and hunting</t>
-  </si>
-  <si>
     <t>31120</t>
   </si>
   <si>
@@ -1105,18 +1105,18 @@
     <t>32110</t>
   </si>
   <si>
+    <t>04.4 - Mining, manufacturing and construction</t>
+  </si>
+  <si>
     <t>04.4.2 - Manufacturing (CS)</t>
   </si>
   <si>
+    <t>320</t>
+  </si>
+  <si>
     <t>321</t>
   </si>
   <si>
-    <t>320</t>
-  </si>
-  <si>
-    <t>04.4 - Mining, manufacturing and construction</t>
-  </si>
-  <si>
     <t>32120</t>
   </si>
   <si>
@@ -1219,12 +1219,12 @@
     <t>33110</t>
   </si>
   <si>
+    <t>330</t>
+  </si>
+  <si>
     <t>331</t>
   </si>
   <si>
-    <t>330</t>
-  </si>
-  <si>
     <t>33120</t>
   </si>
   <si>
@@ -1261,12 +1261,12 @@
     <t>41030</t>
   </si>
   <si>
+    <t>05.4 - Protection of biodiversity and landscape</t>
+  </si>
+  <si>
     <t>05.4.0 - Protection of biodiversity and landscape (CS)</t>
   </si>
   <si>
-    <t>05.4 - Protection of biodiversity and landscape</t>
-  </si>
-  <si>
     <t>41040</t>
   </si>
   <si>
@@ -1279,27 +1279,27 @@
     <t>43010</t>
   </si>
   <si>
+    <t>04.9 - Economic affairs n.e.c.</t>
+  </si>
+  <si>
     <t>04.9.0 - Economic affairs n.e.c. (CS)</t>
   </si>
   <si>
     <t>430</t>
   </si>
   <si>
-    <t>04.9 - Economic affairs n.e.c.</t>
-  </si>
-  <si>
     <t>43030</t>
   </si>
   <si>
     <t>43031</t>
   </si>
   <si>
+    <t>06.2 - Community development</t>
+  </si>
+  <si>
     <t>06.2.0 - Community development (CS)</t>
   </si>
   <si>
-    <t>06.2 - Community development</t>
-  </si>
-  <si>
     <t>43032</t>
   </si>
   <si>
@@ -1318,24 +1318,24 @@
     <t>43060</t>
   </si>
   <si>
+    <t>02.2 - Civil defence</t>
+  </si>
+  <si>
     <t>02.2.0 - Civil defence (CS)</t>
   </si>
   <si>
-    <t>02.2 - Civil defence</t>
-  </si>
-  <si>
     <t>43071</t>
   </si>
   <si>
     <t>43072</t>
   </si>
   <si>
+    <t>10.4 - Family and children</t>
+  </si>
+  <si>
     <t>10.4.0 - Family and children (IS)</t>
   </si>
   <si>
-    <t>10.4 - Family and children</t>
-  </si>
-  <si>
     <t>43073</t>
   </si>
   <si>
@@ -1345,12 +1345,12 @@
     <t>43082</t>
   </si>
   <si>
+    <t>01.4 - Basic research</t>
+  </si>
+  <si>
     <t>01.4.0 - Basic research (CS)</t>
   </si>
   <si>
-    <t>01.4 - Basic research</t>
-  </si>
-  <si>
     <t>51010</t>
   </si>
   <si>
@@ -1375,13 +1375,13 @@
     <t>60010</t>
   </si>
   <si>
+    <t>01.7 - Public debt transactions</t>
+  </si>
+  <si>
     <t>01.7.0 - Public debt transactions (CS)</t>
   </si>
   <si>
     <t>600</t>
-  </si>
-  <si>
-    <t>01.7 - Public debt transactions</t>
   </si>
   <si>
     <t>60020</t>
@@ -1866,7 +1866,7 @@
         <v>15</v>
       </c>
       <c r="D3" t="s">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="E3" t="s">
         <v>11</v>
@@ -1875,7 +1875,7 @@
         <v>12</v>
       </c>
       <c r="G3" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -1912,7 +1912,7 @@
         <v>19</v>
       </c>
       <c r="D5" t="s">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="E5" t="s">
         <v>11</v>
@@ -1921,7 +1921,7 @@
         <v>12</v>
       </c>
       <c r="G5" t="s">
-        <v>20</v>
+        <v>13</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -1958,7 +1958,7 @@
         <v>9</v>
       </c>
       <c r="D7" t="s">
-        <v>23</v>
+        <v>10</v>
       </c>
       <c r="E7" t="s">
         <v>11</v>
@@ -1967,7 +1967,7 @@
         <v>12</v>
       </c>
       <c r="G7" t="s">
-        <v>13</v>
+        <v>24</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -2024,10 +2024,10 @@
         <v>8</v>
       </c>
       <c r="C10" t="s">
+        <v>22</v>
+      </c>
+      <c r="D10" t="s">
         <v>29</v>
-      </c>
-      <c r="D10" t="s">
-        <v>23</v>
       </c>
       <c r="E10" t="s">
         <v>11</v>
@@ -2050,16 +2050,16 @@
         <v>31</v>
       </c>
       <c r="D11" t="s">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="E11" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F11" t="s">
         <v>12</v>
       </c>
       <c r="G11" t="s">
-        <v>33</v>
+        <v>24</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -2073,7 +2073,7 @@
         <v>35</v>
       </c>
       <c r="D12" t="s">
-        <v>23</v>
+        <v>36</v>
       </c>
       <c r="E12" t="s">
         <v>11</v>
@@ -2082,7 +2082,7 @@
         <v>12</v>
       </c>
       <c r="G12" t="s">
-        <v>36</v>
+        <v>24</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -2093,10 +2093,10 @@
         <v>8</v>
       </c>
       <c r="C13" t="s">
+        <v>35</v>
+      </c>
+      <c r="D13" t="s">
         <v>38</v>
-      </c>
-      <c r="D13" t="s">
-        <v>39</v>
       </c>
       <c r="E13" t="s">
         <v>11</v>
@@ -2105,7 +2105,7 @@
         <v>12</v>
       </c>
       <c r="G13" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -2119,7 +2119,7 @@
         <v>41</v>
       </c>
       <c r="D14" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="E14" t="s">
         <v>11</v>
@@ -2128,7 +2128,7 @@
         <v>12</v>
       </c>
       <c r="G14" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -2165,7 +2165,7 @@
         <v>48</v>
       </c>
       <c r="D16" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="E16" t="s">
         <v>11</v>
@@ -2174,7 +2174,7 @@
         <v>12</v>
       </c>
       <c r="G16" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -2191,7 +2191,7 @@
         <v>52</v>
       </c>
       <c r="E17" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F17" t="s">
         <v>53</v>
@@ -2214,7 +2214,7 @@
         <v>52</v>
       </c>
       <c r="E18" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F18" t="s">
         <v>53</v>
@@ -2234,16 +2234,16 @@
         <v>57</v>
       </c>
       <c r="D19" t="s">
-        <v>52</v>
+        <v>58</v>
       </c>
       <c r="E19" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F19" t="s">
         <v>53</v>
       </c>
       <c r="G19" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -2257,16 +2257,16 @@
         <v>60</v>
       </c>
       <c r="D20" t="s">
-        <v>52</v>
+        <v>61</v>
       </c>
       <c r="E20" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F20" t="s">
         <v>53</v>
       </c>
       <c r="G20" t="s">
-        <v>61</v>
+        <v>54</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -2283,7 +2283,7 @@
         <v>52</v>
       </c>
       <c r="E21" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F21" t="s">
         <v>53</v>
@@ -2303,16 +2303,16 @@
         <v>31</v>
       </c>
       <c r="D22" t="s">
-        <v>64</v>
+        <v>32</v>
       </c>
       <c r="E22" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F22" t="s">
         <v>53</v>
       </c>
       <c r="G22" t="s">
-        <v>33</v>
+        <v>64</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -2326,16 +2326,16 @@
         <v>66</v>
       </c>
       <c r="D23" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="E23" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F23" t="s">
         <v>53</v>
       </c>
       <c r="G23" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -2349,16 +2349,16 @@
         <v>31</v>
       </c>
       <c r="D24" t="s">
-        <v>64</v>
+        <v>32</v>
       </c>
       <c r="E24" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F24" t="s">
         <v>53</v>
       </c>
       <c r="G24" t="s">
-        <v>33</v>
+        <v>64</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -2372,16 +2372,16 @@
         <v>31</v>
       </c>
       <c r="D25" t="s">
-        <v>64</v>
+        <v>32</v>
       </c>
       <c r="E25" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F25" t="s">
         <v>53</v>
       </c>
       <c r="G25" t="s">
-        <v>33</v>
+        <v>64</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -2395,16 +2395,16 @@
         <v>31</v>
       </c>
       <c r="D26" t="s">
-        <v>64</v>
+        <v>32</v>
       </c>
       <c r="E26" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F26" t="s">
         <v>53</v>
       </c>
       <c r="G26" t="s">
-        <v>33</v>
+        <v>64</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -2418,16 +2418,16 @@
         <v>31</v>
       </c>
       <c r="D27" t="s">
-        <v>64</v>
+        <v>32</v>
       </c>
       <c r="E27" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F27" t="s">
         <v>53</v>
       </c>
       <c r="G27" t="s">
-        <v>33</v>
+        <v>64</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -2441,16 +2441,16 @@
         <v>31</v>
       </c>
       <c r="D28" t="s">
-        <v>64</v>
+        <v>32</v>
       </c>
       <c r="E28" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F28" t="s">
         <v>53</v>
       </c>
       <c r="G28" t="s">
-        <v>33</v>
+        <v>64</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -2464,16 +2464,16 @@
         <v>31</v>
       </c>
       <c r="D29" t="s">
-        <v>64</v>
+        <v>32</v>
       </c>
       <c r="E29" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F29" t="s">
         <v>53</v>
       </c>
       <c r="G29" t="s">
-        <v>33</v>
+        <v>64</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -2487,16 +2487,16 @@
         <v>51</v>
       </c>
       <c r="D30" t="s">
-        <v>64</v>
+        <v>52</v>
       </c>
       <c r="E30" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F30" t="s">
         <v>53</v>
       </c>
       <c r="G30" t="s">
-        <v>54</v>
+        <v>64</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -2510,16 +2510,16 @@
         <v>31</v>
       </c>
       <c r="D31" t="s">
-        <v>76</v>
+        <v>32</v>
       </c>
       <c r="E31" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F31" t="s">
         <v>53</v>
       </c>
       <c r="G31" t="s">
-        <v>33</v>
+        <v>76</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -2533,16 +2533,16 @@
         <v>31</v>
       </c>
       <c r="D32" t="s">
-        <v>76</v>
+        <v>32</v>
       </c>
       <c r="E32" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F32" t="s">
         <v>53</v>
       </c>
       <c r="G32" t="s">
-        <v>33</v>
+        <v>76</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -2556,16 +2556,16 @@
         <v>31</v>
       </c>
       <c r="D33" t="s">
-        <v>76</v>
+        <v>32</v>
       </c>
       <c r="E33" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F33" t="s">
         <v>53</v>
       </c>
       <c r="G33" t="s">
-        <v>33</v>
+        <v>76</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -2579,16 +2579,16 @@
         <v>31</v>
       </c>
       <c r="D34" t="s">
-        <v>76</v>
+        <v>32</v>
       </c>
       <c r="E34" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F34" t="s">
         <v>53</v>
       </c>
       <c r="G34" t="s">
-        <v>33</v>
+        <v>76</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -2602,16 +2602,16 @@
         <v>31</v>
       </c>
       <c r="D35" t="s">
-        <v>76</v>
+        <v>32</v>
       </c>
       <c r="E35" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F35" t="s">
         <v>53</v>
       </c>
       <c r="G35" t="s">
-        <v>33</v>
+        <v>76</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -2625,16 +2625,16 @@
         <v>57</v>
       </c>
       <c r="D36" t="s">
-        <v>76</v>
+        <v>58</v>
       </c>
       <c r="E36" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F36" t="s">
         <v>53</v>
       </c>
       <c r="G36" t="s">
-        <v>58</v>
+        <v>76</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -2647,14 +2647,14 @@
       <c r="C37" t="s">
         <v>31</v>
       </c>
+      <c r="D37" t="s">
+        <v>32</v>
+      </c>
       <c r="E37" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F37" t="s">
         <v>83</v>
-      </c>
-      <c r="G37" t="s">
-        <v>33</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -2667,14 +2667,14 @@
       <c r="C38" t="s">
         <v>31</v>
       </c>
+      <c r="D38" t="s">
+        <v>32</v>
+      </c>
       <c r="E38" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F38" t="s">
         <v>83</v>
-      </c>
-      <c r="G38" t="s">
-        <v>33</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -2687,14 +2687,14 @@
       <c r="C39" t="s">
         <v>31</v>
       </c>
+      <c r="D39" t="s">
+        <v>32</v>
+      </c>
       <c r="E39" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F39" t="s">
         <v>83</v>
-      </c>
-      <c r="G39" t="s">
-        <v>33</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -2707,14 +2707,14 @@
       <c r="C40" t="s">
         <v>31</v>
       </c>
+      <c r="D40" t="s">
+        <v>32</v>
+      </c>
       <c r="E40" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F40" t="s">
         <v>83</v>
-      </c>
-      <c r="G40" t="s">
-        <v>33</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -2727,14 +2727,14 @@
       <c r="C41" t="s">
         <v>51</v>
       </c>
+      <c r="D41" t="s">
+        <v>52</v>
+      </c>
       <c r="E41" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F41" t="s">
         <v>83</v>
-      </c>
-      <c r="G41" t="s">
-        <v>54</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -2747,14 +2747,14 @@
       <c r="C42" t="s">
         <v>57</v>
       </c>
+      <c r="D42" t="s">
+        <v>58</v>
+      </c>
       <c r="E42" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F42" t="s">
         <v>83</v>
-      </c>
-      <c r="G42" t="s">
-        <v>58</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -2767,13 +2767,13 @@
       <c r="C43" t="s">
         <v>90</v>
       </c>
+      <c r="D43" t="s">
+        <v>91</v>
+      </c>
       <c r="E43" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="F43" t="s">
-        <v>92</v>
-      </c>
-      <c r="G43" t="s">
         <v>93</v>
       </c>
     </row>
@@ -2787,14 +2787,14 @@
       <c r="C44" t="s">
         <v>95</v>
       </c>
+      <c r="D44" t="s">
+        <v>96</v>
+      </c>
       <c r="E44" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="F44" t="s">
-        <v>92</v>
-      </c>
-      <c r="G44" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -2807,13 +2807,13 @@
       <c r="C45" t="s">
         <v>90</v>
       </c>
+      <c r="D45" t="s">
+        <v>91</v>
+      </c>
       <c r="E45" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="F45" t="s">
-        <v>92</v>
-      </c>
-      <c r="G45" t="s">
         <v>93</v>
       </c>
     </row>
@@ -2827,13 +2827,13 @@
       <c r="C46" t="s">
         <v>90</v>
       </c>
+      <c r="D46" t="s">
+        <v>91</v>
+      </c>
       <c r="E46" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="F46" t="s">
-        <v>92</v>
-      </c>
-      <c r="G46" t="s">
         <v>93</v>
       </c>
     </row>
@@ -2847,14 +2847,14 @@
       <c r="C47" t="s">
         <v>101</v>
       </c>
+      <c r="D47" t="s">
+        <v>102</v>
+      </c>
       <c r="E47" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="F47" t="s">
-        <v>92</v>
-      </c>
-      <c r="G47" t="s">
-        <v>102</v>
+        <v>93</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -2867,13 +2867,13 @@
       <c r="C48" t="s">
         <v>90</v>
       </c>
+      <c r="D48" t="s">
+        <v>91</v>
+      </c>
       <c r="E48" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="F48" t="s">
-        <v>92</v>
-      </c>
-      <c r="G48" t="s">
         <v>93</v>
       </c>
     </row>
@@ -2887,13 +2887,13 @@
       <c r="C49" t="s">
         <v>90</v>
       </c>
+      <c r="D49" t="s">
+        <v>91</v>
+      </c>
       <c r="E49" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="F49" t="s">
-        <v>92</v>
-      </c>
-      <c r="G49" t="s">
         <v>93</v>
       </c>
     </row>
@@ -2907,14 +2907,14 @@
       <c r="C50" t="s">
         <v>101</v>
       </c>
+      <c r="D50" t="s">
+        <v>102</v>
+      </c>
       <c r="E50" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="F50" t="s">
-        <v>92</v>
-      </c>
-      <c r="G50" t="s">
-        <v>102</v>
+        <v>93</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -2927,13 +2927,13 @@
       <c r="C51" t="s">
         <v>90</v>
       </c>
+      <c r="D51" t="s">
+        <v>91</v>
+      </c>
       <c r="E51" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="F51" t="s">
-        <v>92</v>
-      </c>
-      <c r="G51" t="s">
         <v>93</v>
       </c>
     </row>
@@ -2947,14 +2947,14 @@
       <c r="C52" t="s">
         <v>108</v>
       </c>
+      <c r="D52" t="s">
+        <v>109</v>
+      </c>
       <c r="E52" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="F52" t="s">
-        <v>92</v>
-      </c>
-      <c r="G52" t="s">
-        <v>109</v>
+        <v>93</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -2967,14 +2967,14 @@
       <c r="C53" t="s">
         <v>9</v>
       </c>
+      <c r="D53" t="s">
+        <v>10</v>
+      </c>
       <c r="E53" t="s">
         <v>11</v>
       </c>
       <c r="F53" t="s">
-        <v>92</v>
-      </c>
-      <c r="G53" t="s">
-        <v>13</v>
+        <v>93</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -3011,7 +3011,7 @@
         <v>118</v>
       </c>
       <c r="D55" t="s">
-        <v>113</v>
+        <v>119</v>
       </c>
       <c r="E55" t="s">
         <v>114</v>
@@ -3020,7 +3020,7 @@
         <v>115</v>
       </c>
       <c r="G55" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -3034,7 +3034,7 @@
         <v>121</v>
       </c>
       <c r="D56" t="s">
-        <v>113</v>
+        <v>122</v>
       </c>
       <c r="E56" t="s">
         <v>114</v>
@@ -3043,7 +3043,7 @@
         <v>115</v>
       </c>
       <c r="G56" t="s">
-        <v>122</v>
+        <v>116</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -3057,16 +3057,16 @@
         <v>124</v>
       </c>
       <c r="D57" t="s">
-        <v>113</v>
+        <v>125</v>
       </c>
       <c r="E57" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="F57" t="s">
         <v>115</v>
       </c>
       <c r="G57" t="s">
-        <v>126</v>
+        <v>116</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -3080,7 +3080,7 @@
         <v>118</v>
       </c>
       <c r="D58" t="s">
-        <v>113</v>
+        <v>119</v>
       </c>
       <c r="E58" t="s">
         <v>114</v>
@@ -3089,7 +3089,7 @@
         <v>115</v>
       </c>
       <c r="G58" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -3103,7 +3103,7 @@
         <v>118</v>
       </c>
       <c r="D59" t="s">
-        <v>113</v>
+        <v>119</v>
       </c>
       <c r="E59" t="s">
         <v>114</v>
@@ -3112,7 +3112,7 @@
         <v>115</v>
       </c>
       <c r="G59" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -3126,7 +3126,7 @@
         <v>118</v>
       </c>
       <c r="D60" t="s">
-        <v>113</v>
+        <v>119</v>
       </c>
       <c r="E60" t="s">
         <v>114</v>
@@ -3135,7 +3135,7 @@
         <v>115</v>
       </c>
       <c r="G60" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -3149,7 +3149,7 @@
         <v>118</v>
       </c>
       <c r="D61" t="s">
-        <v>113</v>
+        <v>119</v>
       </c>
       <c r="E61" t="s">
         <v>114</v>
@@ -3158,7 +3158,7 @@
         <v>115</v>
       </c>
       <c r="G61" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -3172,7 +3172,7 @@
         <v>118</v>
       </c>
       <c r="D62" t="s">
-        <v>113</v>
+        <v>119</v>
       </c>
       <c r="E62" t="s">
         <v>114</v>
@@ -3181,7 +3181,7 @@
         <v>115</v>
       </c>
       <c r="G62" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -3192,10 +3192,10 @@
         <v>8</v>
       </c>
       <c r="C63" t="s">
+        <v>118</v>
+      </c>
+      <c r="D63" t="s">
         <v>133</v>
-      </c>
-      <c r="D63" t="s">
-        <v>113</v>
       </c>
       <c r="E63" t="s">
         <v>114</v>
@@ -3204,7 +3204,7 @@
         <v>115</v>
       </c>
       <c r="G63" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -3215,10 +3215,10 @@
         <v>8</v>
       </c>
       <c r="C64" t="s">
+        <v>118</v>
+      </c>
+      <c r="D64" t="s">
         <v>133</v>
-      </c>
-      <c r="D64" t="s">
-        <v>113</v>
       </c>
       <c r="E64" t="s">
         <v>114</v>
@@ -3227,7 +3227,7 @@
         <v>115</v>
       </c>
       <c r="G64" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -3241,7 +3241,7 @@
         <v>136</v>
       </c>
       <c r="D65" t="s">
-        <v>113</v>
+        <v>137</v>
       </c>
       <c r="E65" t="s">
         <v>114</v>
@@ -3250,7 +3250,7 @@
         <v>115</v>
       </c>
       <c r="G65" t="s">
-        <v>137</v>
+        <v>116</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -3287,7 +3287,7 @@
         <v>118</v>
       </c>
       <c r="D67" t="s">
-        <v>113</v>
+        <v>119</v>
       </c>
       <c r="E67" t="s">
         <v>114</v>
@@ -3296,7 +3296,7 @@
         <v>115</v>
       </c>
       <c r="G67" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -3307,10 +3307,10 @@
         <v>8</v>
       </c>
       <c r="C68" t="s">
+        <v>112</v>
+      </c>
+      <c r="D68" t="s">
         <v>141</v>
-      </c>
-      <c r="D68" t="s">
-        <v>113</v>
       </c>
       <c r="E68" t="s">
         <v>114</v>
@@ -3330,10 +3330,10 @@
         <v>8</v>
       </c>
       <c r="C69" t="s">
+        <v>112</v>
+      </c>
+      <c r="D69" t="s">
         <v>143</v>
-      </c>
-      <c r="D69" t="s">
-        <v>113</v>
       </c>
       <c r="E69" t="s">
         <v>114</v>
@@ -3356,7 +3356,7 @@
         <v>121</v>
       </c>
       <c r="D70" t="s">
-        <v>113</v>
+        <v>122</v>
       </c>
       <c r="E70" t="s">
         <v>114</v>
@@ -3365,7 +3365,7 @@
         <v>115</v>
       </c>
       <c r="G70" t="s">
-        <v>122</v>
+        <v>116</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -3379,7 +3379,7 @@
         <v>121</v>
       </c>
       <c r="D71" t="s">
-        <v>113</v>
+        <v>122</v>
       </c>
       <c r="E71" t="s">
         <v>114</v>
@@ -3388,7 +3388,7 @@
         <v>115</v>
       </c>
       <c r="G71" t="s">
-        <v>122</v>
+        <v>116</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -3425,16 +3425,16 @@
         <v>148</v>
       </c>
       <c r="D73" t="s">
-        <v>113</v>
+        <v>149</v>
       </c>
       <c r="E73" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="F73" t="s">
         <v>115</v>
       </c>
       <c r="G73" t="s">
-        <v>149</v>
+        <v>116</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -3448,16 +3448,16 @@
         <v>151</v>
       </c>
       <c r="D74" t="s">
-        <v>113</v>
+        <v>152</v>
       </c>
       <c r="E74" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="F74" t="s">
         <v>115</v>
       </c>
       <c r="G74" t="s">
-        <v>152</v>
+        <v>116</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -3471,16 +3471,16 @@
         <v>154</v>
       </c>
       <c r="D75" t="s">
-        <v>113</v>
+        <v>155</v>
       </c>
       <c r="E75" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="F75" t="s">
         <v>115</v>
       </c>
       <c r="G75" t="s">
-        <v>155</v>
+        <v>116</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -3494,16 +3494,16 @@
         <v>148</v>
       </c>
       <c r="D76" t="s">
-        <v>113</v>
+        <v>149</v>
       </c>
       <c r="E76" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="F76" t="s">
         <v>115</v>
       </c>
       <c r="G76" t="s">
-        <v>149</v>
+        <v>116</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -3517,16 +3517,16 @@
         <v>148</v>
       </c>
       <c r="D77" t="s">
-        <v>113</v>
+        <v>149</v>
       </c>
       <c r="E77" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="F77" t="s">
         <v>115</v>
       </c>
       <c r="G77" t="s">
-        <v>149</v>
+        <v>116</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -3540,16 +3540,16 @@
         <v>151</v>
       </c>
       <c r="D78" t="s">
-        <v>113</v>
+        <v>152</v>
       </c>
       <c r="E78" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="F78" t="s">
         <v>115</v>
       </c>
       <c r="G78" t="s">
-        <v>152</v>
+        <v>116</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -3563,16 +3563,16 @@
         <v>160</v>
       </c>
       <c r="D79" t="s">
-        <v>113</v>
+        <v>161</v>
       </c>
       <c r="E79" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="F79" t="s">
         <v>115</v>
       </c>
       <c r="G79" t="s">
-        <v>161</v>
+        <v>116</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -3586,16 +3586,16 @@
         <v>163</v>
       </c>
       <c r="D80" t="s">
-        <v>113</v>
+        <v>164</v>
       </c>
       <c r="E80" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="F80" t="s">
         <v>115</v>
       </c>
       <c r="G80" t="s">
-        <v>165</v>
+        <v>116</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -3609,16 +3609,16 @@
         <v>163</v>
       </c>
       <c r="D81" t="s">
-        <v>113</v>
+        <v>164</v>
       </c>
       <c r="E81" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="F81" t="s">
         <v>115</v>
       </c>
       <c r="G81" t="s">
-        <v>165</v>
+        <v>116</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -3632,16 +3632,16 @@
         <v>163</v>
       </c>
       <c r="D82" t="s">
-        <v>113</v>
+        <v>164</v>
       </c>
       <c r="E82" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="F82" t="s">
         <v>115</v>
       </c>
       <c r="G82" t="s">
-        <v>165</v>
+        <v>116</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -3652,10 +3652,10 @@
         <v>8</v>
       </c>
       <c r="C83" t="s">
+        <v>112</v>
+      </c>
+      <c r="D83" t="s">
         <v>143</v>
-      </c>
-      <c r="D83" t="s">
-        <v>113</v>
       </c>
       <c r="E83" t="s">
         <v>114</v>
@@ -3678,7 +3678,7 @@
         <v>170</v>
       </c>
       <c r="D84" t="s">
-        <v>113</v>
+        <v>171</v>
       </c>
       <c r="E84" t="s">
         <v>114</v>
@@ -3687,7 +3687,7 @@
         <v>115</v>
       </c>
       <c r="G84" t="s">
-        <v>171</v>
+        <v>116</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -3698,10 +3698,10 @@
         <v>8</v>
       </c>
       <c r="C85" t="s">
+        <v>118</v>
+      </c>
+      <c r="D85" t="s">
         <v>173</v>
-      </c>
-      <c r="D85" t="s">
-        <v>113</v>
       </c>
       <c r="E85" t="s">
         <v>114</v>
@@ -3710,7 +3710,7 @@
         <v>115</v>
       </c>
       <c r="G85" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -3724,16 +3724,16 @@
         <v>175</v>
       </c>
       <c r="D86" t="s">
-        <v>113</v>
+        <v>176</v>
       </c>
       <c r="E86" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="F86" t="s">
         <v>115</v>
       </c>
       <c r="G86" t="s">
-        <v>176</v>
+        <v>116</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -3744,10 +3744,10 @@
         <v>8</v>
       </c>
       <c r="C87" t="s">
+        <v>118</v>
+      </c>
+      <c r="D87" t="s">
         <v>173</v>
-      </c>
-      <c r="D87" t="s">
-        <v>113</v>
       </c>
       <c r="E87" t="s">
         <v>114</v>
@@ -3756,7 +3756,7 @@
         <v>115</v>
       </c>
       <c r="G87" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -3770,7 +3770,7 @@
         <v>118</v>
       </c>
       <c r="D88" t="s">
-        <v>113</v>
+        <v>119</v>
       </c>
       <c r="E88" t="s">
         <v>114</v>
@@ -3779,7 +3779,7 @@
         <v>115</v>
       </c>
       <c r="G88" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -3793,7 +3793,7 @@
         <v>118</v>
       </c>
       <c r="D89" t="s">
-        <v>113</v>
+        <v>119</v>
       </c>
       <c r="E89" t="s">
         <v>114</v>
@@ -3802,7 +3802,7 @@
         <v>115</v>
       </c>
       <c r="G89" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -3816,16 +3816,16 @@
         <v>124</v>
       </c>
       <c r="D90" t="s">
-        <v>113</v>
+        <v>125</v>
       </c>
       <c r="E90" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="F90" t="s">
         <v>115</v>
       </c>
       <c r="G90" t="s">
-        <v>126</v>
+        <v>116</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -3839,16 +3839,16 @@
         <v>182</v>
       </c>
       <c r="D91" t="s">
-        <v>113</v>
+        <v>183</v>
       </c>
       <c r="E91" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="F91" t="s">
         <v>115</v>
       </c>
       <c r="G91" t="s">
-        <v>184</v>
+        <v>116</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -3862,16 +3862,16 @@
         <v>124</v>
       </c>
       <c r="D92" t="s">
-        <v>113</v>
+        <v>125</v>
       </c>
       <c r="E92" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="F92" t="s">
         <v>115</v>
       </c>
       <c r="G92" t="s">
-        <v>126</v>
+        <v>116</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -3885,7 +3885,7 @@
         <v>121</v>
       </c>
       <c r="D93" t="s">
-        <v>113</v>
+        <v>122</v>
       </c>
       <c r="E93" t="s">
         <v>114</v>
@@ -3894,7 +3894,7 @@
         <v>115</v>
       </c>
       <c r="G93" t="s">
-        <v>122</v>
+        <v>116</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -3908,16 +3908,16 @@
         <v>124</v>
       </c>
       <c r="D94" t="s">
-        <v>113</v>
+        <v>125</v>
       </c>
       <c r="E94" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="F94" t="s">
         <v>115</v>
       </c>
       <c r="G94" t="s">
-        <v>126</v>
+        <v>116</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -3931,7 +3931,7 @@
         <v>189</v>
       </c>
       <c r="D95" t="s">
-        <v>113</v>
+        <v>190</v>
       </c>
       <c r="E95" t="s">
         <v>114</v>
@@ -3940,7 +3940,7 @@
         <v>115</v>
       </c>
       <c r="G95" t="s">
-        <v>190</v>
+        <v>116</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -3954,16 +3954,16 @@
         <v>124</v>
       </c>
       <c r="D96" t="s">
-        <v>192</v>
+        <v>125</v>
       </c>
       <c r="E96" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="F96" t="s">
         <v>115</v>
       </c>
       <c r="G96" t="s">
-        <v>126</v>
+        <v>192</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -3977,16 +3977,16 @@
         <v>124</v>
       </c>
       <c r="D97" t="s">
-        <v>192</v>
+        <v>125</v>
       </c>
       <c r="E97" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="F97" t="s">
         <v>115</v>
       </c>
       <c r="G97" t="s">
-        <v>126</v>
+        <v>192</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -4000,16 +4000,16 @@
         <v>195</v>
       </c>
       <c r="D98" t="s">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="E98" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="F98" t="s">
         <v>115</v>
       </c>
       <c r="G98" t="s">
-        <v>197</v>
+        <v>192</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -4023,16 +4023,16 @@
         <v>124</v>
       </c>
       <c r="D99" t="s">
-        <v>192</v>
+        <v>125</v>
       </c>
       <c r="E99" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="F99" t="s">
         <v>115</v>
       </c>
       <c r="G99" t="s">
-        <v>126</v>
+        <v>192</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -4046,16 +4046,16 @@
         <v>154</v>
       </c>
       <c r="D100" t="s">
-        <v>192</v>
+        <v>155</v>
       </c>
       <c r="E100" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="F100" t="s">
         <v>115</v>
       </c>
       <c r="G100" t="s">
-        <v>155</v>
+        <v>192</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -4069,16 +4069,16 @@
         <v>124</v>
       </c>
       <c r="D101" t="s">
-        <v>192</v>
+        <v>125</v>
       </c>
       <c r="E101" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="F101" t="s">
         <v>115</v>
       </c>
       <c r="G101" t="s">
-        <v>126</v>
+        <v>192</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -4091,13 +4091,13 @@
       <c r="C102" t="s">
         <v>202</v>
       </c>
+      <c r="D102" t="s">
+        <v>203</v>
+      </c>
       <c r="E102" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="F102" t="s">
-        <v>203</v>
-      </c>
-      <c r="G102" t="s">
         <v>204</v>
       </c>
     </row>
@@ -4111,13 +4111,13 @@
       <c r="C103" t="s">
         <v>202</v>
       </c>
+      <c r="D103" t="s">
+        <v>203</v>
+      </c>
       <c r="E103" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="F103" t="s">
-        <v>203</v>
-      </c>
-      <c r="G103" t="s">
         <v>204</v>
       </c>
     </row>
@@ -4131,13 +4131,13 @@
       <c r="C104" t="s">
         <v>202</v>
       </c>
+      <c r="D104" t="s">
+        <v>203</v>
+      </c>
       <c r="E104" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="F104" t="s">
-        <v>203</v>
-      </c>
-      <c r="G104" t="s">
         <v>204</v>
       </c>
     </row>
@@ -4151,14 +4151,14 @@
       <c r="C105" t="s">
         <v>208</v>
       </c>
+      <c r="D105" t="s">
+        <v>209</v>
+      </c>
       <c r="E105" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="F105" t="s">
-        <v>203</v>
-      </c>
-      <c r="G105" t="s">
-        <v>209</v>
+        <v>204</v>
       </c>
     </row>
     <row r="106" spans="1:7">
@@ -4171,13 +4171,13 @@
       <c r="C106" t="s">
         <v>202</v>
       </c>
+      <c r="D106" t="s">
+        <v>203</v>
+      </c>
       <c r="E106" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="F106" t="s">
-        <v>203</v>
-      </c>
-      <c r="G106" t="s">
         <v>204</v>
       </c>
     </row>
@@ -4191,14 +4191,14 @@
       <c r="C107" t="s">
         <v>182</v>
       </c>
+      <c r="D107" t="s">
+        <v>183</v>
+      </c>
       <c r="E107" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="F107" t="s">
-        <v>203</v>
-      </c>
-      <c r="G107" t="s">
-        <v>184</v>
+        <v>204</v>
       </c>
     </row>
     <row r="108" spans="1:7">
@@ -4211,14 +4211,14 @@
       <c r="C108" t="s">
         <v>213</v>
       </c>
+      <c r="D108" t="s">
+        <v>214</v>
+      </c>
       <c r="E108" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="F108" t="s">
-        <v>203</v>
-      </c>
-      <c r="G108" t="s">
-        <v>214</v>
+        <v>204</v>
       </c>
     </row>
     <row r="109" spans="1:7">
@@ -4231,14 +4231,14 @@
       <c r="C109" t="s">
         <v>216</v>
       </c>
+      <c r="D109" t="s">
+        <v>217</v>
+      </c>
       <c r="E109" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="F109" t="s">
-        <v>203</v>
-      </c>
-      <c r="G109" t="s">
-        <v>217</v>
+        <v>204</v>
       </c>
     </row>
     <row r="110" spans="1:7">
@@ -4251,14 +4251,14 @@
       <c r="C110" t="s">
         <v>219</v>
       </c>
+      <c r="D110" t="s">
+        <v>220</v>
+      </c>
       <c r="E110" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="F110" t="s">
-        <v>203</v>
-      </c>
-      <c r="G110" t="s">
-        <v>220</v>
+        <v>204</v>
       </c>
     </row>
     <row r="111" spans="1:7">
@@ -4271,13 +4271,13 @@
       <c r="C111" t="s">
         <v>202</v>
       </c>
+      <c r="D111" t="s">
+        <v>203</v>
+      </c>
       <c r="E111" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="F111" t="s">
-        <v>203</v>
-      </c>
-      <c r="G111" t="s">
         <v>204</v>
       </c>
     </row>
@@ -4291,17 +4291,17 @@
       <c r="C112" t="s">
         <v>223</v>
       </c>
+      <c r="D112" t="s">
+        <v>224</v>
+      </c>
       <c r="E112" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="F112" t="s">
-        <v>203</v>
-      </c>
-      <c r="G112" t="s">
-        <v>225</v>
-      </c>
-    </row>
-    <row r="113" spans="1:7">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="113" spans="1:6">
       <c r="A113" t="s">
         <v>226</v>
       </c>
@@ -4309,19 +4309,19 @@
         <v>8</v>
       </c>
       <c r="C113" t="s">
+        <v>112</v>
+      </c>
+      <c r="D113" t="s">
         <v>143</v>
       </c>
       <c r="E113" t="s">
         <v>114</v>
       </c>
       <c r="F113" t="s">
-        <v>203</v>
-      </c>
-      <c r="G113" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="114" spans="1:7">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="114" spans="1:6">
       <c r="A114" t="s">
         <v>227</v>
       </c>
@@ -4331,17 +4331,17 @@
       <c r="C114" t="s">
         <v>151</v>
       </c>
+      <c r="D114" t="s">
+        <v>152</v>
+      </c>
       <c r="E114" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="F114" t="s">
-        <v>203</v>
-      </c>
-      <c r="G114" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="115" spans="1:7">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="115" spans="1:6">
       <c r="A115" t="s">
         <v>228</v>
       </c>
@@ -4351,17 +4351,17 @@
       <c r="C115" t="s">
         <v>182</v>
       </c>
+      <c r="D115" t="s">
+        <v>183</v>
+      </c>
       <c r="E115" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="F115" t="s">
-        <v>203</v>
-      </c>
-      <c r="G115" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="116" spans="1:7">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="116" spans="1:6">
       <c r="A116" t="s">
         <v>229</v>
       </c>
@@ -4371,17 +4371,17 @@
       <c r="C116" t="s">
         <v>230</v>
       </c>
+      <c r="D116" t="s">
+        <v>231</v>
+      </c>
       <c r="E116" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="F116" t="s">
-        <v>203</v>
-      </c>
-      <c r="G116" t="s">
-        <v>231</v>
-      </c>
-    </row>
-    <row r="117" spans="1:7">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="117" spans="1:6">
       <c r="A117" t="s">
         <v>232</v>
       </c>
@@ -4391,17 +4391,17 @@
       <c r="C117" t="s">
         <v>223</v>
       </c>
+      <c r="D117" t="s">
+        <v>224</v>
+      </c>
       <c r="E117" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="F117" t="s">
-        <v>203</v>
-      </c>
-      <c r="G117" t="s">
-        <v>225</v>
-      </c>
-    </row>
-    <row r="118" spans="1:7">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="118" spans="1:6">
       <c r="A118" t="s">
         <v>233</v>
       </c>
@@ -4409,19 +4409,19 @@
         <v>8</v>
       </c>
       <c r="C118" t="s">
+        <v>163</v>
+      </c>
+      <c r="D118" t="s">
         <v>234</v>
       </c>
       <c r="E118" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="F118" t="s">
-        <v>203</v>
-      </c>
-      <c r="G118" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="119" spans="1:7">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="119" spans="1:6">
       <c r="A119" t="s">
         <v>235</v>
       </c>
@@ -4431,17 +4431,17 @@
       <c r="C119" t="s">
         <v>182</v>
       </c>
+      <c r="D119" t="s">
+        <v>183</v>
+      </c>
       <c r="E119" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="F119" t="s">
-        <v>203</v>
-      </c>
-      <c r="G119" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="120" spans="1:7">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="120" spans="1:6">
       <c r="A120" t="s">
         <v>236</v>
       </c>
@@ -4451,17 +4451,17 @@
       <c r="C120" t="s">
         <v>170</v>
       </c>
+      <c r="D120" t="s">
+        <v>171</v>
+      </c>
       <c r="E120" t="s">
         <v>114</v>
       </c>
       <c r="F120" t="s">
         <v>237</v>
       </c>
-      <c r="G120" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="121" spans="1:7">
+    </row>
+    <row r="121" spans="1:6">
       <c r="A121" t="s">
         <v>238</v>
       </c>
@@ -4469,6 +4469,9 @@
         <v>8</v>
       </c>
       <c r="C121" t="s">
+        <v>112</v>
+      </c>
+      <c r="D121" t="s">
         <v>143</v>
       </c>
       <c r="E121" t="s">
@@ -4477,11 +4480,8 @@
       <c r="F121" t="s">
         <v>237</v>
       </c>
-      <c r="G121" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="122" spans="1:7">
+    </row>
+    <row r="122" spans="1:6">
       <c r="A122" t="s">
         <v>239</v>
       </c>
@@ -4491,17 +4491,17 @@
       <c r="C122" t="s">
         <v>170</v>
       </c>
+      <c r="D122" t="s">
+        <v>171</v>
+      </c>
       <c r="E122" t="s">
         <v>114</v>
       </c>
       <c r="F122" t="s">
         <v>237</v>
       </c>
-      <c r="G122" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="123" spans="1:7">
+    </row>
+    <row r="123" spans="1:6">
       <c r="A123" t="s">
         <v>240</v>
       </c>
@@ -4511,17 +4511,17 @@
       <c r="C123" t="s">
         <v>170</v>
       </c>
+      <c r="D123" t="s">
+        <v>171</v>
+      </c>
       <c r="E123" t="s">
         <v>114</v>
       </c>
       <c r="F123" t="s">
         <v>237</v>
       </c>
-      <c r="G123" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="124" spans="1:7">
+    </row>
+    <row r="124" spans="1:6">
       <c r="A124" t="s">
         <v>241</v>
       </c>
@@ -4531,17 +4531,17 @@
       <c r="C124" t="s">
         <v>242</v>
       </c>
+      <c r="D124" t="s">
+        <v>243</v>
+      </c>
       <c r="E124" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="F124" t="s">
         <v>237</v>
       </c>
-      <c r="G124" t="s">
-        <v>243</v>
-      </c>
-    </row>
-    <row r="125" spans="1:7">
+    </row>
+    <row r="125" spans="1:6">
       <c r="A125" t="s">
         <v>244</v>
       </c>
@@ -4551,17 +4551,17 @@
       <c r="C125" t="s">
         <v>242</v>
       </c>
+      <c r="D125" t="s">
+        <v>243</v>
+      </c>
       <c r="E125" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="F125" t="s">
         <v>237</v>
       </c>
-      <c r="G125" t="s">
-        <v>243</v>
-      </c>
-    </row>
-    <row r="126" spans="1:7">
+    </row>
+    <row r="126" spans="1:6">
       <c r="A126" t="s">
         <v>245</v>
       </c>
@@ -4571,17 +4571,17 @@
       <c r="C126" t="s">
         <v>242</v>
       </c>
+      <c r="D126" t="s">
+        <v>243</v>
+      </c>
       <c r="E126" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="F126" t="s">
         <v>237</v>
       </c>
-      <c r="G126" t="s">
-        <v>243</v>
-      </c>
-    </row>
-    <row r="127" spans="1:7">
+    </row>
+    <row r="127" spans="1:6">
       <c r="A127" t="s">
         <v>246</v>
       </c>
@@ -4591,17 +4591,17 @@
       <c r="C127" t="s">
         <v>242</v>
       </c>
+      <c r="D127" t="s">
+        <v>243</v>
+      </c>
       <c r="E127" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="F127" t="s">
         <v>237</v>
       </c>
-      <c r="G127" t="s">
-        <v>243</v>
-      </c>
-    </row>
-    <row r="128" spans="1:7">
+    </row>
+    <row r="128" spans="1:6">
       <c r="A128" t="s">
         <v>247</v>
       </c>
@@ -4611,14 +4611,14 @@
       <c r="C128" t="s">
         <v>242</v>
       </c>
+      <c r="D128" t="s">
+        <v>243</v>
+      </c>
       <c r="E128" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="F128" t="s">
         <v>237</v>
-      </c>
-      <c r="G128" t="s">
-        <v>243</v>
       </c>
     </row>
     <row r="129" spans="1:7">
@@ -4629,16 +4629,16 @@
         <v>8</v>
       </c>
       <c r="C129" t="s">
+        <v>242</v>
+      </c>
+      <c r="D129" t="s">
         <v>249</v>
       </c>
       <c r="E129" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="F129" t="s">
         <v>237</v>
-      </c>
-      <c r="G129" t="s">
-        <v>243</v>
       </c>
     </row>
     <row r="130" spans="1:7">
@@ -4649,16 +4649,16 @@
         <v>8</v>
       </c>
       <c r="C130" t="s">
+        <v>242</v>
+      </c>
+      <c r="D130" t="s">
         <v>251</v>
       </c>
       <c r="E130" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="F130" t="s">
         <v>237</v>
-      </c>
-      <c r="G130" t="s">
-        <v>243</v>
       </c>
     </row>
     <row r="131" spans="1:7">
@@ -4669,16 +4669,16 @@
         <v>8</v>
       </c>
       <c r="C131" t="s">
+        <v>242</v>
+      </c>
+      <c r="D131" t="s">
         <v>253</v>
       </c>
       <c r="E131" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="F131" t="s">
         <v>237</v>
-      </c>
-      <c r="G131" t="s">
-        <v>243</v>
       </c>
     </row>
     <row r="132" spans="1:7">
@@ -4691,14 +4691,14 @@
       <c r="C132" t="s">
         <v>255</v>
       </c>
+      <c r="D132" t="s">
+        <v>256</v>
+      </c>
       <c r="E132" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="F132" t="s">
         <v>237</v>
-      </c>
-      <c r="G132" t="s">
-        <v>256</v>
       </c>
     </row>
     <row r="133" spans="1:7">
@@ -4711,14 +4711,14 @@
       <c r="C133" t="s">
         <v>189</v>
       </c>
+      <c r="D133" t="s">
+        <v>190</v>
+      </c>
       <c r="E133" t="s">
         <v>114</v>
       </c>
       <c r="F133" t="s">
         <v>237</v>
-      </c>
-      <c r="G133" t="s">
-        <v>190</v>
       </c>
     </row>
     <row r="134" spans="1:7">
@@ -4731,14 +4731,14 @@
       <c r="C134" t="s">
         <v>175</v>
       </c>
+      <c r="D134" t="s">
+        <v>176</v>
+      </c>
       <c r="E134" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="F134" t="s">
         <v>259</v>
-      </c>
-      <c r="G134" t="s">
-        <v>176</v>
       </c>
     </row>
     <row r="135" spans="1:7">
@@ -4751,14 +4751,14 @@
       <c r="C135" t="s">
         <v>175</v>
       </c>
+      <c r="D135" t="s">
+        <v>176</v>
+      </c>
       <c r="E135" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="F135" t="s">
         <v>259</v>
-      </c>
-      <c r="G135" t="s">
-        <v>176</v>
       </c>
     </row>
     <row r="136" spans="1:7">
@@ -4771,14 +4771,14 @@
       <c r="C136" t="s">
         <v>175</v>
       </c>
+      <c r="D136" t="s">
+        <v>176</v>
+      </c>
       <c r="E136" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="F136" t="s">
         <v>259</v>
-      </c>
-      <c r="G136" t="s">
-        <v>176</v>
       </c>
     </row>
     <row r="137" spans="1:7">
@@ -4791,14 +4791,14 @@
       <c r="C137" t="s">
         <v>175</v>
       </c>
+      <c r="D137" t="s">
+        <v>176</v>
+      </c>
       <c r="E137" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="F137" t="s">
         <v>259</v>
-      </c>
-      <c r="G137" t="s">
-        <v>176</v>
       </c>
     </row>
     <row r="138" spans="1:7">
@@ -4811,14 +4811,14 @@
       <c r="C138" t="s">
         <v>175</v>
       </c>
+      <c r="D138" t="s">
+        <v>176</v>
+      </c>
       <c r="E138" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="F138" t="s">
         <v>259</v>
-      </c>
-      <c r="G138" t="s">
-        <v>176</v>
       </c>
     </row>
     <row r="139" spans="1:7">
@@ -4831,14 +4831,14 @@
       <c r="C139" t="s">
         <v>265</v>
       </c>
+      <c r="D139" t="s">
+        <v>266</v>
+      </c>
       <c r="E139" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="F139" t="s">
         <v>259</v>
-      </c>
-      <c r="G139" t="s">
-        <v>266</v>
       </c>
     </row>
     <row r="140" spans="1:7">
@@ -4851,14 +4851,14 @@
       <c r="C140" t="s">
         <v>175</v>
       </c>
+      <c r="D140" t="s">
+        <v>176</v>
+      </c>
       <c r="E140" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="F140" t="s">
         <v>259</v>
-      </c>
-      <c r="G140" t="s">
-        <v>176</v>
       </c>
     </row>
     <row r="141" spans="1:7">
@@ -4875,7 +4875,7 @@
         <v>270</v>
       </c>
       <c r="E141" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="F141" t="s">
         <v>271</v>
@@ -4898,7 +4898,7 @@
         <v>270</v>
       </c>
       <c r="E142" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="F142" t="s">
         <v>271</v>
@@ -4918,16 +4918,16 @@
         <v>275</v>
       </c>
       <c r="D143" t="s">
-        <v>270</v>
+        <v>276</v>
       </c>
       <c r="E143" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="F143" t="s">
         <v>271</v>
       </c>
       <c r="G143" t="s">
-        <v>276</v>
+        <v>272</v>
       </c>
     </row>
     <row r="144" spans="1:7">
@@ -4941,16 +4941,16 @@
         <v>275</v>
       </c>
       <c r="D144" t="s">
-        <v>270</v>
+        <v>276</v>
       </c>
       <c r="E144" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="F144" t="s">
         <v>271</v>
       </c>
       <c r="G144" t="s">
-        <v>276</v>
+        <v>272</v>
       </c>
     </row>
     <row r="145" spans="1:7">
@@ -4964,16 +4964,16 @@
         <v>275</v>
       </c>
       <c r="D145" t="s">
-        <v>270</v>
+        <v>276</v>
       </c>
       <c r="E145" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="F145" t="s">
         <v>271</v>
       </c>
       <c r="G145" t="s">
-        <v>276</v>
+        <v>272</v>
       </c>
     </row>
     <row r="146" spans="1:7">
@@ -4990,7 +4990,7 @@
         <v>270</v>
       </c>
       <c r="E146" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="F146" t="s">
         <v>271</v>
@@ -5010,16 +5010,16 @@
         <v>269</v>
       </c>
       <c r="D147" t="s">
-        <v>281</v>
+        <v>270</v>
       </c>
       <c r="E147" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="F147" t="s">
         <v>271</v>
       </c>
       <c r="G147" t="s">
-        <v>272</v>
+        <v>281</v>
       </c>
     </row>
     <row r="148" spans="1:7">
@@ -5033,16 +5033,16 @@
         <v>269</v>
       </c>
       <c r="D148" t="s">
-        <v>281</v>
+        <v>270</v>
       </c>
       <c r="E148" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="F148" t="s">
         <v>271</v>
       </c>
       <c r="G148" t="s">
-        <v>272</v>
+        <v>281</v>
       </c>
     </row>
     <row r="149" spans="1:7">
@@ -5056,16 +5056,16 @@
         <v>269</v>
       </c>
       <c r="D149" t="s">
-        <v>281</v>
+        <v>270</v>
       </c>
       <c r="E149" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="F149" t="s">
         <v>271</v>
       </c>
       <c r="G149" t="s">
-        <v>272</v>
+        <v>281</v>
       </c>
     </row>
     <row r="150" spans="1:7">
@@ -5079,16 +5079,16 @@
         <v>269</v>
       </c>
       <c r="D150" t="s">
-        <v>281</v>
+        <v>270</v>
       </c>
       <c r="E150" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="F150" t="s">
         <v>271</v>
       </c>
       <c r="G150" t="s">
-        <v>272</v>
+        <v>281</v>
       </c>
     </row>
     <row r="151" spans="1:7">
@@ -5102,16 +5102,16 @@
         <v>269</v>
       </c>
       <c r="D151" t="s">
-        <v>281</v>
+        <v>270</v>
       </c>
       <c r="E151" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="F151" t="s">
         <v>271</v>
       </c>
       <c r="G151" t="s">
-        <v>272</v>
+        <v>281</v>
       </c>
     </row>
     <row r="152" spans="1:7">
@@ -5125,16 +5125,16 @@
         <v>269</v>
       </c>
       <c r="D152" t="s">
-        <v>281</v>
+        <v>270</v>
       </c>
       <c r="E152" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="F152" t="s">
         <v>271</v>
       </c>
       <c r="G152" t="s">
-        <v>272</v>
+        <v>281</v>
       </c>
     </row>
     <row r="153" spans="1:7">
@@ -5148,16 +5148,16 @@
         <v>269</v>
       </c>
       <c r="D153" t="s">
-        <v>281</v>
+        <v>270</v>
       </c>
       <c r="E153" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="F153" t="s">
         <v>271</v>
       </c>
       <c r="G153" t="s">
-        <v>272</v>
+        <v>281</v>
       </c>
     </row>
     <row r="154" spans="1:7">
@@ -5171,16 +5171,16 @@
         <v>269</v>
       </c>
       <c r="D154" t="s">
-        <v>281</v>
+        <v>270</v>
       </c>
       <c r="E154" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="F154" t="s">
         <v>271</v>
       </c>
       <c r="G154" t="s">
-        <v>272</v>
+        <v>281</v>
       </c>
     </row>
     <row r="155" spans="1:7">
@@ -5194,16 +5194,16 @@
         <v>269</v>
       </c>
       <c r="D155" t="s">
-        <v>281</v>
+        <v>270</v>
       </c>
       <c r="E155" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="F155" t="s">
         <v>271</v>
       </c>
       <c r="G155" t="s">
-        <v>272</v>
+        <v>281</v>
       </c>
     </row>
     <row r="156" spans="1:7">
@@ -5217,16 +5217,16 @@
         <v>269</v>
       </c>
       <c r="D156" t="s">
-        <v>291</v>
+        <v>270</v>
       </c>
       <c r="E156" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="F156" t="s">
         <v>271</v>
       </c>
       <c r="G156" t="s">
-        <v>272</v>
+        <v>291</v>
       </c>
     </row>
     <row r="157" spans="1:7">
@@ -5237,19 +5237,19 @@
         <v>8</v>
       </c>
       <c r="C157" t="s">
+        <v>269</v>
+      </c>
+      <c r="D157" t="s">
         <v>293</v>
       </c>
-      <c r="D157" t="s">
-        <v>291</v>
-      </c>
       <c r="E157" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="F157" t="s">
         <v>271</v>
       </c>
       <c r="G157" t="s">
-        <v>272</v>
+        <v>291</v>
       </c>
     </row>
     <row r="158" spans="1:7">
@@ -5263,16 +5263,16 @@
         <v>269</v>
       </c>
       <c r="D158" t="s">
-        <v>291</v>
+        <v>270</v>
       </c>
       <c r="E158" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="F158" t="s">
         <v>271</v>
       </c>
       <c r="G158" t="s">
-        <v>272</v>
+        <v>291</v>
       </c>
     </row>
     <row r="159" spans="1:7">
@@ -5286,16 +5286,16 @@
         <v>269</v>
       </c>
       <c r="D159" t="s">
-        <v>291</v>
+        <v>270</v>
       </c>
       <c r="E159" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="F159" t="s">
         <v>271</v>
       </c>
       <c r="G159" t="s">
-        <v>272</v>
+        <v>291</v>
       </c>
     </row>
     <row r="160" spans="1:7">
@@ -5309,16 +5309,16 @@
         <v>269</v>
       </c>
       <c r="D160" t="s">
-        <v>291</v>
+        <v>270</v>
       </c>
       <c r="E160" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="F160" t="s">
         <v>271</v>
       </c>
       <c r="G160" t="s">
-        <v>272</v>
+        <v>291</v>
       </c>
     </row>
     <row r="161" spans="1:7">
@@ -5332,16 +5332,16 @@
         <v>269</v>
       </c>
       <c r="D161" t="s">
-        <v>291</v>
+        <v>270</v>
       </c>
       <c r="E161" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="F161" t="s">
         <v>271</v>
       </c>
       <c r="G161" t="s">
-        <v>272</v>
+        <v>291</v>
       </c>
     </row>
     <row r="162" spans="1:7">
@@ -5355,16 +5355,16 @@
         <v>269</v>
       </c>
       <c r="D162" t="s">
-        <v>299</v>
+        <v>270</v>
       </c>
       <c r="E162" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="F162" t="s">
         <v>271</v>
       </c>
       <c r="G162" t="s">
-        <v>272</v>
+        <v>299</v>
       </c>
     </row>
     <row r="163" spans="1:7">
@@ -5375,19 +5375,19 @@
         <v>8</v>
       </c>
       <c r="C163" t="s">
+        <v>269</v>
+      </c>
+      <c r="D163" t="s">
         <v>301</v>
       </c>
-      <c r="D163" t="s">
-        <v>302</v>
-      </c>
       <c r="E163" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="F163" t="s">
         <v>271</v>
       </c>
       <c r="G163" t="s">
-        <v>272</v>
+        <v>302</v>
       </c>
     </row>
     <row r="164" spans="1:7">
@@ -5401,16 +5401,16 @@
         <v>269</v>
       </c>
       <c r="D164" t="s">
-        <v>304</v>
+        <v>270</v>
       </c>
       <c r="E164" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="F164" t="s">
         <v>271</v>
       </c>
       <c r="G164" t="s">
-        <v>272</v>
+        <v>304</v>
       </c>
     </row>
     <row r="165" spans="1:7">
@@ -5424,16 +5424,16 @@
         <v>269</v>
       </c>
       <c r="D165" t="s">
-        <v>304</v>
+        <v>270</v>
       </c>
       <c r="E165" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="F165" t="s">
         <v>271</v>
       </c>
       <c r="G165" t="s">
-        <v>272</v>
+        <v>304</v>
       </c>
     </row>
     <row r="166" spans="1:7">
@@ -5447,16 +5447,16 @@
         <v>269</v>
       </c>
       <c r="D166" t="s">
-        <v>304</v>
+        <v>270</v>
       </c>
       <c r="E166" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="F166" t="s">
         <v>271</v>
       </c>
       <c r="G166" t="s">
-        <v>272</v>
+        <v>304</v>
       </c>
     </row>
     <row r="167" spans="1:7">
@@ -5470,16 +5470,16 @@
         <v>269</v>
       </c>
       <c r="D167" t="s">
-        <v>304</v>
+        <v>270</v>
       </c>
       <c r="E167" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="F167" t="s">
         <v>271</v>
       </c>
       <c r="G167" t="s">
-        <v>272</v>
+        <v>304</v>
       </c>
     </row>
     <row r="168" spans="1:7">
@@ -5490,19 +5490,19 @@
         <v>8</v>
       </c>
       <c r="C168" t="s">
+        <v>269</v>
+      </c>
+      <c r="D168" t="s">
         <v>309</v>
       </c>
-      <c r="D168" t="s">
-        <v>304</v>
-      </c>
       <c r="E168" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="F168" t="s">
         <v>271</v>
       </c>
       <c r="G168" t="s">
-        <v>272</v>
+        <v>304</v>
       </c>
     </row>
     <row r="169" spans="1:7">
@@ -5513,19 +5513,19 @@
         <v>8</v>
       </c>
       <c r="C169" t="s">
+        <v>269</v>
+      </c>
+      <c r="D169" t="s">
         <v>309</v>
       </c>
-      <c r="D169" t="s">
-        <v>304</v>
-      </c>
       <c r="E169" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="F169" t="s">
         <v>271</v>
       </c>
       <c r="G169" t="s">
-        <v>272</v>
+        <v>304</v>
       </c>
     </row>
     <row r="170" spans="1:7">
@@ -5539,16 +5539,16 @@
         <v>269</v>
       </c>
       <c r="D170" t="s">
-        <v>304</v>
+        <v>270</v>
       </c>
       <c r="E170" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="F170" t="s">
         <v>271</v>
       </c>
       <c r="G170" t="s">
-        <v>272</v>
+        <v>304</v>
       </c>
     </row>
     <row r="171" spans="1:7">
@@ -5561,14 +5561,14 @@
       <c r="C171" t="s">
         <v>163</v>
       </c>
+      <c r="D171" t="s">
+        <v>164</v>
+      </c>
       <c r="E171" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="F171" t="s">
         <v>313</v>
-      </c>
-      <c r="G171" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="172" spans="1:7">
@@ -5581,14 +5581,14 @@
       <c r="C172" t="s">
         <v>118</v>
       </c>
+      <c r="D172" t="s">
+        <v>119</v>
+      </c>
       <c r="E172" t="s">
         <v>114</v>
       </c>
       <c r="F172" t="s">
         <v>313</v>
-      </c>
-      <c r="G172" t="s">
-        <v>119</v>
       </c>
     </row>
     <row r="173" spans="1:7">
@@ -5601,14 +5601,14 @@
       <c r="C173" t="s">
         <v>163</v>
       </c>
+      <c r="D173" t="s">
+        <v>164</v>
+      </c>
       <c r="E173" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="F173" t="s">
         <v>313</v>
-      </c>
-      <c r="G173" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="174" spans="1:7">
@@ -5621,14 +5621,14 @@
       <c r="C174" t="s">
         <v>163</v>
       </c>
+      <c r="D174" t="s">
+        <v>164</v>
+      </c>
       <c r="E174" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="F174" t="s">
         <v>313</v>
-      </c>
-      <c r="G174" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="175" spans="1:7">
@@ -5641,14 +5641,14 @@
       <c r="C175" t="s">
         <v>163</v>
       </c>
+      <c r="D175" t="s">
+        <v>164</v>
+      </c>
       <c r="E175" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="F175" t="s">
         <v>313</v>
-      </c>
-      <c r="G175" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="176" spans="1:7">
@@ -5661,14 +5661,14 @@
       <c r="C176" t="s">
         <v>163</v>
       </c>
+      <c r="D176" t="s">
+        <v>164</v>
+      </c>
       <c r="E176" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="F176" t="s">
         <v>313</v>
-      </c>
-      <c r="G176" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="177" spans="1:7">
@@ -5681,14 +5681,14 @@
       <c r="C177" t="s">
         <v>163</v>
       </c>
+      <c r="D177" t="s">
+        <v>164</v>
+      </c>
       <c r="E177" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="F177" t="s">
         <v>320</v>
-      </c>
-      <c r="G177" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="178" spans="1:7">
@@ -5701,14 +5701,14 @@
       <c r="C178" t="s">
         <v>163</v>
       </c>
+      <c r="D178" t="s">
+        <v>164</v>
+      </c>
       <c r="E178" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="F178" t="s">
         <v>320</v>
-      </c>
-      <c r="G178" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="179" spans="1:7">
@@ -5721,14 +5721,14 @@
       <c r="C179" t="s">
         <v>163</v>
       </c>
+      <c r="D179" t="s">
+        <v>164</v>
+      </c>
       <c r="E179" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="F179" t="s">
         <v>320</v>
-      </c>
-      <c r="G179" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="180" spans="1:7">
@@ -5741,14 +5741,14 @@
       <c r="C180" t="s">
         <v>163</v>
       </c>
+      <c r="D180" t="s">
+        <v>164</v>
+      </c>
       <c r="E180" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="F180" t="s">
         <v>320</v>
-      </c>
-      <c r="G180" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="181" spans="1:7">
@@ -5765,7 +5765,7 @@
         <v>326</v>
       </c>
       <c r="E181" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="F181" t="s">
         <v>327</v>
@@ -5788,7 +5788,7 @@
         <v>326</v>
       </c>
       <c r="E182" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="F182" t="s">
         <v>327</v>
@@ -5811,7 +5811,7 @@
         <v>326</v>
       </c>
       <c r="E183" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="F183" t="s">
         <v>327</v>
@@ -5834,7 +5834,7 @@
         <v>326</v>
       </c>
       <c r="E184" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="F184" t="s">
         <v>327</v>
@@ -5857,7 +5857,7 @@
         <v>326</v>
       </c>
       <c r="E185" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="F185" t="s">
         <v>327</v>
@@ -5880,7 +5880,7 @@
         <v>326</v>
       </c>
       <c r="E186" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="F186" t="s">
         <v>327</v>
@@ -5903,7 +5903,7 @@
         <v>326</v>
       </c>
       <c r="E187" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="F187" t="s">
         <v>327</v>
@@ -5926,7 +5926,7 @@
         <v>326</v>
       </c>
       <c r="E188" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="F188" t="s">
         <v>327</v>
@@ -5949,7 +5949,7 @@
         <v>326</v>
       </c>
       <c r="E189" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="F189" t="s">
         <v>327</v>
@@ -5972,7 +5972,7 @@
         <v>326</v>
       </c>
       <c r="E190" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="F190" t="s">
         <v>327</v>
@@ -5995,7 +5995,7 @@
         <v>326</v>
       </c>
       <c r="E191" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="F191" t="s">
         <v>327</v>
@@ -6018,7 +6018,7 @@
         <v>326</v>
       </c>
       <c r="E192" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="F192" t="s">
         <v>327</v>
@@ -6035,19 +6035,19 @@
         <v>8</v>
       </c>
       <c r="C193" t="s">
+        <v>275</v>
+      </c>
+      <c r="D193" t="s">
         <v>341</v>
       </c>
-      <c r="D193" t="s">
-        <v>326</v>
-      </c>
       <c r="E193" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="F193" t="s">
         <v>327</v>
       </c>
       <c r="G193" t="s">
-        <v>276</v>
+        <v>328</v>
       </c>
     </row>
     <row r="194" spans="1:7">
@@ -6064,7 +6064,7 @@
         <v>326</v>
       </c>
       <c r="E194" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="F194" t="s">
         <v>327</v>
@@ -6087,7 +6087,7 @@
         <v>326</v>
       </c>
       <c r="E195" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="F195" t="s">
         <v>327</v>
@@ -6110,7 +6110,7 @@
         <v>326</v>
       </c>
       <c r="E196" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="F196" t="s">
         <v>327</v>
@@ -6133,7 +6133,7 @@
         <v>326</v>
       </c>
       <c r="E197" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="F197" t="s">
         <v>327</v>
@@ -6156,7 +6156,7 @@
         <v>326</v>
       </c>
       <c r="E198" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="F198" t="s">
         <v>327</v>
@@ -6173,19 +6173,19 @@
         <v>8</v>
       </c>
       <c r="C199" t="s">
+        <v>325</v>
+      </c>
+      <c r="D199" t="s">
         <v>348</v>
       </c>
-      <c r="D199" t="s">
-        <v>349</v>
-      </c>
       <c r="E199" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="F199" t="s">
         <v>327</v>
       </c>
       <c r="G199" t="s">
-        <v>328</v>
+        <v>349</v>
       </c>
     </row>
     <row r="200" spans="1:7">
@@ -6196,19 +6196,19 @@
         <v>8</v>
       </c>
       <c r="C200" t="s">
+        <v>325</v>
+      </c>
+      <c r="D200" t="s">
         <v>348</v>
       </c>
-      <c r="D200" t="s">
-        <v>349</v>
-      </c>
       <c r="E200" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="F200" t="s">
         <v>327</v>
       </c>
       <c r="G200" t="s">
-        <v>328</v>
+        <v>349</v>
       </c>
     </row>
     <row r="201" spans="1:7">
@@ -6219,19 +6219,19 @@
         <v>8</v>
       </c>
       <c r="C201" t="s">
+        <v>325</v>
+      </c>
+      <c r="D201" t="s">
         <v>348</v>
       </c>
-      <c r="D201" t="s">
-        <v>349</v>
-      </c>
       <c r="E201" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="F201" t="s">
         <v>327</v>
       </c>
       <c r="G201" t="s">
-        <v>328</v>
+        <v>349</v>
       </c>
     </row>
     <row r="202" spans="1:7">
@@ -6242,19 +6242,19 @@
         <v>8</v>
       </c>
       <c r="C202" t="s">
+        <v>325</v>
+      </c>
+      <c r="D202" t="s">
         <v>348</v>
       </c>
-      <c r="D202" t="s">
-        <v>349</v>
-      </c>
       <c r="E202" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="F202" t="s">
         <v>327</v>
       </c>
       <c r="G202" t="s">
-        <v>328</v>
+        <v>349</v>
       </c>
     </row>
     <row r="203" spans="1:7">
@@ -6265,19 +6265,19 @@
         <v>8</v>
       </c>
       <c r="C203" t="s">
+        <v>275</v>
+      </c>
+      <c r="D203" t="s">
         <v>341</v>
       </c>
-      <c r="D203" t="s">
-        <v>349</v>
-      </c>
       <c r="E203" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="F203" t="s">
         <v>327</v>
       </c>
       <c r="G203" t="s">
-        <v>276</v>
+        <v>349</v>
       </c>
     </row>
     <row r="204" spans="1:7">
@@ -6288,19 +6288,19 @@
         <v>8</v>
       </c>
       <c r="C204" t="s">
+        <v>325</v>
+      </c>
+      <c r="D204" t="s">
         <v>348</v>
       </c>
-      <c r="D204" t="s">
-        <v>349</v>
-      </c>
       <c r="E204" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="F204" t="s">
         <v>327</v>
       </c>
       <c r="G204" t="s">
-        <v>328</v>
+        <v>349</v>
       </c>
     </row>
     <row r="205" spans="1:7">
@@ -6311,19 +6311,19 @@
         <v>8</v>
       </c>
       <c r="C205" t="s">
+        <v>325</v>
+      </c>
+      <c r="D205" t="s">
         <v>356</v>
       </c>
-      <c r="D205" t="s">
-        <v>357</v>
-      </c>
       <c r="E205" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="F205" t="s">
         <v>327</v>
       </c>
       <c r="G205" t="s">
-        <v>328</v>
+        <v>357</v>
       </c>
     </row>
     <row r="206" spans="1:7">
@@ -6334,19 +6334,19 @@
         <v>8</v>
       </c>
       <c r="C206" t="s">
+        <v>325</v>
+      </c>
+      <c r="D206" t="s">
         <v>356</v>
       </c>
-      <c r="D206" t="s">
-        <v>357</v>
-      </c>
       <c r="E206" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="F206" t="s">
         <v>327</v>
       </c>
       <c r="G206" t="s">
-        <v>328</v>
+        <v>357</v>
       </c>
     </row>
     <row r="207" spans="1:7">
@@ -6357,19 +6357,19 @@
         <v>8</v>
       </c>
       <c r="C207" t="s">
+        <v>325</v>
+      </c>
+      <c r="D207" t="s">
         <v>356</v>
       </c>
-      <c r="D207" t="s">
-        <v>357</v>
-      </c>
       <c r="E207" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="F207" t="s">
         <v>327</v>
       </c>
       <c r="G207" t="s">
-        <v>328</v>
+        <v>357</v>
       </c>
     </row>
     <row r="208" spans="1:7">
@@ -6380,19 +6380,19 @@
         <v>8</v>
       </c>
       <c r="C208" t="s">
+        <v>275</v>
+      </c>
+      <c r="D208" t="s">
         <v>341</v>
       </c>
-      <c r="D208" t="s">
-        <v>357</v>
-      </c>
       <c r="E208" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="F208" t="s">
         <v>327</v>
       </c>
       <c r="G208" t="s">
-        <v>276</v>
+        <v>357</v>
       </c>
     </row>
     <row r="209" spans="1:7">
@@ -6403,19 +6403,19 @@
         <v>8</v>
       </c>
       <c r="C209" t="s">
+        <v>325</v>
+      </c>
+      <c r="D209" t="s">
         <v>356</v>
       </c>
-      <c r="D209" t="s">
-        <v>357</v>
-      </c>
       <c r="E209" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="F209" t="s">
         <v>327</v>
       </c>
       <c r="G209" t="s">
-        <v>328</v>
+        <v>357</v>
       </c>
     </row>
     <row r="210" spans="1:7">
@@ -6432,7 +6432,7 @@
         <v>364</v>
       </c>
       <c r="E210" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="F210" t="s">
         <v>365</v>
@@ -6455,7 +6455,7 @@
         <v>364</v>
       </c>
       <c r="E211" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="F211" t="s">
         <v>365</v>
@@ -6478,7 +6478,7 @@
         <v>364</v>
       </c>
       <c r="E212" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="F212" t="s">
         <v>365</v>
@@ -6501,7 +6501,7 @@
         <v>364</v>
       </c>
       <c r="E213" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="F213" t="s">
         <v>365</v>
@@ -6524,7 +6524,7 @@
         <v>364</v>
       </c>
       <c r="E214" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="F214" t="s">
         <v>365</v>
@@ -6541,19 +6541,19 @@
         <v>8</v>
       </c>
       <c r="C215" t="s">
+        <v>325</v>
+      </c>
+      <c r="D215" t="s">
         <v>348</v>
       </c>
-      <c r="D215" t="s">
-        <v>364</v>
-      </c>
       <c r="E215" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="F215" t="s">
         <v>365</v>
       </c>
       <c r="G215" t="s">
-        <v>328</v>
+        <v>366</v>
       </c>
     </row>
     <row r="216" spans="1:7">
@@ -6570,7 +6570,7 @@
         <v>364</v>
       </c>
       <c r="E216" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="F216" t="s">
         <v>365</v>
@@ -6593,7 +6593,7 @@
         <v>364</v>
       </c>
       <c r="E217" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="F217" t="s">
         <v>365</v>
@@ -6616,7 +6616,7 @@
         <v>364</v>
       </c>
       <c r="E218" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="F218" t="s">
         <v>365</v>
@@ -6639,7 +6639,7 @@
         <v>364</v>
       </c>
       <c r="E219" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="F219" t="s">
         <v>365</v>
@@ -6656,19 +6656,19 @@
         <v>8</v>
       </c>
       <c r="C220" t="s">
+        <v>269</v>
+      </c>
+      <c r="D220" t="s">
         <v>309</v>
       </c>
-      <c r="D220" t="s">
-        <v>364</v>
-      </c>
       <c r="E220" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="F220" t="s">
         <v>365</v>
       </c>
       <c r="G220" t="s">
-        <v>272</v>
+        <v>366</v>
       </c>
     </row>
     <row r="221" spans="1:7">
@@ -6685,7 +6685,7 @@
         <v>364</v>
       </c>
       <c r="E221" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="F221" t="s">
         <v>365</v>
@@ -6708,7 +6708,7 @@
         <v>364</v>
       </c>
       <c r="E222" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="F222" t="s">
         <v>365</v>
@@ -6731,7 +6731,7 @@
         <v>364</v>
       </c>
       <c r="E223" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="F223" t="s">
         <v>365</v>
@@ -6754,7 +6754,7 @@
         <v>364</v>
       </c>
       <c r="E224" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="F224" t="s">
         <v>365</v>
@@ -6777,7 +6777,7 @@
         <v>364</v>
       </c>
       <c r="E225" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="F225" t="s">
         <v>365</v>
@@ -6797,16 +6797,16 @@
         <v>275</v>
       </c>
       <c r="D226" t="s">
-        <v>364</v>
+        <v>276</v>
       </c>
       <c r="E226" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="F226" t="s">
         <v>365</v>
       </c>
       <c r="G226" t="s">
-        <v>276</v>
+        <v>366</v>
       </c>
     </row>
     <row r="227" spans="1:7">
@@ -6823,7 +6823,7 @@
         <v>364</v>
       </c>
       <c r="E227" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="F227" t="s">
         <v>365</v>
@@ -6843,16 +6843,16 @@
         <v>163</v>
       </c>
       <c r="D228" t="s">
-        <v>364</v>
+        <v>164</v>
       </c>
       <c r="E228" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="F228" t="s">
         <v>365</v>
       </c>
       <c r="G228" t="s">
-        <v>165</v>
+        <v>366</v>
       </c>
     </row>
     <row r="229" spans="1:7">
@@ -6863,19 +6863,19 @@
         <v>8</v>
       </c>
       <c r="C229" t="s">
+        <v>363</v>
+      </c>
+      <c r="D229" t="s">
         <v>386</v>
       </c>
-      <c r="D229" t="s">
-        <v>387</v>
-      </c>
       <c r="E229" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="F229" t="s">
         <v>365</v>
       </c>
       <c r="G229" t="s">
-        <v>366</v>
+        <v>387</v>
       </c>
     </row>
     <row r="230" spans="1:7">
@@ -6886,19 +6886,19 @@
         <v>8</v>
       </c>
       <c r="C230" t="s">
+        <v>363</v>
+      </c>
+      <c r="D230" t="s">
         <v>386</v>
       </c>
-      <c r="D230" t="s">
-        <v>387</v>
-      </c>
       <c r="E230" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="F230" t="s">
         <v>365</v>
       </c>
       <c r="G230" t="s">
-        <v>366</v>
+        <v>387</v>
       </c>
     </row>
     <row r="231" spans="1:7">
@@ -6909,19 +6909,19 @@
         <v>8</v>
       </c>
       <c r="C231" t="s">
+        <v>269</v>
+      </c>
+      <c r="D231" t="s">
         <v>293</v>
       </c>
-      <c r="D231" t="s">
-        <v>387</v>
-      </c>
       <c r="E231" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="F231" t="s">
         <v>365</v>
       </c>
       <c r="G231" t="s">
-        <v>272</v>
+        <v>387</v>
       </c>
     </row>
     <row r="232" spans="1:7">
@@ -6932,19 +6932,19 @@
         <v>8</v>
       </c>
       <c r="C232" t="s">
+        <v>269</v>
+      </c>
+      <c r="D232" t="s">
         <v>309</v>
       </c>
-      <c r="D232" t="s">
-        <v>387</v>
-      </c>
       <c r="E232" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="F232" t="s">
         <v>365</v>
       </c>
       <c r="G232" t="s">
-        <v>272</v>
+        <v>387</v>
       </c>
     </row>
     <row r="233" spans="1:7">
@@ -6955,19 +6955,19 @@
         <v>8</v>
       </c>
       <c r="C233" t="s">
+        <v>363</v>
+      </c>
+      <c r="D233" t="s">
         <v>386</v>
       </c>
-      <c r="D233" t="s">
-        <v>387</v>
-      </c>
       <c r="E233" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="F233" t="s">
         <v>365</v>
       </c>
       <c r="G233" t="s">
-        <v>366</v>
+        <v>387</v>
       </c>
     </row>
     <row r="234" spans="1:7">
@@ -6978,19 +6978,19 @@
         <v>8</v>
       </c>
       <c r="C234" t="s">
+        <v>363</v>
+      </c>
+      <c r="D234" t="s">
         <v>386</v>
       </c>
-      <c r="D234" t="s">
-        <v>387</v>
-      </c>
       <c r="E234" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="F234" t="s">
         <v>365</v>
       </c>
       <c r="G234" t="s">
-        <v>366</v>
+        <v>387</v>
       </c>
     </row>
     <row r="235" spans="1:7">
@@ -7001,19 +7001,19 @@
         <v>8</v>
       </c>
       <c r="C235" t="s">
+        <v>363</v>
+      </c>
+      <c r="D235" t="s">
         <v>386</v>
       </c>
-      <c r="D235" t="s">
-        <v>387</v>
-      </c>
       <c r="E235" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="F235" t="s">
         <v>365</v>
       </c>
       <c r="G235" t="s">
-        <v>366</v>
+        <v>387</v>
       </c>
     </row>
     <row r="236" spans="1:7">
@@ -7024,19 +7024,19 @@
         <v>8</v>
       </c>
       <c r="C236" t="s">
+        <v>363</v>
+      </c>
+      <c r="D236" t="s">
         <v>386</v>
       </c>
-      <c r="D236" t="s">
-        <v>387</v>
-      </c>
       <c r="E236" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="F236" t="s">
         <v>365</v>
       </c>
       <c r="G236" t="s">
-        <v>366</v>
+        <v>387</v>
       </c>
     </row>
     <row r="237" spans="1:7">
@@ -7047,19 +7047,19 @@
         <v>8</v>
       </c>
       <c r="C237" t="s">
+        <v>363</v>
+      </c>
+      <c r="D237" t="s">
         <v>386</v>
       </c>
-      <c r="D237" t="s">
-        <v>387</v>
-      </c>
       <c r="E237" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="F237" t="s">
         <v>365</v>
       </c>
       <c r="G237" t="s">
-        <v>366</v>
+        <v>387</v>
       </c>
     </row>
     <row r="238" spans="1:7">
@@ -7070,19 +7070,19 @@
         <v>8</v>
       </c>
       <c r="C238" t="s">
+        <v>363</v>
+      </c>
+      <c r="D238" t="s">
         <v>386</v>
       </c>
-      <c r="D238" t="s">
-        <v>387</v>
-      </c>
       <c r="E238" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="F238" t="s">
         <v>365</v>
       </c>
       <c r="G238" t="s">
-        <v>366</v>
+        <v>387</v>
       </c>
     </row>
     <row r="239" spans="1:7">
@@ -7093,19 +7093,19 @@
         <v>8</v>
       </c>
       <c r="C239" t="s">
+        <v>363</v>
+      </c>
+      <c r="D239" t="s">
         <v>398</v>
       </c>
-      <c r="D239" t="s">
-        <v>399</v>
-      </c>
       <c r="E239" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="F239" t="s">
         <v>365</v>
       </c>
       <c r="G239" t="s">
-        <v>366</v>
+        <v>399</v>
       </c>
     </row>
     <row r="240" spans="1:7">
@@ -7119,16 +7119,16 @@
         <v>163</v>
       </c>
       <c r="D240" t="s">
+        <v>164</v>
+      </c>
+      <c r="E240" t="s">
+        <v>165</v>
+      </c>
+      <c r="F240" t="s">
         <v>401</v>
       </c>
-      <c r="E240" t="s">
-        <v>164</v>
-      </c>
-      <c r="F240" t="s">
+      <c r="G240" t="s">
         <v>402</v>
-      </c>
-      <c r="G240" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="241" spans="1:7">
@@ -7142,16 +7142,16 @@
         <v>163</v>
       </c>
       <c r="D241" t="s">
+        <v>164</v>
+      </c>
+      <c r="E241" t="s">
+        <v>165</v>
+      </c>
+      <c r="F241" t="s">
         <v>401</v>
       </c>
-      <c r="E241" t="s">
-        <v>164</v>
-      </c>
-      <c r="F241" t="s">
+      <c r="G241" t="s">
         <v>402</v>
-      </c>
-      <c r="G241" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="242" spans="1:7">
@@ -7165,16 +7165,16 @@
         <v>163</v>
       </c>
       <c r="D242" t="s">
+        <v>164</v>
+      </c>
+      <c r="E242" t="s">
+        <v>165</v>
+      </c>
+      <c r="F242" t="s">
         <v>401</v>
       </c>
-      <c r="E242" t="s">
-        <v>164</v>
-      </c>
-      <c r="F242" t="s">
+      <c r="G242" t="s">
         <v>402</v>
-      </c>
-      <c r="G242" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="243" spans="1:7">
@@ -7188,16 +7188,16 @@
         <v>163</v>
       </c>
       <c r="D243" t="s">
+        <v>164</v>
+      </c>
+      <c r="E243" t="s">
+        <v>165</v>
+      </c>
+      <c r="F243" t="s">
         <v>401</v>
       </c>
-      <c r="E243" t="s">
-        <v>164</v>
-      </c>
-      <c r="F243" t="s">
+      <c r="G243" t="s">
         <v>402</v>
-      </c>
-      <c r="G243" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="244" spans="1:7">
@@ -7211,16 +7211,16 @@
         <v>163</v>
       </c>
       <c r="D244" t="s">
+        <v>164</v>
+      </c>
+      <c r="E244" t="s">
+        <v>165</v>
+      </c>
+      <c r="F244" t="s">
         <v>401</v>
       </c>
-      <c r="E244" t="s">
-        <v>164</v>
-      </c>
-      <c r="F244" t="s">
+      <c r="G244" t="s">
         <v>402</v>
-      </c>
-      <c r="G244" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="245" spans="1:7">
@@ -7234,16 +7234,16 @@
         <v>163</v>
       </c>
       <c r="D245" t="s">
+        <v>164</v>
+      </c>
+      <c r="E245" t="s">
+        <v>165</v>
+      </c>
+      <c r="F245" t="s">
         <v>401</v>
       </c>
-      <c r="E245" t="s">
-        <v>164</v>
-      </c>
-      <c r="F245" t="s">
+      <c r="G245" t="s">
         <v>402</v>
-      </c>
-      <c r="G245" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="246" spans="1:7">
@@ -7254,19 +7254,19 @@
         <v>8</v>
       </c>
       <c r="C246" t="s">
+        <v>255</v>
+      </c>
+      <c r="D246" t="s">
         <v>409</v>
       </c>
-      <c r="D246" t="s">
+      <c r="E246" t="s">
+        <v>165</v>
+      </c>
+      <c r="F246" t="s">
+        <v>401</v>
+      </c>
+      <c r="G246" t="s">
         <v>410</v>
-      </c>
-      <c r="E246" t="s">
-        <v>164</v>
-      </c>
-      <c r="F246" t="s">
-        <v>402</v>
-      </c>
-      <c r="G246" t="s">
-        <v>256</v>
       </c>
     </row>
     <row r="247" spans="1:7">
@@ -7279,14 +7279,14 @@
       <c r="C247" t="s">
         <v>95</v>
       </c>
+      <c r="D247" t="s">
+        <v>96</v>
+      </c>
       <c r="E247" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="F247" t="s">
         <v>412</v>
-      </c>
-      <c r="G247" t="s">
-        <v>97</v>
       </c>
     </row>
     <row r="248" spans="1:7">
@@ -7299,14 +7299,14 @@
       <c r="C248" t="s">
         <v>95</v>
       </c>
+      <c r="D248" t="s">
+        <v>96</v>
+      </c>
       <c r="E248" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="F248" t="s">
         <v>412</v>
-      </c>
-      <c r="G248" t="s">
-        <v>97</v>
       </c>
     </row>
     <row r="249" spans="1:7">
@@ -7319,14 +7319,14 @@
       <c r="C249" t="s">
         <v>415</v>
       </c>
+      <c r="D249" t="s">
+        <v>416</v>
+      </c>
       <c r="E249" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="F249" t="s">
         <v>412</v>
-      </c>
-      <c r="G249" t="s">
-        <v>416</v>
       </c>
     </row>
     <row r="250" spans="1:7">
@@ -7339,14 +7339,14 @@
       <c r="C250" t="s">
         <v>95</v>
       </c>
+      <c r="D250" t="s">
+        <v>96</v>
+      </c>
       <c r="E250" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="F250" t="s">
         <v>412</v>
-      </c>
-      <c r="G250" t="s">
-        <v>97</v>
       </c>
     </row>
     <row r="251" spans="1:7">
@@ -7359,14 +7359,14 @@
       <c r="C251" t="s">
         <v>95</v>
       </c>
+      <c r="D251" t="s">
+        <v>96</v>
+      </c>
       <c r="E251" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="F251" t="s">
         <v>412</v>
-      </c>
-      <c r="G251" t="s">
-        <v>97</v>
       </c>
     </row>
     <row r="252" spans="1:7">
@@ -7379,14 +7379,14 @@
       <c r="C252" t="s">
         <v>95</v>
       </c>
+      <c r="D252" t="s">
+        <v>96</v>
+      </c>
       <c r="E252" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="F252" t="s">
         <v>412</v>
-      </c>
-      <c r="G252" t="s">
-        <v>97</v>
       </c>
     </row>
     <row r="253" spans="1:7">
@@ -7399,13 +7399,13 @@
       <c r="C253" t="s">
         <v>421</v>
       </c>
+      <c r="D253" t="s">
+        <v>422</v>
+      </c>
       <c r="E253" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="F253" t="s">
-        <v>422</v>
-      </c>
-      <c r="G253" t="s">
         <v>423</v>
       </c>
     </row>
@@ -7419,14 +7419,14 @@
       <c r="C254" t="s">
         <v>219</v>
       </c>
+      <c r="D254" t="s">
+        <v>220</v>
+      </c>
       <c r="E254" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="F254" t="s">
-        <v>422</v>
-      </c>
-      <c r="G254" t="s">
-        <v>220</v>
+        <v>423</v>
       </c>
     </row>
     <row r="255" spans="1:7">
@@ -7439,14 +7439,14 @@
       <c r="C255" t="s">
         <v>426</v>
       </c>
+      <c r="D255" t="s">
+        <v>427</v>
+      </c>
       <c r="E255" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="F255" t="s">
-        <v>422</v>
-      </c>
-      <c r="G255" t="s">
-        <v>427</v>
+        <v>423</v>
       </c>
     </row>
     <row r="256" spans="1:7">
@@ -7459,17 +7459,17 @@
       <c r="C256" t="s">
         <v>426</v>
       </c>
+      <c r="D256" t="s">
+        <v>427</v>
+      </c>
       <c r="E256" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="F256" t="s">
-        <v>422</v>
-      </c>
-      <c r="G256" t="s">
-        <v>427</v>
-      </c>
-    </row>
-    <row r="257" spans="1:7">
+        <v>423</v>
+      </c>
+    </row>
+    <row r="257" spans="1:6">
       <c r="A257" t="s">
         <v>429</v>
       </c>
@@ -7479,17 +7479,17 @@
       <c r="C257" t="s">
         <v>426</v>
       </c>
+      <c r="D257" t="s">
+        <v>427</v>
+      </c>
       <c r="E257" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="F257" t="s">
-        <v>422</v>
-      </c>
-      <c r="G257" t="s">
-        <v>427</v>
-      </c>
-    </row>
-    <row r="258" spans="1:7">
+        <v>423</v>
+      </c>
+    </row>
+    <row r="258" spans="1:6">
       <c r="A258" t="s">
         <v>430</v>
       </c>
@@ -7499,17 +7499,17 @@
       <c r="C258" t="s">
         <v>325</v>
       </c>
+      <c r="D258" t="s">
+        <v>326</v>
+      </c>
       <c r="E258" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="F258" t="s">
-        <v>422</v>
-      </c>
-      <c r="G258" t="s">
-        <v>328</v>
-      </c>
-    </row>
-    <row r="259" spans="1:7">
+        <v>423</v>
+      </c>
+    </row>
+    <row r="259" spans="1:6">
       <c r="A259" t="s">
         <v>431</v>
       </c>
@@ -7519,17 +7519,17 @@
       <c r="C259" t="s">
         <v>426</v>
       </c>
+      <c r="D259" t="s">
+        <v>427</v>
+      </c>
       <c r="E259" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="F259" t="s">
-        <v>422</v>
-      </c>
-      <c r="G259" t="s">
-        <v>427</v>
-      </c>
-    </row>
-    <row r="260" spans="1:7">
+        <v>423</v>
+      </c>
+    </row>
+    <row r="260" spans="1:6">
       <c r="A260" t="s">
         <v>432</v>
       </c>
@@ -7539,17 +7539,17 @@
       <c r="C260" t="s">
         <v>163</v>
       </c>
+      <c r="D260" t="s">
+        <v>164</v>
+      </c>
       <c r="E260" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="F260" t="s">
-        <v>422</v>
-      </c>
-      <c r="G260" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="261" spans="1:7">
+        <v>423</v>
+      </c>
+    </row>
+    <row r="261" spans="1:6">
       <c r="A261" t="s">
         <v>433</v>
       </c>
@@ -7559,17 +7559,17 @@
       <c r="C261" t="s">
         <v>434</v>
       </c>
+      <c r="D261" t="s">
+        <v>435</v>
+      </c>
       <c r="E261" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="F261" t="s">
-        <v>422</v>
-      </c>
-      <c r="G261" t="s">
-        <v>435</v>
-      </c>
-    </row>
-    <row r="262" spans="1:7">
+        <v>423</v>
+      </c>
+    </row>
+    <row r="262" spans="1:6">
       <c r="A262" t="s">
         <v>436</v>
       </c>
@@ -7579,17 +7579,17 @@
       <c r="C262" t="s">
         <v>163</v>
       </c>
+      <c r="D262" t="s">
+        <v>164</v>
+      </c>
       <c r="E262" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="F262" t="s">
-        <v>422</v>
-      </c>
-      <c r="G262" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="263" spans="1:7">
+        <v>423</v>
+      </c>
+    </row>
+    <row r="263" spans="1:6">
       <c r="A263" t="s">
         <v>437</v>
       </c>
@@ -7599,17 +7599,17 @@
       <c r="C263" t="s">
         <v>438</v>
       </c>
+      <c r="D263" t="s">
+        <v>439</v>
+      </c>
       <c r="E263" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="F263" t="s">
-        <v>422</v>
-      </c>
-      <c r="G263" t="s">
-        <v>439</v>
-      </c>
-    </row>
-    <row r="264" spans="1:7">
+        <v>423</v>
+      </c>
+    </row>
+    <row r="264" spans="1:6">
       <c r="A264" t="s">
         <v>440</v>
       </c>
@@ -7619,17 +7619,17 @@
       <c r="C264" t="s">
         <v>31</v>
       </c>
+      <c r="D264" t="s">
+        <v>32</v>
+      </c>
       <c r="E264" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F264" t="s">
-        <v>422</v>
-      </c>
-      <c r="G264" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="265" spans="1:7">
+        <v>423</v>
+      </c>
+    </row>
+    <row r="265" spans="1:6">
       <c r="A265" t="s">
         <v>441</v>
       </c>
@@ -7639,17 +7639,17 @@
       <c r="C265" t="s">
         <v>9</v>
       </c>
+      <c r="D265" t="s">
+        <v>10</v>
+      </c>
       <c r="E265" t="s">
         <v>11</v>
       </c>
       <c r="F265" t="s">
-        <v>422</v>
-      </c>
-      <c r="G265" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="266" spans="1:7">
+        <v>423</v>
+      </c>
+    </row>
+    <row r="266" spans="1:6">
       <c r="A266" t="s">
         <v>442</v>
       </c>
@@ -7659,17 +7659,17 @@
       <c r="C266" t="s">
         <v>443</v>
       </c>
+      <c r="D266" t="s">
+        <v>444</v>
+      </c>
       <c r="E266" t="s">
         <v>114</v>
       </c>
       <c r="F266" t="s">
-        <v>422</v>
-      </c>
-      <c r="G266" t="s">
-        <v>444</v>
-      </c>
-    </row>
-    <row r="267" spans="1:7">
+        <v>423</v>
+      </c>
+    </row>
+    <row r="267" spans="1:6">
       <c r="A267" t="s">
         <v>445</v>
       </c>
@@ -7679,17 +7679,17 @@
       <c r="C267" t="s">
         <v>118</v>
       </c>
+      <c r="D267" t="s">
+        <v>119</v>
+      </c>
       <c r="E267" t="s">
         <v>114</v>
       </c>
       <c r="F267" t="s">
         <v>446</v>
       </c>
-      <c r="G267" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="268" spans="1:7">
+    </row>
+    <row r="268" spans="1:6">
       <c r="A268" t="s">
         <v>447</v>
       </c>
@@ -7699,17 +7699,17 @@
       <c r="C268" t="s">
         <v>202</v>
       </c>
+      <c r="D268" t="s">
+        <v>203</v>
+      </c>
       <c r="E268" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="F268" t="s">
         <v>448</v>
       </c>
-      <c r="G268" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="269" spans="1:7">
+    </row>
+    <row r="269" spans="1:6">
       <c r="A269" t="s">
         <v>449</v>
       </c>
@@ -7719,17 +7719,17 @@
       <c r="C269" t="s">
         <v>118</v>
       </c>
+      <c r="D269" t="s">
+        <v>119</v>
+      </c>
       <c r="E269" t="s">
         <v>114</v>
       </c>
       <c r="F269" t="s">
         <v>450</v>
       </c>
-      <c r="G269" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="270" spans="1:7">
+    </row>
+    <row r="270" spans="1:6">
       <c r="A270" t="s">
         <v>451</v>
       </c>
@@ -7739,17 +7739,17 @@
       <c r="C270" t="s">
         <v>118</v>
       </c>
+      <c r="D270" t="s">
+        <v>119</v>
+      </c>
       <c r="E270" t="s">
         <v>114</v>
       </c>
       <c r="F270" t="s">
         <v>450</v>
       </c>
-      <c r="G270" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="271" spans="1:7">
+    </row>
+    <row r="271" spans="1:6">
       <c r="A271" t="s">
         <v>452</v>
       </c>
@@ -7759,17 +7759,17 @@
       <c r="C271" t="s">
         <v>453</v>
       </c>
+      <c r="D271" t="s">
+        <v>454</v>
+      </c>
       <c r="E271" t="s">
         <v>114</v>
       </c>
       <c r="F271" t="s">
-        <v>454</v>
-      </c>
-      <c r="G271" t="s">
         <v>455</v>
       </c>
     </row>
-    <row r="272" spans="1:7">
+    <row r="272" spans="1:6">
       <c r="A272" t="s">
         <v>456</v>
       </c>
@@ -7779,17 +7779,17 @@
       <c r="C272" t="s">
         <v>453</v>
       </c>
+      <c r="D272" t="s">
+        <v>454</v>
+      </c>
       <c r="E272" t="s">
         <v>114</v>
       </c>
       <c r="F272" t="s">
-        <v>454</v>
-      </c>
-      <c r="G272" t="s">
         <v>455</v>
       </c>
     </row>
-    <row r="273" spans="1:7">
+    <row r="273" spans="1:6">
       <c r="A273" t="s">
         <v>457</v>
       </c>
@@ -7799,17 +7799,17 @@
       <c r="C273" t="s">
         <v>453</v>
       </c>
+      <c r="D273" t="s">
+        <v>454</v>
+      </c>
       <c r="E273" t="s">
         <v>114</v>
       </c>
       <c r="F273" t="s">
-        <v>454</v>
-      </c>
-      <c r="G273" t="s">
         <v>455</v>
       </c>
     </row>
-    <row r="274" spans="1:7">
+    <row r="274" spans="1:6">
       <c r="A274" t="s">
         <v>458</v>
       </c>
@@ -7819,17 +7819,17 @@
       <c r="C274" t="s">
         <v>453</v>
       </c>
+      <c r="D274" t="s">
+        <v>454</v>
+      </c>
       <c r="E274" t="s">
         <v>114</v>
       </c>
       <c r="F274" t="s">
-        <v>454</v>
-      </c>
-      <c r="G274" t="s">
         <v>455</v>
       </c>
     </row>
-    <row r="275" spans="1:7">
+    <row r="275" spans="1:6">
       <c r="A275" t="s">
         <v>459</v>
       </c>
@@ -7839,17 +7839,17 @@
       <c r="C275" t="s">
         <v>453</v>
       </c>
+      <c r="D275" t="s">
+        <v>454</v>
+      </c>
       <c r="E275" t="s">
         <v>114</v>
       </c>
       <c r="F275" t="s">
-        <v>454</v>
-      </c>
-      <c r="G275" t="s">
         <v>455</v>
       </c>
     </row>
-    <row r="276" spans="1:7">
+    <row r="276" spans="1:6">
       <c r="A276" t="s">
         <v>460</v>
       </c>
@@ -7859,17 +7859,17 @@
       <c r="C276" t="s">
         <v>453</v>
       </c>
+      <c r="D276" t="s">
+        <v>454</v>
+      </c>
       <c r="E276" t="s">
         <v>114</v>
       </c>
       <c r="F276" t="s">
-        <v>454</v>
-      </c>
-      <c r="G276" t="s">
         <v>455</v>
       </c>
     </row>
-    <row r="277" spans="1:7">
+    <row r="277" spans="1:6">
       <c r="A277" t="s">
         <v>461</v>
       </c>
@@ -7879,17 +7879,17 @@
       <c r="C277" t="s">
         <v>453</v>
       </c>
+      <c r="D277" t="s">
+        <v>454</v>
+      </c>
       <c r="E277" t="s">
         <v>114</v>
       </c>
       <c r="F277" t="s">
-        <v>454</v>
-      </c>
-      <c r="G277" t="s">
         <v>455</v>
       </c>
     </row>
-    <row r="278" spans="1:7">
+    <row r="278" spans="1:6">
       <c r="A278" t="s">
         <v>462</v>
       </c>
@@ -7899,17 +7899,17 @@
       <c r="C278" t="s">
         <v>202</v>
       </c>
+      <c r="D278" t="s">
+        <v>203</v>
+      </c>
       <c r="E278" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="F278" t="s">
         <v>463</v>
       </c>
-      <c r="G278" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="279" spans="1:7">
+    </row>
+    <row r="279" spans="1:6">
       <c r="A279" t="s">
         <v>464</v>
       </c>
@@ -7919,17 +7919,17 @@
       <c r="C279" t="s">
         <v>51</v>
       </c>
+      <c r="D279" t="s">
+        <v>52</v>
+      </c>
       <c r="E279" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F279" t="s">
         <v>463</v>
       </c>
-      <c r="G279" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="280" spans="1:7">
+    </row>
+    <row r="280" spans="1:6">
       <c r="A280" t="s">
         <v>465</v>
       </c>
@@ -7939,17 +7939,17 @@
       <c r="C280" t="s">
         <v>9</v>
       </c>
+      <c r="D280" t="s">
+        <v>10</v>
+      </c>
       <c r="E280" t="s">
         <v>11</v>
       </c>
       <c r="F280" t="s">
         <v>463</v>
       </c>
-      <c r="G280" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="281" spans="1:7">
+    </row>
+    <row r="281" spans="1:6">
       <c r="A281" t="s">
         <v>466</v>
       </c>
@@ -7959,17 +7959,17 @@
       <c r="C281" t="s">
         <v>170</v>
       </c>
+      <c r="D281" t="s">
+        <v>171</v>
+      </c>
       <c r="E281" t="s">
         <v>114</v>
       </c>
       <c r="F281" t="s">
         <v>463</v>
       </c>
-      <c r="G281" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="282" spans="1:7">
+    </row>
+    <row r="282" spans="1:6">
       <c r="A282" t="s">
         <v>467</v>
       </c>
@@ -7979,17 +7979,17 @@
       <c r="C282" t="s">
         <v>124</v>
       </c>
+      <c r="D282" t="s">
+        <v>125</v>
+      </c>
       <c r="E282" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="F282" t="s">
         <v>463</v>
       </c>
-      <c r="G282" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="283" spans="1:7">
+    </row>
+    <row r="283" spans="1:6">
       <c r="A283" t="s">
         <v>468</v>
       </c>
@@ -7997,19 +7997,19 @@
         <v>8</v>
       </c>
       <c r="C283" t="s">
+        <v>363</v>
+      </c>
+      <c r="D283" t="s">
         <v>398</v>
       </c>
       <c r="E283" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="F283" t="s">
         <v>469</v>
       </c>
-      <c r="G283" t="s">
-        <v>366</v>
-      </c>
-    </row>
-    <row r="284" spans="1:7">
+    </row>
+    <row r="284" spans="1:6">
       <c r="A284" t="s">
         <v>470</v>
       </c>
@@ -8019,17 +8019,17 @@
       <c r="C284" t="s">
         <v>124</v>
       </c>
+      <c r="D284" t="s">
+        <v>125</v>
+      </c>
       <c r="E284" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="F284" t="s">
         <v>471</v>
       </c>
-      <c r="G284" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="285" spans="1:7">
+    </row>
+    <row r="285" spans="1:6">
       <c r="A285" t="s">
         <v>472</v>
       </c>
@@ -8039,17 +8039,17 @@
       <c r="C285" t="s">
         <v>170</v>
       </c>
+      <c r="D285" t="s">
+        <v>171</v>
+      </c>
       <c r="E285" t="s">
         <v>114</v>
       </c>
       <c r="F285" t="s">
         <v>473</v>
       </c>
-      <c r="G285" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="286" spans="1:7">
+    </row>
+    <row r="286" spans="1:6">
       <c r="A286" t="s">
         <v>474</v>
       </c>
@@ -8059,17 +8059,17 @@
       <c r="C286" t="s">
         <v>438</v>
       </c>
+      <c r="D286" t="s">
+        <v>439</v>
+      </c>
       <c r="E286" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="F286" t="s">
         <v>475</v>
       </c>
-      <c r="G286" t="s">
-        <v>439</v>
-      </c>
-    </row>
-    <row r="287" spans="1:7">
+    </row>
+    <row r="287" spans="1:6">
       <c r="A287" t="s">
         <v>476</v>
       </c>
@@ -8079,17 +8079,17 @@
       <c r="C287" t="s">
         <v>438</v>
       </c>
+      <c r="D287" t="s">
+        <v>439</v>
+      </c>
       <c r="E287" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="F287" t="s">
         <v>475</v>
       </c>
-      <c r="G287" t="s">
-        <v>439</v>
-      </c>
-    </row>
-    <row r="288" spans="1:7">
+    </row>
+    <row r="288" spans="1:6">
       <c r="A288" t="s">
         <v>477</v>
       </c>
@@ -8099,17 +8099,17 @@
       <c r="C288" t="s">
         <v>41</v>
       </c>
+      <c r="D288" t="s">
+        <v>42</v>
+      </c>
       <c r="E288" t="s">
         <v>11</v>
       </c>
       <c r="F288" t="s">
         <v>475</v>
       </c>
-      <c r="G288" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="289" spans="1:7">
+    </row>
+    <row r="289" spans="1:6">
       <c r="A289" t="s">
         <v>478</v>
       </c>
@@ -8119,17 +8119,17 @@
       <c r="C289" t="s">
         <v>31</v>
       </c>
+      <c r="D289" t="s">
+        <v>32</v>
+      </c>
       <c r="E289" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F289" t="s">
         <v>475</v>
       </c>
-      <c r="G289" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="290" spans="1:7">
+    </row>
+    <row r="290" spans="1:6">
       <c r="A290" t="s">
         <v>479</v>
       </c>
@@ -8139,17 +8139,17 @@
       <c r="C290" t="s">
         <v>31</v>
       </c>
+      <c r="D290" t="s">
+        <v>32</v>
+      </c>
       <c r="E290" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F290" t="s">
         <v>475</v>
       </c>
-      <c r="G290" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="291" spans="1:7">
+    </row>
+    <row r="291" spans="1:6">
       <c r="A291" t="s">
         <v>480</v>
       </c>
@@ -8159,17 +8159,17 @@
       <c r="C291" t="s">
         <v>170</v>
       </c>
+      <c r="D291" t="s">
+        <v>171</v>
+      </c>
       <c r="E291" t="s">
         <v>114</v>
       </c>
       <c r="F291" t="s">
         <v>475</v>
       </c>
-      <c r="G291" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="292" spans="1:7">
+    </row>
+    <row r="292" spans="1:6">
       <c r="A292" t="s">
         <v>481</v>
       </c>
@@ -8179,17 +8179,17 @@
       <c r="C292" t="s">
         <v>170</v>
       </c>
+      <c r="D292" t="s">
+        <v>171</v>
+      </c>
       <c r="E292" t="s">
         <v>114</v>
       </c>
       <c r="F292" t="s">
         <v>475</v>
       </c>
-      <c r="G292" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="293" spans="1:7">
+    </row>
+    <row r="293" spans="1:6">
       <c r="A293" t="s">
         <v>482</v>
       </c>
@@ -8199,17 +8199,17 @@
       <c r="C293" t="s">
         <v>170</v>
       </c>
+      <c r="D293" t="s">
+        <v>171</v>
+      </c>
       <c r="E293" t="s">
         <v>114</v>
       </c>
       <c r="F293" t="s">
         <v>475</v>
       </c>
-      <c r="G293" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="294" spans="1:7">
+    </row>
+    <row r="294" spans="1:6">
       <c r="A294" t="s">
         <v>483</v>
       </c>
@@ -8219,17 +8219,17 @@
       <c r="C294" t="s">
         <v>170</v>
       </c>
+      <c r="D294" t="s">
+        <v>171</v>
+      </c>
       <c r="E294" t="s">
         <v>114</v>
       </c>
       <c r="F294" t="s">
         <v>475</v>
       </c>
-      <c r="G294" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="295" spans="1:7">
+    </row>
+    <row r="295" spans="1:6">
       <c r="A295" t="s">
         <v>484</v>
       </c>
@@ -8239,17 +8239,17 @@
       <c r="C295" t="s">
         <v>170</v>
       </c>
+      <c r="D295" t="s">
+        <v>171</v>
+      </c>
       <c r="E295" t="s">
         <v>114</v>
       </c>
       <c r="F295" t="s">
         <v>485</v>
       </c>
-      <c r="G295" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="296" spans="1:7">
+    </row>
+    <row r="296" spans="1:6">
       <c r="A296" t="s">
         <v>486</v>
       </c>
@@ -8259,14 +8259,14 @@
       <c r="C296" t="s">
         <v>170</v>
       </c>
+      <c r="D296" t="s">
+        <v>171</v>
+      </c>
       <c r="E296" t="s">
         <v>114</v>
       </c>
       <c r="F296" t="s">
         <v>485</v>
-      </c>
-      <c r="G296" t="s">
-        <v>171</v>
       </c>
     </row>
   </sheetData>

--- a/api/2/xlsx/fr/SectorCOFOG.xlsx
+++ b/api/2/xlsx/fr/SectorCOFOG.xlsx
@@ -22,18 +22,18 @@
     <t>status</t>
   </si>
   <si>
+    <t>codeforiati:group-code</t>
+  </si>
+  <si>
+    <t>codeforiati:cofog-class</t>
+  </si>
+  <si>
     <t>codeforiati:cofog-group</t>
   </si>
   <si>
-    <t>codeforiati:cofog-class</t>
-  </si>
-  <si>
     <t>codeforiati:cofog-division</t>
   </si>
   <si>
-    <t>codeforiati:group-code</t>
-  </si>
-  <si>
     <t>codeforiati:category-code</t>
   </si>
   <si>
@@ -43,51 +43,51 @@
     <t>active</t>
   </si>
   <si>
+    <t>110</t>
+  </si>
+  <si>
+    <t>09.8.0 - Education n.e.c. (CS)</t>
+  </si>
+  <si>
     <t>09.8 - Education n.e.c.</t>
   </si>
   <si>
-    <t>09.8.0 - Education n.e.c. (CS)</t>
-  </si>
-  <si>
     <t>09 - Education</t>
   </si>
   <si>
-    <t>110</t>
-  </si>
-  <si>
     <t>111</t>
   </si>
   <si>
     <t>11120</t>
   </si>
   <si>
+    <t>09.6.0 - Subsidiary services to education (IS)</t>
+  </si>
+  <si>
     <t>09.6 - Subsidiary services to education</t>
   </si>
   <si>
-    <t>09.6.0 - Subsidiary services to education (IS)</t>
-  </si>
-  <si>
     <t>11130</t>
   </si>
   <si>
     <t>11182</t>
   </si>
   <si>
+    <t>09.7.0 - R&amp;D Education (CS)</t>
+  </si>
+  <si>
     <t>09.7 - R&amp;D Education</t>
   </si>
   <si>
-    <t>09.7.0 - R&amp;D Education (CS)</t>
-  </si>
-  <si>
     <t>11220</t>
   </si>
   <si>
+    <t>09.1.2 - Primary education (IS)</t>
+  </si>
+  <si>
     <t>09.1 - Pre‐primary and primary education</t>
   </si>
   <si>
-    <t>09.1.2 - Primary education (IS)</t>
-  </si>
-  <si>
     <t>112</t>
   </si>
   <si>
@@ -109,24 +109,24 @@
     <t>11250</t>
   </si>
   <si>
+    <t>07.4.0 - Public health services (IS)</t>
+  </si>
+  <si>
     <t>07.4 - Public health services</t>
   </si>
   <si>
-    <t>07.4.0 - Public health services (IS)</t>
-  </si>
-  <si>
     <t>07 - Health</t>
   </si>
   <si>
     <t>11260</t>
   </si>
   <si>
+    <t>09.2.1 - Lower‐secondary education (IS)</t>
+  </si>
+  <si>
     <t>09.2 - Secondary education</t>
   </si>
   <si>
-    <t>09.2.1 - Lower‐secondary education (IS)</t>
-  </si>
-  <si>
     <t>11320</t>
   </si>
   <si>
@@ -139,45 +139,45 @@
     <t>11330</t>
   </si>
   <si>
+    <t>09.5.0 - Education not definable by level (IS)</t>
+  </si>
+  <si>
     <t>09.5 - Education not definable by level</t>
   </si>
   <si>
-    <t>09.5.0 - Education not definable by level (IS)</t>
-  </si>
-  <si>
     <t>11420</t>
   </si>
   <si>
+    <t>09.4.1 - First stage of tertiary education (IS)</t>
+  </si>
+  <si>
     <t>09.4 - Tertiary education</t>
   </si>
   <si>
-    <t>09.4.1 - First stage of tertiary education (IS)</t>
-  </si>
-  <si>
     <t>114</t>
   </si>
   <si>
     <t>11430</t>
   </si>
   <si>
+    <t>09.3.0 - Post‐secondary non‐tertiary education (IS)</t>
+  </si>
+  <si>
     <t>09.3 - Post‐secondary non‐tertiary education</t>
   </si>
   <si>
-    <t>09.3.0 - Post‐secondary non‐tertiary education (IS)</t>
-  </si>
-  <si>
     <t>12110</t>
   </si>
   <si>
+    <t>120</t>
+  </si>
+  <si>
+    <t>07.6.0 - Health n.e.c. (CS)</t>
+  </si>
+  <si>
     <t>07.6 - Health n.e.c.</t>
   </si>
   <si>
-    <t>07.6.0 - Health n.e.c. (CS)</t>
-  </si>
-  <si>
-    <t>120</t>
-  </si>
-  <si>
     <t>121</t>
   </si>
   <si>
@@ -187,21 +187,21 @@
     <t>12182</t>
   </si>
   <si>
+    <t>07.5.0 - R&amp;D Health (CS)</t>
+  </si>
+  <si>
     <t>07.5 - R&amp;D Health</t>
   </si>
   <si>
-    <t>07.5.0 - R&amp;D Health (CS)</t>
-  </si>
-  <si>
     <t>12191</t>
   </si>
   <si>
+    <t>07.2.1 - General medical services (IS)</t>
+  </si>
+  <si>
     <t>07.2 - Outpatient services</t>
   </si>
   <si>
-    <t>07.2.1 - General medical services (IS)</t>
-  </si>
-  <si>
     <t>12196</t>
   </si>
   <si>
@@ -214,12 +214,12 @@
     <t>12230</t>
   </si>
   <si>
+    <t>07.3.1 - General hospital services (IS)</t>
+  </si>
+  <si>
     <t>07.3 - Hospital services</t>
   </si>
   <si>
-    <t>07.3.1 - General hospital services (IS)</t>
-  </si>
-  <si>
     <t>12240</t>
   </si>
   <si>
@@ -286,27 +286,27 @@
     <t>14010</t>
   </si>
   <si>
+    <t>140</t>
+  </si>
+  <si>
+    <t>06.3.0 - Water supply (CS)</t>
+  </si>
+  <si>
     <t>06.3 - Water supply</t>
   </si>
   <si>
-    <t>06.3.0 - Water supply (CS)</t>
-  </si>
-  <si>
     <t>06 - Housing and community amenities</t>
   </si>
   <si>
-    <t>140</t>
-  </si>
-  <si>
     <t>14015</t>
   </si>
   <si>
+    <t>05.6.0 - Environmental protection n.e.c. (CS)</t>
+  </si>
+  <si>
     <t>05.6 - Environmental protection n.e.c.</t>
   </si>
   <si>
-    <t>05.6.0 - Environmental protection n.e.c. (CS)</t>
-  </si>
-  <si>
     <t>05 - Environmental protection</t>
   </si>
   <si>
@@ -319,12 +319,12 @@
     <t>14022</t>
   </si>
   <si>
+    <t>05.2.0 - Waste water management (CS)</t>
+  </si>
+  <si>
     <t>05.2 - Waste water management</t>
   </si>
   <si>
-    <t>05.2.0 - Waste water management (CS)</t>
-  </si>
-  <si>
     <t>14030</t>
   </si>
   <si>
@@ -340,60 +340,60 @@
     <t>14050</t>
   </si>
   <si>
+    <t>05.1.0 - Waste management (CS)</t>
+  </si>
+  <si>
     <t>05.1 - Waste management</t>
   </si>
   <si>
-    <t>05.1.0 - Waste management (CS)</t>
-  </si>
-  <si>
     <t>14081</t>
   </si>
   <si>
     <t>15110</t>
   </si>
   <si>
+    <t>150</t>
+  </si>
+  <si>
+    <t>01.3.1 - General personnel services (CS)</t>
+  </si>
+  <si>
     <t>01.3 - General services</t>
   </si>
   <si>
-    <t>01.3.1 - General personnel services (CS)</t>
-  </si>
-  <si>
     <t>01 - General public services</t>
   </si>
   <si>
-    <t>150</t>
-  </si>
-  <si>
     <t>151</t>
   </si>
   <si>
     <t>15111</t>
   </si>
   <si>
+    <t>01.1.2 - Financial and fiscal affairs (CS)</t>
+  </si>
+  <si>
     <t>01.1 - Executive and legislative organs, financial and fiscal affairs, external affairs</t>
   </si>
   <si>
-    <t>01.1.2 - Financial and fiscal affairs (CS)</t>
-  </si>
-  <si>
     <t>15112</t>
   </si>
   <si>
+    <t>01.8.0 - Transfers of a general character between different levels of government (CS)</t>
+  </si>
+  <si>
     <t>01.8 - Transfers of a general character between different levels of government</t>
   </si>
   <si>
-    <t>01.8.0 - Transfers of a general character between different levels of government (CS)</t>
-  </si>
-  <si>
     <t>15113</t>
   </si>
   <si>
+    <t>03.6.0 - Public order and safety n.e.c. (CS)</t>
+  </si>
+  <si>
     <t>03.6 - Public order and safety n.e.c.</t>
   </si>
   <si>
-    <t>03.6.0 - Public order and safety n.e.c. (CS)</t>
-  </si>
-  <si>
     <t>03 - Public order and safety</t>
   </si>
   <si>
@@ -424,12 +424,12 @@
     <t>15123</t>
   </si>
   <si>
+    <t>01.2.2 - Economic aid routed through international organizations (CS)</t>
+  </si>
+  <si>
     <t>01.2 - Foreign economic aid</t>
   </si>
   <si>
-    <t>01.2.2 - Economic aid routed through international organizations (CS)</t>
-  </si>
-  <si>
     <t>15124</t>
   </si>
   <si>
@@ -460,30 +460,30 @@
     <t>15131</t>
   </si>
   <si>
+    <t>03.3.0 - Law courts (CS)</t>
+  </si>
+  <si>
     <t>03.3 - Law courts</t>
   </si>
   <si>
-    <t>03.3.0 - Law courts (CS)</t>
-  </si>
-  <si>
     <t>15132</t>
   </si>
   <si>
+    <t>03.1.0 - Police services (CS)</t>
+  </si>
+  <si>
     <t>03.1 - Police services</t>
   </si>
   <si>
-    <t>03.1.0 - Police services (CS)</t>
-  </si>
-  <si>
     <t>15133</t>
   </si>
   <si>
+    <t>03.2.0 - Fire‐protection services (CS)</t>
+  </si>
+  <si>
     <t>03.2 - Fire‐protection services</t>
   </si>
   <si>
-    <t>03.2.0 - Fire‐protection services (CS)</t>
-  </si>
-  <si>
     <t>15134</t>
   </si>
   <si>
@@ -496,21 +496,21 @@
     <t>15137</t>
   </si>
   <si>
+    <t>03.4.0 - Prisons (CS)</t>
+  </si>
+  <si>
     <t>03.4 - Prisons</t>
   </si>
   <si>
-    <t>03.4.0 - Prisons (CS)</t>
-  </si>
-  <si>
     <t>15142</t>
   </si>
   <si>
+    <t>04.1.1 - General economic and commercial affairs (CS)</t>
+  </si>
+  <si>
     <t>04.1 - General economic, commercial and labour affairs</t>
   </si>
   <si>
-    <t>04.1.1 - General economic and commercial affairs (CS)</t>
-  </si>
-  <si>
     <t>04 - Economic affairs</t>
   </si>
   <si>
@@ -526,12 +526,12 @@
     <t>15151</t>
   </si>
   <si>
+    <t>01.6.0 - General public services n.e.c. (CS)</t>
+  </si>
+  <si>
     <t>01.6 - General public services n.e.c.</t>
   </si>
   <si>
-    <t>01.6.0 - General public services n.e.c. (CS)</t>
-  </si>
-  <si>
     <t>15152</t>
   </si>
   <si>
@@ -541,12 +541,12 @@
     <t>15153</t>
   </si>
   <si>
+    <t>04.6.0 - Communication (CS)</t>
+  </si>
+  <si>
     <t>04.6 - Communication</t>
   </si>
   <si>
-    <t>04.6.0 - Communication (CS)</t>
-  </si>
-  <si>
     <t>15154</t>
   </si>
   <si>
@@ -562,12 +562,12 @@
     <t>15170</t>
   </si>
   <si>
+    <t>10.7.0 - Social exclusion n.e.c. (IS)</t>
+  </si>
+  <si>
     <t>10.7 - Social exclusion n.e.c.</t>
   </si>
   <si>
-    <t>10.7.0 - Social exclusion n.e.c. (IS)</t>
-  </si>
-  <si>
     <t>10 - Social protection</t>
   </si>
   <si>
@@ -583,12 +583,12 @@
     <t>15196</t>
   </si>
   <si>
+    <t>01.5.0 - R&amp;D General public services (CS)</t>
+  </si>
+  <si>
     <t>01.5 - R&amp;D General public services</t>
   </si>
   <si>
-    <t>01.5.0 - R&amp;D General public services (CS)</t>
-  </si>
-  <si>
     <t>15210</t>
   </si>
   <si>
@@ -601,12 +601,12 @@
     <t>15230</t>
   </si>
   <si>
+    <t>02.3.0 - Foreign military aid (CS)</t>
+  </si>
+  <si>
     <t>02.3 - Foreign military aid</t>
   </si>
   <si>
-    <t>02.3.0 - Foreign military aid (CS)</t>
-  </si>
-  <si>
     <t>02 - Defence</t>
   </si>
   <si>
@@ -622,15 +622,15 @@
     <t>16010</t>
   </si>
   <si>
+    <t>160</t>
+  </si>
+  <si>
+    <t>10.9.0 - Social protection n.e.c. (CS)</t>
+  </si>
+  <si>
     <t>10.9 - Social protection n.e.c.</t>
   </si>
   <si>
-    <t>10.9.0 - Social protection n.e.c. (CS)</t>
-  </si>
-  <si>
-    <t>160</t>
-  </si>
-  <si>
     <t>16011</t>
   </si>
   <si>
@@ -640,12 +640,12 @@
     <t>16013</t>
   </si>
   <si>
+    <t>10.2.0 - Old age (IS)</t>
+  </si>
+  <si>
     <t>10.2 - Old age</t>
   </si>
   <si>
-    <t>10.2.0 - Old age (IS)</t>
-  </si>
-  <si>
     <t>16014</t>
   </si>
   <si>
@@ -655,42 +655,42 @@
     <t>16020</t>
   </si>
   <si>
+    <t>10.5.0 - Unemployment (IS)</t>
+  </si>
+  <si>
     <t>10.5 - Unemployment</t>
   </si>
   <si>
-    <t>10.5.0 - Unemployment (IS)</t>
-  </si>
-  <si>
     <t>16030</t>
   </si>
   <si>
+    <t>06.6.0 - Housing and community amenities n.e.c. (CS)</t>
+  </si>
+  <si>
     <t>06.6 - Housing and community amenities n.e.c.</t>
   </si>
   <si>
-    <t>06.6.0 - Housing and community amenities n.e.c. (CS)</t>
-  </si>
-  <si>
     <t>16040</t>
   </si>
   <si>
+    <t>06.1.0 - Housing development (CS)</t>
+  </si>
+  <si>
     <t>06.1 - Housing development</t>
   </si>
   <si>
-    <t>06.1.0 - Housing development (CS)</t>
-  </si>
-  <si>
     <t>16050</t>
   </si>
   <si>
     <t>16061</t>
   </si>
   <si>
+    <t>08.2.0 - Cultural services (IS)</t>
+  </si>
+  <si>
     <t>08.2 - Cultural services</t>
   </si>
   <si>
-    <t>08.2.0 - Cultural services (IS)</t>
-  </si>
-  <si>
     <t>08 - Recreation, culture and religion</t>
   </si>
   <si>
@@ -706,12 +706,12 @@
     <t>16065</t>
   </si>
   <si>
+    <t>08.1.0 - Recreational and sporting services (IS)</t>
+  </si>
+  <si>
     <t>08.1 - Recreational and sporting services</t>
   </si>
   <si>
-    <t>08.1.0 - Recreational and sporting services (IS)</t>
-  </si>
-  <si>
     <t>16066</t>
   </si>
   <si>
@@ -742,12 +742,12 @@
     <t>21020</t>
   </si>
   <si>
+    <t>04.5.1 - Road transport (CS)</t>
+  </si>
+  <si>
     <t>04.5 - Transport</t>
   </si>
   <si>
-    <t>04.5.1 - Road transport (CS)</t>
-  </si>
-  <si>
     <t>21021</t>
   </si>
   <si>
@@ -781,12 +781,12 @@
     <t>21061</t>
   </si>
   <si>
+    <t>04.7.1 - Distributive trades, storage and warehousing (CS)</t>
+  </si>
+  <si>
     <t>04.7 - Other industries</t>
   </si>
   <si>
-    <t>04.7.1 - Distributive trades, storage and warehousing (CS)</t>
-  </si>
-  <si>
     <t>21081</t>
   </si>
   <si>
@@ -811,27 +811,27 @@
     <t>22030</t>
   </si>
   <si>
+    <t>08.3.0 - Broadcasting and publishing services (CS)</t>
+  </si>
+  <si>
     <t>08.3 - Broadcasting and publishing services</t>
   </si>
   <si>
-    <t>08.3.0 - Broadcasting and publishing services (CS)</t>
-  </si>
-  <si>
     <t>22040</t>
   </si>
   <si>
     <t>23110</t>
   </si>
   <si>
+    <t>230</t>
+  </si>
+  <si>
+    <t>04.3.5 - Electricity (CS)</t>
+  </si>
+  <si>
     <t>04.3 - Fuel and energy</t>
   </si>
   <si>
-    <t>04.3.5 - Electricity (CS)</t>
-  </si>
-  <si>
-    <t>230</t>
-  </si>
-  <si>
     <t>231</t>
   </si>
   <si>
@@ -841,12 +841,12 @@
     <t>23112</t>
   </si>
   <si>
+    <t>04.8.3 - R&amp;D Fuel and energy (CS)</t>
+  </si>
+  <si>
     <t>04.8 - R&amp;D Economic affairs</t>
   </si>
   <si>
-    <t>04.8.3 - R&amp;D Fuel and energy (CS)</t>
-  </si>
-  <si>
     <t>23181</t>
   </si>
   <si>
@@ -991,15 +991,15 @@
     <t>31110</t>
   </si>
   <si>
+    <t>310</t>
+  </si>
+  <si>
+    <t>04.2.1 - Agriculture (CS)</t>
+  </si>
+  <si>
     <t>04.2 - Agriculture, forestry, fishing and hunting</t>
   </si>
   <si>
-    <t>04.2.1 - Agriculture (CS)</t>
-  </si>
-  <si>
-    <t>310</t>
-  </si>
-  <si>
     <t>311</t>
   </si>
   <si>
@@ -1105,15 +1105,15 @@
     <t>32110</t>
   </si>
   <si>
+    <t>320</t>
+  </si>
+  <si>
+    <t>04.4.2 - Manufacturing (CS)</t>
+  </si>
+  <si>
     <t>04.4 - Mining, manufacturing and construction</t>
   </si>
   <si>
-    <t>04.4.2 - Manufacturing (CS)</t>
-  </si>
-  <si>
-    <t>320</t>
-  </si>
-  <si>
     <t>321</t>
   </si>
   <si>
@@ -1261,12 +1261,12 @@
     <t>41030</t>
   </si>
   <si>
+    <t>05.4.0 - Protection of biodiversity and landscape (CS)</t>
+  </si>
+  <si>
     <t>05.4 - Protection of biodiversity and landscape</t>
   </si>
   <si>
-    <t>05.4.0 - Protection of biodiversity and landscape (CS)</t>
-  </si>
-  <si>
     <t>41040</t>
   </si>
   <si>
@@ -1279,27 +1279,27 @@
     <t>43010</t>
   </si>
   <si>
+    <t>430</t>
+  </si>
+  <si>
+    <t>04.9.0 - Economic affairs n.e.c. (CS)</t>
+  </si>
+  <si>
     <t>04.9 - Economic affairs n.e.c.</t>
   </si>
   <si>
-    <t>04.9.0 - Economic affairs n.e.c. (CS)</t>
-  </si>
-  <si>
-    <t>430</t>
-  </si>
-  <si>
     <t>43030</t>
   </si>
   <si>
     <t>43031</t>
   </si>
   <si>
+    <t>06.2.0 - Community development (CS)</t>
+  </si>
+  <si>
     <t>06.2 - Community development</t>
   </si>
   <si>
-    <t>06.2.0 - Community development (CS)</t>
-  </si>
-  <si>
     <t>43032</t>
   </si>
   <si>
@@ -1318,24 +1318,24 @@
     <t>43060</t>
   </si>
   <si>
+    <t>02.2.0 - Civil defence (CS)</t>
+  </si>
+  <si>
     <t>02.2 - Civil defence</t>
   </si>
   <si>
-    <t>02.2.0 - Civil defence (CS)</t>
-  </si>
-  <si>
     <t>43071</t>
   </si>
   <si>
     <t>43072</t>
   </si>
   <si>
+    <t>10.4.0 - Family and children (IS)</t>
+  </si>
+  <si>
     <t>10.4 - Family and children</t>
   </si>
   <si>
-    <t>10.4.0 - Family and children (IS)</t>
-  </si>
-  <si>
     <t>43073</t>
   </si>
   <si>
@@ -1345,12 +1345,12 @@
     <t>43082</t>
   </si>
   <si>
+    <t>01.4.0 - Basic research (CS)</t>
+  </si>
+  <si>
     <t>01.4 - Basic research</t>
   </si>
   <si>
-    <t>01.4.0 - Basic research (CS)</t>
-  </si>
-  <si>
     <t>51010</t>
   </si>
   <si>
@@ -1375,13 +1375,13 @@
     <t>60010</t>
   </si>
   <si>
+    <t>600</t>
+  </si>
+  <si>
+    <t>01.7.0 - Public debt transactions (CS)</t>
+  </si>
+  <si>
     <t>01.7 - Public debt transactions</t>
-  </si>
-  <si>
-    <t>01.7.0 - Public debt transactions (CS)</t>
-  </si>
-  <si>
-    <t>600</t>
   </si>
   <si>
     <t>60020</t>
@@ -1863,13 +1863,13 @@
         <v>8</v>
       </c>
       <c r="C3" t="s">
+        <v>9</v>
+      </c>
+      <c r="D3" t="s">
         <v>15</v>
       </c>
-      <c r="D3" t="s">
+      <c r="E3" t="s">
         <v>16</v>
-      </c>
-      <c r="E3" t="s">
-        <v>11</v>
       </c>
       <c r="F3" t="s">
         <v>12</v>
@@ -1909,13 +1909,13 @@
         <v>8</v>
       </c>
       <c r="C5" t="s">
+        <v>9</v>
+      </c>
+      <c r="D5" t="s">
         <v>19</v>
       </c>
-      <c r="D5" t="s">
+      <c r="E5" t="s">
         <v>20</v>
-      </c>
-      <c r="E5" t="s">
-        <v>11</v>
       </c>
       <c r="F5" t="s">
         <v>12</v>
@@ -1932,13 +1932,13 @@
         <v>8</v>
       </c>
       <c r="C6" t="s">
+        <v>9</v>
+      </c>
+      <c r="D6" t="s">
         <v>22</v>
       </c>
-      <c r="D6" t="s">
+      <c r="E6" t="s">
         <v>23</v>
-      </c>
-      <c r="E6" t="s">
-        <v>11</v>
       </c>
       <c r="F6" t="s">
         <v>12</v>
@@ -1978,13 +1978,13 @@
         <v>8</v>
       </c>
       <c r="C8" t="s">
+        <v>9</v>
+      </c>
+      <c r="D8" t="s">
         <v>22</v>
       </c>
-      <c r="D8" t="s">
+      <c r="E8" t="s">
         <v>23</v>
-      </c>
-      <c r="E8" t="s">
-        <v>11</v>
       </c>
       <c r="F8" t="s">
         <v>12</v>
@@ -2001,13 +2001,13 @@
         <v>8</v>
       </c>
       <c r="C9" t="s">
+        <v>9</v>
+      </c>
+      <c r="D9" t="s">
         <v>22</v>
       </c>
-      <c r="D9" t="s">
+      <c r="E9" t="s">
         <v>23</v>
-      </c>
-      <c r="E9" t="s">
-        <v>11</v>
       </c>
       <c r="F9" t="s">
         <v>12</v>
@@ -2024,13 +2024,13 @@
         <v>8</v>
       </c>
       <c r="C10" t="s">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="D10" t="s">
         <v>29</v>
       </c>
       <c r="E10" t="s">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="F10" t="s">
         <v>12</v>
@@ -2047,16 +2047,16 @@
         <v>8</v>
       </c>
       <c r="C11" t="s">
+        <v>9</v>
+      </c>
+      <c r="D11" t="s">
         <v>31</v>
       </c>
-      <c r="D11" t="s">
+      <c r="E11" t="s">
         <v>32</v>
       </c>
-      <c r="E11" t="s">
+      <c r="F11" t="s">
         <v>33</v>
-      </c>
-      <c r="F11" t="s">
-        <v>12</v>
       </c>
       <c r="G11" t="s">
         <v>24</v>
@@ -2070,13 +2070,13 @@
         <v>8</v>
       </c>
       <c r="C12" t="s">
+        <v>9</v>
+      </c>
+      <c r="D12" t="s">
         <v>35</v>
       </c>
-      <c r="D12" t="s">
+      <c r="E12" t="s">
         <v>36</v>
-      </c>
-      <c r="E12" t="s">
-        <v>11</v>
       </c>
       <c r="F12" t="s">
         <v>12</v>
@@ -2093,13 +2093,13 @@
         <v>8</v>
       </c>
       <c r="C13" t="s">
-        <v>35</v>
+        <v>9</v>
       </c>
       <c r="D13" t="s">
         <v>38</v>
       </c>
       <c r="E13" t="s">
-        <v>11</v>
+        <v>36</v>
       </c>
       <c r="F13" t="s">
         <v>12</v>
@@ -2116,13 +2116,13 @@
         <v>8</v>
       </c>
       <c r="C14" t="s">
+        <v>9</v>
+      </c>
+      <c r="D14" t="s">
         <v>41</v>
       </c>
-      <c r="D14" t="s">
+      <c r="E14" t="s">
         <v>42</v>
-      </c>
-      <c r="E14" t="s">
-        <v>11</v>
       </c>
       <c r="F14" t="s">
         <v>12</v>
@@ -2139,13 +2139,13 @@
         <v>8</v>
       </c>
       <c r="C15" t="s">
+        <v>9</v>
+      </c>
+      <c r="D15" t="s">
         <v>44</v>
       </c>
-      <c r="D15" t="s">
+      <c r="E15" t="s">
         <v>45</v>
-      </c>
-      <c r="E15" t="s">
-        <v>11</v>
       </c>
       <c r="F15" t="s">
         <v>12</v>
@@ -2162,13 +2162,13 @@
         <v>8</v>
       </c>
       <c r="C16" t="s">
+        <v>9</v>
+      </c>
+      <c r="D16" t="s">
         <v>48</v>
       </c>
-      <c r="D16" t="s">
+      <c r="E16" t="s">
         <v>49</v>
-      </c>
-      <c r="E16" t="s">
-        <v>11</v>
       </c>
       <c r="F16" t="s">
         <v>12</v>
@@ -2191,10 +2191,10 @@
         <v>52</v>
       </c>
       <c r="E17" t="s">
+        <v>53</v>
+      </c>
+      <c r="F17" t="s">
         <v>33</v>
-      </c>
-      <c r="F17" t="s">
-        <v>53</v>
       </c>
       <c r="G17" t="s">
         <v>54</v>
@@ -2214,10 +2214,10 @@
         <v>52</v>
       </c>
       <c r="E18" t="s">
+        <v>53</v>
+      </c>
+      <c r="F18" t="s">
         <v>33</v>
-      </c>
-      <c r="F18" t="s">
-        <v>53</v>
       </c>
       <c r="G18" t="s">
         <v>54</v>
@@ -2231,16 +2231,16 @@
         <v>8</v>
       </c>
       <c r="C19" t="s">
+        <v>51</v>
+      </c>
+      <c r="D19" t="s">
         <v>57</v>
       </c>
-      <c r="D19" t="s">
+      <c r="E19" t="s">
         <v>58</v>
       </c>
-      <c r="E19" t="s">
+      <c r="F19" t="s">
         <v>33</v>
-      </c>
-      <c r="F19" t="s">
-        <v>53</v>
       </c>
       <c r="G19" t="s">
         <v>54</v>
@@ -2254,16 +2254,16 @@
         <v>8</v>
       </c>
       <c r="C20" t="s">
+        <v>51</v>
+      </c>
+      <c r="D20" t="s">
         <v>60</v>
       </c>
-      <c r="D20" t="s">
+      <c r="E20" t="s">
         <v>61</v>
       </c>
-      <c r="E20" t="s">
+      <c r="F20" t="s">
         <v>33</v>
-      </c>
-      <c r="F20" t="s">
-        <v>53</v>
       </c>
       <c r="G20" t="s">
         <v>54</v>
@@ -2283,10 +2283,10 @@
         <v>52</v>
       </c>
       <c r="E21" t="s">
+        <v>53</v>
+      </c>
+      <c r="F21" t="s">
         <v>33</v>
-      </c>
-      <c r="F21" t="s">
-        <v>53</v>
       </c>
       <c r="G21" t="s">
         <v>54</v>
@@ -2300,16 +2300,16 @@
         <v>8</v>
       </c>
       <c r="C22" t="s">
+        <v>51</v>
+      </c>
+      <c r="D22" t="s">
         <v>31</v>
       </c>
-      <c r="D22" t="s">
+      <c r="E22" t="s">
         <v>32</v>
       </c>
-      <c r="E22" t="s">
+      <c r="F22" t="s">
         <v>33</v>
-      </c>
-      <c r="F22" t="s">
-        <v>53</v>
       </c>
       <c r="G22" t="s">
         <v>64</v>
@@ -2323,16 +2323,16 @@
         <v>8</v>
       </c>
       <c r="C23" t="s">
+        <v>51</v>
+      </c>
+      <c r="D23" t="s">
         <v>66</v>
       </c>
-      <c r="D23" t="s">
+      <c r="E23" t="s">
         <v>67</v>
       </c>
-      <c r="E23" t="s">
+      <c r="F23" t="s">
         <v>33</v>
-      </c>
-      <c r="F23" t="s">
-        <v>53</v>
       </c>
       <c r="G23" t="s">
         <v>64</v>
@@ -2346,16 +2346,16 @@
         <v>8</v>
       </c>
       <c r="C24" t="s">
+        <v>51</v>
+      </c>
+      <c r="D24" t="s">
         <v>31</v>
       </c>
-      <c r="D24" t="s">
+      <c r="E24" t="s">
         <v>32</v>
       </c>
-      <c r="E24" t="s">
+      <c r="F24" t="s">
         <v>33</v>
-      </c>
-      <c r="F24" t="s">
-        <v>53</v>
       </c>
       <c r="G24" t="s">
         <v>64</v>
@@ -2369,16 +2369,16 @@
         <v>8</v>
       </c>
       <c r="C25" t="s">
+        <v>51</v>
+      </c>
+      <c r="D25" t="s">
         <v>31</v>
       </c>
-      <c r="D25" t="s">
+      <c r="E25" t="s">
         <v>32</v>
       </c>
-      <c r="E25" t="s">
+      <c r="F25" t="s">
         <v>33</v>
-      </c>
-      <c r="F25" t="s">
-        <v>53</v>
       </c>
       <c r="G25" t="s">
         <v>64</v>
@@ -2392,16 +2392,16 @@
         <v>8</v>
       </c>
       <c r="C26" t="s">
+        <v>51</v>
+      </c>
+      <c r="D26" t="s">
         <v>31</v>
       </c>
-      <c r="D26" t="s">
+      <c r="E26" t="s">
         <v>32</v>
       </c>
-      <c r="E26" t="s">
+      <c r="F26" t="s">
         <v>33</v>
-      </c>
-      <c r="F26" t="s">
-        <v>53</v>
       </c>
       <c r="G26" t="s">
         <v>64</v>
@@ -2415,16 +2415,16 @@
         <v>8</v>
       </c>
       <c r="C27" t="s">
+        <v>51</v>
+      </c>
+      <c r="D27" t="s">
         <v>31</v>
       </c>
-      <c r="D27" t="s">
+      <c r="E27" t="s">
         <v>32</v>
       </c>
-      <c r="E27" t="s">
+      <c r="F27" t="s">
         <v>33</v>
-      </c>
-      <c r="F27" t="s">
-        <v>53</v>
       </c>
       <c r="G27" t="s">
         <v>64</v>
@@ -2438,16 +2438,16 @@
         <v>8</v>
       </c>
       <c r="C28" t="s">
+        <v>51</v>
+      </c>
+      <c r="D28" t="s">
         <v>31</v>
       </c>
-      <c r="D28" t="s">
+      <c r="E28" t="s">
         <v>32</v>
       </c>
-      <c r="E28" t="s">
+      <c r="F28" t="s">
         <v>33</v>
-      </c>
-      <c r="F28" t="s">
-        <v>53</v>
       </c>
       <c r="G28" t="s">
         <v>64</v>
@@ -2461,16 +2461,16 @@
         <v>8</v>
       </c>
       <c r="C29" t="s">
+        <v>51</v>
+      </c>
+      <c r="D29" t="s">
         <v>31</v>
       </c>
-      <c r="D29" t="s">
+      <c r="E29" t="s">
         <v>32</v>
       </c>
-      <c r="E29" t="s">
+      <c r="F29" t="s">
         <v>33</v>
-      </c>
-      <c r="F29" t="s">
-        <v>53</v>
       </c>
       <c r="G29" t="s">
         <v>64</v>
@@ -2490,10 +2490,10 @@
         <v>52</v>
       </c>
       <c r="E30" t="s">
+        <v>53</v>
+      </c>
+      <c r="F30" t="s">
         <v>33</v>
-      </c>
-      <c r="F30" t="s">
-        <v>53</v>
       </c>
       <c r="G30" t="s">
         <v>64</v>
@@ -2507,16 +2507,16 @@
         <v>8</v>
       </c>
       <c r="C31" t="s">
+        <v>51</v>
+      </c>
+      <c r="D31" t="s">
         <v>31</v>
       </c>
-      <c r="D31" t="s">
+      <c r="E31" t="s">
         <v>32</v>
       </c>
-      <c r="E31" t="s">
+      <c r="F31" t="s">
         <v>33</v>
-      </c>
-      <c r="F31" t="s">
-        <v>53</v>
       </c>
       <c r="G31" t="s">
         <v>76</v>
@@ -2530,16 +2530,16 @@
         <v>8</v>
       </c>
       <c r="C32" t="s">
+        <v>51</v>
+      </c>
+      <c r="D32" t="s">
         <v>31</v>
       </c>
-      <c r="D32" t="s">
+      <c r="E32" t="s">
         <v>32</v>
       </c>
-      <c r="E32" t="s">
+      <c r="F32" t="s">
         <v>33</v>
-      </c>
-      <c r="F32" t="s">
-        <v>53</v>
       </c>
       <c r="G32" t="s">
         <v>76</v>
@@ -2553,16 +2553,16 @@
         <v>8</v>
       </c>
       <c r="C33" t="s">
+        <v>51</v>
+      </c>
+      <c r="D33" t="s">
         <v>31</v>
       </c>
-      <c r="D33" t="s">
+      <c r="E33" t="s">
         <v>32</v>
       </c>
-      <c r="E33" t="s">
+      <c r="F33" t="s">
         <v>33</v>
-      </c>
-      <c r="F33" t="s">
-        <v>53</v>
       </c>
       <c r="G33" t="s">
         <v>76</v>
@@ -2576,16 +2576,16 @@
         <v>8</v>
       </c>
       <c r="C34" t="s">
+        <v>51</v>
+      </c>
+      <c r="D34" t="s">
         <v>31</v>
       </c>
-      <c r="D34" t="s">
+      <c r="E34" t="s">
         <v>32</v>
       </c>
-      <c r="E34" t="s">
+      <c r="F34" t="s">
         <v>33</v>
-      </c>
-      <c r="F34" t="s">
-        <v>53</v>
       </c>
       <c r="G34" t="s">
         <v>76</v>
@@ -2599,16 +2599,16 @@
         <v>8</v>
       </c>
       <c r="C35" t="s">
+        <v>51</v>
+      </c>
+      <c r="D35" t="s">
         <v>31</v>
       </c>
-      <c r="D35" t="s">
+      <c r="E35" t="s">
         <v>32</v>
       </c>
-      <c r="E35" t="s">
+      <c r="F35" t="s">
         <v>33</v>
-      </c>
-      <c r="F35" t="s">
-        <v>53</v>
       </c>
       <c r="G35" t="s">
         <v>76</v>
@@ -2622,16 +2622,16 @@
         <v>8</v>
       </c>
       <c r="C36" t="s">
+        <v>51</v>
+      </c>
+      <c r="D36" t="s">
         <v>57</v>
       </c>
-      <c r="D36" t="s">
+      <c r="E36" t="s">
         <v>58</v>
       </c>
-      <c r="E36" t="s">
+      <c r="F36" t="s">
         <v>33</v>
-      </c>
-      <c r="F36" t="s">
-        <v>53</v>
       </c>
       <c r="G36" t="s">
         <v>76</v>
@@ -2645,16 +2645,16 @@
         <v>8</v>
       </c>
       <c r="C37" t="s">
+        <v>83</v>
+      </c>
+      <c r="D37" t="s">
         <v>31</v>
       </c>
-      <c r="D37" t="s">
+      <c r="E37" t="s">
         <v>32</v>
       </c>
-      <c r="E37" t="s">
+      <c r="F37" t="s">
         <v>33</v>
-      </c>
-      <c r="F37" t="s">
-        <v>83</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -2665,16 +2665,16 @@
         <v>8</v>
       </c>
       <c r="C38" t="s">
+        <v>83</v>
+      </c>
+      <c r="D38" t="s">
         <v>31</v>
       </c>
-      <c r="D38" t="s">
+      <c r="E38" t="s">
         <v>32</v>
       </c>
-      <c r="E38" t="s">
+      <c r="F38" t="s">
         <v>33</v>
-      </c>
-      <c r="F38" t="s">
-        <v>83</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -2685,16 +2685,16 @@
         <v>8</v>
       </c>
       <c r="C39" t="s">
+        <v>83</v>
+      </c>
+      <c r="D39" t="s">
         <v>31</v>
       </c>
-      <c r="D39" t="s">
+      <c r="E39" t="s">
         <v>32</v>
       </c>
-      <c r="E39" t="s">
+      <c r="F39" t="s">
         <v>33</v>
-      </c>
-      <c r="F39" t="s">
-        <v>83</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -2705,16 +2705,16 @@
         <v>8</v>
       </c>
       <c r="C40" t="s">
+        <v>83</v>
+      </c>
+      <c r="D40" t="s">
         <v>31</v>
       </c>
-      <c r="D40" t="s">
+      <c r="E40" t="s">
         <v>32</v>
       </c>
-      <c r="E40" t="s">
+      <c r="F40" t="s">
         <v>33</v>
-      </c>
-      <c r="F40" t="s">
-        <v>83</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -2725,16 +2725,16 @@
         <v>8</v>
       </c>
       <c r="C41" t="s">
-        <v>51</v>
+        <v>83</v>
       </c>
       <c r="D41" t="s">
         <v>52</v>
       </c>
       <c r="E41" t="s">
+        <v>53</v>
+      </c>
+      <c r="F41" t="s">
         <v>33</v>
-      </c>
-      <c r="F41" t="s">
-        <v>83</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -2745,16 +2745,16 @@
         <v>8</v>
       </c>
       <c r="C42" t="s">
+        <v>83</v>
+      </c>
+      <c r="D42" t="s">
         <v>57</v>
       </c>
-      <c r="D42" t="s">
+      <c r="E42" t="s">
         <v>58</v>
       </c>
-      <c r="E42" t="s">
+      <c r="F42" t="s">
         <v>33</v>
-      </c>
-      <c r="F42" t="s">
-        <v>83</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -2785,16 +2785,16 @@
         <v>8</v>
       </c>
       <c r="C44" t="s">
+        <v>90</v>
+      </c>
+      <c r="D44" t="s">
         <v>95</v>
       </c>
-      <c r="D44" t="s">
+      <c r="E44" t="s">
         <v>96</v>
       </c>
-      <c r="E44" t="s">
+      <c r="F44" t="s">
         <v>97</v>
-      </c>
-      <c r="F44" t="s">
-        <v>93</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -2845,16 +2845,16 @@
         <v>8</v>
       </c>
       <c r="C47" t="s">
+        <v>90</v>
+      </c>
+      <c r="D47" t="s">
         <v>101</v>
       </c>
-      <c r="D47" t="s">
+      <c r="E47" t="s">
         <v>102</v>
       </c>
-      <c r="E47" t="s">
+      <c r="F47" t="s">
         <v>97</v>
-      </c>
-      <c r="F47" t="s">
-        <v>93</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -2905,16 +2905,16 @@
         <v>8</v>
       </c>
       <c r="C50" t="s">
+        <v>90</v>
+      </c>
+      <c r="D50" t="s">
         <v>101</v>
       </c>
-      <c r="D50" t="s">
+      <c r="E50" t="s">
         <v>102</v>
       </c>
-      <c r="E50" t="s">
+      <c r="F50" t="s">
         <v>97</v>
-      </c>
-      <c r="F50" t="s">
-        <v>93</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -2945,16 +2945,16 @@
         <v>8</v>
       </c>
       <c r="C52" t="s">
+        <v>90</v>
+      </c>
+      <c r="D52" t="s">
         <v>108</v>
       </c>
-      <c r="D52" t="s">
+      <c r="E52" t="s">
         <v>109</v>
       </c>
-      <c r="E52" t="s">
+      <c r="F52" t="s">
         <v>97</v>
-      </c>
-      <c r="F52" t="s">
-        <v>93</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -2965,7 +2965,7 @@
         <v>8</v>
       </c>
       <c r="C53" t="s">
-        <v>9</v>
+        <v>90</v>
       </c>
       <c r="D53" t="s">
         <v>10</v>
@@ -2974,7 +2974,7 @@
         <v>11</v>
       </c>
       <c r="F53" t="s">
-        <v>93</v>
+        <v>12</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -3008,13 +3008,13 @@
         <v>8</v>
       </c>
       <c r="C55" t="s">
+        <v>112</v>
+      </c>
+      <c r="D55" t="s">
         <v>118</v>
       </c>
-      <c r="D55" t="s">
+      <c r="E55" t="s">
         <v>119</v>
-      </c>
-      <c r="E55" t="s">
-        <v>114</v>
       </c>
       <c r="F55" t="s">
         <v>115</v>
@@ -3031,13 +3031,13 @@
         <v>8</v>
       </c>
       <c r="C56" t="s">
+        <v>112</v>
+      </c>
+      <c r="D56" t="s">
         <v>121</v>
       </c>
-      <c r="D56" t="s">
+      <c r="E56" t="s">
         <v>122</v>
-      </c>
-      <c r="E56" t="s">
-        <v>114</v>
       </c>
       <c r="F56" t="s">
         <v>115</v>
@@ -3054,16 +3054,16 @@
         <v>8</v>
       </c>
       <c r="C57" t="s">
+        <v>112</v>
+      </c>
+      <c r="D57" t="s">
         <v>124</v>
       </c>
-      <c r="D57" t="s">
+      <c r="E57" t="s">
         <v>125</v>
       </c>
-      <c r="E57" t="s">
+      <c r="F57" t="s">
         <v>126</v>
-      </c>
-      <c r="F57" t="s">
-        <v>115</v>
       </c>
       <c r="G57" t="s">
         <v>116</v>
@@ -3077,13 +3077,13 @@
         <v>8</v>
       </c>
       <c r="C58" t="s">
+        <v>112</v>
+      </c>
+      <c r="D58" t="s">
         <v>118</v>
       </c>
-      <c r="D58" t="s">
+      <c r="E58" t="s">
         <v>119</v>
-      </c>
-      <c r="E58" t="s">
-        <v>114</v>
       </c>
       <c r="F58" t="s">
         <v>115</v>
@@ -3100,13 +3100,13 @@
         <v>8</v>
       </c>
       <c r="C59" t="s">
+        <v>112</v>
+      </c>
+      <c r="D59" t="s">
         <v>118</v>
       </c>
-      <c r="D59" t="s">
+      <c r="E59" t="s">
         <v>119</v>
-      </c>
-      <c r="E59" t="s">
-        <v>114</v>
       </c>
       <c r="F59" t="s">
         <v>115</v>
@@ -3123,13 +3123,13 @@
         <v>8</v>
       </c>
       <c r="C60" t="s">
+        <v>112</v>
+      </c>
+      <c r="D60" t="s">
         <v>118</v>
       </c>
-      <c r="D60" t="s">
+      <c r="E60" t="s">
         <v>119</v>
-      </c>
-      <c r="E60" t="s">
-        <v>114</v>
       </c>
       <c r="F60" t="s">
         <v>115</v>
@@ -3146,13 +3146,13 @@
         <v>8</v>
       </c>
       <c r="C61" t="s">
+        <v>112</v>
+      </c>
+      <c r="D61" t="s">
         <v>118</v>
       </c>
-      <c r="D61" t="s">
+      <c r="E61" t="s">
         <v>119</v>
-      </c>
-      <c r="E61" t="s">
-        <v>114</v>
       </c>
       <c r="F61" t="s">
         <v>115</v>
@@ -3169,13 +3169,13 @@
         <v>8</v>
       </c>
       <c r="C62" t="s">
+        <v>112</v>
+      </c>
+      <c r="D62" t="s">
         <v>118</v>
       </c>
-      <c r="D62" t="s">
+      <c r="E62" t="s">
         <v>119</v>
-      </c>
-      <c r="E62" t="s">
-        <v>114</v>
       </c>
       <c r="F62" t="s">
         <v>115</v>
@@ -3192,13 +3192,13 @@
         <v>8</v>
       </c>
       <c r="C63" t="s">
-        <v>118</v>
+        <v>112</v>
       </c>
       <c r="D63" t="s">
         <v>133</v>
       </c>
       <c r="E63" t="s">
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="F63" t="s">
         <v>115</v>
@@ -3215,13 +3215,13 @@
         <v>8</v>
       </c>
       <c r="C64" t="s">
-        <v>118</v>
+        <v>112</v>
       </c>
       <c r="D64" t="s">
         <v>133</v>
       </c>
       <c r="E64" t="s">
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="F64" t="s">
         <v>115</v>
@@ -3238,13 +3238,13 @@
         <v>8</v>
       </c>
       <c r="C65" t="s">
+        <v>112</v>
+      </c>
+      <c r="D65" t="s">
         <v>136</v>
       </c>
-      <c r="D65" t="s">
+      <c r="E65" t="s">
         <v>137</v>
-      </c>
-      <c r="E65" t="s">
-        <v>114</v>
       </c>
       <c r="F65" t="s">
         <v>115</v>
@@ -3284,13 +3284,13 @@
         <v>8</v>
       </c>
       <c r="C67" t="s">
+        <v>112</v>
+      </c>
+      <c r="D67" t="s">
         <v>118</v>
       </c>
-      <c r="D67" t="s">
+      <c r="E67" t="s">
         <v>119</v>
-      </c>
-      <c r="E67" t="s">
-        <v>114</v>
       </c>
       <c r="F67" t="s">
         <v>115</v>
@@ -3353,13 +3353,13 @@
         <v>8</v>
       </c>
       <c r="C70" t="s">
+        <v>112</v>
+      </c>
+      <c r="D70" t="s">
         <v>121</v>
       </c>
-      <c r="D70" t="s">
+      <c r="E70" t="s">
         <v>122</v>
-      </c>
-      <c r="E70" t="s">
-        <v>114</v>
       </c>
       <c r="F70" t="s">
         <v>115</v>
@@ -3376,13 +3376,13 @@
         <v>8</v>
       </c>
       <c r="C71" t="s">
+        <v>112</v>
+      </c>
+      <c r="D71" t="s">
         <v>121</v>
       </c>
-      <c r="D71" t="s">
+      <c r="E71" t="s">
         <v>122</v>
-      </c>
-      <c r="E71" t="s">
-        <v>114</v>
       </c>
       <c r="F71" t="s">
         <v>115</v>
@@ -3422,16 +3422,16 @@
         <v>8</v>
       </c>
       <c r="C73" t="s">
+        <v>112</v>
+      </c>
+      <c r="D73" t="s">
         <v>148</v>
       </c>
-      <c r="D73" t="s">
+      <c r="E73" t="s">
         <v>149</v>
       </c>
-      <c r="E73" t="s">
+      <c r="F73" t="s">
         <v>126</v>
-      </c>
-      <c r="F73" t="s">
-        <v>115</v>
       </c>
       <c r="G73" t="s">
         <v>116</v>
@@ -3445,16 +3445,16 @@
         <v>8</v>
       </c>
       <c r="C74" t="s">
+        <v>112</v>
+      </c>
+      <c r="D74" t="s">
         <v>151</v>
       </c>
-      <c r="D74" t="s">
+      <c r="E74" t="s">
         <v>152</v>
       </c>
-      <c r="E74" t="s">
+      <c r="F74" t="s">
         <v>126</v>
-      </c>
-      <c r="F74" t="s">
-        <v>115</v>
       </c>
       <c r="G74" t="s">
         <v>116</v>
@@ -3468,16 +3468,16 @@
         <v>8</v>
       </c>
       <c r="C75" t="s">
+        <v>112</v>
+      </c>
+      <c r="D75" t="s">
         <v>154</v>
       </c>
-      <c r="D75" t="s">
+      <c r="E75" t="s">
         <v>155</v>
       </c>
-      <c r="E75" t="s">
+      <c r="F75" t="s">
         <v>126</v>
-      </c>
-      <c r="F75" t="s">
-        <v>115</v>
       </c>
       <c r="G75" t="s">
         <v>116</v>
@@ -3491,16 +3491,16 @@
         <v>8</v>
       </c>
       <c r="C76" t="s">
+        <v>112</v>
+      </c>
+      <c r="D76" t="s">
         <v>148</v>
       </c>
-      <c r="D76" t="s">
+      <c r="E76" t="s">
         <v>149</v>
       </c>
-      <c r="E76" t="s">
+      <c r="F76" t="s">
         <v>126</v>
-      </c>
-      <c r="F76" t="s">
-        <v>115</v>
       </c>
       <c r="G76" t="s">
         <v>116</v>
@@ -3514,16 +3514,16 @@
         <v>8</v>
       </c>
       <c r="C77" t="s">
+        <v>112</v>
+      </c>
+      <c r="D77" t="s">
         <v>148</v>
       </c>
-      <c r="D77" t="s">
+      <c r="E77" t="s">
         <v>149</v>
       </c>
-      <c r="E77" t="s">
+      <c r="F77" t="s">
         <v>126</v>
-      </c>
-      <c r="F77" t="s">
-        <v>115</v>
       </c>
       <c r="G77" t="s">
         <v>116</v>
@@ -3537,16 +3537,16 @@
         <v>8</v>
       </c>
       <c r="C78" t="s">
+        <v>112</v>
+      </c>
+      <c r="D78" t="s">
         <v>151</v>
       </c>
-      <c r="D78" t="s">
+      <c r="E78" t="s">
         <v>152</v>
       </c>
-      <c r="E78" t="s">
+      <c r="F78" t="s">
         <v>126</v>
-      </c>
-      <c r="F78" t="s">
-        <v>115</v>
       </c>
       <c r="G78" t="s">
         <v>116</v>
@@ -3560,16 +3560,16 @@
         <v>8</v>
       </c>
       <c r="C79" t="s">
+        <v>112</v>
+      </c>
+      <c r="D79" t="s">
         <v>160</v>
       </c>
-      <c r="D79" t="s">
+      <c r="E79" t="s">
         <v>161</v>
       </c>
-      <c r="E79" t="s">
+      <c r="F79" t="s">
         <v>126</v>
-      </c>
-      <c r="F79" t="s">
-        <v>115</v>
       </c>
       <c r="G79" t="s">
         <v>116</v>
@@ -3583,16 +3583,16 @@
         <v>8</v>
       </c>
       <c r="C80" t="s">
+        <v>112</v>
+      </c>
+      <c r="D80" t="s">
         <v>163</v>
       </c>
-      <c r="D80" t="s">
+      <c r="E80" t="s">
         <v>164</v>
       </c>
-      <c r="E80" t="s">
-        <v>165</v>
-      </c>
       <c r="F80" t="s">
-        <v>115</v>
+        <v>165</v>
       </c>
       <c r="G80" t="s">
         <v>116</v>
@@ -3606,16 +3606,16 @@
         <v>8</v>
       </c>
       <c r="C81" t="s">
+        <v>112</v>
+      </c>
+      <c r="D81" t="s">
         <v>163</v>
       </c>
-      <c r="D81" t="s">
+      <c r="E81" t="s">
         <v>164</v>
       </c>
-      <c r="E81" t="s">
-        <v>165</v>
-      </c>
       <c r="F81" t="s">
-        <v>115</v>
+        <v>165</v>
       </c>
       <c r="G81" t="s">
         <v>116</v>
@@ -3629,16 +3629,16 @@
         <v>8</v>
       </c>
       <c r="C82" t="s">
+        <v>112</v>
+      </c>
+      <c r="D82" t="s">
         <v>163</v>
       </c>
-      <c r="D82" t="s">
+      <c r="E82" t="s">
         <v>164</v>
       </c>
-      <c r="E82" t="s">
-        <v>165</v>
-      </c>
       <c r="F82" t="s">
-        <v>115</v>
+        <v>165</v>
       </c>
       <c r="G82" t="s">
         <v>116</v>
@@ -3675,13 +3675,13 @@
         <v>8</v>
       </c>
       <c r="C84" t="s">
+        <v>112</v>
+      </c>
+      <c r="D84" t="s">
         <v>170</v>
       </c>
-      <c r="D84" t="s">
+      <c r="E84" t="s">
         <v>171</v>
-      </c>
-      <c r="E84" t="s">
-        <v>114</v>
       </c>
       <c r="F84" t="s">
         <v>115</v>
@@ -3698,13 +3698,13 @@
         <v>8</v>
       </c>
       <c r="C85" t="s">
-        <v>118</v>
+        <v>112</v>
       </c>
       <c r="D85" t="s">
         <v>173</v>
       </c>
       <c r="E85" t="s">
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="F85" t="s">
         <v>115</v>
@@ -3721,16 +3721,16 @@
         <v>8</v>
       </c>
       <c r="C86" t="s">
+        <v>112</v>
+      </c>
+      <c r="D86" t="s">
         <v>175</v>
       </c>
-      <c r="D86" t="s">
+      <c r="E86" t="s">
         <v>176</v>
       </c>
-      <c r="E86" t="s">
-        <v>165</v>
-      </c>
       <c r="F86" t="s">
-        <v>115</v>
+        <v>165</v>
       </c>
       <c r="G86" t="s">
         <v>116</v>
@@ -3744,13 +3744,13 @@
         <v>8</v>
       </c>
       <c r="C87" t="s">
-        <v>118</v>
+        <v>112</v>
       </c>
       <c r="D87" t="s">
         <v>173</v>
       </c>
       <c r="E87" t="s">
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="F87" t="s">
         <v>115</v>
@@ -3767,13 +3767,13 @@
         <v>8</v>
       </c>
       <c r="C88" t="s">
+        <v>112</v>
+      </c>
+      <c r="D88" t="s">
         <v>118</v>
       </c>
-      <c r="D88" t="s">
+      <c r="E88" t="s">
         <v>119</v>
-      </c>
-      <c r="E88" t="s">
-        <v>114</v>
       </c>
       <c r="F88" t="s">
         <v>115</v>
@@ -3790,13 +3790,13 @@
         <v>8</v>
       </c>
       <c r="C89" t="s">
+        <v>112</v>
+      </c>
+      <c r="D89" t="s">
         <v>118</v>
       </c>
-      <c r="D89" t="s">
+      <c r="E89" t="s">
         <v>119</v>
-      </c>
-      <c r="E89" t="s">
-        <v>114</v>
       </c>
       <c r="F89" t="s">
         <v>115</v>
@@ -3813,16 +3813,16 @@
         <v>8</v>
       </c>
       <c r="C90" t="s">
+        <v>112</v>
+      </c>
+      <c r="D90" t="s">
         <v>124</v>
       </c>
-      <c r="D90" t="s">
+      <c r="E90" t="s">
         <v>125</v>
       </c>
-      <c r="E90" t="s">
+      <c r="F90" t="s">
         <v>126</v>
-      </c>
-      <c r="F90" t="s">
-        <v>115</v>
       </c>
       <c r="G90" t="s">
         <v>116</v>
@@ -3836,16 +3836,16 @@
         <v>8</v>
       </c>
       <c r="C91" t="s">
+        <v>112</v>
+      </c>
+      <c r="D91" t="s">
         <v>182</v>
       </c>
-      <c r="D91" t="s">
+      <c r="E91" t="s">
         <v>183</v>
       </c>
-      <c r="E91" t="s">
+      <c r="F91" t="s">
         <v>184</v>
-      </c>
-      <c r="F91" t="s">
-        <v>115</v>
       </c>
       <c r="G91" t="s">
         <v>116</v>
@@ -3859,16 +3859,16 @@
         <v>8</v>
       </c>
       <c r="C92" t="s">
+        <v>112</v>
+      </c>
+      <c r="D92" t="s">
         <v>124</v>
       </c>
-      <c r="D92" t="s">
+      <c r="E92" t="s">
         <v>125</v>
       </c>
-      <c r="E92" t="s">
+      <c r="F92" t="s">
         <v>126</v>
-      </c>
-      <c r="F92" t="s">
-        <v>115</v>
       </c>
       <c r="G92" t="s">
         <v>116</v>
@@ -3882,13 +3882,13 @@
         <v>8</v>
       </c>
       <c r="C93" t="s">
+        <v>112</v>
+      </c>
+      <c r="D93" t="s">
         <v>121</v>
       </c>
-      <c r="D93" t="s">
+      <c r="E93" t="s">
         <v>122</v>
-      </c>
-      <c r="E93" t="s">
-        <v>114</v>
       </c>
       <c r="F93" t="s">
         <v>115</v>
@@ -3905,16 +3905,16 @@
         <v>8</v>
       </c>
       <c r="C94" t="s">
+        <v>112</v>
+      </c>
+      <c r="D94" t="s">
         <v>124</v>
       </c>
-      <c r="D94" t="s">
+      <c r="E94" t="s">
         <v>125</v>
       </c>
-      <c r="E94" t="s">
+      <c r="F94" t="s">
         <v>126</v>
-      </c>
-      <c r="F94" t="s">
-        <v>115</v>
       </c>
       <c r="G94" t="s">
         <v>116</v>
@@ -3928,13 +3928,13 @@
         <v>8</v>
       </c>
       <c r="C95" t="s">
+        <v>112</v>
+      </c>
+      <c r="D95" t="s">
         <v>189</v>
       </c>
-      <c r="D95" t="s">
+      <c r="E95" t="s">
         <v>190</v>
-      </c>
-      <c r="E95" t="s">
-        <v>114</v>
       </c>
       <c r="F95" t="s">
         <v>115</v>
@@ -3951,16 +3951,16 @@
         <v>8</v>
       </c>
       <c r="C96" t="s">
+        <v>112</v>
+      </c>
+      <c r="D96" t="s">
         <v>124</v>
       </c>
-      <c r="D96" t="s">
+      <c r="E96" t="s">
         <v>125</v>
       </c>
-      <c r="E96" t="s">
+      <c r="F96" t="s">
         <v>126</v>
-      </c>
-      <c r="F96" t="s">
-        <v>115</v>
       </c>
       <c r="G96" t="s">
         <v>192</v>
@@ -3974,16 +3974,16 @@
         <v>8</v>
       </c>
       <c r="C97" t="s">
+        <v>112</v>
+      </c>
+      <c r="D97" t="s">
         <v>124</v>
       </c>
-      <c r="D97" t="s">
+      <c r="E97" t="s">
         <v>125</v>
       </c>
-      <c r="E97" t="s">
+      <c r="F97" t="s">
         <v>126</v>
-      </c>
-      <c r="F97" t="s">
-        <v>115</v>
       </c>
       <c r="G97" t="s">
         <v>192</v>
@@ -3997,16 +3997,16 @@
         <v>8</v>
       </c>
       <c r="C98" t="s">
+        <v>112</v>
+      </c>
+      <c r="D98" t="s">
         <v>195</v>
       </c>
-      <c r="D98" t="s">
+      <c r="E98" t="s">
         <v>196</v>
       </c>
-      <c r="E98" t="s">
+      <c r="F98" t="s">
         <v>197</v>
-      </c>
-      <c r="F98" t="s">
-        <v>115</v>
       </c>
       <c r="G98" t="s">
         <v>192</v>
@@ -4020,16 +4020,16 @@
         <v>8</v>
       </c>
       <c r="C99" t="s">
+        <v>112</v>
+      </c>
+      <c r="D99" t="s">
         <v>124</v>
       </c>
-      <c r="D99" t="s">
+      <c r="E99" t="s">
         <v>125</v>
       </c>
-      <c r="E99" t="s">
+      <c r="F99" t="s">
         <v>126</v>
-      </c>
-      <c r="F99" t="s">
-        <v>115</v>
       </c>
       <c r="G99" t="s">
         <v>192</v>
@@ -4043,16 +4043,16 @@
         <v>8</v>
       </c>
       <c r="C100" t="s">
+        <v>112</v>
+      </c>
+      <c r="D100" t="s">
         <v>154</v>
       </c>
-      <c r="D100" t="s">
+      <c r="E100" t="s">
         <v>155</v>
       </c>
-      <c r="E100" t="s">
+      <c r="F100" t="s">
         <v>126</v>
-      </c>
-      <c r="F100" t="s">
-        <v>115</v>
       </c>
       <c r="G100" t="s">
         <v>192</v>
@@ -4066,16 +4066,16 @@
         <v>8</v>
       </c>
       <c r="C101" t="s">
+        <v>112</v>
+      </c>
+      <c r="D101" t="s">
         <v>124</v>
       </c>
-      <c r="D101" t="s">
+      <c r="E101" t="s">
         <v>125</v>
       </c>
-      <c r="E101" t="s">
+      <c r="F101" t="s">
         <v>126</v>
-      </c>
-      <c r="F101" t="s">
-        <v>115</v>
       </c>
       <c r="G101" t="s">
         <v>192</v>
@@ -4095,10 +4095,10 @@
         <v>203</v>
       </c>
       <c r="E102" t="s">
+        <v>204</v>
+      </c>
+      <c r="F102" t="s">
         <v>184</v>
-      </c>
-      <c r="F102" t="s">
-        <v>204</v>
       </c>
     </row>
     <row r="103" spans="1:7">
@@ -4115,10 +4115,10 @@
         <v>203</v>
       </c>
       <c r="E103" t="s">
+        <v>204</v>
+      </c>
+      <c r="F103" t="s">
         <v>184</v>
-      </c>
-      <c r="F103" t="s">
-        <v>204</v>
       </c>
     </row>
     <row r="104" spans="1:7">
@@ -4135,10 +4135,10 @@
         <v>203</v>
       </c>
       <c r="E104" t="s">
+        <v>204</v>
+      </c>
+      <c r="F104" t="s">
         <v>184</v>
-      </c>
-      <c r="F104" t="s">
-        <v>204</v>
       </c>
     </row>
     <row r="105" spans="1:7">
@@ -4149,16 +4149,16 @@
         <v>8</v>
       </c>
       <c r="C105" t="s">
+        <v>202</v>
+      </c>
+      <c r="D105" t="s">
         <v>208</v>
       </c>
-      <c r="D105" t="s">
+      <c r="E105" t="s">
         <v>209</v>
       </c>
-      <c r="E105" t="s">
+      <c r="F105" t="s">
         <v>184</v>
-      </c>
-      <c r="F105" t="s">
-        <v>204</v>
       </c>
     </row>
     <row r="106" spans="1:7">
@@ -4175,10 +4175,10 @@
         <v>203</v>
       </c>
       <c r="E106" t="s">
+        <v>204</v>
+      </c>
+      <c r="F106" t="s">
         <v>184</v>
-      </c>
-      <c r="F106" t="s">
-        <v>204</v>
       </c>
     </row>
     <row r="107" spans="1:7">
@@ -4189,16 +4189,16 @@
         <v>8</v>
       </c>
       <c r="C107" t="s">
+        <v>202</v>
+      </c>
+      <c r="D107" t="s">
         <v>182</v>
       </c>
-      <c r="D107" t="s">
+      <c r="E107" t="s">
         <v>183</v>
       </c>
-      <c r="E107" t="s">
+      <c r="F107" t="s">
         <v>184</v>
-      </c>
-      <c r="F107" t="s">
-        <v>204</v>
       </c>
     </row>
     <row r="108" spans="1:7">
@@ -4209,16 +4209,16 @@
         <v>8</v>
       </c>
       <c r="C108" t="s">
+        <v>202</v>
+      </c>
+      <c r="D108" t="s">
         <v>213</v>
       </c>
-      <c r="D108" t="s">
+      <c r="E108" t="s">
         <v>214</v>
       </c>
-      <c r="E108" t="s">
+      <c r="F108" t="s">
         <v>184</v>
-      </c>
-      <c r="F108" t="s">
-        <v>204</v>
       </c>
     </row>
     <row r="109" spans="1:7">
@@ -4229,16 +4229,16 @@
         <v>8</v>
       </c>
       <c r="C109" t="s">
+        <v>202</v>
+      </c>
+      <c r="D109" t="s">
         <v>216</v>
       </c>
-      <c r="D109" t="s">
+      <c r="E109" t="s">
         <v>217</v>
       </c>
-      <c r="E109" t="s">
-        <v>92</v>
-      </c>
       <c r="F109" t="s">
-        <v>204</v>
+        <v>93</v>
       </c>
     </row>
     <row r="110" spans="1:7">
@@ -4249,16 +4249,16 @@
         <v>8</v>
       </c>
       <c r="C110" t="s">
+        <v>202</v>
+      </c>
+      <c r="D110" t="s">
         <v>219</v>
       </c>
-      <c r="D110" t="s">
+      <c r="E110" t="s">
         <v>220</v>
       </c>
-      <c r="E110" t="s">
-        <v>92</v>
-      </c>
       <c r="F110" t="s">
-        <v>204</v>
+        <v>93</v>
       </c>
     </row>
     <row r="111" spans="1:7">
@@ -4275,10 +4275,10 @@
         <v>203</v>
       </c>
       <c r="E111" t="s">
+        <v>204</v>
+      </c>
+      <c r="F111" t="s">
         <v>184</v>
-      </c>
-      <c r="F111" t="s">
-        <v>204</v>
       </c>
     </row>
     <row r="112" spans="1:7">
@@ -4289,16 +4289,16 @@
         <v>8</v>
       </c>
       <c r="C112" t="s">
+        <v>202</v>
+      </c>
+      <c r="D112" t="s">
         <v>223</v>
       </c>
-      <c r="D112" t="s">
+      <c r="E112" t="s">
         <v>224</v>
       </c>
-      <c r="E112" t="s">
+      <c r="F112" t="s">
         <v>225</v>
-      </c>
-      <c r="F112" t="s">
-        <v>204</v>
       </c>
     </row>
     <row r="113" spans="1:6">
@@ -4309,7 +4309,7 @@
         <v>8</v>
       </c>
       <c r="C113" t="s">
-        <v>112</v>
+        <v>202</v>
       </c>
       <c r="D113" t="s">
         <v>143</v>
@@ -4318,7 +4318,7 @@
         <v>114</v>
       </c>
       <c r="F113" t="s">
-        <v>204</v>
+        <v>115</v>
       </c>
     </row>
     <row r="114" spans="1:6">
@@ -4329,16 +4329,16 @@
         <v>8</v>
       </c>
       <c r="C114" t="s">
+        <v>202</v>
+      </c>
+      <c r="D114" t="s">
         <v>151</v>
       </c>
-      <c r="D114" t="s">
+      <c r="E114" t="s">
         <v>152</v>
       </c>
-      <c r="E114" t="s">
+      <c r="F114" t="s">
         <v>126</v>
-      </c>
-      <c r="F114" t="s">
-        <v>204</v>
       </c>
     </row>
     <row r="115" spans="1:6">
@@ -4349,16 +4349,16 @@
         <v>8</v>
       </c>
       <c r="C115" t="s">
+        <v>202</v>
+      </c>
+      <c r="D115" t="s">
         <v>182</v>
       </c>
-      <c r="D115" t="s">
+      <c r="E115" t="s">
         <v>183</v>
       </c>
-      <c r="E115" t="s">
+      <c r="F115" t="s">
         <v>184</v>
-      </c>
-      <c r="F115" t="s">
-        <v>204</v>
       </c>
     </row>
     <row r="116" spans="1:6">
@@ -4369,16 +4369,16 @@
         <v>8</v>
       </c>
       <c r="C116" t="s">
+        <v>202</v>
+      </c>
+      <c r="D116" t="s">
         <v>230</v>
       </c>
-      <c r="D116" t="s">
+      <c r="E116" t="s">
         <v>231</v>
       </c>
-      <c r="E116" t="s">
+      <c r="F116" t="s">
         <v>225</v>
-      </c>
-      <c r="F116" t="s">
-        <v>204</v>
       </c>
     </row>
     <row r="117" spans="1:6">
@@ -4389,16 +4389,16 @@
         <v>8</v>
       </c>
       <c r="C117" t="s">
+        <v>202</v>
+      </c>
+      <c r="D117" t="s">
         <v>223</v>
       </c>
-      <c r="D117" t="s">
+      <c r="E117" t="s">
         <v>224</v>
       </c>
-      <c r="E117" t="s">
+      <c r="F117" t="s">
         <v>225</v>
-      </c>
-      <c r="F117" t="s">
-        <v>204</v>
       </c>
     </row>
     <row r="118" spans="1:6">
@@ -4409,16 +4409,16 @@
         <v>8</v>
       </c>
       <c r="C118" t="s">
-        <v>163</v>
+        <v>202</v>
       </c>
       <c r="D118" t="s">
         <v>234</v>
       </c>
       <c r="E118" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="F118" t="s">
-        <v>204</v>
+        <v>165</v>
       </c>
     </row>
     <row r="119" spans="1:6">
@@ -4429,16 +4429,16 @@
         <v>8</v>
       </c>
       <c r="C119" t="s">
+        <v>202</v>
+      </c>
+      <c r="D119" t="s">
         <v>182</v>
       </c>
-      <c r="D119" t="s">
+      <c r="E119" t="s">
         <v>183</v>
       </c>
-      <c r="E119" t="s">
+      <c r="F119" t="s">
         <v>184</v>
-      </c>
-      <c r="F119" t="s">
-        <v>204</v>
       </c>
     </row>
     <row r="120" spans="1:6">
@@ -4449,16 +4449,16 @@
         <v>8</v>
       </c>
       <c r="C120" t="s">
+        <v>237</v>
+      </c>
+      <c r="D120" t="s">
         <v>170</v>
       </c>
-      <c r="D120" t="s">
+      <c r="E120" t="s">
         <v>171</v>
       </c>
-      <c r="E120" t="s">
-        <v>114</v>
-      </c>
       <c r="F120" t="s">
-        <v>237</v>
+        <v>115</v>
       </c>
     </row>
     <row r="121" spans="1:6">
@@ -4469,7 +4469,7 @@
         <v>8</v>
       </c>
       <c r="C121" t="s">
-        <v>112</v>
+        <v>237</v>
       </c>
       <c r="D121" t="s">
         <v>143</v>
@@ -4478,7 +4478,7 @@
         <v>114</v>
       </c>
       <c r="F121" t="s">
-        <v>237</v>
+        <v>115</v>
       </c>
     </row>
     <row r="122" spans="1:6">
@@ -4489,16 +4489,16 @@
         <v>8</v>
       </c>
       <c r="C122" t="s">
+        <v>237</v>
+      </c>
+      <c r="D122" t="s">
         <v>170</v>
       </c>
-      <c r="D122" t="s">
+      <c r="E122" t="s">
         <v>171</v>
       </c>
-      <c r="E122" t="s">
-        <v>114</v>
-      </c>
       <c r="F122" t="s">
-        <v>237</v>
+        <v>115</v>
       </c>
     </row>
     <row r="123" spans="1:6">
@@ -4509,16 +4509,16 @@
         <v>8</v>
       </c>
       <c r="C123" t="s">
+        <v>237</v>
+      </c>
+      <c r="D123" t="s">
         <v>170</v>
       </c>
-      <c r="D123" t="s">
+      <c r="E123" t="s">
         <v>171</v>
       </c>
-      <c r="E123" t="s">
-        <v>114</v>
-      </c>
       <c r="F123" t="s">
-        <v>237</v>
+        <v>115</v>
       </c>
     </row>
     <row r="124" spans="1:6">
@@ -4529,16 +4529,16 @@
         <v>8</v>
       </c>
       <c r="C124" t="s">
+        <v>237</v>
+      </c>
+      <c r="D124" t="s">
         <v>242</v>
       </c>
-      <c r="D124" t="s">
+      <c r="E124" t="s">
         <v>243</v>
       </c>
-      <c r="E124" t="s">
-        <v>165</v>
-      </c>
       <c r="F124" t="s">
-        <v>237</v>
+        <v>165</v>
       </c>
     </row>
     <row r="125" spans="1:6">
@@ -4549,16 +4549,16 @@
         <v>8</v>
       </c>
       <c r="C125" t="s">
+        <v>237</v>
+      </c>
+      <c r="D125" t="s">
         <v>242</v>
       </c>
-      <c r="D125" t="s">
+      <c r="E125" t="s">
         <v>243</v>
       </c>
-      <c r="E125" t="s">
-        <v>165</v>
-      </c>
       <c r="F125" t="s">
-        <v>237</v>
+        <v>165</v>
       </c>
     </row>
     <row r="126" spans="1:6">
@@ -4569,16 +4569,16 @@
         <v>8</v>
       </c>
       <c r="C126" t="s">
+        <v>237</v>
+      </c>
+      <c r="D126" t="s">
         <v>242</v>
       </c>
-      <c r="D126" t="s">
+      <c r="E126" t="s">
         <v>243</v>
       </c>
-      <c r="E126" t="s">
-        <v>165</v>
-      </c>
       <c r="F126" t="s">
-        <v>237</v>
+        <v>165</v>
       </c>
     </row>
     <row r="127" spans="1:6">
@@ -4589,16 +4589,16 @@
         <v>8</v>
       </c>
       <c r="C127" t="s">
+        <v>237</v>
+      </c>
+      <c r="D127" t="s">
         <v>242</v>
       </c>
-      <c r="D127" t="s">
+      <c r="E127" t="s">
         <v>243</v>
       </c>
-      <c r="E127" t="s">
-        <v>165</v>
-      </c>
       <c r="F127" t="s">
-        <v>237</v>
+        <v>165</v>
       </c>
     </row>
     <row r="128" spans="1:6">
@@ -4609,16 +4609,16 @@
         <v>8</v>
       </c>
       <c r="C128" t="s">
+        <v>237</v>
+      </c>
+      <c r="D128" t="s">
         <v>242</v>
       </c>
-      <c r="D128" t="s">
+      <c r="E128" t="s">
         <v>243</v>
       </c>
-      <c r="E128" t="s">
-        <v>165</v>
-      </c>
       <c r="F128" t="s">
-        <v>237</v>
+        <v>165</v>
       </c>
     </row>
     <row r="129" spans="1:7">
@@ -4629,16 +4629,16 @@
         <v>8</v>
       </c>
       <c r="C129" t="s">
-        <v>242</v>
+        <v>237</v>
       </c>
       <c r="D129" t="s">
         <v>249</v>
       </c>
       <c r="E129" t="s">
-        <v>165</v>
+        <v>243</v>
       </c>
       <c r="F129" t="s">
-        <v>237</v>
+        <v>165</v>
       </c>
     </row>
     <row r="130" spans="1:7">
@@ -4649,16 +4649,16 @@
         <v>8</v>
       </c>
       <c r="C130" t="s">
-        <v>242</v>
+        <v>237</v>
       </c>
       <c r="D130" t="s">
         <v>251</v>
       </c>
       <c r="E130" t="s">
-        <v>165</v>
+        <v>243</v>
       </c>
       <c r="F130" t="s">
-        <v>237</v>
+        <v>165</v>
       </c>
     </row>
     <row r="131" spans="1:7">
@@ -4669,16 +4669,16 @@
         <v>8</v>
       </c>
       <c r="C131" t="s">
-        <v>242</v>
+        <v>237</v>
       </c>
       <c r="D131" t="s">
         <v>253</v>
       </c>
       <c r="E131" t="s">
-        <v>165</v>
+        <v>243</v>
       </c>
       <c r="F131" t="s">
-        <v>237</v>
+        <v>165</v>
       </c>
     </row>
     <row r="132" spans="1:7">
@@ -4689,16 +4689,16 @@
         <v>8</v>
       </c>
       <c r="C132" t="s">
+        <v>237</v>
+      </c>
+      <c r="D132" t="s">
         <v>255</v>
       </c>
-      <c r="D132" t="s">
+      <c r="E132" t="s">
         <v>256</v>
       </c>
-      <c r="E132" t="s">
-        <v>165</v>
-      </c>
       <c r="F132" t="s">
-        <v>237</v>
+        <v>165</v>
       </c>
     </row>
     <row r="133" spans="1:7">
@@ -4709,16 +4709,16 @@
         <v>8</v>
       </c>
       <c r="C133" t="s">
+        <v>237</v>
+      </c>
+      <c r="D133" t="s">
         <v>189</v>
       </c>
-      <c r="D133" t="s">
+      <c r="E133" t="s">
         <v>190</v>
       </c>
-      <c r="E133" t="s">
-        <v>114</v>
-      </c>
       <c r="F133" t="s">
-        <v>237</v>
+        <v>115</v>
       </c>
     </row>
     <row r="134" spans="1:7">
@@ -4729,16 +4729,16 @@
         <v>8</v>
       </c>
       <c r="C134" t="s">
+        <v>259</v>
+      </c>
+      <c r="D134" t="s">
         <v>175</v>
       </c>
-      <c r="D134" t="s">
+      <c r="E134" t="s">
         <v>176</v>
       </c>
-      <c r="E134" t="s">
-        <v>165</v>
-      </c>
       <c r="F134" t="s">
-        <v>259</v>
+        <v>165</v>
       </c>
     </row>
     <row r="135" spans="1:7">
@@ -4749,16 +4749,16 @@
         <v>8</v>
       </c>
       <c r="C135" t="s">
+        <v>259</v>
+      </c>
+      <c r="D135" t="s">
         <v>175</v>
       </c>
-      <c r="D135" t="s">
+      <c r="E135" t="s">
         <v>176</v>
       </c>
-      <c r="E135" t="s">
-        <v>165</v>
-      </c>
       <c r="F135" t="s">
-        <v>259</v>
+        <v>165</v>
       </c>
     </row>
     <row r="136" spans="1:7">
@@ -4769,16 +4769,16 @@
         <v>8</v>
       </c>
       <c r="C136" t="s">
+        <v>259</v>
+      </c>
+      <c r="D136" t="s">
         <v>175</v>
       </c>
-      <c r="D136" t="s">
+      <c r="E136" t="s">
         <v>176</v>
       </c>
-      <c r="E136" t="s">
-        <v>165</v>
-      </c>
       <c r="F136" t="s">
-        <v>259</v>
+        <v>165</v>
       </c>
     </row>
     <row r="137" spans="1:7">
@@ -4789,16 +4789,16 @@
         <v>8</v>
       </c>
       <c r="C137" t="s">
+        <v>259</v>
+      </c>
+      <c r="D137" t="s">
         <v>175</v>
       </c>
-      <c r="D137" t="s">
+      <c r="E137" t="s">
         <v>176</v>
       </c>
-      <c r="E137" t="s">
-        <v>165</v>
-      </c>
       <c r="F137" t="s">
-        <v>259</v>
+        <v>165</v>
       </c>
     </row>
     <row r="138" spans="1:7">
@@ -4809,16 +4809,16 @@
         <v>8</v>
       </c>
       <c r="C138" t="s">
+        <v>259</v>
+      </c>
+      <c r="D138" t="s">
         <v>175</v>
       </c>
-      <c r="D138" t="s">
+      <c r="E138" t="s">
         <v>176</v>
       </c>
-      <c r="E138" t="s">
-        <v>165</v>
-      </c>
       <c r="F138" t="s">
-        <v>259</v>
+        <v>165</v>
       </c>
     </row>
     <row r="139" spans="1:7">
@@ -4829,16 +4829,16 @@
         <v>8</v>
       </c>
       <c r="C139" t="s">
+        <v>259</v>
+      </c>
+      <c r="D139" t="s">
         <v>265</v>
       </c>
-      <c r="D139" t="s">
+      <c r="E139" t="s">
         <v>266</v>
       </c>
-      <c r="E139" t="s">
+      <c r="F139" t="s">
         <v>225</v>
-      </c>
-      <c r="F139" t="s">
-        <v>259</v>
       </c>
     </row>
     <row r="140" spans="1:7">
@@ -4849,16 +4849,16 @@
         <v>8</v>
       </c>
       <c r="C140" t="s">
+        <v>259</v>
+      </c>
+      <c r="D140" t="s">
         <v>175</v>
       </c>
-      <c r="D140" t="s">
+      <c r="E140" t="s">
         <v>176</v>
       </c>
-      <c r="E140" t="s">
-        <v>165</v>
-      </c>
       <c r="F140" t="s">
-        <v>259</v>
+        <v>165</v>
       </c>
     </row>
     <row r="141" spans="1:7">
@@ -4875,10 +4875,10 @@
         <v>270</v>
       </c>
       <c r="E141" t="s">
-        <v>165</v>
+        <v>271</v>
       </c>
       <c r="F141" t="s">
-        <v>271</v>
+        <v>165</v>
       </c>
       <c r="G141" t="s">
         <v>272</v>
@@ -4898,10 +4898,10 @@
         <v>270</v>
       </c>
       <c r="E142" t="s">
-        <v>165</v>
+        <v>271</v>
       </c>
       <c r="F142" t="s">
-        <v>271</v>
+        <v>165</v>
       </c>
       <c r="G142" t="s">
         <v>272</v>
@@ -4915,16 +4915,16 @@
         <v>8</v>
       </c>
       <c r="C143" t="s">
+        <v>269</v>
+      </c>
+      <c r="D143" t="s">
         <v>275</v>
       </c>
-      <c r="D143" t="s">
+      <c r="E143" t="s">
         <v>276</v>
       </c>
-      <c r="E143" t="s">
-        <v>165</v>
-      </c>
       <c r="F143" t="s">
-        <v>271</v>
+        <v>165</v>
       </c>
       <c r="G143" t="s">
         <v>272</v>
@@ -4938,16 +4938,16 @@
         <v>8</v>
       </c>
       <c r="C144" t="s">
+        <v>269</v>
+      </c>
+      <c r="D144" t="s">
         <v>275</v>
       </c>
-      <c r="D144" t="s">
+      <c r="E144" t="s">
         <v>276</v>
       </c>
-      <c r="E144" t="s">
-        <v>165</v>
-      </c>
       <c r="F144" t="s">
-        <v>271</v>
+        <v>165</v>
       </c>
       <c r="G144" t="s">
         <v>272</v>
@@ -4961,16 +4961,16 @@
         <v>8</v>
       </c>
       <c r="C145" t="s">
+        <v>269</v>
+      </c>
+      <c r="D145" t="s">
         <v>275</v>
       </c>
-      <c r="D145" t="s">
+      <c r="E145" t="s">
         <v>276</v>
       </c>
-      <c r="E145" t="s">
-        <v>165</v>
-      </c>
       <c r="F145" t="s">
-        <v>271</v>
+        <v>165</v>
       </c>
       <c r="G145" t="s">
         <v>272</v>
@@ -4990,10 +4990,10 @@
         <v>270</v>
       </c>
       <c r="E146" t="s">
-        <v>165</v>
+        <v>271</v>
       </c>
       <c r="F146" t="s">
-        <v>271</v>
+        <v>165</v>
       </c>
       <c r="G146" t="s">
         <v>272</v>
@@ -5013,10 +5013,10 @@
         <v>270</v>
       </c>
       <c r="E147" t="s">
-        <v>165</v>
+        <v>271</v>
       </c>
       <c r="F147" t="s">
-        <v>271</v>
+        <v>165</v>
       </c>
       <c r="G147" t="s">
         <v>281</v>
@@ -5036,10 +5036,10 @@
         <v>270</v>
       </c>
       <c r="E148" t="s">
-        <v>165</v>
+        <v>271</v>
       </c>
       <c r="F148" t="s">
-        <v>271</v>
+        <v>165</v>
       </c>
       <c r="G148" t="s">
         <v>281</v>
@@ -5059,10 +5059,10 @@
         <v>270</v>
       </c>
       <c r="E149" t="s">
-        <v>165</v>
+        <v>271</v>
       </c>
       <c r="F149" t="s">
-        <v>271</v>
+        <v>165</v>
       </c>
       <c r="G149" t="s">
         <v>281</v>
@@ -5082,10 +5082,10 @@
         <v>270</v>
       </c>
       <c r="E150" t="s">
-        <v>165</v>
+        <v>271</v>
       </c>
       <c r="F150" t="s">
-        <v>271</v>
+        <v>165</v>
       </c>
       <c r="G150" t="s">
         <v>281</v>
@@ -5105,10 +5105,10 @@
         <v>270</v>
       </c>
       <c r="E151" t="s">
-        <v>165</v>
+        <v>271</v>
       </c>
       <c r="F151" t="s">
-        <v>271</v>
+        <v>165</v>
       </c>
       <c r="G151" t="s">
         <v>281</v>
@@ -5128,10 +5128,10 @@
         <v>270</v>
       </c>
       <c r="E152" t="s">
-        <v>165</v>
+        <v>271</v>
       </c>
       <c r="F152" t="s">
-        <v>271</v>
+        <v>165</v>
       </c>
       <c r="G152" t="s">
         <v>281</v>
@@ -5151,10 +5151,10 @@
         <v>270</v>
       </c>
       <c r="E153" t="s">
-        <v>165</v>
+        <v>271</v>
       </c>
       <c r="F153" t="s">
-        <v>271</v>
+        <v>165</v>
       </c>
       <c r="G153" t="s">
         <v>281</v>
@@ -5174,10 +5174,10 @@
         <v>270</v>
       </c>
       <c r="E154" t="s">
-        <v>165</v>
+        <v>271</v>
       </c>
       <c r="F154" t="s">
-        <v>271</v>
+        <v>165</v>
       </c>
       <c r="G154" t="s">
         <v>281</v>
@@ -5197,10 +5197,10 @@
         <v>270</v>
       </c>
       <c r="E155" t="s">
-        <v>165</v>
+        <v>271</v>
       </c>
       <c r="F155" t="s">
-        <v>271</v>
+        <v>165</v>
       </c>
       <c r="G155" t="s">
         <v>281</v>
@@ -5220,10 +5220,10 @@
         <v>270</v>
       </c>
       <c r="E156" t="s">
-        <v>165</v>
+        <v>271</v>
       </c>
       <c r="F156" t="s">
-        <v>271</v>
+        <v>165</v>
       </c>
       <c r="G156" t="s">
         <v>291</v>
@@ -5243,10 +5243,10 @@
         <v>293</v>
       </c>
       <c r="E157" t="s">
-        <v>165</v>
+        <v>271</v>
       </c>
       <c r="F157" t="s">
-        <v>271</v>
+        <v>165</v>
       </c>
       <c r="G157" t="s">
         <v>291</v>
@@ -5266,10 +5266,10 @@
         <v>270</v>
       </c>
       <c r="E158" t="s">
-        <v>165</v>
+        <v>271</v>
       </c>
       <c r="F158" t="s">
-        <v>271</v>
+        <v>165</v>
       </c>
       <c r="G158" t="s">
         <v>291</v>
@@ -5289,10 +5289,10 @@
         <v>270</v>
       </c>
       <c r="E159" t="s">
-        <v>165</v>
+        <v>271</v>
       </c>
       <c r="F159" t="s">
-        <v>271</v>
+        <v>165</v>
       </c>
       <c r="G159" t="s">
         <v>291</v>
@@ -5312,10 +5312,10 @@
         <v>270</v>
       </c>
       <c r="E160" t="s">
-        <v>165</v>
+        <v>271</v>
       </c>
       <c r="F160" t="s">
-        <v>271</v>
+        <v>165</v>
       </c>
       <c r="G160" t="s">
         <v>291</v>
@@ -5335,10 +5335,10 @@
         <v>270</v>
       </c>
       <c r="E161" t="s">
-        <v>165</v>
+        <v>271</v>
       </c>
       <c r="F161" t="s">
-        <v>271</v>
+        <v>165</v>
       </c>
       <c r="G161" t="s">
         <v>291</v>
@@ -5358,10 +5358,10 @@
         <v>270</v>
       </c>
       <c r="E162" t="s">
-        <v>165</v>
+        <v>271</v>
       </c>
       <c r="F162" t="s">
-        <v>271</v>
+        <v>165</v>
       </c>
       <c r="G162" t="s">
         <v>299</v>
@@ -5381,10 +5381,10 @@
         <v>301</v>
       </c>
       <c r="E163" t="s">
-        <v>165</v>
+        <v>271</v>
       </c>
       <c r="F163" t="s">
-        <v>271</v>
+        <v>165</v>
       </c>
       <c r="G163" t="s">
         <v>302</v>
@@ -5404,10 +5404,10 @@
         <v>270</v>
       </c>
       <c r="E164" t="s">
-        <v>165</v>
+        <v>271</v>
       </c>
       <c r="F164" t="s">
-        <v>271</v>
+        <v>165</v>
       </c>
       <c r="G164" t="s">
         <v>304</v>
@@ -5427,10 +5427,10 @@
         <v>270</v>
       </c>
       <c r="E165" t="s">
-        <v>165</v>
+        <v>271</v>
       </c>
       <c r="F165" t="s">
-        <v>271</v>
+        <v>165</v>
       </c>
       <c r="G165" t="s">
         <v>304</v>
@@ -5450,10 +5450,10 @@
         <v>270</v>
       </c>
       <c r="E166" t="s">
-        <v>165</v>
+        <v>271</v>
       </c>
       <c r="F166" t="s">
-        <v>271</v>
+        <v>165</v>
       </c>
       <c r="G166" t="s">
         <v>304</v>
@@ -5473,10 +5473,10 @@
         <v>270</v>
       </c>
       <c r="E167" t="s">
-        <v>165</v>
+        <v>271</v>
       </c>
       <c r="F167" t="s">
-        <v>271</v>
+        <v>165</v>
       </c>
       <c r="G167" t="s">
         <v>304</v>
@@ -5496,10 +5496,10 @@
         <v>309</v>
       </c>
       <c r="E168" t="s">
-        <v>165</v>
+        <v>271</v>
       </c>
       <c r="F168" t="s">
-        <v>271</v>
+        <v>165</v>
       </c>
       <c r="G168" t="s">
         <v>304</v>
@@ -5519,10 +5519,10 @@
         <v>309</v>
       </c>
       <c r="E169" t="s">
-        <v>165</v>
+        <v>271</v>
       </c>
       <c r="F169" t="s">
-        <v>271</v>
+        <v>165</v>
       </c>
       <c r="G169" t="s">
         <v>304</v>
@@ -5542,10 +5542,10 @@
         <v>270</v>
       </c>
       <c r="E170" t="s">
-        <v>165</v>
+        <v>271</v>
       </c>
       <c r="F170" t="s">
-        <v>271</v>
+        <v>165</v>
       </c>
       <c r="G170" t="s">
         <v>304</v>
@@ -5559,16 +5559,16 @@
         <v>8</v>
       </c>
       <c r="C171" t="s">
+        <v>313</v>
+      </c>
+      <c r="D171" t="s">
         <v>163</v>
       </c>
-      <c r="D171" t="s">
+      <c r="E171" t="s">
         <v>164</v>
       </c>
-      <c r="E171" t="s">
-        <v>165</v>
-      </c>
       <c r="F171" t="s">
-        <v>313</v>
+        <v>165</v>
       </c>
     </row>
     <row r="172" spans="1:7">
@@ -5579,16 +5579,16 @@
         <v>8</v>
       </c>
       <c r="C172" t="s">
+        <v>313</v>
+      </c>
+      <c r="D172" t="s">
         <v>118</v>
       </c>
-      <c r="D172" t="s">
+      <c r="E172" t="s">
         <v>119</v>
       </c>
-      <c r="E172" t="s">
-        <v>114</v>
-      </c>
       <c r="F172" t="s">
-        <v>313</v>
+        <v>115</v>
       </c>
     </row>
     <row r="173" spans="1:7">
@@ -5599,16 +5599,16 @@
         <v>8</v>
       </c>
       <c r="C173" t="s">
+        <v>313</v>
+      </c>
+      <c r="D173" t="s">
         <v>163</v>
       </c>
-      <c r="D173" t="s">
+      <c r="E173" t="s">
         <v>164</v>
       </c>
-      <c r="E173" t="s">
-        <v>165</v>
-      </c>
       <c r="F173" t="s">
-        <v>313</v>
+        <v>165</v>
       </c>
     </row>
     <row r="174" spans="1:7">
@@ -5619,16 +5619,16 @@
         <v>8</v>
       </c>
       <c r="C174" t="s">
+        <v>313</v>
+      </c>
+      <c r="D174" t="s">
         <v>163</v>
       </c>
-      <c r="D174" t="s">
+      <c r="E174" t="s">
         <v>164</v>
       </c>
-      <c r="E174" t="s">
-        <v>165</v>
-      </c>
       <c r="F174" t="s">
-        <v>313</v>
+        <v>165</v>
       </c>
     </row>
     <row r="175" spans="1:7">
@@ -5639,16 +5639,16 @@
         <v>8</v>
       </c>
       <c r="C175" t="s">
+        <v>313</v>
+      </c>
+      <c r="D175" t="s">
         <v>163</v>
       </c>
-      <c r="D175" t="s">
+      <c r="E175" t="s">
         <v>164</v>
       </c>
-      <c r="E175" t="s">
-        <v>165</v>
-      </c>
       <c r="F175" t="s">
-        <v>313</v>
+        <v>165</v>
       </c>
     </row>
     <row r="176" spans="1:7">
@@ -5659,16 +5659,16 @@
         <v>8</v>
       </c>
       <c r="C176" t="s">
+        <v>313</v>
+      </c>
+      <c r="D176" t="s">
         <v>163</v>
       </c>
-      <c r="D176" t="s">
+      <c r="E176" t="s">
         <v>164</v>
       </c>
-      <c r="E176" t="s">
-        <v>165</v>
-      </c>
       <c r="F176" t="s">
-        <v>313</v>
+        <v>165</v>
       </c>
     </row>
     <row r="177" spans="1:7">
@@ -5679,16 +5679,16 @@
         <v>8</v>
       </c>
       <c r="C177" t="s">
+        <v>320</v>
+      </c>
+      <c r="D177" t="s">
         <v>163</v>
       </c>
-      <c r="D177" t="s">
+      <c r="E177" t="s">
         <v>164</v>
       </c>
-      <c r="E177" t="s">
-        <v>165</v>
-      </c>
       <c r="F177" t="s">
-        <v>320</v>
+        <v>165</v>
       </c>
     </row>
     <row r="178" spans="1:7">
@@ -5699,16 +5699,16 @@
         <v>8</v>
       </c>
       <c r="C178" t="s">
+        <v>320</v>
+      </c>
+      <c r="D178" t="s">
         <v>163</v>
       </c>
-      <c r="D178" t="s">
+      <c r="E178" t="s">
         <v>164</v>
       </c>
-      <c r="E178" t="s">
-        <v>165</v>
-      </c>
       <c r="F178" t="s">
-        <v>320</v>
+        <v>165</v>
       </c>
     </row>
     <row r="179" spans="1:7">
@@ -5719,16 +5719,16 @@
         <v>8</v>
       </c>
       <c r="C179" t="s">
+        <v>320</v>
+      </c>
+      <c r="D179" t="s">
         <v>163</v>
       </c>
-      <c r="D179" t="s">
+      <c r="E179" t="s">
         <v>164</v>
       </c>
-      <c r="E179" t="s">
-        <v>165</v>
-      </c>
       <c r="F179" t="s">
-        <v>320</v>
+        <v>165</v>
       </c>
     </row>
     <row r="180" spans="1:7">
@@ -5739,16 +5739,16 @@
         <v>8</v>
       </c>
       <c r="C180" t="s">
+        <v>320</v>
+      </c>
+      <c r="D180" t="s">
         <v>163</v>
       </c>
-      <c r="D180" t="s">
+      <c r="E180" t="s">
         <v>164</v>
       </c>
-      <c r="E180" t="s">
-        <v>165</v>
-      </c>
       <c r="F180" t="s">
-        <v>320</v>
+        <v>165</v>
       </c>
     </row>
     <row r="181" spans="1:7">
@@ -5765,10 +5765,10 @@
         <v>326</v>
       </c>
       <c r="E181" t="s">
-        <v>165</v>
+        <v>327</v>
       </c>
       <c r="F181" t="s">
-        <v>327</v>
+        <v>165</v>
       </c>
       <c r="G181" t="s">
         <v>328</v>
@@ -5788,10 +5788,10 @@
         <v>326</v>
       </c>
       <c r="E182" t="s">
-        <v>165</v>
+        <v>327</v>
       </c>
       <c r="F182" t="s">
-        <v>327</v>
+        <v>165</v>
       </c>
       <c r="G182" t="s">
         <v>328</v>
@@ -5811,10 +5811,10 @@
         <v>326</v>
       </c>
       <c r="E183" t="s">
-        <v>165</v>
+        <v>327</v>
       </c>
       <c r="F183" t="s">
-        <v>327</v>
+        <v>165</v>
       </c>
       <c r="G183" t="s">
         <v>328</v>
@@ -5834,10 +5834,10 @@
         <v>326</v>
       </c>
       <c r="E184" t="s">
-        <v>165</v>
+        <v>327</v>
       </c>
       <c r="F184" t="s">
-        <v>327</v>
+        <v>165</v>
       </c>
       <c r="G184" t="s">
         <v>328</v>
@@ -5857,10 +5857,10 @@
         <v>326</v>
       </c>
       <c r="E185" t="s">
-        <v>165</v>
+        <v>327</v>
       </c>
       <c r="F185" t="s">
-        <v>327</v>
+        <v>165</v>
       </c>
       <c r="G185" t="s">
         <v>328</v>
@@ -5880,10 +5880,10 @@
         <v>326</v>
       </c>
       <c r="E186" t="s">
-        <v>165</v>
+        <v>327</v>
       </c>
       <c r="F186" t="s">
-        <v>327</v>
+        <v>165</v>
       </c>
       <c r="G186" t="s">
         <v>328</v>
@@ -5903,10 +5903,10 @@
         <v>326</v>
       </c>
       <c r="E187" t="s">
-        <v>165</v>
+        <v>327</v>
       </c>
       <c r="F187" t="s">
-        <v>327</v>
+        <v>165</v>
       </c>
       <c r="G187" t="s">
         <v>328</v>
@@ -5926,10 +5926,10 @@
         <v>326</v>
       </c>
       <c r="E188" t="s">
-        <v>165</v>
+        <v>327</v>
       </c>
       <c r="F188" t="s">
-        <v>327</v>
+        <v>165</v>
       </c>
       <c r="G188" t="s">
         <v>328</v>
@@ -5949,10 +5949,10 @@
         <v>326</v>
       </c>
       <c r="E189" t="s">
-        <v>165</v>
+        <v>327</v>
       </c>
       <c r="F189" t="s">
-        <v>327</v>
+        <v>165</v>
       </c>
       <c r="G189" t="s">
         <v>328</v>
@@ -5972,10 +5972,10 @@
         <v>326</v>
       </c>
       <c r="E190" t="s">
-        <v>165</v>
+        <v>327</v>
       </c>
       <c r="F190" t="s">
-        <v>327</v>
+        <v>165</v>
       </c>
       <c r="G190" t="s">
         <v>328</v>
@@ -5995,10 +5995,10 @@
         <v>326</v>
       </c>
       <c r="E191" t="s">
-        <v>165</v>
+        <v>327</v>
       </c>
       <c r="F191" t="s">
-        <v>327</v>
+        <v>165</v>
       </c>
       <c r="G191" t="s">
         <v>328</v>
@@ -6018,10 +6018,10 @@
         <v>326</v>
       </c>
       <c r="E192" t="s">
-        <v>165</v>
+        <v>327</v>
       </c>
       <c r="F192" t="s">
-        <v>327</v>
+        <v>165</v>
       </c>
       <c r="G192" t="s">
         <v>328</v>
@@ -6035,16 +6035,16 @@
         <v>8</v>
       </c>
       <c r="C193" t="s">
-        <v>275</v>
+        <v>325</v>
       </c>
       <c r="D193" t="s">
         <v>341</v>
       </c>
       <c r="E193" t="s">
-        <v>165</v>
+        <v>276</v>
       </c>
       <c r="F193" t="s">
-        <v>327</v>
+        <v>165</v>
       </c>
       <c r="G193" t="s">
         <v>328</v>
@@ -6064,10 +6064,10 @@
         <v>326</v>
       </c>
       <c r="E194" t="s">
-        <v>165</v>
+        <v>327</v>
       </c>
       <c r="F194" t="s">
-        <v>327</v>
+        <v>165</v>
       </c>
       <c r="G194" t="s">
         <v>328</v>
@@ -6087,10 +6087,10 @@
         <v>326</v>
       </c>
       <c r="E195" t="s">
-        <v>165</v>
+        <v>327</v>
       </c>
       <c r="F195" t="s">
-        <v>327</v>
+        <v>165</v>
       </c>
       <c r="G195" t="s">
         <v>328</v>
@@ -6110,10 +6110,10 @@
         <v>326</v>
       </c>
       <c r="E196" t="s">
-        <v>165</v>
+        <v>327</v>
       </c>
       <c r="F196" t="s">
-        <v>327</v>
+        <v>165</v>
       </c>
       <c r="G196" t="s">
         <v>328</v>
@@ -6133,10 +6133,10 @@
         <v>326</v>
       </c>
       <c r="E197" t="s">
-        <v>165</v>
+        <v>327</v>
       </c>
       <c r="F197" t="s">
-        <v>327</v>
+        <v>165</v>
       </c>
       <c r="G197" t="s">
         <v>328</v>
@@ -6156,10 +6156,10 @@
         <v>326</v>
       </c>
       <c r="E198" t="s">
-        <v>165</v>
+        <v>327</v>
       </c>
       <c r="F198" t="s">
-        <v>327</v>
+        <v>165</v>
       </c>
       <c r="G198" t="s">
         <v>328</v>
@@ -6179,10 +6179,10 @@
         <v>348</v>
       </c>
       <c r="E199" t="s">
-        <v>165</v>
+        <v>327</v>
       </c>
       <c r="F199" t="s">
-        <v>327</v>
+        <v>165</v>
       </c>
       <c r="G199" t="s">
         <v>349</v>
@@ -6202,10 +6202,10 @@
         <v>348</v>
       </c>
       <c r="E200" t="s">
-        <v>165</v>
+        <v>327</v>
       </c>
       <c r="F200" t="s">
-        <v>327</v>
+        <v>165</v>
       </c>
       <c r="G200" t="s">
         <v>349</v>
@@ -6225,10 +6225,10 @@
         <v>348</v>
       </c>
       <c r="E201" t="s">
-        <v>165</v>
+        <v>327</v>
       </c>
       <c r="F201" t="s">
-        <v>327</v>
+        <v>165</v>
       </c>
       <c r="G201" t="s">
         <v>349</v>
@@ -6248,10 +6248,10 @@
         <v>348</v>
       </c>
       <c r="E202" t="s">
-        <v>165</v>
+        <v>327</v>
       </c>
       <c r="F202" t="s">
-        <v>327</v>
+        <v>165</v>
       </c>
       <c r="G202" t="s">
         <v>349</v>
@@ -6265,16 +6265,16 @@
         <v>8</v>
       </c>
       <c r="C203" t="s">
-        <v>275</v>
+        <v>325</v>
       </c>
       <c r="D203" t="s">
         <v>341</v>
       </c>
       <c r="E203" t="s">
-        <v>165</v>
+        <v>276</v>
       </c>
       <c r="F203" t="s">
-        <v>327</v>
+        <v>165</v>
       </c>
       <c r="G203" t="s">
         <v>349</v>
@@ -6294,10 +6294,10 @@
         <v>348</v>
       </c>
       <c r="E204" t="s">
-        <v>165</v>
+        <v>327</v>
       </c>
       <c r="F204" t="s">
-        <v>327</v>
+        <v>165</v>
       </c>
       <c r="G204" t="s">
         <v>349</v>
@@ -6317,10 +6317,10 @@
         <v>356</v>
       </c>
       <c r="E205" t="s">
-        <v>165</v>
+        <v>327</v>
       </c>
       <c r="F205" t="s">
-        <v>327</v>
+        <v>165</v>
       </c>
       <c r="G205" t="s">
         <v>357</v>
@@ -6340,10 +6340,10 @@
         <v>356</v>
       </c>
       <c r="E206" t="s">
-        <v>165</v>
+        <v>327</v>
       </c>
       <c r="F206" t="s">
-        <v>327</v>
+        <v>165</v>
       </c>
       <c r="G206" t="s">
         <v>357</v>
@@ -6363,10 +6363,10 @@
         <v>356</v>
       </c>
       <c r="E207" t="s">
-        <v>165</v>
+        <v>327</v>
       </c>
       <c r="F207" t="s">
-        <v>327</v>
+        <v>165</v>
       </c>
       <c r="G207" t="s">
         <v>357</v>
@@ -6380,16 +6380,16 @@
         <v>8</v>
       </c>
       <c r="C208" t="s">
-        <v>275</v>
+        <v>325</v>
       </c>
       <c r="D208" t="s">
         <v>341</v>
       </c>
       <c r="E208" t="s">
-        <v>165</v>
+        <v>276</v>
       </c>
       <c r="F208" t="s">
-        <v>327</v>
+        <v>165</v>
       </c>
       <c r="G208" t="s">
         <v>357</v>
@@ -6409,10 +6409,10 @@
         <v>356</v>
       </c>
       <c r="E209" t="s">
-        <v>165</v>
+        <v>327</v>
       </c>
       <c r="F209" t="s">
-        <v>327</v>
+        <v>165</v>
       </c>
       <c r="G209" t="s">
         <v>357</v>
@@ -6432,10 +6432,10 @@
         <v>364</v>
       </c>
       <c r="E210" t="s">
-        <v>165</v>
+        <v>365</v>
       </c>
       <c r="F210" t="s">
-        <v>365</v>
+        <v>165</v>
       </c>
       <c r="G210" t="s">
         <v>366</v>
@@ -6455,10 +6455,10 @@
         <v>364</v>
       </c>
       <c r="E211" t="s">
-        <v>165</v>
+        <v>365</v>
       </c>
       <c r="F211" t="s">
-        <v>365</v>
+        <v>165</v>
       </c>
       <c r="G211" t="s">
         <v>366</v>
@@ -6478,10 +6478,10 @@
         <v>364</v>
       </c>
       <c r="E212" t="s">
-        <v>165</v>
+        <v>365</v>
       </c>
       <c r="F212" t="s">
-        <v>365</v>
+        <v>165</v>
       </c>
       <c r="G212" t="s">
         <v>366</v>
@@ -6501,10 +6501,10 @@
         <v>364</v>
       </c>
       <c r="E213" t="s">
-        <v>165</v>
+        <v>365</v>
       </c>
       <c r="F213" t="s">
-        <v>365</v>
+        <v>165</v>
       </c>
       <c r="G213" t="s">
         <v>366</v>
@@ -6524,10 +6524,10 @@
         <v>364</v>
       </c>
       <c r="E214" t="s">
-        <v>165</v>
+        <v>365</v>
       </c>
       <c r="F214" t="s">
-        <v>365</v>
+        <v>165</v>
       </c>
       <c r="G214" t="s">
         <v>366</v>
@@ -6541,16 +6541,16 @@
         <v>8</v>
       </c>
       <c r="C215" t="s">
-        <v>325</v>
+        <v>363</v>
       </c>
       <c r="D215" t="s">
         <v>348</v>
       </c>
       <c r="E215" t="s">
-        <v>165</v>
+        <v>327</v>
       </c>
       <c r="F215" t="s">
-        <v>365</v>
+        <v>165</v>
       </c>
       <c r="G215" t="s">
         <v>366</v>
@@ -6570,10 +6570,10 @@
         <v>364</v>
       </c>
       <c r="E216" t="s">
-        <v>165</v>
+        <v>365</v>
       </c>
       <c r="F216" t="s">
-        <v>365</v>
+        <v>165</v>
       </c>
       <c r="G216" t="s">
         <v>366</v>
@@ -6593,10 +6593,10 @@
         <v>364</v>
       </c>
       <c r="E217" t="s">
-        <v>165</v>
+        <v>365</v>
       </c>
       <c r="F217" t="s">
-        <v>365</v>
+        <v>165</v>
       </c>
       <c r="G217" t="s">
         <v>366</v>
@@ -6616,10 +6616,10 @@
         <v>364</v>
       </c>
       <c r="E218" t="s">
-        <v>165</v>
+        <v>365</v>
       </c>
       <c r="F218" t="s">
-        <v>365</v>
+        <v>165</v>
       </c>
       <c r="G218" t="s">
         <v>366</v>
@@ -6639,10 +6639,10 @@
         <v>364</v>
       </c>
       <c r="E219" t="s">
-        <v>165</v>
+        <v>365</v>
       </c>
       <c r="F219" t="s">
-        <v>365</v>
+        <v>165</v>
       </c>
       <c r="G219" t="s">
         <v>366</v>
@@ -6656,16 +6656,16 @@
         <v>8</v>
       </c>
       <c r="C220" t="s">
-        <v>269</v>
+        <v>363</v>
       </c>
       <c r="D220" t="s">
         <v>309</v>
       </c>
       <c r="E220" t="s">
-        <v>165</v>
+        <v>271</v>
       </c>
       <c r="F220" t="s">
-        <v>365</v>
+        <v>165</v>
       </c>
       <c r="G220" t="s">
         <v>366</v>
@@ -6685,10 +6685,10 @@
         <v>364</v>
       </c>
       <c r="E221" t="s">
-        <v>165</v>
+        <v>365</v>
       </c>
       <c r="F221" t="s">
-        <v>365</v>
+        <v>165</v>
       </c>
       <c r="G221" t="s">
         <v>366</v>
@@ -6708,10 +6708,10 @@
         <v>364</v>
       </c>
       <c r="E222" t="s">
-        <v>165</v>
+        <v>365</v>
       </c>
       <c r="F222" t="s">
-        <v>365</v>
+        <v>165</v>
       </c>
       <c r="G222" t="s">
         <v>366</v>
@@ -6731,10 +6731,10 @@
         <v>364</v>
       </c>
       <c r="E223" t="s">
-        <v>165</v>
+        <v>365</v>
       </c>
       <c r="F223" t="s">
-        <v>365</v>
+        <v>165</v>
       </c>
       <c r="G223" t="s">
         <v>366</v>
@@ -6754,10 +6754,10 @@
         <v>364</v>
       </c>
       <c r="E224" t="s">
-        <v>165</v>
+        <v>365</v>
       </c>
       <c r="F224" t="s">
-        <v>365</v>
+        <v>165</v>
       </c>
       <c r="G224" t="s">
         <v>366</v>
@@ -6777,10 +6777,10 @@
         <v>364</v>
       </c>
       <c r="E225" t="s">
-        <v>165</v>
+        <v>365</v>
       </c>
       <c r="F225" t="s">
-        <v>365</v>
+        <v>165</v>
       </c>
       <c r="G225" t="s">
         <v>366</v>
@@ -6794,16 +6794,16 @@
         <v>8</v>
       </c>
       <c r="C226" t="s">
+        <v>363</v>
+      </c>
+      <c r="D226" t="s">
         <v>275</v>
       </c>
-      <c r="D226" t="s">
+      <c r="E226" t="s">
         <v>276</v>
       </c>
-      <c r="E226" t="s">
-        <v>165</v>
-      </c>
       <c r="F226" t="s">
-        <v>365</v>
+        <v>165</v>
       </c>
       <c r="G226" t="s">
         <v>366</v>
@@ -6823,10 +6823,10 @@
         <v>364</v>
       </c>
       <c r="E227" t="s">
-        <v>165</v>
+        <v>365</v>
       </c>
       <c r="F227" t="s">
-        <v>365</v>
+        <v>165</v>
       </c>
       <c r="G227" t="s">
         <v>366</v>
@@ -6840,16 +6840,16 @@
         <v>8</v>
       </c>
       <c r="C228" t="s">
+        <v>363</v>
+      </c>
+      <c r="D228" t="s">
         <v>163</v>
       </c>
-      <c r="D228" t="s">
+      <c r="E228" t="s">
         <v>164</v>
       </c>
-      <c r="E228" t="s">
-        <v>165</v>
-      </c>
       <c r="F228" t="s">
-        <v>365</v>
+        <v>165</v>
       </c>
       <c r="G228" t="s">
         <v>366</v>
@@ -6869,10 +6869,10 @@
         <v>386</v>
       </c>
       <c r="E229" t="s">
-        <v>165</v>
+        <v>365</v>
       </c>
       <c r="F229" t="s">
-        <v>365</v>
+        <v>165</v>
       </c>
       <c r="G229" t="s">
         <v>387</v>
@@ -6892,10 +6892,10 @@
         <v>386</v>
       </c>
       <c r="E230" t="s">
-        <v>165</v>
+        <v>365</v>
       </c>
       <c r="F230" t="s">
-        <v>365</v>
+        <v>165</v>
       </c>
       <c r="G230" t="s">
         <v>387</v>
@@ -6909,16 +6909,16 @@
         <v>8</v>
       </c>
       <c r="C231" t="s">
-        <v>269</v>
+        <v>363</v>
       </c>
       <c r="D231" t="s">
         <v>293</v>
       </c>
       <c r="E231" t="s">
-        <v>165</v>
+        <v>271</v>
       </c>
       <c r="F231" t="s">
-        <v>365</v>
+        <v>165</v>
       </c>
       <c r="G231" t="s">
         <v>387</v>
@@ -6932,16 +6932,16 @@
         <v>8</v>
       </c>
       <c r="C232" t="s">
-        <v>269</v>
+        <v>363</v>
       </c>
       <c r="D232" t="s">
         <v>309</v>
       </c>
       <c r="E232" t="s">
-        <v>165</v>
+        <v>271</v>
       </c>
       <c r="F232" t="s">
-        <v>365</v>
+        <v>165</v>
       </c>
       <c r="G232" t="s">
         <v>387</v>
@@ -6961,10 +6961,10 @@
         <v>386</v>
       </c>
       <c r="E233" t="s">
-        <v>165</v>
+        <v>365</v>
       </c>
       <c r="F233" t="s">
-        <v>365</v>
+        <v>165</v>
       </c>
       <c r="G233" t="s">
         <v>387</v>
@@ -6984,10 +6984,10 @@
         <v>386</v>
       </c>
       <c r="E234" t="s">
-        <v>165</v>
+        <v>365</v>
       </c>
       <c r="F234" t="s">
-        <v>365</v>
+        <v>165</v>
       </c>
       <c r="G234" t="s">
         <v>387</v>
@@ -7007,10 +7007,10 @@
         <v>386</v>
       </c>
       <c r="E235" t="s">
-        <v>165</v>
+        <v>365</v>
       </c>
       <c r="F235" t="s">
-        <v>365</v>
+        <v>165</v>
       </c>
       <c r="G235" t="s">
         <v>387</v>
@@ -7030,10 +7030,10 @@
         <v>386</v>
       </c>
       <c r="E236" t="s">
-        <v>165</v>
+        <v>365</v>
       </c>
       <c r="F236" t="s">
-        <v>365</v>
+        <v>165</v>
       </c>
       <c r="G236" t="s">
         <v>387</v>
@@ -7053,10 +7053,10 @@
         <v>386</v>
       </c>
       <c r="E237" t="s">
-        <v>165</v>
+        <v>365</v>
       </c>
       <c r="F237" t="s">
-        <v>365</v>
+        <v>165</v>
       </c>
       <c r="G237" t="s">
         <v>387</v>
@@ -7076,10 +7076,10 @@
         <v>386</v>
       </c>
       <c r="E238" t="s">
-        <v>165</v>
+        <v>365</v>
       </c>
       <c r="F238" t="s">
-        <v>365</v>
+        <v>165</v>
       </c>
       <c r="G238" t="s">
         <v>387</v>
@@ -7099,10 +7099,10 @@
         <v>398</v>
       </c>
       <c r="E239" t="s">
-        <v>165</v>
+        <v>365</v>
       </c>
       <c r="F239" t="s">
-        <v>365</v>
+        <v>165</v>
       </c>
       <c r="G239" t="s">
         <v>399</v>
@@ -7116,16 +7116,16 @@
         <v>8</v>
       </c>
       <c r="C240" t="s">
+        <v>401</v>
+      </c>
+      <c r="D240" t="s">
         <v>163</v>
       </c>
-      <c r="D240" t="s">
+      <c r="E240" t="s">
         <v>164</v>
       </c>
-      <c r="E240" t="s">
-        <v>165</v>
-      </c>
       <c r="F240" t="s">
-        <v>401</v>
+        <v>165</v>
       </c>
       <c r="G240" t="s">
         <v>402</v>
@@ -7139,16 +7139,16 @@
         <v>8</v>
       </c>
       <c r="C241" t="s">
+        <v>401</v>
+      </c>
+      <c r="D241" t="s">
         <v>163</v>
       </c>
-      <c r="D241" t="s">
+      <c r="E241" t="s">
         <v>164</v>
       </c>
-      <c r="E241" t="s">
-        <v>165</v>
-      </c>
       <c r="F241" t="s">
-        <v>401</v>
+        <v>165</v>
       </c>
       <c r="G241" t="s">
         <v>402</v>
@@ -7162,16 +7162,16 @@
         <v>8</v>
       </c>
       <c r="C242" t="s">
+        <v>401</v>
+      </c>
+      <c r="D242" t="s">
         <v>163</v>
       </c>
-      <c r="D242" t="s">
+      <c r="E242" t="s">
         <v>164</v>
       </c>
-      <c r="E242" t="s">
-        <v>165</v>
-      </c>
       <c r="F242" t="s">
-        <v>401</v>
+        <v>165</v>
       </c>
       <c r="G242" t="s">
         <v>402</v>
@@ -7185,16 +7185,16 @@
         <v>8</v>
       </c>
       <c r="C243" t="s">
+        <v>401</v>
+      </c>
+      <c r="D243" t="s">
         <v>163</v>
       </c>
-      <c r="D243" t="s">
+      <c r="E243" t="s">
         <v>164</v>
       </c>
-      <c r="E243" t="s">
-        <v>165</v>
-      </c>
       <c r="F243" t="s">
-        <v>401</v>
+        <v>165</v>
       </c>
       <c r="G243" t="s">
         <v>402</v>
@@ -7208,16 +7208,16 @@
         <v>8</v>
       </c>
       <c r="C244" t="s">
+        <v>401</v>
+      </c>
+      <c r="D244" t="s">
         <v>163</v>
       </c>
-      <c r="D244" t="s">
+      <c r="E244" t="s">
         <v>164</v>
       </c>
-      <c r="E244" t="s">
-        <v>165</v>
-      </c>
       <c r="F244" t="s">
-        <v>401</v>
+        <v>165</v>
       </c>
       <c r="G244" t="s">
         <v>402</v>
@@ -7231,16 +7231,16 @@
         <v>8</v>
       </c>
       <c r="C245" t="s">
+        <v>401</v>
+      </c>
+      <c r="D245" t="s">
         <v>163</v>
       </c>
-      <c r="D245" t="s">
+      <c r="E245" t="s">
         <v>164</v>
       </c>
-      <c r="E245" t="s">
-        <v>165</v>
-      </c>
       <c r="F245" t="s">
-        <v>401</v>
+        <v>165</v>
       </c>
       <c r="G245" t="s">
         <v>402</v>
@@ -7254,16 +7254,16 @@
         <v>8</v>
       </c>
       <c r="C246" t="s">
-        <v>255</v>
+        <v>401</v>
       </c>
       <c r="D246" t="s">
         <v>409</v>
       </c>
       <c r="E246" t="s">
-        <v>165</v>
+        <v>256</v>
       </c>
       <c r="F246" t="s">
-        <v>401</v>
+        <v>165</v>
       </c>
       <c r="G246" t="s">
         <v>410</v>
@@ -7277,16 +7277,16 @@
         <v>8</v>
       </c>
       <c r="C247" t="s">
+        <v>412</v>
+      </c>
+      <c r="D247" t="s">
         <v>95</v>
       </c>
-      <c r="D247" t="s">
+      <c r="E247" t="s">
         <v>96</v>
       </c>
-      <c r="E247" t="s">
+      <c r="F247" t="s">
         <v>97</v>
-      </c>
-      <c r="F247" t="s">
-        <v>412</v>
       </c>
     </row>
     <row r="248" spans="1:7">
@@ -7297,16 +7297,16 @@
         <v>8</v>
       </c>
       <c r="C248" t="s">
+        <v>412</v>
+      </c>
+      <c r="D248" t="s">
         <v>95</v>
       </c>
-      <c r="D248" t="s">
+      <c r="E248" t="s">
         <v>96</v>
       </c>
-      <c r="E248" t="s">
+      <c r="F248" t="s">
         <v>97</v>
-      </c>
-      <c r="F248" t="s">
-        <v>412</v>
       </c>
     </row>
     <row r="249" spans="1:7">
@@ -7317,16 +7317,16 @@
         <v>8</v>
       </c>
       <c r="C249" t="s">
+        <v>412</v>
+      </c>
+      <c r="D249" t="s">
         <v>415</v>
       </c>
-      <c r="D249" t="s">
+      <c r="E249" t="s">
         <v>416</v>
       </c>
-      <c r="E249" t="s">
+      <c r="F249" t="s">
         <v>97</v>
-      </c>
-      <c r="F249" t="s">
-        <v>412</v>
       </c>
     </row>
     <row r="250" spans="1:7">
@@ -7337,16 +7337,16 @@
         <v>8</v>
       </c>
       <c r="C250" t="s">
+        <v>412</v>
+      </c>
+      <c r="D250" t="s">
         <v>95</v>
       </c>
-      <c r="D250" t="s">
+      <c r="E250" t="s">
         <v>96</v>
       </c>
-      <c r="E250" t="s">
+      <c r="F250" t="s">
         <v>97</v>
-      </c>
-      <c r="F250" t="s">
-        <v>412</v>
       </c>
     </row>
     <row r="251" spans="1:7">
@@ -7357,16 +7357,16 @@
         <v>8</v>
       </c>
       <c r="C251" t="s">
+        <v>412</v>
+      </c>
+      <c r="D251" t="s">
         <v>95</v>
       </c>
-      <c r="D251" t="s">
+      <c r="E251" t="s">
         <v>96</v>
       </c>
-      <c r="E251" t="s">
+      <c r="F251" t="s">
         <v>97</v>
-      </c>
-      <c r="F251" t="s">
-        <v>412</v>
       </c>
     </row>
     <row r="252" spans="1:7">
@@ -7377,16 +7377,16 @@
         <v>8</v>
       </c>
       <c r="C252" t="s">
+        <v>412</v>
+      </c>
+      <c r="D252" t="s">
         <v>95</v>
       </c>
-      <c r="D252" t="s">
+      <c r="E252" t="s">
         <v>96</v>
       </c>
-      <c r="E252" t="s">
+      <c r="F252" t="s">
         <v>97</v>
-      </c>
-      <c r="F252" t="s">
-        <v>412</v>
       </c>
     </row>
     <row r="253" spans="1:7">
@@ -7403,10 +7403,10 @@
         <v>422</v>
       </c>
       <c r="E253" t="s">
-        <v>165</v>
+        <v>423</v>
       </c>
       <c r="F253" t="s">
-        <v>423</v>
+        <v>165</v>
       </c>
     </row>
     <row r="254" spans="1:7">
@@ -7417,16 +7417,16 @@
         <v>8</v>
       </c>
       <c r="C254" t="s">
+        <v>421</v>
+      </c>
+      <c r="D254" t="s">
         <v>219</v>
       </c>
-      <c r="D254" t="s">
+      <c r="E254" t="s">
         <v>220</v>
       </c>
-      <c r="E254" t="s">
-        <v>92</v>
-      </c>
       <c r="F254" t="s">
-        <v>423</v>
+        <v>93</v>
       </c>
     </row>
     <row r="255" spans="1:7">
@@ -7437,16 +7437,16 @@
         <v>8</v>
       </c>
       <c r="C255" t="s">
+        <v>421</v>
+      </c>
+      <c r="D255" t="s">
         <v>426</v>
       </c>
-      <c r="D255" t="s">
+      <c r="E255" t="s">
         <v>427</v>
       </c>
-      <c r="E255" t="s">
-        <v>92</v>
-      </c>
       <c r="F255" t="s">
-        <v>423</v>
+        <v>93</v>
       </c>
     </row>
     <row r="256" spans="1:7">
@@ -7457,16 +7457,16 @@
         <v>8</v>
       </c>
       <c r="C256" t="s">
+        <v>421</v>
+      </c>
+      <c r="D256" t="s">
         <v>426</v>
       </c>
-      <c r="D256" t="s">
+      <c r="E256" t="s">
         <v>427</v>
       </c>
-      <c r="E256" t="s">
-        <v>92</v>
-      </c>
       <c r="F256" t="s">
-        <v>423</v>
+        <v>93</v>
       </c>
     </row>
     <row r="257" spans="1:6">
@@ -7477,16 +7477,16 @@
         <v>8</v>
       </c>
       <c r="C257" t="s">
+        <v>421</v>
+      </c>
+      <c r="D257" t="s">
         <v>426</v>
       </c>
-      <c r="D257" t="s">
+      <c r="E257" t="s">
         <v>427</v>
       </c>
-      <c r="E257" t="s">
-        <v>92</v>
-      </c>
       <c r="F257" t="s">
-        <v>423</v>
+        <v>93</v>
       </c>
     </row>
     <row r="258" spans="1:6">
@@ -7497,16 +7497,16 @@
         <v>8</v>
       </c>
       <c r="C258" t="s">
-        <v>325</v>
+        <v>421</v>
       </c>
       <c r="D258" t="s">
         <v>326</v>
       </c>
       <c r="E258" t="s">
-        <v>165</v>
+        <v>327</v>
       </c>
       <c r="F258" t="s">
-        <v>423</v>
+        <v>165</v>
       </c>
     </row>
     <row r="259" spans="1:6">
@@ -7517,16 +7517,16 @@
         <v>8</v>
       </c>
       <c r="C259" t="s">
+        <v>421</v>
+      </c>
+      <c r="D259" t="s">
         <v>426</v>
       </c>
-      <c r="D259" t="s">
+      <c r="E259" t="s">
         <v>427</v>
       </c>
-      <c r="E259" t="s">
-        <v>92</v>
-      </c>
       <c r="F259" t="s">
-        <v>423</v>
+        <v>93</v>
       </c>
     </row>
     <row r="260" spans="1:6">
@@ -7537,16 +7537,16 @@
         <v>8</v>
       </c>
       <c r="C260" t="s">
+        <v>421</v>
+      </c>
+      <c r="D260" t="s">
         <v>163</v>
       </c>
-      <c r="D260" t="s">
+      <c r="E260" t="s">
         <v>164</v>
       </c>
-      <c r="E260" t="s">
-        <v>165</v>
-      </c>
       <c r="F260" t="s">
-        <v>423</v>
+        <v>165</v>
       </c>
     </row>
     <row r="261" spans="1:6">
@@ -7557,16 +7557,16 @@
         <v>8</v>
       </c>
       <c r="C261" t="s">
+        <v>421</v>
+      </c>
+      <c r="D261" t="s">
         <v>434</v>
       </c>
-      <c r="D261" t="s">
+      <c r="E261" t="s">
         <v>435</v>
       </c>
-      <c r="E261" t="s">
+      <c r="F261" t="s">
         <v>197</v>
-      </c>
-      <c r="F261" t="s">
-        <v>423</v>
       </c>
     </row>
     <row r="262" spans="1:6">
@@ -7577,16 +7577,16 @@
         <v>8</v>
       </c>
       <c r="C262" t="s">
+        <v>421</v>
+      </c>
+      <c r="D262" t="s">
         <v>163</v>
       </c>
-      <c r="D262" t="s">
+      <c r="E262" t="s">
         <v>164</v>
       </c>
-      <c r="E262" t="s">
-        <v>165</v>
-      </c>
       <c r="F262" t="s">
-        <v>423</v>
+        <v>165</v>
       </c>
     </row>
     <row r="263" spans="1:6">
@@ -7597,16 +7597,16 @@
         <v>8</v>
       </c>
       <c r="C263" t="s">
+        <v>421</v>
+      </c>
+      <c r="D263" t="s">
         <v>438</v>
       </c>
-      <c r="D263" t="s">
+      <c r="E263" t="s">
         <v>439</v>
       </c>
-      <c r="E263" t="s">
+      <c r="F263" t="s">
         <v>184</v>
-      </c>
-      <c r="F263" t="s">
-        <v>423</v>
       </c>
     </row>
     <row r="264" spans="1:6">
@@ -7617,16 +7617,16 @@
         <v>8</v>
       </c>
       <c r="C264" t="s">
+        <v>421</v>
+      </c>
+      <c r="D264" t="s">
         <v>31</v>
       </c>
-      <c r="D264" t="s">
+      <c r="E264" t="s">
         <v>32</v>
       </c>
-      <c r="E264" t="s">
+      <c r="F264" t="s">
         <v>33</v>
-      </c>
-      <c r="F264" t="s">
-        <v>423</v>
       </c>
     </row>
     <row r="265" spans="1:6">
@@ -7637,7 +7637,7 @@
         <v>8</v>
       </c>
       <c r="C265" t="s">
-        <v>9</v>
+        <v>421</v>
       </c>
       <c r="D265" t="s">
         <v>10</v>
@@ -7646,7 +7646,7 @@
         <v>11</v>
       </c>
       <c r="F265" t="s">
-        <v>423</v>
+        <v>12</v>
       </c>
     </row>
     <row r="266" spans="1:6">
@@ -7657,16 +7657,16 @@
         <v>8</v>
       </c>
       <c r="C266" t="s">
+        <v>421</v>
+      </c>
+      <c r="D266" t="s">
         <v>443</v>
       </c>
-      <c r="D266" t="s">
+      <c r="E266" t="s">
         <v>444</v>
       </c>
-      <c r="E266" t="s">
-        <v>114</v>
-      </c>
       <c r="F266" t="s">
-        <v>423</v>
+        <v>115</v>
       </c>
     </row>
     <row r="267" spans="1:6">
@@ -7677,16 +7677,16 @@
         <v>8</v>
       </c>
       <c r="C267" t="s">
+        <v>446</v>
+      </c>
+      <c r="D267" t="s">
         <v>118</v>
       </c>
-      <c r="D267" t="s">
+      <c r="E267" t="s">
         <v>119</v>
       </c>
-      <c r="E267" t="s">
-        <v>114</v>
-      </c>
       <c r="F267" t="s">
-        <v>446</v>
+        <v>115</v>
       </c>
     </row>
     <row r="268" spans="1:6">
@@ -7697,16 +7697,16 @@
         <v>8</v>
       </c>
       <c r="C268" t="s">
-        <v>202</v>
+        <v>448</v>
       </c>
       <c r="D268" t="s">
         <v>203</v>
       </c>
       <c r="E268" t="s">
+        <v>204</v>
+      </c>
+      <c r="F268" t="s">
         <v>184</v>
-      </c>
-      <c r="F268" t="s">
-        <v>448</v>
       </c>
     </row>
     <row r="269" spans="1:6">
@@ -7717,16 +7717,16 @@
         <v>8</v>
       </c>
       <c r="C269" t="s">
+        <v>450</v>
+      </c>
+      <c r="D269" t="s">
         <v>118</v>
       </c>
-      <c r="D269" t="s">
+      <c r="E269" t="s">
         <v>119</v>
       </c>
-      <c r="E269" t="s">
-        <v>114</v>
-      </c>
       <c r="F269" t="s">
-        <v>450</v>
+        <v>115</v>
       </c>
     </row>
     <row r="270" spans="1:6">
@@ -7737,16 +7737,16 @@
         <v>8</v>
       </c>
       <c r="C270" t="s">
+        <v>450</v>
+      </c>
+      <c r="D270" t="s">
         <v>118</v>
       </c>
-      <c r="D270" t="s">
+      <c r="E270" t="s">
         <v>119</v>
       </c>
-      <c r="E270" t="s">
-        <v>114</v>
-      </c>
       <c r="F270" t="s">
-        <v>450</v>
+        <v>115</v>
       </c>
     </row>
     <row r="271" spans="1:6">
@@ -7763,10 +7763,10 @@
         <v>454</v>
       </c>
       <c r="E271" t="s">
-        <v>114</v>
+        <v>455</v>
       </c>
       <c r="F271" t="s">
-        <v>455</v>
+        <v>115</v>
       </c>
     </row>
     <row r="272" spans="1:6">
@@ -7783,10 +7783,10 @@
         <v>454</v>
       </c>
       <c r="E272" t="s">
-        <v>114</v>
+        <v>455</v>
       </c>
       <c r="F272" t="s">
-        <v>455</v>
+        <v>115</v>
       </c>
     </row>
     <row r="273" spans="1:6">
@@ -7803,10 +7803,10 @@
         <v>454</v>
       </c>
       <c r="E273" t="s">
-        <v>114</v>
+        <v>455</v>
       </c>
       <c r="F273" t="s">
-        <v>455</v>
+        <v>115</v>
       </c>
     </row>
     <row r="274" spans="1:6">
@@ -7823,10 +7823,10 @@
         <v>454</v>
       </c>
       <c r="E274" t="s">
-        <v>114</v>
+        <v>455</v>
       </c>
       <c r="F274" t="s">
-        <v>455</v>
+        <v>115</v>
       </c>
     </row>
     <row r="275" spans="1:6">
@@ -7843,10 +7843,10 @@
         <v>454</v>
       </c>
       <c r="E275" t="s">
-        <v>114</v>
+        <v>455</v>
       </c>
       <c r="F275" t="s">
-        <v>455</v>
+        <v>115</v>
       </c>
     </row>
     <row r="276" spans="1:6">
@@ -7863,10 +7863,10 @@
         <v>454</v>
       </c>
       <c r="E276" t="s">
-        <v>114</v>
+        <v>455</v>
       </c>
       <c r="F276" t="s">
-        <v>455</v>
+        <v>115</v>
       </c>
     </row>
     <row r="277" spans="1:6">
@@ -7883,10 +7883,10 @@
         <v>454</v>
       </c>
       <c r="E277" t="s">
-        <v>114</v>
+        <v>455</v>
       </c>
       <c r="F277" t="s">
-        <v>455</v>
+        <v>115</v>
       </c>
     </row>
     <row r="278" spans="1:6">
@@ -7897,16 +7897,16 @@
         <v>8</v>
       </c>
       <c r="C278" t="s">
-        <v>202</v>
+        <v>463</v>
       </c>
       <c r="D278" t="s">
         <v>203</v>
       </c>
       <c r="E278" t="s">
+        <v>204</v>
+      </c>
+      <c r="F278" t="s">
         <v>184</v>
-      </c>
-      <c r="F278" t="s">
-        <v>463</v>
       </c>
     </row>
     <row r="279" spans="1:6">
@@ -7917,16 +7917,16 @@
         <v>8</v>
       </c>
       <c r="C279" t="s">
-        <v>51</v>
+        <v>463</v>
       </c>
       <c r="D279" t="s">
         <v>52</v>
       </c>
       <c r="E279" t="s">
+        <v>53</v>
+      </c>
+      <c r="F279" t="s">
         <v>33</v>
-      </c>
-      <c r="F279" t="s">
-        <v>463</v>
       </c>
     </row>
     <row r="280" spans="1:6">
@@ -7937,7 +7937,7 @@
         <v>8</v>
       </c>
       <c r="C280" t="s">
-        <v>9</v>
+        <v>463</v>
       </c>
       <c r="D280" t="s">
         <v>10</v>
@@ -7946,7 +7946,7 @@
         <v>11</v>
       </c>
       <c r="F280" t="s">
-        <v>463</v>
+        <v>12</v>
       </c>
     </row>
     <row r="281" spans="1:6">
@@ -7957,16 +7957,16 @@
         <v>8</v>
       </c>
       <c r="C281" t="s">
+        <v>463</v>
+      </c>
+      <c r="D281" t="s">
         <v>170</v>
       </c>
-      <c r="D281" t="s">
+      <c r="E281" t="s">
         <v>171</v>
       </c>
-      <c r="E281" t="s">
-        <v>114</v>
-      </c>
       <c r="F281" t="s">
-        <v>463</v>
+        <v>115</v>
       </c>
     </row>
     <row r="282" spans="1:6">
@@ -7977,16 +7977,16 @@
         <v>8</v>
       </c>
       <c r="C282" t="s">
+        <v>463</v>
+      </c>
+      <c r="D282" t="s">
         <v>124</v>
       </c>
-      <c r="D282" t="s">
+      <c r="E282" t="s">
         <v>125</v>
       </c>
-      <c r="E282" t="s">
+      <c r="F282" t="s">
         <v>126</v>
-      </c>
-      <c r="F282" t="s">
-        <v>463</v>
       </c>
     </row>
     <row r="283" spans="1:6">
@@ -7997,16 +7997,16 @@
         <v>8</v>
       </c>
       <c r="C283" t="s">
-        <v>363</v>
+        <v>469</v>
       </c>
       <c r="D283" t="s">
         <v>398</v>
       </c>
       <c r="E283" t="s">
-        <v>165</v>
+        <v>365</v>
       </c>
       <c r="F283" t="s">
-        <v>469</v>
+        <v>165</v>
       </c>
     </row>
     <row r="284" spans="1:6">
@@ -8017,16 +8017,16 @@
         <v>8</v>
       </c>
       <c r="C284" t="s">
+        <v>471</v>
+      </c>
+      <c r="D284" t="s">
         <v>124</v>
       </c>
-      <c r="D284" t="s">
+      <c r="E284" t="s">
         <v>125</v>
       </c>
-      <c r="E284" t="s">
+      <c r="F284" t="s">
         <v>126</v>
-      </c>
-      <c r="F284" t="s">
-        <v>471</v>
       </c>
     </row>
     <row r="285" spans="1:6">
@@ -8037,16 +8037,16 @@
         <v>8</v>
       </c>
       <c r="C285" t="s">
+        <v>473</v>
+      </c>
+      <c r="D285" t="s">
         <v>170</v>
       </c>
-      <c r="D285" t="s">
+      <c r="E285" t="s">
         <v>171</v>
       </c>
-      <c r="E285" t="s">
-        <v>114</v>
-      </c>
       <c r="F285" t="s">
-        <v>473</v>
+        <v>115</v>
       </c>
     </row>
     <row r="286" spans="1:6">
@@ -8057,16 +8057,16 @@
         <v>8</v>
       </c>
       <c r="C286" t="s">
+        <v>475</v>
+      </c>
+      <c r="D286" t="s">
         <v>438</v>
       </c>
-      <c r="D286" t="s">
+      <c r="E286" t="s">
         <v>439</v>
       </c>
-      <c r="E286" t="s">
+      <c r="F286" t="s">
         <v>184</v>
-      </c>
-      <c r="F286" t="s">
-        <v>475</v>
       </c>
     </row>
     <row r="287" spans="1:6">
@@ -8077,16 +8077,16 @@
         <v>8</v>
       </c>
       <c r="C287" t="s">
+        <v>475</v>
+      </c>
+      <c r="D287" t="s">
         <v>438</v>
       </c>
-      <c r="D287" t="s">
+      <c r="E287" t="s">
         <v>439</v>
       </c>
-      <c r="E287" t="s">
+      <c r="F287" t="s">
         <v>184</v>
-      </c>
-      <c r="F287" t="s">
-        <v>475</v>
       </c>
     </row>
     <row r="288" spans="1:6">
@@ -8097,16 +8097,16 @@
         <v>8</v>
       </c>
       <c r="C288" t="s">
+        <v>475</v>
+      </c>
+      <c r="D288" t="s">
         <v>41</v>
       </c>
-      <c r="D288" t="s">
+      <c r="E288" t="s">
         <v>42</v>
       </c>
-      <c r="E288" t="s">
-        <v>11</v>
-      </c>
       <c r="F288" t="s">
-        <v>475</v>
+        <v>12</v>
       </c>
     </row>
     <row r="289" spans="1:6">
@@ -8117,16 +8117,16 @@
         <v>8</v>
       </c>
       <c r="C289" t="s">
+        <v>475</v>
+      </c>
+      <c r="D289" t="s">
         <v>31</v>
       </c>
-      <c r="D289" t="s">
+      <c r="E289" t="s">
         <v>32</v>
       </c>
-      <c r="E289" t="s">
+      <c r="F289" t="s">
         <v>33</v>
-      </c>
-      <c r="F289" t="s">
-        <v>475</v>
       </c>
     </row>
     <row r="290" spans="1:6">
@@ -8137,16 +8137,16 @@
         <v>8</v>
       </c>
       <c r="C290" t="s">
+        <v>475</v>
+      </c>
+      <c r="D290" t="s">
         <v>31</v>
       </c>
-      <c r="D290" t="s">
+      <c r="E290" t="s">
         <v>32</v>
       </c>
-      <c r="E290" t="s">
+      <c r="F290" t="s">
         <v>33</v>
-      </c>
-      <c r="F290" t="s">
-        <v>475</v>
       </c>
     </row>
     <row r="291" spans="1:6">
@@ -8157,16 +8157,16 @@
         <v>8</v>
       </c>
       <c r="C291" t="s">
+        <v>475</v>
+      </c>
+      <c r="D291" t="s">
         <v>170</v>
       </c>
-      <c r="D291" t="s">
+      <c r="E291" t="s">
         <v>171</v>
       </c>
-      <c r="E291" t="s">
-        <v>114</v>
-      </c>
       <c r="F291" t="s">
-        <v>475</v>
+        <v>115</v>
       </c>
     </row>
     <row r="292" spans="1:6">
@@ -8177,16 +8177,16 @@
         <v>8</v>
       </c>
       <c r="C292" t="s">
+        <v>475</v>
+      </c>
+      <c r="D292" t="s">
         <v>170</v>
       </c>
-      <c r="D292" t="s">
+      <c r="E292" t="s">
         <v>171</v>
       </c>
-      <c r="E292" t="s">
-        <v>114</v>
-      </c>
       <c r="F292" t="s">
-        <v>475</v>
+        <v>115</v>
       </c>
     </row>
     <row r="293" spans="1:6">
@@ -8197,16 +8197,16 @@
         <v>8</v>
       </c>
       <c r="C293" t="s">
+        <v>475</v>
+      </c>
+      <c r="D293" t="s">
         <v>170</v>
       </c>
-      <c r="D293" t="s">
+      <c r="E293" t="s">
         <v>171</v>
       </c>
-      <c r="E293" t="s">
-        <v>114</v>
-      </c>
       <c r="F293" t="s">
-        <v>475</v>
+        <v>115</v>
       </c>
     </row>
     <row r="294" spans="1:6">
@@ -8217,16 +8217,16 @@
         <v>8</v>
       </c>
       <c r="C294" t="s">
+        <v>475</v>
+      </c>
+      <c r="D294" t="s">
         <v>170</v>
       </c>
-      <c r="D294" t="s">
+      <c r="E294" t="s">
         <v>171</v>
       </c>
-      <c r="E294" t="s">
-        <v>114</v>
-      </c>
       <c r="F294" t="s">
-        <v>475</v>
+        <v>115</v>
       </c>
     </row>
     <row r="295" spans="1:6">
@@ -8237,16 +8237,16 @@
         <v>8</v>
       </c>
       <c r="C295" t="s">
+        <v>485</v>
+      </c>
+      <c r="D295" t="s">
         <v>170</v>
       </c>
-      <c r="D295" t="s">
+      <c r="E295" t="s">
         <v>171</v>
       </c>
-      <c r="E295" t="s">
-        <v>114</v>
-      </c>
       <c r="F295" t="s">
-        <v>485</v>
+        <v>115</v>
       </c>
     </row>
     <row r="296" spans="1:6">
@@ -8257,16 +8257,16 @@
         <v>8</v>
       </c>
       <c r="C296" t="s">
+        <v>485</v>
+      </c>
+      <c r="D296" t="s">
         <v>170</v>
       </c>
-      <c r="D296" t="s">
+      <c r="E296" t="s">
         <v>171</v>
       </c>
-      <c r="E296" t="s">
-        <v>114</v>
-      </c>
       <c r="F296" t="s">
-        <v>485</v>
+        <v>115</v>
       </c>
     </row>
   </sheetData>

--- a/api/2/xlsx/fr/SectorCOFOG.xlsx
+++ b/api/2/xlsx/fr/SectorCOFOG.xlsx
@@ -22,75 +22,75 @@
     <t>status</t>
   </si>
   <si>
+    <t>codeforiati:cofog-division</t>
+  </si>
+  <si>
     <t>codeforiati:group-code</t>
   </si>
   <si>
+    <t>codeforiati:category-code</t>
+  </si>
+  <si>
+    <t>codeforiati:cofog-group</t>
+  </si>
+  <si>
     <t>codeforiati:cofog-class</t>
   </si>
   <si>
-    <t>codeforiati:cofog-group</t>
-  </si>
-  <si>
-    <t>codeforiati:cofog-division</t>
-  </si>
-  <si>
-    <t>codeforiati:category-code</t>
-  </si>
-  <si>
     <t>11110</t>
   </si>
   <si>
     <t>active</t>
   </si>
   <si>
+    <t>09 - Education</t>
+  </si>
+  <si>
     <t>110</t>
   </si>
   <si>
+    <t>111</t>
+  </si>
+  <si>
+    <t>09.8 - Education n.e.c.</t>
+  </si>
+  <si>
     <t>09.8.0 - Education n.e.c. (CS)</t>
   </si>
   <si>
-    <t>09.8 - Education n.e.c.</t>
-  </si>
-  <si>
-    <t>09 - Education</t>
-  </si>
-  <si>
-    <t>111</t>
-  </si>
-  <si>
     <t>11120</t>
   </si>
   <si>
+    <t>09.6 - Subsidiary services to education</t>
+  </si>
+  <si>
     <t>09.6.0 - Subsidiary services to education (IS)</t>
   </si>
   <si>
-    <t>09.6 - Subsidiary services to education</t>
-  </si>
-  <si>
     <t>11130</t>
   </si>
   <si>
     <t>11182</t>
   </si>
   <si>
+    <t>09.7 - R&amp;D Education</t>
+  </si>
+  <si>
     <t>09.7.0 - R&amp;D Education (CS)</t>
   </si>
   <si>
-    <t>09.7 - R&amp;D Education</t>
-  </si>
-  <si>
     <t>11220</t>
   </si>
   <si>
+    <t>112</t>
+  </si>
+  <si>
+    <t>09.1 - Pre‐primary and primary education</t>
+  </si>
+  <si>
     <t>09.1.2 - Primary education (IS)</t>
   </si>
   <si>
-    <t>09.1 - Pre‐primary and primary education</t>
-  </si>
-  <si>
-    <t>112</t>
-  </si>
-  <si>
     <t>11230</t>
   </si>
   <si>
@@ -109,99 +109,99 @@
     <t>11250</t>
   </si>
   <si>
+    <t>07 - Health</t>
+  </si>
+  <si>
+    <t>07.4 - Public health services</t>
+  </si>
+  <si>
     <t>07.4.0 - Public health services (IS)</t>
   </si>
   <si>
-    <t>07.4 - Public health services</t>
-  </si>
-  <si>
-    <t>07 - Health</t>
-  </si>
-  <si>
     <t>11260</t>
   </si>
   <si>
+    <t>09.2 - Secondary education</t>
+  </si>
+  <si>
     <t>09.2.1 - Lower‐secondary education (IS)</t>
   </si>
   <si>
-    <t>09.2 - Secondary education</t>
-  </si>
-  <si>
     <t>11320</t>
   </si>
   <si>
+    <t>113</t>
+  </si>
+  <si>
     <t>09.2.2 - Upper‐secondary education (IS)</t>
   </si>
   <si>
-    <t>113</t>
-  </si>
-  <si>
     <t>11330</t>
   </si>
   <si>
+    <t>09.5 - Education not definable by level</t>
+  </si>
+  <si>
     <t>09.5.0 - Education not definable by level (IS)</t>
   </si>
   <si>
-    <t>09.5 - Education not definable by level</t>
-  </si>
-  <si>
     <t>11420</t>
   </si>
   <si>
+    <t>114</t>
+  </si>
+  <si>
+    <t>09.4 - Tertiary education</t>
+  </si>
+  <si>
     <t>09.4.1 - First stage of tertiary education (IS)</t>
   </si>
   <si>
-    <t>09.4 - Tertiary education</t>
-  </si>
-  <si>
-    <t>114</t>
-  </si>
-  <si>
     <t>11430</t>
   </si>
   <si>
+    <t>09.3 - Post‐secondary non‐tertiary education</t>
+  </si>
+  <si>
     <t>09.3.0 - Post‐secondary non‐tertiary education (IS)</t>
   </si>
   <si>
-    <t>09.3 - Post‐secondary non‐tertiary education</t>
-  </si>
-  <si>
     <t>12110</t>
   </si>
   <si>
     <t>120</t>
   </si>
   <si>
+    <t>121</t>
+  </si>
+  <si>
+    <t>07.6 - Health n.e.c.</t>
+  </si>
+  <si>
     <t>07.6.0 - Health n.e.c. (CS)</t>
   </si>
   <si>
-    <t>07.6 - Health n.e.c.</t>
-  </si>
-  <si>
-    <t>121</t>
-  </si>
-  <si>
     <t>12181</t>
   </si>
   <si>
     <t>12182</t>
   </si>
   <si>
+    <t>07.5 - R&amp;D Health</t>
+  </si>
+  <si>
     <t>07.5.0 - R&amp;D Health (CS)</t>
   </si>
   <si>
-    <t>07.5 - R&amp;D Health</t>
-  </si>
-  <si>
     <t>12191</t>
   </si>
   <si>
+    <t>07.2 - Outpatient services</t>
+  </si>
+  <si>
     <t>07.2.1 - General medical services (IS)</t>
   </si>
   <si>
-    <t>07.2 - Outpatient services</t>
-  </si>
-  <si>
     <t>12196</t>
   </si>
   <si>
@@ -214,12 +214,12 @@
     <t>12230</t>
   </si>
   <si>
+    <t>07.3 - Hospital services</t>
+  </si>
+  <si>
     <t>07.3.1 - General hospital services (IS)</t>
   </si>
   <si>
-    <t>07.3 - Hospital services</t>
-  </si>
-  <si>
     <t>12240</t>
   </si>
   <si>
@@ -286,30 +286,30 @@
     <t>14010</t>
   </si>
   <si>
+    <t>06 - Housing and community amenities</t>
+  </si>
+  <si>
     <t>140</t>
   </si>
   <si>
+    <t>06.3 - Water supply</t>
+  </si>
+  <si>
     <t>06.3.0 - Water supply (CS)</t>
   </si>
   <si>
-    <t>06.3 - Water supply</t>
-  </si>
-  <si>
-    <t>06 - Housing and community amenities</t>
-  </si>
-  <si>
     <t>14015</t>
   </si>
   <si>
+    <t>05 - Environmental protection</t>
+  </si>
+  <si>
+    <t>05.6 - Environmental protection n.e.c.</t>
+  </si>
+  <si>
     <t>05.6.0 - Environmental protection n.e.c. (CS)</t>
   </si>
   <si>
-    <t>05.6 - Environmental protection n.e.c.</t>
-  </si>
-  <si>
-    <t>05 - Environmental protection</t>
-  </si>
-  <si>
     <t>14020</t>
   </si>
   <si>
@@ -319,12 +319,12 @@
     <t>14022</t>
   </si>
   <si>
+    <t>05.2 - Waste water management</t>
+  </si>
+  <si>
     <t>05.2.0 - Waste water management (CS)</t>
   </si>
   <si>
-    <t>05.2 - Waste water management</t>
-  </si>
-  <si>
     <t>14030</t>
   </si>
   <si>
@@ -340,63 +340,63 @@
     <t>14050</t>
   </si>
   <si>
+    <t>05.1 - Waste management</t>
+  </si>
+  <si>
     <t>05.1.0 - Waste management (CS)</t>
   </si>
   <si>
-    <t>05.1 - Waste management</t>
-  </si>
-  <si>
     <t>14081</t>
   </si>
   <si>
     <t>15110</t>
   </si>
   <si>
+    <t>01 - General public services</t>
+  </si>
+  <si>
     <t>150</t>
   </si>
   <si>
+    <t>151</t>
+  </si>
+  <si>
+    <t>01.3 - General services</t>
+  </si>
+  <si>
     <t>01.3.1 - General personnel services (CS)</t>
   </si>
   <si>
-    <t>01.3 - General services</t>
-  </si>
-  <si>
-    <t>01 - General public services</t>
-  </si>
-  <si>
-    <t>151</t>
-  </si>
-  <si>
     <t>15111</t>
   </si>
   <si>
+    <t>01.1 - Executive and legislative organs, financial and fiscal affairs, external affairs</t>
+  </si>
+  <si>
     <t>01.1.2 - Financial and fiscal affairs (CS)</t>
   </si>
   <si>
-    <t>01.1 - Executive and legislative organs, financial and fiscal affairs, external affairs</t>
-  </si>
-  <si>
     <t>15112</t>
   </si>
   <si>
+    <t>01.8 - Transfers of a general character between different levels of government</t>
+  </si>
+  <si>
     <t>01.8.0 - Transfers of a general character between different levels of government (CS)</t>
   </si>
   <si>
-    <t>01.8 - Transfers of a general character between different levels of government</t>
-  </si>
-  <si>
     <t>15113</t>
   </si>
   <si>
+    <t>03 - Public order and safety</t>
+  </si>
+  <si>
+    <t>03.6 - Public order and safety n.e.c.</t>
+  </si>
+  <si>
     <t>03.6.0 - Public order and safety n.e.c. (CS)</t>
   </si>
   <si>
-    <t>03.6 - Public order and safety n.e.c.</t>
-  </si>
-  <si>
-    <t>03 - Public order and safety</t>
-  </si>
-  <si>
     <t>15114</t>
   </si>
   <si>
@@ -424,12 +424,12 @@
     <t>15123</t>
   </si>
   <si>
+    <t>01.2 - Foreign economic aid</t>
+  </si>
+  <si>
     <t>01.2.2 - Economic aid routed through international organizations (CS)</t>
   </si>
   <si>
-    <t>01.2 - Foreign economic aid</t>
-  </si>
-  <si>
     <t>15124</t>
   </si>
   <si>
@@ -460,30 +460,30 @@
     <t>15131</t>
   </si>
   <si>
+    <t>03.3 - Law courts</t>
+  </si>
+  <si>
     <t>03.3.0 - Law courts (CS)</t>
   </si>
   <si>
-    <t>03.3 - Law courts</t>
-  </si>
-  <si>
     <t>15132</t>
   </si>
   <si>
+    <t>03.1 - Police services</t>
+  </si>
+  <si>
     <t>03.1.0 - Police services (CS)</t>
   </si>
   <si>
-    <t>03.1 - Police services</t>
-  </si>
-  <si>
     <t>15133</t>
   </si>
   <si>
+    <t>03.2 - Fire‐protection services</t>
+  </si>
+  <si>
     <t>03.2.0 - Fire‐protection services (CS)</t>
   </si>
   <si>
-    <t>03.2 - Fire‐protection services</t>
-  </si>
-  <si>
     <t>15134</t>
   </si>
   <si>
@@ -496,24 +496,24 @@
     <t>15137</t>
   </si>
   <si>
+    <t>03.4 - Prisons</t>
+  </si>
+  <si>
     <t>03.4.0 - Prisons (CS)</t>
   </si>
   <si>
-    <t>03.4 - Prisons</t>
-  </si>
-  <si>
     <t>15142</t>
   </si>
   <si>
+    <t>04 - Economic affairs</t>
+  </si>
+  <si>
+    <t>04.1 - General economic, commercial and labour affairs</t>
+  </si>
+  <si>
     <t>04.1.1 - General economic and commercial affairs (CS)</t>
   </si>
   <si>
-    <t>04.1 - General economic, commercial and labour affairs</t>
-  </si>
-  <si>
-    <t>04 - Economic affairs</t>
-  </si>
-  <si>
     <t>15143</t>
   </si>
   <si>
@@ -526,12 +526,12 @@
     <t>15151</t>
   </si>
   <si>
+    <t>01.6 - General public services n.e.c.</t>
+  </si>
+  <si>
     <t>01.6.0 - General public services n.e.c. (CS)</t>
   </si>
   <si>
-    <t>01.6 - General public services n.e.c.</t>
-  </si>
-  <si>
     <t>15152</t>
   </si>
   <si>
@@ -541,12 +541,12 @@
     <t>15153</t>
   </si>
   <si>
+    <t>04.6 - Communication</t>
+  </si>
+  <si>
     <t>04.6.0 - Communication (CS)</t>
   </si>
   <si>
-    <t>04.6 - Communication</t>
-  </si>
-  <si>
     <t>15154</t>
   </si>
   <si>
@@ -562,15 +562,15 @@
     <t>15170</t>
   </si>
   <si>
+    <t>10 - Social protection</t>
+  </si>
+  <si>
+    <t>10.7 - Social exclusion n.e.c.</t>
+  </si>
+  <si>
     <t>10.7.0 - Social exclusion n.e.c. (IS)</t>
   </si>
   <si>
-    <t>10.7 - Social exclusion n.e.c.</t>
-  </si>
-  <si>
-    <t>10 - Social protection</t>
-  </si>
-  <si>
     <t>15180</t>
   </si>
   <si>
@@ -583,12 +583,12 @@
     <t>15196</t>
   </si>
   <si>
+    <t>01.5 - R&amp;D General public services</t>
+  </si>
+  <si>
     <t>01.5.0 - R&amp;D General public services (CS)</t>
   </si>
   <si>
-    <t>01.5 - R&amp;D General public services</t>
-  </si>
-  <si>
     <t>15210</t>
   </si>
   <si>
@@ -601,15 +601,15 @@
     <t>15230</t>
   </si>
   <si>
+    <t>02 - Defence</t>
+  </si>
+  <si>
+    <t>02.3 - Foreign military aid</t>
+  </si>
+  <si>
     <t>02.3.0 - Foreign military aid (CS)</t>
   </si>
   <si>
-    <t>02.3 - Foreign military aid</t>
-  </si>
-  <si>
-    <t>02 - Defence</t>
-  </si>
-  <si>
     <t>15240</t>
   </si>
   <si>
@@ -625,12 +625,12 @@
     <t>160</t>
   </si>
   <si>
+    <t>10.9 - Social protection n.e.c.</t>
+  </si>
+  <si>
     <t>10.9.0 - Social protection n.e.c. (CS)</t>
   </si>
   <si>
-    <t>10.9 - Social protection n.e.c.</t>
-  </si>
-  <si>
     <t>16011</t>
   </si>
   <si>
@@ -640,12 +640,12 @@
     <t>16013</t>
   </si>
   <si>
+    <t>10.2 - Old age</t>
+  </si>
+  <si>
     <t>10.2.0 - Old age (IS)</t>
   </si>
   <si>
-    <t>10.2 - Old age</t>
-  </si>
-  <si>
     <t>16014</t>
   </si>
   <si>
@@ -655,45 +655,45 @@
     <t>16020</t>
   </si>
   <si>
+    <t>10.5 - Unemployment</t>
+  </si>
+  <si>
     <t>10.5.0 - Unemployment (IS)</t>
   </si>
   <si>
-    <t>10.5 - Unemployment</t>
-  </si>
-  <si>
     <t>16030</t>
   </si>
   <si>
+    <t>06.6 - Housing and community amenities n.e.c.</t>
+  </si>
+  <si>
     <t>06.6.0 - Housing and community amenities n.e.c. (CS)</t>
   </si>
   <si>
-    <t>06.6 - Housing and community amenities n.e.c.</t>
-  </si>
-  <si>
     <t>16040</t>
   </si>
   <si>
+    <t>06.1 - Housing development</t>
+  </si>
+  <si>
     <t>06.1.0 - Housing development (CS)</t>
   </si>
   <si>
-    <t>06.1 - Housing development</t>
-  </si>
-  <si>
     <t>16050</t>
   </si>
   <si>
     <t>16061</t>
   </si>
   <si>
+    <t>08 - Recreation, culture and religion</t>
+  </si>
+  <si>
+    <t>08.2 - Cultural services</t>
+  </si>
+  <si>
     <t>08.2.0 - Cultural services (IS)</t>
   </si>
   <si>
-    <t>08.2 - Cultural services</t>
-  </si>
-  <si>
-    <t>08 - Recreation, culture and religion</t>
-  </si>
-  <si>
     <t>16062</t>
   </si>
   <si>
@@ -706,12 +706,12 @@
     <t>16065</t>
   </si>
   <si>
+    <t>08.1 - Recreational and sporting services</t>
+  </si>
+  <si>
     <t>08.1.0 - Recreational and sporting services (IS)</t>
   </si>
   <si>
-    <t>08.1 - Recreational and sporting services</t>
-  </si>
-  <si>
     <t>16066</t>
   </si>
   <si>
@@ -742,12 +742,12 @@
     <t>21020</t>
   </si>
   <si>
+    <t>04.5 - Transport</t>
+  </si>
+  <si>
     <t>04.5.1 - Road transport (CS)</t>
   </si>
   <si>
-    <t>04.5 - Transport</t>
-  </si>
-  <si>
     <t>21021</t>
   </si>
   <si>
@@ -781,12 +781,12 @@
     <t>21061</t>
   </si>
   <si>
+    <t>04.7 - Other industries</t>
+  </si>
+  <si>
     <t>04.7.1 - Distributive trades, storage and warehousing (CS)</t>
   </si>
   <si>
-    <t>04.7 - Other industries</t>
-  </si>
-  <si>
     <t>21081</t>
   </si>
   <si>
@@ -811,12 +811,12 @@
     <t>22030</t>
   </si>
   <si>
+    <t>08.3 - Broadcasting and publishing services</t>
+  </si>
+  <si>
     <t>08.3.0 - Broadcasting and publishing services (CS)</t>
   </si>
   <si>
-    <t>08.3 - Broadcasting and publishing services</t>
-  </si>
-  <si>
     <t>22040</t>
   </si>
   <si>
@@ -826,27 +826,27 @@
     <t>230</t>
   </si>
   <si>
+    <t>231</t>
+  </si>
+  <si>
+    <t>04.3 - Fuel and energy</t>
+  </si>
+  <si>
     <t>04.3.5 - Electricity (CS)</t>
   </si>
   <si>
-    <t>04.3 - Fuel and energy</t>
-  </si>
-  <si>
-    <t>231</t>
-  </si>
-  <si>
     <t>23111</t>
   </si>
   <si>
     <t>23112</t>
   </si>
   <si>
+    <t>04.8 - R&amp;D Economic affairs</t>
+  </si>
+  <si>
     <t>04.8.3 - R&amp;D Fuel and energy (CS)</t>
   </si>
   <si>
-    <t>04.8 - R&amp;D Economic affairs</t>
-  </si>
-  <si>
     <t>23181</t>
   </si>
   <si>
@@ -919,12 +919,12 @@
     <t>23510</t>
   </si>
   <si>
+    <t>235</t>
+  </si>
+  <si>
     <t>04.3.3 - Nuclear fuel (CS)</t>
   </si>
   <si>
-    <t>235</t>
-  </si>
-  <si>
     <t>23610</t>
   </si>
   <si>
@@ -994,15 +994,15 @@
     <t>310</t>
   </si>
   <si>
+    <t>311</t>
+  </si>
+  <si>
+    <t>04.2 - Agriculture, forestry, fishing and hunting</t>
+  </si>
+  <si>
     <t>04.2.1 - Agriculture (CS)</t>
   </si>
   <si>
-    <t>04.2 - Agriculture, forestry, fishing and hunting</t>
-  </si>
-  <si>
-    <t>311</t>
-  </si>
-  <si>
     <t>31120</t>
   </si>
   <si>
@@ -1060,12 +1060,12 @@
     <t>31210</t>
   </si>
   <si>
+    <t>312</t>
+  </si>
+  <si>
     <t>04.2.2 - Forestry (CS)</t>
   </si>
   <si>
-    <t>312</t>
-  </si>
-  <si>
     <t>31220</t>
   </si>
   <si>
@@ -1084,12 +1084,12 @@
     <t>31310</t>
   </si>
   <si>
+    <t>313</t>
+  </si>
+  <si>
     <t>04.2.3 - Fishing and hunting (CS)</t>
   </si>
   <si>
-    <t>313</t>
-  </si>
-  <si>
     <t>31320</t>
   </si>
   <si>
@@ -1108,15 +1108,15 @@
     <t>320</t>
   </si>
   <si>
+    <t>321</t>
+  </si>
+  <si>
+    <t>04.4 - Mining, manufacturing and construction</t>
+  </si>
+  <si>
     <t>04.4.2 - Manufacturing (CS)</t>
   </si>
   <si>
-    <t>04.4 - Mining, manufacturing and construction</t>
-  </si>
-  <si>
-    <t>321</t>
-  </si>
-  <si>
     <t>32120</t>
   </si>
   <si>
@@ -1174,12 +1174,12 @@
     <t>32210</t>
   </si>
   <si>
+    <t>322</t>
+  </si>
+  <si>
     <t>04.4.1 - Mining of mineral resources other than mineral fuels (CS)</t>
   </si>
   <si>
-    <t>322</t>
-  </si>
-  <si>
     <t>32220</t>
   </si>
   <si>
@@ -1210,12 +1210,12 @@
     <t>32310</t>
   </si>
   <si>
+    <t>323</t>
+  </si>
+  <si>
     <t>04.4.3 - Construction (CS)</t>
   </si>
   <si>
-    <t>323</t>
-  </si>
-  <si>
     <t>33110</t>
   </si>
   <si>
@@ -1243,12 +1243,12 @@
     <t>33210</t>
   </si>
   <si>
+    <t>332</t>
+  </si>
+  <si>
     <t>04.7.3 - Tourism (CS)</t>
   </si>
   <si>
-    <t>332</t>
-  </si>
-  <si>
     <t>41010</t>
   </si>
   <si>
@@ -1261,12 +1261,12 @@
     <t>41030</t>
   </si>
   <si>
+    <t>05.4 - Protection of biodiversity and landscape</t>
+  </si>
+  <si>
     <t>05.4.0 - Protection of biodiversity and landscape (CS)</t>
   </si>
   <si>
-    <t>05.4 - Protection of biodiversity and landscape</t>
-  </si>
-  <si>
     <t>41040</t>
   </si>
   <si>
@@ -1282,24 +1282,24 @@
     <t>430</t>
   </si>
   <si>
+    <t>04.9 - Economic affairs n.e.c.</t>
+  </si>
+  <si>
     <t>04.9.0 - Economic affairs n.e.c. (CS)</t>
   </si>
   <si>
-    <t>04.9 - Economic affairs n.e.c.</t>
-  </si>
-  <si>
     <t>43030</t>
   </si>
   <si>
     <t>43031</t>
   </si>
   <si>
+    <t>06.2 - Community development</t>
+  </si>
+  <si>
     <t>06.2.0 - Community development (CS)</t>
   </si>
   <si>
-    <t>06.2 - Community development</t>
-  </si>
-  <si>
     <t>43032</t>
   </si>
   <si>
@@ -1318,24 +1318,24 @@
     <t>43060</t>
   </si>
   <si>
+    <t>02.2 - Civil defence</t>
+  </si>
+  <si>
     <t>02.2.0 - Civil defence (CS)</t>
   </si>
   <si>
-    <t>02.2 - Civil defence</t>
-  </si>
-  <si>
     <t>43071</t>
   </si>
   <si>
     <t>43072</t>
   </si>
   <si>
+    <t>10.4 - Family and children</t>
+  </si>
+  <si>
     <t>10.4.0 - Family and children (IS)</t>
   </si>
   <si>
-    <t>10.4 - Family and children</t>
-  </si>
-  <si>
     <t>43073</t>
   </si>
   <si>
@@ -1345,12 +1345,12 @@
     <t>43082</t>
   </si>
   <si>
+    <t>01.4 - Basic research</t>
+  </si>
+  <si>
     <t>01.4.0 - Basic research (CS)</t>
   </si>
   <si>
-    <t>01.4 - Basic research</t>
-  </si>
-  <si>
     <t>51010</t>
   </si>
   <si>
@@ -1378,10 +1378,10 @@
     <t>600</t>
   </si>
   <si>
+    <t>01.7 - Public debt transactions</t>
+  </si>
+  <si>
     <t>01.7.0 - Public debt transactions (CS)</t>
-  </si>
-  <si>
-    <t>01.7 - Public debt transactions</t>
   </si>
   <si>
     <t>60020</t>
@@ -1866,16 +1866,16 @@
         <v>9</v>
       </c>
       <c r="D3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F3" t="s">
         <v>15</v>
       </c>
-      <c r="E3" t="s">
+      <c r="G3" t="s">
         <v>16</v>
-      </c>
-      <c r="F3" t="s">
-        <v>12</v>
-      </c>
-      <c r="G3" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -1912,16 +1912,16 @@
         <v>9</v>
       </c>
       <c r="D5" t="s">
+        <v>10</v>
+      </c>
+      <c r="E5" t="s">
+        <v>11</v>
+      </c>
+      <c r="F5" t="s">
         <v>19</v>
       </c>
-      <c r="E5" t="s">
+      <c r="G5" t="s">
         <v>20</v>
-      </c>
-      <c r="F5" t="s">
-        <v>12</v>
-      </c>
-      <c r="G5" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -1935,13 +1935,13 @@
         <v>9</v>
       </c>
       <c r="D6" t="s">
+        <v>10</v>
+      </c>
+      <c r="E6" t="s">
         <v>22</v>
       </c>
-      <c r="E6" t="s">
+      <c r="F6" t="s">
         <v>23</v>
-      </c>
-      <c r="F6" t="s">
-        <v>12</v>
       </c>
       <c r="G6" t="s">
         <v>24</v>
@@ -1961,13 +1961,13 @@
         <v>10</v>
       </c>
       <c r="E7" t="s">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="F7" t="s">
         <v>12</v>
       </c>
       <c r="G7" t="s">
-        <v>24</v>
+        <v>13</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -1981,13 +1981,13 @@
         <v>9</v>
       </c>
       <c r="D8" t="s">
+        <v>10</v>
+      </c>
+      <c r="E8" t="s">
         <v>22</v>
       </c>
-      <c r="E8" t="s">
+      <c r="F8" t="s">
         <v>23</v>
-      </c>
-      <c r="F8" t="s">
-        <v>12</v>
       </c>
       <c r="G8" t="s">
         <v>24</v>
@@ -2004,13 +2004,13 @@
         <v>9</v>
       </c>
       <c r="D9" t="s">
+        <v>10</v>
+      </c>
+      <c r="E9" t="s">
         <v>22</v>
       </c>
-      <c r="E9" t="s">
+      <c r="F9" t="s">
         <v>23</v>
-      </c>
-      <c r="F9" t="s">
-        <v>12</v>
       </c>
       <c r="G9" t="s">
         <v>24</v>
@@ -2027,16 +2027,16 @@
         <v>9</v>
       </c>
       <c r="D10" t="s">
+        <v>10</v>
+      </c>
+      <c r="E10" t="s">
+        <v>22</v>
+      </c>
+      <c r="F10" t="s">
+        <v>23</v>
+      </c>
+      <c r="G10" t="s">
         <v>29</v>
-      </c>
-      <c r="E10" t="s">
-        <v>23</v>
-      </c>
-      <c r="F10" t="s">
-        <v>12</v>
-      </c>
-      <c r="G10" t="s">
-        <v>24</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -2047,19 +2047,19 @@
         <v>8</v>
       </c>
       <c r="C11" t="s">
-        <v>9</v>
+        <v>31</v>
       </c>
       <c r="D11" t="s">
-        <v>31</v>
+        <v>10</v>
       </c>
       <c r="E11" t="s">
+        <v>22</v>
+      </c>
+      <c r="F11" t="s">
         <v>32</v>
       </c>
-      <c r="F11" t="s">
+      <c r="G11" t="s">
         <v>33</v>
-      </c>
-      <c r="G11" t="s">
-        <v>24</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -2073,16 +2073,16 @@
         <v>9</v>
       </c>
       <c r="D12" t="s">
+        <v>10</v>
+      </c>
+      <c r="E12" t="s">
+        <v>22</v>
+      </c>
+      <c r="F12" t="s">
         <v>35</v>
       </c>
-      <c r="E12" t="s">
+      <c r="G12" t="s">
         <v>36</v>
-      </c>
-      <c r="F12" t="s">
-        <v>12</v>
-      </c>
-      <c r="G12" t="s">
-        <v>24</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -2096,13 +2096,13 @@
         <v>9</v>
       </c>
       <c r="D13" t="s">
+        <v>10</v>
+      </c>
+      <c r="E13" t="s">
         <v>38</v>
       </c>
-      <c r="E13" t="s">
-        <v>36</v>
-      </c>
       <c r="F13" t="s">
-        <v>12</v>
+        <v>35</v>
       </c>
       <c r="G13" t="s">
         <v>39</v>
@@ -2119,16 +2119,16 @@
         <v>9</v>
       </c>
       <c r="D14" t="s">
+        <v>10</v>
+      </c>
+      <c r="E14" t="s">
+        <v>38</v>
+      </c>
+      <c r="F14" t="s">
         <v>41</v>
       </c>
-      <c r="E14" t="s">
+      <c r="G14" t="s">
         <v>42</v>
-      </c>
-      <c r="F14" t="s">
-        <v>12</v>
-      </c>
-      <c r="G14" t="s">
-        <v>39</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -2142,13 +2142,13 @@
         <v>9</v>
       </c>
       <c r="D15" t="s">
+        <v>10</v>
+      </c>
+      <c r="E15" t="s">
         <v>44</v>
       </c>
-      <c r="E15" t="s">
+      <c r="F15" t="s">
         <v>45</v>
-      </c>
-      <c r="F15" t="s">
-        <v>12</v>
       </c>
       <c r="G15" t="s">
         <v>46</v>
@@ -2165,16 +2165,16 @@
         <v>9</v>
       </c>
       <c r="D16" t="s">
+        <v>10</v>
+      </c>
+      <c r="E16" t="s">
+        <v>44</v>
+      </c>
+      <c r="F16" t="s">
         <v>48</v>
       </c>
-      <c r="E16" t="s">
+      <c r="G16" t="s">
         <v>49</v>
-      </c>
-      <c r="F16" t="s">
-        <v>12</v>
-      </c>
-      <c r="G16" t="s">
-        <v>46</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -2185,16 +2185,16 @@
         <v>8</v>
       </c>
       <c r="C17" t="s">
+        <v>31</v>
+      </c>
+      <c r="D17" t="s">
         <v>51</v>
       </c>
-      <c r="D17" t="s">
+      <c r="E17" t="s">
         <v>52</v>
       </c>
-      <c r="E17" t="s">
+      <c r="F17" t="s">
         <v>53</v>
-      </c>
-      <c r="F17" t="s">
-        <v>33</v>
       </c>
       <c r="G17" t="s">
         <v>54</v>
@@ -2208,16 +2208,16 @@
         <v>8</v>
       </c>
       <c r="C18" t="s">
+        <v>31</v>
+      </c>
+      <c r="D18" t="s">
         <v>51</v>
       </c>
-      <c r="D18" t="s">
+      <c r="E18" t="s">
         <v>52</v>
       </c>
-      <c r="E18" t="s">
+      <c r="F18" t="s">
         <v>53</v>
-      </c>
-      <c r="F18" t="s">
-        <v>33</v>
       </c>
       <c r="G18" t="s">
         <v>54</v>
@@ -2231,19 +2231,19 @@
         <v>8</v>
       </c>
       <c r="C19" t="s">
+        <v>31</v>
+      </c>
+      <c r="D19" t="s">
         <v>51</v>
       </c>
-      <c r="D19" t="s">
+      <c r="E19" t="s">
+        <v>52</v>
+      </c>
+      <c r="F19" t="s">
         <v>57</v>
       </c>
-      <c r="E19" t="s">
+      <c r="G19" t="s">
         <v>58</v>
-      </c>
-      <c r="F19" t="s">
-        <v>33</v>
-      </c>
-      <c r="G19" t="s">
-        <v>54</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -2254,19 +2254,19 @@
         <v>8</v>
       </c>
       <c r="C20" t="s">
+        <v>31</v>
+      </c>
+      <c r="D20" t="s">
         <v>51</v>
       </c>
-      <c r="D20" t="s">
+      <c r="E20" t="s">
+        <v>52</v>
+      </c>
+      <c r="F20" t="s">
         <v>60</v>
       </c>
-      <c r="E20" t="s">
+      <c r="G20" t="s">
         <v>61</v>
-      </c>
-      <c r="F20" t="s">
-        <v>33</v>
-      </c>
-      <c r="G20" t="s">
-        <v>54</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -2277,16 +2277,16 @@
         <v>8</v>
       </c>
       <c r="C21" t="s">
+        <v>31</v>
+      </c>
+      <c r="D21" t="s">
         <v>51</v>
       </c>
-      <c r="D21" t="s">
+      <c r="E21" t="s">
         <v>52</v>
       </c>
-      <c r="E21" t="s">
+      <c r="F21" t="s">
         <v>53</v>
-      </c>
-      <c r="F21" t="s">
-        <v>33</v>
       </c>
       <c r="G21" t="s">
         <v>54</v>
@@ -2300,19 +2300,19 @@
         <v>8</v>
       </c>
       <c r="C22" t="s">
+        <v>31</v>
+      </c>
+      <c r="D22" t="s">
         <v>51</v>
       </c>
-      <c r="D22" t="s">
-        <v>31</v>
-      </c>
       <c r="E22" t="s">
+        <v>64</v>
+      </c>
+      <c r="F22" t="s">
         <v>32</v>
       </c>
-      <c r="F22" t="s">
+      <c r="G22" t="s">
         <v>33</v>
-      </c>
-      <c r="G22" t="s">
-        <v>64</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -2323,19 +2323,19 @@
         <v>8</v>
       </c>
       <c r="C23" t="s">
+        <v>31</v>
+      </c>
+      <c r="D23" t="s">
         <v>51</v>
       </c>
-      <c r="D23" t="s">
+      <c r="E23" t="s">
+        <v>64</v>
+      </c>
+      <c r="F23" t="s">
         <v>66</v>
       </c>
-      <c r="E23" t="s">
+      <c r="G23" t="s">
         <v>67</v>
-      </c>
-      <c r="F23" t="s">
-        <v>33</v>
-      </c>
-      <c r="G23" t="s">
-        <v>64</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -2346,19 +2346,19 @@
         <v>8</v>
       </c>
       <c r="C24" t="s">
+        <v>31</v>
+      </c>
+      <c r="D24" t="s">
         <v>51</v>
       </c>
-      <c r="D24" t="s">
-        <v>31</v>
-      </c>
       <c r="E24" t="s">
+        <v>64</v>
+      </c>
+      <c r="F24" t="s">
         <v>32</v>
       </c>
-      <c r="F24" t="s">
+      <c r="G24" t="s">
         <v>33</v>
-      </c>
-      <c r="G24" t="s">
-        <v>64</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -2369,19 +2369,19 @@
         <v>8</v>
       </c>
       <c r="C25" t="s">
+        <v>31</v>
+      </c>
+      <c r="D25" t="s">
         <v>51</v>
       </c>
-      <c r="D25" t="s">
-        <v>31</v>
-      </c>
       <c r="E25" t="s">
+        <v>64</v>
+      </c>
+      <c r="F25" t="s">
         <v>32</v>
       </c>
-      <c r="F25" t="s">
+      <c r="G25" t="s">
         <v>33</v>
-      </c>
-      <c r="G25" t="s">
-        <v>64</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -2392,19 +2392,19 @@
         <v>8</v>
       </c>
       <c r="C26" t="s">
+        <v>31</v>
+      </c>
+      <c r="D26" t="s">
         <v>51</v>
       </c>
-      <c r="D26" t="s">
-        <v>31</v>
-      </c>
       <c r="E26" t="s">
+        <v>64</v>
+      </c>
+      <c r="F26" t="s">
         <v>32</v>
       </c>
-      <c r="F26" t="s">
+      <c r="G26" t="s">
         <v>33</v>
-      </c>
-      <c r="G26" t="s">
-        <v>64</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -2415,19 +2415,19 @@
         <v>8</v>
       </c>
       <c r="C27" t="s">
+        <v>31</v>
+      </c>
+      <c r="D27" t="s">
         <v>51</v>
       </c>
-      <c r="D27" t="s">
-        <v>31</v>
-      </c>
       <c r="E27" t="s">
+        <v>64</v>
+      </c>
+      <c r="F27" t="s">
         <v>32</v>
       </c>
-      <c r="F27" t="s">
+      <c r="G27" t="s">
         <v>33</v>
-      </c>
-      <c r="G27" t="s">
-        <v>64</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -2438,19 +2438,19 @@
         <v>8</v>
       </c>
       <c r="C28" t="s">
+        <v>31</v>
+      </c>
+      <c r="D28" t="s">
         <v>51</v>
       </c>
-      <c r="D28" t="s">
-        <v>31</v>
-      </c>
       <c r="E28" t="s">
+        <v>64</v>
+      </c>
+      <c r="F28" t="s">
         <v>32</v>
       </c>
-      <c r="F28" t="s">
+      <c r="G28" t="s">
         <v>33</v>
-      </c>
-      <c r="G28" t="s">
-        <v>64</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -2461,19 +2461,19 @@
         <v>8</v>
       </c>
       <c r="C29" t="s">
+        <v>31</v>
+      </c>
+      <c r="D29" t="s">
         <v>51</v>
       </c>
-      <c r="D29" t="s">
-        <v>31</v>
-      </c>
       <c r="E29" t="s">
+        <v>64</v>
+      </c>
+      <c r="F29" t="s">
         <v>32</v>
       </c>
-      <c r="F29" t="s">
+      <c r="G29" t="s">
         <v>33</v>
-      </c>
-      <c r="G29" t="s">
-        <v>64</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -2484,19 +2484,19 @@
         <v>8</v>
       </c>
       <c r="C30" t="s">
+        <v>31</v>
+      </c>
+      <c r="D30" t="s">
         <v>51</v>
       </c>
-      <c r="D30" t="s">
-        <v>52</v>
-      </c>
       <c r="E30" t="s">
+        <v>64</v>
+      </c>
+      <c r="F30" t="s">
         <v>53</v>
       </c>
-      <c r="F30" t="s">
-        <v>33</v>
-      </c>
       <c r="G30" t="s">
-        <v>64</v>
+        <v>54</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -2507,19 +2507,19 @@
         <v>8</v>
       </c>
       <c r="C31" t="s">
+        <v>31</v>
+      </c>
+      <c r="D31" t="s">
         <v>51</v>
       </c>
-      <c r="D31" t="s">
-        <v>31</v>
-      </c>
       <c r="E31" t="s">
+        <v>76</v>
+      </c>
+      <c r="F31" t="s">
         <v>32</v>
       </c>
-      <c r="F31" t="s">
+      <c r="G31" t="s">
         <v>33</v>
-      </c>
-      <c r="G31" t="s">
-        <v>76</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -2530,19 +2530,19 @@
         <v>8</v>
       </c>
       <c r="C32" t="s">
+        <v>31</v>
+      </c>
+      <c r="D32" t="s">
         <v>51</v>
       </c>
-      <c r="D32" t="s">
-        <v>31</v>
-      </c>
       <c r="E32" t="s">
+        <v>76</v>
+      </c>
+      <c r="F32" t="s">
         <v>32</v>
       </c>
-      <c r="F32" t="s">
+      <c r="G32" t="s">
         <v>33</v>
-      </c>
-      <c r="G32" t="s">
-        <v>76</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -2553,19 +2553,19 @@
         <v>8</v>
       </c>
       <c r="C33" t="s">
+        <v>31</v>
+      </c>
+      <c r="D33" t="s">
         <v>51</v>
       </c>
-      <c r="D33" t="s">
-        <v>31</v>
-      </c>
       <c r="E33" t="s">
+        <v>76</v>
+      </c>
+      <c r="F33" t="s">
         <v>32</v>
       </c>
-      <c r="F33" t="s">
+      <c r="G33" t="s">
         <v>33</v>
-      </c>
-      <c r="G33" t="s">
-        <v>76</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -2576,19 +2576,19 @@
         <v>8</v>
       </c>
       <c r="C34" t="s">
+        <v>31</v>
+      </c>
+      <c r="D34" t="s">
         <v>51</v>
       </c>
-      <c r="D34" t="s">
-        <v>31</v>
-      </c>
       <c r="E34" t="s">
+        <v>76</v>
+      </c>
+      <c r="F34" t="s">
         <v>32</v>
       </c>
-      <c r="F34" t="s">
+      <c r="G34" t="s">
         <v>33</v>
-      </c>
-      <c r="G34" t="s">
-        <v>76</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -2599,19 +2599,19 @@
         <v>8</v>
       </c>
       <c r="C35" t="s">
+        <v>31</v>
+      </c>
+      <c r="D35" t="s">
         <v>51</v>
       </c>
-      <c r="D35" t="s">
-        <v>31</v>
-      </c>
       <c r="E35" t="s">
+        <v>76</v>
+      </c>
+      <c r="F35" t="s">
         <v>32</v>
       </c>
-      <c r="F35" t="s">
+      <c r="G35" t="s">
         <v>33</v>
-      </c>
-      <c r="G35" t="s">
-        <v>76</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -2622,19 +2622,19 @@
         <v>8</v>
       </c>
       <c r="C36" t="s">
+        <v>31</v>
+      </c>
+      <c r="D36" t="s">
         <v>51</v>
       </c>
-      <c r="D36" t="s">
+      <c r="E36" t="s">
+        <v>76</v>
+      </c>
+      <c r="F36" t="s">
         <v>57</v>
       </c>
-      <c r="E36" t="s">
+      <c r="G36" t="s">
         <v>58</v>
-      </c>
-      <c r="F36" t="s">
-        <v>33</v>
-      </c>
-      <c r="G36" t="s">
-        <v>76</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -2645,15 +2645,15 @@
         <v>8</v>
       </c>
       <c r="C37" t="s">
+        <v>31</v>
+      </c>
+      <c r="D37" t="s">
         <v>83</v>
       </c>
-      <c r="D37" t="s">
-        <v>31</v>
-      </c>
-      <c r="E37" t="s">
+      <c r="F37" t="s">
         <v>32</v>
       </c>
-      <c r="F37" t="s">
+      <c r="G37" t="s">
         <v>33</v>
       </c>
     </row>
@@ -2665,15 +2665,15 @@
         <v>8</v>
       </c>
       <c r="C38" t="s">
+        <v>31</v>
+      </c>
+      <c r="D38" t="s">
         <v>83</v>
       </c>
-      <c r="D38" t="s">
-        <v>31</v>
-      </c>
-      <c r="E38" t="s">
+      <c r="F38" t="s">
         <v>32</v>
       </c>
-      <c r="F38" t="s">
+      <c r="G38" t="s">
         <v>33</v>
       </c>
     </row>
@@ -2685,15 +2685,15 @@
         <v>8</v>
       </c>
       <c r="C39" t="s">
+        <v>31</v>
+      </c>
+      <c r="D39" t="s">
         <v>83</v>
       </c>
-      <c r="D39" t="s">
-        <v>31</v>
-      </c>
-      <c r="E39" t="s">
+      <c r="F39" t="s">
         <v>32</v>
       </c>
-      <c r="F39" t="s">
+      <c r="G39" t="s">
         <v>33</v>
       </c>
     </row>
@@ -2705,15 +2705,15 @@
         <v>8</v>
       </c>
       <c r="C40" t="s">
+        <v>31</v>
+      </c>
+      <c r="D40" t="s">
         <v>83</v>
       </c>
-      <c r="D40" t="s">
-        <v>31</v>
-      </c>
-      <c r="E40" t="s">
+      <c r="F40" t="s">
         <v>32</v>
       </c>
-      <c r="F40" t="s">
+      <c r="G40" t="s">
         <v>33</v>
       </c>
     </row>
@@ -2725,16 +2725,16 @@
         <v>8</v>
       </c>
       <c r="C41" t="s">
+        <v>31</v>
+      </c>
+      <c r="D41" t="s">
         <v>83</v>
       </c>
-      <c r="D41" t="s">
-        <v>52</v>
-      </c>
-      <c r="E41" t="s">
+      <c r="F41" t="s">
         <v>53</v>
       </c>
-      <c r="F41" t="s">
-        <v>33</v>
+      <c r="G41" t="s">
+        <v>54</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -2745,16 +2745,16 @@
         <v>8</v>
       </c>
       <c r="C42" t="s">
+        <v>31</v>
+      </c>
+      <c r="D42" t="s">
         <v>83</v>
       </c>
-      <c r="D42" t="s">
+      <c r="F42" t="s">
         <v>57</v>
       </c>
-      <c r="E42" t="s">
+      <c r="G42" t="s">
         <v>58</v>
-      </c>
-      <c r="F42" t="s">
-        <v>33</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -2770,10 +2770,10 @@
       <c r="D43" t="s">
         <v>91</v>
       </c>
-      <c r="E43" t="s">
+      <c r="F43" t="s">
         <v>92</v>
       </c>
-      <c r="F43" t="s">
+      <c r="G43" t="s">
         <v>93</v>
       </c>
     </row>
@@ -2785,15 +2785,15 @@
         <v>8</v>
       </c>
       <c r="C44" t="s">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="D44" t="s">
-        <v>95</v>
-      </c>
-      <c r="E44" t="s">
+        <v>91</v>
+      </c>
+      <c r="F44" t="s">
         <v>96</v>
       </c>
-      <c r="F44" t="s">
+      <c r="G44" t="s">
         <v>97</v>
       </c>
     </row>
@@ -2810,10 +2810,10 @@
       <c r="D45" t="s">
         <v>91</v>
       </c>
-      <c r="E45" t="s">
+      <c r="F45" t="s">
         <v>92</v>
       </c>
-      <c r="F45" t="s">
+      <c r="G45" t="s">
         <v>93</v>
       </c>
     </row>
@@ -2830,10 +2830,10 @@
       <c r="D46" t="s">
         <v>91</v>
       </c>
-      <c r="E46" t="s">
+      <c r="F46" t="s">
         <v>92</v>
       </c>
-      <c r="F46" t="s">
+      <c r="G46" t="s">
         <v>93</v>
       </c>
     </row>
@@ -2845,16 +2845,16 @@
         <v>8</v>
       </c>
       <c r="C47" t="s">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="D47" t="s">
+        <v>91</v>
+      </c>
+      <c r="F47" t="s">
         <v>101</v>
       </c>
-      <c r="E47" t="s">
+      <c r="G47" t="s">
         <v>102</v>
-      </c>
-      <c r="F47" t="s">
-        <v>97</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -2870,10 +2870,10 @@
       <c r="D48" t="s">
         <v>91</v>
       </c>
-      <c r="E48" t="s">
+      <c r="F48" t="s">
         <v>92</v>
       </c>
-      <c r="F48" t="s">
+      <c r="G48" t="s">
         <v>93</v>
       </c>
     </row>
@@ -2890,10 +2890,10 @@
       <c r="D49" t="s">
         <v>91</v>
       </c>
-      <c r="E49" t="s">
+      <c r="F49" t="s">
         <v>92</v>
       </c>
-      <c r="F49" t="s">
+      <c r="G49" t="s">
         <v>93</v>
       </c>
     </row>
@@ -2905,16 +2905,16 @@
         <v>8</v>
       </c>
       <c r="C50" t="s">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="D50" t="s">
+        <v>91</v>
+      </c>
+      <c r="F50" t="s">
         <v>101</v>
       </c>
-      <c r="E50" t="s">
+      <c r="G50" t="s">
         <v>102</v>
-      </c>
-      <c r="F50" t="s">
-        <v>97</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -2930,10 +2930,10 @@
       <c r="D51" t="s">
         <v>91</v>
       </c>
-      <c r="E51" t="s">
+      <c r="F51" t="s">
         <v>92</v>
       </c>
-      <c r="F51" t="s">
+      <c r="G51" t="s">
         <v>93</v>
       </c>
     </row>
@@ -2945,16 +2945,16 @@
         <v>8</v>
       </c>
       <c r="C52" t="s">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="D52" t="s">
+        <v>91</v>
+      </c>
+      <c r="F52" t="s">
         <v>108</v>
       </c>
-      <c r="E52" t="s">
+      <c r="G52" t="s">
         <v>109</v>
-      </c>
-      <c r="F52" t="s">
-        <v>97</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -2965,16 +2965,16 @@
         <v>8</v>
       </c>
       <c r="C53" t="s">
-        <v>90</v>
+        <v>9</v>
       </c>
       <c r="D53" t="s">
-        <v>10</v>
-      </c>
-      <c r="E53" t="s">
-        <v>11</v>
+        <v>91</v>
       </c>
       <c r="F53" t="s">
         <v>12</v>
+      </c>
+      <c r="G53" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -3011,16 +3011,16 @@
         <v>112</v>
       </c>
       <c r="D55" t="s">
+        <v>113</v>
+      </c>
+      <c r="E55" t="s">
+        <v>114</v>
+      </c>
+      <c r="F55" t="s">
         <v>118</v>
       </c>
-      <c r="E55" t="s">
+      <c r="G55" t="s">
         <v>119</v>
-      </c>
-      <c r="F55" t="s">
-        <v>115</v>
-      </c>
-      <c r="G55" t="s">
-        <v>116</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -3034,16 +3034,16 @@
         <v>112</v>
       </c>
       <c r="D56" t="s">
+        <v>113</v>
+      </c>
+      <c r="E56" t="s">
+        <v>114</v>
+      </c>
+      <c r="F56" t="s">
         <v>121</v>
       </c>
-      <c r="E56" t="s">
+      <c r="G56" t="s">
         <v>122</v>
-      </c>
-      <c r="F56" t="s">
-        <v>115</v>
-      </c>
-      <c r="G56" t="s">
-        <v>116</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -3054,19 +3054,19 @@
         <v>8</v>
       </c>
       <c r="C57" t="s">
-        <v>112</v>
+        <v>124</v>
       </c>
       <c r="D57" t="s">
-        <v>124</v>
+        <v>113</v>
       </c>
       <c r="E57" t="s">
+        <v>114</v>
+      </c>
+      <c r="F57" t="s">
         <v>125</v>
       </c>
-      <c r="F57" t="s">
+      <c r="G57" t="s">
         <v>126</v>
-      </c>
-      <c r="G57" t="s">
-        <v>116</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -3080,16 +3080,16 @@
         <v>112</v>
       </c>
       <c r="D58" t="s">
+        <v>113</v>
+      </c>
+      <c r="E58" t="s">
+        <v>114</v>
+      </c>
+      <c r="F58" t="s">
         <v>118</v>
       </c>
-      <c r="E58" t="s">
+      <c r="G58" t="s">
         <v>119</v>
-      </c>
-      <c r="F58" t="s">
-        <v>115</v>
-      </c>
-      <c r="G58" t="s">
-        <v>116</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -3103,16 +3103,16 @@
         <v>112</v>
       </c>
       <c r="D59" t="s">
+        <v>113</v>
+      </c>
+      <c r="E59" t="s">
+        <v>114</v>
+      </c>
+      <c r="F59" t="s">
         <v>118</v>
       </c>
-      <c r="E59" t="s">
+      <c r="G59" t="s">
         <v>119</v>
-      </c>
-      <c r="F59" t="s">
-        <v>115</v>
-      </c>
-      <c r="G59" t="s">
-        <v>116</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -3126,16 +3126,16 @@
         <v>112</v>
       </c>
       <c r="D60" t="s">
+        <v>113</v>
+      </c>
+      <c r="E60" t="s">
+        <v>114</v>
+      </c>
+      <c r="F60" t="s">
         <v>118</v>
       </c>
-      <c r="E60" t="s">
+      <c r="G60" t="s">
         <v>119</v>
-      </c>
-      <c r="F60" t="s">
-        <v>115</v>
-      </c>
-      <c r="G60" t="s">
-        <v>116</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -3149,16 +3149,16 @@
         <v>112</v>
       </c>
       <c r="D61" t="s">
+        <v>113</v>
+      </c>
+      <c r="E61" t="s">
+        <v>114</v>
+      </c>
+      <c r="F61" t="s">
         <v>118</v>
       </c>
-      <c r="E61" t="s">
+      <c r="G61" t="s">
         <v>119</v>
-      </c>
-      <c r="F61" t="s">
-        <v>115</v>
-      </c>
-      <c r="G61" t="s">
-        <v>116</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -3172,16 +3172,16 @@
         <v>112</v>
       </c>
       <c r="D62" t="s">
+        <v>113</v>
+      </c>
+      <c r="E62" t="s">
+        <v>114</v>
+      </c>
+      <c r="F62" t="s">
         <v>118</v>
       </c>
-      <c r="E62" t="s">
+      <c r="G62" t="s">
         <v>119</v>
-      </c>
-      <c r="F62" t="s">
-        <v>115</v>
-      </c>
-      <c r="G62" t="s">
-        <v>116</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -3195,16 +3195,16 @@
         <v>112</v>
       </c>
       <c r="D63" t="s">
+        <v>113</v>
+      </c>
+      <c r="E63" t="s">
+        <v>114</v>
+      </c>
+      <c r="F63" t="s">
+        <v>118</v>
+      </c>
+      <c r="G63" t="s">
         <v>133</v>
-      </c>
-      <c r="E63" t="s">
-        <v>119</v>
-      </c>
-      <c r="F63" t="s">
-        <v>115</v>
-      </c>
-      <c r="G63" t="s">
-        <v>116</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -3218,16 +3218,16 @@
         <v>112</v>
       </c>
       <c r="D64" t="s">
+        <v>113</v>
+      </c>
+      <c r="E64" t="s">
+        <v>114</v>
+      </c>
+      <c r="F64" t="s">
+        <v>118</v>
+      </c>
+      <c r="G64" t="s">
         <v>133</v>
-      </c>
-      <c r="E64" t="s">
-        <v>119</v>
-      </c>
-      <c r="F64" t="s">
-        <v>115</v>
-      </c>
-      <c r="G64" t="s">
-        <v>116</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -3241,16 +3241,16 @@
         <v>112</v>
       </c>
       <c r="D65" t="s">
+        <v>113</v>
+      </c>
+      <c r="E65" t="s">
+        <v>114</v>
+      </c>
+      <c r="F65" t="s">
         <v>136</v>
       </c>
-      <c r="E65" t="s">
+      <c r="G65" t="s">
         <v>137</v>
-      </c>
-      <c r="F65" t="s">
-        <v>115</v>
-      </c>
-      <c r="G65" t="s">
-        <v>116</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -3287,16 +3287,16 @@
         <v>112</v>
       </c>
       <c r="D67" t="s">
+        <v>113</v>
+      </c>
+      <c r="E67" t="s">
+        <v>114</v>
+      </c>
+      <c r="F67" t="s">
         <v>118</v>
       </c>
-      <c r="E67" t="s">
+      <c r="G67" t="s">
         <v>119</v>
-      </c>
-      <c r="F67" t="s">
-        <v>115</v>
-      </c>
-      <c r="G67" t="s">
-        <v>116</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -3310,7 +3310,7 @@
         <v>112</v>
       </c>
       <c r="D68" t="s">
-        <v>141</v>
+        <v>113</v>
       </c>
       <c r="E68" t="s">
         <v>114</v>
@@ -3319,7 +3319,7 @@
         <v>115</v>
       </c>
       <c r="G68" t="s">
-        <v>116</v>
+        <v>141</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -3333,7 +3333,7 @@
         <v>112</v>
       </c>
       <c r="D69" t="s">
-        <v>143</v>
+        <v>113</v>
       </c>
       <c r="E69" t="s">
         <v>114</v>
@@ -3342,7 +3342,7 @@
         <v>115</v>
       </c>
       <c r="G69" t="s">
-        <v>116</v>
+        <v>143</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -3356,16 +3356,16 @@
         <v>112</v>
       </c>
       <c r="D70" t="s">
+        <v>113</v>
+      </c>
+      <c r="E70" t="s">
+        <v>114</v>
+      </c>
+      <c r="F70" t="s">
         <v>121</v>
       </c>
-      <c r="E70" t="s">
+      <c r="G70" t="s">
         <v>122</v>
-      </c>
-      <c r="F70" t="s">
-        <v>115</v>
-      </c>
-      <c r="G70" t="s">
-        <v>116</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -3379,16 +3379,16 @@
         <v>112</v>
       </c>
       <c r="D71" t="s">
+        <v>113</v>
+      </c>
+      <c r="E71" t="s">
+        <v>114</v>
+      </c>
+      <c r="F71" t="s">
         <v>121</v>
       </c>
-      <c r="E71" t="s">
+      <c r="G71" t="s">
         <v>122</v>
-      </c>
-      <c r="F71" t="s">
-        <v>115</v>
-      </c>
-      <c r="G71" t="s">
-        <v>116</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -3422,19 +3422,19 @@
         <v>8</v>
       </c>
       <c r="C73" t="s">
-        <v>112</v>
+        <v>124</v>
       </c>
       <c r="D73" t="s">
+        <v>113</v>
+      </c>
+      <c r="E73" t="s">
+        <v>114</v>
+      </c>
+      <c r="F73" t="s">
         <v>148</v>
       </c>
-      <c r="E73" t="s">
+      <c r="G73" t="s">
         <v>149</v>
-      </c>
-      <c r="F73" t="s">
-        <v>126</v>
-      </c>
-      <c r="G73" t="s">
-        <v>116</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -3445,19 +3445,19 @@
         <v>8</v>
       </c>
       <c r="C74" t="s">
-        <v>112</v>
+        <v>124</v>
       </c>
       <c r="D74" t="s">
+        <v>113</v>
+      </c>
+      <c r="E74" t="s">
+        <v>114</v>
+      </c>
+      <c r="F74" t="s">
         <v>151</v>
       </c>
-      <c r="E74" t="s">
+      <c r="G74" t="s">
         <v>152</v>
-      </c>
-      <c r="F74" t="s">
-        <v>126</v>
-      </c>
-      <c r="G74" t="s">
-        <v>116</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -3468,19 +3468,19 @@
         <v>8</v>
       </c>
       <c r="C75" t="s">
-        <v>112</v>
+        <v>124</v>
       </c>
       <c r="D75" t="s">
+        <v>113</v>
+      </c>
+      <c r="E75" t="s">
+        <v>114</v>
+      </c>
+      <c r="F75" t="s">
         <v>154</v>
       </c>
-      <c r="E75" t="s">
+      <c r="G75" t="s">
         <v>155</v>
-      </c>
-      <c r="F75" t="s">
-        <v>126</v>
-      </c>
-      <c r="G75" t="s">
-        <v>116</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -3491,19 +3491,19 @@
         <v>8</v>
       </c>
       <c r="C76" t="s">
-        <v>112</v>
+        <v>124</v>
       </c>
       <c r="D76" t="s">
+        <v>113</v>
+      </c>
+      <c r="E76" t="s">
+        <v>114</v>
+      </c>
+      <c r="F76" t="s">
         <v>148</v>
       </c>
-      <c r="E76" t="s">
+      <c r="G76" t="s">
         <v>149</v>
-      </c>
-      <c r="F76" t="s">
-        <v>126</v>
-      </c>
-      <c r="G76" t="s">
-        <v>116</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -3514,19 +3514,19 @@
         <v>8</v>
       </c>
       <c r="C77" t="s">
-        <v>112</v>
+        <v>124</v>
       </c>
       <c r="D77" t="s">
+        <v>113</v>
+      </c>
+      <c r="E77" t="s">
+        <v>114</v>
+      </c>
+      <c r="F77" t="s">
         <v>148</v>
       </c>
-      <c r="E77" t="s">
+      <c r="G77" t="s">
         <v>149</v>
-      </c>
-      <c r="F77" t="s">
-        <v>126</v>
-      </c>
-      <c r="G77" t="s">
-        <v>116</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -3537,19 +3537,19 @@
         <v>8</v>
       </c>
       <c r="C78" t="s">
-        <v>112</v>
+        <v>124</v>
       </c>
       <c r="D78" t="s">
+        <v>113</v>
+      </c>
+      <c r="E78" t="s">
+        <v>114</v>
+      </c>
+      <c r="F78" t="s">
         <v>151</v>
       </c>
-      <c r="E78" t="s">
+      <c r="G78" t="s">
         <v>152</v>
-      </c>
-      <c r="F78" t="s">
-        <v>126</v>
-      </c>
-      <c r="G78" t="s">
-        <v>116</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -3560,19 +3560,19 @@
         <v>8</v>
       </c>
       <c r="C79" t="s">
-        <v>112</v>
+        <v>124</v>
       </c>
       <c r="D79" t="s">
+        <v>113</v>
+      </c>
+      <c r="E79" t="s">
+        <v>114</v>
+      </c>
+      <c r="F79" t="s">
         <v>160</v>
       </c>
-      <c r="E79" t="s">
+      <c r="G79" t="s">
         <v>161</v>
-      </c>
-      <c r="F79" t="s">
-        <v>126</v>
-      </c>
-      <c r="G79" t="s">
-        <v>116</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -3583,19 +3583,19 @@
         <v>8</v>
       </c>
       <c r="C80" t="s">
-        <v>112</v>
+        <v>163</v>
       </c>
       <c r="D80" t="s">
-        <v>163</v>
+        <v>113</v>
       </c>
       <c r="E80" t="s">
+        <v>114</v>
+      </c>
+      <c r="F80" t="s">
         <v>164</v>
       </c>
-      <c r="F80" t="s">
+      <c r="G80" t="s">
         <v>165</v>
-      </c>
-      <c r="G80" t="s">
-        <v>116</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -3606,19 +3606,19 @@
         <v>8</v>
       </c>
       <c r="C81" t="s">
-        <v>112</v>
+        <v>163</v>
       </c>
       <c r="D81" t="s">
-        <v>163</v>
+        <v>113</v>
       </c>
       <c r="E81" t="s">
+        <v>114</v>
+      </c>
+      <c r="F81" t="s">
         <v>164</v>
       </c>
-      <c r="F81" t="s">
+      <c r="G81" t="s">
         <v>165</v>
-      </c>
-      <c r="G81" t="s">
-        <v>116</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -3629,19 +3629,19 @@
         <v>8</v>
       </c>
       <c r="C82" t="s">
-        <v>112</v>
+        <v>163</v>
       </c>
       <c r="D82" t="s">
-        <v>163</v>
+        <v>113</v>
       </c>
       <c r="E82" t="s">
+        <v>114</v>
+      </c>
+      <c r="F82" t="s">
         <v>164</v>
       </c>
-      <c r="F82" t="s">
+      <c r="G82" t="s">
         <v>165</v>
-      </c>
-      <c r="G82" t="s">
-        <v>116</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -3655,7 +3655,7 @@
         <v>112</v>
       </c>
       <c r="D83" t="s">
-        <v>143</v>
+        <v>113</v>
       </c>
       <c r="E83" t="s">
         <v>114</v>
@@ -3664,7 +3664,7 @@
         <v>115</v>
       </c>
       <c r="G83" t="s">
-        <v>116</v>
+        <v>143</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -3678,16 +3678,16 @@
         <v>112</v>
       </c>
       <c r="D84" t="s">
+        <v>113</v>
+      </c>
+      <c r="E84" t="s">
+        <v>114</v>
+      </c>
+      <c r="F84" t="s">
         <v>170</v>
       </c>
-      <c r="E84" t="s">
+      <c r="G84" t="s">
         <v>171</v>
-      </c>
-      <c r="F84" t="s">
-        <v>115</v>
-      </c>
-      <c r="G84" t="s">
-        <v>116</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -3701,16 +3701,16 @@
         <v>112</v>
       </c>
       <c r="D85" t="s">
+        <v>113</v>
+      </c>
+      <c r="E85" t="s">
+        <v>114</v>
+      </c>
+      <c r="F85" t="s">
+        <v>118</v>
+      </c>
+      <c r="G85" t="s">
         <v>173</v>
-      </c>
-      <c r="E85" t="s">
-        <v>119</v>
-      </c>
-      <c r="F85" t="s">
-        <v>115</v>
-      </c>
-      <c r="G85" t="s">
-        <v>116</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -3721,19 +3721,19 @@
         <v>8</v>
       </c>
       <c r="C86" t="s">
-        <v>112</v>
+        <v>163</v>
       </c>
       <c r="D86" t="s">
+        <v>113</v>
+      </c>
+      <c r="E86" t="s">
+        <v>114</v>
+      </c>
+      <c r="F86" t="s">
         <v>175</v>
       </c>
-      <c r="E86" t="s">
+      <c r="G86" t="s">
         <v>176</v>
-      </c>
-      <c r="F86" t="s">
-        <v>165</v>
-      </c>
-      <c r="G86" t="s">
-        <v>116</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -3747,16 +3747,16 @@
         <v>112</v>
       </c>
       <c r="D87" t="s">
+        <v>113</v>
+      </c>
+      <c r="E87" t="s">
+        <v>114</v>
+      </c>
+      <c r="F87" t="s">
+        <v>118</v>
+      </c>
+      <c r="G87" t="s">
         <v>173</v>
-      </c>
-      <c r="E87" t="s">
-        <v>119</v>
-      </c>
-      <c r="F87" t="s">
-        <v>115</v>
-      </c>
-      <c r="G87" t="s">
-        <v>116</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -3770,16 +3770,16 @@
         <v>112</v>
       </c>
       <c r="D88" t="s">
+        <v>113</v>
+      </c>
+      <c r="E88" t="s">
+        <v>114</v>
+      </c>
+      <c r="F88" t="s">
         <v>118</v>
       </c>
-      <c r="E88" t="s">
+      <c r="G88" t="s">
         <v>119</v>
-      </c>
-      <c r="F88" t="s">
-        <v>115</v>
-      </c>
-      <c r="G88" t="s">
-        <v>116</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -3793,16 +3793,16 @@
         <v>112</v>
       </c>
       <c r="D89" t="s">
+        <v>113</v>
+      </c>
+      <c r="E89" t="s">
+        <v>114</v>
+      </c>
+      <c r="F89" t="s">
         <v>118</v>
       </c>
-      <c r="E89" t="s">
+      <c r="G89" t="s">
         <v>119</v>
-      </c>
-      <c r="F89" t="s">
-        <v>115</v>
-      </c>
-      <c r="G89" t="s">
-        <v>116</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -3813,19 +3813,19 @@
         <v>8</v>
       </c>
       <c r="C90" t="s">
-        <v>112</v>
+        <v>124</v>
       </c>
       <c r="D90" t="s">
-        <v>124</v>
+        <v>113</v>
       </c>
       <c r="E90" t="s">
+        <v>114</v>
+      </c>
+      <c r="F90" t="s">
         <v>125</v>
       </c>
-      <c r="F90" t="s">
+      <c r="G90" t="s">
         <v>126</v>
-      </c>
-      <c r="G90" t="s">
-        <v>116</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -3836,19 +3836,19 @@
         <v>8</v>
       </c>
       <c r="C91" t="s">
-        <v>112</v>
+        <v>182</v>
       </c>
       <c r="D91" t="s">
-        <v>182</v>
+        <v>113</v>
       </c>
       <c r="E91" t="s">
+        <v>114</v>
+      </c>
+      <c r="F91" t="s">
         <v>183</v>
       </c>
-      <c r="F91" t="s">
+      <c r="G91" t="s">
         <v>184</v>
-      </c>
-      <c r="G91" t="s">
-        <v>116</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -3859,19 +3859,19 @@
         <v>8</v>
       </c>
       <c r="C92" t="s">
-        <v>112</v>
+        <v>124</v>
       </c>
       <c r="D92" t="s">
-        <v>124</v>
+        <v>113</v>
       </c>
       <c r="E92" t="s">
+        <v>114</v>
+      </c>
+      <c r="F92" t="s">
         <v>125</v>
       </c>
-      <c r="F92" t="s">
+      <c r="G92" t="s">
         <v>126</v>
-      </c>
-      <c r="G92" t="s">
-        <v>116</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -3885,16 +3885,16 @@
         <v>112</v>
       </c>
       <c r="D93" t="s">
+        <v>113</v>
+      </c>
+      <c r="E93" t="s">
+        <v>114</v>
+      </c>
+      <c r="F93" t="s">
         <v>121</v>
       </c>
-      <c r="E93" t="s">
+      <c r="G93" t="s">
         <v>122</v>
-      </c>
-      <c r="F93" t="s">
-        <v>115</v>
-      </c>
-      <c r="G93" t="s">
-        <v>116</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -3905,19 +3905,19 @@
         <v>8</v>
       </c>
       <c r="C94" t="s">
-        <v>112</v>
+        <v>124</v>
       </c>
       <c r="D94" t="s">
-        <v>124</v>
+        <v>113</v>
       </c>
       <c r="E94" t="s">
+        <v>114</v>
+      </c>
+      <c r="F94" t="s">
         <v>125</v>
       </c>
-      <c r="F94" t="s">
+      <c r="G94" t="s">
         <v>126</v>
-      </c>
-      <c r="G94" t="s">
-        <v>116</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -3931,16 +3931,16 @@
         <v>112</v>
       </c>
       <c r="D95" t="s">
+        <v>113</v>
+      </c>
+      <c r="E95" t="s">
+        <v>114</v>
+      </c>
+      <c r="F95" t="s">
         <v>189</v>
       </c>
-      <c r="E95" t="s">
+      <c r="G95" t="s">
         <v>190</v>
-      </c>
-      <c r="F95" t="s">
-        <v>115</v>
-      </c>
-      <c r="G95" t="s">
-        <v>116</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -3951,19 +3951,19 @@
         <v>8</v>
       </c>
       <c r="C96" t="s">
-        <v>112</v>
+        <v>124</v>
       </c>
       <c r="D96" t="s">
-        <v>124</v>
+        <v>113</v>
       </c>
       <c r="E96" t="s">
+        <v>192</v>
+      </c>
+      <c r="F96" t="s">
         <v>125</v>
       </c>
-      <c r="F96" t="s">
+      <c r="G96" t="s">
         <v>126</v>
-      </c>
-      <c r="G96" t="s">
-        <v>192</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -3974,19 +3974,19 @@
         <v>8</v>
       </c>
       <c r="C97" t="s">
-        <v>112</v>
+        <v>124</v>
       </c>
       <c r="D97" t="s">
-        <v>124</v>
+        <v>113</v>
       </c>
       <c r="E97" t="s">
+        <v>192</v>
+      </c>
+      <c r="F97" t="s">
         <v>125</v>
       </c>
-      <c r="F97" t="s">
+      <c r="G97" t="s">
         <v>126</v>
-      </c>
-      <c r="G97" t="s">
-        <v>192</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -3997,19 +3997,19 @@
         <v>8</v>
       </c>
       <c r="C98" t="s">
-        <v>112</v>
+        <v>195</v>
       </c>
       <c r="D98" t="s">
-        <v>195</v>
+        <v>113</v>
       </c>
       <c r="E98" t="s">
+        <v>192</v>
+      </c>
+      <c r="F98" t="s">
         <v>196</v>
       </c>
-      <c r="F98" t="s">
+      <c r="G98" t="s">
         <v>197</v>
-      </c>
-      <c r="G98" t="s">
-        <v>192</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -4020,19 +4020,19 @@
         <v>8</v>
       </c>
       <c r="C99" t="s">
-        <v>112</v>
+        <v>124</v>
       </c>
       <c r="D99" t="s">
-        <v>124</v>
+        <v>113</v>
       </c>
       <c r="E99" t="s">
+        <v>192</v>
+      </c>
+      <c r="F99" t="s">
         <v>125</v>
       </c>
-      <c r="F99" t="s">
+      <c r="G99" t="s">
         <v>126</v>
-      </c>
-      <c r="G99" t="s">
-        <v>192</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -4043,19 +4043,19 @@
         <v>8</v>
       </c>
       <c r="C100" t="s">
-        <v>112</v>
+        <v>124</v>
       </c>
       <c r="D100" t="s">
+        <v>113</v>
+      </c>
+      <c r="E100" t="s">
+        <v>192</v>
+      </c>
+      <c r="F100" t="s">
         <v>154</v>
       </c>
-      <c r="E100" t="s">
+      <c r="G100" t="s">
         <v>155</v>
-      </c>
-      <c r="F100" t="s">
-        <v>126</v>
-      </c>
-      <c r="G100" t="s">
-        <v>192</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -4066,19 +4066,19 @@
         <v>8</v>
       </c>
       <c r="C101" t="s">
-        <v>112</v>
+        <v>124</v>
       </c>
       <c r="D101" t="s">
-        <v>124</v>
+        <v>113</v>
       </c>
       <c r="E101" t="s">
+        <v>192</v>
+      </c>
+      <c r="F101" t="s">
         <v>125</v>
       </c>
-      <c r="F101" t="s">
+      <c r="G101" t="s">
         <v>126</v>
-      </c>
-      <c r="G101" t="s">
-        <v>192</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -4089,16 +4089,16 @@
         <v>8</v>
       </c>
       <c r="C102" t="s">
+        <v>182</v>
+      </c>
+      <c r="D102" t="s">
         <v>202</v>
       </c>
-      <c r="D102" t="s">
+      <c r="F102" t="s">
         <v>203</v>
       </c>
-      <c r="E102" t="s">
+      <c r="G102" t="s">
         <v>204</v>
-      </c>
-      <c r="F102" t="s">
-        <v>184</v>
       </c>
     </row>
     <row r="103" spans="1:7">
@@ -4109,16 +4109,16 @@
         <v>8</v>
       </c>
       <c r="C103" t="s">
+        <v>182</v>
+      </c>
+      <c r="D103" t="s">
         <v>202</v>
       </c>
-      <c r="D103" t="s">
+      <c r="F103" t="s">
         <v>203</v>
       </c>
-      <c r="E103" t="s">
+      <c r="G103" t="s">
         <v>204</v>
-      </c>
-      <c r="F103" t="s">
-        <v>184</v>
       </c>
     </row>
     <row r="104" spans="1:7">
@@ -4129,16 +4129,16 @@
         <v>8</v>
       </c>
       <c r="C104" t="s">
+        <v>182</v>
+      </c>
+      <c r="D104" t="s">
         <v>202</v>
       </c>
-      <c r="D104" t="s">
+      <c r="F104" t="s">
         <v>203</v>
       </c>
-      <c r="E104" t="s">
+      <c r="G104" t="s">
         <v>204</v>
-      </c>
-      <c r="F104" t="s">
-        <v>184</v>
       </c>
     </row>
     <row r="105" spans="1:7">
@@ -4149,16 +4149,16 @@
         <v>8</v>
       </c>
       <c r="C105" t="s">
+        <v>182</v>
+      </c>
+      <c r="D105" t="s">
         <v>202</v>
       </c>
-      <c r="D105" t="s">
+      <c r="F105" t="s">
         <v>208</v>
       </c>
-      <c r="E105" t="s">
+      <c r="G105" t="s">
         <v>209</v>
-      </c>
-      <c r="F105" t="s">
-        <v>184</v>
       </c>
     </row>
     <row r="106" spans="1:7">
@@ -4169,16 +4169,16 @@
         <v>8</v>
       </c>
       <c r="C106" t="s">
+        <v>182</v>
+      </c>
+      <c r="D106" t="s">
         <v>202</v>
       </c>
-      <c r="D106" t="s">
+      <c r="F106" t="s">
         <v>203</v>
       </c>
-      <c r="E106" t="s">
+      <c r="G106" t="s">
         <v>204</v>
-      </c>
-      <c r="F106" t="s">
-        <v>184</v>
       </c>
     </row>
     <row r="107" spans="1:7">
@@ -4189,15 +4189,15 @@
         <v>8</v>
       </c>
       <c r="C107" t="s">
+        <v>182</v>
+      </c>
+      <c r="D107" t="s">
         <v>202</v>
       </c>
-      <c r="D107" t="s">
-        <v>182</v>
-      </c>
-      <c r="E107" t="s">
+      <c r="F107" t="s">
         <v>183</v>
       </c>
-      <c r="F107" t="s">
+      <c r="G107" t="s">
         <v>184</v>
       </c>
     </row>
@@ -4209,16 +4209,16 @@
         <v>8</v>
       </c>
       <c r="C108" t="s">
+        <v>182</v>
+      </c>
+      <c r="D108" t="s">
         <v>202</v>
       </c>
-      <c r="D108" t="s">
+      <c r="F108" t="s">
         <v>213</v>
       </c>
-      <c r="E108" t="s">
+      <c r="G108" t="s">
         <v>214</v>
-      </c>
-      <c r="F108" t="s">
-        <v>184</v>
       </c>
     </row>
     <row r="109" spans="1:7">
@@ -4229,16 +4229,16 @@
         <v>8</v>
       </c>
       <c r="C109" t="s">
+        <v>90</v>
+      </c>
+      <c r="D109" t="s">
         <v>202</v>
       </c>
-      <c r="D109" t="s">
+      <c r="F109" t="s">
         <v>216</v>
       </c>
-      <c r="E109" t="s">
+      <c r="G109" t="s">
         <v>217</v>
-      </c>
-      <c r="F109" t="s">
-        <v>93</v>
       </c>
     </row>
     <row r="110" spans="1:7">
@@ -4249,16 +4249,16 @@
         <v>8</v>
       </c>
       <c r="C110" t="s">
+        <v>90</v>
+      </c>
+      <c r="D110" t="s">
         <v>202</v>
       </c>
-      <c r="D110" t="s">
+      <c r="F110" t="s">
         <v>219</v>
       </c>
-      <c r="E110" t="s">
+      <c r="G110" t="s">
         <v>220</v>
-      </c>
-      <c r="F110" t="s">
-        <v>93</v>
       </c>
     </row>
     <row r="111" spans="1:7">
@@ -4269,16 +4269,16 @@
         <v>8</v>
       </c>
       <c r="C111" t="s">
+        <v>182</v>
+      </c>
+      <c r="D111" t="s">
         <v>202</v>
       </c>
-      <c r="D111" t="s">
+      <c r="F111" t="s">
         <v>203</v>
       </c>
-      <c r="E111" t="s">
+      <c r="G111" t="s">
         <v>204</v>
-      </c>
-      <c r="F111" t="s">
-        <v>184</v>
       </c>
     </row>
     <row r="112" spans="1:7">
@@ -4289,19 +4289,19 @@
         <v>8</v>
       </c>
       <c r="C112" t="s">
+        <v>223</v>
+      </c>
+      <c r="D112" t="s">
         <v>202</v>
       </c>
-      <c r="D112" t="s">
-        <v>223</v>
-      </c>
-      <c r="E112" t="s">
+      <c r="F112" t="s">
         <v>224</v>
       </c>
-      <c r="F112" t="s">
+      <c r="G112" t="s">
         <v>225</v>
       </c>
     </row>
-    <row r="113" spans="1:6">
+    <row r="113" spans="1:7">
       <c r="A113" t="s">
         <v>226</v>
       </c>
@@ -4309,19 +4309,19 @@
         <v>8</v>
       </c>
       <c r="C113" t="s">
+        <v>112</v>
+      </c>
+      <c r="D113" t="s">
         <v>202</v>
-      </c>
-      <c r="D113" t="s">
-        <v>143</v>
-      </c>
-      <c r="E113" t="s">
-        <v>114</v>
       </c>
       <c r="F113" t="s">
         <v>115</v>
       </c>
-    </row>
-    <row r="114" spans="1:6">
+      <c r="G113" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="114" spans="1:7">
       <c r="A114" t="s">
         <v>227</v>
       </c>
@@ -4329,19 +4329,19 @@
         <v>8</v>
       </c>
       <c r="C114" t="s">
+        <v>124</v>
+      </c>
+      <c r="D114" t="s">
         <v>202</v>
       </c>
-      <c r="D114" t="s">
+      <c r="F114" t="s">
         <v>151</v>
       </c>
-      <c r="E114" t="s">
+      <c r="G114" t="s">
         <v>152</v>
       </c>
-      <c r="F114" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="115" spans="1:6">
+    </row>
+    <row r="115" spans="1:7">
       <c r="A115" t="s">
         <v>228</v>
       </c>
@@ -4349,19 +4349,19 @@
         <v>8</v>
       </c>
       <c r="C115" t="s">
+        <v>182</v>
+      </c>
+      <c r="D115" t="s">
         <v>202</v>
       </c>
-      <c r="D115" t="s">
-        <v>182</v>
-      </c>
-      <c r="E115" t="s">
+      <c r="F115" t="s">
         <v>183</v>
       </c>
-      <c r="F115" t="s">
+      <c r="G115" t="s">
         <v>184</v>
       </c>
     </row>
-    <row r="116" spans="1:6">
+    <row r="116" spans="1:7">
       <c r="A116" t="s">
         <v>229</v>
       </c>
@@ -4369,19 +4369,19 @@
         <v>8</v>
       </c>
       <c r="C116" t="s">
+        <v>223</v>
+      </c>
+      <c r="D116" t="s">
         <v>202</v>
       </c>
-      <c r="D116" t="s">
+      <c r="F116" t="s">
         <v>230</v>
       </c>
-      <c r="E116" t="s">
+      <c r="G116" t="s">
         <v>231</v>
       </c>
-      <c r="F116" t="s">
-        <v>225</v>
-      </c>
-    </row>
-    <row r="117" spans="1:6">
+    </row>
+    <row r="117" spans="1:7">
       <c r="A117" t="s">
         <v>232</v>
       </c>
@@ -4389,19 +4389,19 @@
         <v>8</v>
       </c>
       <c r="C117" t="s">
+        <v>223</v>
+      </c>
+      <c r="D117" t="s">
         <v>202</v>
       </c>
-      <c r="D117" t="s">
-        <v>223</v>
-      </c>
-      <c r="E117" t="s">
+      <c r="F117" t="s">
         <v>224</v>
       </c>
-      <c r="F117" t="s">
+      <c r="G117" t="s">
         <v>225</v>
       </c>
     </row>
-    <row r="118" spans="1:6">
+    <row r="118" spans="1:7">
       <c r="A118" t="s">
         <v>233</v>
       </c>
@@ -4409,19 +4409,19 @@
         <v>8</v>
       </c>
       <c r="C118" t="s">
+        <v>163</v>
+      </c>
+      <c r="D118" t="s">
         <v>202</v>
       </c>
-      <c r="D118" t="s">
+      <c r="F118" t="s">
+        <v>164</v>
+      </c>
+      <c r="G118" t="s">
         <v>234</v>
       </c>
-      <c r="E118" t="s">
-        <v>164</v>
-      </c>
-      <c r="F118" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="119" spans="1:6">
+    </row>
+    <row r="119" spans="1:7">
       <c r="A119" t="s">
         <v>235</v>
       </c>
@@ -4429,19 +4429,19 @@
         <v>8</v>
       </c>
       <c r="C119" t="s">
+        <v>182</v>
+      </c>
+      <c r="D119" t="s">
         <v>202</v>
       </c>
-      <c r="D119" t="s">
-        <v>182</v>
-      </c>
-      <c r="E119" t="s">
+      <c r="F119" t="s">
         <v>183</v>
       </c>
-      <c r="F119" t="s">
+      <c r="G119" t="s">
         <v>184</v>
       </c>
     </row>
-    <row r="120" spans="1:6">
+    <row r="120" spans="1:7">
       <c r="A120" t="s">
         <v>236</v>
       </c>
@@ -4449,19 +4449,19 @@
         <v>8</v>
       </c>
       <c r="C120" t="s">
+        <v>112</v>
+      </c>
+      <c r="D120" t="s">
         <v>237</v>
       </c>
-      <c r="D120" t="s">
+      <c r="F120" t="s">
         <v>170</v>
       </c>
-      <c r="E120" t="s">
+      <c r="G120" t="s">
         <v>171</v>
       </c>
-      <c r="F120" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="121" spans="1:6">
+    </row>
+    <row r="121" spans="1:7">
       <c r="A121" t="s">
         <v>238</v>
       </c>
@@ -4469,19 +4469,19 @@
         <v>8</v>
       </c>
       <c r="C121" t="s">
+        <v>112</v>
+      </c>
+      <c r="D121" t="s">
         <v>237</v>
-      </c>
-      <c r="D121" t="s">
-        <v>143</v>
-      </c>
-      <c r="E121" t="s">
-        <v>114</v>
       </c>
       <c r="F121" t="s">
         <v>115</v>
       </c>
-    </row>
-    <row r="122" spans="1:6">
+      <c r="G121" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="122" spans="1:7">
       <c r="A122" t="s">
         <v>239</v>
       </c>
@@ -4489,19 +4489,19 @@
         <v>8</v>
       </c>
       <c r="C122" t="s">
+        <v>112</v>
+      </c>
+      <c r="D122" t="s">
         <v>237</v>
       </c>
-      <c r="D122" t="s">
+      <c r="F122" t="s">
         <v>170</v>
       </c>
-      <c r="E122" t="s">
+      <c r="G122" t="s">
         <v>171</v>
       </c>
-      <c r="F122" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="123" spans="1:6">
+    </row>
+    <row r="123" spans="1:7">
       <c r="A123" t="s">
         <v>240</v>
       </c>
@@ -4509,19 +4509,19 @@
         <v>8</v>
       </c>
       <c r="C123" t="s">
+        <v>112</v>
+      </c>
+      <c r="D123" t="s">
         <v>237</v>
       </c>
-      <c r="D123" t="s">
+      <c r="F123" t="s">
         <v>170</v>
       </c>
-      <c r="E123" t="s">
+      <c r="G123" t="s">
         <v>171</v>
       </c>
-      <c r="F123" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="124" spans="1:6">
+    </row>
+    <row r="124" spans="1:7">
       <c r="A124" t="s">
         <v>241</v>
       </c>
@@ -4529,19 +4529,19 @@
         <v>8</v>
       </c>
       <c r="C124" t="s">
+        <v>163</v>
+      </c>
+      <c r="D124" t="s">
         <v>237</v>
       </c>
-      <c r="D124" t="s">
+      <c r="F124" t="s">
         <v>242</v>
       </c>
-      <c r="E124" t="s">
+      <c r="G124" t="s">
         <v>243</v>
       </c>
-      <c r="F124" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="125" spans="1:6">
+    </row>
+    <row r="125" spans="1:7">
       <c r="A125" t="s">
         <v>244</v>
       </c>
@@ -4549,19 +4549,19 @@
         <v>8</v>
       </c>
       <c r="C125" t="s">
+        <v>163</v>
+      </c>
+      <c r="D125" t="s">
         <v>237</v>
       </c>
-      <c r="D125" t="s">
+      <c r="F125" t="s">
         <v>242</v>
       </c>
-      <c r="E125" t="s">
+      <c r="G125" t="s">
         <v>243</v>
       </c>
-      <c r="F125" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="126" spans="1:6">
+    </row>
+    <row r="126" spans="1:7">
       <c r="A126" t="s">
         <v>245</v>
       </c>
@@ -4569,19 +4569,19 @@
         <v>8</v>
       </c>
       <c r="C126" t="s">
+        <v>163</v>
+      </c>
+      <c r="D126" t="s">
         <v>237</v>
       </c>
-      <c r="D126" t="s">
+      <c r="F126" t="s">
         <v>242</v>
       </c>
-      <c r="E126" t="s">
+      <c r="G126" t="s">
         <v>243</v>
       </c>
-      <c r="F126" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="127" spans="1:6">
+    </row>
+    <row r="127" spans="1:7">
       <c r="A127" t="s">
         <v>246</v>
       </c>
@@ -4589,19 +4589,19 @@
         <v>8</v>
       </c>
       <c r="C127" t="s">
+        <v>163</v>
+      </c>
+      <c r="D127" t="s">
         <v>237</v>
       </c>
-      <c r="D127" t="s">
+      <c r="F127" t="s">
         <v>242</v>
       </c>
-      <c r="E127" t="s">
+      <c r="G127" t="s">
         <v>243</v>
       </c>
-      <c r="F127" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="128" spans="1:6">
+    </row>
+    <row r="128" spans="1:7">
       <c r="A128" t="s">
         <v>247</v>
       </c>
@@ -4609,16 +4609,16 @@
         <v>8</v>
       </c>
       <c r="C128" t="s">
+        <v>163</v>
+      </c>
+      <c r="D128" t="s">
         <v>237</v>
       </c>
-      <c r="D128" t="s">
+      <c r="F128" t="s">
         <v>242</v>
       </c>
-      <c r="E128" t="s">
+      <c r="G128" t="s">
         <v>243</v>
-      </c>
-      <c r="F128" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="129" spans="1:7">
@@ -4629,16 +4629,16 @@
         <v>8</v>
       </c>
       <c r="C129" t="s">
+        <v>163</v>
+      </c>
+      <c r="D129" t="s">
         <v>237</v>
       </c>
-      <c r="D129" t="s">
+      <c r="F129" t="s">
+        <v>242</v>
+      </c>
+      <c r="G129" t="s">
         <v>249</v>
-      </c>
-      <c r="E129" t="s">
-        <v>243</v>
-      </c>
-      <c r="F129" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="130" spans="1:7">
@@ -4649,16 +4649,16 @@
         <v>8</v>
       </c>
       <c r="C130" t="s">
+        <v>163</v>
+      </c>
+      <c r="D130" t="s">
         <v>237</v>
       </c>
-      <c r="D130" t="s">
+      <c r="F130" t="s">
+        <v>242</v>
+      </c>
+      <c r="G130" t="s">
         <v>251</v>
-      </c>
-      <c r="E130" t="s">
-        <v>243</v>
-      </c>
-      <c r="F130" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="131" spans="1:7">
@@ -4669,16 +4669,16 @@
         <v>8</v>
       </c>
       <c r="C131" t="s">
+        <v>163</v>
+      </c>
+      <c r="D131" t="s">
         <v>237</v>
       </c>
-      <c r="D131" t="s">
+      <c r="F131" t="s">
+        <v>242</v>
+      </c>
+      <c r="G131" t="s">
         <v>253</v>
-      </c>
-      <c r="E131" t="s">
-        <v>243</v>
-      </c>
-      <c r="F131" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="132" spans="1:7">
@@ -4689,16 +4689,16 @@
         <v>8</v>
       </c>
       <c r="C132" t="s">
+        <v>163</v>
+      </c>
+      <c r="D132" t="s">
         <v>237</v>
       </c>
-      <c r="D132" t="s">
+      <c r="F132" t="s">
         <v>255</v>
       </c>
-      <c r="E132" t="s">
+      <c r="G132" t="s">
         <v>256</v>
-      </c>
-      <c r="F132" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="133" spans="1:7">
@@ -4709,16 +4709,16 @@
         <v>8</v>
       </c>
       <c r="C133" t="s">
+        <v>112</v>
+      </c>
+      <c r="D133" t="s">
         <v>237</v>
       </c>
-      <c r="D133" t="s">
+      <c r="F133" t="s">
         <v>189</v>
       </c>
-      <c r="E133" t="s">
+      <c r="G133" t="s">
         <v>190</v>
-      </c>
-      <c r="F133" t="s">
-        <v>115</v>
       </c>
     </row>
     <row r="134" spans="1:7">
@@ -4729,16 +4729,16 @@
         <v>8</v>
       </c>
       <c r="C134" t="s">
+        <v>163</v>
+      </c>
+      <c r="D134" t="s">
         <v>259</v>
       </c>
-      <c r="D134" t="s">
+      <c r="F134" t="s">
         <v>175</v>
       </c>
-      <c r="E134" t="s">
+      <c r="G134" t="s">
         <v>176</v>
-      </c>
-      <c r="F134" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="135" spans="1:7">
@@ -4749,16 +4749,16 @@
         <v>8</v>
       </c>
       <c r="C135" t="s">
+        <v>163</v>
+      </c>
+      <c r="D135" t="s">
         <v>259</v>
       </c>
-      <c r="D135" t="s">
+      <c r="F135" t="s">
         <v>175</v>
       </c>
-      <c r="E135" t="s">
+      <c r="G135" t="s">
         <v>176</v>
-      </c>
-      <c r="F135" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="136" spans="1:7">
@@ -4769,16 +4769,16 @@
         <v>8</v>
       </c>
       <c r="C136" t="s">
+        <v>163</v>
+      </c>
+      <c r="D136" t="s">
         <v>259</v>
       </c>
-      <c r="D136" t="s">
+      <c r="F136" t="s">
         <v>175</v>
       </c>
-      <c r="E136" t="s">
+      <c r="G136" t="s">
         <v>176</v>
-      </c>
-      <c r="F136" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="137" spans="1:7">
@@ -4789,16 +4789,16 @@
         <v>8</v>
       </c>
       <c r="C137" t="s">
+        <v>163</v>
+      </c>
+      <c r="D137" t="s">
         <v>259</v>
       </c>
-      <c r="D137" t="s">
+      <c r="F137" t="s">
         <v>175</v>
       </c>
-      <c r="E137" t="s">
+      <c r="G137" t="s">
         <v>176</v>
-      </c>
-      <c r="F137" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="138" spans="1:7">
@@ -4809,16 +4809,16 @@
         <v>8</v>
       </c>
       <c r="C138" t="s">
+        <v>163</v>
+      </c>
+      <c r="D138" t="s">
         <v>259</v>
       </c>
-      <c r="D138" t="s">
+      <c r="F138" t="s">
         <v>175</v>
       </c>
-      <c r="E138" t="s">
+      <c r="G138" t="s">
         <v>176</v>
-      </c>
-      <c r="F138" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="139" spans="1:7">
@@ -4829,16 +4829,16 @@
         <v>8</v>
       </c>
       <c r="C139" t="s">
+        <v>223</v>
+      </c>
+      <c r="D139" t="s">
         <v>259</v>
       </c>
-      <c r="D139" t="s">
+      <c r="F139" t="s">
         <v>265</v>
       </c>
-      <c r="E139" t="s">
+      <c r="G139" t="s">
         <v>266</v>
-      </c>
-      <c r="F139" t="s">
-        <v>225</v>
       </c>
     </row>
     <row r="140" spans="1:7">
@@ -4849,16 +4849,16 @@
         <v>8</v>
       </c>
       <c r="C140" t="s">
+        <v>163</v>
+      </c>
+      <c r="D140" t="s">
         <v>259</v>
       </c>
-      <c r="D140" t="s">
+      <c r="F140" t="s">
         <v>175</v>
       </c>
-      <c r="E140" t="s">
+      <c r="G140" t="s">
         <v>176</v>
-      </c>
-      <c r="F140" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="141" spans="1:7">
@@ -4869,16 +4869,16 @@
         <v>8</v>
       </c>
       <c r="C141" t="s">
+        <v>163</v>
+      </c>
+      <c r="D141" t="s">
         <v>269</v>
       </c>
-      <c r="D141" t="s">
+      <c r="E141" t="s">
         <v>270</v>
       </c>
-      <c r="E141" t="s">
+      <c r="F141" t="s">
         <v>271</v>
-      </c>
-      <c r="F141" t="s">
-        <v>165</v>
       </c>
       <c r="G141" t="s">
         <v>272</v>
@@ -4892,16 +4892,16 @@
         <v>8</v>
       </c>
       <c r="C142" t="s">
+        <v>163</v>
+      </c>
+      <c r="D142" t="s">
         <v>269</v>
       </c>
-      <c r="D142" t="s">
+      <c r="E142" t="s">
         <v>270</v>
       </c>
-      <c r="E142" t="s">
+      <c r="F142" t="s">
         <v>271</v>
-      </c>
-      <c r="F142" t="s">
-        <v>165</v>
       </c>
       <c r="G142" t="s">
         <v>272</v>
@@ -4915,19 +4915,19 @@
         <v>8</v>
       </c>
       <c r="C143" t="s">
+        <v>163</v>
+      </c>
+      <c r="D143" t="s">
         <v>269</v>
       </c>
-      <c r="D143" t="s">
+      <c r="E143" t="s">
+        <v>270</v>
+      </c>
+      <c r="F143" t="s">
         <v>275</v>
       </c>
-      <c r="E143" t="s">
+      <c r="G143" t="s">
         <v>276</v>
-      </c>
-      <c r="F143" t="s">
-        <v>165</v>
-      </c>
-      <c r="G143" t="s">
-        <v>272</v>
       </c>
     </row>
     <row r="144" spans="1:7">
@@ -4938,19 +4938,19 @@
         <v>8</v>
       </c>
       <c r="C144" t="s">
+        <v>163</v>
+      </c>
+      <c r="D144" t="s">
         <v>269</v>
       </c>
-      <c r="D144" t="s">
+      <c r="E144" t="s">
+        <v>270</v>
+      </c>
+      <c r="F144" t="s">
         <v>275</v>
       </c>
-      <c r="E144" t="s">
+      <c r="G144" t="s">
         <v>276</v>
-      </c>
-      <c r="F144" t="s">
-        <v>165</v>
-      </c>
-      <c r="G144" t="s">
-        <v>272</v>
       </c>
     </row>
     <row r="145" spans="1:7">
@@ -4961,19 +4961,19 @@
         <v>8</v>
       </c>
       <c r="C145" t="s">
+        <v>163</v>
+      </c>
+      <c r="D145" t="s">
         <v>269</v>
       </c>
-      <c r="D145" t="s">
+      <c r="E145" t="s">
+        <v>270</v>
+      </c>
+      <c r="F145" t="s">
         <v>275</v>
       </c>
-      <c r="E145" t="s">
+      <c r="G145" t="s">
         <v>276</v>
-      </c>
-      <c r="F145" t="s">
-        <v>165</v>
-      </c>
-      <c r="G145" t="s">
-        <v>272</v>
       </c>
     </row>
     <row r="146" spans="1:7">
@@ -4984,16 +4984,16 @@
         <v>8</v>
       </c>
       <c r="C146" t="s">
+        <v>163</v>
+      </c>
+      <c r="D146" t="s">
         <v>269</v>
       </c>
-      <c r="D146" t="s">
+      <c r="E146" t="s">
         <v>270</v>
       </c>
-      <c r="E146" t="s">
+      <c r="F146" t="s">
         <v>271</v>
-      </c>
-      <c r="F146" t="s">
-        <v>165</v>
       </c>
       <c r="G146" t="s">
         <v>272</v>
@@ -5007,19 +5007,19 @@
         <v>8</v>
       </c>
       <c r="C147" t="s">
+        <v>163</v>
+      </c>
+      <c r="D147" t="s">
         <v>269</v>
       </c>
-      <c r="D147" t="s">
-        <v>270</v>
-      </c>
       <c r="E147" t="s">
+        <v>281</v>
+      </c>
+      <c r="F147" t="s">
         <v>271</v>
       </c>
-      <c r="F147" t="s">
-        <v>165</v>
-      </c>
       <c r="G147" t="s">
-        <v>281</v>
+        <v>272</v>
       </c>
     </row>
     <row r="148" spans="1:7">
@@ -5030,19 +5030,19 @@
         <v>8</v>
       </c>
       <c r="C148" t="s">
+        <v>163</v>
+      </c>
+      <c r="D148" t="s">
         <v>269</v>
       </c>
-      <c r="D148" t="s">
-        <v>270</v>
-      </c>
       <c r="E148" t="s">
+        <v>281</v>
+      </c>
+      <c r="F148" t="s">
         <v>271</v>
       </c>
-      <c r="F148" t="s">
-        <v>165</v>
-      </c>
       <c r="G148" t="s">
-        <v>281</v>
+        <v>272</v>
       </c>
     </row>
     <row r="149" spans="1:7">
@@ -5053,19 +5053,19 @@
         <v>8</v>
       </c>
       <c r="C149" t="s">
+        <v>163</v>
+      </c>
+      <c r="D149" t="s">
         <v>269</v>
       </c>
-      <c r="D149" t="s">
-        <v>270</v>
-      </c>
       <c r="E149" t="s">
+        <v>281</v>
+      </c>
+      <c r="F149" t="s">
         <v>271</v>
       </c>
-      <c r="F149" t="s">
-        <v>165</v>
-      </c>
       <c r="G149" t="s">
-        <v>281</v>
+        <v>272</v>
       </c>
     </row>
     <row r="150" spans="1:7">
@@ -5076,19 +5076,19 @@
         <v>8</v>
       </c>
       <c r="C150" t="s">
+        <v>163</v>
+      </c>
+      <c r="D150" t="s">
         <v>269</v>
       </c>
-      <c r="D150" t="s">
-        <v>270</v>
-      </c>
       <c r="E150" t="s">
+        <v>281</v>
+      </c>
+      <c r="F150" t="s">
         <v>271</v>
       </c>
-      <c r="F150" t="s">
-        <v>165</v>
-      </c>
       <c r="G150" t="s">
-        <v>281</v>
+        <v>272</v>
       </c>
     </row>
     <row r="151" spans="1:7">
@@ -5099,19 +5099,19 @@
         <v>8</v>
       </c>
       <c r="C151" t="s">
+        <v>163</v>
+      </c>
+      <c r="D151" t="s">
         <v>269</v>
       </c>
-      <c r="D151" t="s">
-        <v>270</v>
-      </c>
       <c r="E151" t="s">
+        <v>281</v>
+      </c>
+      <c r="F151" t="s">
         <v>271</v>
       </c>
-      <c r="F151" t="s">
-        <v>165</v>
-      </c>
       <c r="G151" t="s">
-        <v>281</v>
+        <v>272</v>
       </c>
     </row>
     <row r="152" spans="1:7">
@@ -5122,19 +5122,19 @@
         <v>8</v>
       </c>
       <c r="C152" t="s">
+        <v>163</v>
+      </c>
+      <c r="D152" t="s">
         <v>269</v>
       </c>
-      <c r="D152" t="s">
-        <v>270</v>
-      </c>
       <c r="E152" t="s">
+        <v>281</v>
+      </c>
+      <c r="F152" t="s">
         <v>271</v>
       </c>
-      <c r="F152" t="s">
-        <v>165</v>
-      </c>
       <c r="G152" t="s">
-        <v>281</v>
+        <v>272</v>
       </c>
     </row>
     <row r="153" spans="1:7">
@@ -5145,19 +5145,19 @@
         <v>8</v>
       </c>
       <c r="C153" t="s">
+        <v>163</v>
+      </c>
+      <c r="D153" t="s">
         <v>269</v>
       </c>
-      <c r="D153" t="s">
-        <v>270</v>
-      </c>
       <c r="E153" t="s">
+        <v>281</v>
+      </c>
+      <c r="F153" t="s">
         <v>271</v>
       </c>
-      <c r="F153" t="s">
-        <v>165</v>
-      </c>
       <c r="G153" t="s">
-        <v>281</v>
+        <v>272</v>
       </c>
     </row>
     <row r="154" spans="1:7">
@@ -5168,19 +5168,19 @@
         <v>8</v>
       </c>
       <c r="C154" t="s">
+        <v>163</v>
+      </c>
+      <c r="D154" t="s">
         <v>269</v>
       </c>
-      <c r="D154" t="s">
-        <v>270</v>
-      </c>
       <c r="E154" t="s">
+        <v>281</v>
+      </c>
+      <c r="F154" t="s">
         <v>271</v>
       </c>
-      <c r="F154" t="s">
-        <v>165</v>
-      </c>
       <c r="G154" t="s">
-        <v>281</v>
+        <v>272</v>
       </c>
     </row>
     <row r="155" spans="1:7">
@@ -5191,19 +5191,19 @@
         <v>8</v>
       </c>
       <c r="C155" t="s">
+        <v>163</v>
+      </c>
+      <c r="D155" t="s">
         <v>269</v>
       </c>
-      <c r="D155" t="s">
-        <v>270</v>
-      </c>
       <c r="E155" t="s">
+        <v>281</v>
+      </c>
+      <c r="F155" t="s">
         <v>271</v>
       </c>
-      <c r="F155" t="s">
-        <v>165</v>
-      </c>
       <c r="G155" t="s">
-        <v>281</v>
+        <v>272</v>
       </c>
     </row>
     <row r="156" spans="1:7">
@@ -5214,19 +5214,19 @@
         <v>8</v>
       </c>
       <c r="C156" t="s">
+        <v>163</v>
+      </c>
+      <c r="D156" t="s">
         <v>269</v>
       </c>
-      <c r="D156" t="s">
-        <v>270</v>
-      </c>
       <c r="E156" t="s">
+        <v>291</v>
+      </c>
+      <c r="F156" t="s">
         <v>271</v>
       </c>
-      <c r="F156" t="s">
-        <v>165</v>
-      </c>
       <c r="G156" t="s">
-        <v>291</v>
+        <v>272</v>
       </c>
     </row>
     <row r="157" spans="1:7">
@@ -5237,19 +5237,19 @@
         <v>8</v>
       </c>
       <c r="C157" t="s">
+        <v>163</v>
+      </c>
+      <c r="D157" t="s">
         <v>269</v>
       </c>
-      <c r="D157" t="s">
+      <c r="E157" t="s">
+        <v>291</v>
+      </c>
+      <c r="F157" t="s">
+        <v>271</v>
+      </c>
+      <c r="G157" t="s">
         <v>293</v>
-      </c>
-      <c r="E157" t="s">
-        <v>271</v>
-      </c>
-      <c r="F157" t="s">
-        <v>165</v>
-      </c>
-      <c r="G157" t="s">
-        <v>291</v>
       </c>
     </row>
     <row r="158" spans="1:7">
@@ -5260,19 +5260,19 @@
         <v>8</v>
       </c>
       <c r="C158" t="s">
+        <v>163</v>
+      </c>
+      <c r="D158" t="s">
         <v>269</v>
       </c>
-      <c r="D158" t="s">
-        <v>270</v>
-      </c>
       <c r="E158" t="s">
+        <v>291</v>
+      </c>
+      <c r="F158" t="s">
         <v>271</v>
       </c>
-      <c r="F158" t="s">
-        <v>165</v>
-      </c>
       <c r="G158" t="s">
-        <v>291</v>
+        <v>272</v>
       </c>
     </row>
     <row r="159" spans="1:7">
@@ -5283,19 +5283,19 @@
         <v>8</v>
       </c>
       <c r="C159" t="s">
+        <v>163</v>
+      </c>
+      <c r="D159" t="s">
         <v>269</v>
       </c>
-      <c r="D159" t="s">
-        <v>270</v>
-      </c>
       <c r="E159" t="s">
+        <v>291</v>
+      </c>
+      <c r="F159" t="s">
         <v>271</v>
       </c>
-      <c r="F159" t="s">
-        <v>165</v>
-      </c>
       <c r="G159" t="s">
-        <v>291</v>
+        <v>272</v>
       </c>
     </row>
     <row r="160" spans="1:7">
@@ -5306,19 +5306,19 @@
         <v>8</v>
       </c>
       <c r="C160" t="s">
+        <v>163</v>
+      </c>
+      <c r="D160" t="s">
         <v>269</v>
       </c>
-      <c r="D160" t="s">
-        <v>270</v>
-      </c>
       <c r="E160" t="s">
+        <v>291</v>
+      </c>
+      <c r="F160" t="s">
         <v>271</v>
       </c>
-      <c r="F160" t="s">
-        <v>165</v>
-      </c>
       <c r="G160" t="s">
-        <v>291</v>
+        <v>272</v>
       </c>
     </row>
     <row r="161" spans="1:7">
@@ -5329,19 +5329,19 @@
         <v>8</v>
       </c>
       <c r="C161" t="s">
+        <v>163</v>
+      </c>
+      <c r="D161" t="s">
         <v>269</v>
       </c>
-      <c r="D161" t="s">
-        <v>270</v>
-      </c>
       <c r="E161" t="s">
+        <v>291</v>
+      </c>
+      <c r="F161" t="s">
         <v>271</v>
       </c>
-      <c r="F161" t="s">
-        <v>165</v>
-      </c>
       <c r="G161" t="s">
-        <v>291</v>
+        <v>272</v>
       </c>
     </row>
     <row r="162" spans="1:7">
@@ -5352,19 +5352,19 @@
         <v>8</v>
       </c>
       <c r="C162" t="s">
+        <v>163</v>
+      </c>
+      <c r="D162" t="s">
         <v>269</v>
       </c>
-      <c r="D162" t="s">
-        <v>270</v>
-      </c>
       <c r="E162" t="s">
+        <v>299</v>
+      </c>
+      <c r="F162" t="s">
         <v>271</v>
       </c>
-      <c r="F162" t="s">
-        <v>165</v>
-      </c>
       <c r="G162" t="s">
-        <v>299</v>
+        <v>272</v>
       </c>
     </row>
     <row r="163" spans="1:7">
@@ -5375,16 +5375,16 @@
         <v>8</v>
       </c>
       <c r="C163" t="s">
+        <v>163</v>
+      </c>
+      <c r="D163" t="s">
         <v>269</v>
       </c>
-      <c r="D163" t="s">
+      <c r="E163" t="s">
         <v>301</v>
       </c>
-      <c r="E163" t="s">
+      <c r="F163" t="s">
         <v>271</v>
-      </c>
-      <c r="F163" t="s">
-        <v>165</v>
       </c>
       <c r="G163" t="s">
         <v>302</v>
@@ -5398,19 +5398,19 @@
         <v>8</v>
       </c>
       <c r="C164" t="s">
+        <v>163</v>
+      </c>
+      <c r="D164" t="s">
         <v>269</v>
       </c>
-      <c r="D164" t="s">
-        <v>270</v>
-      </c>
       <c r="E164" t="s">
+        <v>304</v>
+      </c>
+      <c r="F164" t="s">
         <v>271</v>
       </c>
-      <c r="F164" t="s">
-        <v>165</v>
-      </c>
       <c r="G164" t="s">
-        <v>304</v>
+        <v>272</v>
       </c>
     </row>
     <row r="165" spans="1:7">
@@ -5421,19 +5421,19 @@
         <v>8</v>
       </c>
       <c r="C165" t="s">
+        <v>163</v>
+      </c>
+      <c r="D165" t="s">
         <v>269</v>
       </c>
-      <c r="D165" t="s">
-        <v>270</v>
-      </c>
       <c r="E165" t="s">
+        <v>304</v>
+      </c>
+      <c r="F165" t="s">
         <v>271</v>
       </c>
-      <c r="F165" t="s">
-        <v>165</v>
-      </c>
       <c r="G165" t="s">
-        <v>304</v>
+        <v>272</v>
       </c>
     </row>
     <row r="166" spans="1:7">
@@ -5444,19 +5444,19 @@
         <v>8</v>
       </c>
       <c r="C166" t="s">
+        <v>163</v>
+      </c>
+      <c r="D166" t="s">
         <v>269</v>
       </c>
-      <c r="D166" t="s">
-        <v>270</v>
-      </c>
       <c r="E166" t="s">
+        <v>304</v>
+      </c>
+      <c r="F166" t="s">
         <v>271</v>
       </c>
-      <c r="F166" t="s">
-        <v>165</v>
-      </c>
       <c r="G166" t="s">
-        <v>304</v>
+        <v>272</v>
       </c>
     </row>
     <row r="167" spans="1:7">
@@ -5467,19 +5467,19 @@
         <v>8</v>
       </c>
       <c r="C167" t="s">
+        <v>163</v>
+      </c>
+      <c r="D167" t="s">
         <v>269</v>
       </c>
-      <c r="D167" t="s">
-        <v>270</v>
-      </c>
       <c r="E167" t="s">
+        <v>304</v>
+      </c>
+      <c r="F167" t="s">
         <v>271</v>
       </c>
-      <c r="F167" t="s">
-        <v>165</v>
-      </c>
       <c r="G167" t="s">
-        <v>304</v>
+        <v>272</v>
       </c>
     </row>
     <row r="168" spans="1:7">
@@ -5490,19 +5490,19 @@
         <v>8</v>
       </c>
       <c r="C168" t="s">
+        <v>163</v>
+      </c>
+      <c r="D168" t="s">
         <v>269</v>
       </c>
-      <c r="D168" t="s">
+      <c r="E168" t="s">
+        <v>304</v>
+      </c>
+      <c r="F168" t="s">
+        <v>271</v>
+      </c>
+      <c r="G168" t="s">
         <v>309</v>
-      </c>
-      <c r="E168" t="s">
-        <v>271</v>
-      </c>
-      <c r="F168" t="s">
-        <v>165</v>
-      </c>
-      <c r="G168" t="s">
-        <v>304</v>
       </c>
     </row>
     <row r="169" spans="1:7">
@@ -5513,19 +5513,19 @@
         <v>8</v>
       </c>
       <c r="C169" t="s">
+        <v>163</v>
+      </c>
+      <c r="D169" t="s">
         <v>269</v>
       </c>
-      <c r="D169" t="s">
+      <c r="E169" t="s">
+        <v>304</v>
+      </c>
+      <c r="F169" t="s">
+        <v>271</v>
+      </c>
+      <c r="G169" t="s">
         <v>309</v>
-      </c>
-      <c r="E169" t="s">
-        <v>271</v>
-      </c>
-      <c r="F169" t="s">
-        <v>165</v>
-      </c>
-      <c r="G169" t="s">
-        <v>304</v>
       </c>
     </row>
     <row r="170" spans="1:7">
@@ -5536,19 +5536,19 @@
         <v>8</v>
       </c>
       <c r="C170" t="s">
+        <v>163</v>
+      </c>
+      <c r="D170" t="s">
         <v>269</v>
       </c>
-      <c r="D170" t="s">
-        <v>270</v>
-      </c>
       <c r="E170" t="s">
+        <v>304</v>
+      </c>
+      <c r="F170" t="s">
         <v>271</v>
       </c>
-      <c r="F170" t="s">
-        <v>165</v>
-      </c>
       <c r="G170" t="s">
-        <v>304</v>
+        <v>272</v>
       </c>
     </row>
     <row r="171" spans="1:7">
@@ -5559,15 +5559,15 @@
         <v>8</v>
       </c>
       <c r="C171" t="s">
+        <v>163</v>
+      </c>
+      <c r="D171" t="s">
         <v>313</v>
       </c>
-      <c r="D171" t="s">
-        <v>163</v>
-      </c>
-      <c r="E171" t="s">
+      <c r="F171" t="s">
         <v>164</v>
       </c>
-      <c r="F171" t="s">
+      <c r="G171" t="s">
         <v>165</v>
       </c>
     </row>
@@ -5579,16 +5579,16 @@
         <v>8</v>
       </c>
       <c r="C172" t="s">
+        <v>112</v>
+      </c>
+      <c r="D172" t="s">
         <v>313</v>
       </c>
-      <c r="D172" t="s">
+      <c r="F172" t="s">
         <v>118</v>
       </c>
-      <c r="E172" t="s">
+      <c r="G172" t="s">
         <v>119</v>
-      </c>
-      <c r="F172" t="s">
-        <v>115</v>
       </c>
     </row>
     <row r="173" spans="1:7">
@@ -5599,15 +5599,15 @@
         <v>8</v>
       </c>
       <c r="C173" t="s">
+        <v>163</v>
+      </c>
+      <c r="D173" t="s">
         <v>313</v>
       </c>
-      <c r="D173" t="s">
-        <v>163</v>
-      </c>
-      <c r="E173" t="s">
+      <c r="F173" t="s">
         <v>164</v>
       </c>
-      <c r="F173" t="s">
+      <c r="G173" t="s">
         <v>165</v>
       </c>
     </row>
@@ -5619,15 +5619,15 @@
         <v>8</v>
       </c>
       <c r="C174" t="s">
+        <v>163</v>
+      </c>
+      <c r="D174" t="s">
         <v>313</v>
       </c>
-      <c r="D174" t="s">
-        <v>163</v>
-      </c>
-      <c r="E174" t="s">
+      <c r="F174" t="s">
         <v>164</v>
       </c>
-      <c r="F174" t="s">
+      <c r="G174" t="s">
         <v>165</v>
       </c>
     </row>
@@ -5639,15 +5639,15 @@
         <v>8</v>
       </c>
       <c r="C175" t="s">
+        <v>163</v>
+      </c>
+      <c r="D175" t="s">
         <v>313</v>
       </c>
-      <c r="D175" t="s">
-        <v>163</v>
-      </c>
-      <c r="E175" t="s">
+      <c r="F175" t="s">
         <v>164</v>
       </c>
-      <c r="F175" t="s">
+      <c r="G175" t="s">
         <v>165</v>
       </c>
     </row>
@@ -5659,15 +5659,15 @@
         <v>8</v>
       </c>
       <c r="C176" t="s">
+        <v>163</v>
+      </c>
+      <c r="D176" t="s">
         <v>313</v>
       </c>
-      <c r="D176" t="s">
-        <v>163</v>
-      </c>
-      <c r="E176" t="s">
+      <c r="F176" t="s">
         <v>164</v>
       </c>
-      <c r="F176" t="s">
+      <c r="G176" t="s">
         <v>165</v>
       </c>
     </row>
@@ -5679,15 +5679,15 @@
         <v>8</v>
       </c>
       <c r="C177" t="s">
+        <v>163</v>
+      </c>
+      <c r="D177" t="s">
         <v>320</v>
       </c>
-      <c r="D177" t="s">
-        <v>163</v>
-      </c>
-      <c r="E177" t="s">
+      <c r="F177" t="s">
         <v>164</v>
       </c>
-      <c r="F177" t="s">
+      <c r="G177" t="s">
         <v>165</v>
       </c>
     </row>
@@ -5699,15 +5699,15 @@
         <v>8</v>
       </c>
       <c r="C178" t="s">
+        <v>163</v>
+      </c>
+      <c r="D178" t="s">
         <v>320</v>
       </c>
-      <c r="D178" t="s">
-        <v>163</v>
-      </c>
-      <c r="E178" t="s">
+      <c r="F178" t="s">
         <v>164</v>
       </c>
-      <c r="F178" t="s">
+      <c r="G178" t="s">
         <v>165</v>
       </c>
     </row>
@@ -5719,15 +5719,15 @@
         <v>8</v>
       </c>
       <c r="C179" t="s">
+        <v>163</v>
+      </c>
+      <c r="D179" t="s">
         <v>320</v>
       </c>
-      <c r="D179" t="s">
-        <v>163</v>
-      </c>
-      <c r="E179" t="s">
+      <c r="F179" t="s">
         <v>164</v>
       </c>
-      <c r="F179" t="s">
+      <c r="G179" t="s">
         <v>165</v>
       </c>
     </row>
@@ -5739,15 +5739,15 @@
         <v>8</v>
       </c>
       <c r="C180" t="s">
+        <v>163</v>
+      </c>
+      <c r="D180" t="s">
         <v>320</v>
       </c>
-      <c r="D180" t="s">
-        <v>163</v>
-      </c>
-      <c r="E180" t="s">
+      <c r="F180" t="s">
         <v>164</v>
       </c>
-      <c r="F180" t="s">
+      <c r="G180" t="s">
         <v>165</v>
       </c>
     </row>
@@ -5759,16 +5759,16 @@
         <v>8</v>
       </c>
       <c r="C181" t="s">
+        <v>163</v>
+      </c>
+      <c r="D181" t="s">
         <v>325</v>
       </c>
-      <c r="D181" t="s">
+      <c r="E181" t="s">
         <v>326</v>
       </c>
-      <c r="E181" t="s">
+      <c r="F181" t="s">
         <v>327</v>
-      </c>
-      <c r="F181" t="s">
-        <v>165</v>
       </c>
       <c r="G181" t="s">
         <v>328</v>
@@ -5782,16 +5782,16 @@
         <v>8</v>
       </c>
       <c r="C182" t="s">
+        <v>163</v>
+      </c>
+      <c r="D182" t="s">
         <v>325</v>
       </c>
-      <c r="D182" t="s">
+      <c r="E182" t="s">
         <v>326</v>
       </c>
-      <c r="E182" t="s">
+      <c r="F182" t="s">
         <v>327</v>
-      </c>
-      <c r="F182" t="s">
-        <v>165</v>
       </c>
       <c r="G182" t="s">
         <v>328</v>
@@ -5805,16 +5805,16 @@
         <v>8</v>
       </c>
       <c r="C183" t="s">
+        <v>163</v>
+      </c>
+      <c r="D183" t="s">
         <v>325</v>
       </c>
-      <c r="D183" t="s">
+      <c r="E183" t="s">
         <v>326</v>
       </c>
-      <c r="E183" t="s">
+      <c r="F183" t="s">
         <v>327</v>
-      </c>
-      <c r="F183" t="s">
-        <v>165</v>
       </c>
       <c r="G183" t="s">
         <v>328</v>
@@ -5828,16 +5828,16 @@
         <v>8</v>
       </c>
       <c r="C184" t="s">
+        <v>163</v>
+      </c>
+      <c r="D184" t="s">
         <v>325</v>
       </c>
-      <c r="D184" t="s">
+      <c r="E184" t="s">
         <v>326</v>
       </c>
-      <c r="E184" t="s">
+      <c r="F184" t="s">
         <v>327</v>
-      </c>
-      <c r="F184" t="s">
-        <v>165</v>
       </c>
       <c r="G184" t="s">
         <v>328</v>
@@ -5851,16 +5851,16 @@
         <v>8</v>
       </c>
       <c r="C185" t="s">
+        <v>163</v>
+      </c>
+      <c r="D185" t="s">
         <v>325</v>
       </c>
-      <c r="D185" t="s">
+      <c r="E185" t="s">
         <v>326</v>
       </c>
-      <c r="E185" t="s">
+      <c r="F185" t="s">
         <v>327</v>
-      </c>
-      <c r="F185" t="s">
-        <v>165</v>
       </c>
       <c r="G185" t="s">
         <v>328</v>
@@ -5874,16 +5874,16 @@
         <v>8</v>
       </c>
       <c r="C186" t="s">
+        <v>163</v>
+      </c>
+      <c r="D186" t="s">
         <v>325</v>
       </c>
-      <c r="D186" t="s">
+      <c r="E186" t="s">
         <v>326</v>
       </c>
-      <c r="E186" t="s">
+      <c r="F186" t="s">
         <v>327</v>
-      </c>
-      <c r="F186" t="s">
-        <v>165</v>
       </c>
       <c r="G186" t="s">
         <v>328</v>
@@ -5897,16 +5897,16 @@
         <v>8</v>
       </c>
       <c r="C187" t="s">
+        <v>163</v>
+      </c>
+      <c r="D187" t="s">
         <v>325</v>
       </c>
-      <c r="D187" t="s">
+      <c r="E187" t="s">
         <v>326</v>
       </c>
-      <c r="E187" t="s">
+      <c r="F187" t="s">
         <v>327</v>
-      </c>
-      <c r="F187" t="s">
-        <v>165</v>
       </c>
       <c r="G187" t="s">
         <v>328</v>
@@ -5920,16 +5920,16 @@
         <v>8</v>
       </c>
       <c r="C188" t="s">
+        <v>163</v>
+      </c>
+      <c r="D188" t="s">
         <v>325</v>
       </c>
-      <c r="D188" t="s">
+      <c r="E188" t="s">
         <v>326</v>
       </c>
-      <c r="E188" t="s">
+      <c r="F188" t="s">
         <v>327</v>
-      </c>
-      <c r="F188" t="s">
-        <v>165</v>
       </c>
       <c r="G188" t="s">
         <v>328</v>
@@ -5943,16 +5943,16 @@
         <v>8</v>
       </c>
       <c r="C189" t="s">
+        <v>163</v>
+      </c>
+      <c r="D189" t="s">
         <v>325</v>
       </c>
-      <c r="D189" t="s">
+      <c r="E189" t="s">
         <v>326</v>
       </c>
-      <c r="E189" t="s">
+      <c r="F189" t="s">
         <v>327</v>
-      </c>
-      <c r="F189" t="s">
-        <v>165</v>
       </c>
       <c r="G189" t="s">
         <v>328</v>
@@ -5966,16 +5966,16 @@
         <v>8</v>
       </c>
       <c r="C190" t="s">
+        <v>163</v>
+      </c>
+      <c r="D190" t="s">
         <v>325</v>
       </c>
-      <c r="D190" t="s">
+      <c r="E190" t="s">
         <v>326</v>
       </c>
-      <c r="E190" t="s">
+      <c r="F190" t="s">
         <v>327</v>
-      </c>
-      <c r="F190" t="s">
-        <v>165</v>
       </c>
       <c r="G190" t="s">
         <v>328</v>
@@ -5989,16 +5989,16 @@
         <v>8</v>
       </c>
       <c r="C191" t="s">
+        <v>163</v>
+      </c>
+      <c r="D191" t="s">
         <v>325</v>
       </c>
-      <c r="D191" t="s">
+      <c r="E191" t="s">
         <v>326</v>
       </c>
-      <c r="E191" t="s">
+      <c r="F191" t="s">
         <v>327</v>
-      </c>
-      <c r="F191" t="s">
-        <v>165</v>
       </c>
       <c r="G191" t="s">
         <v>328</v>
@@ -6012,16 +6012,16 @@
         <v>8</v>
       </c>
       <c r="C192" t="s">
+        <v>163</v>
+      </c>
+      <c r="D192" t="s">
         <v>325</v>
       </c>
-      <c r="D192" t="s">
+      <c r="E192" t="s">
         <v>326</v>
       </c>
-      <c r="E192" t="s">
+      <c r="F192" t="s">
         <v>327</v>
-      </c>
-      <c r="F192" t="s">
-        <v>165</v>
       </c>
       <c r="G192" t="s">
         <v>328</v>
@@ -6035,19 +6035,19 @@
         <v>8</v>
       </c>
       <c r="C193" t="s">
+        <v>163</v>
+      </c>
+      <c r="D193" t="s">
         <v>325</v>
       </c>
-      <c r="D193" t="s">
+      <c r="E193" t="s">
+        <v>326</v>
+      </c>
+      <c r="F193" t="s">
+        <v>275</v>
+      </c>
+      <c r="G193" t="s">
         <v>341</v>
-      </c>
-      <c r="E193" t="s">
-        <v>276</v>
-      </c>
-      <c r="F193" t="s">
-        <v>165</v>
-      </c>
-      <c r="G193" t="s">
-        <v>328</v>
       </c>
     </row>
     <row r="194" spans="1:7">
@@ -6058,16 +6058,16 @@
         <v>8</v>
       </c>
       <c r="C194" t="s">
+        <v>163</v>
+      </c>
+      <c r="D194" t="s">
         <v>325</v>
       </c>
-      <c r="D194" t="s">
+      <c r="E194" t="s">
         <v>326</v>
       </c>
-      <c r="E194" t="s">
+      <c r="F194" t="s">
         <v>327</v>
-      </c>
-      <c r="F194" t="s">
-        <v>165</v>
       </c>
       <c r="G194" t="s">
         <v>328</v>
@@ -6081,16 +6081,16 @@
         <v>8</v>
       </c>
       <c r="C195" t="s">
+        <v>163</v>
+      </c>
+      <c r="D195" t="s">
         <v>325</v>
       </c>
-      <c r="D195" t="s">
+      <c r="E195" t="s">
         <v>326</v>
       </c>
-      <c r="E195" t="s">
+      <c r="F195" t="s">
         <v>327</v>
-      </c>
-      <c r="F195" t="s">
-        <v>165</v>
       </c>
       <c r="G195" t="s">
         <v>328</v>
@@ -6104,16 +6104,16 @@
         <v>8</v>
       </c>
       <c r="C196" t="s">
+        <v>163</v>
+      </c>
+      <c r="D196" t="s">
         <v>325</v>
       </c>
-      <c r="D196" t="s">
+      <c r="E196" t="s">
         <v>326</v>
       </c>
-      <c r="E196" t="s">
+      <c r="F196" t="s">
         <v>327</v>
-      </c>
-      <c r="F196" t="s">
-        <v>165</v>
       </c>
       <c r="G196" t="s">
         <v>328</v>
@@ -6127,16 +6127,16 @@
         <v>8</v>
       </c>
       <c r="C197" t="s">
+        <v>163</v>
+      </c>
+      <c r="D197" t="s">
         <v>325</v>
       </c>
-      <c r="D197" t="s">
+      <c r="E197" t="s">
         <v>326</v>
       </c>
-      <c r="E197" t="s">
+      <c r="F197" t="s">
         <v>327</v>
-      </c>
-      <c r="F197" t="s">
-        <v>165</v>
       </c>
       <c r="G197" t="s">
         <v>328</v>
@@ -6150,16 +6150,16 @@
         <v>8</v>
       </c>
       <c r="C198" t="s">
+        <v>163</v>
+      </c>
+      <c r="D198" t="s">
         <v>325</v>
       </c>
-      <c r="D198" t="s">
+      <c r="E198" t="s">
         <v>326</v>
       </c>
-      <c r="E198" t="s">
+      <c r="F198" t="s">
         <v>327</v>
-      </c>
-      <c r="F198" t="s">
-        <v>165</v>
       </c>
       <c r="G198" t="s">
         <v>328</v>
@@ -6173,16 +6173,16 @@
         <v>8</v>
       </c>
       <c r="C199" t="s">
+        <v>163</v>
+      </c>
+      <c r="D199" t="s">
         <v>325</v>
       </c>
-      <c r="D199" t="s">
+      <c r="E199" t="s">
         <v>348</v>
       </c>
-      <c r="E199" t="s">
+      <c r="F199" t="s">
         <v>327</v>
-      </c>
-      <c r="F199" t="s">
-        <v>165</v>
       </c>
       <c r="G199" t="s">
         <v>349</v>
@@ -6196,16 +6196,16 @@
         <v>8</v>
       </c>
       <c r="C200" t="s">
+        <v>163</v>
+      </c>
+      <c r="D200" t="s">
         <v>325</v>
       </c>
-      <c r="D200" t="s">
+      <c r="E200" t="s">
         <v>348</v>
       </c>
-      <c r="E200" t="s">
+      <c r="F200" t="s">
         <v>327</v>
-      </c>
-      <c r="F200" t="s">
-        <v>165</v>
       </c>
       <c r="G200" t="s">
         <v>349</v>
@@ -6219,16 +6219,16 @@
         <v>8</v>
       </c>
       <c r="C201" t="s">
+        <v>163</v>
+      </c>
+      <c r="D201" t="s">
         <v>325</v>
       </c>
-      <c r="D201" t="s">
+      <c r="E201" t="s">
         <v>348</v>
       </c>
-      <c r="E201" t="s">
+      <c r="F201" t="s">
         <v>327</v>
-      </c>
-      <c r="F201" t="s">
-        <v>165</v>
       </c>
       <c r="G201" t="s">
         <v>349</v>
@@ -6242,16 +6242,16 @@
         <v>8</v>
       </c>
       <c r="C202" t="s">
+        <v>163</v>
+      </c>
+      <c r="D202" t="s">
         <v>325</v>
       </c>
-      <c r="D202" t="s">
+      <c r="E202" t="s">
         <v>348</v>
       </c>
-      <c r="E202" t="s">
+      <c r="F202" t="s">
         <v>327</v>
-      </c>
-      <c r="F202" t="s">
-        <v>165</v>
       </c>
       <c r="G202" t="s">
         <v>349</v>
@@ -6265,19 +6265,19 @@
         <v>8</v>
       </c>
       <c r="C203" t="s">
+        <v>163</v>
+      </c>
+      <c r="D203" t="s">
         <v>325</v>
       </c>
-      <c r="D203" t="s">
+      <c r="E203" t="s">
+        <v>348</v>
+      </c>
+      <c r="F203" t="s">
+        <v>275</v>
+      </c>
+      <c r="G203" t="s">
         <v>341</v>
-      </c>
-      <c r="E203" t="s">
-        <v>276</v>
-      </c>
-      <c r="F203" t="s">
-        <v>165</v>
-      </c>
-      <c r="G203" t="s">
-        <v>349</v>
       </c>
     </row>
     <row r="204" spans="1:7">
@@ -6288,16 +6288,16 @@
         <v>8</v>
       </c>
       <c r="C204" t="s">
+        <v>163</v>
+      </c>
+      <c r="D204" t="s">
         <v>325</v>
       </c>
-      <c r="D204" t="s">
+      <c r="E204" t="s">
         <v>348</v>
       </c>
-      <c r="E204" t="s">
+      <c r="F204" t="s">
         <v>327</v>
-      </c>
-      <c r="F204" t="s">
-        <v>165</v>
       </c>
       <c r="G204" t="s">
         <v>349</v>
@@ -6311,16 +6311,16 @@
         <v>8</v>
       </c>
       <c r="C205" t="s">
+        <v>163</v>
+      </c>
+      <c r="D205" t="s">
         <v>325</v>
       </c>
-      <c r="D205" t="s">
+      <c r="E205" t="s">
         <v>356</v>
       </c>
-      <c r="E205" t="s">
+      <c r="F205" t="s">
         <v>327</v>
-      </c>
-      <c r="F205" t="s">
-        <v>165</v>
       </c>
       <c r="G205" t="s">
         <v>357</v>
@@ -6334,16 +6334,16 @@
         <v>8</v>
       </c>
       <c r="C206" t="s">
+        <v>163</v>
+      </c>
+      <c r="D206" t="s">
         <v>325</v>
       </c>
-      <c r="D206" t="s">
+      <c r="E206" t="s">
         <v>356</v>
       </c>
-      <c r="E206" t="s">
+      <c r="F206" t="s">
         <v>327</v>
-      </c>
-      <c r="F206" t="s">
-        <v>165</v>
       </c>
       <c r="G206" t="s">
         <v>357</v>
@@ -6357,16 +6357,16 @@
         <v>8</v>
       </c>
       <c r="C207" t="s">
+        <v>163</v>
+      </c>
+      <c r="D207" t="s">
         <v>325</v>
       </c>
-      <c r="D207" t="s">
+      <c r="E207" t="s">
         <v>356</v>
       </c>
-      <c r="E207" t="s">
+      <c r="F207" t="s">
         <v>327</v>
-      </c>
-      <c r="F207" t="s">
-        <v>165</v>
       </c>
       <c r="G207" t="s">
         <v>357</v>
@@ -6380,19 +6380,19 @@
         <v>8</v>
       </c>
       <c r="C208" t="s">
+        <v>163</v>
+      </c>
+      <c r="D208" t="s">
         <v>325</v>
       </c>
-      <c r="D208" t="s">
+      <c r="E208" t="s">
+        <v>356</v>
+      </c>
+      <c r="F208" t="s">
+        <v>275</v>
+      </c>
+      <c r="G208" t="s">
         <v>341</v>
-      </c>
-      <c r="E208" t="s">
-        <v>276</v>
-      </c>
-      <c r="F208" t="s">
-        <v>165</v>
-      </c>
-      <c r="G208" t="s">
-        <v>357</v>
       </c>
     </row>
     <row r="209" spans="1:7">
@@ -6403,16 +6403,16 @@
         <v>8</v>
       </c>
       <c r="C209" t="s">
+        <v>163</v>
+      </c>
+      <c r="D209" t="s">
         <v>325</v>
       </c>
-      <c r="D209" t="s">
+      <c r="E209" t="s">
         <v>356</v>
       </c>
-      <c r="E209" t="s">
+      <c r="F209" t="s">
         <v>327</v>
-      </c>
-      <c r="F209" t="s">
-        <v>165</v>
       </c>
       <c r="G209" t="s">
         <v>357</v>
@@ -6426,16 +6426,16 @@
         <v>8</v>
       </c>
       <c r="C210" t="s">
+        <v>163</v>
+      </c>
+      <c r="D210" t="s">
         <v>363</v>
       </c>
-      <c r="D210" t="s">
+      <c r="E210" t="s">
         <v>364</v>
       </c>
-      <c r="E210" t="s">
+      <c r="F210" t="s">
         <v>365</v>
-      </c>
-      <c r="F210" t="s">
-        <v>165</v>
       </c>
       <c r="G210" t="s">
         <v>366</v>
@@ -6449,16 +6449,16 @@
         <v>8</v>
       </c>
       <c r="C211" t="s">
+        <v>163</v>
+      </c>
+      <c r="D211" t="s">
         <v>363</v>
       </c>
-      <c r="D211" t="s">
+      <c r="E211" t="s">
         <v>364</v>
       </c>
-      <c r="E211" t="s">
+      <c r="F211" t="s">
         <v>365</v>
-      </c>
-      <c r="F211" t="s">
-        <v>165</v>
       </c>
       <c r="G211" t="s">
         <v>366</v>
@@ -6472,16 +6472,16 @@
         <v>8</v>
       </c>
       <c r="C212" t="s">
+        <v>163</v>
+      </c>
+      <c r="D212" t="s">
         <v>363</v>
       </c>
-      <c r="D212" t="s">
+      <c r="E212" t="s">
         <v>364</v>
       </c>
-      <c r="E212" t="s">
+      <c r="F212" t="s">
         <v>365</v>
-      </c>
-      <c r="F212" t="s">
-        <v>165</v>
       </c>
       <c r="G212" t="s">
         <v>366</v>
@@ -6495,16 +6495,16 @@
         <v>8</v>
       </c>
       <c r="C213" t="s">
+        <v>163</v>
+      </c>
+      <c r="D213" t="s">
         <v>363</v>
       </c>
-      <c r="D213" t="s">
+      <c r="E213" t="s">
         <v>364</v>
       </c>
-      <c r="E213" t="s">
+      <c r="F213" t="s">
         <v>365</v>
-      </c>
-      <c r="F213" t="s">
-        <v>165</v>
       </c>
       <c r="G213" t="s">
         <v>366</v>
@@ -6518,16 +6518,16 @@
         <v>8</v>
       </c>
       <c r="C214" t="s">
+        <v>163</v>
+      </c>
+      <c r="D214" t="s">
         <v>363</v>
       </c>
-      <c r="D214" t="s">
+      <c r="E214" t="s">
         <v>364</v>
       </c>
-      <c r="E214" t="s">
+      <c r="F214" t="s">
         <v>365</v>
-      </c>
-      <c r="F214" t="s">
-        <v>165</v>
       </c>
       <c r="G214" t="s">
         <v>366</v>
@@ -6541,19 +6541,19 @@
         <v>8</v>
       </c>
       <c r="C215" t="s">
+        <v>163</v>
+      </c>
+      <c r="D215" t="s">
         <v>363</v>
       </c>
-      <c r="D215" t="s">
-        <v>348</v>
-      </c>
       <c r="E215" t="s">
+        <v>364</v>
+      </c>
+      <c r="F215" t="s">
         <v>327</v>
       </c>
-      <c r="F215" t="s">
-        <v>165</v>
-      </c>
       <c r="G215" t="s">
-        <v>366</v>
+        <v>349</v>
       </c>
     </row>
     <row r="216" spans="1:7">
@@ -6564,16 +6564,16 @@
         <v>8</v>
       </c>
       <c r="C216" t="s">
+        <v>163</v>
+      </c>
+      <c r="D216" t="s">
         <v>363</v>
       </c>
-      <c r="D216" t="s">
+      <c r="E216" t="s">
         <v>364</v>
       </c>
-      <c r="E216" t="s">
+      <c r="F216" t="s">
         <v>365</v>
-      </c>
-      <c r="F216" t="s">
-        <v>165</v>
       </c>
       <c r="G216" t="s">
         <v>366</v>
@@ -6587,16 +6587,16 @@
         <v>8</v>
       </c>
       <c r="C217" t="s">
+        <v>163</v>
+      </c>
+      <c r="D217" t="s">
         <v>363</v>
       </c>
-      <c r="D217" t="s">
+      <c r="E217" t="s">
         <v>364</v>
       </c>
-      <c r="E217" t="s">
+      <c r="F217" t="s">
         <v>365</v>
-      </c>
-      <c r="F217" t="s">
-        <v>165</v>
       </c>
       <c r="G217" t="s">
         <v>366</v>
@@ -6610,16 +6610,16 @@
         <v>8</v>
       </c>
       <c r="C218" t="s">
+        <v>163</v>
+      </c>
+      <c r="D218" t="s">
         <v>363</v>
       </c>
-      <c r="D218" t="s">
+      <c r="E218" t="s">
         <v>364</v>
       </c>
-      <c r="E218" t="s">
+      <c r="F218" t="s">
         <v>365</v>
-      </c>
-      <c r="F218" t="s">
-        <v>165</v>
       </c>
       <c r="G218" t="s">
         <v>366</v>
@@ -6633,16 +6633,16 @@
         <v>8</v>
       </c>
       <c r="C219" t="s">
+        <v>163</v>
+      </c>
+      <c r="D219" t="s">
         <v>363</v>
       </c>
-      <c r="D219" t="s">
+      <c r="E219" t="s">
         <v>364</v>
       </c>
-      <c r="E219" t="s">
+      <c r="F219" t="s">
         <v>365</v>
-      </c>
-      <c r="F219" t="s">
-        <v>165</v>
       </c>
       <c r="G219" t="s">
         <v>366</v>
@@ -6656,19 +6656,19 @@
         <v>8</v>
       </c>
       <c r="C220" t="s">
+        <v>163</v>
+      </c>
+      <c r="D220" t="s">
         <v>363</v>
       </c>
-      <c r="D220" t="s">
+      <c r="E220" t="s">
+        <v>364</v>
+      </c>
+      <c r="F220" t="s">
+        <v>271</v>
+      </c>
+      <c r="G220" t="s">
         <v>309</v>
-      </c>
-      <c r="E220" t="s">
-        <v>271</v>
-      </c>
-      <c r="F220" t="s">
-        <v>165</v>
-      </c>
-      <c r="G220" t="s">
-        <v>366</v>
       </c>
     </row>
     <row r="221" spans="1:7">
@@ -6679,16 +6679,16 @@
         <v>8</v>
       </c>
       <c r="C221" t="s">
+        <v>163</v>
+      </c>
+      <c r="D221" t="s">
         <v>363</v>
       </c>
-      <c r="D221" t="s">
+      <c r="E221" t="s">
         <v>364</v>
       </c>
-      <c r="E221" t="s">
+      <c r="F221" t="s">
         <v>365</v>
-      </c>
-      <c r="F221" t="s">
-        <v>165</v>
       </c>
       <c r="G221" t="s">
         <v>366</v>
@@ -6702,16 +6702,16 @@
         <v>8</v>
       </c>
       <c r="C222" t="s">
+        <v>163</v>
+      </c>
+      <c r="D222" t="s">
         <v>363</v>
       </c>
-      <c r="D222" t="s">
+      <c r="E222" t="s">
         <v>364</v>
       </c>
-      <c r="E222" t="s">
+      <c r="F222" t="s">
         <v>365</v>
-      </c>
-      <c r="F222" t="s">
-        <v>165</v>
       </c>
       <c r="G222" t="s">
         <v>366</v>
@@ -6725,16 +6725,16 @@
         <v>8</v>
       </c>
       <c r="C223" t="s">
+        <v>163</v>
+      </c>
+      <c r="D223" t="s">
         <v>363</v>
       </c>
-      <c r="D223" t="s">
+      <c r="E223" t="s">
         <v>364</v>
       </c>
-      <c r="E223" t="s">
+      <c r="F223" t="s">
         <v>365</v>
-      </c>
-      <c r="F223" t="s">
-        <v>165</v>
       </c>
       <c r="G223" t="s">
         <v>366</v>
@@ -6748,16 +6748,16 @@
         <v>8</v>
       </c>
       <c r="C224" t="s">
+        <v>163</v>
+      </c>
+      <c r="D224" t="s">
         <v>363</v>
       </c>
-      <c r="D224" t="s">
+      <c r="E224" t="s">
         <v>364</v>
       </c>
-      <c r="E224" t="s">
+      <c r="F224" t="s">
         <v>365</v>
-      </c>
-      <c r="F224" t="s">
-        <v>165</v>
       </c>
       <c r="G224" t="s">
         <v>366</v>
@@ -6771,16 +6771,16 @@
         <v>8</v>
       </c>
       <c r="C225" t="s">
+        <v>163</v>
+      </c>
+      <c r="D225" t="s">
         <v>363</v>
       </c>
-      <c r="D225" t="s">
+      <c r="E225" t="s">
         <v>364</v>
       </c>
-      <c r="E225" t="s">
+      <c r="F225" t="s">
         <v>365</v>
-      </c>
-      <c r="F225" t="s">
-        <v>165</v>
       </c>
       <c r="G225" t="s">
         <v>366</v>
@@ -6794,19 +6794,19 @@
         <v>8</v>
       </c>
       <c r="C226" t="s">
+        <v>163</v>
+      </c>
+      <c r="D226" t="s">
         <v>363</v>
       </c>
-      <c r="D226" t="s">
+      <c r="E226" t="s">
+        <v>364</v>
+      </c>
+      <c r="F226" t="s">
         <v>275</v>
       </c>
-      <c r="E226" t="s">
+      <c r="G226" t="s">
         <v>276</v>
-      </c>
-      <c r="F226" t="s">
-        <v>165</v>
-      </c>
-      <c r="G226" t="s">
-        <v>366</v>
       </c>
     </row>
     <row r="227" spans="1:7">
@@ -6817,16 +6817,16 @@
         <v>8</v>
       </c>
       <c r="C227" t="s">
+        <v>163</v>
+      </c>
+      <c r="D227" t="s">
         <v>363</v>
       </c>
-      <c r="D227" t="s">
+      <c r="E227" t="s">
         <v>364</v>
       </c>
-      <c r="E227" t="s">
+      <c r="F227" t="s">
         <v>365</v>
-      </c>
-      <c r="F227" t="s">
-        <v>165</v>
       </c>
       <c r="G227" t="s">
         <v>366</v>
@@ -6840,19 +6840,19 @@
         <v>8</v>
       </c>
       <c r="C228" t="s">
+        <v>163</v>
+      </c>
+      <c r="D228" t="s">
         <v>363</v>
       </c>
-      <c r="D228" t="s">
-        <v>163</v>
-      </c>
       <c r="E228" t="s">
+        <v>364</v>
+      </c>
+      <c r="F228" t="s">
         <v>164</v>
       </c>
-      <c r="F228" t="s">
+      <c r="G228" t="s">
         <v>165</v>
-      </c>
-      <c r="G228" t="s">
-        <v>366</v>
       </c>
     </row>
     <row r="229" spans="1:7">
@@ -6863,16 +6863,16 @@
         <v>8</v>
       </c>
       <c r="C229" t="s">
+        <v>163</v>
+      </c>
+      <c r="D229" t="s">
         <v>363</v>
       </c>
-      <c r="D229" t="s">
+      <c r="E229" t="s">
         <v>386</v>
       </c>
-      <c r="E229" t="s">
+      <c r="F229" t="s">
         <v>365</v>
-      </c>
-      <c r="F229" t="s">
-        <v>165</v>
       </c>
       <c r="G229" t="s">
         <v>387</v>
@@ -6886,16 +6886,16 @@
         <v>8</v>
       </c>
       <c r="C230" t="s">
+        <v>163</v>
+      </c>
+      <c r="D230" t="s">
         <v>363</v>
       </c>
-      <c r="D230" t="s">
+      <c r="E230" t="s">
         <v>386</v>
       </c>
-      <c r="E230" t="s">
+      <c r="F230" t="s">
         <v>365</v>
-      </c>
-      <c r="F230" t="s">
-        <v>165</v>
       </c>
       <c r="G230" t="s">
         <v>387</v>
@@ -6909,19 +6909,19 @@
         <v>8</v>
       </c>
       <c r="C231" t="s">
+        <v>163</v>
+      </c>
+      <c r="D231" t="s">
         <v>363</v>
       </c>
-      <c r="D231" t="s">
+      <c r="E231" t="s">
+        <v>386</v>
+      </c>
+      <c r="F231" t="s">
+        <v>271</v>
+      </c>
+      <c r="G231" t="s">
         <v>293</v>
-      </c>
-      <c r="E231" t="s">
-        <v>271</v>
-      </c>
-      <c r="F231" t="s">
-        <v>165</v>
-      </c>
-      <c r="G231" t="s">
-        <v>387</v>
       </c>
     </row>
     <row r="232" spans="1:7">
@@ -6932,19 +6932,19 @@
         <v>8</v>
       </c>
       <c r="C232" t="s">
+        <v>163</v>
+      </c>
+      <c r="D232" t="s">
         <v>363</v>
       </c>
-      <c r="D232" t="s">
+      <c r="E232" t="s">
+        <v>386</v>
+      </c>
+      <c r="F232" t="s">
+        <v>271</v>
+      </c>
+      <c r="G232" t="s">
         <v>309</v>
-      </c>
-      <c r="E232" t="s">
-        <v>271</v>
-      </c>
-      <c r="F232" t="s">
-        <v>165</v>
-      </c>
-      <c r="G232" t="s">
-        <v>387</v>
       </c>
     </row>
     <row r="233" spans="1:7">
@@ -6955,16 +6955,16 @@
         <v>8</v>
       </c>
       <c r="C233" t="s">
+        <v>163</v>
+      </c>
+      <c r="D233" t="s">
         <v>363</v>
       </c>
-      <c r="D233" t="s">
+      <c r="E233" t="s">
         <v>386</v>
       </c>
-      <c r="E233" t="s">
+      <c r="F233" t="s">
         <v>365</v>
-      </c>
-      <c r="F233" t="s">
-        <v>165</v>
       </c>
       <c r="G233" t="s">
         <v>387</v>
@@ -6978,16 +6978,16 @@
         <v>8</v>
       </c>
       <c r="C234" t="s">
+        <v>163</v>
+      </c>
+      <c r="D234" t="s">
         <v>363</v>
       </c>
-      <c r="D234" t="s">
+      <c r="E234" t="s">
         <v>386</v>
       </c>
-      <c r="E234" t="s">
+      <c r="F234" t="s">
         <v>365</v>
-      </c>
-      <c r="F234" t="s">
-        <v>165</v>
       </c>
       <c r="G234" t="s">
         <v>387</v>
@@ -7001,16 +7001,16 @@
         <v>8</v>
       </c>
       <c r="C235" t="s">
+        <v>163</v>
+      </c>
+      <c r="D235" t="s">
         <v>363</v>
       </c>
-      <c r="D235" t="s">
+      <c r="E235" t="s">
         <v>386</v>
       </c>
-      <c r="E235" t="s">
+      <c r="F235" t="s">
         <v>365</v>
-      </c>
-      <c r="F235" t="s">
-        <v>165</v>
       </c>
       <c r="G235" t="s">
         <v>387</v>
@@ -7024,16 +7024,16 @@
         <v>8</v>
       </c>
       <c r="C236" t="s">
+        <v>163</v>
+      </c>
+      <c r="D236" t="s">
         <v>363</v>
       </c>
-      <c r="D236" t="s">
+      <c r="E236" t="s">
         <v>386</v>
       </c>
-      <c r="E236" t="s">
+      <c r="F236" t="s">
         <v>365</v>
-      </c>
-      <c r="F236" t="s">
-        <v>165</v>
       </c>
       <c r="G236" t="s">
         <v>387</v>
@@ -7047,16 +7047,16 @@
         <v>8</v>
       </c>
       <c r="C237" t="s">
+        <v>163</v>
+      </c>
+      <c r="D237" t="s">
         <v>363</v>
       </c>
-      <c r="D237" t="s">
+      <c r="E237" t="s">
         <v>386</v>
       </c>
-      <c r="E237" t="s">
+      <c r="F237" t="s">
         <v>365</v>
-      </c>
-      <c r="F237" t="s">
-        <v>165</v>
       </c>
       <c r="G237" t="s">
         <v>387</v>
@@ -7070,16 +7070,16 @@
         <v>8</v>
       </c>
       <c r="C238" t="s">
+        <v>163</v>
+      </c>
+      <c r="D238" t="s">
         <v>363</v>
       </c>
-      <c r="D238" t="s">
+      <c r="E238" t="s">
         <v>386</v>
       </c>
-      <c r="E238" t="s">
+      <c r="F238" t="s">
         <v>365</v>
-      </c>
-      <c r="F238" t="s">
-        <v>165</v>
       </c>
       <c r="G238" t="s">
         <v>387</v>
@@ -7093,16 +7093,16 @@
         <v>8</v>
       </c>
       <c r="C239" t="s">
+        <v>163</v>
+      </c>
+      <c r="D239" t="s">
         <v>363</v>
       </c>
-      <c r="D239" t="s">
+      <c r="E239" t="s">
         <v>398</v>
       </c>
-      <c r="E239" t="s">
+      <c r="F239" t="s">
         <v>365</v>
-      </c>
-      <c r="F239" t="s">
-        <v>165</v>
       </c>
       <c r="G239" t="s">
         <v>399</v>
@@ -7116,19 +7116,19 @@
         <v>8</v>
       </c>
       <c r="C240" t="s">
+        <v>163</v>
+      </c>
+      <c r="D240" t="s">
         <v>401</v>
       </c>
-      <c r="D240" t="s">
-        <v>163</v>
-      </c>
       <c r="E240" t="s">
+        <v>402</v>
+      </c>
+      <c r="F240" t="s">
         <v>164</v>
       </c>
-      <c r="F240" t="s">
+      <c r="G240" t="s">
         <v>165</v>
-      </c>
-      <c r="G240" t="s">
-        <v>402</v>
       </c>
     </row>
     <row r="241" spans="1:7">
@@ -7139,19 +7139,19 @@
         <v>8</v>
       </c>
       <c r="C241" t="s">
+        <v>163</v>
+      </c>
+      <c r="D241" t="s">
         <v>401</v>
       </c>
-      <c r="D241" t="s">
-        <v>163</v>
-      </c>
       <c r="E241" t="s">
+        <v>402</v>
+      </c>
+      <c r="F241" t="s">
         <v>164</v>
       </c>
-      <c r="F241" t="s">
+      <c r="G241" t="s">
         <v>165</v>
-      </c>
-      <c r="G241" t="s">
-        <v>402</v>
       </c>
     </row>
     <row r="242" spans="1:7">
@@ -7162,19 +7162,19 @@
         <v>8</v>
       </c>
       <c r="C242" t="s">
+        <v>163</v>
+      </c>
+      <c r="D242" t="s">
         <v>401</v>
       </c>
-      <c r="D242" t="s">
-        <v>163</v>
-      </c>
       <c r="E242" t="s">
+        <v>402</v>
+      </c>
+      <c r="F242" t="s">
         <v>164</v>
       </c>
-      <c r="F242" t="s">
+      <c r="G242" t="s">
         <v>165</v>
-      </c>
-      <c r="G242" t="s">
-        <v>402</v>
       </c>
     </row>
     <row r="243" spans="1:7">
@@ -7185,19 +7185,19 @@
         <v>8</v>
       </c>
       <c r="C243" t="s">
+        <v>163</v>
+      </c>
+      <c r="D243" t="s">
         <v>401</v>
       </c>
-      <c r="D243" t="s">
-        <v>163</v>
-      </c>
       <c r="E243" t="s">
+        <v>402</v>
+      </c>
+      <c r="F243" t="s">
         <v>164</v>
       </c>
-      <c r="F243" t="s">
+      <c r="G243" t="s">
         <v>165</v>
-      </c>
-      <c r="G243" t="s">
-        <v>402</v>
       </c>
     </row>
     <row r="244" spans="1:7">
@@ -7208,19 +7208,19 @@
         <v>8</v>
       </c>
       <c r="C244" t="s">
+        <v>163</v>
+      </c>
+      <c r="D244" t="s">
         <v>401</v>
       </c>
-      <c r="D244" t="s">
-        <v>163</v>
-      </c>
       <c r="E244" t="s">
+        <v>402</v>
+      </c>
+      <c r="F244" t="s">
         <v>164</v>
       </c>
-      <c r="F244" t="s">
+      <c r="G244" t="s">
         <v>165</v>
-      </c>
-      <c r="G244" t="s">
-        <v>402</v>
       </c>
     </row>
     <row r="245" spans="1:7">
@@ -7231,19 +7231,19 @@
         <v>8</v>
       </c>
       <c r="C245" t="s">
+        <v>163</v>
+      </c>
+      <c r="D245" t="s">
         <v>401</v>
       </c>
-      <c r="D245" t="s">
-        <v>163</v>
-      </c>
       <c r="E245" t="s">
+        <v>402</v>
+      </c>
+      <c r="F245" t="s">
         <v>164</v>
       </c>
-      <c r="F245" t="s">
+      <c r="G245" t="s">
         <v>165</v>
-      </c>
-      <c r="G245" t="s">
-        <v>402</v>
       </c>
     </row>
     <row r="246" spans="1:7">
@@ -7254,16 +7254,16 @@
         <v>8</v>
       </c>
       <c r="C246" t="s">
+        <v>163</v>
+      </c>
+      <c r="D246" t="s">
         <v>401</v>
       </c>
-      <c r="D246" t="s">
+      <c r="E246" t="s">
         <v>409</v>
       </c>
-      <c r="E246" t="s">
-        <v>256</v>
-      </c>
       <c r="F246" t="s">
-        <v>165</v>
+        <v>255</v>
       </c>
       <c r="G246" t="s">
         <v>410</v>
@@ -7277,15 +7277,15 @@
         <v>8</v>
       </c>
       <c r="C247" t="s">
+        <v>95</v>
+      </c>
+      <c r="D247" t="s">
         <v>412</v>
       </c>
-      <c r="D247" t="s">
-        <v>95</v>
-      </c>
-      <c r="E247" t="s">
+      <c r="F247" t="s">
         <v>96</v>
       </c>
-      <c r="F247" t="s">
+      <c r="G247" t="s">
         <v>97</v>
       </c>
     </row>
@@ -7297,15 +7297,15 @@
         <v>8</v>
       </c>
       <c r="C248" t="s">
+        <v>95</v>
+      </c>
+      <c r="D248" t="s">
         <v>412</v>
       </c>
-      <c r="D248" t="s">
-        <v>95</v>
-      </c>
-      <c r="E248" t="s">
+      <c r="F248" t="s">
         <v>96</v>
       </c>
-      <c r="F248" t="s">
+      <c r="G248" t="s">
         <v>97</v>
       </c>
     </row>
@@ -7317,16 +7317,16 @@
         <v>8</v>
       </c>
       <c r="C249" t="s">
+        <v>95</v>
+      </c>
+      <c r="D249" t="s">
         <v>412</v>
       </c>
-      <c r="D249" t="s">
+      <c r="F249" t="s">
         <v>415</v>
       </c>
-      <c r="E249" t="s">
+      <c r="G249" t="s">
         <v>416</v>
-      </c>
-      <c r="F249" t="s">
-        <v>97</v>
       </c>
     </row>
     <row r="250" spans="1:7">
@@ -7337,15 +7337,15 @@
         <v>8</v>
       </c>
       <c r="C250" t="s">
+        <v>95</v>
+      </c>
+      <c r="D250" t="s">
         <v>412</v>
       </c>
-      <c r="D250" t="s">
-        <v>95</v>
-      </c>
-      <c r="E250" t="s">
+      <c r="F250" t="s">
         <v>96</v>
       </c>
-      <c r="F250" t="s">
+      <c r="G250" t="s">
         <v>97</v>
       </c>
     </row>
@@ -7357,15 +7357,15 @@
         <v>8</v>
       </c>
       <c r="C251" t="s">
+        <v>95</v>
+      </c>
+      <c r="D251" t="s">
         <v>412</v>
       </c>
-      <c r="D251" t="s">
-        <v>95</v>
-      </c>
-      <c r="E251" t="s">
+      <c r="F251" t="s">
         <v>96</v>
       </c>
-      <c r="F251" t="s">
+      <c r="G251" t="s">
         <v>97</v>
       </c>
     </row>
@@ -7377,15 +7377,15 @@
         <v>8</v>
       </c>
       <c r="C252" t="s">
+        <v>95</v>
+      </c>
+      <c r="D252" t="s">
         <v>412</v>
       </c>
-      <c r="D252" t="s">
-        <v>95</v>
-      </c>
-      <c r="E252" t="s">
+      <c r="F252" t="s">
         <v>96</v>
       </c>
-      <c r="F252" t="s">
+      <c r="G252" t="s">
         <v>97</v>
       </c>
     </row>
@@ -7397,16 +7397,16 @@
         <v>8</v>
       </c>
       <c r="C253" t="s">
+        <v>163</v>
+      </c>
+      <c r="D253" t="s">
         <v>421</v>
       </c>
-      <c r="D253" t="s">
+      <c r="F253" t="s">
         <v>422</v>
       </c>
-      <c r="E253" t="s">
+      <c r="G253" t="s">
         <v>423</v>
-      </c>
-      <c r="F253" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="254" spans="1:7">
@@ -7417,16 +7417,16 @@
         <v>8</v>
       </c>
       <c r="C254" t="s">
+        <v>90</v>
+      </c>
+      <c r="D254" t="s">
         <v>421</v>
       </c>
-      <c r="D254" t="s">
+      <c r="F254" t="s">
         <v>219</v>
       </c>
-      <c r="E254" t="s">
+      <c r="G254" t="s">
         <v>220</v>
-      </c>
-      <c r="F254" t="s">
-        <v>93</v>
       </c>
     </row>
     <row r="255" spans="1:7">
@@ -7437,16 +7437,16 @@
         <v>8</v>
       </c>
       <c r="C255" t="s">
+        <v>90</v>
+      </c>
+      <c r="D255" t="s">
         <v>421</v>
       </c>
-      <c r="D255" t="s">
+      <c r="F255" t="s">
         <v>426</v>
       </c>
-      <c r="E255" t="s">
+      <c r="G255" t="s">
         <v>427</v>
-      </c>
-      <c r="F255" t="s">
-        <v>93</v>
       </c>
     </row>
     <row r="256" spans="1:7">
@@ -7457,19 +7457,19 @@
         <v>8</v>
       </c>
       <c r="C256" t="s">
+        <v>90</v>
+      </c>
+      <c r="D256" t="s">
         <v>421</v>
       </c>
-      <c r="D256" t="s">
+      <c r="F256" t="s">
         <v>426</v>
       </c>
-      <c r="E256" t="s">
+      <c r="G256" t="s">
         <v>427</v>
       </c>
-      <c r="F256" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="257" spans="1:6">
+    </row>
+    <row r="257" spans="1:7">
       <c r="A257" t="s">
         <v>429</v>
       </c>
@@ -7477,19 +7477,19 @@
         <v>8</v>
       </c>
       <c r="C257" t="s">
+        <v>90</v>
+      </c>
+      <c r="D257" t="s">
         <v>421</v>
       </c>
-      <c r="D257" t="s">
+      <c r="F257" t="s">
         <v>426</v>
       </c>
-      <c r="E257" t="s">
+      <c r="G257" t="s">
         <v>427</v>
       </c>
-      <c r="F257" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="258" spans="1:6">
+    </row>
+    <row r="258" spans="1:7">
       <c r="A258" t="s">
         <v>430</v>
       </c>
@@ -7497,19 +7497,19 @@
         <v>8</v>
       </c>
       <c r="C258" t="s">
+        <v>163</v>
+      </c>
+      <c r="D258" t="s">
         <v>421</v>
       </c>
-      <c r="D258" t="s">
-        <v>326</v>
-      </c>
-      <c r="E258" t="s">
+      <c r="F258" t="s">
         <v>327</v>
       </c>
-      <c r="F258" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="259" spans="1:6">
+      <c r="G258" t="s">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="259" spans="1:7">
       <c r="A259" t="s">
         <v>431</v>
       </c>
@@ -7517,19 +7517,19 @@
         <v>8</v>
       </c>
       <c r="C259" t="s">
+        <v>90</v>
+      </c>
+      <c r="D259" t="s">
         <v>421</v>
       </c>
-      <c r="D259" t="s">
+      <c r="F259" t="s">
         <v>426</v>
       </c>
-      <c r="E259" t="s">
+      <c r="G259" t="s">
         <v>427</v>
       </c>
-      <c r="F259" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="260" spans="1:6">
+    </row>
+    <row r="260" spans="1:7">
       <c r="A260" t="s">
         <v>432</v>
       </c>
@@ -7537,19 +7537,19 @@
         <v>8</v>
       </c>
       <c r="C260" t="s">
+        <v>163</v>
+      </c>
+      <c r="D260" t="s">
         <v>421</v>
       </c>
-      <c r="D260" t="s">
-        <v>163</v>
-      </c>
-      <c r="E260" t="s">
+      <c r="F260" t="s">
         <v>164</v>
       </c>
-      <c r="F260" t="s">
+      <c r="G260" t="s">
         <v>165</v>
       </c>
     </row>
-    <row r="261" spans="1:6">
+    <row r="261" spans="1:7">
       <c r="A261" t="s">
         <v>433</v>
       </c>
@@ -7557,19 +7557,19 @@
         <v>8</v>
       </c>
       <c r="C261" t="s">
+        <v>195</v>
+      </c>
+      <c r="D261" t="s">
         <v>421</v>
       </c>
-      <c r="D261" t="s">
+      <c r="F261" t="s">
         <v>434</v>
       </c>
-      <c r="E261" t="s">
+      <c r="G261" t="s">
         <v>435</v>
       </c>
-      <c r="F261" t="s">
-        <v>197</v>
-      </c>
-    </row>
-    <row r="262" spans="1:6">
+    </row>
+    <row r="262" spans="1:7">
       <c r="A262" t="s">
         <v>436</v>
       </c>
@@ -7577,19 +7577,19 @@
         <v>8</v>
       </c>
       <c r="C262" t="s">
+        <v>163</v>
+      </c>
+      <c r="D262" t="s">
         <v>421</v>
       </c>
-      <c r="D262" t="s">
-        <v>163</v>
-      </c>
-      <c r="E262" t="s">
+      <c r="F262" t="s">
         <v>164</v>
       </c>
-      <c r="F262" t="s">
+      <c r="G262" t="s">
         <v>165</v>
       </c>
     </row>
-    <row r="263" spans="1:6">
+    <row r="263" spans="1:7">
       <c r="A263" t="s">
         <v>437</v>
       </c>
@@ -7597,19 +7597,19 @@
         <v>8</v>
       </c>
       <c r="C263" t="s">
+        <v>182</v>
+      </c>
+      <c r="D263" t="s">
         <v>421</v>
       </c>
-      <c r="D263" t="s">
+      <c r="F263" t="s">
         <v>438</v>
       </c>
-      <c r="E263" t="s">
+      <c r="G263" t="s">
         <v>439</v>
       </c>
-      <c r="F263" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="264" spans="1:6">
+    </row>
+    <row r="264" spans="1:7">
       <c r="A264" t="s">
         <v>440</v>
       </c>
@@ -7617,19 +7617,19 @@
         <v>8</v>
       </c>
       <c r="C264" t="s">
+        <v>31</v>
+      </c>
+      <c r="D264" t="s">
         <v>421</v>
       </c>
-      <c r="D264" t="s">
-        <v>31</v>
-      </c>
-      <c r="E264" t="s">
+      <c r="F264" t="s">
         <v>32</v>
       </c>
-      <c r="F264" t="s">
+      <c r="G264" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="265" spans="1:6">
+    <row r="265" spans="1:7">
       <c r="A265" t="s">
         <v>441</v>
       </c>
@@ -7637,19 +7637,19 @@
         <v>8</v>
       </c>
       <c r="C265" t="s">
+        <v>9</v>
+      </c>
+      <c r="D265" t="s">
         <v>421</v>
-      </c>
-      <c r="D265" t="s">
-        <v>10</v>
-      </c>
-      <c r="E265" t="s">
-        <v>11</v>
       </c>
       <c r="F265" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="266" spans="1:6">
+      <c r="G265" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="266" spans="1:7">
       <c r="A266" t="s">
         <v>442</v>
       </c>
@@ -7657,19 +7657,19 @@
         <v>8</v>
       </c>
       <c r="C266" t="s">
+        <v>112</v>
+      </c>
+      <c r="D266" t="s">
         <v>421</v>
       </c>
-      <c r="D266" t="s">
+      <c r="F266" t="s">
         <v>443</v>
       </c>
-      <c r="E266" t="s">
+      <c r="G266" t="s">
         <v>444</v>
       </c>
-      <c r="F266" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="267" spans="1:6">
+    </row>
+    <row r="267" spans="1:7">
       <c r="A267" t="s">
         <v>445</v>
       </c>
@@ -7677,19 +7677,19 @@
         <v>8</v>
       </c>
       <c r="C267" t="s">
+        <v>112</v>
+      </c>
+      <c r="D267" t="s">
         <v>446</v>
       </c>
-      <c r="D267" t="s">
+      <c r="F267" t="s">
         <v>118</v>
       </c>
-      <c r="E267" t="s">
+      <c r="G267" t="s">
         <v>119</v>
       </c>
-      <c r="F267" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="268" spans="1:6">
+    </row>
+    <row r="268" spans="1:7">
       <c r="A268" t="s">
         <v>447</v>
       </c>
@@ -7697,19 +7697,19 @@
         <v>8</v>
       </c>
       <c r="C268" t="s">
+        <v>182</v>
+      </c>
+      <c r="D268" t="s">
         <v>448</v>
       </c>
-      <c r="D268" t="s">
+      <c r="F268" t="s">
         <v>203</v>
       </c>
-      <c r="E268" t="s">
+      <c r="G268" t="s">
         <v>204</v>
       </c>
-      <c r="F268" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="269" spans="1:6">
+    </row>
+    <row r="269" spans="1:7">
       <c r="A269" t="s">
         <v>449</v>
       </c>
@@ -7717,19 +7717,19 @@
         <v>8</v>
       </c>
       <c r="C269" t="s">
+        <v>112</v>
+      </c>
+      <c r="D269" t="s">
         <v>450</v>
       </c>
-      <c r="D269" t="s">
+      <c r="F269" t="s">
         <v>118</v>
       </c>
-      <c r="E269" t="s">
+      <c r="G269" t="s">
         <v>119</v>
       </c>
-      <c r="F269" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="270" spans="1:6">
+    </row>
+    <row r="270" spans="1:7">
       <c r="A270" t="s">
         <v>451</v>
       </c>
@@ -7737,19 +7737,19 @@
         <v>8</v>
       </c>
       <c r="C270" t="s">
+        <v>112</v>
+      </c>
+      <c r="D270" t="s">
         <v>450</v>
       </c>
-      <c r="D270" t="s">
+      <c r="F270" t="s">
         <v>118</v>
       </c>
-      <c r="E270" t="s">
+      <c r="G270" t="s">
         <v>119</v>
       </c>
-      <c r="F270" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="271" spans="1:6">
+    </row>
+    <row r="271" spans="1:7">
       <c r="A271" t="s">
         <v>452</v>
       </c>
@@ -7757,19 +7757,19 @@
         <v>8</v>
       </c>
       <c r="C271" t="s">
+        <v>112</v>
+      </c>
+      <c r="D271" t="s">
         <v>453</v>
       </c>
-      <c r="D271" t="s">
+      <c r="F271" t="s">
         <v>454</v>
       </c>
-      <c r="E271" t="s">
+      <c r="G271" t="s">
         <v>455</v>
       </c>
-      <c r="F271" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="272" spans="1:6">
+    </row>
+    <row r="272" spans="1:7">
       <c r="A272" t="s">
         <v>456</v>
       </c>
@@ -7777,19 +7777,19 @@
         <v>8</v>
       </c>
       <c r="C272" t="s">
+        <v>112</v>
+      </c>
+      <c r="D272" t="s">
         <v>453</v>
       </c>
-      <c r="D272" t="s">
+      <c r="F272" t="s">
         <v>454</v>
       </c>
-      <c r="E272" t="s">
+      <c r="G272" t="s">
         <v>455</v>
       </c>
-      <c r="F272" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="273" spans="1:6">
+    </row>
+    <row r="273" spans="1:7">
       <c r="A273" t="s">
         <v>457</v>
       </c>
@@ -7797,19 +7797,19 @@
         <v>8</v>
       </c>
       <c r="C273" t="s">
+        <v>112</v>
+      </c>
+      <c r="D273" t="s">
         <v>453</v>
       </c>
-      <c r="D273" t="s">
+      <c r="F273" t="s">
         <v>454</v>
       </c>
-      <c r="E273" t="s">
+      <c r="G273" t="s">
         <v>455</v>
       </c>
-      <c r="F273" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="274" spans="1:6">
+    </row>
+    <row r="274" spans="1:7">
       <c r="A274" t="s">
         <v>458</v>
       </c>
@@ -7817,19 +7817,19 @@
         <v>8</v>
       </c>
       <c r="C274" t="s">
+        <v>112</v>
+      </c>
+      <c r="D274" t="s">
         <v>453</v>
       </c>
-      <c r="D274" t="s">
+      <c r="F274" t="s">
         <v>454</v>
       </c>
-      <c r="E274" t="s">
+      <c r="G274" t="s">
         <v>455</v>
       </c>
-      <c r="F274" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="275" spans="1:6">
+    </row>
+    <row r="275" spans="1:7">
       <c r="A275" t="s">
         <v>459</v>
       </c>
@@ -7837,19 +7837,19 @@
         <v>8</v>
       </c>
       <c r="C275" t="s">
+        <v>112</v>
+      </c>
+      <c r="D275" t="s">
         <v>453</v>
       </c>
-      <c r="D275" t="s">
+      <c r="F275" t="s">
         <v>454</v>
       </c>
-      <c r="E275" t="s">
+      <c r="G275" t="s">
         <v>455</v>
       </c>
-      <c r="F275" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="276" spans="1:6">
+    </row>
+    <row r="276" spans="1:7">
       <c r="A276" t="s">
         <v>460</v>
       </c>
@@ -7857,19 +7857,19 @@
         <v>8</v>
       </c>
       <c r="C276" t="s">
+        <v>112</v>
+      </c>
+      <c r="D276" t="s">
         <v>453</v>
       </c>
-      <c r="D276" t="s">
+      <c r="F276" t="s">
         <v>454</v>
       </c>
-      <c r="E276" t="s">
+      <c r="G276" t="s">
         <v>455</v>
       </c>
-      <c r="F276" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="277" spans="1:6">
+    </row>
+    <row r="277" spans="1:7">
       <c r="A277" t="s">
         <v>461</v>
       </c>
@@ -7877,19 +7877,19 @@
         <v>8</v>
       </c>
       <c r="C277" t="s">
+        <v>112</v>
+      </c>
+      <c r="D277" t="s">
         <v>453</v>
       </c>
-      <c r="D277" t="s">
+      <c r="F277" t="s">
         <v>454</v>
       </c>
-      <c r="E277" t="s">
+      <c r="G277" t="s">
         <v>455</v>
       </c>
-      <c r="F277" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="278" spans="1:6">
+    </row>
+    <row r="278" spans="1:7">
       <c r="A278" t="s">
         <v>462</v>
       </c>
@@ -7897,19 +7897,19 @@
         <v>8</v>
       </c>
       <c r="C278" t="s">
+        <v>182</v>
+      </c>
+      <c r="D278" t="s">
         <v>463</v>
       </c>
-      <c r="D278" t="s">
+      <c r="F278" t="s">
         <v>203</v>
       </c>
-      <c r="E278" t="s">
+      <c r="G278" t="s">
         <v>204</v>
       </c>
-      <c r="F278" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="279" spans="1:6">
+    </row>
+    <row r="279" spans="1:7">
       <c r="A279" t="s">
         <v>464</v>
       </c>
@@ -7917,19 +7917,19 @@
         <v>8</v>
       </c>
       <c r="C279" t="s">
+        <v>31</v>
+      </c>
+      <c r="D279" t="s">
         <v>463</v>
       </c>
-      <c r="D279" t="s">
-        <v>52</v>
-      </c>
-      <c r="E279" t="s">
+      <c r="F279" t="s">
         <v>53</v>
       </c>
-      <c r="F279" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="280" spans="1:6">
+      <c r="G279" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="280" spans="1:7">
       <c r="A280" t="s">
         <v>465</v>
       </c>
@@ -7937,19 +7937,19 @@
         <v>8</v>
       </c>
       <c r="C280" t="s">
+        <v>9</v>
+      </c>
+      <c r="D280" t="s">
         <v>463</v>
-      </c>
-      <c r="D280" t="s">
-        <v>10</v>
-      </c>
-      <c r="E280" t="s">
-        <v>11</v>
       </c>
       <c r="F280" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="281" spans="1:6">
+      <c r="G280" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="281" spans="1:7">
       <c r="A281" t="s">
         <v>466</v>
       </c>
@@ -7957,19 +7957,19 @@
         <v>8</v>
       </c>
       <c r="C281" t="s">
+        <v>112</v>
+      </c>
+      <c r="D281" t="s">
         <v>463</v>
       </c>
-      <c r="D281" t="s">
+      <c r="F281" t="s">
         <v>170</v>
       </c>
-      <c r="E281" t="s">
+      <c r="G281" t="s">
         <v>171</v>
       </c>
-      <c r="F281" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="282" spans="1:6">
+    </row>
+    <row r="282" spans="1:7">
       <c r="A282" t="s">
         <v>467</v>
       </c>
@@ -7977,19 +7977,19 @@
         <v>8</v>
       </c>
       <c r="C282" t="s">
+        <v>124</v>
+      </c>
+      <c r="D282" t="s">
         <v>463</v>
       </c>
-      <c r="D282" t="s">
-        <v>124</v>
-      </c>
-      <c r="E282" t="s">
+      <c r="F282" t="s">
         <v>125</v>
       </c>
-      <c r="F282" t="s">
+      <c r="G282" t="s">
         <v>126</v>
       </c>
     </row>
-    <row r="283" spans="1:6">
+    <row r="283" spans="1:7">
       <c r="A283" t="s">
         <v>468</v>
       </c>
@@ -7997,19 +7997,19 @@
         <v>8</v>
       </c>
       <c r="C283" t="s">
+        <v>163</v>
+      </c>
+      <c r="D283" t="s">
         <v>469</v>
       </c>
-      <c r="D283" t="s">
-        <v>398</v>
-      </c>
-      <c r="E283" t="s">
+      <c r="F283" t="s">
         <v>365</v>
       </c>
-      <c r="F283" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="284" spans="1:6">
+      <c r="G283" t="s">
+        <v>399</v>
+      </c>
+    </row>
+    <row r="284" spans="1:7">
       <c r="A284" t="s">
         <v>470</v>
       </c>
@@ -8017,19 +8017,19 @@
         <v>8</v>
       </c>
       <c r="C284" t="s">
+        <v>124</v>
+      </c>
+      <c r="D284" t="s">
         <v>471</v>
       </c>
-      <c r="D284" t="s">
-        <v>124</v>
-      </c>
-      <c r="E284" t="s">
+      <c r="F284" t="s">
         <v>125</v>
       </c>
-      <c r="F284" t="s">
+      <c r="G284" t="s">
         <v>126</v>
       </c>
     </row>
-    <row r="285" spans="1:6">
+    <row r="285" spans="1:7">
       <c r="A285" t="s">
         <v>472</v>
       </c>
@@ -8037,19 +8037,19 @@
         <v>8</v>
       </c>
       <c r="C285" t="s">
+        <v>112</v>
+      </c>
+      <c r="D285" t="s">
         <v>473</v>
       </c>
-      <c r="D285" t="s">
+      <c r="F285" t="s">
         <v>170</v>
       </c>
-      <c r="E285" t="s">
+      <c r="G285" t="s">
         <v>171</v>
       </c>
-      <c r="F285" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="286" spans="1:6">
+    </row>
+    <row r="286" spans="1:7">
       <c r="A286" t="s">
         <v>474</v>
       </c>
@@ -8057,19 +8057,19 @@
         <v>8</v>
       </c>
       <c r="C286" t="s">
+        <v>182</v>
+      </c>
+      <c r="D286" t="s">
         <v>475</v>
       </c>
-      <c r="D286" t="s">
+      <c r="F286" t="s">
         <v>438</v>
       </c>
-      <c r="E286" t="s">
+      <c r="G286" t="s">
         <v>439</v>
       </c>
-      <c r="F286" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="287" spans="1:6">
+    </row>
+    <row r="287" spans="1:7">
       <c r="A287" t="s">
         <v>476</v>
       </c>
@@ -8077,19 +8077,19 @@
         <v>8</v>
       </c>
       <c r="C287" t="s">
+        <v>182</v>
+      </c>
+      <c r="D287" t="s">
         <v>475</v>
       </c>
-      <c r="D287" t="s">
+      <c r="F287" t="s">
         <v>438</v>
       </c>
-      <c r="E287" t="s">
+      <c r="G287" t="s">
         <v>439</v>
       </c>
-      <c r="F287" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="288" spans="1:6">
+    </row>
+    <row r="288" spans="1:7">
       <c r="A288" t="s">
         <v>477</v>
       </c>
@@ -8097,19 +8097,19 @@
         <v>8</v>
       </c>
       <c r="C288" t="s">
+        <v>9</v>
+      </c>
+      <c r="D288" t="s">
         <v>475</v>
       </c>
-      <c r="D288" t="s">
+      <c r="F288" t="s">
         <v>41</v>
       </c>
-      <c r="E288" t="s">
+      <c r="G288" t="s">
         <v>42</v>
       </c>
-      <c r="F288" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="289" spans="1:6">
+    </row>
+    <row r="289" spans="1:7">
       <c r="A289" t="s">
         <v>478</v>
       </c>
@@ -8117,19 +8117,19 @@
         <v>8</v>
       </c>
       <c r="C289" t="s">
+        <v>31</v>
+      </c>
+      <c r="D289" t="s">
         <v>475</v>
       </c>
-      <c r="D289" t="s">
-        <v>31</v>
-      </c>
-      <c r="E289" t="s">
+      <c r="F289" t="s">
         <v>32</v>
       </c>
-      <c r="F289" t="s">
+      <c r="G289" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="290" spans="1:6">
+    <row r="290" spans="1:7">
       <c r="A290" t="s">
         <v>479</v>
       </c>
@@ -8137,19 +8137,19 @@
         <v>8</v>
       </c>
       <c r="C290" t="s">
+        <v>31</v>
+      </c>
+      <c r="D290" t="s">
         <v>475</v>
       </c>
-      <c r="D290" t="s">
-        <v>31</v>
-      </c>
-      <c r="E290" t="s">
+      <c r="F290" t="s">
         <v>32</v>
       </c>
-      <c r="F290" t="s">
+      <c r="G290" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="291" spans="1:6">
+    <row r="291" spans="1:7">
       <c r="A291" t="s">
         <v>480</v>
       </c>
@@ -8157,19 +8157,19 @@
         <v>8</v>
       </c>
       <c r="C291" t="s">
+        <v>112</v>
+      </c>
+      <c r="D291" t="s">
         <v>475</v>
       </c>
-      <c r="D291" t="s">
+      <c r="F291" t="s">
         <v>170</v>
       </c>
-      <c r="E291" t="s">
+      <c r="G291" t="s">
         <v>171</v>
       </c>
-      <c r="F291" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="292" spans="1:6">
+    </row>
+    <row r="292" spans="1:7">
       <c r="A292" t="s">
         <v>481</v>
       </c>
@@ -8177,19 +8177,19 @@
         <v>8</v>
       </c>
       <c r="C292" t="s">
+        <v>112</v>
+      </c>
+      <c r="D292" t="s">
         <v>475</v>
       </c>
-      <c r="D292" t="s">
+      <c r="F292" t="s">
         <v>170</v>
       </c>
-      <c r="E292" t="s">
+      <c r="G292" t="s">
         <v>171</v>
       </c>
-      <c r="F292" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="293" spans="1:6">
+    </row>
+    <row r="293" spans="1:7">
       <c r="A293" t="s">
         <v>482</v>
       </c>
@@ -8197,19 +8197,19 @@
         <v>8</v>
       </c>
       <c r="C293" t="s">
+        <v>112</v>
+      </c>
+      <c r="D293" t="s">
         <v>475</v>
       </c>
-      <c r="D293" t="s">
+      <c r="F293" t="s">
         <v>170</v>
       </c>
-      <c r="E293" t="s">
+      <c r="G293" t="s">
         <v>171</v>
       </c>
-      <c r="F293" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="294" spans="1:6">
+    </row>
+    <row r="294" spans="1:7">
       <c r="A294" t="s">
         <v>483</v>
       </c>
@@ -8217,19 +8217,19 @@
         <v>8</v>
       </c>
       <c r="C294" t="s">
+        <v>112</v>
+      </c>
+      <c r="D294" t="s">
         <v>475</v>
       </c>
-      <c r="D294" t="s">
+      <c r="F294" t="s">
         <v>170</v>
       </c>
-      <c r="E294" t="s">
+      <c r="G294" t="s">
         <v>171</v>
       </c>
-      <c r="F294" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="295" spans="1:6">
+    </row>
+    <row r="295" spans="1:7">
       <c r="A295" t="s">
         <v>484</v>
       </c>
@@ -8237,19 +8237,19 @@
         <v>8</v>
       </c>
       <c r="C295" t="s">
+        <v>112</v>
+      </c>
+      <c r="D295" t="s">
         <v>485</v>
       </c>
-      <c r="D295" t="s">
+      <c r="F295" t="s">
         <v>170</v>
       </c>
-      <c r="E295" t="s">
+      <c r="G295" t="s">
         <v>171</v>
       </c>
-      <c r="F295" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="296" spans="1:6">
+    </row>
+    <row r="296" spans="1:7">
       <c r="A296" t="s">
         <v>486</v>
       </c>
@@ -8257,16 +8257,16 @@
         <v>8</v>
       </c>
       <c r="C296" t="s">
+        <v>112</v>
+      </c>
+      <c r="D296" t="s">
         <v>485</v>
       </c>
-      <c r="D296" t="s">
+      <c r="F296" t="s">
         <v>170</v>
       </c>
-      <c r="E296" t="s">
+      <c r="G296" t="s">
         <v>171</v>
-      </c>
-      <c r="F296" t="s">
-        <v>115</v>
       </c>
     </row>
   </sheetData>

--- a/api/2/xlsx/fr/SectorCOFOG.xlsx
+++ b/api/2/xlsx/fr/SectorCOFOG.xlsx
@@ -22,18 +22,18 @@
     <t>status</t>
   </si>
   <si>
+    <t>codeforiati:category-code</t>
+  </si>
+  <si>
     <t>codeforiati:cofog-division</t>
   </si>
   <si>
+    <t>codeforiati:cofog-group</t>
+  </si>
+  <si>
     <t>codeforiati:group-code</t>
   </si>
   <si>
-    <t>codeforiati:category-code</t>
-  </si>
-  <si>
-    <t>codeforiati:cofog-group</t>
-  </si>
-  <si>
     <t>codeforiati:cofog-class</t>
   </si>
   <si>
@@ -43,18 +43,18 @@
     <t>active</t>
   </si>
   <si>
+    <t>111</t>
+  </si>
+  <si>
     <t>09 - Education</t>
   </si>
   <si>
+    <t>09.8 - Education n.e.c.</t>
+  </si>
+  <si>
     <t>110</t>
   </si>
   <si>
-    <t>111</t>
-  </si>
-  <si>
-    <t>09.8 - Education n.e.c.</t>
-  </si>
-  <si>
     <t>09.8.0 - Education n.e.c. (CS)</t>
   </si>
   <si>
@@ -169,15 +169,15 @@
     <t>12110</t>
   </si>
   <si>
+    <t>121</t>
+  </si>
+  <si>
+    <t>07.6 - Health n.e.c.</t>
+  </si>
+  <si>
     <t>120</t>
   </si>
   <si>
-    <t>121</t>
-  </si>
-  <si>
-    <t>07.6 - Health n.e.c.</t>
-  </si>
-  <si>
     <t>07.6.0 - Health n.e.c. (CS)</t>
   </si>
   <si>
@@ -289,12 +289,12 @@
     <t>06 - Housing and community amenities</t>
   </si>
   <si>
+    <t>06.3 - Water supply</t>
+  </si>
+  <si>
     <t>140</t>
   </si>
   <si>
-    <t>06.3 - Water supply</t>
-  </si>
-  <si>
     <t>06.3.0 - Water supply (CS)</t>
   </si>
   <si>
@@ -352,18 +352,18 @@
     <t>15110</t>
   </si>
   <si>
+    <t>151</t>
+  </si>
+  <si>
     <t>01 - General public services</t>
   </si>
   <si>
+    <t>01.3 - General services</t>
+  </si>
+  <si>
     <t>150</t>
   </si>
   <si>
-    <t>151</t>
-  </si>
-  <si>
-    <t>01.3 - General services</t>
-  </si>
-  <si>
     <t>01.3.1 - General personnel services (CS)</t>
   </si>
   <si>
@@ -622,12 +622,12 @@
     <t>16010</t>
   </si>
   <si>
+    <t>10.9 - Social protection n.e.c.</t>
+  </si>
+  <si>
     <t>160</t>
   </si>
   <si>
-    <t>10.9 - Social protection n.e.c.</t>
-  </si>
-  <si>
     <t>10.9.0 - Social protection n.e.c. (CS)</t>
   </si>
   <si>
@@ -823,15 +823,15 @@
     <t>23110</t>
   </si>
   <si>
+    <t>231</t>
+  </si>
+  <si>
+    <t>04.3 - Fuel and energy</t>
+  </si>
+  <si>
     <t>230</t>
   </si>
   <si>
-    <t>231</t>
-  </si>
-  <si>
-    <t>04.3 - Fuel and energy</t>
-  </si>
-  <si>
     <t>04.3.5 - Electricity (CS)</t>
   </si>
   <si>
@@ -991,15 +991,15 @@
     <t>31110</t>
   </si>
   <si>
+    <t>311</t>
+  </si>
+  <si>
+    <t>04.2 - Agriculture, forestry, fishing and hunting</t>
+  </si>
+  <si>
     <t>310</t>
   </si>
   <si>
-    <t>311</t>
-  </si>
-  <si>
-    <t>04.2 - Agriculture, forestry, fishing and hunting</t>
-  </si>
-  <si>
     <t>04.2.1 - Agriculture (CS)</t>
   </si>
   <si>
@@ -1105,15 +1105,15 @@
     <t>32110</t>
   </si>
   <si>
+    <t>321</t>
+  </si>
+  <si>
+    <t>04.4 - Mining, manufacturing and construction</t>
+  </si>
+  <si>
     <t>320</t>
   </si>
   <si>
-    <t>321</t>
-  </si>
-  <si>
-    <t>04.4 - Mining, manufacturing and construction</t>
-  </si>
-  <si>
     <t>04.4.2 - Manufacturing (CS)</t>
   </si>
   <si>
@@ -1219,12 +1219,12 @@
     <t>33110</t>
   </si>
   <si>
+    <t>331</t>
+  </si>
+  <si>
     <t>330</t>
   </si>
   <si>
-    <t>331</t>
-  </si>
-  <si>
     <t>33120</t>
   </si>
   <si>
@@ -1279,12 +1279,12 @@
     <t>43010</t>
   </si>
   <si>
+    <t>04.9 - Economic affairs n.e.c.</t>
+  </si>
+  <si>
     <t>430</t>
   </si>
   <si>
-    <t>04.9 - Economic affairs n.e.c.</t>
-  </si>
-  <si>
     <t>04.9.0 - Economic affairs n.e.c. (CS)</t>
   </si>
   <si>
@@ -1375,10 +1375,10 @@
     <t>60010</t>
   </si>
   <si>
+    <t>01.7 - Public debt transactions</t>
+  </si>
+  <si>
     <t>600</t>
-  </si>
-  <si>
-    <t>01.7 - Public debt transactions</t>
   </si>
   <si>
     <t>01.7.0 - Public debt transactions (CS)</t>
@@ -1869,10 +1869,10 @@
         <v>10</v>
       </c>
       <c r="E3" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="F3" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="G3" t="s">
         <v>16</v>
@@ -1915,10 +1915,10 @@
         <v>10</v>
       </c>
       <c r="E5" t="s">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="F5" t="s">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="G5" t="s">
         <v>20</v>
@@ -1932,16 +1932,16 @@
         <v>8</v>
       </c>
       <c r="C6" t="s">
-        <v>9</v>
+        <v>22</v>
       </c>
       <c r="D6" t="s">
         <v>10</v>
       </c>
       <c r="E6" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F6" t="s">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="G6" t="s">
         <v>24</v>
@@ -1955,13 +1955,13 @@
         <v>8</v>
       </c>
       <c r="C7" t="s">
-        <v>9</v>
+        <v>22</v>
       </c>
       <c r="D7" t="s">
         <v>10</v>
       </c>
       <c r="E7" t="s">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="F7" t="s">
         <v>12</v>
@@ -1978,16 +1978,16 @@
         <v>8</v>
       </c>
       <c r="C8" t="s">
-        <v>9</v>
+        <v>22</v>
       </c>
       <c r="D8" t="s">
         <v>10</v>
       </c>
       <c r="E8" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F8" t="s">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="G8" t="s">
         <v>24</v>
@@ -2001,16 +2001,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="s">
-        <v>9</v>
+        <v>22</v>
       </c>
       <c r="D9" t="s">
         <v>10</v>
       </c>
       <c r="E9" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F9" t="s">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="G9" t="s">
         <v>24</v>
@@ -2024,16 +2024,16 @@
         <v>8</v>
       </c>
       <c r="C10" t="s">
-        <v>9</v>
+        <v>22</v>
       </c>
       <c r="D10" t="s">
         <v>10</v>
       </c>
       <c r="E10" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F10" t="s">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="G10" t="s">
         <v>29</v>
@@ -2047,16 +2047,16 @@
         <v>8</v>
       </c>
       <c r="C11" t="s">
+        <v>22</v>
+      </c>
+      <c r="D11" t="s">
         <v>31</v>
       </c>
-      <c r="D11" t="s">
-        <v>10</v>
-      </c>
       <c r="E11" t="s">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="F11" t="s">
-        <v>32</v>
+        <v>12</v>
       </c>
       <c r="G11" t="s">
         <v>33</v>
@@ -2070,16 +2070,16 @@
         <v>8</v>
       </c>
       <c r="C12" t="s">
-        <v>9</v>
+        <v>22</v>
       </c>
       <c r="D12" t="s">
         <v>10</v>
       </c>
       <c r="E12" t="s">
-        <v>22</v>
+        <v>35</v>
       </c>
       <c r="F12" t="s">
-        <v>35</v>
+        <v>12</v>
       </c>
       <c r="G12" t="s">
         <v>36</v>
@@ -2093,16 +2093,16 @@
         <v>8</v>
       </c>
       <c r="C13" t="s">
-        <v>9</v>
+        <v>38</v>
       </c>
       <c r="D13" t="s">
         <v>10</v>
       </c>
       <c r="E13" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="F13" t="s">
-        <v>35</v>
+        <v>12</v>
       </c>
       <c r="G13" t="s">
         <v>39</v>
@@ -2116,16 +2116,16 @@
         <v>8</v>
       </c>
       <c r="C14" t="s">
-        <v>9</v>
+        <v>38</v>
       </c>
       <c r="D14" t="s">
         <v>10</v>
       </c>
       <c r="E14" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="F14" t="s">
-        <v>41</v>
+        <v>12</v>
       </c>
       <c r="G14" t="s">
         <v>42</v>
@@ -2139,16 +2139,16 @@
         <v>8</v>
       </c>
       <c r="C15" t="s">
-        <v>9</v>
+        <v>44</v>
       </c>
       <c r="D15" t="s">
         <v>10</v>
       </c>
       <c r="E15" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F15" t="s">
-        <v>45</v>
+        <v>12</v>
       </c>
       <c r="G15" t="s">
         <v>46</v>
@@ -2162,16 +2162,16 @@
         <v>8</v>
       </c>
       <c r="C16" t="s">
-        <v>9</v>
+        <v>44</v>
       </c>
       <c r="D16" t="s">
         <v>10</v>
       </c>
       <c r="E16" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="F16" t="s">
-        <v>48</v>
+        <v>12</v>
       </c>
       <c r="G16" t="s">
         <v>49</v>
@@ -2185,10 +2185,10 @@
         <v>8</v>
       </c>
       <c r="C17" t="s">
+        <v>51</v>
+      </c>
+      <c r="D17" t="s">
         <v>31</v>
-      </c>
-      <c r="D17" t="s">
-        <v>51</v>
       </c>
       <c r="E17" t="s">
         <v>52</v>
@@ -2208,10 +2208,10 @@
         <v>8</v>
       </c>
       <c r="C18" t="s">
+        <v>51</v>
+      </c>
+      <c r="D18" t="s">
         <v>31</v>
-      </c>
-      <c r="D18" t="s">
-        <v>51</v>
       </c>
       <c r="E18" t="s">
         <v>52</v>
@@ -2231,16 +2231,16 @@
         <v>8</v>
       </c>
       <c r="C19" t="s">
+        <v>51</v>
+      </c>
+      <c r="D19" t="s">
         <v>31</v>
       </c>
-      <c r="D19" t="s">
-        <v>51</v>
-      </c>
       <c r="E19" t="s">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="F19" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="G19" t="s">
         <v>58</v>
@@ -2254,16 +2254,16 @@
         <v>8</v>
       </c>
       <c r="C20" t="s">
+        <v>51</v>
+      </c>
+      <c r="D20" t="s">
         <v>31</v>
       </c>
-      <c r="D20" t="s">
-        <v>51</v>
-      </c>
       <c r="E20" t="s">
-        <v>52</v>
+        <v>60</v>
       </c>
       <c r="F20" t="s">
-        <v>60</v>
+        <v>53</v>
       </c>
       <c r="G20" t="s">
         <v>61</v>
@@ -2277,10 +2277,10 @@
         <v>8</v>
       </c>
       <c r="C21" t="s">
+        <v>51</v>
+      </c>
+      <c r="D21" t="s">
         <v>31</v>
-      </c>
-      <c r="D21" t="s">
-        <v>51</v>
       </c>
       <c r="E21" t="s">
         <v>52</v>
@@ -2300,16 +2300,16 @@
         <v>8</v>
       </c>
       <c r="C22" t="s">
+        <v>64</v>
+      </c>
+      <c r="D22" t="s">
         <v>31</v>
       </c>
-      <c r="D22" t="s">
-        <v>51</v>
-      </c>
       <c r="E22" t="s">
-        <v>64</v>
+        <v>32</v>
       </c>
       <c r="F22" t="s">
-        <v>32</v>
+        <v>53</v>
       </c>
       <c r="G22" t="s">
         <v>33</v>
@@ -2323,16 +2323,16 @@
         <v>8</v>
       </c>
       <c r="C23" t="s">
+        <v>64</v>
+      </c>
+      <c r="D23" t="s">
         <v>31</v>
       </c>
-      <c r="D23" t="s">
-        <v>51</v>
-      </c>
       <c r="E23" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="F23" t="s">
-        <v>66</v>
+        <v>53</v>
       </c>
       <c r="G23" t="s">
         <v>67</v>
@@ -2346,16 +2346,16 @@
         <v>8</v>
       </c>
       <c r="C24" t="s">
+        <v>64</v>
+      </c>
+      <c r="D24" t="s">
         <v>31</v>
       </c>
-      <c r="D24" t="s">
-        <v>51</v>
-      </c>
       <c r="E24" t="s">
-        <v>64</v>
+        <v>32</v>
       </c>
       <c r="F24" t="s">
-        <v>32</v>
+        <v>53</v>
       </c>
       <c r="G24" t="s">
         <v>33</v>
@@ -2369,16 +2369,16 @@
         <v>8</v>
       </c>
       <c r="C25" t="s">
+        <v>64</v>
+      </c>
+      <c r="D25" t="s">
         <v>31</v>
       </c>
-      <c r="D25" t="s">
-        <v>51</v>
-      </c>
       <c r="E25" t="s">
-        <v>64</v>
+        <v>32</v>
       </c>
       <c r="F25" t="s">
-        <v>32</v>
+        <v>53</v>
       </c>
       <c r="G25" t="s">
         <v>33</v>
@@ -2392,16 +2392,16 @@
         <v>8</v>
       </c>
       <c r="C26" t="s">
+        <v>64</v>
+      </c>
+      <c r="D26" t="s">
         <v>31</v>
       </c>
-      <c r="D26" t="s">
-        <v>51</v>
-      </c>
       <c r="E26" t="s">
-        <v>64</v>
+        <v>32</v>
       </c>
       <c r="F26" t="s">
-        <v>32</v>
+        <v>53</v>
       </c>
       <c r="G26" t="s">
         <v>33</v>
@@ -2415,16 +2415,16 @@
         <v>8</v>
       </c>
       <c r="C27" t="s">
+        <v>64</v>
+      </c>
+      <c r="D27" t="s">
         <v>31</v>
       </c>
-      <c r="D27" t="s">
-        <v>51</v>
-      </c>
       <c r="E27" t="s">
-        <v>64</v>
+        <v>32</v>
       </c>
       <c r="F27" t="s">
-        <v>32</v>
+        <v>53</v>
       </c>
       <c r="G27" t="s">
         <v>33</v>
@@ -2438,16 +2438,16 @@
         <v>8</v>
       </c>
       <c r="C28" t="s">
+        <v>64</v>
+      </c>
+      <c r="D28" t="s">
         <v>31</v>
       </c>
-      <c r="D28" t="s">
-        <v>51</v>
-      </c>
       <c r="E28" t="s">
-        <v>64</v>
+        <v>32</v>
       </c>
       <c r="F28" t="s">
-        <v>32</v>
+        <v>53</v>
       </c>
       <c r="G28" t="s">
         <v>33</v>
@@ -2461,16 +2461,16 @@
         <v>8</v>
       </c>
       <c r="C29" t="s">
+        <v>64</v>
+      </c>
+      <c r="D29" t="s">
         <v>31</v>
       </c>
-      <c r="D29" t="s">
-        <v>51</v>
-      </c>
       <c r="E29" t="s">
-        <v>64</v>
+        <v>32</v>
       </c>
       <c r="F29" t="s">
-        <v>32</v>
+        <v>53</v>
       </c>
       <c r="G29" t="s">
         <v>33</v>
@@ -2484,13 +2484,13 @@
         <v>8</v>
       </c>
       <c r="C30" t="s">
+        <v>64</v>
+      </c>
+      <c r="D30" t="s">
         <v>31</v>
       </c>
-      <c r="D30" t="s">
-        <v>51</v>
-      </c>
       <c r="E30" t="s">
-        <v>64</v>
+        <v>52</v>
       </c>
       <c r="F30" t="s">
         <v>53</v>
@@ -2507,16 +2507,16 @@
         <v>8</v>
       </c>
       <c r="C31" t="s">
+        <v>76</v>
+      </c>
+      <c r="D31" t="s">
         <v>31</v>
       </c>
-      <c r="D31" t="s">
-        <v>51</v>
-      </c>
       <c r="E31" t="s">
-        <v>76</v>
+        <v>32</v>
       </c>
       <c r="F31" t="s">
-        <v>32</v>
+        <v>53</v>
       </c>
       <c r="G31" t="s">
         <v>33</v>
@@ -2530,16 +2530,16 @@
         <v>8</v>
       </c>
       <c r="C32" t="s">
+        <v>76</v>
+      </c>
+      <c r="D32" t="s">
         <v>31</v>
       </c>
-      <c r="D32" t="s">
-        <v>51</v>
-      </c>
       <c r="E32" t="s">
-        <v>76</v>
+        <v>32</v>
       </c>
       <c r="F32" t="s">
-        <v>32</v>
+        <v>53</v>
       </c>
       <c r="G32" t="s">
         <v>33</v>
@@ -2553,16 +2553,16 @@
         <v>8</v>
       </c>
       <c r="C33" t="s">
+        <v>76</v>
+      </c>
+      <c r="D33" t="s">
         <v>31</v>
       </c>
-      <c r="D33" t="s">
-        <v>51</v>
-      </c>
       <c r="E33" t="s">
-        <v>76</v>
+        <v>32</v>
       </c>
       <c r="F33" t="s">
-        <v>32</v>
+        <v>53</v>
       </c>
       <c r="G33" t="s">
         <v>33</v>
@@ -2576,16 +2576,16 @@
         <v>8</v>
       </c>
       <c r="C34" t="s">
+        <v>76</v>
+      </c>
+      <c r="D34" t="s">
         <v>31</v>
       </c>
-      <c r="D34" t="s">
-        <v>51</v>
-      </c>
       <c r="E34" t="s">
-        <v>76</v>
+        <v>32</v>
       </c>
       <c r="F34" t="s">
-        <v>32</v>
+        <v>53</v>
       </c>
       <c r="G34" t="s">
         <v>33</v>
@@ -2599,16 +2599,16 @@
         <v>8</v>
       </c>
       <c r="C35" t="s">
+        <v>76</v>
+      </c>
+      <c r="D35" t="s">
         <v>31</v>
       </c>
-      <c r="D35" t="s">
-        <v>51</v>
-      </c>
       <c r="E35" t="s">
-        <v>76</v>
+        <v>32</v>
       </c>
       <c r="F35" t="s">
-        <v>32</v>
+        <v>53</v>
       </c>
       <c r="G35" t="s">
         <v>33</v>
@@ -2622,16 +2622,16 @@
         <v>8</v>
       </c>
       <c r="C36" t="s">
+        <v>76</v>
+      </c>
+      <c r="D36" t="s">
         <v>31</v>
       </c>
-      <c r="D36" t="s">
-        <v>51</v>
-      </c>
       <c r="E36" t="s">
-        <v>76</v>
+        <v>57</v>
       </c>
       <c r="F36" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="G36" t="s">
         <v>58</v>
@@ -2644,14 +2644,14 @@
       <c r="B37" t="s">
         <v>8</v>
       </c>
-      <c r="C37" t="s">
+      <c r="D37" t="s">
         <v>31</v>
       </c>
-      <c r="D37" t="s">
+      <c r="E37" t="s">
+        <v>32</v>
+      </c>
+      <c r="F37" t="s">
         <v>83</v>
-      </c>
-      <c r="F37" t="s">
-        <v>32</v>
       </c>
       <c r="G37" t="s">
         <v>33</v>
@@ -2664,14 +2664,14 @@
       <c r="B38" t="s">
         <v>8</v>
       </c>
-      <c r="C38" t="s">
+      <c r="D38" t="s">
         <v>31</v>
       </c>
-      <c r="D38" t="s">
+      <c r="E38" t="s">
+        <v>32</v>
+      </c>
+      <c r="F38" t="s">
         <v>83</v>
-      </c>
-      <c r="F38" t="s">
-        <v>32</v>
       </c>
       <c r="G38" t="s">
         <v>33</v>
@@ -2684,14 +2684,14 @@
       <c r="B39" t="s">
         <v>8</v>
       </c>
-      <c r="C39" t="s">
+      <c r="D39" t="s">
         <v>31</v>
       </c>
-      <c r="D39" t="s">
+      <c r="E39" t="s">
+        <v>32</v>
+      </c>
+      <c r="F39" t="s">
         <v>83</v>
-      </c>
-      <c r="F39" t="s">
-        <v>32</v>
       </c>
       <c r="G39" t="s">
         <v>33</v>
@@ -2704,14 +2704,14 @@
       <c r="B40" t="s">
         <v>8</v>
       </c>
-      <c r="C40" t="s">
+      <c r="D40" t="s">
         <v>31</v>
       </c>
-      <c r="D40" t="s">
+      <c r="E40" t="s">
+        <v>32</v>
+      </c>
+      <c r="F40" t="s">
         <v>83</v>
-      </c>
-      <c r="F40" t="s">
-        <v>32</v>
       </c>
       <c r="G40" t="s">
         <v>33</v>
@@ -2724,14 +2724,14 @@
       <c r="B41" t="s">
         <v>8</v>
       </c>
-      <c r="C41" t="s">
+      <c r="D41" t="s">
         <v>31</v>
       </c>
-      <c r="D41" t="s">
+      <c r="E41" t="s">
+        <v>52</v>
+      </c>
+      <c r="F41" t="s">
         <v>83</v>
-      </c>
-      <c r="F41" t="s">
-        <v>53</v>
       </c>
       <c r="G41" t="s">
         <v>54</v>
@@ -2744,14 +2744,14 @@
       <c r="B42" t="s">
         <v>8</v>
       </c>
-      <c r="C42" t="s">
+      <c r="D42" t="s">
         <v>31</v>
       </c>
-      <c r="D42" t="s">
+      <c r="E42" t="s">
+        <v>57</v>
+      </c>
+      <c r="F42" t="s">
         <v>83</v>
-      </c>
-      <c r="F42" t="s">
-        <v>57</v>
       </c>
       <c r="G42" t="s">
         <v>58</v>
@@ -2764,10 +2764,10 @@
       <c r="B43" t="s">
         <v>8</v>
       </c>
-      <c r="C43" t="s">
+      <c r="D43" t="s">
         <v>90</v>
       </c>
-      <c r="D43" t="s">
+      <c r="E43" t="s">
         <v>91</v>
       </c>
       <c r="F43" t="s">
@@ -2784,14 +2784,14 @@
       <c r="B44" t="s">
         <v>8</v>
       </c>
-      <c r="C44" t="s">
+      <c r="D44" t="s">
         <v>95</v>
       </c>
-      <c r="D44" t="s">
-        <v>91</v>
+      <c r="E44" t="s">
+        <v>96</v>
       </c>
       <c r="F44" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="G44" t="s">
         <v>97</v>
@@ -2804,10 +2804,10 @@
       <c r="B45" t="s">
         <v>8</v>
       </c>
-      <c r="C45" t="s">
+      <c r="D45" t="s">
         <v>90</v>
       </c>
-      <c r="D45" t="s">
+      <c r="E45" t="s">
         <v>91</v>
       </c>
       <c r="F45" t="s">
@@ -2824,10 +2824,10 @@
       <c r="B46" t="s">
         <v>8</v>
       </c>
-      <c r="C46" t="s">
+      <c r="D46" t="s">
         <v>90</v>
       </c>
-      <c r="D46" t="s">
+      <c r="E46" t="s">
         <v>91</v>
       </c>
       <c r="F46" t="s">
@@ -2844,14 +2844,14 @@
       <c r="B47" t="s">
         <v>8</v>
       </c>
-      <c r="C47" t="s">
+      <c r="D47" t="s">
         <v>95</v>
       </c>
-      <c r="D47" t="s">
-        <v>91</v>
+      <c r="E47" t="s">
+        <v>101</v>
       </c>
       <c r="F47" t="s">
-        <v>101</v>
+        <v>92</v>
       </c>
       <c r="G47" t="s">
         <v>102</v>
@@ -2864,10 +2864,10 @@
       <c r="B48" t="s">
         <v>8</v>
       </c>
-      <c r="C48" t="s">
+      <c r="D48" t="s">
         <v>90</v>
       </c>
-      <c r="D48" t="s">
+      <c r="E48" t="s">
         <v>91</v>
       </c>
       <c r="F48" t="s">
@@ -2884,10 +2884,10 @@
       <c r="B49" t="s">
         <v>8</v>
       </c>
-      <c r="C49" t="s">
+      <c r="D49" t="s">
         <v>90</v>
       </c>
-      <c r="D49" t="s">
+      <c r="E49" t="s">
         <v>91</v>
       </c>
       <c r="F49" t="s">
@@ -2904,14 +2904,14 @@
       <c r="B50" t="s">
         <v>8</v>
       </c>
-      <c r="C50" t="s">
+      <c r="D50" t="s">
         <v>95</v>
       </c>
-      <c r="D50" t="s">
-        <v>91</v>
+      <c r="E50" t="s">
+        <v>101</v>
       </c>
       <c r="F50" t="s">
-        <v>101</v>
+        <v>92</v>
       </c>
       <c r="G50" t="s">
         <v>102</v>
@@ -2924,10 +2924,10 @@
       <c r="B51" t="s">
         <v>8</v>
       </c>
-      <c r="C51" t="s">
+      <c r="D51" t="s">
         <v>90</v>
       </c>
-      <c r="D51" t="s">
+      <c r="E51" t="s">
         <v>91</v>
       </c>
       <c r="F51" t="s">
@@ -2944,14 +2944,14 @@
       <c r="B52" t="s">
         <v>8</v>
       </c>
-      <c r="C52" t="s">
+      <c r="D52" t="s">
         <v>95</v>
       </c>
-      <c r="D52" t="s">
-        <v>91</v>
+      <c r="E52" t="s">
+        <v>108</v>
       </c>
       <c r="F52" t="s">
-        <v>108</v>
+        <v>92</v>
       </c>
       <c r="G52" t="s">
         <v>109</v>
@@ -2964,14 +2964,14 @@
       <c r="B53" t="s">
         <v>8</v>
       </c>
-      <c r="C53" t="s">
-        <v>9</v>
-      </c>
       <c r="D53" t="s">
-        <v>91</v>
+        <v>10</v>
+      </c>
+      <c r="E53" t="s">
+        <v>11</v>
       </c>
       <c r="F53" t="s">
-        <v>12</v>
+        <v>92</v>
       </c>
       <c r="G53" t="s">
         <v>13</v>
@@ -3014,10 +3014,10 @@
         <v>113</v>
       </c>
       <c r="E55" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="F55" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="G55" t="s">
         <v>119</v>
@@ -3037,10 +3037,10 @@
         <v>113</v>
       </c>
       <c r="E56" t="s">
-        <v>114</v>
+        <v>121</v>
       </c>
       <c r="F56" t="s">
-        <v>121</v>
+        <v>115</v>
       </c>
       <c r="G56" t="s">
         <v>122</v>
@@ -3054,16 +3054,16 @@
         <v>8</v>
       </c>
       <c r="C57" t="s">
+        <v>112</v>
+      </c>
+      <c r="D57" t="s">
         <v>124</v>
       </c>
-      <c r="D57" t="s">
-        <v>113</v>
-      </c>
       <c r="E57" t="s">
-        <v>114</v>
+        <v>125</v>
       </c>
       <c r="F57" t="s">
-        <v>125</v>
+        <v>115</v>
       </c>
       <c r="G57" t="s">
         <v>126</v>
@@ -3083,10 +3083,10 @@
         <v>113</v>
       </c>
       <c r="E58" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="F58" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="G58" t="s">
         <v>119</v>
@@ -3106,10 +3106,10 @@
         <v>113</v>
       </c>
       <c r="E59" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="F59" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="G59" t="s">
         <v>119</v>
@@ -3129,10 +3129,10 @@
         <v>113</v>
       </c>
       <c r="E60" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="F60" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="G60" t="s">
         <v>119</v>
@@ -3152,10 +3152,10 @@
         <v>113</v>
       </c>
       <c r="E61" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="F61" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="G61" t="s">
         <v>119</v>
@@ -3175,10 +3175,10 @@
         <v>113</v>
       </c>
       <c r="E62" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="F62" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="G62" t="s">
         <v>119</v>
@@ -3198,10 +3198,10 @@
         <v>113</v>
       </c>
       <c r="E63" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="F63" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="G63" t="s">
         <v>133</v>
@@ -3221,10 +3221,10 @@
         <v>113</v>
       </c>
       <c r="E64" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="F64" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="G64" t="s">
         <v>133</v>
@@ -3244,10 +3244,10 @@
         <v>113</v>
       </c>
       <c r="E65" t="s">
-        <v>114</v>
+        <v>136</v>
       </c>
       <c r="F65" t="s">
-        <v>136</v>
+        <v>115</v>
       </c>
       <c r="G65" t="s">
         <v>137</v>
@@ -3290,10 +3290,10 @@
         <v>113</v>
       </c>
       <c r="E67" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="F67" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="G67" t="s">
         <v>119</v>
@@ -3359,10 +3359,10 @@
         <v>113</v>
       </c>
       <c r="E70" t="s">
-        <v>114</v>
+        <v>121</v>
       </c>
       <c r="F70" t="s">
-        <v>121</v>
+        <v>115</v>
       </c>
       <c r="G70" t="s">
         <v>122</v>
@@ -3382,10 +3382,10 @@
         <v>113</v>
       </c>
       <c r="E71" t="s">
-        <v>114</v>
+        <v>121</v>
       </c>
       <c r="F71" t="s">
-        <v>121</v>
+        <v>115</v>
       </c>
       <c r="G71" t="s">
         <v>122</v>
@@ -3422,16 +3422,16 @@
         <v>8</v>
       </c>
       <c r="C73" t="s">
+        <v>112</v>
+      </c>
+      <c r="D73" t="s">
         <v>124</v>
       </c>
-      <c r="D73" t="s">
-        <v>113</v>
-      </c>
       <c r="E73" t="s">
-        <v>114</v>
+        <v>148</v>
       </c>
       <c r="F73" t="s">
-        <v>148</v>
+        <v>115</v>
       </c>
       <c r="G73" t="s">
         <v>149</v>
@@ -3445,16 +3445,16 @@
         <v>8</v>
       </c>
       <c r="C74" t="s">
+        <v>112</v>
+      </c>
+      <c r="D74" t="s">
         <v>124</v>
       </c>
-      <c r="D74" t="s">
-        <v>113</v>
-      </c>
       <c r="E74" t="s">
-        <v>114</v>
+        <v>151</v>
       </c>
       <c r="F74" t="s">
-        <v>151</v>
+        <v>115</v>
       </c>
       <c r="G74" t="s">
         <v>152</v>
@@ -3468,16 +3468,16 @@
         <v>8</v>
       </c>
       <c r="C75" t="s">
+        <v>112</v>
+      </c>
+      <c r="D75" t="s">
         <v>124</v>
       </c>
-      <c r="D75" t="s">
-        <v>113</v>
-      </c>
       <c r="E75" t="s">
-        <v>114</v>
+        <v>154</v>
       </c>
       <c r="F75" t="s">
-        <v>154</v>
+        <v>115</v>
       </c>
       <c r="G75" t="s">
         <v>155</v>
@@ -3491,16 +3491,16 @@
         <v>8</v>
       </c>
       <c r="C76" t="s">
+        <v>112</v>
+      </c>
+      <c r="D76" t="s">
         <v>124</v>
       </c>
-      <c r="D76" t="s">
-        <v>113</v>
-      </c>
       <c r="E76" t="s">
-        <v>114</v>
+        <v>148</v>
       </c>
       <c r="F76" t="s">
-        <v>148</v>
+        <v>115</v>
       </c>
       <c r="G76" t="s">
         <v>149</v>
@@ -3514,16 +3514,16 @@
         <v>8</v>
       </c>
       <c r="C77" t="s">
+        <v>112</v>
+      </c>
+      <c r="D77" t="s">
         <v>124</v>
       </c>
-      <c r="D77" t="s">
-        <v>113</v>
-      </c>
       <c r="E77" t="s">
-        <v>114</v>
+        <v>148</v>
       </c>
       <c r="F77" t="s">
-        <v>148</v>
+        <v>115</v>
       </c>
       <c r="G77" t="s">
         <v>149</v>
@@ -3537,16 +3537,16 @@
         <v>8</v>
       </c>
       <c r="C78" t="s">
+        <v>112</v>
+      </c>
+      <c r="D78" t="s">
         <v>124</v>
       </c>
-      <c r="D78" t="s">
-        <v>113</v>
-      </c>
       <c r="E78" t="s">
-        <v>114</v>
+        <v>151</v>
       </c>
       <c r="F78" t="s">
-        <v>151</v>
+        <v>115</v>
       </c>
       <c r="G78" t="s">
         <v>152</v>
@@ -3560,16 +3560,16 @@
         <v>8</v>
       </c>
       <c r="C79" t="s">
+        <v>112</v>
+      </c>
+      <c r="D79" t="s">
         <v>124</v>
       </c>
-      <c r="D79" t="s">
-        <v>113</v>
-      </c>
       <c r="E79" t="s">
-        <v>114</v>
+        <v>160</v>
       </c>
       <c r="F79" t="s">
-        <v>160</v>
+        <v>115</v>
       </c>
       <c r="G79" t="s">
         <v>161</v>
@@ -3583,16 +3583,16 @@
         <v>8</v>
       </c>
       <c r="C80" t="s">
-        <v>163</v>
+        <v>112</v>
       </c>
       <c r="D80" t="s">
-        <v>113</v>
+        <v>163</v>
       </c>
       <c r="E80" t="s">
-        <v>114</v>
+        <v>164</v>
       </c>
       <c r="F80" t="s">
-        <v>164</v>
+        <v>115</v>
       </c>
       <c r="G80" t="s">
         <v>165</v>
@@ -3606,16 +3606,16 @@
         <v>8</v>
       </c>
       <c r="C81" t="s">
-        <v>163</v>
+        <v>112</v>
       </c>
       <c r="D81" t="s">
-        <v>113</v>
+        <v>163</v>
       </c>
       <c r="E81" t="s">
-        <v>114</v>
+        <v>164</v>
       </c>
       <c r="F81" t="s">
-        <v>164</v>
+        <v>115</v>
       </c>
       <c r="G81" t="s">
         <v>165</v>
@@ -3629,16 +3629,16 @@
         <v>8</v>
       </c>
       <c r="C82" t="s">
-        <v>163</v>
+        <v>112</v>
       </c>
       <c r="D82" t="s">
-        <v>113</v>
+        <v>163</v>
       </c>
       <c r="E82" t="s">
-        <v>114</v>
+        <v>164</v>
       </c>
       <c r="F82" t="s">
-        <v>164</v>
+        <v>115</v>
       </c>
       <c r="G82" t="s">
         <v>165</v>
@@ -3681,10 +3681,10 @@
         <v>113</v>
       </c>
       <c r="E84" t="s">
-        <v>114</v>
+        <v>170</v>
       </c>
       <c r="F84" t="s">
-        <v>170</v>
+        <v>115</v>
       </c>
       <c r="G84" t="s">
         <v>171</v>
@@ -3704,10 +3704,10 @@
         <v>113</v>
       </c>
       <c r="E85" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="F85" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="G85" t="s">
         <v>173</v>
@@ -3721,16 +3721,16 @@
         <v>8</v>
       </c>
       <c r="C86" t="s">
-        <v>163</v>
+        <v>112</v>
       </c>
       <c r="D86" t="s">
-        <v>113</v>
+        <v>163</v>
       </c>
       <c r="E86" t="s">
-        <v>114</v>
+        <v>175</v>
       </c>
       <c r="F86" t="s">
-        <v>175</v>
+        <v>115</v>
       </c>
       <c r="G86" t="s">
         <v>176</v>
@@ -3750,10 +3750,10 @@
         <v>113</v>
       </c>
       <c r="E87" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="F87" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="G87" t="s">
         <v>173</v>
@@ -3773,10 +3773,10 @@
         <v>113</v>
       </c>
       <c r="E88" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="F88" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="G88" t="s">
         <v>119</v>
@@ -3796,10 +3796,10 @@
         <v>113</v>
       </c>
       <c r="E89" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="F89" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="G89" t="s">
         <v>119</v>
@@ -3813,16 +3813,16 @@
         <v>8</v>
       </c>
       <c r="C90" t="s">
+        <v>112</v>
+      </c>
+      <c r="D90" t="s">
         <v>124</v>
       </c>
-      <c r="D90" t="s">
-        <v>113</v>
-      </c>
       <c r="E90" t="s">
-        <v>114</v>
+        <v>125</v>
       </c>
       <c r="F90" t="s">
-        <v>125</v>
+        <v>115</v>
       </c>
       <c r="G90" t="s">
         <v>126</v>
@@ -3836,16 +3836,16 @@
         <v>8</v>
       </c>
       <c r="C91" t="s">
+        <v>112</v>
+      </c>
+      <c r="D91" t="s">
         <v>182</v>
       </c>
-      <c r="D91" t="s">
-        <v>113</v>
-      </c>
       <c r="E91" t="s">
-        <v>114</v>
+        <v>183</v>
       </c>
       <c r="F91" t="s">
-        <v>183</v>
+        <v>115</v>
       </c>
       <c r="G91" t="s">
         <v>184</v>
@@ -3859,16 +3859,16 @@
         <v>8</v>
       </c>
       <c r="C92" t="s">
+        <v>112</v>
+      </c>
+      <c r="D92" t="s">
         <v>124</v>
       </c>
-      <c r="D92" t="s">
-        <v>113</v>
-      </c>
       <c r="E92" t="s">
-        <v>114</v>
+        <v>125</v>
       </c>
       <c r="F92" t="s">
-        <v>125</v>
+        <v>115</v>
       </c>
       <c r="G92" t="s">
         <v>126</v>
@@ -3888,10 +3888,10 @@
         <v>113</v>
       </c>
       <c r="E93" t="s">
-        <v>114</v>
+        <v>121</v>
       </c>
       <c r="F93" t="s">
-        <v>121</v>
+        <v>115</v>
       </c>
       <c r="G93" t="s">
         <v>122</v>
@@ -3905,16 +3905,16 @@
         <v>8</v>
       </c>
       <c r="C94" t="s">
+        <v>112</v>
+      </c>
+      <c r="D94" t="s">
         <v>124</v>
       </c>
-      <c r="D94" t="s">
-        <v>113</v>
-      </c>
       <c r="E94" t="s">
-        <v>114</v>
+        <v>125</v>
       </c>
       <c r="F94" t="s">
-        <v>125</v>
+        <v>115</v>
       </c>
       <c r="G94" t="s">
         <v>126</v>
@@ -3934,10 +3934,10 @@
         <v>113</v>
       </c>
       <c r="E95" t="s">
-        <v>114</v>
+        <v>189</v>
       </c>
       <c r="F95" t="s">
-        <v>189</v>
+        <v>115</v>
       </c>
       <c r="G95" t="s">
         <v>190</v>
@@ -3951,16 +3951,16 @@
         <v>8</v>
       </c>
       <c r="C96" t="s">
+        <v>192</v>
+      </c>
+      <c r="D96" t="s">
         <v>124</v>
       </c>
-      <c r="D96" t="s">
-        <v>113</v>
-      </c>
       <c r="E96" t="s">
-        <v>192</v>
+        <v>125</v>
       </c>
       <c r="F96" t="s">
-        <v>125</v>
+        <v>115</v>
       </c>
       <c r="G96" t="s">
         <v>126</v>
@@ -3974,16 +3974,16 @@
         <v>8</v>
       </c>
       <c r="C97" t="s">
+        <v>192</v>
+      </c>
+      <c r="D97" t="s">
         <v>124</v>
       </c>
-      <c r="D97" t="s">
-        <v>113</v>
-      </c>
       <c r="E97" t="s">
-        <v>192</v>
+        <v>125</v>
       </c>
       <c r="F97" t="s">
-        <v>125</v>
+        <v>115</v>
       </c>
       <c r="G97" t="s">
         <v>126</v>
@@ -3997,16 +3997,16 @@
         <v>8</v>
       </c>
       <c r="C98" t="s">
+        <v>192</v>
+      </c>
+      <c r="D98" t="s">
         <v>195</v>
       </c>
-      <c r="D98" t="s">
-        <v>113</v>
-      </c>
       <c r="E98" t="s">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="F98" t="s">
-        <v>196</v>
+        <v>115</v>
       </c>
       <c r="G98" t="s">
         <v>197</v>
@@ -4020,16 +4020,16 @@
         <v>8</v>
       </c>
       <c r="C99" t="s">
+        <v>192</v>
+      </c>
+      <c r="D99" t="s">
         <v>124</v>
       </c>
-      <c r="D99" t="s">
-        <v>113</v>
-      </c>
       <c r="E99" t="s">
-        <v>192</v>
+        <v>125</v>
       </c>
       <c r="F99" t="s">
-        <v>125</v>
+        <v>115</v>
       </c>
       <c r="G99" t="s">
         <v>126</v>
@@ -4043,16 +4043,16 @@
         <v>8</v>
       </c>
       <c r="C100" t="s">
+        <v>192</v>
+      </c>
+      <c r="D100" t="s">
         <v>124</v>
       </c>
-      <c r="D100" t="s">
-        <v>113</v>
-      </c>
       <c r="E100" t="s">
-        <v>192</v>
+        <v>154</v>
       </c>
       <c r="F100" t="s">
-        <v>154</v>
+        <v>115</v>
       </c>
       <c r="G100" t="s">
         <v>155</v>
@@ -4066,16 +4066,16 @@
         <v>8</v>
       </c>
       <c r="C101" t="s">
+        <v>192</v>
+      </c>
+      <c r="D101" t="s">
         <v>124</v>
       </c>
-      <c r="D101" t="s">
-        <v>113</v>
-      </c>
       <c r="E101" t="s">
-        <v>192</v>
+        <v>125</v>
       </c>
       <c r="F101" t="s">
-        <v>125</v>
+        <v>115</v>
       </c>
       <c r="G101" t="s">
         <v>126</v>
@@ -4088,10 +4088,10 @@
       <c r="B102" t="s">
         <v>8</v>
       </c>
-      <c r="C102" t="s">
+      <c r="D102" t="s">
         <v>182</v>
       </c>
-      <c r="D102" t="s">
+      <c r="E102" t="s">
         <v>202</v>
       </c>
       <c r="F102" t="s">
@@ -4108,10 +4108,10 @@
       <c r="B103" t="s">
         <v>8</v>
       </c>
-      <c r="C103" t="s">
+      <c r="D103" t="s">
         <v>182</v>
       </c>
-      <c r="D103" t="s">
+      <c r="E103" t="s">
         <v>202</v>
       </c>
       <c r="F103" t="s">
@@ -4128,10 +4128,10 @@
       <c r="B104" t="s">
         <v>8</v>
       </c>
-      <c r="C104" t="s">
+      <c r="D104" t="s">
         <v>182</v>
       </c>
-      <c r="D104" t="s">
+      <c r="E104" t="s">
         <v>202</v>
       </c>
       <c r="F104" t="s">
@@ -4148,14 +4148,14 @@
       <c r="B105" t="s">
         <v>8</v>
       </c>
-      <c r="C105" t="s">
+      <c r="D105" t="s">
         <v>182</v>
       </c>
-      <c r="D105" t="s">
-        <v>202</v>
+      <c r="E105" t="s">
+        <v>208</v>
       </c>
       <c r="F105" t="s">
-        <v>208</v>
+        <v>203</v>
       </c>
       <c r="G105" t="s">
         <v>209</v>
@@ -4168,10 +4168,10 @@
       <c r="B106" t="s">
         <v>8</v>
       </c>
-      <c r="C106" t="s">
+      <c r="D106" t="s">
         <v>182</v>
       </c>
-      <c r="D106" t="s">
+      <c r="E106" t="s">
         <v>202</v>
       </c>
       <c r="F106" t="s">
@@ -4188,14 +4188,14 @@
       <c r="B107" t="s">
         <v>8</v>
       </c>
-      <c r="C107" t="s">
+      <c r="D107" t="s">
         <v>182</v>
       </c>
-      <c r="D107" t="s">
-        <v>202</v>
+      <c r="E107" t="s">
+        <v>183</v>
       </c>
       <c r="F107" t="s">
-        <v>183</v>
+        <v>203</v>
       </c>
       <c r="G107" t="s">
         <v>184</v>
@@ -4208,14 +4208,14 @@
       <c r="B108" t="s">
         <v>8</v>
       </c>
-      <c r="C108" t="s">
+      <c r="D108" t="s">
         <v>182</v>
       </c>
-      <c r="D108" t="s">
-        <v>202</v>
+      <c r="E108" t="s">
+        <v>213</v>
       </c>
       <c r="F108" t="s">
-        <v>213</v>
+        <v>203</v>
       </c>
       <c r="G108" t="s">
         <v>214</v>
@@ -4228,14 +4228,14 @@
       <c r="B109" t="s">
         <v>8</v>
       </c>
-      <c r="C109" t="s">
+      <c r="D109" t="s">
         <v>90</v>
       </c>
-      <c r="D109" t="s">
-        <v>202</v>
+      <c r="E109" t="s">
+        <v>216</v>
       </c>
       <c r="F109" t="s">
-        <v>216</v>
+        <v>203</v>
       </c>
       <c r="G109" t="s">
         <v>217</v>
@@ -4248,14 +4248,14 @@
       <c r="B110" t="s">
         <v>8</v>
       </c>
-      <c r="C110" t="s">
+      <c r="D110" t="s">
         <v>90</v>
       </c>
-      <c r="D110" t="s">
-        <v>202</v>
+      <c r="E110" t="s">
+        <v>219</v>
       </c>
       <c r="F110" t="s">
-        <v>219</v>
+        <v>203</v>
       </c>
       <c r="G110" t="s">
         <v>220</v>
@@ -4268,10 +4268,10 @@
       <c r="B111" t="s">
         <v>8</v>
       </c>
-      <c r="C111" t="s">
+      <c r="D111" t="s">
         <v>182</v>
       </c>
-      <c r="D111" t="s">
+      <c r="E111" t="s">
         <v>202</v>
       </c>
       <c r="F111" t="s">
@@ -4288,14 +4288,14 @@
       <c r="B112" t="s">
         <v>8</v>
       </c>
-      <c r="C112" t="s">
+      <c r="D112" t="s">
         <v>223</v>
       </c>
-      <c r="D112" t="s">
-        <v>202</v>
+      <c r="E112" t="s">
+        <v>224</v>
       </c>
       <c r="F112" t="s">
-        <v>224</v>
+        <v>203</v>
       </c>
       <c r="G112" t="s">
         <v>225</v>
@@ -4308,14 +4308,14 @@
       <c r="B113" t="s">
         <v>8</v>
       </c>
-      <c r="C113" t="s">
-        <v>112</v>
-      </c>
       <c r="D113" t="s">
-        <v>202</v>
+        <v>113</v>
+      </c>
+      <c r="E113" t="s">
+        <v>114</v>
       </c>
       <c r="F113" t="s">
-        <v>115</v>
+        <v>203</v>
       </c>
       <c r="G113" t="s">
         <v>143</v>
@@ -4328,14 +4328,14 @@
       <c r="B114" t="s">
         <v>8</v>
       </c>
-      <c r="C114" t="s">
+      <c r="D114" t="s">
         <v>124</v>
       </c>
-      <c r="D114" t="s">
-        <v>202</v>
+      <c r="E114" t="s">
+        <v>151</v>
       </c>
       <c r="F114" t="s">
-        <v>151</v>
+        <v>203</v>
       </c>
       <c r="G114" t="s">
         <v>152</v>
@@ -4348,14 +4348,14 @@
       <c r="B115" t="s">
         <v>8</v>
       </c>
-      <c r="C115" t="s">
+      <c r="D115" t="s">
         <v>182</v>
       </c>
-      <c r="D115" t="s">
-        <v>202</v>
+      <c r="E115" t="s">
+        <v>183</v>
       </c>
       <c r="F115" t="s">
-        <v>183</v>
+        <v>203</v>
       </c>
       <c r="G115" t="s">
         <v>184</v>
@@ -4368,14 +4368,14 @@
       <c r="B116" t="s">
         <v>8</v>
       </c>
-      <c r="C116" t="s">
+      <c r="D116" t="s">
         <v>223</v>
       </c>
-      <c r="D116" t="s">
-        <v>202</v>
+      <c r="E116" t="s">
+        <v>230</v>
       </c>
       <c r="F116" t="s">
-        <v>230</v>
+        <v>203</v>
       </c>
       <c r="G116" t="s">
         <v>231</v>
@@ -4388,14 +4388,14 @@
       <c r="B117" t="s">
         <v>8</v>
       </c>
-      <c r="C117" t="s">
+      <c r="D117" t="s">
         <v>223</v>
       </c>
-      <c r="D117" t="s">
-        <v>202</v>
+      <c r="E117" t="s">
+        <v>224</v>
       </c>
       <c r="F117" t="s">
-        <v>224</v>
+        <v>203</v>
       </c>
       <c r="G117" t="s">
         <v>225</v>
@@ -4408,14 +4408,14 @@
       <c r="B118" t="s">
         <v>8</v>
       </c>
-      <c r="C118" t="s">
-        <v>163</v>
-      </c>
       <c r="D118" t="s">
-        <v>202</v>
+        <v>163</v>
+      </c>
+      <c r="E118" t="s">
+        <v>164</v>
       </c>
       <c r="F118" t="s">
-        <v>164</v>
+        <v>203</v>
       </c>
       <c r="G118" t="s">
         <v>234</v>
@@ -4428,14 +4428,14 @@
       <c r="B119" t="s">
         <v>8</v>
       </c>
-      <c r="C119" t="s">
+      <c r="D119" t="s">
         <v>182</v>
       </c>
-      <c r="D119" t="s">
-        <v>202</v>
+      <c r="E119" t="s">
+        <v>183</v>
       </c>
       <c r="F119" t="s">
-        <v>183</v>
+        <v>203</v>
       </c>
       <c r="G119" t="s">
         <v>184</v>
@@ -4448,14 +4448,14 @@
       <c r="B120" t="s">
         <v>8</v>
       </c>
-      <c r="C120" t="s">
-        <v>112</v>
-      </c>
       <c r="D120" t="s">
+        <v>113</v>
+      </c>
+      <c r="E120" t="s">
+        <v>170</v>
+      </c>
+      <c r="F120" t="s">
         <v>237</v>
-      </c>
-      <c r="F120" t="s">
-        <v>170</v>
       </c>
       <c r="G120" t="s">
         <v>171</v>
@@ -4468,14 +4468,14 @@
       <c r="B121" t="s">
         <v>8</v>
       </c>
-      <c r="C121" t="s">
-        <v>112</v>
-      </c>
       <c r="D121" t="s">
+        <v>113</v>
+      </c>
+      <c r="E121" t="s">
+        <v>114</v>
+      </c>
+      <c r="F121" t="s">
         <v>237</v>
-      </c>
-      <c r="F121" t="s">
-        <v>115</v>
       </c>
       <c r="G121" t="s">
         <v>143</v>
@@ -4488,14 +4488,14 @@
       <c r="B122" t="s">
         <v>8</v>
       </c>
-      <c r="C122" t="s">
-        <v>112</v>
-      </c>
       <c r="D122" t="s">
+        <v>113</v>
+      </c>
+      <c r="E122" t="s">
+        <v>170</v>
+      </c>
+      <c r="F122" t="s">
         <v>237</v>
-      </c>
-      <c r="F122" t="s">
-        <v>170</v>
       </c>
       <c r="G122" t="s">
         <v>171</v>
@@ -4508,14 +4508,14 @@
       <c r="B123" t="s">
         <v>8</v>
       </c>
-      <c r="C123" t="s">
-        <v>112</v>
-      </c>
       <c r="D123" t="s">
+        <v>113</v>
+      </c>
+      <c r="E123" t="s">
+        <v>170</v>
+      </c>
+      <c r="F123" t="s">
         <v>237</v>
-      </c>
-      <c r="F123" t="s">
-        <v>170</v>
       </c>
       <c r="G123" t="s">
         <v>171</v>
@@ -4528,14 +4528,14 @@
       <c r="B124" t="s">
         <v>8</v>
       </c>
-      <c r="C124" t="s">
-        <v>163</v>
-      </c>
       <c r="D124" t="s">
+        <v>163</v>
+      </c>
+      <c r="E124" t="s">
+        <v>242</v>
+      </c>
+      <c r="F124" t="s">
         <v>237</v>
-      </c>
-      <c r="F124" t="s">
-        <v>242</v>
       </c>
       <c r="G124" t="s">
         <v>243</v>
@@ -4548,14 +4548,14 @@
       <c r="B125" t="s">
         <v>8</v>
       </c>
-      <c r="C125" t="s">
-        <v>163</v>
-      </c>
       <c r="D125" t="s">
+        <v>163</v>
+      </c>
+      <c r="E125" t="s">
+        <v>242</v>
+      </c>
+      <c r="F125" t="s">
         <v>237</v>
-      </c>
-      <c r="F125" t="s">
-        <v>242</v>
       </c>
       <c r="G125" t="s">
         <v>243</v>
@@ -4568,14 +4568,14 @@
       <c r="B126" t="s">
         <v>8</v>
       </c>
-      <c r="C126" t="s">
-        <v>163</v>
-      </c>
       <c r="D126" t="s">
+        <v>163</v>
+      </c>
+      <c r="E126" t="s">
+        <v>242</v>
+      </c>
+      <c r="F126" t="s">
         <v>237</v>
-      </c>
-      <c r="F126" t="s">
-        <v>242</v>
       </c>
       <c r="G126" t="s">
         <v>243</v>
@@ -4588,14 +4588,14 @@
       <c r="B127" t="s">
         <v>8</v>
       </c>
-      <c r="C127" t="s">
-        <v>163</v>
-      </c>
       <c r="D127" t="s">
+        <v>163</v>
+      </c>
+      <c r="E127" t="s">
+        <v>242</v>
+      </c>
+      <c r="F127" t="s">
         <v>237</v>
-      </c>
-      <c r="F127" t="s">
-        <v>242</v>
       </c>
       <c r="G127" t="s">
         <v>243</v>
@@ -4608,14 +4608,14 @@
       <c r="B128" t="s">
         <v>8</v>
       </c>
-      <c r="C128" t="s">
-        <v>163</v>
-      </c>
       <c r="D128" t="s">
+        <v>163</v>
+      </c>
+      <c r="E128" t="s">
+        <v>242</v>
+      </c>
+      <c r="F128" t="s">
         <v>237</v>
-      </c>
-      <c r="F128" t="s">
-        <v>242</v>
       </c>
       <c r="G128" t="s">
         <v>243</v>
@@ -4628,14 +4628,14 @@
       <c r="B129" t="s">
         <v>8</v>
       </c>
-      <c r="C129" t="s">
-        <v>163</v>
-      </c>
       <c r="D129" t="s">
+        <v>163</v>
+      </c>
+      <c r="E129" t="s">
+        <v>242</v>
+      </c>
+      <c r="F129" t="s">
         <v>237</v>
-      </c>
-      <c r="F129" t="s">
-        <v>242</v>
       </c>
       <c r="G129" t="s">
         <v>249</v>
@@ -4648,14 +4648,14 @@
       <c r="B130" t="s">
         <v>8</v>
       </c>
-      <c r="C130" t="s">
-        <v>163</v>
-      </c>
       <c r="D130" t="s">
+        <v>163</v>
+      </c>
+      <c r="E130" t="s">
+        <v>242</v>
+      </c>
+      <c r="F130" t="s">
         <v>237</v>
-      </c>
-      <c r="F130" t="s">
-        <v>242</v>
       </c>
       <c r="G130" t="s">
         <v>251</v>
@@ -4668,14 +4668,14 @@
       <c r="B131" t="s">
         <v>8</v>
       </c>
-      <c r="C131" t="s">
-        <v>163</v>
-      </c>
       <c r="D131" t="s">
+        <v>163</v>
+      </c>
+      <c r="E131" t="s">
+        <v>242</v>
+      </c>
+      <c r="F131" t="s">
         <v>237</v>
-      </c>
-      <c r="F131" t="s">
-        <v>242</v>
       </c>
       <c r="G131" t="s">
         <v>253</v>
@@ -4688,14 +4688,14 @@
       <c r="B132" t="s">
         <v>8</v>
       </c>
-      <c r="C132" t="s">
-        <v>163</v>
-      </c>
       <c r="D132" t="s">
+        <v>163</v>
+      </c>
+      <c r="E132" t="s">
+        <v>255</v>
+      </c>
+      <c r="F132" t="s">
         <v>237</v>
-      </c>
-      <c r="F132" t="s">
-        <v>255</v>
       </c>
       <c r="G132" t="s">
         <v>256</v>
@@ -4708,14 +4708,14 @@
       <c r="B133" t="s">
         <v>8</v>
       </c>
-      <c r="C133" t="s">
-        <v>112</v>
-      </c>
       <c r="D133" t="s">
+        <v>113</v>
+      </c>
+      <c r="E133" t="s">
+        <v>189</v>
+      </c>
+      <c r="F133" t="s">
         <v>237</v>
-      </c>
-      <c r="F133" t="s">
-        <v>189</v>
       </c>
       <c r="G133" t="s">
         <v>190</v>
@@ -4728,14 +4728,14 @@
       <c r="B134" t="s">
         <v>8</v>
       </c>
-      <c r="C134" t="s">
-        <v>163</v>
-      </c>
       <c r="D134" t="s">
+        <v>163</v>
+      </c>
+      <c r="E134" t="s">
+        <v>175</v>
+      </c>
+      <c r="F134" t="s">
         <v>259</v>
-      </c>
-      <c r="F134" t="s">
-        <v>175</v>
       </c>
       <c r="G134" t="s">
         <v>176</v>
@@ -4748,14 +4748,14 @@
       <c r="B135" t="s">
         <v>8</v>
       </c>
-      <c r="C135" t="s">
-        <v>163</v>
-      </c>
       <c r="D135" t="s">
+        <v>163</v>
+      </c>
+      <c r="E135" t="s">
+        <v>175</v>
+      </c>
+      <c r="F135" t="s">
         <v>259</v>
-      </c>
-      <c r="F135" t="s">
-        <v>175</v>
       </c>
       <c r="G135" t="s">
         <v>176</v>
@@ -4768,14 +4768,14 @@
       <c r="B136" t="s">
         <v>8</v>
       </c>
-      <c r="C136" t="s">
-        <v>163</v>
-      </c>
       <c r="D136" t="s">
+        <v>163</v>
+      </c>
+      <c r="E136" t="s">
+        <v>175</v>
+      </c>
+      <c r="F136" t="s">
         <v>259</v>
-      </c>
-      <c r="F136" t="s">
-        <v>175</v>
       </c>
       <c r="G136" t="s">
         <v>176</v>
@@ -4788,14 +4788,14 @@
       <c r="B137" t="s">
         <v>8</v>
       </c>
-      <c r="C137" t="s">
-        <v>163</v>
-      </c>
       <c r="D137" t="s">
+        <v>163</v>
+      </c>
+      <c r="E137" t="s">
+        <v>175</v>
+      </c>
+      <c r="F137" t="s">
         <v>259</v>
-      </c>
-      <c r="F137" t="s">
-        <v>175</v>
       </c>
       <c r="G137" t="s">
         <v>176</v>
@@ -4808,14 +4808,14 @@
       <c r="B138" t="s">
         <v>8</v>
       </c>
-      <c r="C138" t="s">
-        <v>163</v>
-      </c>
       <c r="D138" t="s">
+        <v>163</v>
+      </c>
+      <c r="E138" t="s">
+        <v>175</v>
+      </c>
+      <c r="F138" t="s">
         <v>259</v>
-      </c>
-      <c r="F138" t="s">
-        <v>175</v>
       </c>
       <c r="G138" t="s">
         <v>176</v>
@@ -4828,14 +4828,14 @@
       <c r="B139" t="s">
         <v>8</v>
       </c>
-      <c r="C139" t="s">
+      <c r="D139" t="s">
         <v>223</v>
       </c>
-      <c r="D139" t="s">
+      <c r="E139" t="s">
+        <v>265</v>
+      </c>
+      <c r="F139" t="s">
         <v>259</v>
-      </c>
-      <c r="F139" t="s">
-        <v>265</v>
       </c>
       <c r="G139" t="s">
         <v>266</v>
@@ -4848,14 +4848,14 @@
       <c r="B140" t="s">
         <v>8</v>
       </c>
-      <c r="C140" t="s">
-        <v>163</v>
-      </c>
       <c r="D140" t="s">
+        <v>163</v>
+      </c>
+      <c r="E140" t="s">
+        <v>175</v>
+      </c>
+      <c r="F140" t="s">
         <v>259</v>
-      </c>
-      <c r="F140" t="s">
-        <v>175</v>
       </c>
       <c r="G140" t="s">
         <v>176</v>
@@ -4869,10 +4869,10 @@
         <v>8</v>
       </c>
       <c r="C141" t="s">
-        <v>163</v>
+        <v>269</v>
       </c>
       <c r="D141" t="s">
-        <v>269</v>
+        <v>163</v>
       </c>
       <c r="E141" t="s">
         <v>270</v>
@@ -4892,10 +4892,10 @@
         <v>8</v>
       </c>
       <c r="C142" t="s">
-        <v>163</v>
+        <v>269</v>
       </c>
       <c r="D142" t="s">
-        <v>269</v>
+        <v>163</v>
       </c>
       <c r="E142" t="s">
         <v>270</v>
@@ -4915,16 +4915,16 @@
         <v>8</v>
       </c>
       <c r="C143" t="s">
-        <v>163</v>
+        <v>269</v>
       </c>
       <c r="D143" t="s">
-        <v>269</v>
+        <v>163</v>
       </c>
       <c r="E143" t="s">
-        <v>270</v>
+        <v>275</v>
       </c>
       <c r="F143" t="s">
-        <v>275</v>
+        <v>271</v>
       </c>
       <c r="G143" t="s">
         <v>276</v>
@@ -4938,16 +4938,16 @@
         <v>8</v>
       </c>
       <c r="C144" t="s">
-        <v>163</v>
+        <v>269</v>
       </c>
       <c r="D144" t="s">
-        <v>269</v>
+        <v>163</v>
       </c>
       <c r="E144" t="s">
-        <v>270</v>
+        <v>275</v>
       </c>
       <c r="F144" t="s">
-        <v>275</v>
+        <v>271</v>
       </c>
       <c r="G144" t="s">
         <v>276</v>
@@ -4961,16 +4961,16 @@
         <v>8</v>
       </c>
       <c r="C145" t="s">
-        <v>163</v>
+        <v>269</v>
       </c>
       <c r="D145" t="s">
-        <v>269</v>
+        <v>163</v>
       </c>
       <c r="E145" t="s">
-        <v>270</v>
+        <v>275</v>
       </c>
       <c r="F145" t="s">
-        <v>275</v>
+        <v>271</v>
       </c>
       <c r="G145" t="s">
         <v>276</v>
@@ -4984,10 +4984,10 @@
         <v>8</v>
       </c>
       <c r="C146" t="s">
-        <v>163</v>
+        <v>269</v>
       </c>
       <c r="D146" t="s">
-        <v>269</v>
+        <v>163</v>
       </c>
       <c r="E146" t="s">
         <v>270</v>
@@ -5007,13 +5007,13 @@
         <v>8</v>
       </c>
       <c r="C147" t="s">
-        <v>163</v>
+        <v>281</v>
       </c>
       <c r="D147" t="s">
-        <v>269</v>
+        <v>163</v>
       </c>
       <c r="E147" t="s">
-        <v>281</v>
+        <v>270</v>
       </c>
       <c r="F147" t="s">
         <v>271</v>
@@ -5030,13 +5030,13 @@
         <v>8</v>
       </c>
       <c r="C148" t="s">
-        <v>163</v>
+        <v>281</v>
       </c>
       <c r="D148" t="s">
-        <v>269</v>
+        <v>163</v>
       </c>
       <c r="E148" t="s">
-        <v>281</v>
+        <v>270</v>
       </c>
       <c r="F148" t="s">
         <v>271</v>
@@ -5053,13 +5053,13 @@
         <v>8</v>
       </c>
       <c r="C149" t="s">
-        <v>163</v>
+        <v>281</v>
       </c>
       <c r="D149" t="s">
-        <v>269</v>
+        <v>163</v>
       </c>
       <c r="E149" t="s">
-        <v>281</v>
+        <v>270</v>
       </c>
       <c r="F149" t="s">
         <v>271</v>
@@ -5076,13 +5076,13 @@
         <v>8</v>
       </c>
       <c r="C150" t="s">
-        <v>163</v>
+        <v>281</v>
       </c>
       <c r="D150" t="s">
-        <v>269</v>
+        <v>163</v>
       </c>
       <c r="E150" t="s">
-        <v>281</v>
+        <v>270</v>
       </c>
       <c r="F150" t="s">
         <v>271</v>
@@ -5099,13 +5099,13 @@
         <v>8</v>
       </c>
       <c r="C151" t="s">
-        <v>163</v>
+        <v>281</v>
       </c>
       <c r="D151" t="s">
-        <v>269</v>
+        <v>163</v>
       </c>
       <c r="E151" t="s">
-        <v>281</v>
+        <v>270</v>
       </c>
       <c r="F151" t="s">
         <v>271</v>
@@ -5122,13 +5122,13 @@
         <v>8</v>
       </c>
       <c r="C152" t="s">
-        <v>163</v>
+        <v>281</v>
       </c>
       <c r="D152" t="s">
-        <v>269</v>
+        <v>163</v>
       </c>
       <c r="E152" t="s">
-        <v>281</v>
+        <v>270</v>
       </c>
       <c r="F152" t="s">
         <v>271</v>
@@ -5145,13 +5145,13 @@
         <v>8</v>
       </c>
       <c r="C153" t="s">
-        <v>163</v>
+        <v>281</v>
       </c>
       <c r="D153" t="s">
-        <v>269</v>
+        <v>163</v>
       </c>
       <c r="E153" t="s">
-        <v>281</v>
+        <v>270</v>
       </c>
       <c r="F153" t="s">
         <v>271</v>
@@ -5168,13 +5168,13 @@
         <v>8</v>
       </c>
       <c r="C154" t="s">
-        <v>163</v>
+        <v>281</v>
       </c>
       <c r="D154" t="s">
-        <v>269</v>
+        <v>163</v>
       </c>
       <c r="E154" t="s">
-        <v>281</v>
+        <v>270</v>
       </c>
       <c r="F154" t="s">
         <v>271</v>
@@ -5191,13 +5191,13 @@
         <v>8</v>
       </c>
       <c r="C155" t="s">
-        <v>163</v>
+        <v>281</v>
       </c>
       <c r="D155" t="s">
-        <v>269</v>
+        <v>163</v>
       </c>
       <c r="E155" t="s">
-        <v>281</v>
+        <v>270</v>
       </c>
       <c r="F155" t="s">
         <v>271</v>
@@ -5214,13 +5214,13 @@
         <v>8</v>
       </c>
       <c r="C156" t="s">
-        <v>163</v>
+        <v>291</v>
       </c>
       <c r="D156" t="s">
-        <v>269</v>
+        <v>163</v>
       </c>
       <c r="E156" t="s">
-        <v>291</v>
+        <v>270</v>
       </c>
       <c r="F156" t="s">
         <v>271</v>
@@ -5237,13 +5237,13 @@
         <v>8</v>
       </c>
       <c r="C157" t="s">
-        <v>163</v>
+        <v>291</v>
       </c>
       <c r="D157" t="s">
-        <v>269</v>
+        <v>163</v>
       </c>
       <c r="E157" t="s">
-        <v>291</v>
+        <v>270</v>
       </c>
       <c r="F157" t="s">
         <v>271</v>
@@ -5260,13 +5260,13 @@
         <v>8</v>
       </c>
       <c r="C158" t="s">
-        <v>163</v>
+        <v>291</v>
       </c>
       <c r="D158" t="s">
-        <v>269</v>
+        <v>163</v>
       </c>
       <c r="E158" t="s">
-        <v>291</v>
+        <v>270</v>
       </c>
       <c r="F158" t="s">
         <v>271</v>
@@ -5283,13 +5283,13 @@
         <v>8</v>
       </c>
       <c r="C159" t="s">
-        <v>163</v>
+        <v>291</v>
       </c>
       <c r="D159" t="s">
-        <v>269</v>
+        <v>163</v>
       </c>
       <c r="E159" t="s">
-        <v>291</v>
+        <v>270</v>
       </c>
       <c r="F159" t="s">
         <v>271</v>
@@ -5306,13 +5306,13 @@
         <v>8</v>
       </c>
       <c r="C160" t="s">
-        <v>163</v>
+        <v>291</v>
       </c>
       <c r="D160" t="s">
-        <v>269</v>
+        <v>163</v>
       </c>
       <c r="E160" t="s">
-        <v>291</v>
+        <v>270</v>
       </c>
       <c r="F160" t="s">
         <v>271</v>
@@ -5329,13 +5329,13 @@
         <v>8</v>
       </c>
       <c r="C161" t="s">
-        <v>163</v>
+        <v>291</v>
       </c>
       <c r="D161" t="s">
-        <v>269</v>
+        <v>163</v>
       </c>
       <c r="E161" t="s">
-        <v>291</v>
+        <v>270</v>
       </c>
       <c r="F161" t="s">
         <v>271</v>
@@ -5352,13 +5352,13 @@
         <v>8</v>
       </c>
       <c r="C162" t="s">
-        <v>163</v>
+        <v>299</v>
       </c>
       <c r="D162" t="s">
-        <v>269</v>
+        <v>163</v>
       </c>
       <c r="E162" t="s">
-        <v>299</v>
+        <v>270</v>
       </c>
       <c r="F162" t="s">
         <v>271</v>
@@ -5375,13 +5375,13 @@
         <v>8</v>
       </c>
       <c r="C163" t="s">
-        <v>163</v>
+        <v>301</v>
       </c>
       <c r="D163" t="s">
-        <v>269</v>
+        <v>163</v>
       </c>
       <c r="E163" t="s">
-        <v>301</v>
+        <v>270</v>
       </c>
       <c r="F163" t="s">
         <v>271</v>
@@ -5398,13 +5398,13 @@
         <v>8</v>
       </c>
       <c r="C164" t="s">
-        <v>163</v>
+        <v>304</v>
       </c>
       <c r="D164" t="s">
-        <v>269</v>
+        <v>163</v>
       </c>
       <c r="E164" t="s">
-        <v>304</v>
+        <v>270</v>
       </c>
       <c r="F164" t="s">
         <v>271</v>
@@ -5421,13 +5421,13 @@
         <v>8</v>
       </c>
       <c r="C165" t="s">
-        <v>163</v>
+        <v>304</v>
       </c>
       <c r="D165" t="s">
-        <v>269</v>
+        <v>163</v>
       </c>
       <c r="E165" t="s">
-        <v>304</v>
+        <v>270</v>
       </c>
       <c r="F165" t="s">
         <v>271</v>
@@ -5444,13 +5444,13 @@
         <v>8</v>
       </c>
       <c r="C166" t="s">
-        <v>163</v>
+        <v>304</v>
       </c>
       <c r="D166" t="s">
-        <v>269</v>
+        <v>163</v>
       </c>
       <c r="E166" t="s">
-        <v>304</v>
+        <v>270</v>
       </c>
       <c r="F166" t="s">
         <v>271</v>
@@ -5467,13 +5467,13 @@
         <v>8</v>
       </c>
       <c r="C167" t="s">
-        <v>163</v>
+        <v>304</v>
       </c>
       <c r="D167" t="s">
-        <v>269</v>
+        <v>163</v>
       </c>
       <c r="E167" t="s">
-        <v>304</v>
+        <v>270</v>
       </c>
       <c r="F167" t="s">
         <v>271</v>
@@ -5490,13 +5490,13 @@
         <v>8</v>
       </c>
       <c r="C168" t="s">
-        <v>163</v>
+        <v>304</v>
       </c>
       <c r="D168" t="s">
-        <v>269</v>
+        <v>163</v>
       </c>
       <c r="E168" t="s">
-        <v>304</v>
+        <v>270</v>
       </c>
       <c r="F168" t="s">
         <v>271</v>
@@ -5513,13 +5513,13 @@
         <v>8</v>
       </c>
       <c r="C169" t="s">
-        <v>163</v>
+        <v>304</v>
       </c>
       <c r="D169" t="s">
-        <v>269</v>
+        <v>163</v>
       </c>
       <c r="E169" t="s">
-        <v>304</v>
+        <v>270</v>
       </c>
       <c r="F169" t="s">
         <v>271</v>
@@ -5536,13 +5536,13 @@
         <v>8</v>
       </c>
       <c r="C170" t="s">
-        <v>163</v>
+        <v>304</v>
       </c>
       <c r="D170" t="s">
-        <v>269</v>
+        <v>163</v>
       </c>
       <c r="E170" t="s">
-        <v>304</v>
+        <v>270</v>
       </c>
       <c r="F170" t="s">
         <v>271</v>
@@ -5558,14 +5558,14 @@
       <c r="B171" t="s">
         <v>8</v>
       </c>
-      <c r="C171" t="s">
-        <v>163</v>
-      </c>
       <c r="D171" t="s">
+        <v>163</v>
+      </c>
+      <c r="E171" t="s">
+        <v>164</v>
+      </c>
+      <c r="F171" t="s">
         <v>313</v>
-      </c>
-      <c r="F171" t="s">
-        <v>164</v>
       </c>
       <c r="G171" t="s">
         <v>165</v>
@@ -5578,14 +5578,14 @@
       <c r="B172" t="s">
         <v>8</v>
       </c>
-      <c r="C172" t="s">
-        <v>112</v>
-      </c>
       <c r="D172" t="s">
+        <v>113</v>
+      </c>
+      <c r="E172" t="s">
+        <v>118</v>
+      </c>
+      <c r="F172" t="s">
         <v>313</v>
-      </c>
-      <c r="F172" t="s">
-        <v>118</v>
       </c>
       <c r="G172" t="s">
         <v>119</v>
@@ -5598,14 +5598,14 @@
       <c r="B173" t="s">
         <v>8</v>
       </c>
-      <c r="C173" t="s">
-        <v>163</v>
-      </c>
       <c r="D173" t="s">
+        <v>163</v>
+      </c>
+      <c r="E173" t="s">
+        <v>164</v>
+      </c>
+      <c r="F173" t="s">
         <v>313</v>
-      </c>
-      <c r="F173" t="s">
-        <v>164</v>
       </c>
       <c r="G173" t="s">
         <v>165</v>
@@ -5618,14 +5618,14 @@
       <c r="B174" t="s">
         <v>8</v>
       </c>
-      <c r="C174" t="s">
-        <v>163</v>
-      </c>
       <c r="D174" t="s">
+        <v>163</v>
+      </c>
+      <c r="E174" t="s">
+        <v>164</v>
+      </c>
+      <c r="F174" t="s">
         <v>313</v>
-      </c>
-      <c r="F174" t="s">
-        <v>164</v>
       </c>
       <c r="G174" t="s">
         <v>165</v>
@@ -5638,14 +5638,14 @@
       <c r="B175" t="s">
         <v>8</v>
       </c>
-      <c r="C175" t="s">
-        <v>163</v>
-      </c>
       <c r="D175" t="s">
+        <v>163</v>
+      </c>
+      <c r="E175" t="s">
+        <v>164</v>
+      </c>
+      <c r="F175" t="s">
         <v>313</v>
-      </c>
-      <c r="F175" t="s">
-        <v>164</v>
       </c>
       <c r="G175" t="s">
         <v>165</v>
@@ -5658,14 +5658,14 @@
       <c r="B176" t="s">
         <v>8</v>
       </c>
-      <c r="C176" t="s">
-        <v>163</v>
-      </c>
       <c r="D176" t="s">
+        <v>163</v>
+      </c>
+      <c r="E176" t="s">
+        <v>164</v>
+      </c>
+      <c r="F176" t="s">
         <v>313</v>
-      </c>
-      <c r="F176" t="s">
-        <v>164</v>
       </c>
       <c r="G176" t="s">
         <v>165</v>
@@ -5678,14 +5678,14 @@
       <c r="B177" t="s">
         <v>8</v>
       </c>
-      <c r="C177" t="s">
-        <v>163</v>
-      </c>
       <c r="D177" t="s">
+        <v>163</v>
+      </c>
+      <c r="E177" t="s">
+        <v>164</v>
+      </c>
+      <c r="F177" t="s">
         <v>320</v>
-      </c>
-      <c r="F177" t="s">
-        <v>164</v>
       </c>
       <c r="G177" t="s">
         <v>165</v>
@@ -5698,14 +5698,14 @@
       <c r="B178" t="s">
         <v>8</v>
       </c>
-      <c r="C178" t="s">
-        <v>163</v>
-      </c>
       <c r="D178" t="s">
+        <v>163</v>
+      </c>
+      <c r="E178" t="s">
+        <v>164</v>
+      </c>
+      <c r="F178" t="s">
         <v>320</v>
-      </c>
-      <c r="F178" t="s">
-        <v>164</v>
       </c>
       <c r="G178" t="s">
         <v>165</v>
@@ -5718,14 +5718,14 @@
       <c r="B179" t="s">
         <v>8</v>
       </c>
-      <c r="C179" t="s">
-        <v>163</v>
-      </c>
       <c r="D179" t="s">
+        <v>163</v>
+      </c>
+      <c r="E179" t="s">
+        <v>164</v>
+      </c>
+      <c r="F179" t="s">
         <v>320</v>
-      </c>
-      <c r="F179" t="s">
-        <v>164</v>
       </c>
       <c r="G179" t="s">
         <v>165</v>
@@ -5738,14 +5738,14 @@
       <c r="B180" t="s">
         <v>8</v>
       </c>
-      <c r="C180" t="s">
-        <v>163</v>
-      </c>
       <c r="D180" t="s">
+        <v>163</v>
+      </c>
+      <c r="E180" t="s">
+        <v>164</v>
+      </c>
+      <c r="F180" t="s">
         <v>320</v>
-      </c>
-      <c r="F180" t="s">
-        <v>164</v>
       </c>
       <c r="G180" t="s">
         <v>165</v>
@@ -5759,10 +5759,10 @@
         <v>8</v>
       </c>
       <c r="C181" t="s">
-        <v>163</v>
+        <v>325</v>
       </c>
       <c r="D181" t="s">
-        <v>325</v>
+        <v>163</v>
       </c>
       <c r="E181" t="s">
         <v>326</v>
@@ -5782,10 +5782,10 @@
         <v>8</v>
       </c>
       <c r="C182" t="s">
-        <v>163</v>
+        <v>325</v>
       </c>
       <c r="D182" t="s">
-        <v>325</v>
+        <v>163</v>
       </c>
       <c r="E182" t="s">
         <v>326</v>
@@ -5805,10 +5805,10 @@
         <v>8</v>
       </c>
       <c r="C183" t="s">
-        <v>163</v>
+        <v>325</v>
       </c>
       <c r="D183" t="s">
-        <v>325</v>
+        <v>163</v>
       </c>
       <c r="E183" t="s">
         <v>326</v>
@@ -5828,10 +5828,10 @@
         <v>8</v>
       </c>
       <c r="C184" t="s">
-        <v>163</v>
+        <v>325</v>
       </c>
       <c r="D184" t="s">
-        <v>325</v>
+        <v>163</v>
       </c>
       <c r="E184" t="s">
         <v>326</v>
@@ -5851,10 +5851,10 @@
         <v>8</v>
       </c>
       <c r="C185" t="s">
-        <v>163</v>
+        <v>325</v>
       </c>
       <c r="D185" t="s">
-        <v>325</v>
+        <v>163</v>
       </c>
       <c r="E185" t="s">
         <v>326</v>
@@ -5874,10 +5874,10 @@
         <v>8</v>
       </c>
       <c r="C186" t="s">
-        <v>163</v>
+        <v>325</v>
       </c>
       <c r="D186" t="s">
-        <v>325</v>
+        <v>163</v>
       </c>
       <c r="E186" t="s">
         <v>326</v>
@@ -5897,10 +5897,10 @@
         <v>8</v>
       </c>
       <c r="C187" t="s">
-        <v>163</v>
+        <v>325</v>
       </c>
       <c r="D187" t="s">
-        <v>325</v>
+        <v>163</v>
       </c>
       <c r="E187" t="s">
         <v>326</v>
@@ -5920,10 +5920,10 @@
         <v>8</v>
       </c>
       <c r="C188" t="s">
-        <v>163</v>
+        <v>325</v>
       </c>
       <c r="D188" t="s">
-        <v>325</v>
+        <v>163</v>
       </c>
       <c r="E188" t="s">
         <v>326</v>
@@ -5943,10 +5943,10 @@
         <v>8</v>
       </c>
       <c r="C189" t="s">
-        <v>163</v>
+        <v>325</v>
       </c>
       <c r="D189" t="s">
-        <v>325</v>
+        <v>163</v>
       </c>
       <c r="E189" t="s">
         <v>326</v>
@@ -5966,10 +5966,10 @@
         <v>8</v>
       </c>
       <c r="C190" t="s">
-        <v>163</v>
+        <v>325</v>
       </c>
       <c r="D190" t="s">
-        <v>325</v>
+        <v>163</v>
       </c>
       <c r="E190" t="s">
         <v>326</v>
@@ -5989,10 +5989,10 @@
         <v>8</v>
       </c>
       <c r="C191" t="s">
-        <v>163</v>
+        <v>325</v>
       </c>
       <c r="D191" t="s">
-        <v>325</v>
+        <v>163</v>
       </c>
       <c r="E191" t="s">
         <v>326</v>
@@ -6012,10 +6012,10 @@
         <v>8</v>
       </c>
       <c r="C192" t="s">
-        <v>163</v>
+        <v>325</v>
       </c>
       <c r="D192" t="s">
-        <v>325</v>
+        <v>163</v>
       </c>
       <c r="E192" t="s">
         <v>326</v>
@@ -6035,16 +6035,16 @@
         <v>8</v>
       </c>
       <c r="C193" t="s">
-        <v>163</v>
+        <v>325</v>
       </c>
       <c r="D193" t="s">
-        <v>325</v>
+        <v>163</v>
       </c>
       <c r="E193" t="s">
-        <v>326</v>
+        <v>275</v>
       </c>
       <c r="F193" t="s">
-        <v>275</v>
+        <v>327</v>
       </c>
       <c r="G193" t="s">
         <v>341</v>
@@ -6058,10 +6058,10 @@
         <v>8</v>
       </c>
       <c r="C194" t="s">
-        <v>163</v>
+        <v>325</v>
       </c>
       <c r="D194" t="s">
-        <v>325</v>
+        <v>163</v>
       </c>
       <c r="E194" t="s">
         <v>326</v>
@@ -6081,10 +6081,10 @@
         <v>8</v>
       </c>
       <c r="C195" t="s">
-        <v>163</v>
+        <v>325</v>
       </c>
       <c r="D195" t="s">
-        <v>325</v>
+        <v>163</v>
       </c>
       <c r="E195" t="s">
         <v>326</v>
@@ -6104,10 +6104,10 @@
         <v>8</v>
       </c>
       <c r="C196" t="s">
-        <v>163</v>
+        <v>325</v>
       </c>
       <c r="D196" t="s">
-        <v>325</v>
+        <v>163</v>
       </c>
       <c r="E196" t="s">
         <v>326</v>
@@ -6127,10 +6127,10 @@
         <v>8</v>
       </c>
       <c r="C197" t="s">
-        <v>163</v>
+        <v>325</v>
       </c>
       <c r="D197" t="s">
-        <v>325</v>
+        <v>163</v>
       </c>
       <c r="E197" t="s">
         <v>326</v>
@@ -6150,10 +6150,10 @@
         <v>8</v>
       </c>
       <c r="C198" t="s">
-        <v>163</v>
+        <v>325</v>
       </c>
       <c r="D198" t="s">
-        <v>325</v>
+        <v>163</v>
       </c>
       <c r="E198" t="s">
         <v>326</v>
@@ -6173,13 +6173,13 @@
         <v>8</v>
       </c>
       <c r="C199" t="s">
-        <v>163</v>
+        <v>348</v>
       </c>
       <c r="D199" t="s">
-        <v>325</v>
+        <v>163</v>
       </c>
       <c r="E199" t="s">
-        <v>348</v>
+        <v>326</v>
       </c>
       <c r="F199" t="s">
         <v>327</v>
@@ -6196,13 +6196,13 @@
         <v>8</v>
       </c>
       <c r="C200" t="s">
-        <v>163</v>
+        <v>348</v>
       </c>
       <c r="D200" t="s">
-        <v>325</v>
+        <v>163</v>
       </c>
       <c r="E200" t="s">
-        <v>348</v>
+        <v>326</v>
       </c>
       <c r="F200" t="s">
         <v>327</v>
@@ -6219,13 +6219,13 @@
         <v>8</v>
       </c>
       <c r="C201" t="s">
-        <v>163</v>
+        <v>348</v>
       </c>
       <c r="D201" t="s">
-        <v>325</v>
+        <v>163</v>
       </c>
       <c r="E201" t="s">
-        <v>348</v>
+        <v>326</v>
       </c>
       <c r="F201" t="s">
         <v>327</v>
@@ -6242,13 +6242,13 @@
         <v>8</v>
       </c>
       <c r="C202" t="s">
-        <v>163</v>
+        <v>348</v>
       </c>
       <c r="D202" t="s">
-        <v>325</v>
+        <v>163</v>
       </c>
       <c r="E202" t="s">
-        <v>348</v>
+        <v>326</v>
       </c>
       <c r="F202" t="s">
         <v>327</v>
@@ -6265,16 +6265,16 @@
         <v>8</v>
       </c>
       <c r="C203" t="s">
-        <v>163</v>
+        <v>348</v>
       </c>
       <c r="D203" t="s">
-        <v>325</v>
+        <v>163</v>
       </c>
       <c r="E203" t="s">
-        <v>348</v>
+        <v>275</v>
       </c>
       <c r="F203" t="s">
-        <v>275</v>
+        <v>327</v>
       </c>
       <c r="G203" t="s">
         <v>341</v>
@@ -6288,13 +6288,13 @@
         <v>8</v>
       </c>
       <c r="C204" t="s">
-        <v>163</v>
+        <v>348</v>
       </c>
       <c r="D204" t="s">
-        <v>325</v>
+        <v>163</v>
       </c>
       <c r="E204" t="s">
-        <v>348</v>
+        <v>326</v>
       </c>
       <c r="F204" t="s">
         <v>327</v>
@@ -6311,13 +6311,13 @@
         <v>8</v>
       </c>
       <c r="C205" t="s">
-        <v>163</v>
+        <v>356</v>
       </c>
       <c r="D205" t="s">
-        <v>325</v>
+        <v>163</v>
       </c>
       <c r="E205" t="s">
-        <v>356</v>
+        <v>326</v>
       </c>
       <c r="F205" t="s">
         <v>327</v>
@@ -6334,13 +6334,13 @@
         <v>8</v>
       </c>
       <c r="C206" t="s">
-        <v>163</v>
+        <v>356</v>
       </c>
       <c r="D206" t="s">
-        <v>325</v>
+        <v>163</v>
       </c>
       <c r="E206" t="s">
-        <v>356</v>
+        <v>326</v>
       </c>
       <c r="F206" t="s">
         <v>327</v>
@@ -6357,13 +6357,13 @@
         <v>8</v>
       </c>
       <c r="C207" t="s">
-        <v>163</v>
+        <v>356</v>
       </c>
       <c r="D207" t="s">
-        <v>325</v>
+        <v>163</v>
       </c>
       <c r="E207" t="s">
-        <v>356</v>
+        <v>326</v>
       </c>
       <c r="F207" t="s">
         <v>327</v>
@@ -6380,16 +6380,16 @@
         <v>8</v>
       </c>
       <c r="C208" t="s">
-        <v>163</v>
+        <v>356</v>
       </c>
       <c r="D208" t="s">
-        <v>325</v>
+        <v>163</v>
       </c>
       <c r="E208" t="s">
-        <v>356</v>
+        <v>275</v>
       </c>
       <c r="F208" t="s">
-        <v>275</v>
+        <v>327</v>
       </c>
       <c r="G208" t="s">
         <v>341</v>
@@ -6403,13 +6403,13 @@
         <v>8</v>
       </c>
       <c r="C209" t="s">
-        <v>163</v>
+        <v>356</v>
       </c>
       <c r="D209" t="s">
-        <v>325</v>
+        <v>163</v>
       </c>
       <c r="E209" t="s">
-        <v>356</v>
+        <v>326</v>
       </c>
       <c r="F209" t="s">
         <v>327</v>
@@ -6426,10 +6426,10 @@
         <v>8</v>
       </c>
       <c r="C210" t="s">
-        <v>163</v>
+        <v>363</v>
       </c>
       <c r="D210" t="s">
-        <v>363</v>
+        <v>163</v>
       </c>
       <c r="E210" t="s">
         <v>364</v>
@@ -6449,10 +6449,10 @@
         <v>8</v>
       </c>
       <c r="C211" t="s">
-        <v>163</v>
+        <v>363</v>
       </c>
       <c r="D211" t="s">
-        <v>363</v>
+        <v>163</v>
       </c>
       <c r="E211" t="s">
         <v>364</v>
@@ -6472,10 +6472,10 @@
         <v>8</v>
       </c>
       <c r="C212" t="s">
-        <v>163</v>
+        <v>363</v>
       </c>
       <c r="D212" t="s">
-        <v>363</v>
+        <v>163</v>
       </c>
       <c r="E212" t="s">
         <v>364</v>
@@ -6495,10 +6495,10 @@
         <v>8</v>
       </c>
       <c r="C213" t="s">
-        <v>163</v>
+        <v>363</v>
       </c>
       <c r="D213" t="s">
-        <v>363</v>
+        <v>163</v>
       </c>
       <c r="E213" t="s">
         <v>364</v>
@@ -6518,10 +6518,10 @@
         <v>8</v>
       </c>
       <c r="C214" t="s">
-        <v>163</v>
+        <v>363</v>
       </c>
       <c r="D214" t="s">
-        <v>363</v>
+        <v>163</v>
       </c>
       <c r="E214" t="s">
         <v>364</v>
@@ -6541,16 +6541,16 @@
         <v>8</v>
       </c>
       <c r="C215" t="s">
-        <v>163</v>
+        <v>363</v>
       </c>
       <c r="D215" t="s">
-        <v>363</v>
+        <v>163</v>
       </c>
       <c r="E215" t="s">
-        <v>364</v>
+        <v>326</v>
       </c>
       <c r="F215" t="s">
-        <v>327</v>
+        <v>365</v>
       </c>
       <c r="G215" t="s">
         <v>349</v>
@@ -6564,10 +6564,10 @@
         <v>8</v>
       </c>
       <c r="C216" t="s">
-        <v>163</v>
+        <v>363</v>
       </c>
       <c r="D216" t="s">
-        <v>363</v>
+        <v>163</v>
       </c>
       <c r="E216" t="s">
         <v>364</v>
@@ -6587,10 +6587,10 @@
         <v>8</v>
       </c>
       <c r="C217" t="s">
-        <v>163</v>
+        <v>363</v>
       </c>
       <c r="D217" t="s">
-        <v>363</v>
+        <v>163</v>
       </c>
       <c r="E217" t="s">
         <v>364</v>
@@ -6610,10 +6610,10 @@
         <v>8</v>
       </c>
       <c r="C218" t="s">
-        <v>163</v>
+        <v>363</v>
       </c>
       <c r="D218" t="s">
-        <v>363</v>
+        <v>163</v>
       </c>
       <c r="E218" t="s">
         <v>364</v>
@@ -6633,10 +6633,10 @@
         <v>8</v>
       </c>
       <c r="C219" t="s">
-        <v>163</v>
+        <v>363</v>
       </c>
       <c r="D219" t="s">
-        <v>363</v>
+        <v>163</v>
       </c>
       <c r="E219" t="s">
         <v>364</v>
@@ -6656,16 +6656,16 @@
         <v>8</v>
       </c>
       <c r="C220" t="s">
-        <v>163</v>
+        <v>363</v>
       </c>
       <c r="D220" t="s">
-        <v>363</v>
+        <v>163</v>
       </c>
       <c r="E220" t="s">
-        <v>364</v>
+        <v>270</v>
       </c>
       <c r="F220" t="s">
-        <v>271</v>
+        <v>365</v>
       </c>
       <c r="G220" t="s">
         <v>309</v>
@@ -6679,10 +6679,10 @@
         <v>8</v>
       </c>
       <c r="C221" t="s">
-        <v>163</v>
+        <v>363</v>
       </c>
       <c r="D221" t="s">
-        <v>363</v>
+        <v>163</v>
       </c>
       <c r="E221" t="s">
         <v>364</v>
@@ -6702,10 +6702,10 @@
         <v>8</v>
       </c>
       <c r="C222" t="s">
-        <v>163</v>
+        <v>363</v>
       </c>
       <c r="D222" t="s">
-        <v>363</v>
+        <v>163</v>
       </c>
       <c r="E222" t="s">
         <v>364</v>
@@ -6725,10 +6725,10 @@
         <v>8</v>
       </c>
       <c r="C223" t="s">
-        <v>163</v>
+        <v>363</v>
       </c>
       <c r="D223" t="s">
-        <v>363</v>
+        <v>163</v>
       </c>
       <c r="E223" t="s">
         <v>364</v>
@@ -6748,10 +6748,10 @@
         <v>8</v>
       </c>
       <c r="C224" t="s">
-        <v>163</v>
+        <v>363</v>
       </c>
       <c r="D224" t="s">
-        <v>363</v>
+        <v>163</v>
       </c>
       <c r="E224" t="s">
         <v>364</v>
@@ -6771,10 +6771,10 @@
         <v>8</v>
       </c>
       <c r="C225" t="s">
-        <v>163</v>
+        <v>363</v>
       </c>
       <c r="D225" t="s">
-        <v>363</v>
+        <v>163</v>
       </c>
       <c r="E225" t="s">
         <v>364</v>
@@ -6794,16 +6794,16 @@
         <v>8</v>
       </c>
       <c r="C226" t="s">
-        <v>163</v>
+        <v>363</v>
       </c>
       <c r="D226" t="s">
-        <v>363</v>
+        <v>163</v>
       </c>
       <c r="E226" t="s">
-        <v>364</v>
+        <v>275</v>
       </c>
       <c r="F226" t="s">
-        <v>275</v>
+        <v>365</v>
       </c>
       <c r="G226" t="s">
         <v>276</v>
@@ -6817,10 +6817,10 @@
         <v>8</v>
       </c>
       <c r="C227" t="s">
-        <v>163</v>
+        <v>363</v>
       </c>
       <c r="D227" t="s">
-        <v>363</v>
+        <v>163</v>
       </c>
       <c r="E227" t="s">
         <v>364</v>
@@ -6840,16 +6840,16 @@
         <v>8</v>
       </c>
       <c r="C228" t="s">
-        <v>163</v>
+        <v>363</v>
       </c>
       <c r="D228" t="s">
-        <v>363</v>
+        <v>163</v>
       </c>
       <c r="E228" t="s">
-        <v>364</v>
+        <v>164</v>
       </c>
       <c r="F228" t="s">
-        <v>164</v>
+        <v>365</v>
       </c>
       <c r="G228" t="s">
         <v>165</v>
@@ -6863,13 +6863,13 @@
         <v>8</v>
       </c>
       <c r="C229" t="s">
-        <v>163</v>
+        <v>386</v>
       </c>
       <c r="D229" t="s">
-        <v>363</v>
+        <v>163</v>
       </c>
       <c r="E229" t="s">
-        <v>386</v>
+        <v>364</v>
       </c>
       <c r="F229" t="s">
         <v>365</v>
@@ -6886,13 +6886,13 @@
         <v>8</v>
       </c>
       <c r="C230" t="s">
-        <v>163</v>
+        <v>386</v>
       </c>
       <c r="D230" t="s">
-        <v>363</v>
+        <v>163</v>
       </c>
       <c r="E230" t="s">
-        <v>386</v>
+        <v>364</v>
       </c>
       <c r="F230" t="s">
         <v>365</v>
@@ -6909,16 +6909,16 @@
         <v>8</v>
       </c>
       <c r="C231" t="s">
-        <v>163</v>
+        <v>386</v>
       </c>
       <c r="D231" t="s">
-        <v>363</v>
+        <v>163</v>
       </c>
       <c r="E231" t="s">
-        <v>386</v>
+        <v>270</v>
       </c>
       <c r="F231" t="s">
-        <v>271</v>
+        <v>365</v>
       </c>
       <c r="G231" t="s">
         <v>293</v>
@@ -6932,16 +6932,16 @@
         <v>8</v>
       </c>
       <c r="C232" t="s">
-        <v>163</v>
+        <v>386</v>
       </c>
       <c r="D232" t="s">
-        <v>363</v>
+        <v>163</v>
       </c>
       <c r="E232" t="s">
-        <v>386</v>
+        <v>270</v>
       </c>
       <c r="F232" t="s">
-        <v>271</v>
+        <v>365</v>
       </c>
       <c r="G232" t="s">
         <v>309</v>
@@ -6955,13 +6955,13 @@
         <v>8</v>
       </c>
       <c r="C233" t="s">
-        <v>163</v>
+        <v>386</v>
       </c>
       <c r="D233" t="s">
-        <v>363</v>
+        <v>163</v>
       </c>
       <c r="E233" t="s">
-        <v>386</v>
+        <v>364</v>
       </c>
       <c r="F233" t="s">
         <v>365</v>
@@ -6978,13 +6978,13 @@
         <v>8</v>
       </c>
       <c r="C234" t="s">
-        <v>163</v>
+        <v>386</v>
       </c>
       <c r="D234" t="s">
-        <v>363</v>
+        <v>163</v>
       </c>
       <c r="E234" t="s">
-        <v>386</v>
+        <v>364</v>
       </c>
       <c r="F234" t="s">
         <v>365</v>
@@ -7001,13 +7001,13 @@
         <v>8</v>
       </c>
       <c r="C235" t="s">
-        <v>163</v>
+        <v>386</v>
       </c>
       <c r="D235" t="s">
-        <v>363</v>
+        <v>163</v>
       </c>
       <c r="E235" t="s">
-        <v>386</v>
+        <v>364</v>
       </c>
       <c r="F235" t="s">
         <v>365</v>
@@ -7024,13 +7024,13 @@
         <v>8</v>
       </c>
       <c r="C236" t="s">
-        <v>163</v>
+        <v>386</v>
       </c>
       <c r="D236" t="s">
-        <v>363</v>
+        <v>163</v>
       </c>
       <c r="E236" t="s">
-        <v>386</v>
+        <v>364</v>
       </c>
       <c r="F236" t="s">
         <v>365</v>
@@ -7047,13 +7047,13 @@
         <v>8</v>
       </c>
       <c r="C237" t="s">
-        <v>163</v>
+        <v>386</v>
       </c>
       <c r="D237" t="s">
-        <v>363</v>
+        <v>163</v>
       </c>
       <c r="E237" t="s">
-        <v>386</v>
+        <v>364</v>
       </c>
       <c r="F237" t="s">
         <v>365</v>
@@ -7070,13 +7070,13 @@
         <v>8</v>
       </c>
       <c r="C238" t="s">
-        <v>163</v>
+        <v>386</v>
       </c>
       <c r="D238" t="s">
-        <v>363</v>
+        <v>163</v>
       </c>
       <c r="E238" t="s">
-        <v>386</v>
+        <v>364</v>
       </c>
       <c r="F238" t="s">
         <v>365</v>
@@ -7093,13 +7093,13 @@
         <v>8</v>
       </c>
       <c r="C239" t="s">
-        <v>163</v>
+        <v>398</v>
       </c>
       <c r="D239" t="s">
-        <v>363</v>
+        <v>163</v>
       </c>
       <c r="E239" t="s">
-        <v>398</v>
+        <v>364</v>
       </c>
       <c r="F239" t="s">
         <v>365</v>
@@ -7116,16 +7116,16 @@
         <v>8</v>
       </c>
       <c r="C240" t="s">
-        <v>163</v>
+        <v>401</v>
       </c>
       <c r="D240" t="s">
-        <v>401</v>
+        <v>163</v>
       </c>
       <c r="E240" t="s">
+        <v>164</v>
+      </c>
+      <c r="F240" t="s">
         <v>402</v>
-      </c>
-      <c r="F240" t="s">
-        <v>164</v>
       </c>
       <c r="G240" t="s">
         <v>165</v>
@@ -7139,16 +7139,16 @@
         <v>8</v>
       </c>
       <c r="C241" t="s">
-        <v>163</v>
+        <v>401</v>
       </c>
       <c r="D241" t="s">
-        <v>401</v>
+        <v>163</v>
       </c>
       <c r="E241" t="s">
+        <v>164</v>
+      </c>
+      <c r="F241" t="s">
         <v>402</v>
-      </c>
-      <c r="F241" t="s">
-        <v>164</v>
       </c>
       <c r="G241" t="s">
         <v>165</v>
@@ -7162,16 +7162,16 @@
         <v>8</v>
       </c>
       <c r="C242" t="s">
-        <v>163</v>
+        <v>401</v>
       </c>
       <c r="D242" t="s">
-        <v>401</v>
+        <v>163</v>
       </c>
       <c r="E242" t="s">
+        <v>164</v>
+      </c>
+      <c r="F242" t="s">
         <v>402</v>
-      </c>
-      <c r="F242" t="s">
-        <v>164</v>
       </c>
       <c r="G242" t="s">
         <v>165</v>
@@ -7185,16 +7185,16 @@
         <v>8</v>
       </c>
       <c r="C243" t="s">
-        <v>163</v>
+        <v>401</v>
       </c>
       <c r="D243" t="s">
-        <v>401</v>
+        <v>163</v>
       </c>
       <c r="E243" t="s">
+        <v>164</v>
+      </c>
+      <c r="F243" t="s">
         <v>402</v>
-      </c>
-      <c r="F243" t="s">
-        <v>164</v>
       </c>
       <c r="G243" t="s">
         <v>165</v>
@@ -7208,16 +7208,16 @@
         <v>8</v>
       </c>
       <c r="C244" t="s">
-        <v>163</v>
+        <v>401</v>
       </c>
       <c r="D244" t="s">
-        <v>401</v>
+        <v>163</v>
       </c>
       <c r="E244" t="s">
+        <v>164</v>
+      </c>
+      <c r="F244" t="s">
         <v>402</v>
-      </c>
-      <c r="F244" t="s">
-        <v>164</v>
       </c>
       <c r="G244" t="s">
         <v>165</v>
@@ -7231,16 +7231,16 @@
         <v>8</v>
       </c>
       <c r="C245" t="s">
-        <v>163</v>
+        <v>401</v>
       </c>
       <c r="D245" t="s">
-        <v>401</v>
+        <v>163</v>
       </c>
       <c r="E245" t="s">
+        <v>164</v>
+      </c>
+      <c r="F245" t="s">
         <v>402</v>
-      </c>
-      <c r="F245" t="s">
-        <v>164</v>
       </c>
       <c r="G245" t="s">
         <v>165</v>
@@ -7254,16 +7254,16 @@
         <v>8</v>
       </c>
       <c r="C246" t="s">
-        <v>163</v>
+        <v>409</v>
       </c>
       <c r="D246" t="s">
-        <v>401</v>
+        <v>163</v>
       </c>
       <c r="E246" t="s">
-        <v>409</v>
+        <v>255</v>
       </c>
       <c r="F246" t="s">
-        <v>255</v>
+        <v>402</v>
       </c>
       <c r="G246" t="s">
         <v>410</v>
@@ -7276,14 +7276,14 @@
       <c r="B247" t="s">
         <v>8</v>
       </c>
-      <c r="C247" t="s">
+      <c r="D247" t="s">
         <v>95</v>
       </c>
-      <c r="D247" t="s">
+      <c r="E247" t="s">
+        <v>96</v>
+      </c>
+      <c r="F247" t="s">
         <v>412</v>
-      </c>
-      <c r="F247" t="s">
-        <v>96</v>
       </c>
       <c r="G247" t="s">
         <v>97</v>
@@ -7296,14 +7296,14 @@
       <c r="B248" t="s">
         <v>8</v>
       </c>
-      <c r="C248" t="s">
+      <c r="D248" t="s">
         <v>95</v>
       </c>
-      <c r="D248" t="s">
+      <c r="E248" t="s">
+        <v>96</v>
+      </c>
+      <c r="F248" t="s">
         <v>412</v>
-      </c>
-      <c r="F248" t="s">
-        <v>96</v>
       </c>
       <c r="G248" t="s">
         <v>97</v>
@@ -7316,14 +7316,14 @@
       <c r="B249" t="s">
         <v>8</v>
       </c>
-      <c r="C249" t="s">
+      <c r="D249" t="s">
         <v>95</v>
       </c>
-      <c r="D249" t="s">
+      <c r="E249" t="s">
+        <v>415</v>
+      </c>
+      <c r="F249" t="s">
         <v>412</v>
-      </c>
-      <c r="F249" t="s">
-        <v>415</v>
       </c>
       <c r="G249" t="s">
         <v>416</v>
@@ -7336,14 +7336,14 @@
       <c r="B250" t="s">
         <v>8</v>
       </c>
-      <c r="C250" t="s">
+      <c r="D250" t="s">
         <v>95</v>
       </c>
-      <c r="D250" t="s">
+      <c r="E250" t="s">
+        <v>96</v>
+      </c>
+      <c r="F250" t="s">
         <v>412</v>
-      </c>
-      <c r="F250" t="s">
-        <v>96</v>
       </c>
       <c r="G250" t="s">
         <v>97</v>
@@ -7356,14 +7356,14 @@
       <c r="B251" t="s">
         <v>8</v>
       </c>
-      <c r="C251" t="s">
+      <c r="D251" t="s">
         <v>95</v>
       </c>
-      <c r="D251" t="s">
+      <c r="E251" t="s">
+        <v>96</v>
+      </c>
+      <c r="F251" t="s">
         <v>412</v>
-      </c>
-      <c r="F251" t="s">
-        <v>96</v>
       </c>
       <c r="G251" t="s">
         <v>97</v>
@@ -7376,14 +7376,14 @@
       <c r="B252" t="s">
         <v>8</v>
       </c>
-      <c r="C252" t="s">
+      <c r="D252" t="s">
         <v>95</v>
       </c>
-      <c r="D252" t="s">
+      <c r="E252" t="s">
+        <v>96</v>
+      </c>
+      <c r="F252" t="s">
         <v>412</v>
-      </c>
-      <c r="F252" t="s">
-        <v>96</v>
       </c>
       <c r="G252" t="s">
         <v>97</v>
@@ -7396,10 +7396,10 @@
       <c r="B253" t="s">
         <v>8</v>
       </c>
-      <c r="C253" t="s">
-        <v>163</v>
-      </c>
       <c r="D253" t="s">
+        <v>163</v>
+      </c>
+      <c r="E253" t="s">
         <v>421</v>
       </c>
       <c r="F253" t="s">
@@ -7416,14 +7416,14 @@
       <c r="B254" t="s">
         <v>8</v>
       </c>
-      <c r="C254" t="s">
+      <c r="D254" t="s">
         <v>90</v>
       </c>
-      <c r="D254" t="s">
-        <v>421</v>
+      <c r="E254" t="s">
+        <v>219</v>
       </c>
       <c r="F254" t="s">
-        <v>219</v>
+        <v>422</v>
       </c>
       <c r="G254" t="s">
         <v>220</v>
@@ -7436,14 +7436,14 @@
       <c r="B255" t="s">
         <v>8</v>
       </c>
-      <c r="C255" t="s">
+      <c r="D255" t="s">
         <v>90</v>
       </c>
-      <c r="D255" t="s">
-        <v>421</v>
+      <c r="E255" t="s">
+        <v>426</v>
       </c>
       <c r="F255" t="s">
-        <v>426</v>
+        <v>422</v>
       </c>
       <c r="G255" t="s">
         <v>427</v>
@@ -7456,14 +7456,14 @@
       <c r="B256" t="s">
         <v>8</v>
       </c>
-      <c r="C256" t="s">
+      <c r="D256" t="s">
         <v>90</v>
       </c>
-      <c r="D256" t="s">
-        <v>421</v>
+      <c r="E256" t="s">
+        <v>426</v>
       </c>
       <c r="F256" t="s">
-        <v>426</v>
+        <v>422</v>
       </c>
       <c r="G256" t="s">
         <v>427</v>
@@ -7476,14 +7476,14 @@
       <c r="B257" t="s">
         <v>8</v>
       </c>
-      <c r="C257" t="s">
+      <c r="D257" t="s">
         <v>90</v>
       </c>
-      <c r="D257" t="s">
-        <v>421</v>
+      <c r="E257" t="s">
+        <v>426</v>
       </c>
       <c r="F257" t="s">
-        <v>426</v>
+        <v>422</v>
       </c>
       <c r="G257" t="s">
         <v>427</v>
@@ -7496,14 +7496,14 @@
       <c r="B258" t="s">
         <v>8</v>
       </c>
-      <c r="C258" t="s">
-        <v>163</v>
-      </c>
       <c r="D258" t="s">
-        <v>421</v>
+        <v>163</v>
+      </c>
+      <c r="E258" t="s">
+        <v>326</v>
       </c>
       <c r="F258" t="s">
-        <v>327</v>
+        <v>422</v>
       </c>
       <c r="G258" t="s">
         <v>328</v>
@@ -7516,14 +7516,14 @@
       <c r="B259" t="s">
         <v>8</v>
       </c>
-      <c r="C259" t="s">
+      <c r="D259" t="s">
         <v>90</v>
       </c>
-      <c r="D259" t="s">
-        <v>421</v>
+      <c r="E259" t="s">
+        <v>426</v>
       </c>
       <c r="F259" t="s">
-        <v>426</v>
+        <v>422</v>
       </c>
       <c r="G259" t="s">
         <v>427</v>
@@ -7536,14 +7536,14 @@
       <c r="B260" t="s">
         <v>8</v>
       </c>
-      <c r="C260" t="s">
-        <v>163</v>
-      </c>
       <c r="D260" t="s">
-        <v>421</v>
+        <v>163</v>
+      </c>
+      <c r="E260" t="s">
+        <v>164</v>
       </c>
       <c r="F260" t="s">
-        <v>164</v>
+        <v>422</v>
       </c>
       <c r="G260" t="s">
         <v>165</v>
@@ -7556,14 +7556,14 @@
       <c r="B261" t="s">
         <v>8</v>
       </c>
-      <c r="C261" t="s">
+      <c r="D261" t="s">
         <v>195</v>
       </c>
-      <c r="D261" t="s">
-        <v>421</v>
+      <c r="E261" t="s">
+        <v>434</v>
       </c>
       <c r="F261" t="s">
-        <v>434</v>
+        <v>422</v>
       </c>
       <c r="G261" t="s">
         <v>435</v>
@@ -7576,14 +7576,14 @@
       <c r="B262" t="s">
         <v>8</v>
       </c>
-      <c r="C262" t="s">
-        <v>163</v>
-      </c>
       <c r="D262" t="s">
-        <v>421</v>
+        <v>163</v>
+      </c>
+      <c r="E262" t="s">
+        <v>164</v>
       </c>
       <c r="F262" t="s">
-        <v>164</v>
+        <v>422</v>
       </c>
       <c r="G262" t="s">
         <v>165</v>
@@ -7596,14 +7596,14 @@
       <c r="B263" t="s">
         <v>8</v>
       </c>
-      <c r="C263" t="s">
+      <c r="D263" t="s">
         <v>182</v>
       </c>
-      <c r="D263" t="s">
-        <v>421</v>
+      <c r="E263" t="s">
+        <v>438</v>
       </c>
       <c r="F263" t="s">
-        <v>438</v>
+        <v>422</v>
       </c>
       <c r="G263" t="s">
         <v>439</v>
@@ -7616,14 +7616,14 @@
       <c r="B264" t="s">
         <v>8</v>
       </c>
-      <c r="C264" t="s">
+      <c r="D264" t="s">
         <v>31</v>
       </c>
-      <c r="D264" t="s">
-        <v>421</v>
+      <c r="E264" t="s">
+        <v>32</v>
       </c>
       <c r="F264" t="s">
-        <v>32</v>
+        <v>422</v>
       </c>
       <c r="G264" t="s">
         <v>33</v>
@@ -7636,14 +7636,14 @@
       <c r="B265" t="s">
         <v>8</v>
       </c>
-      <c r="C265" t="s">
-        <v>9</v>
-      </c>
       <c r="D265" t="s">
-        <v>421</v>
+        <v>10</v>
+      </c>
+      <c r="E265" t="s">
+        <v>11</v>
       </c>
       <c r="F265" t="s">
-        <v>12</v>
+        <v>422</v>
       </c>
       <c r="G265" t="s">
         <v>13</v>
@@ -7656,14 +7656,14 @@
       <c r="B266" t="s">
         <v>8</v>
       </c>
-      <c r="C266" t="s">
-        <v>112</v>
-      </c>
       <c r="D266" t="s">
-        <v>421</v>
+        <v>113</v>
+      </c>
+      <c r="E266" t="s">
+        <v>443</v>
       </c>
       <c r="F266" t="s">
-        <v>443</v>
+        <v>422</v>
       </c>
       <c r="G266" t="s">
         <v>444</v>
@@ -7676,14 +7676,14 @@
       <c r="B267" t="s">
         <v>8</v>
       </c>
-      <c r="C267" t="s">
-        <v>112</v>
-      </c>
       <c r="D267" t="s">
+        <v>113</v>
+      </c>
+      <c r="E267" t="s">
+        <v>118</v>
+      </c>
+      <c r="F267" t="s">
         <v>446</v>
-      </c>
-      <c r="F267" t="s">
-        <v>118</v>
       </c>
       <c r="G267" t="s">
         <v>119</v>
@@ -7696,14 +7696,14 @@
       <c r="B268" t="s">
         <v>8</v>
       </c>
-      <c r="C268" t="s">
+      <c r="D268" t="s">
         <v>182</v>
       </c>
-      <c r="D268" t="s">
+      <c r="E268" t="s">
+        <v>202</v>
+      </c>
+      <c r="F268" t="s">
         <v>448</v>
-      </c>
-      <c r="F268" t="s">
-        <v>203</v>
       </c>
       <c r="G268" t="s">
         <v>204</v>
@@ -7716,14 +7716,14 @@
       <c r="B269" t="s">
         <v>8</v>
       </c>
-      <c r="C269" t="s">
-        <v>112</v>
-      </c>
       <c r="D269" t="s">
+        <v>113</v>
+      </c>
+      <c r="E269" t="s">
+        <v>118</v>
+      </c>
+      <c r="F269" t="s">
         <v>450</v>
-      </c>
-      <c r="F269" t="s">
-        <v>118</v>
       </c>
       <c r="G269" t="s">
         <v>119</v>
@@ -7736,14 +7736,14 @@
       <c r="B270" t="s">
         <v>8</v>
       </c>
-      <c r="C270" t="s">
-        <v>112</v>
-      </c>
       <c r="D270" t="s">
+        <v>113</v>
+      </c>
+      <c r="E270" t="s">
+        <v>118</v>
+      </c>
+      <c r="F270" t="s">
         <v>450</v>
-      </c>
-      <c r="F270" t="s">
-        <v>118</v>
       </c>
       <c r="G270" t="s">
         <v>119</v>
@@ -7756,10 +7756,10 @@
       <c r="B271" t="s">
         <v>8</v>
       </c>
-      <c r="C271" t="s">
-        <v>112</v>
-      </c>
       <c r="D271" t="s">
+        <v>113</v>
+      </c>
+      <c r="E271" t="s">
         <v>453</v>
       </c>
       <c r="F271" t="s">
@@ -7776,10 +7776,10 @@
       <c r="B272" t="s">
         <v>8</v>
       </c>
-      <c r="C272" t="s">
-        <v>112</v>
-      </c>
       <c r="D272" t="s">
+        <v>113</v>
+      </c>
+      <c r="E272" t="s">
         <v>453</v>
       </c>
       <c r="F272" t="s">
@@ -7796,10 +7796,10 @@
       <c r="B273" t="s">
         <v>8</v>
       </c>
-      <c r="C273" t="s">
-        <v>112</v>
-      </c>
       <c r="D273" t="s">
+        <v>113</v>
+      </c>
+      <c r="E273" t="s">
         <v>453</v>
       </c>
       <c r="F273" t="s">
@@ -7816,10 +7816,10 @@
       <c r="B274" t="s">
         <v>8</v>
       </c>
-      <c r="C274" t="s">
-        <v>112</v>
-      </c>
       <c r="D274" t="s">
+        <v>113</v>
+      </c>
+      <c r="E274" t="s">
         <v>453</v>
       </c>
       <c r="F274" t="s">
@@ -7836,10 +7836,10 @@
       <c r="B275" t="s">
         <v>8</v>
       </c>
-      <c r="C275" t="s">
-        <v>112</v>
-      </c>
       <c r="D275" t="s">
+        <v>113</v>
+      </c>
+      <c r="E275" t="s">
         <v>453</v>
       </c>
       <c r="F275" t="s">
@@ -7856,10 +7856,10 @@
       <c r="B276" t="s">
         <v>8</v>
       </c>
-      <c r="C276" t="s">
-        <v>112</v>
-      </c>
       <c r="D276" t="s">
+        <v>113</v>
+      </c>
+      <c r="E276" t="s">
         <v>453</v>
       </c>
       <c r="F276" t="s">
@@ -7876,10 +7876,10 @@
       <c r="B277" t="s">
         <v>8</v>
       </c>
-      <c r="C277" t="s">
-        <v>112</v>
-      </c>
       <c r="D277" t="s">
+        <v>113</v>
+      </c>
+      <c r="E277" t="s">
         <v>453</v>
       </c>
       <c r="F277" t="s">
@@ -7896,14 +7896,14 @@
       <c r="B278" t="s">
         <v>8</v>
       </c>
-      <c r="C278" t="s">
+      <c r="D278" t="s">
         <v>182</v>
       </c>
-      <c r="D278" t="s">
+      <c r="E278" t="s">
+        <v>202</v>
+      </c>
+      <c r="F278" t="s">
         <v>463</v>
-      </c>
-      <c r="F278" t="s">
-        <v>203</v>
       </c>
       <c r="G278" t="s">
         <v>204</v>
@@ -7916,14 +7916,14 @@
       <c r="B279" t="s">
         <v>8</v>
       </c>
-      <c r="C279" t="s">
+      <c r="D279" t="s">
         <v>31</v>
       </c>
-      <c r="D279" t="s">
+      <c r="E279" t="s">
+        <v>52</v>
+      </c>
+      <c r="F279" t="s">
         <v>463</v>
-      </c>
-      <c r="F279" t="s">
-        <v>53</v>
       </c>
       <c r="G279" t="s">
         <v>54</v>
@@ -7936,14 +7936,14 @@
       <c r="B280" t="s">
         <v>8</v>
       </c>
-      <c r="C280" t="s">
-        <v>9</v>
-      </c>
       <c r="D280" t="s">
+        <v>10</v>
+      </c>
+      <c r="E280" t="s">
+        <v>11</v>
+      </c>
+      <c r="F280" t="s">
         <v>463</v>
-      </c>
-      <c r="F280" t="s">
-        <v>12</v>
       </c>
       <c r="G280" t="s">
         <v>13</v>
@@ -7956,14 +7956,14 @@
       <c r="B281" t="s">
         <v>8</v>
       </c>
-      <c r="C281" t="s">
-        <v>112</v>
-      </c>
       <c r="D281" t="s">
+        <v>113</v>
+      </c>
+      <c r="E281" t="s">
+        <v>170</v>
+      </c>
+      <c r="F281" t="s">
         <v>463</v>
-      </c>
-      <c r="F281" t="s">
-        <v>170</v>
       </c>
       <c r="G281" t="s">
         <v>171</v>
@@ -7976,14 +7976,14 @@
       <c r="B282" t="s">
         <v>8</v>
       </c>
-      <c r="C282" t="s">
+      <c r="D282" t="s">
         <v>124</v>
       </c>
-      <c r="D282" t="s">
+      <c r="E282" t="s">
+        <v>125</v>
+      </c>
+      <c r="F282" t="s">
         <v>463</v>
-      </c>
-      <c r="F282" t="s">
-        <v>125</v>
       </c>
       <c r="G282" t="s">
         <v>126</v>
@@ -7996,14 +7996,14 @@
       <c r="B283" t="s">
         <v>8</v>
       </c>
-      <c r="C283" t="s">
-        <v>163</v>
-      </c>
       <c r="D283" t="s">
+        <v>163</v>
+      </c>
+      <c r="E283" t="s">
+        <v>364</v>
+      </c>
+      <c r="F283" t="s">
         <v>469</v>
-      </c>
-      <c r="F283" t="s">
-        <v>365</v>
       </c>
       <c r="G283" t="s">
         <v>399</v>
@@ -8016,14 +8016,14 @@
       <c r="B284" t="s">
         <v>8</v>
       </c>
-      <c r="C284" t="s">
+      <c r="D284" t="s">
         <v>124</v>
       </c>
-      <c r="D284" t="s">
+      <c r="E284" t="s">
+        <v>125</v>
+      </c>
+      <c r="F284" t="s">
         <v>471</v>
-      </c>
-      <c r="F284" t="s">
-        <v>125</v>
       </c>
       <c r="G284" t="s">
         <v>126</v>
@@ -8036,14 +8036,14 @@
       <c r="B285" t="s">
         <v>8</v>
       </c>
-      <c r="C285" t="s">
-        <v>112</v>
-      </c>
       <c r="D285" t="s">
+        <v>113</v>
+      </c>
+      <c r="E285" t="s">
+        <v>170</v>
+      </c>
+      <c r="F285" t="s">
         <v>473</v>
-      </c>
-      <c r="F285" t="s">
-        <v>170</v>
       </c>
       <c r="G285" t="s">
         <v>171</v>
@@ -8056,14 +8056,14 @@
       <c r="B286" t="s">
         <v>8</v>
       </c>
-      <c r="C286" t="s">
+      <c r="D286" t="s">
         <v>182</v>
       </c>
-      <c r="D286" t="s">
+      <c r="E286" t="s">
+        <v>438</v>
+      </c>
+      <c r="F286" t="s">
         <v>475</v>
-      </c>
-      <c r="F286" t="s">
-        <v>438</v>
       </c>
       <c r="G286" t="s">
         <v>439</v>
@@ -8076,14 +8076,14 @@
       <c r="B287" t="s">
         <v>8</v>
       </c>
-      <c r="C287" t="s">
+      <c r="D287" t="s">
         <v>182</v>
       </c>
-      <c r="D287" t="s">
+      <c r="E287" t="s">
+        <v>438</v>
+      </c>
+      <c r="F287" t="s">
         <v>475</v>
-      </c>
-      <c r="F287" t="s">
-        <v>438</v>
       </c>
       <c r="G287" t="s">
         <v>439</v>
@@ -8096,14 +8096,14 @@
       <c r="B288" t="s">
         <v>8</v>
       </c>
-      <c r="C288" t="s">
-        <v>9</v>
-      </c>
       <c r="D288" t="s">
+        <v>10</v>
+      </c>
+      <c r="E288" t="s">
+        <v>41</v>
+      </c>
+      <c r="F288" t="s">
         <v>475</v>
-      </c>
-      <c r="F288" t="s">
-        <v>41</v>
       </c>
       <c r="G288" t="s">
         <v>42</v>
@@ -8116,14 +8116,14 @@
       <c r="B289" t="s">
         <v>8</v>
       </c>
-      <c r="C289" t="s">
+      <c r="D289" t="s">
         <v>31</v>
       </c>
-      <c r="D289" t="s">
+      <c r="E289" t="s">
+        <v>32</v>
+      </c>
+      <c r="F289" t="s">
         <v>475</v>
-      </c>
-      <c r="F289" t="s">
-        <v>32</v>
       </c>
       <c r="G289" t="s">
         <v>33</v>
@@ -8136,14 +8136,14 @@
       <c r="B290" t="s">
         <v>8</v>
       </c>
-      <c r="C290" t="s">
+      <c r="D290" t="s">
         <v>31</v>
       </c>
-      <c r="D290" t="s">
+      <c r="E290" t="s">
+        <v>32</v>
+      </c>
+      <c r="F290" t="s">
         <v>475</v>
-      </c>
-      <c r="F290" t="s">
-        <v>32</v>
       </c>
       <c r="G290" t="s">
         <v>33</v>
@@ -8156,14 +8156,14 @@
       <c r="B291" t="s">
         <v>8</v>
       </c>
-      <c r="C291" t="s">
-        <v>112</v>
-      </c>
       <c r="D291" t="s">
+        <v>113</v>
+      </c>
+      <c r="E291" t="s">
+        <v>170</v>
+      </c>
+      <c r="F291" t="s">
         <v>475</v>
-      </c>
-      <c r="F291" t="s">
-        <v>170</v>
       </c>
       <c r="G291" t="s">
         <v>171</v>
@@ -8176,14 +8176,14 @@
       <c r="B292" t="s">
         <v>8</v>
       </c>
-      <c r="C292" t="s">
-        <v>112</v>
-      </c>
       <c r="D292" t="s">
+        <v>113</v>
+      </c>
+      <c r="E292" t="s">
+        <v>170</v>
+      </c>
+      <c r="F292" t="s">
         <v>475</v>
-      </c>
-      <c r="F292" t="s">
-        <v>170</v>
       </c>
       <c r="G292" t="s">
         <v>171</v>
@@ -8196,14 +8196,14 @@
       <c r="B293" t="s">
         <v>8</v>
       </c>
-      <c r="C293" t="s">
-        <v>112</v>
-      </c>
       <c r="D293" t="s">
+        <v>113</v>
+      </c>
+      <c r="E293" t="s">
+        <v>170</v>
+      </c>
+      <c r="F293" t="s">
         <v>475</v>
-      </c>
-      <c r="F293" t="s">
-        <v>170</v>
       </c>
       <c r="G293" t="s">
         <v>171</v>
@@ -8216,14 +8216,14 @@
       <c r="B294" t="s">
         <v>8</v>
       </c>
-      <c r="C294" t="s">
-        <v>112</v>
-      </c>
       <c r="D294" t="s">
+        <v>113</v>
+      </c>
+      <c r="E294" t="s">
+        <v>170</v>
+      </c>
+      <c r="F294" t="s">
         <v>475</v>
-      </c>
-      <c r="F294" t="s">
-        <v>170</v>
       </c>
       <c r="G294" t="s">
         <v>171</v>
@@ -8236,14 +8236,14 @@
       <c r="B295" t="s">
         <v>8</v>
       </c>
-      <c r="C295" t="s">
-        <v>112</v>
-      </c>
       <c r="D295" t="s">
+        <v>113</v>
+      </c>
+      <c r="E295" t="s">
+        <v>170</v>
+      </c>
+      <c r="F295" t="s">
         <v>485</v>
-      </c>
-      <c r="F295" t="s">
-        <v>170</v>
       </c>
       <c r="G295" t="s">
         <v>171</v>
@@ -8256,14 +8256,14 @@
       <c r="B296" t="s">
         <v>8</v>
       </c>
-      <c r="C296" t="s">
-        <v>112</v>
-      </c>
       <c r="D296" t="s">
+        <v>113</v>
+      </c>
+      <c r="E296" t="s">
+        <v>170</v>
+      </c>
+      <c r="F296" t="s">
         <v>485</v>
-      </c>
-      <c r="F296" t="s">
-        <v>170</v>
       </c>
       <c r="G296" t="s">
         <v>171</v>

--- a/api/2/xlsx/fr/SectorCOFOG.xlsx
+++ b/api/2/xlsx/fr/SectorCOFOG.xlsx
@@ -25,18 +25,18 @@
     <t>codeforiati:category-code</t>
   </si>
   <si>
+    <t>codeforiati:cofog-class</t>
+  </si>
+  <si>
+    <t>codeforiati:cofog-group</t>
+  </si>
+  <si>
     <t>codeforiati:cofog-division</t>
   </si>
   <si>
-    <t>codeforiati:cofog-group</t>
-  </si>
-  <si>
     <t>codeforiati:group-code</t>
   </si>
   <si>
-    <t>codeforiati:cofog-class</t>
-  </si>
-  <si>
     <t>11110</t>
   </si>
   <si>
@@ -46,51 +46,51 @@
     <t>111</t>
   </si>
   <si>
+    <t>09.8.0 - Education n.e.c. (CS)</t>
+  </si>
+  <si>
+    <t>09.8 - Education n.e.c.</t>
+  </si>
+  <si>
     <t>09 - Education</t>
   </si>
   <si>
-    <t>09.8 - Education n.e.c.</t>
-  </si>
-  <si>
     <t>110</t>
   </si>
   <si>
-    <t>09.8.0 - Education n.e.c. (CS)</t>
-  </si>
-  <si>
     <t>11120</t>
   </si>
   <si>
+    <t>09.6.0 - Subsidiary services to education (IS)</t>
+  </si>
+  <si>
     <t>09.6 - Subsidiary services to education</t>
   </si>
   <si>
-    <t>09.6.0 - Subsidiary services to education (IS)</t>
-  </si>
-  <si>
     <t>11130</t>
   </si>
   <si>
     <t>11182</t>
   </si>
   <si>
+    <t>09.7.0 - R&amp;D Education (CS)</t>
+  </si>
+  <si>
     <t>09.7 - R&amp;D Education</t>
   </si>
   <si>
-    <t>09.7.0 - R&amp;D Education (CS)</t>
-  </si>
-  <si>
     <t>11220</t>
   </si>
   <si>
     <t>112</t>
   </si>
   <si>
+    <t>09.1.2 - Primary education (IS)</t>
+  </si>
+  <si>
     <t>09.1 - Pre‐primary and primary education</t>
   </si>
   <si>
-    <t>09.1.2 - Primary education (IS)</t>
-  </si>
-  <si>
     <t>11230</t>
   </si>
   <si>
@@ -109,24 +109,24 @@
     <t>11250</t>
   </si>
   <si>
+    <t>07.4.0 - Public health services (IS)</t>
+  </si>
+  <si>
+    <t>07.4 - Public health services</t>
+  </si>
+  <si>
     <t>07 - Health</t>
   </si>
   <si>
-    <t>07.4 - Public health services</t>
-  </si>
-  <si>
-    <t>07.4.0 - Public health services (IS)</t>
-  </si>
-  <si>
     <t>11260</t>
   </si>
   <si>
+    <t>09.2.1 - Lower‐secondary education (IS)</t>
+  </si>
+  <si>
     <t>09.2 - Secondary education</t>
   </si>
   <si>
-    <t>09.2.1 - Lower‐secondary education (IS)</t>
-  </si>
-  <si>
     <t>11320</t>
   </si>
   <si>
@@ -139,69 +139,69 @@
     <t>11330</t>
   </si>
   <si>
+    <t>09.5.0 - Education not definable by level (IS)</t>
+  </si>
+  <si>
     <t>09.5 - Education not definable by level</t>
   </si>
   <si>
-    <t>09.5.0 - Education not definable by level (IS)</t>
-  </si>
-  <si>
     <t>11420</t>
   </si>
   <si>
     <t>114</t>
   </si>
   <si>
+    <t>09.4.1 - First stage of tertiary education (IS)</t>
+  </si>
+  <si>
     <t>09.4 - Tertiary education</t>
   </si>
   <si>
-    <t>09.4.1 - First stage of tertiary education (IS)</t>
-  </si>
-  <si>
     <t>11430</t>
   </si>
   <si>
+    <t>09.3.0 - Post‐secondary non‐tertiary education (IS)</t>
+  </si>
+  <si>
     <t>09.3 - Post‐secondary non‐tertiary education</t>
   </si>
   <si>
-    <t>09.3.0 - Post‐secondary non‐tertiary education (IS)</t>
-  </si>
-  <si>
     <t>12110</t>
   </si>
   <si>
     <t>121</t>
   </si>
   <si>
+    <t>07.6.0 - Health n.e.c. (CS)</t>
+  </si>
+  <si>
     <t>07.6 - Health n.e.c.</t>
   </si>
   <si>
     <t>120</t>
   </si>
   <si>
-    <t>07.6.0 - Health n.e.c. (CS)</t>
-  </si>
-  <si>
     <t>12181</t>
   </si>
   <si>
     <t>12182</t>
   </si>
   <si>
+    <t>07.5.0 - R&amp;D Health (CS)</t>
+  </si>
+  <si>
     <t>07.5 - R&amp;D Health</t>
   </si>
   <si>
-    <t>07.5.0 - R&amp;D Health (CS)</t>
-  </si>
-  <si>
     <t>12191</t>
   </si>
   <si>
+    <t>07.2.1 - General medical services (IS)</t>
+  </si>
+  <si>
     <t>07.2 - Outpatient services</t>
   </si>
   <si>
-    <t>07.2.1 - General medical services (IS)</t>
-  </si>
-  <si>
     <t>12196</t>
   </si>
   <si>
@@ -214,12 +214,12 @@
     <t>12230</t>
   </si>
   <si>
+    <t>07.3.1 - General hospital services (IS)</t>
+  </si>
+  <si>
     <t>07.3 - Hospital services</t>
   </si>
   <si>
-    <t>07.3.1 - General hospital services (IS)</t>
-  </si>
-  <si>
     <t>12240</t>
   </si>
   <si>
@@ -286,30 +286,30 @@
     <t>14010</t>
   </si>
   <si>
+    <t>06.3.0 - Water supply (CS)</t>
+  </si>
+  <si>
+    <t>06.3 - Water supply</t>
+  </si>
+  <si>
     <t>06 - Housing and community amenities</t>
   </si>
   <si>
-    <t>06.3 - Water supply</t>
-  </si>
-  <si>
     <t>140</t>
   </si>
   <si>
-    <t>06.3.0 - Water supply (CS)</t>
-  </si>
-  <si>
     <t>14015</t>
   </si>
   <si>
+    <t>05.6.0 - Environmental protection n.e.c. (CS)</t>
+  </si>
+  <si>
+    <t>05.6 - Environmental protection n.e.c.</t>
+  </si>
+  <si>
     <t>05 - Environmental protection</t>
   </si>
   <si>
-    <t>05.6 - Environmental protection n.e.c.</t>
-  </si>
-  <si>
-    <t>05.6.0 - Environmental protection n.e.c. (CS)</t>
-  </si>
-  <si>
     <t>14020</t>
   </si>
   <si>
@@ -319,12 +319,12 @@
     <t>14022</t>
   </si>
   <si>
+    <t>05.2.0 - Waste water management (CS)</t>
+  </si>
+  <si>
     <t>05.2 - Waste water management</t>
   </si>
   <si>
-    <t>05.2.0 - Waste water management (CS)</t>
-  </si>
-  <si>
     <t>14030</t>
   </si>
   <si>
@@ -340,12 +340,12 @@
     <t>14050</t>
   </si>
   <si>
+    <t>05.1.0 - Waste management (CS)</t>
+  </si>
+  <si>
     <t>05.1 - Waste management</t>
   </si>
   <si>
-    <t>05.1.0 - Waste management (CS)</t>
-  </si>
-  <si>
     <t>14081</t>
   </si>
   <si>
@@ -355,48 +355,48 @@
     <t>151</t>
   </si>
   <si>
+    <t>01.3.1 - General personnel services (CS)</t>
+  </si>
+  <si>
+    <t>01.3 - General services</t>
+  </si>
+  <si>
     <t>01 - General public services</t>
   </si>
   <si>
-    <t>01.3 - General services</t>
-  </si>
-  <si>
     <t>150</t>
   </si>
   <si>
-    <t>01.3.1 - General personnel services (CS)</t>
-  </si>
-  <si>
     <t>15111</t>
   </si>
   <si>
+    <t>01.1.2 - Financial and fiscal affairs (CS)</t>
+  </si>
+  <si>
     <t>01.1 - Executive and legislative organs, financial and fiscal affairs, external affairs</t>
   </si>
   <si>
-    <t>01.1.2 - Financial and fiscal affairs (CS)</t>
-  </si>
-  <si>
     <t>15112</t>
   </si>
   <si>
+    <t>01.8.0 - Transfers of a general character between different levels of government (CS)</t>
+  </si>
+  <si>
     <t>01.8 - Transfers of a general character between different levels of government</t>
   </si>
   <si>
-    <t>01.8.0 - Transfers of a general character between different levels of government (CS)</t>
-  </si>
-  <si>
     <t>15113</t>
   </si>
   <si>
+    <t>03.6.0 - Public order and safety n.e.c. (CS)</t>
+  </si>
+  <si>
+    <t>03.6 - Public order and safety n.e.c.</t>
+  </si>
+  <si>
     <t>03 - Public order and safety</t>
   </si>
   <si>
-    <t>03.6 - Public order and safety n.e.c.</t>
-  </si>
-  <si>
-    <t>03.6.0 - Public order and safety n.e.c. (CS)</t>
-  </si>
-  <si>
     <t>15114</t>
   </si>
   <si>
@@ -424,12 +424,12 @@
     <t>15123</t>
   </si>
   <si>
+    <t>01.2.2 - Economic aid routed through international organizations (CS)</t>
+  </si>
+  <si>
     <t>01.2 - Foreign economic aid</t>
   </si>
   <si>
-    <t>01.2.2 - Economic aid routed through international organizations (CS)</t>
-  </si>
-  <si>
     <t>15124</t>
   </si>
   <si>
@@ -460,30 +460,30 @@
     <t>15131</t>
   </si>
   <si>
+    <t>03.3.0 - Law courts (CS)</t>
+  </si>
+  <si>
     <t>03.3 - Law courts</t>
   </si>
   <si>
-    <t>03.3.0 - Law courts (CS)</t>
-  </si>
-  <si>
     <t>15132</t>
   </si>
   <si>
+    <t>03.1.0 - Police services (CS)</t>
+  </si>
+  <si>
     <t>03.1 - Police services</t>
   </si>
   <si>
-    <t>03.1.0 - Police services (CS)</t>
-  </si>
-  <si>
     <t>15133</t>
   </si>
   <si>
+    <t>03.2.0 - Fire‐protection services (CS)</t>
+  </si>
+  <si>
     <t>03.2 - Fire‐protection services</t>
   </si>
   <si>
-    <t>03.2.0 - Fire‐protection services (CS)</t>
-  </si>
-  <si>
     <t>15134</t>
   </si>
   <si>
@@ -496,24 +496,24 @@
     <t>15137</t>
   </si>
   <si>
+    <t>03.4.0 - Prisons (CS)</t>
+  </si>
+  <si>
     <t>03.4 - Prisons</t>
   </si>
   <si>
-    <t>03.4.0 - Prisons (CS)</t>
-  </si>
-  <si>
     <t>15142</t>
   </si>
   <si>
+    <t>04.1.1 - General economic and commercial affairs (CS)</t>
+  </si>
+  <si>
+    <t>04.1 - General economic, commercial and labour affairs</t>
+  </si>
+  <si>
     <t>04 - Economic affairs</t>
   </si>
   <si>
-    <t>04.1 - General economic, commercial and labour affairs</t>
-  </si>
-  <si>
-    <t>04.1.1 - General economic and commercial affairs (CS)</t>
-  </si>
-  <si>
     <t>15143</t>
   </si>
   <si>
@@ -526,12 +526,12 @@
     <t>15151</t>
   </si>
   <si>
+    <t>01.6.0 - General public services n.e.c. (CS)</t>
+  </si>
+  <si>
     <t>01.6 - General public services n.e.c.</t>
   </si>
   <si>
-    <t>01.6.0 - General public services n.e.c. (CS)</t>
-  </si>
-  <si>
     <t>15152</t>
   </si>
   <si>
@@ -541,12 +541,12 @@
     <t>15153</t>
   </si>
   <si>
+    <t>04.6.0 - Communication (CS)</t>
+  </si>
+  <si>
     <t>04.6 - Communication</t>
   </si>
   <si>
-    <t>04.6.0 - Communication (CS)</t>
-  </si>
-  <si>
     <t>15154</t>
   </si>
   <si>
@@ -562,15 +562,15 @@
     <t>15170</t>
   </si>
   <si>
+    <t>10.7.0 - Social exclusion n.e.c. (IS)</t>
+  </si>
+  <si>
+    <t>10.7 - Social exclusion n.e.c.</t>
+  </si>
+  <si>
     <t>10 - Social protection</t>
   </si>
   <si>
-    <t>10.7 - Social exclusion n.e.c.</t>
-  </si>
-  <si>
-    <t>10.7.0 - Social exclusion n.e.c. (IS)</t>
-  </si>
-  <si>
     <t>15180</t>
   </si>
   <si>
@@ -583,12 +583,12 @@
     <t>15196</t>
   </si>
   <si>
+    <t>01.5.0 - R&amp;D General public services (CS)</t>
+  </si>
+  <si>
     <t>01.5 - R&amp;D General public services</t>
   </si>
   <si>
-    <t>01.5.0 - R&amp;D General public services (CS)</t>
-  </si>
-  <si>
     <t>15210</t>
   </si>
   <si>
@@ -601,15 +601,15 @@
     <t>15230</t>
   </si>
   <si>
+    <t>02.3.0 - Foreign military aid (CS)</t>
+  </si>
+  <si>
+    <t>02.3 - Foreign military aid</t>
+  </si>
+  <si>
     <t>02 - Defence</t>
   </si>
   <si>
-    <t>02.3 - Foreign military aid</t>
-  </si>
-  <si>
-    <t>02.3.0 - Foreign military aid (CS)</t>
-  </si>
-  <si>
     <t>15240</t>
   </si>
   <si>
@@ -622,15 +622,15 @@
     <t>16010</t>
   </si>
   <si>
+    <t>10.9.0 - Social protection n.e.c. (CS)</t>
+  </si>
+  <si>
     <t>10.9 - Social protection n.e.c.</t>
   </si>
   <si>
     <t>160</t>
   </si>
   <si>
-    <t>10.9.0 - Social protection n.e.c. (CS)</t>
-  </si>
-  <si>
     <t>16011</t>
   </si>
   <si>
@@ -640,12 +640,12 @@
     <t>16013</t>
   </si>
   <si>
+    <t>10.2.0 - Old age (IS)</t>
+  </si>
+  <si>
     <t>10.2 - Old age</t>
   </si>
   <si>
-    <t>10.2.0 - Old age (IS)</t>
-  </si>
-  <si>
     <t>16014</t>
   </si>
   <si>
@@ -655,45 +655,45 @@
     <t>16020</t>
   </si>
   <si>
+    <t>10.5.0 - Unemployment (IS)</t>
+  </si>
+  <si>
     <t>10.5 - Unemployment</t>
   </si>
   <si>
-    <t>10.5.0 - Unemployment (IS)</t>
-  </si>
-  <si>
     <t>16030</t>
   </si>
   <si>
+    <t>06.6.0 - Housing and community amenities n.e.c. (CS)</t>
+  </si>
+  <si>
     <t>06.6 - Housing and community amenities n.e.c.</t>
   </si>
   <si>
-    <t>06.6.0 - Housing and community amenities n.e.c. (CS)</t>
-  </si>
-  <si>
     <t>16040</t>
   </si>
   <si>
+    <t>06.1.0 - Housing development (CS)</t>
+  </si>
+  <si>
     <t>06.1 - Housing development</t>
   </si>
   <si>
-    <t>06.1.0 - Housing development (CS)</t>
-  </si>
-  <si>
     <t>16050</t>
   </si>
   <si>
     <t>16061</t>
   </si>
   <si>
+    <t>08.2.0 - Cultural services (IS)</t>
+  </si>
+  <si>
+    <t>08.2 - Cultural services</t>
+  </si>
+  <si>
     <t>08 - Recreation, culture and religion</t>
   </si>
   <si>
-    <t>08.2 - Cultural services</t>
-  </si>
-  <si>
-    <t>08.2.0 - Cultural services (IS)</t>
-  </si>
-  <si>
     <t>16062</t>
   </si>
   <si>
@@ -706,12 +706,12 @@
     <t>16065</t>
   </si>
   <si>
+    <t>08.1.0 - Recreational and sporting services (IS)</t>
+  </si>
+  <si>
     <t>08.1 - Recreational and sporting services</t>
   </si>
   <si>
-    <t>08.1.0 - Recreational and sporting services (IS)</t>
-  </si>
-  <si>
     <t>16066</t>
   </si>
   <si>
@@ -742,12 +742,12 @@
     <t>21020</t>
   </si>
   <si>
+    <t>04.5.1 - Road transport (CS)</t>
+  </si>
+  <si>
     <t>04.5 - Transport</t>
   </si>
   <si>
-    <t>04.5.1 - Road transport (CS)</t>
-  </si>
-  <si>
     <t>21021</t>
   </si>
   <si>
@@ -781,12 +781,12 @@
     <t>21061</t>
   </si>
   <si>
+    <t>04.7.1 - Distributive trades, storage and warehousing (CS)</t>
+  </si>
+  <si>
     <t>04.7 - Other industries</t>
   </si>
   <si>
-    <t>04.7.1 - Distributive trades, storage and warehousing (CS)</t>
-  </si>
-  <si>
     <t>21081</t>
   </si>
   <si>
@@ -811,12 +811,12 @@
     <t>22030</t>
   </si>
   <si>
+    <t>08.3.0 - Broadcasting and publishing services (CS)</t>
+  </si>
+  <si>
     <t>08.3 - Broadcasting and publishing services</t>
   </si>
   <si>
-    <t>08.3.0 - Broadcasting and publishing services (CS)</t>
-  </si>
-  <si>
     <t>22040</t>
   </si>
   <si>
@@ -826,27 +826,27 @@
     <t>231</t>
   </si>
   <si>
+    <t>04.3.5 - Electricity (CS)</t>
+  </si>
+  <si>
     <t>04.3 - Fuel and energy</t>
   </si>
   <si>
     <t>230</t>
   </si>
   <si>
-    <t>04.3.5 - Electricity (CS)</t>
-  </si>
-  <si>
     <t>23111</t>
   </si>
   <si>
     <t>23112</t>
   </si>
   <si>
+    <t>04.8.3 - R&amp;D Fuel and energy (CS)</t>
+  </si>
+  <si>
     <t>04.8 - R&amp;D Economic affairs</t>
   </si>
   <si>
-    <t>04.8.3 - R&amp;D Fuel and energy (CS)</t>
-  </si>
-  <si>
     <t>23181</t>
   </si>
   <si>
@@ -994,15 +994,15 @@
     <t>311</t>
   </si>
   <si>
+    <t>04.2.1 - Agriculture (CS)</t>
+  </si>
+  <si>
     <t>04.2 - Agriculture, forestry, fishing and hunting</t>
   </si>
   <si>
     <t>310</t>
   </si>
   <si>
-    <t>04.2.1 - Agriculture (CS)</t>
-  </si>
-  <si>
     <t>31120</t>
   </si>
   <si>
@@ -1108,15 +1108,15 @@
     <t>321</t>
   </si>
   <si>
+    <t>04.4.2 - Manufacturing (CS)</t>
+  </si>
+  <si>
     <t>04.4 - Mining, manufacturing and construction</t>
   </si>
   <si>
     <t>320</t>
   </si>
   <si>
-    <t>04.4.2 - Manufacturing (CS)</t>
-  </si>
-  <si>
     <t>32120</t>
   </si>
   <si>
@@ -1261,12 +1261,12 @@
     <t>41030</t>
   </si>
   <si>
+    <t>05.4.0 - Protection of biodiversity and landscape (CS)</t>
+  </si>
+  <si>
     <t>05.4 - Protection of biodiversity and landscape</t>
   </si>
   <si>
-    <t>05.4.0 - Protection of biodiversity and landscape (CS)</t>
-  </si>
-  <si>
     <t>41040</t>
   </si>
   <si>
@@ -1279,27 +1279,27 @@
     <t>43010</t>
   </si>
   <si>
+    <t>04.9.0 - Economic affairs n.e.c. (CS)</t>
+  </si>
+  <si>
     <t>04.9 - Economic affairs n.e.c.</t>
   </si>
   <si>
     <t>430</t>
   </si>
   <si>
-    <t>04.9.0 - Economic affairs n.e.c. (CS)</t>
-  </si>
-  <si>
     <t>43030</t>
   </si>
   <si>
     <t>43031</t>
   </si>
   <si>
+    <t>06.2.0 - Community development (CS)</t>
+  </si>
+  <si>
     <t>06.2 - Community development</t>
   </si>
   <si>
-    <t>06.2.0 - Community development (CS)</t>
-  </si>
-  <si>
     <t>43032</t>
   </si>
   <si>
@@ -1318,24 +1318,24 @@
     <t>43060</t>
   </si>
   <si>
+    <t>02.2.0 - Civil defence (CS)</t>
+  </si>
+  <si>
     <t>02.2 - Civil defence</t>
   </si>
   <si>
-    <t>02.2.0 - Civil defence (CS)</t>
-  </si>
-  <si>
     <t>43071</t>
   </si>
   <si>
     <t>43072</t>
   </si>
   <si>
+    <t>10.4.0 - Family and children (IS)</t>
+  </si>
+  <si>
     <t>10.4 - Family and children</t>
   </si>
   <si>
-    <t>10.4.0 - Family and children (IS)</t>
-  </si>
-  <si>
     <t>43073</t>
   </si>
   <si>
@@ -1345,12 +1345,12 @@
     <t>43082</t>
   </si>
   <si>
+    <t>01.4.0 - Basic research (CS)</t>
+  </si>
+  <si>
     <t>01.4 - Basic research</t>
   </si>
   <si>
-    <t>01.4.0 - Basic research (CS)</t>
-  </si>
-  <si>
     <t>51010</t>
   </si>
   <si>
@@ -1375,13 +1375,13 @@
     <t>60010</t>
   </si>
   <si>
+    <t>01.7.0 - Public debt transactions (CS)</t>
+  </si>
+  <si>
     <t>01.7 - Public debt transactions</t>
   </si>
   <si>
     <t>600</t>
-  </si>
-  <si>
-    <t>01.7.0 - Public debt transactions (CS)</t>
   </si>
   <si>
     <t>60020</t>
@@ -1866,16 +1866,16 @@
         <v>9</v>
       </c>
       <c r="D3" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="E3" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F3" t="s">
         <v>12</v>
       </c>
       <c r="G3" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -1912,16 +1912,16 @@
         <v>9</v>
       </c>
       <c r="D5" t="s">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="E5" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F5" t="s">
         <v>12</v>
       </c>
       <c r="G5" t="s">
-        <v>20</v>
+        <v>13</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -1935,16 +1935,16 @@
         <v>22</v>
       </c>
       <c r="D6" t="s">
-        <v>10</v>
+        <v>23</v>
       </c>
       <c r="E6" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F6" t="s">
         <v>12</v>
       </c>
       <c r="G6" t="s">
-        <v>24</v>
+        <v>13</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -1981,16 +1981,16 @@
         <v>22</v>
       </c>
       <c r="D8" t="s">
-        <v>10</v>
+        <v>23</v>
       </c>
       <c r="E8" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F8" t="s">
         <v>12</v>
       </c>
       <c r="G8" t="s">
-        <v>24</v>
+        <v>13</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -2004,16 +2004,16 @@
         <v>22</v>
       </c>
       <c r="D9" t="s">
-        <v>10</v>
+        <v>23</v>
       </c>
       <c r="E9" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F9" t="s">
         <v>12</v>
       </c>
       <c r="G9" t="s">
-        <v>24</v>
+        <v>13</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -2027,16 +2027,16 @@
         <v>22</v>
       </c>
       <c r="D10" t="s">
-        <v>10</v>
+        <v>29</v>
       </c>
       <c r="E10" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F10" t="s">
         <v>12</v>
       </c>
       <c r="G10" t="s">
-        <v>29</v>
+        <v>13</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -2056,10 +2056,10 @@
         <v>32</v>
       </c>
       <c r="F11" t="s">
-        <v>12</v>
+        <v>33</v>
       </c>
       <c r="G11" t="s">
-        <v>33</v>
+        <v>13</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -2073,16 +2073,16 @@
         <v>22</v>
       </c>
       <c r="D12" t="s">
-        <v>10</v>
+        <v>35</v>
       </c>
       <c r="E12" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F12" t="s">
         <v>12</v>
       </c>
       <c r="G12" t="s">
-        <v>36</v>
+        <v>13</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -2096,16 +2096,16 @@
         <v>38</v>
       </c>
       <c r="D13" t="s">
-        <v>10</v>
+        <v>39</v>
       </c>
       <c r="E13" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F13" t="s">
         <v>12</v>
       </c>
       <c r="G13" t="s">
-        <v>39</v>
+        <v>13</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -2119,16 +2119,16 @@
         <v>38</v>
       </c>
       <c r="D14" t="s">
-        <v>10</v>
+        <v>41</v>
       </c>
       <c r="E14" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F14" t="s">
         <v>12</v>
       </c>
       <c r="G14" t="s">
-        <v>42</v>
+        <v>13</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -2142,16 +2142,16 @@
         <v>44</v>
       </c>
       <c r="D15" t="s">
-        <v>10</v>
+        <v>45</v>
       </c>
       <c r="E15" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F15" t="s">
         <v>12</v>
       </c>
       <c r="G15" t="s">
-        <v>46</v>
+        <v>13</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -2165,16 +2165,16 @@
         <v>44</v>
       </c>
       <c r="D16" t="s">
-        <v>10</v>
+        <v>48</v>
       </c>
       <c r="E16" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F16" t="s">
         <v>12</v>
       </c>
       <c r="G16" t="s">
-        <v>49</v>
+        <v>13</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -2188,13 +2188,13 @@
         <v>51</v>
       </c>
       <c r="D17" t="s">
-        <v>31</v>
+        <v>52</v>
       </c>
       <c r="E17" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F17" t="s">
-        <v>53</v>
+        <v>33</v>
       </c>
       <c r="G17" t="s">
         <v>54</v>
@@ -2211,13 +2211,13 @@
         <v>51</v>
       </c>
       <c r="D18" t="s">
-        <v>31</v>
+        <v>52</v>
       </c>
       <c r="E18" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F18" t="s">
-        <v>53</v>
+        <v>33</v>
       </c>
       <c r="G18" t="s">
         <v>54</v>
@@ -2234,16 +2234,16 @@
         <v>51</v>
       </c>
       <c r="D19" t="s">
-        <v>31</v>
+        <v>57</v>
       </c>
       <c r="E19" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="F19" t="s">
-        <v>53</v>
+        <v>33</v>
       </c>
       <c r="G19" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -2257,16 +2257,16 @@
         <v>51</v>
       </c>
       <c r="D20" t="s">
-        <v>31</v>
+        <v>60</v>
       </c>
       <c r="E20" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F20" t="s">
-        <v>53</v>
+        <v>33</v>
       </c>
       <c r="G20" t="s">
-        <v>61</v>
+        <v>54</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -2280,13 +2280,13 @@
         <v>51</v>
       </c>
       <c r="D21" t="s">
-        <v>31</v>
+        <v>52</v>
       </c>
       <c r="E21" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F21" t="s">
-        <v>53</v>
+        <v>33</v>
       </c>
       <c r="G21" t="s">
         <v>54</v>
@@ -2309,10 +2309,10 @@
         <v>32</v>
       </c>
       <c r="F22" t="s">
-        <v>53</v>
+        <v>33</v>
       </c>
       <c r="G22" t="s">
-        <v>33</v>
+        <v>54</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -2326,16 +2326,16 @@
         <v>64</v>
       </c>
       <c r="D23" t="s">
-        <v>31</v>
+        <v>66</v>
       </c>
       <c r="E23" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="F23" t="s">
-        <v>53</v>
+        <v>33</v>
       </c>
       <c r="G23" t="s">
-        <v>67</v>
+        <v>54</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -2355,10 +2355,10 @@
         <v>32</v>
       </c>
       <c r="F24" t="s">
-        <v>53</v>
+        <v>33</v>
       </c>
       <c r="G24" t="s">
-        <v>33</v>
+        <v>54</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -2378,10 +2378,10 @@
         <v>32</v>
       </c>
       <c r="F25" t="s">
-        <v>53</v>
+        <v>33</v>
       </c>
       <c r="G25" t="s">
-        <v>33</v>
+        <v>54</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -2401,10 +2401,10 @@
         <v>32</v>
       </c>
       <c r="F26" t="s">
-        <v>53</v>
+        <v>33</v>
       </c>
       <c r="G26" t="s">
-        <v>33</v>
+        <v>54</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -2424,10 +2424,10 @@
         <v>32</v>
       </c>
       <c r="F27" t="s">
-        <v>53</v>
+        <v>33</v>
       </c>
       <c r="G27" t="s">
-        <v>33</v>
+        <v>54</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -2447,10 +2447,10 @@
         <v>32</v>
       </c>
       <c r="F28" t="s">
-        <v>53</v>
+        <v>33</v>
       </c>
       <c r="G28" t="s">
-        <v>33</v>
+        <v>54</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -2470,10 +2470,10 @@
         <v>32</v>
       </c>
       <c r="F29" t="s">
-        <v>53</v>
+        <v>33</v>
       </c>
       <c r="G29" t="s">
-        <v>33</v>
+        <v>54</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -2487,13 +2487,13 @@
         <v>64</v>
       </c>
       <c r="D30" t="s">
-        <v>31</v>
+        <v>52</v>
       </c>
       <c r="E30" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F30" t="s">
-        <v>53</v>
+        <v>33</v>
       </c>
       <c r="G30" t="s">
         <v>54</v>
@@ -2516,10 +2516,10 @@
         <v>32</v>
       </c>
       <c r="F31" t="s">
-        <v>53</v>
+        <v>33</v>
       </c>
       <c r="G31" t="s">
-        <v>33</v>
+        <v>54</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -2539,10 +2539,10 @@
         <v>32</v>
       </c>
       <c r="F32" t="s">
-        <v>53</v>
+        <v>33</v>
       </c>
       <c r="G32" t="s">
-        <v>33</v>
+        <v>54</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -2562,10 +2562,10 @@
         <v>32</v>
       </c>
       <c r="F33" t="s">
-        <v>53</v>
+        <v>33</v>
       </c>
       <c r="G33" t="s">
-        <v>33</v>
+        <v>54</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -2585,10 +2585,10 @@
         <v>32</v>
       </c>
       <c r="F34" t="s">
-        <v>53</v>
+        <v>33</v>
       </c>
       <c r="G34" t="s">
-        <v>33</v>
+        <v>54</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -2608,10 +2608,10 @@
         <v>32</v>
       </c>
       <c r="F35" t="s">
-        <v>53</v>
+        <v>33</v>
       </c>
       <c r="G35" t="s">
-        <v>33</v>
+        <v>54</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -2625,16 +2625,16 @@
         <v>76</v>
       </c>
       <c r="D36" t="s">
-        <v>31</v>
+        <v>57</v>
       </c>
       <c r="E36" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="F36" t="s">
-        <v>53</v>
+        <v>33</v>
       </c>
       <c r="G36" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -2651,10 +2651,10 @@
         <v>32</v>
       </c>
       <c r="F37" t="s">
+        <v>33</v>
+      </c>
+      <c r="G37" t="s">
         <v>83</v>
-      </c>
-      <c r="G37" t="s">
-        <v>33</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -2671,10 +2671,10 @@
         <v>32</v>
       </c>
       <c r="F38" t="s">
+        <v>33</v>
+      </c>
+      <c r="G38" t="s">
         <v>83</v>
-      </c>
-      <c r="G38" t="s">
-        <v>33</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -2691,10 +2691,10 @@
         <v>32</v>
       </c>
       <c r="F39" t="s">
+        <v>33</v>
+      </c>
+      <c r="G39" t="s">
         <v>83</v>
-      </c>
-      <c r="G39" t="s">
-        <v>33</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -2711,10 +2711,10 @@
         <v>32</v>
       </c>
       <c r="F40" t="s">
+        <v>33</v>
+      </c>
+      <c r="G40" t="s">
         <v>83</v>
-      </c>
-      <c r="G40" t="s">
-        <v>33</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -2725,16 +2725,16 @@
         <v>8</v>
       </c>
       <c r="D41" t="s">
-        <v>31</v>
+        <v>52</v>
       </c>
       <c r="E41" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F41" t="s">
+        <v>33</v>
+      </c>
+      <c r="G41" t="s">
         <v>83</v>
-      </c>
-      <c r="G41" t="s">
-        <v>54</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -2745,16 +2745,16 @@
         <v>8</v>
       </c>
       <c r="D42" t="s">
-        <v>31</v>
+        <v>57</v>
       </c>
       <c r="E42" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="F42" t="s">
+        <v>33</v>
+      </c>
+      <c r="G42" t="s">
         <v>83</v>
-      </c>
-      <c r="G42" t="s">
-        <v>58</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -2791,10 +2791,10 @@
         <v>96</v>
       </c>
       <c r="F44" t="s">
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="G44" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -2845,16 +2845,16 @@
         <v>8</v>
       </c>
       <c r="D47" t="s">
-        <v>95</v>
+        <v>101</v>
       </c>
       <c r="E47" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="F47" t="s">
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="G47" t="s">
-        <v>102</v>
+        <v>93</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -2905,16 +2905,16 @@
         <v>8</v>
       </c>
       <c r="D50" t="s">
-        <v>95</v>
+        <v>101</v>
       </c>
       <c r="E50" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="F50" t="s">
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="G50" t="s">
-        <v>102</v>
+        <v>93</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -2945,16 +2945,16 @@
         <v>8</v>
       </c>
       <c r="D52" t="s">
-        <v>95</v>
+        <v>108</v>
       </c>
       <c r="E52" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="F52" t="s">
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="G52" t="s">
-        <v>109</v>
+        <v>93</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -2971,10 +2971,10 @@
         <v>11</v>
       </c>
       <c r="F53" t="s">
-        <v>92</v>
+        <v>12</v>
       </c>
       <c r="G53" t="s">
-        <v>13</v>
+        <v>93</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -3011,16 +3011,16 @@
         <v>112</v>
       </c>
       <c r="D55" t="s">
-        <v>113</v>
+        <v>118</v>
       </c>
       <c r="E55" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="F55" t="s">
         <v>115</v>
       </c>
       <c r="G55" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -3034,16 +3034,16 @@
         <v>112</v>
       </c>
       <c r="D56" t="s">
-        <v>113</v>
+        <v>121</v>
       </c>
       <c r="E56" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="F56" t="s">
         <v>115</v>
       </c>
       <c r="G56" t="s">
-        <v>122</v>
+        <v>116</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -3063,10 +3063,10 @@
         <v>125</v>
       </c>
       <c r="F57" t="s">
-        <v>115</v>
+        <v>126</v>
       </c>
       <c r="G57" t="s">
-        <v>126</v>
+        <v>116</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -3080,16 +3080,16 @@
         <v>112</v>
       </c>
       <c r="D58" t="s">
-        <v>113</v>
+        <v>118</v>
       </c>
       <c r="E58" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="F58" t="s">
         <v>115</v>
       </c>
       <c r="G58" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -3103,16 +3103,16 @@
         <v>112</v>
       </c>
       <c r="D59" t="s">
-        <v>113</v>
+        <v>118</v>
       </c>
       <c r="E59" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="F59" t="s">
         <v>115</v>
       </c>
       <c r="G59" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -3126,16 +3126,16 @@
         <v>112</v>
       </c>
       <c r="D60" t="s">
-        <v>113</v>
+        <v>118</v>
       </c>
       <c r="E60" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="F60" t="s">
         <v>115</v>
       </c>
       <c r="G60" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -3149,16 +3149,16 @@
         <v>112</v>
       </c>
       <c r="D61" t="s">
-        <v>113</v>
+        <v>118</v>
       </c>
       <c r="E61" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="F61" t="s">
         <v>115</v>
       </c>
       <c r="G61" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -3172,16 +3172,16 @@
         <v>112</v>
       </c>
       <c r="D62" t="s">
-        <v>113</v>
+        <v>118</v>
       </c>
       <c r="E62" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="F62" t="s">
         <v>115</v>
       </c>
       <c r="G62" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -3195,16 +3195,16 @@
         <v>112</v>
       </c>
       <c r="D63" t="s">
-        <v>113</v>
+        <v>133</v>
       </c>
       <c r="E63" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="F63" t="s">
         <v>115</v>
       </c>
       <c r="G63" t="s">
-        <v>133</v>
+        <v>116</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -3218,16 +3218,16 @@
         <v>112</v>
       </c>
       <c r="D64" t="s">
-        <v>113</v>
+        <v>133</v>
       </c>
       <c r="E64" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="F64" t="s">
         <v>115</v>
       </c>
       <c r="G64" t="s">
-        <v>133</v>
+        <v>116</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -3241,16 +3241,16 @@
         <v>112</v>
       </c>
       <c r="D65" t="s">
-        <v>113</v>
+        <v>136</v>
       </c>
       <c r="E65" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="F65" t="s">
         <v>115</v>
       </c>
       <c r="G65" t="s">
-        <v>137</v>
+        <v>116</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -3287,16 +3287,16 @@
         <v>112</v>
       </c>
       <c r="D67" t="s">
-        <v>113</v>
+        <v>118</v>
       </c>
       <c r="E67" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="F67" t="s">
         <v>115</v>
       </c>
       <c r="G67" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -3310,7 +3310,7 @@
         <v>112</v>
       </c>
       <c r="D68" t="s">
-        <v>113</v>
+        <v>141</v>
       </c>
       <c r="E68" t="s">
         <v>114</v>
@@ -3319,7 +3319,7 @@
         <v>115</v>
       </c>
       <c r="G68" t="s">
-        <v>141</v>
+        <v>116</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -3333,7 +3333,7 @@
         <v>112</v>
       </c>
       <c r="D69" t="s">
-        <v>113</v>
+        <v>143</v>
       </c>
       <c r="E69" t="s">
         <v>114</v>
@@ -3342,7 +3342,7 @@
         <v>115</v>
       </c>
       <c r="G69" t="s">
-        <v>143</v>
+        <v>116</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -3356,16 +3356,16 @@
         <v>112</v>
       </c>
       <c r="D70" t="s">
-        <v>113</v>
+        <v>121</v>
       </c>
       <c r="E70" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="F70" t="s">
         <v>115</v>
       </c>
       <c r="G70" t="s">
-        <v>122</v>
+        <v>116</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -3379,16 +3379,16 @@
         <v>112</v>
       </c>
       <c r="D71" t="s">
-        <v>113</v>
+        <v>121</v>
       </c>
       <c r="E71" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="F71" t="s">
         <v>115</v>
       </c>
       <c r="G71" t="s">
-        <v>122</v>
+        <v>116</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -3425,16 +3425,16 @@
         <v>112</v>
       </c>
       <c r="D73" t="s">
-        <v>124</v>
+        <v>148</v>
       </c>
       <c r="E73" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="F73" t="s">
-        <v>115</v>
+        <v>126</v>
       </c>
       <c r="G73" t="s">
-        <v>149</v>
+        <v>116</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -3448,16 +3448,16 @@
         <v>112</v>
       </c>
       <c r="D74" t="s">
-        <v>124</v>
+        <v>151</v>
       </c>
       <c r="E74" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="F74" t="s">
-        <v>115</v>
+        <v>126</v>
       </c>
       <c r="G74" t="s">
-        <v>152</v>
+        <v>116</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -3471,16 +3471,16 @@
         <v>112</v>
       </c>
       <c r="D75" t="s">
-        <v>124</v>
+        <v>154</v>
       </c>
       <c r="E75" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="F75" t="s">
-        <v>115</v>
+        <v>126</v>
       </c>
       <c r="G75" t="s">
-        <v>155</v>
+        <v>116</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -3494,16 +3494,16 @@
         <v>112</v>
       </c>
       <c r="D76" t="s">
-        <v>124</v>
+        <v>148</v>
       </c>
       <c r="E76" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="F76" t="s">
-        <v>115</v>
+        <v>126</v>
       </c>
       <c r="G76" t="s">
-        <v>149</v>
+        <v>116</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -3517,16 +3517,16 @@
         <v>112</v>
       </c>
       <c r="D77" t="s">
-        <v>124</v>
+        <v>148</v>
       </c>
       <c r="E77" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="F77" t="s">
-        <v>115</v>
+        <v>126</v>
       </c>
       <c r="G77" t="s">
-        <v>149</v>
+        <v>116</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -3540,16 +3540,16 @@
         <v>112</v>
       </c>
       <c r="D78" t="s">
-        <v>124</v>
+        <v>151</v>
       </c>
       <c r="E78" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="F78" t="s">
-        <v>115</v>
+        <v>126</v>
       </c>
       <c r="G78" t="s">
-        <v>152</v>
+        <v>116</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -3563,16 +3563,16 @@
         <v>112</v>
       </c>
       <c r="D79" t="s">
-        <v>124</v>
+        <v>160</v>
       </c>
       <c r="E79" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="F79" t="s">
-        <v>115</v>
+        <v>126</v>
       </c>
       <c r="G79" t="s">
-        <v>161</v>
+        <v>116</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -3592,10 +3592,10 @@
         <v>164</v>
       </c>
       <c r="F80" t="s">
-        <v>115</v>
+        <v>165</v>
       </c>
       <c r="G80" t="s">
-        <v>165</v>
+        <v>116</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -3615,10 +3615,10 @@
         <v>164</v>
       </c>
       <c r="F81" t="s">
-        <v>115</v>
+        <v>165</v>
       </c>
       <c r="G81" t="s">
-        <v>165</v>
+        <v>116</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -3638,10 +3638,10 @@
         <v>164</v>
       </c>
       <c r="F82" t="s">
-        <v>115</v>
+        <v>165</v>
       </c>
       <c r="G82" t="s">
-        <v>165</v>
+        <v>116</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -3655,7 +3655,7 @@
         <v>112</v>
       </c>
       <c r="D83" t="s">
-        <v>113</v>
+        <v>143</v>
       </c>
       <c r="E83" t="s">
         <v>114</v>
@@ -3664,7 +3664,7 @@
         <v>115</v>
       </c>
       <c r="G83" t="s">
-        <v>143</v>
+        <v>116</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -3678,16 +3678,16 @@
         <v>112</v>
       </c>
       <c r="D84" t="s">
-        <v>113</v>
+        <v>170</v>
       </c>
       <c r="E84" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F84" t="s">
         <v>115</v>
       </c>
       <c r="G84" t="s">
-        <v>171</v>
+        <v>116</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -3701,16 +3701,16 @@
         <v>112</v>
       </c>
       <c r="D85" t="s">
-        <v>113</v>
+        <v>173</v>
       </c>
       <c r="E85" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="F85" t="s">
         <v>115</v>
       </c>
       <c r="G85" t="s">
-        <v>173</v>
+        <v>116</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -3724,16 +3724,16 @@
         <v>112</v>
       </c>
       <c r="D86" t="s">
-        <v>163</v>
+        <v>175</v>
       </c>
       <c r="E86" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="F86" t="s">
-        <v>115</v>
+        <v>165</v>
       </c>
       <c r="G86" t="s">
-        <v>176</v>
+        <v>116</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -3747,16 +3747,16 @@
         <v>112</v>
       </c>
       <c r="D87" t="s">
-        <v>113</v>
+        <v>173</v>
       </c>
       <c r="E87" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="F87" t="s">
         <v>115</v>
       </c>
       <c r="G87" t="s">
-        <v>173</v>
+        <v>116</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -3770,16 +3770,16 @@
         <v>112</v>
       </c>
       <c r="D88" t="s">
-        <v>113</v>
+        <v>118</v>
       </c>
       <c r="E88" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="F88" t="s">
         <v>115</v>
       </c>
       <c r="G88" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -3793,16 +3793,16 @@
         <v>112</v>
       </c>
       <c r="D89" t="s">
-        <v>113</v>
+        <v>118</v>
       </c>
       <c r="E89" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="F89" t="s">
         <v>115</v>
       </c>
       <c r="G89" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -3822,10 +3822,10 @@
         <v>125</v>
       </c>
       <c r="F90" t="s">
-        <v>115</v>
+        <v>126</v>
       </c>
       <c r="G90" t="s">
-        <v>126</v>
+        <v>116</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -3845,10 +3845,10 @@
         <v>183</v>
       </c>
       <c r="F91" t="s">
-        <v>115</v>
+        <v>184</v>
       </c>
       <c r="G91" t="s">
-        <v>184</v>
+        <v>116</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -3868,10 +3868,10 @@
         <v>125</v>
       </c>
       <c r="F92" t="s">
-        <v>115</v>
+        <v>126</v>
       </c>
       <c r="G92" t="s">
-        <v>126</v>
+        <v>116</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -3885,16 +3885,16 @@
         <v>112</v>
       </c>
       <c r="D93" t="s">
-        <v>113</v>
+        <v>121</v>
       </c>
       <c r="E93" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="F93" t="s">
         <v>115</v>
       </c>
       <c r="G93" t="s">
-        <v>122</v>
+        <v>116</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -3914,10 +3914,10 @@
         <v>125</v>
       </c>
       <c r="F94" t="s">
-        <v>115</v>
+        <v>126</v>
       </c>
       <c r="G94" t="s">
-        <v>126</v>
+        <v>116</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -3931,16 +3931,16 @@
         <v>112</v>
       </c>
       <c r="D95" t="s">
-        <v>113</v>
+        <v>189</v>
       </c>
       <c r="E95" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="F95" t="s">
         <v>115</v>
       </c>
       <c r="G95" t="s">
-        <v>190</v>
+        <v>116</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -3960,10 +3960,10 @@
         <v>125</v>
       </c>
       <c r="F96" t="s">
-        <v>115</v>
+        <v>126</v>
       </c>
       <c r="G96" t="s">
-        <v>126</v>
+        <v>116</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -3983,10 +3983,10 @@
         <v>125</v>
       </c>
       <c r="F97" t="s">
-        <v>115</v>
+        <v>126</v>
       </c>
       <c r="G97" t="s">
-        <v>126</v>
+        <v>116</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -4006,10 +4006,10 @@
         <v>196</v>
       </c>
       <c r="F98" t="s">
-        <v>115</v>
+        <v>197</v>
       </c>
       <c r="G98" t="s">
-        <v>197</v>
+        <v>116</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -4029,10 +4029,10 @@
         <v>125</v>
       </c>
       <c r="F99" t="s">
-        <v>115</v>
+        <v>126</v>
       </c>
       <c r="G99" t="s">
-        <v>126</v>
+        <v>116</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -4046,16 +4046,16 @@
         <v>192</v>
       </c>
       <c r="D100" t="s">
-        <v>124</v>
+        <v>154</v>
       </c>
       <c r="E100" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="F100" t="s">
-        <v>115</v>
+        <v>126</v>
       </c>
       <c r="G100" t="s">
-        <v>155</v>
+        <v>116</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -4075,10 +4075,10 @@
         <v>125</v>
       </c>
       <c r="F101" t="s">
-        <v>115</v>
+        <v>126</v>
       </c>
       <c r="G101" t="s">
-        <v>126</v>
+        <v>116</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -4089,13 +4089,13 @@
         <v>8</v>
       </c>
       <c r="D102" t="s">
-        <v>182</v>
+        <v>202</v>
       </c>
       <c r="E102" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="F102" t="s">
-        <v>203</v>
+        <v>184</v>
       </c>
       <c r="G102" t="s">
         <v>204</v>
@@ -4109,13 +4109,13 @@
         <v>8</v>
       </c>
       <c r="D103" t="s">
-        <v>182</v>
+        <v>202</v>
       </c>
       <c r="E103" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="F103" t="s">
-        <v>203</v>
+        <v>184</v>
       </c>
       <c r="G103" t="s">
         <v>204</v>
@@ -4129,13 +4129,13 @@
         <v>8</v>
       </c>
       <c r="D104" t="s">
-        <v>182</v>
+        <v>202</v>
       </c>
       <c r="E104" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="F104" t="s">
-        <v>203</v>
+        <v>184</v>
       </c>
       <c r="G104" t="s">
         <v>204</v>
@@ -4149,16 +4149,16 @@
         <v>8</v>
       </c>
       <c r="D105" t="s">
-        <v>182</v>
+        <v>208</v>
       </c>
       <c r="E105" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="F105" t="s">
-        <v>203</v>
+        <v>184</v>
       </c>
       <c r="G105" t="s">
-        <v>209</v>
+        <v>204</v>
       </c>
     </row>
     <row r="106" spans="1:7">
@@ -4169,13 +4169,13 @@
         <v>8</v>
       </c>
       <c r="D106" t="s">
-        <v>182</v>
+        <v>202</v>
       </c>
       <c r="E106" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="F106" t="s">
-        <v>203</v>
+        <v>184</v>
       </c>
       <c r="G106" t="s">
         <v>204</v>
@@ -4195,10 +4195,10 @@
         <v>183</v>
       </c>
       <c r="F107" t="s">
-        <v>203</v>
+        <v>184</v>
       </c>
       <c r="G107" t="s">
-        <v>184</v>
+        <v>204</v>
       </c>
     </row>
     <row r="108" spans="1:7">
@@ -4209,16 +4209,16 @@
         <v>8</v>
       </c>
       <c r="D108" t="s">
-        <v>182</v>
+        <v>213</v>
       </c>
       <c r="E108" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="F108" t="s">
-        <v>203</v>
+        <v>184</v>
       </c>
       <c r="G108" t="s">
-        <v>214</v>
+        <v>204</v>
       </c>
     </row>
     <row r="109" spans="1:7">
@@ -4229,16 +4229,16 @@
         <v>8</v>
       </c>
       <c r="D109" t="s">
-        <v>90</v>
+        <v>216</v>
       </c>
       <c r="E109" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="F109" t="s">
-        <v>203</v>
+        <v>92</v>
       </c>
       <c r="G109" t="s">
-        <v>217</v>
+        <v>204</v>
       </c>
     </row>
     <row r="110" spans="1:7">
@@ -4249,16 +4249,16 @@
         <v>8</v>
       </c>
       <c r="D110" t="s">
-        <v>90</v>
+        <v>219</v>
       </c>
       <c r="E110" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="F110" t="s">
-        <v>203</v>
+        <v>92</v>
       </c>
       <c r="G110" t="s">
-        <v>220</v>
+        <v>204</v>
       </c>
     </row>
     <row r="111" spans="1:7">
@@ -4269,13 +4269,13 @@
         <v>8</v>
       </c>
       <c r="D111" t="s">
-        <v>182</v>
+        <v>202</v>
       </c>
       <c r="E111" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="F111" t="s">
-        <v>203</v>
+        <v>184</v>
       </c>
       <c r="G111" t="s">
         <v>204</v>
@@ -4295,10 +4295,10 @@
         <v>224</v>
       </c>
       <c r="F112" t="s">
-        <v>203</v>
+        <v>225</v>
       </c>
       <c r="G112" t="s">
-        <v>225</v>
+        <v>204</v>
       </c>
     </row>
     <row r="113" spans="1:7">
@@ -4309,16 +4309,16 @@
         <v>8</v>
       </c>
       <c r="D113" t="s">
-        <v>113</v>
+        <v>143</v>
       </c>
       <c r="E113" t="s">
         <v>114</v>
       </c>
       <c r="F113" t="s">
-        <v>203</v>
+        <v>115</v>
       </c>
       <c r="G113" t="s">
-        <v>143</v>
+        <v>204</v>
       </c>
     </row>
     <row r="114" spans="1:7">
@@ -4329,16 +4329,16 @@
         <v>8</v>
       </c>
       <c r="D114" t="s">
-        <v>124</v>
+        <v>151</v>
       </c>
       <c r="E114" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="F114" t="s">
-        <v>203</v>
+        <v>126</v>
       </c>
       <c r="G114" t="s">
-        <v>152</v>
+        <v>204</v>
       </c>
     </row>
     <row r="115" spans="1:7">
@@ -4355,10 +4355,10 @@
         <v>183</v>
       </c>
       <c r="F115" t="s">
-        <v>203</v>
+        <v>184</v>
       </c>
       <c r="G115" t="s">
-        <v>184</v>
+        <v>204</v>
       </c>
     </row>
     <row r="116" spans="1:7">
@@ -4369,16 +4369,16 @@
         <v>8</v>
       </c>
       <c r="D116" t="s">
-        <v>223</v>
+        <v>230</v>
       </c>
       <c r="E116" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="F116" t="s">
-        <v>203</v>
+        <v>225</v>
       </c>
       <c r="G116" t="s">
-        <v>231</v>
+        <v>204</v>
       </c>
     </row>
     <row r="117" spans="1:7">
@@ -4395,10 +4395,10 @@
         <v>224</v>
       </c>
       <c r="F117" t="s">
-        <v>203</v>
+        <v>225</v>
       </c>
       <c r="G117" t="s">
-        <v>225</v>
+        <v>204</v>
       </c>
     </row>
     <row r="118" spans="1:7">
@@ -4409,16 +4409,16 @@
         <v>8</v>
       </c>
       <c r="D118" t="s">
-        <v>163</v>
+        <v>234</v>
       </c>
       <c r="E118" t="s">
         <v>164</v>
       </c>
       <c r="F118" t="s">
-        <v>203</v>
+        <v>165</v>
       </c>
       <c r="G118" t="s">
-        <v>234</v>
+        <v>204</v>
       </c>
     </row>
     <row r="119" spans="1:7">
@@ -4435,10 +4435,10 @@
         <v>183</v>
       </c>
       <c r="F119" t="s">
-        <v>203</v>
+        <v>184</v>
       </c>
       <c r="G119" t="s">
-        <v>184</v>
+        <v>204</v>
       </c>
     </row>
     <row r="120" spans="1:7">
@@ -4449,16 +4449,16 @@
         <v>8</v>
       </c>
       <c r="D120" t="s">
-        <v>113</v>
+        <v>170</v>
       </c>
       <c r="E120" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F120" t="s">
+        <v>115</v>
+      </c>
+      <c r="G120" t="s">
         <v>237</v>
-      </c>
-      <c r="G120" t="s">
-        <v>171</v>
       </c>
     </row>
     <row r="121" spans="1:7">
@@ -4469,16 +4469,16 @@
         <v>8</v>
       </c>
       <c r="D121" t="s">
-        <v>113</v>
+        <v>143</v>
       </c>
       <c r="E121" t="s">
         <v>114</v>
       </c>
       <c r="F121" t="s">
+        <v>115</v>
+      </c>
+      <c r="G121" t="s">
         <v>237</v>
-      </c>
-      <c r="G121" t="s">
-        <v>143</v>
       </c>
     </row>
     <row r="122" spans="1:7">
@@ -4489,16 +4489,16 @@
         <v>8</v>
       </c>
       <c r="D122" t="s">
-        <v>113</v>
+        <v>170</v>
       </c>
       <c r="E122" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F122" t="s">
+        <v>115</v>
+      </c>
+      <c r="G122" t="s">
         <v>237</v>
-      </c>
-      <c r="G122" t="s">
-        <v>171</v>
       </c>
     </row>
     <row r="123" spans="1:7">
@@ -4509,16 +4509,16 @@
         <v>8</v>
       </c>
       <c r="D123" t="s">
-        <v>113</v>
+        <v>170</v>
       </c>
       <c r="E123" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F123" t="s">
+        <v>115</v>
+      </c>
+      <c r="G123" t="s">
         <v>237</v>
-      </c>
-      <c r="G123" t="s">
-        <v>171</v>
       </c>
     </row>
     <row r="124" spans="1:7">
@@ -4529,16 +4529,16 @@
         <v>8</v>
       </c>
       <c r="D124" t="s">
-        <v>163</v>
+        <v>242</v>
       </c>
       <c r="E124" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="F124" t="s">
+        <v>165</v>
+      </c>
+      <c r="G124" t="s">
         <v>237</v>
-      </c>
-      <c r="G124" t="s">
-        <v>243</v>
       </c>
     </row>
     <row r="125" spans="1:7">
@@ -4549,16 +4549,16 @@
         <v>8</v>
       </c>
       <c r="D125" t="s">
-        <v>163</v>
+        <v>242</v>
       </c>
       <c r="E125" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="F125" t="s">
+        <v>165</v>
+      </c>
+      <c r="G125" t="s">
         <v>237</v>
-      </c>
-      <c r="G125" t="s">
-        <v>243</v>
       </c>
     </row>
     <row r="126" spans="1:7">
@@ -4569,16 +4569,16 @@
         <v>8</v>
       </c>
       <c r="D126" t="s">
-        <v>163</v>
+        <v>242</v>
       </c>
       <c r="E126" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="F126" t="s">
+        <v>165</v>
+      </c>
+      <c r="G126" t="s">
         <v>237</v>
-      </c>
-      <c r="G126" t="s">
-        <v>243</v>
       </c>
     </row>
     <row r="127" spans="1:7">
@@ -4589,16 +4589,16 @@
         <v>8</v>
       </c>
       <c r="D127" t="s">
-        <v>163</v>
+        <v>242</v>
       </c>
       <c r="E127" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="F127" t="s">
+        <v>165</v>
+      </c>
+      <c r="G127" t="s">
         <v>237</v>
-      </c>
-      <c r="G127" t="s">
-        <v>243</v>
       </c>
     </row>
     <row r="128" spans="1:7">
@@ -4609,16 +4609,16 @@
         <v>8</v>
       </c>
       <c r="D128" t="s">
-        <v>163</v>
+        <v>242</v>
       </c>
       <c r="E128" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="F128" t="s">
+        <v>165</v>
+      </c>
+      <c r="G128" t="s">
         <v>237</v>
-      </c>
-      <c r="G128" t="s">
-        <v>243</v>
       </c>
     </row>
     <row r="129" spans="1:7">
@@ -4629,16 +4629,16 @@
         <v>8</v>
       </c>
       <c r="D129" t="s">
-        <v>163</v>
+        <v>249</v>
       </c>
       <c r="E129" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="F129" t="s">
+        <v>165</v>
+      </c>
+      <c r="G129" t="s">
         <v>237</v>
-      </c>
-      <c r="G129" t="s">
-        <v>249</v>
       </c>
     </row>
     <row r="130" spans="1:7">
@@ -4649,16 +4649,16 @@
         <v>8</v>
       </c>
       <c r="D130" t="s">
-        <v>163</v>
+        <v>251</v>
       </c>
       <c r="E130" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="F130" t="s">
+        <v>165</v>
+      </c>
+      <c r="G130" t="s">
         <v>237</v>
-      </c>
-      <c r="G130" t="s">
-        <v>251</v>
       </c>
     </row>
     <row r="131" spans="1:7">
@@ -4669,16 +4669,16 @@
         <v>8</v>
       </c>
       <c r="D131" t="s">
-        <v>163</v>
+        <v>253</v>
       </c>
       <c r="E131" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="F131" t="s">
+        <v>165</v>
+      </c>
+      <c r="G131" t="s">
         <v>237</v>
-      </c>
-      <c r="G131" t="s">
-        <v>253</v>
       </c>
     </row>
     <row r="132" spans="1:7">
@@ -4689,16 +4689,16 @@
         <v>8</v>
       </c>
       <c r="D132" t="s">
-        <v>163</v>
+        <v>255</v>
       </c>
       <c r="E132" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="F132" t="s">
+        <v>165</v>
+      </c>
+      <c r="G132" t="s">
         <v>237</v>
-      </c>
-      <c r="G132" t="s">
-        <v>256</v>
       </c>
     </row>
     <row r="133" spans="1:7">
@@ -4709,16 +4709,16 @@
         <v>8</v>
       </c>
       <c r="D133" t="s">
-        <v>113</v>
+        <v>189</v>
       </c>
       <c r="E133" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="F133" t="s">
+        <v>115</v>
+      </c>
+      <c r="G133" t="s">
         <v>237</v>
-      </c>
-      <c r="G133" t="s">
-        <v>190</v>
       </c>
     </row>
     <row r="134" spans="1:7">
@@ -4729,16 +4729,16 @@
         <v>8</v>
       </c>
       <c r="D134" t="s">
-        <v>163</v>
+        <v>175</v>
       </c>
       <c r="E134" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="F134" t="s">
+        <v>165</v>
+      </c>
+      <c r="G134" t="s">
         <v>259</v>
-      </c>
-      <c r="G134" t="s">
-        <v>176</v>
       </c>
     </row>
     <row r="135" spans="1:7">
@@ -4749,16 +4749,16 @@
         <v>8</v>
       </c>
       <c r="D135" t="s">
-        <v>163</v>
+        <v>175</v>
       </c>
       <c r="E135" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="F135" t="s">
+        <v>165</v>
+      </c>
+      <c r="G135" t="s">
         <v>259</v>
-      </c>
-      <c r="G135" t="s">
-        <v>176</v>
       </c>
     </row>
     <row r="136" spans="1:7">
@@ -4769,16 +4769,16 @@
         <v>8</v>
       </c>
       <c r="D136" t="s">
-        <v>163</v>
+        <v>175</v>
       </c>
       <c r="E136" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="F136" t="s">
+        <v>165</v>
+      </c>
+      <c r="G136" t="s">
         <v>259</v>
-      </c>
-      <c r="G136" t="s">
-        <v>176</v>
       </c>
     </row>
     <row r="137" spans="1:7">
@@ -4789,16 +4789,16 @@
         <v>8</v>
       </c>
       <c r="D137" t="s">
-        <v>163</v>
+        <v>175</v>
       </c>
       <c r="E137" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="F137" t="s">
+        <v>165</v>
+      </c>
+      <c r="G137" t="s">
         <v>259</v>
-      </c>
-      <c r="G137" t="s">
-        <v>176</v>
       </c>
     </row>
     <row r="138" spans="1:7">
@@ -4809,16 +4809,16 @@
         <v>8</v>
       </c>
       <c r="D138" t="s">
-        <v>163</v>
+        <v>175</v>
       </c>
       <c r="E138" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="F138" t="s">
+        <v>165</v>
+      </c>
+      <c r="G138" t="s">
         <v>259</v>
-      </c>
-      <c r="G138" t="s">
-        <v>176</v>
       </c>
     </row>
     <row r="139" spans="1:7">
@@ -4829,16 +4829,16 @@
         <v>8</v>
       </c>
       <c r="D139" t="s">
-        <v>223</v>
+        <v>265</v>
       </c>
       <c r="E139" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="F139" t="s">
+        <v>225</v>
+      </c>
+      <c r="G139" t="s">
         <v>259</v>
-      </c>
-      <c r="G139" t="s">
-        <v>266</v>
       </c>
     </row>
     <row r="140" spans="1:7">
@@ -4849,16 +4849,16 @@
         <v>8</v>
       </c>
       <c r="D140" t="s">
-        <v>163</v>
+        <v>175</v>
       </c>
       <c r="E140" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="F140" t="s">
+        <v>165</v>
+      </c>
+      <c r="G140" t="s">
         <v>259</v>
-      </c>
-      <c r="G140" t="s">
-        <v>176</v>
       </c>
     </row>
     <row r="141" spans="1:7">
@@ -4872,13 +4872,13 @@
         <v>269</v>
       </c>
       <c r="D141" t="s">
-        <v>163</v>
+        <v>270</v>
       </c>
       <c r="E141" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="F141" t="s">
-        <v>271</v>
+        <v>165</v>
       </c>
       <c r="G141" t="s">
         <v>272</v>
@@ -4895,13 +4895,13 @@
         <v>269</v>
       </c>
       <c r="D142" t="s">
-        <v>163</v>
+        <v>270</v>
       </c>
       <c r="E142" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="F142" t="s">
-        <v>271</v>
+        <v>165</v>
       </c>
       <c r="G142" t="s">
         <v>272</v>
@@ -4918,16 +4918,16 @@
         <v>269</v>
       </c>
       <c r="D143" t="s">
-        <v>163</v>
+        <v>275</v>
       </c>
       <c r="E143" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="F143" t="s">
-        <v>271</v>
+        <v>165</v>
       </c>
       <c r="G143" t="s">
-        <v>276</v>
+        <v>272</v>
       </c>
     </row>
     <row r="144" spans="1:7">
@@ -4941,16 +4941,16 @@
         <v>269</v>
       </c>
       <c r="D144" t="s">
-        <v>163</v>
+        <v>275</v>
       </c>
       <c r="E144" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="F144" t="s">
-        <v>271</v>
+        <v>165</v>
       </c>
       <c r="G144" t="s">
-        <v>276</v>
+        <v>272</v>
       </c>
     </row>
     <row r="145" spans="1:7">
@@ -4964,16 +4964,16 @@
         <v>269</v>
       </c>
       <c r="D145" t="s">
-        <v>163</v>
+        <v>275</v>
       </c>
       <c r="E145" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="F145" t="s">
-        <v>271</v>
+        <v>165</v>
       </c>
       <c r="G145" t="s">
-        <v>276</v>
+        <v>272</v>
       </c>
     </row>
     <row r="146" spans="1:7">
@@ -4987,13 +4987,13 @@
         <v>269</v>
       </c>
       <c r="D146" t="s">
-        <v>163</v>
+        <v>270</v>
       </c>
       <c r="E146" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="F146" t="s">
-        <v>271</v>
+        <v>165</v>
       </c>
       <c r="G146" t="s">
         <v>272</v>
@@ -5010,13 +5010,13 @@
         <v>281</v>
       </c>
       <c r="D147" t="s">
-        <v>163</v>
+        <v>270</v>
       </c>
       <c r="E147" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="F147" t="s">
-        <v>271</v>
+        <v>165</v>
       </c>
       <c r="G147" t="s">
         <v>272</v>
@@ -5033,13 +5033,13 @@
         <v>281</v>
       </c>
       <c r="D148" t="s">
-        <v>163</v>
+        <v>270</v>
       </c>
       <c r="E148" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="F148" t="s">
-        <v>271</v>
+        <v>165</v>
       </c>
       <c r="G148" t="s">
         <v>272</v>
@@ -5056,13 +5056,13 @@
         <v>281</v>
       </c>
       <c r="D149" t="s">
-        <v>163</v>
+        <v>270</v>
       </c>
       <c r="E149" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="F149" t="s">
-        <v>271</v>
+        <v>165</v>
       </c>
       <c r="G149" t="s">
         <v>272</v>
@@ -5079,13 +5079,13 @@
         <v>281</v>
       </c>
       <c r="D150" t="s">
-        <v>163</v>
+        <v>270</v>
       </c>
       <c r="E150" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="F150" t="s">
-        <v>271</v>
+        <v>165</v>
       </c>
       <c r="G150" t="s">
         <v>272</v>
@@ -5102,13 +5102,13 @@
         <v>281</v>
       </c>
       <c r="D151" t="s">
-        <v>163</v>
+        <v>270</v>
       </c>
       <c r="E151" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="F151" t="s">
-        <v>271</v>
+        <v>165</v>
       </c>
       <c r="G151" t="s">
         <v>272</v>
@@ -5125,13 +5125,13 @@
         <v>281</v>
       </c>
       <c r="D152" t="s">
-        <v>163</v>
+        <v>270</v>
       </c>
       <c r="E152" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="F152" t="s">
-        <v>271</v>
+        <v>165</v>
       </c>
       <c r="G152" t="s">
         <v>272</v>
@@ -5148,13 +5148,13 @@
         <v>281</v>
       </c>
       <c r="D153" t="s">
-        <v>163</v>
+        <v>270</v>
       </c>
       <c r="E153" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="F153" t="s">
-        <v>271</v>
+        <v>165</v>
       </c>
       <c r="G153" t="s">
         <v>272</v>
@@ -5171,13 +5171,13 @@
         <v>281</v>
       </c>
       <c r="D154" t="s">
-        <v>163</v>
+        <v>270</v>
       </c>
       <c r="E154" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="F154" t="s">
-        <v>271</v>
+        <v>165</v>
       </c>
       <c r="G154" t="s">
         <v>272</v>
@@ -5194,13 +5194,13 @@
         <v>281</v>
       </c>
       <c r="D155" t="s">
-        <v>163</v>
+        <v>270</v>
       </c>
       <c r="E155" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="F155" t="s">
-        <v>271</v>
+        <v>165</v>
       </c>
       <c r="G155" t="s">
         <v>272</v>
@@ -5217,13 +5217,13 @@
         <v>291</v>
       </c>
       <c r="D156" t="s">
-        <v>163</v>
+        <v>270</v>
       </c>
       <c r="E156" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="F156" t="s">
-        <v>271</v>
+        <v>165</v>
       </c>
       <c r="G156" t="s">
         <v>272</v>
@@ -5240,16 +5240,16 @@
         <v>291</v>
       </c>
       <c r="D157" t="s">
-        <v>163</v>
+        <v>293</v>
       </c>
       <c r="E157" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="F157" t="s">
-        <v>271</v>
+        <v>165</v>
       </c>
       <c r="G157" t="s">
-        <v>293</v>
+        <v>272</v>
       </c>
     </row>
     <row r="158" spans="1:7">
@@ -5263,13 +5263,13 @@
         <v>291</v>
       </c>
       <c r="D158" t="s">
-        <v>163</v>
+        <v>270</v>
       </c>
       <c r="E158" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="F158" t="s">
-        <v>271</v>
+        <v>165</v>
       </c>
       <c r="G158" t="s">
         <v>272</v>
@@ -5286,13 +5286,13 @@
         <v>291</v>
       </c>
       <c r="D159" t="s">
-        <v>163</v>
+        <v>270</v>
       </c>
       <c r="E159" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="F159" t="s">
-        <v>271</v>
+        <v>165</v>
       </c>
       <c r="G159" t="s">
         <v>272</v>
@@ -5309,13 +5309,13 @@
         <v>291</v>
       </c>
       <c r="D160" t="s">
-        <v>163</v>
+        <v>270</v>
       </c>
       <c r="E160" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="F160" t="s">
-        <v>271</v>
+        <v>165</v>
       </c>
       <c r="G160" t="s">
         <v>272</v>
@@ -5332,13 +5332,13 @@
         <v>291</v>
       </c>
       <c r="D161" t="s">
-        <v>163</v>
+        <v>270</v>
       </c>
       <c r="E161" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="F161" t="s">
-        <v>271</v>
+        <v>165</v>
       </c>
       <c r="G161" t="s">
         <v>272</v>
@@ -5355,13 +5355,13 @@
         <v>299</v>
       </c>
       <c r="D162" t="s">
-        <v>163</v>
+        <v>270</v>
       </c>
       <c r="E162" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="F162" t="s">
-        <v>271</v>
+        <v>165</v>
       </c>
       <c r="G162" t="s">
         <v>272</v>
@@ -5378,16 +5378,16 @@
         <v>301</v>
       </c>
       <c r="D163" t="s">
-        <v>163</v>
+        <v>302</v>
       </c>
       <c r="E163" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="F163" t="s">
-        <v>271</v>
+        <v>165</v>
       </c>
       <c r="G163" t="s">
-        <v>302</v>
+        <v>272</v>
       </c>
     </row>
     <row r="164" spans="1:7">
@@ -5401,13 +5401,13 @@
         <v>304</v>
       </c>
       <c r="D164" t="s">
-        <v>163</v>
+        <v>270</v>
       </c>
       <c r="E164" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="F164" t="s">
-        <v>271</v>
+        <v>165</v>
       </c>
       <c r="G164" t="s">
         <v>272</v>
@@ -5424,13 +5424,13 @@
         <v>304</v>
       </c>
       <c r="D165" t="s">
-        <v>163</v>
+        <v>270</v>
       </c>
       <c r="E165" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="F165" t="s">
-        <v>271</v>
+        <v>165</v>
       </c>
       <c r="G165" t="s">
         <v>272</v>
@@ -5447,13 +5447,13 @@
         <v>304</v>
       </c>
       <c r="D166" t="s">
-        <v>163</v>
+        <v>270</v>
       </c>
       <c r="E166" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="F166" t="s">
-        <v>271</v>
+        <v>165</v>
       </c>
       <c r="G166" t="s">
         <v>272</v>
@@ -5470,13 +5470,13 @@
         <v>304</v>
       </c>
       <c r="D167" t="s">
-        <v>163</v>
+        <v>270</v>
       </c>
       <c r="E167" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="F167" t="s">
-        <v>271</v>
+        <v>165</v>
       </c>
       <c r="G167" t="s">
         <v>272</v>
@@ -5493,16 +5493,16 @@
         <v>304</v>
       </c>
       <c r="D168" t="s">
-        <v>163</v>
+        <v>309</v>
       </c>
       <c r="E168" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="F168" t="s">
-        <v>271</v>
+        <v>165</v>
       </c>
       <c r="G168" t="s">
-        <v>309</v>
+        <v>272</v>
       </c>
     </row>
     <row r="169" spans="1:7">
@@ -5516,16 +5516,16 @@
         <v>304</v>
       </c>
       <c r="D169" t="s">
-        <v>163</v>
+        <v>309</v>
       </c>
       <c r="E169" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="F169" t="s">
-        <v>271</v>
+        <v>165</v>
       </c>
       <c r="G169" t="s">
-        <v>309</v>
+        <v>272</v>
       </c>
     </row>
     <row r="170" spans="1:7">
@@ -5539,13 +5539,13 @@
         <v>304</v>
       </c>
       <c r="D170" t="s">
-        <v>163</v>
+        <v>270</v>
       </c>
       <c r="E170" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="F170" t="s">
-        <v>271</v>
+        <v>165</v>
       </c>
       <c r="G170" t="s">
         <v>272</v>
@@ -5565,10 +5565,10 @@
         <v>164</v>
       </c>
       <c r="F171" t="s">
+        <v>165</v>
+      </c>
+      <c r="G171" t="s">
         <v>313</v>
-      </c>
-      <c r="G171" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="172" spans="1:7">
@@ -5579,16 +5579,16 @@
         <v>8</v>
       </c>
       <c r="D172" t="s">
-        <v>113</v>
+        <v>118</v>
       </c>
       <c r="E172" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="F172" t="s">
+        <v>115</v>
+      </c>
+      <c r="G172" t="s">
         <v>313</v>
-      </c>
-      <c r="G172" t="s">
-        <v>119</v>
       </c>
     </row>
     <row r="173" spans="1:7">
@@ -5605,10 +5605,10 @@
         <v>164</v>
       </c>
       <c r="F173" t="s">
+        <v>165</v>
+      </c>
+      <c r="G173" t="s">
         <v>313</v>
-      </c>
-      <c r="G173" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="174" spans="1:7">
@@ -5625,10 +5625,10 @@
         <v>164</v>
       </c>
       <c r="F174" t="s">
+        <v>165</v>
+      </c>
+      <c r="G174" t="s">
         <v>313</v>
-      </c>
-      <c r="G174" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="175" spans="1:7">
@@ -5645,10 +5645,10 @@
         <v>164</v>
       </c>
       <c r="F175" t="s">
+        <v>165</v>
+      </c>
+      <c r="G175" t="s">
         <v>313</v>
-      </c>
-      <c r="G175" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="176" spans="1:7">
@@ -5665,10 +5665,10 @@
         <v>164</v>
       </c>
       <c r="F176" t="s">
+        <v>165</v>
+      </c>
+      <c r="G176" t="s">
         <v>313</v>
-      </c>
-      <c r="G176" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="177" spans="1:7">
@@ -5685,10 +5685,10 @@
         <v>164</v>
       </c>
       <c r="F177" t="s">
+        <v>165</v>
+      </c>
+      <c r="G177" t="s">
         <v>320</v>
-      </c>
-      <c r="G177" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="178" spans="1:7">
@@ -5705,10 +5705,10 @@
         <v>164</v>
       </c>
       <c r="F178" t="s">
+        <v>165</v>
+      </c>
+      <c r="G178" t="s">
         <v>320</v>
-      </c>
-      <c r="G178" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="179" spans="1:7">
@@ -5725,10 +5725,10 @@
         <v>164</v>
       </c>
       <c r="F179" t="s">
+        <v>165</v>
+      </c>
+      <c r="G179" t="s">
         <v>320</v>
-      </c>
-      <c r="G179" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="180" spans="1:7">
@@ -5745,10 +5745,10 @@
         <v>164</v>
       </c>
       <c r="F180" t="s">
+        <v>165</v>
+      </c>
+      <c r="G180" t="s">
         <v>320</v>
-      </c>
-      <c r="G180" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="181" spans="1:7">
@@ -5762,13 +5762,13 @@
         <v>325</v>
       </c>
       <c r="D181" t="s">
-        <v>163</v>
+        <v>326</v>
       </c>
       <c r="E181" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="F181" t="s">
-        <v>327</v>
+        <v>165</v>
       </c>
       <c r="G181" t="s">
         <v>328</v>
@@ -5785,13 +5785,13 @@
         <v>325</v>
       </c>
       <c r="D182" t="s">
-        <v>163</v>
+        <v>326</v>
       </c>
       <c r="E182" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="F182" t="s">
-        <v>327</v>
+        <v>165</v>
       </c>
       <c r="G182" t="s">
         <v>328</v>
@@ -5808,13 +5808,13 @@
         <v>325</v>
       </c>
       <c r="D183" t="s">
-        <v>163</v>
+        <v>326</v>
       </c>
       <c r="E183" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="F183" t="s">
-        <v>327</v>
+        <v>165</v>
       </c>
       <c r="G183" t="s">
         <v>328</v>
@@ -5831,13 +5831,13 @@
         <v>325</v>
       </c>
       <c r="D184" t="s">
-        <v>163</v>
+        <v>326</v>
       </c>
       <c r="E184" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="F184" t="s">
-        <v>327</v>
+        <v>165</v>
       </c>
       <c r="G184" t="s">
         <v>328</v>
@@ -5854,13 +5854,13 @@
         <v>325</v>
       </c>
       <c r="D185" t="s">
-        <v>163</v>
+        <v>326</v>
       </c>
       <c r="E185" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="F185" t="s">
-        <v>327</v>
+        <v>165</v>
       </c>
       <c r="G185" t="s">
         <v>328</v>
@@ -5877,13 +5877,13 @@
         <v>325</v>
       </c>
       <c r="D186" t="s">
-        <v>163</v>
+        <v>326</v>
       </c>
       <c r="E186" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="F186" t="s">
-        <v>327</v>
+        <v>165</v>
       </c>
       <c r="G186" t="s">
         <v>328</v>
@@ -5900,13 +5900,13 @@
         <v>325</v>
       </c>
       <c r="D187" t="s">
-        <v>163</v>
+        <v>326</v>
       </c>
       <c r="E187" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="F187" t="s">
-        <v>327</v>
+        <v>165</v>
       </c>
       <c r="G187" t="s">
         <v>328</v>
@@ -5923,13 +5923,13 @@
         <v>325</v>
       </c>
       <c r="D188" t="s">
-        <v>163</v>
+        <v>326</v>
       </c>
       <c r="E188" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="F188" t="s">
-        <v>327</v>
+        <v>165</v>
       </c>
       <c r="G188" t="s">
         <v>328</v>
@@ -5946,13 +5946,13 @@
         <v>325</v>
       </c>
       <c r="D189" t="s">
-        <v>163</v>
+        <v>326</v>
       </c>
       <c r="E189" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="F189" t="s">
-        <v>327</v>
+        <v>165</v>
       </c>
       <c r="G189" t="s">
         <v>328</v>
@@ -5969,13 +5969,13 @@
         <v>325</v>
       </c>
       <c r="D190" t="s">
-        <v>163</v>
+        <v>326</v>
       </c>
       <c r="E190" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="F190" t="s">
-        <v>327</v>
+        <v>165</v>
       </c>
       <c r="G190" t="s">
         <v>328</v>
@@ -5992,13 +5992,13 @@
         <v>325</v>
       </c>
       <c r="D191" t="s">
-        <v>163</v>
+        <v>326</v>
       </c>
       <c r="E191" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="F191" t="s">
-        <v>327</v>
+        <v>165</v>
       </c>
       <c r="G191" t="s">
         <v>328</v>
@@ -6015,13 +6015,13 @@
         <v>325</v>
       </c>
       <c r="D192" t="s">
-        <v>163</v>
+        <v>326</v>
       </c>
       <c r="E192" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="F192" t="s">
-        <v>327</v>
+        <v>165</v>
       </c>
       <c r="G192" t="s">
         <v>328</v>
@@ -6038,16 +6038,16 @@
         <v>325</v>
       </c>
       <c r="D193" t="s">
-        <v>163</v>
+        <v>341</v>
       </c>
       <c r="E193" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="F193" t="s">
-        <v>327</v>
+        <v>165</v>
       </c>
       <c r="G193" t="s">
-        <v>341</v>
+        <v>328</v>
       </c>
     </row>
     <row r="194" spans="1:7">
@@ -6061,13 +6061,13 @@
         <v>325</v>
       </c>
       <c r="D194" t="s">
-        <v>163</v>
+        <v>326</v>
       </c>
       <c r="E194" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="F194" t="s">
-        <v>327</v>
+        <v>165</v>
       </c>
       <c r="G194" t="s">
         <v>328</v>
@@ -6084,13 +6084,13 @@
         <v>325</v>
       </c>
       <c r="D195" t="s">
-        <v>163</v>
+        <v>326</v>
       </c>
       <c r="E195" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="F195" t="s">
-        <v>327</v>
+        <v>165</v>
       </c>
       <c r="G195" t="s">
         <v>328</v>
@@ -6107,13 +6107,13 @@
         <v>325</v>
       </c>
       <c r="D196" t="s">
-        <v>163</v>
+        <v>326</v>
       </c>
       <c r="E196" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="F196" t="s">
-        <v>327</v>
+        <v>165</v>
       </c>
       <c r="G196" t="s">
         <v>328</v>
@@ -6130,13 +6130,13 @@
         <v>325</v>
       </c>
       <c r="D197" t="s">
-        <v>163</v>
+        <v>326</v>
       </c>
       <c r="E197" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="F197" t="s">
-        <v>327</v>
+        <v>165</v>
       </c>
       <c r="G197" t="s">
         <v>328</v>
@@ -6153,13 +6153,13 @@
         <v>325</v>
       </c>
       <c r="D198" t="s">
-        <v>163</v>
+        <v>326</v>
       </c>
       <c r="E198" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="F198" t="s">
-        <v>327</v>
+        <v>165</v>
       </c>
       <c r="G198" t="s">
         <v>328</v>
@@ -6176,16 +6176,16 @@
         <v>348</v>
       </c>
       <c r="D199" t="s">
-        <v>163</v>
+        <v>349</v>
       </c>
       <c r="E199" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="F199" t="s">
-        <v>327</v>
+        <v>165</v>
       </c>
       <c r="G199" t="s">
-        <v>349</v>
+        <v>328</v>
       </c>
     </row>
     <row r="200" spans="1:7">
@@ -6199,16 +6199,16 @@
         <v>348</v>
       </c>
       <c r="D200" t="s">
-        <v>163</v>
+        <v>349</v>
       </c>
       <c r="E200" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="F200" t="s">
-        <v>327</v>
+        <v>165</v>
       </c>
       <c r="G200" t="s">
-        <v>349</v>
+        <v>328</v>
       </c>
     </row>
     <row r="201" spans="1:7">
@@ -6222,16 +6222,16 @@
         <v>348</v>
       </c>
       <c r="D201" t="s">
-        <v>163</v>
+        <v>349</v>
       </c>
       <c r="E201" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="F201" t="s">
-        <v>327</v>
+        <v>165</v>
       </c>
       <c r="G201" t="s">
-        <v>349</v>
+        <v>328</v>
       </c>
     </row>
     <row r="202" spans="1:7">
@@ -6245,16 +6245,16 @@
         <v>348</v>
       </c>
       <c r="D202" t="s">
-        <v>163</v>
+        <v>349</v>
       </c>
       <c r="E202" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="F202" t="s">
-        <v>327</v>
+        <v>165</v>
       </c>
       <c r="G202" t="s">
-        <v>349</v>
+        <v>328</v>
       </c>
     </row>
     <row r="203" spans="1:7">
@@ -6268,16 +6268,16 @@
         <v>348</v>
       </c>
       <c r="D203" t="s">
-        <v>163</v>
+        <v>341</v>
       </c>
       <c r="E203" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="F203" t="s">
-        <v>327</v>
+        <v>165</v>
       </c>
       <c r="G203" t="s">
-        <v>341</v>
+        <v>328</v>
       </c>
     </row>
     <row r="204" spans="1:7">
@@ -6291,16 +6291,16 @@
         <v>348</v>
       </c>
       <c r="D204" t="s">
-        <v>163</v>
+        <v>349</v>
       </c>
       <c r="E204" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="F204" t="s">
-        <v>327</v>
+        <v>165</v>
       </c>
       <c r="G204" t="s">
-        <v>349</v>
+        <v>328</v>
       </c>
     </row>
     <row r="205" spans="1:7">
@@ -6314,16 +6314,16 @@
         <v>356</v>
       </c>
       <c r="D205" t="s">
-        <v>163</v>
+        <v>357</v>
       </c>
       <c r="E205" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="F205" t="s">
-        <v>327</v>
+        <v>165</v>
       </c>
       <c r="G205" t="s">
-        <v>357</v>
+        <v>328</v>
       </c>
     </row>
     <row r="206" spans="1:7">
@@ -6337,16 +6337,16 @@
         <v>356</v>
       </c>
       <c r="D206" t="s">
-        <v>163</v>
+        <v>357</v>
       </c>
       <c r="E206" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="F206" t="s">
-        <v>327</v>
+        <v>165</v>
       </c>
       <c r="G206" t="s">
-        <v>357</v>
+        <v>328</v>
       </c>
     </row>
     <row r="207" spans="1:7">
@@ -6360,16 +6360,16 @@
         <v>356</v>
       </c>
       <c r="D207" t="s">
-        <v>163</v>
+        <v>357</v>
       </c>
       <c r="E207" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="F207" t="s">
-        <v>327</v>
+        <v>165</v>
       </c>
       <c r="G207" t="s">
-        <v>357</v>
+        <v>328</v>
       </c>
     </row>
     <row r="208" spans="1:7">
@@ -6383,16 +6383,16 @@
         <v>356</v>
       </c>
       <c r="D208" t="s">
-        <v>163</v>
+        <v>341</v>
       </c>
       <c r="E208" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="F208" t="s">
-        <v>327</v>
+        <v>165</v>
       </c>
       <c r="G208" t="s">
-        <v>341</v>
+        <v>328</v>
       </c>
     </row>
     <row r="209" spans="1:7">
@@ -6406,16 +6406,16 @@
         <v>356</v>
       </c>
       <c r="D209" t="s">
-        <v>163</v>
+        <v>357</v>
       </c>
       <c r="E209" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="F209" t="s">
-        <v>327</v>
+        <v>165</v>
       </c>
       <c r="G209" t="s">
-        <v>357</v>
+        <v>328</v>
       </c>
     </row>
     <row r="210" spans="1:7">
@@ -6429,13 +6429,13 @@
         <v>363</v>
       </c>
       <c r="D210" t="s">
-        <v>163</v>
+        <v>364</v>
       </c>
       <c r="E210" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="F210" t="s">
-        <v>365</v>
+        <v>165</v>
       </c>
       <c r="G210" t="s">
         <v>366</v>
@@ -6452,13 +6452,13 @@
         <v>363</v>
       </c>
       <c r="D211" t="s">
-        <v>163</v>
+        <v>364</v>
       </c>
       <c r="E211" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="F211" t="s">
-        <v>365</v>
+        <v>165</v>
       </c>
       <c r="G211" t="s">
         <v>366</v>
@@ -6475,13 +6475,13 @@
         <v>363</v>
       </c>
       <c r="D212" t="s">
-        <v>163</v>
+        <v>364</v>
       </c>
       <c r="E212" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="F212" t="s">
-        <v>365</v>
+        <v>165</v>
       </c>
       <c r="G212" t="s">
         <v>366</v>
@@ -6498,13 +6498,13 @@
         <v>363</v>
       </c>
       <c r="D213" t="s">
-        <v>163</v>
+        <v>364</v>
       </c>
       <c r="E213" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="F213" t="s">
-        <v>365</v>
+        <v>165</v>
       </c>
       <c r="G213" t="s">
         <v>366</v>
@@ -6521,13 +6521,13 @@
         <v>363</v>
       </c>
       <c r="D214" t="s">
-        <v>163</v>
+        <v>364</v>
       </c>
       <c r="E214" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="F214" t="s">
-        <v>365</v>
+        <v>165</v>
       </c>
       <c r="G214" t="s">
         <v>366</v>
@@ -6544,16 +6544,16 @@
         <v>363</v>
       </c>
       <c r="D215" t="s">
-        <v>163</v>
+        <v>349</v>
       </c>
       <c r="E215" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="F215" t="s">
-        <v>365</v>
+        <v>165</v>
       </c>
       <c r="G215" t="s">
-        <v>349</v>
+        <v>366</v>
       </c>
     </row>
     <row r="216" spans="1:7">
@@ -6567,13 +6567,13 @@
         <v>363</v>
       </c>
       <c r="D216" t="s">
-        <v>163</v>
+        <v>364</v>
       </c>
       <c r="E216" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="F216" t="s">
-        <v>365</v>
+        <v>165</v>
       </c>
       <c r="G216" t="s">
         <v>366</v>
@@ -6590,13 +6590,13 @@
         <v>363</v>
       </c>
       <c r="D217" t="s">
-        <v>163</v>
+        <v>364</v>
       </c>
       <c r="E217" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="F217" t="s">
-        <v>365</v>
+        <v>165</v>
       </c>
       <c r="G217" t="s">
         <v>366</v>
@@ -6613,13 +6613,13 @@
         <v>363</v>
       </c>
       <c r="D218" t="s">
-        <v>163</v>
+        <v>364</v>
       </c>
       <c r="E218" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="F218" t="s">
-        <v>365</v>
+        <v>165</v>
       </c>
       <c r="G218" t="s">
         <v>366</v>
@@ -6636,13 +6636,13 @@
         <v>363</v>
       </c>
       <c r="D219" t="s">
-        <v>163</v>
+        <v>364</v>
       </c>
       <c r="E219" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="F219" t="s">
-        <v>365</v>
+        <v>165</v>
       </c>
       <c r="G219" t="s">
         <v>366</v>
@@ -6659,16 +6659,16 @@
         <v>363</v>
       </c>
       <c r="D220" t="s">
-        <v>163</v>
+        <v>309</v>
       </c>
       <c r="E220" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="F220" t="s">
-        <v>365</v>
+        <v>165</v>
       </c>
       <c r="G220" t="s">
-        <v>309</v>
+        <v>366</v>
       </c>
     </row>
     <row r="221" spans="1:7">
@@ -6682,13 +6682,13 @@
         <v>363</v>
       </c>
       <c r="D221" t="s">
-        <v>163</v>
+        <v>364</v>
       </c>
       <c r="E221" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="F221" t="s">
-        <v>365</v>
+        <v>165</v>
       </c>
       <c r="G221" t="s">
         <v>366</v>
@@ -6705,13 +6705,13 @@
         <v>363</v>
       </c>
       <c r="D222" t="s">
-        <v>163</v>
+        <v>364</v>
       </c>
       <c r="E222" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="F222" t="s">
-        <v>365</v>
+        <v>165</v>
       </c>
       <c r="G222" t="s">
         <v>366</v>
@@ -6728,13 +6728,13 @@
         <v>363</v>
       </c>
       <c r="D223" t="s">
-        <v>163</v>
+        <v>364</v>
       </c>
       <c r="E223" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="F223" t="s">
-        <v>365</v>
+        <v>165</v>
       </c>
       <c r="G223" t="s">
         <v>366</v>
@@ -6751,13 +6751,13 @@
         <v>363</v>
       </c>
       <c r="D224" t="s">
-        <v>163</v>
+        <v>364</v>
       </c>
       <c r="E224" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="F224" t="s">
-        <v>365</v>
+        <v>165</v>
       </c>
       <c r="G224" t="s">
         <v>366</v>
@@ -6774,13 +6774,13 @@
         <v>363</v>
       </c>
       <c r="D225" t="s">
-        <v>163</v>
+        <v>364</v>
       </c>
       <c r="E225" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="F225" t="s">
-        <v>365</v>
+        <v>165</v>
       </c>
       <c r="G225" t="s">
         <v>366</v>
@@ -6797,16 +6797,16 @@
         <v>363</v>
       </c>
       <c r="D226" t="s">
-        <v>163</v>
+        <v>275</v>
       </c>
       <c r="E226" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="F226" t="s">
-        <v>365</v>
+        <v>165</v>
       </c>
       <c r="G226" t="s">
-        <v>276</v>
+        <v>366</v>
       </c>
     </row>
     <row r="227" spans="1:7">
@@ -6820,13 +6820,13 @@
         <v>363</v>
       </c>
       <c r="D227" t="s">
-        <v>163</v>
+        <v>364</v>
       </c>
       <c r="E227" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="F227" t="s">
-        <v>365</v>
+        <v>165</v>
       </c>
       <c r="G227" t="s">
         <v>366</v>
@@ -6849,10 +6849,10 @@
         <v>164</v>
       </c>
       <c r="F228" t="s">
-        <v>365</v>
+        <v>165</v>
       </c>
       <c r="G228" t="s">
-        <v>165</v>
+        <v>366</v>
       </c>
     </row>
     <row r="229" spans="1:7">
@@ -6866,16 +6866,16 @@
         <v>386</v>
       </c>
       <c r="D229" t="s">
-        <v>163</v>
+        <v>387</v>
       </c>
       <c r="E229" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="F229" t="s">
-        <v>365</v>
+        <v>165</v>
       </c>
       <c r="G229" t="s">
-        <v>387</v>
+        <v>366</v>
       </c>
     </row>
     <row r="230" spans="1:7">
@@ -6889,16 +6889,16 @@
         <v>386</v>
       </c>
       <c r="D230" t="s">
-        <v>163</v>
+        <v>387</v>
       </c>
       <c r="E230" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="F230" t="s">
-        <v>365</v>
+        <v>165</v>
       </c>
       <c r="G230" t="s">
-        <v>387</v>
+        <v>366</v>
       </c>
     </row>
     <row r="231" spans="1:7">
@@ -6912,16 +6912,16 @@
         <v>386</v>
       </c>
       <c r="D231" t="s">
-        <v>163</v>
+        <v>293</v>
       </c>
       <c r="E231" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="F231" t="s">
-        <v>365</v>
+        <v>165</v>
       </c>
       <c r="G231" t="s">
-        <v>293</v>
+        <v>366</v>
       </c>
     </row>
     <row r="232" spans="1:7">
@@ -6935,16 +6935,16 @@
         <v>386</v>
       </c>
       <c r="D232" t="s">
-        <v>163</v>
+        <v>309</v>
       </c>
       <c r="E232" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="F232" t="s">
-        <v>365</v>
+        <v>165</v>
       </c>
       <c r="G232" t="s">
-        <v>309</v>
+        <v>366</v>
       </c>
     </row>
     <row r="233" spans="1:7">
@@ -6958,16 +6958,16 @@
         <v>386</v>
       </c>
       <c r="D233" t="s">
-        <v>163</v>
+        <v>387</v>
       </c>
       <c r="E233" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="F233" t="s">
-        <v>365</v>
+        <v>165</v>
       </c>
       <c r="G233" t="s">
-        <v>387</v>
+        <v>366</v>
       </c>
     </row>
     <row r="234" spans="1:7">
@@ -6981,16 +6981,16 @@
         <v>386</v>
       </c>
       <c r="D234" t="s">
-        <v>163</v>
+        <v>387</v>
       </c>
       <c r="E234" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="F234" t="s">
-        <v>365</v>
+        <v>165</v>
       </c>
       <c r="G234" t="s">
-        <v>387</v>
+        <v>366</v>
       </c>
     </row>
     <row r="235" spans="1:7">
@@ -7004,16 +7004,16 @@
         <v>386</v>
       </c>
       <c r="D235" t="s">
-        <v>163</v>
+        <v>387</v>
       </c>
       <c r="E235" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="F235" t="s">
-        <v>365</v>
+        <v>165</v>
       </c>
       <c r="G235" t="s">
-        <v>387</v>
+        <v>366</v>
       </c>
     </row>
     <row r="236" spans="1:7">
@@ -7027,16 +7027,16 @@
         <v>386</v>
       </c>
       <c r="D236" t="s">
-        <v>163</v>
+        <v>387</v>
       </c>
       <c r="E236" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="F236" t="s">
-        <v>365</v>
+        <v>165</v>
       </c>
       <c r="G236" t="s">
-        <v>387</v>
+        <v>366</v>
       </c>
     </row>
     <row r="237" spans="1:7">
@@ -7050,16 +7050,16 @@
         <v>386</v>
       </c>
       <c r="D237" t="s">
-        <v>163</v>
+        <v>387</v>
       </c>
       <c r="E237" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="F237" t="s">
-        <v>365</v>
+        <v>165</v>
       </c>
       <c r="G237" t="s">
-        <v>387</v>
+        <v>366</v>
       </c>
     </row>
     <row r="238" spans="1:7">
@@ -7073,16 +7073,16 @@
         <v>386</v>
       </c>
       <c r="D238" t="s">
-        <v>163</v>
+        <v>387</v>
       </c>
       <c r="E238" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="F238" t="s">
-        <v>365</v>
+        <v>165</v>
       </c>
       <c r="G238" t="s">
-        <v>387</v>
+        <v>366</v>
       </c>
     </row>
     <row r="239" spans="1:7">
@@ -7096,16 +7096,16 @@
         <v>398</v>
       </c>
       <c r="D239" t="s">
-        <v>163</v>
+        <v>399</v>
       </c>
       <c r="E239" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="F239" t="s">
-        <v>365</v>
+        <v>165</v>
       </c>
       <c r="G239" t="s">
-        <v>399</v>
+        <v>366</v>
       </c>
     </row>
     <row r="240" spans="1:7">
@@ -7125,10 +7125,10 @@
         <v>164</v>
       </c>
       <c r="F240" t="s">
+        <v>165</v>
+      </c>
+      <c r="G240" t="s">
         <v>402</v>
-      </c>
-      <c r="G240" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="241" spans="1:7">
@@ -7148,10 +7148,10 @@
         <v>164</v>
       </c>
       <c r="F241" t="s">
+        <v>165</v>
+      </c>
+      <c r="G241" t="s">
         <v>402</v>
-      </c>
-      <c r="G241" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="242" spans="1:7">
@@ -7171,10 +7171,10 @@
         <v>164</v>
       </c>
       <c r="F242" t="s">
+        <v>165</v>
+      </c>
+      <c r="G242" t="s">
         <v>402</v>
-      </c>
-      <c r="G242" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="243" spans="1:7">
@@ -7194,10 +7194,10 @@
         <v>164</v>
       </c>
       <c r="F243" t="s">
+        <v>165</v>
+      </c>
+      <c r="G243" t="s">
         <v>402</v>
-      </c>
-      <c r="G243" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="244" spans="1:7">
@@ -7217,10 +7217,10 @@
         <v>164</v>
       </c>
       <c r="F244" t="s">
+        <v>165</v>
+      </c>
+      <c r="G244" t="s">
         <v>402</v>
-      </c>
-      <c r="G244" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="245" spans="1:7">
@@ -7240,10 +7240,10 @@
         <v>164</v>
       </c>
       <c r="F245" t="s">
+        <v>165</v>
+      </c>
+      <c r="G245" t="s">
         <v>402</v>
-      </c>
-      <c r="G245" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="246" spans="1:7">
@@ -7257,16 +7257,16 @@
         <v>409</v>
       </c>
       <c r="D246" t="s">
-        <v>163</v>
+        <v>410</v>
       </c>
       <c r="E246" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="F246" t="s">
+        <v>165</v>
+      </c>
+      <c r="G246" t="s">
         <v>402</v>
-      </c>
-      <c r="G246" t="s">
-        <v>410</v>
       </c>
     </row>
     <row r="247" spans="1:7">
@@ -7283,10 +7283,10 @@
         <v>96</v>
       </c>
       <c r="F247" t="s">
+        <v>97</v>
+      </c>
+      <c r="G247" t="s">
         <v>412</v>
-      </c>
-      <c r="G247" t="s">
-        <v>97</v>
       </c>
     </row>
     <row r="248" spans="1:7">
@@ -7303,10 +7303,10 @@
         <v>96</v>
       </c>
       <c r="F248" t="s">
+        <v>97</v>
+      </c>
+      <c r="G248" t="s">
         <v>412</v>
-      </c>
-      <c r="G248" t="s">
-        <v>97</v>
       </c>
     </row>
     <row r="249" spans="1:7">
@@ -7317,16 +7317,16 @@
         <v>8</v>
       </c>
       <c r="D249" t="s">
-        <v>95</v>
+        <v>415</v>
       </c>
       <c r="E249" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="F249" t="s">
+        <v>97</v>
+      </c>
+      <c r="G249" t="s">
         <v>412</v>
-      </c>
-      <c r="G249" t="s">
-        <v>416</v>
       </c>
     </row>
     <row r="250" spans="1:7">
@@ -7343,10 +7343,10 @@
         <v>96</v>
       </c>
       <c r="F250" t="s">
+        <v>97</v>
+      </c>
+      <c r="G250" t="s">
         <v>412</v>
-      </c>
-      <c r="G250" t="s">
-        <v>97</v>
       </c>
     </row>
     <row r="251" spans="1:7">
@@ -7363,10 +7363,10 @@
         <v>96</v>
       </c>
       <c r="F251" t="s">
+        <v>97</v>
+      </c>
+      <c r="G251" t="s">
         <v>412</v>
-      </c>
-      <c r="G251" t="s">
-        <v>97</v>
       </c>
     </row>
     <row r="252" spans="1:7">
@@ -7383,10 +7383,10 @@
         <v>96</v>
       </c>
       <c r="F252" t="s">
+        <v>97</v>
+      </c>
+      <c r="G252" t="s">
         <v>412</v>
-      </c>
-      <c r="G252" t="s">
-        <v>97</v>
       </c>
     </row>
     <row r="253" spans="1:7">
@@ -7397,13 +7397,13 @@
         <v>8</v>
       </c>
       <c r="D253" t="s">
-        <v>163</v>
+        <v>421</v>
       </c>
       <c r="E253" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="F253" t="s">
-        <v>422</v>
+        <v>165</v>
       </c>
       <c r="G253" t="s">
         <v>423</v>
@@ -7417,16 +7417,16 @@
         <v>8</v>
       </c>
       <c r="D254" t="s">
-        <v>90</v>
+        <v>219</v>
       </c>
       <c r="E254" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="F254" t="s">
-        <v>422</v>
+        <v>92</v>
       </c>
       <c r="G254" t="s">
-        <v>220</v>
+        <v>423</v>
       </c>
     </row>
     <row r="255" spans="1:7">
@@ -7437,16 +7437,16 @@
         <v>8</v>
       </c>
       <c r="D255" t="s">
-        <v>90</v>
+        <v>426</v>
       </c>
       <c r="E255" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="F255" t="s">
-        <v>422</v>
+        <v>92</v>
       </c>
       <c r="G255" t="s">
-        <v>427</v>
+        <v>423</v>
       </c>
     </row>
     <row r="256" spans="1:7">
@@ -7457,16 +7457,16 @@
         <v>8</v>
       </c>
       <c r="D256" t="s">
-        <v>90</v>
+        <v>426</v>
       </c>
       <c r="E256" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="F256" t="s">
-        <v>422</v>
+        <v>92</v>
       </c>
       <c r="G256" t="s">
-        <v>427</v>
+        <v>423</v>
       </c>
     </row>
     <row r="257" spans="1:7">
@@ -7477,16 +7477,16 @@
         <v>8</v>
       </c>
       <c r="D257" t="s">
-        <v>90</v>
+        <v>426</v>
       </c>
       <c r="E257" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="F257" t="s">
-        <v>422</v>
+        <v>92</v>
       </c>
       <c r="G257" t="s">
-        <v>427</v>
+        <v>423</v>
       </c>
     </row>
     <row r="258" spans="1:7">
@@ -7497,16 +7497,16 @@
         <v>8</v>
       </c>
       <c r="D258" t="s">
-        <v>163</v>
+        <v>326</v>
       </c>
       <c r="E258" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="F258" t="s">
-        <v>422</v>
+        <v>165</v>
       </c>
       <c r="G258" t="s">
-        <v>328</v>
+        <v>423</v>
       </c>
     </row>
     <row r="259" spans="1:7">
@@ -7517,16 +7517,16 @@
         <v>8</v>
       </c>
       <c r="D259" t="s">
-        <v>90</v>
+        <v>426</v>
       </c>
       <c r="E259" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="F259" t="s">
-        <v>422</v>
+        <v>92</v>
       </c>
       <c r="G259" t="s">
-        <v>427</v>
+        <v>423</v>
       </c>
     </row>
     <row r="260" spans="1:7">
@@ -7543,10 +7543,10 @@
         <v>164</v>
       </c>
       <c r="F260" t="s">
-        <v>422</v>
+        <v>165</v>
       </c>
       <c r="G260" t="s">
-        <v>165</v>
+        <v>423</v>
       </c>
     </row>
     <row r="261" spans="1:7">
@@ -7557,16 +7557,16 @@
         <v>8</v>
       </c>
       <c r="D261" t="s">
-        <v>195</v>
+        <v>434</v>
       </c>
       <c r="E261" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="F261" t="s">
-        <v>422</v>
+        <v>197</v>
       </c>
       <c r="G261" t="s">
-        <v>435</v>
+        <v>423</v>
       </c>
     </row>
     <row r="262" spans="1:7">
@@ -7583,10 +7583,10 @@
         <v>164</v>
       </c>
       <c r="F262" t="s">
-        <v>422</v>
+        <v>165</v>
       </c>
       <c r="G262" t="s">
-        <v>165</v>
+        <v>423</v>
       </c>
     </row>
     <row r="263" spans="1:7">
@@ -7597,16 +7597,16 @@
         <v>8</v>
       </c>
       <c r="D263" t="s">
-        <v>182</v>
+        <v>438</v>
       </c>
       <c r="E263" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="F263" t="s">
-        <v>422</v>
+        <v>184</v>
       </c>
       <c r="G263" t="s">
-        <v>439</v>
+        <v>423</v>
       </c>
     </row>
     <row r="264" spans="1:7">
@@ -7623,10 +7623,10 @@
         <v>32</v>
       </c>
       <c r="F264" t="s">
-        <v>422</v>
+        <v>33</v>
       </c>
       <c r="G264" t="s">
-        <v>33</v>
+        <v>423</v>
       </c>
     </row>
     <row r="265" spans="1:7">
@@ -7643,10 +7643,10 @@
         <v>11</v>
       </c>
       <c r="F265" t="s">
-        <v>422</v>
+        <v>12</v>
       </c>
       <c r="G265" t="s">
-        <v>13</v>
+        <v>423</v>
       </c>
     </row>
     <row r="266" spans="1:7">
@@ -7657,16 +7657,16 @@
         <v>8</v>
       </c>
       <c r="D266" t="s">
-        <v>113</v>
+        <v>443</v>
       </c>
       <c r="E266" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="F266" t="s">
-        <v>422</v>
+        <v>115</v>
       </c>
       <c r="G266" t="s">
-        <v>444</v>
+        <v>423</v>
       </c>
     </row>
     <row r="267" spans="1:7">
@@ -7677,16 +7677,16 @@
         <v>8</v>
       </c>
       <c r="D267" t="s">
-        <v>113</v>
+        <v>118</v>
       </c>
       <c r="E267" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="F267" t="s">
+        <v>115</v>
+      </c>
+      <c r="G267" t="s">
         <v>446</v>
-      </c>
-      <c r="G267" t="s">
-        <v>119</v>
       </c>
     </row>
     <row r="268" spans="1:7">
@@ -7697,16 +7697,16 @@
         <v>8</v>
       </c>
       <c r="D268" t="s">
-        <v>182</v>
+        <v>202</v>
       </c>
       <c r="E268" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="F268" t="s">
+        <v>184</v>
+      </c>
+      <c r="G268" t="s">
         <v>448</v>
-      </c>
-      <c r="G268" t="s">
-        <v>204</v>
       </c>
     </row>
     <row r="269" spans="1:7">
@@ -7717,16 +7717,16 @@
         <v>8</v>
       </c>
       <c r="D269" t="s">
-        <v>113</v>
+        <v>118</v>
       </c>
       <c r="E269" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="F269" t="s">
+        <v>115</v>
+      </c>
+      <c r="G269" t="s">
         <v>450</v>
-      </c>
-      <c r="G269" t="s">
-        <v>119</v>
       </c>
     </row>
     <row r="270" spans="1:7">
@@ -7737,16 +7737,16 @@
         <v>8</v>
       </c>
       <c r="D270" t="s">
-        <v>113</v>
+        <v>118</v>
       </c>
       <c r="E270" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="F270" t="s">
+        <v>115</v>
+      </c>
+      <c r="G270" t="s">
         <v>450</v>
-      </c>
-      <c r="G270" t="s">
-        <v>119</v>
       </c>
     </row>
     <row r="271" spans="1:7">
@@ -7757,13 +7757,13 @@
         <v>8</v>
       </c>
       <c r="D271" t="s">
-        <v>113</v>
+        <v>453</v>
       </c>
       <c r="E271" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="F271" t="s">
-        <v>454</v>
+        <v>115</v>
       </c>
       <c r="G271" t="s">
         <v>455</v>
@@ -7777,13 +7777,13 @@
         <v>8</v>
       </c>
       <c r="D272" t="s">
-        <v>113</v>
+        <v>453</v>
       </c>
       <c r="E272" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="F272" t="s">
-        <v>454</v>
+        <v>115</v>
       </c>
       <c r="G272" t="s">
         <v>455</v>
@@ -7797,13 +7797,13 @@
         <v>8</v>
       </c>
       <c r="D273" t="s">
-        <v>113</v>
+        <v>453</v>
       </c>
       <c r="E273" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="F273" t="s">
-        <v>454</v>
+        <v>115</v>
       </c>
       <c r="G273" t="s">
         <v>455</v>
@@ -7817,13 +7817,13 @@
         <v>8</v>
       </c>
       <c r="D274" t="s">
-        <v>113</v>
+        <v>453</v>
       </c>
       <c r="E274" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="F274" t="s">
-        <v>454</v>
+        <v>115</v>
       </c>
       <c r="G274" t="s">
         <v>455</v>
@@ -7837,13 +7837,13 @@
         <v>8</v>
       </c>
       <c r="D275" t="s">
-        <v>113</v>
+        <v>453</v>
       </c>
       <c r="E275" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="F275" t="s">
-        <v>454</v>
+        <v>115</v>
       </c>
       <c r="G275" t="s">
         <v>455</v>
@@ -7857,13 +7857,13 @@
         <v>8</v>
       </c>
       <c r="D276" t="s">
-        <v>113</v>
+        <v>453</v>
       </c>
       <c r="E276" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="F276" t="s">
-        <v>454</v>
+        <v>115</v>
       </c>
       <c r="G276" t="s">
         <v>455</v>
@@ -7877,13 +7877,13 @@
         <v>8</v>
       </c>
       <c r="D277" t="s">
-        <v>113</v>
+        <v>453</v>
       </c>
       <c r="E277" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="F277" t="s">
-        <v>454</v>
+        <v>115</v>
       </c>
       <c r="G277" t="s">
         <v>455</v>
@@ -7897,16 +7897,16 @@
         <v>8</v>
       </c>
       <c r="D278" t="s">
-        <v>182</v>
+        <v>202</v>
       </c>
       <c r="E278" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="F278" t="s">
+        <v>184</v>
+      </c>
+      <c r="G278" t="s">
         <v>463</v>
-      </c>
-      <c r="G278" t="s">
-        <v>204</v>
       </c>
     </row>
     <row r="279" spans="1:7">
@@ -7917,16 +7917,16 @@
         <v>8</v>
       </c>
       <c r="D279" t="s">
-        <v>31</v>
+        <v>52</v>
       </c>
       <c r="E279" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F279" t="s">
+        <v>33</v>
+      </c>
+      <c r="G279" t="s">
         <v>463</v>
-      </c>
-      <c r="G279" t="s">
-        <v>54</v>
       </c>
     </row>
     <row r="280" spans="1:7">
@@ -7943,10 +7943,10 @@
         <v>11</v>
       </c>
       <c r="F280" t="s">
+        <v>12</v>
+      </c>
+      <c r="G280" t="s">
         <v>463</v>
-      </c>
-      <c r="G280" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="281" spans="1:7">
@@ -7957,16 +7957,16 @@
         <v>8</v>
       </c>
       <c r="D281" t="s">
-        <v>113</v>
+        <v>170</v>
       </c>
       <c r="E281" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F281" t="s">
+        <v>115</v>
+      </c>
+      <c r="G281" t="s">
         <v>463</v>
-      </c>
-      <c r="G281" t="s">
-        <v>171</v>
       </c>
     </row>
     <row r="282" spans="1:7">
@@ -7983,10 +7983,10 @@
         <v>125</v>
       </c>
       <c r="F282" t="s">
+        <v>126</v>
+      </c>
+      <c r="G282" t="s">
         <v>463</v>
-      </c>
-      <c r="G282" t="s">
-        <v>126</v>
       </c>
     </row>
     <row r="283" spans="1:7">
@@ -7997,16 +7997,16 @@
         <v>8</v>
       </c>
       <c r="D283" t="s">
-        <v>163</v>
+        <v>399</v>
       </c>
       <c r="E283" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="F283" t="s">
+        <v>165</v>
+      </c>
+      <c r="G283" t="s">
         <v>469</v>
-      </c>
-      <c r="G283" t="s">
-        <v>399</v>
       </c>
     </row>
     <row r="284" spans="1:7">
@@ -8023,10 +8023,10 @@
         <v>125</v>
       </c>
       <c r="F284" t="s">
+        <v>126</v>
+      </c>
+      <c r="G284" t="s">
         <v>471</v>
-      </c>
-      <c r="G284" t="s">
-        <v>126</v>
       </c>
     </row>
     <row r="285" spans="1:7">
@@ -8037,16 +8037,16 @@
         <v>8</v>
       </c>
       <c r="D285" t="s">
-        <v>113</v>
+        <v>170</v>
       </c>
       <c r="E285" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F285" t="s">
+        <v>115</v>
+      </c>
+      <c r="G285" t="s">
         <v>473</v>
-      </c>
-      <c r="G285" t="s">
-        <v>171</v>
       </c>
     </row>
     <row r="286" spans="1:7">
@@ -8057,16 +8057,16 @@
         <v>8</v>
       </c>
       <c r="D286" t="s">
-        <v>182</v>
+        <v>438</v>
       </c>
       <c r="E286" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="F286" t="s">
+        <v>184</v>
+      </c>
+      <c r="G286" t="s">
         <v>475</v>
-      </c>
-      <c r="G286" t="s">
-        <v>439</v>
       </c>
     </row>
     <row r="287" spans="1:7">
@@ -8077,16 +8077,16 @@
         <v>8</v>
       </c>
       <c r="D287" t="s">
-        <v>182</v>
+        <v>438</v>
       </c>
       <c r="E287" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="F287" t="s">
+        <v>184</v>
+      </c>
+      <c r="G287" t="s">
         <v>475</v>
-      </c>
-      <c r="G287" t="s">
-        <v>439</v>
       </c>
     </row>
     <row r="288" spans="1:7">
@@ -8097,16 +8097,16 @@
         <v>8</v>
       </c>
       <c r="D288" t="s">
-        <v>10</v>
+        <v>41</v>
       </c>
       <c r="E288" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F288" t="s">
+        <v>12</v>
+      </c>
+      <c r="G288" t="s">
         <v>475</v>
-      </c>
-      <c r="G288" t="s">
-        <v>42</v>
       </c>
     </row>
     <row r="289" spans="1:7">
@@ -8123,10 +8123,10 @@
         <v>32</v>
       </c>
       <c r="F289" t="s">
+        <v>33</v>
+      </c>
+      <c r="G289" t="s">
         <v>475</v>
-      </c>
-      <c r="G289" t="s">
-        <v>33</v>
       </c>
     </row>
     <row r="290" spans="1:7">
@@ -8143,10 +8143,10 @@
         <v>32</v>
       </c>
       <c r="F290" t="s">
+        <v>33</v>
+      </c>
+      <c r="G290" t="s">
         <v>475</v>
-      </c>
-      <c r="G290" t="s">
-        <v>33</v>
       </c>
     </row>
     <row r="291" spans="1:7">
@@ -8157,16 +8157,16 @@
         <v>8</v>
       </c>
       <c r="D291" t="s">
-        <v>113</v>
+        <v>170</v>
       </c>
       <c r="E291" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F291" t="s">
+        <v>115</v>
+      </c>
+      <c r="G291" t="s">
         <v>475</v>
-      </c>
-      <c r="G291" t="s">
-        <v>171</v>
       </c>
     </row>
     <row r="292" spans="1:7">
@@ -8177,16 +8177,16 @@
         <v>8</v>
       </c>
       <c r="D292" t="s">
-        <v>113</v>
+        <v>170</v>
       </c>
       <c r="E292" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F292" t="s">
+        <v>115</v>
+      </c>
+      <c r="G292" t="s">
         <v>475</v>
-      </c>
-      <c r="G292" t="s">
-        <v>171</v>
       </c>
     </row>
     <row r="293" spans="1:7">
@@ -8197,16 +8197,16 @@
         <v>8</v>
       </c>
       <c r="D293" t="s">
-        <v>113</v>
+        <v>170</v>
       </c>
       <c r="E293" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F293" t="s">
+        <v>115</v>
+      </c>
+      <c r="G293" t="s">
         <v>475</v>
-      </c>
-      <c r="G293" t="s">
-        <v>171</v>
       </c>
     </row>
     <row r="294" spans="1:7">
@@ -8217,16 +8217,16 @@
         <v>8</v>
       </c>
       <c r="D294" t="s">
-        <v>113</v>
+        <v>170</v>
       </c>
       <c r="E294" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F294" t="s">
+        <v>115</v>
+      </c>
+      <c r="G294" t="s">
         <v>475</v>
-      </c>
-      <c r="G294" t="s">
-        <v>171</v>
       </c>
     </row>
     <row r="295" spans="1:7">
@@ -8237,16 +8237,16 @@
         <v>8</v>
       </c>
       <c r="D295" t="s">
-        <v>113</v>
+        <v>170</v>
       </c>
       <c r="E295" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F295" t="s">
+        <v>115</v>
+      </c>
+      <c r="G295" t="s">
         <v>485</v>
-      </c>
-      <c r="G295" t="s">
-        <v>171</v>
       </c>
     </row>
     <row r="296" spans="1:7">
@@ -8257,16 +8257,16 @@
         <v>8</v>
       </c>
       <c r="D296" t="s">
-        <v>113</v>
+        <v>170</v>
       </c>
       <c r="E296" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F296" t="s">
+        <v>115</v>
+      </c>
+      <c r="G296" t="s">
         <v>485</v>
-      </c>
-      <c r="G296" t="s">
-        <v>171</v>
       </c>
     </row>
   </sheetData>

--- a/api/2/xlsx/fr/SectorCOFOG.xlsx
+++ b/api/2/xlsx/fr/SectorCOFOG.xlsx
@@ -22,42 +22,42 @@
     <t>status</t>
   </si>
   <si>
+    <t>codeforiati:cofog-class</t>
+  </si>
+  <si>
+    <t>codeforiati:cofog-group</t>
+  </si>
+  <si>
+    <t>codeforiati:group-code</t>
+  </si>
+  <si>
+    <t>codeforiati:cofog-division</t>
+  </si>
+  <si>
     <t>codeforiati:category-code</t>
   </si>
   <si>
-    <t>codeforiati:cofog-class</t>
-  </si>
-  <si>
-    <t>codeforiati:cofog-group</t>
-  </si>
-  <si>
-    <t>codeforiati:cofog-division</t>
-  </si>
-  <si>
-    <t>codeforiati:group-code</t>
-  </si>
-  <si>
     <t>11110</t>
   </si>
   <si>
     <t>active</t>
   </si>
   <si>
+    <t>09.8.0 - Education n.e.c. (CS)</t>
+  </si>
+  <si>
+    <t>09.8 - Education n.e.c.</t>
+  </si>
+  <si>
+    <t>110</t>
+  </si>
+  <si>
+    <t>09 - Education</t>
+  </si>
+  <si>
     <t>111</t>
   </si>
   <si>
-    <t>09.8.0 - Education n.e.c. (CS)</t>
-  </si>
-  <si>
-    <t>09.8 - Education n.e.c.</t>
-  </si>
-  <si>
-    <t>09 - Education</t>
-  </si>
-  <si>
-    <t>110</t>
-  </si>
-  <si>
     <t>11120</t>
   </si>
   <si>
@@ -82,15 +82,15 @@
     <t>11220</t>
   </si>
   <si>
+    <t>09.1.2 - Primary education (IS)</t>
+  </si>
+  <si>
+    <t>09.1 - Pre‐primary and primary education</t>
+  </si>
+  <si>
     <t>112</t>
   </si>
   <si>
-    <t>09.1.2 - Primary education (IS)</t>
-  </si>
-  <si>
-    <t>09.1 - Pre‐primary and primary education</t>
-  </si>
-  <si>
     <t>11230</t>
   </si>
   <si>
@@ -130,12 +130,12 @@
     <t>11320</t>
   </si>
   <si>
+    <t>09.2.2 - Upper‐secondary education (IS)</t>
+  </si>
+  <si>
     <t>113</t>
   </si>
   <si>
-    <t>09.2.2 - Upper‐secondary education (IS)</t>
-  </si>
-  <si>
     <t>11330</t>
   </si>
   <si>
@@ -148,15 +148,15 @@
     <t>11420</t>
   </si>
   <si>
+    <t>09.4.1 - First stage of tertiary education (IS)</t>
+  </si>
+  <si>
+    <t>09.4 - Tertiary education</t>
+  </si>
+  <si>
     <t>114</t>
   </si>
   <si>
-    <t>09.4.1 - First stage of tertiary education (IS)</t>
-  </si>
-  <si>
-    <t>09.4 - Tertiary education</t>
-  </si>
-  <si>
     <t>11430</t>
   </si>
   <si>
@@ -169,18 +169,18 @@
     <t>12110</t>
   </si>
   <si>
+    <t>07.6.0 - Health n.e.c. (CS)</t>
+  </si>
+  <si>
+    <t>07.6 - Health n.e.c.</t>
+  </si>
+  <si>
+    <t>120</t>
+  </si>
+  <si>
     <t>121</t>
   </si>
   <si>
-    <t>07.6.0 - Health n.e.c. (CS)</t>
-  </si>
-  <si>
-    <t>07.6 - Health n.e.c.</t>
-  </si>
-  <si>
-    <t>120</t>
-  </si>
-  <si>
     <t>12181</t>
   </si>
   <si>
@@ -292,12 +292,12 @@
     <t>06.3 - Water supply</t>
   </si>
   <si>
+    <t>140</t>
+  </si>
+  <si>
     <t>06 - Housing and community amenities</t>
   </si>
   <si>
-    <t>140</t>
-  </si>
-  <si>
     <t>14015</t>
   </si>
   <si>
@@ -352,21 +352,21 @@
     <t>15110</t>
   </si>
   <si>
+    <t>01.3.1 - General personnel services (CS)</t>
+  </si>
+  <si>
+    <t>01.3 - General services</t>
+  </si>
+  <si>
+    <t>150</t>
+  </si>
+  <si>
+    <t>01 - General public services</t>
+  </si>
+  <si>
     <t>151</t>
   </si>
   <si>
-    <t>01.3.1 - General personnel services (CS)</t>
-  </si>
-  <si>
-    <t>01.3 - General services</t>
-  </si>
-  <si>
-    <t>01 - General public services</t>
-  </si>
-  <si>
-    <t>150</t>
-  </si>
-  <si>
     <t>15111</t>
   </si>
   <si>
@@ -823,18 +823,18 @@
     <t>23110</t>
   </si>
   <si>
+    <t>04.3.5 - Electricity (CS)</t>
+  </si>
+  <si>
+    <t>04.3 - Fuel and energy</t>
+  </si>
+  <si>
+    <t>230</t>
+  </si>
+  <si>
     <t>231</t>
   </si>
   <si>
-    <t>04.3.5 - Electricity (CS)</t>
-  </si>
-  <si>
-    <t>04.3 - Fuel and energy</t>
-  </si>
-  <si>
-    <t>230</t>
-  </si>
-  <si>
     <t>23111</t>
   </si>
   <si>
@@ -919,12 +919,12 @@
     <t>23510</t>
   </si>
   <si>
+    <t>04.3.3 - Nuclear fuel (CS)</t>
+  </si>
+  <si>
     <t>235</t>
   </si>
   <si>
-    <t>04.3.3 - Nuclear fuel (CS)</t>
-  </si>
-  <si>
     <t>23610</t>
   </si>
   <si>
@@ -991,18 +991,18 @@
     <t>31110</t>
   </si>
   <si>
+    <t>04.2.1 - Agriculture (CS)</t>
+  </si>
+  <si>
+    <t>04.2 - Agriculture, forestry, fishing and hunting</t>
+  </si>
+  <si>
+    <t>310</t>
+  </si>
+  <si>
     <t>311</t>
   </si>
   <si>
-    <t>04.2.1 - Agriculture (CS)</t>
-  </si>
-  <si>
-    <t>04.2 - Agriculture, forestry, fishing and hunting</t>
-  </si>
-  <si>
-    <t>310</t>
-  </si>
-  <si>
     <t>31120</t>
   </si>
   <si>
@@ -1060,12 +1060,12 @@
     <t>31210</t>
   </si>
   <si>
+    <t>04.2.2 - Forestry (CS)</t>
+  </si>
+  <si>
     <t>312</t>
   </si>
   <si>
-    <t>04.2.2 - Forestry (CS)</t>
-  </si>
-  <si>
     <t>31220</t>
   </si>
   <si>
@@ -1084,12 +1084,12 @@
     <t>31310</t>
   </si>
   <si>
+    <t>04.2.3 - Fishing and hunting (CS)</t>
+  </si>
+  <si>
     <t>313</t>
   </si>
   <si>
-    <t>04.2.3 - Fishing and hunting (CS)</t>
-  </si>
-  <si>
     <t>31320</t>
   </si>
   <si>
@@ -1105,18 +1105,18 @@
     <t>32110</t>
   </si>
   <si>
+    <t>04.4.2 - Manufacturing (CS)</t>
+  </si>
+  <si>
+    <t>04.4 - Mining, manufacturing and construction</t>
+  </si>
+  <si>
+    <t>320</t>
+  </si>
+  <si>
     <t>321</t>
   </si>
   <si>
-    <t>04.4.2 - Manufacturing (CS)</t>
-  </si>
-  <si>
-    <t>04.4 - Mining, manufacturing and construction</t>
-  </si>
-  <si>
-    <t>320</t>
-  </si>
-  <si>
     <t>32120</t>
   </si>
   <si>
@@ -1174,12 +1174,12 @@
     <t>32210</t>
   </si>
   <si>
+    <t>04.4.1 - Mining of mineral resources other than mineral fuels (CS)</t>
+  </si>
+  <si>
     <t>322</t>
   </si>
   <si>
-    <t>04.4.1 - Mining of mineral resources other than mineral fuels (CS)</t>
-  </si>
-  <si>
     <t>32220</t>
   </si>
   <si>
@@ -1210,21 +1210,21 @@
     <t>32310</t>
   </si>
   <si>
+    <t>04.4.3 - Construction (CS)</t>
+  </si>
+  <si>
     <t>323</t>
   </si>
   <si>
-    <t>04.4.3 - Construction (CS)</t>
-  </si>
-  <si>
     <t>33110</t>
   </si>
   <si>
+    <t>330</t>
+  </si>
+  <si>
     <t>331</t>
   </si>
   <si>
-    <t>330</t>
-  </si>
-  <si>
     <t>33120</t>
   </si>
   <si>
@@ -1243,10 +1243,10 @@
     <t>33210</t>
   </si>
   <si>
+    <t>04.7.3 - Tourism (CS)</t>
+  </si>
+  <si>
     <t>332</t>
-  </si>
-  <si>
-    <t>04.7.3 - Tourism (CS)</t>
   </si>
   <si>
     <t>41010</t>
@@ -1863,13 +1863,13 @@
         <v>8</v>
       </c>
       <c r="C3" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="D3" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E3" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="F3" t="s">
         <v>12</v>
@@ -1909,13 +1909,13 @@
         <v>8</v>
       </c>
       <c r="C5" t="s">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="D5" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E5" t="s">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="F5" t="s">
         <v>12</v>
@@ -1938,13 +1938,13 @@
         <v>23</v>
       </c>
       <c r="E6" t="s">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="F6" t="s">
         <v>12</v>
       </c>
       <c r="G6" t="s">
-        <v>13</v>
+        <v>24</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -1955,7 +1955,7 @@
         <v>8</v>
       </c>
       <c r="C7" t="s">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="D7" t="s">
         <v>10</v>
@@ -1967,7 +1967,7 @@
         <v>12</v>
       </c>
       <c r="G7" t="s">
-        <v>13</v>
+        <v>24</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -1984,13 +1984,13 @@
         <v>23</v>
       </c>
       <c r="E8" t="s">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="F8" t="s">
         <v>12</v>
       </c>
       <c r="G8" t="s">
-        <v>13</v>
+        <v>24</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -2007,13 +2007,13 @@
         <v>23</v>
       </c>
       <c r="E9" t="s">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="F9" t="s">
         <v>12</v>
       </c>
       <c r="G9" t="s">
-        <v>13</v>
+        <v>24</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -2024,19 +2024,19 @@
         <v>8</v>
       </c>
       <c r="C10" t="s">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="D10" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="E10" t="s">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="F10" t="s">
         <v>12</v>
       </c>
       <c r="G10" t="s">
-        <v>13</v>
+        <v>24</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -2047,19 +2047,19 @@
         <v>8</v>
       </c>
       <c r="C11" t="s">
-        <v>22</v>
+        <v>31</v>
       </c>
       <c r="D11" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E11" t="s">
-        <v>32</v>
+        <v>11</v>
       </c>
       <c r="F11" t="s">
         <v>33</v>
       </c>
       <c r="G11" t="s">
-        <v>13</v>
+        <v>24</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -2070,19 +2070,19 @@
         <v>8</v>
       </c>
       <c r="C12" t="s">
-        <v>22</v>
+        <v>35</v>
       </c>
       <c r="D12" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E12" t="s">
-        <v>36</v>
+        <v>11</v>
       </c>
       <c r="F12" t="s">
         <v>12</v>
       </c>
       <c r="G12" t="s">
-        <v>13</v>
+        <v>24</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -2096,16 +2096,16 @@
         <v>38</v>
       </c>
       <c r="D13" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="E13" t="s">
-        <v>36</v>
+        <v>11</v>
       </c>
       <c r="F13" t="s">
         <v>12</v>
       </c>
       <c r="G13" t="s">
-        <v>13</v>
+        <v>39</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -2116,19 +2116,19 @@
         <v>8</v>
       </c>
       <c r="C14" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="D14" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="E14" t="s">
-        <v>42</v>
+        <v>11</v>
       </c>
       <c r="F14" t="s">
         <v>12</v>
       </c>
       <c r="G14" t="s">
-        <v>13</v>
+        <v>39</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -2145,13 +2145,13 @@
         <v>45</v>
       </c>
       <c r="E15" t="s">
-        <v>46</v>
+        <v>11</v>
       </c>
       <c r="F15" t="s">
         <v>12</v>
       </c>
       <c r="G15" t="s">
-        <v>13</v>
+        <v>46</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -2162,19 +2162,19 @@
         <v>8</v>
       </c>
       <c r="C16" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="D16" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="E16" t="s">
-        <v>49</v>
+        <v>11</v>
       </c>
       <c r="F16" t="s">
         <v>12</v>
       </c>
       <c r="G16" t="s">
-        <v>13</v>
+        <v>46</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -2231,13 +2231,13 @@
         <v>8</v>
       </c>
       <c r="C19" t="s">
-        <v>51</v>
+        <v>57</v>
       </c>
       <c r="D19" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E19" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="F19" t="s">
         <v>33</v>
@@ -2254,13 +2254,13 @@
         <v>8</v>
       </c>
       <c r="C20" t="s">
-        <v>51</v>
+        <v>60</v>
       </c>
       <c r="D20" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E20" t="s">
-        <v>61</v>
+        <v>53</v>
       </c>
       <c r="F20" t="s">
         <v>33</v>
@@ -2300,19 +2300,19 @@
         <v>8</v>
       </c>
       <c r="C22" t="s">
-        <v>64</v>
+        <v>31</v>
       </c>
       <c r="D22" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E22" t="s">
-        <v>32</v>
+        <v>53</v>
       </c>
       <c r="F22" t="s">
         <v>33</v>
       </c>
       <c r="G22" t="s">
-        <v>54</v>
+        <v>64</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -2323,19 +2323,19 @@
         <v>8</v>
       </c>
       <c r="C23" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="D23" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="E23" t="s">
-        <v>67</v>
+        <v>53</v>
       </c>
       <c r="F23" t="s">
         <v>33</v>
       </c>
       <c r="G23" t="s">
-        <v>54</v>
+        <v>64</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -2346,19 +2346,19 @@
         <v>8</v>
       </c>
       <c r="C24" t="s">
-        <v>64</v>
+        <v>31</v>
       </c>
       <c r="D24" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E24" t="s">
-        <v>32</v>
+        <v>53</v>
       </c>
       <c r="F24" t="s">
         <v>33</v>
       </c>
       <c r="G24" t="s">
-        <v>54</v>
+        <v>64</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -2369,19 +2369,19 @@
         <v>8</v>
       </c>
       <c r="C25" t="s">
-        <v>64</v>
+        <v>31</v>
       </c>
       <c r="D25" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E25" t="s">
-        <v>32</v>
+        <v>53</v>
       </c>
       <c r="F25" t="s">
         <v>33</v>
       </c>
       <c r="G25" t="s">
-        <v>54</v>
+        <v>64</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -2392,19 +2392,19 @@
         <v>8</v>
       </c>
       <c r="C26" t="s">
-        <v>64</v>
+        <v>31</v>
       </c>
       <c r="D26" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E26" t="s">
-        <v>32</v>
+        <v>53</v>
       </c>
       <c r="F26" t="s">
         <v>33</v>
       </c>
       <c r="G26" t="s">
-        <v>54</v>
+        <v>64</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -2415,19 +2415,19 @@
         <v>8</v>
       </c>
       <c r="C27" t="s">
-        <v>64</v>
+        <v>31</v>
       </c>
       <c r="D27" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E27" t="s">
-        <v>32</v>
+        <v>53</v>
       </c>
       <c r="F27" t="s">
         <v>33</v>
       </c>
       <c r="G27" t="s">
-        <v>54</v>
+        <v>64</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -2438,19 +2438,19 @@
         <v>8</v>
       </c>
       <c r="C28" t="s">
-        <v>64</v>
+        <v>31</v>
       </c>
       <c r="D28" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E28" t="s">
-        <v>32</v>
+        <v>53</v>
       </c>
       <c r="F28" t="s">
         <v>33</v>
       </c>
       <c r="G28" t="s">
-        <v>54</v>
+        <v>64</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -2461,19 +2461,19 @@
         <v>8</v>
       </c>
       <c r="C29" t="s">
-        <v>64</v>
+        <v>31</v>
       </c>
       <c r="D29" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E29" t="s">
-        <v>32</v>
+        <v>53</v>
       </c>
       <c r="F29" t="s">
         <v>33</v>
       </c>
       <c r="G29" t="s">
-        <v>54</v>
+        <v>64</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -2484,7 +2484,7 @@
         <v>8</v>
       </c>
       <c r="C30" t="s">
-        <v>64</v>
+        <v>51</v>
       </c>
       <c r="D30" t="s">
         <v>52</v>
@@ -2496,7 +2496,7 @@
         <v>33</v>
       </c>
       <c r="G30" t="s">
-        <v>54</v>
+        <v>64</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -2507,19 +2507,19 @@
         <v>8</v>
       </c>
       <c r="C31" t="s">
-        <v>76</v>
+        <v>31</v>
       </c>
       <c r="D31" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E31" t="s">
-        <v>32</v>
+        <v>53</v>
       </c>
       <c r="F31" t="s">
         <v>33</v>
       </c>
       <c r="G31" t="s">
-        <v>54</v>
+        <v>76</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -2530,19 +2530,19 @@
         <v>8</v>
       </c>
       <c r="C32" t="s">
-        <v>76</v>
+        <v>31</v>
       </c>
       <c r="D32" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E32" t="s">
-        <v>32</v>
+        <v>53</v>
       </c>
       <c r="F32" t="s">
         <v>33</v>
       </c>
       <c r="G32" t="s">
-        <v>54</v>
+        <v>76</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -2553,19 +2553,19 @@
         <v>8</v>
       </c>
       <c r="C33" t="s">
-        <v>76</v>
+        <v>31</v>
       </c>
       <c r="D33" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E33" t="s">
-        <v>32</v>
+        <v>53</v>
       </c>
       <c r="F33" t="s">
         <v>33</v>
       </c>
       <c r="G33" t="s">
-        <v>54</v>
+        <v>76</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -2576,19 +2576,19 @@
         <v>8</v>
       </c>
       <c r="C34" t="s">
-        <v>76</v>
+        <v>31</v>
       </c>
       <c r="D34" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E34" t="s">
-        <v>32</v>
+        <v>53</v>
       </c>
       <c r="F34" t="s">
         <v>33</v>
       </c>
       <c r="G34" t="s">
-        <v>54</v>
+        <v>76</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -2599,19 +2599,19 @@
         <v>8</v>
       </c>
       <c r="C35" t="s">
-        <v>76</v>
+        <v>31</v>
       </c>
       <c r="D35" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E35" t="s">
-        <v>32</v>
+        <v>53</v>
       </c>
       <c r="F35" t="s">
         <v>33</v>
       </c>
       <c r="G35" t="s">
-        <v>54</v>
+        <v>76</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -2622,19 +2622,19 @@
         <v>8</v>
       </c>
       <c r="C36" t="s">
-        <v>76</v>
+        <v>57</v>
       </c>
       <c r="D36" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E36" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="F36" t="s">
         <v>33</v>
       </c>
       <c r="G36" t="s">
-        <v>54</v>
+        <v>76</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -2644,17 +2644,17 @@
       <c r="B37" t="s">
         <v>8</v>
       </c>
+      <c r="C37" t="s">
+        <v>31</v>
+      </c>
       <c r="D37" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E37" t="s">
-        <v>32</v>
+        <v>83</v>
       </c>
       <c r="F37" t="s">
         <v>33</v>
-      </c>
-      <c r="G37" t="s">
-        <v>83</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -2664,17 +2664,17 @@
       <c r="B38" t="s">
         <v>8</v>
       </c>
+      <c r="C38" t="s">
+        <v>31</v>
+      </c>
       <c r="D38" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E38" t="s">
-        <v>32</v>
+        <v>83</v>
       </c>
       <c r="F38" t="s">
         <v>33</v>
-      </c>
-      <c r="G38" t="s">
-        <v>83</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -2684,17 +2684,17 @@
       <c r="B39" t="s">
         <v>8</v>
       </c>
+      <c r="C39" t="s">
+        <v>31</v>
+      </c>
       <c r="D39" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E39" t="s">
-        <v>32</v>
+        <v>83</v>
       </c>
       <c r="F39" t="s">
         <v>33</v>
-      </c>
-      <c r="G39" t="s">
-        <v>83</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -2704,17 +2704,17 @@
       <c r="B40" t="s">
         <v>8</v>
       </c>
+      <c r="C40" t="s">
+        <v>31</v>
+      </c>
       <c r="D40" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E40" t="s">
-        <v>32</v>
+        <v>83</v>
       </c>
       <c r="F40" t="s">
         <v>33</v>
-      </c>
-      <c r="G40" t="s">
-        <v>83</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -2724,17 +2724,17 @@
       <c r="B41" t="s">
         <v>8</v>
       </c>
+      <c r="C41" t="s">
+        <v>51</v>
+      </c>
       <c r="D41" t="s">
         <v>52</v>
       </c>
       <c r="E41" t="s">
-        <v>53</v>
+        <v>83</v>
       </c>
       <c r="F41" t="s">
         <v>33</v>
-      </c>
-      <c r="G41" t="s">
-        <v>83</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -2744,17 +2744,17 @@
       <c r="B42" t="s">
         <v>8</v>
       </c>
+      <c r="C42" t="s">
+        <v>57</v>
+      </c>
       <c r="D42" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E42" t="s">
-        <v>58</v>
+        <v>83</v>
       </c>
       <c r="F42" t="s">
         <v>33</v>
-      </c>
-      <c r="G42" t="s">
-        <v>83</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -2764,16 +2764,16 @@
       <c r="B43" t="s">
         <v>8</v>
       </c>
+      <c r="C43" t="s">
+        <v>90</v>
+      </c>
       <c r="D43" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="E43" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="F43" t="s">
-        <v>92</v>
-      </c>
-      <c r="G43" t="s">
         <v>93</v>
       </c>
     </row>
@@ -2784,17 +2784,17 @@
       <c r="B44" t="s">
         <v>8</v>
       </c>
+      <c r="C44" t="s">
+        <v>95</v>
+      </c>
       <c r="D44" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="E44" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="F44" t="s">
         <v>97</v>
-      </c>
-      <c r="G44" t="s">
-        <v>93</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -2804,16 +2804,16 @@
       <c r="B45" t="s">
         <v>8</v>
       </c>
+      <c r="C45" t="s">
+        <v>90</v>
+      </c>
       <c r="D45" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="E45" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="F45" t="s">
-        <v>92</v>
-      </c>
-      <c r="G45" t="s">
         <v>93</v>
       </c>
     </row>
@@ -2824,16 +2824,16 @@
       <c r="B46" t="s">
         <v>8</v>
       </c>
+      <c r="C46" t="s">
+        <v>90</v>
+      </c>
       <c r="D46" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="E46" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="F46" t="s">
-        <v>92</v>
-      </c>
-      <c r="G46" t="s">
         <v>93</v>
       </c>
     </row>
@@ -2844,17 +2844,17 @@
       <c r="B47" t="s">
         <v>8</v>
       </c>
+      <c r="C47" t="s">
+        <v>101</v>
+      </c>
       <c r="D47" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="E47" t="s">
-        <v>102</v>
+        <v>92</v>
       </c>
       <c r="F47" t="s">
         <v>97</v>
-      </c>
-      <c r="G47" t="s">
-        <v>93</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -2864,16 +2864,16 @@
       <c r="B48" t="s">
         <v>8</v>
       </c>
+      <c r="C48" t="s">
+        <v>90</v>
+      </c>
       <c r="D48" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="E48" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="F48" t="s">
-        <v>92</v>
-      </c>
-      <c r="G48" t="s">
         <v>93</v>
       </c>
     </row>
@@ -2884,16 +2884,16 @@
       <c r="B49" t="s">
         <v>8</v>
       </c>
+      <c r="C49" t="s">
+        <v>90</v>
+      </c>
       <c r="D49" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="E49" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="F49" t="s">
-        <v>92</v>
-      </c>
-      <c r="G49" t="s">
         <v>93</v>
       </c>
     </row>
@@ -2904,17 +2904,17 @@
       <c r="B50" t="s">
         <v>8</v>
       </c>
+      <c r="C50" t="s">
+        <v>101</v>
+      </c>
       <c r="D50" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="E50" t="s">
-        <v>102</v>
+        <v>92</v>
       </c>
       <c r="F50" t="s">
         <v>97</v>
-      </c>
-      <c r="G50" t="s">
-        <v>93</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -2924,16 +2924,16 @@
       <c r="B51" t="s">
         <v>8</v>
       </c>
+      <c r="C51" t="s">
+        <v>90</v>
+      </c>
       <c r="D51" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="E51" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="F51" t="s">
-        <v>92</v>
-      </c>
-      <c r="G51" t="s">
         <v>93</v>
       </c>
     </row>
@@ -2944,17 +2944,17 @@
       <c r="B52" t="s">
         <v>8</v>
       </c>
+      <c r="C52" t="s">
+        <v>108</v>
+      </c>
       <c r="D52" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E52" t="s">
-        <v>109</v>
+        <v>92</v>
       </c>
       <c r="F52" t="s">
         <v>97</v>
-      </c>
-      <c r="G52" t="s">
-        <v>93</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -2964,17 +2964,17 @@
       <c r="B53" t="s">
         <v>8</v>
       </c>
+      <c r="C53" t="s">
+        <v>9</v>
+      </c>
       <c r="D53" t="s">
         <v>10</v>
       </c>
       <c r="E53" t="s">
-        <v>11</v>
+        <v>92</v>
       </c>
       <c r="F53" t="s">
         <v>12</v>
-      </c>
-      <c r="G53" t="s">
-        <v>93</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -3008,13 +3008,13 @@
         <v>8</v>
       </c>
       <c r="C55" t="s">
-        <v>112</v>
+        <v>118</v>
       </c>
       <c r="D55" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="E55" t="s">
-        <v>119</v>
+        <v>114</v>
       </c>
       <c r="F55" t="s">
         <v>115</v>
@@ -3031,13 +3031,13 @@
         <v>8</v>
       </c>
       <c r="C56" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="D56" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="E56" t="s">
-        <v>122</v>
+        <v>114</v>
       </c>
       <c r="F56" t="s">
         <v>115</v>
@@ -3054,13 +3054,13 @@
         <v>8</v>
       </c>
       <c r="C57" t="s">
-        <v>112</v>
+        <v>124</v>
       </c>
       <c r="D57" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="E57" t="s">
-        <v>125</v>
+        <v>114</v>
       </c>
       <c r="F57" t="s">
         <v>126</v>
@@ -3077,13 +3077,13 @@
         <v>8</v>
       </c>
       <c r="C58" t="s">
-        <v>112</v>
+        <v>118</v>
       </c>
       <c r="D58" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="E58" t="s">
-        <v>119</v>
+        <v>114</v>
       </c>
       <c r="F58" t="s">
         <v>115</v>
@@ -3100,13 +3100,13 @@
         <v>8</v>
       </c>
       <c r="C59" t="s">
-        <v>112</v>
+        <v>118</v>
       </c>
       <c r="D59" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="E59" t="s">
-        <v>119</v>
+        <v>114</v>
       </c>
       <c r="F59" t="s">
         <v>115</v>
@@ -3123,13 +3123,13 @@
         <v>8</v>
       </c>
       <c r="C60" t="s">
-        <v>112</v>
+        <v>118</v>
       </c>
       <c r="D60" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="E60" t="s">
-        <v>119</v>
+        <v>114</v>
       </c>
       <c r="F60" t="s">
         <v>115</v>
@@ -3146,13 +3146,13 @@
         <v>8</v>
       </c>
       <c r="C61" t="s">
-        <v>112</v>
+        <v>118</v>
       </c>
       <c r="D61" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="E61" t="s">
-        <v>119</v>
+        <v>114</v>
       </c>
       <c r="F61" t="s">
         <v>115</v>
@@ -3169,13 +3169,13 @@
         <v>8</v>
       </c>
       <c r="C62" t="s">
-        <v>112</v>
+        <v>118</v>
       </c>
       <c r="D62" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="E62" t="s">
-        <v>119</v>
+        <v>114</v>
       </c>
       <c r="F62" t="s">
         <v>115</v>
@@ -3192,13 +3192,13 @@
         <v>8</v>
       </c>
       <c r="C63" t="s">
-        <v>112</v>
+        <v>133</v>
       </c>
       <c r="D63" t="s">
-        <v>133</v>
+        <v>119</v>
       </c>
       <c r="E63" t="s">
-        <v>119</v>
+        <v>114</v>
       </c>
       <c r="F63" t="s">
         <v>115</v>
@@ -3215,13 +3215,13 @@
         <v>8</v>
       </c>
       <c r="C64" t="s">
-        <v>112</v>
+        <v>133</v>
       </c>
       <c r="D64" t="s">
-        <v>133</v>
+        <v>119</v>
       </c>
       <c r="E64" t="s">
-        <v>119</v>
+        <v>114</v>
       </c>
       <c r="F64" t="s">
         <v>115</v>
@@ -3238,13 +3238,13 @@
         <v>8</v>
       </c>
       <c r="C65" t="s">
-        <v>112</v>
+        <v>136</v>
       </c>
       <c r="D65" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="E65" t="s">
-        <v>137</v>
+        <v>114</v>
       </c>
       <c r="F65" t="s">
         <v>115</v>
@@ -3284,13 +3284,13 @@
         <v>8</v>
       </c>
       <c r="C67" t="s">
-        <v>112</v>
+        <v>118</v>
       </c>
       <c r="D67" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="E67" t="s">
-        <v>119</v>
+        <v>114</v>
       </c>
       <c r="F67" t="s">
         <v>115</v>
@@ -3307,10 +3307,10 @@
         <v>8</v>
       </c>
       <c r="C68" t="s">
-        <v>112</v>
+        <v>141</v>
       </c>
       <c r="D68" t="s">
-        <v>141</v>
+        <v>113</v>
       </c>
       <c r="E68" t="s">
         <v>114</v>
@@ -3330,10 +3330,10 @@
         <v>8</v>
       </c>
       <c r="C69" t="s">
-        <v>112</v>
+        <v>143</v>
       </c>
       <c r="D69" t="s">
-        <v>143</v>
+        <v>113</v>
       </c>
       <c r="E69" t="s">
         <v>114</v>
@@ -3353,13 +3353,13 @@
         <v>8</v>
       </c>
       <c r="C70" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="D70" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="E70" t="s">
-        <v>122</v>
+        <v>114</v>
       </c>
       <c r="F70" t="s">
         <v>115</v>
@@ -3376,13 +3376,13 @@
         <v>8</v>
       </c>
       <c r="C71" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="D71" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="E71" t="s">
-        <v>122</v>
+        <v>114</v>
       </c>
       <c r="F71" t="s">
         <v>115</v>
@@ -3422,13 +3422,13 @@
         <v>8</v>
       </c>
       <c r="C73" t="s">
-        <v>112</v>
+        <v>148</v>
       </c>
       <c r="D73" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="E73" t="s">
-        <v>149</v>
+        <v>114</v>
       </c>
       <c r="F73" t="s">
         <v>126</v>
@@ -3445,13 +3445,13 @@
         <v>8</v>
       </c>
       <c r="C74" t="s">
-        <v>112</v>
+        <v>151</v>
       </c>
       <c r="D74" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="E74" t="s">
-        <v>152</v>
+        <v>114</v>
       </c>
       <c r="F74" t="s">
         <v>126</v>
@@ -3468,13 +3468,13 @@
         <v>8</v>
       </c>
       <c r="C75" t="s">
-        <v>112</v>
+        <v>154</v>
       </c>
       <c r="D75" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="E75" t="s">
-        <v>155</v>
+        <v>114</v>
       </c>
       <c r="F75" t="s">
         <v>126</v>
@@ -3491,13 +3491,13 @@
         <v>8</v>
       </c>
       <c r="C76" t="s">
-        <v>112</v>
+        <v>148</v>
       </c>
       <c r="D76" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="E76" t="s">
-        <v>149</v>
+        <v>114</v>
       </c>
       <c r="F76" t="s">
         <v>126</v>
@@ -3514,13 +3514,13 @@
         <v>8</v>
       </c>
       <c r="C77" t="s">
-        <v>112</v>
+        <v>148</v>
       </c>
       <c r="D77" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="E77" t="s">
-        <v>149</v>
+        <v>114</v>
       </c>
       <c r="F77" t="s">
         <v>126</v>
@@ -3537,13 +3537,13 @@
         <v>8</v>
       </c>
       <c r="C78" t="s">
-        <v>112</v>
+        <v>151</v>
       </c>
       <c r="D78" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="E78" t="s">
-        <v>152</v>
+        <v>114</v>
       </c>
       <c r="F78" t="s">
         <v>126</v>
@@ -3560,13 +3560,13 @@
         <v>8</v>
       </c>
       <c r="C79" t="s">
-        <v>112</v>
+        <v>160</v>
       </c>
       <c r="D79" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="E79" t="s">
-        <v>161</v>
+        <v>114</v>
       </c>
       <c r="F79" t="s">
         <v>126</v>
@@ -3583,13 +3583,13 @@
         <v>8</v>
       </c>
       <c r="C80" t="s">
-        <v>112</v>
+        <v>163</v>
       </c>
       <c r="D80" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="E80" t="s">
-        <v>164</v>
+        <v>114</v>
       </c>
       <c r="F80" t="s">
         <v>165</v>
@@ -3606,13 +3606,13 @@
         <v>8</v>
       </c>
       <c r="C81" t="s">
-        <v>112</v>
+        <v>163</v>
       </c>
       <c r="D81" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="E81" t="s">
-        <v>164</v>
+        <v>114</v>
       </c>
       <c r="F81" t="s">
         <v>165</v>
@@ -3629,13 +3629,13 @@
         <v>8</v>
       </c>
       <c r="C82" t="s">
-        <v>112</v>
+        <v>163</v>
       </c>
       <c r="D82" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="E82" t="s">
-        <v>164</v>
+        <v>114</v>
       </c>
       <c r="F82" t="s">
         <v>165</v>
@@ -3652,10 +3652,10 @@
         <v>8</v>
       </c>
       <c r="C83" t="s">
-        <v>112</v>
+        <v>143</v>
       </c>
       <c r="D83" t="s">
-        <v>143</v>
+        <v>113</v>
       </c>
       <c r="E83" t="s">
         <v>114</v>
@@ -3675,13 +3675,13 @@
         <v>8</v>
       </c>
       <c r="C84" t="s">
-        <v>112</v>
+        <v>170</v>
       </c>
       <c r="D84" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="E84" t="s">
-        <v>171</v>
+        <v>114</v>
       </c>
       <c r="F84" t="s">
         <v>115</v>
@@ -3698,13 +3698,13 @@
         <v>8</v>
       </c>
       <c r="C85" t="s">
-        <v>112</v>
+        <v>173</v>
       </c>
       <c r="D85" t="s">
-        <v>173</v>
+        <v>119</v>
       </c>
       <c r="E85" t="s">
-        <v>119</v>
+        <v>114</v>
       </c>
       <c r="F85" t="s">
         <v>115</v>
@@ -3721,13 +3721,13 @@
         <v>8</v>
       </c>
       <c r="C86" t="s">
-        <v>112</v>
+        <v>175</v>
       </c>
       <c r="D86" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="E86" t="s">
-        <v>176</v>
+        <v>114</v>
       </c>
       <c r="F86" t="s">
         <v>165</v>
@@ -3744,13 +3744,13 @@
         <v>8</v>
       </c>
       <c r="C87" t="s">
-        <v>112</v>
+        <v>173</v>
       </c>
       <c r="D87" t="s">
-        <v>173</v>
+        <v>119</v>
       </c>
       <c r="E87" t="s">
-        <v>119</v>
+        <v>114</v>
       </c>
       <c r="F87" t="s">
         <v>115</v>
@@ -3767,13 +3767,13 @@
         <v>8</v>
       </c>
       <c r="C88" t="s">
-        <v>112</v>
+        <v>118</v>
       </c>
       <c r="D88" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="E88" t="s">
-        <v>119</v>
+        <v>114</v>
       </c>
       <c r="F88" t="s">
         <v>115</v>
@@ -3790,13 +3790,13 @@
         <v>8</v>
       </c>
       <c r="C89" t="s">
-        <v>112</v>
+        <v>118</v>
       </c>
       <c r="D89" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="E89" t="s">
-        <v>119</v>
+        <v>114</v>
       </c>
       <c r="F89" t="s">
         <v>115</v>
@@ -3813,13 +3813,13 @@
         <v>8</v>
       </c>
       <c r="C90" t="s">
-        <v>112</v>
+        <v>124</v>
       </c>
       <c r="D90" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="E90" t="s">
-        <v>125</v>
+        <v>114</v>
       </c>
       <c r="F90" t="s">
         <v>126</v>
@@ -3836,13 +3836,13 @@
         <v>8</v>
       </c>
       <c r="C91" t="s">
-        <v>112</v>
+        <v>182</v>
       </c>
       <c r="D91" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="E91" t="s">
-        <v>183</v>
+        <v>114</v>
       </c>
       <c r="F91" t="s">
         <v>184</v>
@@ -3859,13 +3859,13 @@
         <v>8</v>
       </c>
       <c r="C92" t="s">
-        <v>112</v>
+        <v>124</v>
       </c>
       <c r="D92" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="E92" t="s">
-        <v>125</v>
+        <v>114</v>
       </c>
       <c r="F92" t="s">
         <v>126</v>
@@ -3882,13 +3882,13 @@
         <v>8</v>
       </c>
       <c r="C93" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="D93" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="E93" t="s">
-        <v>122</v>
+        <v>114</v>
       </c>
       <c r="F93" t="s">
         <v>115</v>
@@ -3905,13 +3905,13 @@
         <v>8</v>
       </c>
       <c r="C94" t="s">
-        <v>112</v>
+        <v>124</v>
       </c>
       <c r="D94" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="E94" t="s">
-        <v>125</v>
+        <v>114</v>
       </c>
       <c r="F94" t="s">
         <v>126</v>
@@ -3928,13 +3928,13 @@
         <v>8</v>
       </c>
       <c r="C95" t="s">
-        <v>112</v>
+        <v>189</v>
       </c>
       <c r="D95" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="E95" t="s">
-        <v>190</v>
+        <v>114</v>
       </c>
       <c r="F95" t="s">
         <v>115</v>
@@ -3951,19 +3951,19 @@
         <v>8</v>
       </c>
       <c r="C96" t="s">
-        <v>192</v>
+        <v>124</v>
       </c>
       <c r="D96" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="E96" t="s">
-        <v>125</v>
+        <v>114</v>
       </c>
       <c r="F96" t="s">
         <v>126</v>
       </c>
       <c r="G96" t="s">
-        <v>116</v>
+        <v>192</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -3974,19 +3974,19 @@
         <v>8</v>
       </c>
       <c r="C97" t="s">
-        <v>192</v>
+        <v>124</v>
       </c>
       <c r="D97" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="E97" t="s">
-        <v>125</v>
+        <v>114</v>
       </c>
       <c r="F97" t="s">
         <v>126</v>
       </c>
       <c r="G97" t="s">
-        <v>116</v>
+        <v>192</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -3997,19 +3997,19 @@
         <v>8</v>
       </c>
       <c r="C98" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="D98" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="E98" t="s">
-        <v>196</v>
+        <v>114</v>
       </c>
       <c r="F98" t="s">
         <v>197</v>
       </c>
       <c r="G98" t="s">
-        <v>116</v>
+        <v>192</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -4020,19 +4020,19 @@
         <v>8</v>
       </c>
       <c r="C99" t="s">
-        <v>192</v>
+        <v>124</v>
       </c>
       <c r="D99" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="E99" t="s">
-        <v>125</v>
+        <v>114</v>
       </c>
       <c r="F99" t="s">
         <v>126</v>
       </c>
       <c r="G99" t="s">
-        <v>116</v>
+        <v>192</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -4043,19 +4043,19 @@
         <v>8</v>
       </c>
       <c r="C100" t="s">
-        <v>192</v>
+        <v>154</v>
       </c>
       <c r="D100" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="E100" t="s">
-        <v>155</v>
+        <v>114</v>
       </c>
       <c r="F100" t="s">
         <v>126</v>
       </c>
       <c r="G100" t="s">
-        <v>116</v>
+        <v>192</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -4066,19 +4066,19 @@
         <v>8</v>
       </c>
       <c r="C101" t="s">
-        <v>192</v>
+        <v>124</v>
       </c>
       <c r="D101" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="E101" t="s">
-        <v>125</v>
+        <v>114</v>
       </c>
       <c r="F101" t="s">
         <v>126</v>
       </c>
       <c r="G101" t="s">
-        <v>116</v>
+        <v>192</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -4088,17 +4088,17 @@
       <c r="B102" t="s">
         <v>8</v>
       </c>
+      <c r="C102" t="s">
+        <v>202</v>
+      </c>
       <c r="D102" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="E102" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="F102" t="s">
         <v>184</v>
-      </c>
-      <c r="G102" t="s">
-        <v>204</v>
       </c>
     </row>
     <row r="103" spans="1:7">
@@ -4108,17 +4108,17 @@
       <c r="B103" t="s">
         <v>8</v>
       </c>
+      <c r="C103" t="s">
+        <v>202</v>
+      </c>
       <c r="D103" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="E103" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="F103" t="s">
         <v>184</v>
-      </c>
-      <c r="G103" t="s">
-        <v>204</v>
       </c>
     </row>
     <row r="104" spans="1:7">
@@ -4128,17 +4128,17 @@
       <c r="B104" t="s">
         <v>8</v>
       </c>
+      <c r="C104" t="s">
+        <v>202</v>
+      </c>
       <c r="D104" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="E104" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="F104" t="s">
         <v>184</v>
-      </c>
-      <c r="G104" t="s">
-        <v>204</v>
       </c>
     </row>
     <row r="105" spans="1:7">
@@ -4148,17 +4148,17 @@
       <c r="B105" t="s">
         <v>8</v>
       </c>
+      <c r="C105" t="s">
+        <v>208</v>
+      </c>
       <c r="D105" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="E105" t="s">
-        <v>209</v>
+        <v>204</v>
       </c>
       <c r="F105" t="s">
         <v>184</v>
-      </c>
-      <c r="G105" t="s">
-        <v>204</v>
       </c>
     </row>
     <row r="106" spans="1:7">
@@ -4168,17 +4168,17 @@
       <c r="B106" t="s">
         <v>8</v>
       </c>
+      <c r="C106" t="s">
+        <v>202</v>
+      </c>
       <c r="D106" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="E106" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="F106" t="s">
         <v>184</v>
-      </c>
-      <c r="G106" t="s">
-        <v>204</v>
       </c>
     </row>
     <row r="107" spans="1:7">
@@ -4188,17 +4188,17 @@
       <c r="B107" t="s">
         <v>8</v>
       </c>
+      <c r="C107" t="s">
+        <v>182</v>
+      </c>
       <c r="D107" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="E107" t="s">
-        <v>183</v>
+        <v>204</v>
       </c>
       <c r="F107" t="s">
         <v>184</v>
-      </c>
-      <c r="G107" t="s">
-        <v>204</v>
       </c>
     </row>
     <row r="108" spans="1:7">
@@ -4208,17 +4208,17 @@
       <c r="B108" t="s">
         <v>8</v>
       </c>
+      <c r="C108" t="s">
+        <v>213</v>
+      </c>
       <c r="D108" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="E108" t="s">
-        <v>214</v>
+        <v>204</v>
       </c>
       <c r="F108" t="s">
         <v>184</v>
-      </c>
-      <c r="G108" t="s">
-        <v>204</v>
       </c>
     </row>
     <row r="109" spans="1:7">
@@ -4228,17 +4228,17 @@
       <c r="B109" t="s">
         <v>8</v>
       </c>
+      <c r="C109" t="s">
+        <v>216</v>
+      </c>
       <c r="D109" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="E109" t="s">
-        <v>217</v>
+        <v>204</v>
       </c>
       <c r="F109" t="s">
-        <v>92</v>
-      </c>
-      <c r="G109" t="s">
-        <v>204</v>
+        <v>93</v>
       </c>
     </row>
     <row r="110" spans="1:7">
@@ -4248,17 +4248,17 @@
       <c r="B110" t="s">
         <v>8</v>
       </c>
+      <c r="C110" t="s">
+        <v>219</v>
+      </c>
       <c r="D110" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="E110" t="s">
-        <v>220</v>
+        <v>204</v>
       </c>
       <c r="F110" t="s">
-        <v>92</v>
-      </c>
-      <c r="G110" t="s">
-        <v>204</v>
+        <v>93</v>
       </c>
     </row>
     <row r="111" spans="1:7">
@@ -4268,17 +4268,17 @@
       <c r="B111" t="s">
         <v>8</v>
       </c>
+      <c r="C111" t="s">
+        <v>202</v>
+      </c>
       <c r="D111" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="E111" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="F111" t="s">
         <v>184</v>
-      </c>
-      <c r="G111" t="s">
-        <v>204</v>
       </c>
     </row>
     <row r="112" spans="1:7">
@@ -4288,337 +4288,337 @@
       <c r="B112" t="s">
         <v>8</v>
       </c>
+      <c r="C112" t="s">
+        <v>223</v>
+      </c>
       <c r="D112" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="E112" t="s">
-        <v>224</v>
+        <v>204</v>
       </c>
       <c r="F112" t="s">
         <v>225</v>
       </c>
-      <c r="G112" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="113" spans="1:7">
+    </row>
+    <row r="113" spans="1:6">
       <c r="A113" t="s">
         <v>226</v>
       </c>
       <c r="B113" t="s">
         <v>8</v>
       </c>
+      <c r="C113" t="s">
+        <v>143</v>
+      </c>
       <c r="D113" t="s">
-        <v>143</v>
+        <v>113</v>
       </c>
       <c r="E113" t="s">
-        <v>114</v>
+        <v>204</v>
       </c>
       <c r="F113" t="s">
         <v>115</v>
       </c>
-      <c r="G113" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="114" spans="1:7">
+    </row>
+    <row r="114" spans="1:6">
       <c r="A114" t="s">
         <v>227</v>
       </c>
       <c r="B114" t="s">
         <v>8</v>
       </c>
+      <c r="C114" t="s">
+        <v>151</v>
+      </c>
       <c r="D114" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="E114" t="s">
-        <v>152</v>
+        <v>204</v>
       </c>
       <c r="F114" t="s">
         <v>126</v>
       </c>
-      <c r="G114" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="115" spans="1:7">
+    </row>
+    <row r="115" spans="1:6">
       <c r="A115" t="s">
         <v>228</v>
       </c>
       <c r="B115" t="s">
         <v>8</v>
       </c>
+      <c r="C115" t="s">
+        <v>182</v>
+      </c>
       <c r="D115" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="E115" t="s">
-        <v>183</v>
+        <v>204</v>
       </c>
       <c r="F115" t="s">
         <v>184</v>
       </c>
-      <c r="G115" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="116" spans="1:7">
+    </row>
+    <row r="116" spans="1:6">
       <c r="A116" t="s">
         <v>229</v>
       </c>
       <c r="B116" t="s">
         <v>8</v>
       </c>
+      <c r="C116" t="s">
+        <v>230</v>
+      </c>
       <c r="D116" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="E116" t="s">
-        <v>231</v>
+        <v>204</v>
       </c>
       <c r="F116" t="s">
         <v>225</v>
       </c>
-      <c r="G116" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="117" spans="1:7">
+    </row>
+    <row r="117" spans="1:6">
       <c r="A117" t="s">
         <v>232</v>
       </c>
       <c r="B117" t="s">
         <v>8</v>
       </c>
+      <c r="C117" t="s">
+        <v>223</v>
+      </c>
       <c r="D117" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="E117" t="s">
-        <v>224</v>
+        <v>204</v>
       </c>
       <c r="F117" t="s">
         <v>225</v>
       </c>
-      <c r="G117" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="118" spans="1:7">
+    </row>
+    <row r="118" spans="1:6">
       <c r="A118" t="s">
         <v>233</v>
       </c>
       <c r="B118" t="s">
         <v>8</v>
       </c>
+      <c r="C118" t="s">
+        <v>234</v>
+      </c>
       <c r="D118" t="s">
-        <v>234</v>
+        <v>164</v>
       </c>
       <c r="E118" t="s">
-        <v>164</v>
+        <v>204</v>
       </c>
       <c r="F118" t="s">
         <v>165</v>
       </c>
-      <c r="G118" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="119" spans="1:7">
+    </row>
+    <row r="119" spans="1:6">
       <c r="A119" t="s">
         <v>235</v>
       </c>
       <c r="B119" t="s">
         <v>8</v>
       </c>
+      <c r="C119" t="s">
+        <v>182</v>
+      </c>
       <c r="D119" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="E119" t="s">
-        <v>183</v>
+        <v>204</v>
       </c>
       <c r="F119" t="s">
         <v>184</v>
       </c>
-      <c r="G119" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="120" spans="1:7">
+    </row>
+    <row r="120" spans="1:6">
       <c r="A120" t="s">
         <v>236</v>
       </c>
       <c r="B120" t="s">
         <v>8</v>
       </c>
+      <c r="C120" t="s">
+        <v>170</v>
+      </c>
       <c r="D120" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="E120" t="s">
-        <v>171</v>
+        <v>237</v>
       </c>
       <c r="F120" t="s">
         <v>115</v>
       </c>
-      <c r="G120" t="s">
-        <v>237</v>
-      </c>
-    </row>
-    <row r="121" spans="1:7">
+    </row>
+    <row r="121" spans="1:6">
       <c r="A121" t="s">
         <v>238</v>
       </c>
       <c r="B121" t="s">
         <v>8</v>
       </c>
+      <c r="C121" t="s">
+        <v>143</v>
+      </c>
       <c r="D121" t="s">
-        <v>143</v>
+        <v>113</v>
       </c>
       <c r="E121" t="s">
-        <v>114</v>
+        <v>237</v>
       </c>
       <c r="F121" t="s">
         <v>115</v>
       </c>
-      <c r="G121" t="s">
-        <v>237</v>
-      </c>
-    </row>
-    <row r="122" spans="1:7">
+    </row>
+    <row r="122" spans="1:6">
       <c r="A122" t="s">
         <v>239</v>
       </c>
       <c r="B122" t="s">
         <v>8</v>
       </c>
+      <c r="C122" t="s">
+        <v>170</v>
+      </c>
       <c r="D122" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="E122" t="s">
-        <v>171</v>
+        <v>237</v>
       </c>
       <c r="F122" t="s">
         <v>115</v>
       </c>
-      <c r="G122" t="s">
-        <v>237</v>
-      </c>
-    </row>
-    <row r="123" spans="1:7">
+    </row>
+    <row r="123" spans="1:6">
       <c r="A123" t="s">
         <v>240</v>
       </c>
       <c r="B123" t="s">
         <v>8</v>
       </c>
+      <c r="C123" t="s">
+        <v>170</v>
+      </c>
       <c r="D123" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="E123" t="s">
-        <v>171</v>
+        <v>237</v>
       </c>
       <c r="F123" t="s">
         <v>115</v>
       </c>
-      <c r="G123" t="s">
-        <v>237</v>
-      </c>
-    </row>
-    <row r="124" spans="1:7">
+    </row>
+    <row r="124" spans="1:6">
       <c r="A124" t="s">
         <v>241</v>
       </c>
       <c r="B124" t="s">
         <v>8</v>
       </c>
+      <c r="C124" t="s">
+        <v>242</v>
+      </c>
       <c r="D124" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="E124" t="s">
-        <v>243</v>
+        <v>237</v>
       </c>
       <c r="F124" t="s">
         <v>165</v>
       </c>
-      <c r="G124" t="s">
-        <v>237</v>
-      </c>
-    </row>
-    <row r="125" spans="1:7">
+    </row>
+    <row r="125" spans="1:6">
       <c r="A125" t="s">
         <v>244</v>
       </c>
       <c r="B125" t="s">
         <v>8</v>
       </c>
+      <c r="C125" t="s">
+        <v>242</v>
+      </c>
       <c r="D125" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="E125" t="s">
-        <v>243</v>
+        <v>237</v>
       </c>
       <c r="F125" t="s">
         <v>165</v>
       </c>
-      <c r="G125" t="s">
-        <v>237</v>
-      </c>
-    </row>
-    <row r="126" spans="1:7">
+    </row>
+    <row r="126" spans="1:6">
       <c r="A126" t="s">
         <v>245</v>
       </c>
       <c r="B126" t="s">
         <v>8</v>
       </c>
+      <c r="C126" t="s">
+        <v>242</v>
+      </c>
       <c r="D126" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="E126" t="s">
-        <v>243</v>
+        <v>237</v>
       </c>
       <c r="F126" t="s">
         <v>165</v>
       </c>
-      <c r="G126" t="s">
-        <v>237</v>
-      </c>
-    </row>
-    <row r="127" spans="1:7">
+    </row>
+    <row r="127" spans="1:6">
       <c r="A127" t="s">
         <v>246</v>
       </c>
       <c r="B127" t="s">
         <v>8</v>
       </c>
+      <c r="C127" t="s">
+        <v>242</v>
+      </c>
       <c r="D127" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="E127" t="s">
-        <v>243</v>
+        <v>237</v>
       </c>
       <c r="F127" t="s">
         <v>165</v>
       </c>
-      <c r="G127" t="s">
-        <v>237</v>
-      </c>
-    </row>
-    <row r="128" spans="1:7">
+    </row>
+    <row r="128" spans="1:6">
       <c r="A128" t="s">
         <v>247</v>
       </c>
       <c r="B128" t="s">
         <v>8</v>
       </c>
+      <c r="C128" t="s">
+        <v>242</v>
+      </c>
       <c r="D128" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="E128" t="s">
-        <v>243</v>
+        <v>237</v>
       </c>
       <c r="F128" t="s">
         <v>165</v>
-      </c>
-      <c r="G128" t="s">
-        <v>237</v>
       </c>
     </row>
     <row r="129" spans="1:7">
@@ -4628,17 +4628,17 @@
       <c r="B129" t="s">
         <v>8</v>
       </c>
+      <c r="C129" t="s">
+        <v>249</v>
+      </c>
       <c r="D129" t="s">
-        <v>249</v>
+        <v>243</v>
       </c>
       <c r="E129" t="s">
-        <v>243</v>
+        <v>237</v>
       </c>
       <c r="F129" t="s">
         <v>165</v>
-      </c>
-      <c r="G129" t="s">
-        <v>237</v>
       </c>
     </row>
     <row r="130" spans="1:7">
@@ -4648,17 +4648,17 @@
       <c r="B130" t="s">
         <v>8</v>
       </c>
+      <c r="C130" t="s">
+        <v>251</v>
+      </c>
       <c r="D130" t="s">
-        <v>251</v>
+        <v>243</v>
       </c>
       <c r="E130" t="s">
-        <v>243</v>
+        <v>237</v>
       </c>
       <c r="F130" t="s">
         <v>165</v>
-      </c>
-      <c r="G130" t="s">
-        <v>237</v>
       </c>
     </row>
     <row r="131" spans="1:7">
@@ -4668,17 +4668,17 @@
       <c r="B131" t="s">
         <v>8</v>
       </c>
+      <c r="C131" t="s">
+        <v>253</v>
+      </c>
       <c r="D131" t="s">
-        <v>253</v>
+        <v>243</v>
       </c>
       <c r="E131" t="s">
-        <v>243</v>
+        <v>237</v>
       </c>
       <c r="F131" t="s">
         <v>165</v>
-      </c>
-      <c r="G131" t="s">
-        <v>237</v>
       </c>
     </row>
     <row r="132" spans="1:7">
@@ -4688,17 +4688,17 @@
       <c r="B132" t="s">
         <v>8</v>
       </c>
+      <c r="C132" t="s">
+        <v>255</v>
+      </c>
       <c r="D132" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="E132" t="s">
-        <v>256</v>
+        <v>237</v>
       </c>
       <c r="F132" t="s">
         <v>165</v>
-      </c>
-      <c r="G132" t="s">
-        <v>237</v>
       </c>
     </row>
     <row r="133" spans="1:7">
@@ -4708,17 +4708,17 @@
       <c r="B133" t="s">
         <v>8</v>
       </c>
+      <c r="C133" t="s">
+        <v>189</v>
+      </c>
       <c r="D133" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="E133" t="s">
-        <v>190</v>
+        <v>237</v>
       </c>
       <c r="F133" t="s">
         <v>115</v>
-      </c>
-      <c r="G133" t="s">
-        <v>237</v>
       </c>
     </row>
     <row r="134" spans="1:7">
@@ -4728,17 +4728,17 @@
       <c r="B134" t="s">
         <v>8</v>
       </c>
+      <c r="C134" t="s">
+        <v>175</v>
+      </c>
       <c r="D134" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="E134" t="s">
-        <v>176</v>
+        <v>259</v>
       </c>
       <c r="F134" t="s">
         <v>165</v>
-      </c>
-      <c r="G134" t="s">
-        <v>259</v>
       </c>
     </row>
     <row r="135" spans="1:7">
@@ -4748,17 +4748,17 @@
       <c r="B135" t="s">
         <v>8</v>
       </c>
+      <c r="C135" t="s">
+        <v>175</v>
+      </c>
       <c r="D135" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="E135" t="s">
-        <v>176</v>
+        <v>259</v>
       </c>
       <c r="F135" t="s">
         <v>165</v>
-      </c>
-      <c r="G135" t="s">
-        <v>259</v>
       </c>
     </row>
     <row r="136" spans="1:7">
@@ -4768,17 +4768,17 @@
       <c r="B136" t="s">
         <v>8</v>
       </c>
+      <c r="C136" t="s">
+        <v>175</v>
+      </c>
       <c r="D136" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="E136" t="s">
-        <v>176</v>
+        <v>259</v>
       </c>
       <c r="F136" t="s">
         <v>165</v>
-      </c>
-      <c r="G136" t="s">
-        <v>259</v>
       </c>
     </row>
     <row r="137" spans="1:7">
@@ -4788,17 +4788,17 @@
       <c r="B137" t="s">
         <v>8</v>
       </c>
+      <c r="C137" t="s">
+        <v>175</v>
+      </c>
       <c r="D137" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="E137" t="s">
-        <v>176</v>
+        <v>259</v>
       </c>
       <c r="F137" t="s">
         <v>165</v>
-      </c>
-      <c r="G137" t="s">
-        <v>259</v>
       </c>
     </row>
     <row r="138" spans="1:7">
@@ -4808,17 +4808,17 @@
       <c r="B138" t="s">
         <v>8</v>
       </c>
+      <c r="C138" t="s">
+        <v>175</v>
+      </c>
       <c r="D138" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="E138" t="s">
-        <v>176</v>
+        <v>259</v>
       </c>
       <c r="F138" t="s">
         <v>165</v>
-      </c>
-      <c r="G138" t="s">
-        <v>259</v>
       </c>
     </row>
     <row r="139" spans="1:7">
@@ -4828,17 +4828,17 @@
       <c r="B139" t="s">
         <v>8</v>
       </c>
+      <c r="C139" t="s">
+        <v>265</v>
+      </c>
       <c r="D139" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="E139" t="s">
-        <v>266</v>
+        <v>259</v>
       </c>
       <c r="F139" t="s">
         <v>225</v>
-      </c>
-      <c r="G139" t="s">
-        <v>259</v>
       </c>
     </row>
     <row r="140" spans="1:7">
@@ -4848,17 +4848,17 @@
       <c r="B140" t="s">
         <v>8</v>
       </c>
+      <c r="C140" t="s">
+        <v>175</v>
+      </c>
       <c r="D140" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="E140" t="s">
-        <v>176</v>
+        <v>259</v>
       </c>
       <c r="F140" t="s">
         <v>165</v>
-      </c>
-      <c r="G140" t="s">
-        <v>259</v>
       </c>
     </row>
     <row r="141" spans="1:7">
@@ -4915,13 +4915,13 @@
         <v>8</v>
       </c>
       <c r="C143" t="s">
-        <v>269</v>
+        <v>275</v>
       </c>
       <c r="D143" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="E143" t="s">
-        <v>276</v>
+        <v>271</v>
       </c>
       <c r="F143" t="s">
         <v>165</v>
@@ -4938,13 +4938,13 @@
         <v>8</v>
       </c>
       <c r="C144" t="s">
-        <v>269</v>
+        <v>275</v>
       </c>
       <c r="D144" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="E144" t="s">
-        <v>276</v>
+        <v>271</v>
       </c>
       <c r="F144" t="s">
         <v>165</v>
@@ -4961,13 +4961,13 @@
         <v>8</v>
       </c>
       <c r="C145" t="s">
-        <v>269</v>
+        <v>275</v>
       </c>
       <c r="D145" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="E145" t="s">
-        <v>276</v>
+        <v>271</v>
       </c>
       <c r="F145" t="s">
         <v>165</v>
@@ -5007,7 +5007,7 @@
         <v>8</v>
       </c>
       <c r="C147" t="s">
-        <v>281</v>
+        <v>269</v>
       </c>
       <c r="D147" t="s">
         <v>270</v>
@@ -5019,7 +5019,7 @@
         <v>165</v>
       </c>
       <c r="G147" t="s">
-        <v>272</v>
+        <v>281</v>
       </c>
     </row>
     <row r="148" spans="1:7">
@@ -5030,7 +5030,7 @@
         <v>8</v>
       </c>
       <c r="C148" t="s">
-        <v>281</v>
+        <v>269</v>
       </c>
       <c r="D148" t="s">
         <v>270</v>
@@ -5042,7 +5042,7 @@
         <v>165</v>
       </c>
       <c r="G148" t="s">
-        <v>272</v>
+        <v>281</v>
       </c>
     </row>
     <row r="149" spans="1:7">
@@ -5053,7 +5053,7 @@
         <v>8</v>
       </c>
       <c r="C149" t="s">
-        <v>281</v>
+        <v>269</v>
       </c>
       <c r="D149" t="s">
         <v>270</v>
@@ -5065,7 +5065,7 @@
         <v>165</v>
       </c>
       <c r="G149" t="s">
-        <v>272</v>
+        <v>281</v>
       </c>
     </row>
     <row r="150" spans="1:7">
@@ -5076,7 +5076,7 @@
         <v>8</v>
       </c>
       <c r="C150" t="s">
-        <v>281</v>
+        <v>269</v>
       </c>
       <c r="D150" t="s">
         <v>270</v>
@@ -5088,7 +5088,7 @@
         <v>165</v>
       </c>
       <c r="G150" t="s">
-        <v>272</v>
+        <v>281</v>
       </c>
     </row>
     <row r="151" spans="1:7">
@@ -5099,7 +5099,7 @@
         <v>8</v>
       </c>
       <c r="C151" t="s">
-        <v>281</v>
+        <v>269</v>
       </c>
       <c r="D151" t="s">
         <v>270</v>
@@ -5111,7 +5111,7 @@
         <v>165</v>
       </c>
       <c r="G151" t="s">
-        <v>272</v>
+        <v>281</v>
       </c>
     </row>
     <row r="152" spans="1:7">
@@ -5122,7 +5122,7 @@
         <v>8</v>
       </c>
       <c r="C152" t="s">
-        <v>281</v>
+        <v>269</v>
       </c>
       <c r="D152" t="s">
         <v>270</v>
@@ -5134,7 +5134,7 @@
         <v>165</v>
       </c>
       <c r="G152" t="s">
-        <v>272</v>
+        <v>281</v>
       </c>
     </row>
     <row r="153" spans="1:7">
@@ -5145,7 +5145,7 @@
         <v>8</v>
       </c>
       <c r="C153" t="s">
-        <v>281</v>
+        <v>269</v>
       </c>
       <c r="D153" t="s">
         <v>270</v>
@@ -5157,7 +5157,7 @@
         <v>165</v>
       </c>
       <c r="G153" t="s">
-        <v>272</v>
+        <v>281</v>
       </c>
     </row>
     <row r="154" spans="1:7">
@@ -5168,7 +5168,7 @@
         <v>8</v>
       </c>
       <c r="C154" t="s">
-        <v>281</v>
+        <v>269</v>
       </c>
       <c r="D154" t="s">
         <v>270</v>
@@ -5180,7 +5180,7 @@
         <v>165</v>
       </c>
       <c r="G154" t="s">
-        <v>272</v>
+        <v>281</v>
       </c>
     </row>
     <row r="155" spans="1:7">
@@ -5191,7 +5191,7 @@
         <v>8</v>
       </c>
       <c r="C155" t="s">
-        <v>281</v>
+        <v>269</v>
       </c>
       <c r="D155" t="s">
         <v>270</v>
@@ -5203,7 +5203,7 @@
         <v>165</v>
       </c>
       <c r="G155" t="s">
-        <v>272</v>
+        <v>281</v>
       </c>
     </row>
     <row r="156" spans="1:7">
@@ -5214,7 +5214,7 @@
         <v>8</v>
       </c>
       <c r="C156" t="s">
-        <v>291</v>
+        <v>269</v>
       </c>
       <c r="D156" t="s">
         <v>270</v>
@@ -5226,7 +5226,7 @@
         <v>165</v>
       </c>
       <c r="G156" t="s">
-        <v>272</v>
+        <v>291</v>
       </c>
     </row>
     <row r="157" spans="1:7">
@@ -5237,10 +5237,10 @@
         <v>8</v>
       </c>
       <c r="C157" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="D157" t="s">
-        <v>293</v>
+        <v>270</v>
       </c>
       <c r="E157" t="s">
         <v>271</v>
@@ -5249,7 +5249,7 @@
         <v>165</v>
       </c>
       <c r="G157" t="s">
-        <v>272</v>
+        <v>291</v>
       </c>
     </row>
     <row r="158" spans="1:7">
@@ -5260,7 +5260,7 @@
         <v>8</v>
       </c>
       <c r="C158" t="s">
-        <v>291</v>
+        <v>269</v>
       </c>
       <c r="D158" t="s">
         <v>270</v>
@@ -5272,7 +5272,7 @@
         <v>165</v>
       </c>
       <c r="G158" t="s">
-        <v>272</v>
+        <v>291</v>
       </c>
     </row>
     <row r="159" spans="1:7">
@@ -5283,7 +5283,7 @@
         <v>8</v>
       </c>
       <c r="C159" t="s">
-        <v>291</v>
+        <v>269</v>
       </c>
       <c r="D159" t="s">
         <v>270</v>
@@ -5295,7 +5295,7 @@
         <v>165</v>
       </c>
       <c r="G159" t="s">
-        <v>272</v>
+        <v>291</v>
       </c>
     </row>
     <row r="160" spans="1:7">
@@ -5306,7 +5306,7 @@
         <v>8</v>
       </c>
       <c r="C160" t="s">
-        <v>291</v>
+        <v>269</v>
       </c>
       <c r="D160" t="s">
         <v>270</v>
@@ -5318,7 +5318,7 @@
         <v>165</v>
       </c>
       <c r="G160" t="s">
-        <v>272</v>
+        <v>291</v>
       </c>
     </row>
     <row r="161" spans="1:7">
@@ -5329,7 +5329,7 @@
         <v>8</v>
       </c>
       <c r="C161" t="s">
-        <v>291</v>
+        <v>269</v>
       </c>
       <c r="D161" t="s">
         <v>270</v>
@@ -5341,7 +5341,7 @@
         <v>165</v>
       </c>
       <c r="G161" t="s">
-        <v>272</v>
+        <v>291</v>
       </c>
     </row>
     <row r="162" spans="1:7">
@@ -5352,7 +5352,7 @@
         <v>8</v>
       </c>
       <c r="C162" t="s">
-        <v>299</v>
+        <v>269</v>
       </c>
       <c r="D162" t="s">
         <v>270</v>
@@ -5364,7 +5364,7 @@
         <v>165</v>
       </c>
       <c r="G162" t="s">
-        <v>272</v>
+        <v>299</v>
       </c>
     </row>
     <row r="163" spans="1:7">
@@ -5378,7 +5378,7 @@
         <v>301</v>
       </c>
       <c r="D163" t="s">
-        <v>302</v>
+        <v>270</v>
       </c>
       <c r="E163" t="s">
         <v>271</v>
@@ -5387,7 +5387,7 @@
         <v>165</v>
       </c>
       <c r="G163" t="s">
-        <v>272</v>
+        <v>302</v>
       </c>
     </row>
     <row r="164" spans="1:7">
@@ -5398,7 +5398,7 @@
         <v>8</v>
       </c>
       <c r="C164" t="s">
-        <v>304</v>
+        <v>269</v>
       </c>
       <c r="D164" t="s">
         <v>270</v>
@@ -5410,7 +5410,7 @@
         <v>165</v>
       </c>
       <c r="G164" t="s">
-        <v>272</v>
+        <v>304</v>
       </c>
     </row>
     <row r="165" spans="1:7">
@@ -5421,7 +5421,7 @@
         <v>8</v>
       </c>
       <c r="C165" t="s">
-        <v>304</v>
+        <v>269</v>
       </c>
       <c r="D165" t="s">
         <v>270</v>
@@ -5433,7 +5433,7 @@
         <v>165</v>
       </c>
       <c r="G165" t="s">
-        <v>272</v>
+        <v>304</v>
       </c>
     </row>
     <row r="166" spans="1:7">
@@ -5444,7 +5444,7 @@
         <v>8</v>
       </c>
       <c r="C166" t="s">
-        <v>304</v>
+        <v>269</v>
       </c>
       <c r="D166" t="s">
         <v>270</v>
@@ -5456,7 +5456,7 @@
         <v>165</v>
       </c>
       <c r="G166" t="s">
-        <v>272</v>
+        <v>304</v>
       </c>
     </row>
     <row r="167" spans="1:7">
@@ -5467,7 +5467,7 @@
         <v>8</v>
       </c>
       <c r="C167" t="s">
-        <v>304</v>
+        <v>269</v>
       </c>
       <c r="D167" t="s">
         <v>270</v>
@@ -5479,7 +5479,7 @@
         <v>165</v>
       </c>
       <c r="G167" t="s">
-        <v>272</v>
+        <v>304</v>
       </c>
     </row>
     <row r="168" spans="1:7">
@@ -5490,10 +5490,10 @@
         <v>8</v>
       </c>
       <c r="C168" t="s">
-        <v>304</v>
+        <v>309</v>
       </c>
       <c r="D168" t="s">
-        <v>309</v>
+        <v>270</v>
       </c>
       <c r="E168" t="s">
         <v>271</v>
@@ -5502,7 +5502,7 @@
         <v>165</v>
       </c>
       <c r="G168" t="s">
-        <v>272</v>
+        <v>304</v>
       </c>
     </row>
     <row r="169" spans="1:7">
@@ -5513,10 +5513,10 @@
         <v>8</v>
       </c>
       <c r="C169" t="s">
-        <v>304</v>
+        <v>309</v>
       </c>
       <c r="D169" t="s">
-        <v>309</v>
+        <v>270</v>
       </c>
       <c r="E169" t="s">
         <v>271</v>
@@ -5525,7 +5525,7 @@
         <v>165</v>
       </c>
       <c r="G169" t="s">
-        <v>272</v>
+        <v>304</v>
       </c>
     </row>
     <row r="170" spans="1:7">
@@ -5536,7 +5536,7 @@
         <v>8</v>
       </c>
       <c r="C170" t="s">
-        <v>304</v>
+        <v>269</v>
       </c>
       <c r="D170" t="s">
         <v>270</v>
@@ -5548,7 +5548,7 @@
         <v>165</v>
       </c>
       <c r="G170" t="s">
-        <v>272</v>
+        <v>304</v>
       </c>
     </row>
     <row r="171" spans="1:7">
@@ -5558,17 +5558,17 @@
       <c r="B171" t="s">
         <v>8</v>
       </c>
+      <c r="C171" t="s">
+        <v>163</v>
+      </c>
       <c r="D171" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="E171" t="s">
-        <v>164</v>
+        <v>313</v>
       </c>
       <c r="F171" t="s">
         <v>165</v>
-      </c>
-      <c r="G171" t="s">
-        <v>313</v>
       </c>
     </row>
     <row r="172" spans="1:7">
@@ -5578,17 +5578,17 @@
       <c r="B172" t="s">
         <v>8</v>
       </c>
+      <c r="C172" t="s">
+        <v>118</v>
+      </c>
       <c r="D172" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="E172" t="s">
-        <v>119</v>
+        <v>313</v>
       </c>
       <c r="F172" t="s">
         <v>115</v>
-      </c>
-      <c r="G172" t="s">
-        <v>313</v>
       </c>
     </row>
     <row r="173" spans="1:7">
@@ -5598,17 +5598,17 @@
       <c r="B173" t="s">
         <v>8</v>
       </c>
+      <c r="C173" t="s">
+        <v>163</v>
+      </c>
       <c r="D173" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="E173" t="s">
-        <v>164</v>
+        <v>313</v>
       </c>
       <c r="F173" t="s">
         <v>165</v>
-      </c>
-      <c r="G173" t="s">
-        <v>313</v>
       </c>
     </row>
     <row r="174" spans="1:7">
@@ -5618,17 +5618,17 @@
       <c r="B174" t="s">
         <v>8</v>
       </c>
+      <c r="C174" t="s">
+        <v>163</v>
+      </c>
       <c r="D174" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="E174" t="s">
-        <v>164</v>
+        <v>313</v>
       </c>
       <c r="F174" t="s">
         <v>165</v>
-      </c>
-      <c r="G174" t="s">
-        <v>313</v>
       </c>
     </row>
     <row r="175" spans="1:7">
@@ -5638,17 +5638,17 @@
       <c r="B175" t="s">
         <v>8</v>
       </c>
+      <c r="C175" t="s">
+        <v>163</v>
+      </c>
       <c r="D175" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="E175" t="s">
-        <v>164</v>
+        <v>313</v>
       </c>
       <c r="F175" t="s">
         <v>165</v>
-      </c>
-      <c r="G175" t="s">
-        <v>313</v>
       </c>
     </row>
     <row r="176" spans="1:7">
@@ -5658,17 +5658,17 @@
       <c r="B176" t="s">
         <v>8</v>
       </c>
+      <c r="C176" t="s">
+        <v>163</v>
+      </c>
       <c r="D176" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="E176" t="s">
-        <v>164</v>
+        <v>313</v>
       </c>
       <c r="F176" t="s">
         <v>165</v>
-      </c>
-      <c r="G176" t="s">
-        <v>313</v>
       </c>
     </row>
     <row r="177" spans="1:7">
@@ -5678,17 +5678,17 @@
       <c r="B177" t="s">
         <v>8</v>
       </c>
+      <c r="C177" t="s">
+        <v>163</v>
+      </c>
       <c r="D177" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="E177" t="s">
-        <v>164</v>
+        <v>320</v>
       </c>
       <c r="F177" t="s">
         <v>165</v>
-      </c>
-      <c r="G177" t="s">
-        <v>320</v>
       </c>
     </row>
     <row r="178" spans="1:7">
@@ -5698,17 +5698,17 @@
       <c r="B178" t="s">
         <v>8</v>
       </c>
+      <c r="C178" t="s">
+        <v>163</v>
+      </c>
       <c r="D178" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="E178" t="s">
-        <v>164</v>
+        <v>320</v>
       </c>
       <c r="F178" t="s">
         <v>165</v>
-      </c>
-      <c r="G178" t="s">
-        <v>320</v>
       </c>
     </row>
     <row r="179" spans="1:7">
@@ -5718,17 +5718,17 @@
       <c r="B179" t="s">
         <v>8</v>
       </c>
+      <c r="C179" t="s">
+        <v>163</v>
+      </c>
       <c r="D179" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="E179" t="s">
-        <v>164</v>
+        <v>320</v>
       </c>
       <c r="F179" t="s">
         <v>165</v>
-      </c>
-      <c r="G179" t="s">
-        <v>320</v>
       </c>
     </row>
     <row r="180" spans="1:7">
@@ -5738,17 +5738,17 @@
       <c r="B180" t="s">
         <v>8</v>
       </c>
+      <c r="C180" t="s">
+        <v>163</v>
+      </c>
       <c r="D180" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="E180" t="s">
-        <v>164</v>
+        <v>320</v>
       </c>
       <c r="F180" t="s">
         <v>165</v>
-      </c>
-      <c r="G180" t="s">
-        <v>320</v>
       </c>
     </row>
     <row r="181" spans="1:7">
@@ -6035,13 +6035,13 @@
         <v>8</v>
       </c>
       <c r="C193" t="s">
-        <v>325</v>
+        <v>341</v>
       </c>
       <c r="D193" t="s">
-        <v>341</v>
+        <v>276</v>
       </c>
       <c r="E193" t="s">
-        <v>276</v>
+        <v>327</v>
       </c>
       <c r="F193" t="s">
         <v>165</v>
@@ -6176,7 +6176,7 @@
         <v>348</v>
       </c>
       <c r="D199" t="s">
-        <v>349</v>
+        <v>326</v>
       </c>
       <c r="E199" t="s">
         <v>327</v>
@@ -6185,7 +6185,7 @@
         <v>165</v>
       </c>
       <c r="G199" t="s">
-        <v>328</v>
+        <v>349</v>
       </c>
     </row>
     <row r="200" spans="1:7">
@@ -6199,7 +6199,7 @@
         <v>348</v>
       </c>
       <c r="D200" t="s">
-        <v>349</v>
+        <v>326</v>
       </c>
       <c r="E200" t="s">
         <v>327</v>
@@ -6208,7 +6208,7 @@
         <v>165</v>
       </c>
       <c r="G200" t="s">
-        <v>328</v>
+        <v>349</v>
       </c>
     </row>
     <row r="201" spans="1:7">
@@ -6222,7 +6222,7 @@
         <v>348</v>
       </c>
       <c r="D201" t="s">
-        <v>349</v>
+        <v>326</v>
       </c>
       <c r="E201" t="s">
         <v>327</v>
@@ -6231,7 +6231,7 @@
         <v>165</v>
       </c>
       <c r="G201" t="s">
-        <v>328</v>
+        <v>349</v>
       </c>
     </row>
     <row r="202" spans="1:7">
@@ -6245,7 +6245,7 @@
         <v>348</v>
       </c>
       <c r="D202" t="s">
-        <v>349</v>
+        <v>326</v>
       </c>
       <c r="E202" t="s">
         <v>327</v>
@@ -6254,7 +6254,7 @@
         <v>165</v>
       </c>
       <c r="G202" t="s">
-        <v>328</v>
+        <v>349</v>
       </c>
     </row>
     <row r="203" spans="1:7">
@@ -6265,19 +6265,19 @@
         <v>8</v>
       </c>
       <c r="C203" t="s">
-        <v>348</v>
+        <v>341</v>
       </c>
       <c r="D203" t="s">
-        <v>341</v>
+        <v>276</v>
       </c>
       <c r="E203" t="s">
-        <v>276</v>
+        <v>327</v>
       </c>
       <c r="F203" t="s">
         <v>165</v>
       </c>
       <c r="G203" t="s">
-        <v>328</v>
+        <v>349</v>
       </c>
     </row>
     <row r="204" spans="1:7">
@@ -6291,7 +6291,7 @@
         <v>348</v>
       </c>
       <c r="D204" t="s">
-        <v>349</v>
+        <v>326</v>
       </c>
       <c r="E204" t="s">
         <v>327</v>
@@ -6300,7 +6300,7 @@
         <v>165</v>
       </c>
       <c r="G204" t="s">
-        <v>328</v>
+        <v>349</v>
       </c>
     </row>
     <row r="205" spans="1:7">
@@ -6314,7 +6314,7 @@
         <v>356</v>
       </c>
       <c r="D205" t="s">
-        <v>357</v>
+        <v>326</v>
       </c>
       <c r="E205" t="s">
         <v>327</v>
@@ -6323,7 +6323,7 @@
         <v>165</v>
       </c>
       <c r="G205" t="s">
-        <v>328</v>
+        <v>357</v>
       </c>
     </row>
     <row r="206" spans="1:7">
@@ -6337,7 +6337,7 @@
         <v>356</v>
       </c>
       <c r="D206" t="s">
-        <v>357</v>
+        <v>326</v>
       </c>
       <c r="E206" t="s">
         <v>327</v>
@@ -6346,7 +6346,7 @@
         <v>165</v>
       </c>
       <c r="G206" t="s">
-        <v>328</v>
+        <v>357</v>
       </c>
     </row>
     <row r="207" spans="1:7">
@@ -6360,7 +6360,7 @@
         <v>356</v>
       </c>
       <c r="D207" t="s">
-        <v>357</v>
+        <v>326</v>
       </c>
       <c r="E207" t="s">
         <v>327</v>
@@ -6369,7 +6369,7 @@
         <v>165</v>
       </c>
       <c r="G207" t="s">
-        <v>328</v>
+        <v>357</v>
       </c>
     </row>
     <row r="208" spans="1:7">
@@ -6380,19 +6380,19 @@
         <v>8</v>
       </c>
       <c r="C208" t="s">
-        <v>356</v>
+        <v>341</v>
       </c>
       <c r="D208" t="s">
-        <v>341</v>
+        <v>276</v>
       </c>
       <c r="E208" t="s">
-        <v>276</v>
+        <v>327</v>
       </c>
       <c r="F208" t="s">
         <v>165</v>
       </c>
       <c r="G208" t="s">
-        <v>328</v>
+        <v>357</v>
       </c>
     </row>
     <row r="209" spans="1:7">
@@ -6406,7 +6406,7 @@
         <v>356</v>
       </c>
       <c r="D209" t="s">
-        <v>357</v>
+        <v>326</v>
       </c>
       <c r="E209" t="s">
         <v>327</v>
@@ -6415,7 +6415,7 @@
         <v>165</v>
       </c>
       <c r="G209" t="s">
-        <v>328</v>
+        <v>357</v>
       </c>
     </row>
     <row r="210" spans="1:7">
@@ -6541,13 +6541,13 @@
         <v>8</v>
       </c>
       <c r="C215" t="s">
-        <v>363</v>
+        <v>348</v>
       </c>
       <c r="D215" t="s">
-        <v>349</v>
+        <v>326</v>
       </c>
       <c r="E215" t="s">
-        <v>327</v>
+        <v>365</v>
       </c>
       <c r="F215" t="s">
         <v>165</v>
@@ -6656,13 +6656,13 @@
         <v>8</v>
       </c>
       <c r="C220" t="s">
-        <v>363</v>
+        <v>309</v>
       </c>
       <c r="D220" t="s">
-        <v>309</v>
+        <v>270</v>
       </c>
       <c r="E220" t="s">
-        <v>271</v>
+        <v>365</v>
       </c>
       <c r="F220" t="s">
         <v>165</v>
@@ -6794,13 +6794,13 @@
         <v>8</v>
       </c>
       <c r="C226" t="s">
-        <v>363</v>
+        <v>275</v>
       </c>
       <c r="D226" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="E226" t="s">
-        <v>276</v>
+        <v>365</v>
       </c>
       <c r="F226" t="s">
         <v>165</v>
@@ -6840,13 +6840,13 @@
         <v>8</v>
       </c>
       <c r="C228" t="s">
-        <v>363</v>
+        <v>163</v>
       </c>
       <c r="D228" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="E228" t="s">
-        <v>164</v>
+        <v>365</v>
       </c>
       <c r="F228" t="s">
         <v>165</v>
@@ -6866,7 +6866,7 @@
         <v>386</v>
       </c>
       <c r="D229" t="s">
-        <v>387</v>
+        <v>364</v>
       </c>
       <c r="E229" t="s">
         <v>365</v>
@@ -6875,7 +6875,7 @@
         <v>165</v>
       </c>
       <c r="G229" t="s">
-        <v>366</v>
+        <v>387</v>
       </c>
     </row>
     <row r="230" spans="1:7">
@@ -6889,7 +6889,7 @@
         <v>386</v>
       </c>
       <c r="D230" t="s">
-        <v>387</v>
+        <v>364</v>
       </c>
       <c r="E230" t="s">
         <v>365</v>
@@ -6898,7 +6898,7 @@
         <v>165</v>
       </c>
       <c r="G230" t="s">
-        <v>366</v>
+        <v>387</v>
       </c>
     </row>
     <row r="231" spans="1:7">
@@ -6909,19 +6909,19 @@
         <v>8</v>
       </c>
       <c r="C231" t="s">
-        <v>386</v>
+        <v>293</v>
       </c>
       <c r="D231" t="s">
-        <v>293</v>
+        <v>270</v>
       </c>
       <c r="E231" t="s">
-        <v>271</v>
+        <v>365</v>
       </c>
       <c r="F231" t="s">
         <v>165</v>
       </c>
       <c r="G231" t="s">
-        <v>366</v>
+        <v>387</v>
       </c>
     </row>
     <row r="232" spans="1:7">
@@ -6932,19 +6932,19 @@
         <v>8</v>
       </c>
       <c r="C232" t="s">
-        <v>386</v>
+        <v>309</v>
       </c>
       <c r="D232" t="s">
-        <v>309</v>
+        <v>270</v>
       </c>
       <c r="E232" t="s">
-        <v>271</v>
+        <v>365</v>
       </c>
       <c r="F232" t="s">
         <v>165</v>
       </c>
       <c r="G232" t="s">
-        <v>366</v>
+        <v>387</v>
       </c>
     </row>
     <row r="233" spans="1:7">
@@ -6958,7 +6958,7 @@
         <v>386</v>
       </c>
       <c r="D233" t="s">
-        <v>387</v>
+        <v>364</v>
       </c>
       <c r="E233" t="s">
         <v>365</v>
@@ -6967,7 +6967,7 @@
         <v>165</v>
       </c>
       <c r="G233" t="s">
-        <v>366</v>
+        <v>387</v>
       </c>
     </row>
     <row r="234" spans="1:7">
@@ -6981,7 +6981,7 @@
         <v>386</v>
       </c>
       <c r="D234" t="s">
-        <v>387</v>
+        <v>364</v>
       </c>
       <c r="E234" t="s">
         <v>365</v>
@@ -6990,7 +6990,7 @@
         <v>165</v>
       </c>
       <c r="G234" t="s">
-        <v>366</v>
+        <v>387</v>
       </c>
     </row>
     <row r="235" spans="1:7">
@@ -7004,7 +7004,7 @@
         <v>386</v>
       </c>
       <c r="D235" t="s">
-        <v>387</v>
+        <v>364</v>
       </c>
       <c r="E235" t="s">
         <v>365</v>
@@ -7013,7 +7013,7 @@
         <v>165</v>
       </c>
       <c r="G235" t="s">
-        <v>366</v>
+        <v>387</v>
       </c>
     </row>
     <row r="236" spans="1:7">
@@ -7027,7 +7027,7 @@
         <v>386</v>
       </c>
       <c r="D236" t="s">
-        <v>387</v>
+        <v>364</v>
       </c>
       <c r="E236" t="s">
         <v>365</v>
@@ -7036,7 +7036,7 @@
         <v>165</v>
       </c>
       <c r="G236" t="s">
-        <v>366</v>
+        <v>387</v>
       </c>
     </row>
     <row r="237" spans="1:7">
@@ -7050,7 +7050,7 @@
         <v>386</v>
       </c>
       <c r="D237" t="s">
-        <v>387</v>
+        <v>364</v>
       </c>
       <c r="E237" t="s">
         <v>365</v>
@@ -7059,7 +7059,7 @@
         <v>165</v>
       </c>
       <c r="G237" t="s">
-        <v>366</v>
+        <v>387</v>
       </c>
     </row>
     <row r="238" spans="1:7">
@@ -7073,7 +7073,7 @@
         <v>386</v>
       </c>
       <c r="D238" t="s">
-        <v>387</v>
+        <v>364</v>
       </c>
       <c r="E238" t="s">
         <v>365</v>
@@ -7082,7 +7082,7 @@
         <v>165</v>
       </c>
       <c r="G238" t="s">
-        <v>366</v>
+        <v>387</v>
       </c>
     </row>
     <row r="239" spans="1:7">
@@ -7096,7 +7096,7 @@
         <v>398</v>
       </c>
       <c r="D239" t="s">
-        <v>399</v>
+        <v>364</v>
       </c>
       <c r="E239" t="s">
         <v>365</v>
@@ -7105,7 +7105,7 @@
         <v>165</v>
       </c>
       <c r="G239" t="s">
-        <v>366</v>
+        <v>399</v>
       </c>
     </row>
     <row r="240" spans="1:7">
@@ -7116,13 +7116,13 @@
         <v>8</v>
       </c>
       <c r="C240" t="s">
+        <v>163</v>
+      </c>
+      <c r="D240" t="s">
+        <v>164</v>
+      </c>
+      <c r="E240" t="s">
         <v>401</v>
-      </c>
-      <c r="D240" t="s">
-        <v>163</v>
-      </c>
-      <c r="E240" t="s">
-        <v>164</v>
       </c>
       <c r="F240" t="s">
         <v>165</v>
@@ -7139,13 +7139,13 @@
         <v>8</v>
       </c>
       <c r="C241" t="s">
+        <v>163</v>
+      </c>
+      <c r="D241" t="s">
+        <v>164</v>
+      </c>
+      <c r="E241" t="s">
         <v>401</v>
-      </c>
-      <c r="D241" t="s">
-        <v>163</v>
-      </c>
-      <c r="E241" t="s">
-        <v>164</v>
       </c>
       <c r="F241" t="s">
         <v>165</v>
@@ -7162,13 +7162,13 @@
         <v>8</v>
       </c>
       <c r="C242" t="s">
+        <v>163</v>
+      </c>
+      <c r="D242" t="s">
+        <v>164</v>
+      </c>
+      <c r="E242" t="s">
         <v>401</v>
-      </c>
-      <c r="D242" t="s">
-        <v>163</v>
-      </c>
-      <c r="E242" t="s">
-        <v>164</v>
       </c>
       <c r="F242" t="s">
         <v>165</v>
@@ -7185,13 +7185,13 @@
         <v>8</v>
       </c>
       <c r="C243" t="s">
+        <v>163</v>
+      </c>
+      <c r="D243" t="s">
+        <v>164</v>
+      </c>
+      <c r="E243" t="s">
         <v>401</v>
-      </c>
-      <c r="D243" t="s">
-        <v>163</v>
-      </c>
-      <c r="E243" t="s">
-        <v>164</v>
       </c>
       <c r="F243" t="s">
         <v>165</v>
@@ -7208,13 +7208,13 @@
         <v>8</v>
       </c>
       <c r="C244" t="s">
+        <v>163</v>
+      </c>
+      <c r="D244" t="s">
+        <v>164</v>
+      </c>
+      <c r="E244" t="s">
         <v>401</v>
-      </c>
-      <c r="D244" t="s">
-        <v>163</v>
-      </c>
-      <c r="E244" t="s">
-        <v>164</v>
       </c>
       <c r="F244" t="s">
         <v>165</v>
@@ -7231,13 +7231,13 @@
         <v>8</v>
       </c>
       <c r="C245" t="s">
+        <v>163</v>
+      </c>
+      <c r="D245" t="s">
+        <v>164</v>
+      </c>
+      <c r="E245" t="s">
         <v>401</v>
-      </c>
-      <c r="D245" t="s">
-        <v>163</v>
-      </c>
-      <c r="E245" t="s">
-        <v>164</v>
       </c>
       <c r="F245" t="s">
         <v>165</v>
@@ -7257,16 +7257,16 @@
         <v>409</v>
       </c>
       <c r="D246" t="s">
+        <v>256</v>
+      </c>
+      <c r="E246" t="s">
+        <v>401</v>
+      </c>
+      <c r="F246" t="s">
+        <v>165</v>
+      </c>
+      <c r="G246" t="s">
         <v>410</v>
-      </c>
-      <c r="E246" t="s">
-        <v>256</v>
-      </c>
-      <c r="F246" t="s">
-        <v>165</v>
-      </c>
-      <c r="G246" t="s">
-        <v>402</v>
       </c>
     </row>
     <row r="247" spans="1:7">
@@ -7276,17 +7276,17 @@
       <c r="B247" t="s">
         <v>8</v>
       </c>
+      <c r="C247" t="s">
+        <v>95</v>
+      </c>
       <c r="D247" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="E247" t="s">
-        <v>96</v>
+        <v>412</v>
       </c>
       <c r="F247" t="s">
         <v>97</v>
-      </c>
-      <c r="G247" t="s">
-        <v>412</v>
       </c>
     </row>
     <row r="248" spans="1:7">
@@ -7296,17 +7296,17 @@
       <c r="B248" t="s">
         <v>8</v>
       </c>
+      <c r="C248" t="s">
+        <v>95</v>
+      </c>
       <c r="D248" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="E248" t="s">
-        <v>96</v>
+        <v>412</v>
       </c>
       <c r="F248" t="s">
         <v>97</v>
-      </c>
-      <c r="G248" t="s">
-        <v>412</v>
       </c>
     </row>
     <row r="249" spans="1:7">
@@ -7316,17 +7316,17 @@
       <c r="B249" t="s">
         <v>8</v>
       </c>
+      <c r="C249" t="s">
+        <v>415</v>
+      </c>
       <c r="D249" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="E249" t="s">
-        <v>416</v>
+        <v>412</v>
       </c>
       <c r="F249" t="s">
         <v>97</v>
-      </c>
-      <c r="G249" t="s">
-        <v>412</v>
       </c>
     </row>
     <row r="250" spans="1:7">
@@ -7336,17 +7336,17 @@
       <c r="B250" t="s">
         <v>8</v>
       </c>
+      <c r="C250" t="s">
+        <v>95</v>
+      </c>
       <c r="D250" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="E250" t="s">
-        <v>96</v>
+        <v>412</v>
       </c>
       <c r="F250" t="s">
         <v>97</v>
-      </c>
-      <c r="G250" t="s">
-        <v>412</v>
       </c>
     </row>
     <row r="251" spans="1:7">
@@ -7356,17 +7356,17 @@
       <c r="B251" t="s">
         <v>8</v>
       </c>
+      <c r="C251" t="s">
+        <v>95</v>
+      </c>
       <c r="D251" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="E251" t="s">
-        <v>96</v>
+        <v>412</v>
       </c>
       <c r="F251" t="s">
         <v>97</v>
-      </c>
-      <c r="G251" t="s">
-        <v>412</v>
       </c>
     </row>
     <row r="252" spans="1:7">
@@ -7376,17 +7376,17 @@
       <c r="B252" t="s">
         <v>8</v>
       </c>
+      <c r="C252" t="s">
+        <v>95</v>
+      </c>
       <c r="D252" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="E252" t="s">
-        <v>96</v>
+        <v>412</v>
       </c>
       <c r="F252" t="s">
         <v>97</v>
-      </c>
-      <c r="G252" t="s">
-        <v>412</v>
       </c>
     </row>
     <row r="253" spans="1:7">
@@ -7396,17 +7396,17 @@
       <c r="B253" t="s">
         <v>8</v>
       </c>
+      <c r="C253" t="s">
+        <v>421</v>
+      </c>
       <c r="D253" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="E253" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="F253" t="s">
         <v>165</v>
-      </c>
-      <c r="G253" t="s">
-        <v>423</v>
       </c>
     </row>
     <row r="254" spans="1:7">
@@ -7416,17 +7416,17 @@
       <c r="B254" t="s">
         <v>8</v>
       </c>
+      <c r="C254" t="s">
+        <v>219</v>
+      </c>
       <c r="D254" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="E254" t="s">
-        <v>220</v>
+        <v>423</v>
       </c>
       <c r="F254" t="s">
-        <v>92</v>
-      </c>
-      <c r="G254" t="s">
-        <v>423</v>
+        <v>93</v>
       </c>
     </row>
     <row r="255" spans="1:7">
@@ -7436,17 +7436,17 @@
       <c r="B255" t="s">
         <v>8</v>
       </c>
+      <c r="C255" t="s">
+        <v>426</v>
+      </c>
       <c r="D255" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="E255" t="s">
-        <v>427</v>
+        <v>423</v>
       </c>
       <c r="F255" t="s">
-        <v>92</v>
-      </c>
-      <c r="G255" t="s">
-        <v>423</v>
+        <v>93</v>
       </c>
     </row>
     <row r="256" spans="1:7">
@@ -7456,817 +7456,817 @@
       <c r="B256" t="s">
         <v>8</v>
       </c>
+      <c r="C256" t="s">
+        <v>426</v>
+      </c>
       <c r="D256" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="E256" t="s">
-        <v>427</v>
+        <v>423</v>
       </c>
       <c r="F256" t="s">
-        <v>92</v>
-      </c>
-      <c r="G256" t="s">
-        <v>423</v>
-      </c>
-    </row>
-    <row r="257" spans="1:7">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="257" spans="1:6">
       <c r="A257" t="s">
         <v>429</v>
       </c>
       <c r="B257" t="s">
         <v>8</v>
       </c>
+      <c r="C257" t="s">
+        <v>426</v>
+      </c>
       <c r="D257" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="E257" t="s">
-        <v>427</v>
+        <v>423</v>
       </c>
       <c r="F257" t="s">
-        <v>92</v>
-      </c>
-      <c r="G257" t="s">
-        <v>423</v>
-      </c>
-    </row>
-    <row r="258" spans="1:7">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="258" spans="1:6">
       <c r="A258" t="s">
         <v>430</v>
       </c>
       <c r="B258" t="s">
         <v>8</v>
       </c>
+      <c r="C258" t="s">
+        <v>325</v>
+      </c>
       <c r="D258" t="s">
         <v>326</v>
       </c>
       <c r="E258" t="s">
-        <v>327</v>
+        <v>423</v>
       </c>
       <c r="F258" t="s">
         <v>165</v>
       </c>
-      <c r="G258" t="s">
-        <v>423</v>
-      </c>
-    </row>
-    <row r="259" spans="1:7">
+    </row>
+    <row r="259" spans="1:6">
       <c r="A259" t="s">
         <v>431</v>
       </c>
       <c r="B259" t="s">
         <v>8</v>
       </c>
+      <c r="C259" t="s">
+        <v>426</v>
+      </c>
       <c r="D259" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="E259" t="s">
-        <v>427</v>
+        <v>423</v>
       </c>
       <c r="F259" t="s">
-        <v>92</v>
-      </c>
-      <c r="G259" t="s">
-        <v>423</v>
-      </c>
-    </row>
-    <row r="260" spans="1:7">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="260" spans="1:6">
       <c r="A260" t="s">
         <v>432</v>
       </c>
       <c r="B260" t="s">
         <v>8</v>
       </c>
+      <c r="C260" t="s">
+        <v>163</v>
+      </c>
       <c r="D260" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="E260" t="s">
-        <v>164</v>
+        <v>423</v>
       </c>
       <c r="F260" t="s">
         <v>165</v>
       </c>
-      <c r="G260" t="s">
-        <v>423</v>
-      </c>
-    </row>
-    <row r="261" spans="1:7">
+    </row>
+    <row r="261" spans="1:6">
       <c r="A261" t="s">
         <v>433</v>
       </c>
       <c r="B261" t="s">
         <v>8</v>
       </c>
+      <c r="C261" t="s">
+        <v>434</v>
+      </c>
       <c r="D261" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="E261" t="s">
-        <v>435</v>
+        <v>423</v>
       </c>
       <c r="F261" t="s">
         <v>197</v>
       </c>
-      <c r="G261" t="s">
-        <v>423</v>
-      </c>
-    </row>
-    <row r="262" spans="1:7">
+    </row>
+    <row r="262" spans="1:6">
       <c r="A262" t="s">
         <v>436</v>
       </c>
       <c r="B262" t="s">
         <v>8</v>
       </c>
+      <c r="C262" t="s">
+        <v>163</v>
+      </c>
       <c r="D262" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="E262" t="s">
-        <v>164</v>
+        <v>423</v>
       </c>
       <c r="F262" t="s">
         <v>165</v>
       </c>
-      <c r="G262" t="s">
-        <v>423</v>
-      </c>
-    </row>
-    <row r="263" spans="1:7">
+    </row>
+    <row r="263" spans="1:6">
       <c r="A263" t="s">
         <v>437</v>
       </c>
       <c r="B263" t="s">
         <v>8</v>
       </c>
+      <c r="C263" t="s">
+        <v>438</v>
+      </c>
       <c r="D263" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="E263" t="s">
-        <v>439</v>
+        <v>423</v>
       </c>
       <c r="F263" t="s">
         <v>184</v>
       </c>
-      <c r="G263" t="s">
-        <v>423</v>
-      </c>
-    </row>
-    <row r="264" spans="1:7">
+    </row>
+    <row r="264" spans="1:6">
       <c r="A264" t="s">
         <v>440</v>
       </c>
       <c r="B264" t="s">
         <v>8</v>
       </c>
+      <c r="C264" t="s">
+        <v>31</v>
+      </c>
       <c r="D264" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E264" t="s">
-        <v>32</v>
+        <v>423</v>
       </c>
       <c r="F264" t="s">
         <v>33</v>
       </c>
-      <c r="G264" t="s">
-        <v>423</v>
-      </c>
-    </row>
-    <row r="265" spans="1:7">
+    </row>
+    <row r="265" spans="1:6">
       <c r="A265" t="s">
         <v>441</v>
       </c>
       <c r="B265" t="s">
         <v>8</v>
       </c>
+      <c r="C265" t="s">
+        <v>9</v>
+      </c>
       <c r="D265" t="s">
         <v>10</v>
       </c>
       <c r="E265" t="s">
-        <v>11</v>
+        <v>423</v>
       </c>
       <c r="F265" t="s">
         <v>12</v>
       </c>
-      <c r="G265" t="s">
-        <v>423</v>
-      </c>
-    </row>
-    <row r="266" spans="1:7">
+    </row>
+    <row r="266" spans="1:6">
       <c r="A266" t="s">
         <v>442</v>
       </c>
       <c r="B266" t="s">
         <v>8</v>
       </c>
+      <c r="C266" t="s">
+        <v>443</v>
+      </c>
       <c r="D266" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="E266" t="s">
-        <v>444</v>
+        <v>423</v>
       </c>
       <c r="F266" t="s">
         <v>115</v>
       </c>
-      <c r="G266" t="s">
-        <v>423</v>
-      </c>
-    </row>
-    <row r="267" spans="1:7">
+    </row>
+    <row r="267" spans="1:6">
       <c r="A267" t="s">
         <v>445</v>
       </c>
       <c r="B267" t="s">
         <v>8</v>
       </c>
+      <c r="C267" t="s">
+        <v>118</v>
+      </c>
       <c r="D267" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="E267" t="s">
-        <v>119</v>
+        <v>446</v>
       </c>
       <c r="F267" t="s">
         <v>115</v>
       </c>
-      <c r="G267" t="s">
-        <v>446</v>
-      </c>
-    </row>
-    <row r="268" spans="1:7">
+    </row>
+    <row r="268" spans="1:6">
       <c r="A268" t="s">
         <v>447</v>
       </c>
       <c r="B268" t="s">
         <v>8</v>
       </c>
+      <c r="C268" t="s">
+        <v>202</v>
+      </c>
       <c r="D268" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="E268" t="s">
-        <v>203</v>
+        <v>448</v>
       </c>
       <c r="F268" t="s">
         <v>184</v>
       </c>
-      <c r="G268" t="s">
-        <v>448</v>
-      </c>
-    </row>
-    <row r="269" spans="1:7">
+    </row>
+    <row r="269" spans="1:6">
       <c r="A269" t="s">
         <v>449</v>
       </c>
       <c r="B269" t="s">
         <v>8</v>
       </c>
+      <c r="C269" t="s">
+        <v>118</v>
+      </c>
       <c r="D269" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="E269" t="s">
-        <v>119</v>
+        <v>450</v>
       </c>
       <c r="F269" t="s">
         <v>115</v>
       </c>
-      <c r="G269" t="s">
-        <v>450</v>
-      </c>
-    </row>
-    <row r="270" spans="1:7">
+    </row>
+    <row r="270" spans="1:6">
       <c r="A270" t="s">
         <v>451</v>
       </c>
       <c r="B270" t="s">
         <v>8</v>
       </c>
+      <c r="C270" t="s">
+        <v>118</v>
+      </c>
       <c r="D270" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="E270" t="s">
-        <v>119</v>
+        <v>450</v>
       </c>
       <c r="F270" t="s">
         <v>115</v>
       </c>
-      <c r="G270" t="s">
-        <v>450</v>
-      </c>
-    </row>
-    <row r="271" spans="1:7">
+    </row>
+    <row r="271" spans="1:6">
       <c r="A271" t="s">
         <v>452</v>
       </c>
       <c r="B271" t="s">
         <v>8</v>
       </c>
+      <c r="C271" t="s">
+        <v>453</v>
+      </c>
       <c r="D271" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="E271" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="F271" t="s">
         <v>115</v>
       </c>
-      <c r="G271" t="s">
-        <v>455</v>
-      </c>
-    </row>
-    <row r="272" spans="1:7">
+    </row>
+    <row r="272" spans="1:6">
       <c r="A272" t="s">
         <v>456</v>
       </c>
       <c r="B272" t="s">
         <v>8</v>
       </c>
+      <c r="C272" t="s">
+        <v>453</v>
+      </c>
       <c r="D272" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="E272" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="F272" t="s">
         <v>115</v>
       </c>
-      <c r="G272" t="s">
-        <v>455</v>
-      </c>
-    </row>
-    <row r="273" spans="1:7">
+    </row>
+    <row r="273" spans="1:6">
       <c r="A273" t="s">
         <v>457</v>
       </c>
       <c r="B273" t="s">
         <v>8</v>
       </c>
+      <c r="C273" t="s">
+        <v>453</v>
+      </c>
       <c r="D273" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="E273" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="F273" t="s">
         <v>115</v>
       </c>
-      <c r="G273" t="s">
-        <v>455</v>
-      </c>
-    </row>
-    <row r="274" spans="1:7">
+    </row>
+    <row r="274" spans="1:6">
       <c r="A274" t="s">
         <v>458</v>
       </c>
       <c r="B274" t="s">
         <v>8</v>
       </c>
+      <c r="C274" t="s">
+        <v>453</v>
+      </c>
       <c r="D274" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="E274" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="F274" t="s">
         <v>115</v>
       </c>
-      <c r="G274" t="s">
-        <v>455</v>
-      </c>
-    </row>
-    <row r="275" spans="1:7">
+    </row>
+    <row r="275" spans="1:6">
       <c r="A275" t="s">
         <v>459</v>
       </c>
       <c r="B275" t="s">
         <v>8</v>
       </c>
+      <c r="C275" t="s">
+        <v>453</v>
+      </c>
       <c r="D275" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="E275" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="F275" t="s">
         <v>115</v>
       </c>
-      <c r="G275" t="s">
-        <v>455</v>
-      </c>
-    </row>
-    <row r="276" spans="1:7">
+    </row>
+    <row r="276" spans="1:6">
       <c r="A276" t="s">
         <v>460</v>
       </c>
       <c r="B276" t="s">
         <v>8</v>
       </c>
+      <c r="C276" t="s">
+        <v>453</v>
+      </c>
       <c r="D276" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="E276" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="F276" t="s">
         <v>115</v>
       </c>
-      <c r="G276" t="s">
-        <v>455</v>
-      </c>
-    </row>
-    <row r="277" spans="1:7">
+    </row>
+    <row r="277" spans="1:6">
       <c r="A277" t="s">
         <v>461</v>
       </c>
       <c r="B277" t="s">
         <v>8</v>
       </c>
+      <c r="C277" t="s">
+        <v>453</v>
+      </c>
       <c r="D277" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="E277" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="F277" t="s">
         <v>115</v>
       </c>
-      <c r="G277" t="s">
-        <v>455</v>
-      </c>
-    </row>
-    <row r="278" spans="1:7">
+    </row>
+    <row r="278" spans="1:6">
       <c r="A278" t="s">
         <v>462</v>
       </c>
       <c r="B278" t="s">
         <v>8</v>
       </c>
+      <c r="C278" t="s">
+        <v>202</v>
+      </c>
       <c r="D278" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="E278" t="s">
-        <v>203</v>
+        <v>463</v>
       </c>
       <c r="F278" t="s">
         <v>184</v>
       </c>
-      <c r="G278" t="s">
-        <v>463</v>
-      </c>
-    </row>
-    <row r="279" spans="1:7">
+    </row>
+    <row r="279" spans="1:6">
       <c r="A279" t="s">
         <v>464</v>
       </c>
       <c r="B279" t="s">
         <v>8</v>
       </c>
+      <c r="C279" t="s">
+        <v>51</v>
+      </c>
       <c r="D279" t="s">
         <v>52</v>
       </c>
       <c r="E279" t="s">
-        <v>53</v>
+        <v>463</v>
       </c>
       <c r="F279" t="s">
         <v>33</v>
       </c>
-      <c r="G279" t="s">
-        <v>463</v>
-      </c>
-    </row>
-    <row r="280" spans="1:7">
+    </row>
+    <row r="280" spans="1:6">
       <c r="A280" t="s">
         <v>465</v>
       </c>
       <c r="B280" t="s">
         <v>8</v>
       </c>
+      <c r="C280" t="s">
+        <v>9</v>
+      </c>
       <c r="D280" t="s">
         <v>10</v>
       </c>
       <c r="E280" t="s">
-        <v>11</v>
+        <v>463</v>
       </c>
       <c r="F280" t="s">
         <v>12</v>
       </c>
-      <c r="G280" t="s">
-        <v>463</v>
-      </c>
-    </row>
-    <row r="281" spans="1:7">
+    </row>
+    <row r="281" spans="1:6">
       <c r="A281" t="s">
         <v>466</v>
       </c>
       <c r="B281" t="s">
         <v>8</v>
       </c>
+      <c r="C281" t="s">
+        <v>170</v>
+      </c>
       <c r="D281" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="E281" t="s">
-        <v>171</v>
+        <v>463</v>
       </c>
       <c r="F281" t="s">
         <v>115</v>
       </c>
-      <c r="G281" t="s">
-        <v>463</v>
-      </c>
-    </row>
-    <row r="282" spans="1:7">
+    </row>
+    <row r="282" spans="1:6">
       <c r="A282" t="s">
         <v>467</v>
       </c>
       <c r="B282" t="s">
         <v>8</v>
       </c>
+      <c r="C282" t="s">
+        <v>124</v>
+      </c>
       <c r="D282" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="E282" t="s">
-        <v>125</v>
+        <v>463</v>
       </c>
       <c r="F282" t="s">
         <v>126</v>
       </c>
-      <c r="G282" t="s">
-        <v>463</v>
-      </c>
-    </row>
-    <row r="283" spans="1:7">
+    </row>
+    <row r="283" spans="1:6">
       <c r="A283" t="s">
         <v>468</v>
       </c>
       <c r="B283" t="s">
         <v>8</v>
       </c>
+      <c r="C283" t="s">
+        <v>398</v>
+      </c>
       <c r="D283" t="s">
-        <v>399</v>
+        <v>364</v>
       </c>
       <c r="E283" t="s">
-        <v>365</v>
+        <v>469</v>
       </c>
       <c r="F283" t="s">
         <v>165</v>
       </c>
-      <c r="G283" t="s">
-        <v>469</v>
-      </c>
-    </row>
-    <row r="284" spans="1:7">
+    </row>
+    <row r="284" spans="1:6">
       <c r="A284" t="s">
         <v>470</v>
       </c>
       <c r="B284" t="s">
         <v>8</v>
       </c>
+      <c r="C284" t="s">
+        <v>124</v>
+      </c>
       <c r="D284" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="E284" t="s">
-        <v>125</v>
+        <v>471</v>
       </c>
       <c r="F284" t="s">
         <v>126</v>
       </c>
-      <c r="G284" t="s">
-        <v>471</v>
-      </c>
-    </row>
-    <row r="285" spans="1:7">
+    </row>
+    <row r="285" spans="1:6">
       <c r="A285" t="s">
         <v>472</v>
       </c>
       <c r="B285" t="s">
         <v>8</v>
       </c>
+      <c r="C285" t="s">
+        <v>170</v>
+      </c>
       <c r="D285" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="E285" t="s">
-        <v>171</v>
+        <v>473</v>
       </c>
       <c r="F285" t="s">
         <v>115</v>
       </c>
-      <c r="G285" t="s">
-        <v>473</v>
-      </c>
-    </row>
-    <row r="286" spans="1:7">
+    </row>
+    <row r="286" spans="1:6">
       <c r="A286" t="s">
         <v>474</v>
       </c>
       <c r="B286" t="s">
         <v>8</v>
       </c>
+      <c r="C286" t="s">
+        <v>438</v>
+      </c>
       <c r="D286" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="E286" t="s">
-        <v>439</v>
+        <v>475</v>
       </c>
       <c r="F286" t="s">
         <v>184</v>
       </c>
-      <c r="G286" t="s">
-        <v>475</v>
-      </c>
-    </row>
-    <row r="287" spans="1:7">
+    </row>
+    <row r="287" spans="1:6">
       <c r="A287" t="s">
         <v>476</v>
       </c>
       <c r="B287" t="s">
         <v>8</v>
       </c>
+      <c r="C287" t="s">
+        <v>438</v>
+      </c>
       <c r="D287" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="E287" t="s">
-        <v>439</v>
+        <v>475</v>
       </c>
       <c r="F287" t="s">
         <v>184</v>
       </c>
-      <c r="G287" t="s">
-        <v>475</v>
-      </c>
-    </row>
-    <row r="288" spans="1:7">
+    </row>
+    <row r="288" spans="1:6">
       <c r="A288" t="s">
         <v>477</v>
       </c>
       <c r="B288" t="s">
         <v>8</v>
       </c>
+      <c r="C288" t="s">
+        <v>41</v>
+      </c>
       <c r="D288" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="E288" t="s">
-        <v>42</v>
+        <v>475</v>
       </c>
       <c r="F288" t="s">
         <v>12</v>
       </c>
-      <c r="G288" t="s">
-        <v>475</v>
-      </c>
-    </row>
-    <row r="289" spans="1:7">
+    </row>
+    <row r="289" spans="1:6">
       <c r="A289" t="s">
         <v>478</v>
       </c>
       <c r="B289" t="s">
         <v>8</v>
       </c>
+      <c r="C289" t="s">
+        <v>31</v>
+      </c>
       <c r="D289" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E289" t="s">
-        <v>32</v>
+        <v>475</v>
       </c>
       <c r="F289" t="s">
         <v>33</v>
       </c>
-      <c r="G289" t="s">
-        <v>475</v>
-      </c>
-    </row>
-    <row r="290" spans="1:7">
+    </row>
+    <row r="290" spans="1:6">
       <c r="A290" t="s">
         <v>479</v>
       </c>
       <c r="B290" t="s">
         <v>8</v>
       </c>
+      <c r="C290" t="s">
+        <v>31</v>
+      </c>
       <c r="D290" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E290" t="s">
-        <v>32</v>
+        <v>475</v>
       </c>
       <c r="F290" t="s">
         <v>33</v>
       </c>
-      <c r="G290" t="s">
-        <v>475</v>
-      </c>
-    </row>
-    <row r="291" spans="1:7">
+    </row>
+    <row r="291" spans="1:6">
       <c r="A291" t="s">
         <v>480</v>
       </c>
       <c r="B291" t="s">
         <v>8</v>
       </c>
+      <c r="C291" t="s">
+        <v>170</v>
+      </c>
       <c r="D291" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="E291" t="s">
-        <v>171</v>
+        <v>475</v>
       </c>
       <c r="F291" t="s">
         <v>115</v>
       </c>
-      <c r="G291" t="s">
-        <v>475</v>
-      </c>
-    </row>
-    <row r="292" spans="1:7">
+    </row>
+    <row r="292" spans="1:6">
       <c r="A292" t="s">
         <v>481</v>
       </c>
       <c r="B292" t="s">
         <v>8</v>
       </c>
+      <c r="C292" t="s">
+        <v>170</v>
+      </c>
       <c r="D292" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="E292" t="s">
-        <v>171</v>
+        <v>475</v>
       </c>
       <c r="F292" t="s">
         <v>115</v>
       </c>
-      <c r="G292" t="s">
-        <v>475</v>
-      </c>
-    </row>
-    <row r="293" spans="1:7">
+    </row>
+    <row r="293" spans="1:6">
       <c r="A293" t="s">
         <v>482</v>
       </c>
       <c r="B293" t="s">
         <v>8</v>
       </c>
+      <c r="C293" t="s">
+        <v>170</v>
+      </c>
       <c r="D293" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="E293" t="s">
-        <v>171</v>
+        <v>475</v>
       </c>
       <c r="F293" t="s">
         <v>115</v>
       </c>
-      <c r="G293" t="s">
-        <v>475</v>
-      </c>
-    </row>
-    <row r="294" spans="1:7">
+    </row>
+    <row r="294" spans="1:6">
       <c r="A294" t="s">
         <v>483</v>
       </c>
       <c r="B294" t="s">
         <v>8</v>
       </c>
+      <c r="C294" t="s">
+        <v>170</v>
+      </c>
       <c r="D294" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="E294" t="s">
-        <v>171</v>
+        <v>475</v>
       </c>
       <c r="F294" t="s">
         <v>115</v>
       </c>
-      <c r="G294" t="s">
-        <v>475</v>
-      </c>
-    </row>
-    <row r="295" spans="1:7">
+    </row>
+    <row r="295" spans="1:6">
       <c r="A295" t="s">
         <v>484</v>
       </c>
       <c r="B295" t="s">
         <v>8</v>
       </c>
+      <c r="C295" t="s">
+        <v>170</v>
+      </c>
       <c r="D295" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="E295" t="s">
-        <v>171</v>
+        <v>485</v>
       </c>
       <c r="F295" t="s">
         <v>115</v>
       </c>
-      <c r="G295" t="s">
-        <v>485</v>
-      </c>
-    </row>
-    <row r="296" spans="1:7">
+    </row>
+    <row r="296" spans="1:6">
       <c r="A296" t="s">
         <v>486</v>
       </c>
       <c r="B296" t="s">
         <v>8</v>
       </c>
+      <c r="C296" t="s">
+        <v>170</v>
+      </c>
       <c r="D296" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="E296" t="s">
-        <v>171</v>
+        <v>485</v>
       </c>
       <c r="F296" t="s">
         <v>115</v>
-      </c>
-      <c r="G296" t="s">
-        <v>485</v>
       </c>
     </row>
   </sheetData>

--- a/api/2/xlsx/fr/SectorCOFOG.xlsx
+++ b/api/2/xlsx/fr/SectorCOFOG.xlsx
@@ -22,42 +22,42 @@
     <t>status</t>
   </si>
   <si>
+    <t>codeforiati:category-code</t>
+  </si>
+  <si>
+    <t>codeforiati:group-code</t>
+  </si>
+  <si>
+    <t>codeforiati:cofog-division</t>
+  </si>
+  <si>
     <t>codeforiati:cofog-class</t>
   </si>
   <si>
     <t>codeforiati:cofog-group</t>
   </si>
   <si>
-    <t>codeforiati:group-code</t>
-  </si>
-  <si>
-    <t>codeforiati:cofog-division</t>
-  </si>
-  <si>
-    <t>codeforiati:category-code</t>
-  </si>
-  <si>
     <t>11110</t>
   </si>
   <si>
     <t>active</t>
   </si>
   <si>
+    <t>111</t>
+  </si>
+  <si>
+    <t>110</t>
+  </si>
+  <si>
+    <t>09 - Education</t>
+  </si>
+  <si>
     <t>09.8.0 - Education n.e.c. (CS)</t>
   </si>
   <si>
     <t>09.8 - Education n.e.c.</t>
   </si>
   <si>
-    <t>110</t>
-  </si>
-  <si>
-    <t>09 - Education</t>
-  </si>
-  <si>
-    <t>111</t>
-  </si>
-  <si>
     <t>11120</t>
   </si>
   <si>
@@ -82,15 +82,15 @@
     <t>11220</t>
   </si>
   <si>
+    <t>112</t>
+  </si>
+  <si>
     <t>09.1.2 - Primary education (IS)</t>
   </si>
   <si>
     <t>09.1 - Pre‐primary and primary education</t>
   </si>
   <si>
-    <t>112</t>
-  </si>
-  <si>
     <t>11230</t>
   </si>
   <si>
@@ -109,15 +109,15 @@
     <t>11250</t>
   </si>
   <si>
+    <t>07 - Health</t>
+  </si>
+  <si>
     <t>07.4.0 - Public health services (IS)</t>
   </si>
   <si>
     <t>07.4 - Public health services</t>
   </si>
   <si>
-    <t>07 - Health</t>
-  </si>
-  <si>
     <t>11260</t>
   </si>
   <si>
@@ -130,12 +130,12 @@
     <t>11320</t>
   </si>
   <si>
+    <t>113</t>
+  </si>
+  <si>
     <t>09.2.2 - Upper‐secondary education (IS)</t>
   </si>
   <si>
-    <t>113</t>
-  </si>
-  <si>
     <t>11330</t>
   </si>
   <si>
@@ -148,15 +148,15 @@
     <t>11420</t>
   </si>
   <si>
+    <t>114</t>
+  </si>
+  <si>
     <t>09.4.1 - First stage of tertiary education (IS)</t>
   </si>
   <si>
     <t>09.4 - Tertiary education</t>
   </si>
   <si>
-    <t>114</t>
-  </si>
-  <si>
     <t>11430</t>
   </si>
   <si>
@@ -169,18 +169,18 @@
     <t>12110</t>
   </si>
   <si>
+    <t>121</t>
+  </si>
+  <si>
+    <t>120</t>
+  </si>
+  <si>
     <t>07.6.0 - Health n.e.c. (CS)</t>
   </si>
   <si>
     <t>07.6 - Health n.e.c.</t>
   </si>
   <si>
-    <t>120</t>
-  </si>
-  <si>
-    <t>121</t>
-  </si>
-  <si>
     <t>12181</t>
   </si>
   <si>
@@ -286,30 +286,30 @@
     <t>14010</t>
   </si>
   <si>
+    <t>140</t>
+  </si>
+  <si>
+    <t>06 - Housing and community amenities</t>
+  </si>
+  <si>
     <t>06.3.0 - Water supply (CS)</t>
   </si>
   <si>
     <t>06.3 - Water supply</t>
   </si>
   <si>
-    <t>140</t>
-  </si>
-  <si>
-    <t>06 - Housing and community amenities</t>
-  </si>
-  <si>
     <t>14015</t>
   </si>
   <si>
+    <t>05 - Environmental protection</t>
+  </si>
+  <si>
     <t>05.6.0 - Environmental protection n.e.c. (CS)</t>
   </si>
   <si>
     <t>05.6 - Environmental protection n.e.c.</t>
   </si>
   <si>
-    <t>05 - Environmental protection</t>
-  </si>
-  <si>
     <t>14020</t>
   </si>
   <si>
@@ -352,21 +352,21 @@
     <t>15110</t>
   </si>
   <si>
+    <t>151</t>
+  </si>
+  <si>
+    <t>150</t>
+  </si>
+  <si>
+    <t>01 - General public services</t>
+  </si>
+  <si>
     <t>01.3.1 - General personnel services (CS)</t>
   </si>
   <si>
     <t>01.3 - General services</t>
   </si>
   <si>
-    <t>150</t>
-  </si>
-  <si>
-    <t>01 - General public services</t>
-  </si>
-  <si>
-    <t>151</t>
-  </si>
-  <si>
     <t>15111</t>
   </si>
   <si>
@@ -388,15 +388,15 @@
     <t>15113</t>
   </si>
   <si>
+    <t>03 - Public order and safety</t>
+  </si>
+  <si>
     <t>03.6.0 - Public order and safety n.e.c. (CS)</t>
   </si>
   <si>
     <t>03.6 - Public order and safety n.e.c.</t>
   </si>
   <si>
-    <t>03 - Public order and safety</t>
-  </si>
-  <si>
     <t>15114</t>
   </si>
   <si>
@@ -505,15 +505,15 @@
     <t>15142</t>
   </si>
   <si>
+    <t>04 - Economic affairs</t>
+  </si>
+  <si>
     <t>04.1.1 - General economic and commercial affairs (CS)</t>
   </si>
   <si>
     <t>04.1 - General economic, commercial and labour affairs</t>
   </si>
   <si>
-    <t>04 - Economic affairs</t>
-  </si>
-  <si>
     <t>15143</t>
   </si>
   <si>
@@ -562,15 +562,15 @@
     <t>15170</t>
   </si>
   <si>
+    <t>10 - Social protection</t>
+  </si>
+  <si>
     <t>10.7.0 - Social exclusion n.e.c. (IS)</t>
   </si>
   <si>
     <t>10.7 - Social exclusion n.e.c.</t>
   </si>
   <si>
-    <t>10 - Social protection</t>
-  </si>
-  <si>
     <t>15180</t>
   </si>
   <si>
@@ -601,15 +601,15 @@
     <t>15230</t>
   </si>
   <si>
+    <t>02 - Defence</t>
+  </si>
+  <si>
     <t>02.3.0 - Foreign military aid (CS)</t>
   </si>
   <si>
     <t>02.3 - Foreign military aid</t>
   </si>
   <si>
-    <t>02 - Defence</t>
-  </si>
-  <si>
     <t>15240</t>
   </si>
   <si>
@@ -622,15 +622,15 @@
     <t>16010</t>
   </si>
   <si>
+    <t>160</t>
+  </si>
+  <si>
     <t>10.9.0 - Social protection n.e.c. (CS)</t>
   </si>
   <si>
     <t>10.9 - Social protection n.e.c.</t>
   </si>
   <si>
-    <t>160</t>
-  </si>
-  <si>
     <t>16011</t>
   </si>
   <si>
@@ -685,15 +685,15 @@
     <t>16061</t>
   </si>
   <si>
+    <t>08 - Recreation, culture and religion</t>
+  </si>
+  <si>
     <t>08.2.0 - Cultural services (IS)</t>
   </si>
   <si>
     <t>08.2 - Cultural services</t>
   </si>
   <si>
-    <t>08 - Recreation, culture and religion</t>
-  </si>
-  <si>
     <t>16062</t>
   </si>
   <si>
@@ -823,18 +823,18 @@
     <t>23110</t>
   </si>
   <si>
+    <t>231</t>
+  </si>
+  <si>
+    <t>230</t>
+  </si>
+  <si>
     <t>04.3.5 - Electricity (CS)</t>
   </si>
   <si>
     <t>04.3 - Fuel and energy</t>
   </si>
   <si>
-    <t>230</t>
-  </si>
-  <si>
-    <t>231</t>
-  </si>
-  <si>
     <t>23111</t>
   </si>
   <si>
@@ -919,12 +919,12 @@
     <t>23510</t>
   </si>
   <si>
+    <t>235</t>
+  </si>
+  <si>
     <t>04.3.3 - Nuclear fuel (CS)</t>
   </si>
   <si>
-    <t>235</t>
-  </si>
-  <si>
     <t>23610</t>
   </si>
   <si>
@@ -991,18 +991,18 @@
     <t>31110</t>
   </si>
   <si>
+    <t>311</t>
+  </si>
+  <si>
+    <t>310</t>
+  </si>
+  <si>
     <t>04.2.1 - Agriculture (CS)</t>
   </si>
   <si>
     <t>04.2 - Agriculture, forestry, fishing and hunting</t>
   </si>
   <si>
-    <t>310</t>
-  </si>
-  <si>
-    <t>311</t>
-  </si>
-  <si>
     <t>31120</t>
   </si>
   <si>
@@ -1060,12 +1060,12 @@
     <t>31210</t>
   </si>
   <si>
+    <t>312</t>
+  </si>
+  <si>
     <t>04.2.2 - Forestry (CS)</t>
   </si>
   <si>
-    <t>312</t>
-  </si>
-  <si>
     <t>31220</t>
   </si>
   <si>
@@ -1084,12 +1084,12 @@
     <t>31310</t>
   </si>
   <si>
+    <t>313</t>
+  </si>
+  <si>
     <t>04.2.3 - Fishing and hunting (CS)</t>
   </si>
   <si>
-    <t>313</t>
-  </si>
-  <si>
     <t>31320</t>
   </si>
   <si>
@@ -1105,18 +1105,18 @@
     <t>32110</t>
   </si>
   <si>
+    <t>321</t>
+  </si>
+  <si>
+    <t>320</t>
+  </si>
+  <si>
     <t>04.4.2 - Manufacturing (CS)</t>
   </si>
   <si>
     <t>04.4 - Mining, manufacturing and construction</t>
   </si>
   <si>
-    <t>320</t>
-  </si>
-  <si>
-    <t>321</t>
-  </si>
-  <si>
     <t>32120</t>
   </si>
   <si>
@@ -1174,12 +1174,12 @@
     <t>32210</t>
   </si>
   <si>
+    <t>322</t>
+  </si>
+  <si>
     <t>04.4.1 - Mining of mineral resources other than mineral fuels (CS)</t>
   </si>
   <si>
-    <t>322</t>
-  </si>
-  <si>
     <t>32220</t>
   </si>
   <si>
@@ -1210,21 +1210,21 @@
     <t>32310</t>
   </si>
   <si>
+    <t>323</t>
+  </si>
+  <si>
     <t>04.4.3 - Construction (CS)</t>
   </si>
   <si>
-    <t>323</t>
-  </si>
-  <si>
     <t>33110</t>
   </si>
   <si>
+    <t>331</t>
+  </si>
+  <si>
     <t>330</t>
   </si>
   <si>
-    <t>331</t>
-  </si>
-  <si>
     <t>33120</t>
   </si>
   <si>
@@ -1243,12 +1243,12 @@
     <t>33210</t>
   </si>
   <si>
+    <t>332</t>
+  </si>
+  <si>
     <t>04.7.3 - Tourism (CS)</t>
   </si>
   <si>
-    <t>332</t>
-  </si>
-  <si>
     <t>41010</t>
   </si>
   <si>
@@ -1279,15 +1279,15 @@
     <t>43010</t>
   </si>
   <si>
+    <t>430</t>
+  </si>
+  <si>
     <t>04.9.0 - Economic affairs n.e.c. (CS)</t>
   </si>
   <si>
     <t>04.9 - Economic affairs n.e.c.</t>
   </si>
   <si>
-    <t>430</t>
-  </si>
-  <si>
     <t>43030</t>
   </si>
   <si>
@@ -1375,13 +1375,13 @@
     <t>60010</t>
   </si>
   <si>
+    <t>600</t>
+  </si>
+  <si>
     <t>01.7.0 - Public debt transactions (CS)</t>
   </si>
   <si>
     <t>01.7 - Public debt transactions</t>
-  </si>
-  <si>
-    <t>600</t>
   </si>
   <si>
     <t>60020</t>
@@ -1863,19 +1863,19 @@
         <v>8</v>
       </c>
       <c r="C3" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="D3" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="E3" t="s">
         <v>11</v>
       </c>
       <c r="F3" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="G3" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -1909,19 +1909,19 @@
         <v>8</v>
       </c>
       <c r="C5" t="s">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="D5" t="s">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="E5" t="s">
         <v>11</v>
       </c>
       <c r="F5" t="s">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="G5" t="s">
-        <v>13</v>
+        <v>20</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -1935,13 +1935,13 @@
         <v>22</v>
       </c>
       <c r="D6" t="s">
-        <v>23</v>
+        <v>10</v>
       </c>
       <c r="E6" t="s">
         <v>11</v>
       </c>
       <c r="F6" t="s">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="G6" t="s">
         <v>24</v>
@@ -1955,7 +1955,7 @@
         <v>8</v>
       </c>
       <c r="C7" t="s">
-        <v>9</v>
+        <v>22</v>
       </c>
       <c r="D7" t="s">
         <v>10</v>
@@ -1967,7 +1967,7 @@
         <v>12</v>
       </c>
       <c r="G7" t="s">
-        <v>24</v>
+        <v>13</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -1981,13 +1981,13 @@
         <v>22</v>
       </c>
       <c r="D8" t="s">
-        <v>23</v>
+        <v>10</v>
       </c>
       <c r="E8" t="s">
         <v>11</v>
       </c>
       <c r="F8" t="s">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="G8" t="s">
         <v>24</v>
@@ -2004,13 +2004,13 @@
         <v>22</v>
       </c>
       <c r="D9" t="s">
-        <v>23</v>
+        <v>10</v>
       </c>
       <c r="E9" t="s">
         <v>11</v>
       </c>
       <c r="F9" t="s">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="G9" t="s">
         <v>24</v>
@@ -2024,16 +2024,16 @@
         <v>8</v>
       </c>
       <c r="C10" t="s">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="D10" t="s">
-        <v>23</v>
+        <v>10</v>
       </c>
       <c r="E10" t="s">
         <v>11</v>
       </c>
       <c r="F10" t="s">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="G10" t="s">
         <v>24</v>
@@ -2047,19 +2047,19 @@
         <v>8</v>
       </c>
       <c r="C11" t="s">
+        <v>22</v>
+      </c>
+      <c r="D11" t="s">
+        <v>10</v>
+      </c>
+      <c r="E11" t="s">
         <v>31</v>
       </c>
-      <c r="D11" t="s">
+      <c r="F11" t="s">
         <v>32</v>
       </c>
-      <c r="E11" t="s">
-        <v>11</v>
-      </c>
-      <c r="F11" t="s">
+      <c r="G11" t="s">
         <v>33</v>
-      </c>
-      <c r="G11" t="s">
-        <v>24</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -2070,19 +2070,19 @@
         <v>8</v>
       </c>
       <c r="C12" t="s">
-        <v>35</v>
+        <v>22</v>
       </c>
       <c r="D12" t="s">
-        <v>36</v>
+        <v>10</v>
       </c>
       <c r="E12" t="s">
         <v>11</v>
       </c>
       <c r="F12" t="s">
-        <v>12</v>
+        <v>35</v>
       </c>
       <c r="G12" t="s">
-        <v>24</v>
+        <v>36</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -2096,16 +2096,16 @@
         <v>38</v>
       </c>
       <c r="D13" t="s">
-        <v>36</v>
+        <v>10</v>
       </c>
       <c r="E13" t="s">
         <v>11</v>
       </c>
       <c r="F13" t="s">
-        <v>12</v>
+        <v>39</v>
       </c>
       <c r="G13" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -2116,19 +2116,19 @@
         <v>8</v>
       </c>
       <c r="C14" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="D14" t="s">
-        <v>42</v>
+        <v>10</v>
       </c>
       <c r="E14" t="s">
         <v>11</v>
       </c>
       <c r="F14" t="s">
-        <v>12</v>
+        <v>41</v>
       </c>
       <c r="G14" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -2142,13 +2142,13 @@
         <v>44</v>
       </c>
       <c r="D15" t="s">
-        <v>45</v>
+        <v>10</v>
       </c>
       <c r="E15" t="s">
         <v>11</v>
       </c>
       <c r="F15" t="s">
-        <v>12</v>
+        <v>45</v>
       </c>
       <c r="G15" t="s">
         <v>46</v>
@@ -2162,19 +2162,19 @@
         <v>8</v>
       </c>
       <c r="C16" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="D16" t="s">
-        <v>49</v>
+        <v>10</v>
       </c>
       <c r="E16" t="s">
         <v>11</v>
       </c>
       <c r="F16" t="s">
-        <v>12</v>
+        <v>48</v>
       </c>
       <c r="G16" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -2191,10 +2191,10 @@
         <v>52</v>
       </c>
       <c r="E17" t="s">
+        <v>31</v>
+      </c>
+      <c r="F17" t="s">
         <v>53</v>
-      </c>
-      <c r="F17" t="s">
-        <v>33</v>
       </c>
       <c r="G17" t="s">
         <v>54</v>
@@ -2214,10 +2214,10 @@
         <v>52</v>
       </c>
       <c r="E18" t="s">
+        <v>31</v>
+      </c>
+      <c r="F18" t="s">
         <v>53</v>
-      </c>
-      <c r="F18" t="s">
-        <v>33</v>
       </c>
       <c r="G18" t="s">
         <v>54</v>
@@ -2231,19 +2231,19 @@
         <v>8</v>
       </c>
       <c r="C19" t="s">
+        <v>51</v>
+      </c>
+      <c r="D19" t="s">
+        <v>52</v>
+      </c>
+      <c r="E19" t="s">
+        <v>31</v>
+      </c>
+      <c r="F19" t="s">
         <v>57</v>
       </c>
-      <c r="D19" t="s">
+      <c r="G19" t="s">
         <v>58</v>
-      </c>
-      <c r="E19" t="s">
-        <v>53</v>
-      </c>
-      <c r="F19" t="s">
-        <v>33</v>
-      </c>
-      <c r="G19" t="s">
-        <v>54</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -2254,19 +2254,19 @@
         <v>8</v>
       </c>
       <c r="C20" t="s">
+        <v>51</v>
+      </c>
+      <c r="D20" t="s">
+        <v>52</v>
+      </c>
+      <c r="E20" t="s">
+        <v>31</v>
+      </c>
+      <c r="F20" t="s">
         <v>60</v>
       </c>
-      <c r="D20" t="s">
+      <c r="G20" t="s">
         <v>61</v>
-      </c>
-      <c r="E20" t="s">
-        <v>53</v>
-      </c>
-      <c r="F20" t="s">
-        <v>33</v>
-      </c>
-      <c r="G20" t="s">
-        <v>54</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -2283,10 +2283,10 @@
         <v>52</v>
       </c>
       <c r="E21" t="s">
+        <v>31</v>
+      </c>
+      <c r="F21" t="s">
         <v>53</v>
-      </c>
-      <c r="F21" t="s">
-        <v>33</v>
       </c>
       <c r="G21" t="s">
         <v>54</v>
@@ -2300,19 +2300,19 @@
         <v>8</v>
       </c>
       <c r="C22" t="s">
+        <v>64</v>
+      </c>
+      <c r="D22" t="s">
+        <v>52</v>
+      </c>
+      <c r="E22" t="s">
         <v>31</v>
       </c>
-      <c r="D22" t="s">
+      <c r="F22" t="s">
         <v>32</v>
       </c>
-      <c r="E22" t="s">
-        <v>53</v>
-      </c>
-      <c r="F22" t="s">
+      <c r="G22" t="s">
         <v>33</v>
-      </c>
-      <c r="G22" t="s">
-        <v>64</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -2323,19 +2323,19 @@
         <v>8</v>
       </c>
       <c r="C23" t="s">
+        <v>64</v>
+      </c>
+      <c r="D23" t="s">
+        <v>52</v>
+      </c>
+      <c r="E23" t="s">
+        <v>31</v>
+      </c>
+      <c r="F23" t="s">
         <v>66</v>
       </c>
-      <c r="D23" t="s">
+      <c r="G23" t="s">
         <v>67</v>
-      </c>
-      <c r="E23" t="s">
-        <v>53</v>
-      </c>
-      <c r="F23" t="s">
-        <v>33</v>
-      </c>
-      <c r="G23" t="s">
-        <v>64</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -2346,19 +2346,19 @@
         <v>8</v>
       </c>
       <c r="C24" t="s">
+        <v>64</v>
+      </c>
+      <c r="D24" t="s">
+        <v>52</v>
+      </c>
+      <c r="E24" t="s">
         <v>31</v>
       </c>
-      <c r="D24" t="s">
+      <c r="F24" t="s">
         <v>32</v>
       </c>
-      <c r="E24" t="s">
-        <v>53</v>
-      </c>
-      <c r="F24" t="s">
+      <c r="G24" t="s">
         <v>33</v>
-      </c>
-      <c r="G24" t="s">
-        <v>64</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -2369,19 +2369,19 @@
         <v>8</v>
       </c>
       <c r="C25" t="s">
+        <v>64</v>
+      </c>
+      <c r="D25" t="s">
+        <v>52</v>
+      </c>
+      <c r="E25" t="s">
         <v>31</v>
       </c>
-      <c r="D25" t="s">
+      <c r="F25" t="s">
         <v>32</v>
       </c>
-      <c r="E25" t="s">
-        <v>53</v>
-      </c>
-      <c r="F25" t="s">
+      <c r="G25" t="s">
         <v>33</v>
-      </c>
-      <c r="G25" t="s">
-        <v>64</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -2392,19 +2392,19 @@
         <v>8</v>
       </c>
       <c r="C26" t="s">
+        <v>64</v>
+      </c>
+      <c r="D26" t="s">
+        <v>52</v>
+      </c>
+      <c r="E26" t="s">
         <v>31</v>
       </c>
-      <c r="D26" t="s">
+      <c r="F26" t="s">
         <v>32</v>
       </c>
-      <c r="E26" t="s">
-        <v>53</v>
-      </c>
-      <c r="F26" t="s">
+      <c r="G26" t="s">
         <v>33</v>
-      </c>
-      <c r="G26" t="s">
-        <v>64</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -2415,19 +2415,19 @@
         <v>8</v>
       </c>
       <c r="C27" t="s">
+        <v>64</v>
+      </c>
+      <c r="D27" t="s">
+        <v>52</v>
+      </c>
+      <c r="E27" t="s">
         <v>31</v>
       </c>
-      <c r="D27" t="s">
+      <c r="F27" t="s">
         <v>32</v>
       </c>
-      <c r="E27" t="s">
-        <v>53</v>
-      </c>
-      <c r="F27" t="s">
+      <c r="G27" t="s">
         <v>33</v>
-      </c>
-      <c r="G27" t="s">
-        <v>64</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -2438,19 +2438,19 @@
         <v>8</v>
       </c>
       <c r="C28" t="s">
+        <v>64</v>
+      </c>
+      <c r="D28" t="s">
+        <v>52</v>
+      </c>
+      <c r="E28" t="s">
         <v>31</v>
       </c>
-      <c r="D28" t="s">
+      <c r="F28" t="s">
         <v>32</v>
       </c>
-      <c r="E28" t="s">
-        <v>53</v>
-      </c>
-      <c r="F28" t="s">
+      <c r="G28" t="s">
         <v>33</v>
-      </c>
-      <c r="G28" t="s">
-        <v>64</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -2461,19 +2461,19 @@
         <v>8</v>
       </c>
       <c r="C29" t="s">
+        <v>64</v>
+      </c>
+      <c r="D29" t="s">
+        <v>52</v>
+      </c>
+      <c r="E29" t="s">
         <v>31</v>
       </c>
-      <c r="D29" t="s">
+      <c r="F29" t="s">
         <v>32</v>
       </c>
-      <c r="E29" t="s">
-        <v>53</v>
-      </c>
-      <c r="F29" t="s">
+      <c r="G29" t="s">
         <v>33</v>
-      </c>
-      <c r="G29" t="s">
-        <v>64</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -2484,19 +2484,19 @@
         <v>8</v>
       </c>
       <c r="C30" t="s">
-        <v>51</v>
+        <v>64</v>
       </c>
       <c r="D30" t="s">
         <v>52</v>
       </c>
       <c r="E30" t="s">
+        <v>31</v>
+      </c>
+      <c r="F30" t="s">
         <v>53</v>
       </c>
-      <c r="F30" t="s">
-        <v>33</v>
-      </c>
       <c r="G30" t="s">
-        <v>64</v>
+        <v>54</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -2507,19 +2507,19 @@
         <v>8</v>
       </c>
       <c r="C31" t="s">
+        <v>76</v>
+      </c>
+      <c r="D31" t="s">
+        <v>52</v>
+      </c>
+      <c r="E31" t="s">
         <v>31</v>
       </c>
-      <c r="D31" t="s">
+      <c r="F31" t="s">
         <v>32</v>
       </c>
-      <c r="E31" t="s">
-        <v>53</v>
-      </c>
-      <c r="F31" t="s">
+      <c r="G31" t="s">
         <v>33</v>
-      </c>
-      <c r="G31" t="s">
-        <v>76</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -2530,19 +2530,19 @@
         <v>8</v>
       </c>
       <c r="C32" t="s">
+        <v>76</v>
+      </c>
+      <c r="D32" t="s">
+        <v>52</v>
+      </c>
+      <c r="E32" t="s">
         <v>31</v>
       </c>
-      <c r="D32" t="s">
+      <c r="F32" t="s">
         <v>32</v>
       </c>
-      <c r="E32" t="s">
-        <v>53</v>
-      </c>
-      <c r="F32" t="s">
+      <c r="G32" t="s">
         <v>33</v>
-      </c>
-      <c r="G32" t="s">
-        <v>76</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -2553,19 +2553,19 @@
         <v>8</v>
       </c>
       <c r="C33" t="s">
+        <v>76</v>
+      </c>
+      <c r="D33" t="s">
+        <v>52</v>
+      </c>
+      <c r="E33" t="s">
         <v>31</v>
       </c>
-      <c r="D33" t="s">
+      <c r="F33" t="s">
         <v>32</v>
       </c>
-      <c r="E33" t="s">
-        <v>53</v>
-      </c>
-      <c r="F33" t="s">
+      <c r="G33" t="s">
         <v>33</v>
-      </c>
-      <c r="G33" t="s">
-        <v>76</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -2576,19 +2576,19 @@
         <v>8</v>
       </c>
       <c r="C34" t="s">
+        <v>76</v>
+      </c>
+      <c r="D34" t="s">
+        <v>52</v>
+      </c>
+      <c r="E34" t="s">
         <v>31</v>
       </c>
-      <c r="D34" t="s">
+      <c r="F34" t="s">
         <v>32</v>
       </c>
-      <c r="E34" t="s">
-        <v>53</v>
-      </c>
-      <c r="F34" t="s">
+      <c r="G34" t="s">
         <v>33</v>
-      </c>
-      <c r="G34" t="s">
-        <v>76</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -2599,19 +2599,19 @@
         <v>8</v>
       </c>
       <c r="C35" t="s">
+        <v>76</v>
+      </c>
+      <c r="D35" t="s">
+        <v>52</v>
+      </c>
+      <c r="E35" t="s">
         <v>31</v>
       </c>
-      <c r="D35" t="s">
+      <c r="F35" t="s">
         <v>32</v>
       </c>
-      <c r="E35" t="s">
-        <v>53</v>
-      </c>
-      <c r="F35" t="s">
+      <c r="G35" t="s">
         <v>33</v>
-      </c>
-      <c r="G35" t="s">
-        <v>76</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -2622,19 +2622,19 @@
         <v>8</v>
       </c>
       <c r="C36" t="s">
+        <v>76</v>
+      </c>
+      <c r="D36" t="s">
+        <v>52</v>
+      </c>
+      <c r="E36" t="s">
+        <v>31</v>
+      </c>
+      <c r="F36" t="s">
         <v>57</v>
       </c>
-      <c r="D36" t="s">
+      <c r="G36" t="s">
         <v>58</v>
-      </c>
-      <c r="E36" t="s">
-        <v>53</v>
-      </c>
-      <c r="F36" t="s">
-        <v>33</v>
-      </c>
-      <c r="G36" t="s">
-        <v>76</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -2644,16 +2644,16 @@
       <c r="B37" t="s">
         <v>8</v>
       </c>
-      <c r="C37" t="s">
+      <c r="D37" t="s">
+        <v>83</v>
+      </c>
+      <c r="E37" t="s">
         <v>31</v>
       </c>
-      <c r="D37" t="s">
+      <c r="F37" t="s">
         <v>32</v>
       </c>
-      <c r="E37" t="s">
-        <v>83</v>
-      </c>
-      <c r="F37" t="s">
+      <c r="G37" t="s">
         <v>33</v>
       </c>
     </row>
@@ -2664,16 +2664,16 @@
       <c r="B38" t="s">
         <v>8</v>
       </c>
-      <c r="C38" t="s">
+      <c r="D38" t="s">
+        <v>83</v>
+      </c>
+      <c r="E38" t="s">
         <v>31</v>
       </c>
-      <c r="D38" t="s">
+      <c r="F38" t="s">
         <v>32</v>
       </c>
-      <c r="E38" t="s">
-        <v>83</v>
-      </c>
-      <c r="F38" t="s">
+      <c r="G38" t="s">
         <v>33</v>
       </c>
     </row>
@@ -2684,16 +2684,16 @@
       <c r="B39" t="s">
         <v>8</v>
       </c>
-      <c r="C39" t="s">
+      <c r="D39" t="s">
+        <v>83</v>
+      </c>
+      <c r="E39" t="s">
         <v>31</v>
       </c>
-      <c r="D39" t="s">
+      <c r="F39" t="s">
         <v>32</v>
       </c>
-      <c r="E39" t="s">
-        <v>83</v>
-      </c>
-      <c r="F39" t="s">
+      <c r="G39" t="s">
         <v>33</v>
       </c>
     </row>
@@ -2704,16 +2704,16 @@
       <c r="B40" t="s">
         <v>8</v>
       </c>
-      <c r="C40" t="s">
+      <c r="D40" t="s">
+        <v>83</v>
+      </c>
+      <c r="E40" t="s">
         <v>31</v>
       </c>
-      <c r="D40" t="s">
+      <c r="F40" t="s">
         <v>32</v>
       </c>
-      <c r="E40" t="s">
-        <v>83</v>
-      </c>
-      <c r="F40" t="s">
+      <c r="G40" t="s">
         <v>33</v>
       </c>
     </row>
@@ -2724,17 +2724,17 @@
       <c r="B41" t="s">
         <v>8</v>
       </c>
-      <c r="C41" t="s">
-        <v>51</v>
-      </c>
       <c r="D41" t="s">
-        <v>52</v>
+        <v>83</v>
       </c>
       <c r="E41" t="s">
-        <v>83</v>
+        <v>31</v>
       </c>
       <c r="F41" t="s">
-        <v>33</v>
+        <v>53</v>
+      </c>
+      <c r="G41" t="s">
+        <v>54</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -2744,17 +2744,17 @@
       <c r="B42" t="s">
         <v>8</v>
       </c>
-      <c r="C42" t="s">
+      <c r="D42" t="s">
+        <v>83</v>
+      </c>
+      <c r="E42" t="s">
+        <v>31</v>
+      </c>
+      <c r="F42" t="s">
         <v>57</v>
       </c>
-      <c r="D42" t="s">
+      <c r="G42" t="s">
         <v>58</v>
-      </c>
-      <c r="E42" t="s">
-        <v>83</v>
-      </c>
-      <c r="F42" t="s">
-        <v>33</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -2764,16 +2764,16 @@
       <c r="B43" t="s">
         <v>8</v>
       </c>
-      <c r="C43" t="s">
+      <c r="D43" t="s">
         <v>90</v>
       </c>
-      <c r="D43" t="s">
+      <c r="E43" t="s">
         <v>91</v>
       </c>
-      <c r="E43" t="s">
+      <c r="F43" t="s">
         <v>92</v>
       </c>
-      <c r="F43" t="s">
+      <c r="G43" t="s">
         <v>93</v>
       </c>
     </row>
@@ -2784,16 +2784,16 @@
       <c r="B44" t="s">
         <v>8</v>
       </c>
-      <c r="C44" t="s">
+      <c r="D44" t="s">
+        <v>90</v>
+      </c>
+      <c r="E44" t="s">
         <v>95</v>
       </c>
-      <c r="D44" t="s">
+      <c r="F44" t="s">
         <v>96</v>
       </c>
-      <c r="E44" t="s">
-        <v>92</v>
-      </c>
-      <c r="F44" t="s">
+      <c r="G44" t="s">
         <v>97</v>
       </c>
     </row>
@@ -2804,16 +2804,16 @@
       <c r="B45" t="s">
         <v>8</v>
       </c>
-      <c r="C45" t="s">
+      <c r="D45" t="s">
         <v>90</v>
       </c>
-      <c r="D45" t="s">
+      <c r="E45" t="s">
         <v>91</v>
       </c>
-      <c r="E45" t="s">
+      <c r="F45" t="s">
         <v>92</v>
       </c>
-      <c r="F45" t="s">
+      <c r="G45" t="s">
         <v>93</v>
       </c>
     </row>
@@ -2824,16 +2824,16 @@
       <c r="B46" t="s">
         <v>8</v>
       </c>
-      <c r="C46" t="s">
+      <c r="D46" t="s">
         <v>90</v>
       </c>
-      <c r="D46" t="s">
+      <c r="E46" t="s">
         <v>91</v>
       </c>
-      <c r="E46" t="s">
+      <c r="F46" t="s">
         <v>92</v>
       </c>
-      <c r="F46" t="s">
+      <c r="G46" t="s">
         <v>93</v>
       </c>
     </row>
@@ -2844,17 +2844,17 @@
       <c r="B47" t="s">
         <v>8</v>
       </c>
-      <c r="C47" t="s">
+      <c r="D47" t="s">
+        <v>90</v>
+      </c>
+      <c r="E47" t="s">
+        <v>95</v>
+      </c>
+      <c r="F47" t="s">
         <v>101</v>
       </c>
-      <c r="D47" t="s">
+      <c r="G47" t="s">
         <v>102</v>
-      </c>
-      <c r="E47" t="s">
-        <v>92</v>
-      </c>
-      <c r="F47" t="s">
-        <v>97</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -2864,16 +2864,16 @@
       <c r="B48" t="s">
         <v>8</v>
       </c>
-      <c r="C48" t="s">
+      <c r="D48" t="s">
         <v>90</v>
       </c>
-      <c r="D48" t="s">
+      <c r="E48" t="s">
         <v>91</v>
       </c>
-      <c r="E48" t="s">
+      <c r="F48" t="s">
         <v>92</v>
       </c>
-      <c r="F48" t="s">
+      <c r="G48" t="s">
         <v>93</v>
       </c>
     </row>
@@ -2884,16 +2884,16 @@
       <c r="B49" t="s">
         <v>8</v>
       </c>
-      <c r="C49" t="s">
+      <c r="D49" t="s">
         <v>90</v>
       </c>
-      <c r="D49" t="s">
+      <c r="E49" t="s">
         <v>91</v>
       </c>
-      <c r="E49" t="s">
+      <c r="F49" t="s">
         <v>92</v>
       </c>
-      <c r="F49" t="s">
+      <c r="G49" t="s">
         <v>93</v>
       </c>
     </row>
@@ -2904,17 +2904,17 @@
       <c r="B50" t="s">
         <v>8</v>
       </c>
-      <c r="C50" t="s">
+      <c r="D50" t="s">
+        <v>90</v>
+      </c>
+      <c r="E50" t="s">
+        <v>95</v>
+      </c>
+      <c r="F50" t="s">
         <v>101</v>
       </c>
-      <c r="D50" t="s">
+      <c r="G50" t="s">
         <v>102</v>
-      </c>
-      <c r="E50" t="s">
-        <v>92</v>
-      </c>
-      <c r="F50" t="s">
-        <v>97</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -2924,16 +2924,16 @@
       <c r="B51" t="s">
         <v>8</v>
       </c>
-      <c r="C51" t="s">
+      <c r="D51" t="s">
         <v>90</v>
       </c>
-      <c r="D51" t="s">
+      <c r="E51" t="s">
         <v>91</v>
       </c>
-      <c r="E51" t="s">
+      <c r="F51" t="s">
         <v>92</v>
       </c>
-      <c r="F51" t="s">
+      <c r="G51" t="s">
         <v>93</v>
       </c>
     </row>
@@ -2944,17 +2944,17 @@
       <c r="B52" t="s">
         <v>8</v>
       </c>
-      <c r="C52" t="s">
+      <c r="D52" t="s">
+        <v>90</v>
+      </c>
+      <c r="E52" t="s">
+        <v>95</v>
+      </c>
+      <c r="F52" t="s">
         <v>108</v>
       </c>
-      <c r="D52" t="s">
+      <c r="G52" t="s">
         <v>109</v>
-      </c>
-      <c r="E52" t="s">
-        <v>92</v>
-      </c>
-      <c r="F52" t="s">
-        <v>97</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -2964,17 +2964,17 @@
       <c r="B53" t="s">
         <v>8</v>
       </c>
-      <c r="C53" t="s">
-        <v>9</v>
-      </c>
       <c r="D53" t="s">
-        <v>10</v>
+        <v>90</v>
       </c>
       <c r="E53" t="s">
-        <v>92</v>
+        <v>11</v>
       </c>
       <c r="F53" t="s">
         <v>12</v>
+      </c>
+      <c r="G53" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -3008,19 +3008,19 @@
         <v>8</v>
       </c>
       <c r="C55" t="s">
-        <v>118</v>
+        <v>112</v>
       </c>
       <c r="D55" t="s">
-        <v>119</v>
+        <v>113</v>
       </c>
       <c r="E55" t="s">
         <v>114</v>
       </c>
       <c r="F55" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="G55" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -3031,19 +3031,19 @@
         <v>8</v>
       </c>
       <c r="C56" t="s">
-        <v>121</v>
+        <v>112</v>
       </c>
       <c r="D56" t="s">
-        <v>122</v>
+        <v>113</v>
       </c>
       <c r="E56" t="s">
         <v>114</v>
       </c>
       <c r="F56" t="s">
-        <v>115</v>
+        <v>121</v>
       </c>
       <c r="G56" t="s">
-        <v>116</v>
+        <v>122</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -3054,19 +3054,19 @@
         <v>8</v>
       </c>
       <c r="C57" t="s">
+        <v>112</v>
+      </c>
+      <c r="D57" t="s">
+        <v>113</v>
+      </c>
+      <c r="E57" t="s">
         <v>124</v>
       </c>
-      <c r="D57" t="s">
+      <c r="F57" t="s">
         <v>125</v>
       </c>
-      <c r="E57" t="s">
-        <v>114</v>
-      </c>
-      <c r="F57" t="s">
+      <c r="G57" t="s">
         <v>126</v>
-      </c>
-      <c r="G57" t="s">
-        <v>116</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -3077,19 +3077,19 @@
         <v>8</v>
       </c>
       <c r="C58" t="s">
-        <v>118</v>
+        <v>112</v>
       </c>
       <c r="D58" t="s">
-        <v>119</v>
+        <v>113</v>
       </c>
       <c r="E58" t="s">
         <v>114</v>
       </c>
       <c r="F58" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="G58" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -3100,19 +3100,19 @@
         <v>8</v>
       </c>
       <c r="C59" t="s">
-        <v>118</v>
+        <v>112</v>
       </c>
       <c r="D59" t="s">
-        <v>119</v>
+        <v>113</v>
       </c>
       <c r="E59" t="s">
         <v>114</v>
       </c>
       <c r="F59" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="G59" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -3123,19 +3123,19 @@
         <v>8</v>
       </c>
       <c r="C60" t="s">
-        <v>118</v>
+        <v>112</v>
       </c>
       <c r="D60" t="s">
-        <v>119</v>
+        <v>113</v>
       </c>
       <c r="E60" t="s">
         <v>114</v>
       </c>
       <c r="F60" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="G60" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -3146,19 +3146,19 @@
         <v>8</v>
       </c>
       <c r="C61" t="s">
-        <v>118</v>
+        <v>112</v>
       </c>
       <c r="D61" t="s">
-        <v>119</v>
+        <v>113</v>
       </c>
       <c r="E61" t="s">
         <v>114</v>
       </c>
       <c r="F61" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="G61" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -3169,19 +3169,19 @@
         <v>8</v>
       </c>
       <c r="C62" t="s">
-        <v>118</v>
+        <v>112</v>
       </c>
       <c r="D62" t="s">
-        <v>119</v>
+        <v>113</v>
       </c>
       <c r="E62" t="s">
         <v>114</v>
       </c>
       <c r="F62" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="G62" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -3192,19 +3192,19 @@
         <v>8</v>
       </c>
       <c r="C63" t="s">
-        <v>133</v>
+        <v>112</v>
       </c>
       <c r="D63" t="s">
-        <v>119</v>
+        <v>113</v>
       </c>
       <c r="E63" t="s">
         <v>114</v>
       </c>
       <c r="F63" t="s">
-        <v>115</v>
+        <v>133</v>
       </c>
       <c r="G63" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -3215,19 +3215,19 @@
         <v>8</v>
       </c>
       <c r="C64" t="s">
-        <v>133</v>
+        <v>112</v>
       </c>
       <c r="D64" t="s">
-        <v>119</v>
+        <v>113</v>
       </c>
       <c r="E64" t="s">
         <v>114</v>
       </c>
       <c r="F64" t="s">
-        <v>115</v>
+        <v>133</v>
       </c>
       <c r="G64" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -3238,19 +3238,19 @@
         <v>8</v>
       </c>
       <c r="C65" t="s">
-        <v>136</v>
+        <v>112</v>
       </c>
       <c r="D65" t="s">
-        <v>137</v>
+        <v>113</v>
       </c>
       <c r="E65" t="s">
         <v>114</v>
       </c>
       <c r="F65" t="s">
-        <v>115</v>
+        <v>136</v>
       </c>
       <c r="G65" t="s">
-        <v>116</v>
+        <v>137</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -3284,19 +3284,19 @@
         <v>8</v>
       </c>
       <c r="C67" t="s">
-        <v>118</v>
+        <v>112</v>
       </c>
       <c r="D67" t="s">
-        <v>119</v>
+        <v>113</v>
       </c>
       <c r="E67" t="s">
         <v>114</v>
       </c>
       <c r="F67" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="G67" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -3307,7 +3307,7 @@
         <v>8</v>
       </c>
       <c r="C68" t="s">
-        <v>141</v>
+        <v>112</v>
       </c>
       <c r="D68" t="s">
         <v>113</v>
@@ -3316,7 +3316,7 @@
         <v>114</v>
       </c>
       <c r="F68" t="s">
-        <v>115</v>
+        <v>141</v>
       </c>
       <c r="G68" t="s">
         <v>116</v>
@@ -3330,7 +3330,7 @@
         <v>8</v>
       </c>
       <c r="C69" t="s">
-        <v>143</v>
+        <v>112</v>
       </c>
       <c r="D69" t="s">
         <v>113</v>
@@ -3339,7 +3339,7 @@
         <v>114</v>
       </c>
       <c r="F69" t="s">
-        <v>115</v>
+        <v>143</v>
       </c>
       <c r="G69" t="s">
         <v>116</v>
@@ -3353,19 +3353,19 @@
         <v>8</v>
       </c>
       <c r="C70" t="s">
-        <v>121</v>
+        <v>112</v>
       </c>
       <c r="D70" t="s">
-        <v>122</v>
+        <v>113</v>
       </c>
       <c r="E70" t="s">
         <v>114</v>
       </c>
       <c r="F70" t="s">
-        <v>115</v>
+        <v>121</v>
       </c>
       <c r="G70" t="s">
-        <v>116</v>
+        <v>122</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -3376,19 +3376,19 @@
         <v>8</v>
       </c>
       <c r="C71" t="s">
-        <v>121</v>
+        <v>112</v>
       </c>
       <c r="D71" t="s">
-        <v>122</v>
+        <v>113</v>
       </c>
       <c r="E71" t="s">
         <v>114</v>
       </c>
       <c r="F71" t="s">
-        <v>115</v>
+        <v>121</v>
       </c>
       <c r="G71" t="s">
-        <v>116</v>
+        <v>122</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -3422,19 +3422,19 @@
         <v>8</v>
       </c>
       <c r="C73" t="s">
+        <v>112</v>
+      </c>
+      <c r="D73" t="s">
+        <v>113</v>
+      </c>
+      <c r="E73" t="s">
+        <v>124</v>
+      </c>
+      <c r="F73" t="s">
         <v>148</v>
       </c>
-      <c r="D73" t="s">
+      <c r="G73" t="s">
         <v>149</v>
-      </c>
-      <c r="E73" t="s">
-        <v>114</v>
-      </c>
-      <c r="F73" t="s">
-        <v>126</v>
-      </c>
-      <c r="G73" t="s">
-        <v>116</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -3445,19 +3445,19 @@
         <v>8</v>
       </c>
       <c r="C74" t="s">
+        <v>112</v>
+      </c>
+      <c r="D74" t="s">
+        <v>113</v>
+      </c>
+      <c r="E74" t="s">
+        <v>124</v>
+      </c>
+      <c r="F74" t="s">
         <v>151</v>
       </c>
-      <c r="D74" t="s">
+      <c r="G74" t="s">
         <v>152</v>
-      </c>
-      <c r="E74" t="s">
-        <v>114</v>
-      </c>
-      <c r="F74" t="s">
-        <v>126</v>
-      </c>
-      <c r="G74" t="s">
-        <v>116</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -3468,19 +3468,19 @@
         <v>8</v>
       </c>
       <c r="C75" t="s">
+        <v>112</v>
+      </c>
+      <c r="D75" t="s">
+        <v>113</v>
+      </c>
+      <c r="E75" t="s">
+        <v>124</v>
+      </c>
+      <c r="F75" t="s">
         <v>154</v>
       </c>
-      <c r="D75" t="s">
+      <c r="G75" t="s">
         <v>155</v>
-      </c>
-      <c r="E75" t="s">
-        <v>114</v>
-      </c>
-      <c r="F75" t="s">
-        <v>126</v>
-      </c>
-      <c r="G75" t="s">
-        <v>116</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -3491,19 +3491,19 @@
         <v>8</v>
       </c>
       <c r="C76" t="s">
+        <v>112</v>
+      </c>
+      <c r="D76" t="s">
+        <v>113</v>
+      </c>
+      <c r="E76" t="s">
+        <v>124</v>
+      </c>
+      <c r="F76" t="s">
         <v>148</v>
       </c>
-      <c r="D76" t="s">
+      <c r="G76" t="s">
         <v>149</v>
-      </c>
-      <c r="E76" t="s">
-        <v>114</v>
-      </c>
-      <c r="F76" t="s">
-        <v>126</v>
-      </c>
-      <c r="G76" t="s">
-        <v>116</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -3514,19 +3514,19 @@
         <v>8</v>
       </c>
       <c r="C77" t="s">
+        <v>112</v>
+      </c>
+      <c r="D77" t="s">
+        <v>113</v>
+      </c>
+      <c r="E77" t="s">
+        <v>124</v>
+      </c>
+      <c r="F77" t="s">
         <v>148</v>
       </c>
-      <c r="D77" t="s">
+      <c r="G77" t="s">
         <v>149</v>
-      </c>
-      <c r="E77" t="s">
-        <v>114</v>
-      </c>
-      <c r="F77" t="s">
-        <v>126</v>
-      </c>
-      <c r="G77" t="s">
-        <v>116</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -3537,19 +3537,19 @@
         <v>8</v>
       </c>
       <c r="C78" t="s">
+        <v>112</v>
+      </c>
+      <c r="D78" t="s">
+        <v>113</v>
+      </c>
+      <c r="E78" t="s">
+        <v>124</v>
+      </c>
+      <c r="F78" t="s">
         <v>151</v>
       </c>
-      <c r="D78" t="s">
+      <c r="G78" t="s">
         <v>152</v>
-      </c>
-      <c r="E78" t="s">
-        <v>114</v>
-      </c>
-      <c r="F78" t="s">
-        <v>126</v>
-      </c>
-      <c r="G78" t="s">
-        <v>116</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -3560,19 +3560,19 @@
         <v>8</v>
       </c>
       <c r="C79" t="s">
+        <v>112</v>
+      </c>
+      <c r="D79" t="s">
+        <v>113</v>
+      </c>
+      <c r="E79" t="s">
+        <v>124</v>
+      </c>
+      <c r="F79" t="s">
         <v>160</v>
       </c>
-      <c r="D79" t="s">
+      <c r="G79" t="s">
         <v>161</v>
-      </c>
-      <c r="E79" t="s">
-        <v>114</v>
-      </c>
-      <c r="F79" t="s">
-        <v>126</v>
-      </c>
-      <c r="G79" t="s">
-        <v>116</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -3583,19 +3583,19 @@
         <v>8</v>
       </c>
       <c r="C80" t="s">
-        <v>163</v>
+        <v>112</v>
       </c>
       <c r="D80" t="s">
+        <v>113</v>
+      </c>
+      <c r="E80" t="s">
+        <v>163</v>
+      </c>
+      <c r="F80" t="s">
         <v>164</v>
       </c>
-      <c r="E80" t="s">
-        <v>114</v>
-      </c>
-      <c r="F80" t="s">
+      <c r="G80" t="s">
         <v>165</v>
-      </c>
-      <c r="G80" t="s">
-        <v>116</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -3606,19 +3606,19 @@
         <v>8</v>
       </c>
       <c r="C81" t="s">
-        <v>163</v>
+        <v>112</v>
       </c>
       <c r="D81" t="s">
+        <v>113</v>
+      </c>
+      <c r="E81" t="s">
+        <v>163</v>
+      </c>
+      <c r="F81" t="s">
         <v>164</v>
       </c>
-      <c r="E81" t="s">
-        <v>114</v>
-      </c>
-      <c r="F81" t="s">
+      <c r="G81" t="s">
         <v>165</v>
-      </c>
-      <c r="G81" t="s">
-        <v>116</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -3629,19 +3629,19 @@
         <v>8</v>
       </c>
       <c r="C82" t="s">
-        <v>163</v>
+        <v>112</v>
       </c>
       <c r="D82" t="s">
+        <v>113</v>
+      </c>
+      <c r="E82" t="s">
+        <v>163</v>
+      </c>
+      <c r="F82" t="s">
         <v>164</v>
       </c>
-      <c r="E82" t="s">
-        <v>114</v>
-      </c>
-      <c r="F82" t="s">
+      <c r="G82" t="s">
         <v>165</v>
-      </c>
-      <c r="G82" t="s">
-        <v>116</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -3652,7 +3652,7 @@
         <v>8</v>
       </c>
       <c r="C83" t="s">
-        <v>143</v>
+        <v>112</v>
       </c>
       <c r="D83" t="s">
         <v>113</v>
@@ -3661,7 +3661,7 @@
         <v>114</v>
       </c>
       <c r="F83" t="s">
-        <v>115</v>
+        <v>143</v>
       </c>
       <c r="G83" t="s">
         <v>116</v>
@@ -3675,19 +3675,19 @@
         <v>8</v>
       </c>
       <c r="C84" t="s">
-        <v>170</v>
+        <v>112</v>
       </c>
       <c r="D84" t="s">
-        <v>171</v>
+        <v>113</v>
       </c>
       <c r="E84" t="s">
         <v>114</v>
       </c>
       <c r="F84" t="s">
-        <v>115</v>
+        <v>170</v>
       </c>
       <c r="G84" t="s">
-        <v>116</v>
+        <v>171</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -3698,19 +3698,19 @@
         <v>8</v>
       </c>
       <c r="C85" t="s">
-        <v>173</v>
+        <v>112</v>
       </c>
       <c r="D85" t="s">
-        <v>119</v>
+        <v>113</v>
       </c>
       <c r="E85" t="s">
         <v>114</v>
       </c>
       <c r="F85" t="s">
-        <v>115</v>
+        <v>173</v>
       </c>
       <c r="G85" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -3721,19 +3721,19 @@
         <v>8</v>
       </c>
       <c r="C86" t="s">
+        <v>112</v>
+      </c>
+      <c r="D86" t="s">
+        <v>113</v>
+      </c>
+      <c r="E86" t="s">
+        <v>163</v>
+      </c>
+      <c r="F86" t="s">
         <v>175</v>
       </c>
-      <c r="D86" t="s">
+      <c r="G86" t="s">
         <v>176</v>
-      </c>
-      <c r="E86" t="s">
-        <v>114</v>
-      </c>
-      <c r="F86" t="s">
-        <v>165</v>
-      </c>
-      <c r="G86" t="s">
-        <v>116</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -3744,19 +3744,19 @@
         <v>8</v>
       </c>
       <c r="C87" t="s">
-        <v>173</v>
+        <v>112</v>
       </c>
       <c r="D87" t="s">
-        <v>119</v>
+        <v>113</v>
       </c>
       <c r="E87" t="s">
         <v>114</v>
       </c>
       <c r="F87" t="s">
-        <v>115</v>
+        <v>173</v>
       </c>
       <c r="G87" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -3767,19 +3767,19 @@
         <v>8</v>
       </c>
       <c r="C88" t="s">
-        <v>118</v>
+        <v>112</v>
       </c>
       <c r="D88" t="s">
-        <v>119</v>
+        <v>113</v>
       </c>
       <c r="E88" t="s">
         <v>114</v>
       </c>
       <c r="F88" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="G88" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -3790,19 +3790,19 @@
         <v>8</v>
       </c>
       <c r="C89" t="s">
-        <v>118</v>
+        <v>112</v>
       </c>
       <c r="D89" t="s">
-        <v>119</v>
+        <v>113</v>
       </c>
       <c r="E89" t="s">
         <v>114</v>
       </c>
       <c r="F89" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="G89" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -3813,19 +3813,19 @@
         <v>8</v>
       </c>
       <c r="C90" t="s">
+        <v>112</v>
+      </c>
+      <c r="D90" t="s">
+        <v>113</v>
+      </c>
+      <c r="E90" t="s">
         <v>124</v>
       </c>
-      <c r="D90" t="s">
+      <c r="F90" t="s">
         <v>125</v>
       </c>
-      <c r="E90" t="s">
-        <v>114</v>
-      </c>
-      <c r="F90" t="s">
+      <c r="G90" t="s">
         <v>126</v>
-      </c>
-      <c r="G90" t="s">
-        <v>116</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -3836,19 +3836,19 @@
         <v>8</v>
       </c>
       <c r="C91" t="s">
+        <v>112</v>
+      </c>
+      <c r="D91" t="s">
+        <v>113</v>
+      </c>
+      <c r="E91" t="s">
         <v>182</v>
       </c>
-      <c r="D91" t="s">
+      <c r="F91" t="s">
         <v>183</v>
       </c>
-      <c r="E91" t="s">
-        <v>114</v>
-      </c>
-      <c r="F91" t="s">
+      <c r="G91" t="s">
         <v>184</v>
-      </c>
-      <c r="G91" t="s">
-        <v>116</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -3859,19 +3859,19 @@
         <v>8</v>
       </c>
       <c r="C92" t="s">
+        <v>112</v>
+      </c>
+      <c r="D92" t="s">
+        <v>113</v>
+      </c>
+      <c r="E92" t="s">
         <v>124</v>
       </c>
-      <c r="D92" t="s">
+      <c r="F92" t="s">
         <v>125</v>
       </c>
-      <c r="E92" t="s">
-        <v>114</v>
-      </c>
-      <c r="F92" t="s">
+      <c r="G92" t="s">
         <v>126</v>
-      </c>
-      <c r="G92" t="s">
-        <v>116</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -3882,19 +3882,19 @@
         <v>8</v>
       </c>
       <c r="C93" t="s">
-        <v>121</v>
+        <v>112</v>
       </c>
       <c r="D93" t="s">
-        <v>122</v>
+        <v>113</v>
       </c>
       <c r="E93" t="s">
         <v>114</v>
       </c>
       <c r="F93" t="s">
-        <v>115</v>
+        <v>121</v>
       </c>
       <c r="G93" t="s">
-        <v>116</v>
+        <v>122</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -3905,19 +3905,19 @@
         <v>8</v>
       </c>
       <c r="C94" t="s">
+        <v>112</v>
+      </c>
+      <c r="D94" t="s">
+        <v>113</v>
+      </c>
+      <c r="E94" t="s">
         <v>124</v>
       </c>
-      <c r="D94" t="s">
+      <c r="F94" t="s">
         <v>125</v>
       </c>
-      <c r="E94" t="s">
-        <v>114</v>
-      </c>
-      <c r="F94" t="s">
+      <c r="G94" t="s">
         <v>126</v>
-      </c>
-      <c r="G94" t="s">
-        <v>116</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -3928,19 +3928,19 @@
         <v>8</v>
       </c>
       <c r="C95" t="s">
-        <v>189</v>
+        <v>112</v>
       </c>
       <c r="D95" t="s">
-        <v>190</v>
+        <v>113</v>
       </c>
       <c r="E95" t="s">
         <v>114</v>
       </c>
       <c r="F95" t="s">
-        <v>115</v>
+        <v>189</v>
       </c>
       <c r="G95" t="s">
-        <v>116</v>
+        <v>190</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -3951,19 +3951,19 @@
         <v>8</v>
       </c>
       <c r="C96" t="s">
+        <v>192</v>
+      </c>
+      <c r="D96" t="s">
+        <v>113</v>
+      </c>
+      <c r="E96" t="s">
         <v>124</v>
       </c>
-      <c r="D96" t="s">
+      <c r="F96" t="s">
         <v>125</v>
       </c>
-      <c r="E96" t="s">
-        <v>114</v>
-      </c>
-      <c r="F96" t="s">
+      <c r="G96" t="s">
         <v>126</v>
-      </c>
-      <c r="G96" t="s">
-        <v>192</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -3974,19 +3974,19 @@
         <v>8</v>
       </c>
       <c r="C97" t="s">
+        <v>192</v>
+      </c>
+      <c r="D97" t="s">
+        <v>113</v>
+      </c>
+      <c r="E97" t="s">
         <v>124</v>
       </c>
-      <c r="D97" t="s">
+      <c r="F97" t="s">
         <v>125</v>
       </c>
-      <c r="E97" t="s">
-        <v>114</v>
-      </c>
-      <c r="F97" t="s">
+      <c r="G97" t="s">
         <v>126</v>
-      </c>
-      <c r="G97" t="s">
-        <v>192</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -3997,19 +3997,19 @@
         <v>8</v>
       </c>
       <c r="C98" t="s">
+        <v>192</v>
+      </c>
+      <c r="D98" t="s">
+        <v>113</v>
+      </c>
+      <c r="E98" t="s">
         <v>195</v>
       </c>
-      <c r="D98" t="s">
+      <c r="F98" t="s">
         <v>196</v>
       </c>
-      <c r="E98" t="s">
-        <v>114</v>
-      </c>
-      <c r="F98" t="s">
+      <c r="G98" t="s">
         <v>197</v>
-      </c>
-      <c r="G98" t="s">
-        <v>192</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -4020,19 +4020,19 @@
         <v>8</v>
       </c>
       <c r="C99" t="s">
+        <v>192</v>
+      </c>
+      <c r="D99" t="s">
+        <v>113</v>
+      </c>
+      <c r="E99" t="s">
         <v>124</v>
       </c>
-      <c r="D99" t="s">
+      <c r="F99" t="s">
         <v>125</v>
       </c>
-      <c r="E99" t="s">
-        <v>114</v>
-      </c>
-      <c r="F99" t="s">
+      <c r="G99" t="s">
         <v>126</v>
-      </c>
-      <c r="G99" t="s">
-        <v>192</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -4043,19 +4043,19 @@
         <v>8</v>
       </c>
       <c r="C100" t="s">
+        <v>192</v>
+      </c>
+      <c r="D100" t="s">
+        <v>113</v>
+      </c>
+      <c r="E100" t="s">
+        <v>124</v>
+      </c>
+      <c r="F100" t="s">
         <v>154</v>
       </c>
-      <c r="D100" t="s">
+      <c r="G100" t="s">
         <v>155</v>
-      </c>
-      <c r="E100" t="s">
-        <v>114</v>
-      </c>
-      <c r="F100" t="s">
-        <v>126</v>
-      </c>
-      <c r="G100" t="s">
-        <v>192</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -4066,19 +4066,19 @@
         <v>8</v>
       </c>
       <c r="C101" t="s">
+        <v>192</v>
+      </c>
+      <c r="D101" t="s">
+        <v>113</v>
+      </c>
+      <c r="E101" t="s">
         <v>124</v>
       </c>
-      <c r="D101" t="s">
+      <c r="F101" t="s">
         <v>125</v>
       </c>
-      <c r="E101" t="s">
-        <v>114</v>
-      </c>
-      <c r="F101" t="s">
+      <c r="G101" t="s">
         <v>126</v>
-      </c>
-      <c r="G101" t="s">
-        <v>192</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -4088,17 +4088,17 @@
       <c r="B102" t="s">
         <v>8</v>
       </c>
-      <c r="C102" t="s">
+      <c r="D102" t="s">
         <v>202</v>
       </c>
-      <c r="D102" t="s">
+      <c r="E102" t="s">
+        <v>182</v>
+      </c>
+      <c r="F102" t="s">
         <v>203</v>
       </c>
-      <c r="E102" t="s">
+      <c r="G102" t="s">
         <v>204</v>
-      </c>
-      <c r="F102" t="s">
-        <v>184</v>
       </c>
     </row>
     <row r="103" spans="1:7">
@@ -4108,17 +4108,17 @@
       <c r="B103" t="s">
         <v>8</v>
       </c>
-      <c r="C103" t="s">
+      <c r="D103" t="s">
         <v>202</v>
       </c>
-      <c r="D103" t="s">
+      <c r="E103" t="s">
+        <v>182</v>
+      </c>
+      <c r="F103" t="s">
         <v>203</v>
       </c>
-      <c r="E103" t="s">
+      <c r="G103" t="s">
         <v>204</v>
-      </c>
-      <c r="F103" t="s">
-        <v>184</v>
       </c>
     </row>
     <row r="104" spans="1:7">
@@ -4128,17 +4128,17 @@
       <c r="B104" t="s">
         <v>8</v>
       </c>
-      <c r="C104" t="s">
+      <c r="D104" t="s">
         <v>202</v>
       </c>
-      <c r="D104" t="s">
+      <c r="E104" t="s">
+        <v>182</v>
+      </c>
+      <c r="F104" t="s">
         <v>203</v>
       </c>
-      <c r="E104" t="s">
+      <c r="G104" t="s">
         <v>204</v>
-      </c>
-      <c r="F104" t="s">
-        <v>184</v>
       </c>
     </row>
     <row r="105" spans="1:7">
@@ -4148,17 +4148,17 @@
       <c r="B105" t="s">
         <v>8</v>
       </c>
-      <c r="C105" t="s">
+      <c r="D105" t="s">
+        <v>202</v>
+      </c>
+      <c r="E105" t="s">
+        <v>182</v>
+      </c>
+      <c r="F105" t="s">
         <v>208</v>
       </c>
-      <c r="D105" t="s">
+      <c r="G105" t="s">
         <v>209</v>
-      </c>
-      <c r="E105" t="s">
-        <v>204</v>
-      </c>
-      <c r="F105" t="s">
-        <v>184</v>
       </c>
     </row>
     <row r="106" spans="1:7">
@@ -4168,17 +4168,17 @@
       <c r="B106" t="s">
         <v>8</v>
       </c>
-      <c r="C106" t="s">
+      <c r="D106" t="s">
         <v>202</v>
       </c>
-      <c r="D106" t="s">
+      <c r="E106" t="s">
+        <v>182</v>
+      </c>
+      <c r="F106" t="s">
         <v>203</v>
       </c>
-      <c r="E106" t="s">
+      <c r="G106" t="s">
         <v>204</v>
-      </c>
-      <c r="F106" t="s">
-        <v>184</v>
       </c>
     </row>
     <row r="107" spans="1:7">
@@ -4188,16 +4188,16 @@
       <c r="B107" t="s">
         <v>8</v>
       </c>
-      <c r="C107" t="s">
+      <c r="D107" t="s">
+        <v>202</v>
+      </c>
+      <c r="E107" t="s">
         <v>182</v>
       </c>
-      <c r="D107" t="s">
+      <c r="F107" t="s">
         <v>183</v>
       </c>
-      <c r="E107" t="s">
-        <v>204</v>
-      </c>
-      <c r="F107" t="s">
+      <c r="G107" t="s">
         <v>184</v>
       </c>
     </row>
@@ -4208,17 +4208,17 @@
       <c r="B108" t="s">
         <v>8</v>
       </c>
-      <c r="C108" t="s">
+      <c r="D108" t="s">
+        <v>202</v>
+      </c>
+      <c r="E108" t="s">
+        <v>182</v>
+      </c>
+      <c r="F108" t="s">
         <v>213</v>
       </c>
-      <c r="D108" t="s">
+      <c r="G108" t="s">
         <v>214</v>
-      </c>
-      <c r="E108" t="s">
-        <v>204</v>
-      </c>
-      <c r="F108" t="s">
-        <v>184</v>
       </c>
     </row>
     <row r="109" spans="1:7">
@@ -4228,17 +4228,17 @@
       <c r="B109" t="s">
         <v>8</v>
       </c>
-      <c r="C109" t="s">
+      <c r="D109" t="s">
+        <v>202</v>
+      </c>
+      <c r="E109" t="s">
+        <v>91</v>
+      </c>
+      <c r="F109" t="s">
         <v>216</v>
       </c>
-      <c r="D109" t="s">
+      <c r="G109" t="s">
         <v>217</v>
-      </c>
-      <c r="E109" t="s">
-        <v>204</v>
-      </c>
-      <c r="F109" t="s">
-        <v>93</v>
       </c>
     </row>
     <row r="110" spans="1:7">
@@ -4248,17 +4248,17 @@
       <c r="B110" t="s">
         <v>8</v>
       </c>
-      <c r="C110" t="s">
+      <c r="D110" t="s">
+        <v>202</v>
+      </c>
+      <c r="E110" t="s">
+        <v>91</v>
+      </c>
+      <c r="F110" t="s">
         <v>219</v>
       </c>
-      <c r="D110" t="s">
+      <c r="G110" t="s">
         <v>220</v>
-      </c>
-      <c r="E110" t="s">
-        <v>204</v>
-      </c>
-      <c r="F110" t="s">
-        <v>93</v>
       </c>
     </row>
     <row r="111" spans="1:7">
@@ -4268,17 +4268,17 @@
       <c r="B111" t="s">
         <v>8</v>
       </c>
-      <c r="C111" t="s">
+      <c r="D111" t="s">
         <v>202</v>
       </c>
-      <c r="D111" t="s">
+      <c r="E111" t="s">
+        <v>182</v>
+      </c>
+      <c r="F111" t="s">
         <v>203</v>
       </c>
-      <c r="E111" t="s">
+      <c r="G111" t="s">
         <v>204</v>
-      </c>
-      <c r="F111" t="s">
-        <v>184</v>
       </c>
     </row>
     <row r="112" spans="1:7">
@@ -4288,337 +4288,337 @@
       <c r="B112" t="s">
         <v>8</v>
       </c>
-      <c r="C112" t="s">
+      <c r="D112" t="s">
+        <v>202</v>
+      </c>
+      <c r="E112" t="s">
         <v>223</v>
       </c>
-      <c r="D112" t="s">
+      <c r="F112" t="s">
         <v>224</v>
       </c>
-      <c r="E112" t="s">
-        <v>204</v>
-      </c>
-      <c r="F112" t="s">
+      <c r="G112" t="s">
         <v>225</v>
       </c>
     </row>
-    <row r="113" spans="1:6">
+    <row r="113" spans="1:7">
       <c r="A113" t="s">
         <v>226</v>
       </c>
       <c r="B113" t="s">
         <v>8</v>
       </c>
-      <c r="C113" t="s">
+      <c r="D113" t="s">
+        <v>202</v>
+      </c>
+      <c r="E113" t="s">
+        <v>114</v>
+      </c>
+      <c r="F113" t="s">
         <v>143</v>
       </c>
-      <c r="D113" t="s">
-        <v>113</v>
-      </c>
-      <c r="E113" t="s">
-        <v>204</v>
-      </c>
-      <c r="F113" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="114" spans="1:6">
+      <c r="G113" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="114" spans="1:7">
       <c r="A114" t="s">
         <v>227</v>
       </c>
       <c r="B114" t="s">
         <v>8</v>
       </c>
-      <c r="C114" t="s">
+      <c r="D114" t="s">
+        <v>202</v>
+      </c>
+      <c r="E114" t="s">
+        <v>124</v>
+      </c>
+      <c r="F114" t="s">
         <v>151</v>
       </c>
-      <c r="D114" t="s">
+      <c r="G114" t="s">
         <v>152</v>
       </c>
-      <c r="E114" t="s">
-        <v>204</v>
-      </c>
-      <c r="F114" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="115" spans="1:6">
+    </row>
+    <row r="115" spans="1:7">
       <c r="A115" t="s">
         <v>228</v>
       </c>
       <c r="B115" t="s">
         <v>8</v>
       </c>
-      <c r="C115" t="s">
+      <c r="D115" t="s">
+        <v>202</v>
+      </c>
+      <c r="E115" t="s">
         <v>182</v>
       </c>
-      <c r="D115" t="s">
+      <c r="F115" t="s">
         <v>183</v>
       </c>
-      <c r="E115" t="s">
-        <v>204</v>
-      </c>
-      <c r="F115" t="s">
+      <c r="G115" t="s">
         <v>184</v>
       </c>
     </row>
-    <row r="116" spans="1:6">
+    <row r="116" spans="1:7">
       <c r="A116" t="s">
         <v>229</v>
       </c>
       <c r="B116" t="s">
         <v>8</v>
       </c>
-      <c r="C116" t="s">
+      <c r="D116" t="s">
+        <v>202</v>
+      </c>
+      <c r="E116" t="s">
+        <v>223</v>
+      </c>
+      <c r="F116" t="s">
         <v>230</v>
       </c>
-      <c r="D116" t="s">
+      <c r="G116" t="s">
         <v>231</v>
       </c>
-      <c r="E116" t="s">
-        <v>204</v>
-      </c>
-      <c r="F116" t="s">
-        <v>225</v>
-      </c>
-    </row>
-    <row r="117" spans="1:6">
+    </row>
+    <row r="117" spans="1:7">
       <c r="A117" t="s">
         <v>232</v>
       </c>
       <c r="B117" t="s">
         <v>8</v>
       </c>
-      <c r="C117" t="s">
+      <c r="D117" t="s">
+        <v>202</v>
+      </c>
+      <c r="E117" t="s">
         <v>223</v>
       </c>
-      <c r="D117" t="s">
+      <c r="F117" t="s">
         <v>224</v>
       </c>
-      <c r="E117" t="s">
-        <v>204</v>
-      </c>
-      <c r="F117" t="s">
+      <c r="G117" t="s">
         <v>225</v>
       </c>
     </row>
-    <row r="118" spans="1:6">
+    <row r="118" spans="1:7">
       <c r="A118" t="s">
         <v>233</v>
       </c>
       <c r="B118" t="s">
         <v>8</v>
       </c>
-      <c r="C118" t="s">
+      <c r="D118" t="s">
+        <v>202</v>
+      </c>
+      <c r="E118" t="s">
+        <v>163</v>
+      </c>
+      <c r="F118" t="s">
         <v>234</v>
       </c>
-      <c r="D118" t="s">
-        <v>164</v>
-      </c>
-      <c r="E118" t="s">
-        <v>204</v>
-      </c>
-      <c r="F118" t="s">
+      <c r="G118" t="s">
         <v>165</v>
       </c>
     </row>
-    <row r="119" spans="1:6">
+    <row r="119" spans="1:7">
       <c r="A119" t="s">
         <v>235</v>
       </c>
       <c r="B119" t="s">
         <v>8</v>
       </c>
-      <c r="C119" t="s">
+      <c r="D119" t="s">
+        <v>202</v>
+      </c>
+      <c r="E119" t="s">
         <v>182</v>
       </c>
-      <c r="D119" t="s">
+      <c r="F119" t="s">
         <v>183</v>
       </c>
-      <c r="E119" t="s">
-        <v>204</v>
-      </c>
-      <c r="F119" t="s">
+      <c r="G119" t="s">
         <v>184</v>
       </c>
     </row>
-    <row r="120" spans="1:6">
+    <row r="120" spans="1:7">
       <c r="A120" t="s">
         <v>236</v>
       </c>
       <c r="B120" t="s">
         <v>8</v>
       </c>
-      <c r="C120" t="s">
+      <c r="D120" t="s">
+        <v>237</v>
+      </c>
+      <c r="E120" t="s">
+        <v>114</v>
+      </c>
+      <c r="F120" t="s">
         <v>170</v>
       </c>
-      <c r="D120" t="s">
+      <c r="G120" t="s">
         <v>171</v>
       </c>
-      <c r="E120" t="s">
-        <v>237</v>
-      </c>
-      <c r="F120" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="121" spans="1:6">
+    </row>
+    <row r="121" spans="1:7">
       <c r="A121" t="s">
         <v>238</v>
       </c>
       <c r="B121" t="s">
         <v>8</v>
       </c>
-      <c r="C121" t="s">
+      <c r="D121" t="s">
+        <v>237</v>
+      </c>
+      <c r="E121" t="s">
+        <v>114</v>
+      </c>
+      <c r="F121" t="s">
         <v>143</v>
       </c>
-      <c r="D121" t="s">
-        <v>113</v>
-      </c>
-      <c r="E121" t="s">
-        <v>237</v>
-      </c>
-      <c r="F121" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="122" spans="1:6">
+      <c r="G121" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="122" spans="1:7">
       <c r="A122" t="s">
         <v>239</v>
       </c>
       <c r="B122" t="s">
         <v>8</v>
       </c>
-      <c r="C122" t="s">
+      <c r="D122" t="s">
+        <v>237</v>
+      </c>
+      <c r="E122" t="s">
+        <v>114</v>
+      </c>
+      <c r="F122" t="s">
         <v>170</v>
       </c>
-      <c r="D122" t="s">
+      <c r="G122" t="s">
         <v>171</v>
       </c>
-      <c r="E122" t="s">
-        <v>237</v>
-      </c>
-      <c r="F122" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="123" spans="1:6">
+    </row>
+    <row r="123" spans="1:7">
       <c r="A123" t="s">
         <v>240</v>
       </c>
       <c r="B123" t="s">
         <v>8</v>
       </c>
-      <c r="C123" t="s">
+      <c r="D123" t="s">
+        <v>237</v>
+      </c>
+      <c r="E123" t="s">
+        <v>114</v>
+      </c>
+      <c r="F123" t="s">
         <v>170</v>
       </c>
-      <c r="D123" t="s">
+      <c r="G123" t="s">
         <v>171</v>
       </c>
-      <c r="E123" t="s">
-        <v>237</v>
-      </c>
-      <c r="F123" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="124" spans="1:6">
+    </row>
+    <row r="124" spans="1:7">
       <c r="A124" t="s">
         <v>241</v>
       </c>
       <c r="B124" t="s">
         <v>8</v>
       </c>
-      <c r="C124" t="s">
+      <c r="D124" t="s">
+        <v>237</v>
+      </c>
+      <c r="E124" t="s">
+        <v>163</v>
+      </c>
+      <c r="F124" t="s">
         <v>242</v>
       </c>
-      <c r="D124" t="s">
+      <c r="G124" t="s">
         <v>243</v>
       </c>
-      <c r="E124" t="s">
-        <v>237</v>
-      </c>
-      <c r="F124" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="125" spans="1:6">
+    </row>
+    <row r="125" spans="1:7">
       <c r="A125" t="s">
         <v>244</v>
       </c>
       <c r="B125" t="s">
         <v>8</v>
       </c>
-      <c r="C125" t="s">
+      <c r="D125" t="s">
+        <v>237</v>
+      </c>
+      <c r="E125" t="s">
+        <v>163</v>
+      </c>
+      <c r="F125" t="s">
         <v>242</v>
       </c>
-      <c r="D125" t="s">
+      <c r="G125" t="s">
         <v>243</v>
       </c>
-      <c r="E125" t="s">
-        <v>237</v>
-      </c>
-      <c r="F125" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="126" spans="1:6">
+    </row>
+    <row r="126" spans="1:7">
       <c r="A126" t="s">
         <v>245</v>
       </c>
       <c r="B126" t="s">
         <v>8</v>
       </c>
-      <c r="C126" t="s">
+      <c r="D126" t="s">
+        <v>237</v>
+      </c>
+      <c r="E126" t="s">
+        <v>163</v>
+      </c>
+      <c r="F126" t="s">
         <v>242</v>
       </c>
-      <c r="D126" t="s">
+      <c r="G126" t="s">
         <v>243</v>
       </c>
-      <c r="E126" t="s">
-        <v>237</v>
-      </c>
-      <c r="F126" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="127" spans="1:6">
+    </row>
+    <row r="127" spans="1:7">
       <c r="A127" t="s">
         <v>246</v>
       </c>
       <c r="B127" t="s">
         <v>8</v>
       </c>
-      <c r="C127" t="s">
+      <c r="D127" t="s">
+        <v>237</v>
+      </c>
+      <c r="E127" t="s">
+        <v>163</v>
+      </c>
+      <c r="F127" t="s">
         <v>242</v>
       </c>
-      <c r="D127" t="s">
+      <c r="G127" t="s">
         <v>243</v>
       </c>
-      <c r="E127" t="s">
-        <v>237</v>
-      </c>
-      <c r="F127" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="128" spans="1:6">
+    </row>
+    <row r="128" spans="1:7">
       <c r="A128" t="s">
         <v>247</v>
       </c>
       <c r="B128" t="s">
         <v>8</v>
       </c>
-      <c r="C128" t="s">
+      <c r="D128" t="s">
+        <v>237</v>
+      </c>
+      <c r="E128" t="s">
+        <v>163</v>
+      </c>
+      <c r="F128" t="s">
         <v>242</v>
       </c>
-      <c r="D128" t="s">
+      <c r="G128" t="s">
         <v>243</v>
-      </c>
-      <c r="E128" t="s">
-        <v>237</v>
-      </c>
-      <c r="F128" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="129" spans="1:7">
@@ -4628,17 +4628,17 @@
       <c r="B129" t="s">
         <v>8</v>
       </c>
-      <c r="C129" t="s">
+      <c r="D129" t="s">
+        <v>237</v>
+      </c>
+      <c r="E129" t="s">
+        <v>163</v>
+      </c>
+      <c r="F129" t="s">
         <v>249</v>
       </c>
-      <c r="D129" t="s">
+      <c r="G129" t="s">
         <v>243</v>
-      </c>
-      <c r="E129" t="s">
-        <v>237</v>
-      </c>
-      <c r="F129" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="130" spans="1:7">
@@ -4648,17 +4648,17 @@
       <c r="B130" t="s">
         <v>8</v>
       </c>
-      <c r="C130" t="s">
+      <c r="D130" t="s">
+        <v>237</v>
+      </c>
+      <c r="E130" t="s">
+        <v>163</v>
+      </c>
+      <c r="F130" t="s">
         <v>251</v>
       </c>
-      <c r="D130" t="s">
+      <c r="G130" t="s">
         <v>243</v>
-      </c>
-      <c r="E130" t="s">
-        <v>237</v>
-      </c>
-      <c r="F130" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="131" spans="1:7">
@@ -4668,17 +4668,17 @@
       <c r="B131" t="s">
         <v>8</v>
       </c>
-      <c r="C131" t="s">
+      <c r="D131" t="s">
+        <v>237</v>
+      </c>
+      <c r="E131" t="s">
+        <v>163</v>
+      </c>
+      <c r="F131" t="s">
         <v>253</v>
       </c>
-      <c r="D131" t="s">
+      <c r="G131" t="s">
         <v>243</v>
-      </c>
-      <c r="E131" t="s">
-        <v>237</v>
-      </c>
-      <c r="F131" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="132" spans="1:7">
@@ -4688,17 +4688,17 @@
       <c r="B132" t="s">
         <v>8</v>
       </c>
-      <c r="C132" t="s">
+      <c r="D132" t="s">
+        <v>237</v>
+      </c>
+      <c r="E132" t="s">
+        <v>163</v>
+      </c>
+      <c r="F132" t="s">
         <v>255</v>
       </c>
-      <c r="D132" t="s">
+      <c r="G132" t="s">
         <v>256</v>
-      </c>
-      <c r="E132" t="s">
-        <v>237</v>
-      </c>
-      <c r="F132" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="133" spans="1:7">
@@ -4708,17 +4708,17 @@
       <c r="B133" t="s">
         <v>8</v>
       </c>
-      <c r="C133" t="s">
+      <c r="D133" t="s">
+        <v>237</v>
+      </c>
+      <c r="E133" t="s">
+        <v>114</v>
+      </c>
+      <c r="F133" t="s">
         <v>189</v>
       </c>
-      <c r="D133" t="s">
+      <c r="G133" t="s">
         <v>190</v>
-      </c>
-      <c r="E133" t="s">
-        <v>237</v>
-      </c>
-      <c r="F133" t="s">
-        <v>115</v>
       </c>
     </row>
     <row r="134" spans="1:7">
@@ -4728,17 +4728,17 @@
       <c r="B134" t="s">
         <v>8</v>
       </c>
-      <c r="C134" t="s">
+      <c r="D134" t="s">
+        <v>259</v>
+      </c>
+      <c r="E134" t="s">
+        <v>163</v>
+      </c>
+      <c r="F134" t="s">
         <v>175</v>
       </c>
-      <c r="D134" t="s">
+      <c r="G134" t="s">
         <v>176</v>
-      </c>
-      <c r="E134" t="s">
-        <v>259</v>
-      </c>
-      <c r="F134" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="135" spans="1:7">
@@ -4748,17 +4748,17 @@
       <c r="B135" t="s">
         <v>8</v>
       </c>
-      <c r="C135" t="s">
+      <c r="D135" t="s">
+        <v>259</v>
+      </c>
+      <c r="E135" t="s">
+        <v>163</v>
+      </c>
+      <c r="F135" t="s">
         <v>175</v>
       </c>
-      <c r="D135" t="s">
+      <c r="G135" t="s">
         <v>176</v>
-      </c>
-      <c r="E135" t="s">
-        <v>259</v>
-      </c>
-      <c r="F135" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="136" spans="1:7">
@@ -4768,17 +4768,17 @@
       <c r="B136" t="s">
         <v>8</v>
       </c>
-      <c r="C136" t="s">
+      <c r="D136" t="s">
+        <v>259</v>
+      </c>
+      <c r="E136" t="s">
+        <v>163</v>
+      </c>
+      <c r="F136" t="s">
         <v>175</v>
       </c>
-      <c r="D136" t="s">
+      <c r="G136" t="s">
         <v>176</v>
-      </c>
-      <c r="E136" t="s">
-        <v>259</v>
-      </c>
-      <c r="F136" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="137" spans="1:7">
@@ -4788,17 +4788,17 @@
       <c r="B137" t="s">
         <v>8</v>
       </c>
-      <c r="C137" t="s">
+      <c r="D137" t="s">
+        <v>259</v>
+      </c>
+      <c r="E137" t="s">
+        <v>163</v>
+      </c>
+      <c r="F137" t="s">
         <v>175</v>
       </c>
-      <c r="D137" t="s">
+      <c r="G137" t="s">
         <v>176</v>
-      </c>
-      <c r="E137" t="s">
-        <v>259</v>
-      </c>
-      <c r="F137" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="138" spans="1:7">
@@ -4808,17 +4808,17 @@
       <c r="B138" t="s">
         <v>8</v>
       </c>
-      <c r="C138" t="s">
+      <c r="D138" t="s">
+        <v>259</v>
+      </c>
+      <c r="E138" t="s">
+        <v>163</v>
+      </c>
+      <c r="F138" t="s">
         <v>175</v>
       </c>
-      <c r="D138" t="s">
+      <c r="G138" t="s">
         <v>176</v>
-      </c>
-      <c r="E138" t="s">
-        <v>259</v>
-      </c>
-      <c r="F138" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="139" spans="1:7">
@@ -4828,17 +4828,17 @@
       <c r="B139" t="s">
         <v>8</v>
       </c>
-      <c r="C139" t="s">
+      <c r="D139" t="s">
+        <v>259</v>
+      </c>
+      <c r="E139" t="s">
+        <v>223</v>
+      </c>
+      <c r="F139" t="s">
         <v>265</v>
       </c>
-      <c r="D139" t="s">
+      <c r="G139" t="s">
         <v>266</v>
-      </c>
-      <c r="E139" t="s">
-        <v>259</v>
-      </c>
-      <c r="F139" t="s">
-        <v>225</v>
       </c>
     </row>
     <row r="140" spans="1:7">
@@ -4848,17 +4848,17 @@
       <c r="B140" t="s">
         <v>8</v>
       </c>
-      <c r="C140" t="s">
+      <c r="D140" t="s">
+        <v>259</v>
+      </c>
+      <c r="E140" t="s">
+        <v>163</v>
+      </c>
+      <c r="F140" t="s">
         <v>175</v>
       </c>
-      <c r="D140" t="s">
+      <c r="G140" t="s">
         <v>176</v>
-      </c>
-      <c r="E140" t="s">
-        <v>259</v>
-      </c>
-      <c r="F140" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="141" spans="1:7">
@@ -4875,10 +4875,10 @@
         <v>270</v>
       </c>
       <c r="E141" t="s">
+        <v>163</v>
+      </c>
+      <c r="F141" t="s">
         <v>271</v>
-      </c>
-      <c r="F141" t="s">
-        <v>165</v>
       </c>
       <c r="G141" t="s">
         <v>272</v>
@@ -4898,10 +4898,10 @@
         <v>270</v>
       </c>
       <c r="E142" t="s">
+        <v>163</v>
+      </c>
+      <c r="F142" t="s">
         <v>271</v>
-      </c>
-      <c r="F142" t="s">
-        <v>165</v>
       </c>
       <c r="G142" t="s">
         <v>272</v>
@@ -4915,19 +4915,19 @@
         <v>8</v>
       </c>
       <c r="C143" t="s">
+        <v>269</v>
+      </c>
+      <c r="D143" t="s">
+        <v>270</v>
+      </c>
+      <c r="E143" t="s">
+        <v>163</v>
+      </c>
+      <c r="F143" t="s">
         <v>275</v>
       </c>
-      <c r="D143" t="s">
+      <c r="G143" t="s">
         <v>276</v>
-      </c>
-      <c r="E143" t="s">
-        <v>271</v>
-      </c>
-      <c r="F143" t="s">
-        <v>165</v>
-      </c>
-      <c r="G143" t="s">
-        <v>272</v>
       </c>
     </row>
     <row r="144" spans="1:7">
@@ -4938,19 +4938,19 @@
         <v>8</v>
       </c>
       <c r="C144" t="s">
+        <v>269</v>
+      </c>
+      <c r="D144" t="s">
+        <v>270</v>
+      </c>
+      <c r="E144" t="s">
+        <v>163</v>
+      </c>
+      <c r="F144" t="s">
         <v>275</v>
       </c>
-      <c r="D144" t="s">
+      <c r="G144" t="s">
         <v>276</v>
-      </c>
-      <c r="E144" t="s">
-        <v>271</v>
-      </c>
-      <c r="F144" t="s">
-        <v>165</v>
-      </c>
-      <c r="G144" t="s">
-        <v>272</v>
       </c>
     </row>
     <row r="145" spans="1:7">
@@ -4961,19 +4961,19 @@
         <v>8</v>
       </c>
       <c r="C145" t="s">
+        <v>269</v>
+      </c>
+      <c r="D145" t="s">
+        <v>270</v>
+      </c>
+      <c r="E145" t="s">
+        <v>163</v>
+      </c>
+      <c r="F145" t="s">
         <v>275</v>
       </c>
-      <c r="D145" t="s">
+      <c r="G145" t="s">
         <v>276</v>
-      </c>
-      <c r="E145" t="s">
-        <v>271</v>
-      </c>
-      <c r="F145" t="s">
-        <v>165</v>
-      </c>
-      <c r="G145" t="s">
-        <v>272</v>
       </c>
     </row>
     <row r="146" spans="1:7">
@@ -4990,10 +4990,10 @@
         <v>270</v>
       </c>
       <c r="E146" t="s">
+        <v>163</v>
+      </c>
+      <c r="F146" t="s">
         <v>271</v>
-      </c>
-      <c r="F146" t="s">
-        <v>165</v>
       </c>
       <c r="G146" t="s">
         <v>272</v>
@@ -5007,19 +5007,19 @@
         <v>8</v>
       </c>
       <c r="C147" t="s">
-        <v>269</v>
+        <v>281</v>
       </c>
       <c r="D147" t="s">
         <v>270</v>
       </c>
       <c r="E147" t="s">
+        <v>163</v>
+      </c>
+      <c r="F147" t="s">
         <v>271</v>
       </c>
-      <c r="F147" t="s">
-        <v>165</v>
-      </c>
       <c r="G147" t="s">
-        <v>281</v>
+        <v>272</v>
       </c>
     </row>
     <row r="148" spans="1:7">
@@ -5030,19 +5030,19 @@
         <v>8</v>
       </c>
       <c r="C148" t="s">
-        <v>269</v>
+        <v>281</v>
       </c>
       <c r="D148" t="s">
         <v>270</v>
       </c>
       <c r="E148" t="s">
+        <v>163</v>
+      </c>
+      <c r="F148" t="s">
         <v>271</v>
       </c>
-      <c r="F148" t="s">
-        <v>165</v>
-      </c>
       <c r="G148" t="s">
-        <v>281</v>
+        <v>272</v>
       </c>
     </row>
     <row r="149" spans="1:7">
@@ -5053,19 +5053,19 @@
         <v>8</v>
       </c>
       <c r="C149" t="s">
-        <v>269</v>
+        <v>281</v>
       </c>
       <c r="D149" t="s">
         <v>270</v>
       </c>
       <c r="E149" t="s">
+        <v>163</v>
+      </c>
+      <c r="F149" t="s">
         <v>271</v>
       </c>
-      <c r="F149" t="s">
-        <v>165</v>
-      </c>
       <c r="G149" t="s">
-        <v>281</v>
+        <v>272</v>
       </c>
     </row>
     <row r="150" spans="1:7">
@@ -5076,19 +5076,19 @@
         <v>8</v>
       </c>
       <c r="C150" t="s">
-        <v>269</v>
+        <v>281</v>
       </c>
       <c r="D150" t="s">
         <v>270</v>
       </c>
       <c r="E150" t="s">
+        <v>163</v>
+      </c>
+      <c r="F150" t="s">
         <v>271</v>
       </c>
-      <c r="F150" t="s">
-        <v>165</v>
-      </c>
       <c r="G150" t="s">
-        <v>281</v>
+        <v>272</v>
       </c>
     </row>
     <row r="151" spans="1:7">
@@ -5099,19 +5099,19 @@
         <v>8</v>
       </c>
       <c r="C151" t="s">
-        <v>269</v>
+        <v>281</v>
       </c>
       <c r="D151" t="s">
         <v>270</v>
       </c>
       <c r="E151" t="s">
+        <v>163</v>
+      </c>
+      <c r="F151" t="s">
         <v>271</v>
       </c>
-      <c r="F151" t="s">
-        <v>165</v>
-      </c>
       <c r="G151" t="s">
-        <v>281</v>
+        <v>272</v>
       </c>
     </row>
     <row r="152" spans="1:7">
@@ -5122,19 +5122,19 @@
         <v>8</v>
       </c>
       <c r="C152" t="s">
-        <v>269</v>
+        <v>281</v>
       </c>
       <c r="D152" t="s">
         <v>270</v>
       </c>
       <c r="E152" t="s">
+        <v>163</v>
+      </c>
+      <c r="F152" t="s">
         <v>271</v>
       </c>
-      <c r="F152" t="s">
-        <v>165</v>
-      </c>
       <c r="G152" t="s">
-        <v>281</v>
+        <v>272</v>
       </c>
     </row>
     <row r="153" spans="1:7">
@@ -5145,19 +5145,19 @@
         <v>8</v>
       </c>
       <c r="C153" t="s">
-        <v>269</v>
+        <v>281</v>
       </c>
       <c r="D153" t="s">
         <v>270</v>
       </c>
       <c r="E153" t="s">
+        <v>163</v>
+      </c>
+      <c r="F153" t="s">
         <v>271</v>
       </c>
-      <c r="F153" t="s">
-        <v>165</v>
-      </c>
       <c r="G153" t="s">
-        <v>281</v>
+        <v>272</v>
       </c>
     </row>
     <row r="154" spans="1:7">
@@ -5168,19 +5168,19 @@
         <v>8</v>
       </c>
       <c r="C154" t="s">
-        <v>269</v>
+        <v>281</v>
       </c>
       <c r="D154" t="s">
         <v>270</v>
       </c>
       <c r="E154" t="s">
+        <v>163</v>
+      </c>
+      <c r="F154" t="s">
         <v>271</v>
       </c>
-      <c r="F154" t="s">
-        <v>165</v>
-      </c>
       <c r="G154" t="s">
-        <v>281</v>
+        <v>272</v>
       </c>
     </row>
     <row r="155" spans="1:7">
@@ -5191,19 +5191,19 @@
         <v>8</v>
       </c>
       <c r="C155" t="